--- a/farmakologia_ARCYBAZA_OnlyPharms.xlsx
+++ b/farmakologia_ARCYBAZA_OnlyPharms.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Pytania" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Pytania'!$A$1:$Q$1266</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Pytania'!$A$1:$Q$1106</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -424,5 +424,5 @@
 </a:theme>
 </file>
 
-<file path=xl/worksheets/sheet1.xml><worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><sheetPr><outlinePr summaryBelow="1" summaryRight="1" /><pageSetUpPr /></sheetPr><dimension ref="A1:Q1266" /><sheetFormatPr baseColWidth="8" defaultRowHeight="15" /><cols><col width="30" customWidth="1" min="1" max="1" /><col width="21" customWidth="1" min="2" max="2" /><col width="9" customWidth="1" min="3" max="3" /><col width="9" customWidth="1" min="4" max="4" /><col width="60" customWidth="1" min="5" max="5" /><col width="32" customWidth="1" min="6" max="6" /><col width="32" customWidth="1" min="7" max="7" /><col width="32" customWidth="1" min="8" max="8" /><col width="32" customWidth="1" min="9" max="9" /><col width="32" customWidth="1" min="10" max="10" /><col width="32" customWidth="1" min="11" max="11" /><col width="32" customWidth="1" min="12" max="12" /><col width="32" customWidth="1" min="13" max="13" /><col width="32" customWidth="1" min="14" max="14" /><col width="32" customWidth="1" min="15" max="15" /><col width="26" customWidth="1" min="16" max="16" /><col width="10" customWidth="1" min="17" max="17" /></cols><sheetData><row r="1"><c r="A1" s="1" t="inlineStr"><is><t>Section</t></is></c><c r="B1" s="1" t="inlineStr"><is><t>Category</t></is></c><c r="C1" s="1" t="inlineStr"><is><t>Poziom</t></is></c><c r="D1" s="1" t="inlineStr"><is><t>Type</t></is></c><c r="E1" s="1" t="inlineStr"><is><t>Question</t></is></c><c r="F1" s="1" t="inlineStr"><is><t>True 1</t></is></c><c r="G1" s="1" t="inlineStr"><is><t>True 2</t></is></c><c r="H1" s="1" t="inlineStr"><is><t>True 3</t></is></c><c r="I1" s="1" t="inlineStr"><is><t>True 4</t></is></c><c r="J1" s="1" t="inlineStr"><is><t>True 5</t></is></c><c r="K1" s="1" t="inlineStr"><is><t>False 1</t></is></c><c r="L1" s="1" t="inlineStr"><is><t>False 2</t></is></c><c r="M1" s="1" t="inlineStr"><is><t>False 3</t></is></c><c r="N1" s="1" t="inlineStr"><is><t>False 4</t></is></c><c r="O1" s="1" t="inlineStr"><is><t>False 5</t></is></c><c r="P1" s="1" t="inlineStr"><is><t>Zrodlo</t></is></c><c r="Q1" s="1" t="inlineStr"><is><t>Pewnosc</t></is></c></row><row r="2"><c r="A2" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B2" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C2" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D2" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E2" s="2" t="inlineStr"><is><t>Czarne zabarwienie stolca powoduje podanie preparatów:</t></is></c><c r="F2" s="2" t="inlineStr"><is><t>Bizmutu</t></is></c><c r="G2" s="2" t="inlineStr"><is><t>Żelaza</t></is></c><c r="H2" s="2" t="inlineStr" /><c r="I2" s="2" t="inlineStr" /><c r="J2" s="2" t="inlineStr" /><c r="K2" s="2" t="inlineStr"><is><t>Wapnia</t></is></c><c r="L2" s="2" t="inlineStr"><is><t>Glinu</t></is></c><c r="M2" s="2" t="inlineStr" /><c r="N2" s="2" t="inlineStr" /><c r="O2" s="2" t="inlineStr" /><c r="P2" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q2" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="3"><c r="A3" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B3" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C3" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D3" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E3" s="2" t="inlineStr"><is><t>Uzasadnionym wskazaniem do przewlekłego stosowania inhibitorów pompy protonowej jest:</t></is></c><c r="F3" s="2" t="inlineStr"><is><t>Choroba refluksowa żołądka</t></is></c><c r="G3" s="2" t="inlineStr"><is><t>Profilaktyka gastropatii u osób leczonych niesteroidowymi lekami przeciwzapalnymi powyżej 65 r.ż</t></is></c><c r="H3" s="2" t="inlineStr"><is><t>Eradykacja Helicobacter Pylori</t></is></c><c r="I3" s="2" t="inlineStr" /><c r="J3" s="2" t="inlineStr" /><c r="K3" s="2" t="inlineStr"><is><t>Profilaktyka wrzodów stresowych</t></is></c><c r="L3" s="2" t="inlineStr" /><c r="M3" s="2" t="inlineStr" /><c r="N3" s="2" t="inlineStr" /><c r="O3" s="2" t="inlineStr" /><c r="P3" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q3" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="4"><c r="A4" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B4" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C4" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D4" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E4" s="2" t="inlineStr"><is><t>Wybierz prawidłowe połączenie lek – wskazanie</t></is></c><c r="F4" s="2" t="inlineStr"><is><t>Mesalazyna – choroba Leśniowskiego crohna</t></is></c><c r="G4" s="2" t="inlineStr"><is><t>Rifaksymina – biegunka podróżnych</t></is></c><c r="H4" s="2" t="inlineStr"><is><t>Metylonaltrekson – zaparcia w trakcie terapii opioidami</t></is></c><c r="I4" s="2" t="inlineStr" /><c r="J4" s="2" t="inlineStr" /><c r="K4" s="2" t="inlineStr"><is><t>Racekadotryl – śpiączka wątrobowa</t></is></c><c r="L4" s="2" t="inlineStr" /><c r="M4" s="2" t="inlineStr" /><c r="N4" s="2" t="inlineStr" /><c r="O4" s="2" t="inlineStr" /><c r="P4" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q4" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="5"><c r="A5" s="2" t="inlineStr"><is><t>ZNIECZULENIA OGÓLNE</t></is></c><c r="B5" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C5" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D5" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E5" s="2" t="inlineStr"><is><t>Do leków które wykazują miejscowe działanie przeciwbólowe po podaniu na skórę należy:</t></is></c><c r="F5" s="2" t="inlineStr"><is><t>Kapsaicyna</t></is></c><c r="G5" s="2" t="inlineStr"><is><t>Ketoprofen</t></is></c><c r="H5" s="2" t="inlineStr" /><c r="I5" s="2" t="inlineStr" /><c r="J5" s="2" t="inlineStr" /><c r="K5" s="2" t="inlineStr"><is><t>Propofol</t></is></c><c r="L5" s="2" t="inlineStr"><is><t>Tiopental</t></is></c><c r="M5" s="2" t="inlineStr" /><c r="N5" s="2" t="inlineStr" /><c r="O5" s="2" t="inlineStr" /><c r="P5" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q5" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="6"><c r="A6" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B6" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C6" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D6" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E6" s="2" t="inlineStr"><is><t>Ryzyko uszkodzenia wątroby przez paracetamol rośnie w przypadku:</t></is></c><c r="F6" s="2" t="inlineStr"><is><t>Zespołu zależności alkoholowej (ZAA)</t></is></c><c r="G6" s="2" t="inlineStr"><is><t>Wygłodzenia (kacheksji)</t></is></c><c r="H6" s="2" t="inlineStr"><is><t>Indukcji enzymów mikrosomalnych wątroby</t></is></c><c r="I6" s="2" t="inlineStr"><is><t>Przedawkowania</t></is></c><c r="J6" s="2" t="inlineStr" /><c r="K6" s="2" t="inlineStr" /><c r="L6" s="2" t="inlineStr" /><c r="M6" s="2" t="inlineStr" /><c r="N6" s="2" t="inlineStr" /><c r="O6" s="2" t="inlineStr" /><c r="P6" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q6" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="7"><c r="A7" s="2" t="inlineStr"><is><t>BÓLE GŁOWY</t></is></c><c r="B7" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C7" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D7" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E7" s="2" t="inlineStr"><is><t>W przerywaniu bólów migrenowych stosuje się:</t></is></c><c r="F7" s="2" t="inlineStr"><is><t>Kwas acetylosalicylowy</t></is></c><c r="G7" s="2" t="inlineStr"><is><t>Dihydroergotaminę</t></is></c><c r="H7" s="2" t="inlineStr"><is><t>Zolmitryptan</t></is></c><c r="I7" s="2" t="inlineStr" /><c r="J7" s="2" t="inlineStr" /><c r="K7" s="2" t="inlineStr"><is><t>Morfinę</t></is></c><c r="L7" s="2" t="inlineStr" /><c r="M7" s="2" t="inlineStr" /><c r="N7" s="2" t="inlineStr" /><c r="O7" s="2" t="inlineStr" /><c r="P7" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q7" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="8"><c r="A8" s="2" t="inlineStr"><is><t>JASKRA</t></is></c><c r="B8" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C8" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D8" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E8" s="2" t="inlineStr"><is><t>Analogi prostaglandyny E1 mogą powodować</t></is></c><c r="F8" s="2" t="inlineStr"><is><t>Hamowanie wydzielania soku żołądkowego</t></is></c><c r="G8" s="2" t="inlineStr" /><c r="H8" s="2" t="inlineStr" /><c r="I8" s="2" t="inlineStr" /><c r="J8" s="2" t="inlineStr" /><c r="K8" s="2" t="inlineStr"><is><t>Poprawę odpływu cieczy wodnistej z oka</t></is></c><c r="L8" s="2" t="inlineStr"><is><t>Rozszerzanie naczyń krwionośnych tętniczych</t></is></c><c r="M8" s="2" t="inlineStr"><is><t>Hamowanie agregacji płytek krwi</t></is></c><c r="N8" s="2" t="inlineStr" /><c r="O8" s="2" t="inlineStr" /><c r="P8" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q8" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="9"><c r="A9" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B9" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C9" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D9" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E9" s="2" t="inlineStr"><is><t>Substytucja enzymów trzustkowych jest wskazana:</t></is></c><c r="F9" s="2" t="inlineStr"><is><t>W mukowiscydozie</t></is></c><c r="G9" s="2" t="inlineStr"><is><t>Po resekcji trzustki</t></is></c><c r="H9" s="2" t="inlineStr" /><c r="I9" s="2" t="inlineStr" /><c r="J9" s="2" t="inlineStr" /><c r="K9" s="2" t="inlineStr"><is><t>W cukrzycy typu 1</t></is></c><c r="L9" s="2" t="inlineStr"><is><t>W anoreksji</t></is></c><c r="M9" s="2" t="inlineStr" /><c r="N9" s="2" t="inlineStr" /><c r="O9" s="2" t="inlineStr" /><c r="P9" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q9" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="10"><c r="A10" s="2" t="inlineStr"><is><t>PADACZKA</t></is></c><c r="B10" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C10" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D10" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E10" s="2" t="inlineStr"><is><t>Wybierz prawidłowe połączenie lek – wskazanie do podania:</t></is></c><c r="F10" s="2" t="inlineStr"><is><t>Haloperydol – agresja u pacjentów z ograniczonym uszkodzeniem mózgu</t></is></c><c r="G10" s="2" t="inlineStr"><is><t>Betahistyna – zawroty głowy w przebiegu choroby Meniere’a</t></is></c><c r="H10" s="2" t="inlineStr"><is><t>Topiramat – profilaktyka migreny</t></is></c><c r="I10" s="2" t="inlineStr"><is><t>Lamotrygina – profilaktyka choroby afektywnej dwubiegunowej</t></is></c><c r="J10" s="2" t="inlineStr" /><c r="K10" s="2" t="inlineStr" /><c r="L10" s="2" t="inlineStr" /><c r="M10" s="2" t="inlineStr" /><c r="N10" s="2" t="inlineStr" /><c r="O10" s="2" t="inlineStr" /><c r="P10" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q10" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="11"><c r="A11" s="2" t="inlineStr"><is><t>FARMAKOKINETYKA</t></is></c><c r="B11" s="2" t="inlineStr"><is><t>Farmakokinetyka</t></is></c><c r="C11" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D11" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E11" s="2" t="inlineStr"><is><t>Kwas acetylosalicylowy:</t></is></c><c r="F11" s="2" t="inlineStr"><is><t>Ma eliminację metabolitów zgodnie z kinetyką I rzędu po podaniu małych dawek kardiologicznych</t></is></c><c r="G11" s="2" t="inlineStr"><is><t>Może być przyczyną zapalenia jelita cienkiego</t></is></c><c r="H11" s="2" t="inlineStr"><is><t>Po przedawkowaniu szybciej wydala się przez nerki po dożylnym podaniu wodorowęglanu sodu</t></is></c><c r="I11" s="2" t="inlineStr" /><c r="J11" s="2" t="inlineStr" /><c r="K11" s="2" t="inlineStr"><is><t>Słabiej zapobiega powstawaniu zakrzepu na blaszce miażdżycowej</t></is></c><c r="L11" s="2" t="inlineStr" /><c r="M11" s="2" t="inlineStr" /><c r="N11" s="2" t="inlineStr" /><c r="O11" s="2" t="inlineStr" /><c r="P11" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q11" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="12"><c r="A12" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B12" s="2" t="inlineStr"><is><t>Antidotum</t></is></c><c r="C12" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D12" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E12" s="2" t="inlineStr"><is><t>Wskaż prawdziwe stwierdzenie dotyczące leczenia heparyną niefrakcjonowaną:</t></is></c><c r="F12" s="2" t="inlineStr"><is><t>Może być podawana podskórnie ale jej biodostępność jest wtedy mała i zmienna osobniczo</t></is></c><c r="G12" s="2" t="inlineStr"><is><t>Białka osoczowe mogą zmniejszać jej działanie przeciwkrzepliwe i być przyczyną oporności na leczenie</t></is></c><c r="H12" s="2" t="inlineStr"><is><t>Przedłużenie aPTT 1,5-2 razy w stosunku do wartości wyjściowej jest pożądanym efektem terapeutycznym</t></is></c><c r="I12" s="2" t="inlineStr"><is><t>Jej antidotum jest siarczan protaminy</t></is></c><c r="J12" s="2" t="inlineStr" /><c r="K12" s="2" t="inlineStr" /><c r="L12" s="2" t="inlineStr" /><c r="M12" s="2" t="inlineStr" /><c r="N12" s="2" t="inlineStr" /><c r="O12" s="2" t="inlineStr" /><c r="P12" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q12" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="13"><c r="A13" s="2" t="inlineStr"><is><t>UKŁAD PRZYWSPÓŁCZULNY</t></is></c><c r="B13" s="2" t="inlineStr"><is><t>Przeciwwskazania</t></is></c><c r="C13" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D13" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E13" s="2" t="inlineStr"><is><t>Przeciwwskazaniem do podania cholinolityków jest:</t></is></c><c r="F13" s="2" t="inlineStr"><is><t>Rozrost gruczołu krokowego</t></is></c><c r="G13" s="2" t="inlineStr"><is><t>Jaskra</t></is></c><c r="H13" s="2" t="inlineStr" /><c r="I13" s="2" t="inlineStr" /><c r="J13" s="2" t="inlineStr" /><c r="K13" s="2" t="inlineStr"><is><t>Choroba wrzodowa żołądka i dwunastnicy</t></is></c><c r="L13" s="2" t="inlineStr"><is><t>Choroba lokomocyjna</t></is></c><c r="M13" s="2" t="inlineStr" /><c r="N13" s="2" t="inlineStr" /><c r="O13" s="2" t="inlineStr" /><c r="P13" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q13" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="14"><c r="A14" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B14" s="2" t="inlineStr"><is><t>Monitorowanie</t></is></c><c r="C14" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D14" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E14" s="2" t="inlineStr"><is><t>Warfaryna:</t></is></c><c r="F14" s="2" t="inlineStr"><is><t>Jest sotosowana w profilaktyce i leczeniu żylnej choroby zakrzepowo-zatorowej</t></is></c><c r="G14" s="2" t="inlineStr"><is><t>Może być przyczyną zespołu purpurowego palucha</t></is></c><c r="H14" s="2" t="inlineStr" /><c r="I14" s="2" t="inlineStr" /><c r="J14" s="2" t="inlineStr" /><c r="K14" s="2" t="inlineStr"><is><t>Wymaga utrzymania INR&gt;4</t></is></c><c r="L14" s="2" t="inlineStr"><is><t>Jest eliminowana niezmieniona przez nerki</t></is></c><c r="M14" s="2" t="inlineStr" /><c r="N14" s="2" t="inlineStr" /><c r="O14" s="2" t="inlineStr" /><c r="P14" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q14" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="15"><c r="A15" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B15" s="2" t="inlineStr"><is><t>Monitorowanie</t></is></c><c r="C15" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D15" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E15" s="2" t="inlineStr"><is><t>Fondaparynuks:</t></is></c><c r="F15" s="2" t="inlineStr"><is><t>Jest stosowana u osób z zawałem serca z przetrwałym uniesieniem odcinka ST (STEMI) oraz bez jego uniesienia (NSTEMI)</t></is></c><c r="G15" s="2" t="inlineStr" /><c r="H15" s="2" t="inlineStr" /><c r="I15" s="2" t="inlineStr" /><c r="J15" s="2" t="inlineStr" /><c r="K15" s="2" t="inlineStr"><is><t>Wybiórczo hamuje czynnik IIa</t></is></c><c r="L15" s="2" t="inlineStr"><is><t>W zalecanych dawkach hamuje istotnie wydłuża aPTT</t></is></c><c r="M15" s="2" t="inlineStr"><is><t>Nie jest wydalany przez nerki i może być stosowany u pacjentów z klirensem kreatyniny poniżej 30ml/min</t></is></c><c r="N15" s="2" t="inlineStr" /><c r="O15" s="2" t="inlineStr" /><c r="P15" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q15" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="16"><c r="A16" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B16" s="2" t="inlineStr"><is><t>Sposób podania</t></is></c><c r="C16" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D16" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E16" s="2" t="inlineStr"><is><t>Bezpośrednim inhibitorem trombiny podawanym dożylnie jest:</t></is></c><c r="F16" s="2" t="inlineStr"><is><t>Argatroban</t></is></c><c r="G16" s="2" t="inlineStr"><is><t>Biwalirudyna</t></is></c><c r="H16" s="2" t="inlineStr" /><c r="I16" s="2" t="inlineStr" /><c r="J16" s="2" t="inlineStr" /><c r="K16" s="2" t="inlineStr"><is><t>Dabigatran</t></is></c><c r="L16" s="2" t="inlineStr"><is><t>Dalteparyna</t></is></c><c r="M16" s="2" t="inlineStr" /><c r="N16" s="2" t="inlineStr" /><c r="O16" s="2" t="inlineStr" /><c r="P16" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q16" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="17"><c r="A17" s="2" t="inlineStr"><is><t>UKŁAD PRZYWSPÓŁCZULNY</t></is></c><c r="B17" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C17" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D17" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E17" s="2" t="inlineStr"><is><t>Odwracalne inhibitory acetylocholinesterazy są stosowane w leczeniu:</t></is></c><c r="F17" s="2" t="inlineStr"><is><t>Nużliwości mięśni</t></is></c><c r="G17" s="2" t="inlineStr"><is><t>Pooperacyjnej niedrożności jelit</t></is></c><c r="H17" s="2" t="inlineStr"><is><t>Choroby Alzheimera</t></is></c><c r="I17" s="2" t="inlineStr" /><c r="J17" s="2" t="inlineStr" /><c r="K17" s="2" t="inlineStr"><is><t>Zatruć związakmi fosfoorganicznymi</t></is></c><c r="L17" s="2" t="inlineStr" /><c r="M17" s="2" t="inlineStr" /><c r="N17" s="2" t="inlineStr" /><c r="O17" s="2" t="inlineStr" /><c r="P17" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q17" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="18"><c r="A18" s="2" t="inlineStr"><is><t>NADCIŚNIENIE TĘTNICZE</t></is></c><c r="B18" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C18" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D18" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E18" s="2" t="inlineStr"><is><t>Zaznacza prawidłowe pary dotyczące leczenia uzależnień i wybranego leku:</t></is></c><c r="F18" s="2" t="inlineStr"><is><t>Uzależnienie od alkoholu – nalmefen</t></is></c><c r="G18" s="2" t="inlineStr"><is><t>Uzależnienie od heroiny – metadon</t></is></c><c r="H18" s="2" t="inlineStr" /><c r="I18" s="2" t="inlineStr" /><c r="J18" s="2" t="inlineStr" /><c r="K18" s="2" t="inlineStr"><is><t>Uzależnienie od nikotyny – klonidyna</t></is></c><c r="L18" s="2" t="inlineStr"><is><t>Uzależnienie od amfetaminy – wereniklina</t></is></c><c r="M18" s="2" t="inlineStr" /><c r="N18" s="2" t="inlineStr" /><c r="O18" s="2" t="inlineStr" /><c r="P18" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q18" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="19"><c r="A19" s="2" t="inlineStr"><is><t>STANY NAGŁE</t></is></c><c r="B19" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C19" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D19" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E19" s="2" t="inlineStr"><is><t>Wskaż prawidłowe pary płyn infuzyjny – możliwe działania niepożądane:</t></is></c><c r="F19" s="2" t="inlineStr"><is><t>5% roztwór glukozy – hiponatremia</t></is></c><c r="G19" s="2" t="inlineStr"><is><t>HES (hydroksyetylowana skrobia) – ostre uszkodzenie nerek</t></is></c><c r="H19" s="2" t="inlineStr"><is><t>5% roztwór albuminy – anafilaksja</t></is></c><c r="I19" s="2" t="inlineStr"><is><t>Dekstran 70000 – działanie przeciwkrzepliwe</t></is></c><c r="J19" s="2" t="inlineStr" /><c r="K19" s="2" t="inlineStr" /><c r="L19" s="2" t="inlineStr" /><c r="M19" s="2" t="inlineStr" /><c r="N19" s="2" t="inlineStr" /><c r="O19" s="2" t="inlineStr" /><c r="P19" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q19" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="20"><c r="A20" s="2" t="inlineStr"><is><t>NADCIŚNIENIE TĘTNICZE</t></is></c><c r="B20" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C20" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D20" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E20" s="2" t="inlineStr"><is><t>Wskaż prawidłowe stwierdzenie dotyczące leczenia hipotensyjnego:</t></is></c><c r="F20" s="2" t="inlineStr"><is><t>Tiazydy mogą bezpośrednio oddziaływać na ścianę naczyń i zmniejszać systemowy opór naczyniowy</t></is></c><c r="G20" s="2" t="inlineStr"><is><t>Pełny efekt hipotensyjny występuje po kilkunastu dniach leczenia</t></is></c><c r="H20" s="2" t="inlineStr"><is><t>Blokada kotransportera Na-Cl w kanaliku dystalnym prowadzi do zwiększeniu natriurezy</t></is></c><c r="I20" s="2" t="inlineStr" /><c r="J20" s="2" t="inlineStr" /><c r="K20" s="2" t="inlineStr"><is><t>Ich skuteczność w leczeniu przewlekłym wynika przede wszystkim ze zmniejszenia objętości osocza i rzutu serca</t></is></c><c r="L20" s="2" t="inlineStr" /><c r="M20" s="2" t="inlineStr" /><c r="N20" s="2" t="inlineStr" /><c r="O20" s="2" t="inlineStr" /><c r="P20" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q20" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="21"><c r="A21" s="2" t="inlineStr"><is><t>UKŁAD PRZYWSPÓŁCZULNY</t></is></c><c r="B21" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C21" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D21" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E21" s="2" t="inlineStr"><is><t>Suksametonium może być przyczyną:</t></is></c><c r="F21" s="2" t="inlineStr"><is><t>Drżenia włókienkowego mięśni szkieletowych</t></is></c><c r="G21" s="2" t="inlineStr"><is><t>Zaburzeń oddychania</t></is></c><c r="H21" s="2" t="inlineStr"><is><t>Zespołu hipertermii złośliwej</t></is></c><c r="I21" s="2" t="inlineStr"><is><t>Długotrwałego efektu zwiotczającego u osób z dysfunkcją acetylocholinesterazy</t></is></c><c r="J21" s="2" t="inlineStr" /><c r="K21" s="2" t="inlineStr" /><c r="L21" s="2" t="inlineStr" /><c r="M21" s="2" t="inlineStr" /><c r="N21" s="2" t="inlineStr" /><c r="O21" s="2" t="inlineStr" /><c r="P21" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q21" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="22"><c r="A22" s="2" t="inlineStr"><is><t>UKŁAD ODDECHOWY</t></is></c><c r="B22" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C22" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D22" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E22" s="2" t="inlineStr"><is><t>W celu łagodzenia suchego kaszlu można wybrać:</t></is></c><c r="F22" s="2" t="inlineStr"><is><t>Dekstrometorfan</t></is></c><c r="G22" s="2" t="inlineStr"><is><t>Kodeinę</t></is></c><c r="H22" s="2" t="inlineStr"><is><t>Butamirat</t></is></c><c r="I22" s="2" t="inlineStr" /><c r="J22" s="2" t="inlineStr" /><c r="K22" s="2" t="inlineStr"><is><t>Bromheksynę</t></is></c><c r="L22" s="2" t="inlineStr" /><c r="M22" s="2" t="inlineStr" /><c r="N22" s="2" t="inlineStr" /><c r="O22" s="2" t="inlineStr" /><c r="P22" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q22" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="23"><c r="A23" s="2" t="inlineStr"><is><t>LEKI PRZECIWPASOŻYTNICZE</t></is></c><c r="B23" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C23" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D23" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E23" s="2" t="inlineStr"><is><t>Albendazol stosowany jest w jelitowej infestacji:</t></is></c><c r="F23" s="2" t="inlineStr"><is><t>Glistą ludzką</t></is></c><c r="G23" s="2" t="inlineStr"><is><t>Tasiemcem uzbrojonym</t></is></c><c r="H23" s="2" t="inlineStr"><is><t>Owsikami</t></is></c><c r="I23" s="2" t="inlineStr" /><c r="J23" s="2" t="inlineStr" /><c r="K23" s="2" t="inlineStr"><is><t>Lambliami</t></is></c><c r="L23" s="2" t="inlineStr" /><c r="M23" s="2" t="inlineStr" /><c r="N23" s="2" t="inlineStr" /><c r="O23" s="2" t="inlineStr" /><c r="P23" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q23" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="24"><c r="A24" s="2" t="inlineStr"><is><t>PADACZKA</t></is></c><c r="B24" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C24" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D24" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E24" s="2" t="inlineStr"><is><t>Napad paniki należy leczyć stosując doraźnie:</t></is></c><c r="F24" s="2" t="inlineStr"><is><t>Techniki relaksacyjne</t></is></c><c r="G24" s="2" t="inlineStr"><is><t>Alprazolam</t></is></c><c r="H24" s="2" t="inlineStr" /><c r="I24" s="2" t="inlineStr" /><c r="J24" s="2" t="inlineStr" /><c r="K24" s="2" t="inlineStr"><is><t>Pregabalinę</t></is></c><c r="L24" s="2" t="inlineStr"><is><t>Fluoksetynę</t></is></c><c r="M24" s="2" t="inlineStr" /><c r="N24" s="2" t="inlineStr" /><c r="O24" s="2" t="inlineStr" /><c r="P24" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q24" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="25"><c r="A25" s="2" t="inlineStr"><is><t>UKŁAD WSPÓŁCZULNY</t></is></c><c r="B25" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C25" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D25" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E25" s="2" t="inlineStr"><is><t>Fenoterol może być przyczyną:</t></is></c><c r="F25" s="2" t="inlineStr"><is><t>Tachykardii</t></is></c><c r="G25" s="2" t="inlineStr"><is><t>Drżenia mięśni</t></is></c><c r="H25" s="2" t="inlineStr"><is><t>Hiperglikemii</t></is></c><c r="I25" s="2" t="inlineStr"><is><t>Hamowania skurczów ciężarnej macicy</t></is></c><c r="J25" s="2" t="inlineStr" /><c r="K25" s="2" t="inlineStr" /><c r="L25" s="2" t="inlineStr" /><c r="M25" s="2" t="inlineStr" /><c r="N25" s="2" t="inlineStr" /><c r="O25" s="2" t="inlineStr" /><c r="P25" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q25" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="26"><c r="A26" s="2" t="inlineStr"><is><t>UKŁAD WSPÓŁCZULNY</t></is></c><c r="B26" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C26" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D26" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E26" s="2" t="inlineStr"><is><t>Długo działające beta2-mimetyki (LABA):</t></is></c><c r="F26" s="2" t="inlineStr"><is><t>Podawane przewlekle powodują down-regulację receptorów beta2-adrenergicznych w oskrzelach</t></is></c><c r="G26" s="2" t="inlineStr" /><c r="H26" s="2" t="inlineStr" /><c r="I26" s="2" t="inlineStr" /><c r="J26" s="2" t="inlineStr" /><c r="K26" s="2" t="inlineStr"><is><t>Nie powinny być podawane razem z glikokortykosteroidami które blokują wytwarzanie białek receptorów beta2-adrenergicznych</t></is></c><c r="L26" s="2" t="inlineStr"><is><t>Mogą być przyczyną istotnej klinicznie hieprkaliemi</t></is></c><c r="M26" s="2" t="inlineStr"><is><t>Wykazują działanie przeciwzapalne</t></is></c><c r="N26" s="2" t="inlineStr" /><c r="O26" s="2" t="inlineStr" /><c r="P26" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q26" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="27"><c r="A27" s="2" t="inlineStr"><is><t>NIEOPIOIDOWE LEKI PRZECIWBÓLOWE</t></is></c><c r="B27" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C27" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D27" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E27" s="2" t="inlineStr"><is><t>Wskaż prawidłowe stwierdzenie dotyczące NLPZ:</t></is></c><c r="F27" s="2" t="inlineStr"><is><t>Ketoprofen powoduje większe ryzyko krwawienia z górnego odcinka przewodu pokarmowego niż ibuprofen</t></is></c><c r="G27" s="2" t="inlineStr" /><c r="H27" s="2" t="inlineStr" /><c r="I27" s="2" t="inlineStr" /><c r="J27" s="2" t="inlineStr" /><c r="K27" s="2" t="inlineStr"><is><t>Meloksykam jest preferencyjnym inhibitorem COX-1</t></is></c><c r="L27" s="2" t="inlineStr"><is><t>Zastąpienie drogi doustnej podania diklofenaku drogą doodbytniczą zmniejsza ryzyko wystąpienia działań niepożądanych</t></is></c><c r="M27" s="2" t="inlineStr"><is><t>Nimesulid należy do najmniej hepatotoksycznych NLPZ</t></is></c><c r="N27" s="2" t="inlineStr" /><c r="O27" s="2" t="inlineStr" /><c r="P27" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q27" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="28"><c r="A28" s="2" t="inlineStr"><is><t>NADCIŚNIENIE TĘTNICZE</t></is></c><c r="B28" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C28" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D28" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E28" s="2" t="inlineStr"><is><t>Lekiem prkeursorowym jest:</t></is></c><c r="F28" s="2" t="inlineStr"><is><t>Enalapryl</t></is></c><c r="G28" s="2" t="inlineStr"><is><t>Cyklezonid</t></is></c><c r="H28" s="2" t="inlineStr"><is><t>Lewodopa</t></is></c><c r="I28" s="2" t="inlineStr" /><c r="J28" s="2" t="inlineStr" /><c r="K28" s="2" t="inlineStr"><is><t>Furosemid</t></is></c><c r="L28" s="2" t="inlineStr" /><c r="M28" s="2" t="inlineStr" /><c r="N28" s="2" t="inlineStr" /><c r="O28" s="2" t="inlineStr" /><c r="P28" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q28" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="29"><c r="A29" s="2" t="inlineStr"><is><t>LEKI IMMUNOSUPRESYJNE</t></is></c><c r="B29" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C29" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D29" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E29" s="2" t="inlineStr"><is><t>Cyklosporyna:</t></is></c><c r="F29" s="2" t="inlineStr"><is><t>Jest stosowana w zapobieganiu odrzucania przeszczepu allogenicznego narządów unaczynionych</t></is></c><c r="G29" s="2" t="inlineStr"><is><t>Zwiększa ryzyko chorób rozrostowych układu chłonnego</t></is></c><c r="H29" s="2" t="inlineStr" /><c r="I29" s="2" t="inlineStr" /><c r="J29" s="2" t="inlineStr" /><c r="K29" s="2" t="inlineStr"><is><t>Jest rekombinowanym w pełni ludzkim przeciwciałem monoklonalnym</t></is></c><c r="L29" s="2" t="inlineStr"><is><t>Neutralizuje biologiczną aktywność TNF</t></is></c><c r="M29" s="2" t="inlineStr" /><c r="N29" s="2" t="inlineStr" /><c r="O29" s="2" t="inlineStr" /><c r="P29" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q29" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="30"><c r="A30" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B30" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C30" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D30" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E30" s="2" t="inlineStr"><is><t>Do leków o udowodnionym korzystnym działaniu w profilaktyce wtórnej niedokrwiennego udaru mózgu należy:</t></is></c><c r="F30" s="2" t="inlineStr"><is><t>Kwas acetylosalicylowy</t></is></c><c r="G30" s="2" t="inlineStr"><is><t>Atorwastatyna</t></is></c><c r="H30" s="2" t="inlineStr"><is><t>Klopidogrel</t></is></c><c r="I30" s="2" t="inlineStr" /><c r="J30" s="2" t="inlineStr" /><c r="K30" s="2" t="inlineStr"><is><t>Kwas traneksamowy</t></is></c><c r="L30" s="2" t="inlineStr" /><c r="M30" s="2" t="inlineStr" /><c r="N30" s="2" t="inlineStr" /><c r="O30" s="2" t="inlineStr" /><c r="P30" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q30" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="31"><c r="A31" s="2" t="inlineStr"><is><t>CHOROBA PARKINSONA</t></is></c><c r="B31" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C31" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D31" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E31" s="2" t="inlineStr"><is><t>Lewodopa:</t></is></c><c r="F31" s="2" t="inlineStr"><is><t>Jest jednym z najskuteczniejszych leków stosowanych w terapii choroby Parkinsona</t></is></c><c r="G31" s="2" t="inlineStr"><is><t>Ma krótki okres półtrwania i dlatego wymaga wielokrotnego podawania w ciągu doby</t></is></c><c r="H31" s="2" t="inlineStr"><is><t>Podczas długotrwałego leczenia może wywołać fluktuacje ruchowe i dyskinezy</t></is></c><c r="I31" s="2" t="inlineStr"><is><t>Może wywoływać działania niepożądane ze strony przewodu pokarmowego</t></is></c><c r="J31" s="2" t="inlineStr" /><c r="K31" s="2" t="inlineStr" /><c r="L31" s="2" t="inlineStr" /><c r="M31" s="2" t="inlineStr" /><c r="N31" s="2" t="inlineStr" /><c r="O31" s="2" t="inlineStr" /><c r="P31" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q31" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="32"><c r="A32" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B32" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C32" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D32" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E32" s="2" t="inlineStr"><is><t>Kokaina:</t></is></c><c r="F32" s="2" t="inlineStr"><is><t>Hamuje wychwyt zwrotny dopaminy w szczelinie synaptycznej</t></is></c><c r="G32" s="2" t="inlineStr"><is><t>Może powodować wystąpienie zawału mięśnia sercowego</t></is></c><c r="H32" s="2" t="inlineStr"><is><t>Może powodować krwawienia wewnątrzczaszkowe</t></is></c><c r="I32" s="2" t="inlineStr" /><c r="J32" s="2" t="inlineStr" /><c r="K32" s="2" t="inlineStr"><is><t>Hamuje aktywność receptora dla kwasu glutaminowego</t></is></c><c r="L32" s="2" t="inlineStr" /><c r="M32" s="2" t="inlineStr" /><c r="N32" s="2" t="inlineStr" /><c r="O32" s="2" t="inlineStr" /><c r="P32" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q32" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="33"><c r="A33" s="2" t="inlineStr"><is><t>LEKI PRZECIWHISTAMINOWE</t></is></c><c r="B33" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C33" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D33" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E33" s="2" t="inlineStr"><is><t>W alergicznym zapaleniu spojówek może stosować dospojówkowo:</t></is></c><c r="F33" s="2" t="inlineStr"><is><t>Antazolinę</t></is></c><c r="G33" s="2" t="inlineStr"><is><t>Azelastynę</t></is></c><c r="H33" s="2" t="inlineStr"><is><t>Kromoglikan sodowy</t></is></c><c r="I33" s="2" t="inlineStr"><is><t>Olopatadynę</t></is></c><c r="J33" s="2" t="inlineStr" /><c r="K33" s="2" t="inlineStr" /><c r="L33" s="2" t="inlineStr" /><c r="M33" s="2" t="inlineStr" /><c r="N33" s="2" t="inlineStr" /><c r="O33" s="2" t="inlineStr" /><c r="P33" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q33" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="34"><c r="A34" s="2" t="inlineStr"><is><t>NARKOTYCZNE LEKI PRZECIWBÓLOWE</t></is></c><c r="B34" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C34" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D34" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E34" s="2" t="inlineStr"><is><t>Stosowanie preparatu złożonego bupropionu z naltreksonem w leczeniu otyłości:</t></is></c><c r="F34" s="2" t="inlineStr"><is><t>Ma wpływ na ośrodkowy układ nagrody</t></is></c><c r="G34" s="2" t="inlineStr"><is><t>Zwiększa i wydłuża uczucie sytości</t></is></c><c r="H34" s="2" t="inlineStr"><is><t>Ma zwiększoną skuteczność kliniczną ze względu na efekt synergistyczny bupropionu i naltreksonu</t></is></c><c r="I34" s="2" t="inlineStr" /><c r="J34" s="2" t="inlineStr" /><c r="K34" s="2" t="inlineStr"><is><t>Jest wskazane dla wszystkich osób z wyjściową wartością BMI wynoszącą ≥27</t></is></c><c r="L34" s="2" t="inlineStr" /><c r="M34" s="2" t="inlineStr" /><c r="N34" s="2" t="inlineStr" /><c r="O34" s="2" t="inlineStr" /><c r="P34" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q34" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="35"><c r="A35" s="2" t="inlineStr"><is><t>UKŁAD WSPÓŁCZULNY</t></is></c><c r="B35" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C35" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D35" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E35" s="2" t="inlineStr"><is><t>Dodatek adrenaliny do lidokainy w lekach do znieczulania miejscowego może powodować:</t></is></c><c r="F35" s="2" t="inlineStr"><is><t>Zwiększone ryzyko martwicy tkanek po podaniach obwodowych</t></is></c><c r="G35" s="2" t="inlineStr"><is><t>Wydłużenie czasu działania lidokainy</t></is></c><c r="H35" s="2" t="inlineStr" /><c r="I35" s="2" t="inlineStr" /><c r="J35" s="2" t="inlineStr" /><c r="K35" s="2" t="inlineStr"><is><t>Zwiększone niebezpieczeństwo zatrzymania oddechu</t></is></c><c r="L35" s="2" t="inlineStr"><is><t>Zahamowanie metabolizmu lidokainy</t></is></c><c r="M35" s="2" t="inlineStr" /><c r="N35" s="2" t="inlineStr" /><c r="O35" s="2" t="inlineStr" /><c r="P35" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q35" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="36"><c r="A36" s="2" t="inlineStr"><is><t>NIEWYDOLNOŚĆ SERCA</t></is></c><c r="B36" s="2" t="inlineStr"><is><t>Sposób podania</t></is></c><c r="C36" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D36" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E36" s="2" t="inlineStr"><is><t>Digoksyna</t></is></c><c r="F36" s="2" t="inlineStr"><is><t>Podtrzymuje aktywację baroreceptorów zatoki szyjnej przy obniżeniu ciśnienia krwi u osób z niewydolnością serca</t></is></c><c r="G36" s="2" t="inlineStr"><is><t>Podana doustnie może być nieskuteczna z powodu dezaktywacji przez bakterie jelitowe</t></is></c><c r="H36" s="2" t="inlineStr" /><c r="I36" s="2" t="inlineStr" /><c r="J36" s="2" t="inlineStr" /><c r="K36" s="2" t="inlineStr"><is><t>Powoduje kardiowersję migotania przedsionków do rytmu zatokowego</t></is></c><c r="L36" s="2" t="inlineStr"><is><t>Jest lekiem o korzystnym działaniu rokowniczym w skurczowej niewydolności serca</t></is></c><c r="M36" s="2" t="inlineStr" /><c r="N36" s="2" t="inlineStr" /><c r="O36" s="2" t="inlineStr" /><c r="P36" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q36" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="37"><c r="A37" s="2" t="inlineStr"><is><t>UKŁAD WSPÓŁCZULNY</t></is></c><c r="B37" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C37" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D37" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E37" s="2" t="inlineStr"><is><t>Teoretyczną przesłanką stosowania beta-adrenolityków w przewlekłej skurczowej niewydolności serca jest:</t></is></c><c r="F37" s="2" t="inlineStr"><is><t>Odwracanie beta-down regulacji</t></is></c><c r="G37" s="2" t="inlineStr"><is><t>Zapobieganie proarytmicznemu działaniu katecholamin</t></is></c><c r="H37" s="2" t="inlineStr" /><c r="I37" s="2" t="inlineStr" /><c r="J37" s="2" t="inlineStr" /><c r="K37" s="2" t="inlineStr"><is><t>Korzystny bezpośredni wpływ hemodynamiczny</t></is></c><c r="L37" s="2" t="inlineStr"><is><t>Zwiększenie naprężenia ściany lewej komory</t></is></c><c r="M37" s="2" t="inlineStr" /><c r="N37" s="2" t="inlineStr" /><c r="O37" s="2" t="inlineStr" /><c r="P37" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q37" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="38"><c r="A38" s="2" t="inlineStr"><is><t>LEKI PRZECIWHISTAMINOWE</t></is></c><c r="B38" s="2" t="inlineStr"><is><t>Farmakokinetyka</t></is></c><c r="C38" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D38" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E38" s="2" t="inlineStr"><is><t>Rupatadyna:</t></is></c><c r="F38" s="2" t="inlineStr"><is><t>Ma minimalny potencjał sedatywny</t></is></c><c r="G38" s="2" t="inlineStr"><is><t>Oprócz antagonizmu wobec receptora H1 wykazuje przeciwzapalną aktywność pozareceptorową</t></is></c><c r="H38" s="2" t="inlineStr"><is><t>W znacznym stopniu ulega efektowi pierwszego przejścia z powstaniem aktywnych metabolitów</t></is></c><c r="I38" s="2" t="inlineStr"><is><t>W dawkach zalecanych nie wydłuża skorygowanego odstępu cQT</t></is></c><c r="J38" s="2" t="inlineStr" /><c r="K38" s="2" t="inlineStr" /><c r="L38" s="2" t="inlineStr" /><c r="M38" s="2" t="inlineStr" /><c r="N38" s="2" t="inlineStr" /><c r="O38" s="2" t="inlineStr" /><c r="P38" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q38" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="39"><c r="A39" s="2" t="inlineStr"><is><t>NADCIŚNIENIE TĘTNICZE</t></is></c><c r="B39" s="2" t="inlineStr"><is><t>Przeciwwskazania</t></is></c><c r="C39" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D39" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E39" s="2" t="inlineStr"><is><t>U pacjentów z eGFR&lt;30ml/min należy rezygnować ze stosowania:</t></is></c><c r="F39" s="2" t="inlineStr"><is><t>Metyforminy</t></is></c><c r="G39" s="2" t="inlineStr"><is><t>Hydrochlorotiazydu</t></is></c><c r="H39" s="2" t="inlineStr" /><c r="I39" s="2" t="inlineStr" /><c r="J39" s="2" t="inlineStr" /><c r="K39" s="2" t="inlineStr"><is><t>Metoprololu</t></is></c><c r="L39" s="2" t="inlineStr"><is><t>Amlodypiny</t></is></c><c r="M39" s="2" t="inlineStr" /><c r="N39" s="2" t="inlineStr" /><c r="O39" s="2" t="inlineStr" /><c r="P39" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q39" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="40"><c r="A40" s="2" t="inlineStr"><is><t>UKŁAD PRZYWSPÓŁCZULNY</t></is></c><c r="B40" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C40" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D40" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E40" s="2" t="inlineStr"><is><t>Wenlafaksyna:</t></is></c><c r="F40" s="2" t="inlineStr"><is><t>Może być podawana w uogólnionych zaburzeniach lękowych</t></is></c><c r="G40" s="2" t="inlineStr"><is><t>Stosowana razem z tryptanami może powodować wystąpienie zespołu serotoninowego</t></is></c><c r="H40" s="2" t="inlineStr" /><c r="I40" s="2" t="inlineStr" /><c r="J40" s="2" t="inlineStr" /><c r="K40" s="2" t="inlineStr"><is><t>Ma istotne działanie cholinolityczne</t></is></c><c r="L40" s="2" t="inlineStr"><is><t>Można ją bezpiecznie stosować w terapii skojarzonej z inhibitorami MAO</t></is></c><c r="M40" s="2" t="inlineStr" /><c r="N40" s="2" t="inlineStr" /><c r="O40" s="2" t="inlineStr" /><c r="P40" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q40" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="41"><c r="A41" s="2" t="inlineStr"><is><t>LEKI IMMUNOSUPRESYJNE</t></is></c><c r="B41" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C41" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D41" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E41" s="2" t="inlineStr"><is><t>Czy słuszna jest przedstawiona interpretacja działania leku na podstawie nazwy międzynarodowej:</t></is></c><c r="F41" s="2" t="inlineStr"><is><t>Paliwizumab – humanizowane przeciwciało monoklonalne o działaniu p￾wirusowym</t></is></c><c r="G41" s="2" t="inlineStr"><is><t>Ekulizumab – humanizowane przeciwciało monoklonalne o wpływie na układ odpornościowy</t></is></c><c r="H41" s="2" t="inlineStr" /><c r="I41" s="2" t="inlineStr" /><c r="J41" s="2" t="inlineStr" /><c r="K41" s="2" t="inlineStr"><is><t>Ofatumumab – mysie przeciwciało monoklonalne o wpływie p-nowotworowym</t></is></c><c r="L41" s="2" t="inlineStr"><is><t>Pomalidomid – mysie przeciwciało monoklonalne o wpływie na układ odpornościowy</t></is></c><c r="M41" s="2" t="inlineStr" /><c r="N41" s="2" t="inlineStr" /><c r="O41" s="2" t="inlineStr" /><c r="P41" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q41" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="42"><c r="A42" s="2" t="inlineStr"><is><t>LEKI PRZECIWNOWOTWOROWE</t></is></c><c r="B42" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C42" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D42" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E42" s="2" t="inlineStr"><is><t>Do przeciwciał monoklonalnych anty-TNF należy:</t></is></c><c r="F42" s="2" t="inlineStr"><is><t>Adalimumab</t></is></c><c r="G42" s="2" t="inlineStr" /><c r="H42" s="2" t="inlineStr" /><c r="I42" s="2" t="inlineStr" /><c r="J42" s="2" t="inlineStr" /><c r="K42" s="2" t="inlineStr"><is><t>Omalizumab</t></is></c><c r="L42" s="2" t="inlineStr"><is><t>Trastuzumab</t></is></c><c r="M42" s="2" t="inlineStr"><is><t>Rytuksymab</t></is></c><c r="N42" s="2" t="inlineStr" /><c r="O42" s="2" t="inlineStr" /><c r="P42" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q42" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="43"><c r="A43" s="2" t="inlineStr"><is><t>ZABURZENIA RYTMU SERCA</t></is></c><c r="B43" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C43" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D43" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E43" s="2" t="inlineStr"><is><t>Werapamil można stosować w:</t></is></c><c r="F43" s="2" t="inlineStr"><is><t>Postaci naczynioskurczowej choroby niedokrwiennej serca</t></is></c><c r="G43" s="2" t="inlineStr"><is><t>Napadowym częstoskurczu z łącza przedsionkowo-komorowego</t></is></c><c r="H43" s="2" t="inlineStr" /><c r="I43" s="2" t="inlineStr" /><c r="J43" s="2" t="inlineStr" /><c r="K43" s="2" t="inlineStr"><is><t>Bradykardii</t></is></c><c r="L43" s="2" t="inlineStr"><is><t>Migotaniu przedsionków u osób z zespołem preekscytacji</t></is></c><c r="M43" s="2" t="inlineStr" /><c r="N43" s="2" t="inlineStr" /><c r="O43" s="2" t="inlineStr" /><c r="P43" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q43" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="44"><c r="A44" s="2" t="inlineStr"><is><t>NIEWYDOLNOŚĆ SERCA</t></is></c><c r="B44" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C44" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D44" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E44" s="2" t="inlineStr"><is><t>Inhibitory neprylizyny:</t></is></c><c r="F44" s="2" t="inlineStr"><is><t>Zmniejszają przebudowę mięśnia sercowego</t></is></c><c r="G44" s="2" t="inlineStr"><is><t>Zwiększają stężenie angiotensyny II</t></is></c><c r="H44" s="2" t="inlineStr"><is><t>Są stosowane w przewlekłej niewydolności serca z upośledzoną frakcją wyrzutową</t></is></c><c r="I44" s="2" t="inlineStr" /><c r="J44" s="2" t="inlineStr" /><c r="K44" s="2" t="inlineStr"><is><t>Rozkładają peptydy natriuretyczne</t></is></c><c r="L44" s="2" t="inlineStr" /><c r="M44" s="2" t="inlineStr" /><c r="N44" s="2" t="inlineStr" /><c r="O44" s="2" t="inlineStr" /><c r="P44" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q44" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="45"><c r="A45" s="2" t="inlineStr"><is><t>FARMAKOKINETYKA</t></is></c><c r="B45" s="2" t="inlineStr"><is><t>Farmakokinetyka</t></is></c><c r="C45" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D45" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E45" s="2" t="inlineStr"><is><t>Biodostępność leku A po jednorazowym podaniu doustnym wynosi 50%. Tmax wynosi 30min, Cmax 2µg/dl. Oznacza to, że:</t></is></c><c r="F45" s="2" t="inlineStr"><is><t>Lek A może podlegać nawet w 50% efektowi pierwszego przejścia</t></is></c><c r="G45" s="2" t="inlineStr" /><c r="H45" s="2" t="inlineStr" /><c r="I45" s="2" t="inlineStr" /><c r="J45" s="2" t="inlineStr" /><c r="K45" s="2" t="inlineStr"><is><t>Dawka wynosiła 4µg</t></is></c><c r="L45" s="2" t="inlineStr"><is><t>Lek A słabo się wiąże z białkami krwi</t></is></c><c r="M45" s="2" t="inlineStr"><is><t>Okres półtrwania leku A wynosi również około 30min</t></is></c><c r="N45" s="2" t="inlineStr" /><c r="O45" s="2" t="inlineStr" /><c r="P45" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q45" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="46"><c r="A46" s="2" t="inlineStr"><is><t>FARMAKOKINETYKA</t></is></c><c r="B46" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C46" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D46" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E46" s="2" t="inlineStr"><is><t>Podanie doodbytnicze leku:</t></is></c><c r="F46" s="2" t="inlineStr"><is><t>Może łatwo doprowadzić do miejscowego uszkodzenia błony śluzowej odbytnicy</t></is></c><c r="G46" s="2" t="inlineStr" /><c r="H46" s="2" t="inlineStr" /><c r="I46" s="2" t="inlineStr" /><c r="J46" s="2" t="inlineStr" /><c r="K46" s="2" t="inlineStr"><is><t>Zwiększa efekt pierwszego przejścia</t></is></c><c r="L46" s="2" t="inlineStr"><is><t>Jest metodą z wyboru u dzieci</t></is></c><c r="M46" s="2" t="inlineStr"><is><t>Wymaga podania większej dawki leku w porównaniu do podania doustnego</t></is></c><c r="N46" s="2" t="inlineStr" /><c r="O46" s="2" t="inlineStr" /><c r="P46" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q46" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="47"><c r="A47" s="2" t="inlineStr"><is><t>NADCIŚNIENIE TĘTNICZE</t></is></c><c r="B47" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C47" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D47" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E47" s="2" t="inlineStr"><is><t>Zaburzenia erekcji mogą być spowodowane stosowaniem:</t></is></c><c r="F47" s="2" t="inlineStr"><is><t>Inhibitorów 5-alfa reduktazy</t></is></c><c r="G47" s="2" t="inlineStr"><is><t>Tiazydów moczopędnych</t></is></c><c r="H47" s="2" t="inlineStr"><is><t>Beta-adrenolityków niekardioselektywnych</t></is></c><c r="I47" s="2" t="inlineStr"><is><t>Inhibitorów wychwytu zwrotnego serotoniny</t></is></c><c r="J47" s="2" t="inlineStr" /><c r="K47" s="2" t="inlineStr" /><c r="L47" s="2" t="inlineStr" /><c r="M47" s="2" t="inlineStr" /><c r="N47" s="2" t="inlineStr" /><c r="O47" s="2" t="inlineStr" /><c r="P47" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q47" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="48"><c r="A48" s="2" t="inlineStr"><is><t>LEKI PRZECIWDEPRESYJNE</t></is></c><c r="B48" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C48" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D48" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E48" s="2" t="inlineStr"><is><t>Doneuronalny wychwyt monoamin jest hamowany przez:</t></is></c><c r="F48" s="2" t="inlineStr"><is><t>Citalopram</t></is></c><c r="G48" s="2" t="inlineStr"><is><t>Reboksetynę</t></is></c><c r="H48" s="2" t="inlineStr" /><c r="I48" s="2" t="inlineStr" /><c r="J48" s="2" t="inlineStr" /><c r="K48" s="2" t="inlineStr"><is><t>Tianeptynę</t></is></c><c r="L48" s="2" t="inlineStr"><is><t>Mirtazapinę</t></is></c><c r="M48" s="2" t="inlineStr" /><c r="N48" s="2" t="inlineStr" /><c r="O48" s="2" t="inlineStr" /><c r="P48" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q48" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="49"><c r="A49" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B49" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C49" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D49" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E49" s="2" t="inlineStr"><is><t>W leczeniu gruźlicy płucnej lekowrażliwej:</t></is></c><c r="F49" s="2" t="inlineStr"><is><t>Leczenie wyjaławiające powinno trwać co najmniej 4 miesiące</t></is></c><c r="G49" s="2" t="inlineStr"><is><t>U kobiet ciężarnych podaje się leki według zwykłego schematu z wyłączeniem streptomycyny</t></is></c><c r="H49" s="2" t="inlineStr" /><c r="I49" s="2" t="inlineStr" /><c r="J49" s="2" t="inlineStr" /><c r="K49" s="2" t="inlineStr"><is><t>W intensywnej fazie leczenia przez 2 miesiące podaje się 2 leki – rifampicynę i izoniazyd</t></is></c><c r="L49" s="2" t="inlineStr"><is><t>W fazie kontynuacji każdy pacjent powinien otrzymać etambutol</t></is></c><c r="M49" s="2" t="inlineStr" /><c r="N49" s="2" t="inlineStr" /><c r="O49" s="2" t="inlineStr" /><c r="P49" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q49" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="50"><c r="A50" s="2" t="inlineStr"><is><t>LEKI PRZECIWDEPRESYJNE</t></is></c><c r="B50" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C50" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D50" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E50" s="2" t="inlineStr"><is><t>Wskaż prawdziwe połączenie lek-wskazanie:</t></is></c><c r="F50" s="2" t="inlineStr"><is><t>Sulpiryd – schizofrenia</t></is></c><c r="G50" s="2" t="inlineStr"><is><t>Metylofenidat – ADHD</t></is></c><c r="H50" s="2" t="inlineStr" /><c r="I50" s="2" t="inlineStr" /><c r="J50" s="2" t="inlineStr" /><c r="K50" s="2" t="inlineStr"><is><t>Moklobemid – bezsenność</t></is></c><c r="L50" s="2" t="inlineStr"><is><t>Sertindol – depresja</t></is></c><c r="M50" s="2" t="inlineStr" /><c r="N50" s="2" t="inlineStr" /><c r="O50" s="2" t="inlineStr" /><c r="P50" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q50" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="51"><c r="A51" s="2" t="inlineStr"><is><t>LEKI PRZECIWPSYCHOTYCZNE</t></is></c><c r="B51" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C51" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D51" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E51" s="2" t="inlineStr"><is><t>Hiperprolaktynemia może wiązać się z leczeniem:</t></is></c><c r="F51" s="2" t="inlineStr"><is><t>Promazyną</t></is></c><c r="G51" s="2" t="inlineStr"><is><t>Rysperydonem</t></is></c><c r="H51" s="2" t="inlineStr"><is><t>Metoklopramidem</t></is></c><c r="I51" s="2" t="inlineStr" /><c r="J51" s="2" t="inlineStr" /><c r="K51" s="2" t="inlineStr"><is><t>Bromokryptyną</t></is></c><c r="L51" s="2" t="inlineStr" /><c r="M51" s="2" t="inlineStr" /><c r="N51" s="2" t="inlineStr" /><c r="O51" s="2" t="inlineStr" /><c r="P51" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q51" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="52"><c r="A52" s="2" t="inlineStr"><is><t>UKŁAD WSPÓŁCZULNY</t></is></c><c r="B52" s="2" t="inlineStr"><is><t>Antidotum</t></is></c><c r="C52" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D52" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E52" s="2" t="inlineStr"><is><t>Ośrodkowy zespół cholinolityczny może wystąpić w wyniku ostrego przedawkowania:</t></is></c><c r="F52" s="2" t="inlineStr"><is><t>Doksepiny</t></is></c><c r="G52" s="2" t="inlineStr"><is><t>Olanzapiny</t></is></c><c r="H52" s="2" t="inlineStr"><is><t>Perfenazyny</t></is></c><c r="I52" s="2" t="inlineStr"><is><t>Klemastyny</t></is></c><c r="J52" s="2" t="inlineStr" /><c r="K52" s="2" t="inlineStr" /><c r="L52" s="2" t="inlineStr" /><c r="M52" s="2" t="inlineStr" /><c r="N52" s="2" t="inlineStr" /><c r="O52" s="2" t="inlineStr" /><c r="P52" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q52" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="53"><c r="A53" s="2" t="inlineStr"><is><t>NIEOPIOIDOWE LEKI PRZECIWBÓLOWE</t></is></c><c r="B53" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C53" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D53" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E53" s="2" t="inlineStr"><is><t>Wskaż prawdziwe stwierdzenie dotyczące metamizolu:</t></is></c><c r="F53" s="2" t="inlineStr"><is><t>Podczas szybkiego wstrzykiwania dożylnego leku może dojść do gwałtownych spadków ciśnienia krwi</t></is></c><c r="G53" s="2" t="inlineStr"><is><t>Może powodować ciężkie uszkodzenia szpiku w mechanizmie nadwrażliwości</t></is></c><c r="H53" s="2" t="inlineStr"><is><t>Zwiększa częstość występowania guzów Wilmsa (nephroblastoma, nerczak zarodkowy)</t></is></c><c r="I53" s="2" t="inlineStr" /><c r="J53" s="2" t="inlineStr" /><c r="K53" s="2" t="inlineStr"><is><t>Ma silne działanie przeciwzapalne</t></is></c><c r="L53" s="2" t="inlineStr" /><c r="M53" s="2" t="inlineStr" /><c r="N53" s="2" t="inlineStr" /><c r="O53" s="2" t="inlineStr" /><c r="P53" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q53" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="54"><c r="A54" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B54" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C54" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D54" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E54" s="2" t="inlineStr"><is><t>Które połączenie lekowe jest bezwzględnie konieczne w wymienionej sytuacji klinicznej:</t></is></c><c r="F54" s="2" t="inlineStr"><is><t>Sartan + sakubitryl w skurczowej niewydolności serca</t></is></c><c r="G54" s="2" t="inlineStr"><is><t>Kwas acetylosalicylowy + antagonista receptorów P2Y12 po angioplastyce wieńcowej z implantacją stentu</t></is></c><c r="H54" s="2" t="inlineStr" /><c r="I54" s="2" t="inlineStr" /><c r="J54" s="2" t="inlineStr" /><c r="K54" s="2" t="inlineStr"><is><t>Heparyna drobnocząsteczkowa + ksaban w początkowym okresie leczenia żylnej choroby zakrzepowo zatorowej</t></is></c><c r="L54" s="2" t="inlineStr"><is><t>Adrenalina + atropina w resuscytacji krążeniowo-oddechowej w przebiegu NZK z asystolią</t></is></c><c r="M54" s="2" t="inlineStr" /><c r="N54" s="2" t="inlineStr" /><c r="O54" s="2" t="inlineStr" /><c r="P54" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q54" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="55"><c r="A55" s="2" t="inlineStr"><is><t>UKŁAD PRZYWSPÓŁCZULNY</t></is></c><c r="B55" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C55" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D55" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E55" s="2" t="inlineStr"><is><t>Efekt prokinetyczny można uzyskać:</t></is></c><c r="F55" s="2" t="inlineStr"><is><t>Pobudzając receptory 5-HT4</t></is></c><c r="G55" s="2" t="inlineStr"><is><t>Blokując receptory dopaminowe D2</t></is></c><c r="H55" s="2" t="inlineStr"><is><t>Hamując aktywność acetylocholinoesterazy</t></is></c><c r="I55" s="2" t="inlineStr"><is><t>Pobudzając receptory motylinowe</t></is></c><c r="J55" s="2" t="inlineStr" /><c r="K55" s="2" t="inlineStr" /><c r="L55" s="2" t="inlineStr" /><c r="M55" s="2" t="inlineStr" /><c r="N55" s="2" t="inlineStr" /><c r="O55" s="2" t="inlineStr" /><c r="P55" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q55" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="56"><c r="A56" s="2" t="inlineStr"><is><t>CUKRZYCA</t></is></c><c r="B56" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C56" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D56" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E56" s="2" t="inlineStr"><is><t>Glukagon:</t></is></c><c r="F56" s="2" t="inlineStr"><is><t>Stosowany jest w leczeniu ciężkiej hipoglikemii gdy nie można podać dożylnie glukozy</t></is></c><c r="G56" s="2" t="inlineStr"><is><t>Jest podawany parenteralnie</t></is></c><c r="H56" s="2" t="inlineStr"><is><t>Ma zastosowanie w zatruciach lekami beta-adrenolitycznymi</t></is></c><c r="I56" s="2" t="inlineStr"><is><t>Jest nieskuteczny w przypadku glikemii</t></is></c><c r="J56" s="2" t="inlineStr" /><c r="K56" s="2" t="inlineStr" /><c r="L56" s="2" t="inlineStr" /><c r="M56" s="2" t="inlineStr" /><c r="N56" s="2" t="inlineStr" /><c r="O56" s="2" t="inlineStr" /><c r="P56" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q56" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="57"><c r="A57" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B57" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C57" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D57" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E57" s="2" t="inlineStr"><is><t>Ryzyko encefalopatii w przebiegu marskości wątroby zmniejsza stosowanie:</t></is></c><c r="F57" s="2" t="inlineStr"><is><t>Ryfaksyminy</t></is></c><c r="G57" s="2" t="inlineStr"><is><t>Asparaginianu ornityny</t></is></c><c r="H57" s="2" t="inlineStr"><is><t>Laktulozy</t></is></c><c r="I57" s="2" t="inlineStr" /><c r="J57" s="2" t="inlineStr" /><c r="K57" s="2" t="inlineStr"><is><t>Benzodiazepin</t></is></c><c r="L57" s="2" t="inlineStr" /><c r="M57" s="2" t="inlineStr" /><c r="N57" s="2" t="inlineStr" /><c r="O57" s="2" t="inlineStr" /><c r="P57" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q57" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="58"><c r="A58" s="2" t="inlineStr"><is><t>UKŁAD ODDECHOWY</t></is></c><c r="B58" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C58" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D58" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E58" s="2" t="inlineStr"><is><t>W celu przerwania ataku duszności uzasadnione jest podanie wziewne:</t></is></c><c r="F58" s="2" t="inlineStr"><is><t>Bromku ipratriopium</t></is></c><c r="G58" s="2" t="inlineStr"><is><t>Salbutamolu</t></is></c><c r="H58" s="2" t="inlineStr" /><c r="I58" s="2" t="inlineStr" /><c r="J58" s="2" t="inlineStr" /><c r="K58" s="2" t="inlineStr"><is><t>Roflumilastu</t></is></c><c r="L58" s="2" t="inlineStr"><is><t>flutykazonu</t></is></c><c r="M58" s="2" t="inlineStr" /><c r="N58" s="2" t="inlineStr" /><c r="O58" s="2" t="inlineStr" /><c r="P58" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q58" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="59"><c r="A59" s="2" t="inlineStr"><is><t>GLIKOKORTYKOSTEROIDY</t></is></c><c r="B59" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C59" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D59" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E59" s="2" t="inlineStr"><is><t>W leczeniu małopłytkowości stosuje się:</t></is></c><c r="F59" s="2" t="inlineStr"><is><t>Preparaty immunoglobulin poliwalentnych</t></is></c><c r="G59" s="2" t="inlineStr"><is><t>Eltrombopag</t></is></c><c r="H59" s="2" t="inlineStr"><is><t>Romiplostym</t></is></c><c r="I59" s="2" t="inlineStr"><is><t>Prednizon</t></is></c><c r="J59" s="2" t="inlineStr" /><c r="K59" s="2" t="inlineStr" /><c r="L59" s="2" t="inlineStr" /><c r="M59" s="2" t="inlineStr" /><c r="N59" s="2" t="inlineStr" /><c r="O59" s="2" t="inlineStr" /><c r="P59" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q59" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="60"><c r="A60" s="2" t="inlineStr"><is><t>LEKI PRZECIWNOWOTWOROWE</t></is></c><c r="B60" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C60" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D60" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E60" s="2" t="inlineStr"><is><t>Ewerolimus jest stosowany w:</t></is></c><c r="F60" s="2" t="inlineStr"><is><t>Kardiologii (stenty wieńcowe)</t></is></c><c r="G60" s="2" t="inlineStr"><is><t>Onkologii (wybrane zaawansowane nowotwory piersi i nerki)</t></is></c><c r="H60" s="2" t="inlineStr" /><c r="I60" s="2" t="inlineStr" /><c r="J60" s="2" t="inlineStr" /><c r="K60" s="2" t="inlineStr"><is><t>Neurologii (stwardnienie rozsiane)</t></is></c><c r="L60" s="2" t="inlineStr"><is><t>Dermatologii (łuszczyca)</t></is></c><c r="M60" s="2" t="inlineStr" /><c r="N60" s="2" t="inlineStr" /><c r="O60" s="2" t="inlineStr" /><c r="P60" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q60" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="61"><c r="A61" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B61" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C61" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D61" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E61" s="2" t="inlineStr"><is><t>Wskaż prawdziwe zdanie:</t></is></c><c r="F61" s="2" t="inlineStr"><is><t>W chromaniu przestankowym znaczenie kliniczne ma leczenie przeciwpłytkowe i hipolipemizujące</t></is></c><c r="G61" s="2" t="inlineStr"><is><t>Zaleca się podawanie inhibitora P2Y12 przed przezskórną interwencją wieńcową u osoby z ostrym zespołem wieńcowym, a następnie kontynuację tego leczenia przez co najmniej 12 miesięcy</t></is></c><c r="H61" s="2" t="inlineStr"><is><t>Po rozpoczęciu leczenia inhibitorami konwertazy angiotensyny należy się spodziewać niewielkiego wzrostu stężenia kreatyniny we krwi</t></is></c><c r="I61" s="2" t="inlineStr" /><c r="J61" s="2" t="inlineStr" /><c r="K61" s="2" t="inlineStr"><is><t>Niedihydropirydynowi antagoniści wapnia są wskazani w leczeniu pacjentów z niewydolnością serca z obniżoną frakcją wyrzutową</t></is></c><c r="L61" s="2" t="inlineStr" /><c r="M61" s="2" t="inlineStr" /><c r="N61" s="2" t="inlineStr" /><c r="O61" s="2" t="inlineStr" /><c r="P61" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q61" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="62"><c r="A62" s="2" t="inlineStr"><is><t>ZABURZENIA RYTMU SERCA</t></is></c><c r="B62" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C62" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D62" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E62" s="2" t="inlineStr"><is><t>U osób z pierwotnym wydłużenie QTc bezpieczne jest zastosowanie:</t></is></c><c r="F62" s="2" t="inlineStr"><is><t>Propranololu</t></is></c><c r="G62" s="2" t="inlineStr" /><c r="H62" s="2" t="inlineStr" /><c r="I62" s="2" t="inlineStr" /><c r="J62" s="2" t="inlineStr" /><c r="K62" s="2" t="inlineStr"><is><t>Digoksyny</t></is></c><c r="L62" s="2" t="inlineStr"><is><t>Sotalolu</t></is></c><c r="M62" s="2" t="inlineStr"><is><t>Amiodaronu</t></is></c><c r="N62" s="2" t="inlineStr" /><c r="O62" s="2" t="inlineStr" /><c r="P62" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q62" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="63"><c r="A63" s="2" t="inlineStr"><is><t>CHOROBA NIEDOKRWIENNA SERCA</t></is></c><c r="B63" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C63" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D63" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E63" s="2" t="inlineStr"><is><t>Beta-adrenolityki można zastosować w:</t></is></c><c r="F63" s="2" t="inlineStr"><is><t>Tachykardii zatokowej</t></is></c><c r="G63" s="2" t="inlineStr"><is><t>Niewydolności mięśnia serca z upośledzoną frakcją wyrzutową</t></is></c><c r="H63" s="2" t="inlineStr"><is><t>W kontroli rytmu komór w migotaniu przedsionków</t></is></c><c r="I63" s="2" t="inlineStr" /><c r="J63" s="2" t="inlineStr" /><c r="K63" s="2" t="inlineStr"><is><t>Naczynioskurczowym wariancie choroby niedokrwiennej serca</t></is></c><c r="L63" s="2" t="inlineStr" /><c r="M63" s="2" t="inlineStr" /><c r="N63" s="2" t="inlineStr" /><c r="O63" s="2" t="inlineStr" /><c r="P63" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q63" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="64"><c r="A64" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B64" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C64" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D64" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E64" s="2" t="inlineStr"><is><t>Lidokaina:</t></is></c><c r="F64" s="2" t="inlineStr"><is><t>Jest skuteczna w znieczulaniu nasiękowym</t></is></c><c r="G64" s="2" t="inlineStr"><is><t>Jest metabolizowana w wątrobie</t></is></c><c r="H64" s="2" t="inlineStr"><is><t>Może powodować drgawki</t></is></c><c r="I64" s="2" t="inlineStr" /><c r="J64" s="2" t="inlineStr" /><c r="K64" s="2" t="inlineStr"><is><t>Silnie blokuje kanały potasowe</t></is></c><c r="L64" s="2" t="inlineStr" /><c r="M64" s="2" t="inlineStr" /><c r="N64" s="2" t="inlineStr" /><c r="O64" s="2" t="inlineStr" /><c r="P64" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q64" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="65"><c r="A65" s="2" t="inlineStr"><is><t>NADCIŚNIENIE TĘTNICZE</t></is></c><c r="B65" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C65" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D65" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E65" s="2" t="inlineStr"><is><t>Wskaż prawdziwe połączenie lek-działanie niepożądane:</t></is></c><c r="F65" s="2" t="inlineStr"><is><t>Ramipryl-obrzęk naczynioruchowy</t></is></c><c r="G65" s="2" t="inlineStr"><is><t>Metoprolol-zasłabnięcie lub omdlenie</t></is></c><c r="H65" s="2" t="inlineStr" /><c r="I65" s="2" t="inlineStr" /><c r="J65" s="2" t="inlineStr" /><c r="K65" s="2" t="inlineStr"><is><t>Losartan-zwiększenie stężenia kwasu moczowego</t></is></c><c r="L65" s="2" t="inlineStr"><is><t>Simwastatyna-poprawa tolerancji glukozy</t></is></c><c r="M65" s="2" t="inlineStr" /><c r="N65" s="2" t="inlineStr" /><c r="O65" s="2" t="inlineStr" /><c r="P65" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q65" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="66"><c r="A66" s="2" t="inlineStr"><is><t>LEKI MOCZOPĘDNE</t></is></c><c r="B66" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C66" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D66" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E66" s="2" t="inlineStr"><is><t>Która ordynacja jest błędna i wymaga korekty?</t></is></c><c r="F66" s="2" t="inlineStr"><is><t>Furosemid p.o. 1xd w obrzękach pochodzenia sercowego</t></is></c><c r="G66" s="2" t="inlineStr"><is><t>Hydrochlorotiazyd p.o. 1xd w obrzękach kończyn dolnych w przebiegu zespołu pozakrzepowego podudzi</t></is></c><c r="H66" s="2" t="inlineStr" /><c r="I66" s="2" t="inlineStr" /><c r="J66" s="2" t="inlineStr" /><c r="K66" s="2" t="inlineStr"><is><t>Torasemid p.o. 1xd w obrzękach pochodzenia nerkowego</t></is></c><c r="L66" s="2" t="inlineStr"><is><t>Spironolakton p.o. 1xd w wodobrzuszu w przebiegu niewydolności wątroby</t></is></c><c r="M66" s="2" t="inlineStr" /><c r="N66" s="2" t="inlineStr" /><c r="O66" s="2" t="inlineStr" /><c r="P66" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q66" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="67"><c r="A67" s="2" t="inlineStr"><is><t>NADCIŚNIENIE TĘTNICZE</t></is></c><c r="B67" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C67" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D67" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E67" s="2" t="inlineStr"><is><t>Koangiokardianem, czyli lekiem działającym bezpośrednio na serce i naczynia jest:</t></is></c><c r="F67" s="2" t="inlineStr"><is><t>Lewosymendan</t></is></c><c r="G67" s="2" t="inlineStr" /><c r="H67" s="2" t="inlineStr" /><c r="I67" s="2" t="inlineStr" /><c r="J67" s="2" t="inlineStr" /><c r="K67" s="2" t="inlineStr"><is><t>Midodryna</t></is></c><c r="L67" s="2" t="inlineStr"><is><t>Epoprostenol</t></is></c><c r="M67" s="2" t="inlineStr"><is><t>Riocyguat</t></is></c><c r="N67" s="2" t="inlineStr" /><c r="O67" s="2" t="inlineStr" /><c r="P67" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q67" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="68"><c r="A68" s="2" t="inlineStr"><is><t>OSTEOPOROZA</t></is></c><c r="B68" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C68" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D68" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E68" s="2" t="inlineStr"><is><t>Wskaż prawdziwe stwierdzenie dotyczące bisfosfonianów:</t></is></c><c r="F68" s="2" t="inlineStr"><is><t>Są lekami pierwszego rzutu w profilaktyce i leczeniu osteoporozy pomenopauzalnej u kobiet</t></is></c><c r="G68" s="2" t="inlineStr"><is><t>Mogą być stosowane w zapobieganiu i leczeniu osteoporozy posteroidowej</t></is></c><c r="H68" s="2" t="inlineStr"><is><t>U osób z przerzutami nowotworowymi do układu kostnego łagodzą bóle kostne</t></is></c><c r="I68" s="2" t="inlineStr"><is><t>Przeciwwskazaniem do ich podawania jest ciężka niewydolność nerek (GFR&lt;30)</t></is></c><c r="J68" s="2" t="inlineStr" /><c r="K68" s="2" t="inlineStr" /><c r="L68" s="2" t="inlineStr" /><c r="M68" s="2" t="inlineStr" /><c r="N68" s="2" t="inlineStr" /><c r="O68" s="2" t="inlineStr" /><c r="P68" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q68" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="69"><c r="A69" s="2" t="inlineStr"><is><t>LEKI HIPOLIPEMIZUJĄCE</t></is></c><c r="B69" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C69" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D69" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E69" s="2" t="inlineStr"><is><t>Zmniejszenie hipertriglicerydemii można osiągnąć stosując:</t></is></c><c r="F69" s="2" t="inlineStr"><is><t>Atorwastatynę</t></is></c><c r="G69" s="2" t="inlineStr"><is><t>Fenofibrat</t></is></c><c r="H69" s="2" t="inlineStr"><is><t>PUFA-wielonienasycone kwasy tłuszczowe</t></is></c><c r="I69" s="2" t="inlineStr" /><c r="J69" s="2" t="inlineStr" /><c r="K69" s="2" t="inlineStr"><is><t>Koleswelam</t></is></c><c r="L69" s="2" t="inlineStr" /><c r="M69" s="2" t="inlineStr" /><c r="N69" s="2" t="inlineStr" /><c r="O69" s="2" t="inlineStr" /><c r="P69" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q69" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="70"><c r="A70" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B70" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C70" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D70" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E70" s="2" t="inlineStr"><is><t>Lekiem wydłużającym dystans chromania przestankowego jest:</t></is></c><c r="F70" s="2" t="inlineStr"><is><t>Natydrofuryl</t></is></c><c r="G70" s="2" t="inlineStr"><is><t>Cilostazol</t></is></c><c r="H70" s="2" t="inlineStr" /><c r="I70" s="2" t="inlineStr" /><c r="J70" s="2" t="inlineStr" /><c r="K70" s="2" t="inlineStr"><is><t>Pentoksyfilina</t></is></c><c r="L70" s="2" t="inlineStr"><is><t>Diosmina mikronizowana</t></is></c><c r="M70" s="2" t="inlineStr" /><c r="N70" s="2" t="inlineStr" /><c r="O70" s="2" t="inlineStr" /><c r="P70" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q70" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="71"><c r="A71" s="2" t="inlineStr"><is><t>LEKI HIPOLIPEMIZUJĄCE</t></is></c><c r="B71" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C71" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D71" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E71" s="2" t="inlineStr"><is><t>W prawidłowo przeprowadzonym leczeniu statynami należy:</t></is></c><c r="F71" s="2" t="inlineStr"><is><t>Oznaczyć aktywność ALAT i CK w surowicy przed rozpoczęciem leczenia</t></is></c><c r="G71" s="2" t="inlineStr"><is><t>Odstawić statynę jeśli aktywność ALAT przekroczy w surowicy 3-krotnie górną granicę wartości prawidłowych</t></is></c><c r="H71" s="2" t="inlineStr" /><c r="I71" s="2" t="inlineStr" /><c r="J71" s="2" t="inlineStr" /><c r="K71" s="2" t="inlineStr"><is><t>Ocenić skuteczność leczenia hipolipemizującego po 2 tygodniach od jego rozpoczęcia</t></is></c><c r="L71" s="2" t="inlineStr"><is><t>Mintorować aktywność CK u każdego pacjenta</t></is></c><c r="M71" s="2" t="inlineStr" /><c r="N71" s="2" t="inlineStr" /><c r="O71" s="2" t="inlineStr" /><c r="P71" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q71" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="72"><c r="A72" s="2" t="inlineStr"><is><t>NADCIŚNIENIE TĘTNICZE</t></is></c><c r="B72" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C72" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D72" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E72" s="2" t="inlineStr"><is><t>Na kanały sodowe ma wpływ:</t></is></c><c r="F72" s="2" t="inlineStr"><is><t>Ranolazyna</t></is></c><c r="G72" s="2" t="inlineStr"><is><t>Iwabradyna</t></is></c><c r="H72" s="2" t="inlineStr" /><c r="I72" s="2" t="inlineStr" /><c r="J72" s="2" t="inlineStr" /><c r="K72" s="2" t="inlineStr"><is><t>Adenozyna</t></is></c><c r="L72" s="2" t="inlineStr"><is><t>Nitrendypina</t></is></c><c r="M72" s="2" t="inlineStr" /><c r="N72" s="2" t="inlineStr" /><c r="O72" s="2" t="inlineStr" /><c r="P72" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q72" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="73"><c r="A73" s="2" t="inlineStr"><is><t>FARMAKOKINETYKA</t></is></c><c r="B73" s="2" t="inlineStr"><is><t>Interakcje</t></is></c><c r="C73" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D73" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E73" s="2" t="inlineStr"><is><t>Interakcją farmakokinetyczną jest:</t></is></c><c r="F73" s="2" t="inlineStr"><is><t>Hamowanie wchłaniania z przewodu pokarmowego leków podawanych jednocześnie</t></is></c><c r="G73" s="2" t="inlineStr"><is><t>Zwiększanie metabolizmu leków podawanych jednocześnie</t></is></c><c r="H73" s="2" t="inlineStr" /><c r="I73" s="2" t="inlineStr" /><c r="J73" s="2" t="inlineStr" /><c r="K73" s="2" t="inlineStr"><is><t>Wytrącanie się osadu po zmieszaniu dwóch leków w jednym roztworze do wstrzyknięcia</t></is></c><c r="L73" s="2" t="inlineStr"><is><t>Nasilenie sedacji po skojarzeniu opioidów z etanolem</t></is></c><c r="M73" s="2" t="inlineStr" /><c r="N73" s="2" t="inlineStr" /><c r="O73" s="2" t="inlineStr" /><c r="P73" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q73" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="74"><c r="A74" s="2" t="inlineStr"><is><t>NARKOTYCZNE LEKI PRZECIWBÓLOWE</t></is></c><c r="B74" s="2" t="inlineStr"><is><t>Antidotum</t></is></c><c r="C74" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D74" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E74" s="2" t="inlineStr"><is><t>Właściwości farmakodynamiczne i parametry farmakokinetyczne leków mają wpływ na podejmowanie decyzji klinicznych. Czy słuszne jest wobec tego:</t></is></c><c r="F74" s="2" t="inlineStr"><is><t>Wielokrotne powtórzenie dawki naloksonu(t1/2=63min+/-12min) po przedawkowaniu metadonu</t></is></c><c r="G74" s="2" t="inlineStr" /><c r="H74" s="2" t="inlineStr" /><c r="I74" s="2" t="inlineStr" /><c r="J74" s="2" t="inlineStr" /><c r="K74" s="2" t="inlineStr"><is><t>Przetoczenie koncentratu płytek krwi 13h po podaniu tikagrelolu (tikagrelol ze swoim czynnym metabolitem mają łączny czas półtrwania eliminacji 12h)</t></is></c><c r="L74" s="2" t="inlineStr"><is><t>Odstawienie suplementacji potasu w hiperaldosteronizmie pierwotnym po 16-17h po włączeniu spironolaktonu (Cmax karnenonu=16,5h po podaniu spironolaktonu)</t></is></c><c r="M74" s="2" t="inlineStr"><is><t>Przeprowadzenie operacji neurochirurgicznej po 36h po odstawieniu klopidogrelu(t1/2=6h, jego aktywne mają pomijalnie krótki t1/2)</t></is></c><c r="N74" s="2" t="inlineStr" /><c r="O74" s="2" t="inlineStr" /><c r="P74" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q74" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="75"><c r="A75" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B75" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C75" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D75" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E75" s="2" t="inlineStr"><is><t>Kolistyna:</t></is></c><c r="F75" s="2" t="inlineStr"><is><t>Może być podawana wziewnie u osób z mukowiscydozą</t></is></c><c r="G75" s="2" t="inlineStr"><is><t>Może być stosowana w leczeniu ciężkich zakażeń uogólnionych wywołanych prze Klebsiella pneumoniae wytwarzającą karbapenemazy</t></is></c><c r="H75" s="2" t="inlineStr"><is><t>Wykazuje aktywność wobec Pseudomonas aeruginosa</t></is></c><c r="I75" s="2" t="inlineStr" /><c r="J75" s="2" t="inlineStr" /><c r="K75" s="2" t="inlineStr"><is><t>Jest skuteczna w neuroinfekcjach</t></is></c><c r="L75" s="2" t="inlineStr" /><c r="M75" s="2" t="inlineStr" /><c r="N75" s="2" t="inlineStr" /><c r="O75" s="2" t="inlineStr" /><c r="P75" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q75" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="76"><c r="A76" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B76" s="2" t="inlineStr"><is><t>Ciąża</t></is></c><c r="C76" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D76" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E76" s="2" t="inlineStr"><is><t>Doksycyklina</t></is></c><c r="F76" s="2" t="inlineStr"><is><t>Działa na bakterie atypowe</t></is></c><c r="G76" s="2" t="inlineStr" /><c r="H76" s="2" t="inlineStr" /><c r="I76" s="2" t="inlineStr" /><c r="J76" s="2" t="inlineStr" /><c r="K76" s="2" t="inlineStr"><is><t>Może być bezpiecznie stosowana u dzieci powyżej 2r.ż</t></is></c><c r="L76" s="2" t="inlineStr"><is><t>Jest anatgonistą receptorów GABA-A wywołujących efekt sedatywny</t></is></c><c r="M76" s="2" t="inlineStr"><is><t>Jest bezpieczna w terapii kobiet w ciąży</t></is></c><c r="N76" s="2" t="inlineStr" /><c r="O76" s="2" t="inlineStr" /><c r="P76" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q76" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="77"><c r="A77" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B77" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C77" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D77" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E77" s="2" t="inlineStr"><is><t>Wskaż prawdziwe połączenie lek-mechanizm działania:</t></is></c><c r="F77" s="2" t="inlineStr"><is><t>Fosfomycyna-blokowanie syntezy ściany komórkowej bakterii</t></is></c><c r="G77" s="2" t="inlineStr" /><c r="H77" s="2" t="inlineStr" /><c r="I77" s="2" t="inlineStr" /><c r="J77" s="2" t="inlineStr" /><c r="K77" s="2" t="inlineStr"><is><t>Cefepim-hamowanie topoizomerazy II</t></is></c><c r="L77" s="2" t="inlineStr"><is><t>Pefloksacyna-hamowanie biosyntezy białka w komórkach bakterii poprzez wiązanie się z podjednostką 50S rybosomu</t></is></c><c r="M77" s="2" t="inlineStr"><is><t>Trimetoprim-bezpośrednie uszkodzenie DNA</t></is></c><c r="N77" s="2" t="inlineStr" /><c r="O77" s="2" t="inlineStr" /><c r="P77" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q77" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="78"><c r="A78" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B78" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C78" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D78" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E78" s="2" t="inlineStr"><is><t>Wskaż prawdziwe połączenie lek-działania niepożądane:</t></is></c><c r="F78" s="2" t="inlineStr"><is><t>Amoksycylina-leukopenia w mechanizmie nadwrażliwości immunologicznej</t></is></c><c r="G78" s="2" t="inlineStr"><is><t>Tynidazol-neuropatia obwodowa</t></is></c><c r="H78" s="2" t="inlineStr"><is><t>Amikacyna-zaburzenia słuchu i równowagi</t></is></c><c r="I78" s="2" t="inlineStr" /><c r="J78" s="2" t="inlineStr" /><c r="K78" s="2" t="inlineStr"><is><t>Roksytromycyna-uszkodzenie nerek</t></is></c><c r="L78" s="2" t="inlineStr" /><c r="M78" s="2" t="inlineStr" /><c r="N78" s="2" t="inlineStr" /><c r="O78" s="2" t="inlineStr" /><c r="P78" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q78" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="79"><c r="A79" s="2" t="inlineStr"><is><t>LEKI PRZECIWWIRUSOWE</t></is></c><c r="B79" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C79" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D79" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E79" s="2" t="inlineStr"><is><t>Właściwy wybór leku przeciwwirusowego w zakażeniu to:</t></is></c><c r="F79" s="2" t="inlineStr"><is><t>Wirus HBV-lamiwudyna</t></is></c><c r="G79" s="2" t="inlineStr"><is><t>Cytomegalowirus-walgancyklowir</t></is></c><c r="H79" s="2" t="inlineStr" /><c r="I79" s="2" t="inlineStr" /><c r="J79" s="2" t="inlineStr" /><c r="K79" s="2" t="inlineStr"><is><t>Norowirus-sakwinawir</t></is></c><c r="L79" s="2" t="inlineStr"><is><t>Wirus opryszczki-rybawiryna</t></is></c><c r="M79" s="2" t="inlineStr" /><c r="N79" s="2" t="inlineStr" /><c r="O79" s="2" t="inlineStr" /><c r="P79" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q79" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="80"><c r="A80" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B80" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C80" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D80" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E80" s="2" t="inlineStr"><is><t>Wskaż prawdziwe połączenie lek-wrażliwy drobnoustrój:</t></is></c><c r="F80" s="2" t="inlineStr"><is><t>Lewofloksacyna-Streptococcus pneumoniae</t></is></c><c r="G80" s="2" t="inlineStr"><is><t>Aksetyl cefuroksymu-Hemophilus influenzae</t></is></c><c r="H80" s="2" t="inlineStr" /><c r="I80" s="2" t="inlineStr" /><c r="J80" s="2" t="inlineStr" /><c r="K80" s="2" t="inlineStr"><is><t>Fenoksymetylopenicylina-Staphylococcus aureus MSSA</t></is></c><c r="L80" s="2" t="inlineStr"><is><t>Fidaksomycyna-Bacteroides fragilis</t></is></c><c r="M80" s="2" t="inlineStr" /><c r="N80" s="2" t="inlineStr" /><c r="O80" s="2" t="inlineStr" /><c r="P80" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q80" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="81"><c r="A81" s="2" t="inlineStr"><is><t>LEKI PRZECIWGRZYBICZE</t></is></c><c r="B81" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C81" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D81" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E81" s="2" t="inlineStr"><is><t>Flukonazol:</t></is></c><c r="F81" s="2" t="inlineStr"><is><t>W leczeniu kandydozy jamy ustnej nie jest skuteczny po podaniu dawki jednorazowej</t></is></c><c r="G81" s="2" t="inlineStr" /><c r="H81" s="2" t="inlineStr" /><c r="I81" s="2" t="inlineStr" /><c r="J81" s="2" t="inlineStr" /><c r="K81" s="2" t="inlineStr"><is><t>Ma małą biodostępność po podaniu doustnym</t></is></c><c r="L81" s="2" t="inlineStr"><is><t>Powinien być podawany profilaktycznie pacjentom leczonym szerokospektralnymi lekami przeciwbakteryjnymi z powodu zakażenia układu oddechowego</t></is></c><c r="M81" s="2" t="inlineStr"><is><t>Istotnie hamuje syntezę hormonów steroidowych</t></is></c><c r="N81" s="2" t="inlineStr" /><c r="O81" s="2" t="inlineStr" /><c r="P81" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q81" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="82"><c r="A82" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B82" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C82" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D82" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E82" s="2" t="inlineStr"><is><t>Wyłącznie na ustroje gram dodatnie działa:</t></is></c><c r="F82" s="2" t="inlineStr"><is><t>Mupriocyna</t></is></c><c r="G82" s="2" t="inlineStr" /><c r="H82" s="2" t="inlineStr" /><c r="I82" s="2" t="inlineStr" /><c r="J82" s="2" t="inlineStr" /><c r="K82" s="2" t="inlineStr"><is><t>Metronidazol</t></is></c><c r="L82" s="2" t="inlineStr"><is><t>Fosfomycyna</t></is></c><c r="M82" s="2" t="inlineStr"><is><t>Gentamycyna</t></is></c><c r="N82" s="2" t="inlineStr" /><c r="O82" s="2" t="inlineStr" /><c r="P82" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q82" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="83"><c r="A83" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B83" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C83" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D83" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E83" s="2" t="inlineStr"><is><t>W leczeniu rzęsistkowicy (Trichomonas Vaginalis) wykorzystuje się:</t></is></c><c r="F83" s="2" t="inlineStr"><is><t>Tynidazol</t></is></c><c r="G83" s="2" t="inlineStr"><is><t>Metronidazol</t></is></c><c r="H83" s="2" t="inlineStr" /><c r="I83" s="2" t="inlineStr" /><c r="J83" s="2" t="inlineStr" /><c r="K83" s="2" t="inlineStr"><is><t>Sulfametoksazol+trymetoprym</t></is></c><c r="L83" s="2" t="inlineStr"><is><t>Spiramycynę</t></is></c><c r="M83" s="2" t="inlineStr" /><c r="N83" s="2" t="inlineStr" /><c r="O83" s="2" t="inlineStr" /><c r="P83" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q83" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="84"><c r="A84" s="2" t="inlineStr"><is><t>LEKI PRZECIWWIRUSOWE</t></is></c><c r="B84" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C84" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D84" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E84" s="2" t="inlineStr"><is><t>Do charakterystycznych działań niepożądanych inhibitorów proteazy HIV należy/należą:</t></is></c><c r="F84" s="2" t="inlineStr"><is><t>Liczne interakcje lekowe</t></is></c><c r="G84" s="2" t="inlineStr"><is><t>Cukrzyca</t></is></c><c r="H84" s="2" t="inlineStr"><is><t>Uszkodzenie wątroby</t></is></c><c r="I84" s="2" t="inlineStr"><is><t>Hipertriglicerydemia</t></is></c><c r="J84" s="2" t="inlineStr" /><c r="K84" s="2" t="inlineStr" /><c r="L84" s="2" t="inlineStr" /><c r="M84" s="2" t="inlineStr" /><c r="N84" s="2" t="inlineStr" /><c r="O84" s="2" t="inlineStr" /><c r="P84" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q84" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="85"><c r="A85" s="2" t="inlineStr"><is><t>LEKI PRZECIWGRZYBICZE</t></is></c><c r="B85" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C85" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D85" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E85" s="2" t="inlineStr"><is><t>W zakażeniu o etiologii Candida albicans można zastosować miejscowo:</t></is></c><c r="F85" s="2" t="inlineStr"><is><t>Natamycynę</t></is></c><c r="G85" s="2" t="inlineStr"><is><t>Mykonazol</t></is></c><c r="H85" s="2" t="inlineStr" /><c r="I85" s="2" t="inlineStr" /><c r="J85" s="2" t="inlineStr" /><c r="K85" s="2" t="inlineStr"><is><t>Mykafunginę</t></is></c><c r="L85" s="2" t="inlineStr"><is><t>Izawukonazol</t></is></c><c r="M85" s="2" t="inlineStr" /><c r="N85" s="2" t="inlineStr" /><c r="O85" s="2" t="inlineStr" /><c r="P85" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q85" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="86"><c r="A86" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B86" s="2" t="inlineStr"><is><t>Monitorowanie</t></is></c><c r="C86" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D86" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E86" s="2" t="inlineStr"><is><t>Jeśli celem farmakodynamicznym dla stosowanego antybiotyku jest wysoka wartość T&gt;MIC to powinno się:</t></is></c><c r="F86" s="2" t="inlineStr"><is><t>Monitorować stężenie leku we krwi w celu modyfikacji dawkowania</t></is></c><c r="G86" s="2" t="inlineStr"><is><t>Podawać lek w przedłużonym wlewie dożylnym</t></is></c><c r="H86" s="2" t="inlineStr"><is><t>Zwiększać częstość podawania leku w ciągu doby</t></is></c><c r="I86" s="2" t="inlineStr" /><c r="J86" s="2" t="inlineStr" /><c r="K86" s="2" t="inlineStr"><is><t>Podać lek w pojedynczej skumulowanej dawce dobowej</t></is></c><c r="L86" s="2" t="inlineStr" /><c r="M86" s="2" t="inlineStr" /><c r="N86" s="2" t="inlineStr" /><c r="O86" s="2" t="inlineStr" /><c r="P86" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q86" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="87"><c r="A87" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B87" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C87" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D87" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E87" s="2" t="inlineStr"><is><t>Do przestarzałych środków odkażających, które z powodu braku skuteczności lub istotnych działań niepożądanych nie powinny być obecnie stosowane należy:</t></is></c><c r="F87" s="2" t="inlineStr"><is><t>Nadmanganian potasu</t></is></c><c r="G87" s="2" t="inlineStr"><is><t>Tetraboran sodowy</t></is></c><c r="H87" s="2" t="inlineStr" /><c r="I87" s="2" t="inlineStr" /><c r="J87" s="2" t="inlineStr" /><c r="K87" s="2" t="inlineStr"><is><t>Oktenidyna</t></is></c><c r="L87" s="2" t="inlineStr"><is><t>Jodopowidon</t></is></c><c r="M87" s="2" t="inlineStr" /><c r="N87" s="2" t="inlineStr" /><c r="O87" s="2" t="inlineStr" /><c r="P87" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q87" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="88"><c r="A88" s="2" t="inlineStr"><is><t>LEKI PRZECIWPASOŻYTNICZE</t></is></c><c r="B88" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C88" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D88" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E88" s="2" t="inlineStr"><is><t>Wskaż prawidłowe stwierdzenia dotyczące profilaktyki i leczenia malarii:</t></is></c><c r="F88" s="2" t="inlineStr"><is><t>Lumefantryna w połączeniu z artemeterem może być skuteczna w zakażeniu Plasmodium falciparum</t></is></c><c r="G88" s="2" t="inlineStr"><is><t>W przypadkach wymagających profilaktyki długoterminowej można zastosować chlorochinę</t></is></c><c r="H88" s="2" t="inlineStr" /><c r="I88" s="2" t="inlineStr" /><c r="J88" s="2" t="inlineStr" /><c r="K88" s="2" t="inlineStr"><is><t>Pochodne artemizyniny zalecane są tylko do profilaktyki malarii</t></is></c><c r="L88" s="2" t="inlineStr"><is><t>Atowakwon z proguanilem może być stosowany u osób z upośledzoną czynnością nerek (GFR&lt;30)</t></is></c><c r="M88" s="2" t="inlineStr" /><c r="N88" s="2" t="inlineStr" /><c r="O88" s="2" t="inlineStr" /><c r="P88" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q88" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="89"><c r="A89" s="2" t="inlineStr"><is><t>NADCIŚNIENIE TĘTNICZE</t></is></c><c r="B89" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C89" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D89" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E89" s="2" t="inlineStr"><is><t>Do przyczyn jatrogennej nefropatii można zaliczyć stosowanie:</t></is></c><c r="F89" s="2" t="inlineStr"><is><t>Jodowych środków kontrastowych podczas koronarografii</t></is></c><c r="G89" s="2" t="inlineStr"><is><t>Ibuprofenu przewlekle w reumatoidalnym zapaleniu stawów</t></is></c><c r="H89" s="2" t="inlineStr"><is><t>Ramiprylu w niewydolności serca</t></is></c><c r="I89" s="2" t="inlineStr" /><c r="J89" s="2" t="inlineStr" /><c r="K89" s="2" t="inlineStr"><is><t>Loratadyny przewlekle w alergicznym zapaleniu błony śluzowej nosa</t></is></c><c r="L89" s="2" t="inlineStr" /><c r="M89" s="2" t="inlineStr" /><c r="N89" s="2" t="inlineStr" /><c r="O89" s="2" t="inlineStr" /><c r="P89" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q89" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="90"><c r="A90" s="2" t="inlineStr"><is><t>FARMAKOKINETYKA</t></is></c><c r="B90" s="2" t="inlineStr"><is><t>Farmakokinetyka</t></is></c><c r="C90" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D90" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E90" s="2" t="inlineStr"><is><t>Wskaż prawdziwe zdania dotyczące leczenia morfiną:</t></is></c><c r="F90" s="2" t="inlineStr"><is><t>Metabolity morfiny wydalane są przez nerki</t></is></c><c r="G90" s="2" t="inlineStr"><is><t>Przy przewlekłym stosowaniu morfiny powstaje morfino-6-glukuronian – metabolit, którego siła działania analgetycznego przewyższa siłę działania związku macierzystego</t></is></c><c r="H90" s="2" t="inlineStr"><is><t>Morfina może być podawana zewnątrzoponowo</t></is></c><c r="I90" s="2" t="inlineStr" /><c r="J90" s="2" t="inlineStr" /><c r="K90" s="2" t="inlineStr"><is><t>Morfina ma dużą biodostępność po podaniu doustnym</t></is></c><c r="L90" s="2" t="inlineStr" /><c r="M90" s="2" t="inlineStr" /><c r="N90" s="2" t="inlineStr" /><c r="O90" s="2" t="inlineStr" /><c r="P90" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q90" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="91"><c r="A91" s="2" t="inlineStr"><is><t>CUKRZYCA</t></is></c><c r="B91" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C91" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D91" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E91" s="2" t="inlineStr"><is><t>Wskazanie do insulinoterapii jest:</t></is></c><c r="F91" s="2" t="inlineStr"><is><t>Cukrzyca typu LADA</t></is></c><c r="G91" s="2" t="inlineStr"><is><t>Ostry zespół wieńcowy u osoby z cukrzycą typu II</t></is></c><c r="H91" s="2" t="inlineStr"><is><t>Znaczna hiperglikemia (&gt;300) w przebiegu cukrzycy typu II</t></is></c><c r="I91" s="2" t="inlineStr"><is><t>Cukrzyca ciężarnych</t></is></c><c r="J91" s="2" t="inlineStr" /><c r="K91" s="2" t="inlineStr" /><c r="L91" s="2" t="inlineStr" /><c r="M91" s="2" t="inlineStr" /><c r="N91" s="2" t="inlineStr" /><c r="O91" s="2" t="inlineStr" /><c r="P91" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q91" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="92"><c r="A92" s="2" t="inlineStr"><is><t>CUKRZYCA</t></is></c><c r="B92" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C92" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D92" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E92" s="2" t="inlineStr"><is><t>Długodziałające analogii insuliny w porównaniu do insuliny protaminowo-cynkowej (NPH) charakteryzują się:</t></is></c><c r="F92" s="2" t="inlineStr"><is><t>Mniejszym ryzykiem hipoglikemii</t></is></c><c r="G92" s="2" t="inlineStr" /><c r="H92" s="2" t="inlineStr" /><c r="I92" s="2" t="inlineStr" /><c r="J92" s="2" t="inlineStr" /><c r="K92" s="2" t="inlineStr"><is><t>Mniejszym ryzykiem onkologicznym</t></is></c><c r="L92" s="2" t="inlineStr"><is><t>Większym ryzykiem zjawiska brzasku</t></is></c><c r="M92" s="2" t="inlineStr"><is><t>Działaniem anorektycznym</t></is></c><c r="N92" s="2" t="inlineStr" /><c r="O92" s="2" t="inlineStr" /><c r="P92" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q92" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="93"><c r="A93" s="2" t="inlineStr"><is><t>TARCZYCA</t></is></c><c r="B93" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C93" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D93" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E93" s="2" t="inlineStr"><is><t>Zmniejszenie obwodowej konwersji tyroksyny do trójjodotyroniny jest efektem stosowania:</t></is></c><c r="F93" s="2" t="inlineStr"><is><t>Hydrokortyzonu</t></is></c><c r="G93" s="2" t="inlineStr"><is><t>Propylotiouracylu</t></is></c><c r="H93" s="2" t="inlineStr"><is><t>Propanololu</t></is></c><c r="I93" s="2" t="inlineStr" /><c r="J93" s="2" t="inlineStr" /><c r="K93" s="2" t="inlineStr"><is><t>Płynu Lugola</t></is></c><c r="L93" s="2" t="inlineStr" /><c r="M93" s="2" t="inlineStr" /><c r="N93" s="2" t="inlineStr" /><c r="O93" s="2" t="inlineStr" /><c r="P93" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q93" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="94"><c r="A94" s="2" t="inlineStr"><is><t>OSTEOPOROZA</t></is></c><c r="B94" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C94" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D94" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E94" s="2" t="inlineStr"><is><t>Wskazaniem do stosowania hormonalnej terapii zastępczej u kobiet po menopauzie jest:</t></is></c><c r="F94" s="2" t="inlineStr"><is><t>Obecność objawów wypadowych</t></is></c><c r="G94" s="2" t="inlineStr" /><c r="H94" s="2" t="inlineStr" /><c r="I94" s="2" t="inlineStr" /><c r="J94" s="2" t="inlineStr" /><c r="K94" s="2" t="inlineStr"><is><t>Wtórna profilaktyka chorób układu krążenia</t></is></c><c r="L94" s="2" t="inlineStr"><is><t>Profilaktyka osteoporozy</t></is></c><c r="M94" s="2" t="inlineStr"><is><t>Zapobieganie chorobie Alzheimera</t></is></c><c r="N94" s="2" t="inlineStr" /><c r="O94" s="2" t="inlineStr" /><c r="P94" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q94" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="95"><c r="A95" s="2" t="inlineStr"><is><t>NIEOPIOIDOWE LEKI PRZECIWBÓLOWE</t></is></c><c r="B95" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C95" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D95" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E95" s="2" t="inlineStr"><is><t>Przeciwbólowy efekt pułapowy wykazuje:</t></is></c><c r="F95" s="2" t="inlineStr"><is><t>Naproksen</t></is></c><c r="G95" s="2" t="inlineStr"><is><t>Buprenorfina</t></is></c><c r="H95" s="2" t="inlineStr"><is><t>Ibuprofen</t></is></c><c r="I95" s="2" t="inlineStr" /><c r="J95" s="2" t="inlineStr" /><c r="K95" s="2" t="inlineStr"><is><t>Oksykodon</t></is></c><c r="L95" s="2" t="inlineStr" /><c r="M95" s="2" t="inlineStr" /><c r="N95" s="2" t="inlineStr" /><c r="O95" s="2" t="inlineStr" /><c r="P95" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q95" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="96"><c r="A96" s="2" t="inlineStr"><is><t>ZABURZENIA RYTMU SERCA</t></is></c><c r="B96" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C96" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D96" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E96" s="2" t="inlineStr"><is><t>Teofilina:</t></is></c><c r="F96" s="2" t="inlineStr"><is><t>Jest anatgonistą receptora adenozynowego</t></is></c><c r="G96" s="2" t="inlineStr"><is><t>Hamuje aktywność fosfodiesteraz</t></is></c><c r="H96" s="2" t="inlineStr"><is><t>Zwiększa przepływ nerkowy</t></is></c><c r="I96" s="2" t="inlineStr"><is><t>Pobudza ośrodek oddechowy w rdzeniu przedłużonym</t></is></c><c r="J96" s="2" t="inlineStr" /><c r="K96" s="2" t="inlineStr" /><c r="L96" s="2" t="inlineStr" /><c r="M96" s="2" t="inlineStr" /><c r="N96" s="2" t="inlineStr" /><c r="O96" s="2" t="inlineStr" /><c r="P96" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q96" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="97"><c r="A97" s="2" t="inlineStr"><is><t>FARMAKOKINETYKA</t></is></c><c r="B97" s="2" t="inlineStr"><is><t>Farmakokinetyka</t></is></c><c r="C97" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D97" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E97" s="2" t="inlineStr"><is><t>Idealny glikokortykosteroid wziewny:</t></is></c><c r="F97" s="2" t="inlineStr"><is><t>Połknięty charakteryzuje się niewielką biodostępnością</t></is></c><c r="G97" s="2" t="inlineStr" /><c r="H97" s="2" t="inlineStr" /><c r="I97" s="2" t="inlineStr" /><c r="J97" s="2" t="inlineStr" /><c r="K97" s="2" t="inlineStr"><is><t>Dobrze wchłania się z pęcherzyków płucnych</t></is></c><c r="L97" s="2" t="inlineStr"><is><t>Nie podlega efektowi pierwszego przejścia przez wątrobę</t></is></c><c r="M97" s="2" t="inlineStr"><is><t>Ma krótki okres półtrwania kompleksu glikokortkosteroidu z receptorem t1/2=2-3h</t></is></c><c r="N97" s="2" t="inlineStr" /><c r="O97" s="2" t="inlineStr" /><c r="P97" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q97" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="98"><c r="A98" s="2" t="inlineStr"><is><t>NIEOPIOIDOWE LEKI PRZECIWBÓLOWE</t></is></c><c r="B98" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C98" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D98" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E98" s="2" t="inlineStr"><is><t>Działanie keratolityczne wykazuje:</t></is></c><c r="F98" s="2" t="inlineStr"><is><t>Mocznik</t></is></c><c r="G98" s="2" t="inlineStr"><is><t>Kwas salicylowy</t></is></c><c r="H98" s="2" t="inlineStr"><is><t>Nadtlenek benzoilu</t></is></c><c r="I98" s="2" t="inlineStr" /><c r="J98" s="2" t="inlineStr" /><c r="K98" s="2" t="inlineStr"><is><t>Metoksalen</t></is></c><c r="L98" s="2" t="inlineStr" /><c r="M98" s="2" t="inlineStr" /><c r="N98" s="2" t="inlineStr" /><c r="O98" s="2" t="inlineStr" /><c r="P98" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q98" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="99"><c r="A99" s="2" t="inlineStr"><is><t>LEKI PRZECIWDEPRESYJNE</t></is></c><c r="B99" s="2" t="inlineStr"><is><t>Antidotum</t></is></c><c r="C99" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D99" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E99" s="2" t="inlineStr"><is><t>W zatruciu solami litu:</t></is></c><c r="F99" s="2" t="inlineStr"><is><t>Należy natychmiast zakończyć podawanie litu</t></is></c><c r="G99" s="2" t="inlineStr"><is><t>W leczeniu ostrego zatrucia istotne znaczenie ma intensywne wyrównanie zaburzeń gospodarki wodno-elektrolitowej, zwłaszcza uzupełnianie niedoboru sodu poprzez przetaczanie roztworu 0,9% NaCl dożylnie</t></is></c><c r="H99" s="2" t="inlineStr"><is><t>Podstawową metodą eliminacji leku jest hemodializa</t></is></c><c r="I99" s="2" t="inlineStr" /><c r="J99" s="2" t="inlineStr" /><c r="K99" s="2" t="inlineStr"><is><t>Korzystne działanie ma stosowanie węgla aktywowanego</t></is></c><c r="L99" s="2" t="inlineStr" /><c r="M99" s="2" t="inlineStr" /><c r="N99" s="2" t="inlineStr" /><c r="O99" s="2" t="inlineStr" /><c r="P99" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q99" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="100"><c r="A100" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B100" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C100" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D100" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E100" s="2" t="inlineStr"><is><t>Doksycyklina:</t></is></c><c r="F100" s="2" t="inlineStr"><is><t>w niewielkim stopniu penetruje do ośrodkowego układu nerwowego</t></is></c><c r="G100" s="2" t="inlineStr"><is><t>tworzy chelaty z solami żelaza</t></is></c><c r="H100" s="2" t="inlineStr"><is><t>jest stosowana w leczeniu zakażeń układu moczowego o etiologii Chlamydia trachomatis</t></is></c><c r="I100" s="2" t="inlineStr"><is><t>nie wykazuje aktywności wobec Pseudomonas aeruginosa</t></is></c><c r="J100" s="2" t="inlineStr" /><c r="K100" s="2" t="inlineStr" /><c r="L100" s="2" t="inlineStr" /><c r="M100" s="2" t="inlineStr" /><c r="N100" s="2" t="inlineStr" /><c r="O100" s="2" t="inlineStr" /><c r="P100" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q100" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="101"><c r="A101" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B101" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C101" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D101" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E101" s="2" t="inlineStr"><is><t>Fluorochinolony:</t></is></c><c r="F101" s="2" t="inlineStr"><is><t>mogą spowodować zapalenie ścięgien</t></is></c><c r="G101" s="2" t="inlineStr"><is><t>mogą być przyczyną zaburzeń rytmu serca</t></is></c><c r="H101" s="2" t="inlineStr" /><c r="I101" s="2" t="inlineStr" /><c r="J101" s="2" t="inlineStr" /><c r="K101" s="2" t="inlineStr"><is><t>wszystkie generacje mają zbliżoną skuteczność przeciwko Gram ujemnym pałeczkom niefermentującym</t></is></c><c r="L101" s="2" t="inlineStr"><is><t>są agonistami receptorów GABA-A wywołując efekt sedatywny</t></is></c><c r="M101" s="2" t="inlineStr" /><c r="N101" s="2" t="inlineStr" /><c r="O101" s="2" t="inlineStr" /><c r="P101" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q101" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="102"><c r="A102" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B102" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C102" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D102" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E102" s="2" t="inlineStr"><is><t>Wskaż prawdziwe połączenie lek – mechanizm działania:</t></is></c><c r="F102" s="2" t="inlineStr"><is><t>linezolid- hamowanie biosyntezy białka w komórkach bakterii poprzez wiązanie się z podjednostką 50 S rybosomu</t></is></c><c r="G102" s="2" t="inlineStr" /><c r="H102" s="2" t="inlineStr" /><c r="I102" s="2" t="inlineStr" /><c r="J102" s="2" t="inlineStr" /><c r="K102" s="2" t="inlineStr"><is><t>cefuroksym – hamowanie topoizomerazy II</t></is></c><c r="L102" s="2" t="inlineStr"><is><t>moksyfloksacyna - blokowanie syntezy ściany komórkowej bakterii</t></is></c><c r="M102" s="2" t="inlineStr"><is><t>wankomycyna - uszkodzenie DNA</t></is></c><c r="N102" s="2" t="inlineStr" /><c r="O102" s="2" t="inlineStr" /><c r="P102" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q102" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="103"><c r="A103" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B103" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C103" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D103" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E103" s="2" t="inlineStr"><is><t>Wskaż prawdziwe połączenie lek – działania niepożądane:</t></is></c><c r="F103" s="2" t="inlineStr"><is><t>tygecyklina - nadwrażliwość na światło</t></is></c><c r="G103" s="2" t="inlineStr"><is><t>metronidazol - neuropatia obwodowa</t></is></c><c r="H103" s="2" t="inlineStr"><is><t>wankomycyna – uwalnianie histaminy</t></is></c><c r="I103" s="2" t="inlineStr" /><c r="J103" s="2" t="inlineStr" /><c r="K103" s="2" t="inlineStr"><is><t>azytromycyna – blokowanie wątrobowych enzymów mikrosomalnych (CYP)</t></is></c><c r="L103" s="2" t="inlineStr" /><c r="M103" s="2" t="inlineStr" /><c r="N103" s="2" t="inlineStr" /><c r="O103" s="2" t="inlineStr" /><c r="P103" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q103" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="104"><c r="A104" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B104" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C104" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D104" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E104" s="2" t="inlineStr"><is><t>Błędny schemat terapeutyczny to zastosowanie:</t></is></c><c r="F104" s="2" t="inlineStr"><is><t>loperamidu w zapalnej biegunce poantybiotykowej przez 10 dni</t></is></c><c r="G104" s="2" t="inlineStr" /><c r="H104" s="2" t="inlineStr" /><c r="I104" s="2" t="inlineStr" /><c r="J104" s="2" t="inlineStr" /><c r="K104" s="2" t="inlineStr"><is><t>azytromycyny w krztuścu przez 5 dni</t></is></c><c r="L104" s="2" t="inlineStr"><is><t>kotrymoksazolu w niepowikłanym zakażeniu układu moczowego przez 3 dni</t></is></c><c r="M104" s="2" t="inlineStr"><is><t>fenoksymetylpenicyliny w anginie paciorkowcowej przez 10 dni</t></is></c><c r="N104" s="2" t="inlineStr" /><c r="O104" s="2" t="inlineStr" /><c r="P104" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q104" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="105"><c r="A105" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B105" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C105" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D105" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E105" s="2" t="inlineStr"><is><t>W leczeniu 60-letniego pacjenta z pozaszpitalnym zapaleniem płuc (skala CURB-0pkt) uwzględniającym typową etiologię zakażenia u dorosłych należy:</t></is></c><c r="F105" s="2" t="inlineStr"><is><t>stosować stałe optymalne przedziały dawkowania w ciągu całej doby</t></is></c><c r="G105" s="2" t="inlineStr"><is><t>w razie nadwrażliwości na leczenie początkowe w wywiadach zastosować lewofloksacynę lub moksyfloksacynę</t></is></c><c r="H105" s="2" t="inlineStr" /><c r="I105" s="2" t="inlineStr" /><c r="J105" s="2" t="inlineStr" /><c r="K105" s="2" t="inlineStr"><is><t>leczyć 2 lekami przeciwbakteryjnymi o różnych mechanizmach działania</t></is></c><c r="L105" s="2" t="inlineStr"><is><t>prowadzić terapię co najmniej 21 dni</t></is></c><c r="M105" s="2" t="inlineStr" /><c r="N105" s="2" t="inlineStr" /><c r="O105" s="2" t="inlineStr" /><c r="P105" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q105" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="106"><c r="A106" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B106" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C106" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D106" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E106" s="2" t="inlineStr"><is><t>W leczeniu zapalenia opon mózgowo-rdzeniowych uzasadnione jest zastosowanie:</t></is></c><c r="F106" s="2" t="inlineStr"><is><t>ceftriaksonu</t></is></c><c r="G106" s="2" t="inlineStr"><is><t>acyklowiru</t></is></c><c r="H106" s="2" t="inlineStr"><is><t>meropenemu</t></is></c><c r="I106" s="2" t="inlineStr"><is><t>flukonazol</t></is></c><c r="J106" s="2" t="inlineStr" /><c r="K106" s="2" t="inlineStr" /><c r="L106" s="2" t="inlineStr" /><c r="M106" s="2" t="inlineStr" /><c r="N106" s="2" t="inlineStr" /><c r="O106" s="2" t="inlineStr" /><c r="P106" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q106" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="107"><c r="A107" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B107" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C107" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D107" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E107" s="2" t="inlineStr"><is><t>Wyłącznie na drobnoustroje Gram ujemne działa:</t></is></c><c r="F107" s="2" t="inlineStr"><is><t>aztreonam</t></is></c><c r="G107" s="2" t="inlineStr" /><c r="H107" s="2" t="inlineStr" /><c r="I107" s="2" t="inlineStr" /><c r="J107" s="2" t="inlineStr" /><c r="K107" s="2" t="inlineStr"><is><t>mupirocyna</t></is></c><c r="L107" s="2" t="inlineStr"><is><t>kwas fusydowy</t></is></c><c r="M107" s="2" t="inlineStr"><is><t>metronidazol</t></is></c><c r="N107" s="2" t="inlineStr" /><c r="O107" s="2" t="inlineStr" /><c r="P107" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q107" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="108"><c r="A108" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B108" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C108" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D108" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E108" s="2" t="inlineStr"><is><t>W leczeniu toksoplazmozy wykorzystuje się:</t></is></c><c r="F108" s="2" t="inlineStr"><is><t>pirymetaminę z sulfadiazyną</t></is></c><c r="G108" s="2" t="inlineStr"><is><t>spiramycynę</t></is></c><c r="H108" s="2" t="inlineStr" /><c r="I108" s="2" t="inlineStr" /><c r="J108" s="2" t="inlineStr" /><c r="K108" s="2" t="inlineStr"><is><t>dalfoprystynę/chinuprystynę</t></is></c><c r="L108" s="2" t="inlineStr"><is><t>oksytetracyklinę</t></is></c><c r="M108" s="2" t="inlineStr" /><c r="N108" s="2" t="inlineStr" /><c r="O108" s="2" t="inlineStr" /><c r="P108" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q108" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="109"><c r="A109" s="2" t="inlineStr"><is><t>CUKRZYCA</t></is></c><c r="B109" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C109" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D109" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E109" s="2" t="inlineStr"><is><t>Do odległych działań niepożądanych terapii HAART (Highly Active Antiretroviral Therapy) należy:</t></is></c><c r="F109" s="2" t="inlineStr"><is><t>uszkodzenie wątroby</t></is></c><c r="G109" s="2" t="inlineStr"><is><t>lipodystrofia</t></is></c><c r="H109" s="2" t="inlineStr"><is><t>kwasica mleczanowa</t></is></c><c r="I109" s="2" t="inlineStr"><is><t>insulinooporność</t></is></c><c r="J109" s="2" t="inlineStr" /><c r="K109" s="2" t="inlineStr" /><c r="L109" s="2" t="inlineStr" /><c r="M109" s="2" t="inlineStr" /><c r="N109" s="2" t="inlineStr" /><c r="O109" s="2" t="inlineStr" /><c r="P109" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q109" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="110"><c r="A110" s="2" t="inlineStr"><is><t>LEKI PRZECIWGRZYBICZE</t></is></c><c r="B110" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C110" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D110" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E110" s="2" t="inlineStr"><is><t>W grzybiczym zakażeniu paznokci można zastosować</t></is></c><c r="F110" s="2" t="inlineStr"><is><t>amorolfinę</t></is></c><c r="G110" s="2" t="inlineStr" /><c r="H110" s="2" t="inlineStr" /><c r="I110" s="2" t="inlineStr" /><c r="J110" s="2" t="inlineStr" /><c r="K110" s="2" t="inlineStr"><is><t>natamycynę</t></is></c><c r="L110" s="2" t="inlineStr"><is><t>klotrymazol</t></is></c><c r="M110" s="2" t="inlineStr"><is><t>kaspofunginę</t></is></c><c r="N110" s="2" t="inlineStr" /><c r="O110" s="2" t="inlineStr" /><c r="P110" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q110" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="111"><c r="A111" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B111" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C111" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D111" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E111" s="2" t="inlineStr"><is><t>Efekt bakteriobójczy zależny od skumulowanej ekspozycji (AUC24/MIC) wykazuje:</t></is></c><c r="F111" s="2" t="inlineStr"><is><t>lewofloksacyna</t></is></c><c r="G111" s="2" t="inlineStr"><is><t>azytromycyna</t></is></c><c r="H111" s="2" t="inlineStr" /><c r="I111" s="2" t="inlineStr" /><c r="J111" s="2" t="inlineStr" /><c r="K111" s="2" t="inlineStr"><is><t>amoksycylina z kwasem klawulanowym</t></is></c><c r="L111" s="2" t="inlineStr"><is><t>amikacyna</t></is></c><c r="M111" s="2" t="inlineStr" /><c r="N111" s="2" t="inlineStr" /><c r="O111" s="2" t="inlineStr" /><c r="P111" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q111" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="112"><c r="A112" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B112" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C112" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D112" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E112" s="2" t="inlineStr"><is><t>Do odkażania rany w obrębie skóry można zastosować:</t></is></c><c r="F112" s="2" t="inlineStr"><is><t>oktenidynę</t></is></c><c r="G112" s="2" t="inlineStr"><is><t>jodopowidon</t></is></c><c r="H112" s="2" t="inlineStr" /><c r="I112" s="2" t="inlineStr" /><c r="J112" s="2" t="inlineStr" /><c r="K112" s="2" t="inlineStr"><is><t>wodę do wstrzyknięć</t></is></c><c r="L112" s="2" t="inlineStr"><is><t>kwas borowy</t></is></c><c r="M112" s="2" t="inlineStr" /><c r="N112" s="2" t="inlineStr" /><c r="O112" s="2" t="inlineStr" /><c r="P112" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q112" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="113"><c r="A113" s="2" t="inlineStr"><is><t>FARMAKOLOGIA OGÓLNA I EBM</t></is></c><c r="B113" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C113" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D113" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E113" s="2" t="inlineStr"><is><t>Koszt dodatkowego roku życia skorygowanego o jakość (ang. QALY – quality adjusted life year):</t></is></c><c r="F113" s="2" t="inlineStr"><is><t>stanowi formalne kryterium refundacyjne zgodnie z obowiązującymi regulacjami prawnymi</t></is></c><c r="G113" s="2" t="inlineStr"><is><t>jest wynikiem analizy kosztów użyteczności</t></is></c><c r="H113" s="2" t="inlineStr"><is><t>jego wartość progowa, czyli maksymalna dla procedur uznanych za kosztowo efektywne, stanowi 3-krotność produktu krajowego brutto per capita zgodnie z obowiązującymi regulacjami prawnymi</t></is></c><c r="I113" s="2" t="inlineStr" /><c r="J113" s="2" t="inlineStr" /><c r="K113" s="2" t="inlineStr"><is><t>możliwy jest do oszacowania tylko w przypadku procedur zmniejszających umieralność całkowitą</t></is></c><c r="L113" s="2" t="inlineStr" /><c r="M113" s="2" t="inlineStr" /><c r="N113" s="2" t="inlineStr" /><c r="O113" s="2" t="inlineStr" /><c r="P113" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q113" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="114"><c r="A114" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B114" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C114" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D114" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E114" s="2" t="inlineStr"><is><t>U pacjenta z niewydolnością nerek należy dokonać modyfikacji dawek:</t></is></c><c r="F114" s="2" t="inlineStr"><is><t>wankomycyny</t></is></c><c r="G114" s="2" t="inlineStr"><is><t>cyprofloksacyny</t></is></c><c r="H114" s="2" t="inlineStr"><is><t>gentamycyny</t></is></c><c r="I114" s="2" t="inlineStr" /><c r="J114" s="2" t="inlineStr" /><c r="K114" s="2" t="inlineStr"><is><t>erytromycyny</t></is></c><c r="L114" s="2" t="inlineStr" /><c r="M114" s="2" t="inlineStr" /><c r="N114" s="2" t="inlineStr" /><c r="O114" s="2" t="inlineStr" /><c r="P114" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q114" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="115"><c r="A115" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B115" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C115" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D115" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E115" s="2" t="inlineStr"><is><t>Rotacja opioidów jest uzasadniona w przypadku:</t></is></c><c r="F115" s="2" t="inlineStr"><is><t>nudności</t></is></c><c r="G115" s="2" t="inlineStr"><is><t>zaburzeń świadomości</t></is></c><c r="H115" s="2" t="inlineStr"><is><t>długotrwałej (bezterminowej) terapii w celu ułatwienia jej prowadzenia</t></is></c><c r="I115" s="2" t="inlineStr" /><c r="J115" s="2" t="inlineStr" /><c r="K115" s="2" t="inlineStr"><is><t>zaparć</t></is></c><c r="L115" s="2" t="inlineStr" /><c r="M115" s="2" t="inlineStr" /><c r="N115" s="2" t="inlineStr" /><c r="O115" s="2" t="inlineStr" /><c r="P115" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q115" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="116"><c r="A116" s="2" t="inlineStr"><is><t>CUKRZYCA</t></is></c><c r="B116" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C116" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D116" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E116" s="2" t="inlineStr"><is><t>Dapagliflozyna:</t></is></c><c r="F116" s="2" t="inlineStr"><is><t>zwiększa ryzyko zakażeń układu moczowo-płciowego</t></is></c><c r="G116" s="2" t="inlineStr"><is><t>może spowodować kwasicę ketonową</t></is></c><c r="H116" s="2" t="inlineStr" /><c r="I116" s="2" t="inlineStr" /><c r="J116" s="2" t="inlineStr" /><c r="K116" s="2" t="inlineStr"><is><t>zmniejsza glukozurię</t></is></c><c r="L116" s="2" t="inlineStr"><is><t>nie może być stosowana łącznie z insuliną</t></is></c><c r="M116" s="2" t="inlineStr" /><c r="N116" s="2" t="inlineStr" /><c r="O116" s="2" t="inlineStr" /><c r="P116" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q116" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="117"><c r="A117" s="2" t="inlineStr"><is><t>CUKRZYCA</t></is></c><c r="B117" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C117" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D117" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E117" s="2" t="inlineStr"><is><t>Wskaż zdanie prawdziwe:</t></is></c><c r="F117" s="2" t="inlineStr"><is><t>zwiększenie stężenia glukozy w godzinach porannych poprzedzone hipoglikemią nocną może być wskazaniem do zmniejszenia dawki insuliny bazowej</t></is></c><c r="G117" s="2" t="inlineStr"><is><t>efekt brzasku może zmniejszyć zastosowanie długodziałających bezszczytowych analogów insuliny</t></is></c><c r="H117" s="2" t="inlineStr"><is><t>kardioprotekcyjne działanie empagliflozyny może mieć związek z usprawnieniem procesów energetycznych w komórkach mięśnia sercowego</t></is></c><c r="I117" s="2" t="inlineStr" /><c r="J117" s="2" t="inlineStr" /><c r="K117" s="2" t="inlineStr"><is><t>insulina izofanowa (NPH) jest przeznaczona do stosowana przed głównymi posiłkami</t></is></c><c r="L117" s="2" t="inlineStr" /><c r="M117" s="2" t="inlineStr" /><c r="N117" s="2" t="inlineStr" /><c r="O117" s="2" t="inlineStr" /><c r="P117" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q117" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="118"><c r="A118" s="2" t="inlineStr"><is><t>TARCZYCA</t></is></c><c r="B118" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C118" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D118" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E118" s="2" t="inlineStr"><is><t>W leczeniu nadczynności tarczycy można zastosować:</t></is></c><c r="F118" s="2" t="inlineStr"><is><t>jod promieniotwórczy 131 I</t></is></c><c r="G118" s="2" t="inlineStr"><is><t>płyn Lugola</t></is></c><c r="H118" s="2" t="inlineStr"><is><t>tiamazol</t></is></c><c r="I118" s="2" t="inlineStr"><is><t>propranolol</t></is></c><c r="J118" s="2" t="inlineStr" /><c r="K118" s="2" t="inlineStr" /><c r="L118" s="2" t="inlineStr" /><c r="M118" s="2" t="inlineStr" /><c r="N118" s="2" t="inlineStr" /><c r="O118" s="2" t="inlineStr" /><c r="P118" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q118" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="119"><c r="A119" s="2" t="inlineStr"><is><t>HORMONY PŁCIOWE</t></is></c><c r="B119" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C119" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D119" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E119" s="2" t="inlineStr"><is><t>Do progestagenów należy:</t></is></c><c r="F119" s="2" t="inlineStr"><is><t>megestrol</t></is></c><c r="G119" s="2" t="inlineStr"><is><t>noretysteron</t></is></c><c r="H119" s="2" t="inlineStr" /><c r="I119" s="2" t="inlineStr" /><c r="J119" s="2" t="inlineStr" /><c r="K119" s="2" t="inlineStr"><is><t>dutasteryd</t></is></c><c r="L119" s="2" t="inlineStr"><is><t>anastrozol</t></is></c><c r="M119" s="2" t="inlineStr" /><c r="N119" s="2" t="inlineStr" /><c r="O119" s="2" t="inlineStr" /><c r="P119" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q119" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="120"><c r="A120" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B120" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C120" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D120" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E120" s="2" t="inlineStr"><is><t>Do leków antyagregacyjnych stosowanych w profilaktyce wtórnej udaru niedokrwiennego mózgu na podłożu miażdżycy naczyń do- i mózgowych należą:</t></is></c><c r="F120" s="2" t="inlineStr"><is><t>klopidogrel</t></is></c><c r="G120" s="2" t="inlineStr"><is><t>kwas acetylosalicylowy</t></is></c><c r="H120" s="2" t="inlineStr" /><c r="I120" s="2" t="inlineStr" /><c r="J120" s="2" t="inlineStr" /><c r="K120" s="2" t="inlineStr"><is><t>tikagrelor</t></is></c><c r="L120" s="2" t="inlineStr"><is><t>prasugrel</t></is></c><c r="M120" s="2" t="inlineStr" /><c r="N120" s="2" t="inlineStr" /><c r="O120" s="2" t="inlineStr" /><c r="P120" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q120" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="121"><c r="A121" s="2" t="inlineStr"><is><t>LEKI MOCZOPĘDNE</t></is></c><c r="B121" s="2" t="inlineStr"><is><t>Sposób podania</t></is></c><c r="C121" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D121" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E121" s="2" t="inlineStr"><is><t>W ciężkiej hiperkalcemii (&gt;15mg/dl) można zastosować dożylnie:</t></is></c><c r="F121" s="2" t="inlineStr"><is><t>kalcytoninę</t></is></c><c r="G121" s="2" t="inlineStr"><is><t>pamidronian</t></is></c><c r="H121" s="2" t="inlineStr"><is><t>hydrokortyzon</t></is></c><c r="I121" s="2" t="inlineStr"><is><t>furosemid</t></is></c><c r="J121" s="2" t="inlineStr" /><c r="K121" s="2" t="inlineStr" /><c r="L121" s="2" t="inlineStr" /><c r="M121" s="2" t="inlineStr" /><c r="N121" s="2" t="inlineStr" /><c r="O121" s="2" t="inlineStr" /><c r="P121" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q121" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="122"><c r="A122" s="2" t="inlineStr"><is><t>GLIKOKORTYKOSTEROIDY</t></is></c><c r="B122" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C122" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D122" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E122" s="2" t="inlineStr"><is><t>Immunosupresyjne działanie glikokortykosteroidów jest spowodowane:</t></is></c><c r="F122" s="2" t="inlineStr"><is><t>redukcją liczby limfocytów T</t></is></c><c r="G122" s="2" t="inlineStr"><is><t>zahamowaniem funkcji makrofagów tkankowych</t></is></c><c r="H122" s="2" t="inlineStr" /><c r="I122" s="2" t="inlineStr" /><c r="J122" s="2" t="inlineStr" /><c r="K122" s="2" t="inlineStr"><is><t>zwiększeniem syntezy IL-2</t></is></c><c r="L122" s="2" t="inlineStr"><is><t>aktywacją fosfolipazy A2 i zmniejszeniem syntezy prostaglandyn</t></is></c><c r="M122" s="2" t="inlineStr" /><c r="N122" s="2" t="inlineStr" /><c r="O122" s="2" t="inlineStr" /><c r="P122" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q122" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="123"><c r="A123" s="2" t="inlineStr"><is><t>OSTEOPOROZA</t></is></c><c r="B123" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C123" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D123" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E123" s="2" t="inlineStr"><is><t>91-letni mężczyzna jest leczony od co najmniej 6 miesięcy tamsulozyną, finasterydem, diosminą, piracetamem, zolpidemem, witaminą D3 w dużej dawce i węglanem wapnia. Na tej podstawie można powiedzieć, że:</t></is></c><c r="F123" s="2" t="inlineStr"><is><t>choruje na rozrost gruczołu krokowego</t></is></c><c r="G123" s="2" t="inlineStr"><is><t>jest uzależniony od zolpidemu</t></is></c><c r="H123" s="2" t="inlineStr"><is><t>można bez konsekwencji odstawić piracetam</t></is></c><c r="I123" s="2" t="inlineStr"><is><t>terapia zmniejsza ryzyko osteoporotycznych złamań kości</t></is></c><c r="J123" s="2" t="inlineStr" /><c r="K123" s="2" t="inlineStr" /><c r="L123" s="2" t="inlineStr" /><c r="M123" s="2" t="inlineStr" /><c r="N123" s="2" t="inlineStr" /><c r="O123" s="2" t="inlineStr" /><c r="P123" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q123" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="124"><c r="A124" s="2" t="inlineStr"><is><t>STANY NAGŁE</t></is></c><c r="B124" s="2" t="inlineStr"><is><t>Antidotum</t></is></c><c r="C124" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D124" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E124" s="2" t="inlineStr"><is><t>Witamina K1 (fitomenadion):</t></is></c><c r="F124" s="2" t="inlineStr"><is><t>może być wskazana u osób ze spontanicznym zwiększeniem INR&gt;GGN (górnej granicy normy) spowodowanym antybiotykami niszczącymi fizjologiczną florę jelit</t></is></c><c r="G124" s="2" t="inlineStr"><is><t>nie antagonizuje działania heparyny</t></is></c><c r="H124" s="2" t="inlineStr"><is><t>może spowodować reakcję rzekomoanafilaktyczną</t></is></c><c r="I124" s="2" t="inlineStr"><is><t>jest antidotum w przedawkowaniu pochodnych hydroksykumaryny</t></is></c><c r="J124" s="2" t="inlineStr" /><c r="K124" s="2" t="inlineStr" /><c r="L124" s="2" t="inlineStr" /><c r="M124" s="2" t="inlineStr" /><c r="N124" s="2" t="inlineStr" /><c r="O124" s="2" t="inlineStr" /><c r="P124" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q124" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="125"><c r="A125" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B125" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C125" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D125" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E125" s="2" t="inlineStr"><is><t>Działanie zapierające wykazuje:</t></is></c><c r="F125" s="2" t="inlineStr"><is><t>oksykodon</t></is></c><c r="G125" s="2" t="inlineStr"><is><t>werapamil</t></is></c><c r="H125" s="2" t="inlineStr"><is><t>oktreotyd</t></is></c><c r="I125" s="2" t="inlineStr" /><c r="J125" s="2" t="inlineStr" /><c r="K125" s="2" t="inlineStr"><is><t>fosforan sodu</t></is></c><c r="L125" s="2" t="inlineStr" /><c r="M125" s="2" t="inlineStr" /><c r="N125" s="2" t="inlineStr" /><c r="O125" s="2" t="inlineStr" /><c r="P125" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q125" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="126"><c r="A126" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B126" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C126" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D126" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E126" s="2" t="inlineStr"><is><t>W leczeniu ostrej biegunki u dzieci uzasadnione jest zastosowanie:</t></is></c><c r="F126" s="2" t="inlineStr"><is><t>probiotyku S. boulardi</t></is></c><c r="G126" s="2" t="inlineStr"><is><t>racekadotrylu</t></is></c><c r="H126" s="2" t="inlineStr"><is><t>doustnego płynu nawadniającego</t></is></c><c r="I126" s="2" t="inlineStr" /><c r="J126" s="2" t="inlineStr" /><c r="K126" s="2" t="inlineStr"><is><t>loperamidu</t></is></c><c r="L126" s="2" t="inlineStr" /><c r="M126" s="2" t="inlineStr" /><c r="N126" s="2" t="inlineStr" /><c r="O126" s="2" t="inlineStr" /><c r="P126" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q126" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="127"><c r="A127" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B127" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C127" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D127" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E127" s="2" t="inlineStr"><is><t>Wybierz prawidłowe połączenie lek - mechanizm działania:</t></is></c><c r="F127" s="2" t="inlineStr"><is><t>itopryd - antagonista receptora D2</t></is></c><c r="G127" s="2" t="inlineStr"><is><t>alwimopan - antagonista receptora μ</t></is></c><c r="H127" s="2" t="inlineStr" /><c r="I127" s="2" t="inlineStr" /><c r="J127" s="2" t="inlineStr" /><c r="K127" s="2" t="inlineStr"><is><t>alweryna - agonista receptora motylinowego</t></is></c><c r="L127" s="2" t="inlineStr"><is><t>simetykon - agonista receptora 5-HT4</t></is></c><c r="M127" s="2" t="inlineStr" /><c r="N127" s="2" t="inlineStr" /><c r="O127" s="2" t="inlineStr" /><c r="P127" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q127" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="128"><c r="A128" s="2" t="inlineStr"><is><t>UKŁAD PRZYWSPÓŁCZULNY</t></is></c><c r="B128" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C128" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D128" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E128" s="2" t="inlineStr"><is><t>W kolce wątrobowej uzasadnione jest podanie:</t></is></c><c r="F128" s="2" t="inlineStr"><is><t>ketoprofenu i.v</t></is></c><c r="G128" s="2" t="inlineStr"><is><t>papaweryny i.m</t></is></c><c r="H128" s="2" t="inlineStr"><is><t>butylobromku skopolaminy p.r</t></is></c><c r="I128" s="2" t="inlineStr"><is><t>buprenorfiny i.m</t></is></c><c r="J128" s="2" t="inlineStr" /><c r="K128" s="2" t="inlineStr" /><c r="L128" s="2" t="inlineStr" /><c r="M128" s="2" t="inlineStr" /><c r="N128" s="2" t="inlineStr" /><c r="O128" s="2" t="inlineStr" /><c r="P128" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q128" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="129"><c r="A129" s="2" t="inlineStr"><is><t>BÓLE GŁOWY</t></is></c><c r="B129" s="2" t="inlineStr"><is><t>Ciąża</t></is></c><c r="C129" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D129" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E129" s="2" t="inlineStr"><is><t>Sumatryptan:</t></is></c><c r="F129" s="2" t="inlineStr"><is><t>pobudzając receptory 5-HT1D wywołuje wybiórczy skurcz naczyń i przerywa napad migreny</t></is></c><c r="G129" s="2" t="inlineStr"><is><t>jest niezalecany u pacjentów z chorobą niedokrwienną serca</t></is></c><c r="H129" s="2" t="inlineStr" /><c r="I129" s="2" t="inlineStr" /><c r="J129" s="2" t="inlineStr" /><c r="K129" s="2" t="inlineStr"><is><t>może być stosowany jedynie podskórnie</t></is></c><c r="L129" s="2" t="inlineStr"><is><t>może być podawany w czasie ciąży</t></is></c><c r="M129" s="2" t="inlineStr" /><c r="N129" s="2" t="inlineStr" /><c r="O129" s="2" t="inlineStr" /><c r="P129" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q129" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="130"><c r="A130" s="2" t="inlineStr"><is><t>UKŁAD WSPÓŁCZULNY</t></is></c><c r="B130" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C130" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D130" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E130" s="2" t="inlineStr"><is><t>W profilaktyce bólów migrenowych znalazł zastosowanie:</t></is></c><c r="F130" s="2" t="inlineStr"><is><t>topiramat</t></is></c><c r="G130" s="2" t="inlineStr"><is><t>erenumab</t></is></c><c r="H130" s="2" t="inlineStr"><is><t>propranolol</t></is></c><c r="I130" s="2" t="inlineStr"><is><t>toksyna botulinowa</t></is></c><c r="J130" s="2" t="inlineStr" /><c r="K130" s="2" t="inlineStr" /><c r="L130" s="2" t="inlineStr" /><c r="M130" s="2" t="inlineStr" /><c r="N130" s="2" t="inlineStr" /><c r="O130" s="2" t="inlineStr" /><c r="P130" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q130" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="131"><c r="A131" s="2" t="inlineStr"><is><t>NADCIŚNIENIE TĘTNICZE</t></is></c><c r="B131" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C131" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D131" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E131" s="2" t="inlineStr"><is><t>Erytropoetyna może zwiększyć:</t></is></c><c r="F131" s="2" t="inlineStr"><is><t>wartości ciśnienia tętniczego</t></is></c><c r="G131" s="2" t="inlineStr"><is><t>krzepliwość krwi</t></is></c><c r="H131" s="2" t="inlineStr"><is><t>maksymalną wydolność wysiłkową</t></is></c><c r="I131" s="2" t="inlineStr" /><c r="J131" s="2" t="inlineStr" /><c r="K131" s="2" t="inlineStr"><is><t>aktywność amylazy w surowicy</t></is></c><c r="L131" s="2" t="inlineStr" /><c r="M131" s="2" t="inlineStr" /><c r="N131" s="2" t="inlineStr" /><c r="O131" s="2" t="inlineStr" /><c r="P131" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q131" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="132"><c r="A132" s="2" t="inlineStr"><is><t>UKŁAD PRZYWSPÓŁCZULNY</t></is></c><c r="B132" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C132" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D132" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E132" s="2" t="inlineStr"><is><t>W profilaktyce wymiotów w przebiegu kinetoz stosuje się:</t></is></c><c r="F132" s="2" t="inlineStr"><is><t>skopolaminę</t></is></c><c r="G132" s="2" t="inlineStr"><is><t>dimenhydrinat</t></is></c><c r="H132" s="2" t="inlineStr" /><c r="I132" s="2" t="inlineStr" /><c r="J132" s="2" t="inlineStr" /><c r="K132" s="2" t="inlineStr"><is><t>haloperydol</t></is></c><c r="L132" s="2" t="inlineStr"><is><t>betahistynę</t></is></c><c r="M132" s="2" t="inlineStr" /><c r="N132" s="2" t="inlineStr" /><c r="O132" s="2" t="inlineStr" /><c r="P132" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q132" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="133"><c r="A133" s="2" t="inlineStr"><is><t>UKŁAD WSPÓŁCZULNY</t></is></c><c r="B133" s="2" t="inlineStr"><is><t>Sposób podania</t></is></c><c r="C133" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D133" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E133" s="2" t="inlineStr"><is><t>Oksymetazolina:</t></is></c><c r="F133" s="2" t="inlineStr"><is><t>może doprowadzić do wystąpienia tzw. efektu „ z odbicia”</t></is></c><c r="G133" s="2" t="inlineStr" /><c r="H133" s="2" t="inlineStr" /><c r="I133" s="2" t="inlineStr" /><c r="J133" s="2" t="inlineStr" /><c r="K133" s="2" t="inlineStr"><is><t>jest antagonistą receptorów adrenergicznych alfa</t></is></c><c r="L133" s="2" t="inlineStr"><is><t>wykazuje skuteczność kliniczną po 5. dniach terapii</t></is></c><c r="M133" s="2" t="inlineStr"><is><t>jest podawana doustnie</t></is></c><c r="N133" s="2" t="inlineStr" /><c r="O133" s="2" t="inlineStr" /><c r="P133" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q133" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="134"><c r="A134" s="2" t="inlineStr"><is><t>UKŁAD PRZYWSPÓŁCZULNY</t></is></c><c r="B134" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C134" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D134" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E134" s="2" t="inlineStr"><is><t>Petydyna:</t></is></c><c r="F134" s="2" t="inlineStr"><is><t>ma działanie zapierające</t></is></c><c r="G134" s="2" t="inlineStr"><is><t>nietypowo dla swojej grupy farmakologicznej rozszerza źrenice</t></is></c><c r="H134" s="2" t="inlineStr"><is><t>hamuje ośrodek oddechowy</t></is></c><c r="I134" s="2" t="inlineStr"><is><t>stosowana długotrwale działa neurotoksycznie przez kumulujący się metabolit</t></is></c><c r="J134" s="2" t="inlineStr" /><c r="K134" s="2" t="inlineStr" /><c r="L134" s="2" t="inlineStr" /><c r="M134" s="2" t="inlineStr" /><c r="N134" s="2" t="inlineStr" /><c r="O134" s="2" t="inlineStr" /><c r="P134" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q134" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="135"><c r="A135" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B135" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C135" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D135" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E135" s="2" t="inlineStr"><is><t>Wskaż prawdziwe stwierdzenie dotyczące małopłytkowości typu II wywołanej heparyną:</t></is></c><c r="F135" s="2" t="inlineStr"><is><t>stwierdzenie małopłytkowości immunologicznej w przebiegu leczenia heparyną jest wskazaniem do jej natychmiastowego odstawienia</t></is></c><c r="G135" s="2" t="inlineStr"><is><t>HIT II wiąże się z 20–40-krotnym zwiększeniem ryzyka zakrzepicy żylnej</t></is></c><c r="H135" s="2" t="inlineStr" /><c r="I135" s="2" t="inlineStr" /><c r="J135" s="2" t="inlineStr" /><c r="K135" s="2" t="inlineStr"><is><t>HIT II występuje najczęściej po 3 tygodniach od rozpoczęcia terapii heparyną</t></is></c><c r="L135" s="2" t="inlineStr"><is><t>heparyny drobnocząsteczkowe nie stwarzają ryzyka wystąpienia trombocytopenii immunologicznej</t></is></c><c r="M135" s="2" t="inlineStr" /><c r="N135" s="2" t="inlineStr" /><c r="O135" s="2" t="inlineStr" /><c r="P135" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q135" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="136"><c r="A136" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B136" s="2" t="inlineStr"><is><t>Ciąża</t></is></c><c r="C136" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D136" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E136" s="2" t="inlineStr"><is><t>U kobiet w trzecim trymestrze ciąży przeciwwskazany/-a jest:</t></is></c><c r="F136" s="2" t="inlineStr"><is><t>ketoprofen</t></is></c><c r="G136" s="2" t="inlineStr"><is><t>walsartan</t></is></c><c r="H136" s="2" t="inlineStr"><is><t>acenokumarol</t></is></c><c r="I136" s="2" t="inlineStr" /><c r="J136" s="2" t="inlineStr" /><c r="K136" s="2" t="inlineStr"><is><t>enoksaparyna</t></is></c><c r="L136" s="2" t="inlineStr" /><c r="M136" s="2" t="inlineStr" /><c r="N136" s="2" t="inlineStr" /><c r="O136" s="2" t="inlineStr" /><c r="P136" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q136" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="137"><c r="A137" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B137" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C137" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D137" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E137" s="2" t="inlineStr"><is><t>U pacjenta leczonego przeciwzakrzepowo dabigatranem ze stwierdzonym umiarkowanym aktywnym krwawieniem należy:</t></is></c><c r="F137" s="2" t="inlineStr"><is><t>odroczyć podanie kolejnej dawki leku</t></is></c><c r="G137" s="2" t="inlineStr"><is><t>zapewnić podaż płynów</t></is></c><c r="H137" s="2" t="inlineStr"><is><t>rozważyć podanie węgla aktywowanego jeśli dabigatran był podany niedawno</t></is></c><c r="I137" s="2" t="inlineStr" /><c r="J137" s="2" t="inlineStr" /><c r="K137" s="2" t="inlineStr"><is><t>zastosować siarczan protaminy</t></is></c><c r="L137" s="2" t="inlineStr" /><c r="M137" s="2" t="inlineStr" /><c r="N137" s="2" t="inlineStr" /><c r="O137" s="2" t="inlineStr" /><c r="P137" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q137" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="138"><c r="A138" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B138" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C138" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D138" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E138" s="2" t="inlineStr"><is><t>Nadroparyna:</t></is></c><c r="F138" s="2" t="inlineStr"><is><t>może być podawana dożylnie</t></is></c><c r="G138" s="2" t="inlineStr"><is><t>jest skuteczna w leczeniu zakrzepicy żył głębokich</t></is></c><c r="H138" s="2" t="inlineStr" /><c r="I138" s="2" t="inlineStr" /><c r="J138" s="2" t="inlineStr" /><c r="K138" s="2" t="inlineStr"><is><t>jest antagonistą receptora PAR-1</t></is></c><c r="L138" s="2" t="inlineStr"><is><t>w profilaktyce zakrzepicy żylnej powinna być podana nie później niż 36 godzin przed zabiegiem chirurgicznym</t></is></c><c r="M138" s="2" t="inlineStr" /><c r="N138" s="2" t="inlineStr" /><c r="O138" s="2" t="inlineStr" /><c r="P138" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q138" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="139"><c r="A139" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B139" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C139" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D139" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E139" s="2" t="inlineStr"><is><t>Wskazaniem do podania tkankowego aktywatora plazminogenu (t-PA) może być:</t></is></c><c r="F139" s="2" t="inlineStr"><is><t>zatorowość płucna wysokiego ryzyka (czyli z niestabilnością hemodynamiczną)</t></is></c><c r="G139" s="2" t="inlineStr"><is><t>ostry zator tętnicy kończyny dolnej</t></is></c><c r="H139" s="2" t="inlineStr"><is><t>ostry udar niedokrwienny mózgu</t></is></c><c r="I139" s="2" t="inlineStr" /><c r="J139" s="2" t="inlineStr" /><c r="K139" s="2" t="inlineStr"><is><t>ostry zespół wieńcowy bez uniesienia odcinka ST</t></is></c><c r="L139" s="2" t="inlineStr" /><c r="M139" s="2" t="inlineStr" /><c r="N139" s="2" t="inlineStr" /><c r="O139" s="2" t="inlineStr" /><c r="P139" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q139" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="140"><c r="A140" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B140" s="2" t="inlineStr"><is><t>Sposób podania</t></is></c><c r="C140" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D140" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E140" s="2" t="inlineStr"><is><t>W udarze niedokrwiennym mózgu należy:</t></is></c><c r="F140" s="2" t="inlineStr"><is><t>obniżać ciśnienie tętnicze jeśli przekracza wartości 220/120 mmHg</t></is></c><c r="G140" s="2" t="inlineStr"><is><t>podać doustnie kwas acetylosalicylowy jeżeli nie można zastosować leczenia trombolitycznego</t></is></c><c r="H140" s="2" t="inlineStr" /><c r="I140" s="2" t="inlineStr" /><c r="J140" s="2" t="inlineStr" /><c r="K140" s="2" t="inlineStr"><is><t>stosować duże dawki heparyny niefrakcjonowanej</t></is></c><c r="L140" s="2" t="inlineStr"><is><t>profilaktycznie podawać antybiotyki β-laktamowe ze względu na bardzo częste występowanie infekcji dróg oddechowych</t></is></c><c r="M140" s="2" t="inlineStr" /><c r="N140" s="2" t="inlineStr" /><c r="O140" s="2" t="inlineStr" /><c r="P140" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q140" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="141"><c r="A141" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B141" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C141" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D141" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E141" s="2" t="inlineStr"><is><t>Inhibitory reduktazy HMG-CoA zwiększają produkcję:</t></is></c><c r="F141" s="2" t="inlineStr"><is><t>tkankowego aktywatora plazminogenu</t></is></c><c r="G141" s="2" t="inlineStr"><is><t>tlenku azotu</t></is></c><c r="H141" s="2" t="inlineStr" /><c r="I141" s="2" t="inlineStr" /><c r="J141" s="2" t="inlineStr" /><c r="K141" s="2" t="inlineStr"><is><t>metaloproteinaz</t></is></c><c r="L141" s="2" t="inlineStr"><is><t>tromboksanu A2</t></is></c><c r="M141" s="2" t="inlineStr" /><c r="N141" s="2" t="inlineStr" /><c r="O141" s="2" t="inlineStr" /><c r="P141" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q141" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="142"><c r="A142" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B142" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C142" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D142" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E142" s="2" t="inlineStr"><is><t>20% roztwór albumin:</t></is></c><c r="F142" s="2" t="inlineStr"><is><t>powoduje ponad 100% przyrost objętości osocza</t></is></c><c r="G142" s="2" t="inlineStr"><is><t>działa objętościowo do 6 h</t></is></c><c r="H142" s="2" t="inlineStr" /><c r="I142" s="2" t="inlineStr" /><c r="J142" s="2" t="inlineStr" /><c r="K142" s="2" t="inlineStr"><is><t>może spowodować uszkodzenie nerek</t></is></c><c r="L142" s="2" t="inlineStr"><is><t>ma istotny wpływ na krzepnięcie krwi</t></is></c><c r="M142" s="2" t="inlineStr" /><c r="N142" s="2" t="inlineStr" /><c r="O142" s="2" t="inlineStr" /><c r="P142" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q142" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="143"><c r="A143" s="2" t="inlineStr"><is><t>UKŁAD PRZYWSPÓŁCZULNY</t></is></c><c r="B143" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C143" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D143" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E143" s="2" t="inlineStr"><is><t>Zastosowanie atrakurium może być przyczyną:</t></is></c><c r="F143" s="2" t="inlineStr"><is><t>długotrwałego efektu zwiotczającego</t></is></c><c r="G143" s="2" t="inlineStr" /><c r="H143" s="2" t="inlineStr" /><c r="I143" s="2" t="inlineStr" /><c r="J143" s="2" t="inlineStr" /><c r="K143" s="2" t="inlineStr"><is><t>drżenia włókienkowego mięśni szkieletowych</t></is></c><c r="L143" s="2" t="inlineStr"><is><t>anestezji</t></is></c><c r="M143" s="2" t="inlineStr"><is><t>hipertermii złośliwej</t></is></c><c r="N143" s="2" t="inlineStr" /><c r="O143" s="2" t="inlineStr" /><c r="P143" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q143" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="144"><c r="A144" s="2" t="inlineStr"><is><t>LEKI MOCZOPĘDNE</t></is></c><c r="B144" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C144" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D144" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E144" s="2" t="inlineStr"><is><t>Torasemid:</t></is></c><c r="F144" s="2" t="inlineStr"><is><t>hamuje symporter sodowo-potasowo-chlorkowy części grubościennej ramienia wstępującego pętli Henlego</t></is></c><c r="G144" s="2" t="inlineStr"><is><t>zwiększa aktywność reninową osocza</t></is></c><c r="H144" s="2" t="inlineStr" /><c r="I144" s="2" t="inlineStr" /><c r="J144" s="2" t="inlineStr" /><c r="K144" s="2" t="inlineStr"><is><t>zmniejsza wydalanie wapnia z moczem</t></is></c><c r="L144" s="2" t="inlineStr"><is><t>jest nieskuteczny, jeśli eGFRr &lt; 30 ml/min</t></is></c><c r="M144" s="2" t="inlineStr" /><c r="N144" s="2" t="inlineStr" /><c r="O144" s="2" t="inlineStr" /><c r="P144" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q144" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="145"><c r="A145" s="2" t="inlineStr"><is><t>FARMAKOLOGIA OGÓLNA I EBM</t></is></c><c r="B145" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C145" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D145" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E145" s="2" t="inlineStr"><is><t>Formularz świadomej zgody uczestnika na udział w badaniu klinicznym powinien zostać podpisany:</t></is></c><c r="F145" s="2" t="inlineStr"><is><t>przez uczestnika badania</t></is></c><c r="G145" s="2" t="inlineStr"><is><t>przez badacza</t></is></c><c r="H145" s="2" t="inlineStr"><is><t>w dwóch egzemplarzach</t></is></c><c r="I145" s="2" t="inlineStr" /><c r="J145" s="2" t="inlineStr" /><c r="K145" s="2" t="inlineStr"><is><t>bezpośrednio po badaniach oceniających czy pacjent spełnia kryteria włączenia do badania</t></is></c><c r="L145" s="2" t="inlineStr" /><c r="M145" s="2" t="inlineStr" /><c r="N145" s="2" t="inlineStr" /><c r="O145" s="2" t="inlineStr" /><c r="P145" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q145" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="146"><c r="A146" s="2" t="inlineStr"><is><t>LEKI PRZECIWPASOŻYTNICZE</t></is></c><c r="B146" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C146" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D146" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E146" s="2" t="inlineStr"><is><t>W leczeniu zarażenia owsikiem skuteczny jest:</t></is></c><c r="F146" s="2" t="inlineStr"><is><t>mebendazol</t></is></c><c r="G146" s="2" t="inlineStr"><is><t>albendazol</t></is></c><c r="H146" s="2" t="inlineStr"><is><t>pyrantel</t></is></c><c r="I146" s="2" t="inlineStr" /><c r="J146" s="2" t="inlineStr" /><c r="K146" s="2" t="inlineStr"><is><t>tynidazol</t></is></c><c r="L146" s="2" t="inlineStr" /><c r="M146" s="2" t="inlineStr" /><c r="N146" s="2" t="inlineStr" /><c r="O146" s="2" t="inlineStr" /><c r="P146" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q146" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="147"><c r="A147" s="2" t="inlineStr"><is><t>LEKI PRZECIWWIRUSOWE</t></is></c><c r="B147" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C147" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D147" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E147" s="2" t="inlineStr"><is><t>Cytomegalię u osób z niedoborami odporności należy leczyć stosując:</t></is></c><c r="F147" s="2" t="inlineStr"><is><t>gancyklowir</t></is></c><c r="G147" s="2" t="inlineStr" /><c r="H147" s="2" t="inlineStr" /><c r="I147" s="2" t="inlineStr" /><c r="J147" s="2" t="inlineStr" /><c r="K147" s="2" t="inlineStr"><is><t>zanamiwir</t></is></c><c r="L147" s="2" t="inlineStr"><is><t>acyklowir</t></is></c><c r="M147" s="2" t="inlineStr"><is><t>oseltamiwir</t></is></c><c r="N147" s="2" t="inlineStr" /><c r="O147" s="2" t="inlineStr" /><c r="P147" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q147" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="148"><c r="A148" s="2" t="inlineStr"><is><t>UKŁAD ODDECHOWY</t></is></c><c r="B148" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C148" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D148" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E148" s="2" t="inlineStr"><is><t>W terapii POChP u osób o wysokim ryzyku zaostrzeń i dużym nasileniu objawów (grupa</t></is></c><c r="F148" s="2" t="inlineStr"><is><t>bromek tiotropium z formoterolem i cyklezonidem</t></is></c><c r="G148" s="2" t="inlineStr"><is><t>budezonid z formoterolem</t></is></c><c r="H148" s="2" t="inlineStr"><is><t>bromek aklidynium z salmeterolem i flutikazonem</t></is></c><c r="I148" s="2" t="inlineStr"><is><t>bromek glikopironium z roflumilastem</t></is></c><c r="J148" s="2" t="inlineStr" /><c r="K148" s="2" t="inlineStr"><is><t>można zastosować:</t></is></c><c r="L148" s="2" t="inlineStr" /><c r="M148" s="2" t="inlineStr" /><c r="N148" s="2" t="inlineStr" /><c r="O148" s="2" t="inlineStr" /><c r="P148" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q148" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="149"><c r="A149" s="2" t="inlineStr"><is><t>UKŁAD ODDECHOWY</t></is></c><c r="B149" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C149" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D149" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E149" s="2" t="inlineStr"><is><t>Wskaż prawidłowe twierdzenie dotyczące farmakoterapii astmy oskrzelowej :</t></is></c><c r="F149" s="2" t="inlineStr"><is><t>wziewne glikokortykosteroidy zmniejszają częstość/liczbę hospitalizacji i umieralność z powodu astmy</t></is></c><c r="G149" s="2" t="inlineStr"><is><t>długodziałające wziewne betaadrenomimetyki w monoterapii mogą zwiększać ryzyko zgonu z powodu astmy</t></is></c><c r="H149" s="2" t="inlineStr"><is><t>kromony mogą być skuteczne u chorych ze skurczem oskrzeli wywoływanym przez wysiłek fizyczny</t></is></c><c r="I149" s="2" t="inlineStr" /><c r="J149" s="2" t="inlineStr" /><c r="K149" s="2" t="inlineStr"><is><t>leki przeciwleukotrienowe w monoterapii są bardziej skuteczne od wziewnych glikokortykosteroidów w małych dawkach</t></is></c><c r="L149" s="2" t="inlineStr" /><c r="M149" s="2" t="inlineStr" /><c r="N149" s="2" t="inlineStr" /><c r="O149" s="2" t="inlineStr" /><c r="P149" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q149" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="150"><c r="A150" s="2" t="inlineStr"><is><t>NADCIŚNIENIE TĘTNICZE</t></is></c><c r="B150" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C150" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D150" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E150" s="2" t="inlineStr"><is><t>W leczeniu wodobrzusza w przebiegu marskości wątroby wskazane jest stosowanie:</t></is></c><c r="F150" s="2" t="inlineStr"><is><t>furosemidu</t></is></c><c r="G150" s="2" t="inlineStr"><is><t>spironolaktonu</t></is></c><c r="H150" s="2" t="inlineStr"><is><t>karwedilolu</t></is></c><c r="I150" s="2" t="inlineStr" /><c r="J150" s="2" t="inlineStr" /><c r="K150" s="2" t="inlineStr"><is><t>ramiprylu</t></is></c><c r="L150" s="2" t="inlineStr" /><c r="M150" s="2" t="inlineStr" /><c r="N150" s="2" t="inlineStr" /><c r="O150" s="2" t="inlineStr" /><c r="P150" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q150" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="151"><c r="A151" s="2" t="inlineStr"><is><t>LEKI MOCZOPĘDNE</t></is></c><c r="B151" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C151" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D151" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E151" s="2" t="inlineStr"><is><t>W leczeniu dny moczanowej należy:</t></is></c><c r="F151" s="2" t="inlineStr"><is><t>stosować dietę z ograniczeniem podaży mięs, podrobów i fruktozy</t></is></c><c r="G151" s="2" t="inlineStr"><is><t>objawowo stosować leki z grupy NLPZ</t></is></c><c r="H151" s="2" t="inlineStr" /><c r="I151" s="2" t="inlineStr" /><c r="J151" s="2" t="inlineStr" /><c r="K151" s="2" t="inlineStr"><is><t>podać jak najszybciej allopurynol przy podejrzeniu ostrego napadu</t></is></c><c r="L151" s="2" t="inlineStr"><is><t>w każdym przypadku bezobjawowej hiperurykemii stosować kolchicynę</t></is></c><c r="M151" s="2" t="inlineStr" /><c r="N151" s="2" t="inlineStr" /><c r="O151" s="2" t="inlineStr" /><c r="P151" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q151" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="152"><c r="A152" s="2" t="inlineStr"><is><t>NIEOPIOIDOWE LEKI PRZECIWBÓLOWE</t></is></c><c r="B152" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C152" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D152" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E152" s="2" t="inlineStr"><is><t>Zotarolimus:</t></is></c><c r="F152" s="2" t="inlineStr"><is><t>jest stosowany w stentach wieńcowych uwalniających lek</t></is></c><c r="G152" s="2" t="inlineStr" /><c r="H152" s="2" t="inlineStr" /><c r="I152" s="2" t="inlineStr" /><c r="J152" s="2" t="inlineStr" /><c r="K152" s="2" t="inlineStr"><is><t>jest rekombinowanym w pełni ludzkim przeciwciałem monoklonalnym</t></is></c><c r="L152" s="2" t="inlineStr"><is><t>nie może być stosowany łącznie z kwasem acetylosalicylowym</t></is></c><c r="M152" s="2" t="inlineStr"><is><t>neutralizuje biologiczną aktywność TNF</t></is></c><c r="N152" s="2" t="inlineStr" /><c r="O152" s="2" t="inlineStr" /><c r="P152" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q152" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="153"><c r="A153" s="2" t="inlineStr"><is><t>OTĘPIENIE</t></is></c><c r="B153" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C153" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D153" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E153" s="2" t="inlineStr"><is><t>W leczeniu choroby Alzheimera:</t></is></c><c r="F153" s="2" t="inlineStr"><is><t>w zaawansowanych przypadkach wskazane jest włączenie do leczenia antagonisty receptorów NMDA</t></is></c><c r="G153" s="2" t="inlineStr"><is><t>donepezil korzystnie wpływa na globalne zdolności intelektualne w łagodnych stadiach choroby</t></is></c><c r="H153" s="2" t="inlineStr" /><c r="I153" s="2" t="inlineStr" /><c r="J153" s="2" t="inlineStr" /><c r="K153" s="2" t="inlineStr"><is><t>stosuje się leki cholinolityczne</t></is></c><c r="L153" s="2" t="inlineStr"><is><t>istotną rolę odgrywa zastosowanie piracetamu</t></is></c><c r="M153" s="2" t="inlineStr" /><c r="N153" s="2" t="inlineStr" /><c r="O153" s="2" t="inlineStr" /><c r="P153" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q153" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="154"><c r="A154" s="2" t="inlineStr"><is><t>PADACZKA</t></is></c><c r="B154" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C154" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D154" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E154" s="2" t="inlineStr"><is><t>Przewlekłe stosowanie lorazepamu może spowodować:</t></is></c><c r="F154" s="2" t="inlineStr"><is><t>otępienie</t></is></c><c r="G154" s="2" t="inlineStr"><is><t>tolerancję na jego działanie</t></is></c><c r="H154" s="2" t="inlineStr"><is><t>uzależnienie psychiczne i fizyczne</t></is></c><c r="I154" s="2" t="inlineStr" /><c r="J154" s="2" t="inlineStr" /><c r="K154" s="2" t="inlineStr"><is><t>stan padaczkowy</t></is></c><c r="L154" s="2" t="inlineStr" /><c r="M154" s="2" t="inlineStr" /><c r="N154" s="2" t="inlineStr" /><c r="O154" s="2" t="inlineStr" /><c r="P154" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q154" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="155"><c r="A155" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B155" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C155" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D155" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E155" s="2" t="inlineStr"><is><t>Wybierz prawidłowe połączenie lek - mechanizm działania:</t></is></c><c r="F155" s="2" t="inlineStr"><is><t>orlistat - blokowanie lipaz wytwarzanych w przewodzie pokarmowym</t></is></c><c r="G155" s="2" t="inlineStr"><is><t>tramadol – blokowanie zwrotnego wychwytu noradrenaliny i serotoniny w synapsach zstępującego układu analgetycznego</t></is></c><c r="H155" s="2" t="inlineStr"><is><t>ezetymib – hamowanie aktywności białka NPC1L1 w nabłonku błony śluzowej jelita</t></is></c><c r="I155" s="2" t="inlineStr"><is><t>celekoksyb -wybiórcze zablokowanie COX-2</t></is></c><c r="J155" s="2" t="inlineStr" /><c r="K155" s="2" t="inlineStr" /><c r="L155" s="2" t="inlineStr" /><c r="M155" s="2" t="inlineStr" /><c r="N155" s="2" t="inlineStr" /><c r="O155" s="2" t="inlineStr" /><c r="P155" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q155" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="156"><c r="A156" s="2" t="inlineStr"><is><t>LEKI MOCZOPĘDNE</t></is></c><c r="B156" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C156" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D156" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E156" s="2" t="inlineStr"><is><t>Do leczenia ostrego zamknięcia kąta przesączania (potocznie ataku jaskry) można zastosować:</t></is></c><c r="F156" s="2" t="inlineStr"><is><t>tymolol</t></is></c><c r="G156" s="2" t="inlineStr"><is><t>acetazolamid</t></is></c><c r="H156" s="2" t="inlineStr"><is><t>mannitol</t></is></c><c r="I156" s="2" t="inlineStr" /><c r="J156" s="2" t="inlineStr" /><c r="K156" s="2" t="inlineStr"><is><t>zydowudynę</t></is></c><c r="L156" s="2" t="inlineStr" /><c r="M156" s="2" t="inlineStr" /><c r="N156" s="2" t="inlineStr" /><c r="O156" s="2" t="inlineStr" /><c r="P156" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q156" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="157"><c r="A157" s="2" t="inlineStr"><is><t>PADACZKA</t></is></c><c r="B157" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C157" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D157" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E157" s="2" t="inlineStr"><is><t>W leczeniu stanu padaczkowego:</t></is></c><c r="F157" s="2" t="inlineStr"><is><t>lekiem pierwszego rzutu jest diazepam i.v</t></is></c><c r="G157" s="2" t="inlineStr"><is><t>w przypadku postaci opornej na leczenie można zastosować wlew dożylny midazolamu</t></is></c><c r="H157" s="2" t="inlineStr" /><c r="I157" s="2" t="inlineStr" /><c r="J157" s="2" t="inlineStr" /><c r="K157" s="2" t="inlineStr"><is><t>nie powinno się stosować fenytoiny we wlewie dożylnym</t></is></c><c r="L157" s="2" t="inlineStr"><is><t>należy stosować duże dawki steroidów i.v</t></is></c><c r="M157" s="2" t="inlineStr" /><c r="N157" s="2" t="inlineStr" /><c r="O157" s="2" t="inlineStr" /><c r="P157" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q157" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="158"><c r="A158" s="2" t="inlineStr"><is><t>FARMAKOLOGIA OGÓLNA I EBM</t></is></c><c r="B158" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C158" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D158" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E158" s="2" t="inlineStr"><is><t>Charakterystyka Produktu Leczniczego (ChPL) zawiera informacje o:</t></is></c><c r="F158" s="2" t="inlineStr"><is><t>specjalnych środkach ostrożności podczas przechowywania produktu leczniczego</t></is></c><c r="G158" s="2" t="inlineStr"><is><t>właściwościach farmakokinetycznych leku</t></is></c><c r="H158" s="2" t="inlineStr"><is><t>dacie wydania pierwszego pozwolenia na dopuszczenie do obrotu</t></is></c><c r="I158" s="2" t="inlineStr" /><c r="J158" s="2" t="inlineStr" /><c r="K158" s="2" t="inlineStr"><is><t>cenie produktu leczniczego</t></is></c><c r="L158" s="2" t="inlineStr" /><c r="M158" s="2" t="inlineStr" /><c r="N158" s="2" t="inlineStr" /><c r="O158" s="2" t="inlineStr" /><c r="P158" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q158" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="159"><c r="A159" s="2" t="inlineStr"><is><t>FARMAKOLOGIA OGÓLNA I EBM</t></is></c><c r="B159" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C159" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D159" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E159" s="2" t="inlineStr"><is><t>Agencja Oceny Technologii Medycznych i Taryfikacji:</t></is></c><c r="F159" s="2" t="inlineStr"><is><t>wycenia procedury medyczne</t></is></c><c r="G159" s="2" t="inlineStr"><is><t>zajmuje stanowisko w sprawie skuteczności i bezpieczeństwa leków</t></is></c><c r="H159" s="2" t="inlineStr"><is><t>rekomenduje leki do refundacji</t></is></c><c r="I159" s="2" t="inlineStr" /><c r="J159" s="2" t="inlineStr" /><c r="K159" s="2" t="inlineStr"><is><t>rejestruje leki</t></is></c><c r="L159" s="2" t="inlineStr" /><c r="M159" s="2" t="inlineStr" /><c r="N159" s="2" t="inlineStr" /><c r="O159" s="2" t="inlineStr" /><c r="P159" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q159" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="160"><c r="A160" s="2" t="inlineStr"><is><t>FARMAKOLOGIA OGÓLNA I EBM</t></is></c><c r="B160" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C160" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D160" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E160" s="2" t="inlineStr"><is><t>W hierarchii badań naukowych:</t></is></c><c r="F160" s="2" t="inlineStr"><is><t>badania kohortowe mają wyższą pozycję niż serie przypadków</t></is></c><c r="G160" s="2" t="inlineStr" /><c r="H160" s="2" t="inlineStr" /><c r="I160" s="2" t="inlineStr" /><c r="J160" s="2" t="inlineStr" /><c r="K160" s="2" t="inlineStr"><is><t>metaanalizy są na tym samym poziomie co randomizowane badania kontrolowane</t></is></c><c r="L160" s="2" t="inlineStr"><is><t>najwyższą pozycję mają randomizowane badania kontrolowane</t></is></c><c r="M160" s="2" t="inlineStr"><is><t>badania kohortowe są na tym samym poziomie co randomizowane badania kliniczne</t></is></c><c r="N160" s="2" t="inlineStr" /><c r="O160" s="2" t="inlineStr" /><c r="P160" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q160" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="161"><c r="A161" s="2" t="inlineStr"><is><t>LEKI PRZECIWHISTAMINOWE</t></is></c><c r="B161" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C161" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D161" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E161" s="2" t="inlineStr"><is><t>Desloratadyna:</t></is></c><c r="F161" s="2" t="inlineStr"><is><t>selektywnie blokuje receptory H1</t></is></c><c r="G161" s="2" t="inlineStr"><is><t>ma zastosowanie w leczeniu przewlekłego alergicznego nieżytu nosa</t></is></c><c r="H161" s="2" t="inlineStr" /><c r="I161" s="2" t="inlineStr" /><c r="J161" s="2" t="inlineStr" /><c r="K161" s="2" t="inlineStr"><is><t>dobrze przenika przez barierę krew- mózg</t></is></c><c r="L161" s="2" t="inlineStr"><is><t>ma znaczące działanie proarytmiczne</t></is></c><c r="M161" s="2" t="inlineStr" /><c r="N161" s="2" t="inlineStr" /><c r="O161" s="2" t="inlineStr" /><c r="P161" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q161" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="162"><c r="A162" s="2" t="inlineStr"><is><t>LEKI MOCZOPĘDNE</t></is></c><c r="B162" s="2" t="inlineStr"><is><t>Farmakokinetyka</t></is></c><c r="C162" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D162" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E162" s="2" t="inlineStr"><is><t>Mannitol podany iv. zmniejsza:</t></is></c><c r="F162" s="2" t="inlineStr"><is><t>ciśnienie wewnątrzczaszkowe</t></is></c><c r="G162" s="2" t="inlineStr" /><c r="H162" s="2" t="inlineStr" /><c r="I162" s="2" t="inlineStr" /><c r="J162" s="2" t="inlineStr" /><c r="K162" s="2" t="inlineStr"><is><t>ciśnienie osmotyczne płynu zewnątrzkomórkowego</t></is></c><c r="L162" s="2" t="inlineStr"><is><t>wydalanie sodu i chlorków</t></is></c><c r="M162" s="2" t="inlineStr"><is><t>filtrację nerkową</t></is></c><c r="N162" s="2" t="inlineStr" /><c r="O162" s="2" t="inlineStr" /><c r="P162" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q162" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="163"><c r="A163" s="2" t="inlineStr"><is><t>LEKI PRZECIWDEPRESYJNE</t></is></c><c r="B163" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C163" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D163" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E163" s="2" t="inlineStr"><is><t>Podanie inhibitorów wychwytu zwrotnego serotoniny (SSRI) jest uzasadnione u pacjentów z:</t></is></c><c r="F163" s="2" t="inlineStr"><is><t>lękiem uogólnionym</t></is></c><c r="G163" s="2" t="inlineStr"><is><t>chorobą afektywną dwubiegunową</t></is></c><c r="H163" s="2" t="inlineStr"><is><t>nerwicą natręctw</t></is></c><c r="I163" s="2" t="inlineStr"><is><t>chorobą afektywną jednobiegunową</t></is></c><c r="J163" s="2" t="inlineStr" /><c r="K163" s="2" t="inlineStr" /><c r="L163" s="2" t="inlineStr" /><c r="M163" s="2" t="inlineStr" /><c r="N163" s="2" t="inlineStr" /><c r="O163" s="2" t="inlineStr" /><c r="P163" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q163" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="164"><c r="A164" s="2" t="inlineStr"><is><t>LEKI PRZECIWDEPRESYJNE</t></is></c><c r="B164" s="2" t="inlineStr"><is><t>Struktura chemiczna</t></is></c><c r="C164" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D164" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E164" s="2" t="inlineStr"><is><t>Do wspólnych cech wenlafaksyny i amitryptyliny należy:</t></is></c><c r="F164" s="2" t="inlineStr"><is><t>hamowanie wychwytu zwrotnego serotoniny i noradrenaliny</t></is></c><c r="G164" s="2" t="inlineStr" /><c r="H164" s="2" t="inlineStr" /><c r="I164" s="2" t="inlineStr" /><c r="J164" s="2" t="inlineStr" /><c r="K164" s="2" t="inlineStr"><is><t>trójpierścieniowa budowa chemiczna</t></is></c><c r="L164" s="2" t="inlineStr"><is><t>konieczność znacznych ograniczeń dietetycznych podczas ich stosowania ze względu na ryzyko wystąpienia tzw. zespołu serowego (cheese effect)</t></is></c><c r="M164" s="2" t="inlineStr"><is><t>antagonizm wobec receptorów muskarynowych M1</t></is></c><c r="N164" s="2" t="inlineStr" /><c r="O164" s="2" t="inlineStr" /><c r="P164" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q164" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="165"><c r="A165" s="2" t="inlineStr"><is><t>LEKI IMMUNOSUPRESYJNE</t></is></c><c r="B165" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C165" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D165" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E165" s="2" t="inlineStr"><is><t>Leki, które hamują kompleks kalcyneuryny to:</t></is></c><c r="F165" s="2" t="inlineStr"><is><t>cyklosporyna</t></is></c><c r="G165" s="2" t="inlineStr"><is><t>takrolimus</t></is></c><c r="H165" s="2" t="inlineStr" /><c r="I165" s="2" t="inlineStr" /><c r="J165" s="2" t="inlineStr" /><c r="K165" s="2" t="inlineStr"><is><t>talidomid</t></is></c><c r="L165" s="2" t="inlineStr"><is><t>mykofenolan mofetylu</t></is></c><c r="M165" s="2" t="inlineStr" /><c r="N165" s="2" t="inlineStr" /><c r="O165" s="2" t="inlineStr" /><c r="P165" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q165" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="166"><c r="A166" s="2" t="inlineStr"><is><t>ZABURZENIA RYTMU SERCA</t></is></c><c r="B166" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C166" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D166" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E166" s="2" t="inlineStr"><is><t>Lacydypina:</t></is></c><c r="F166" s="2" t="inlineStr"><is><t>zmniejsza obciążenie następcze serca</t></is></c><c r="G166" s="2" t="inlineStr" /><c r="H166" s="2" t="inlineStr" /><c r="I166" s="2" t="inlineStr" /><c r="J166" s="2" t="inlineStr" /><c r="K166" s="2" t="inlineStr"><is><t>ma silne działanie inotropowe ujemne</t></is></c><c r="L166" s="2" t="inlineStr"><is><t>ma działanie dromotropowe ujemne</t></is></c><c r="M166" s="2" t="inlineStr"><is><t>ma działanie chronotropowe dodatnie</t></is></c><c r="N166" s="2" t="inlineStr" /><c r="O166" s="2" t="inlineStr" /><c r="P166" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q166" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="167"><c r="A167" s="2" t="inlineStr"><is><t>CHOROBA NIEDOKRWIENNA SERCA</t></is></c><c r="B167" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C167" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D167" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E167" s="2" t="inlineStr"><is><t>Do donorów tlenku azotu należy:</t></is></c><c r="F167" s="2" t="inlineStr"><is><t>nikorandil</t></is></c><c r="G167" s="2" t="inlineStr"><is><t>molsidomina</t></is></c><c r="H167" s="2" t="inlineStr"><is><t>diazotan izosorbitolu</t></is></c><c r="I167" s="2" t="inlineStr" /><c r="J167" s="2" t="inlineStr" /><c r="K167" s="2" t="inlineStr"><is><t>trimetazydyna</t></is></c><c r="L167" s="2" t="inlineStr" /><c r="M167" s="2" t="inlineStr" /><c r="N167" s="2" t="inlineStr" /><c r="O167" s="2" t="inlineStr" /><c r="P167" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q167" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="168"><c r="A168" s="2" t="inlineStr"><is><t>FARMAKOKINETYKA</t></is></c><c r="B168" s="2" t="inlineStr"><is><t>Sposób podania</t></is></c><c r="C168" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D168" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E168" s="2" t="inlineStr"><is><t>Względna dostępność biologiczna leku (biorównoważność) może być określona przez porównanie AUC:</t></is></c><c r="F168" s="2" t="inlineStr"><is><t>leku wzorcowego podanego drogą pozanaczyniową i dożylnie</t></is></c><c r="G168" s="2" t="inlineStr"><is><t>leku wzorcowego i badanego podanych tą samą drogą</t></is></c><c r="H168" s="2" t="inlineStr" /><c r="I168" s="2" t="inlineStr" /><c r="J168" s="2" t="inlineStr" /><c r="K168" s="2" t="inlineStr"><is><t>tylko leków podawanych drogą dożylną</t></is></c><c r="L168" s="2" t="inlineStr"><is><t>leku badanego podanego drogą pozanaczyniową i wzorcowego podanego dożylnie</t></is></c><c r="M168" s="2" t="inlineStr" /><c r="N168" s="2" t="inlineStr" /><c r="O168" s="2" t="inlineStr" /><c r="P168" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q168" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="169"><c r="A169" s="2" t="inlineStr"><is><t>LEKI PRZECIWLĘKOWE</t></is></c><c r="B169" s="2" t="inlineStr"><is><t>Farmakokinetyka</t></is></c><c r="C169" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D169" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E169" s="2" t="inlineStr"><is><t>Benzodiazepiną, która nie podlega metabolizmowi wątrobowemu jest:</t></is></c><c r="F169" s="2" t="inlineStr"><is><t>lorazepam</t></is></c><c r="G169" s="2" t="inlineStr"><is><t>oksazepam</t></is></c><c r="H169" s="2" t="inlineStr" /><c r="I169" s="2" t="inlineStr" /><c r="J169" s="2" t="inlineStr" /><c r="K169" s="2" t="inlineStr"><is><t>nitrazepam</t></is></c><c r="L169" s="2" t="inlineStr"><is><t>diazepam</t></is></c><c r="M169" s="2" t="inlineStr" /><c r="N169" s="2" t="inlineStr" /><c r="O169" s="2" t="inlineStr" /><c r="P169" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q169" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="170"><c r="A170" s="2" t="inlineStr"><is><t>FARMAKOKINETYKA</t></is></c><c r="B170" s="2" t="inlineStr"><is><t>Farmakokinetyka</t></is></c><c r="C170" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D170" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E170" s="2" t="inlineStr"><is><t>Objętość dystrybucji ma znaczenie w określeniu wielkości dawki:</t></is></c><c r="F170" s="2" t="inlineStr"><is><t>nasycającej</t></is></c><c r="G170" s="2" t="inlineStr"><is><t>podtrzymującej</t></is></c><c r="H170" s="2" t="inlineStr" /><c r="I170" s="2" t="inlineStr" /><c r="J170" s="2" t="inlineStr" /><c r="K170" s="2" t="inlineStr"><is><t>śmiertelnej</t></is></c><c r="L170" s="2" t="inlineStr"><is><t>toksycznej</t></is></c><c r="M170" s="2" t="inlineStr" /><c r="N170" s="2" t="inlineStr" /><c r="O170" s="2" t="inlineStr" /><c r="P170" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q170" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="171"><c r="A171" s="2" t="inlineStr"><is><t>NIEOPIOIDOWE LEKI PRZECIWBÓLOWE</t></is></c><c r="B171" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C171" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D171" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E171" s="2" t="inlineStr"><is><t>Do obniżenia gorączki u 2-letniego dziecka można zastosować:</t></is></c><c r="F171" s="2" t="inlineStr"><is><t>czopek doodbytniczy zawierający paracetamol</t></is></c><c r="G171" s="2" t="inlineStr"><is><t>zawiesinę doustną zawierającą ibuprofen</t></is></c><c r="H171" s="2" t="inlineStr" /><c r="I171" s="2" t="inlineStr" /><c r="J171" s="2" t="inlineStr" /><c r="K171" s="2" t="inlineStr"><is><t>tabletki o natychmiastowym uwalnianiu w jamie ustnej zawierające kwas acetylosalicylowy</t></is></c><c r="L171" s="2" t="inlineStr"><is><t>wstrzyknięcie domięśniowe metamizolu</t></is></c><c r="M171" s="2" t="inlineStr" /><c r="N171" s="2" t="inlineStr" /><c r="O171" s="2" t="inlineStr" /><c r="P171" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q171" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="172"><c r="A172" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B172" s="2" t="inlineStr"><is><t>Monitorowanie</t></is></c><c r="C172" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D172" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E172" s="2" t="inlineStr"><is><t>Typowe leki podlegające monitorowaniu stężeń to:</t></is></c><c r="F172" s="2" t="inlineStr"><is><t>cyklosporyna</t></is></c><c r="G172" s="2" t="inlineStr"><is><t>fenytoina</t></is></c><c r="H172" s="2" t="inlineStr"><is><t>gentamycyna</t></is></c><c r="I172" s="2" t="inlineStr"><is><t>Digoksyna</t></is></c><c r="J172" s="2" t="inlineStr" /><c r="K172" s="2" t="inlineStr" /><c r="L172" s="2" t="inlineStr" /><c r="M172" s="2" t="inlineStr" /><c r="N172" s="2" t="inlineStr" /><c r="O172" s="2" t="inlineStr" /><c r="P172" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q172" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="173"><c r="A173" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B173" s="2" t="inlineStr"><is><t>Ciąża</t></is></c><c r="C173" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D173" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E173" s="2" t="inlineStr"><is><t>Izoniazyd:</t></is></c><c r="F173" s="2" t="inlineStr"><is><t>działa bakteriobójczo na prątki szybko namnażające się</t></is></c><c r="G173" s="2" t="inlineStr" /><c r="H173" s="2" t="inlineStr" /><c r="I173" s="2" t="inlineStr" /><c r="J173" s="2" t="inlineStr" /><c r="K173" s="2" t="inlineStr"><is><t>nie powinien być stosowany przez kobiety w ciąży</t></is></c><c r="L173" s="2" t="inlineStr"><is><t>nie jest stosowany w leczeniu gruźlicy pozapłucnej</t></is></c><c r="M173" s="2" t="inlineStr"><is><t>może spowodować neuropatię obwodową</t></is></c><c r="N173" s="2" t="inlineStr" /><c r="O173" s="2" t="inlineStr" /><c r="P173" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q173" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="174"><c r="A174" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B174" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C174" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D174" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E174" s="2" t="inlineStr"><is><t>Wskaż prawdziwe połączenie lek-działanie niepożądne:</t></is></c><c r="F174" s="2" t="inlineStr"><is><t>zolpidem – niepamięć następcza</t></is></c><c r="G174" s="2" t="inlineStr"><is><t>rotygotyna – nudności i wymioty</t></is></c><c r="H174" s="2" t="inlineStr"><is><t>alprazolam - senność</t></is></c><c r="I174" s="2" t="inlineStr"><is><t>fluoksetyna – zaburzenia libido i funkcji seksualnych</t></is></c><c r="J174" s="2" t="inlineStr" /><c r="K174" s="2" t="inlineStr" /><c r="L174" s="2" t="inlineStr" /><c r="M174" s="2" t="inlineStr" /><c r="N174" s="2" t="inlineStr" /><c r="O174" s="2" t="inlineStr" /><c r="P174" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q174" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="175"><c r="A175" s="2" t="inlineStr"><is><t>LEKI PRZECIWPSYCHOTYCZNE</t></is></c><c r="B175" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C175" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D175" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E175" s="2" t="inlineStr"><is><t>Do leczenia zaburzeń psychotycznych z nasilonymi objawami negatywnymi należy wybrać:</t></is></c><c r="F175" s="2" t="inlineStr"><is><t>amisulpiryd</t></is></c><c r="G175" s="2" t="inlineStr"><is><t>olanzapinę</t></is></c><c r="H175" s="2" t="inlineStr" /><c r="I175" s="2" t="inlineStr" /><c r="J175" s="2" t="inlineStr" /><c r="K175" s="2" t="inlineStr"><is><t>haloperydol</t></is></c><c r="L175" s="2" t="inlineStr"><is><t>chlorpromazynę</t></is></c><c r="M175" s="2" t="inlineStr" /><c r="N175" s="2" t="inlineStr" /><c r="O175" s="2" t="inlineStr" /><c r="P175" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q175" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="176"><c r="A176" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B176" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C176" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D176" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E176" s="2" t="inlineStr"><is><t>Działanie przeciwwymiotne metoklopramidu wynika z blokady receptorów:</t></is></c><c r="F176" s="2" t="inlineStr"><is><t>dopaminowych (D2)</t></is></c><c r="G176" s="2" t="inlineStr"><is><t>serotoninowych (5-HT3)</t></is></c><c r="H176" s="2" t="inlineStr" /><c r="I176" s="2" t="inlineStr" /><c r="J176" s="2" t="inlineStr" /><c r="K176" s="2" t="inlineStr"><is><t>neurokininowych (NK1)</t></is></c><c r="L176" s="2" t="inlineStr"><is><t>kannabinoidowych (CB1)</t></is></c><c r="M176" s="2" t="inlineStr" /><c r="N176" s="2" t="inlineStr" /><c r="O176" s="2" t="inlineStr" /><c r="P176" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q176" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="177"><c r="A177" s="2" t="inlineStr"><is><t>UKŁAD PRZYWSPÓŁCZULNY</t></is></c><c r="B177" s="2" t="inlineStr"><is><t>Antidotum</t></is></c><c r="C177" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D177" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E177" s="2" t="inlineStr"><is><t>Rozszerzenie źrenic, suchość w ustach, osłabienie lub porażenie perystaltyki jelit obserwowane jest w przebiegu zatrucia:</t></is></c><c r="F177" s="2" t="inlineStr"><is><t>amitryptyliną</t></is></c><c r="G177" s="2" t="inlineStr" /><c r="H177" s="2" t="inlineStr" /><c r="I177" s="2" t="inlineStr" /><c r="J177" s="2" t="inlineStr" /><c r="K177" s="2" t="inlineStr"><is><t>escitalopramem</t></is></c><c r="L177" s="2" t="inlineStr"><is><t>pestycydami fosforoorganicznymi</t></is></c><c r="M177" s="2" t="inlineStr"><is><t>glikozydami naparstnicy</t></is></c><c r="N177" s="2" t="inlineStr" /><c r="O177" s="2" t="inlineStr" /><c r="P177" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q177" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="178"><c r="A178" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B178" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C178" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D178" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E178" s="2" t="inlineStr"><is><t>U 70-letniego mężczyzny z przewlekłą niewydolnością żylną wspomagająco do kompresjoterapii należy zastosować:</t></is></c><c r="F178" s="2" t="inlineStr"><is><t>mikronizowaną diosminę + hesperydynę</t></is></c><c r="G178" s="2" t="inlineStr" /><c r="H178" s="2" t="inlineStr" /><c r="I178" s="2" t="inlineStr" /><c r="J178" s="2" t="inlineStr" /><c r="K178" s="2" t="inlineStr"><is><t>kwas acetylosalicylowy w dawce antyagregacyjnej</t></is></c><c r="L178" s="2" t="inlineStr"><is><t>enoksaparynę w dawce profilaktycznej</t></is></c><c r="M178" s="2" t="inlineStr"><is><t>furosemid w dawce leczniczej</t></is></c><c r="N178" s="2" t="inlineStr" /><c r="O178" s="2" t="inlineStr" /><c r="P178" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q178" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="179"><c r="A179" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B179" s="2" t="inlineStr"><is><t>Antidotum</t></is></c><c r="C179" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D179" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E179" s="2" t="inlineStr"><is><t>Nie powinno się zwalniać pasażu jelitowego w przebiegu:</t></is></c><c r="F179" s="2" t="inlineStr"><is><t>zatrucia z objawami ogólnymi</t></is></c><c r="G179" s="2" t="inlineStr"><is><t>biegunki z krwią w stolcu i gorączką</t></is></c><c r="H179" s="2" t="inlineStr"><is><t>ostrej biegunki o niewielkim nasileniu</t></is></c><c r="I179" s="2" t="inlineStr" /><c r="J179" s="2" t="inlineStr" /><c r="K179" s="2" t="inlineStr"><is><t>przewlekłej biegunki związanej z chorobą zapalną jelit</t></is></c><c r="L179" s="2" t="inlineStr" /><c r="M179" s="2" t="inlineStr" /><c r="N179" s="2" t="inlineStr" /><c r="O179" s="2" t="inlineStr" /><c r="P179" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q179" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="180"><c r="A180" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B180" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C180" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D180" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E180" s="2" t="inlineStr"><is><t>Związki bizmutu:</t></is></c><c r="F180" s="2" t="inlineStr"><is><t>tworzą nierozpuszczalne kompleksy z białkami wysiękowymi na powierzchni owrzodzenia, działając osłaniająco wobec kwasu solnego i pepsyny na uszkodzoną błonę śluzową żołądka i dwunastnicy</t></is></c><c r="G180" s="2" t="inlineStr"><is><t>wchłaniają się z przewodu pokarmowego</t></is></c><c r="H180" s="2" t="inlineStr"><is><t>bezpośrednio niszczą komórki Helicobacter pylori</t></is></c><c r="I180" s="2" t="inlineStr"><is><t>mogą spowodować czarne zabarwienie języka i kału</t></is></c><c r="J180" s="2" t="inlineStr" /><c r="K180" s="2" t="inlineStr" /><c r="L180" s="2" t="inlineStr" /><c r="M180" s="2" t="inlineStr" /><c r="N180" s="2" t="inlineStr" /><c r="O180" s="2" t="inlineStr" /><c r="P180" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q180" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="181"><c r="A181" s="2" t="inlineStr"><is><t>UKŁAD WSPÓŁCZULNY</t></is></c><c r="B181" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C181" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D181" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E181" s="2" t="inlineStr"><is><t>Wskaż prawidłowe połączenie lek – wskazanie - dawka:</t></is></c><c r="F181" s="2" t="inlineStr"><is><t>dobutamina – diagnostyka niedokrwienia mięśnia serca –wlew 2-20 mcg/kg m.c./min</t></is></c><c r="G181" s="2" t="inlineStr"><is><t>adrenalina – resuscytacja krążeniowo-oddechowa– w dawkach frakcjonowanych i.v. po 1 mg w rozcieńczeniu w 10 ml 0,9% NaCl</t></is></c><c r="H181" s="2" t="inlineStr" /><c r="I181" s="2" t="inlineStr" /><c r="J181" s="2" t="inlineStr" /><c r="K181" s="2" t="inlineStr"><is><t>noradrenalina – ciężka hipotonia – wlew 2-10 mcg/kg m.c./min</t></is></c><c r="L181" s="2" t="inlineStr"><is><t>dopamina – ostra niewydolność mięśnia sercowego – wlew 1-3 mcg/kg m.c./min</t></is></c><c r="M181" s="2" t="inlineStr" /><c r="N181" s="2" t="inlineStr" /><c r="O181" s="2" t="inlineStr" /><c r="P181" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q181" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="182"><c r="A182" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B182" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C182" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D182" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E182" s="2" t="inlineStr"><is><t>Skala HAS-BLED określa ryzyko krwawienia u osób z migotaniem przedsionków stosujących leczenie przeciwkrzepliwe na podstawie oceny:</t></is></c><c r="F182" s="2" t="inlineStr"><is><t>wartości skurczowego ciśnienia tętniczego</t></is></c><c r="G182" s="2" t="inlineStr"><is><t>czynności wątroby</t></is></c><c r="H182" s="2" t="inlineStr"><is><t>stężenia kreatyniny</t></is></c><c r="I182" s="2" t="inlineStr" /><c r="J182" s="2" t="inlineStr" /><c r="K182" s="2" t="inlineStr"><is><t>glikemii</t></is></c><c r="L182" s="2" t="inlineStr" /><c r="M182" s="2" t="inlineStr" /><c r="N182" s="2" t="inlineStr" /><c r="O182" s="2" t="inlineStr" /><c r="P182" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q182" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="183"><c r="A183" s="2" t="inlineStr"><is><t>UKŁAD WSPÓŁCZULNY</t></is></c><c r="B183" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C183" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D183" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E183" s="2" t="inlineStr"><is><t>Wskaż prawdziwe połączenie substancja uzależniająca - lek stosowany w terapii uzależnienia:</t></is></c><c r="F183" s="2" t="inlineStr"><is><t>heroina - metadon</t></is></c><c r="G183" s="2" t="inlineStr"><is><t>nikotyna – wareniklina</t></is></c><c r="H183" s="2" t="inlineStr"><is><t>alkohol - nalmefen</t></is></c><c r="I183" s="2" t="inlineStr" /><c r="J183" s="2" t="inlineStr" /><c r="K183" s="2" t="inlineStr"><is><t>amfetamina - deferoksamina</t></is></c><c r="L183" s="2" t="inlineStr" /><c r="M183" s="2" t="inlineStr" /><c r="N183" s="2" t="inlineStr" /><c r="O183" s="2" t="inlineStr" /><c r="P183" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q183" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="184"><c r="A184" s="2" t="inlineStr"><is><t>LEKI MOCZOPĘDNE</t></is></c><c r="B184" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C184" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D184" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E184" s="2" t="inlineStr"><is><t>Peptydy natriuretyczne zwiększają:</t></is></c><c r="F184" s="2" t="inlineStr"><is><t>filtrację kłębuszkową</t></is></c><c r="G184" s="2" t="inlineStr" /><c r="H184" s="2" t="inlineStr" /><c r="I184" s="2" t="inlineStr" /><c r="J184" s="2" t="inlineStr" /><c r="K184" s="2" t="inlineStr"><is><t>wydzielanie aldosteronu</t></is></c><c r="L184" s="2" t="inlineStr"><is><t>glikemię</t></is></c><c r="M184" s="2" t="inlineStr"><is><t>aktywność układu współczulnego</t></is></c><c r="N184" s="2" t="inlineStr" /><c r="O184" s="2" t="inlineStr" /><c r="P184" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q184" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="185"><c r="A185" s="2" t="inlineStr"><is><t>ZABURZENIA RYTMU SERCA</t></is></c><c r="B185" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C185" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D185" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E185" s="2" t="inlineStr"><is><t>Pacjent z objawową bradykardią = 35 uderzeń/min jest leczony poniższym zestawem leków. Który z nich należy niezwłocznie odstawić?</t></is></c><c r="F185" s="2" t="inlineStr"><is><t>digoksynę</t></is></c><c r="G185" s="2" t="inlineStr"><is><t>amiodaron</t></is></c><c r="H185" s="2" t="inlineStr"><is><t>betaksolol</t></is></c><c r="I185" s="2" t="inlineStr" /><c r="J185" s="2" t="inlineStr" /><c r="K185" s="2" t="inlineStr"><is><t>losartan</t></is></c><c r="L185" s="2" t="inlineStr" /><c r="M185" s="2" t="inlineStr" /><c r="N185" s="2" t="inlineStr" /><c r="O185" s="2" t="inlineStr" /><c r="P185" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q185" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="186"><c r="A186" s="2" t="inlineStr"><is><t>NADCIŚNIENIE TĘTNICZE</t></is></c><c r="B186" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C186" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D186" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E186" s="2" t="inlineStr"><is><t>Irbesartan zwiększa w osoczu stężenie:</t></is></c><c r="F186" s="2" t="inlineStr"><is><t>reniny</t></is></c><c r="G186" s="2" t="inlineStr"><is><t>potasu</t></is></c><c r="H186" s="2" t="inlineStr" /><c r="I186" s="2" t="inlineStr" /><c r="J186" s="2" t="inlineStr" /><c r="K186" s="2" t="inlineStr"><is><t>bradykininy</t></is></c><c r="L186" s="2" t="inlineStr"><is><t>aldosteronu</t></is></c><c r="M186" s="2" t="inlineStr" /><c r="N186" s="2" t="inlineStr" /><c r="O186" s="2" t="inlineStr" /><c r="P186" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q186" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="187"><c r="A187" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B187" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C187" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D187" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E187" s="2" t="inlineStr"><is><t>70-letnia kobieta od miesiąca po wypisie ze szpitala otrzymuje kwas acetylosalicylowy + klopidogrel. Na tej podstawie można sądzić, że przebyła:</t></is></c><c r="F187" s="2" t="inlineStr"><is><t>angioplastykę wieńcową z wszczepieniem stentu</t></is></c><c r="G187" s="2" t="inlineStr"><is><t>zawał serca</t></is></c><c r="H187" s="2" t="inlineStr" /><c r="I187" s="2" t="inlineStr" /><c r="J187" s="2" t="inlineStr" /><c r="K187" s="2" t="inlineStr"><is><t>udar niedokrwienny mózgu</t></is></c><c r="L187" s="2" t="inlineStr"><is><t>zatorowość płucną niewysokiego ryzyka</t></is></c><c r="M187" s="2" t="inlineStr" /><c r="N187" s="2" t="inlineStr" /><c r="O187" s="2" t="inlineStr" /><c r="P187" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q187" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="188"><c r="A188" s="2" t="inlineStr"><is><t>ZABURZENIA RYTMU SERCA</t></is></c><c r="B188" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C188" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D188" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E188" s="2" t="inlineStr"><is><t>Wskaż prawdziwe połączenie lek – działanie niepożądane:</t></is></c><c r="F188" s="2" t="inlineStr"><is><t>metoprolol – blok przedsionkowo-komorowy I stopnia</t></is></c><c r="G188" s="2" t="inlineStr"><is><t>sotalol - wydłużenie odstępu QT</t></is></c><c r="H188" s="2" t="inlineStr"><is><t>propafenon - zaburzenia hematopoezy</t></is></c><c r="I188" s="2" t="inlineStr"><is><t>adenozyna - ból w klatce piersiowej</t></is></c><c r="J188" s="2" t="inlineStr" /><c r="K188" s="2" t="inlineStr" /><c r="L188" s="2" t="inlineStr" /><c r="M188" s="2" t="inlineStr" /><c r="N188" s="2" t="inlineStr" /><c r="O188" s="2" t="inlineStr" /><c r="P188" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q188" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="189"><c r="A189" s="2" t="inlineStr"><is><t>NADCIŚNIENIE TĘTNICZE</t></is></c><c r="B189" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C189" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D189" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E189" s="2" t="inlineStr"><is><t>59-letni mężczyzna z pozawałową niewydolnością serca (EF ok. 30%), z implantowanym ICD (kardiowerterem defibrylatorem) w prewencji pierwotnej NZK, z eGFR = 95%, z bólami pleców na skutek wielopoziomowej dyskopatii jest leczony: ramiprylem, karwedilolem, eplerenonem, indapamidem, preparatami chlorku potasu, magnezu z witaminą B6 i węglanu wapnia oraz paracetamolem i ketoprofenem. Które stwierdzenie jest prawdziwe?</t></is></c><c r="F189" s="2" t="inlineStr"><is><t>opisana terapia stwarza zagrożenie hiperkaliemią, co trzeba monitorować</t></is></c><c r="G189" s="2" t="inlineStr"><is><t>należy odstawić ketoprofen, bo może on osłabiać działanie leków w niewydolności serca</t></is></c><c r="H189" s="2" t="inlineStr" /><c r="I189" s="2" t="inlineStr" /><c r="J189" s="2" t="inlineStr" /><c r="K189" s="2" t="inlineStr"><is><t>ze względu na lepszą kontrolę choroby zamiast ramiprylu należy podać walsartan</t></is></c><c r="L189" s="2" t="inlineStr"><is><t>indapamid jako lek potencjalnie nieskuteczny powinien zostać zastąpiony torasemidem</t></is></c><c r="M189" s="2" t="inlineStr" /><c r="N189" s="2" t="inlineStr" /><c r="O189" s="2" t="inlineStr" /><c r="P189" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q189" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="190"><c r="A190" s="2" t="inlineStr"><is><t>NADCIŚNIENIE TĘTNICZE</t></is></c><c r="B190" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C190" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D190" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E190" s="2" t="inlineStr"><is><t>Wartości ciśnienia tętniczego może zwiększyć stosowanie:</t></is></c><c r="F190" s="2" t="inlineStr"><is><t>piroksykamu</t></is></c><c r="G190" s="2" t="inlineStr"><is><t>prednizonu</t></is></c><c r="H190" s="2" t="inlineStr" /><c r="I190" s="2" t="inlineStr" /><c r="J190" s="2" t="inlineStr" /><c r="K190" s="2" t="inlineStr"><is><t>eplerenonu</t></is></c><c r="L190" s="2" t="inlineStr"><is><t>morfiny</t></is></c><c r="M190" s="2" t="inlineStr" /><c r="N190" s="2" t="inlineStr" /><c r="O190" s="2" t="inlineStr" /><c r="P190" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q190" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="191"><c r="A191" s="2" t="inlineStr"><is><t>OSTEOPOROZA</t></is></c><c r="B191" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C191" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D191" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E191" s="2" t="inlineStr"><is><t>Kwas ibandronowy:</t></is></c><c r="F191" s="2" t="inlineStr"><is><t>z dużym powinowactwem wiąże się ze zmineralizowaną kością</t></is></c><c r="G191" s="2" t="inlineStr"><is><t>zmniejsza ryzyko złamania kręgów kręgosłupa u kobiet po menopauzie</t></is></c><c r="H191" s="2" t="inlineStr"><is><t>hamuje aktywację osteoklastów</t></is></c><c r="I191" s="2" t="inlineStr"><is><t>może spowodować martwicę szczęki</t></is></c><c r="J191" s="2" t="inlineStr" /><c r="K191" s="2" t="inlineStr" /><c r="L191" s="2" t="inlineStr" /><c r="M191" s="2" t="inlineStr" /><c r="N191" s="2" t="inlineStr" /><c r="O191" s="2" t="inlineStr" /><c r="P191" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q191" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="192"><c r="A192" s="2" t="inlineStr"><is><t>LEKI HIPOLIPEMIZUJĄCE</t></is></c><c r="B192" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C192" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D192" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E192" s="2" t="inlineStr"><is><t>Dodatkowe zmniejszenie stężenia cholesterolu LDL w surowicy można osiągnąć przez dodanie do statyn:</t></is></c><c r="F192" s="2" t="inlineStr"><is><t>kolesewelamu</t></is></c><c r="G192" s="2" t="inlineStr"><is><t>ewolokumabu</t></is></c><c r="H192" s="2" t="inlineStr"><is><t>ezetymibu</t></is></c><c r="I192" s="2" t="inlineStr" /><c r="J192" s="2" t="inlineStr" /><c r="K192" s="2" t="inlineStr"><is><t>PUFA – wielonienasyconych kwasów tłuszczowych</t></is></c><c r="L192" s="2" t="inlineStr" /><c r="M192" s="2" t="inlineStr" /><c r="N192" s="2" t="inlineStr" /><c r="O192" s="2" t="inlineStr" /><c r="P192" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q192" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="193"><c r="A193" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B193" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C193" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D193" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E193" s="2" t="inlineStr"><is><t>Które stwierdzenie jest prawdziwe:</t></is></c><c r="F193" s="2" t="inlineStr"><is><t>cilostazol wydłuża dystans marszu bez bólu u pacjentów z chromaniem przestankowym</t></is></c><c r="G193" s="2" t="inlineStr"><is><t>stosowanie serelaksyny może przynieść korzyści pacjentom z ostrą niewydolnością mięśnia sercowego</t></is></c><c r="H193" s="2" t="inlineStr"><is><t>do działań niepożądanych milrynonu należą zaburzenia rytmu serca</t></is></c><c r="I193" s="2" t="inlineStr" /><c r="J193" s="2" t="inlineStr" /><c r="K193" s="2" t="inlineStr"><is><t>inhibitory fosfodiesterazy 5 mogą być podane łącznie z azotanami</t></is></c><c r="L193" s="2" t="inlineStr" /><c r="M193" s="2" t="inlineStr" /><c r="N193" s="2" t="inlineStr" /><c r="O193" s="2" t="inlineStr" /><c r="P193" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q193" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="194"><c r="A194" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B194" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C194" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D194" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E194" s="2" t="inlineStr"><is><t>Fibraty (pochodne kwasu fibrynowego):</t></is></c><c r="F194" s="2" t="inlineStr"><is><t>hamują uwalnianie frakcji lipidowej VLDL z wątroby</t></is></c><c r="G194" s="2" t="inlineStr"><is><t>nasilają aktywność lipazy lipoproteinowej</t></is></c><c r="H194" s="2" t="inlineStr" /><c r="I194" s="2" t="inlineStr" /><c r="J194" s="2" t="inlineStr" /><c r="K194" s="2" t="inlineStr"><is><t>hamują wchłanianie tłuszczów złożonych z przewodu pokarmowego</t></is></c><c r="L194" s="2" t="inlineStr"><is><t>zmniejszają stężenie frakcji HDL poprzez spadek syntezy Apo-A1 i Apo-AII</t></is></c><c r="M194" s="2" t="inlineStr" /><c r="N194" s="2" t="inlineStr" /><c r="O194" s="2" t="inlineStr" /><c r="P194" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q194" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="195"><c r="A195" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B195" s="2" t="inlineStr"><is><t>Farmakokinetyka</t></is></c><c r="C195" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D195" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E195" s="2" t="inlineStr"><is><t>U chorych ze zdekompensowaną obukomorową niewydolnością serca:</t></is></c><c r="F195" s="2" t="inlineStr"><is><t>znacznie opóźnione jest wchłanianie leków z przewodu pokarmowego</t></is></c><c r="G195" s="2" t="inlineStr"><is><t>leki hydrofilne dystrybuują się do płynu obrzękowego, co dodatkowo negatywnie wpływa na ich dystrybucję do narządów docelowych</t></is></c><c r="H195" s="2" t="inlineStr"><is><t>zmniejsza się klirens wątrobowy wszystkich leków metabolizowanych w wątrobie niezależnie od stopnia ich ekstrakcji wątrobowej</t></is></c><c r="I195" s="2" t="inlineStr" /><c r="J195" s="2" t="inlineStr" /><c r="K195" s="2" t="inlineStr"><is><t>stosunkowo mało zmniejsza się klirens nerkowy leków</t></is></c><c r="L195" s="2" t="inlineStr" /><c r="M195" s="2" t="inlineStr" /><c r="N195" s="2" t="inlineStr" /><c r="O195" s="2" t="inlineStr" /><c r="P195" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q195" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="196"><c r="A196" s="2" t="inlineStr"><is><t>FARMAKOKINETYKA</t></is></c><c r="B196" s="2" t="inlineStr"><is><t>Interakcje</t></is></c><c r="C196" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D196" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E196" s="2" t="inlineStr"><is><t>Interakcją farmakodynamiczną jest:</t></is></c><c r="F196" s="2" t="inlineStr"><is><t>nasilenie depresji OUN po skojarzeniu opioidów z etanolem</t></is></c><c r="G196" s="2" t="inlineStr" /><c r="H196" s="2" t="inlineStr" /><c r="I196" s="2" t="inlineStr" /><c r="J196" s="2" t="inlineStr" /><c r="K196" s="2" t="inlineStr"><is><t>hamowanie wchłaniania z przewodu pokarmowego leków podawanych jednocześnie</t></is></c><c r="L196" s="2" t="inlineStr"><is><t>wytrącenie się osadu po zmieszaniu dwóch leków w jednym roztworze do wstrzyknięcia</t></is></c><c r="M196" s="2" t="inlineStr"><is><t>zwiększenie metabolizmu leków podawanych jednocześnie</t></is></c><c r="N196" s="2" t="inlineStr" /><c r="O196" s="2" t="inlineStr" /><c r="P196" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q196" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="197"><c r="A197" s="2" t="inlineStr"><is><t>LEKI MOCZOPĘDNE</t></is></c><c r="B197" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C197" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D197" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E197" s="2" t="inlineStr"><is><t>Kwasicę metaboliczną mogą powodować:</t></is></c><c r="F197" s="2" t="inlineStr"><is><t>metformina</t></is></c><c r="G197" s="2" t="inlineStr"><is><t>kwas acetylosalicylowy</t></is></c><c r="H197" s="2" t="inlineStr" /><c r="I197" s="2" t="inlineStr" /><c r="J197" s="2" t="inlineStr" /><c r="K197" s="2" t="inlineStr"><is><t>diuretyki pętlowe</t></is></c><c r="L197" s="2" t="inlineStr"><is><t>etanol</t></is></c><c r="M197" s="2" t="inlineStr" /><c r="N197" s="2" t="inlineStr" /><c r="O197" s="2" t="inlineStr" /><c r="P197" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q197" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="198"><c r="A198" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B198" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C198" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D198" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E198" s="2" t="inlineStr"><is><t>Klindamycyna:</t></is></c><c r="F198" s="2" t="inlineStr"><is><t>jest aktywna wobec beztlenowców</t></is></c><c r="G198" s="2" t="inlineStr" /><c r="H198" s="2" t="inlineStr" /><c r="I198" s="2" t="inlineStr" /><c r="J198" s="2" t="inlineStr" /><c r="K198" s="2" t="inlineStr"><is><t>dobrze przenika do płynu mózgowo-rdzeniowego</t></is></c><c r="L198" s="2" t="inlineStr"><is><t>słabo selekcjonuje szczepy Clostridium difficile w jelicie</t></is></c><c r="M198" s="2" t="inlineStr"><is><t>stosowana jest jako lek z wyboru w nierzeżączkowym zapaleniu cewki moczowej</t></is></c><c r="N198" s="2" t="inlineStr" /><c r="O198" s="2" t="inlineStr" /><c r="P198" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q198" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="199"><c r="A199" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B199" s="2" t="inlineStr"><is><t>Struktura chemiczna</t></is></c><c r="C199" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D199" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E199" s="2" t="inlineStr"><is><t>Pierścień beta-laktamowy znajduje się w cząsteczce:</t></is></c><c r="F199" s="2" t="inlineStr"><is><t>kloksacyliny</t></is></c><c r="G199" s="2" t="inlineStr"><is><t>ceftazydymu</t></is></c><c r="H199" s="2" t="inlineStr"><is><t>meropenemu</t></is></c><c r="I199" s="2" t="inlineStr" /><c r="J199" s="2" t="inlineStr" /><c r="K199" s="2" t="inlineStr"><is><t>wankomycyny</t></is></c><c r="L199" s="2" t="inlineStr" /><c r="M199" s="2" t="inlineStr" /><c r="N199" s="2" t="inlineStr" /><c r="O199" s="2" t="inlineStr" /><c r="P199" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q199" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="200"><c r="A200" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B200" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C200" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D200" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E200" s="2" t="inlineStr"><is><t>Wskaż prawdziwe połączenie lek – mechanizm działania:</t></is></c><c r="F200" s="2" t="inlineStr"><is><t>tygecyklina - hamowanie biosyntezy białka w komórkach bakterii poprzez wiązanie się z podjednostką 30 S rybosomu</t></is></c><c r="G200" s="2" t="inlineStr"><is><t>trimetoprim - inhibicja reduktazy kwasu dihydrofoliowego (DHFR)</t></is></c><c r="H200" s="2" t="inlineStr" /><c r="I200" s="2" t="inlineStr" /><c r="J200" s="2" t="inlineStr" /><c r="K200" s="2" t="inlineStr"><is><t>metronidazol - blokowanie syntezy ściany komórkowej bakterii</t></is></c><c r="L200" s="2" t="inlineStr"><is><t>teikoplanina - uszkodzenie DNA</t></is></c><c r="M200" s="2" t="inlineStr" /><c r="N200" s="2" t="inlineStr" /><c r="O200" s="2" t="inlineStr" /><c r="P200" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q200" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="201"><c r="A201" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B201" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C201" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D201" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E201" s="2" t="inlineStr"><is><t>Wskaż prawdziwe połączenie lek – działania niepożądane:</t></is></c><c r="F201" s="2" t="inlineStr"><is><t>lewofloksacyna - drgawki</t></is></c><c r="G201" s="2" t="inlineStr"><is><t>ceftriakson – zagęszczenie żółci</t></is></c><c r="H201" s="2" t="inlineStr"><is><t>wankomycyna – zespół czerwonego karku</t></is></c><c r="I201" s="2" t="inlineStr"><is><t>linezolid – trombocytopenia</t></is></c><c r="J201" s="2" t="inlineStr" /><c r="K201" s="2" t="inlineStr"><is><t>W celu zwiększenia bezpieczeństwa leczenia amikacyną mężczyzny z powikłanym zakażeniem układu moczowego należy:</t></is></c><c r="L201" s="2" t="inlineStr" /><c r="M201" s="2" t="inlineStr" /><c r="N201" s="2" t="inlineStr" /><c r="O201" s="2" t="inlineStr" /><c r="P201" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q201" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="202"><c r="A202" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B202" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C202" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D202" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E202" s="2" t="inlineStr"><is><t>W leczeniu pacjentki z niepowikłanym zapaleniem pęcherza moczowego można zastosować:</t></is></c><c r="F202" s="2" t="inlineStr"><is><t>amoksycylinę z inhibitorem beta-laktamazy</t></is></c><c r="G202" s="2" t="inlineStr"><is><t>fosfomycynę</t></is></c><c r="H202" s="2" t="inlineStr"><is><t>cyprofloksacynę</t></is></c><c r="I202" s="2" t="inlineStr"><is><t>furazydynę</t></is></c><c r="J202" s="2" t="inlineStr" /><c r="K202" s="2" t="inlineStr" /><c r="L202" s="2" t="inlineStr" /><c r="M202" s="2" t="inlineStr" /><c r="N202" s="2" t="inlineStr" /><c r="O202" s="2" t="inlineStr" /><c r="P202" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q202" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="203"><c r="A203" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B203" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C203" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D203" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E203" s="2" t="inlineStr"><is><t>Lekiem przeciwbakteryjnym o wąskim zakresie działania przeciwbakteryjnego jest:</t></is></c><c r="F203" s="2" t="inlineStr"><is><t>fenoksymetylopenicylina</t></is></c><c r="G203" s="2" t="inlineStr"><is><t>nystatyna</t></is></c><c r="H203" s="2" t="inlineStr" /><c r="I203" s="2" t="inlineStr" /><c r="J203" s="2" t="inlineStr" /><c r="K203" s="2" t="inlineStr"><is><t>aksetyl cefuroksymu</t></is></c><c r="L203" s="2" t="inlineStr"><is><t>chloramfenikol</t></is></c><c r="M203" s="2" t="inlineStr" /><c r="N203" s="2" t="inlineStr" /><c r="O203" s="2" t="inlineStr" /><c r="P203" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q203" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="204"><c r="A204" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B204" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C204" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D204" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E204" s="2" t="inlineStr"><is><t>Aktywność przeciwbakteryjną względem opornych na metycylinę szczepów Staphylococcus aureus (MRSA) ma:</t></is></c><c r="F204" s="2" t="inlineStr"><is><t>linezolid</t></is></c><c r="G204" s="2" t="inlineStr"><is><t>mupirocyna</t></is></c><c r="H204" s="2" t="inlineStr"><is><t>wankomycyna</t></is></c><c r="I204" s="2" t="inlineStr"><is><t>dalfoprystyna/chinuprystyna</t></is></c><c r="J204" s="2" t="inlineStr" /><c r="K204" s="2" t="inlineStr" /><c r="L204" s="2" t="inlineStr" /><c r="M204" s="2" t="inlineStr" /><c r="N204" s="2" t="inlineStr" /><c r="O204" s="2" t="inlineStr" /><c r="P204" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q204" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="205"><c r="A205" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B205" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C205" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D205" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E205" s="2" t="inlineStr"><is><t>Profilaktyka infekcyjnego zapalenia wsierdzia (IZW) jest wskazana u osób z grup wysokiego ryzyka IZW w przypadku procedur:</t></is></c><c r="F205" s="2" t="inlineStr"><is><t>dentystycznych z manipulacją w obrębie dziąseł lub okolicy około-wierzchołkowej zębów</t></is></c><c r="G205" s="2" t="inlineStr"><is><t>inwazyjnych w obrębie górnych dróg oddechowych, tj. usunięcie migdałka</t></is></c><c r="H205" s="2" t="inlineStr" /><c r="I205" s="2" t="inlineStr" /><c r="J205" s="2" t="inlineStr" /><c r="K205" s="2" t="inlineStr"><is><t>inwazyjnych w obrębie układu moczowo-płciowego</t></is></c><c r="L205" s="2" t="inlineStr"><is><t>inwazyjnych w obrębie przewodu pokarmowego</t></is></c><c r="M205" s="2" t="inlineStr" /><c r="N205" s="2" t="inlineStr" /><c r="O205" s="2" t="inlineStr" /><c r="P205" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q205" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="206"><c r="A206" s="2" t="inlineStr"><is><t>LEKI PRZECIWWIRUSOWE</t></is></c><c r="B206" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C206" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D206" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E206" s="2" t="inlineStr"><is><t>Gancyklowir:</t></is></c><c r="F206" s="2" t="inlineStr"><is><t>może powodować uszkodzenie szpiku</t></is></c><c r="G206" s="2" t="inlineStr" /><c r="H206" s="2" t="inlineStr" /><c r="I206" s="2" t="inlineStr" /><c r="J206" s="2" t="inlineStr" /><c r="K206" s="2" t="inlineStr"><is><t>jest inhibitorem proteazy wirusowej</t></is></c><c r="L206" s="2" t="inlineStr"><is><t>bezpośrednio hamuje uwalnianie wirusów z zakażonych komórek</t></is></c><c r="M206" s="2" t="inlineStr"><is><t>nie przenika do ośrodkowego układu nerwowego</t></is></c><c r="N206" s="2" t="inlineStr" /><c r="O206" s="2" t="inlineStr" /><c r="P206" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q206" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="207"><c r="A207" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B207" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C207" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D207" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E207" s="2" t="inlineStr"><is><t>W standardowej profilaktyce okołooperacyjnej wskazane jest stosowanie:</t></is></c><c r="F207" s="2" t="inlineStr"><is><t>wankomycyny</t></is></c><c r="G207" s="2" t="inlineStr"><is><t>metronidazolu</t></is></c><c r="H207" s="2" t="inlineStr"><is><t>cyprofloksacyny</t></is></c><c r="I207" s="2" t="inlineStr"><is><t>cefazoliny</t></is></c><c r="J207" s="2" t="inlineStr" /><c r="K207" s="2" t="inlineStr" /><c r="L207" s="2" t="inlineStr" /><c r="M207" s="2" t="inlineStr" /><c r="N207" s="2" t="inlineStr" /><c r="O207" s="2" t="inlineStr" /><c r="P207" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q207" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="208"><c r="A208" s="2" t="inlineStr"><is><t>LEKI PRZECIWGRZYBICZE</t></is></c><c r="B208" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C208" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D208" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E208" s="2" t="inlineStr"><is><t>W grzybiczym zakażeniu skóry gładkiej można zastosować miejscowo:</t></is></c><c r="F208" s="2" t="inlineStr"><is><t>cyklopiroksolaminę</t></is></c><c r="G208" s="2" t="inlineStr"><is><t>natamycynę</t></is></c><c r="H208" s="2" t="inlineStr"><is><t>klotrimazol</t></is></c><c r="I208" s="2" t="inlineStr" /><c r="J208" s="2" t="inlineStr" /><c r="K208" s="2" t="inlineStr"><is><t>kaspofunginę</t></is></c><c r="L208" s="2" t="inlineStr" /><c r="M208" s="2" t="inlineStr" /><c r="N208" s="2" t="inlineStr" /><c r="O208" s="2" t="inlineStr" /><c r="P208" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q208" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="209"><c r="A209" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B209" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C209" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D209" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E209" s="2" t="inlineStr"><is><t>Wskaż poprawną strategię postępowania w zakresie leczenia zakażeń:</t></is></c><c r="F209" s="2" t="inlineStr"><is><t>leczenie empiryczne powinno uwzględniać miejsce powstania zakażenia: domowe lub związane z kontaktem ze służbą zdrowia</t></is></c><c r="G209" s="2" t="inlineStr"><is><t>na podstawie antybiogramu należy dokonać deeskalacji leczenia</t></is></c><c r="H209" s="2" t="inlineStr"><is><t>zasadą jest doustne leczenie przeciwinfekcyjne poza uzasadnionymi wyjątkami poza dekolonizacją MRSA przed operacjami</t></is></c><c r="I209" s="2" t="inlineStr" /><c r="J209" s="2" t="inlineStr" /><c r="K209" s="2" t="inlineStr" /><c r="L209" s="2" t="inlineStr" /><c r="M209" s="2" t="inlineStr" /><c r="N209" s="2" t="inlineStr" /><c r="O209" s="2" t="inlineStr" /><c r="P209" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q209" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="210"><c r="A210" s="2" t="inlineStr"><is><t>LEKI PRZECIWNOWOTWOROWE</t></is></c><c r="B210" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C210" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D210" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E210" s="2" t="inlineStr"><is><t>W Polsce granica opłacalności procedur medycznych jest:</t></is></c><c r="F210" s="2" t="inlineStr"><is><t>wykorzystywanym i usankcjonowanym prawnie kryterium refundacyjnym</t></is></c><c r="G210" s="2" t="inlineStr"><is><t>ustalona w oparciu o roczny koszt dializoterapii – przewlekłej, powszechnej i jednej z najdroższych procedur medycznych</t></is></c><c r="H210" s="2" t="inlineStr"><is><t>ustalona w oparciu o 3 krotność produktu krajowego brutto per capita</t></is></c><c r="I210" s="2" t="inlineStr"><is><t>odmienna dla leków stosowanych w chorobach onkologicznych</t></is></c><c r="J210" s="2" t="inlineStr" /><c r="K210" s="2" t="inlineStr" /><c r="L210" s="2" t="inlineStr" /><c r="M210" s="2" t="inlineStr" /><c r="N210" s="2" t="inlineStr" /><c r="O210" s="2" t="inlineStr" /><c r="P210" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q210" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="211"><c r="A211" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B211" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C211" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D211" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E211" s="2" t="inlineStr"><is><t>W leczeniu trądziku młodzieńczego racjonalne jest zastosowanie:</t></is></c><c r="F211" s="2" t="inlineStr"><is><t>klindamycyny</t></is></c><c r="G211" s="2" t="inlineStr"><is><t>doksycykliny</t></is></c><c r="H211" s="2" t="inlineStr"><is><t>izotretinoiny</t></is></c><c r="I211" s="2" t="inlineStr" /><c r="J211" s="2" t="inlineStr" /><c r="K211" s="2" t="inlineStr"><is><t>norfloksacyny</t></is></c><c r="L211" s="2" t="inlineStr" /><c r="M211" s="2" t="inlineStr" /><c r="N211" s="2" t="inlineStr" /><c r="O211" s="2" t="inlineStr" /><c r="P211" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q211" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="212"><c r="A212" s="2" t="inlineStr"><is><t>LEKI PRZECIWWIRUSOWE</t></is></c><c r="B212" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C212" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D212" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E212" s="2" t="inlineStr"><is><t>Istotne genetycznie uwarunkowane różnice działania stwierdzono dla:</t></is></c><c r="F212" s="2" t="inlineStr"><is><t>abakawiru</t></is></c><c r="G212" s="2" t="inlineStr"><is><t>karbamazepiny</t></is></c><c r="H212" s="2" t="inlineStr"><is><t>warfaryny</t></is></c><c r="I212" s="2" t="inlineStr" /><c r="J212" s="2" t="inlineStr" /><c r="K212" s="2" t="inlineStr"><is><t>diltiazemu</t></is></c><c r="L212" s="2" t="inlineStr" /><c r="M212" s="2" t="inlineStr" /><c r="N212" s="2" t="inlineStr" /><c r="O212" s="2" t="inlineStr" /><c r="P212" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q212" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="213"><c r="A213" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B213" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C213" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D213" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E213" s="2" t="inlineStr"><is><t>Inhibitory dipeptydylopeptydazy IV (DPP IV):</t></is></c><c r="F213" s="2" t="inlineStr"><is><t>mogą być stosowane łącznie z insuliną</t></is></c><c r="G213" s="2" t="inlineStr"><is><t>zwiększają ryzyko wystąpienia dolegliwości ze strony przewodu pokarmowego</t></is></c><c r="H213" s="2" t="inlineStr" /><c r="I213" s="2" t="inlineStr" /><c r="J213" s="2" t="inlineStr" /><c r="K213" s="2" t="inlineStr"><is><t>powodują przyrost masy ciała</t></is></c><c r="L213" s="2" t="inlineStr"><is><t>są podawane podskórnie</t></is></c><c r="M213" s="2" t="inlineStr" /><c r="N213" s="2" t="inlineStr" /><c r="O213" s="2" t="inlineStr" /><c r="P213" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q213" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="214"><c r="A214" s="2" t="inlineStr"><is><t>CUKRZYCA</t></is></c><c r="B214" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C214" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D214" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E214" s="2" t="inlineStr"><is><t>Wskaż zdanie/zdania prawdziwe:</t></is></c><c r="F214" s="2" t="inlineStr"><is><t>empagliflozyna – zmniejsza ryzyko śmierci z przyczyn sercowo￾naczyniowych u chorych z cukrzycą typu 2</t></is></c><c r="G214" s="2" t="inlineStr"><is><t>metformina – zmniejsza ryzyko powikłań makroangiopatycznych</t></is></c><c r="H214" s="2" t="inlineStr" /><c r="I214" s="2" t="inlineStr" /><c r="J214" s="2" t="inlineStr" /><c r="K214" s="2" t="inlineStr"><is><t>sitagliptyna - pomimo euglikemii może spowodować kwasicę ketonową</t></is></c><c r="L214" s="2" t="inlineStr"><is><t>gliklazyd – powoduje redukcję masy ciała</t></is></c><c r="M214" s="2" t="inlineStr" /><c r="N214" s="2" t="inlineStr" /><c r="O214" s="2" t="inlineStr" /><c r="P214" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q214" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="215"><c r="A215" s="2" t="inlineStr"><is><t>TARCZYCA</t></is></c><c r="B215" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C215" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D215" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E215" s="2" t="inlineStr"><is><t>Stosowanie tiamazolu może być przyczyną:</t></is></c><c r="F215" s="2" t="inlineStr"><is><t>żółtaczki cholestatycznej</t></is></c><c r="G215" s="2" t="inlineStr"><is><t>agranulocytozy</t></is></c><c r="H215" s="2" t="inlineStr"><is><t>wysypki skórnej</t></is></c><c r="I215" s="2" t="inlineStr"><is><t>niedoczynności tarczycy</t></is></c><c r="J215" s="2" t="inlineStr" /><c r="K215" s="2" t="inlineStr" /><c r="L215" s="2" t="inlineStr" /><c r="M215" s="2" t="inlineStr" /><c r="N215" s="2" t="inlineStr" /><c r="O215" s="2" t="inlineStr" /><c r="P215" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q215" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="216"><c r="A216" s="2" t="inlineStr"><is><t>UKŁAD PRZYWSPÓŁCZULNY</t></is></c><c r="B216" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C216" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D216" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E216" s="2" t="inlineStr"><is><t>Leczenie triamcynolonem może pogorszyć przebieg:</t></is></c><c r="F216" s="2" t="inlineStr"><is><t>jaskry</t></is></c><c r="G216" s="2" t="inlineStr"><is><t>zaburzeń nastroju</t></is></c><c r="H216" s="2" t="inlineStr"><is><t>zaćmy</t></is></c><c r="I216" s="2" t="inlineStr"><is><t>osteoporozy</t></is></c><c r="J216" s="2" t="inlineStr" /><c r="K216" s="2" t="inlineStr" /><c r="L216" s="2" t="inlineStr" /><c r="M216" s="2" t="inlineStr" /><c r="N216" s="2" t="inlineStr" /><c r="O216" s="2" t="inlineStr" /><c r="P216" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q216" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="217"><c r="A217" s="2" t="inlineStr"><is><t>CUKRZYCA</t></is></c><c r="B217" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C217" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D217" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E217" s="2" t="inlineStr"><is><t>Pacjent nieprzytomny, z hipoglikemią po spożyciu alkoholu, powinien otrzymać:</t></is></c><c r="F217" s="2" t="inlineStr"><is><t>20% roztwór glukozy i.v</t></is></c><c r="G217" s="2" t="inlineStr" /><c r="H217" s="2" t="inlineStr" /><c r="I217" s="2" t="inlineStr" /><c r="J217" s="2" t="inlineStr" /><c r="K217" s="2" t="inlineStr"><is><t>glukagon i.m</t></is></c><c r="L217" s="2" t="inlineStr"><is><t>glukozę p.o</t></is></c><c r="M217" s="2" t="inlineStr"><is><t>glukagon s.c</t></is></c><c r="N217" s="2" t="inlineStr" /><c r="O217" s="2" t="inlineStr" /><c r="P217" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q217" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="218"><c r="A218" s="2" t="inlineStr"><is><t>OSTEOPOROZA</t></is></c><c r="B218" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C218" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D218" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E218" s="2" t="inlineStr"><is><t>Potwierdzone klinicznie zmniejszenie ryzyka złamania kości udowej w przebiegu osteoporozy występuje w wyniku leczenia:</t></is></c><c r="F218" s="2" t="inlineStr"><is><t>ranelinianem strontu</t></is></c><c r="G218" s="2" t="inlineStr"><is><t>kwasem ibandronowy</t></is></c><c r="H218" s="2" t="inlineStr" /><c r="I218" s="2" t="inlineStr" /><c r="J218" s="2" t="inlineStr" /><c r="K218" s="2" t="inlineStr"><is><t>raloksyfenem</t></is></c><c r="L218" s="2" t="inlineStr"><is><t>kalcytoniną</t></is></c><c r="M218" s="2" t="inlineStr" /><c r="N218" s="2" t="inlineStr" /><c r="O218" s="2" t="inlineStr" /><c r="P218" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q218" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="219"><c r="A219" s="2" t="inlineStr"><is><t>GLIKOKORTYKOSTEROIDY</t></is></c><c r="B219" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C219" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D219" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E219" s="2" t="inlineStr"><is><t>Wskaż prawidłowe połączenie - wskazanie do stosowania glikokortykosteroidów - uzasadnienie zastosowania:</t></is></c><c r="F219" s="2" t="inlineStr"><is><t>poród przedwczesny – stymulowanie dojrzewania płuc płodu</t></is></c><c r="G219" s="2" t="inlineStr"><is><t>astma – ograniczenie procesu zapalnego</t></is></c><c r="H219" s="2" t="inlineStr"><is><t>przełom nadnerczowy – leczenie substytucyjne</t></is></c><c r="I219" s="2" t="inlineStr" /><c r="J219" s="2" t="inlineStr" /><c r="K219" s="2" t="inlineStr"><is><t>mononukleoza zakaźna – efekt immunosupresyjny</t></is></c><c r="L219" s="2" t="inlineStr" /><c r="M219" s="2" t="inlineStr" /><c r="N219" s="2" t="inlineStr" /><c r="O219" s="2" t="inlineStr" /><c r="P219" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q219" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="220"><c r="A220" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B220" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C220" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D220" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E220" s="2" t="inlineStr"><is><t>Do działań niepożądanych środków antykoncepcyjnych zalicza się:</t></is></c><c r="F220" s="2" t="inlineStr"><is><t>trądzik</t></is></c><c r="G220" s="2" t="inlineStr"><is><t>depresję</t></is></c><c r="H220" s="2" t="inlineStr"><is><t>zwiększenie ryzyka udaru mózgu</t></is></c><c r="I220" s="2" t="inlineStr" /><c r="J220" s="2" t="inlineStr" /><c r="K220" s="2" t="inlineStr"><is><t>zwiększenie ryzyka raka jajnika</t></is></c><c r="L220" s="2" t="inlineStr" /><c r="M220" s="2" t="inlineStr" /><c r="N220" s="2" t="inlineStr" /><c r="O220" s="2" t="inlineStr" /><c r="P220" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q220" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="221"><c r="A221" s="2" t="inlineStr"><is><t>TARCZYCA</t></is></c><c r="B221" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C221" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D221" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E221" s="2" t="inlineStr"><is><t>Witamina D3 (cholekalcyferol):</t></is></c><c r="F221" s="2" t="inlineStr"><is><t>może być stosowana w niedoczynności przytarczyc</t></is></c><c r="G221" s="2" t="inlineStr"><is><t>w nadmiarze hamuje wzrost kości</t></is></c><c r="H221" s="2" t="inlineStr" /><c r="I221" s="2" t="inlineStr" /><c r="J221" s="2" t="inlineStr" /><c r="K221" s="2" t="inlineStr"><is><t>mimo stosowania w dużych dawkach nie chroni przed osteoporotycznymi złamaniami kości</t></is></c><c r="L221" s="2" t="inlineStr"><is><t>jest nieaktywna u chorych z niewydolnością nerek</t></is></c><c r="M221" s="2" t="inlineStr" /><c r="N221" s="2" t="inlineStr" /><c r="O221" s="2" t="inlineStr" /><c r="P221" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q221" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="222"><c r="A222" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B222" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C222" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D222" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E222" s="2" t="inlineStr"><is><t>Działanie przeczyszczające wykazuje:</t></is></c><c r="F222" s="2" t="inlineStr"><is><t>siarczan magnezu</t></is></c><c r="G222" s="2" t="inlineStr"><is><t>dokusan sodowy</t></is></c><c r="H222" s="2" t="inlineStr" /><c r="I222" s="2" t="inlineStr" /><c r="J222" s="2" t="inlineStr" /><c r="K222" s="2" t="inlineStr"><is><t>werapamil</t></is></c><c r="L222" s="2" t="inlineStr"><is><t>racekadotryl</t></is></c><c r="M222" s="2" t="inlineStr" /><c r="N222" s="2" t="inlineStr" /><c r="O222" s="2" t="inlineStr" /><c r="P222" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q222" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="223"><c r="A223" s="2" t="inlineStr"><is><t>LEKI PRZECIWNOWOTWOROWE</t></is></c><c r="B223" s="2" t="inlineStr"><is><t>Antidotum</t></is></c><c r="C223" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D223" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E223" s="2" t="inlineStr"><is><t>Mesna :</t></is></c><c r="F223" s="2" t="inlineStr"><is><t>powoduje upłynnienie wydzieliny w drzewie oskrzelowym</t></is></c><c r="G223" s="2" t="inlineStr"><is><t>jest antidotum przeciw metabolitowi cyklofosfamidu drażniącemu błonę śluzową dróg moczowych</t></is></c><c r="H223" s="2" t="inlineStr"><is><t>jest stosowana miejscowo w postaci inhalacji</t></is></c><c r="I223" s="2" t="inlineStr"><is><t>może wywołać skurcz oskrzeli</t></is></c><c r="J223" s="2" t="inlineStr" /><c r="K223" s="2" t="inlineStr" /><c r="L223" s="2" t="inlineStr" /><c r="M223" s="2" t="inlineStr" /><c r="N223" s="2" t="inlineStr" /><c r="O223" s="2" t="inlineStr" /><c r="P223" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q223" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="224"><c r="A224" s="2" t="inlineStr"><is><t>ZNIECZULENIA MIEJSCOWE</t></is></c><c r="B224" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C224" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D224" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E224" s="2" t="inlineStr"><is><t>Do leków znieczulających miejscowo stosowanych na błony śluzowe należy:</t></is></c><c r="F224" s="2" t="inlineStr"><is><t>prylokaina</t></is></c><c r="G224" s="2" t="inlineStr"><is><t>lidokaina</t></is></c><c r="H224" s="2" t="inlineStr" /><c r="I224" s="2" t="inlineStr" /><c r="J224" s="2" t="inlineStr" /><c r="K224" s="2" t="inlineStr"><is><t>chlorek etylu</t></is></c><c r="L224" s="2" t="inlineStr"><is><t>kapsaicyna</t></is></c><c r="M224" s="2" t="inlineStr" /><c r="N224" s="2" t="inlineStr" /><c r="O224" s="2" t="inlineStr" /><c r="P224" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q224" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="225"><c r="A225" s="2" t="inlineStr"><is><t>LEKI PRZECIWNOWOTWOROWE</t></is></c><c r="B225" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C225" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D225" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E225" s="2" t="inlineStr"><is><t>Inhibitorem kinaz białkowych jest:</t></is></c><c r="F225" s="2" t="inlineStr"><is><t>rapamycyna</t></is></c><c r="G225" s="2" t="inlineStr"><is><t>imatynib</t></is></c><c r="H225" s="2" t="inlineStr" /><c r="I225" s="2" t="inlineStr" /><c r="J225" s="2" t="inlineStr" /><c r="K225" s="2" t="inlineStr"><is><t>bortezomib</t></is></c><c r="L225" s="2" t="inlineStr"><is><t>lenalidomid</t></is></c><c r="M225" s="2" t="inlineStr" /><c r="N225" s="2" t="inlineStr" /><c r="O225" s="2" t="inlineStr" /><c r="P225" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q225" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="226"><c r="A226" s="2" t="inlineStr"><is><t>LEKI PRZECIWHISTAMINOWE</t></is></c><c r="B226" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C226" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D226" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E226" s="2" t="inlineStr"><is><t>Betahistyna:</t></is></c><c r="F226" s="2" t="inlineStr"><is><t>zwiększa przepływ krwi w uchu wewnętrznym</t></is></c><c r="G226" s="2" t="inlineStr"><is><t>jest stosowana w leczeniu choroby Méniére'a</t></is></c><c r="H226" s="2" t="inlineStr" /><c r="I226" s="2" t="inlineStr" /><c r="J226" s="2" t="inlineStr" /><c r="K226" s="2" t="inlineStr"><is><t>jest agonistą receptorów H3</t></is></c><c r="L226" s="2" t="inlineStr"><is><t>jest lekiem z wyboru w przedsionkowych zawrotach głowy</t></is></c><c r="M226" s="2" t="inlineStr" /><c r="N226" s="2" t="inlineStr" /><c r="O226" s="2" t="inlineStr" /><c r="P226" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q226" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="227"><c r="A227" s="2" t="inlineStr"><is><t>PADACZKA</t></is></c><c r="B227" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C227" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D227" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E227" s="2" t="inlineStr"><is><t>Lekiem stosowanym w neuropatii popółpaścowej jest:</t></is></c><c r="F227" s="2" t="inlineStr"><is><t>amitryptylina</t></is></c><c r="G227" s="2" t="inlineStr"><is><t>pregabalina</t></is></c><c r="H227" s="2" t="inlineStr"><is><t>lidokaina</t></is></c><c r="I227" s="2" t="inlineStr"><is><t>gabapentyna</t></is></c><c r="J227" s="2" t="inlineStr" /><c r="K227" s="2" t="inlineStr" /><c r="L227" s="2" t="inlineStr" /><c r="M227" s="2" t="inlineStr" /><c r="N227" s="2" t="inlineStr" /><c r="O227" s="2" t="inlineStr" /><c r="P227" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q227" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="228"><c r="A228" s="2" t="inlineStr"><is><t>NARKOTYCZNE LEKI PRZECIWBÓLOWE</t></is></c><c r="B228" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C228" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D228" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E228" s="2" t="inlineStr"><is><t>Na drugim stopniu drabiny analgetycznej wg WHO znajduje się:</t></is></c><c r="F228" s="2" t="inlineStr"><is><t>morfina w dawce ≤ 30 mg/dobę</t></is></c><c r="G228" s="2" t="inlineStr"><is><t>kodeina w dawce ≤360 mg/dobę</t></is></c><c r="H228" s="2" t="inlineStr"><is><t>oksykodon w dawce ≤20 mg/dobę</t></is></c><c r="I228" s="2" t="inlineStr" /><c r="J228" s="2" t="inlineStr" /><c r="K228" s="2" t="inlineStr"><is><t>fentanyl w dawce ≤ 10 mg/dobę</t></is></c><c r="L228" s="2" t="inlineStr" /><c r="M228" s="2" t="inlineStr" /><c r="N228" s="2" t="inlineStr" /><c r="O228" s="2" t="inlineStr" /><c r="P228" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q228" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="229"><c r="A229" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B229" s="2" t="inlineStr"><is><t>Farmakokinetyka</t></is></c><c r="C229" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D229" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E229" s="2" t="inlineStr"><is><t>Wskaż prawidłowe zdanie:</t></is></c><c r="F229" s="2" t="inlineStr"><is><t>czas odstawienia rywaroksabanu przed planowanym zabiegiem chirurgicznym zależy od ryzyka krwawienia</t></is></c><c r="G229" s="2" t="inlineStr"><is><t>jeśli uzyskano stabilną hemostazę antagonisty witaminy K włącza się w 1. dobie po zabiegu chirurgicznym</t></is></c><c r="H229" s="2" t="inlineStr" /><c r="I229" s="2" t="inlineStr" /><c r="J229" s="2" t="inlineStr" /><c r="K229" s="2" t="inlineStr"><is><t>warfaryny nie należy odstawiać wcześniej niż na 2 dni przed planowanym zabiegiem chirurgicznym</t></is></c><c r="L229" s="2" t="inlineStr"><is><t>czas odstawienia edoksabanu przed zabiegiem chirurgicznym nie zależy od wartości klirensu kreatyniny</t></is></c><c r="M229" s="2" t="inlineStr" /><c r="N229" s="2" t="inlineStr" /><c r="O229" s="2" t="inlineStr" /><c r="P229" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q229" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="230"><c r="A230" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B230" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C230" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D230" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E230" s="2" t="inlineStr"><is><t>Wskaż prawidłowy lek przeciwzakrzepowego u osoby z:</t></is></c><c r="F230" s="2" t="inlineStr"><is><t>zapaleniem żył głębokich - rywaroksaban</t></is></c><c r="G230" s="2" t="inlineStr"><is><t>ciążą - enoksaparyna</t></is></c><c r="H230" s="2" t="inlineStr"><is><t>mechaniczną zastawką serca – warfaryna</t></is></c><c r="I230" s="2" t="inlineStr" /><c r="J230" s="2" t="inlineStr" /><c r="K230" s="2" t="inlineStr"><is><t>niewydolnością nerek (CCr &lt;30ml/min) – dabigatran</t></is></c><c r="L230" s="2" t="inlineStr" /><c r="M230" s="2" t="inlineStr" /><c r="N230" s="2" t="inlineStr" /><c r="O230" s="2" t="inlineStr" /><c r="P230" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q230" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="231"><c r="A231" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B231" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C231" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D231" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E231" s="2" t="inlineStr"><is><t>Podczas leczenia przeciwzakrzepowego z zastosowaniem nadroparyny należy:</t></is></c><c r="F231" s="2" t="inlineStr"><is><t>kontrolować liczbę płytek</t></is></c><c r="G231" s="2" t="inlineStr"><is><t>rozważyć korektę dawek u osób otyłych</t></is></c><c r="H231" s="2" t="inlineStr" /><c r="I231" s="2" t="inlineStr" /><c r="J231" s="2" t="inlineStr" /><c r="K231" s="2" t="inlineStr"><is><t>monitorować dawki za pomocą oznaczenia APTT</t></is></c><c r="L231" s="2" t="inlineStr"><is><t>zmniejszyć dawkę w każdym przypadku, jeśli eGFR osiąga wartość mniejszą niż 90 ml/min</t></is></c><c r="M231" s="2" t="inlineStr" /><c r="N231" s="2" t="inlineStr" /><c r="O231" s="2" t="inlineStr" /><c r="P231" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q231" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="232"><c r="A232" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B232" s="2" t="inlineStr"><is><t>Sposób podania</t></is></c><c r="C232" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D232" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E232" s="2" t="inlineStr"><is><t>Kangrelor:</t></is></c><c r="F232" s="2" t="inlineStr"><is><t>jest wskazany podczas przezskórnych interwencji wieńcowych łącznie z kwasem acetylosalicylowym</t></is></c><c r="G232" s="2" t="inlineStr" /><c r="H232" s="2" t="inlineStr" /><c r="I232" s="2" t="inlineStr" /><c r="J232" s="2" t="inlineStr" /><c r="K232" s="2" t="inlineStr"><is><t>jest agonistą receptora P2Y12</t></is></c><c r="L232" s="2" t="inlineStr"><is><t>wymaga aktywacji w przewodzie pokarmowym</t></is></c><c r="M232" s="2" t="inlineStr"><is><t>działa przez 1-2 doby</t></is></c><c r="N232" s="2" t="inlineStr" /><c r="O232" s="2" t="inlineStr" /><c r="P232" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q232" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="233"><c r="A233" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B233" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C233" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D233" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E233" s="2" t="inlineStr"><is><t>Na istotnie zmniejszoną skuteczność doustnych antagonistów witaminy K może mieć wpływ spożywanie:</t></is></c><c r="F233" s="2" t="inlineStr"><is><t>szpinaku</t></is></c><c r="G233" s="2" t="inlineStr" /><c r="H233" s="2" t="inlineStr" /><c r="I233" s="2" t="inlineStr" /><c r="J233" s="2" t="inlineStr" /><c r="K233" s="2" t="inlineStr"><is><t>oleju rybnego zawierającego nienasycone kwasy tłuszczowe omega -3</t></is></c><c r="L233" s="2" t="inlineStr"><is><t>witaminy E</t></is></c><c r="M233" s="2" t="inlineStr"><is><t>czosnku</t></is></c><c r="N233" s="2" t="inlineStr" /><c r="O233" s="2" t="inlineStr" /><c r="P233" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q233" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="234"><c r="A234" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B234" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C234" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D234" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E234" s="2" t="inlineStr"><is><t>Pacjentom, którzy przebyli udar niedokrwienny mózgu należy zalecić profilaktykę wtórną. Do leków o udokumentowanym działaniu zmniejszających ryzyko następnego udaru należy:</t></is></c><c r="F234" s="2" t="inlineStr"><is><t>simwastatyna</t></is></c><c r="G234" s="2" t="inlineStr"><is><t>klopidogrel</t></is></c><c r="H234" s="2" t="inlineStr"><is><t>lizynopryl</t></is></c><c r="I234" s="2" t="inlineStr"><is><t>kwas acetylosalicylowy</t></is></c><c r="J234" s="2" t="inlineStr" /><c r="K234" s="2" t="inlineStr" /><c r="L234" s="2" t="inlineStr" /><c r="M234" s="2" t="inlineStr" /><c r="N234" s="2" t="inlineStr" /><c r="O234" s="2" t="inlineStr" /><c r="P234" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q234" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="235"><c r="A235" s="2" t="inlineStr"><is><t>LEKI HIPOLIPEMIZUJĄCE</t></is></c><c r="B235" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C235" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D235" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E235" s="2" t="inlineStr"><is><t>Fenofibrat:</t></is></c><c r="F235" s="2" t="inlineStr"><is><t>zmniejsza stężenie trójglicerydów i zwiększa stężenie cholesterolu HDL</t></is></c><c r="G235" s="2" t="inlineStr"><is><t>zwiększa ryzyko kamicy pęcherzyka żółciowego</t></is></c><c r="H235" s="2" t="inlineStr" /><c r="I235" s="2" t="inlineStr" /><c r="J235" s="2" t="inlineStr" /><c r="K235" s="2" t="inlineStr"><is><t>hamuje reduktazę 3-hydroksy-3-metyloglutarylo-CoA (HMG-CoA)</t></is></c><c r="L235" s="2" t="inlineStr"><is><t>nie może być stosowany w połączeniu ze statyną</t></is></c><c r="M235" s="2" t="inlineStr" /><c r="N235" s="2" t="inlineStr" /><c r="O235" s="2" t="inlineStr" /><c r="P235" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q235" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="236"><c r="A236" s="2" t="inlineStr"><is><t>LEKI MOCZOPĘDNE</t></is></c><c r="B236" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C236" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D236" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E236" s="2" t="inlineStr"><is><t>Hiperurykemię może spowodować:</t></is></c><c r="F236" s="2" t="inlineStr"><is><t>torasemid</t></is></c><c r="G236" s="2" t="inlineStr"><is><t>kwas acetylosalicylowy</t></is></c><c r="H236" s="2" t="inlineStr" /><c r="I236" s="2" t="inlineStr" /><c r="J236" s="2" t="inlineStr" /><c r="K236" s="2" t="inlineStr"><is><t>losartan</t></is></c><c r="L236" s="2" t="inlineStr"><is><t>allopurynol</t></is></c><c r="M236" s="2" t="inlineStr" /><c r="N236" s="2" t="inlineStr" /><c r="O236" s="2" t="inlineStr" /><c r="P236" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q236" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="237"><c r="A237" s="2" t="inlineStr"><is><t>ZABURZENIA RYTMU SERCA</t></is></c><c r="B237" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C237" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D237" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E237" s="2" t="inlineStr"><is><t>Odstęp QT mogą wydłużać:</t></is></c><c r="F237" s="2" t="inlineStr"><is><t>amiodaron</t></is></c><c r="G237" s="2" t="inlineStr"><is><t>sotalol</t></is></c><c r="H237" s="2" t="inlineStr" /><c r="I237" s="2" t="inlineStr" /><c r="J237" s="2" t="inlineStr" /><c r="K237" s="2" t="inlineStr"><is><t>propranolol</t></is></c><c r="L237" s="2" t="inlineStr"><is><t>diltiazem</t></is></c><c r="M237" s="2" t="inlineStr" /><c r="N237" s="2" t="inlineStr" /><c r="O237" s="2" t="inlineStr" /><c r="P237" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q237" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="238"><c r="A238" s="2" t="inlineStr"><is><t>NADCIŚNIENIE TĘTNICZE</t></is></c><c r="B238" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C238" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D238" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E238" s="2" t="inlineStr"><is><t>Indapamid:</t></is></c><c r="F238" s="2" t="inlineStr"><is><t>ma działanie naczyniorozszerzające</t></is></c><c r="G238" s="2" t="inlineStr"><is><t>może spowodować hiponatremię</t></is></c><c r="H238" s="2" t="inlineStr"><is><t>zmniejsza wydalanie wapnia z moczem</t></is></c><c r="I238" s="2" t="inlineStr"><is><t>jest chętnie stosowany w przewlekłej terapii nadciśnienia tętniczego u osób po 80 roku życia</t></is></c><c r="J238" s="2" t="inlineStr" /><c r="K238" s="2" t="inlineStr" /><c r="L238" s="2" t="inlineStr" /><c r="M238" s="2" t="inlineStr" /><c r="N238" s="2" t="inlineStr" /><c r="O238" s="2" t="inlineStr" /><c r="P238" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q238" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="239"><c r="A239" s="2" t="inlineStr"><is><t>LEKI ROŚLINNE I SUPLEMENTY</t></is></c><c r="B239" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C239" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D239" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E239" s="2" t="inlineStr"><is><t>Produkty biopodobne:</t></is></c><c r="F239" s="2" t="inlineStr"><is><t>są automatycznie zamienne (substytucja)</t></is></c><c r="G239" s="2" t="inlineStr"><is><t>muszą mieć potwierdzoną podobną immunogenność</t></is></c><c r="H239" s="2" t="inlineStr" /><c r="I239" s="2" t="inlineStr" /><c r="J239" s="2" t="inlineStr" /><c r="K239" s="2" t="inlineStr"><is><t>są rejestrowane w procedurze zdecentralizowanej</t></is></c><c r="L239" s="2" t="inlineStr"><is><t>po dopuszczeniu do obrotu mogą być stosowane we wszystkich wskazaniach zamiennie</t></is></c><c r="M239" s="2" t="inlineStr" /><c r="N239" s="2" t="inlineStr" /><c r="O239" s="2" t="inlineStr" /><c r="P239" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q239" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="240"><c r="A240" s="2" t="inlineStr"><is><t>LEKI PRZECIWPASOŻYTNICZE</t></is></c><c r="B240" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C240" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D240" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E240" s="2" t="inlineStr"><is><t>W leczeniu zarażenia glistą ludzką stosujemy:</t></is></c><c r="F240" s="2" t="inlineStr"><is><t>pyrantel</t></is></c><c r="G240" s="2" t="inlineStr"><is><t>albendazol</t></is></c><c r="H240" s="2" t="inlineStr" /><c r="I240" s="2" t="inlineStr" /><c r="J240" s="2" t="inlineStr" /><c r="K240" s="2" t="inlineStr"><is><t>tynidazol</t></is></c><c r="L240" s="2" t="inlineStr"><is><t>krotamiton</t></is></c><c r="M240" s="2" t="inlineStr" /><c r="N240" s="2" t="inlineStr" /><c r="O240" s="2" t="inlineStr" /><c r="P240" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q240" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="241"><c r="A241" s="2" t="inlineStr"><is><t>LEKI PRZECIWWIRUSOWE</t></is></c><c r="B241" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C241" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D241" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E241" s="2" t="inlineStr"><is><t>W leczeniu grypy zaleca się:</t></is></c><c r="F241" s="2" t="inlineStr"><is><t>zanamiwir</t></is></c><c r="G241" s="2" t="inlineStr"><is><t>oseltamiwir</t></is></c><c r="H241" s="2" t="inlineStr" /><c r="I241" s="2" t="inlineStr" /><c r="J241" s="2" t="inlineStr" /><c r="K241" s="2" t="inlineStr"><is><t>acyklowir</t></is></c><c r="L241" s="2" t="inlineStr"><is><t>foskarnet</t></is></c><c r="M241" s="2" t="inlineStr" /><c r="N241" s="2" t="inlineStr" /><c r="O241" s="2" t="inlineStr" /><c r="P241" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q241" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="242"><c r="A242" s="2" t="inlineStr"><is><t>UKŁAD ODDECHOWY</t></is></c><c r="B242" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C242" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D242" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E242" s="2" t="inlineStr"><is><t>W przypadku dotychczas nieleczonych chorych, u których objawy astmy oskrzelowej w ciągu dnia występują sporadycznie (&lt;2 razy w miesiącu), objawy nocne nie występują, nie ma czynników ryzyka zaostrzeń (także w wywiadzie), a czynność płuc jest prawidłowa należy zastosować:</t></is></c><c r="F242" s="2" t="inlineStr"><is><t>fenoterol doraźnie</t></is></c><c r="G242" s="2" t="inlineStr" /><c r="H242" s="2" t="inlineStr" /><c r="I242" s="2" t="inlineStr" /><c r="J242" s="2" t="inlineStr" /><c r="K242" s="2" t="inlineStr"><is><t>montelukast przewlekle</t></is></c><c r="L242" s="2" t="inlineStr"><is><t>regularnie małe dawki cyklezonidu</t></is></c><c r="M242" s="2" t="inlineStr"><is><t>teofilinę krótkodziałającą</t></is></c><c r="N242" s="2" t="inlineStr" /><c r="O242" s="2" t="inlineStr" /><c r="P242" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q242" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="243"><c r="A243" s="2" t="inlineStr"><is><t>UKŁAD PRZYWSPÓŁCZULNY</t></is></c><c r="B243" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C243" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D243" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E243" s="2" t="inlineStr"><is><t>Bromek glikopironium :</t></is></c><c r="F243" s="2" t="inlineStr"><is><t>wykazuje synergizm działania bronchodylatacyjnego z indakaterolem</t></is></c><c r="G243" s="2" t="inlineStr"><is><t>jest stosowany w leczeniu podtrzymującym w POChP</t></is></c><c r="H243" s="2" t="inlineStr" /><c r="I243" s="2" t="inlineStr" /><c r="J243" s="2" t="inlineStr" /><c r="K243" s="2" t="inlineStr"><is><t>jest wziewnym agonistą receptorów muskarynowych</t></is></c><c r="L243" s="2" t="inlineStr"><is><t>rozszczepia wiązania disiarczkowe w glikoproteinach śluzu</t></is></c><c r="M243" s="2" t="inlineStr" /><c r="N243" s="2" t="inlineStr" /><c r="O243" s="2" t="inlineStr" /><c r="P243" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q243" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="244"><c r="A244" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B244" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C244" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D244" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E244" s="2" t="inlineStr"><is><t>W leczeniu przewlekłego zapalenia trzustki celowe może być zastosowanie:</t></is></c><c r="F244" s="2" t="inlineStr"><is><t>suplementacji enzymów trzustkowych</t></is></c><c r="G244" s="2" t="inlineStr"><is><t>tramadolu</t></is></c><c r="H244" s="2" t="inlineStr"><is><t>pantoprazolu</t></is></c><c r="I244" s="2" t="inlineStr"><is><t>fluoksetyny</t></is></c><c r="J244" s="2" t="inlineStr" /><c r="K244" s="2" t="inlineStr" /><c r="L244" s="2" t="inlineStr" /><c r="M244" s="2" t="inlineStr" /><c r="N244" s="2" t="inlineStr" /><c r="O244" s="2" t="inlineStr" /><c r="P244" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q244" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="245"><c r="A245" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B245" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C245" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D245" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E245" s="2" t="inlineStr"><is><t>Profilaktyka przeciwmalaryczna w warunkach wysokiego ryzyka zakażenia Plasmodium falciparum obejmuje stosowanie:</t></is></c><c r="F245" s="2" t="inlineStr"><is><t>repelentów</t></is></c><c r="G245" s="2" t="inlineStr"><is><t>atowakwonu/proguanilu</t></is></c><c r="H245" s="2" t="inlineStr"><is><t>doksycykliny</t></is></c><c r="I245" s="2" t="inlineStr" /><c r="J245" s="2" t="inlineStr" /><c r="K245" s="2" t="inlineStr"><is><t>artemetru/lumefantryny</t></is></c><c r="L245" s="2" t="inlineStr" /><c r="M245" s="2" t="inlineStr" /><c r="N245" s="2" t="inlineStr" /><c r="O245" s="2" t="inlineStr" /><c r="P245" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q245" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="246"><c r="A246" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B246" s="2" t="inlineStr"><is><t>Przeciwwskazania</t></is></c><c r="C246" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D246" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E246" s="2" t="inlineStr"><is><t>Adalimumab:</t></is></c><c r="F246" s="2" t="inlineStr"><is><t>jest rekombinowanym w pełni ludzkim przeciwciałem monoklonalnym</t></is></c><c r="G246" s="2" t="inlineStr"><is><t>neutralizuje biologiczną czynność TNF</t></is></c><c r="H246" s="2" t="inlineStr"><is><t>jest przeciwwskazany w ciężkich zakażeniach</t></is></c><c r="I246" s="2" t="inlineStr" /><c r="J246" s="2" t="inlineStr" /><c r="K246" s="2" t="inlineStr"><is><t>jest wytwarzany z użyciem komórek zwierzęcych, co wiadomo na podstawie ujednoliconych zasad nadawania nazw przeciwciałom monoklonalnym</t></is></c><c r="L246" s="2" t="inlineStr" /><c r="M246" s="2" t="inlineStr" /><c r="N246" s="2" t="inlineStr" /><c r="O246" s="2" t="inlineStr" /><c r="P246" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q246" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="247"><c r="A247" s="2" t="inlineStr"><is><t>CUKRZYCA</t></is></c><c r="B247" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C247" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D247" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E247" s="2" t="inlineStr"><is><t>Dla insuliny aspart u pacjentów z umiarkowaną i ciężką niewydolnością wątroby stwierdzono: t max = ok. 85 min (tmax = ok. 40 minut u pacjentów z prawidłową czynnością wątroby); AUC, Cmax i CL/F były podobne do pacjentów z prawidłową czynnością wątroby. Na tej podstawie u osób z niewydolnością wątroby uzasadnione jest:</t></is></c><c r="F247" s="2" t="inlineStr"><is><t>wcześniejsze podanie leku przed posiłkiem</t></is></c><c r="G247" s="2" t="inlineStr"><is><t>stosowanie leku u osób z 7-15 pkt wg skali Childa-Pugha</t></is></c><c r="H247" s="2" t="inlineStr" /><c r="I247" s="2" t="inlineStr" /><c r="J247" s="2" t="inlineStr" /><c r="K247" s="2" t="inlineStr"><is><t>wyłącznie dożylne podawanie leku</t></is></c><c r="L247" s="2" t="inlineStr"><is><t>redukcja dawki początkowej o ½ oszacowanej na podstawie m.c. i wyjściowej glikemii</t></is></c><c r="M247" s="2" t="inlineStr" /><c r="N247" s="2" t="inlineStr" /><c r="O247" s="2" t="inlineStr" /><c r="P247" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q247" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="248"><c r="A248" s="2" t="inlineStr"><is><t>NADCIŚNIENIE TĘTNICZE</t></is></c><c r="B248" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C248" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D248" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E248" s="2" t="inlineStr"><is><t>Wartości ciśnienia tętniczego mogą się zwiększyć po włączeniu:</t></is></c><c r="F248" s="2" t="inlineStr"><is><t>metyloprednizolonu</t></is></c><c r="G248" s="2" t="inlineStr"><is><t>diklofenaku</t></is></c><c r="H248" s="2" t="inlineStr" /><c r="I248" s="2" t="inlineStr" /><c r="J248" s="2" t="inlineStr" /><c r="K248" s="2" t="inlineStr"><is><t>eplerenonu</t></is></c><c r="L248" s="2" t="inlineStr"><is><t>urapidylu</t></is></c><c r="M248" s="2" t="inlineStr" /><c r="N248" s="2" t="inlineStr" /><c r="O248" s="2" t="inlineStr" /><c r="P248" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q248" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="249"><c r="A249" s="2" t="inlineStr"><is><t>CHOROBA NIEDOKRWIENNA SERCA</t></is></c><c r="B249" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C249" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D249" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E249" s="2" t="inlineStr"><is><t>Farmakoterapię otyłości należy rozważyć, gdy:</t></is></c><c r="F249" s="2" t="inlineStr"><is><t>BMI&gt; 27 kg/m2 i glikemia na czczo &gt;100mg/dl</t></is></c><c r="G249" s="2" t="inlineStr"><is><t>BMI≥ 30 kg/m2 i stwierdzono ponowny wzrost masy ciała pomimo wdrożonych procedur niefarmakologicznych</t></is></c><c r="H249" s="2" t="inlineStr"><is><t>BMI&gt; 27 kg/m2 i SBP ≥160 mmHg</t></is></c><c r="I249" s="2" t="inlineStr" /><c r="J249" s="2" t="inlineStr" /><c r="K249" s="2" t="inlineStr"><is><t>BMI≥ 30 kg/m2, a wcześniejsze procedury niefarmakologiczne spowodowały redukcję masy ciała w przedziale 7-10 kg</t></is></c><c r="L249" s="2" t="inlineStr" /><c r="M249" s="2" t="inlineStr" /><c r="N249" s="2" t="inlineStr" /><c r="O249" s="2" t="inlineStr" /><c r="P249" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q249" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="250"><c r="A250" s="2" t="inlineStr"><is><t>CUKRZYCA</t></is></c><c r="B250" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C250" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D250" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E250" s="2" t="inlineStr"><is><t>Wzrost masy ciała mogą spowodować:</t></is></c><c r="F250" s="2" t="inlineStr"><is><t>chlorpromazyna</t></is></c><c r="G250" s="2" t="inlineStr"><is><t>insulina</t></is></c><c r="H250" s="2" t="inlineStr"><is><t>kwas walproinowy</t></is></c><c r="I250" s="2" t="inlineStr" /><c r="J250" s="2" t="inlineStr" /><c r="K250" s="2" t="inlineStr"><is><t>liraglutyd</t></is></c><c r="L250" s="2" t="inlineStr" /><c r="M250" s="2" t="inlineStr" /><c r="N250" s="2" t="inlineStr" /><c r="O250" s="2" t="inlineStr" /><c r="P250" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q250" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="251"><c r="A251" s="2" t="inlineStr"><is><t>NARKOTYCZNE LEKI PRZECIWBÓLOWE</t></is></c><c r="B251" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C251" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D251" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E251" s="2" t="inlineStr"><is><t>Który z leków istotnie zwiększa ryzyko napadów drgawkowych:</t></is></c><c r="F251" s="2" t="inlineStr"><is><t>tramadol</t></is></c><c r="G251" s="2" t="inlineStr"><is><t>amitryptylina</t></is></c><c r="H251" s="2" t="inlineStr"><is><t>prometazyna</t></is></c><c r="I251" s="2" t="inlineStr" /><c r="J251" s="2" t="inlineStr" /><c r="K251" s="2" t="inlineStr"><is><t>klorazepan</t></is></c><c r="L251" s="2" t="inlineStr" /><c r="M251" s="2" t="inlineStr" /><c r="N251" s="2" t="inlineStr" /><c r="O251" s="2" t="inlineStr" /><c r="P251" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q251" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="252"><c r="A252" s="2" t="inlineStr"><is><t>FARMAKOLOGIA OGÓLNA I EBM</t></is></c><c r="B252" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C252" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D252" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E252" s="2" t="inlineStr"><is><t>Zgoda komisji bioetycznej jest niezbędna, gdy planowane jest przeprowadzenie:</t></is></c><c r="F252" s="2" t="inlineStr"><is><t>badania klinicznego fazy III</t></is></c><c r="G252" s="2" t="inlineStr"><is><t>eksperymentu leczniczego</t></is></c><c r="H252" s="2" t="inlineStr"><is><t>badania klinicznego niekomercyjnego</t></is></c><c r="I252" s="2" t="inlineStr" /><c r="J252" s="2" t="inlineStr" /><c r="K252" s="2" t="inlineStr"><is><t>zastosowania leku off-label, ale zgodnie z aktualną wiedzą medyczną</t></is></c><c r="L252" s="2" t="inlineStr" /><c r="M252" s="2" t="inlineStr" /><c r="N252" s="2" t="inlineStr" /><c r="O252" s="2" t="inlineStr" /><c r="P252" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q252" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="253"><c r="A253" s="2" t="inlineStr"><is><t>LEKI PRZECIWWIRUSOWE</t></is></c><c r="B253" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C253" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D253" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E253" s="2" t="inlineStr"><is><t>W procedurze centralnej rejestruje się leki stosowane w:</t></is></c><c r="F253" s="2" t="inlineStr"><is><t>chorobach rzadkich</t></is></c><c r="G253" s="2" t="inlineStr"><is><t>terapii HIV</t></is></c><c r="H253" s="2" t="inlineStr"><is><t>terapii genowej</t></is></c><c r="I253" s="2" t="inlineStr" /><c r="J253" s="2" t="inlineStr" /><c r="K253" s="2" t="inlineStr"><is><t>populacji geriatrycznej</t></is></c><c r="L253" s="2" t="inlineStr" /><c r="M253" s="2" t="inlineStr" /><c r="N253" s="2" t="inlineStr" /><c r="O253" s="2" t="inlineStr" /><c r="P253" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q253" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="254"><c r="A254" s="2" t="inlineStr"><is><t>FARMAKOLOGIA OGÓLNA I EBM</t></is></c><c r="B254" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C254" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D254" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E254" s="2" t="inlineStr"><is><t>Pierwotnym źródłem wiedzy o lekach są:</t></is></c><c r="F254" s="2" t="inlineStr"><is><t>publikacje wyników badań klinicznych</t></is></c><c r="G254" s="2" t="inlineStr" /><c r="H254" s="2" t="inlineStr" /><c r="I254" s="2" t="inlineStr" /><c r="J254" s="2" t="inlineStr" /><c r="K254" s="2" t="inlineStr"><is><t>wytyczne praktyki klinicznej</t></is></c><c r="L254" s="2" t="inlineStr"><is><t>charakterystyki produktów leczniczych</t></is></c><c r="M254" s="2" t="inlineStr"><is><t>podręczniki farmakologii i indeksy leków</t></is></c><c r="N254" s="2" t="inlineStr" /><c r="O254" s="2" t="inlineStr" /><c r="P254" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q254" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="255"><c r="A255" s="2" t="inlineStr"><is><t>LEKI ROŚLINNE I SUPLEMENTY</t></is></c><c r="B255" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C255" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D255" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E255" s="2" t="inlineStr"><is><t>Wskazaniem do stosowania retinolu jest:</t></is></c><c r="F255" s="2" t="inlineStr"><is><t>łuszczyca</t></is></c><c r="G255" s="2" t="inlineStr"><is><t>niedowidzenie o zmierzchu</t></is></c><c r="H255" s="2" t="inlineStr" /><c r="I255" s="2" t="inlineStr" /><c r="J255" s="2" t="inlineStr" /><c r="K255" s="2" t="inlineStr"><is><t>polineuropatia obwodowa</t></is></c><c r="L255" s="2" t="inlineStr"><is><t>osteomalacja</t></is></c><c r="M255" s="2" t="inlineStr" /><c r="N255" s="2" t="inlineStr" /><c r="O255" s="2" t="inlineStr" /><c r="P255" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q255" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="256"><c r="A256" s="2" t="inlineStr"><is><t>CHOROBA NIEDOKRWIENNA SERCA</t></is></c><c r="B256" s="2" t="inlineStr"><is><t>Przeciwwskazania</t></is></c><c r="C256" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D256" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E256" s="2" t="inlineStr"><is><t>Feksofenadyna:</t></is></c><c r="F256" s="2" t="inlineStr"><is><t>jest podawana doustnie</t></is></c><c r="G256" s="2" t="inlineStr" /><c r="H256" s="2" t="inlineStr" /><c r="I256" s="2" t="inlineStr" /><c r="J256" s="2" t="inlineStr" /><c r="K256" s="2" t="inlineStr"><is><t>działa nieselektywnie na rec. H1</t></is></c><c r="L256" s="2" t="inlineStr"><is><t>przenika w znacznym stopniu przez barierę krew- mózg</t></is></c><c r="M256" s="2" t="inlineStr"><is><t>działa kardiotoksycznie i jest przeciwwskazana w chorobie niedokrwiennej serca</t></is></c><c r="N256" s="2" t="inlineStr" /><c r="O256" s="2" t="inlineStr" /><c r="P256" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q256" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="257"><c r="A257" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B257" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C257" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D257" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E257" s="2" t="inlineStr"><is><t>Wskaż wady dekstranów:</t></is></c><c r="F257" s="2" t="inlineStr"><is><t>utrudniają wiarygodne oznaczenie grupy krwi i próby krzyżowej</t></is></c><c r="G257" s="2" t="inlineStr"><is><t>są immunogenne</t></is></c><c r="H257" s="2" t="inlineStr" /><c r="I257" s="2" t="inlineStr" /><c r="J257" s="2" t="inlineStr" /><c r="K257" s="2" t="inlineStr"><is><t>powodują przyrost objętości wewnątrznaczyniowej przekraczający ich objętość</t></is></c><c r="L257" s="2" t="inlineStr"><is><t>działają prozakrzepowo</t></is></c><c r="M257" s="2" t="inlineStr" /><c r="N257" s="2" t="inlineStr" /><c r="O257" s="2" t="inlineStr" /><c r="P257" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q257" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="258"><c r="A258" s="2" t="inlineStr"><is><t>OTĘPIENIE</t></is></c><c r="B258" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C258" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D258" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E258" s="2" t="inlineStr"><is><t>Podanie rywastygminy jest uzasadnione u pacjentów z:</t></is></c><c r="F258" s="2" t="inlineStr"><is><t>otępieniem w przebiegu choroby Parkinsona</t></is></c><c r="G258" s="2" t="inlineStr"><is><t>chorobą Alzheimera</t></is></c><c r="H258" s="2" t="inlineStr" /><c r="I258" s="2" t="inlineStr" /><c r="J258" s="2" t="inlineStr" /><c r="K258" s="2" t="inlineStr"><is><t>otępieniem naczyniopochodnym</t></is></c><c r="L258" s="2" t="inlineStr"><is><t>otępieniem czołowo-skroniowym</t></is></c><c r="M258" s="2" t="inlineStr" /><c r="N258" s="2" t="inlineStr" /><c r="O258" s="2" t="inlineStr" /><c r="P258" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q258" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="259"><c r="A259" s="2" t="inlineStr"><is><t>LEKI PRZECIWLĘKOWE</t></is></c><c r="B259" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C259" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D259" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E259" s="2" t="inlineStr"><is><t>W alkoholowym zespole odstawiennym celowe może być zastosowanie:</t></is></c><c r="F259" s="2" t="inlineStr"><is><t>tiaminy</t></is></c><c r="G259" s="2" t="inlineStr"><is><t>diazepamu</t></is></c><c r="H259" s="2" t="inlineStr"><is><t>płynoterapia z suplementacją elektrolitów</t></is></c><c r="I259" s="2" t="inlineStr" /><c r="J259" s="2" t="inlineStr" /><c r="K259" s="2" t="inlineStr"><is><t>akamprozatu</t></is></c><c r="L259" s="2" t="inlineStr" /><c r="M259" s="2" t="inlineStr" /><c r="N259" s="2" t="inlineStr" /><c r="O259" s="2" t="inlineStr" /><c r="P259" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q259" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="260"><c r="A260" s="2" t="inlineStr"><is><t>LEKI IMMUNOSUPRESYJNE</t></is></c><c r="B260" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C260" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D260" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E260" s="2" t="inlineStr"><is><t>Mykofenolan mofetylu:</t></is></c><c r="F260" s="2" t="inlineStr"><is><t>jest wskazany w profilaktyce ostrego odrzucania przeszczepu serca</t></is></c><c r="G260" s="2" t="inlineStr"><is><t>zwiększa ryzyko wystąpienia nowotworów</t></is></c><c r="H260" s="2" t="inlineStr" /><c r="I260" s="2" t="inlineStr" /><c r="J260" s="2" t="inlineStr" /><c r="K260" s="2" t="inlineStr"><is><t>należy do inhibitorów mTOR</t></is></c><c r="L260" s="2" t="inlineStr"><is><t>stosowany w czasie ciąży jest bezpieczny dla płodu</t></is></c><c r="M260" s="2" t="inlineStr" /><c r="N260" s="2" t="inlineStr" /><c r="O260" s="2" t="inlineStr" /><c r="P260" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q260" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="261"><c r="A261" s="2" t="inlineStr"><is><t>NIEWYDOLNOŚĆ SERCA</t></is></c><c r="B261" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C261" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D261" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E261" s="2" t="inlineStr"><is><t>Iwabradyna:</t></is></c><c r="F261" s="2" t="inlineStr"><is><t>może powodować zaburzenia widzenia</t></is></c><c r="G261" s="2" t="inlineStr"><is><t>wybiórczo i swoiście wpływa na na prąd If rozrusznika serca</t></is></c><c r="H261" s="2" t="inlineStr" /><c r="I261" s="2" t="inlineStr" /><c r="J261" s="2" t="inlineStr" /><c r="K261" s="2" t="inlineStr"><is><t>obniża kurczliwość mięśnia sercowego</t></is></c><c r="L261" s="2" t="inlineStr"><is><t>wydłuża czas repolaryzacji komór</t></is></c><c r="M261" s="2" t="inlineStr" /><c r="N261" s="2" t="inlineStr" /><c r="O261" s="2" t="inlineStr" /><c r="P261" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q261" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="262"><c r="A262" s="2" t="inlineStr"><is><t>CHOROBA NIEDOKRWIENNA SERCA</t></is></c><c r="B262" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C262" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D262" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E262" s="2" t="inlineStr"><is><t>Monoazotan izosorbidu:</t></is></c><c r="F262" s="2" t="inlineStr"><is><t>jest skuteczny po podaniu doustnym</t></is></c><c r="G262" s="2" t="inlineStr"><is><t>poprawia ukrwienie obszarów podwsierdziowych serca</t></is></c><c r="H262" s="2" t="inlineStr" /><c r="I262" s="2" t="inlineStr" /><c r="J262" s="2" t="inlineStr" /><c r="K262" s="2" t="inlineStr"><is><t>podlega istotnemu efektowi pierwszego przejścia przez wątrobę</t></is></c><c r="L262" s="2" t="inlineStr"><is><t>jest przeciwwskazany w naczynioskurczowej postaci choroby wieńcowej</t></is></c><c r="M262" s="2" t="inlineStr" /><c r="N262" s="2" t="inlineStr" /><c r="O262" s="2" t="inlineStr" /><c r="P262" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q262" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="263"><c r="A263" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B263" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C263" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D263" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E263" s="2" t="inlineStr"><is><t>W leczeniu owrzodzeń żylnych, jako leczenie uzupełniające, skuteczne są:</t></is></c><c r="F263" s="2" t="inlineStr"><is><t>mikronizowana diosmina</t></is></c><c r="G263" s="2" t="inlineStr"><is><t>opatrunki ze srebrem</t></is></c><c r="H263" s="2" t="inlineStr"><is><t>pentoksyfilina</t></is></c><c r="I263" s="2" t="inlineStr"><is><t>filgrastym</t></is></c><c r="J263" s="2" t="inlineStr" /><c r="K263" s="2" t="inlineStr" /><c r="L263" s="2" t="inlineStr" /><c r="M263" s="2" t="inlineStr" /><c r="N263" s="2" t="inlineStr" /><c r="O263" s="2" t="inlineStr" /><c r="P263" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q263" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="264"><c r="A264" s="2" t="inlineStr"><is><t>OTĘPIENIE</t></is></c><c r="B264" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C264" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D264" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E264" s="2" t="inlineStr"><is><t>Funkcje kognitywne u osób bez zaburzeń poznawczych poprawiają:</t></is></c><c r="F264" s="2" t="inlineStr"><is><t>piracetam</t></is></c><c r="G264" s="2" t="inlineStr"><is><t>winpocetyna</t></is></c><c r="H264" s="2" t="inlineStr"><is><t>nicergolina</t></is></c><c r="I264" s="2" t="inlineStr"><is><t>metylfenidat</t></is></c><c r="J264" s="2" t="inlineStr" /><c r="K264" s="2" t="inlineStr" /><c r="L264" s="2" t="inlineStr" /><c r="M264" s="2" t="inlineStr" /><c r="N264" s="2" t="inlineStr" /><c r="O264" s="2" t="inlineStr" /><c r="P264" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q264" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="265"><c r="A265" s="2" t="inlineStr"><is><t>LEKI PRZECIWPSYCHOTYCZNE</t></is></c><c r="B265" s="2" t="inlineStr"><is><t>Monitorowanie</t></is></c><c r="C265" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D265" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E265" s="2" t="inlineStr"><is><t>Klozapina:</t></is></c><c r="F265" s="2" t="inlineStr"><is><t>może być skuteczna w lekoopornej schizofrenii</t></is></c><c r="G265" s="2" t="inlineStr"><is><t>wymaga monitorowania morfologii krwi</t></is></c><c r="H265" s="2" t="inlineStr"><is><t>nasila objawy zespołu metabolicznego</t></is></c><c r="I265" s="2" t="inlineStr" /><c r="J265" s="2" t="inlineStr" /><c r="K265" s="2" t="inlineStr"><is><t>w małych dawkach zalecana jest do leczenia bezsenności</t></is></c><c r="L265" s="2" t="inlineStr" /><c r="M265" s="2" t="inlineStr" /><c r="N265" s="2" t="inlineStr" /><c r="O265" s="2" t="inlineStr" /><c r="P265" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q265" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="266"><c r="A266" s="2" t="inlineStr"><is><t>NARKOTYCZNE LEKI PRZECIWBÓLOWE</t></is></c><c r="B266" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C266" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D266" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E266" s="2" t="inlineStr"><is><t>W terapii substytucyjnej uzależnienia od opioidów celowe może być zastosowanie:</t></is></c><c r="F266" s="2" t="inlineStr"><is><t>buprenorfiny</t></is></c><c r="G266" s="2" t="inlineStr"><is><t>metadonu</t></is></c><c r="H266" s="2" t="inlineStr" /><c r="I266" s="2" t="inlineStr" /><c r="J266" s="2" t="inlineStr" /><c r="K266" s="2" t="inlineStr"><is><t>nalokson</t></is></c><c r="L266" s="2" t="inlineStr"><is><t>warenikliny</t></is></c><c r="M266" s="2" t="inlineStr" /><c r="N266" s="2" t="inlineStr" /><c r="O266" s="2" t="inlineStr" /><c r="P266" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q266" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="267"><c r="A267" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B267" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C267" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D267" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E267" s="2" t="inlineStr"><is><t>Silnie hepatotoksycznie działa:</t></is></c><c r="F267" s="2" t="inlineStr"><is><t>izoniazyd</t></is></c><c r="G267" s="2" t="inlineStr"><is><t>pirazynamid</t></is></c><c r="H267" s="2" t="inlineStr"><is><t>ryfampicyna</t></is></c><c r="I267" s="2" t="inlineStr" /><c r="J267" s="2" t="inlineStr" /><c r="K267" s="2" t="inlineStr"><is><t>streptomycyna</t></is></c><c r="L267" s="2" t="inlineStr" /><c r="M267" s="2" t="inlineStr" /><c r="N267" s="2" t="inlineStr" /><c r="O267" s="2" t="inlineStr" /><c r="P267" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q267" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="268"><c r="A268" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B268" s="2" t="inlineStr"><is><t>Ciąża</t></is></c><c r="C268" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D268" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E268" s="2" t="inlineStr"><is><t>Etambutol:</t></is></c><c r="F268" s="2" t="inlineStr"><is><t>zapobiega powstawaniu lekooporności na inne leki przeciwprątkowe</t></is></c><c r="G268" s="2" t="inlineStr"><is><t>może spowodować zaburzenia widzenia barwnego</t></is></c><c r="H268" s="2" t="inlineStr" /><c r="I268" s="2" t="inlineStr" /><c r="J268" s="2" t="inlineStr" /><c r="K268" s="2" t="inlineStr"><is><t>nie powinien być stosowany przez kobiety w ciąży</t></is></c><c r="L268" s="2" t="inlineStr"><is><t>nie jest stosowany w leczeniu gruźlicy pozapłucnej</t></is></c><c r="M268" s="2" t="inlineStr" /><c r="N268" s="2" t="inlineStr" /><c r="O268" s="2" t="inlineStr" /><c r="P268" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q268" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="269"><c r="A269" s="2" t="inlineStr"><is><t>LEKI NASENNE</t></is></c><c r="B269" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C269" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D269" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E269" s="2" t="inlineStr"><is><t>Wskaż prawdziwe połączenie lek – wskazanie:</t></is></c><c r="F269" s="2" t="inlineStr"><is><t>zolpidem - bezsenność</t></is></c><c r="G269" s="2" t="inlineStr"><is><t>rotygotyna – zespół niespokojnych nóg</t></is></c><c r="H269" s="2" t="inlineStr"><is><t>alprazolam - napady paniki</t></is></c><c r="I269" s="2" t="inlineStr"><is><t>fluoksetyna – zaburzenia kompulsywne</t></is></c><c r="J269" s="2" t="inlineStr" /><c r="K269" s="2" t="inlineStr" /><c r="L269" s="2" t="inlineStr" /><c r="M269" s="2" t="inlineStr" /><c r="N269" s="2" t="inlineStr" /><c r="O269" s="2" t="inlineStr" /><c r="P269" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q269" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="270"><c r="A270" s="2" t="inlineStr"><is><t>LEKI PRZECIWDEPRESYJNE</t></is></c><c r="B270" s="2" t="inlineStr"><is><t>Struktura chemiczna</t></is></c><c r="C270" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D270" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E270" s="2" t="inlineStr"><is><t>Jeśli leczymy depresję, to:</t></is></c><c r="F270" s="2" t="inlineStr"><is><t>u pacjentów z niewydolnością nerek lekiem pierwszego wyboru może być sertralina</t></is></c><c r="G270" s="2" t="inlineStr"><is><t>istnieje zwiększone ryzyko zachowań samobójczych u pacjentów w wieku poniżej 25 lat w okresie rozpoczynania leczenia przeciwdepresyjnego</t></is></c><c r="H270" s="2" t="inlineStr" /><c r="I270" s="2" t="inlineStr" /><c r="J270" s="2" t="inlineStr" /><c r="K270" s="2" t="inlineStr"><is><t>u osób starszych preferujemy trójpierścieniowe laki przeciwdepresyjne</t></is></c><c r="L270" s="2" t="inlineStr"><is><t>brak poprawy po 4 tygodniach leczenia sugeruje rozpoznanie depresji lekoopornej</t></is></c><c r="M270" s="2" t="inlineStr" /><c r="N270" s="2" t="inlineStr" /><c r="O270" s="2" t="inlineStr" /><c r="P270" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q270" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="271"><c r="A271" s="2" t="inlineStr"><is><t>UKŁAD ODDECHOWY</t></is></c><c r="B271" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C271" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D271" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E271" s="2" t="inlineStr"><is><t>Działanie przeciwkaszlowe wykazuje:</t></is></c><c r="F271" s="2" t="inlineStr"><is><t>dekstrometorfan</t></is></c><c r="G271" s="2" t="inlineStr"><is><t>kodeina</t></is></c><c r="H271" s="2" t="inlineStr" /><c r="I271" s="2" t="inlineStr" /><c r="J271" s="2" t="inlineStr" /><c r="K271" s="2" t="inlineStr"><is><t>loperamid</t></is></c><c r="L271" s="2" t="inlineStr"><is><t>prometazyna</t></is></c><c r="M271" s="2" t="inlineStr" /><c r="N271" s="2" t="inlineStr" /><c r="O271" s="2" t="inlineStr" /><c r="P271" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q271" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="272"><c r="A272" s="2" t="inlineStr"><is><t>NIEWYDOLNOŚĆ SERCA</t></is></c><c r="B272" s="2" t="inlineStr"><is><t>Antidotum</t></is></c><c r="C272" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D272" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E272" s="2" t="inlineStr"><is><t>Atropina jest stosowana w przypadku zatrucia:</t></is></c><c r="F272" s="2" t="inlineStr"><is><t>grzybami strzępiakami i lejkówkami</t></is></c><c r="G272" s="2" t="inlineStr"><is><t>glikozydami naparstnicy</t></is></c><c r="H272" s="2" t="inlineStr"><is><t>związkami fosforoorganicznymi</t></is></c><c r="I272" s="2" t="inlineStr" /><c r="J272" s="2" t="inlineStr" /><c r="K272" s="2" t="inlineStr"><is><t>pokrzykiem wilczą jagodą</t></is></c><c r="L272" s="2" t="inlineStr" /><c r="M272" s="2" t="inlineStr" /><c r="N272" s="2" t="inlineStr" /><c r="O272" s="2" t="inlineStr" /><c r="P272" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q272" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="273"><c r="A273" s="2" t="inlineStr"><is><t>TARCZYCA</t></is></c><c r="B273" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C273" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D273" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E273" s="2" t="inlineStr"><is><t>W porównaniu do osób dorosłych w populacji pediatrycznej:</t></is></c><c r="F273" s="2" t="inlineStr"><is><t>zmieniona reakcja na leki jest uwarunkowana przede wszystkim zmianami w farmakokinetyce leków</t></is></c><c r="G273" s="2" t="inlineStr"><is><t>do osiągnięcia stężenia terapeutycznego leku mogą wystarczyć w pierwszym kwartale życia (w przeliczeniu na masę ciała) mniejsze dawki leku</t></is></c><c r="H273" s="2" t="inlineStr"><is><t>w pierwszym półroczu życia leki wydalane przez nerki są eliminowane wolniej, a ich biologiczny okres półtrwania jest dłuższy</t></is></c><c r="I273" s="2" t="inlineStr"><is><t>w pierwszym roku życia frakcja wolna leku może być większa</t></is></c><c r="J273" s="2" t="inlineStr" /><c r="K273" s="2" t="inlineStr" /><c r="L273" s="2" t="inlineStr" /><c r="M273" s="2" t="inlineStr" /><c r="N273" s="2" t="inlineStr" /><c r="O273" s="2" t="inlineStr" /><c r="P273" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q273" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="274"><c r="A274" s="2" t="inlineStr"><is><t>NIEWYDOLNOŚĆ SERCA</t></is></c><c r="B274" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C274" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D274" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E274" s="2" t="inlineStr"><is><t>Inhibitory fosfodiesterazy typu 5:</t></is></c><c r="F274" s="2" t="inlineStr"><is><t>są skuteczne w leczeniu zaburzeń erekcji</t></is></c><c r="G274" s="2" t="inlineStr"><is><t>nie mogą być przyjmowane jednocześnie z azotanami z uwagi na duże ryzyko wystąpienia ciężkiej, niekorygowalnej hipotonii</t></is></c><c r="H274" s="2" t="inlineStr" /><c r="I274" s="2" t="inlineStr" /><c r="J274" s="2" t="inlineStr" /><c r="K274" s="2" t="inlineStr"><is><t>wydłużają dystans marszu bez bólu u pacjentów z chromaniem przestankowym</t></is></c><c r="L274" s="2" t="inlineStr"><is><t>mają działanie inotropowe dodatnie</t></is></c><c r="M274" s="2" t="inlineStr" /><c r="N274" s="2" t="inlineStr" /><c r="O274" s="2" t="inlineStr" /><c r="P274" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q274" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="275"><c r="A275" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B275" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C275" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D275" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E275" s="2" t="inlineStr"><is><t>Wpływ rozkurczający na mięśniówkę przewodu pokarmowego ma:</t></is></c><c r="F275" s="2" t="inlineStr"><is><t>drotaweryna</t></is></c><c r="G275" s="2" t="inlineStr" /><c r="H275" s="2" t="inlineStr" /><c r="I275" s="2" t="inlineStr" /><c r="J275" s="2" t="inlineStr" /><c r="K275" s="2" t="inlineStr"><is><t>itopryd</t></is></c><c r="L275" s="2" t="inlineStr"><is><t>mesalazyna</t></is></c><c r="M275" s="2" t="inlineStr"><is><t>ryfaksymina</t></is></c><c r="N275" s="2" t="inlineStr" /><c r="O275" s="2" t="inlineStr" /><c r="P275" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q275" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="276"><c r="A276" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B276" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C276" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D276" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E276" s="2" t="inlineStr"><is><t>Lanzoprazol stosowany przewlekle powoduje:</t></is></c><c r="F276" s="2" t="inlineStr"><is><t>wzrost ryzyka zakażenia Clostridum difficile</t></is></c><c r="G276" s="2" t="inlineStr"><is><t>wzrost ryzyka infekcji dróg oddechowych</t></is></c><c r="H276" s="2" t="inlineStr"><is><t>zmniejszenie wchłaniania wapnia z przewodu pokarmowego</t></is></c><c r="I276" s="2" t="inlineStr"><is><t>zmniejszenie przekształcania klopidogrelu do aktywnych pochodnych</t></is></c><c r="J276" s="2" t="inlineStr" /><c r="K276" s="2" t="inlineStr" /><c r="L276" s="2" t="inlineStr" /><c r="M276" s="2" t="inlineStr" /><c r="N276" s="2" t="inlineStr" /><c r="O276" s="2" t="inlineStr" /><c r="P276" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q276" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="277"><c r="A277" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B277" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C277" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D277" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E277" s="2" t="inlineStr"><is><t>Sposób eradykacji Helicobacter pylori zalecany w Polsce to:</t></is></c><c r="F277" s="2" t="inlineStr"><is><t>podwójna dawka IPP, metronidazol, tetracyklina, cytrynian bizmutu przez 14 dni</t></is></c><c r="G277" s="2" t="inlineStr" /><c r="H277" s="2" t="inlineStr" /><c r="I277" s="2" t="inlineStr" /><c r="J277" s="2" t="inlineStr" /><c r="K277" s="2" t="inlineStr"><is><t>terapia sekwencyjna przez 10 dni - podwójna dawka IPP (inhibitora pompy protonowej) z amoksycyliną (dni 1-5), a następnie z klarytromycyną i metronidazolem (dni 6-10)</t></is></c><c r="L277" s="2" t="inlineStr"><is><t>podwójna dawka IPP, amoksycylina, klarytromycyna przez 10 dni</t></is></c><c r="M277" s="2" t="inlineStr"><is><t>podwójna dawka IPP, amoksycylina, klarytromycyna, metronidazol przez 14 dni</t></is></c><c r="N277" s="2" t="inlineStr" /><c r="O277" s="2" t="inlineStr" /><c r="P277" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q277" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="278"><c r="A278" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B278" s="2" t="inlineStr"><is><t>Ciąża</t></is></c><c r="C278" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D278" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E278" s="2" t="inlineStr"><is><t>Udokumentowane działanie teratogenne wykazuje:</t></is></c><c r="F278" s="2" t="inlineStr"><is><t>trimetoprim-sulfametoksazol</t></is></c><c r="G278" s="2" t="inlineStr"><is><t>warfaryna</t></is></c><c r="H278" s="2" t="inlineStr"><is><t>kwas walproinowy</t></is></c><c r="I278" s="2" t="inlineStr"><is><t>gentamycyna</t></is></c><c r="J278" s="2" t="inlineStr" /><c r="K278" s="2" t="inlineStr" /><c r="L278" s="2" t="inlineStr" /><c r="M278" s="2" t="inlineStr" /><c r="N278" s="2" t="inlineStr" /><c r="O278" s="2" t="inlineStr" /><c r="P278" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q278" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="279"><c r="A279" s="2" t="inlineStr"><is><t>LEKI PRZECIWDEPRESYJNE</t></is></c><c r="B279" s="2" t="inlineStr"><is><t>Antidotum</t></is></c><c r="C279" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D279" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E279" s="2" t="inlineStr"><is><t>Wskaż prawdziwe połączenie lek – odtrutka:</t></is></c><c r="F279" s="2" t="inlineStr"><is><t>oksazepam - flumazenil</t></is></c><c r="G279" s="2" t="inlineStr"><is><t>trójpierścieniowe leki przeciwdepresyjne – wodorowęglan sodu</t></is></c><c r="H279" s="2" t="inlineStr"><is><t>żelazo - deferoksamina</t></is></c><c r="I279" s="2" t="inlineStr"><is><t>warfaryna - fitomenadion</t></is></c><c r="J279" s="2" t="inlineStr" /><c r="K279" s="2" t="inlineStr" /><c r="L279" s="2" t="inlineStr" /><c r="M279" s="2" t="inlineStr" /><c r="N279" s="2" t="inlineStr" /><c r="O279" s="2" t="inlineStr" /><c r="P279" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q279" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="280"><c r="A280" s="2" t="inlineStr"><is><t>CHOROBA NIEDOKRWIENNA SERCA</t></is></c><c r="B280" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C280" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D280" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E280" s="2" t="inlineStr"><is><t>Wazodylatacyjny mechanizm działania azotanów zależy od:</t></is></c><c r="F280" s="2" t="inlineStr"><is><t>wzrostu stężenia cGMP</t></is></c><c r="G280" s="2" t="inlineStr"><is><t>defosforylacji łańcuchów lekkich miozyny</t></is></c><c r="H280" s="2" t="inlineStr" /><c r="I280" s="2" t="inlineStr" /><c r="J280" s="2" t="inlineStr" /><c r="K280" s="2" t="inlineStr"><is><t>hamowania aktywności cyklazy guanylowej</t></is></c><c r="L280" s="2" t="inlineStr"><is><t>pobudzania kanałów potasowych</t></is></c><c r="M280" s="2" t="inlineStr" /><c r="N280" s="2" t="inlineStr" /><c r="O280" s="2" t="inlineStr" /><c r="P280" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q280" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="281"><c r="A281" s="2" t="inlineStr"><is><t>ZABURZENIA RYTMU SERCA</t></is></c><c r="B281" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C281" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D281" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E281" s="2" t="inlineStr"><is><t>Bradykardia może wystąpić po zastosowaniu:</t></is></c><c r="F281" s="2" t="inlineStr"><is><t>werapamilu</t></is></c><c r="G281" s="2" t="inlineStr" /><c r="H281" s="2" t="inlineStr" /><c r="I281" s="2" t="inlineStr" /><c r="J281" s="2" t="inlineStr" /><c r="K281" s="2" t="inlineStr"><is><t>nifedypiny</t></is></c><c r="L281" s="2" t="inlineStr"><is><t>trimetazydyny</t></is></c><c r="M281" s="2" t="inlineStr"><is><t>spironolaktonu</t></is></c><c r="N281" s="2" t="inlineStr" /><c r="O281" s="2" t="inlineStr" /><c r="P281" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q281" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="282"><c r="A282" s="2" t="inlineStr"><is><t>UKŁAD WSPÓŁCZULNY</t></is></c><c r="B282" s="2" t="inlineStr"><is><t>Farmakokinetyka</t></is></c><c r="C282" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D282" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E282" s="2" t="inlineStr"><is><t>Teoretyczną przesłanką stosowania beta-adrenolityków w chorobie wieńcowej serca jest:</t></is></c><c r="F282" s="2" t="inlineStr"><is><t>usprawnienie metabolizmu kardiomiocytów</t></is></c><c r="G282" s="2" t="inlineStr"><is><t>zapobieganie proarytmicznemu działaniu katecholamin</t></is></c><c r="H282" s="2" t="inlineStr"><is><t>poprawa perfuzji warstwy podwsierdziowej</t></is></c><c r="I282" s="2" t="inlineStr"><is><t>korzystny wpływ hemodynamiczny zmniejszający zapotrzebowanie mięśnia sercowego na tlen</t></is></c><c r="J282" s="2" t="inlineStr" /><c r="K282" s="2" t="inlineStr" /><c r="L282" s="2" t="inlineStr" /><c r="M282" s="2" t="inlineStr" /><c r="N282" s="2" t="inlineStr" /><c r="O282" s="2" t="inlineStr" /><c r="P282" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q282" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="283"><c r="A283" s="2" t="inlineStr"><is><t>NIEWYDOLNOŚĆ SERCA</t></is></c><c r="B283" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C283" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D283" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E283" s="2" t="inlineStr"><is><t>Digoksyna:</t></is></c><c r="F283" s="2" t="inlineStr"><is><t>aktywuje układ przywspółczulny</t></is></c><c r="G283" s="2" t="inlineStr"><is><t>wywiera arytmie i zaburzenia przewodzenia</t></is></c><c r="H283" s="2" t="inlineStr"><is><t>jest stosowana w celu kontroli częstotliwości rytmu komór u chorych z migotaniem przedsionków</t></is></c><c r="I283" s="2" t="inlineStr"><is><t>w zatruciu można zastosować fragmenty Fab przeciwciał wiążących</t></is></c><c r="J283" s="2" t="inlineStr" /><c r="K283" s="2" t="inlineStr" /><c r="L283" s="2" t="inlineStr" /><c r="M283" s="2" t="inlineStr" /><c r="N283" s="2" t="inlineStr" /><c r="O283" s="2" t="inlineStr" /><c r="P283" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q283" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="284"><c r="A284" s="2" t="inlineStr"><is><t>NADCIŚNIENIE TĘTNICZE</t></is></c><c r="B284" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C284" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D284" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E284" s="2" t="inlineStr"><is><t>Wskaż prawdziwe połączenie lek – wskazanie:</t></is></c><c r="F284" s="2" t="inlineStr"><is><t>ranolazyna - stabilna choroba niedokrwienna serca</t></is></c><c r="G284" s="2" t="inlineStr" /><c r="H284" s="2" t="inlineStr" /><c r="I284" s="2" t="inlineStr" /><c r="J284" s="2" t="inlineStr" /><c r="K284" s="2" t="inlineStr"><is><t>cilostazol - ostra niewydolność mięśnia sercowego</t></is></c><c r="L284" s="2" t="inlineStr"><is><t>milrynon - migotanie przedsionków</t></is></c><c r="M284" s="2" t="inlineStr"><is><t>riocyguat - nadciśnienie tętnicze</t></is></c><c r="N284" s="2" t="inlineStr" /><c r="O284" s="2" t="inlineStr" /><c r="P284" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q284" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="285"><c r="A285" s="2" t="inlineStr"><is><t>NADCIŚNIENIE TĘTNICZE</t></is></c><c r="B285" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C285" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D285" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E285" s="2" t="inlineStr"><is><t>Do leków stosowanych w leczeniu nadciśnienia tętniczego ze wskazań naglących (RR&gt;180/120 mmHg z powikłaniami narządowymi) należą:</t></is></c><c r="F285" s="2" t="inlineStr"><is><t>esmolol</t></is></c><c r="G285" s="2" t="inlineStr"><is><t>urapidyl</t></is></c><c r="H285" s="2" t="inlineStr" /><c r="I285" s="2" t="inlineStr" /><c r="J285" s="2" t="inlineStr" /><c r="K285" s="2" t="inlineStr"><is><t>doksazosyna</t></is></c><c r="L285" s="2" t="inlineStr"><is><t>kaptopryl</t></is></c><c r="M285" s="2" t="inlineStr" /><c r="N285" s="2" t="inlineStr" /><c r="O285" s="2" t="inlineStr" /><c r="P285" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q285" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="286"><c r="A286" s="2" t="inlineStr"><is><t>NIEWYDOLNOŚĆ SERCA</t></is></c><c r="B286" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C286" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D286" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E286" s="2" t="inlineStr"><is><t>Do leków zmniejszających ryzyko zgonu sercowo-naczyniowego w przebiegu skurczowej niewydolności serca należy:</t></is></c><c r="F286" s="2" t="inlineStr"><is><t>bisoprolol</t></is></c><c r="G286" s="2" t="inlineStr"><is><t>eplerenon</t></is></c><c r="H286" s="2" t="inlineStr"><is><t>sakubitril w skojarzeniu z walsartanem</t></is></c><c r="I286" s="2" t="inlineStr" /><c r="J286" s="2" t="inlineStr" /><c r="K286" s="2" t="inlineStr"><is><t>digoksyna</t></is></c><c r="L286" s="2" t="inlineStr" /><c r="M286" s="2" t="inlineStr" /><c r="N286" s="2" t="inlineStr" /><c r="O286" s="2" t="inlineStr" /><c r="P286" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q286" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="287"><c r="A287" s="2" t="inlineStr"><is><t>CHOROBA NIEDOKRWIENNA SERCA</t></is></c><c r="B287" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C287" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D287" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E287" s="2" t="inlineStr"><is><t>U 67-letniej kobiety z dyskomfortem zamostkowym występującym przy wchodzeniu na 3 piętro i ustępującym w spoczynku, z blokiem przedsionkowo-komorowym II stopnia typu Mobitza w badaniu met. Holtera należy zastosować:</t></is></c><c r="F287" s="2" t="inlineStr"><is><t>rosuwastatynę</t></is></c><c r="G287" s="2" t="inlineStr"><is><t>kwas acetylosalicylowy</t></is></c><c r="H287" s="2" t="inlineStr"><is><t>triazotan glicerolu w aerozolu</t></is></c><c r="I287" s="2" t="inlineStr" /><c r="J287" s="2" t="inlineStr" /><c r="K287" s="2" t="inlineStr"><is><t>nebiwolol</t></is></c><c r="L287" s="2" t="inlineStr" /><c r="M287" s="2" t="inlineStr" /><c r="N287" s="2" t="inlineStr" /><c r="O287" s="2" t="inlineStr" /><c r="P287" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q287" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="288"><c r="A288" s="2" t="inlineStr"><is><t>FARMAKOKINETYKA</t></is></c><c r="B288" s="2" t="inlineStr"><is><t>Monitorowanie</t></is></c><c r="C288" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D288" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E288" s="2" t="inlineStr"><is><t>Wskaż prawidłowe zasady prowadzenia terapii monitorowanej stężeniami leku:</t></is></c><c r="F288" s="2" t="inlineStr"><is><t>oznaczenia należy wykonywać po osiągnięciu przez lek stanu stacjonarnego</t></is></c><c r="G288" s="2" t="inlineStr"><is><t>pomiary należy wykonywać w momencie Cmin, czyli tuż przed podaniem kolejnej, zwykle porannej dawki leku</t></is></c><c r="H288" s="2" t="inlineStr"><is><t>w większości przypadków wystarczy oznaczenie całkowitego stężenia leku</t></is></c><c r="I288" s="2" t="inlineStr"><is><t>w przypadku leków o kinetyce liniowej można wyliczyć modyfikację dawki na podstawie pomiarów aktualnych i znajomości docelowych stężeń leku we krwi</t></is></c><c r="J288" s="2" t="inlineStr" /><c r="K288" s="2" t="inlineStr" /><c r="L288" s="2" t="inlineStr" /><c r="M288" s="2" t="inlineStr" /><c r="N288" s="2" t="inlineStr" /><c r="O288" s="2" t="inlineStr" /><c r="P288" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q288" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="289"><c r="A289" s="2" t="inlineStr"><is><t>ZABURZENIA RYTMU SERCA</t></is></c><c r="B289" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C289" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D289" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E289" s="2" t="inlineStr"><is><t>Które stwierdzenie jest prawdziwe:</t></is></c><c r="F289" s="2" t="inlineStr"><is><t>propafenon nie jest zalecany u pacjentów z chorobą wieńcową</t></is></c><c r="G289" s="2" t="inlineStr"><is><t>amiodaron można stosować w celu zwiększenia skuteczności kardiowersji elektrycznej</t></is></c><c r="H289" s="2" t="inlineStr" /><c r="I289" s="2" t="inlineStr" /><c r="J289" s="2" t="inlineStr" /><c r="K289" s="2" t="inlineStr"><is><t>dronedaron zmniejsza umieralność u pacjentów z niewydolnością serca w klasie III/IV NYHA</t></is></c><c r="L289" s="2" t="inlineStr"><is><t>beta-adrenolityki stosuje się w celu kardiowersji farmakologicznej</t></is></c><c r="M289" s="2" t="inlineStr" /><c r="N289" s="2" t="inlineStr" /><c r="O289" s="2" t="inlineStr" /><c r="P289" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q289" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="290"><c r="A290" s="2" t="inlineStr"><is><t>LEKI HIPOLIPEMIZUJĄCE</t></is></c><c r="B290" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C290" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D290" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E290" s="2" t="inlineStr"><is><t>W celu oceny działań niepożądanych w trakcie leczenia atorwastatyną należy sprawdzić:</t></is></c><c r="F290" s="2" t="inlineStr"><is><t>aktywność kinazy fosfokreatynowej (CPK)</t></is></c><c r="G290" s="2" t="inlineStr"><is><t>aktywność enzymów wątrobowych (AST/ALT)</t></is></c><c r="H290" s="2" t="inlineStr" /><c r="I290" s="2" t="inlineStr" /><c r="J290" s="2" t="inlineStr" /><c r="K290" s="2" t="inlineStr"><is><t>stężenie glukozy</t></is></c><c r="L290" s="2" t="inlineStr"><is><t>stężenie peptydu natriuretycznego typu B (BNP)</t></is></c><c r="M290" s="2" t="inlineStr" /><c r="N290" s="2" t="inlineStr" /><c r="O290" s="2" t="inlineStr" /><c r="P290" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q290" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="291"><c r="A291" s="2" t="inlineStr"><is><t>LEKI MOCZOPĘDNE</t></is></c><c r="B291" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C291" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D291" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E291" s="2" t="inlineStr"><is><t>W leczeniu zagrażającej życiu hiperkaliemii można zastosować:</t></is></c><c r="F291" s="2" t="inlineStr"><is><t>10 ml 10% chlorku lub glukonianu wapnia i.v. w 10 min bolusie</t></is></c><c r="G291" s="2" t="inlineStr"><is><t>500 ml 20% glukozy z 20 j.m. insuliny krótkodziałającej i.v. przez 1-2 godziny</t></is></c><c r="H291" s="2" t="inlineStr"><is><t>hemodializę</t></is></c><c r="I291" s="2" t="inlineStr" /><c r="J291" s="2" t="inlineStr" /><c r="K291" s="2" t="inlineStr"><is><t>diuretyki pętlowe i.v</t></is></c><c r="L291" s="2" t="inlineStr" /><c r="M291" s="2" t="inlineStr" /><c r="N291" s="2" t="inlineStr" /><c r="O291" s="2" t="inlineStr" /><c r="P291" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q291" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="292"><c r="A292" s="2" t="inlineStr"><is><t>UKŁAD WSPÓŁCZULNY</t></is></c><c r="B292" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C292" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D292" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E292" s="2" t="inlineStr"><is><t>Powinowactwo do receptorów alfa-1-adrenergicznych wykazuje:</t></is></c><c r="F292" s="2" t="inlineStr"><is><t>doksazosyna</t></is></c><c r="G292" s="2" t="inlineStr"><is><t>labetalol</t></is></c><c r="H292" s="2" t="inlineStr"><is><t>adrenalina</t></is></c><c r="I292" s="2" t="inlineStr"><is><t>karwedilol</t></is></c><c r="J292" s="2" t="inlineStr" /><c r="K292" s="2" t="inlineStr" /><c r="L292" s="2" t="inlineStr" /><c r="M292" s="2" t="inlineStr" /><c r="N292" s="2" t="inlineStr" /><c r="O292" s="2" t="inlineStr" /><c r="P292" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q292" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="293"><c r="A293" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B293" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C293" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D293" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E293" s="2" t="inlineStr"><is><t>Apiksaban jest substratem dla P-gp. Co to oznacza?</t></is></c><c r="F293" s="2" t="inlineStr"><is><t>silne induktory P-gp o działaniu ogólnoustrojowym zmniejszają skuteczność apiksabanu</t></is></c><c r="G293" s="2" t="inlineStr" /><c r="H293" s="2" t="inlineStr" /><c r="I293" s="2" t="inlineStr" /><c r="J293" s="2" t="inlineStr" /><c r="K293" s="2" t="inlineStr"><is><t>lek jest wchłaniany z p. pokarmowego z wykorzystaniem transportu ułatwionego</t></is></c><c r="L293" s="2" t="inlineStr"><is><t>jest metabolizowany w wątrobie i nie powinien być stosowany u osób z 10- 15 pkt wg skali Childa-Pugha</t></is></c><c r="M293" s="2" t="inlineStr"><is><t>jest prawdopodobne, że hemodializa byłaby skutecznym środkiem zaradczym podczas przedawkowania apiksabanu</t></is></c><c r="N293" s="2" t="inlineStr" /><c r="O293" s="2" t="inlineStr" /><c r="P293" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q293" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="294"><c r="A294" s="2" t="inlineStr"><is><t>FARMAKOKINETYKA</t></is></c><c r="B294" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C294" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D294" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E294" s="2" t="inlineStr"><is><t>Opis rzedowości procesu:</t></is></c><c r="F294" s="2" t="inlineStr"><is><t>Dotyczy wszystkich etapów farmakokinetycznych</t></is></c><c r="G294" s="2" t="inlineStr"><is><t>Definiuje dynamiki zmian w układzie stężenie-czas w zależności od budowy chemicznej leku</t></is></c><c r="H294" s="2" t="inlineStr"><is><t>Może się zmienić dla leku w trakcie pojedynczej ekspozycji</t></is></c><c r="I294" s="2" t="inlineStr"><is><t>Powstaje ostatecznie w badaniach w medelu zwierzęcym</t></is></c><c r="J294" s="2" t="inlineStr" /><c r="K294" s="2" t="inlineStr" /><c r="L294" s="2" t="inlineStr" /><c r="M294" s="2" t="inlineStr" /><c r="N294" s="2" t="inlineStr" /><c r="O294" s="2" t="inlineStr" /><c r="P294" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q294" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="295"><c r="A295" s="2" t="inlineStr"><is><t>FARMAKOKINETYKA</t></is></c><c r="B295" s="2" t="inlineStr"><is><t>Farmakokinetyka</t></is></c><c r="C295" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D295" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E295" s="2" t="inlineStr"><is><t>Jeśli proces eliminacji leku przez nerki jest opisany kinetyką zerowego rzędu to:</t></is></c><c r="F295" s="2" t="inlineStr"><is><t>Procesy wchłaniania i dystrybucji również opisane są kinetyką zerowego rzędu</t></is></c><c r="G295" s="2" t="inlineStr"><is><t>Szybkość procesu eliminacji nerkowej jest stała</t></is></c><c r="H295" s="2" t="inlineStr" /><c r="I295" s="2" t="inlineStr" /><c r="J295" s="2" t="inlineStr" /><c r="K295" s="2" t="inlineStr"><is><t>Stężenie leku w moczu jest odwrotnie proporocjonalne do stężenia leku we krwi</t></is></c><c r="L295" s="2" t="inlineStr"><is><t>Klirens nerkowy leku jest wprost proporcjonalny do stężeniu leku</t></is></c><c r="M295" s="2" t="inlineStr" /><c r="N295" s="2" t="inlineStr" /><c r="O295" s="2" t="inlineStr" /><c r="P295" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q295" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="296"><c r="A296" s="2" t="inlineStr"><is><t>FARMAKOKINETYKA</t></is></c><c r="B296" s="2" t="inlineStr"><is><t>Farmakokinetyka</t></is></c><c r="C296" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D296" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E296" s="2" t="inlineStr"><is><t>Wskaż właściwie zdefiniowane parametry farmakokinetyczne</t></is></c><c r="F296" s="2" t="inlineStr"><is><t>AUC – pole pod krzywą zmian stężenia leku we krwi w czasie</t></is></c><c r="G296" s="2" t="inlineStr" /><c r="H296" s="2" t="inlineStr" /><c r="I296" s="2" t="inlineStr" /><c r="J296" s="2" t="inlineStr" /><c r="K296" s="2" t="inlineStr"><is><t>T1/2 – czas po którym stężenie leku we krwi jest równe stężeniu leku gdyby biodostępność wynosiła 50%</t></is></c><c r="L296" s="2" t="inlineStr"><is><t>Tmax – maksymalny czas w którym stężeniu leku we krwi jest wykrywalne</t></is></c><c r="M296" s="2" t="inlineStr"><is><t>Cmax – stężenie leku we krwi osiągane po podaniu dożylnym</t></is></c><c r="N296" s="2" t="inlineStr" /><c r="O296" s="2" t="inlineStr" /><c r="P296" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q296" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="297"><c r="A297" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B297" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C297" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D297" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E297" s="2" t="inlineStr"><is><t>Do zwiększenia przepuszczalności bariery krew mózg dla leków dochodzi w przypadku</t></is></c><c r="F297" s="2" t="inlineStr"><is><t>Zapalenia opon mózgowo-rdzeniowych</t></is></c><c r="G297" s="2" t="inlineStr"><is><t>Niedokrwienia mózgu</t></is></c><c r="H297" s="2" t="inlineStr" /><c r="I297" s="2" t="inlineStr" /><c r="J297" s="2" t="inlineStr" /><c r="K297" s="2" t="inlineStr"><is><t>Chorób neurodegeneracyjnych</t></is></c><c r="L297" s="2" t="inlineStr"><is><t>Chorób autoimmunologicznych</t></is></c><c r="M297" s="2" t="inlineStr"><is><t>Wskaż prawidłowe połączenie antybiotyk – mechanizm działania</t></is></c><c r="N297" s="2" t="inlineStr" /><c r="O297" s="2" t="inlineStr" /><c r="P297" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q297" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="298"><c r="A298" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B298" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C298" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D298" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E298" s="2" t="inlineStr"><is><t>Azytromycyna</t></is></c><c r="F298" s="2" t="inlineStr"><is><t>Kumuluje się w makrofagach</t></is></c><c r="G298" s="2" t="inlineStr"><is><t>Ma długi okres półtrwania</t></is></c><c r="H298" s="2" t="inlineStr" /><c r="I298" s="2" t="inlineStr" /><c r="J298" s="2" t="inlineStr" /><c r="K298" s="2" t="inlineStr"><is><t>Słabo wchłania się z PP</t></is></c><c r="L298" s="2" t="inlineStr"><is><t>Hamuje enzymy cytochromu P-450</t></is></c><c r="M298" s="2" t="inlineStr" /><c r="N298" s="2" t="inlineStr" /><c r="O298" s="2" t="inlineStr" /><c r="P298" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q298" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="299"><c r="A299" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B299" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C299" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D299" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E299" s="2" t="inlineStr"><is><t>Działanie ototoksyczne wskazują</t></is></c><c r="F299" s="2" t="inlineStr"><is><t>Salicylany</t></is></c><c r="G299" s="2" t="inlineStr"><is><t>Aminoglikozydy</t></is></c><c r="H299" s="2" t="inlineStr" /><c r="I299" s="2" t="inlineStr" /><c r="J299" s="2" t="inlineStr" /><c r="K299" s="2" t="inlineStr"><is><t>Glitazony</t></is></c><c r="L299" s="2" t="inlineStr"><is><t>Penicyliny</t></is></c><c r="M299" s="2" t="inlineStr" /><c r="N299" s="2" t="inlineStr" /><c r="O299" s="2" t="inlineStr" /><c r="P299" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q299" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="300"><c r="A300" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B300" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C300" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D300" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E300" s="2" t="inlineStr"><is><t>W leczeniu boreliozy można użyć</t></is></c><c r="F300" s="2" t="inlineStr"><is><t>Amoksycyliny</t></is></c><c r="G300" s="2" t="inlineStr"><is><t>Cefuroksymu aksetylu</t></is></c><c r="H300" s="2" t="inlineStr"><is><t>Azytromycyny</t></is></c><c r="I300" s="2" t="inlineStr"><is><t>Doksycykliny</t></is></c><c r="J300" s="2" t="inlineStr" /><c r="K300" s="2" t="inlineStr" /><c r="L300" s="2" t="inlineStr" /><c r="M300" s="2" t="inlineStr" /><c r="N300" s="2" t="inlineStr" /><c r="O300" s="2" t="inlineStr" /><c r="P300" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q300" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="301"><c r="A301" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B301" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C301" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D301" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E301" s="2" t="inlineStr"><is><t>Syntezę ściany komórkowej hamuje</t></is></c><c r="F301" s="2" t="inlineStr"><is><t>Imipenem</t></is></c><c r="G301" s="2" t="inlineStr"><is><t>Wankomycyna</t></is></c><c r="H301" s="2" t="inlineStr" /><c r="I301" s="2" t="inlineStr" /><c r="J301" s="2" t="inlineStr" /><c r="K301" s="2" t="inlineStr"><is><t>Erytromycyna</t></is></c><c r="L301" s="2" t="inlineStr"><is><t>Mupirocyna</t></is></c><c r="M301" s="2" t="inlineStr" /><c r="N301" s="2" t="inlineStr" /><c r="O301" s="2" t="inlineStr" /><c r="P301" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q301" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="302"><c r="A302" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B302" s="2" t="inlineStr"><is><t>Interakcje</t></is></c><c r="C302" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D302" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E302" s="2" t="inlineStr"><is><t>Reakcje disulfiramową może spowodować spożycie alkoholu podczas terapii</t></is></c><c r="F302" s="2" t="inlineStr"><is><t>Metronidazol</t></is></c><c r="G302" s="2" t="inlineStr" /><c r="H302" s="2" t="inlineStr" /><c r="I302" s="2" t="inlineStr" /><c r="J302" s="2" t="inlineStr" /><c r="K302" s="2" t="inlineStr"><is><t>Klindamycyną</t></is></c><c r="L302" s="2" t="inlineStr"><is><t>Piperalicyna</t></is></c><c r="M302" s="2" t="inlineStr"><is><t>Cyprofloksacyna</t></is></c><c r="N302" s="2" t="inlineStr" /><c r="O302" s="2" t="inlineStr" /><c r="P302" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q302" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="303"><c r="A303" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B303" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C303" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D303" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E303" s="2" t="inlineStr"><is><t>W zakażeniach Mycoplasama pneumoniae można zastosować</t></is></c><c r="F303" s="2" t="inlineStr"><is><t>Doksycykline</t></is></c><c r="G303" s="2" t="inlineStr"><is><t>Klarytromycyne</t></is></c><c r="H303" s="2" t="inlineStr" /><c r="I303" s="2" t="inlineStr" /><c r="J303" s="2" t="inlineStr" /><c r="K303" s="2" t="inlineStr"><is><t>Amoksycyline</t></is></c><c r="L303" s="2" t="inlineStr"><is><t>Ceftriakson</t></is></c><c r="M303" s="2" t="inlineStr" /><c r="N303" s="2" t="inlineStr" /><c r="O303" s="2" t="inlineStr" /><c r="P303" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q303" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="304"><c r="A304" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B304" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C304" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D304" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E304" s="2" t="inlineStr"><is><t>Makrolidy mogą być skuteczne w zakażeniach</t></is></c><c r="F304" s="2" t="inlineStr"><is><t>H. influenza</t></is></c><c r="G304" s="2" t="inlineStr"><is><t>L. pneumophila</t></is></c><c r="H304" s="2" t="inlineStr"><is><t>H. pylori</t></is></c><c r="I304" s="2" t="inlineStr"><is><t>T. gondi</t></is></c><c r="J304" s="2" t="inlineStr" /><c r="K304" s="2" t="inlineStr" /><c r="L304" s="2" t="inlineStr" /><c r="M304" s="2" t="inlineStr" /><c r="N304" s="2" t="inlineStr" /><c r="O304" s="2" t="inlineStr" /><c r="P304" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q304" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="305"><c r="A305" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B305" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C305" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D305" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E305" s="2" t="inlineStr"><is><t>W zakazeniu Clostridium diff. skuteczne sa:</t></is></c><c r="F305" s="2" t="inlineStr"><is><t>Metronidazol</t></is></c><c r="G305" s="2" t="inlineStr"><is><t>Wankomycyna</t></is></c><c r="H305" s="2" t="inlineStr" /><c r="I305" s="2" t="inlineStr" /><c r="J305" s="2" t="inlineStr" /><c r="K305" s="2" t="inlineStr"><is><t>Amoksycylina</t></is></c><c r="L305" s="2" t="inlineStr"><is><t>Klindamycyna</t></is></c><c r="M305" s="2" t="inlineStr" /><c r="N305" s="2" t="inlineStr" /><c r="O305" s="2" t="inlineStr" /><c r="P305" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q305" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="306"><c r="A306" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B306" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C306" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D306" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E306" s="2" t="inlineStr"><is><t>Na MRSA działa</t></is></c><c r="F306" s="2" t="inlineStr"><is><t>Wankomycyna</t></is></c><c r="G306" s="2" t="inlineStr"><is><t>Linezolid</t></is></c><c r="H306" s="2" t="inlineStr" /><c r="I306" s="2" t="inlineStr" /><c r="J306" s="2" t="inlineStr" /><c r="K306" s="2" t="inlineStr"><is><t>Cefazolina</t></is></c><c r="L306" s="2" t="inlineStr"><is><t>Meropenem</t></is></c><c r="M306" s="2" t="inlineStr" /><c r="N306" s="2" t="inlineStr" /><c r="O306" s="2" t="inlineStr" /><c r="P306" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q306" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="307"><c r="A307" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B307" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C307" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D307" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E307" s="2" t="inlineStr"><is><t>Kolistyna</t></is></c><c r="F307" s="2" t="inlineStr"><is><t>Działa nefrotoksycznie</t></is></c><c r="G307" s="2" t="inlineStr" /><c r="H307" s="2" t="inlineStr" /><c r="I307" s="2" t="inlineStr" /><c r="J307" s="2" t="inlineStr" /><c r="K307" s="2" t="inlineStr"><is><t>Działa głównie na bakterie Gram+</t></is></c><c r="L307" s="2" t="inlineStr"><is><t>Dobrze wchłania się po podaniu PO</t></is></c><c r="M307" s="2" t="inlineStr"><is><t>Jest wydalana głównie z kałem</t></is></c><c r="N307" s="2" t="inlineStr" /><c r="O307" s="2" t="inlineStr" /><c r="P307" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q307" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="308"><c r="A308" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B308" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C308" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D308" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E308" s="2" t="inlineStr"><is><t>Zagrożenia dla płodu jest mało prawdopodobne po</t></is></c><c r="F308" s="2" t="inlineStr"><is><t>Amoksycyliny z kwasem klawulanowym</t></is></c><c r="G308" s="2" t="inlineStr"><is><t>Erytromycyny</t></is></c><c r="H308" s="2" t="inlineStr"><is><t>Cefuroksymu</t></is></c><c r="I308" s="2" t="inlineStr" /><c r="J308" s="2" t="inlineStr" /><c r="K308" s="2" t="inlineStr"><is><t>Amikacyny</t></is></c><c r="L308" s="2" t="inlineStr" /><c r="M308" s="2" t="inlineStr" /><c r="N308" s="2" t="inlineStr" /><c r="O308" s="2" t="inlineStr" /><c r="P308" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q308" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="309"><c r="A309" s="2" t="inlineStr"><is><t>LEKI PRZECIWGRZYBICZE</t></is></c><c r="B309" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C309" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D309" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E309" s="2" t="inlineStr"><is><t>Ketokonazol</t></is></c><c r="F309" s="2" t="inlineStr"><is><t>Jest dostępny w postaci szamponu</t></is></c><c r="G309" s="2" t="inlineStr"><is><t>Ma zostosowanie w zespole Cushinga</t></is></c><c r="H309" s="2" t="inlineStr"><is><t>Wykazuje działanie hepatotoksyczne</t></is></c><c r="I309" s="2" t="inlineStr" /><c r="J309" s="2" t="inlineStr" /><c r="K309" s="2" t="inlineStr"><is><t>Nie wchłania się po podaniu doustnym</t></is></c><c r="L309" s="2" t="inlineStr" /><c r="M309" s="2" t="inlineStr" /><c r="N309" s="2" t="inlineStr" /><c r="O309" s="2" t="inlineStr" /><c r="P309" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q309" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="310"><c r="A310" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B310" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C310" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D310" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E310" s="2" t="inlineStr"><is><t>Do leków i rzutu w gruźlicy należy</t></is></c><c r="F310" s="2" t="inlineStr"><is><t>Ryfampicyna</t></is></c><c r="G310" s="2" t="inlineStr"><is><t>Izoniazyd</t></is></c><c r="H310" s="2" t="inlineStr"><is><t>Pyryzynamid</t></is></c><c r="I310" s="2" t="inlineStr" /><c r="J310" s="2" t="inlineStr" /><c r="K310" s="2" t="inlineStr"><is><t>Kanamycna</t></is></c><c r="L310" s="2" t="inlineStr" /><c r="M310" s="2" t="inlineStr" /><c r="N310" s="2" t="inlineStr" /><c r="O310" s="2" t="inlineStr" /><c r="P310" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q310" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="311"><c r="A311" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B311" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C311" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D311" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E311" s="2" t="inlineStr"><is><t>Podczas stosowania morfiny nie rozwija się tolerancja na TYLKO NA TE!!!</t></is></c><c r="F311" s="2" t="inlineStr"><is><t>Zaparcia</t></is></c><c r="G311" s="2" t="inlineStr"><is><t>Zwężenie źrenic</t></is></c><c r="H311" s="2" t="inlineStr" /><c r="I311" s="2" t="inlineStr" /><c r="J311" s="2" t="inlineStr" /><c r="K311" s="2" t="inlineStr"><is><t>Wymioty</t></is></c><c r="L311" s="2" t="inlineStr"><is><t>Depresję oddechową</t></is></c><c r="M311" s="2" t="inlineStr" /><c r="N311" s="2" t="inlineStr" /><c r="O311" s="2" t="inlineStr" /><c r="P311" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q311" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="312"><c r="A312" s="2" t="inlineStr"><is><t>NARKOTYCZNE LEKI PRZECIWBÓLOWE</t></is></c><c r="B312" s="2" t="inlineStr"><is><t>Sposób podania</t></is></c><c r="C312" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D312" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E312" s="2" t="inlineStr"><is><t>W farmakoterapii silnego bólu przebijającego stosujemy</t></is></c><c r="F312" s="2" t="inlineStr"><is><t>Morfinę doustnie w dawkach ratunkowych</t></is></c><c r="G312" s="2" t="inlineStr"><is><t>Fentanyl w postaci dopoliczkowej</t></is></c><c r="H312" s="2" t="inlineStr"><is><t>Buprenorfinę podjęzykowo</t></is></c><c r="I312" s="2" t="inlineStr"><is><t>Fentanyl w postaci donosowej</t></is></c><c r="J312" s="2" t="inlineStr" /><c r="K312" s="2" t="inlineStr" /><c r="L312" s="2" t="inlineStr" /><c r="M312" s="2" t="inlineStr" /><c r="N312" s="2" t="inlineStr" /><c r="O312" s="2" t="inlineStr" /><c r="P312" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q312" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="313"><c r="A313" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B313" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C313" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D313" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E313" s="2" t="inlineStr"><is><t>Ośrodkowe działania opioidów obejmują</t></is></c><c r="F313" s="2" t="inlineStr"><is><t>Działanie przeciwkaszlowe</t></is></c><c r="G313" s="2" t="inlineStr"><is><t>Wymioty</t></is></c><c r="H313" s="2" t="inlineStr" /><c r="I313" s="2" t="inlineStr" /><c r="J313" s="2" t="inlineStr" /><c r="K313" s="2" t="inlineStr"><is><t>Zwiększenie ciśnienia w drogach żółciowych</t></is></c><c r="L313" s="2" t="inlineStr"><is><t>Zaparcia</t></is></c><c r="M313" s="2" t="inlineStr" /><c r="N313" s="2" t="inlineStr" /><c r="O313" s="2" t="inlineStr" /><c r="P313" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q313" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="314"><c r="A314" s="2" t="inlineStr"><is><t>NARKOTYCZNE LEKI PRZECIWBÓLOWE</t></is></c><c r="B314" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C314" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D314" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E314" s="2" t="inlineStr"><is><t>Efekt pułapowy wykazuje</t></is></c><c r="F314" s="2" t="inlineStr"><is><t>Buprenorfina</t></is></c><c r="G314" s="2" t="inlineStr" /><c r="H314" s="2" t="inlineStr" /><c r="I314" s="2" t="inlineStr" /><c r="J314" s="2" t="inlineStr" /><c r="K314" s="2" t="inlineStr"><is><t>Morfina</t></is></c><c r="L314" s="2" t="inlineStr"><is><t>Kodeina</t></is></c><c r="M314" s="2" t="inlineStr"><is><t>Metadon</t></is></c><c r="N314" s="2" t="inlineStr" /><c r="O314" s="2" t="inlineStr" /><c r="P314" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q314" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="315"><c r="A315" s="2" t="inlineStr"><is><t>CUKRZYCA</t></is></c><c r="B315" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C315" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D315" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E315" s="2" t="inlineStr"><is><t>Metformina</t></is></c><c r="F315" s="2" t="inlineStr"><is><t>Zaburza wchłanianie witaminy B12</t></is></c><c r="G315" s="2" t="inlineStr"><is><t>Może powodować kwasicę metaboliczną</t></is></c><c r="H315" s="2" t="inlineStr" /><c r="I315" s="2" t="inlineStr" /><c r="J315" s="2" t="inlineStr" /><c r="K315" s="2" t="inlineStr"><is><t>Stymuluje wydzielanie insuliny</t></is></c><c r="L315" s="2" t="inlineStr"><is><t>Powoduje przyrost masy ciała</t></is></c><c r="M315" s="2" t="inlineStr" /><c r="N315" s="2" t="inlineStr" /><c r="O315" s="2" t="inlineStr" /><c r="P315" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q315" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="316"><c r="A316" s="2" t="inlineStr"><is><t>CUKRZYCA</t></is></c><c r="B316" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C316" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D316" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E316" s="2" t="inlineStr"><is><t>Szybkie analogi insuliny</t></is></c><c r="F316" s="2" t="inlineStr"><is><t>Lispro</t></is></c><c r="G316" s="2" t="inlineStr"><is><t>Aspart</t></is></c><c r="H316" s="2" t="inlineStr" /><c r="I316" s="2" t="inlineStr" /><c r="J316" s="2" t="inlineStr" /><c r="K316" s="2" t="inlineStr"><is><t>Glargina</t></is></c><c r="L316" s="2" t="inlineStr"><is><t>Detemir</t></is></c><c r="M316" s="2" t="inlineStr" /><c r="N316" s="2" t="inlineStr" /><c r="O316" s="2" t="inlineStr" /><c r="P316" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q316" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="317"><c r="A317" s="2" t="inlineStr"><is><t>ANTYKONCEPCJA</t></is></c><c r="B317" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C317" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D317" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E317" s="2" t="inlineStr"><is><t>Działania niepożądane hormonalnych środków antykoncepcyjnych z powodu obecności gestagenu</t></is></c><c r="F317" s="2" t="inlineStr"><is><t>Przyrost masy ciała</t></is></c><c r="G317" s="2" t="inlineStr"><is><t>Obniżenie libido</t></is></c><c r="H317" s="2" t="inlineStr"><is><t>Depresja</t></is></c><c r="I317" s="2" t="inlineStr"><is><t>Hirsutyzm</t></is></c><c r="J317" s="2" t="inlineStr" /><c r="K317" s="2" t="inlineStr" /><c r="L317" s="2" t="inlineStr" /><c r="M317" s="2" t="inlineStr" /><c r="N317" s="2" t="inlineStr" /><c r="O317" s="2" t="inlineStr" /><c r="P317" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q317" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="318"><c r="A318" s="2" t="inlineStr"><is><t>HORMONY PŁCIOWE</t></is></c><c r="B318" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C318" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D318" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E318" s="2" t="inlineStr"><is><t>Hiperprolaktynemia</t></is></c><c r="F318" s="2" t="inlineStr"><is><t>Karbegolina</t></is></c><c r="G318" s="2" t="inlineStr"><is><t>Bromokryptyna</t></is></c><c r="H318" s="2" t="inlineStr" /><c r="I318" s="2" t="inlineStr" /><c r="J318" s="2" t="inlineStr" /><c r="K318" s="2" t="inlineStr"><is><t>Gorserelina</t></is></c><c r="L318" s="2" t="inlineStr"><is><t>Finasteryd</t></is></c><c r="M318" s="2" t="inlineStr" /><c r="N318" s="2" t="inlineStr" /><c r="O318" s="2" t="inlineStr" /><c r="P318" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q318" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="319"><c r="A319" s="2" t="inlineStr"><is><t>CUKRZYCA</t></is></c><c r="B319" s="2" t="inlineStr"><is><t>Sposób podania</t></is></c><c r="C319" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D319" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E319" s="2" t="inlineStr"><is><t>Terapia cukrzycy typu 2 podskórnie</t></is></c><c r="F319" s="2" t="inlineStr"><is><t>Detemir</t></is></c><c r="G319" s="2" t="inlineStr" /><c r="H319" s="2" t="inlineStr" /><c r="I319" s="2" t="inlineStr" /><c r="J319" s="2" t="inlineStr" /><c r="K319" s="2" t="inlineStr"><is><t>Glipizyd</t></is></c><c r="L319" s="2" t="inlineStr"><is><t>Liraglutyd</t></is></c><c r="M319" s="2" t="inlineStr"><is><t>Linagliptyna</t></is></c><c r="N319" s="2" t="inlineStr" /><c r="O319" s="2" t="inlineStr" /><c r="P319" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q319" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="320"><c r="A320" s="2" t="inlineStr"><is><t>TARCZYCA</t></is></c><c r="B320" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C320" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D320" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E320" s="2" t="inlineStr"><is><t>Terapia nadczynności tarczycy</t></is></c><c r="F320" s="2" t="inlineStr"><is><t>Jod radioaktywny</t></is></c><c r="G320" s="2" t="inlineStr"><is><t>Bisoprolol</t></is></c><c r="H320" s="2" t="inlineStr"><is><t>Tiamazol</t></is></c><c r="I320" s="2" t="inlineStr"><is><t>Propylotiouracyl</t></is></c><c r="J320" s="2" t="inlineStr" /><c r="K320" s="2" t="inlineStr" /><c r="L320" s="2" t="inlineStr" /><c r="M320" s="2" t="inlineStr" /><c r="N320" s="2" t="inlineStr" /><c r="O320" s="2" t="inlineStr" /><c r="P320" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q320" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="321"><c r="A321" s="2" t="inlineStr"><is><t>LEKI IMMUNOSUPRESYJNE</t></is></c><c r="B321" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C321" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D321" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E321" s="2" t="inlineStr"><is><t>Cyklosporyna</t></is></c><c r="F321" s="2" t="inlineStr"><is><t>Jest eliminowana przez wątrobę</t></is></c><c r="G321" s="2" t="inlineStr"><is><t>Jest stosowana w celu zapobiegania odrzucania przeszczepów</t></is></c><c r="H321" s="2" t="inlineStr" /><c r="I321" s="2" t="inlineStr" /><c r="J321" s="2" t="inlineStr" /><c r="K321" s="2" t="inlineStr"><is><t>Jest aktywatorem kalcyneuryny</t></is></c><c r="L321" s="2" t="inlineStr"><is><t>Może powodować atrofię dziąseł</t></is></c><c r="M321" s="2" t="inlineStr" /><c r="N321" s="2" t="inlineStr" /><c r="O321" s="2" t="inlineStr" /><c r="P321" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q321" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="322"><c r="A322" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B322" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C322" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D322" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E322" s="2" t="inlineStr"><is><t>Podczas terapii GKS może dojsć do pogorszenia przebiegu</t></is></c><c r="F322" s="2" t="inlineStr"><is><t>Cukrzycy</t></is></c><c r="G322" s="2" t="inlineStr"><is><t>Gruźlicy</t></is></c><c r="H322" s="2" t="inlineStr"><is><t>Osteoporozy</t></is></c><c r="I322" s="2" t="inlineStr" /><c r="J322" s="2" t="inlineStr" /><c r="K322" s="2" t="inlineStr"><is><t>Małopłytkowości idiopatycznej</t></is></c><c r="L322" s="2" t="inlineStr" /><c r="M322" s="2" t="inlineStr" /><c r="N322" s="2" t="inlineStr" /><c r="O322" s="2" t="inlineStr" /><c r="P322" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q322" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="323"><c r="A323" s="2" t="inlineStr"><is><t>NIEOPIOIDOWE LEKI PRZECIWBÓLOWE</t></is></c><c r="B323" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C323" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D323" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E323" s="2" t="inlineStr"><is><t>Wzrostu ryzyka sercowo-naczyniowego NIE powoduje</t></is></c><c r="F323" s="2" t="inlineStr"><is><t>Kwas acetylosalicylowy</t></is></c><c r="G323" s="2" t="inlineStr" /><c r="H323" s="2" t="inlineStr" /><c r="I323" s="2" t="inlineStr" /><c r="J323" s="2" t="inlineStr" /><c r="K323" s="2" t="inlineStr"><is><t>Celekoksyb</t></is></c><c r="L323" s="2" t="inlineStr"><is><t>Indometacyna</t></is></c><c r="M323" s="2" t="inlineStr"><is><t>Ketoprofen</t></is></c><c r="N323" s="2" t="inlineStr" /><c r="O323" s="2" t="inlineStr" /><c r="P323" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q323" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="324"><c r="A324" s="2" t="inlineStr"><is><t>NIEOPIOIDOWE LEKI PRZECIWBÓLOWE</t></is></c><c r="B324" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C324" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D324" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E324" s="2" t="inlineStr"><is><t>Zmniejszenie ryzyka gastrotoksyczności NLPZ – co możemy</t></is></c><c r="F324" s="2" t="inlineStr"><is><t>Analogi PGE1</t></is></c><c r="G324" s="2" t="inlineStr"><is><t>IPP</t></is></c><c r="H324" s="2" t="inlineStr" /><c r="I324" s="2" t="inlineStr" /><c r="J324" s="2" t="inlineStr" /><c r="K324" s="2" t="inlineStr"><is><t>GKS</t></is></c><c r="L324" s="2" t="inlineStr"><is><t>Preparaty o wybiórczym powinowactwie do COX1</t></is></c><c r="M324" s="2" t="inlineStr" /><c r="N324" s="2" t="inlineStr" /><c r="O324" s="2" t="inlineStr" /><c r="P324" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q324" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="325"><c r="A325" s="2" t="inlineStr"><is><t>NIEOPIOIDOWE LEKI PRZECIWBÓLOWE</t></is></c><c r="B325" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C325" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D325" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E325" s="2" t="inlineStr"><is><t>Paracetamol</t></is></c><c r="F325" s="2" t="inlineStr"><is><t>Jest metabolizowany przez enzymy cytochromu P-450</t></is></c><c r="G325" s="2" t="inlineStr" /><c r="H325" s="2" t="inlineStr" /><c r="I325" s="2" t="inlineStr" /><c r="J325" s="2" t="inlineStr" /><c r="K325" s="2" t="inlineStr"><is><t>Działa silnie przeciwzapalnie</t></is></c><c r="L325" s="2" t="inlineStr"><is><t>Hamuje COX2 w OUN</t></is></c><c r="M325" s="2" t="inlineStr"><is><t>Wykazuje działanie gastrotoksyczne</t></is></c><c r="N325" s="2" t="inlineStr" /><c r="O325" s="2" t="inlineStr" /><c r="P325" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q325" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="326"><c r="A326" s="2" t="inlineStr"><is><t>LEKI PRZECIWNOWOTWOROWE</t></is></c><c r="B326" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C326" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D326" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E326" s="2" t="inlineStr"><is><t>Leki immunosupresyjne</t></is></c><c r="F326" s="2" t="inlineStr"><is><t>Powodują upośledzenie odporności komórkowej</t></is></c><c r="G326" s="2" t="inlineStr"><is><t>Są lekami o wąskim wskaźniku terapeutycznym</t></is></c><c r="H326" s="2" t="inlineStr" /><c r="I326" s="2" t="inlineStr" /><c r="J326" s="2" t="inlineStr" /><c r="K326" s="2" t="inlineStr"><is><t>Zapobiegają rozwojowi nowotworów</t></is></c><c r="L326" s="2" t="inlineStr"><is><t>Znajdują zastosowanie w terapii chorób neurodegeneracyjnych</t></is></c><c r="M326" s="2" t="inlineStr" /><c r="N326" s="2" t="inlineStr" /><c r="O326" s="2" t="inlineStr" /><c r="P326" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q326" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="327"><c r="A327" s="2" t="inlineStr"><is><t>UKŁAD ODDECHOWY</t></is></c><c r="B327" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C327" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D327" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E327" s="2" t="inlineStr"><is><t>Wskaż prawidłowe pary lek – wskazanie</t></is></c><c r="F327" s="2" t="inlineStr"><is><t>Bromoheksyna – astma oskrzelowa</t></is></c><c r="G327" s="2" t="inlineStr" /><c r="H327" s="2" t="inlineStr" /><c r="I327" s="2" t="inlineStr" /><c r="J327" s="2" t="inlineStr" /><c r="K327" s="2" t="inlineStr"><is><t>Acetylocysteina – ostre zapalenie zatok obocznych nosa</t></is></c><c r="L327" s="2" t="inlineStr"><is><t>Dornaza alfa – sarkoidoza</t></is></c><c r="M327" s="2" t="inlineStr"><is><t>Ambroksol – infekcyjne zaostrzenie POChP</t></is></c><c r="N327" s="2" t="inlineStr" /><c r="O327" s="2" t="inlineStr" /><c r="P327" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q327" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="328"><c r="A328" s="2" t="inlineStr"><is><t>UKŁAD WSPÓŁCZULNY</t></is></c><c r="B328" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C328" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D328" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E328" s="2" t="inlineStr"><is><t>W celu przerwania ataku duszności Zależy jakiej dusznosći. Duszności przygodnej będą same SABA, jak mamy zaostrzenie astmy to GKS też</t></is></c><c r="F328" s="2" t="inlineStr"><is><t>Fenoterol</t></is></c><c r="G328" s="2" t="inlineStr"><is><t>Salbutamol</t></is></c><c r="H328" s="2" t="inlineStr" /><c r="I328" s="2" t="inlineStr" /><c r="J328" s="2" t="inlineStr" /><c r="K328" s="2" t="inlineStr"><is><t>Salmeterol</t></is></c><c r="L328" s="2" t="inlineStr"><is><t>Flutikazon</t></is></c><c r="M328" s="2" t="inlineStr" /><c r="N328" s="2" t="inlineStr" /><c r="O328" s="2" t="inlineStr" /><c r="P328" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q328" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="329"><c r="A329" s="2" t="inlineStr"><is><t>UKŁAD ODDECHOWY</t></is></c><c r="B329" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C329" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D329" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E329" s="2" t="inlineStr"><is><t>Omalizumab</t></is></c><c r="F329" s="2" t="inlineStr"><is><t>Blokuje łączenie IgE z komórkami tucznymi</t></is></c><c r="G329" s="2" t="inlineStr"><is><t>Zmniejsza liczbę zaostrzeń astmy</t></is></c><c r="H329" s="2" t="inlineStr" /><c r="I329" s="2" t="inlineStr" /><c r="J329" s="2" t="inlineStr" /><c r="K329" s="2" t="inlineStr"><is><t>Stosowany jest w astmie o umiarkowanej ciężkości</t></is></c><c r="L329" s="2" t="inlineStr"><is><t>Zwiększa zapotrzebowanie na GKS</t></is></c><c r="M329" s="2" t="inlineStr" /><c r="N329" s="2" t="inlineStr" /><c r="O329" s="2" t="inlineStr" /><c r="P329" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q329" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="330"><c r="A330" s="2" t="inlineStr"><is><t>UKŁAD WSPÓŁCZULNY</t></is></c><c r="B330" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C330" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D330" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E330" s="2" t="inlineStr"><is><t>Farmakoterapia POChP kategoria A i B</t></is></c><c r="F330" s="2" t="inlineStr"><is><t>Krótko i długo działające cholinolityki</t></is></c><c r="G330" s="2" t="inlineStr"><is><t>Krótko i długo działające beta2 adrenomimetyki</t></is></c><c r="H330" s="2" t="inlineStr" /><c r="I330" s="2" t="inlineStr" /><c r="J330" s="2" t="inlineStr" /><c r="K330" s="2" t="inlineStr"><is><t>GKS</t></is></c><c r="L330" s="2" t="inlineStr"><is><t>Inhibitory fosfodiesterazy 4</t></is></c><c r="M330" s="2" t="inlineStr" /><c r="N330" s="2" t="inlineStr" /><c r="O330" s="2" t="inlineStr" /><c r="P330" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q330" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="331"><c r="A331" s="2" t="inlineStr"><is><t>FARMAKOKINETYKA</t></is></c><c r="B331" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C331" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D331" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E331" s="2" t="inlineStr"><is><t>Omeprazol</t></is></c><c r="F331" s="2" t="inlineStr"><is><t>Powoduje nieodwracalne zablokowanie pompy protonowej</t></is></c><c r="G331" s="2" t="inlineStr"><is><t>Jest inhibitorem enzymów cytochromu P-450</t></is></c><c r="H331" s="2" t="inlineStr" /><c r="I331" s="2" t="inlineStr" /><c r="J331" s="2" t="inlineStr" /><c r="K331" s="2" t="inlineStr"><is><t>Hamuje wydzielanie kwasu solnego przez 6-12h</t></is></c><c r="L331" s="2" t="inlineStr"><is><t>Jest aktywowany przez pepsynę</t></is></c><c r="M331" s="2" t="inlineStr" /><c r="N331" s="2" t="inlineStr" /><c r="O331" s="2" t="inlineStr" /><c r="P331" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q331" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="332"><c r="A332" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B332" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C332" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D332" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E332" s="2" t="inlineStr"><is><t>Metoklopramid</t></is></c><c r="F332" s="2" t="inlineStr"><is><t>Jest agonistą receptorów dopaminowych</t></is></c><c r="G332" s="2" t="inlineStr"><is><t>Działa przeciwwymiotnie</t></is></c><c r="H332" s="2" t="inlineStr" /><c r="I332" s="2" t="inlineStr" /><c r="J332" s="2" t="inlineStr" /><c r="K332" s="2" t="inlineStr"><is><t>Zmniejsza objawy pozapiramidowe</t></is></c><c r="L332" s="2" t="inlineStr"><is><t>Zmniejsza stężenie prolaktyny</t></is></c><c r="M332" s="2" t="inlineStr" /><c r="N332" s="2" t="inlineStr" /><c r="O332" s="2" t="inlineStr" /><c r="P332" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q332" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="333"><c r="A333" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B333" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C333" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D333" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E333" s="2" t="inlineStr"><is><t>Przewlekłe zapalenie trzustki z alkoholu</t></is></c><c r="F333" s="2" t="inlineStr"><is><t>Preparaty enzymów trzustkowych</t></is></c><c r="G333" s="2" t="inlineStr"><is><t>Leki przeciwbólowe</t></is></c><c r="H333" s="2" t="inlineStr" /><c r="I333" s="2" t="inlineStr" /><c r="J333" s="2" t="inlineStr" /><c r="K333" s="2" t="inlineStr"><is><t>GKS</t></is></c><c r="L333" s="2" t="inlineStr"><is><t>Leki przeciwbakteryjne</t></is></c><c r="M333" s="2" t="inlineStr" /><c r="N333" s="2" t="inlineStr" /><c r="O333" s="2" t="inlineStr" /><c r="P333" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q333" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="334"><c r="A334" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B334" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C334" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D334" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E334" s="2" t="inlineStr"><is><t>Chory z encefalopatią wątrobową, możemy</t></is></c><c r="F334" s="2" t="inlineStr"><is><t>Asparaginian ornityny</t></is></c><c r="G334" s="2" t="inlineStr"><is><t>Laktuloza</t></is></c><c r="H334" s="2" t="inlineStr"><is><t>Ryfaksymina</t></is></c><c r="I334" s="2" t="inlineStr" /><c r="J334" s="2" t="inlineStr" /><c r="K334" s="2" t="inlineStr"><is><t>Piracetam</t></is></c><c r="L334" s="2" t="inlineStr" /><c r="M334" s="2" t="inlineStr" /><c r="N334" s="2" t="inlineStr" /><c r="O334" s="2" t="inlineStr" /><c r="P334" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q334" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="335"><c r="A335" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B335" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C335" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D335" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E335" s="2" t="inlineStr"><is><t>Schematy eradykacji H. Pylori (rekomendowane)</t></is></c><c r="F335" s="2" t="inlineStr"><is><t>Pantoprazol/cytrynian bizmutu/tetracyklina/metronidazol</t></is></c><c r="G335" s="2" t="inlineStr" /><c r="H335" s="2" t="inlineStr" /><c r="I335" s="2" t="inlineStr" /><c r="J335" s="2" t="inlineStr" /><c r="K335" s="2" t="inlineStr"><is><t>Cytrynian bizmutu/metronidazol</t></is></c><c r="L335" s="2" t="inlineStr"><is><t>Mizoprostol/metronidazol/klarytromycyna</t></is></c><c r="M335" s="2" t="inlineStr"><is><t>Ranitydyna/amoksycylina/metronidazol</t></is></c><c r="N335" s="2" t="inlineStr" /><c r="O335" s="2" t="inlineStr" /><c r="P335" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q335" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="336"><c r="A336" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B336" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C336" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D336" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E336" s="2" t="inlineStr"><is><t>Lek przeciwzakrzepowy – czas odstawienia (planowa, duże ryzyko krwawienia, nerki prawidłowe)</t></is></c><c r="F336" s="2" t="inlineStr"><is><t>Dabigatran – 1 dzień</t></is></c><c r="G336" s="2" t="inlineStr" /><c r="H336" s="2" t="inlineStr" /><c r="I336" s="2" t="inlineStr" /><c r="J336" s="2" t="inlineStr" /><c r="K336" s="2" t="inlineStr"><is><t>Warfaryna – 2 dni</t></is></c><c r="L336" s="2" t="inlineStr"><is><t>Acenokumarol – 10 dni</t></is></c><c r="M336" s="2" t="inlineStr"><is><t>Kwas acetylosalicylowy – 5 dni</t></is></c><c r="N336" s="2" t="inlineStr" /><c r="O336" s="2" t="inlineStr" /><c r="P336" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q336" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="337"><c r="A337" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B337" s="2" t="inlineStr"><is><t>Monitorowanie</t></is></c><c r="C337" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D337" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E337" s="2" t="inlineStr"><is><t>Lek – monitorowanie</t></is></c><c r="F337" s="2" t="inlineStr"><is><t>Heparyna niefrakcjonowana – APTT</t></is></c><c r="G337" s="2" t="inlineStr" /><c r="H337" s="2" t="inlineStr" /><c r="I337" s="2" t="inlineStr" /><c r="J337" s="2" t="inlineStr" /><c r="K337" s="2" t="inlineStr"><is><t>Dabigatran – INR</t></is></c><c r="L337" s="2" t="inlineStr"><is><t>Acenokumarol – czas ekarynowy</t></is></c><c r="M337" s="2" t="inlineStr"><is><t>Rywaroksaban – czas trombinowy</t></is></c><c r="N337" s="2" t="inlineStr" /><c r="O337" s="2" t="inlineStr" /><c r="P337" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q337" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="338"><c r="A338" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B338" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C338" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D338" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E338" s="2" t="inlineStr"><is><t>Działanie antyagregacyjne</t></is></c><c r="F338" s="2" t="inlineStr"><is><t>Antagoniści receptorów P2Y12</t></is></c><c r="G338" s="2" t="inlineStr" /><c r="H338" s="2" t="inlineStr" /><c r="I338" s="2" t="inlineStr" /><c r="J338" s="2" t="inlineStr" /><c r="K338" s="2" t="inlineStr"><is><t>Agoniści receptorów GP IIb/IIIa</t></is></c><c r="L338" s="2" t="inlineStr"><is><t>Inhibitory COX2</t></is></c><c r="M338" s="2" t="inlineStr"><is><t>Agoniści receptorów TXA2</t></is></c><c r="N338" s="2" t="inlineStr" /><c r="O338" s="2" t="inlineStr" /><c r="P338" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q338" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="339"><c r="A339" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B339" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C339" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D339" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E339" s="2" t="inlineStr"><is><t>Zahamowanie agregacji płytek zależne od ADP po</t></is></c><c r="F339" s="2" t="inlineStr"><is><t>Klopidogrelu</t></is></c><c r="G339" s="2" t="inlineStr"><is><t>Tikagreloru</t></is></c><c r="H339" s="2" t="inlineStr" /><c r="I339" s="2" t="inlineStr" /><c r="J339" s="2" t="inlineStr" /><c r="K339" s="2" t="inlineStr"><is><t>Enoksaparyny</t></is></c><c r="L339" s="2" t="inlineStr"><is><t>Dipyridamolu</t></is></c><c r="M339" s="2" t="inlineStr" /><c r="N339" s="2" t="inlineStr" /><c r="O339" s="2" t="inlineStr" /><c r="P339" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q339" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="340"><c r="A340" s="2" t="inlineStr"><is><t>LEKI HIPOLIPEMIZUJĄCE</t></is></c><c r="B340" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C340" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D340" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E340" s="2" t="inlineStr"><is><t>Statyny</t></is></c><c r="F340" s="2" t="inlineStr"><is><t>Zmniejszają stężenie cholesterolu LDL</t></is></c><c r="G340" s="2" t="inlineStr"><is><t>Zmniejszą stężenie triglicerydów</t></is></c><c r="H340" s="2" t="inlineStr" /><c r="I340" s="2" t="inlineStr" /><c r="J340" s="2" t="inlineStr" /><c r="K340" s="2" t="inlineStr"><is><t>Nie wpływają na stężenie cholesterolu wewnątrzkomórkowego</t></is></c><c r="L340" s="2" t="inlineStr"><is><t>Zmniejszają stężęnie cholesterolu HDL</t></is></c><c r="M340" s="2" t="inlineStr" /><c r="N340" s="2" t="inlineStr" /><c r="O340" s="2" t="inlineStr" /><c r="P340" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q340" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="341"><c r="A341" s="2" t="inlineStr"><is><t>LEKI HIPOLIPEMIZUJĄCE</t></is></c><c r="B341" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C341" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D341" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E341" s="2" t="inlineStr"><is><t>Wielokierunkowe działanie statyn</t></is></c><c r="F341" s="2" t="inlineStr"><is><t>Poprawę funkcji śródbłonka</t></is></c><c r="G341" s="2" t="inlineStr"><is><t>Efekt przeciwzapalny</t></is></c><c r="H341" s="2" t="inlineStr"><is><t>Wpływ na fibrynolizę</t></is></c><c r="I341" s="2" t="inlineStr"><is><t>Stabilizację blaszki miażdżycowej</t></is></c><c r="J341" s="2" t="inlineStr" /><c r="K341" s="2" t="inlineStr" /><c r="L341" s="2" t="inlineStr" /><c r="M341" s="2" t="inlineStr" /><c r="N341" s="2" t="inlineStr" /><c r="O341" s="2" t="inlineStr" /><c r="P341" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q341" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="342"><c r="A342" s="2" t="inlineStr"><is><t>CUKRZYCA</t></is></c><c r="B342" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C342" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D342" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E342" s="2" t="inlineStr"><is><t>Farmakoterapia otyłości</t></is></c><c r="F342" s="2" t="inlineStr"><is><t>Liraglutyd</t></is></c><c r="G342" s="2" t="inlineStr"><is><t>Orlistat</t></is></c><c r="H342" s="2" t="inlineStr" /><c r="I342" s="2" t="inlineStr" /><c r="J342" s="2" t="inlineStr" /><c r="K342" s="2" t="inlineStr"><is><t>Paroksetyna</t></is></c><c r="L342" s="2" t="inlineStr"><is><t>Naltrekson</t></is></c><c r="M342" s="2" t="inlineStr" /><c r="N342" s="2" t="inlineStr" /><c r="O342" s="2" t="inlineStr" /><c r="P342" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q342" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="343"><c r="A343" s="2" t="inlineStr"><is><t>UKŁAD WSPÓŁCZULNY</t></is></c><c r="B343" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C343" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D343" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E343" s="2" t="inlineStr"><is><t>Do beta adrenolityków zmniejszających śmiertelność w skurczowej niewydolności serca</t></is></c><c r="F343" s="2" t="inlineStr"><is><t>Nebiwolol</t></is></c><c r="G343" s="2" t="inlineStr" /><c r="H343" s="2" t="inlineStr" /><c r="I343" s="2" t="inlineStr" /><c r="J343" s="2" t="inlineStr" /><c r="K343" s="2" t="inlineStr"><is><t>Atenolol</t></is></c><c r="L343" s="2" t="inlineStr"><is><t>Esmolol</t></is></c><c r="M343" s="2" t="inlineStr"><is><t>Acebutolol</t></is></c><c r="N343" s="2" t="inlineStr" /><c r="O343" s="2" t="inlineStr" /><c r="P343" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q343" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="344"><c r="A344" s="2" t="inlineStr"><is><t>CHOROBA NIEDOKRWIENNA SERCA</t></is></c><c r="B344" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C344" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D344" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E344" s="2" t="inlineStr"><is><t>Donory NO</t></is></c><c r="F344" s="2" t="inlineStr"><is><t>Nikorandil</t></is></c><c r="G344" s="2" t="inlineStr"><is><t>Molsidomina</t></is></c><c r="H344" s="2" t="inlineStr"><is><t>Diazontanizosorbitol</t></is></c><c r="I344" s="2" t="inlineStr" /><c r="J344" s="2" t="inlineStr" /><c r="K344" s="2" t="inlineStr"><is><t>Trimetazydyna</t></is></c><c r="L344" s="2" t="inlineStr" /><c r="M344" s="2" t="inlineStr" /><c r="N344" s="2" t="inlineStr" /><c r="O344" s="2" t="inlineStr" /><c r="P344" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q344" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="345"><c r="A345" s="2" t="inlineStr"><is><t>UKŁAD WSPÓŁCZULNY</t></is></c><c r="B345" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C345" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D345" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E345" s="2" t="inlineStr"><is><t>Leki I wyborou w monoterapii NT</t></is></c><c r="F345" s="2" t="inlineStr"><is><t>Antagoniści receptora angiotensynowego</t></is></c><c r="G345" s="2" t="inlineStr"><is><t>Antagoniści kanałów wapniowych</t></is></c><c r="H345" s="2" t="inlineStr" /><c r="I345" s="2" t="inlineStr" /><c r="J345" s="2" t="inlineStr" /><c r="K345" s="2" t="inlineStr"><is><t>Alfa1 adrenolityki</t></is></c><c r="L345" s="2" t="inlineStr"><is><t>Inhibitory reniny</t></is></c><c r="M345" s="2" t="inlineStr" /><c r="N345" s="2" t="inlineStr" /><c r="O345" s="2" t="inlineStr" /><c r="P345" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q345" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="346"><c r="A346" s="2" t="inlineStr"><is><t>LEKI MOCZOPĘDNE</t></is></c><c r="B346" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C346" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D346" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E346" s="2" t="inlineStr"><is><t>Zmniejszenie śmiertnelności w skurczowej niewydolności serca</t></is></c><c r="F346" s="2" t="inlineStr"><is><t>Inhibitory konwertazy angiotensyny</t></is></c><c r="G346" s="2" t="inlineStr"><is><t>Antagoniści aldosteronu</t></is></c><c r="H346" s="2" t="inlineStr" /><c r="I346" s="2" t="inlineStr" /><c r="J346" s="2" t="inlineStr" /><c r="K346" s="2" t="inlineStr"><is><t>Waptany</t></is></c><c r="L346" s="2" t="inlineStr"><is><t>Diuretyki pętlowe</t></is></c><c r="M346" s="2" t="inlineStr" /><c r="N346" s="2" t="inlineStr" /><c r="O346" s="2" t="inlineStr" /><c r="P346" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q346" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="347"><c r="A347" s="2" t="inlineStr"><is><t>NADCIŚNIENIE TĘTNICZE</t></is></c><c r="B347" s="2" t="inlineStr"><is><t>Interakcje</t></is></c><c r="C347" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D347" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E347" s="2" t="inlineStr"><is><t>Przeciwskane jest jednoczesne stosowanie beta adrenolityków i</t></is></c><c r="F347" s="2" t="inlineStr"><is><t>Werapamilu</t></is></c><c r="G347" s="2" t="inlineStr" /><c r="H347" s="2" t="inlineStr" /><c r="I347" s="2" t="inlineStr" /><c r="J347" s="2" t="inlineStr" /><c r="K347" s="2" t="inlineStr"><is><t>Kaptoprylu</t></is></c><c r="L347" s="2" t="inlineStr"><is><t>Torasemidu</t></is></c><c r="M347" s="2" t="inlineStr"><is><t>Irbesartanu</t></is></c><c r="N347" s="2" t="inlineStr" /><c r="O347" s="2" t="inlineStr" /><c r="P347" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q347" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="348"><c r="A348" s="2" t="inlineStr"><is><t>NADCIŚNIENIE TĘTNICZE</t></is></c><c r="B348" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C348" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D348" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E348" s="2" t="inlineStr"><is><t>Stan kliniczny – lek nadciśnieniowy</t></is></c><c r="F348" s="2" t="inlineStr"><is><t>Mikroalbuminuria – peryndopryl</t></is></c><c r="G348" s="2" t="inlineStr"><is><t>Tętniak aorty – bisoprolol</t></is></c><c r="H348" s="2" t="inlineStr"><is><t>Ciąża – metyldopa</t></is></c><c r="I348" s="2" t="inlineStr"><is><t>Chory po 80 rż. – indapamid</t></is></c><c r="J348" s="2" t="inlineStr" /><c r="K348" s="2" t="inlineStr" /><c r="L348" s="2" t="inlineStr" /><c r="M348" s="2" t="inlineStr" /><c r="N348" s="2" t="inlineStr" /><c r="O348" s="2" t="inlineStr" /><c r="P348" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q348" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="349"><c r="A349" s="2" t="inlineStr"><is><t>NIEWYDOLNOŚĆ SERCA</t></is></c><c r="B349" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C349" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D349" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E349" s="2" t="inlineStr"><is><t>Inotropowe dodatnie</t></is></c><c r="F349" s="2" t="inlineStr"><is><t>Lewosymendan</t></is></c><c r="G349" s="2" t="inlineStr"><is><t>Milrinon</t></is></c><c r="H349" s="2" t="inlineStr" /><c r="I349" s="2" t="inlineStr" /><c r="J349" s="2" t="inlineStr" /><c r="K349" s="2" t="inlineStr"><is><t>Nesirytyd</t></is></c><c r="L349" s="2" t="inlineStr"><is><t>Sakubitryl</t></is></c><c r="M349" s="2" t="inlineStr" /><c r="N349" s="2" t="inlineStr" /><c r="O349" s="2" t="inlineStr" /><c r="P349" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q349" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="350"><c r="A350" s="2" t="inlineStr"><is><t>NADCIŚNIENIE TĘTNICZE</t></is></c><c r="B350" s="2" t="inlineStr"><is><t>Interakcje</t></is></c><c r="C350" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D350" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E350" s="2" t="inlineStr"><is><t>Skojarzenia leków w nadciśnieniu</t></is></c><c r="F350" s="2" t="inlineStr"><is><t>Inhibitor konwertazy angiotensyny + diuretyk tiazydowy</t></is></c><c r="G350" s="2" t="inlineStr"><is><t>Inhibitor konwertazy angiotensyny + antagonista wapnia</t></is></c><c r="H350" s="2" t="inlineStr"><is><t>Diuretyk tiazydowy + antagonista wapnia</t></is></c><c r="I350" s="2" t="inlineStr" /><c r="J350" s="2" t="inlineStr" /><c r="K350" s="2" t="inlineStr"><is><t>Sartan + inhibitor konwertazy angiotensyny</t></is></c><c r="L350" s="2" t="inlineStr" /><c r="M350" s="2" t="inlineStr" /><c r="N350" s="2" t="inlineStr" /><c r="O350" s="2" t="inlineStr" /><c r="P350" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q350" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="351"><c r="A351" s="2" t="inlineStr"><is><t>ZABURZENIA RYTMU SERCA</t></is></c><c r="B351" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C351" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D351" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E351" s="2" t="inlineStr"><is><t>Amlodypina – działanie</t></is></c><c r="F351" s="2" t="inlineStr"><is><t>Zmniejszające opór obwodowy</t></is></c><c r="G351" s="2" t="inlineStr" /><c r="H351" s="2" t="inlineStr" /><c r="I351" s="2" t="inlineStr" /><c r="J351" s="2" t="inlineStr" /><c r="K351" s="2" t="inlineStr"><is><t>Chronotropowe dodatnie</t></is></c><c r="L351" s="2" t="inlineStr"><is><t>Inotropowe ujemne</t></is></c><c r="M351" s="2" t="inlineStr"><is><t>Dromotropowe ujemne</t></is></c><c r="N351" s="2" t="inlineStr" /><c r="O351" s="2" t="inlineStr" /><c r="P351" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q351" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="352"><c r="A352" s="2" t="inlineStr"><is><t>ZABURZENIA RYTMU SERCA</t></is></c><c r="B352" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C352" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D352" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E352" s="2" t="inlineStr"><is><t>Dławica naczynioskurczowa (Prinzmetala)</t></is></c><c r="F352" s="2" t="inlineStr"><is><t>Diltiazem</t></is></c><c r="G352" s="2" t="inlineStr"><is><t>Werapamil</t></is></c><c r="H352" s="2" t="inlineStr" /><c r="I352" s="2" t="inlineStr" /><c r="J352" s="2" t="inlineStr" /><c r="K352" s="2" t="inlineStr"><is><t>Atenolol</t></is></c><c r="L352" s="2" t="inlineStr"><is><t>Prazosyna</t></is></c><c r="M352" s="2" t="inlineStr" /><c r="N352" s="2" t="inlineStr" /><c r="O352" s="2" t="inlineStr" /><c r="P352" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q352" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="353"><c r="A353" s="2" t="inlineStr"><is><t>NADCIŚNIENIE TĘTNICZE</t></is></c><c r="B353" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C353" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D353" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E353" s="2" t="inlineStr"><is><t>Hiperkaliemia przy stosowaniu</t></is></c><c r="F353" s="2" t="inlineStr"><is><t>Kaptoprylu</t></is></c><c r="G353" s="2" t="inlineStr"><is><t>Amilorlydu</t></is></c><c r="H353" s="2" t="inlineStr" /><c r="I353" s="2" t="inlineStr" /><c r="J353" s="2" t="inlineStr" /><c r="K353" s="2" t="inlineStr"><is><t>Torasemidu</t></is></c><c r="L353" s="2" t="inlineStr"><is><t>Hydrochlortiazydu</t></is></c><c r="M353" s="2" t="inlineStr" /><c r="N353" s="2" t="inlineStr" /><c r="O353" s="2" t="inlineStr" /><c r="P353" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q353" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="354"><c r="A354" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B354" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C354" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D354" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E354" s="2" t="inlineStr"><is><t>OZW – postepowanie</t></is></c><c r="F354" s="2" t="inlineStr"><is><t>Furasemidu i.m</t></is></c><c r="G354" s="2" t="inlineStr"><is><t>Tikaglerolu p.o Klopidogrel bardziej, ale powiedzmy ze tak</t></is></c><c r="H354" s="2" t="inlineStr"><is><t>Morfiny s.c</t></is></c><c r="I354" s="2" t="inlineStr"><is><t>Kwasu acetylosalicylowego p.o</t></is></c><c r="J354" s="2" t="inlineStr" /><c r="K354" s="2" t="inlineStr" /><c r="L354" s="2" t="inlineStr" /><c r="M354" s="2" t="inlineStr" /><c r="N354" s="2" t="inlineStr" /><c r="O354" s="2" t="inlineStr" /><c r="P354" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q354" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="355"><c r="A355" s="2" t="inlineStr"><is><t>ZABURZENIA RYTMU SERCA</t></is></c><c r="B355" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C355" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D355" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E355" s="2" t="inlineStr"><is><t>Amiodaron ???</t></is></c><c r="F355" s="2" t="inlineStr"><is><t>Jest stosowany w arytmiach opornych na inne leki</t></is></c><c r="G355" s="2" t="inlineStr" /><c r="H355" s="2" t="inlineStr" /><c r="I355" s="2" t="inlineStr" /><c r="J355" s="2" t="inlineStr" /><c r="K355" s="2" t="inlineStr"><is><t>Działa inotropowo ujemnie</t></is></c><c r="L355" s="2" t="inlineStr"><is><t>Jest skuteczny wyłącznie w arytmiach komorowych</t></is></c><c r="M355" s="2" t="inlineStr"><is><t>Jest agonistą kanałów potasowych</t></is></c><c r="N355" s="2" t="inlineStr" /><c r="O355" s="2" t="inlineStr" /><c r="P355" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q355" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="356"><c r="A356" s="2" t="inlineStr"><is><t>LEKI MOCZOPĘDNE</t></is></c><c r="B356" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C356" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D356" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E356" s="2" t="inlineStr"><is><t>Eplerenon</t></is></c><c r="F356" s="2" t="inlineStr"><is><t>Selektywnie wiąże się z receptorem dla mineralokortykoidów</t></is></c><c r="G356" s="2" t="inlineStr" /><c r="H356" s="2" t="inlineStr" /><c r="I356" s="2" t="inlineStr" /><c r="J356" s="2" t="inlineStr" /><c r="K356" s="2" t="inlineStr"><is><t>Nie powoduje hiperkaliemii</t></is></c><c r="L356" s="2" t="inlineStr"><is><t>Jest agonistą receptorów dla androgenów</t></is></c><c r="M356" s="2" t="inlineStr"><is><t>Powoduje hipernatremię</t></is></c><c r="N356" s="2" t="inlineStr" /><c r="O356" s="2" t="inlineStr" /><c r="P356" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q356" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="357"><c r="A357" s="2" t="inlineStr"><is><t>PADACZKA</t></is></c><c r="B357" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C357" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D357" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E357" s="2" t="inlineStr"><is><t>TLPD – działania niepożądane</t></is></c><c r="F357" s="2" t="inlineStr"><is><t>Zwiększenie masy ciała</t></is></c><c r="G357" s="2" t="inlineStr"><is><t>Obniżenie progu drgawkowego</t></is></c><c r="H357" s="2" t="inlineStr"><is><t>Suchowść w ustach</t></is></c><c r="I357" s="2" t="inlineStr"><is><t>Nad lub niedociśnienie tętnicze</t></is></c><c r="J357" s="2" t="inlineStr" /><c r="K357" s="2" t="inlineStr" /><c r="L357" s="2" t="inlineStr" /><c r="M357" s="2" t="inlineStr" /><c r="N357" s="2" t="inlineStr" /><c r="O357" s="2" t="inlineStr" /><c r="P357" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q357" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="358"><c r="A358" s="2" t="inlineStr"><is><t>PADACZKA</t></is></c><c r="B358" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C358" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D358" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E358" s="2" t="inlineStr"><is><t>Lek przeciwpadaczkowy – mechanizm</t></is></c><c r="F358" s="2" t="inlineStr"><is><t>Gabapentyna – nasilenie transmisji GABA</t></is></c><c r="G358" s="2" t="inlineStr"><is><t>Karbamazepina – blokokowanie kanałów sodowych</t></is></c><c r="H358" s="2" t="inlineStr"><is><t>Etosuksymid – blokowanie kanałów wapniowych</t></is></c><c r="I358" s="2" t="inlineStr" /><c r="J358" s="2" t="inlineStr" /><c r="K358" s="2" t="inlineStr"><is><t>Lamotrygina – pobudzenie synaptycznego uwalniania aminokwasów</t></is></c><c r="L358" s="2" t="inlineStr" /><c r="M358" s="2" t="inlineStr" /><c r="N358" s="2" t="inlineStr" /><c r="O358" s="2" t="inlineStr" /><c r="P358" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q358" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="359"><c r="A359" s="2" t="inlineStr"><is><t>LEKI HIPOLIPEMIZUJĄCE</t></is></c><c r="B359" s="2" t="inlineStr"><is><t>Monitorowanie</t></is></c><c r="C359" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D359" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E359" s="2" t="inlineStr"><is><t>Klozapina wymaga monitorowania Wszystkie wymagają LPP</t></is></c><c r="F359" s="2" t="inlineStr"><is><t>Morfologii</t></is></c><c r="G359" s="2" t="inlineStr"><is><t>Masy ciała</t></is></c><c r="H359" s="2" t="inlineStr"><is><t>Lipidogramu</t></is></c><c r="I359" s="2" t="inlineStr"><is><t>Glikemii</t></is></c><c r="J359" s="2" t="inlineStr" /><c r="K359" s="2" t="inlineStr" /><c r="L359" s="2" t="inlineStr" /><c r="M359" s="2" t="inlineStr" /><c r="N359" s="2" t="inlineStr" /><c r="O359" s="2" t="inlineStr" /><c r="P359" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q359" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="360"><c r="A360" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B360" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C360" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D360" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E360" s="2" t="inlineStr"><is><t>Fluoksetyna</t></is></c><c r="F360" s="2" t="inlineStr"><is><t>Hamuje wychwyt zwrotny serotoniny</t></is></c><c r="G360" s="2" t="inlineStr" /><c r="H360" s="2" t="inlineStr" /><c r="I360" s="2" t="inlineStr" /><c r="J360" s="2" t="inlineStr" /><c r="K360" s="2" t="inlineStr"><is><t>Ma istotny wpływ na układ krążenia</t></is></c><c r="L360" s="2" t="inlineStr"><is><t>Często powoduje zaparcia</t></is></c><c r="M360" s="2" t="inlineStr"><is><t>Nie działa na enzymy cytochromu P-450</t></is></c><c r="N360" s="2" t="inlineStr" /><c r="O360" s="2" t="inlineStr" /><c r="P360" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q360" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="361"><c r="A361" s="2" t="inlineStr"><is><t>LEKI PRZECIWDEPRESYJNE</t></is></c><c r="B361" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C361" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D361" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E361" s="2" t="inlineStr"><is><t>Zespoł serotoninowy – fluoksetyna i… MAO A i = 5-HT, NA, A, DA, tyramina.... MAO B i = DA i 5-HT</t></is></c><c r="F361" s="2" t="inlineStr"><is><t>Klomipramina</t></is></c><c r="G361" s="2" t="inlineStr"><is><t>Linezolid</t></is></c><c r="H361" s="2" t="inlineStr"><is><t>Wenlafaksyna</t></is></c><c r="I361" s="2" t="inlineStr"><is><t>Moklobemid</t></is></c><c r="J361" s="2" t="inlineStr" /><c r="K361" s="2" t="inlineStr" /><c r="L361" s="2" t="inlineStr" /><c r="M361" s="2" t="inlineStr" /><c r="N361" s="2" t="inlineStr" /><c r="O361" s="2" t="inlineStr" /><c r="P361" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q361" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="362"><c r="A362" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B362" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C362" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D362" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E362" s="2" t="inlineStr"><is><t>Choroba Wilsona</t></is></c><c r="F362" s="2" t="inlineStr"><is><t>Siarczan cynku</t></is></c><c r="G362" s="2" t="inlineStr"><is><t>D-penicylamina</t></is></c><c r="H362" s="2" t="inlineStr" /><c r="I362" s="2" t="inlineStr" /><c r="J362" s="2" t="inlineStr" /><c r="K362" s="2" t="inlineStr"><is><t>Ropinirol</t></is></c><c r="L362" s="2" t="inlineStr"><is><t>Siarczan magnezu</t></is></c><c r="M362" s="2" t="inlineStr" /><c r="N362" s="2" t="inlineStr" /><c r="O362" s="2" t="inlineStr" /><c r="P362" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q362" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="363"><c r="A363" s="2" t="inlineStr"><is><t>PADACZKA</t></is></c><c r="B363" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C363" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D363" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E363" s="2" t="inlineStr"><is><t>Farmakoterapia bólu neuropatycznego jakiego? :D Tako to wszystkie LPD i przeciwpadaczkowe</t></is></c><c r="F363" s="2" t="inlineStr"><is><t>Gabapentyna</t></is></c><c r="G363" s="2" t="inlineStr"><is><t>Amitryptylina</t></is></c><c r="H363" s="2" t="inlineStr"><is><t>Duloksetyna</t></is></c><c r="I363" s="2" t="inlineStr" /><c r="J363" s="2" t="inlineStr" /><c r="K363" s="2" t="inlineStr"><is><t>Ibuprofen</t></is></c><c r="L363" s="2" t="inlineStr" /><c r="M363" s="2" t="inlineStr" /><c r="N363" s="2" t="inlineStr" /><c r="O363" s="2" t="inlineStr" /><c r="P363" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q363" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="364"><c r="A364" s="2" t="inlineStr"><is><t>UKŁAD WSPÓŁCZULNY</t></is></c><c r="B364" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C364" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D364" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E364" s="2" t="inlineStr"><is><t>Profilaktyka migreny</t></is></c><c r="F364" s="2" t="inlineStr"><is><t>Metoprolol</t></is></c><c r="G364" s="2" t="inlineStr"><is><t>Flunaryzyna</t></is></c><c r="H364" s="2" t="inlineStr" /><c r="I364" s="2" t="inlineStr" /><c r="J364" s="2" t="inlineStr" /><c r="K364" s="2" t="inlineStr"><is><t>Indometacyna to w hemikranii</t></is></c><c r="L364" s="2" t="inlineStr"><is><t>Toksyna botulinowa</t></is></c><c r="M364" s="2" t="inlineStr" /><c r="N364" s="2" t="inlineStr" /><c r="O364" s="2" t="inlineStr" /><c r="P364" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q364" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="365"><c r="A365" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B365" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C365" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D365" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E365" s="2" t="inlineStr"><is><t>Alteplaza</t></is></c><c r="F365" s="2" t="inlineStr"><is><t>W udarze niedokrwiennym mózgu</t></is></c><c r="G365" s="2" t="inlineStr" /><c r="H365" s="2" t="inlineStr" /><c r="I365" s="2" t="inlineStr" /><c r="J365" s="2" t="inlineStr" /><c r="K365" s="2" t="inlineStr"><is><t>Przed planowaną kardiowersją</t></is></c><c r="L365" s="2" t="inlineStr"><is><t>W zatorowości płucnej niewysokiego ryzyka</t></is></c><c r="M365" s="2" t="inlineStr"><is><t>W TIA</t></is></c><c r="N365" s="2" t="inlineStr" /><c r="O365" s="2" t="inlineStr" /><c r="P365" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q365" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="366"><c r="A366" s="2" t="inlineStr"><is><t>LEKI HIPOLIPEMIZUJĄCE</t></is></c><c r="B366" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C366" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D366" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E366" s="2" t="inlineStr"><is><t>Profilaktyka wtórna udaru mózgu</t></is></c><c r="F366" s="2" t="inlineStr"><is><t>Dipirydamol</t></is></c><c r="G366" s="2" t="inlineStr"><is><t>Atorwastatyna</t></is></c><c r="H366" s="2" t="inlineStr"><is><t>Enoksapyrana</t></is></c><c r="I366" s="2" t="inlineStr"><is><t>Kwas acetylosalicylowy</t></is></c><c r="J366" s="2" t="inlineStr" /><c r="K366" s="2" t="inlineStr" /><c r="L366" s="2" t="inlineStr" /><c r="M366" s="2" t="inlineStr" /><c r="N366" s="2" t="inlineStr" /><c r="O366" s="2" t="inlineStr" /><c r="P366" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q366" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="367"><c r="A367" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B367" s="2" t="inlineStr"><is><t>Interakcje</t></is></c><c r="C367" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D367" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E367" s="2" t="inlineStr"><is><t>Azytromycyna:</t></is></c><c r="F367" s="2" t="inlineStr"><is><t>jest stosowana w nierzeżączkowym zapaleniu cewki moczowej</t></is></c><c r="G367" s="2" t="inlineStr" /><c r="H367" s="2" t="inlineStr" /><c r="I367" s="2" t="inlineStr" /><c r="J367" s="2" t="inlineStr" /><c r="K367" s="2" t="inlineStr"><is><t>jest słabo wchłaniana z przewodu pokarmowego</t></is></c><c r="L367" s="2" t="inlineStr"><is><t>ma bardzo krótki okres półtrwania</t></is></c><c r="M367" s="2" t="inlineStr"><is><t>istotnie klinicznie hamuje aktywność izoenzymu CYP3A4</t></is></c><c r="N367" s="2" t="inlineStr" /><c r="O367" s="2" t="inlineStr" /><c r="P367" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q367" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="368"><c r="A368" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B368" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C368" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D368" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E368" s="2" t="inlineStr"><is><t>Do działań niepożądanych doksycykliny zaliczamy:</t></is></c><c r="F368" s="2" t="inlineStr"><is><t>fotodermatozy</t></is></c><c r="G368" s="2" t="inlineStr"><is><t>zaburzenia czynności cewek nerkowych wywołane przez jej produkty rozpadu</t></is></c><c r="H368" s="2" t="inlineStr"><is><t>zapalenie wątroby</t></is></c><c r="I368" s="2" t="inlineStr"><is><t>zaburzenia rozwoju zębów i kości</t></is></c><c r="J368" s="2" t="inlineStr" /><c r="K368" s="2" t="inlineStr" /><c r="L368" s="2" t="inlineStr" /><c r="M368" s="2" t="inlineStr" /><c r="N368" s="2" t="inlineStr" /><c r="O368" s="2" t="inlineStr" /><c r="P368" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q368" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="369"><c r="A369" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B369" s="2" t="inlineStr"><is><t>Sposób podania</t></is></c><c r="C369" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D369" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E369" s="2" t="inlineStr"><is><t>Ceftriakson:</t></is></c><c r="F369" s="2" t="inlineStr"><is><t>należy do cefalosporyn III generacji</t></is></c><c r="G369" s="2" t="inlineStr"><is><t>może być podawany dożylnie</t></is></c><c r="H369" s="2" t="inlineStr" /><c r="I369" s="2" t="inlineStr" /><c r="J369" s="2" t="inlineStr" /><c r="K369" s="2" t="inlineStr"><is><t>wykazuje aktywność wobec MRSA</t></is></c><c r="L369" s="2" t="inlineStr"><is><t>nie wykazuje aktywności wobec Borrelia burgdorferi</t></is></c><c r="M369" s="2" t="inlineStr" /><c r="N369" s="2" t="inlineStr" /><c r="O369" s="2" t="inlineStr" /><c r="P369" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q369" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="370"><c r="A370" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B370" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C370" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D370" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E370" s="2" t="inlineStr"><is><t>Pseudomonas aeruginosa jest wrażliwy na działanie:</t></is></c><c r="F370" s="2" t="inlineStr"><is><t>kolistyny</t></is></c><c r="G370" s="2" t="inlineStr"><is><t>tobramycyn</t></is></c><c r="H370" s="2" t="inlineStr" /><c r="I370" s="2" t="inlineStr" /><c r="J370" s="2" t="inlineStr" /><c r="K370" s="2" t="inlineStr"><is><t>telawancyny</t></is></c><c r="L370" s="2" t="inlineStr"><is><t>cefazoliny</t></is></c><c r="M370" s="2" t="inlineStr" /><c r="N370" s="2" t="inlineStr" /><c r="O370" s="2" t="inlineStr" /><c r="P370" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q370" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="371"><c r="A371" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B371" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C371" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D371" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E371" s="2" t="inlineStr"><is><t>W terapii empirycznej bakteryjnego zapalenia opon mózgowo-rdzeniowych u osób dorosłych zalecane są:</t></is></c><c r="F371" s="2" t="inlineStr"><is><t>cefotaksym z wankomycyną</t></is></c><c r="G371" s="2" t="inlineStr"><is><t>ceftriakson z wankomycyną</t></is></c><c r="H371" s="2" t="inlineStr" /><c r="I371" s="2" t="inlineStr" /><c r="J371" s="2" t="inlineStr" /><c r="K371" s="2" t="inlineStr"><is><t>ampicylina z gentamycyną</t></is></c><c r="L371" s="2" t="inlineStr"><is><t>ampicylina z deksametazonem</t></is></c><c r="M371" s="2" t="inlineStr" /><c r="N371" s="2" t="inlineStr" /><c r="O371" s="2" t="inlineStr" /><c r="P371" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q371" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="372"><c r="A372" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B372" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C372" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D372" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E372" s="2" t="inlineStr"><is><t>Efekt bakteriobójczy zależny od czasu, w którym stężenie leku jest większe od MIC wykazują:</t></is></c><c r="F372" s="2" t="inlineStr"><is><t>amoksycylina z kwasem klawulanowym</t></is></c><c r="G372" s="2" t="inlineStr"><is><t>ceftriakson</t></is></c><c r="H372" s="2" t="inlineStr" /><c r="I372" s="2" t="inlineStr" /><c r="J372" s="2" t="inlineStr" /><c r="K372" s="2" t="inlineStr"><is><t>lewofloksacyna</t></is></c><c r="L372" s="2" t="inlineStr"><is><t>amikacyna</t></is></c><c r="M372" s="2" t="inlineStr" /><c r="N372" s="2" t="inlineStr" /><c r="O372" s="2" t="inlineStr" /><c r="P372" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q372" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="373"><c r="A373" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B373" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C373" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D373" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E373" s="2" t="inlineStr"><is><t>Leki przeciwdrobnoustrojowe, których mechanizm działania polega na hamowaniu biosyntezy ściany komórkowej bakterii to:</t></is></c><c r="F373" s="2" t="inlineStr"><is><t>cefadroksyl</t></is></c><c r="G373" s="2" t="inlineStr"><is><t>wankomycyna</t></is></c><c r="H373" s="2" t="inlineStr"><is><t>bacytracyna</t></is></c><c r="I373" s="2" t="inlineStr" /><c r="J373" s="2" t="inlineStr" /><c r="K373" s="2" t="inlineStr"><is><t>klindamycyna</t></is></c><c r="L373" s="2" t="inlineStr" /><c r="M373" s="2" t="inlineStr" /><c r="N373" s="2" t="inlineStr" /><c r="O373" s="2" t="inlineStr" /><c r="P373" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q373" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="374"><c r="A374" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B374" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C374" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D374" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E374" s="2" t="inlineStr"><is><t>Aktywność przeciwbakteryjną względem Legionella spp. ma:</t></is></c><c r="F374" s="2" t="inlineStr"><is><t>moksyfloksacyna</t></is></c><c r="G374" s="2" t="inlineStr"><is><t>azytromycyna</t></is></c><c r="H374" s="2" t="inlineStr"><is><t>tygecyklina</t></is></c><c r="I374" s="2" t="inlineStr" /><c r="J374" s="2" t="inlineStr" /><c r="K374" s="2" t="inlineStr"><is><t>metronidazol</t></is></c><c r="L374" s="2" t="inlineStr" /><c r="M374" s="2" t="inlineStr" /><c r="N374" s="2" t="inlineStr" /><c r="O374" s="2" t="inlineStr" /><c r="P374" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q374" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="375"><c r="A375" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B375" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C375" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D375" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E375" s="2" t="inlineStr"><is><t>Jodopowidon znalazł zastosowanie w:</t></is></c><c r="F375" s="2" t="inlineStr"><is><t>dezynfekcji skóry przed nakłuciem</t></is></c><c r="G375" s="2" t="inlineStr"><is><t>leczeniu zakażeń pochwy florą mieszaną</t></is></c><c r="H375" s="2" t="inlineStr"><is><t>profilaktyce zakażeń ran</t></is></c><c r="I375" s="2" t="inlineStr"><is><t>leczeniu zakażeń błony śluzowej jamy ustnej</t></is></c><c r="J375" s="2" t="inlineStr" /><c r="K375" s="2" t="inlineStr" /><c r="L375" s="2" t="inlineStr" /><c r="M375" s="2" t="inlineStr" /><c r="N375" s="2" t="inlineStr" /><c r="O375" s="2" t="inlineStr" /><c r="P375" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q375" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="376"><c r="A376" s="2" t="inlineStr"><is><t>LEKI PRZECIWWIRUSOWE</t></is></c><c r="B376" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C376" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D376" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E376" s="2" t="inlineStr"><is><t>Inhibitory neuraminidazy:</t></is></c><c r="F376" s="2" t="inlineStr"><is><t>hamują uwalnianie wirusów z zakażonych komórek</t></is></c><c r="G376" s="2" t="inlineStr"><is><t>można je stosować w leczeniu grypy typu A i B</t></is></c><c r="H376" s="2" t="inlineStr" /><c r="I376" s="2" t="inlineStr" /><c r="J376" s="2" t="inlineStr" /><c r="K376" s="2" t="inlineStr"><is><t>nie różnią się między sobą pod względem skuteczności i działań niepożądanych</t></is></c><c r="L376" s="2" t="inlineStr"><is><t>nie są skuteczne w profilaktyce grypy</t></is></c><c r="M376" s="2" t="inlineStr" /><c r="N376" s="2" t="inlineStr" /><c r="O376" s="2" t="inlineStr" /><c r="P376" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q376" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="377"><c r="A377" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B377" s="2" t="inlineStr"><is><t>Interakcje</t></is></c><c r="C377" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D377" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E377" s="2" t="inlineStr"><is><t>Cyprofloksacyna:</t></is></c><c r="F377" s="2" t="inlineStr"><is><t>ma efekt działania zależny od skumulowanej ekspozycji</t></is></c><c r="G377" s="2" t="inlineStr"><is><t>jest stosowana w leczeniu empirycznym niepowikłanego ostrego odmiedniczkowego zapalenia nerek</t></is></c><c r="H377" s="2" t="inlineStr"><is><t>może być podawana dożylnie</t></is></c><c r="I377" s="2" t="inlineStr" /><c r="J377" s="2" t="inlineStr" /><c r="K377" s="2" t="inlineStr"><is><t>nie wydłuża odstępu QT</t></is></c><c r="L377" s="2" t="inlineStr" /><c r="M377" s="2" t="inlineStr" /><c r="N377" s="2" t="inlineStr" /><c r="O377" s="2" t="inlineStr" /><c r="P377" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q377" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="378"><c r="A378" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B378" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C378" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D378" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E378" s="2" t="inlineStr"><is><t>Leczenie przeciwbakteryjne powinno być zlecone, jeśli w badaniu mikrobiologicznym zostanie stwierdzone:</t></is></c><c r="F378" s="2" t="inlineStr"><is><t>obecność Escherichia coli w dwóch posiewach krwi obwodowej</t></is></c><c r="G378" s="2" t="inlineStr"><is><t>brak wzrostu bakterii we krwi u osoby z klinicznymi i radiologicznymi cechami zapalenia płuc</t></is></c><c r="H378" s="2" t="inlineStr" /><c r="I378" s="2" t="inlineStr" /><c r="J378" s="2" t="inlineStr" /><c r="K378" s="2" t="inlineStr"><is><t>nosicielstwo szczepu alarmowego w przewodzie pokarmowym</t></is></c><c r="L378" s="2" t="inlineStr"><is><t>trzy gatunki bakterii w posiewie moczu</t></is></c><c r="M378" s="2" t="inlineStr" /><c r="N378" s="2" t="inlineStr" /><c r="O378" s="2" t="inlineStr" /><c r="P378" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q378" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="379"><c r="A379" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B379" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C379" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D379" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E379" s="2" t="inlineStr"><is><t>Przeciwinfekcyjna farmakoprofilaktyka medyczna jest zalecana:</t></is></c><c r="F379" s="2" t="inlineStr"><is><t>w ciężkiej neutropenii trwającej &gt; 7 dni u osób z ostrymi białaczkami</t></is></c><c r="G379" s="2" t="inlineStr"><is><t>nieszczepionym osobom z grup ryzyka ciężkiego przebiegu choroby po kontakcie z chorym na grypę</t></is></c><c r="H379" s="2" t="inlineStr" /><c r="I379" s="2" t="inlineStr" /><c r="J379" s="2" t="inlineStr" /><c r="K379" s="2" t="inlineStr"><is><t>po implantacji stentów wieńcowych przez 12 miesięcy</t></is></c><c r="L379" s="2" t="inlineStr"><is><t>podczas przewlekłego cewnikowania pęcherza moczowego</t></is></c><c r="M379" s="2" t="inlineStr" /><c r="N379" s="2" t="inlineStr" /><c r="O379" s="2" t="inlineStr" /><c r="P379" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q379" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="380"><c r="A380" s="2" t="inlineStr"><is><t>LEKI PRZECIWGRZYBICZE</t></is></c><c r="B380" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C380" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D380" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E380" s="2" t="inlineStr"><is><t>W grzybiczym zakażeniu paznokci zastosowanie ma:</t></is></c><c r="F380" s="2" t="inlineStr"><is><t>itrakonazol</t></is></c><c r="G380" s="2" t="inlineStr"><is><t>terbinafina</t></is></c><c r="H380" s="2" t="inlineStr" /><c r="I380" s="2" t="inlineStr" /><c r="J380" s="2" t="inlineStr" /><c r="K380" s="2" t="inlineStr"><is><t>natamycyna</t></is></c><c r="L380" s="2" t="inlineStr"><is><t>kaspofungina</t></is></c><c r="M380" s="2" t="inlineStr" /><c r="N380" s="2" t="inlineStr" /><c r="O380" s="2" t="inlineStr" /><c r="P380" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q380" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="381"><c r="A381" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B381" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C381" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D381" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E381" s="2" t="inlineStr"><is><t>Po ugryzieniu przez kleszcza, gdy obserwujemy rumień wędrujący, racjonalne jest zastosowanie:</t></is></c><c r="F381" s="2" t="inlineStr"><is><t>amoksycyliny</t></is></c><c r="G381" s="2" t="inlineStr"><is><t>doksycykliny</t></is></c><c r="H381" s="2" t="inlineStr"><is><t>cefuroksymu</t></is></c><c r="I381" s="2" t="inlineStr"><is><t>azytromycyny</t></is></c><c r="J381" s="2" t="inlineStr" /><c r="K381" s="2" t="inlineStr" /><c r="L381" s="2" t="inlineStr" /><c r="M381" s="2" t="inlineStr" /><c r="N381" s="2" t="inlineStr" /><c r="O381" s="2" t="inlineStr" /><c r="P381" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q381" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="382"><c r="A382" s="2" t="inlineStr"><is><t>LEKI PRZECIWWIRUSOWE</t></is></c><c r="B382" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C382" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D382" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E382" s="2" t="inlineStr"><is><t>W leczeniu zakażenia wirusem opryszczki (Herpes) stosuje się:</t></is></c><c r="F382" s="2" t="inlineStr"><is><t>foskarnet</t></is></c><c r="G382" s="2" t="inlineStr"><is><t>acyklowir</t></is></c><c r="H382" s="2" t="inlineStr" /><c r="I382" s="2" t="inlineStr" /><c r="J382" s="2" t="inlineStr" /><c r="K382" s="2" t="inlineStr"><is><t>rymantadynę</t></is></c><c r="L382" s="2" t="inlineStr"><is><t>lamiwudynę</t></is></c><c r="M382" s="2" t="inlineStr" /><c r="N382" s="2" t="inlineStr" /><c r="O382" s="2" t="inlineStr" /><c r="P382" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q382" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="383"><c r="A383" s="2" t="inlineStr"><is><t>CUKRZYCA</t></is></c><c r="B383" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C383" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D383" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E383" s="2" t="inlineStr"><is><t>Metformina:</t></is></c><c r="F383" s="2" t="inlineStr"><is><t>jest wskazana w stanie przedcukrzycowym</t></is></c><c r="G383" s="2" t="inlineStr"><is><t>zmniejsza śmiertelność w cukrzycy typu 2</t></is></c><c r="H383" s="2" t="inlineStr" /><c r="I383" s="2" t="inlineStr" /><c r="J383" s="2" t="inlineStr" /><c r="K383" s="2" t="inlineStr"><is><t>hamuje kanały potasowe zależne od ATP w komórkach B trzustki</t></is></c><c r="L383" s="2" t="inlineStr"><is><t>nie może być stosowana w skojarzeniu z insuliną</t></is></c><c r="M383" s="2" t="inlineStr" /><c r="N383" s="2" t="inlineStr" /><c r="O383" s="2" t="inlineStr" /><c r="P383" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q383" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="384"><c r="A384" s="2" t="inlineStr"><is><t>CUKRZYCA</t></is></c><c r="B384" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C384" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D384" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E384" s="2" t="inlineStr"><is><t>W leczeniu hipoglikemii stosuje się:</t></is></c><c r="F384" s="2" t="inlineStr"><is><t>węglowodany proste doustnie</t></is></c><c r="G384" s="2" t="inlineStr"><is><t>glukozę dożylnie</t></is></c><c r="H384" s="2" t="inlineStr"><is><t>węglowodany złożone doustnie</t></is></c><c r="I384" s="2" t="inlineStr" /><c r="J384" s="2" t="inlineStr" /><c r="K384" s="2" t="inlineStr"><is><t>glukagon doustnie</t></is></c><c r="L384" s="2" t="inlineStr" /><c r="M384" s="2" t="inlineStr" /><c r="N384" s="2" t="inlineStr" /><c r="O384" s="2" t="inlineStr" /><c r="P384" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q384" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="385"><c r="A385" s="2" t="inlineStr"><is><t>TARCZYCA</t></is></c><c r="B385" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C385" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D385" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E385" s="2" t="inlineStr"><is><t>Liotyronina:</t></is></c><c r="F385" s="2" t="inlineStr"><is><t>odpowiada ona naturalnemu hormonowi T3</t></is></c><c r="G385" s="2" t="inlineStr"><is><t>ma krótszy okres półtrwania niż lewotyroksyna</t></is></c><c r="H385" s="2" t="inlineStr" /><c r="I385" s="2" t="inlineStr" /><c r="J385" s="2" t="inlineStr" /><c r="K385" s="2" t="inlineStr"><is><t>jest lekiem z wyboru w niedoczynności tarczycy</t></is></c><c r="L385" s="2" t="inlineStr"><is><t>jest przeciwwskazana w leczeniu śpiączki hipometabolicznej</t></is></c><c r="M385" s="2" t="inlineStr" /><c r="N385" s="2" t="inlineStr" /><c r="O385" s="2" t="inlineStr" /><c r="P385" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q385" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="386"><c r="A386" s="2" t="inlineStr"><is><t>TARCZYCA</t></is></c><c r="B386" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C386" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D386" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E386" s="2" t="inlineStr"><is><t>Wskazaniem do zastosowania jodku potasu może być:</t></is></c><c r="F386" s="2" t="inlineStr"><is><t>ochrona tarczycy przed jodem radioaktywnym</t></is></c><c r="G386" s="2" t="inlineStr"><is><t>przygotowanie do usunięcia tarczycy</t></is></c><c r="H386" s="2" t="inlineStr"><is><t>przełom tyreotoksyczny</t></is></c><c r="I386" s="2" t="inlineStr"><is><t>zapobieganie powstawaniu wola z niedoboru jodu</t></is></c><c r="J386" s="2" t="inlineStr" /><c r="K386" s="2" t="inlineStr" /><c r="L386" s="2" t="inlineStr" /><c r="M386" s="2" t="inlineStr" /><c r="N386" s="2" t="inlineStr" /><c r="O386" s="2" t="inlineStr" /><c r="P386" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q386" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="387"><c r="A387" s="2" t="inlineStr"><is><t>LEKI HIPOLIPEMIZUJĄCE</t></is></c><c r="B387" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C387" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D387" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E387" s="2" t="inlineStr"><is><t>W leczeniu hiperprolaktynemii stosuje się:</t></is></c><c r="F387" s="2" t="inlineStr"><is><t>bromokryptynę</t></is></c><c r="G387" s="2" t="inlineStr"><is><t>karbegolinę</t></is></c><c r="H387" s="2" t="inlineStr" /><c r="I387" s="2" t="inlineStr" /><c r="J387" s="2" t="inlineStr" /><c r="K387" s="2" t="inlineStr"><is><t>somatostatynę</t></is></c><c r="L387" s="2" t="inlineStr"><is><t>terlipresynę</t></is></c><c r="M387" s="2" t="inlineStr" /><c r="N387" s="2" t="inlineStr" /><c r="O387" s="2" t="inlineStr" /><c r="P387" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q387" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="388"><c r="A388" s="2" t="inlineStr"><is><t>HORMONY PŁCIOWE</t></is></c><c r="B388" s="2" t="inlineStr"><is><t>Interakcje</t></is></c><c r="C388" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D388" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E388" s="2" t="inlineStr"><is><t>Działanie antyandrogenne wykazuje:</t></is></c><c r="F388" s="2" t="inlineStr"><is><t>octan cyproteronu</t></is></c><c r="G388" s="2" t="inlineStr"><is><t>ketokonazol</t></is></c><c r="H388" s="2" t="inlineStr"><is><t>finasteryd</t></is></c><c r="I388" s="2" t="inlineStr"><is><t>bikalutamid</t></is></c><c r="J388" s="2" t="inlineStr" /><c r="K388" s="2" t="inlineStr" /><c r="L388" s="2" t="inlineStr" /><c r="M388" s="2" t="inlineStr" /><c r="N388" s="2" t="inlineStr" /><c r="O388" s="2" t="inlineStr" /><c r="P388" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q388" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="389"><c r="A389" s="2" t="inlineStr"><is><t>GLIKOKORTYKOSTEROIDY</t></is></c><c r="B389" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C389" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D389" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E389" s="2" t="inlineStr"><is><t>Glikokortykosteroidy zwiększają:</t></is></c><c r="F389" s="2" t="inlineStr"><is><t>produkcję surfaktantu</t></is></c><c r="G389" s="2" t="inlineStr" /><c r="H389" s="2" t="inlineStr" /><c r="I389" s="2" t="inlineStr" /><c r="J389" s="2" t="inlineStr" /><c r="K389" s="2" t="inlineStr"><is><t>ekspresję genu osteokalcyny</t></is></c><c r="L389" s="2" t="inlineStr"><is><t>stężenie wapnia w surowicy krwi</t></is></c><c r="M389" s="2" t="inlineStr"><is><t>syntezę testosteronu</t></is></c><c r="N389" s="2" t="inlineStr" /><c r="O389" s="2" t="inlineStr" /><c r="P389" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q389" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="390"><c r="A390" s="2" t="inlineStr"><is><t>HORMONY PŁCIOWE</t></is></c><c r="B390" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C390" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D390" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E390" s="2" t="inlineStr"><is><t>Efektem nadmiaru gestagenów może być:</t></is></c><c r="F390" s="2" t="inlineStr"><is><t>depresja</t></is></c><c r="G390" s="2" t="inlineStr"><is><t>łojotok skóry</t></is></c><c r="H390" s="2" t="inlineStr"><is><t>przyrost masy ciała</t></is></c><c r="I390" s="2" t="inlineStr"><is><t>hirsutyzm</t></is></c><c r="J390" s="2" t="inlineStr" /><c r="K390" s="2" t="inlineStr" /><c r="L390" s="2" t="inlineStr" /><c r="M390" s="2" t="inlineStr" /><c r="N390" s="2" t="inlineStr" /><c r="O390" s="2" t="inlineStr" /><c r="P390" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q390" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="391"><c r="A391" s="2" t="inlineStr"><is><t>LEKI PRZECIWPASOŻYTNICZE</t></is></c><c r="B391" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C391" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D391" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E391" s="2" t="inlineStr"><is><t>W leczeniu wągrzycy (cysticerkozy) stosujemy:</t></is></c><c r="F391" s="2" t="inlineStr"><is><t>prazykwantel</t></is></c><c r="G391" s="2" t="inlineStr"><is><t>albendazol</t></is></c><c r="H391" s="2" t="inlineStr" /><c r="I391" s="2" t="inlineStr" /><c r="J391" s="2" t="inlineStr" /><c r="K391" s="2" t="inlineStr"><is><t>metronidazol</t></is></c><c r="L391" s="2" t="inlineStr"><is><t>iwermektynę bo</t></is></c><c r="M391" s="2" t="inlineStr" /><c r="N391" s="2" t="inlineStr" /><c r="O391" s="2" t="inlineStr" /><c r="P391" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q391" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="392"><c r="A392" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B392" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C392" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D392" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E392" s="2" t="inlineStr"><is><t>Działanie zapierające wykazuje:</t></is></c><c r="F392" s="2" t="inlineStr"><is><t>werapamil</t></is></c><c r="G392" s="2" t="inlineStr"><is><t>węglan wapnia</t></is></c><c r="H392" s="2" t="inlineStr"><is><t>odwar z suchych owoców borówki czernicy</t></is></c><c r="I392" s="2" t="inlineStr" /><c r="J392" s="2" t="inlineStr" /><c r="K392" s="2" t="inlineStr"><is><t>erytromycyna</t></is></c><c r="L392" s="2" t="inlineStr" /><c r="M392" s="2" t="inlineStr" /><c r="N392" s="2" t="inlineStr" /><c r="O392" s="2" t="inlineStr" /><c r="P392" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q392" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="393"><c r="A393" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B393" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C393" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D393" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E393" s="2" t="inlineStr"><is><t>Stosowanie kwasu acetylosalicylowego może być przyczyną:</t></is></c><c r="F393" s="2" t="inlineStr"><is><t>zaostrzenia astmy</t></is></c><c r="G393" s="2" t="inlineStr"><is><t>retencji sodu i wody</t></is></c><c r="H393" s="2" t="inlineStr"><is><t>niedokrwistości</t></is></c><c r="I393" s="2" t="inlineStr" /><c r="J393" s="2" t="inlineStr" /><c r="K393" s="2" t="inlineStr"><is><t>zakrzepicy żył głębokich</t></is></c><c r="L393" s="2" t="inlineStr" /><c r="M393" s="2" t="inlineStr" /><c r="N393" s="2" t="inlineStr" /><c r="O393" s="2" t="inlineStr" /><c r="P393" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q393" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="394"><c r="A394" s="2" t="inlineStr"><is><t>LEKI PRZECIWDEPRESYJNE</t></is></c><c r="B394" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C394" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D394" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E394" s="2" t="inlineStr"><is><t>Efekty gastrotoksyczne związane ze stosowaniem niesteroidowych leków przeciwzapalnych może nasilać:</t></is></c><c r="F394" s="2" t="inlineStr"><is><t>zolendronian</t></is></c><c r="G394" s="2" t="inlineStr"><is><t>fluoksetyna tak, SSRI też</t></is></c><c r="H394" s="2" t="inlineStr"><is><t>acenokumarol</t></is></c><c r="I394" s="2" t="inlineStr"><is><t>prednizon</t></is></c><c r="J394" s="2" t="inlineStr" /><c r="K394" s="2" t="inlineStr" /><c r="L394" s="2" t="inlineStr" /><c r="M394" s="2" t="inlineStr" /><c r="N394" s="2" t="inlineStr" /><c r="O394" s="2" t="inlineStr" /><c r="P394" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q394" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="395"><c r="A395" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B395" s="2" t="inlineStr"><is><t>Ciąża</t></is></c><c r="C395" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D395" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E395" s="2" t="inlineStr"><is><t>Zastosowanie ibuprofenu w 3 trymestrze ciąży może spowodować:</t></is></c><c r="F395" s="2" t="inlineStr"><is><t>przedwczesne zamknięcie przewodu Botalla</t></is></c><c r="G395" s="2" t="inlineStr"><is><t>zwiększone ryzyko krwawienia u matki</t></is></c><c r="H395" s="2" t="inlineStr"><is><t>zwiększone ryzyko obrzęków u matki</t></is></c><c r="I395" s="2" t="inlineStr" /><c r="J395" s="2" t="inlineStr" /><c r="K395" s="2" t="inlineStr"><is><t>zwiększenie czynności skurczowej macicy</t></is></c><c r="L395" s="2" t="inlineStr" /><c r="M395" s="2" t="inlineStr" /><c r="N395" s="2" t="inlineStr" /><c r="O395" s="2" t="inlineStr" /><c r="P395" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q395" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="396"><c r="A396" s="2" t="inlineStr"><is><t>BÓLE GŁOWY</t></is></c><c r="B396" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C396" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D396" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E396" s="2" t="inlineStr"><is><t>Napad migreny przerywa:</t></is></c><c r="F396" s="2" t="inlineStr"><is><t>winian ergotaminy</t></is></c><c r="G396" s="2" t="inlineStr"><is><t>sumatryptan</t></is></c><c r="H396" s="2" t="inlineStr"><is><t>ibuprofen</t></is></c><c r="I396" s="2" t="inlineStr" /><c r="J396" s="2" t="inlineStr" /><c r="K396" s="2" t="inlineStr"><is><t>metoklopramid</t></is></c><c r="L396" s="2" t="inlineStr" /><c r="M396" s="2" t="inlineStr" /><c r="N396" s="2" t="inlineStr" /><c r="O396" s="2" t="inlineStr" /><c r="P396" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q396" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="397"><c r="A397" s="2" t="inlineStr"><is><t>ZNIECZULENIA MIEJSCOWE</t></is></c><c r="B397" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C397" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D397" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E397" s="2" t="inlineStr"><is><t>W leczeniu neuralgii popółpaśćcowej można zastosować:</t></is></c><c r="F397" s="2" t="inlineStr"><is><t>8% kapsaicynę w kremie</t></is></c><c r="G397" s="2" t="inlineStr"><is><t>5% lidokainę w plastrach</t></is></c><c r="H397" s="2" t="inlineStr"><is><t>amitryptylinę</t></is></c><c r="I397" s="2" t="inlineStr" /><c r="J397" s="2" t="inlineStr" /><c r="K397" s="2" t="inlineStr"><is><t>metamizol</t></is></c><c r="L397" s="2" t="inlineStr" /><c r="M397" s="2" t="inlineStr" /><c r="N397" s="2" t="inlineStr" /><c r="O397" s="2" t="inlineStr" /><c r="P397" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q397" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="398"><c r="A398" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B398" s="2" t="inlineStr"><is><t>Przeciwwskazania</t></is></c><c r="C398" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D398" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E398" s="2" t="inlineStr"><is><t>Loperamid:</t></is></c><c r="F398" s="2" t="inlineStr"><is><t>w dawkach terapeutycznych nie działa ośrodkowo</t></is></c><c r="G398" s="2" t="inlineStr"><is><t>jest przeciwwskazany we wrzodziejącym zapaleniu jelita grubego</t></is></c><c r="H398" s="2" t="inlineStr" /><c r="I398" s="2" t="inlineStr" /><c r="J398" s="2" t="inlineStr" /><c r="K398" s="2" t="inlineStr"><is><t>jest agonistą receptorów serotoninowych w jelicie</t></is></c><c r="L398" s="2" t="inlineStr"><is><t>wykazuje działanie przeciwbólowe</t></is></c><c r="M398" s="2" t="inlineStr" /><c r="N398" s="2" t="inlineStr" /><c r="O398" s="2" t="inlineStr" /><c r="P398" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q398" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="399"><c r="A399" s="2" t="inlineStr"><is><t>NARKOTYCZNE LEKI PRZECIWBÓLOWE</t></is></c><c r="B399" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C399" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D399" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E399" s="2" t="inlineStr"><is><t>Fentanyl:</t></is></c><c r="F399" s="2" t="inlineStr"><is><t>hamuje ośrodek oddechowy</t></is></c><c r="G399" s="2" t="inlineStr" /><c r="H399" s="2" t="inlineStr" /><c r="I399" s="2" t="inlineStr" /><c r="J399" s="2" t="inlineStr" /><c r="K399" s="2" t="inlineStr"><is><t>działa neurotoksycznie</t></is></c><c r="L399" s="2" t="inlineStr"><is><t>ma aktywne metabolity</t></is></c><c r="M399" s="2" t="inlineStr"><is><t>uwalnia histaminę</t></is></c><c r="N399" s="2" t="inlineStr" /><c r="O399" s="2" t="inlineStr" /><c r="P399" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q399" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="400"><c r="A400" s="2" t="inlineStr"><is><t>NIEOPIOIDOWE LEKI PRZECIWBÓLOWE</t></is></c><c r="B400" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C400" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D400" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E400" s="2" t="inlineStr"><is><t>Nefopam</t></is></c><c r="F400" s="2" t="inlineStr"><is><t>jest inhibitorem wychwytu zwrotnego serotoniny i noradrenaliny</t></is></c><c r="G400" s="2" t="inlineStr"><is><t>u osób starszych może wywoływać omamy</t></is></c><c r="H400" s="2" t="inlineStr" /><c r="I400" s="2" t="inlineStr" /><c r="J400" s="2" t="inlineStr" /><c r="K400" s="2" t="inlineStr"><is><t>hamuje wybiórczo cyklooksygenazę typu 2</t></is></c><c r="L400" s="2" t="inlineStr"><is><t>u dzieci może być stosowany w profilaktyce drgawek gorączkowych</t></is></c><c r="M400" s="2" t="inlineStr" /><c r="N400" s="2" t="inlineStr" /><c r="O400" s="2" t="inlineStr" /><c r="P400" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q400" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="401"><c r="A401" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B401" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C401" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D401" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E401" s="2" t="inlineStr"><is><t>W zespole abstynencyjnym w uzależnieniu od opioidów występują:</t></is></c><c r="F401" s="2" t="inlineStr"><is><t>rozszerzenie źrenic</t></is></c><c r="G401" s="2" t="inlineStr"><is><t>wymioty i biegunka</t></is></c><c r="H401" s="2" t="inlineStr"><is><t>bezsenność</t></is></c><c r="I401" s="2" t="inlineStr"><is><t>łzawienie i wyciek z nosa</t></is></c><c r="J401" s="2" t="inlineStr" /><c r="K401" s="2" t="inlineStr" /><c r="L401" s="2" t="inlineStr" /><c r="M401" s="2" t="inlineStr" /><c r="N401" s="2" t="inlineStr" /><c r="O401" s="2" t="inlineStr" /><c r="P401" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q401" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="402"><c r="A402" s="2" t="inlineStr"><is><t>CUKRZYCA</t></is></c><c r="B402" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C402" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D402" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E402" s="2" t="inlineStr"><is><t>Redukcję masy ciała może powodować stosowanie:</t></is></c><c r="F402" s="2" t="inlineStr"><is><t>fluoksetyny</t></is></c><c r="G402" s="2" t="inlineStr"><is><t>metforminy</t></is></c><c r="H402" s="2" t="inlineStr"><is><t>liraglutydu</t></is></c><c r="I402" s="2" t="inlineStr" /><c r="J402" s="2" t="inlineStr" /><c r="K402" s="2" t="inlineStr"><is><t>insuliny</t></is></c><c r="L402" s="2" t="inlineStr" /><c r="M402" s="2" t="inlineStr" /><c r="N402" s="2" t="inlineStr" /><c r="O402" s="2" t="inlineStr" /><c r="P402" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q402" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="403"><c r="A403" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B403" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C403" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D403" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E403" s="2" t="inlineStr"><is><t>W udarze niedokrwiennym mózgu możesz zastosować tkankowy aktywator plazminogenu jeśli stwierdzisz, że pacjent:</t></is></c><c r="F403" s="2" t="inlineStr"><is><t>doustne leczenie przeciwkrzepliwe (INR=1.5)</t></is></c><c r="G403" s="2" t="inlineStr"><is><t>ma wartości ciśnienia tętniczego: SBP ≤ 185 mm Hg lub DBP ≤ 110 mm Hg</t></is></c><c r="H403" s="2" t="inlineStr"><is><t>ma czas od wystąpienia objawów udaru mózgu nie przekraczający 4.5h</t></is></c><c r="I403" s="2" t="inlineStr" /><c r="J403" s="2" t="inlineStr" /><c r="K403" s="2" t="inlineStr"><is><t>jest w podeszłym wieku (&gt; 80 lat)</t></is></c><c r="L403" s="2" t="inlineStr" /><c r="M403" s="2" t="inlineStr" /><c r="N403" s="2" t="inlineStr" /><c r="O403" s="2" t="inlineStr" /><c r="P403" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q403" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="404"><c r="A404" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B404" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C404" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D404" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E404" s="2" t="inlineStr"><is><t>U 76 letniej kobiety z napadowym migotaniem przedsionków, cukrzycą i nadciśnieniem tętniczym (Cha2DS2VASc = 5 pkt) i niskim ryzykiem krwawienia (HAS-BLED = 2 pkt) wskazane w przewlekłej profilaktyce są:</t></is></c><c r="F404" s="2" t="inlineStr"><is><t>warfaryna</t></is></c><c r="G404" s="2" t="inlineStr"><is><t>eteksylan dabigatranu</t></is></c><c r="H404" s="2" t="inlineStr" /><c r="I404" s="2" t="inlineStr" /><c r="J404" s="2" t="inlineStr" /><c r="K404" s="2" t="inlineStr"><is><t>kwas acetylosalicylowy</t></is></c><c r="L404" s="2" t="inlineStr"><is><t>fondaparynuks</t></is></c><c r="M404" s="2" t="inlineStr" /><c r="N404" s="2" t="inlineStr" /><c r="O404" s="2" t="inlineStr" /><c r="P404" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q404" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="405"><c r="A405" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B405" s="2" t="inlineStr"><is><t>Ciąża</t></is></c><c r="C405" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D405" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E405" s="2" t="inlineStr"><is><t>Rywaroksaban:</t></is></c><c r="F405" s="2" t="inlineStr"><is><t>wymaga redukcji dawki w niewydolności nerek</t></is></c><c r="G405" s="2" t="inlineStr" /><c r="H405" s="2" t="inlineStr" /><c r="I405" s="2" t="inlineStr" /><c r="J405" s="2" t="inlineStr" /><c r="K405" s="2" t="inlineStr"><is><t>odwracalnie blokuje receptor GP IIb/IIIa</t></is></c><c r="L405" s="2" t="inlineStr"><is><t>występuje w postaci proleku</t></is></c><c r="M405" s="2" t="inlineStr"><is><t>jest stosowany w profilaktyce choroby zakrzepowo-zatorowej w czasie ciąży</t></is></c><c r="N405" s="2" t="inlineStr" /><c r="O405" s="2" t="inlineStr" /><c r="P405" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q405" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="406"><c r="A406" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B406" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C406" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D406" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E406" s="2" t="inlineStr"><is><t>Do leków działających na receptor P2Y12 zaliczamy:</t></is></c><c r="F406" s="2" t="inlineStr"><is><t>prasugrel</t></is></c><c r="G406" s="2" t="inlineStr" /><c r="H406" s="2" t="inlineStr" /><c r="I406" s="2" t="inlineStr" /><c r="J406" s="2" t="inlineStr" /><c r="K406" s="2" t="inlineStr"><is><t>apiksaban</t></is></c><c r="L406" s="2" t="inlineStr"><is><t>worapaksar</t></is></c><c r="M406" s="2" t="inlineStr"><is><t>dypirydamol</t></is></c><c r="N406" s="2" t="inlineStr" /><c r="O406" s="2" t="inlineStr" /><c r="P406" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q406" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="407"><c r="A407" s="2" t="inlineStr"><is><t>LEKI HIPOLIPEMIZUJĄCE</t></is></c><c r="B407" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C407" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D407" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E407" s="2" t="inlineStr"><is><t>Do częstych działań niepożądanych atorwastatyny należy:</t></is></c><c r="F407" s="2" t="inlineStr"><is><t>uszkodzenie wątroby</t></is></c><c r="G407" s="2" t="inlineStr" /><c r="H407" s="2" t="inlineStr" /><c r="I407" s="2" t="inlineStr" /><c r="J407" s="2" t="inlineStr" /><c r="K407" s="2" t="inlineStr"><is><t>rogowacenie ciemne</t></is></c><c r="L407" s="2" t="inlineStr"><is><t>miopatia</t></is></c><c r="M407" s="2" t="inlineStr"><is><t>uderzenia gorąca</t></is></c><c r="N407" s="2" t="inlineStr" /><c r="O407" s="2" t="inlineStr" /><c r="P407" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q407" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="408"><c r="A408" s="2" t="inlineStr"><is><t>FARMAKOKINETYKA</t></is></c><c r="B408" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C408" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D408" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E408" s="2" t="inlineStr"><is><t>Orlistat:</t></is></c><c r="F408" s="2" t="inlineStr"><is><t>może być przyczyną wystąpienia tłuszczowych stolców</t></is></c><c r="G408" s="2" t="inlineStr"><is><t>może być stosowany u osób z chorobami układu krążenia</t></is></c><c r="H408" s="2" t="inlineStr" /><c r="I408" s="2" t="inlineStr" /><c r="J408" s="2" t="inlineStr" /><c r="K408" s="2" t="inlineStr"><is><t>ma wysoką biodostępność po podaniu doustnym</t></is></c><c r="L408" s="2" t="inlineStr"><is><t>zwiększa wchłanianie witaminy D</t></is></c><c r="M408" s="2" t="inlineStr" /><c r="N408" s="2" t="inlineStr" /><c r="O408" s="2" t="inlineStr" /><c r="P408" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q408" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="409"><c r="A409" s="2" t="inlineStr"><is><t>NADCIŚNIENIE TĘTNICZE</t></is></c><c r="B409" s="2" t="inlineStr"><is><t>Farmakokinetyka</t></is></c><c r="C409" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D409" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E409" s="2" t="inlineStr"><is><t>Wybierz właściwe zestawienia lek prekursorowy – jego aktywny metabolit:</t></is></c><c r="F409" s="2" t="inlineStr"><is><t>cileksetyl kandesartanu → kandesartan</t></is></c><c r="G409" s="2" t="inlineStr" /><c r="H409" s="2" t="inlineStr" /><c r="I409" s="2" t="inlineStr" /><c r="J409" s="2" t="inlineStr" /><c r="K409" s="2" t="inlineStr"><is><t>eplerenon → kanrenon</t></is></c><c r="L409" s="2" t="inlineStr"><is><t>lizynopryl → lizynoprylat</t></is></c><c r="M409" s="2" t="inlineStr"><is><t>nebiwolol → tlenek azotu</t></is></c><c r="N409" s="2" t="inlineStr" /><c r="O409" s="2" t="inlineStr" /><c r="P409" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q409" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="410"><c r="A410" s="2" t="inlineStr"><is><t>LEKI MOCZOPĘDNE</t></is></c><c r="B410" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C410" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D410" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E410" s="2" t="inlineStr"><is><t>Torasemid w przeciwieństwie do furosemidu nie powoduje:</t></is></c><c r="F410" s="2" t="inlineStr"><is><t>retencji sodu po efekcie natiuretycznym przy podaniu 1 x 24 h</t></is></c><c r="G410" s="2" t="inlineStr" /><c r="H410" s="2" t="inlineStr" /><c r="I410" s="2" t="inlineStr" /><c r="J410" s="2" t="inlineStr" /><c r="K410" s="2" t="inlineStr"><is><t>efektu natiuretycznego po podaniu doustnym</t></is></c><c r="L410" s="2" t="inlineStr"><is><t>reakcji alergicznych w nadwrażliwości na związki sulfonamidowe</t></is></c><c r="M410" s="2" t="inlineStr"><is><t>hiperkalcemii</t></is></c><c r="N410" s="2" t="inlineStr" /><c r="O410" s="2" t="inlineStr" /><c r="P410" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q410" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="411"><c r="A411" s="2" t="inlineStr"><is><t>NADCIŚNIENIE TĘTNICZE</t></is></c><c r="B411" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C411" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D411" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E411" s="2" t="inlineStr"><is><t>Hiponatremię z dużym stężeniem Na+ w moczu (&gt; 20 mmol/l) może spowodować:</t></is></c><c r="F411" s="2" t="inlineStr"><is><t>karbamazepina</t></is></c><c r="G411" s="2" t="inlineStr"><is><t>fluoksetyna</t></is></c><c r="H411" s="2" t="inlineStr"><is><t>indapamid</t></is></c><c r="I411" s="2" t="inlineStr" /><c r="J411" s="2" t="inlineStr" /><c r="K411" s="2" t="inlineStr"><is><t>prednizon</t></is></c><c r="L411" s="2" t="inlineStr" /><c r="M411" s="2" t="inlineStr" /><c r="N411" s="2" t="inlineStr" /><c r="O411" s="2" t="inlineStr" /><c r="P411" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q411" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="412"><c r="A412" s="2" t="inlineStr"><is><t>LEKI IMMUNOSUPRESYJNE</t></is></c><c r="B412" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C412" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D412" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E412" s="2" t="inlineStr"><is><t>Wskaż prawidłowe połączenie lek-wskazanie:</t></is></c><c r="F412" s="2" t="inlineStr"><is><t>omalizumab – astma</t></is></c><c r="G412" s="2" t="inlineStr"><is><t>denosumab – osteoporoza</t></is></c><c r="H412" s="2" t="inlineStr" /><c r="I412" s="2" t="inlineStr" /><c r="J412" s="2" t="inlineStr" /><c r="K412" s="2" t="inlineStr"><is><t>natalizumab – reumatoidalne zapalenie stawów</t></is></c><c r="L412" s="2" t="inlineStr"><is><t>infliksymab – stwardnienie rozsiane</t></is></c><c r="M412" s="2" t="inlineStr" /><c r="N412" s="2" t="inlineStr" /><c r="O412" s="2" t="inlineStr" /><c r="P412" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q412" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="413"><c r="A413" s="2" t="inlineStr"><is><t>FARMAKOKINETYKA</t></is></c><c r="B413" s="2" t="inlineStr"><is><t>Farmakokinetyka</t></is></c><c r="C413" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D413" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E413" s="2" t="inlineStr"><is><t>Jeśli wartość AUC leku oceniona w badaniach przedklinicznych jest większa po podaniu dożylnym niż po podaniu doustnym, to oznacza, że:</t></is></c><c r="F413" s="2" t="inlineStr"><is><t>brak jest wystarczających danych do określenia przyczyny mniejszej wartości AUC leku po podaniu p.o</t></is></c><c r="G413" s="2" t="inlineStr"><is><t>biodostępność leku po podaniu i.v. jest większa niż po podaniu p.o</t></is></c><c r="H413" s="2" t="inlineStr" /><c r="I413" s="2" t="inlineStr" /><c r="J413" s="2" t="inlineStr" /><c r="K413" s="2" t="inlineStr"><is><t>AUC leku ocenione w badaniach klinicznych będzie podobne</t></is></c><c r="L413" s="2" t="inlineStr"><is><t>lek powinien być stosowany na czczo</t></is></c><c r="M413" s="2" t="inlineStr" /><c r="N413" s="2" t="inlineStr" /><c r="O413" s="2" t="inlineStr" /><c r="P413" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q413" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="414"><c r="A414" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B414" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C414" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D414" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E414" s="2" t="inlineStr"><is><t>Daptomycyna ma dwukompartmentowy model rozmieszczenia w organizmie (t 1/2 α= 7 min i t 1/2β = 5 h). Na tej podstawie uzasadniony jest następujący wniosek:</t></is></c><c r="F414" s="2" t="inlineStr"><is><t>po szybkiej fazie dystrybucji następuje wolniejsza faza eliminacji</t></is></c><c r="G414" s="2" t="inlineStr"><is><t>występuje utrudnienie w redystrybucji leku z tkanek do krążenia ogólnego</t></is></c><c r="H414" s="2" t="inlineStr" /><c r="I414" s="2" t="inlineStr" /><c r="J414" s="2" t="inlineStr" /><c r="K414" s="2" t="inlineStr"><is><t>lek wchłania się na dużej długości przewodu pokarmowego</t></is></c><c r="L414" s="2" t="inlineStr"><is><t>lek rozmieszcza się głównie w obszarach hydrofilnych</t></is></c><c r="M414" s="2" t="inlineStr" /><c r="N414" s="2" t="inlineStr" /><c r="O414" s="2" t="inlineStr" /><c r="P414" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q414" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="415"><c r="A415" s="2" t="inlineStr"><is><t>UKŁAD ODDECHOWY</t></is></c><c r="B415" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C415" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D415" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E415" s="2" t="inlineStr"><is><t>W terapii POChP u osób o niewielkim ryzyku i nasilonych objawach (kategoria B) stosuje się:</t></is></c><c r="F415" s="2" t="inlineStr"><is><t>salmeterol</t></is></c><c r="G415" s="2" t="inlineStr"><is><t>bromek aklidynium</t></is></c><c r="H415" s="2" t="inlineStr" /><c r="I415" s="2" t="inlineStr" /><c r="J415" s="2" t="inlineStr" /><c r="K415" s="2" t="inlineStr"><is><t>wziewne glikokortykosteroidy</t></is></c><c r="L415" s="2" t="inlineStr"><is><t>roflumilast</t></is></c><c r="M415" s="2" t="inlineStr" /><c r="N415" s="2" t="inlineStr" /><c r="O415" s="2" t="inlineStr" /><c r="P415" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q415" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="416"><c r="A416" s="2" t="inlineStr"><is><t>UKŁAD ODDECHOWY</t></is></c><c r="B416" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C416" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D416" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E416" s="2" t="inlineStr"><is><t>Działanie wykrztuśne ma:</t></is></c><c r="F416" s="2" t="inlineStr"><is><t>wyciąg z prawoślazu lekarskiego</t></is></c><c r="G416" s="2" t="inlineStr"><is><t>gwajafenazyna</t></is></c><c r="H416" s="2" t="inlineStr" /><c r="I416" s="2" t="inlineStr" /><c r="J416" s="2" t="inlineStr" /><c r="K416" s="2" t="inlineStr"><is><t>oksykodon</t></is></c><c r="L416" s="2" t="inlineStr"><is><t>mesna</t></is></c><c r="M416" s="2" t="inlineStr" /><c r="N416" s="2" t="inlineStr" /><c r="O416" s="2" t="inlineStr" /><c r="P416" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q416" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="417"><c r="A417" s="2" t="inlineStr"><is><t>UKŁAD WSPÓŁCZULNY</t></is></c><c r="B417" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C417" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D417" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E417" s="2" t="inlineStr"><is><t>Indakaterol:</t></is></c><c r="F417" s="2" t="inlineStr"><is><t>zwiększa aktywność ruchową rzęsek</t></is></c><c r="G417" s="2" t="inlineStr"><is><t>wykazuje synergizm działania z glikokortykosteroidami</t></is></c><c r="H417" s="2" t="inlineStr" /><c r="I417" s="2" t="inlineStr" /><c r="J417" s="2" t="inlineStr" /><c r="K417" s="2" t="inlineStr"><is><t>jest beta-adrenomimetykiem wziewnym o krótkim czasie działania (SABA)</t></is></c><c r="L417" s="2" t="inlineStr"><is><t>rozszczepia wiązania disiarczkowe w glikoproteinach śluzu</t></is></c><c r="M417" s="2" t="inlineStr" /><c r="N417" s="2" t="inlineStr" /><c r="O417" s="2" t="inlineStr" /><c r="P417" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q417" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="418"><c r="A418" s="2" t="inlineStr"><is><t>CHOROBA NIEDOKRWIENNA SERCA</t></is></c><c r="B418" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C418" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D418" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E418" s="2" t="inlineStr"><is><t>Meta-analiza badań klinicznych:</t></is></c><c r="F418" s="2" t="inlineStr"><is><t>jest uzupełnieniem przeglądu systematycznego</t></is></c><c r="G418" s="2" t="inlineStr"><is><t>może przynieść zupełnie nowe - odmienne wyniki niż badania, na których jest oparta</t></is></c><c r="H418" s="2" t="inlineStr"><is><t>pozwala zwiększyć precyzję oszacowania efektu klinicznego</t></is></c><c r="I418" s="2" t="inlineStr"><is><t>charakteryzuje się heterogenicznością statystyczną, która istotnie wpływa na interpretację wyników</t></is></c><c r="J418" s="2" t="inlineStr" /><c r="K418" s="2" t="inlineStr" /><c r="L418" s="2" t="inlineStr" /><c r="M418" s="2" t="inlineStr" /><c r="N418" s="2" t="inlineStr" /><c r="O418" s="2" t="inlineStr" /><c r="P418" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q418" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="419"><c r="A419" s="2" t="inlineStr"><is><t>LEKI PRZECIWWIRUSOWE</t></is></c><c r="B419" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C419" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D419" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E419" s="2" t="inlineStr"><is><t>Mieloidalne czynniki wzrostu (G-CSF oraz GM-CSF) znalazły zastosowanie u pacjentów:</t></is></c><c r="F419" s="2" t="inlineStr"><is><t>z ciężką przewlekłą neutropenią</t></is></c><c r="G419" s="2" t="inlineStr"><is><t>po przeszczepieniu komórek macierzystych szpiku kostnego</t></is></c><c r="H419" s="2" t="inlineStr" /><c r="I419" s="2" t="inlineStr" /><c r="J419" s="2" t="inlineStr" /><c r="K419" s="2" t="inlineStr"><is><t>zakażonych wirusem HIV</t></is></c><c r="L419" s="2" t="inlineStr"><is><t>z idiopatyczną plamicą małopłytkową</t></is></c><c r="M419" s="2" t="inlineStr" /><c r="N419" s="2" t="inlineStr" /><c r="O419" s="2" t="inlineStr" /><c r="P419" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q419" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="420"><c r="A420" s="2" t="inlineStr"><is><t>LEKI PRZECIWPASOŻYTNICZE</t></is></c><c r="B420" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C420" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D420" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E420" s="2" t="inlineStr"><is><t>Które stwierdzenie dotyczące profilaktyki malarii jest prawdziwe?</t></is></c><c r="F420" s="2" t="inlineStr"><is><t>dla większości leków standardowy czas rozpoczynania stosowania leku w profilaktyce wynosi tydzień przed planowaną podróżą</t></is></c><c r="G420" s="2" t="inlineStr"><is><t>nie dysponujemy uniwersalnym lekiem stosowanym w profilaktyce</t></is></c><c r="H420" s="2" t="inlineStr"><is><t>profilaktyka farmakologiczna stanowi uzupełnienie profilaktyki barierowej (odpowiednie ubrania, moskitiery i siatki nasączone DEET)</t></is></c><c r="I420" s="2" t="inlineStr" /><c r="J420" s="2" t="inlineStr" /><c r="K420" s="2" t="inlineStr"><is><t>leki stosuje się profilaktycznie tylko przez tydzień w czasie pobytu na terenie endemicznym</t></is></c><c r="L420" s="2" t="inlineStr" /><c r="M420" s="2" t="inlineStr" /><c r="N420" s="2" t="inlineStr" /><c r="O420" s="2" t="inlineStr" /><c r="P420" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q420" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="421"><c r="A421" s="2" t="inlineStr"><is><t>FARMAKOLOGIA OGÓLNA I EBM</t></is></c><c r="B421" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C421" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D421" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E421" s="2" t="inlineStr"><is><t>Przeprowadzenie eksperymentu leczniczego:</t></is></c><c r="F421" s="2" t="inlineStr"><is><t>jest możliwe, jeśli dostępne metody leczenia okazały się nieskuteczne</t></is></c><c r="G421" s="2" t="inlineStr"><is><t>wymaga świadomej zgody pacjenta</t></is></c><c r="H421" s="2" t="inlineStr" /><c r="I421" s="2" t="inlineStr" /><c r="J421" s="2" t="inlineStr" /><c r="K421" s="2" t="inlineStr"><is><t>ma na celu głównie poszerzenie wiedzy medycznej</t></is></c><c r="L421" s="2" t="inlineStr"><is><t>nie wymaga pozytywnej opinii Komisji Bioetycznej</t></is></c><c r="M421" s="2" t="inlineStr" /><c r="N421" s="2" t="inlineStr" /><c r="O421" s="2" t="inlineStr" /><c r="P421" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q421" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="422"><c r="A422" s="2" t="inlineStr"><is><t>LEKI ROŚLINNE I SUPLEMENTY</t></is></c><c r="B422" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C422" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D422" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E422" s="2" t="inlineStr"><is><t>W leczeniu niedokrwistości megaloblastycznej zastosowanie ma:</t></is></c><c r="F422" s="2" t="inlineStr"><is><t>cyjanokobalamina</t></is></c><c r="G422" s="2" t="inlineStr"><is><t>kwas foliowy</t></is></c><c r="H422" s="2" t="inlineStr" /><c r="I422" s="2" t="inlineStr" /><c r="J422" s="2" t="inlineStr" /><c r="K422" s="2" t="inlineStr"><is><t>siarczan żelaza</t></is></c><c r="L422" s="2" t="inlineStr"><is><t>erytropoetyna</t></is></c><c r="M422" s="2" t="inlineStr" /><c r="N422" s="2" t="inlineStr" /><c r="O422" s="2" t="inlineStr" /><c r="P422" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q422" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="423"><c r="A423" s="2" t="inlineStr"><is><t>NARKOTYCZNE LEKI PRZECIWBÓLOWE</t></is></c><c r="B423" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C423" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D423" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E423" s="2" t="inlineStr"><is><t>Preparat złożony naltreksonu z bupropionem:</t></is></c><c r="F423" s="2" t="inlineStr"><is><t>istotnie obniża masę ciała w porównaniu z placebo</t></is></c><c r="G423" s="2" t="inlineStr"><is><t>jest zarejestrowany w Europie do leczenia otyłości</t></is></c><c r="H423" s="2" t="inlineStr"><is><t>sprzyja pojawianiu się myśli samobójczych</t></is></c><c r="I423" s="2" t="inlineStr"><is><t>działa antagonistycznie na receptory 5HT2c</t></is></c><c r="J423" s="2" t="inlineStr" /><c r="K423" s="2" t="inlineStr" /><c r="L423" s="2" t="inlineStr" /><c r="M423" s="2" t="inlineStr" /><c r="N423" s="2" t="inlineStr" /><c r="O423" s="2" t="inlineStr" /><c r="P423" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q423" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="424"><c r="A424" s="2" t="inlineStr"><is><t>LEKI PRZECIWDEPRESYJNE</t></is></c><c r="B424" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C424" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D424" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E424" s="2" t="inlineStr"><is><t>W leczeniu uzależnienia od nikotyny wykazano skuteczność:</t></is></c><c r="F424" s="2" t="inlineStr"><is><t>warenikliny</t></is></c><c r="G424" s="2" t="inlineStr"><is><t>cytyzyny</t></is></c><c r="H424" s="2" t="inlineStr"><is><t>nikotynowej terapii zastępczej</t></is></c><c r="I424" s="2" t="inlineStr" /><c r="J424" s="2" t="inlineStr" /><c r="K424" s="2" t="inlineStr"><is><t>benzodiazepin</t></is></c><c r="L424" s="2" t="inlineStr" /><c r="M424" s="2" t="inlineStr" /><c r="N424" s="2" t="inlineStr" /><c r="O424" s="2" t="inlineStr" /><c r="P424" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q424" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="425"><c r="A425" s="2" t="inlineStr"><is><t>FARMAKOLOGIA OGÓLNA I EBM</t></is></c><c r="B425" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C425" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D425" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E425" s="2" t="inlineStr"><is><t>Elementami nadzoru nad bezpieczeństwem farmakoterapii jest:</t></is></c><c r="F425" s="2" t="inlineStr"><is><t>plan Zarządzania Ryzykiem</t></is></c><c r="G425" s="2" t="inlineStr"><is><t>strona internetowa Urzędu Rejestracji Produktów Leczniczych, Wyrobów Medycznych i Produktów Biobójczych</t></is></c><c r="H425" s="2" t="inlineStr"><is><t>raport PSUR</t></is></c><c r="I425" s="2" t="inlineStr"><is><t>baza zarejestrowanych produktów leczniczych prowadzona przez Europejską Agencję Leków</t></is></c><c r="J425" s="2" t="inlineStr" /><c r="K425" s="2" t="inlineStr" /><c r="L425" s="2" t="inlineStr" /><c r="M425" s="2" t="inlineStr" /><c r="N425" s="2" t="inlineStr" /><c r="O425" s="2" t="inlineStr" /><c r="P425" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q425" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="426"><c r="A426" s="2" t="inlineStr"><is><t>LEKI ROŚLINNE I SUPLEMENTY</t></is></c><c r="B426" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C426" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D426" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E426" s="2" t="inlineStr"><is><t>URPL - Urząd Rejestracji Produktów Leczniczych, Wyrobów Medycznych i Produktów Biobójczych ocenia działania niepożądane zarejestrowanych:</t></is></c><c r="F426" s="2" t="inlineStr"><is><t>leków homeopatycznych</t></is></c><c r="G426" s="2" t="inlineStr"><is><t>leków dostępnych bez recepty</t></is></c><c r="H426" s="2" t="inlineStr"><is><t>leków pochodzenia roślinnego</t></is></c><c r="I426" s="2" t="inlineStr" /><c r="J426" s="2" t="inlineStr" /><c r="K426" s="2" t="inlineStr"><is><t>suplementów diety</t></is></c><c r="L426" s="2" t="inlineStr" /><c r="M426" s="2" t="inlineStr" /><c r="N426" s="2" t="inlineStr" /><c r="O426" s="2" t="inlineStr" /><c r="P426" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q426" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="427"><c r="A427" s="2" t="inlineStr"><is><t>LEKI PRZECIWNOWOTWOROWE</t></is></c><c r="B427" s="2" t="inlineStr"><is><t>Ciąża</t></is></c><c r="C427" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D427" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E427" s="2" t="inlineStr"><is><t>Teratogenem człowieka o udokumentowanym działaniu jest:</t></is></c><c r="F427" s="2" t="inlineStr"><is><t>metotreksat</t></is></c><c r="G427" s="2" t="inlineStr"><is><t>kwas walproinowy</t></is></c><c r="H427" s="2" t="inlineStr"><is><t>lit</t></is></c><c r="I427" s="2" t="inlineStr" /><c r="J427" s="2" t="inlineStr" /><c r="K427" s="2" t="inlineStr"><is><t>tiamazol tiamazol ma kategorię D</t></is></c><c r="L427" s="2" t="inlineStr" /><c r="M427" s="2" t="inlineStr" /><c r="N427" s="2" t="inlineStr" /><c r="O427" s="2" t="inlineStr" /><c r="P427" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q427" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="428"><c r="A428" s="2" t="inlineStr"><is><t>LEKI PRZECIWWIRUSOWE</t></is></c><c r="B428" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C428" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D428" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E428" s="2" t="inlineStr"><is><t>Alfakalcydol:</t></is></c><c r="F428" s="2" t="inlineStr"><is><t>koryguje zaburzenia wapniowe w przewlekłej chorobie nerek</t></is></c><c r="G428" s="2" t="inlineStr"><is><t>koryguje zaburzenia wapniowe w niedoczynności przytarczyc</t></is></c><c r="H428" s="2" t="inlineStr"><is><t>zmniejsza ryzyko osteoporotycznych złamań kości</t></is></c><c r="I428" s="2" t="inlineStr" /><c r="J428" s="2" t="inlineStr" /><c r="K428" s="2" t="inlineStr"><is><t>chroni przed chorobami wirusowymi</t></is></c><c r="L428" s="2" t="inlineStr" /><c r="M428" s="2" t="inlineStr" /><c r="N428" s="2" t="inlineStr" /><c r="O428" s="2" t="inlineStr" /><c r="P428" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q428" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="429"><c r="A429" s="2" t="inlineStr"><is><t>LEKI MOCZOPĘDNE</t></is></c><c r="B429" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C429" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D429" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E429" s="2" t="inlineStr"><is><t>Wskaż prawdziwe stwierdzenie:</t></is></c><c r="F429" s="2" t="inlineStr"><is><t>5% roztwór glukozy jest izotoniczny in vitro i hipotoniczny in vivo</t></is></c><c r="G429" s="2" t="inlineStr"><is><t>15% roztwór mannitolu jest hipertonicznym płynem stosowanym do leczenia obrzęku mózgu</t></is></c><c r="H429" s="2" t="inlineStr" /><c r="I429" s="2" t="inlineStr" /><c r="J429" s="2" t="inlineStr" /><c r="K429" s="2" t="inlineStr"><is><t>stosowanie roztworów hipotonicznych grozi dehydratacją komórek i plazmolizą</t></is></c><c r="L429" s="2" t="inlineStr"><is><t>stosowanie roztworów hipertonicznych grozi obrzękiem komórek i ich lizą</t></is></c><c r="M429" s="2" t="inlineStr" /><c r="N429" s="2" t="inlineStr" /><c r="O429" s="2" t="inlineStr" /><c r="P429" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q429" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="430"><c r="A430" s="2" t="inlineStr"><is><t>OTĘPIENIE</t></is></c><c r="B430" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C430" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D430" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E430" s="2" t="inlineStr"><is><t>Podanie rywastygminy jest uzasadnione u pacjentów z:</t></is></c><c r="F430" s="2" t="inlineStr"><is><t>otępieniem w przebiegu choroby Parkinsona</t></is></c><c r="G430" s="2" t="inlineStr"><is><t>chorobą Alzheimera</t></is></c><c r="H430" s="2" t="inlineStr" /><c r="I430" s="2" t="inlineStr" /><c r="J430" s="2" t="inlineStr" /><c r="K430" s="2" t="inlineStr"><is><t>otępieniem naczyniopochodnym</t></is></c><c r="L430" s="2" t="inlineStr"><is><t>łagodnymi zaburzeniami poznawczymi</t></is></c><c r="M430" s="2" t="inlineStr" /><c r="N430" s="2" t="inlineStr" /><c r="O430" s="2" t="inlineStr" /><c r="P430" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q430" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="431"><c r="A431" s="2" t="inlineStr"><is><t>LEKI PRZECIWHISTAMINOWE</t></is></c><c r="B431" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C431" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D431" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E431" s="2" t="inlineStr"><is><t>Klemastyna:</t></is></c><c r="F431" s="2" t="inlineStr"><is><t>dobrze przenika przez barierę krew- mózg 22</t></is></c><c r="G431" s="2" t="inlineStr"><is><t>może być stosowana od 2 r. ż</t></is></c><c r="H431" s="2" t="inlineStr" /><c r="I431" s="2" t="inlineStr" /><c r="J431" s="2" t="inlineStr" /><c r="K431" s="2" t="inlineStr"><is><t>selektywnie działa na rec. H1</t></is></c><c r="L431" s="2" t="inlineStr"><is><t>jest lekiem z wyboru w leczeniu przewlekłego alergicznego nieżytu nosa</t></is></c><c r="M431" s="2" t="inlineStr" /><c r="N431" s="2" t="inlineStr" /><c r="O431" s="2" t="inlineStr" /><c r="P431" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q431" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="432"><c r="A432" s="2" t="inlineStr"><is><t>PADACZKA</t></is></c><c r="B432" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C432" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D432" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E432" s="2" t="inlineStr"><is><t>W stanie padaczkowym zalecane jest zastosowanie:</t></is></c><c r="F432" s="2" t="inlineStr"><is><t>lorazepamu dożylnie</t></is></c><c r="G432" s="2" t="inlineStr"><is><t>fenytoiny we wlewie dożylnym</t></is></c><c r="H432" s="2" t="inlineStr" /><c r="I432" s="2" t="inlineStr" /><c r="J432" s="2" t="inlineStr" /><c r="K432" s="2" t="inlineStr"><is><t>diazepamu domięśniowo</t></is></c><c r="L432" s="2" t="inlineStr"><is><t>fenobarbitalu podskórnie</t></is></c><c r="M432" s="2" t="inlineStr" /><c r="N432" s="2" t="inlineStr" /><c r="O432" s="2" t="inlineStr" /><c r="P432" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q432" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="433"><c r="A433" s="2" t="inlineStr"><is><t>LEKI PRZECIWNOWOTWOROWE</t></is></c><c r="B433" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C433" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D433" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E433" s="2" t="inlineStr"><is><t>Inhibitorem kinazy tyrozynowej o działaniu przeciwnowotworowym jest:</t></is></c><c r="F433" s="2" t="inlineStr"><is><t>imatynib</t></is></c><c r="G433" s="2" t="inlineStr"><is><t>sunitynib</t></is></c><c r="H433" s="2" t="inlineStr" /><c r="I433" s="2" t="inlineStr" /><c r="J433" s="2" t="inlineStr" /><c r="K433" s="2" t="inlineStr"><is><t>ewerolimus</t></is></c><c r="L433" s="2" t="inlineStr"><is><t>bortezomib</t></is></c><c r="M433" s="2" t="inlineStr" /><c r="N433" s="2" t="inlineStr" /><c r="O433" s="2" t="inlineStr" /><c r="P433" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q433" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="434"><c r="A434" s="2" t="inlineStr"><is><t>PADACZKA</t></is></c><c r="B434" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C434" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D434" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E434" s="2" t="inlineStr"><is><t>Wskaż prawidłowe połączenie lek – wskazanie:</t></is></c><c r="F434" s="2" t="inlineStr"><is><t>drżenie samoistne – propranolol</t></is></c><c r="G434" s="2" t="inlineStr"><is><t>zespół niespokojnych nóg – pramipeksol</t></is></c><c r="H434" s="2" t="inlineStr"><is><t>padaczka z napadami uogólnionymi toniczno-klonicznymi – kwas walproinowy</t></is></c><c r="I434" s="2" t="inlineStr"><is><t>immunologiczny obrzęk mózgu – deksametazon</t></is></c><c r="J434" s="2" t="inlineStr" /><c r="K434" s="2" t="inlineStr" /><c r="L434" s="2" t="inlineStr" /><c r="M434" s="2" t="inlineStr" /><c r="N434" s="2" t="inlineStr" /><c r="O434" s="2" t="inlineStr" /><c r="P434" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q434" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="435"><c r="A435" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B435" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C435" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D435" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E435" s="2" t="inlineStr"><is><t>Skuteczne leczenie w owrzodzeniach żylnych obejmuje:</t></is></c><c r="F435" s="2" t="inlineStr"><is><t>opatrunki hydrokoloidowe</t></is></c><c r="G435" s="2" t="inlineStr" /><c r="H435" s="2" t="inlineStr" /><c r="I435" s="2" t="inlineStr" /><c r="J435" s="2" t="inlineStr" /><c r="K435" s="2" t="inlineStr"><is><t>wyciągi zawierające glikozydy kasztanowca</t></is></c><c r="L435" s="2" t="inlineStr"><is><t>heparynoidy do stosowania miejscowego</t></is></c><c r="M435" s="2" t="inlineStr"><is><t>dobesylan wapnia</t></is></c><c r="N435" s="2" t="inlineStr" /><c r="O435" s="2" t="inlineStr" /><c r="P435" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q435" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="436"><c r="A436" s="2" t="inlineStr"><is><t>LEKI PRZECIWPSYCHOTYCZNE</t></is></c><c r="B436" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C436" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D436" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E436" s="2" t="inlineStr"><is><t>W leczeniu zaburzeń lękowych z napadami paniki można zastosować:</t></is></c><c r="F436" s="2" t="inlineStr"><is><t>doksepinę</t></is></c><c r="G436" s="2" t="inlineStr"><is><t>alprazolam</t></is></c><c r="H436" s="2" t="inlineStr" /><c r="I436" s="2" t="inlineStr" /><c r="J436" s="2" t="inlineStr" /><c r="K436" s="2" t="inlineStr"><is><t>rysperydon</t></is></c><c r="L436" s="2" t="inlineStr"><is><t>haloperydol</t></is></c><c r="M436" s="2" t="inlineStr" /><c r="N436" s="2" t="inlineStr" /><c r="O436" s="2" t="inlineStr" /><c r="P436" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q436" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="437"><c r="A437" s="2" t="inlineStr"><is><t>UKŁAD PRZYWSPÓŁCZULNY</t></is></c><c r="B437" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C437" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D437" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E437" s="2" t="inlineStr"><is><t>Działanie przeciwwymiotne ma:</t></is></c><c r="F437" s="2" t="inlineStr"><is><t>skopolamina</t></is></c><c r="G437" s="2" t="inlineStr"><is><t>dimenhydrinat</t></is></c><c r="H437" s="2" t="inlineStr" /><c r="I437" s="2" t="inlineStr" /><c r="J437" s="2" t="inlineStr" /><c r="K437" s="2" t="inlineStr"><is><t>lewetyracetam</t></is></c><c r="L437" s="2" t="inlineStr"><is><t>wortioksetyna</t></is></c><c r="M437" s="2" t="inlineStr" /><c r="N437" s="2" t="inlineStr" /><c r="O437" s="2" t="inlineStr" /><c r="P437" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q437" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="438"><c r="A438" s="2" t="inlineStr"><is><t>UKŁAD WSPÓŁCZULNY</t></is></c><c r="B438" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C438" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D438" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E438" s="2" t="inlineStr"><is><t>Amfetamina:</t></is></c><c r="F438" s="2" t="inlineStr"><is><t>może działać neurotoksycznie</t></is></c><c r="G438" s="2" t="inlineStr" /><c r="H438" s="2" t="inlineStr" /><c r="I438" s="2" t="inlineStr" /><c r="J438" s="2" t="inlineStr" /><c r="K438" s="2" t="inlineStr"><is><t>bezpośrednio pobudza receptory dopaminergiczne</t></is></c><c r="L438" s="2" t="inlineStr"><is><t>wzmaga apetyt</t></is></c><c r="M438" s="2" t="inlineStr"><is><t>obniża ciśnienie tętnicze krwi</t></is></c><c r="N438" s="2" t="inlineStr" /><c r="O438" s="2" t="inlineStr" /><c r="P438" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q438" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="439"><c r="A439" s="2" t="inlineStr"><is><t>UKŁAD PRZYWSPÓŁCZULNY</t></is></c><c r="B439" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C439" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D439" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E439" s="2" t="inlineStr"><is><t>Kwetiapina:</t></is></c><c r="F439" s="2" t="inlineStr"><is><t>zwiększa ryzyko wystąpienia zespołu metabolicznego</t></is></c><c r="G439" s="2" t="inlineStr"><is><t>może być stosowana jako lek normotymiczny</t></is></c><c r="H439" s="2" t="inlineStr" /><c r="I439" s="2" t="inlineStr" /><c r="J439" s="2" t="inlineStr" /><c r="K439" s="2" t="inlineStr"><is><t>nie powoduje złośliwego zespołu neuroleptycznego</t></is></c><c r="L439" s="2" t="inlineStr"><is><t>nie wykazuje aktywności cholinolitycznej</t></is></c><c r="M439" s="2" t="inlineStr" /><c r="N439" s="2" t="inlineStr" /><c r="O439" s="2" t="inlineStr" /><c r="P439" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q439" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="440"><c r="A440" s="2" t="inlineStr"><is><t>CHOROBA PARKINSONA</t></is></c><c r="B440" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C440" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D440" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E440" s="2" t="inlineStr"><is><t>W chorobie Parkinsona lewodopę można podawać jednocześnie z:</t></is></c><c r="F440" s="2" t="inlineStr"><is><t>benserazydem</t></is></c><c r="G440" s="2" t="inlineStr"><is><t>bromokryptyną</t></is></c><c r="H440" s="2" t="inlineStr"><is><t>rotygotyną</t></is></c><c r="I440" s="2" t="inlineStr"><is><t>entekaponem</t></is></c><c r="J440" s="2" t="inlineStr" /><c r="K440" s="2" t="inlineStr" /><c r="L440" s="2" t="inlineStr" /><c r="M440" s="2" t="inlineStr" /><c r="N440" s="2" t="inlineStr" /><c r="O440" s="2" t="inlineStr" /><c r="P440" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q440" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="441"><c r="A441" s="2" t="inlineStr"><is><t>LEKI PRZECIWPSYCHOTYCZNE</t></is></c><c r="B441" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C441" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D441" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E441" s="2" t="inlineStr"><is><t>Wystąpienie objawów pozapiramidowych w przebiegu leczenia lekami przeciwpsychotycznymi:</t></is></c><c r="F441" s="2" t="inlineStr"><is><t>jest wskazaniem do modyfikacji dawki leku</t></is></c><c r="G441" s="2" t="inlineStr"><is><t>zależy od procentu zablokowania receptorów D2 w układzie nigrostriatalnym</t></is></c><c r="H441" s="2" t="inlineStr" /><c r="I441" s="2" t="inlineStr" /><c r="J441" s="2" t="inlineStr" /><c r="K441" s="2" t="inlineStr"><is><t>jest wskazaniem do natychmiastowej zmiany leku</t></is></c><c r="L441" s="2" t="inlineStr"><is><t>jest nieodłącznym elementem leczenia przeciwpsychotycznego, obserwowanym u wszystkich leczonych pacjentów</t></is></c><c r="M441" s="2" t="inlineStr" /><c r="N441" s="2" t="inlineStr" /><c r="O441" s="2" t="inlineStr" /><c r="P441" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q441" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="442"><c r="A442" s="2" t="inlineStr"><is><t>LEKI PRZECIWDEPRESYJNE</t></is></c><c r="B442" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C442" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D442" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E442" s="2" t="inlineStr"><is><t>W leczeniu epizodu depresyjnego można zastosować w monoterapii:</t></is></c><c r="F442" s="2" t="inlineStr"><is><t>sertralinę</t></is></c><c r="G442" s="2" t="inlineStr"><is><t>mirtazapinę</t></is></c><c r="H442" s="2" t="inlineStr" /><c r="I442" s="2" t="inlineStr" /><c r="J442" s="2" t="inlineStr" /><c r="K442" s="2" t="inlineStr"><is><t>sulpiryd</t></is></c><c r="L442" s="2" t="inlineStr"><is><t>sertindol</t></is></c><c r="M442" s="2" t="inlineStr" /><c r="N442" s="2" t="inlineStr" /><c r="O442" s="2" t="inlineStr" /><c r="P442" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q442" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="443"><c r="A443" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B443" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C443" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D443" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E443" s="2" t="inlineStr"><is><t>U chorego leczonego escitalopramem ryzyko wystąpienia zespołu serotoninergicznego rośnie gdy dołączymy do terapii:</t></is></c><c r="F443" s="2" t="inlineStr"><is><t>linezolid</t></is></c><c r="G443" s="2" t="inlineStr"><is><t>tramadol</t></is></c><c r="H443" s="2" t="inlineStr"><is><t>ziele dziurawca</t></is></c><c r="I443" s="2" t="inlineStr"><is><t>korzeń żeń-szenia</t></is></c><c r="J443" s="2" t="inlineStr" /><c r="K443" s="2" t="inlineStr" /><c r="L443" s="2" t="inlineStr" /><c r="M443" s="2" t="inlineStr" /><c r="N443" s="2" t="inlineStr" /><c r="O443" s="2" t="inlineStr" /><c r="P443" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q443" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="444"><c r="A444" s="2" t="inlineStr"><is><t>LEKI PRZECIWLĘKOWE</t></is></c><c r="B444" s="2" t="inlineStr"><is><t>Antidotum</t></is></c><c r="C444" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D444" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E444" s="2" t="inlineStr"><is><t>Podanie węgla aktywowanego nie przyniesie efektu w przypadku zatrucia:</t></is></c><c r="F444" s="2" t="inlineStr"><is><t>etanolem</t></is></c><c r="G444" s="2" t="inlineStr"><is><t>ołowiem</t></is></c><c r="H444" s="2" t="inlineStr"><is><t>benzyną</t></is></c><c r="I444" s="2" t="inlineStr" /><c r="J444" s="2" t="inlineStr" /><c r="K444" s="2" t="inlineStr"><is><t>benzodiazepinami</t></is></c><c r="L444" s="2" t="inlineStr" /><c r="M444" s="2" t="inlineStr" /><c r="N444" s="2" t="inlineStr" /><c r="O444" s="2" t="inlineStr" /><c r="P444" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q444" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="445"><c r="A445" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B445" s="2" t="inlineStr"><is><t>Farmakokinetyka</t></is></c><c r="C445" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D445" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E445" s="2" t="inlineStr"><is><t>U osób w starszym wieku na zmiany farmakokinetyki leków mogą wpływać:</t></is></c><c r="F445" s="2" t="inlineStr"><is><t>hipoproteinemia</t></is></c><c r="G445" s="2" t="inlineStr"><is><t>spadek masy wątroby</t></is></c><c r="H445" s="2" t="inlineStr" /><c r="I445" s="2" t="inlineStr" /><c r="J445" s="2" t="inlineStr" /><c r="K445" s="2" t="inlineStr"><is><t>zanik kosmków jelitowych</t></is></c><c r="L445" s="2" t="inlineStr"><is><t>obniżenie stężenia kwaśnej alfa-1 glikoproteiny</t></is></c><c r="M445" s="2" t="inlineStr" /><c r="N445" s="2" t="inlineStr" /><c r="O445" s="2" t="inlineStr" /><c r="P445" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q445" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="446"><c r="A446" s="2" t="inlineStr"><is><t>UKŁAD PRZYWSPÓŁCZULNY</t></is></c><c r="B446" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C446" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D446" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E446" s="2" t="inlineStr"><is><t>Inhibitorem fosfodiesterazy typu 5 jest:</t></is></c><c r="F446" s="2" t="inlineStr"><is><t>tadalafil</t></is></c><c r="G446" s="2" t="inlineStr" /><c r="H446" s="2" t="inlineStr" /><c r="I446" s="2" t="inlineStr" /><c r="J446" s="2" t="inlineStr" /><c r="K446" s="2" t="inlineStr"><is><t>trospium</t></is></c><c r="L446" s="2" t="inlineStr"><is><t>alprostadyl</t></is></c><c r="M446" s="2" t="inlineStr"><is><t>solifenacyna</t></is></c><c r="N446" s="2" t="inlineStr" /><c r="O446" s="2" t="inlineStr" /><c r="P446" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q446" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="447"><c r="A447" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B447" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C447" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D447" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E447" s="2" t="inlineStr"><is><t>W zespole jelita drażliwego może być skuteczne zastosowanie:</t></is></c><c r="F447" s="2" t="inlineStr"><is><t>mebeweryny</t></is></c><c r="G447" s="2" t="inlineStr"><is><t>atropiny z difenoksylatem</t></is></c><c r="H447" s="2" t="inlineStr"><is><t>trimebutyny</t></is></c><c r="I447" s="2" t="inlineStr"><is><t>Bifidobacterium</t></is></c><c r="J447" s="2" t="inlineStr" /><c r="K447" s="2" t="inlineStr" /><c r="L447" s="2" t="inlineStr" /><c r="M447" s="2" t="inlineStr" /><c r="N447" s="2" t="inlineStr" /><c r="O447" s="2" t="inlineStr" /><c r="P447" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q447" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="448"><c r="A448" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B448" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C448" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D448" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E448" s="2" t="inlineStr"><is><t>Przewlekłe stosowanie pantoprazolu:</t></is></c><c r="F448" s="2" t="inlineStr"><is><t>zwiększa ryzyko zakażeń dróg oddechowych</t></is></c><c r="G448" s="2" t="inlineStr"><is><t>zaburza wchłanianie wapnia z przewodu pokarmowego</t></is></c><c r="H448" s="2" t="inlineStr"><is><t>zmniejsza działanie klopidogrelu</t></is></c><c r="I448" s="2" t="inlineStr" /><c r="J448" s="2" t="inlineStr" /><c r="K448" s="2" t="inlineStr"><is><t>zmniejsza ryzyko złamania szyjki kości udowej</t></is></c><c r="L448" s="2" t="inlineStr" /><c r="M448" s="2" t="inlineStr" /><c r="N448" s="2" t="inlineStr" /><c r="O448" s="2" t="inlineStr" /><c r="P448" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q448" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="449"><c r="A449" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B449" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C449" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D449" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E449" s="2" t="inlineStr"><is><t>Wskazaniem do eradykacji Helicobacter pylori może być:</t></is></c><c r="F449" s="2" t="inlineStr"><is><t>planowane leczenie niesteroidowymi lekami przeciwzapalnymi</t></is></c><c r="G449" s="2" t="inlineStr"><is><t>niedokrwistość syderopeniczna</t></is></c><c r="H449" s="2" t="inlineStr"><is><t>chłoniak żołądka typu MALT</t></is></c><c r="I449" s="2" t="inlineStr"><is><t>aktywna choroba wrzodowa żołądka/dwunastnicy</t></is></c><c r="J449" s="2" t="inlineStr" /><c r="K449" s="2" t="inlineStr" /><c r="L449" s="2" t="inlineStr" /><c r="M449" s="2" t="inlineStr" /><c r="N449" s="2" t="inlineStr" /><c r="O449" s="2" t="inlineStr" /><c r="P449" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q449" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="450"><c r="A450" s="2" t="inlineStr"><is><t>NADCIŚNIENIE TĘTNICZE</t></is></c><c r="B450" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C450" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D450" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E450" s="2" t="inlineStr"><is><t>W profilaktyce krwawienia z żylaków przełyku w przebiegu nadciśnienia wrotnego stosuje się:</t></is></c><c r="F450" s="2" t="inlineStr"><is><t>propranolol</t></is></c><c r="G450" s="2" t="inlineStr"><is><t>karwedilol</t></is></c><c r="H450" s="2" t="inlineStr" /><c r="I450" s="2" t="inlineStr" /><c r="J450" s="2" t="inlineStr" /><c r="K450" s="2" t="inlineStr"><is><t>doksazosynę</t></is></c><c r="L450" s="2" t="inlineStr"><is><t>klonidynę</t></is></c><c r="M450" s="2" t="inlineStr" /><c r="N450" s="2" t="inlineStr" /><c r="O450" s="2" t="inlineStr" /><c r="P450" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q450" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="451"><c r="A451" s="2" t="inlineStr"><is><t>NIEWYDOLNOŚĆ SERCA</t></is></c><c r="B451" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C451" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D451" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E451" s="2" t="inlineStr"><is><t>Noradrenalinę (NA) podaje się w dawce 0,2-1 μg/kg/min rozpoczynając od najmniejszej dawki. Wskaż właściwą szybkość wlewu w początkowym leczeniu 50 kg kobiety z ciśnieniem skurczowym ok. 60 mmHg w przebiegu ostrej niewydolności serca:</t></is></c><c r="F451" s="2" t="inlineStr"><is><t>roztwór 4 mg NA/40 ml 0,9% NaCl – 6 ml/h</t></is></c><c r="G451" s="2" t="inlineStr"><is><t>roztwór 1 mg NA/50 ml 0,9% NaCl – 30 ml/h</t></is></c><c r="H451" s="2" t="inlineStr"><is><t>roztwór 5 mg NA/25 ml 0,9% NaCl - 3 ml/h</t></is></c><c r="I451" s="2" t="inlineStr"><is><t>roztwór 3 mg NA/30 ml 0,9 % NaCl – 6 ml/h</t></is></c><c r="J451" s="2" t="inlineStr" /><c r="K451" s="2" t="inlineStr" /><c r="L451" s="2" t="inlineStr" /><c r="M451" s="2" t="inlineStr" /><c r="N451" s="2" t="inlineStr" /><c r="O451" s="2" t="inlineStr" /><c r="P451" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q451" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="452"><c r="A452" s="2" t="inlineStr"><is><t>NADCIŚNIENIE TĘTNICZE</t></is></c><c r="B452" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C452" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D452" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E452" s="2" t="inlineStr"><is><t>Działanie naczyniorozszerzające ma:</t></is></c><c r="F452" s="2" t="inlineStr"><is><t>terazosyna</t></is></c><c r="G452" s="2" t="inlineStr"><is><t>nebiwolol</t></is></c><c r="H452" s="2" t="inlineStr"><is><t>zofenopryl</t></is></c><c r="I452" s="2" t="inlineStr"><is><t>lerkanidypina</t></is></c><c r="J452" s="2" t="inlineStr" /><c r="K452" s="2" t="inlineStr" /><c r="L452" s="2" t="inlineStr" /><c r="M452" s="2" t="inlineStr" /><c r="N452" s="2" t="inlineStr" /><c r="O452" s="2" t="inlineStr" /><c r="P452" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q452" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="453"><c r="A453" s="2" t="inlineStr"><is><t>CHOROBA NIEDOKRWIENNA SERCA</t></is></c><c r="B453" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C453" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D453" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E453" s="2" t="inlineStr"><is><t>Podobny mechanizm działania na poziomie molekularnym mają:</t></is></c><c r="F453" s="2" t="inlineStr"><is><t>monoazotan izosorbidu</t></is></c><c r="G453" s="2" t="inlineStr"><is><t>nesirytyd</t></is></c><c r="H453" s="2" t="inlineStr"><is><t>riociguat</t></is></c><c r="I453" s="2" t="inlineStr"><is><t>wardenafil</t></is></c><c r="J453" s="2" t="inlineStr" /><c r="K453" s="2" t="inlineStr" /><c r="L453" s="2" t="inlineStr" /><c r="M453" s="2" t="inlineStr" /><c r="N453" s="2" t="inlineStr" /><c r="O453" s="2" t="inlineStr" /><c r="P453" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q453" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="454"><c r="A454" s="2" t="inlineStr"><is><t>UKŁAD WSPÓŁCZULNY</t></is></c><c r="B454" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C454" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D454" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E454" s="2" t="inlineStr"><is><t>Beta-adrenolityki w chorobie niedokrwiennej serca:</t></is></c><c r="F454" s="2" t="inlineStr"><is><t>zmniejszają agregację płytek krwi</t></is></c><c r="G454" s="2" t="inlineStr"><is><t>zwiększają przepływ wieńcowy</t></is></c><c r="H454" s="2" t="inlineStr"><is><t>zapobiegają proarytmicznemu działaniu katecholamin</t></is></c><c r="I454" s="2" t="inlineStr"><is><t>zmniejszają kurczliwość mięśnia sercowego</t></is></c><c r="J454" s="2" t="inlineStr" /><c r="K454" s="2" t="inlineStr" /><c r="L454" s="2" t="inlineStr" /><c r="M454" s="2" t="inlineStr" /><c r="N454" s="2" t="inlineStr" /><c r="O454" s="2" t="inlineStr" /><c r="P454" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q454" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="455"><c r="A455" s="2" t="inlineStr"><is><t>NIEWYDOLNOŚĆ SERCA</t></is></c><c r="B455" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C455" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D455" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E455" s="2" t="inlineStr"><is><t>Digoksyna:</t></is></c><c r="F455" s="2" t="inlineStr"><is><t>zmniejsza aktywację układu współczulnego u osób z niewydolnością serca</t></is></c><c r="G455" s="2" t="inlineStr"><is><t>może sprzyjać wystąpieniu depresji</t></is></c><c r="H455" s="2" t="inlineStr"><is><t>jest stosowana w celu kontroli rytmu serca w utrwalonym migotaniu przedsionków</t></is></c><c r="I455" s="2" t="inlineStr"><is><t>może być nieskuteczna z powodu dezaktywacji przez bakterie jelitowe</t></is></c><c r="J455" s="2" t="inlineStr" /><c r="K455" s="2" t="inlineStr" /><c r="L455" s="2" t="inlineStr" /><c r="M455" s="2" t="inlineStr" /><c r="N455" s="2" t="inlineStr" /><c r="O455" s="2" t="inlineStr" /><c r="P455" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q455" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="456"><c r="A456" s="2" t="inlineStr"><is><t>NIEWYDOLNOŚĆ SERCA</t></is></c><c r="B456" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C456" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D456" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E456" s="2" t="inlineStr"><is><t>Ranolazyna ma działanie:</t></is></c><c r="F456" s="2" t="inlineStr"><is><t>antyarytmiczne</t></is></c><c r="G456" s="2" t="inlineStr"><is><t>korzystne metaboliczne w kardiomiocytach</t></is></c><c r="H456" s="2" t="inlineStr"><is><t>zmniejszające naprężenie ściany lewej komory</t></is></c><c r="I456" s="2" t="inlineStr" /><c r="J456" s="2" t="inlineStr" /><c r="K456" s="2" t="inlineStr"><is><t>inotropowe dodatnie</t></is></c><c r="L456" s="2" t="inlineStr" /><c r="M456" s="2" t="inlineStr" /><c r="N456" s="2" t="inlineStr" /><c r="O456" s="2" t="inlineStr" /><c r="P456" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q456" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="457"><c r="A457" s="2" t="inlineStr"><is><t>LEKI HIPOLIPEMIZUJĄCE</t></is></c><c r="B457" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C457" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D457" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E457" s="2" t="inlineStr"><is><t>Jakie leki zlecisz 48-letniemu bezobjawowemu mężczyźnie z BMI = 24,1 kg/m2, palącemu 20 papierosów dziennie od ok. 30 lat, z ciśnieniem tętniczym 150-155 mmHg w powtarzanych pomiarach i ze stężeniem cholesterolu LDL w surowicy = 200 mg/dl:</t></is></c><c r="F457" s="2" t="inlineStr"><is><t>ramipryl</t></is></c><c r="G457" s="2" t="inlineStr"><is><t>nikotynę w inhalacjach pod warunkiem zaprzestania palenia papierosów</t></is></c><c r="H457" s="2" t="inlineStr"><is><t>rosuwastatynę</t></is></c><c r="I457" s="2" t="inlineStr" /><c r="J457" s="2" t="inlineStr" /><c r="K457" s="2" t="inlineStr"><is><t>klopidogrel</t></is></c><c r="L457" s="2" t="inlineStr" /><c r="M457" s="2" t="inlineStr" /><c r="N457" s="2" t="inlineStr" /><c r="O457" s="2" t="inlineStr" /><c r="P457" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q457" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="458"><c r="A458" s="2" t="inlineStr"><is><t>NIEWYDOLNOŚĆ SERCA</t></is></c><c r="B458" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C458" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D458" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E458" s="2" t="inlineStr"><is><t>W niewydolności serca przeżycie chorych poprawia:</t></is></c><c r="F458" s="2" t="inlineStr"><is><t>eplerenon</t></is></c><c r="G458" s="2" t="inlineStr" /><c r="H458" s="2" t="inlineStr" /><c r="I458" s="2" t="inlineStr" /><c r="J458" s="2" t="inlineStr" /><c r="K458" s="2" t="inlineStr"><is><t>atenolol</t></is></c><c r="L458" s="2" t="inlineStr"><is><t>tolwaptan</t></is></c><c r="M458" s="2" t="inlineStr"><is><t>digoksyna</t></is></c><c r="N458" s="2" t="inlineStr" /><c r="O458" s="2" t="inlineStr" /><c r="P458" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q458" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="459"><c r="A459" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B459" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C459" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D459" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E459" s="2" t="inlineStr"><is><t>55-letni mężczyzna ma trwający od ok. 60-min ucisk za mostkiem, który wystąpił podczas ubierania się po wstaniu z łóżka, w EKG rozlane obniżenia ST w odprowadzeniach znad ściany przedniej. Jako lekarz pierwszego kontaktu medycznego zastosujesz:</t></is></c><c r="F459" s="2" t="inlineStr"><is><t>tikagrelor w dawce 180 mg p.o</t></is></c><c r="G459" s="2" t="inlineStr"><is><t>kwas acetylosalicylowy w dawce 300 mg p.o</t></is></c><c r="H459" s="2" t="inlineStr" /><c r="I459" s="2" t="inlineStr" /><c r="J459" s="2" t="inlineStr" /><c r="K459" s="2" t="inlineStr"><is><t>morfinę w dawkach frakcjonowanych i.v</t></is></c><c r="L459" s="2" t="inlineStr"><is><t>enoksaparynę w dawce leczniczej s.c</t></is></c><c r="M459" s="2" t="inlineStr" /><c r="N459" s="2" t="inlineStr" /><c r="O459" s="2" t="inlineStr" /><c r="P459" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q459" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="460"><c r="A460" s="2" t="inlineStr"><is><t>ZABURZENIA RYTMU SERCA</t></is></c><c r="B460" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C460" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D460" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E460" s="2" t="inlineStr"><is><t>Amiodaron:</t></is></c><c r="F460" s="2" t="inlineStr"><is><t>obniża energię potrzebną do skutecznej defibrylacji elektrycznej</t></is></c><c r="G460" s="2" t="inlineStr"><is><t>może być rozpuszczany w 5% glukozie</t></is></c><c r="H460" s="2" t="inlineStr" /><c r="I460" s="2" t="inlineStr" /><c r="J460" s="2" t="inlineStr" /><c r="K460" s="2" t="inlineStr"><is><t>jest antagonistą sercowych kanałów potasowych z wyjątkiem ikr</t></is></c><c r="L460" s="2" t="inlineStr"><is><t>jest stosowany alternatywnie z lidokainą w resuscytacji krążeniowo-oddechowej</t></is></c><c r="M460" s="2" t="inlineStr" /><c r="N460" s="2" t="inlineStr" /><c r="O460" s="2" t="inlineStr" /><c r="P460" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q460" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="461"><c r="A461" s="2" t="inlineStr"><is><t>CUKRZYCA</t></is></c><c r="B461" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C461" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D461" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E461" s="2" t="inlineStr"><is><t>Które stwierdzenie dotyczące redukcji ryzyka sercowo-naczyniowego jest prawdziwe:</t></is></c><c r="F461" s="2" t="inlineStr"><is><t>nikotynowa terapia zastępcza jest bezpieczna i powinna być rutynowo oferowana</t></is></c><c r="G461" s="2" t="inlineStr" /><c r="H461" s="2" t="inlineStr" /><c r="I461" s="2" t="inlineStr" /><c r="J461" s="2" t="inlineStr" /><c r="K461" s="2" t="inlineStr"><is><t>niezależnie od wieku należy dążyć do redukcji ciśnienia tętniczego do &lt; 140/90 mmHg</t></is></c><c r="L461" s="2" t="inlineStr"><is><t>obniżenie poziomu hemoglobiny glikowanej HgbA1c do ≤ 6% u osób z cukrzycą poprawia przeżycie w porównaniu z wyższymi wartościami HbA1c</t></is></c><c r="M461" s="2" t="inlineStr"><is><t>wysokie prawidłowe ciśnienie krwi powinno być leczone farmakologicznie</t></is></c><c r="N461" s="2" t="inlineStr" /><c r="O461" s="2" t="inlineStr" /><c r="P461" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q461" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="462"><c r="A462" s="2" t="inlineStr"><is><t>NADCIŚNIENIE TĘTNICZE</t></is></c><c r="B462" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C462" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D462" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E462" s="2" t="inlineStr"><is><t>W leczeniu nadciśnienia tętniczego przeciwwskazane jest połączenie:</t></is></c><c r="F462" s="2" t="inlineStr"><is><t>ramipryl + telmisartan</t></is></c><c r="G462" s="2" t="inlineStr" /><c r="H462" s="2" t="inlineStr" /><c r="I462" s="2" t="inlineStr" /><c r="J462" s="2" t="inlineStr" /><c r="K462" s="2" t="inlineStr"><is><t>amlodypina + chlortalidon</t></is></c><c r="L462" s="2" t="inlineStr"><is><t>amlodypina + peryndopryl</t></is></c><c r="M462" s="2" t="inlineStr"><is><t>peryndopryl + indapamid</t></is></c><c r="N462" s="2" t="inlineStr" /><c r="O462" s="2" t="inlineStr" /><c r="P462" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q462" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="463"><c r="A463" s="2" t="inlineStr"><is><t>CHOROBA NIEDOKRWIENNA SERCA</t></is></c><c r="B463" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C463" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D463" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E463" s="2" t="inlineStr"><is><t>U pacjenta z dławicą piersiową i niskim ciśnieniem tętniczym krwi można zastosować:</t></is></c><c r="F463" s="2" t="inlineStr"><is><t>ranolazynę</t></is></c><c r="G463" s="2" t="inlineStr"><is><t>iwabradynę</t></is></c><c r="H463" s="2" t="inlineStr"><is><t>trimetazydynę</t></is></c><c r="I463" s="2" t="inlineStr" /><c r="J463" s="2" t="inlineStr" /><c r="K463" s="2" t="inlineStr"><is><t>werapamil</t></is></c><c r="L463" s="2" t="inlineStr" /><c r="M463" s="2" t="inlineStr" /><c r="N463" s="2" t="inlineStr" /><c r="O463" s="2" t="inlineStr" /><c r="P463" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q463" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="464"><c r="A464" s="2" t="inlineStr"><is><t>ZABURZENIA RYTMU SERCA</t></is></c><c r="B464" s="2" t="inlineStr"><is><t>Przeciwwskazania</t></is></c><c r="C464" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D464" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E464" s="2" t="inlineStr"><is><t>Propafenon:</t></is></c><c r="F464" s="2" t="inlineStr"><is><t>jest antagonistą kanału sodowego</t></is></c><c r="G464" s="2" t="inlineStr"><is><t>ma działanie betaadrenolityczne</t></is></c><c r="H464" s="2" t="inlineStr" /><c r="I464" s="2" t="inlineStr" /><c r="J464" s="2" t="inlineStr" /><c r="K464" s="2" t="inlineStr"><is><t>rozszerza nasierdziowe tętnice wieńcowe</t></is></c><c r="L464" s="2" t="inlineStr"><is><t>jest przeciwwskazany w zespole preekscytacji (WPW)</t></is></c><c r="M464" s="2" t="inlineStr" /><c r="N464" s="2" t="inlineStr" /><c r="O464" s="2" t="inlineStr" /><c r="P464" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q464" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="465"><c r="A465" s="2" t="inlineStr"><is><t>NADCIŚNIENIE TĘTNICZE</t></is></c><c r="B465" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C465" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D465" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E465" s="2" t="inlineStr"><is><t>Teoretyczną przesłanką stosowania inhibitorów konwertazy angiotensyny w przewlekłej skurczowej niewydolności serca jest:</t></is></c><c r="F465" s="2" t="inlineStr"><is><t>odwracanie włóknienia miokardium</t></is></c><c r="G465" s="2" t="inlineStr"><is><t>odwracanie przerostu kardiomiocytów</t></is></c><c r="H465" s="2" t="inlineStr"><is><t>korzystne bezpośrednie działanie hemodynamiczne</t></is></c><c r="I465" s="2" t="inlineStr" /><c r="J465" s="2" t="inlineStr" /><c r="K465" s="2" t="inlineStr"><is><t>zwiększenie naprężenia ściany lewej komory</t></is></c><c r="L465" s="2" t="inlineStr" /><c r="M465" s="2" t="inlineStr" /><c r="N465" s="2" t="inlineStr" /><c r="O465" s="2" t="inlineStr" /><c r="P465" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q465" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="466"><c r="A466" s="2" t="inlineStr"><is><t>CUKRZYCA</t></is></c><c r="B466" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C466" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D466" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E466" s="2" t="inlineStr"><is><t>Metformina:</t></is></c><c r="F466" s="2" t="inlineStr"><is><t>wpływa korzystnie na profil lipidowy</t></is></c><c r="G466" s="2" t="inlineStr" /><c r="H466" s="2" t="inlineStr" /><c r="I466" s="2" t="inlineStr" /><c r="J466" s="2" t="inlineStr" /><c r="K466" s="2" t="inlineStr"><is><t>powoduje przyrost masy ciała</t></is></c><c r="L466" s="2" t="inlineStr"><is><t>zwiększa ryzyko hipoglikemii</t></is></c><c r="M466" s="2" t="inlineStr"><is><t>może być przyczyną uporczywych zaparć</t></is></c><c r="N466" s="2" t="inlineStr" /><c r="O466" s="2" t="inlineStr" /><c r="P466" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2019/20 - 1 termin</t></is></c><c r="Q466" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="467"><c r="A467" s="2" t="inlineStr"><is><t>NIEOPIOIDOWE LEKI PRZECIWBÓLOWE</t></is></c><c r="B467" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C467" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D467" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E467" s="2" t="inlineStr"><is><t>Wskaż prawidłowe stwierdzenie:</t></is></c><c r="F467" s="2" t="inlineStr"><is><t>Diklofenak działa hepatotoksycznie</t></is></c><c r="G467" s="2" t="inlineStr" /><c r="H467" s="2" t="inlineStr" /><c r="I467" s="2" t="inlineStr" /><c r="J467" s="2" t="inlineStr" /><c r="K467" s="2" t="inlineStr"><is><t>Paracetamol działa antyagregacyjnie</t></is></c><c r="L467" s="2" t="inlineStr"><is><t>Naproksen działa hipotensyjnie</t></is></c><c r="M467" s="2" t="inlineStr"><is><t>Metamizol działa prozakrzepowo</t></is></c><c r="N467" s="2" t="inlineStr" /><c r="O467" s="2" t="inlineStr" /><c r="P467" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2019/20 - 1 termin</t></is></c><c r="Q467" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="468"><c r="A468" s="2" t="inlineStr"><is><t>NARKOTYCZNE LEKI PRZECIWBÓLOWE</t></is></c><c r="B468" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C468" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D468" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E468" s="2" t="inlineStr"><is><t>Tramadol jest:</t></is></c><c r="F468" s="2" t="inlineStr"><is><t>Inhibitorem wychwytu zwrotnego serotoniny</t></is></c><c r="G468" s="2" t="inlineStr"><is><t>Agonistą receptorów opioidowych typu μ</t></is></c><c r="H468" s="2" t="inlineStr" /><c r="I468" s="2" t="inlineStr" /><c r="J468" s="2" t="inlineStr" /><c r="K468" s="2" t="inlineStr"><is><t>Inhibitorem wychwytu zwrotnego dopaminy</t></is></c><c r="L468" s="2" t="inlineStr"><is><t>Agonistą receptorów NMDA</t></is></c><c r="M468" s="2" t="inlineStr" /><c r="N468" s="2" t="inlineStr" /><c r="O468" s="2" t="inlineStr" /><c r="P468" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2019/20 - 1 termin</t></is></c><c r="Q468" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="469"><c r="A469" s="2" t="inlineStr"><is><t>CUKRZYCA</t></is></c><c r="B469" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C469" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D469" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E469" s="2" t="inlineStr"><is><t>Hamowanie enzymu stanowi zasadniczy mechanizm działania:</t></is></c><c r="F469" s="2" t="inlineStr"><is><t>cyklosporyny</t></is></c><c r="G469" s="2" t="inlineStr" /><c r="H469" s="2" t="inlineStr" /><c r="I469" s="2" t="inlineStr" /><c r="J469" s="2" t="inlineStr" /><c r="K469" s="2" t="inlineStr"><is><t>Liraglutydu</t></is></c><c r="L469" s="2" t="inlineStr"><is><t>Lorazepamu</t></is></c><c r="M469" s="2" t="inlineStr"><is><t>Buprenorfiny</t></is></c><c r="N469" s="2" t="inlineStr" /><c r="O469" s="2" t="inlineStr" /><c r="P469" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2019/20 - 1 termin</t></is></c><c r="Q469" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="470"><c r="A470" s="2" t="inlineStr"><is><t>CUKRZYCA</t></is></c><c r="B470" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C470" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D470" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E470" s="2" t="inlineStr"><is><t>Ryzyko wzrostu masy ciała jest związane z terapią:</t></is></c><c r="F470" s="2" t="inlineStr"><is><t>Olanzapiną</t></is></c><c r="G470" s="2" t="inlineStr"><is><t>Insuliną</t></is></c><c r="H470" s="2" t="inlineStr"><is><t>prednizonem</t></is></c><c r="I470" s="2" t="inlineStr" /><c r="J470" s="2" t="inlineStr" /><c r="K470" s="2" t="inlineStr"><is><t>Liraglutydem</t></is></c><c r="L470" s="2" t="inlineStr" /><c r="M470" s="2" t="inlineStr" /><c r="N470" s="2" t="inlineStr" /><c r="O470" s="2" t="inlineStr" /><c r="P470" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2019/20 - 1 termin</t></is></c><c r="Q470" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="471"><c r="A471" s="2" t="inlineStr"><is><t>NIEOPIOIDOWE LEKI PRZECIWBÓLOWE</t></is></c><c r="B471" s="2" t="inlineStr"><is><t>Sposób podania</t></is></c><c r="C471" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D471" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E471" s="2" t="inlineStr"><is><t>Lek A jest stosowany doustnie. Ma właściwości przeciwbólowe, ale nie ma właściwości przeciwzapalnych. Nie powoduje istotnego wzrostu ryzyka powikłań sercowo – naczyniowych. Lekiem A może być:</t></is></c><c r="F471" s="2" t="inlineStr"><is><t>Tramadol</t></is></c><c r="G471" s="2" t="inlineStr"><is><t>Paracetamol</t></is></c><c r="H471" s="2" t="inlineStr" /><c r="I471" s="2" t="inlineStr" /><c r="J471" s="2" t="inlineStr" /><c r="K471" s="2" t="inlineStr"><is><t>Naproksen</t></is></c><c r="L471" s="2" t="inlineStr"><is><t>Celekoksyb</t></is></c><c r="M471" s="2" t="inlineStr" /><c r="N471" s="2" t="inlineStr" /><c r="O471" s="2" t="inlineStr" /><c r="P471" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2019/20 - 1 termin</t></is></c><c r="Q471" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="472"><c r="A472" s="2" t="inlineStr"><is><t>OSTEOPOROZA</t></is></c><c r="B472" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C472" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D472" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E472" s="2" t="inlineStr"><is><t>Bisfosfoniany są stosowane:</t></is></c><c r="F472" s="2" t="inlineStr"><is><t>w leczeniu osteoporozy posteroidowej</t></is></c><c r="G472" s="2" t="inlineStr"><is><t>w leczeniu ciężkiej hiperkalcemii</t></is></c><c r="H472" s="2" t="inlineStr" /><c r="I472" s="2" t="inlineStr" /><c r="J472" s="2" t="inlineStr" /><c r="K472" s="2" t="inlineStr"><is><t>w celu przyspieszania zrostu kości po złamaniach</t></is></c><c r="L472" s="2" t="inlineStr"><is><t>przeciwbólowo w chorobie zwyrodnieniowej stawów</t></is></c><c r="M472" s="2" t="inlineStr" /><c r="N472" s="2" t="inlineStr" /><c r="O472" s="2" t="inlineStr" /><c r="P472" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2019/20 - 1 termin</t></is></c><c r="Q472" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="473"><c r="A473" s="2" t="inlineStr"><is><t>STANY NAGŁE</t></is></c><c r="B473" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C473" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D473" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E473" s="2" t="inlineStr"><is><t>20% roztwór albumin to:</t></is></c><c r="F473" s="2" t="inlineStr"><is><t>lek krwiopochodny</t></is></c><c r="G473" s="2" t="inlineStr"><is><t>koloid zatrzymujący płyny w przestrzeni wewnątrznaczyniowej</t></is></c><c r="H473" s="2" t="inlineStr" /><c r="I473" s="2" t="inlineStr" /><c r="J473" s="2" t="inlineStr" /><c r="K473" s="2" t="inlineStr"><is><t>substancja do żywienia pozajelitowego</t></is></c><c r="L473" s="2" t="inlineStr"><is><t>łatwo dostępny i tani płyn do nawadniania</t></is></c><c r="M473" s="2" t="inlineStr" /><c r="N473" s="2" t="inlineStr" /><c r="O473" s="2" t="inlineStr" /><c r="P473" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2019/20 - 1 termin</t></is></c><c r="Q473" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="474"><c r="A474" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B474" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C474" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D474" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E474" s="2" t="inlineStr"><is><t>W leczeniu wymiotów indukowanych chemioterapią znajduje zastosowanie:</t></is></c><c r="F474" s="2" t="inlineStr"><is><t>Deksametazon</t></is></c><c r="G474" s="2" t="inlineStr"><is><t>Palonosetron</t></is></c><c r="H474" s="2" t="inlineStr"><is><t>metoklopramid</t></is></c><c r="I474" s="2" t="inlineStr" /><c r="J474" s="2" t="inlineStr" /><c r="K474" s="2" t="inlineStr"><is><t>Dimenhydrynat</t></is></c><c r="L474" s="2" t="inlineStr" /><c r="M474" s="2" t="inlineStr" /><c r="N474" s="2" t="inlineStr" /><c r="O474" s="2" t="inlineStr" /><c r="P474" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2019/20 - 1 termin</t></is></c><c r="Q474" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="475"><c r="A475" s="2" t="inlineStr"><is><t>LEKI PRZECIWPSYCHOTYCZNE</t></is></c><c r="B475" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C475" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D475" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E475" s="2" t="inlineStr"><is><t>Klozapina może być przyczyną:</t></is></c><c r="F475" s="2" t="inlineStr"><is><t>obniżenia progu drgawkowego</t></is></c><c r="G475" s="2" t="inlineStr"><is><t>przyrostu masy ciała</t></is></c><c r="H475" s="2" t="inlineStr"><is><t>agranulocytozy</t></is></c><c r="I475" s="2" t="inlineStr" /><c r="J475" s="2" t="inlineStr" /><c r="K475" s="2" t="inlineStr"><is><t>Hiperprolaktynemii</t></is></c><c r="L475" s="2" t="inlineStr" /><c r="M475" s="2" t="inlineStr" /><c r="N475" s="2" t="inlineStr" /><c r="O475" s="2" t="inlineStr" /><c r="P475" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2019/20 - 1 termin</t></is></c><c r="Q475" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="476"><c r="A476" s="2" t="inlineStr"><is><t>LEKI PRZECIWLĘKOWE</t></is></c><c r="B476" s="2" t="inlineStr"><is><t>Interakcje</t></is></c><c r="C476" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D476" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E476" s="2" t="inlineStr"><is><t>Wskaż prawidłowe skojarzenie lek – mechanizm działania:</t></is></c><c r="F476" s="2" t="inlineStr"><is><t>buspiron – agonista rec. 5HT1A</t></is></c><c r="G476" s="2" t="inlineStr"><is><t>diazepam – agonista rec. GABA-A</t></is></c><c r="H476" s="2" t="inlineStr" /><c r="I476" s="2" t="inlineStr" /><c r="J476" s="2" t="inlineStr" /><c r="K476" s="2" t="inlineStr"><is><t>zolpidem – agonista rec. H2</t></is></c><c r="L476" s="2" t="inlineStr"><is><t>mirtazapina – agonista rec. alfa2</t></is></c><c r="M476" s="2" t="inlineStr" /><c r="N476" s="2" t="inlineStr" /><c r="O476" s="2" t="inlineStr" /><c r="P476" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2019/20 - 1 termin</t></is></c><c r="Q476" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="477"><c r="A477" s="2" t="inlineStr"><is><t>NARKOTYCZNE LEKI PRZECIWBÓLOWE</t></is></c><c r="B477" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C477" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D477" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E477" s="2" t="inlineStr"><is><t>Benzodiazepiny są stosowane w:</t></is></c><c r="F477" s="2" t="inlineStr"><is><t>premedykacji</t></is></c><c r="G477" s="2" t="inlineStr"><is><t>terapii padaczki</t></is></c><c r="H477" s="2" t="inlineStr" /><c r="I477" s="2" t="inlineStr" /><c r="J477" s="2" t="inlineStr" /><c r="K477" s="2" t="inlineStr"><is><t>długotrwałej terapii bezsenności</t></is></c><c r="L477" s="2" t="inlineStr"><is><t>zespole abstynencyjnym u chorych uzależnionych od morfiny</t></is></c><c r="M477" s="2" t="inlineStr" /><c r="N477" s="2" t="inlineStr" /><c r="O477" s="2" t="inlineStr" /><c r="P477" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2019/20 - 1 termin</t></is></c><c r="Q477" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="478"><c r="A478" s="2" t="inlineStr"><is><t>NARKOTYCZNE LEKI PRZECIWBÓLOWE</t></is></c><c r="B478" s="2" t="inlineStr"><is><t>Interakcje</t></is></c><c r="C478" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D478" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E478" s="2" t="inlineStr"><is><t>Zespół serotoninowy może być wynikiem interakcji cytalopramu z:</t></is></c><c r="F478" s="2" t="inlineStr"><is><t>Tramadolem</t></is></c><c r="G478" s="2" t="inlineStr"><is><t>klomipraminą</t></is></c><c r="H478" s="2" t="inlineStr" /><c r="I478" s="2" t="inlineStr" /><c r="J478" s="2" t="inlineStr" /><c r="K478" s="2" t="inlineStr"><is><t>Oksazepamem</t></is></c><c r="L478" s="2" t="inlineStr"><is><t>Buprenorfiną</t></is></c><c r="M478" s="2" t="inlineStr" /><c r="N478" s="2" t="inlineStr" /><c r="O478" s="2" t="inlineStr" /><c r="P478" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2019/20 - 1 termin</t></is></c><c r="Q478" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="479"><c r="A479" s="2" t="inlineStr"><is><t>FARMAKOLOGIA OGÓLNA I EBM</t></is></c><c r="B479" s="2" t="inlineStr"><is><t>Przeciwwskazania</t></is></c><c r="C479" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D479" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E479" s="2" t="inlineStr"><is><t>Charakterystyka Produktu Leczniczego zawiera informacje o:</t></is></c><c r="F479" s="2" t="inlineStr"><is><t>przeciwwskazaniach do stosowania</t></is></c><c r="G479" s="2" t="inlineStr"><is><t>właściwościach farmakokinetycznych</t></is></c><c r="H479" s="2" t="inlineStr"><is><t>okresie ważności</t></is></c><c r="I479" s="2" t="inlineStr" /><c r="J479" s="2" t="inlineStr" /><c r="K479" s="2" t="inlineStr"><is><t>zakresie refundacji</t></is></c><c r="L479" s="2" t="inlineStr" /><c r="M479" s="2" t="inlineStr" /><c r="N479" s="2" t="inlineStr" /><c r="O479" s="2" t="inlineStr" /><c r="P479" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2019/20 - 1 termin</t></is></c><c r="Q479" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="480"><c r="A480" s="2" t="inlineStr"><is><t>FARMAKOKINETYKA</t></is></c><c r="B480" s="2" t="inlineStr"><is><t>Farmakokinetyka</t></is></c><c r="C480" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D480" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E480" s="2" t="inlineStr"><is><t>Przyczyną nieliniowego przebiegu procesów farmakokinetycznych może być:</t></is></c><c r="F480" s="2" t="inlineStr"><is><t>autoindukcja metabolizmu</t></is></c><c r="G480" s="2" t="inlineStr"><is><t>niedobór kosubstratów w procesie sprzęgania</t></is></c><c r="H480" s="2" t="inlineStr"><is><t>wysycenie transporterów</t></is></c><c r="I480" s="2" t="inlineStr" /><c r="J480" s="2" t="inlineStr" /><c r="K480" s="2" t="inlineStr"><is><t>wąski wskaźnik terapeutyczny leku</t></is></c><c r="L480" s="2" t="inlineStr" /><c r="M480" s="2" t="inlineStr" /><c r="N480" s="2" t="inlineStr" /><c r="O480" s="2" t="inlineStr" /><c r="P480" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2019/20 - 1 termin</t></is></c><c r="Q480" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="481"><c r="A481" s="2" t="inlineStr"><is><t>CUKRZYCA</t></is></c><c r="B481" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C481" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D481" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E481" s="2" t="inlineStr"><is><t>Insulina aspart:</t></is></c><c r="F481" s="2" t="inlineStr"><is><t>działa za pośrednictwem receptora błonowego</t></is></c><c r="G481" s="2" t="inlineStr"><is><t>może być podawana we wstrzyknięciu podskórnym</t></is></c><c r="H481" s="2" t="inlineStr" /><c r="I481" s="2" t="inlineStr" /><c r="J481" s="2" t="inlineStr" /><c r="K481" s="2" t="inlineStr"><is><t>jest stosowana wyłącznie w cukrzycy typu 1</t></is></c><c r="L481" s="2" t="inlineStr"><is><t>jest analogiem długodziałającym</t></is></c><c r="M481" s="2" t="inlineStr" /><c r="N481" s="2" t="inlineStr" /><c r="O481" s="2" t="inlineStr" /><c r="P481" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2019/20 - 1 termin</t></is></c><c r="Q481" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="482"><c r="A482" s="2" t="inlineStr"><is><t>STANY NAGŁE</t></is></c><c r="B482" s="2" t="inlineStr"><is><t>Farmakokinetyka</t></is></c><c r="C482" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D482" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E482" s="2" t="inlineStr"><is><t>Na proces dystrybucji leku może mieć wpływ:</t></is></c><c r="F482" s="2" t="inlineStr"><is><t>niewydolność krążenia</t></is></c><c r="G482" s="2" t="inlineStr"><is><t>Hipoalbuminemia</t></is></c><c r="H482" s="2" t="inlineStr" /><c r="I482" s="2" t="inlineStr" /><c r="J482" s="2" t="inlineStr" /><c r="K482" s="2" t="inlineStr"><is><t>obecność pokarmu w przypadku podania doustnego</t></is></c><c r="L482" s="2" t="inlineStr"><is><t>możliwość sprzęgania z kwasem glukuronowym</t></is></c><c r="M482" s="2" t="inlineStr" /><c r="N482" s="2" t="inlineStr" /><c r="O482" s="2" t="inlineStr" /><c r="P482" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2019/20 - 1 termin</t></is></c><c r="Q482" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="483"><c r="A483" s="2" t="inlineStr"><is><t>NIEWYDOLNOŚĆ SERCA</t></is></c><c r="B483" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C483" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D483" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E483" s="2" t="inlineStr"><is><t>Agonistą receptorów jest:</t></is></c><c r="F483" s="2" t="inlineStr"><is><t>tapentadol</t></is></c><c r="G483" s="2" t="inlineStr" /><c r="H483" s="2" t="inlineStr" /><c r="I483" s="2" t="inlineStr" /><c r="J483" s="2" t="inlineStr" /><c r="K483" s="2" t="inlineStr"><is><t>Sertralina</t></is></c><c r="L483" s="2" t="inlineStr"><is><t>Eplerenon</t></is></c><c r="M483" s="2" t="inlineStr"><is><t>Fenytoina</t></is></c><c r="N483" s="2" t="inlineStr" /><c r="O483" s="2" t="inlineStr" /><c r="P483" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2019/20 - 1 termin</t></is></c><c r="Q483" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="484"><c r="A484" s="2" t="inlineStr"><is><t>NADCIŚNIENIE TĘTNICZE</t></is></c><c r="B484" s="2" t="inlineStr"><is><t>Monitorowanie</t></is></c><c r="C484" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D484" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E484" s="2" t="inlineStr"><is><t>W trakcie długotrwałej terapii glikokortykosteroidami, wskazane jest monitorowanie:</t></is></c><c r="F484" s="2" t="inlineStr"><is><t>stężenia potasu we krwi</t></is></c><c r="G484" s="2" t="inlineStr"><is><t>ciśnienia tętniczego krwi</t></is></c><c r="H484" s="2" t="inlineStr"><is><t>ciśnienia wewnątrzgałkowego</t></is></c><c r="I484" s="2" t="inlineStr"><is><t>glikemii</t></is></c><c r="J484" s="2" t="inlineStr" /><c r="K484" s="2" t="inlineStr" /><c r="L484" s="2" t="inlineStr" /><c r="M484" s="2" t="inlineStr" /><c r="N484" s="2" t="inlineStr" /><c r="O484" s="2" t="inlineStr" /><c r="P484" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2019/20 - 1 termin</t></is></c><c r="Q484" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="485"><c r="A485" s="2" t="inlineStr"><is><t>CUKRZYCA</t></is></c><c r="B485" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C485" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D485" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E485" s="2" t="inlineStr"><is><t>Inhibitory kotransportera sodowo-glukozowego 2 (SGLT-2, flozyny):</t></is></c><c r="F485" s="2" t="inlineStr"><is><t>Mogą być stosowane łącznie z metforminą</t></is></c><c r="G485" s="2" t="inlineStr"><is><t>Mogą zwiększać diurezę</t></is></c><c r="H485" s="2" t="inlineStr"><is><t>Mają udowodnione korzystne działanie w zakresie ryzyka sercowo-naczyniowego</t></is></c><c r="I485" s="2" t="inlineStr" /><c r="J485" s="2" t="inlineStr" /><c r="K485" s="2" t="inlineStr"><is><t>Charakteryzują się wysokim ryzykiem wystąpienia hipoglikemii</t></is></c><c r="L485" s="2" t="inlineStr" /><c r="M485" s="2" t="inlineStr" /><c r="N485" s="2" t="inlineStr" /><c r="O485" s="2" t="inlineStr" /><c r="P485" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2019/20 - 1 termin</t></is></c><c r="Q485" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="486"><c r="A486" s="2" t="inlineStr"><is><t>LEKI IMMUNOSUPRESYJNE</t></is></c><c r="B486" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C486" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D486" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E486" s="2" t="inlineStr"><is><t>Przeciwciała monoklonalne znajdują zastosowanie w terapii:</t></is></c><c r="F486" s="2" t="inlineStr"><is><t>choroby Leśniowskiego i Crohna</t></is></c><c r="G486" s="2" t="inlineStr"><is><t>stwardnienia rozsianego</t></is></c><c r="H486" s="2" t="inlineStr"><is><t>reumatoidalnego zapalenia stawów</t></is></c><c r="I486" s="2" t="inlineStr" /><c r="J486" s="2" t="inlineStr" /><c r="K486" s="2" t="inlineStr"><is><t>mononukleozy</t></is></c><c r="L486" s="2" t="inlineStr" /><c r="M486" s="2" t="inlineStr" /><c r="N486" s="2" t="inlineStr" /><c r="O486" s="2" t="inlineStr" /><c r="P486" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2019/20 - 1 termin</t></is></c><c r="Q486" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="487"><c r="A487" s="2" t="inlineStr"><is><t>LEKI PRZECIWPSYCHOTYCZNE</t></is></c><c r="B487" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C487" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D487" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E487" s="2" t="inlineStr"><is><t>Zaburzenia rytmu serca mogą wystąpić w trakcie podawania:</t></is></c><c r="F487" s="2" t="inlineStr"><is><t>Amisulpirydu</t></is></c><c r="G487" s="2" t="inlineStr"><is><t>Ondansetronu</t></is></c><c r="H487" s="2" t="inlineStr"><is><t>Chlorpromazyny</t></is></c><c r="I487" s="2" t="inlineStr"><is><t>metadonu</t></is></c><c r="J487" s="2" t="inlineStr" /><c r="K487" s="2" t="inlineStr" /><c r="L487" s="2" t="inlineStr" /><c r="M487" s="2" t="inlineStr" /><c r="N487" s="2" t="inlineStr" /><c r="O487" s="2" t="inlineStr" /><c r="P487" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2019/20 - 1 termin</t></is></c><c r="Q487" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="488"><c r="A488" s="2" t="inlineStr"><is><t>LEKI ROŚLINNE I SUPLEMENTY</t></is></c><c r="B488" s="2" t="inlineStr"><is><t>Przeciwwskazania</t></is></c><c r="C488" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D488" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E488" s="2" t="inlineStr"><is><t>Wskaż prawidłowe stwierdzenie dotyczące terapii niedokrwistości z niedoboru żelaza:</t></is></c><c r="F488" s="2" t="inlineStr"><is><t>preferowana jest doustna suplementacja żelaza</t></is></c><c r="G488" s="2" t="inlineStr" /><c r="H488" s="2" t="inlineStr" /><c r="I488" s="2" t="inlineStr" /><c r="J488" s="2" t="inlineStr" /><c r="K488" s="2" t="inlineStr"><is><t>terapia trwa 2 tygodnie</t></is></c><c r="L488" s="2" t="inlineStr"><is><t>preparaty dożylne żelaza są przeciwwskazane u chorych z przewlekłą niewydolnością nerek</t></is></c><c r="M488" s="2" t="inlineStr"><is><t>tabletki z żelazem należy popijać herbatą</t></is></c><c r="N488" s="2" t="inlineStr" /><c r="O488" s="2" t="inlineStr" /><c r="P488" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2019/20 - 1 termin</t></is></c><c r="Q488" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="489"><c r="A489" s="2" t="inlineStr"><is><t>PADACZKA</t></is></c><c r="B489" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C489" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D489" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E489" s="2" t="inlineStr"><is><t>Działanie normotymizujące wykazują:</t></is></c><c r="F489" s="2" t="inlineStr"><is><t>kwas walproinowy</t></is></c><c r="G489" s="2" t="inlineStr"><is><t>Lamotrygina</t></is></c><c r="H489" s="2" t="inlineStr"><is><t>Olanzapina</t></is></c><c r="I489" s="2" t="inlineStr"><is><t>sole litu</t></is></c><c r="J489" s="2" t="inlineStr" /><c r="K489" s="2" t="inlineStr" /><c r="L489" s="2" t="inlineStr" /><c r="M489" s="2" t="inlineStr" /><c r="N489" s="2" t="inlineStr" /><c r="O489" s="2" t="inlineStr" /><c r="P489" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2019/20 - 1 termin</t></is></c><c r="Q489" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="490"><c r="A490" s="2" t="inlineStr"><is><t>NARKOTYCZNE LEKI PRZECIWBÓLOWE</t></is></c><c r="B490" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C490" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D490" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E490" s="2" t="inlineStr"><is><t>Wskaż prawidłowe stwierdzenie:</t></is></c><c r="F490" s="2" t="inlineStr"><is><t>buprenorfina może być stosowana w leczeniu substytucyjnym zamiast metadonu</t></is></c><c r="G490" s="2" t="inlineStr"><is><t>petydyna nie powinna być stosowana w okołoporodowym postępowaniu</t></is></c><c r="H490" s="2" t="inlineStr" /><c r="I490" s="2" t="inlineStr" /><c r="J490" s="2" t="inlineStr" /><c r="K490" s="2" t="inlineStr"><is><t>nalokson jest podawany dożylnie, z oksykodonem, w celu zapobiegania występowaniu zaparć poopioidowych</t></is></c><c r="L490" s="2" t="inlineStr"><is><t>fentanyl w plastrach jest stosowany w terapii pooperacyjnego bólu ostrego</t></is></c><c r="M490" s="2" t="inlineStr" /><c r="N490" s="2" t="inlineStr" /><c r="O490" s="2" t="inlineStr" /><c r="P490" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2019/20 - 1 termin</t></is></c><c r="Q490" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="491"><c r="A491" s="2" t="inlineStr"><is><t>LEKI PRZECIWNOWOTWOROWE</t></is></c><c r="B491" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C491" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D491" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E491" s="2" t="inlineStr"><is><t>Udowodnione działanie immunostymulujące wykazuje:</t></is></c><c r="F491" s="2" t="inlineStr"><is><t>filgrastym</t></is></c><c r="G491" s="2" t="inlineStr" /><c r="H491" s="2" t="inlineStr" /><c r="I491" s="2" t="inlineStr" /><c r="J491" s="2" t="inlineStr" /><c r="K491" s="2" t="inlineStr"><is><t>wyciąg z korzenia jeżówki purpurowej</t></is></c><c r="L491" s="2" t="inlineStr"><is><t>pranobeks inozyny</t></is></c><c r="M491" s="2" t="inlineStr"><is><t>alkoholowy wyciąg z dziurawca</t></is></c><c r="N491" s="2" t="inlineStr" /><c r="O491" s="2" t="inlineStr" /><c r="P491" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2019/20 - 1 termin</t></is></c><c r="Q491" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="492"><c r="A492" s="2" t="inlineStr"><is><t>CHOROBA NIEDOKRWIENNA SERCA</t></is></c><c r="B492" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C492" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D492" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E492" s="2" t="inlineStr"><is><t>Ryzyka rozwoju zależności można się spodziewać przy stosowaniu:</t></is></c><c r="F492" s="2" t="inlineStr"><is><t>Dihydrokodeiny</t></is></c><c r="G492" s="2" t="inlineStr"><is><t>Diazepamu</t></is></c><c r="H492" s="2" t="inlineStr" /><c r="I492" s="2" t="inlineStr" /><c r="J492" s="2" t="inlineStr" /><c r="K492" s="2" t="inlineStr"><is><t>Diklofenaku</t></is></c><c r="L492" s="2" t="inlineStr"><is><t>duloksetyny</t></is></c><c r="M492" s="2" t="inlineStr" /><c r="N492" s="2" t="inlineStr" /><c r="O492" s="2" t="inlineStr" /><c r="P492" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2019/20 - 1 termin</t></is></c><c r="Q492" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="493"><c r="A493" s="2" t="inlineStr"><is><t>LEKI PRZECIWDEPRESYJNE</t></is></c><c r="B493" s="2" t="inlineStr"><is><t>Interakcje</t></is></c><c r="C493" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D493" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E493" s="2" t="inlineStr"><is><t>Wskaż prawidłowe skojarzenie lek przeciwdepresyjny – mechanizm działania:</t></is></c><c r="F493" s="2" t="inlineStr"><is><t>reboksetyna – selektywny inhibitor wychwytu zwrotnego noradrenaliny</t></is></c><c r="G493" s="2" t="inlineStr"><is><t>bupropion – inhibitor wychwytu zwrotnego noradrenaliny i dopaminy</t></is></c><c r="H493" s="2" t="inlineStr"><is><t>fluoksetyna – selektywny inhibitor wychwytu zwrotnego serotoniny</t></is></c><c r="I493" s="2" t="inlineStr"><is><t>wenlafaksyna – inhibitor wychwytu zwrotnego serotoniny i noradrenaliny</t></is></c><c r="J493" s="2" t="inlineStr" /><c r="K493" s="2" t="inlineStr" /><c r="L493" s="2" t="inlineStr" /><c r="M493" s="2" t="inlineStr" /><c r="N493" s="2" t="inlineStr" /><c r="O493" s="2" t="inlineStr" /><c r="P493" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2019/20 - 1 termin</t></is></c><c r="Q493" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="494"><c r="A494" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B494" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C494" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D494" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E494" s="2" t="inlineStr"><is><t>Ryzyko gastrotoksycznego działania ketoprofenu może istotnie wzrosnąć przy jednoczesnym podawaniu:</t></is></c><c r="F494" s="2" t="inlineStr"><is><t>Spironolaktonu</t></is></c><c r="G494" s="2" t="inlineStr"><is><t>prednizonu</t></is></c><c r="H494" s="2" t="inlineStr" /><c r="I494" s="2" t="inlineStr" /><c r="J494" s="2" t="inlineStr" /><c r="K494" s="2" t="inlineStr"><is><t>Mizoprostolu</t></is></c><c r="L494" s="2" t="inlineStr"><is><t>Omeprazolu</t></is></c><c r="M494" s="2" t="inlineStr" /><c r="N494" s="2" t="inlineStr" /><c r="O494" s="2" t="inlineStr" /><c r="P494" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2019/20 - 1 termin</t></is></c><c r="Q494" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="495"><c r="A495" s="2" t="inlineStr"><is><t>LEKI MOCZOPĘDNE</t></is></c><c r="B495" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C495" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D495" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E495" s="2" t="inlineStr"><is><t>Morfina może być przyczyną:</t></is></c><c r="F495" s="2" t="inlineStr"><is><t>obniżenia progu drgawkowego</t></is></c><c r="G495" s="2" t="inlineStr"><is><t>skurczu oskrzeli</t></is></c><c r="H495" s="2" t="inlineStr" /><c r="I495" s="2" t="inlineStr" /><c r="J495" s="2" t="inlineStr" /><c r="K495" s="2" t="inlineStr"><is><t>rozszerzenia źrenic</t></is></c><c r="L495" s="2" t="inlineStr"><is><t>działania moczopędnego</t></is></c><c r="M495" s="2" t="inlineStr" /><c r="N495" s="2" t="inlineStr" /><c r="O495" s="2" t="inlineStr" /><c r="P495" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2019/20 - 1 termin</t></is></c><c r="Q495" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="496"><c r="A496" s="2" t="inlineStr"><is><t>LEKI ROŚLINNE I SUPLEMENTY</t></is></c><c r="B496" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C496" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D496" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E496" s="2" t="inlineStr"><is><t>Wskaż fałszywe stwierdzenie:</t></is></c><c r="F496" s="2" t="inlineStr"><is><t>suplement diety to lek stosowany wspomagająco</t></is></c><c r="G496" s="2" t="inlineStr" /><c r="H496" s="2" t="inlineStr" /><c r="I496" s="2" t="inlineStr" /><c r="J496" s="2" t="inlineStr" /><c r="K496" s="2" t="inlineStr"><is><t>produkt leczniczy to substancja, której przypisuje się, między innymi, właściwości zapobiegania chorobom występującym u ludzi</t></is></c><c r="L496" s="2" t="inlineStr"><is><t>wyrób medyczny to przyrząd lub inny artykuł stosowany w celu diagnozowania, zapobiegania, monitorowania, leczenia lub łagodzenia przebiegu chorób</t></is></c><c r="M496" s="2" t="inlineStr"><is><t>roztwór albumin należy do kategorii produktów krwiopochodnych</t></is></c><c r="N496" s="2" t="inlineStr" /><c r="O496" s="2" t="inlineStr" /><c r="P496" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2019/20 - 2 termin</t></is></c><c r="Q496" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="497"><c r="A497" s="2" t="inlineStr"><is><t>CUKRZYCA</t></is></c><c r="B497" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C497" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D497" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E497" s="2" t="inlineStr"><is><t>Wskaż prawdziwe stwierdzenie:</t></is></c><c r="F497" s="2" t="inlineStr"><is><t>gliklazyd może powodować przyrost masy ciała</t></is></c><c r="G497" s="2" t="inlineStr"><is><t>metformina może być przyczyną kwasicy mleczanowej</t></is></c><c r="H497" s="2" t="inlineStr"><is><t>empagliflozyna zwiększa ryzyko zakażeń w obrębie miednicy mniejszej</t></is></c><c r="I497" s="2" t="inlineStr" /><c r="J497" s="2" t="inlineStr" /><c r="K497" s="2" t="inlineStr"><is><t>liraglutyd wykazuje niekorzystny efekt sercowo-naczyniowy</t></is></c><c r="L497" s="2" t="inlineStr" /><c r="M497" s="2" t="inlineStr" /><c r="N497" s="2" t="inlineStr" /><c r="O497" s="2" t="inlineStr" /><c r="P497" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2019/20 - 2 termin</t></is></c><c r="Q497" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="498"><c r="A498" s="2" t="inlineStr"><is><t>NARKOTYCZNE LEKI PRZECIWBÓLOWE</t></is></c><c r="B498" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C498" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D498" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E498" s="2" t="inlineStr"><is><t>Nalokson:</t></is></c><c r="F498" s="2" t="inlineStr"><is><t>słabo wchłania się z przewodu pokarmowego</t></is></c><c r="G498" s="2" t="inlineStr"><is><t>nie wywołuje uzależnienia</t></is></c><c r="H498" s="2" t="inlineStr" /><c r="I498" s="2" t="inlineStr" /><c r="J498" s="2" t="inlineStr" /><c r="K498" s="2" t="inlineStr"><is><t>jest agonistą receptorów opioidowych</t></is></c><c r="L498" s="2" t="inlineStr"><is><t>powoduje depresję ośrodka oddechowego</t></is></c><c r="M498" s="2" t="inlineStr" /><c r="N498" s="2" t="inlineStr" /><c r="O498" s="2" t="inlineStr" /><c r="P498" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2019/20 - 2 termin</t></is></c><c r="Q498" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="499"><c r="A499" s="2" t="inlineStr"><is><t>LEKI PRZECIWLĘKOWE</t></is></c><c r="B499" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C499" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D499" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E499" s="2" t="inlineStr"><is><t>Antagonizm wobec receptora stanowi zasadniczy mechanizm działania:</t></is></c><c r="F499" s="2" t="inlineStr"><is><t>flumazenilu</t></is></c><c r="G499" s="2" t="inlineStr" /><c r="H499" s="2" t="inlineStr" /><c r="I499" s="2" t="inlineStr" /><c r="J499" s="2" t="inlineStr" /><c r="K499" s="2" t="inlineStr"><is><t>Cyklosporyny</t></is></c><c r="L499" s="2" t="inlineStr"><is><t>Lorazepamu</t></is></c><c r="M499" s="2" t="inlineStr"><is><t>Tapentadolu</t></is></c><c r="N499" s="2" t="inlineStr" /><c r="O499" s="2" t="inlineStr" /><c r="P499" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2019/20 - 2 termin</t></is></c><c r="Q499" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="500"><c r="A500" s="2" t="inlineStr"><is><t>CUKRZYCA</t></is></c><c r="B500" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C500" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D500" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E500" s="2" t="inlineStr"><is><t>Zmniejszenie masy ciała może wiązać się z terapią:</t></is></c><c r="F500" s="2" t="inlineStr"><is><t>Lewotyroksyną</t></is></c><c r="G500" s="2" t="inlineStr"><is><t>metforminą</t></is></c><c r="H500" s="2" t="inlineStr" /><c r="I500" s="2" t="inlineStr" /><c r="J500" s="2" t="inlineStr" /><c r="K500" s="2" t="inlineStr"><is><t>Olanzapiną</t></is></c><c r="L500" s="2" t="inlineStr"><is><t>Prednizonem</t></is></c><c r="M500" s="2" t="inlineStr" /><c r="N500" s="2" t="inlineStr" /><c r="O500" s="2" t="inlineStr" /><c r="P500" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2019/20 - 2 termin</t></is></c><c r="Q500" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="501"><c r="A501" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B501" s="2" t="inlineStr"><is><t>Interakcje</t></is></c><c r="C501" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D501" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E501" s="2" t="inlineStr"><is><t>Wskaż prawidłowe skojarzenie lek – działanie niepożądane:</t></is></c><c r="F501" s="2" t="inlineStr"><is><t>tietylperazyna - akatyzja</t></is></c><c r="G501" s="2" t="inlineStr"><is><t>metoklopramid – późne dyskinezy</t></is></c><c r="H501" s="2" t="inlineStr"><is><t>ondansetron – wydłużenie odstępu QT</t></is></c><c r="I501" s="2" t="inlineStr" /><c r="J501" s="2" t="inlineStr" /><c r="K501" s="2" t="inlineStr"><is><t>dimenhydrynat - wymioty</t></is></c><c r="L501" s="2" t="inlineStr" /><c r="M501" s="2" t="inlineStr" /><c r="N501" s="2" t="inlineStr" /><c r="O501" s="2" t="inlineStr" /><c r="P501" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2019/20 - 2 termin</t></is></c><c r="Q501" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="502"><c r="A502" s="2" t="inlineStr"><is><t>FARMAKOKINETYKA</t></is></c><c r="B502" s="2" t="inlineStr"><is><t>Interakcje</t></is></c><c r="C502" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D502" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E502" s="2" t="inlineStr"><is><t>Charakterystyka Produktu Leczniczego zawiera informacje o:</t></is></c><c r="F502" s="2" t="inlineStr"><is><t>mechanizmie działania</t></is></c><c r="G502" s="2" t="inlineStr"><is><t>interakcjach</t></is></c><c r="H502" s="2" t="inlineStr"><is><t>substancjach pomocniczych</t></is></c><c r="I502" s="2" t="inlineStr"><is><t>działaniach niepożądanych</t></is></c><c r="J502" s="2" t="inlineStr" /><c r="K502" s="2" t="inlineStr" /><c r="L502" s="2" t="inlineStr" /><c r="M502" s="2" t="inlineStr" /><c r="N502" s="2" t="inlineStr" /><c r="O502" s="2" t="inlineStr" /><c r="P502" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2019/20 - 2 termin</t></is></c><c r="Q502" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="503"><c r="A503" s="2" t="inlineStr"><is><t>LEKI PRZECIWPSYCHOTYCZNE</t></is></c><c r="B503" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C503" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D503" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E503" s="2" t="inlineStr"><is><t>Kwetiapina:</t></is></c><c r="F503" s="2" t="inlineStr"><is><t>wpływa na przekaźnictwo serotoninergiczne</t></is></c><c r="G503" s="2" t="inlineStr"><is><t>może być przyczyną zwiększenia masy ciała</t></is></c><c r="H503" s="2" t="inlineStr"><is><t>jest preferowana u pacjentów z współistniejącą chorobą Parkinsona</t></is></c><c r="I503" s="2" t="inlineStr"><is><t>reprezentuje neuroleptyki atypowe</t></is></c><c r="J503" s="2" t="inlineStr" /><c r="K503" s="2" t="inlineStr" /><c r="L503" s="2" t="inlineStr" /><c r="M503" s="2" t="inlineStr" /><c r="N503" s="2" t="inlineStr" /><c r="O503" s="2" t="inlineStr" /><c r="P503" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2019/20 - 2 termin</t></is></c><c r="Q503" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="504"><c r="A504" s="2" t="inlineStr"><is><t>LEKI PRZECIWDEPRESYJNE</t></is></c><c r="B504" s="2" t="inlineStr"><is><t>Struktura chemiczna</t></is></c><c r="C504" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D504" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E504" s="2" t="inlineStr"><is><t>Trójpierścieniowe leki przeciwdepresyjne:</t></is></c><c r="F504" s="2" t="inlineStr"><is><t>blokują receptory histaminowe</t></is></c><c r="G504" s="2" t="inlineStr"><is><t>hamują wychwyt zwrotny dopaminy</t></is></c><c r="H504" s="2" t="inlineStr" /><c r="I504" s="2" t="inlineStr" /><c r="J504" s="2" t="inlineStr" /><c r="K504" s="2" t="inlineStr"><is><t>pobudzają receptory muskarynowe</t></is></c><c r="L504" s="2" t="inlineStr"><is><t>nie wpływają na przekaźnictwo serotoninergiczne</t></is></c><c r="M504" s="2" t="inlineStr" /><c r="N504" s="2" t="inlineStr" /><c r="O504" s="2" t="inlineStr" /><c r="P504" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2019/20 - 2 termin</t></is></c><c r="Q504" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="505"><c r="A505" s="2" t="inlineStr"><is><t>FARMAKOKINETYKA</t></is></c><c r="B505" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C505" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D505" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E505" s="2" t="inlineStr"><is><t>Na dostępność biologiczną leku może mieć wpływ:</t></is></c><c r="F505" s="2" t="inlineStr"><is><t>stopień uwalniania substancji czynnej</t></is></c><c r="G505" s="2" t="inlineStr"><is><t>efekt I przejścia</t></is></c><c r="H505" s="2" t="inlineStr"><is><t>szybkość transportu substancji czynnej przez błony biologiczne</t></is></c><c r="I505" s="2" t="inlineStr" /><c r="J505" s="2" t="inlineStr" /><c r="K505" s="2" t="inlineStr"><is><t>stopień wiązania z białkami krwi</t></is></c><c r="L505" s="2" t="inlineStr" /><c r="M505" s="2" t="inlineStr" /><c r="N505" s="2" t="inlineStr" /><c r="O505" s="2" t="inlineStr" /><c r="P505" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2019/20 - 2 termin</t></is></c><c r="Q505" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="506"><c r="A506" s="2" t="inlineStr"><is><t>FARMAKOKINETYKA</t></is></c><c r="B506" s="2" t="inlineStr"><is><t>Farmakokinetyka</t></is></c><c r="C506" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D506" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E506" s="2" t="inlineStr"><is><t>Stan stacjonarny leku ustala się:</t></is></c><c r="F506" s="2" t="inlineStr"><is><t>po okresie równym około 4–5 T1/2</t></is></c><c r="G506" s="2" t="inlineStr" /><c r="H506" s="2" t="inlineStr" /><c r="I506" s="2" t="inlineStr" /><c r="J506" s="2" t="inlineStr" /><c r="K506" s="2" t="inlineStr"><is><t>w momencie, który zależy od dawki leku</t></is></c><c r="L506" s="2" t="inlineStr"><is><t>jedynie w wyniku wielokrotnego podania doustnego</t></is></c><c r="M506" s="2" t="inlineStr"><is><t>w czasie wprost proporcjonalnym do klirensu leku</t></is></c><c r="N506" s="2" t="inlineStr" /><c r="O506" s="2" t="inlineStr" /><c r="P506" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2019/20 - 2 termin</t></is></c><c r="Q506" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="507"><c r="A507" s="2" t="inlineStr"><is><t>FARMAKOKINETYKA</t></is></c><c r="B507" s="2" t="inlineStr"><is><t>Farmakokinetyka</t></is></c><c r="C507" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D507" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E507" s="2" t="inlineStr"><is><t>Biologiczny okres półtrwania (T1/2):</t></is></c><c r="F507" s="2" t="inlineStr"><is><t>zależy od objętości dystrybucji</t></is></c><c r="G507" s="2" t="inlineStr"><is><t>jest odwrotnie proporcjonalny do klirensu całkowitego</t></is></c><c r="H507" s="2" t="inlineStr"><is><t>ma wpływ na moment osiągnięcia stanu stacjonarnego</t></is></c><c r="I507" s="2" t="inlineStr" /><c r="J507" s="2" t="inlineStr" /><c r="K507" s="2" t="inlineStr"><is><t>zależy od szybkości wchłaniania</t></is></c><c r="L507" s="2" t="inlineStr" /><c r="M507" s="2" t="inlineStr" /><c r="N507" s="2" t="inlineStr" /><c r="O507" s="2" t="inlineStr" /><c r="P507" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2019/20 - 2 termin</t></is></c><c r="Q507" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="508"><c r="A508" s="2" t="inlineStr"><is><t>NARKOTYCZNE LEKI PRZECIWBÓLOWE</t></is></c><c r="B508" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C508" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D508" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E508" s="2" t="inlineStr"><is><t>Wskaż prawidłowe stwierdzenie:</t></is></c><c r="F508" s="2" t="inlineStr"><is><t>tramadol jest inhibitorem wychwytu zwrotnego serotoniny</t></is></c><c r="G508" s="2" t="inlineStr"><is><t>petydyna jest metabolizowana do neurotoksycznego metabolitu</t></is></c><c r="H508" s="2" t="inlineStr" /><c r="I508" s="2" t="inlineStr" /><c r="J508" s="2" t="inlineStr" /><c r="K508" s="2" t="inlineStr"><is><t>buprenorfinę charakteryzuje wysoki potencjał uzależniający</t></is></c><c r="L508" s="2" t="inlineStr"><is><t>fentanyl w plastrach jest stosowany w leczeniu pooperacyjnego bólu ostrego</t></is></c><c r="M508" s="2" t="inlineStr" /><c r="N508" s="2" t="inlineStr" /><c r="O508" s="2" t="inlineStr" /><c r="P508" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2019/20 - 2 termin</t></is></c><c r="Q508" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="509"><c r="A509" s="2" t="inlineStr"><is><t>NADCIŚNIENIE TĘTNICZE</t></is></c><c r="B509" s="2" t="inlineStr"><is><t>Antidotum</t></is></c><c r="C509" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D509" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E509" s="2" t="inlineStr"><is><t>Do typowych objawów zatrucia opioidami należą:</t></is></c><c r="F509" s="2" t="inlineStr"><is><t>Śpiączka</t></is></c><c r="G509" s="2" t="inlineStr"><is><t>Depresja oddechowa</t></is></c><c r="H509" s="2" t="inlineStr" /><c r="I509" s="2" t="inlineStr" /><c r="J509" s="2" t="inlineStr" /><c r="K509" s="2" t="inlineStr"><is><t>Wzrost ciśnienia tętniczego</t></is></c><c r="L509" s="2" t="inlineStr"><is><t>wzrost temperatury ciała</t></is></c><c r="M509" s="2" t="inlineStr" /><c r="N509" s="2" t="inlineStr" /><c r="O509" s="2" t="inlineStr" /><c r="P509" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2019/20 - 2 termin</t></is></c><c r="Q509" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="510"><c r="A510" s="2" t="inlineStr"><is><t>CUKRZYCA</t></is></c><c r="B510" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C510" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D510" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E510" s="2" t="inlineStr"><is><t>Wskaż prawidłowe stwierdzenie dotyczące glikokortykosteroidów:</t></is></c><c r="F510" s="2" t="inlineStr"><is><t>Działają za pośrednictwem receptorów wewnątrzkomórkowych</t></is></c><c r="G510" s="2" t="inlineStr"><is><t>mechanizm niegenomowy odpowiedzialny jest za ich działanie rozkurczające mięśniówkę dróg oddechowych</t></is></c><c r="H510" s="2" t="inlineStr"><is><t>Nagłe ich odstawienie po co najmniej tygodniowym zastosowaniu dawek farmakologicznych może być przyczyną ostrej niewydolności kory nadnerczy</t></is></c><c r="I510" s="2" t="inlineStr" /><c r="J510" s="2" t="inlineStr" /><c r="K510" s="2" t="inlineStr"><is><t>Powodują zmniejszenie zapotrzebowania na insulinę u chorych na cukrzycę</t></is></c><c r="L510" s="2" t="inlineStr" /><c r="M510" s="2" t="inlineStr" /><c r="N510" s="2" t="inlineStr" /><c r="O510" s="2" t="inlineStr" /><c r="P510" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2019/20 - 2 termin</t></is></c><c r="Q510" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="511"><c r="A511" s="2" t="inlineStr"><is><t>CUKRZYCA</t></is></c><c r="B511" s="2" t="inlineStr"><is><t>Sposób podania</t></is></c><c r="C511" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D511" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E511" s="2" t="inlineStr"><is><t>Insulina ludzka neutralna:</t></is></c><c r="F511" s="2" t="inlineStr"><is><t>działa za pośrednictwem receptora błonowego</t></is></c><c r="G511" s="2" t="inlineStr"><is><t>jest otrzymywana metodą rekombinacji DNA</t></is></c><c r="H511" s="2" t="inlineStr" /><c r="I511" s="2" t="inlineStr" /><c r="J511" s="2" t="inlineStr" /><c r="K511" s="2" t="inlineStr"><is><t>może być podawana doustnie</t></is></c><c r="L511" s="2" t="inlineStr"><is><t>jest analogiem długodziałającym</t></is></c><c r="M511" s="2" t="inlineStr" /><c r="N511" s="2" t="inlineStr" /><c r="O511" s="2" t="inlineStr" /><c r="P511" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2019/20 - 2 termin</t></is></c><c r="Q511" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="512"><c r="A512" s="2" t="inlineStr"><is><t>LEKI PRZECIWNOWOTWOROWE</t></is></c><c r="B512" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C512" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D512" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E512" s="2" t="inlineStr"><is><t>Wskaż prawdziwe połączenie lek – wskazanie:</t></is></c><c r="F512" s="2" t="inlineStr"><is><t>zolpidem-bezsenność</t></is></c><c r="G512" s="2" t="inlineStr"><is><t>ondansetron – wymioty w przebiegu chemioterapii przeciwnowotworowej</t></is></c><c r="H512" s="2" t="inlineStr"><is><t>alprazolam-napady paniki</t></is></c><c r="I512" s="2" t="inlineStr"><is><t>fluoksetyna–epizody dużej depresji</t></is></c><c r="J512" s="2" t="inlineStr" /><c r="K512" s="2" t="inlineStr" /><c r="L512" s="2" t="inlineStr" /><c r="M512" s="2" t="inlineStr" /><c r="N512" s="2" t="inlineStr" /><c r="O512" s="2" t="inlineStr" /><c r="P512" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2019/20 - 2 termin</t></is></c><c r="Q512" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="513"><c r="A513" s="2" t="inlineStr"><is><t>NADCIŚNIENIE TĘTNICZE</t></is></c><c r="B513" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C513" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D513" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E513" s="2" t="inlineStr"><is><t>Stosowanie estrogenów może być przyczyną:</t></is></c><c r="F513" s="2" t="inlineStr"><is><t>wzrostu ciśnienia tętniczego krwi</t></is></c><c r="G513" s="2" t="inlineStr"><is><t>kamicy żółciowej</t></is></c><c r="H513" s="2" t="inlineStr"><is><t>wzrostu ryzyka wystąpienia raka piersi</t></is></c><c r="I513" s="2" t="inlineStr"><is><t>zatorowości płucnej</t></is></c><c r="J513" s="2" t="inlineStr" /><c r="K513" s="2" t="inlineStr" /><c r="L513" s="2" t="inlineStr" /><c r="M513" s="2" t="inlineStr" /><c r="N513" s="2" t="inlineStr" /><c r="O513" s="2" t="inlineStr" /><c r="P513" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2019/20 - 2 termin</t></is></c><c r="Q513" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="514"><c r="A514" s="2" t="inlineStr"><is><t>NIEOPIOIDOWE LEKI PRZECIWBÓLOWE</t></is></c><c r="B514" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C514" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D514" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E514" s="2" t="inlineStr"><is><t>Kwas acetylosalicylowy:</t></is></c><c r="F514" s="2" t="inlineStr"><is><t>może być przyczyną wystąpienia szczególnej postaci astmy</t></is></c><c r="G514" s="2" t="inlineStr"><is><t>nieodwracalnie hamuje COX</t></is></c><c r="H514" s="2" t="inlineStr" /><c r="I514" s="2" t="inlineStr" /><c r="J514" s="2" t="inlineStr" /><c r="K514" s="2" t="inlineStr"><is><t>zwiększa ryzyko sercowo-naczyniowe</t></is></c><c r="L514" s="2" t="inlineStr"><is><t>podawany łącznie z ibuprofenem wykazuje silniejszy efekt przeciwzapalny</t></is></c><c r="M514" s="2" t="inlineStr" /><c r="N514" s="2" t="inlineStr" /><c r="O514" s="2" t="inlineStr" /><c r="P514" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2019/20 - 2 termin</t></is></c><c r="Q514" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="515"><c r="A515" s="2" t="inlineStr"><is><t>NIEOPIOIDOWE LEKI PRZECIWBÓLOWE</t></is></c><c r="B515" s="2" t="inlineStr"><is><t>Ciąża</t></is></c><c r="C515" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D515" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E515" s="2" t="inlineStr"><is><t>Paracetamol:</t></is></c><c r="F515" s="2" t="inlineStr"><is><t>u chorych przewlekle niedożywionych może działać hepatotoksycznie</t></is></c><c r="G515" s="2" t="inlineStr" /><c r="H515" s="2" t="inlineStr" /><c r="I515" s="2" t="inlineStr" /><c r="J515" s="2" t="inlineStr" /><c r="K515" s="2" t="inlineStr"><is><t>działa przeciwbólowo i przeciwzapalnie</t></is></c><c r="L515" s="2" t="inlineStr"><is><t>zwiększa ryzyko sercowo-naczyniowe</t></is></c><c r="M515" s="2" t="inlineStr"><is><t>wykazuje działanie teratogenne</t></is></c><c r="N515" s="2" t="inlineStr" /><c r="O515" s="2" t="inlineStr" /><c r="P515" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2019/20 - 2 termin</t></is></c><c r="Q515" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="516"><c r="A516" s="2" t="inlineStr"><is><t>NIEOPIOIDOWE LEKI PRZECIWBÓLOWE</t></is></c><c r="B516" s="2" t="inlineStr"><is><t>Ciąża</t></is></c><c r="C516" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D516" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E516" s="2" t="inlineStr"><is><t>Metamizol:</t></is></c><c r="F516" s="2" t="inlineStr"><is><t>działa przeciwbólowo i przeciwgorączkowo</t></is></c><c r="G516" s="2" t="inlineStr"><is><t>działa spazmolitycznie</t></is></c><c r="H516" s="2" t="inlineStr"><is><t>może być przyczyną agranulocytozy</t></is></c><c r="I516" s="2" t="inlineStr" /><c r="J516" s="2" t="inlineStr" /><c r="K516" s="2" t="inlineStr"><is><t>może być bezpiecznie stosowany w ciąży</t></is></c><c r="L516" s="2" t="inlineStr" /><c r="M516" s="2" t="inlineStr" /><c r="N516" s="2" t="inlineStr" /><c r="O516" s="2" t="inlineStr" /><c r="P516" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2019/20 - 2 termin</t></is></c><c r="Q516" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="517"><c r="A517" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B517" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C517" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D517" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E517" s="2" t="inlineStr"><is><t>Do leków biotechnologicznych należą:</t></is></c><c r="F517" s="2" t="inlineStr"><is><t>szczepionki</t></is></c><c r="G517" s="2" t="inlineStr"><is><t>przeciwciała monoklonalne</t></is></c><c r="H517" s="2" t="inlineStr"><is><t>Hormony</t></is></c><c r="I517" s="2" t="inlineStr"><is><t>czynniki krzepnięcia</t></is></c><c r="J517" s="2" t="inlineStr" /><c r="K517" s="2" t="inlineStr" /><c r="L517" s="2" t="inlineStr" /><c r="M517" s="2" t="inlineStr" /><c r="N517" s="2" t="inlineStr" /><c r="O517" s="2" t="inlineStr" /><c r="P517" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2019/20 - 2 termin</t></is></c><c r="Q517" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="518"><c r="A518" s="2" t="inlineStr"><is><t>LEKI PRZECIWDEPRESYJNE</t></is></c><c r="B518" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C518" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D518" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E518" s="2" t="inlineStr"><is><t>Wskaż prawidłowe stwierdzenie:</t></is></c><c r="F518" s="2" t="inlineStr"><is><t>amitryptylina znajduje zastosowanie w terapii bólu neuropatycznego</t></is></c><c r="G518" s="2" t="inlineStr"><is><t>escitalopram hamuje wychwyt zwrotny serotoniny</t></is></c><c r="H518" s="2" t="inlineStr"><is><t>moklobemid może być niebezpieczny u pacjentów spożywających sery dojrzewające</t></is></c><c r="I518" s="2" t="inlineStr"><is><t>mianseryna jest przeciwskazana u osób z padaczką</t></is></c><c r="J518" s="2" t="inlineStr" /><c r="K518" s="2" t="inlineStr" /><c r="L518" s="2" t="inlineStr" /><c r="M518" s="2" t="inlineStr" /><c r="N518" s="2" t="inlineStr" /><c r="O518" s="2" t="inlineStr" /><c r="P518" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2019/20 - 2 termin</t></is></c><c r="Q518" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="519"><c r="A519" s="2" t="inlineStr"><is><t>LEKI ROŚLINNE I SUPLEMENTY</t></is></c><c r="B519" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C519" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D519" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E519" s="2" t="inlineStr"><is><t>Doustne preparaty żelaza:</t></is></c><c r="F519" s="2" t="inlineStr"><is><t>najlepiej przyswajalne zawierają żelazo dwuwartościowe</t></is></c><c r="G519" s="2" t="inlineStr"><is><t>należy przyjmować przez okres 3 miesięcy po uzyskaniu normalizacji morfologii</t></is></c><c r="H519" s="2" t="inlineStr" /><c r="I519" s="2" t="inlineStr" /><c r="J519" s="2" t="inlineStr" /><c r="K519" s="2" t="inlineStr"><is><t>należy przyjmować z posiłkiem wysokotłuszczowym</t></is></c><c r="L519" s="2" t="inlineStr"><is><t>mogą być przyczyną jasno-żółtego zabarwienia stolca</t></is></c><c r="M519" s="2" t="inlineStr" /><c r="N519" s="2" t="inlineStr" /><c r="O519" s="2" t="inlineStr" /><c r="P519" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2019/20 - 2 termin</t></is></c><c r="Q519" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="520"><c r="A520" s="2" t="inlineStr"><is><t>PADACZKA</t></is></c><c r="B520" s="2" t="inlineStr"><is><t>Farmakokinetyka</t></is></c><c r="C520" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D520" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E520" s="2" t="inlineStr"><is><t>Diazepam:</t></is></c><c r="F520" s="2" t="inlineStr"><is><t>działa sedatywnie</t></is></c><c r="G520" s="2" t="inlineStr"><is><t>działa powyżej 24 godzin</t></is></c><c r="H520" s="2" t="inlineStr" /><c r="I520" s="2" t="inlineStr" /><c r="J520" s="2" t="inlineStr" /><c r="K520" s="2" t="inlineStr"><is><t>obniża próg drgawkowy</t></is></c><c r="L520" s="2" t="inlineStr"><is><t>nie podlega metabolizmowi</t></is></c><c r="M520" s="2" t="inlineStr" /><c r="N520" s="2" t="inlineStr" /><c r="O520" s="2" t="inlineStr" /><c r="P520" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2019/20 - 2 termin</t></is></c><c r="Q520" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="521"><c r="A521" s="2" t="inlineStr"><is><t>PADACZKA</t></is></c><c r="B521" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C521" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D521" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E521" s="2" t="inlineStr"><is><t>Wskaż prawidłowe połączenie lek przeciwpadaczkowy – mechanizm działania: B</t></is></c><c r="F521" s="2" t="inlineStr"><is><t>fenytoina – hamowanie kanałów sodowych</t></is></c><c r="G521" s="2" t="inlineStr"><is><t>karbamazepina - hamowanie kanałów sodowych i kanałów wapniowych</t></is></c><c r="H521" s="2" t="inlineStr" /><c r="I521" s="2" t="inlineStr" /><c r="J521" s="2" t="inlineStr" /><c r="K521" s="2" t="inlineStr"><is><t>fenobarbital – hamowanie transmisji GABA-ergicznej</t></is></c><c r="L521" s="2" t="inlineStr"><is><t>kwas walproinowy – hamowanie kanałów sodowych i transmisji GABA-ergicznej</t></is></c><c r="M521" s="2" t="inlineStr" /><c r="N521" s="2" t="inlineStr" /><c r="O521" s="2" t="inlineStr" /><c r="P521" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2019/20 - 2 termin</t></is></c><c r="Q521" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="522"><c r="A522" s="2" t="inlineStr"><is><t>PADACZKA</t></is></c><c r="B522" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C522" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D522" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E522" s="2" t="inlineStr"><is><t>Selektywne inhibitory wychwytu zwrotnego serotoniny (SSRI) charakteryzuje:</t></is></c><c r="F522" s="2" t="inlineStr"><is><t>niewielki wpływ na układ krążenia</t></is></c><c r="G522" s="2" t="inlineStr"><is><t>małe ryzyko teratogenności</t></is></c><c r="H522" s="2" t="inlineStr" /><c r="I522" s="2" t="inlineStr" /><c r="J522" s="2" t="inlineStr" /><c r="K522" s="2" t="inlineStr"><is><t>obniżanie progu drgawkowego</t></is></c><c r="L522" s="2" t="inlineStr"><is><t>brak ryzyka wystąpienia istotnych interakcji z inhibitorami MAO</t></is></c><c r="M522" s="2" t="inlineStr" /><c r="N522" s="2" t="inlineStr" /><c r="O522" s="2" t="inlineStr" /><c r="P522" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2019/20 - 2 termin</t></is></c><c r="Q522" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="523"><c r="A523" s="2" t="inlineStr"><is><t>NARKOTYCZNE LEKI PRZECIWBÓLOWE</t></is></c><c r="B523" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C523" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D523" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E523" s="2" t="inlineStr"><is><t>Potencjał uzależniający wykazują:</t></is></c><c r="F523" s="2" t="inlineStr"><is><t>Kanabinoidy</t></is></c><c r="G523" s="2" t="inlineStr"><is><t>dysocjacyjne środki znieczulające</t></is></c><c r="H523" s="2" t="inlineStr"><is><t>Benzodiazepiny</t></is></c><c r="I523" s="2" t="inlineStr"><is><t>opioidy</t></is></c><c r="J523" s="2" t="inlineStr" /><c r="K523" s="2" t="inlineStr" /><c r="L523" s="2" t="inlineStr" /><c r="M523" s="2" t="inlineStr" /><c r="N523" s="2" t="inlineStr" /><c r="O523" s="2" t="inlineStr" /><c r="P523" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2019/20 - 2 termin</t></is></c><c r="Q523" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="524"><c r="A524" s="2" t="inlineStr"><is><t>LEKI IMMUNOSUPRESYJNE</t></is></c><c r="B524" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C524" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D524" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E524" s="2" t="inlineStr"><is><t>Działanie immunosupresyjne wykazują:</t></is></c><c r="F524" s="2" t="inlineStr"><is><t>inhibitory kalcyneuryny</t></is></c><c r="G524" s="2" t="inlineStr"><is><t>alkilujące inhibitory proliferacji</t></is></c><c r="H524" s="2" t="inlineStr" /><c r="I524" s="2" t="inlineStr" /><c r="J524" s="2" t="inlineStr" /><c r="K524" s="2" t="inlineStr"><is><t>czynniki stymulujące tworzenie kolonii granulocytów</t></is></c><c r="L524" s="2" t="inlineStr"><is><t>interferon beta</t></is></c><c r="M524" s="2" t="inlineStr" /><c r="N524" s="2" t="inlineStr" /><c r="O524" s="2" t="inlineStr" /><c r="P524" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2019/20 - 2 termin</t></is></c><c r="Q524" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="525"><c r="A525" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B525" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C525" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D525" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E525" s="2" t="inlineStr"><is><t>Hamowanie transmisji dopaminergicznej może być przyczyną wystąpienia:</t></is></c><c r="F525" s="2" t="inlineStr"><is><t>Dyskinez</t></is></c><c r="G525" s="2" t="inlineStr"><is><t>zwiększenia masy ciała</t></is></c><c r="H525" s="2" t="inlineStr"><is><t>działania przeciwwymiotnego</t></is></c><c r="I525" s="2" t="inlineStr" /><c r="J525" s="2" t="inlineStr" /><c r="K525" s="2" t="inlineStr"><is><t>hipoprolaktynemii</t></is></c><c r="L525" s="2" t="inlineStr" /><c r="M525" s="2" t="inlineStr" /><c r="N525" s="2" t="inlineStr" /><c r="O525" s="2" t="inlineStr" /><c r="P525" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2019/20 - 2 termin</t></is></c><c r="Q525" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="526"><c r="A526" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B526" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C526" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D526" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E526" s="2" t="inlineStr"><is><t>W przypadku rozpoznania anginy paciorkowcowej można zastosować:</t></is></c><c r="F526" s="2" t="inlineStr"><is><t>Klindamycynę</t></is></c><c r="G526" s="2" t="inlineStr"><is><t>Fenoksymetylopenicylinę</t></is></c><c r="H526" s="2" t="inlineStr" /><c r="I526" s="2" t="inlineStr" /><c r="J526" s="2" t="inlineStr" /><c r="K526" s="2" t="inlineStr"><is><t>Cyprofloksacynę</t></is></c><c r="L526" s="2" t="inlineStr"><is><t>Amikacynę</t></is></c><c r="M526" s="2" t="inlineStr" /><c r="N526" s="2" t="inlineStr" /><c r="O526" s="2" t="inlineStr" /><c r="P526" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2019/20 - 1 termin (online)</t></is></c><c r="Q526" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="527"><c r="A527" s="2" t="inlineStr"><is><t>LEKI PRZECIWWIRUSOWE</t></is></c><c r="B527" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C527" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D527" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E527" s="2" t="inlineStr"><is><t>Wskaż prawidłowe stwierdzenie:</t></is></c><c r="F527" s="2" t="inlineStr"><is><t>Replikacja wirusa może zostać wznowiona po odstawieniu leków, które hamują czynną replikację</t></is></c><c r="G527" s="2" t="inlineStr"><is><t>Obecnie stosowane leki wykazują aktywność wobec wirusów w fazie replikacji</t></is></c><c r="H527" s="2" t="inlineStr" /><c r="I527" s="2" t="inlineStr" /><c r="J527" s="2" t="inlineStr" /><c r="K527" s="2" t="inlineStr"><is><t>Niektóre leki działają na wirusy będące w fazie utajenia</t></is></c><c r="L527" s="2" t="inlineStr"><is><t>Większość wirusów opornych na lek pochodzi od pacjentów z prawidłową odpornością</t></is></c><c r="M527" s="2" t="inlineStr" /><c r="N527" s="2" t="inlineStr" /><c r="O527" s="2" t="inlineStr" /><c r="P527" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2019/20 - 1 termin (online)</t></is></c><c r="Q527" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="528"><c r="A528" s="2" t="inlineStr"><is><t>LEKI PRZECIWPASOŻYTNICZE</t></is></c><c r="B528" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C528" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D528" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E528" s="2" t="inlineStr"><is><t>Chlorochina:</t></is></c><c r="F528" s="2" t="inlineStr"><is><t>Może być przyczyną wypadania włosów</t></is></c><c r="G528" s="2" t="inlineStr"><is><t>Niszczy formy wewnątrzkrwinkowe pierwotniaka</t></is></c><c r="H528" s="2" t="inlineStr" /><c r="I528" s="2" t="inlineStr" /><c r="J528" s="2" t="inlineStr" /><c r="K528" s="2" t="inlineStr"><is><t>Jest stosowana w każdym schemacie profilaktyki malarii</t></is></c><c r="L528" s="2" t="inlineStr"><is><t>Jest szczególnie skuteczna w leczeniu zakażenia Plasmodium falciparium</t></is></c><c r="M528" s="2" t="inlineStr" /><c r="N528" s="2" t="inlineStr" /><c r="O528" s="2" t="inlineStr" /><c r="P528" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2019/20 - 1 termin (online)</t></is></c><c r="Q528" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="529"><c r="A529" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B529" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C529" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D529" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E529" s="2" t="inlineStr"><is><t>Lek bakteriobójczy, którego aktywność przeciwbakteryjną najlepiej charakteryzuje AUC24/MIC, działający na bakterie atypowe. Lek jest wydalany głównie z moczem i jego stosowanie związane jest z ryzykiem wydłużenia odstępu QT. Opis może dotyczyć:</t></is></c><c r="F529" s="2" t="inlineStr"><is><t>Lewofloksacyny</t></is></c><c r="G529" s="2" t="inlineStr" /><c r="H529" s="2" t="inlineStr" /><c r="I529" s="2" t="inlineStr" /><c r="J529" s="2" t="inlineStr" /><c r="K529" s="2" t="inlineStr"><is><t>Doksycyliny</t></is></c><c r="L529" s="2" t="inlineStr"><is><t>Klarytromycyny</t></is></c><c r="M529" s="2" t="inlineStr"><is><t>Linezolidu</t></is></c><c r="N529" s="2" t="inlineStr" /><c r="O529" s="2" t="inlineStr" /><c r="P529" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2019/20 - 1 termin (online)</t></is></c><c r="Q529" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="530"><c r="A530" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B530" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C530" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D530" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E530" s="2" t="inlineStr"><is><t>W zakażeniach o etiologii Pseudomonas aeruginosa uzasadnione może być podanie:</t></is></c><c r="F530" s="2" t="inlineStr"><is><t>Piperacykliny z tazobaktamem</t></is></c><c r="G530" s="2" t="inlineStr"><is><t>Gentamycyny</t></is></c><c r="H530" s="2" t="inlineStr"><is><t>Cyprofloksacyny</t></is></c><c r="I530" s="2" t="inlineStr"><is><t>Ceftazydymu</t></is></c><c r="J530" s="2" t="inlineStr" /><c r="K530" s="2" t="inlineStr" /><c r="L530" s="2" t="inlineStr" /><c r="M530" s="2" t="inlineStr" /><c r="N530" s="2" t="inlineStr" /><c r="O530" s="2" t="inlineStr" /><c r="P530" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2019/20 - 1 termin (online)</t></is></c><c r="Q530" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="531"><c r="A531" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B531" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C531" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D531" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E531" s="2" t="inlineStr"><is><t>Po podaniu doustnym działa miejscowo:</t></is></c><c r="F531" s="2" t="inlineStr"><is><t>Ryfaksymina</t></is></c><c r="G531" s="2" t="inlineStr"><is><t>Fidaksomycyna</t></is></c><c r="H531" s="2" t="inlineStr" /><c r="I531" s="2" t="inlineStr" /><c r="J531" s="2" t="inlineStr" /><c r="K531" s="2" t="inlineStr"><is><t>Kwas fusydowy</t></is></c><c r="L531" s="2" t="inlineStr"><is><t>Norfloksacyna</t></is></c><c r="M531" s="2" t="inlineStr" /><c r="N531" s="2" t="inlineStr" /><c r="O531" s="2" t="inlineStr" /><c r="P531" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2019/20 - 1 termin (online)</t></is></c><c r="Q531" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="532"><c r="A532" s="2" t="inlineStr"><is><t>LEKI PRZECIWWIRUSOWE</t></is></c><c r="B532" s="2" t="inlineStr"><is><t>Interakcje</t></is></c><c r="C532" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D532" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E532" s="2" t="inlineStr"><is><t>Wskaż prawidłowe skojarzenie lek – punkt uchwytu:</t></is></c><c r="F532" s="2" t="inlineStr"><is><t>Acyklowir – polimeraza DNA</t></is></c><c r="G532" s="2" t="inlineStr"><is><t>Oseltamiwir – neuraminidaza</t></is></c><c r="H532" s="2" t="inlineStr"><is><t>Lamiwudyna – odwrotna transkryptaza</t></is></c><c r="I532" s="2" t="inlineStr"><is><t>Raltegrawir – integraza</t></is></c><c r="J532" s="2" t="inlineStr" /><c r="K532" s="2" t="inlineStr" /><c r="L532" s="2" t="inlineStr" /><c r="M532" s="2" t="inlineStr" /><c r="N532" s="2" t="inlineStr" /><c r="O532" s="2" t="inlineStr" /><c r="P532" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2019/20 - 1 termin (online)</t></is></c><c r="Q532" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="533"><c r="A533" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B533" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C533" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D533" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E533" s="2" t="inlineStr"><is><t>Wybierz właściwe skojarzenie wskazanie – lek, który można zastosować jako alternatywę dla antybiotków beta-laktamowych u pacjenta z nadwrażliwością na tę grupę leków przeciwbakteryjnych</t></is></c><c r="F533" s="2" t="inlineStr"><is><t>Borelioza – azytromycyna</t></is></c><c r="G533" s="2" t="inlineStr"><is><t>Zapalenie płuc o etiologii pneumokokowej – lewofloksacyna</t></is></c><c r="H533" s="2" t="inlineStr"><is><t>Profilaktyka okołozabiegowa - wankomycyna</t></is></c><c r="I533" s="2" t="inlineStr" /><c r="J533" s="2" t="inlineStr" /><c r="K533" s="2" t="inlineStr"><is><t>Urosepsa o etiologii Escherichia coli – linezolid</t></is></c><c r="L533" s="2" t="inlineStr" /><c r="M533" s="2" t="inlineStr" /><c r="N533" s="2" t="inlineStr" /><c r="O533" s="2" t="inlineStr" /><c r="P533" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2019/20 - 1 termin (online)</t></is></c><c r="Q533" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="534"><c r="A534" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B534" s="2" t="inlineStr"><is><t>Interakcje</t></is></c><c r="C534" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D534" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E534" s="2" t="inlineStr"><is><t>Wskaż prawidłowe skojarzenie lek – wskazanie:</t></is></c><c r="F534" s="2" t="inlineStr"><is><t>Metronidazol – lamblioza</t></is></c><c r="G534" s="2" t="inlineStr"><is><t>Spiramycyna – toksoplazmoza</t></is></c><c r="H534" s="2" t="inlineStr" /><c r="I534" s="2" t="inlineStr" /><c r="J534" s="2" t="inlineStr" /><c r="K534" s="2" t="inlineStr"><is><t>Nifuroksazyd – biegunka poantybiotykowa</t></is></c><c r="L534" s="2" t="inlineStr"><is><t>Amikacyna – borelioza</t></is></c><c r="M534" s="2" t="inlineStr" /><c r="N534" s="2" t="inlineStr" /><c r="O534" s="2" t="inlineStr" /><c r="P534" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2019/20 - 1 termin (online)</t></is></c><c r="Q534" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="535"><c r="A535" s="2" t="inlineStr"><is><t>LEKI PRZECIWGRZYBICZE</t></is></c><c r="B535" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C535" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D535" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E535" s="2" t="inlineStr"><is><t>Wskazaniem do doustnej terapii przeciwgrzybiczej jest:</t></is></c><c r="F535" s="2" t="inlineStr"><is><t>Nieskuteczność leczenia miejscowego</t></is></c><c r="G535" s="2" t="inlineStr"><is><t>Grzybica inwazyjna</t></is></c><c r="H535" s="2" t="inlineStr"><is><t>Stwierdzenie rozległych zmian skórnych</t></is></c><c r="I535" s="2" t="inlineStr" /><c r="J535" s="2" t="inlineStr" /><c r="K535" s="2" t="inlineStr"><is><t>Grzybica paznokci dotycząca pojedynczych płytek paznokciowych</t></is></c><c r="L535" s="2" t="inlineStr" /><c r="M535" s="2" t="inlineStr" /><c r="N535" s="2" t="inlineStr" /><c r="O535" s="2" t="inlineStr" /><c r="P535" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2019/20 - 1 termin (online)</t></is></c><c r="Q535" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="536"><c r="A536" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B536" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C536" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D536" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E536" s="2" t="inlineStr"><is><t>Działanie neurotoksyczne wykazuje:</t></is></c><c r="F536" s="2" t="inlineStr"><is><t>Linezolid</t></is></c><c r="G536" s="2" t="inlineStr"><is><t>Cyprofloksacyna</t></is></c><c r="H536" s="2" t="inlineStr"><is><t>Metronidazol</t></is></c><c r="I536" s="2" t="inlineStr" /><c r="J536" s="2" t="inlineStr" /><c r="K536" s="2" t="inlineStr"><is><t>Klindamycyna</t></is></c><c r="L536" s="2" t="inlineStr" /><c r="M536" s="2" t="inlineStr" /><c r="N536" s="2" t="inlineStr" /><c r="O536" s="2" t="inlineStr" /><c r="P536" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2019/20 - 1 termin (online)</t></is></c><c r="Q536" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="537"><c r="A537" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B537" s="2" t="inlineStr"><is><t>Interakcje</t></is></c><c r="C537" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D537" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E537" s="2" t="inlineStr"><is><t>Wskaż prawidłowe skojarzenie lek – mechanizm działania (należy uwzględnić główny mechanizm działania):</t></is></c><c r="F537" s="2" t="inlineStr"><is><t>Azytromycyna – hamowanie syntezy białek</t></is></c><c r="G537" s="2" t="inlineStr"><is><t>Daptomycyna – uszkodzenie błony komórkowej</t></is></c><c r="H537" s="2" t="inlineStr" /><c r="I537" s="2" t="inlineStr" /><c r="J537" s="2" t="inlineStr" /><c r="K537" s="2" t="inlineStr"><is><t>Cyprofloksacyna – hamowanie biosyntezy ściany komórkowej</t></is></c><c r="L537" s="2" t="inlineStr"><is><t>Amoksycyina – hamowanie syntezy DNA</t></is></c><c r="M537" s="2" t="inlineStr" /><c r="N537" s="2" t="inlineStr" /><c r="O537" s="2" t="inlineStr" /><c r="P537" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2019/20 - 1 termin (online)</t></is></c><c r="Q537" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="538"><c r="A538" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B538" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C538" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D538" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E538" s="2" t="inlineStr"><is><t>W schematach eradykacji Helicobacter pylori znajdują zastosowanie:</t></is></c><c r="F538" s="2" t="inlineStr"><is><t>Amoksycylina</t></is></c><c r="G538" s="2" t="inlineStr"><is><t>Metronidazol</t></is></c><c r="H538" s="2" t="inlineStr" /><c r="I538" s="2" t="inlineStr" /><c r="J538" s="2" t="inlineStr" /><c r="K538" s="2" t="inlineStr"><is><t>Lewofloksacyna</t></is></c><c r="L538" s="2" t="inlineStr"><is><t>Tetracyklina</t></is></c><c r="M538" s="2" t="inlineStr" /><c r="N538" s="2" t="inlineStr" /><c r="O538" s="2" t="inlineStr" /><c r="P538" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2019/20 - 1 termin (online)</t></is></c><c r="Q538" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="539"><c r="A539" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B539" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C539" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D539" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E539" s="2" t="inlineStr"><is><t>Linezolid może być skuteczny w zakażeniach szczepami:</t></is></c><c r="F539" s="2" t="inlineStr"><is><t>MRSA (methicyllin-resistant Staphylococcus aureus)</t></is></c><c r="G539" s="2" t="inlineStr"><is><t>MSSA (methicyllin-sensitive Staphylococcus aureus)</t></is></c><c r="H539" s="2" t="inlineStr"><is><t>VRE (Vancomycin-resistant Enterococcus)</t></is></c><c r="I539" s="2" t="inlineStr" /><c r="J539" s="2" t="inlineStr" /><c r="K539" s="2" t="inlineStr"><is><t>CPE (Carbapenemase-producing Enterobacteriaceae)</t></is></c><c r="L539" s="2" t="inlineStr" /><c r="M539" s="2" t="inlineStr" /><c r="N539" s="2" t="inlineStr" /><c r="O539" s="2" t="inlineStr" /><c r="P539" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2019/20 - 1 termin (online)</t></is></c><c r="Q539" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="540"><c r="A540" s="2" t="inlineStr"><is><t>TARCZYCA</t></is></c><c r="B540" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C540" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D540" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E540" s="2" t="inlineStr"><is><t>Profilaktyczne zastosowanie leków przeciwinfekcyjnych jest uzasadnione:</t></is></c><c r="F540" s="2" t="inlineStr"><is><t>W planowej operacji cięcia cesarskiego (pole czyste-skażone)</t></is></c><c r="G540" s="2" t="inlineStr"><is><t>W planowej implantacji endoprotezy stawu kolanowego (pole czyste)</t></is></c><c r="H540" s="2" t="inlineStr" /><c r="I540" s="2" t="inlineStr" /><c r="J540" s="2" t="inlineStr" /><c r="K540" s="2" t="inlineStr"><is><t>W planowanym usunięciu zmiany skórnej w obrębie dłoni (pole czyste)</t></is></c><c r="L540" s="2" t="inlineStr"><is><t>W planowym usunięciu tarczycy w wolu guzkowym nadczynnym (pole czyste)</t></is></c><c r="M540" s="2" t="inlineStr" /><c r="N540" s="2" t="inlineStr" /><c r="O540" s="2" t="inlineStr" /><c r="P540" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2019/20 - 1 termin (online)</t></is></c><c r="Q540" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="541"><c r="A541" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B541" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C541" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D541" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E541" s="2" t="inlineStr"><is><t>Do bezpiecznych i skutecznych środków do dezynfekcji należą:</t></is></c><c r="F541" s="2" t="inlineStr"><is><t>Oktenidyna</t></is></c><c r="G541" s="2" t="inlineStr" /><c r="H541" s="2" t="inlineStr" /><c r="I541" s="2" t="inlineStr" /><c r="J541" s="2" t="inlineStr" /><c r="K541" s="2" t="inlineStr"><is><t>Spirytus salicylowy</t></is></c><c r="L541" s="2" t="inlineStr"><is><t>Woda utleniona</t></is></c><c r="M541" s="2" t="inlineStr"><is><t>Mleczan etakrydyny</t></is></c><c r="N541" s="2" t="inlineStr" /><c r="O541" s="2" t="inlineStr" /><c r="P541" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2019/20 - 1 termin (online)</t></is></c><c r="Q541" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="542"><c r="A542" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B542" s="2" t="inlineStr"><is><t>Interakcje</t></is></c><c r="C542" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D542" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E542" s="2" t="inlineStr"><is><t>Wskaż prawidłowe skojarzenie lek - działanie niepożądane:</t></is></c><c r="F542" s="2" t="inlineStr"><is><t>Izoniazyd – toczen polekowy</t></is></c><c r="G542" s="2" t="inlineStr"><is><t>Ryfampicyna - śródmiąższowe zapalenie nerek</t></is></c><c r="H542" s="2" t="inlineStr"><is><t>Pirazynamid – hiperurykemia</t></is></c><c r="I542" s="2" t="inlineStr"><is><t>Etambutol - pozagałkowa zapalenie nerwu wzrokowego</t></is></c><c r="J542" s="2" t="inlineStr" /><c r="K542" s="2" t="inlineStr" /><c r="L542" s="2" t="inlineStr" /><c r="M542" s="2" t="inlineStr" /><c r="N542" s="2" t="inlineStr" /><c r="O542" s="2" t="inlineStr" /><c r="P542" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2019/20 - 1 termin (online)</t></is></c><c r="Q542" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="543"><c r="A543" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B543" s="2" t="inlineStr"><is><t>Ciąża</t></is></c><c r="C543" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D543" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E543" s="2" t="inlineStr"><is><t>U kobiety w ciąży można bezpiecznie zastosować:</t></is></c><c r="F543" s="2" t="inlineStr"><is><t>Cefuroksym</t></is></c><c r="G543" s="2" t="inlineStr"><is><t>Fenoksymetylopenicylinę</t></is></c><c r="H543" s="2" t="inlineStr" /><c r="I543" s="2" t="inlineStr" /><c r="J543" s="2" t="inlineStr" /><c r="K543" s="2" t="inlineStr"><is><t>Amikacynę</t></is></c><c r="L543" s="2" t="inlineStr"><is><t>Moksyfloksacynę</t></is></c><c r="M543" s="2" t="inlineStr" /><c r="N543" s="2" t="inlineStr" /><c r="O543" s="2" t="inlineStr" /><c r="P543" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2019/20 - 1 termin (online)</t></is></c><c r="Q543" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="544"><c r="A544" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B544" s="2" t="inlineStr"><is><t>Interakcje</t></is></c><c r="C544" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D544" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E544" s="2" t="inlineStr"><is><t>Wskaż właściwe skojarzenie lek – potencjalne działanie nipożądane:</t></is></c><c r="F544" s="2" t="inlineStr"><is><t>Doksycyklina – fotodermatoza</t></is></c><c r="G544" s="2" t="inlineStr"><is><t>Linezolid - zespół serotoninowy</t></is></c><c r="H544" s="2" t="inlineStr" /><c r="I544" s="2" t="inlineStr" /><c r="J544" s="2" t="inlineStr" /><c r="K544" s="2" t="inlineStr"><is><t>Mupirocyna - zespół czerwonego dziecka</t></is></c><c r="L544" s="2" t="inlineStr"><is><t>Gentamycyna - żółtaczka cholestatyczna</t></is></c><c r="M544" s="2" t="inlineStr" /><c r="N544" s="2" t="inlineStr" /><c r="O544" s="2" t="inlineStr" /><c r="P544" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2019/20 - 1 termin (online)</t></is></c><c r="Q544" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="545"><c r="A545" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B545" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C545" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D545" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E545" s="2" t="inlineStr"><is><t>Działanie nefrotoksyczne wykazuje:</t></is></c><c r="F545" s="2" t="inlineStr"><is><t>Gentamycyna</t></is></c><c r="G545" s="2" t="inlineStr"><is><t>Kolistyna</t></is></c><c r="H545" s="2" t="inlineStr"><is><t>Wankomycyna</t></is></c><c r="I545" s="2" t="inlineStr" /><c r="J545" s="2" t="inlineStr" /><c r="K545" s="2" t="inlineStr"><is><t>Klindamycyna</t></is></c><c r="L545" s="2" t="inlineStr" /><c r="M545" s="2" t="inlineStr" /><c r="N545" s="2" t="inlineStr" /><c r="O545" s="2" t="inlineStr" /><c r="P545" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2019/20 - 1 termin (online)</t></is></c><c r="Q545" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="546"><c r="A546" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B546" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C546" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D546" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E546" s="2" t="inlineStr"><is><t>Syntezę ściany komórkowej hamuje:</t></is></c><c r="F546" s="2" t="inlineStr"><is><t>Kaspofungina</t></is></c><c r="G546" s="2" t="inlineStr"><is><t>Imipenem</t></is></c><c r="H546" s="2" t="inlineStr" /><c r="I546" s="2" t="inlineStr" /><c r="J546" s="2" t="inlineStr" /><c r="K546" s="2" t="inlineStr"><is><t>Nystatyna</t></is></c><c r="L546" s="2" t="inlineStr"><is><t>Tygecyklina</t></is></c><c r="M546" s="2" t="inlineStr" /><c r="N546" s="2" t="inlineStr" /><c r="O546" s="2" t="inlineStr" /><c r="P546" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2019/20 - 1 termin (online)</t></is></c><c r="Q546" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="547"><c r="A547" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B547" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C547" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D547" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E547" s="2" t="inlineStr"><is><t>W biegunce o etiologii Clostridioides difficile uzasadnione może być podanie doustne:</t></is></c><c r="F547" s="2" t="inlineStr"><is><t>Fidaksomycyny</t></is></c><c r="G547" s="2" t="inlineStr"><is><t>Metronidazolu</t></is></c><c r="H547" s="2" t="inlineStr" /><c r="I547" s="2" t="inlineStr" /><c r="J547" s="2" t="inlineStr" /><c r="K547" s="2" t="inlineStr"><is><t>Neomycyny</t></is></c><c r="L547" s="2" t="inlineStr"><is><t>Nifuroksazydu</t></is></c><c r="M547" s="2" t="inlineStr" /><c r="N547" s="2" t="inlineStr" /><c r="O547" s="2" t="inlineStr" /><c r="P547" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2019/20 - 1 termin (online)</t></is></c><c r="Q547" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="548"><c r="A548" s="2" t="inlineStr"><is><t>LEKI PRZECIWGRZYBICZE</t></is></c><c r="B548" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C548" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D548" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E548" s="2" t="inlineStr"><is><t>Wskaż stwierdzenie/a prawdziwe:</t></is></c><c r="F548" s="2" t="inlineStr"><is><t>Ketokonazol stosuje się wyłącznie miejscowo w leczeniu grzybic</t></is></c><c r="G548" s="2" t="inlineStr" /><c r="H548" s="2" t="inlineStr" /><c r="I548" s="2" t="inlineStr" /><c r="J548" s="2" t="inlineStr" /><c r="K548" s="2" t="inlineStr"><is><t>Terbinafina hamuje enzym związany z ukłądem CYP450</t></is></c><c r="L548" s="2" t="inlineStr"><is><t>Zastosowanie technologii liposomów pozwoliło na otrzymanie preparatów amfoterycyny B o istotnie zmniejszonej hepatotoksyczności</t></is></c><c r="M548" s="2" t="inlineStr"><is><t>Kaspofungina osiąga bardzo wysokie stężenia w OUN</t></is></c><c r="N548" s="2" t="inlineStr" /><c r="O548" s="2" t="inlineStr" /><c r="P548" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2019/20 - 1 termin (online)</t></is></c><c r="Q548" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="549"><c r="A549" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B549" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C549" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D549" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E549" s="2" t="inlineStr"><is><t>Metronidazol:</t></is></c><c r="F549" s="2" t="inlineStr"><is><t>Dobrze penetruje do OUN</t></is></c><c r="G549" s="2" t="inlineStr"><is><t>Działa na Entamoeba histolytica</t></is></c><c r="H549" s="2" t="inlineStr" /><c r="I549" s="2" t="inlineStr" /><c r="J549" s="2" t="inlineStr" /><c r="K549" s="2" t="inlineStr"><is><t>Bardzo często jest przyczyną zapalenia ścięgna Achillesa</t></is></c><c r="L549" s="2" t="inlineStr"><is><t>Jest stosowany w wewnątrzbrzusznych zakażeniach szczepami wielolekoopornymi</t></is></c><c r="M549" s="2" t="inlineStr" /><c r="N549" s="2" t="inlineStr" /><c r="O549" s="2" t="inlineStr" /><c r="P549" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2019/20 - 1 termin (online)</t></is></c><c r="Q549" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="550"><c r="A550" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B550" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C550" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D550" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E550" s="2" t="inlineStr"><is><t>Lek bakteriobójczy, którego aktywność przeciwbakteryjną najlepiej charakteryzuje AUC24/MIC, działający na bakterie G(+). Lek nie ma aktywnych metabolitów i działa nefrotoksycznie. Opis może dotyczyć:</t></is></c><c r="F550" s="2" t="inlineStr"><is><t>Wankomycyny</t></is></c><c r="G550" s="2" t="inlineStr" /><c r="H550" s="2" t="inlineStr" /><c r="I550" s="2" t="inlineStr" /><c r="J550" s="2" t="inlineStr" /><c r="K550" s="2" t="inlineStr"><is><t>Kolistyny</t></is></c><c r="L550" s="2" t="inlineStr"><is><t>Klindamycyny</t></is></c><c r="M550" s="2" t="inlineStr"><is><t>Gentamycyny</t></is></c><c r="N550" s="2" t="inlineStr" /><c r="O550" s="2" t="inlineStr" /><c r="P550" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2019/20 - 1 termin (online)</t></is></c><c r="Q550" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="551"><c r="A551" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B551" s="2" t="inlineStr"><is><t>Interakcje</t></is></c><c r="C551" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D551" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E551" s="2" t="inlineStr"><is><t>Wskaż prawidłowe skojarzenie drobnoustrój - lek, który może być skuteczny w zakażeniu o takiej etiologii:</t></is></c><c r="F551" s="2" t="inlineStr"><is><t>Staphylococcus aureus (MSSA) - kloksacylina</t></is></c><c r="G551" s="2" t="inlineStr"><is><t>Clostridioides difficile – wankomycyna</t></is></c><c r="H551" s="2" t="inlineStr" /><c r="I551" s="2" t="inlineStr" /><c r="J551" s="2" t="inlineStr" /><c r="K551" s="2" t="inlineStr"><is><t>Staphylococcus aureus (MRSA) - meropenem</t></is></c><c r="L551" s="2" t="inlineStr"><is><t>Trichomonas vaginalis - ketokonazol</t></is></c><c r="M551" s="2" t="inlineStr" /><c r="N551" s="2" t="inlineStr" /><c r="O551" s="2" t="inlineStr" /><c r="P551" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2019/20 - 1 termin (online)</t></is></c><c r="Q551" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="552"><c r="A552" s="2" t="inlineStr"><is><t>LEKI PRZECIWGRZYBICZE</t></is></c><c r="B552" s="2" t="inlineStr"><is><t>Interakcje</t></is></c><c r="C552" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D552" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E552" s="2" t="inlineStr"><is><t>Wskaż prawidłowe stwierdzenie:</t></is></c><c r="F552" s="2" t="inlineStr"><is><t>Worykonazol wykazuje aktywność wobec Aspergillus spp</t></is></c><c r="G552" s="2" t="inlineStr" /><c r="H552" s="2" t="inlineStr" /><c r="I552" s="2" t="inlineStr" /><c r="J552" s="2" t="inlineStr" /><c r="K552" s="2" t="inlineStr"><is><t>Flukonazol nie wykazuje istotnych klinicznie interakcji na poziomie cytochromu P450</t></is></c><c r="L552" s="2" t="inlineStr"><is><t>Itrakonazol nie wchłania się po podaniu doustnym</t></is></c><c r="M552" s="2" t="inlineStr"><is><t>Posakonazol hamuje syntezę ściany komórkowej grzyba</t></is></c><c r="N552" s="2" t="inlineStr" /><c r="O552" s="2" t="inlineStr" /><c r="P552" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2019/20 - 1 termin (online)</t></is></c><c r="Q552" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="553"><c r="A553" s="2" t="inlineStr"><is><t>LEKI PRZECIWWIRUSOWE</t></is></c><c r="B553" s="2" t="inlineStr"><is><t>Interakcje</t></is></c><c r="C553" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D553" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E553" s="2" t="inlineStr"><is><t>Wskaż prawidłowe skojarzenie lek – wskazanie do leczenia:</t></is></c><c r="F553" s="2" t="inlineStr"><is><t>Acyklowir - półpasiec</t></is></c><c r="G553" s="2" t="inlineStr"><is><t>Gancyklowir – cytomegalowirusowe zapalenie siatkówki</t></is></c><c r="H553" s="2" t="inlineStr"><is><t>Osetamiwir – grypa</t></is></c><c r="I553" s="2" t="inlineStr" /><c r="J553" s="2" t="inlineStr" /><c r="K553" s="2" t="inlineStr"><is><t>Amantadyna – mononukleoza</t></is></c><c r="L553" s="2" t="inlineStr" /><c r="M553" s="2" t="inlineStr" /><c r="N553" s="2" t="inlineStr" /><c r="O553" s="2" t="inlineStr" /><c r="P553" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2019/20 - 1 termin (online)</t></is></c><c r="Q553" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="554"><c r="A554" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B554" s="2" t="inlineStr"><is><t>Interakcje</t></is></c><c r="C554" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D554" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E554" s="2" t="inlineStr"><is><t>Wskaż prawidłowe skojarzenie drobnoustrój - lek, który może być skuteczny w zakażeniu o tej etiologii:</t></is></c><c r="F554" s="2" t="inlineStr"><is><t>Helicobacter pylori – tetracyklina</t></is></c><c r="G554" s="2" t="inlineStr"><is><t>Staphylococcus aureus (MSSA) - cefazolina</t></is></c><c r="H554" s="2" t="inlineStr" /><c r="I554" s="2" t="inlineStr" /><c r="J554" s="2" t="inlineStr" /><c r="K554" s="2" t="inlineStr"><is><t>Escherichia coli – klindamycyna</t></is></c><c r="L554" s="2" t="inlineStr"><is><t>Mycoplasma pneumoniae - teikoplanina</t></is></c><c r="M554" s="2" t="inlineStr" /><c r="N554" s="2" t="inlineStr" /><c r="O554" s="2" t="inlineStr" /><c r="P554" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2019/20 - 1 termin (online)</t></is></c><c r="Q554" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="555"><c r="A555" s="2" t="inlineStr"><is><t>FARMAKOLOGIA OGÓLNA I EBM</t></is></c><c r="B555" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C555" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D555" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E555" s="2" t="inlineStr"><is><t>Wytyczne PRISMA:</t></is></c><c r="F555" s="2" t="inlineStr"><is><t>dotyczą prowadzenia przeglądów systematycznych i metaanaliz</t></is></c><c r="G555" s="2" t="inlineStr" /><c r="H555" s="2" t="inlineStr" /><c r="I555" s="2" t="inlineStr" /><c r="J555" s="2" t="inlineStr" /><c r="K555" s="2" t="inlineStr"><is><t>dotyczą prowadzenia randomizowanych badań klinicznych</t></is></c><c r="L555" s="2" t="inlineStr"><is><t>dotyczą formułowania wytycznych klinicznych</t></is></c><c r="M555" s="2" t="inlineStr"><is><t>dotyczą prowadzenia badań obserwacyjnych</t></is></c><c r="N555" s="2" t="inlineStr" /><c r="O555" s="2" t="inlineStr" /><c r="P555" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2018/19</t></is></c><c r="Q555" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="556"><c r="A556" s="2" t="inlineStr"><is><t>FARMAKOKINETYKA</t></is></c><c r="B556" s="2" t="inlineStr"><is><t>Dawkowanie</t></is></c><c r="C556" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D556" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E556" s="2" t="inlineStr"><is><t>Lek ma Vd=6 l/kg m.c. i CL=10 ml/min/kg m.c. Na tej podstawie spodziewasz się, że lek będzie:</t></is></c><c r="F556" s="2" t="inlineStr"><is><t>wymagał dużej dawki nasycającej</t></is></c><c r="G556" s="2" t="inlineStr" /><c r="H556" s="2" t="inlineStr" /><c r="I556" s="2" t="inlineStr" /><c r="J556" s="2" t="inlineStr" /><c r="K556" s="2" t="inlineStr"><is><t>kumulował się w tkance tłuszczowej</t></is></c><c r="L556" s="2" t="inlineStr"><is><t>miał długi okres półtrwania</t></is></c><c r="M556" s="2" t="inlineStr"><is><t>wymagał korekty dawkowania w niewydolności nerek</t></is></c><c r="N556" s="2" t="inlineStr" /><c r="O556" s="2" t="inlineStr" /><c r="P556" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2018/19</t></is></c><c r="Q556" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="557"><c r="A557" s="2" t="inlineStr"><is><t>FARMAKOKINETYKA</t></is></c><c r="B557" s="2" t="inlineStr"><is><t>Interakcje</t></is></c><c r="C557" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D557" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E557" s="2" t="inlineStr"><is><t>Wskaż prawidłowe stwierdzenia dotyczące wiązania leków z białkami osocza:</t></is></c><c r="F557" s="2" t="inlineStr"><is><t>może być przyczyną istotnych klinicznie interakcji lekowych</t></is></c><c r="G557" s="2" t="inlineStr" /><c r="H557" s="2" t="inlineStr" /><c r="I557" s="2" t="inlineStr" /><c r="J557" s="2" t="inlineStr" /><c r="K557" s="2" t="inlineStr"><is><t>z powodu zmniejszenia stężenia albumin we krwi leki o dużym stopniu wiązaniu z albuminami mogą wykazywać niedostateczny efekt terapeutyczny</t></is></c><c r="L557" s="2" t="inlineStr"><is><t>jest istotne klinicznie wtedy, gdy frakcja wolna wynosi 80%</t></is></c><c r="M557" s="2" t="inlineStr"><is><t>przebiega w wątrobie, gdzie zachodzi sprzęganie leku z albuminami</t></is></c><c r="N557" s="2" t="inlineStr" /><c r="O557" s="2" t="inlineStr" /><c r="P557" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2018/19</t></is></c><c r="Q557" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="558"><c r="A558" s="2" t="inlineStr"><is><t>FARMAKOKINETYKA</t></is></c><c r="B558" s="2" t="inlineStr"><is><t>Sposób podania</t></is></c><c r="C558" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D558" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E558" s="2" t="inlineStr"><is><t>Lek o kinetyce pierwszego rzędu po podaniu doustnym ma biodostępność ok. 100% i okres półtrwania =12 godzin. Pacjent A przyjmuje doustnie ten lek w dawce D co 12 godzin (o godz. 8:00 i 20:00). Pacjent B przyjmuje doustnie ten lek w dawce 2D co 24 godziny (o godz. 8:00). Pacjent C przyjmuje ten lek w ciągłym wlewie dożylnym w dawce odpowiadającej 2D/24h. Wszyscy pacjenci mają prawidłową czynność narządów uczestniczących w eliminacji. Wskaż prawdziwe stwierdzenie:</t></is></c><c r="F558" s="2" t="inlineStr"><is><t>czas eliminacji leku po zakończeniu podawania jest taki sam u wszystkich pacjentów</t></is></c><c r="G558" s="2" t="inlineStr" /><c r="H558" s="2" t="inlineStr" /><c r="I558" s="2" t="inlineStr" /><c r="J558" s="2" t="inlineStr" /><c r="K558" s="2" t="inlineStr"><is><t>w stanie stacjonarnym po pobraniu próbki krwi o godzinie 7:30 rano stężenie tego leku we krwi ma taką samą wartość u wszystkich pacjentów</t></is></c><c r="L558" s="2" t="inlineStr"><is><t>stan stacjonarny ustala się szybciej u pacjenta A niż u pacjenta B</t></is></c><c r="M558" s="2" t="inlineStr"><is><t>wiązanie leku z białkami jest największe u pacjenta C, a najmniejsze u pacjenta A</t></is></c><c r="N558" s="2" t="inlineStr" /><c r="O558" s="2" t="inlineStr" /><c r="P558" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2018/19</t></is></c><c r="Q558" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="559"><c r="A559" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B559" s="2" t="inlineStr"><is><t>Interakcje</t></is></c><c r="C559" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D559" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E559" s="2" t="inlineStr"><is><t>Wskaż prawidłowe stwierdzenie dotyczące warfaryny:</t></is></c><c r="F559" s="2" t="inlineStr"><is><t>blokuje aktywność reduktazy epoksydowej fitomenadionu</t></is></c><c r="G559" s="2" t="inlineStr"><is><t>aktywność warfaryny zależy od polimorfizmu genetycznego izoenzymu CYP2C9</t></is></c><c r="H559" s="2" t="inlineStr" /><c r="I559" s="2" t="inlineStr" /><c r="J559" s="2" t="inlineStr" /><c r="K559" s="2" t="inlineStr"><is><t>zwiększa aktywność białka C i jego kofaktora - białka S o działaniu przeciwzakrzepowym</t></is></c><c r="L559" s="2" t="inlineStr"><is><t>zmniejsza aktywność biologiczną czynników krzepnięcia zespołu protrombiny skutecznie zapobiegając zakrzepicy od 2. doby po włączeniuleczenia</t></is></c><c r="M559" s="2" t="inlineStr" /><c r="N559" s="2" t="inlineStr" /><c r="O559" s="2" t="inlineStr" /><c r="P559" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2018/19</t></is></c><c r="Q559" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="560"><c r="A560" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B560" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C560" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D560" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E560" s="2" t="inlineStr"><is><t>Wskaż prawdziwe stwierdzenie dotyczące małopłytkowości indukowanej heparyną (HIT) typu II:</t></is></c><c r="F560" s="2" t="inlineStr"><is><t>jest związana z podawaniem heparyny niefrakcjonowanej oraz heparyn drobnocząsteczkowych, ale nie fondaparyny</t></is></c><c r="G560" s="2" t="inlineStr"><is><t>charakteryzuje się spadkiem liczby płytek krwi do 30-50 tys./μl najczęściej w 5-10 dniu od rozpoczęcia leczenia</t></is></c><c r="H560" s="2" t="inlineStr"><is><t>bezpośrednie inhibitory trombiny są lekami z wyboru w leczeniu HIT II</t></is></c><c r="I560" s="2" t="inlineStr" /><c r="J560" s="2" t="inlineStr" /><c r="K560" s="2" t="inlineStr"><is><t>w ocenie klinicznej istotne dla rozpoznania HIT II jest stwierdzenie krwawienia z przewodu pokarmowego</t></is></c><c r="L560" s="2" t="inlineStr" /><c r="M560" s="2" t="inlineStr" /><c r="N560" s="2" t="inlineStr" /><c r="O560" s="2" t="inlineStr" /><c r="P560" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2018/19</t></is></c><c r="Q560" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="561"><c r="A561" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B561" s="2" t="inlineStr"><is><t>Antidotum</t></is></c><c r="C561" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D561" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E561" s="2" t="inlineStr"><is><t>Kwas traneksamowy:</t></is></c><c r="F561" s="2" t="inlineStr"><is><t>hamuje aktywatory plazminogenu</t></is></c><c r="G561" s="2" t="inlineStr"><is><t>powoduje zagrożenie powikłaniami zakrzepowo-zatorowymi</t></is></c><c r="H561" s="2" t="inlineStr"><is><t>jest antidotum w krwawieniach związanych ze stosowaniem leków fibrynolitycznych</t></is></c><c r="I561" s="2" t="inlineStr" /><c r="J561" s="2" t="inlineStr" /><c r="K561" s="2" t="inlineStr"><is><t>zwiększa śmiertelność w krwotokach operacyjnych i pourazowych</t></is></c><c r="L561" s="2" t="inlineStr" /><c r="M561" s="2" t="inlineStr" /><c r="N561" s="2" t="inlineStr" /><c r="O561" s="2" t="inlineStr" /><c r="P561" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2018/19</t></is></c><c r="Q561" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="562"><c r="A562" s="2" t="inlineStr"><is><t>NARKOTYCZNE LEKI PRZECIWBÓLOWE</t></is></c><c r="B562" s="2" t="inlineStr"><is><t>Sposób podania</t></is></c><c r="C562" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D562" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E562" s="2" t="inlineStr"><is><t>Efekt działania w czasie do 10 minut od podania występuje po podaniu:</t></is></c><c r="F562" s="2" t="inlineStr"><is><t>fentanylu donosowo</t></is></c><c r="G562" s="2" t="inlineStr"><is><t>naloksonu dożylnie</t></is></c><c r="H562" s="2" t="inlineStr"><is><t>glukagonu domięśniowo</t></is></c><c r="I562" s="2" t="inlineStr" /><c r="J562" s="2" t="inlineStr" /><c r="K562" s="2" t="inlineStr"><is><t>węgla medycznego (aktywowanego) w dawce 1 g przez zgłębnik nosowo￾żoładkowy</t></is></c><c r="L562" s="2" t="inlineStr" /><c r="M562" s="2" t="inlineStr" /><c r="N562" s="2" t="inlineStr" /><c r="O562" s="2" t="inlineStr" /><c r="P562" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2018/19</t></is></c><c r="Q562" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="563"><c r="A563" s="2" t="inlineStr"><is><t>CUKRZYCA</t></is></c><c r="B563" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C563" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D563" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E563" s="2" t="inlineStr"><is><t>Wskaż prawdziwe połączenie lek – mechanizm działania:</t></is></c><c r="F563" s="2" t="inlineStr"><is><t>linagliptyna – pośrednio aktywacja wydzielania insuliny przez pobudzenie receptora dla GLP-1 (peptydu glukagonopodobnego typu 1)</t></is></c><c r="G563" s="2" t="inlineStr"><is><t>empagliflozyna – indukcja stałej łagodnej hiperketonemii ze zwiększeniem stężenia kwasu beta-hydroksymasłowego w surowicy</t></is></c><c r="H563" s="2" t="inlineStr"><is><t>ezetymib – redukcja jelitowego wchłaniania cholesterolu i steroli roślinnych</t></is></c><c r="I563" s="2" t="inlineStr" /><c r="J563" s="2" t="inlineStr" /><c r="K563" s="2" t="inlineStr"><is><t>orlistat – aktywacja lipazy trzustkowej w świetle przewodu pokarmowego</t></is></c><c r="L563" s="2" t="inlineStr" /><c r="M563" s="2" t="inlineStr" /><c r="N563" s="2" t="inlineStr" /><c r="O563" s="2" t="inlineStr" /><c r="P563" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2018/19</t></is></c><c r="Q563" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="564"><c r="A564" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B564" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C564" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D564" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E564" s="2" t="inlineStr"><is><t>Wskaż zestaw, gdzie prawidłowo uszeregowano insuliny od najkrócej do najdłużej działającej:</t></is></c><c r="F564" s="2" t="inlineStr"><is><t>lispro–insulina ludzka–glargina</t></is></c><c r="G564" s="2" t="inlineStr"><is><t>glulizyna–insulina ludzka izofanowa–degludec</t></is></c><c r="H564" s="2" t="inlineStr" /><c r="I564" s="2" t="inlineStr" /><c r="J564" s="2" t="inlineStr" /><c r="K564" s="2" t="inlineStr"><is><t>aspart – degludec – detemir</t></is></c><c r="L564" s="2" t="inlineStr"><is><t>detemir–glulizyna–insulina protaminowo-cynkowa</t></is></c><c r="M564" s="2" t="inlineStr" /><c r="N564" s="2" t="inlineStr" /><c r="O564" s="2" t="inlineStr" /><c r="P564" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2018/19</t></is></c><c r="Q564" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="565"><c r="A565" s="2" t="inlineStr"><is><t>CUKRZYCA</t></is></c><c r="B565" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C565" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D565" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E565" s="2" t="inlineStr"><is><t>Metformina:</t></is></c><c r="F565" s="2" t="inlineStr"><is><t>ma klirens nerkowy i nie powinna być stosowana jeśli eGFR &lt; 30 ml/min</t></is></c><c r="G565" s="2" t="inlineStr"><is><t>aktywuje kinazę AMP, co powoduje zwiększenie beztlenowego metabolizm glukozy w komórkach</t></is></c><c r="H565" s="2" t="inlineStr" /><c r="I565" s="2" t="inlineStr" /><c r="J565" s="2" t="inlineStr" /><c r="K565" s="2" t="inlineStr"><is><t>nie powoduje hipoglikemii u chorych na cukrzycę, ale ma taki efekt u osób bez cukrzycy</t></is></c><c r="L565" s="2" t="inlineStr"><is><t>nie jest skuteczna w zapobieganiu progresji stanu przedcukrzycowego do cukrzycy typu 2</t></is></c><c r="M565" s="2" t="inlineStr" /><c r="N565" s="2" t="inlineStr" /><c r="O565" s="2" t="inlineStr" /><c r="P565" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2018/19</t></is></c><c r="Q565" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="566"><c r="A566" s="2" t="inlineStr"><is><t>LEKI HIPOLIPEMIZUJĄCE</t></is></c><c r="B566" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C566" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D566" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E566" s="2" t="inlineStr"><is><t>Ostre zapalenie trzustki może być powikłaniem stosowania:</t></is></c><c r="F566" s="2" t="inlineStr"><is><t>inhibitorów dipeptydylopeptydazy 4 (DPP-4)</t></is></c><c r="G566" s="2" t="inlineStr"><is><t>inhibitory reduktazy HMG-Ca</t></is></c><c r="H566" s="2" t="inlineStr"><is><t>związków kwasu 5-aminosalicylowego</t></is></c><c r="I566" s="2" t="inlineStr"><is><t>doustnych środków antykoncepcyjnych</t></is></c><c r="J566" s="2" t="inlineStr" /><c r="K566" s="2" t="inlineStr" /><c r="L566" s="2" t="inlineStr" /><c r="M566" s="2" t="inlineStr" /><c r="N566" s="2" t="inlineStr" /><c r="O566" s="2" t="inlineStr" /><c r="P566" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2018/19</t></is></c><c r="Q566" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="567"><c r="A567" s="2" t="inlineStr"><is><t>NADCIŚNIENIE TĘTNICZE</t></is></c><c r="B567" s="2" t="inlineStr"><is><t>Przeciwwskazania</t></is></c><c r="C567" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D567" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E567" s="2" t="inlineStr"><is><t>Pacjentka z obustronnym ostrym pozagałkowym zapaleniem nerwu wzrokowego, co zagraża ślepotą, wymaga leczenia metyloprednizolonem (brak alternatywy leczniczej). Zostałeś poproszona/-y o konsultację w celu oceny przeciwwskazań do steroidoterapii. Która z chorób współistniejących jest w tej sytuacji przeciwwskazaniem do zastosowania leku:</t></is></c><c r="F567" s="2" t="inlineStr"><is><t>ciężka sepsa o niejasnej etiologii</t></is></c><c r="G567" s="2" t="inlineStr" /><c r="H567" s="2" t="inlineStr" /><c r="I567" s="2" t="inlineStr" /><c r="J567" s="2" t="inlineStr" /><c r="K567" s="2" t="inlineStr"><is><t>cukrzyca typu 1</t></is></c><c r="L567" s="2" t="inlineStr"><is><t>nadciśnienie tętnicze</t></is></c><c r="M567" s="2" t="inlineStr"><is><t>zaburzenia psychotyczne pod postacią omamów i agresji</t></is></c><c r="N567" s="2" t="inlineStr" /><c r="O567" s="2" t="inlineStr" /><c r="P567" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2018/19</t></is></c><c r="Q567" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="568"><c r="A568" s="2" t="inlineStr"><is><t>LEKI HIPOLIPEMIZUJĄCE</t></is></c><c r="B568" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C568" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D568" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E568" s="2" t="inlineStr"><is><t>Które połączenie rozważysz w przypadku nie osiągnięcia zakładanej redukcji stężenia cholesterolu frakcji LDL podczas stosowania diety i atorwastatyny?</t></is></c><c r="F568" s="2" t="inlineStr"><is><t>atorwastatyna + anacetrapib</t></is></c><c r="G568" s="2" t="inlineStr"><is><t>atorwastatyna + ezetymib</t></is></c><c r="H568" s="2" t="inlineStr"><is><t>atorwastatyna + kwas eikozapentaenowy</t></is></c><c r="I568" s="2" t="inlineStr"><is><t>atorwastatyna + ewolokumab</t></is></c><c r="J568" s="2" t="inlineStr" /><c r="K568" s="2" t="inlineStr" /><c r="L568" s="2" t="inlineStr" /><c r="M568" s="2" t="inlineStr" /><c r="N568" s="2" t="inlineStr" /><c r="O568" s="2" t="inlineStr" /><c r="P568" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2018/19</t></is></c><c r="Q568" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="569"><c r="A569" s="2" t="inlineStr"><is><t>LEKI IMMUNOSUPRESYJNE</t></is></c><c r="B569" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C569" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D569" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E569" s="2" t="inlineStr"><is><t>Które stwierdzenie jest prawdziwe?</t></is></c><c r="F569" s="2" t="inlineStr"><is><t>takrolimus i ewerolimus tworzą kompleks z immunofiliną FKBP</t></is></c><c r="G569" s="2" t="inlineStr"><is><t>takrolimus i ewerolimus należą do leków o wąskim indeksie (wskaźniku) terapeutycznym</t></is></c><c r="H569" s="2" t="inlineStr" /><c r="I569" s="2" t="inlineStr" /><c r="J569" s="2" t="inlineStr" /><c r="K569" s="2" t="inlineStr"><is><t>takrolimus i ewerolimus mają ten sam mechanizm działania</t></is></c><c r="L569" s="2" t="inlineStr"><is><t>takrolimus i ewerolimus działają przeciwnowotorowo</t></is></c><c r="M569" s="2" t="inlineStr" /><c r="N569" s="2" t="inlineStr" /><c r="O569" s="2" t="inlineStr" /><c r="P569" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2018/19</t></is></c><c r="Q569" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="570"><c r="A570" s="2" t="inlineStr"><is><t>LEKI IMMUNOSUPRESYJNE</t></is></c><c r="B570" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C570" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D570" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E570" s="2" t="inlineStr"><is><t>Taki sam mechanizm działania mają:</t></is></c><c r="F570" s="2" t="inlineStr"><is><t>bazyliksymab i daklizumab</t></is></c><c r="G570" s="2" t="inlineStr"><is><t>rytuksymab i okrelizumab</t></is></c><c r="H570" s="2" t="inlineStr" /><c r="I570" s="2" t="inlineStr" /><c r="J570" s="2" t="inlineStr" /><c r="K570" s="2" t="inlineStr"><is><t>natalizumab i fingolimod</t></is></c><c r="L570" s="2" t="inlineStr"><is><t>filgrastym i romiplostym</t></is></c><c r="M570" s="2" t="inlineStr" /><c r="N570" s="2" t="inlineStr" /><c r="O570" s="2" t="inlineStr" /><c r="P570" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2018/19</t></is></c><c r="Q570" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="571"><c r="A571" s="2" t="inlineStr"><is><t>LEKI ROŚLINNE I SUPLEMENTY</t></is></c><c r="B571" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C571" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D571" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E571" s="2" t="inlineStr"><is><t>Powikłaniem stosowania inhibitora H+ K+ –ATPazy komórek okładzinowych może być:</t></is></c><c r="F571" s="2" t="inlineStr"><is><t>niedokrwistość makrocytarna z powodu niedoboru witaminy B12</t></is></c><c r="G571" s="2" t="inlineStr"><is><t>osteoporoza z powodu zaburzeń wchłaniania wapnia</t></is></c><c r="H571" s="2" t="inlineStr"><is><t>bakteryjne zakażenia przewodu pokarmowego</t></is></c><c r="I571" s="2" t="inlineStr"><is><t>zmiany wchłaniania wielu leków z przewodu pokarmowego</t></is></c><c r="J571" s="2" t="inlineStr" /><c r="K571" s="2" t="inlineStr" /><c r="L571" s="2" t="inlineStr" /><c r="M571" s="2" t="inlineStr" /><c r="N571" s="2" t="inlineStr" /><c r="O571" s="2" t="inlineStr" /><c r="P571" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2018/19</t></is></c><c r="Q571" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="572"><c r="A572" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B572" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C572" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D572" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E572" s="2" t="inlineStr"><is><t>Lekiem stosowanym w objawach ze strony przewodu pokarmowego o wpływie na układ opioidowy jest:</t></is></c><c r="F572" s="2" t="inlineStr"><is><t>trimebutyna</t></is></c><c r="G572" s="2" t="inlineStr"><is><t>racekadotryl</t></is></c><c r="H572" s="2" t="inlineStr"><is><t>metylnaltrekson</t></is></c><c r="I572" s="2" t="inlineStr" /><c r="J572" s="2" t="inlineStr" /><c r="K572" s="2" t="inlineStr"><is><t>dekstrometorfan</t></is></c><c r="L572" s="2" t="inlineStr" /><c r="M572" s="2" t="inlineStr" /><c r="N572" s="2" t="inlineStr" /><c r="O572" s="2" t="inlineStr" /><c r="P572" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2018/19</t></is></c><c r="Q572" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="573"><c r="A573" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B573" s="2" t="inlineStr"><is><t>Dawkowanie</t></is></c><c r="C573" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D573" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E573" s="2" t="inlineStr"><is><t>W niewydolności nerek należy zmodyfikować dawkowanie:</t></is></c><c r="F573" s="2" t="inlineStr"><is><t>eteksylanu dabigatranu</t></is></c><c r="G573" s="2" t="inlineStr" /><c r="H573" s="2" t="inlineStr" /><c r="I573" s="2" t="inlineStr" /><c r="J573" s="2" t="inlineStr" /><c r="K573" s="2" t="inlineStr"><is><t>atorwastatyny</t></is></c><c r="L573" s="2" t="inlineStr"><is><t>kwasu acetylosalicylowego</t></is></c><c r="M573" s="2" t="inlineStr"><is><t>lewotyroksyny</t></is></c><c r="N573" s="2" t="inlineStr" /><c r="O573" s="2" t="inlineStr" /><c r="P573" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2018/19</t></is></c><c r="Q573" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="574"><c r="A574" s="2" t="inlineStr"><is><t>NIEOPIOIDOWE LEKI PRZECIWBÓLOWE</t></is></c><c r="B574" s="2" t="inlineStr"><is><t>Dawkowanie</t></is></c><c r="C574" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D574" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E574" s="2" t="inlineStr"><is><t>Paracetamol:</t></is></c><c r="F574" s="2" t="inlineStr"><is><t>jest prawdopodobnie słabym niewybiórczym inhibitorem cyklooksygenaz (COX), ale bez działania przeciwzapalnego</t></is></c><c r="G574" s="2" t="inlineStr"><is><t>via aktywny metabolit hamuje wychwyt zwrotny endokanabinoidów</t></is></c><c r="H574" s="2" t="inlineStr"><is><t>ma maksymalną dawkę dobową ustaloną na 4 g/d (a u osób z zespołem zależności alkoholowej na 2 g/d)</t></is></c><c r="I574" s="2" t="inlineStr" /><c r="J574" s="2" t="inlineStr" /><c r="K574" s="2" t="inlineStr"><is><t>po przedawkowaniu jest antagonizowany przez dożylne wlewy glutationu (GSH)</t></is></c><c r="L574" s="2" t="inlineStr" /><c r="M574" s="2" t="inlineStr" /><c r="N574" s="2" t="inlineStr" /><c r="O574" s="2" t="inlineStr" /><c r="P574" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2018/19</t></is></c><c r="Q574" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="575"><c r="A575" s="2" t="inlineStr"><is><t>CUKRZYCA</t></is></c><c r="B575" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C575" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D575" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E575" s="2" t="inlineStr"><is><t>Tramadol:</t></is></c><c r="F575" s="2" t="inlineStr"><is><t>ma mechanizm działania podobny do tapentadolu</t></is></c><c r="G575" s="2" t="inlineStr"><is><t>może powodować drgawki</t></is></c><c r="H575" s="2" t="inlineStr" /><c r="I575" s="2" t="inlineStr" /><c r="J575" s="2" t="inlineStr" /><c r="K575" s="2" t="inlineStr"><is><t>może zwiększać ryzyko hiperglikemii i pogarszać kontrolę cukrzycy</t></is></c><c r="L575" s="2" t="inlineStr"><is><t>działa przeciwbólowo skuteczniej w połączeniu z lekami przeciwdepresyjnymi z powodu synergizmu działania</t></is></c><c r="M575" s="2" t="inlineStr" /><c r="N575" s="2" t="inlineStr" /><c r="O575" s="2" t="inlineStr" /><c r="P575" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2018/19</t></is></c><c r="Q575" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="576"><c r="A576" s="2" t="inlineStr"><is><t>NARKOTYCZNE LEKI PRZECIWBÓLOWE</t></is></c><c r="B576" s="2" t="inlineStr"><is><t>Sposób podania</t></is></c><c r="C576" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D576" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E576" s="2" t="inlineStr"><is><t>Rotacja opioidów:</t></is></c><c r="F576" s="2" t="inlineStr"><is><t>wymaga ustalenia ekwianelgetycznych dawek zamienianych opioidów, np. morfina : oksykodon p.o. odpowiednio 10 mg : 6,67 mg</t></is></c><c r="G576" s="2" t="inlineStr" /><c r="H576" s="2" t="inlineStr" /><c r="I576" s="2" t="inlineStr" /><c r="J576" s="2" t="inlineStr" /><c r="K576" s="2" t="inlineStr"><is><t>wymaga nie łączenia opioidów z innymi lekami przeciwbólowymi</t></is></c><c r="L576" s="2" t="inlineStr"><is><t>pomaga zapobiec immunosupresyjnemu działaniu opioidów</t></is></c><c r="M576" s="2" t="inlineStr"><is><t>powinna być oparta o tą samą drogę podania, to znaczy rotowane opioidy powinny mieć tę samą postać farmaceutyczną</t></is></c><c r="N576" s="2" t="inlineStr" /><c r="O576" s="2" t="inlineStr" /><c r="P576" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2018/19</t></is></c><c r="Q576" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="577"><c r="A577" s="2" t="inlineStr"><is><t>UKŁAD PRZYWSPÓŁCZULNY</t></is></c><c r="B577" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C577" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D577" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E577" s="2" t="inlineStr"><is><t>Pasażerowie podróżujący wagonem metra, w którym odnaleziono porzucony bagaż, zostali przyjęci na oddział ratunkowy z powodu bolesnych skurczów jelit, wymiotów, duszności i osłabienia siły mięśniowej. W badaniu fizykalnym stwierdzono zwiększoną częstość oddechów, świsty oskrzelowe, bradykardię i zwężenie źrenic. Lek/leki z wyboru w powyższej sytuacji to:</t></is></c><c r="F577" s="2" t="inlineStr"><is><t>acetylocysteina</t></is></c><c r="G577" s="2" t="inlineStr"><is><t>pralidoksym</t></is></c><c r="H577" s="2" t="inlineStr"><is><t>pirydostygmina</t></is></c><c r="I577" s="2" t="inlineStr"><is><t>atropina</t></is></c><c r="J577" s="2" t="inlineStr" /><c r="K577" s="2" t="inlineStr" /><c r="L577" s="2" t="inlineStr" /><c r="M577" s="2" t="inlineStr" /><c r="N577" s="2" t="inlineStr" /><c r="O577" s="2" t="inlineStr" /><c r="P577" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2018/19</t></is></c><c r="Q577" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="578"><c r="A578" s="2" t="inlineStr"><is><t>LEKI PRZECIWNOWOTWOROWE</t></is></c><c r="B578" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C578" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D578" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E578" s="2" t="inlineStr"><is><t>Inhibitory immunologicznych punktów kontrolnych:</t></is></c><c r="F578" s="2" t="inlineStr"><is><t>są przeciwciałami monoklonalnymi przeciw CLTA-4, PD-1 i PDL-1</t></is></c><c r="G578" s="2" t="inlineStr"><is><t>nawiązują koncepcyjnie do immunostymulującego działania szczepionki BCG w raku pęcherza moczowego</t></is></c><c r="H578" s="2" t="inlineStr"><is><t>są skuteczne w leczeniu różnych typów nowotworów</t></is></c><c r="I578" s="2" t="inlineStr"><is><t>indukują zjawiska autoimmunologiczne</t></is></c><c r="J578" s="2" t="inlineStr" /><c r="K578" s="2" t="inlineStr" /><c r="L578" s="2" t="inlineStr" /><c r="M578" s="2" t="inlineStr" /><c r="N578" s="2" t="inlineStr" /><c r="O578" s="2" t="inlineStr" /><c r="P578" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2018/19</t></is></c><c r="Q578" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="579"><c r="A579" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B579" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C579" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D579" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E579" s="2" t="inlineStr"><is><t>Projektant mody Alexander McQeen (1969-2010) był uzależniony od wielu substancji psychoaktywnych. Które cechy opisu jego zachowania z filmu biograficznego „Wizjoner. Buntownik. Geniusz” wskazują na ekspozycję na kokainę?</t></is></c><c r="F579" s="2" t="inlineStr"><is><t>gadatliwy, w świetnym nastroju, pełen energii i bardzo ruchliwy mimo 16 h pracy przed pokazem, ale spocony i z nawracającymi krwawieniami z nosa</t></is></c><c r="G579" s="2" t="inlineStr" /><c r="H579" s="2" t="inlineStr" /><c r="I579" s="2" t="inlineStr" /><c r="J579" s="2" t="inlineStr" /><c r="K579" s="2" t="inlineStr"><is><t>brawurowy i agresywny, z zaburzeniami mowy i równowagi ruchowej</t></is></c><c r="L579" s="2" t="inlineStr"><is><t>błyskotliwy, dowcipny, szybko przyswajający duże ilości nowych informacji, ale ciągle głodny i z okresowymi napadami paniki</t></is></c><c r="M579" s="2" t="inlineStr"><is><t>w euforii, komplementujący współpracowników, okresowo z barwnymi wizjami, okresowo podsypiający, z przekrwionymi twardówkami</t></is></c><c r="N579" s="2" t="inlineStr" /><c r="O579" s="2" t="inlineStr" /><c r="P579" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2018/19</t></is></c><c r="Q579" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="580"><c r="A580" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B580" s="2" t="inlineStr"><is><t>Antidotum</t></is></c><c r="C580" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D580" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E580" s="2" t="inlineStr"><is><t>Działanie farmakologiczne inne niż suplementacja w stanach niedoboru ma:</t></is></c><c r="F580" s="2" t="inlineStr"><is><t>fitomenadion w niewydolności wątroby i przedawkowaniu warfaryny</t></is></c><c r="G580" s="2" t="inlineStr"><is><t>cholekalcyferol w profilaktyce i leczeniu osteoporozy</t></is></c><c r="H580" s="2" t="inlineStr" /><c r="I580" s="2" t="inlineStr" /><c r="J580" s="2" t="inlineStr" /><c r="K580" s="2" t="inlineStr"><is><t>nikotynamid w hiperurykemii i atakach dny moczanowej</t></is></c><c r="L580" s="2" t="inlineStr"><is><t>tokoferol w profilatyce raka płuc</t></is></c><c r="M580" s="2" t="inlineStr" /><c r="N580" s="2" t="inlineStr" /><c r="O580" s="2" t="inlineStr" /><c r="P580" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2018/19</t></is></c><c r="Q580" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="581"><c r="A581" s="2" t="inlineStr"><is><t>CUKRZYCA</t></is></c><c r="B581" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C581" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D581" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E581" s="2" t="inlineStr"><is><t>Obniżenie stężenia potasu w surowicy może być spowodowane zastosowaniem:</t></is></c><c r="F581" s="2" t="inlineStr"><is><t>bisakodylu</t></is></c><c r="G581" s="2" t="inlineStr"><is><t>prednizonu</t></is></c><c r="H581" s="2" t="inlineStr"><is><t>glukozy z insuliną</t></is></c><c r="I581" s="2" t="inlineStr" /><c r="J581" s="2" t="inlineStr" /><c r="K581" s="2" t="inlineStr"><is><t>glukonianu wapnia</t></is></c><c r="L581" s="2" t="inlineStr" /><c r="M581" s="2" t="inlineStr" /><c r="N581" s="2" t="inlineStr" /><c r="O581" s="2" t="inlineStr" /><c r="P581" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2018/19</t></is></c><c r="Q581" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="582"><c r="A582" s="2" t="inlineStr"><is><t>STANY NAGŁE</t></is></c><c r="B582" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C582" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D582" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E582" s="2" t="inlineStr"><is><t>Zasadzką płynoterapii jest:</t></is></c><c r="F582" s="2" t="inlineStr"><is><t>obrzęk płuc po nawadnianiu płynem wieloelektrolitowym</t></is></c><c r="G582" s="2" t="inlineStr"><is><t>brak możliwości wiarygodnego oznaczenia grupy krwi i wykonania próby krzyżowej po padaniu dekstranu 70 000</t></is></c><c r="H582" s="2" t="inlineStr"><is><t>hiperonkotyczna niewydolność nerek po podaniu hydroksyetylowanej skrobi 130/0,4</t></is></c><c r="I582" s="2" t="inlineStr" /><c r="J582" s="2" t="inlineStr" /><c r="K582" s="2" t="inlineStr"><is><t>zakrzepica podczas stosowania 20% roztworu albumin</t></is></c><c r="L582" s="2" t="inlineStr" /><c r="M582" s="2" t="inlineStr" /><c r="N582" s="2" t="inlineStr" /><c r="O582" s="2" t="inlineStr" /><c r="P582" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2018/19</t></is></c><c r="Q582" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="583"><c r="A583" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B583" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C583" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D583" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E583" s="2" t="inlineStr"><is><t>Wskaż prawdziwe stwierdzenia:</t></is></c><c r="F583" s="2" t="inlineStr"><is><t>w USA obowiązuje nazewnictwo leków w pewnym zakresie autonomiczne od tworzonej przez WHO listy nazw międzynarodowych, przykłady paracetamol i acetaminofen czy petydyna i meperydyna</t></is></c><c r="G583" s="2" t="inlineStr" /><c r="H583" s="2" t="inlineStr" /><c r="I583" s="2" t="inlineStr" /><c r="J583" s="2" t="inlineStr" /><c r="K583" s="2" t="inlineStr"><is><t>po wygaśnięciu ochrony patentowej enoksaparyny wprowadzono jej odtwórcze odpowiedniki tylko na podstawie wykazania ich biorównoważności</t></is></c><c r="L583" s="2" t="inlineStr"><is><t>antysensowne oligonukleotydy mają w nazwie końcówkę -stim</t></is></c><c r="M583" s="2" t="inlineStr"><is><t>przy konwersji między lekami biopodobnymi obowiązuje zasada zamiany automatycznej (substytucji)</t></is></c><c r="N583" s="2" t="inlineStr" /><c r="O583" s="2" t="inlineStr" /><c r="P583" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2018/19</t></is></c><c r="Q583" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="584"><c r="A584" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B584" s="2" t="inlineStr"><is><t>Interakcje</t></is></c><c r="C584" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D584" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E584" s="2" t="inlineStr"><is><t>Wskaż prawidłowe zestawienia lek-spektrum działania:</t></is></c><c r="F584" s="2" t="inlineStr"><is><t>cyprofloksacyna – Pseudomonas aeruginosa, Mycoplasma pneumoniae</t></is></c><c r="G584" s="2" t="inlineStr"><is><t>penicylina G – Fusobacterium spp., Streptococcus pyogenes</t></is></c><c r="H584" s="2" t="inlineStr"><is><t>rifaksymina – Escherichia coli, Campylobacter jejuni</t></is></c><c r="I584" s="2" t="inlineStr" /><c r="J584" s="2" t="inlineStr" /><c r="K584" s="2" t="inlineStr"><is><t>gentamycyna – Clostridium spp., Helicobacter pylori</t></is></c><c r="L584" s="2" t="inlineStr" /><c r="M584" s="2" t="inlineStr" /><c r="N584" s="2" t="inlineStr" /><c r="O584" s="2" t="inlineStr" /><c r="P584" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2018/19</t></is></c><c r="Q584" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="585"><c r="A585" s="2" t="inlineStr"><is><t>LEKI PRZECIWGRZYBICZE</t></is></c><c r="B585" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C585" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D585" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E585" s="2" t="inlineStr"><is><t>Wskaż zdania prawdziwe:</t></is></c><c r="F585" s="2" t="inlineStr"><is><t>zastosowanie technologii liposomów pozwoliło na otrzymanie preparatów amfoterycyny B o zmniejszonej nefrotoksyczności</t></is></c><c r="G585" s="2" t="inlineStr" /><c r="H585" s="2" t="inlineStr" /><c r="I585" s="2" t="inlineStr" /><c r="J585" s="2" t="inlineStr" /><c r="K585" s="2" t="inlineStr"><is><t>w przeciwieństwie do terbinafiny, azole hamują enzym szlaku biosyntezy ergosterolu niezwiązany z układem CYP450</t></is></c><c r="L585" s="2" t="inlineStr"><is><t>kaspofungina może być skuteczna w leczeniu i profilaktyce zapalenia opon mózgowo-rdzeniowych o etiologii Cryptococcus neoformans</t></is></c><c r="M585" s="2" t="inlineStr"><is><t>dla uzyskania możliwie najlepszych efektów leczenia amfoterycyną B najistotniejsze z punktu widzenia PK/PD jest, aby stężenie leku pomiędzy kolejnymi podaniami utrzymywało się na poziomie 4 x MIC optymalnie przez 100% czasu</t></is></c><c r="N585" s="2" t="inlineStr" /><c r="O585" s="2" t="inlineStr" /><c r="P585" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2018/19</t></is></c><c r="Q585" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="586"><c r="A586" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B586" s="2" t="inlineStr"><is><t>Dawkowanie</t></is></c><c r="C586" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D586" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E586" s="2" t="inlineStr"><is><t>Modyfikacja dawki nie jest wymagana u pacjenta z eGFR wg wzoru Cockcrofta- Gaulta = 24 ml/min podczas stosowania:</t></is></c><c r="F586" s="2" t="inlineStr"><is><t>ceftriaksonu</t></is></c><c r="G586" s="2" t="inlineStr"><is><t>cefoperazonu</t></is></c><c r="H586" s="2" t="inlineStr" /><c r="I586" s="2" t="inlineStr" /><c r="J586" s="2" t="inlineStr" /><c r="K586" s="2" t="inlineStr"><is><t>ceftazydymu</t></is></c><c r="L586" s="2" t="inlineStr"><is><t>cefepimu</t></is></c><c r="M586" s="2" t="inlineStr" /><c r="N586" s="2" t="inlineStr" /><c r="O586" s="2" t="inlineStr" /><c r="P586" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2018/19</t></is></c><c r="Q586" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="587"><c r="A587" s="2" t="inlineStr"><is><t>TARCZYCA</t></is></c><c r="B587" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C587" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D587" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E587" s="2" t="inlineStr"><is><t>Profilaktyczne zastosowanie leków przeciwinfekcyjnych jest uzasadnione:</t></is></c><c r="F587" s="2" t="inlineStr"><is><t>w planowej operacji zmniejszenia żołądka w leczeniu otyłości olbrzymiej(pole czyste-skażone)</t></is></c><c r="G587" s="2" t="inlineStr"><is><t>w planowej implantacji sztucznej protezy stawu biodrowego (pole czyste)</t></is></c><c r="H587" s="2" t="inlineStr" /><c r="I587" s="2" t="inlineStr" /><c r="J587" s="2" t="inlineStr" /><c r="K587" s="2" t="inlineStr"><is><t>w planowym usunięciu znamienia skórnego do diagnostyki histo-patologicznej (pole czyste)</t></is></c><c r="L587" s="2" t="inlineStr"><is><t>w planowym usunięciu tarczycy w wolu guzkowym nadczynnym (pole czyste)</t></is></c><c r="M587" s="2" t="inlineStr" /><c r="N587" s="2" t="inlineStr" /><c r="O587" s="2" t="inlineStr" /><c r="P587" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2018/19</t></is></c><c r="Q587" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="588"><c r="A588" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B588" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C588" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D588" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E588" s="2" t="inlineStr"><is><t>Jaki lek można opisać w następujący sposób: ma działanie bójcze, jego celem farmakodynamicznym jest jak największy stosunek AUC24:MIC i łatwa jest jego sekwencja do stosowania doustnego:</t></is></c><c r="F588" s="2" t="inlineStr"><is><t>Lewofloksacyna</t></is></c><c r="G588" s="2" t="inlineStr" /><c r="H588" s="2" t="inlineStr" /><c r="I588" s="2" t="inlineStr" /><c r="J588" s="2" t="inlineStr" /><c r="K588" s="2" t="inlineStr"><is><t>Neomycyna</t></is></c><c r="L588" s="2" t="inlineStr"><is><t>Wankomycyna</t></is></c><c r="M588" s="2" t="inlineStr"><is><t>Klarytromycyna</t></is></c><c r="N588" s="2" t="inlineStr" /><c r="O588" s="2" t="inlineStr" /><c r="P588" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2018/19</t></is></c><c r="Q588" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="589"><c r="A589" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B589" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C589" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D589" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E589" s="2" t="inlineStr"><is><t>Które stwierdzenie jest prawdziwe w leczeniu zakażeń?</t></is></c><c r="F589" s="2" t="inlineStr"><is><t>leki przeciwinfekcyjne są jedynie uzupełnieniem leczenia zabiegowego w postaci aspiracji lub drenażu w przypadku ropni i ropniaków</t></is></c><c r="G589" s="2" t="inlineStr"><is><t>leczenie zakażenia w obrębie tylnej komory oka (szklistki) wymaga podania leków przeciwinfekcyjnych doszklistkowo</t></is></c><c r="H589" s="2" t="inlineStr"><is><t>nie jest możliwe wyleczenia „zakażenia” sztucznych materiałów: protez, cewników, sztucznych zastawek</t></is></c><c r="I589" s="2" t="inlineStr"><is><t>w przewlekłym zapaleniu zatok konieczne jest chirurgiczna korekta nieprawidłowości anatomicznych, tj. polip czy, skrzywienie przegrody nosa</t></is></c><c r="J589" s="2" t="inlineStr" /><c r="K589" s="2" t="inlineStr" /><c r="L589" s="2" t="inlineStr" /><c r="M589" s="2" t="inlineStr" /><c r="N589" s="2" t="inlineStr" /><c r="O589" s="2" t="inlineStr" /><c r="P589" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2018/19</t></is></c><c r="Q589" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="590"><c r="A590" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B590" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C590" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D590" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E590" s="2" t="inlineStr"><is><t>U pacjenta z podejrzeniem atypowego zakażenia układu oddechowego, stosującego na co dzień leki z grupy inhibitorów reduktazy HMG-CoA (pacjent nie pamięta nazwy leku), planujesz włączyć antybiotyk makrolidowy. Za bezpieczną opcję terapeutyczną w tej sytuacji uznasz:</t></is></c><c r="F590" s="2" t="inlineStr"><is><t>azytromycynę</t></is></c><c r="G590" s="2" t="inlineStr" /><c r="H590" s="2" t="inlineStr" /><c r="I590" s="2" t="inlineStr" /><c r="J590" s="2" t="inlineStr" /><c r="K590" s="2" t="inlineStr"><is><t>klarytromycynę</t></is></c><c r="L590" s="2" t="inlineStr"><is><t>telitromycynę</t></is></c><c r="M590" s="2" t="inlineStr"><is><t>erytromycynę</t></is></c><c r="N590" s="2" t="inlineStr" /><c r="O590" s="2" t="inlineStr" /><c r="P590" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2018/19</t></is></c><c r="Q590" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="591"><c r="A591" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B591" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C591" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D591" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E591" s="2" t="inlineStr"><is><t>Wskaż prawidłowe zestawienia lek-działanie niepożądane:</t></is></c><c r="F591" s="2" t="inlineStr"><is><t>izoniazyd – toczeń polekowy</t></is></c><c r="G591" s="2" t="inlineStr"><is><t>pirazynamid– hiperurikemia</t></is></c><c r="H591" s="2" t="inlineStr"><is><t>ryfampicyna – małopłytkowość</t></is></c><c r="I591" s="2" t="inlineStr"><is><t>etambutol – pozagałkowe zapalenie nerwu wzrokowego</t></is></c><c r="J591" s="2" t="inlineStr" /><c r="K591" s="2" t="inlineStr" /><c r="L591" s="2" t="inlineStr" /><c r="M591" s="2" t="inlineStr" /><c r="N591" s="2" t="inlineStr" /><c r="O591" s="2" t="inlineStr" /><c r="P591" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2018/19</t></is></c><c r="Q591" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="592"><c r="A592" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B592" s="2" t="inlineStr"><is><t>Interakcje</t></is></c><c r="C592" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D592" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E592" s="2" t="inlineStr"><is><t>Leki przeciwbakteryjne o wysokim potencjale do selekcji szczepów Clostridium difficile to:</t></is></c><c r="F592" s="2" t="inlineStr"><is><t>klindamycyna</t></is></c><c r="G592" s="2" t="inlineStr"><is><t>cyprofloksacyna</t></is></c><c r="H592" s="2" t="inlineStr" /><c r="I592" s="2" t="inlineStr" /><c r="J592" s="2" t="inlineStr" /><c r="K592" s="2" t="inlineStr"><is><t>wankomycyna</t></is></c><c r="L592" s="2" t="inlineStr"><is><t>fidaksomycyna</t></is></c><c r="M592" s="2" t="inlineStr" /><c r="N592" s="2" t="inlineStr" /><c r="O592" s="2" t="inlineStr" /><c r="P592" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2018/19</t></is></c><c r="Q592" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="593"><c r="A593" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B593" s="2" t="inlineStr"><is><t>Farmakokinetyka</t></is></c><c r="C593" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D593" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E593" s="2" t="inlineStr"><is><t>Pacjent leczony jest dożylnie lekiem, którego farmakokinetyka opisana jest następująco: słabo wchłania się z przewodu pokarmowego, podlega ograniczonej dystrybucji do tkanek, nie jest metabolizowany (bądź jest metabolizowany w minimalnym stopniu), wydalany jest głównie przez nerki. Lekiem tym może być:</t></is></c><c r="F593" s="2" t="inlineStr"><is><t>wankomycyna</t></is></c><c r="G593" s="2" t="inlineStr"><is><t>kolistymetat sodu</t></is></c><c r="H593" s="2" t="inlineStr"><is><t>amikacyna</t></is></c><c r="I593" s="2" t="inlineStr" /><c r="J593" s="2" t="inlineStr" /><c r="K593" s="2" t="inlineStr"><is><t>erytromycyna</t></is></c><c r="L593" s="2" t="inlineStr" /><c r="M593" s="2" t="inlineStr" /><c r="N593" s="2" t="inlineStr" /><c r="O593" s="2" t="inlineStr" /><c r="P593" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2018/19</t></is></c><c r="Q593" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="594"><c r="A594" s="2" t="inlineStr"><is><t>LEKI PRZECIWGRZYBICZE</t></is></c><c r="B594" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C594" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D594" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E594" s="2" t="inlineStr"><is><t>W leczeniu inwazyjnej aspergilozy znalazły zastosowanie:</t></is></c><c r="F594" s="2" t="inlineStr"><is><t>amfoterycyna B podawana dożylnie</t></is></c><c r="G594" s="2" t="inlineStr"><is><t>worykonazol podawany dożylnie</t></is></c><c r="H594" s="2" t="inlineStr" /><c r="I594" s="2" t="inlineStr" /><c r="J594" s="2" t="inlineStr" /><c r="K594" s="2" t="inlineStr"><is><t>kaspofungina podawana doustnie</t></is></c><c r="L594" s="2" t="inlineStr"><is><t>terbinafina podawana doustnie</t></is></c><c r="M594" s="2" t="inlineStr" /><c r="N594" s="2" t="inlineStr" /><c r="O594" s="2" t="inlineStr" /><c r="P594" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2018/19</t></is></c><c r="Q594" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="595"><c r="A595" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B595" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C595" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D595" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E595" s="2" t="inlineStr"><is><t>Dobrą dystrybucją do ośrodkowego układu nerwowego charakteryzuje się:</t></is></c><c r="F595" s="2" t="inlineStr"><is><t>ceftriakson</t></is></c><c r="G595" s="2" t="inlineStr"><is><t>linezolid</t></is></c><c r="H595" s="2" t="inlineStr"><is><t>flukonazol</t></is></c><c r="I595" s="2" t="inlineStr" /><c r="J595" s="2" t="inlineStr" /><c r="K595" s="2" t="inlineStr"><is><t>kaspofungina</t></is></c><c r="L595" s="2" t="inlineStr" /><c r="M595" s="2" t="inlineStr" /><c r="N595" s="2" t="inlineStr" /><c r="O595" s="2" t="inlineStr" /><c r="P595" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2018/19</t></is></c><c r="Q595" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="596"><c r="A596" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B596" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C596" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D596" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E596" s="2" t="inlineStr"><is><t>W schematach eradykacji Helicobacter pylori są stosowane:</t></is></c><c r="F596" s="2" t="inlineStr"><is><t>klarytromycyna</t></is></c><c r="G596" s="2" t="inlineStr"><is><t>Amoksycylina</t></is></c><c r="H596" s="2" t="inlineStr"><is><t>metronidazol</t></is></c><c r="I596" s="2" t="inlineStr"><is><t>tetracyklina</t></is></c><c r="J596" s="2" t="inlineStr" /><c r="K596" s="2" t="inlineStr" /><c r="L596" s="2" t="inlineStr" /><c r="M596" s="2" t="inlineStr" /><c r="N596" s="2" t="inlineStr" /><c r="O596" s="2" t="inlineStr" /><c r="P596" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2018/19</t></is></c><c r="Q596" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="597"><c r="A597" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B597" s="2" t="inlineStr"><is><t>Ciąża</t></is></c><c r="C597" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D597" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E597" s="2" t="inlineStr"><is><t>U kobiety w ciąży z rumieniem wędrującym można zastosować:</t></is></c><c r="F597" s="2" t="inlineStr"><is><t>azytromycynę</t></is></c><c r="G597" s="2" t="inlineStr"><is><t>amoksycylinę</t></is></c><c r="H597" s="2" t="inlineStr" /><c r="I597" s="2" t="inlineStr" /><c r="J597" s="2" t="inlineStr" /><c r="K597" s="2" t="inlineStr"><is><t>doksycyklinę</t></is></c><c r="L597" s="2" t="inlineStr"><is><t>klindamycynę</t></is></c><c r="M597" s="2" t="inlineStr" /><c r="N597" s="2" t="inlineStr" /><c r="O597" s="2" t="inlineStr" /><c r="P597" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2018/19</t></is></c><c r="Q597" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="598"><c r="A598" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B598" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C598" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D598" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E598" s="2" t="inlineStr"><is><t>Syntezę ściany komórkowej hamuje:</t></is></c><c r="F598" s="2" t="inlineStr"><is><t>fosfomycyna</t></is></c><c r="G598" s="2" t="inlineStr"><is><t>mykafungina</t></is></c><c r="H598" s="2" t="inlineStr"><is><t>teikoplanina</t></is></c><c r="I598" s="2" t="inlineStr" /><c r="J598" s="2" t="inlineStr" /><c r="K598" s="2" t="inlineStr"><is><t>nystatyna</t></is></c><c r="L598" s="2" t="inlineStr" /><c r="M598" s="2" t="inlineStr" /><c r="N598" s="2" t="inlineStr" /><c r="O598" s="2" t="inlineStr" /><c r="P598" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2018/19</t></is></c><c r="Q598" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="599"><c r="A599" s="2" t="inlineStr"><is><t>LEKI PRZECIWGRZYBICZE</t></is></c><c r="B599" s="2" t="inlineStr"><is><t>Interakcje</t></is></c><c r="C599" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D599" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E599" s="2" t="inlineStr"><is><t>Wskaż prawidłowe stwierdzenie:</t></is></c><c r="F599" s="2" t="inlineStr"><is><t>worykonazol jest istotnym klinicznie inhibitorem CYP3A4</t></is></c><c r="G599" s="2" t="inlineStr"><is><t>posakonazol hamuje syntezę ergosterolu</t></is></c><c r="H599" s="2" t="inlineStr" /><c r="I599" s="2" t="inlineStr" /><c r="J599" s="2" t="inlineStr" /><c r="K599" s="2" t="inlineStr"><is><t>flukonazol wykazuje aktywność wobec Aspergillus spp</t></is></c><c r="L599" s="2" t="inlineStr"><is><t>itrakonazol bardzo dobrze wchłania się z przewodu pokarmowego</t></is></c><c r="M599" s="2" t="inlineStr" /><c r="N599" s="2" t="inlineStr" /><c r="O599" s="2" t="inlineStr" /><c r="P599" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2018/19</t></is></c><c r="Q599" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="600"><c r="A600" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B600" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C600" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D600" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E600" s="2" t="inlineStr"><is><t>W zakażeniu o etiologii MRSA(methicyllin-resistant Staphylococcus aureus) zasadne jest zastosowanie:</t></is></c><c r="F600" s="2" t="inlineStr"><is><t>ceftaroliny</t></is></c><c r="G600" s="2" t="inlineStr"><is><t>linezolidu</t></is></c><c r="H600" s="2" t="inlineStr" /><c r="I600" s="2" t="inlineStr" /><c r="J600" s="2" t="inlineStr" /><c r="K600" s="2" t="inlineStr"><is><t>kloksacyliny</t></is></c><c r="L600" s="2" t="inlineStr"><is><t>meropenemu</t></is></c><c r="M600" s="2" t="inlineStr" /><c r="N600" s="2" t="inlineStr" /><c r="O600" s="2" t="inlineStr" /><c r="P600" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2018/19</t></is></c><c r="Q600" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="601"><c r="A601" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B601" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C601" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D601" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E601" s="2" t="inlineStr"><is><t>W biegunce o etiologii Clostridium difficile uzasadnione może być podanie doustne:</t></is></c><c r="F601" s="2" t="inlineStr"><is><t>wankomycyny</t></is></c><c r="G601" s="2" t="inlineStr"><is><t>metronidazolu</t></is></c><c r="H601" s="2" t="inlineStr"><is><t>fidaksomycyny</t></is></c><c r="I601" s="2" t="inlineStr" /><c r="J601" s="2" t="inlineStr" /><c r="K601" s="2" t="inlineStr"><is><t>nifuroksazydu</t></is></c><c r="L601" s="2" t="inlineStr" /><c r="M601" s="2" t="inlineStr" /><c r="N601" s="2" t="inlineStr" /><c r="O601" s="2" t="inlineStr" /><c r="P601" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2018/19</t></is></c><c r="Q601" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="602"><c r="A602" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B602" s="2" t="inlineStr"><is><t>Interakcje</t></is></c><c r="C602" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D602" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E602" s="2" t="inlineStr"><is><t>Wskaż właściwe skojarzenie lek – potencjalne działanie niepożądane:</t></is></c><c r="F602" s="2" t="inlineStr"><is><t>chloramfenikol – zespół szarego dziecka</t></is></c><c r="G602" s="2" t="inlineStr"><is><t>doksycyklina - fotodermatoza</t></is></c><c r="H602" s="2" t="inlineStr" /><c r="I602" s="2" t="inlineStr" /><c r="J602" s="2" t="inlineStr" /><c r="K602" s="2" t="inlineStr"><is><t>gentamycyna - żółtaczka cholestatyczna</t></is></c><c r="L602" s="2" t="inlineStr"><is><t>klindamycyna – zespół serotoninowy</t></is></c><c r="M602" s="2" t="inlineStr" /><c r="N602" s="2" t="inlineStr" /><c r="O602" s="2" t="inlineStr" /><c r="P602" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2018/19</t></is></c><c r="Q602" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="603"><c r="A603" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B603" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C603" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D603" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E603" s="2" t="inlineStr"><is><t>Zaburzenia rytmu serca mogą wystąpić w trakcie stosowania:</t></is></c><c r="F603" s="2" t="inlineStr"><is><t>moksyfloksacyny</t></is></c><c r="G603" s="2" t="inlineStr"><is><t>klarytromycyny</t></is></c><c r="H603" s="2" t="inlineStr" /><c r="I603" s="2" t="inlineStr" /><c r="J603" s="2" t="inlineStr" /><c r="K603" s="2" t="inlineStr"><is><t>fidaksomycyny</t></is></c><c r="L603" s="2" t="inlineStr"><is><t>Mupirocyny</t></is></c><c r="M603" s="2" t="inlineStr" /><c r="N603" s="2" t="inlineStr" /><c r="O603" s="2" t="inlineStr" /><c r="P603" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2018/19</t></is></c><c r="Q603" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="604"><c r="A604" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B604" s="2" t="inlineStr"><is><t>Interakcje</t></is></c><c r="C604" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D604" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E604" s="2" t="inlineStr"><is><t>Wskaż prawidłowe skojarzenie lek – wskazanie:</t></is></c><c r="F604" s="2" t="inlineStr"><is><t>spiramycyna – toksoplazmoza</t></is></c><c r="G604" s="2" t="inlineStr"><is><t>fenoksymetylopenicylina – angina paciorkowcowa</t></is></c><c r="H604" s="2" t="inlineStr"><is><t>metronidazol - lamblioza</t></is></c><c r="I604" s="2" t="inlineStr" /><c r="J604" s="2" t="inlineStr" /><c r="K604" s="2" t="inlineStr"><is><t>neomycyna – biegunka poantybiotykowa</t></is></c><c r="L604" s="2" t="inlineStr" /><c r="M604" s="2" t="inlineStr" /><c r="N604" s="2" t="inlineStr" /><c r="O604" s="2" t="inlineStr" /><c r="P604" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2018/19</t></is></c><c r="Q604" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="605"><c r="A605" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B605" s="2" t="inlineStr"><is><t>Farmakokinetyka</t></is></c><c r="C605" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D605" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E605" s="2" t="inlineStr"><is><t>Kolistymetat sodu:</t></is></c><c r="F605" s="2" t="inlineStr"><is><t>jest prolekiem</t></is></c><c r="G605" s="2" t="inlineStr"><is><t>jest zarezerwowany do leczenia zakażeń szczepami wielolekoopornymi G(-)</t></is></c><c r="H605" s="2" t="inlineStr" /><c r="I605" s="2" t="inlineStr" /><c r="J605" s="2" t="inlineStr" /><c r="K605" s="2" t="inlineStr"><is><t>działa na VRE (Vancomycin-Resistant Enterococcus)</t></is></c><c r="L605" s="2" t="inlineStr"><is><t>dobrze wchłania się z przewodu pokarmowego</t></is></c><c r="M605" s="2" t="inlineStr" /><c r="N605" s="2" t="inlineStr" /><c r="O605" s="2" t="inlineStr" /><c r="P605" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2018/19</t></is></c><c r="Q605" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="606"><c r="A606" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B606" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C606" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D606" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E606" s="2" t="inlineStr"><is><t>Działanie neurotoksyczne wykazuje:</t></is></c><c r="F606" s="2" t="inlineStr"><is><t>linezolid</t></is></c><c r="G606" s="2" t="inlineStr"><is><t>cyprofloksacyna</t></is></c><c r="H606" s="2" t="inlineStr"><is><t>kolistyna</t></is></c><c r="I606" s="2" t="inlineStr"><is><t>metronidazol</t></is></c><c r="J606" s="2" t="inlineStr" /><c r="K606" s="2" t="inlineStr" /><c r="L606" s="2" t="inlineStr" /><c r="M606" s="2" t="inlineStr" /><c r="N606" s="2" t="inlineStr" /><c r="O606" s="2" t="inlineStr" /><c r="P606" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2018/19</t></is></c><c r="Q606" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="607"><c r="A607" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B607" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C607" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D607" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E607" s="2" t="inlineStr"><is><t>Tygecyklina:</t></is></c><c r="F607" s="2" t="inlineStr"><is><t>jest stosowana w wewnątrzbrzusznych zakażeniach szczepami wielolekoopornymi</t></is></c><c r="G607" s="2" t="inlineStr" /><c r="H607" s="2" t="inlineStr" /><c r="I607" s="2" t="inlineStr" /><c r="J607" s="2" t="inlineStr" /><c r="K607" s="2" t="inlineStr"><is><t>dobrze wchłania się z przewodu pokarmowego</t></is></c><c r="L607" s="2" t="inlineStr"><is><t>bardzo często jest przyczyną zapalenia ścięgna Achillesa</t></is></c><c r="M607" s="2" t="inlineStr"><is><t>działa na Pseudomonas aeruginosa</t></is></c><c r="N607" s="2" t="inlineStr" /><c r="O607" s="2" t="inlineStr" /><c r="P607" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2018/19</t></is></c><c r="Q607" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="608"><c r="A608" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B608" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C608" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D608" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E608" s="2" t="inlineStr"><is><t>Daptomycyna może być skuteczna w zakażeniach szczepami:</t></is></c><c r="F608" s="2" t="inlineStr"><is><t>MRSA (methicyllin-resistant Staphylococcus aureus)</t></is></c><c r="G608" s="2" t="inlineStr"><is><t>MSSA (methicillin-sensitive Staphylococcus aureus)</t></is></c><c r="H608" s="2" t="inlineStr"><is><t>VRE (Vancomycin-Resistant Enterococcus)</t></is></c><c r="I608" s="2" t="inlineStr" /><c r="J608" s="2" t="inlineStr" /><c r="K608" s="2" t="inlineStr"><is><t>CPE (Carbapenemase-producing Enterobacteriaceae)</t></is></c><c r="L608" s="2" t="inlineStr" /><c r="M608" s="2" t="inlineStr" /><c r="N608" s="2" t="inlineStr" /><c r="O608" s="2" t="inlineStr" /><c r="P608" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2018/19</t></is></c><c r="Q608" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="609"><c r="A609" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B609" s="2" t="inlineStr"><is><t>Interakcje</t></is></c><c r="C609" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D609" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E609" s="2" t="inlineStr"><is><t>Wskaż prawidłowe skojarzenie lek – mechanizm działania:</t></is></c><c r="F609" s="2" t="inlineStr"><is><t>plazomycyna – hamuje syntezę białek</t></is></c><c r="G609" s="2" t="inlineStr" /><c r="H609" s="2" t="inlineStr" /><c r="I609" s="2" t="inlineStr" /><c r="J609" s="2" t="inlineStr" /><c r="K609" s="2" t="inlineStr"><is><t>dalbawancyna – hamuje syntezy DNA</t></is></c><c r="L609" s="2" t="inlineStr"><is><t>spiramycyna – hamuje syntezę RNA</t></is></c><c r="M609" s="2" t="inlineStr"><is><t>telitromycyna – hamuje syntezę ściany komórkowej</t></is></c><c r="N609" s="2" t="inlineStr" /><c r="O609" s="2" t="inlineStr" /><c r="P609" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2018/19</t></is></c><c r="Q609" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="610"><c r="A610" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B610" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C610" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D610" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E610" s="2" t="inlineStr"><is><t>Do bezpiecznych i skutecznych środków do dezynfekcji należą:</t></is></c><c r="F610" s="2" t="inlineStr"><is><t>oktenidyna</t></is></c><c r="G610" s="2" t="inlineStr" /><c r="H610" s="2" t="inlineStr" /><c r="I610" s="2" t="inlineStr" /><c r="J610" s="2" t="inlineStr" /><c r="K610" s="2" t="inlineStr"><is><t>woda utleniona</t></is></c><c r="L610" s="2" t="inlineStr"><is><t>spirytusowy roztwór fioletu gencjanowego</t></is></c><c r="M610" s="2" t="inlineStr"><is><t>mleczan etakrydyny</t></is></c><c r="N610" s="2" t="inlineStr" /><c r="O610" s="2" t="inlineStr" /><c r="P610" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2018/19</t></is></c><c r="Q610" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="611"><c r="A611" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B611" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C611" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D611" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E611" s="2" t="inlineStr"><is><t>Lewofloksacyna:</t></is></c><c r="F611" s="2" t="inlineStr"><is><t>wykazuje aktywność wobec Streptococcus pneumoniae</t></is></c><c r="G611" s="2" t="inlineStr"><is><t>wykazuje aktywność wobec Legionella pneumophila</t></is></c><c r="H611" s="2" t="inlineStr" /><c r="I611" s="2" t="inlineStr" /><c r="J611" s="2" t="inlineStr" /><c r="K611" s="2" t="inlineStr"><is><t>ma taki sam zakres działania jak moksyfloksacyna</t></is></c><c r="L611" s="2" t="inlineStr"><is><t>nie działa na Pseudomonas aeruginosa</t></is></c><c r="M611" s="2" t="inlineStr" /><c r="N611" s="2" t="inlineStr" /><c r="O611" s="2" t="inlineStr" /><c r="P611" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2018/19</t></is></c><c r="Q611" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="612"><c r="A612" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B612" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C612" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D612" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E612" s="2" t="inlineStr"><is><t>W przypadku rozpoznania anginy paciorkowcowej u osoby uczulonej na antybiotyki beta￾laktamowe, można zastosować:</t></is></c><c r="F612" s="2" t="inlineStr"><is><t>klindamycynę</t></is></c><c r="G612" s="2" t="inlineStr"><is><t>azytromycynę</t></is></c><c r="H612" s="2" t="inlineStr" /><c r="I612" s="2" t="inlineStr" /><c r="J612" s="2" t="inlineStr" /><c r="K612" s="2" t="inlineStr"><is><t>norfloksacynę</t></is></c><c r="L612" s="2" t="inlineStr"><is><t>kloksacylinę</t></is></c><c r="M612" s="2" t="inlineStr" /><c r="N612" s="2" t="inlineStr" /><c r="O612" s="2" t="inlineStr" /><c r="P612" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2018/19</t></is></c><c r="Q612" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="613"><c r="A613" s="2" t="inlineStr"><is><t>LEKI PRZECIWWIRUSOWE</t></is></c><c r="B613" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C613" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D613" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E613" s="2" t="inlineStr"><is><t>Wskaż prawidłowe połączenie:</t></is></c><c r="F613" s="2" t="inlineStr"><is><t>owsica – pyrantel, WZW C (wirusowe zapalenie wątroby typu C) – daklataswir</t></is></c><c r="G613" s="2" t="inlineStr"><is><t>wszawica – permetryna, CMV – walgancyklowir</t></is></c><c r="H613" s="2" t="inlineStr" /><c r="I613" s="2" t="inlineStr" /><c r="J613" s="2" t="inlineStr" /><c r="K613" s="2" t="inlineStr"><is><t>CMV (cytomegalovirus) – acyklowir, owsica – pyrantel</t></is></c><c r="L613" s="2" t="inlineStr"><is><t>acyklowir – HSV-2 (herpes simplex 2), amantadyna – profilaktyka grypy typu B</t></is></c><c r="M613" s="2" t="inlineStr" /><c r="N613" s="2" t="inlineStr" /><c r="O613" s="2" t="inlineStr" /><c r="P613" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2018/19</t></is></c><c r="Q613" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="614"><c r="A614" s="2" t="inlineStr"><is><t>NADCIŚNIENIE TĘTNICZE</t></is></c><c r="B614" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C614" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D614" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E614" s="2" t="inlineStr"><is><t>Które pary leków mających ten sam zasadniczy mechanizm działania różnią się istotnie profilem działań klinicznych?</t></is></c><c r="F614" s="2" t="inlineStr"><is><t>werapamil i nitrendypina</t></is></c><c r="G614" s="2" t="inlineStr"><is><t>doksazosyna i tamsulozyna</t></is></c><c r="H614" s="2" t="inlineStr"><is><t>spironolakton i eplerenon</t></is></c><c r="I614" s="2" t="inlineStr" /><c r="J614" s="2" t="inlineStr" /><c r="K614" s="2" t="inlineStr"><is><t>moksonidyna i rylmenidyna</t></is></c><c r="L614" s="2" t="inlineStr" /><c r="M614" s="2" t="inlineStr" /><c r="N614" s="2" t="inlineStr" /><c r="O614" s="2" t="inlineStr" /><c r="P614" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2018/19</t></is></c><c r="Q614" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="615"><c r="A615" s="2" t="inlineStr"><is><t>ZABURZENIA RYTMU SERCA</t></is></c><c r="B615" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C615" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D615" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E615" s="2" t="inlineStr"><is><t>Amiodaron:</t></is></c><c r="F615" s="2" t="inlineStr"><is><t>ma niezgodność farmaceutyczną z 0,9% NaCl</t></is></c><c r="G615" s="2" t="inlineStr"><is><t>ma działanie chronotropowe ujemne i hipotensyjne</t></is></c><c r="H615" s="2" t="inlineStr" /><c r="I615" s="2" t="inlineStr" /><c r="J615" s="2" t="inlineStr" /><c r="K615" s="2" t="inlineStr"><is><t>to niewybiórczy antagonista kanałów potasowych wiążący się z nimi w okresie ich otwarcia</t></is></c><c r="L615" s="2" t="inlineStr"><is><t>zwiększa próg defibrylacji elektrycznej</t></is></c><c r="M615" s="2" t="inlineStr" /><c r="N615" s="2" t="inlineStr" /><c r="O615" s="2" t="inlineStr" /><c r="P615" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2018/19</t></is></c><c r="Q615" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="616"><c r="A616" s="2" t="inlineStr"><is><t>NADCIŚNIENIE TĘTNICZE</t></is></c><c r="B616" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C616" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D616" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E616" s="2" t="inlineStr"><is><t>Do leków aktywujących pośrednio lub bezpośrednio cyklazę guanylową komórek mięśniówki gładkiej naczyń należy:</t></is></c><c r="F616" s="2" t="inlineStr"><is><t>nitroprusydek sodu</t></is></c><c r="G616" s="2" t="inlineStr"><is><t>riocyguat</t></is></c><c r="H616" s="2" t="inlineStr"><is><t>sakubitryl</t></is></c><c r="I616" s="2" t="inlineStr" /><c r="J616" s="2" t="inlineStr" /><c r="K616" s="2" t="inlineStr"><is><t>wardenafil</t></is></c><c r="L616" s="2" t="inlineStr" /><c r="M616" s="2" t="inlineStr" /><c r="N616" s="2" t="inlineStr" /><c r="O616" s="2" t="inlineStr" /><c r="P616" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2018/19</t></is></c><c r="Q616" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="617"><c r="A617" s="2" t="inlineStr"><is><t>NIEWYDOLNOŚĆ SERCA</t></is></c><c r="B617" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C617" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D617" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E617" s="2" t="inlineStr"><is><t>Czy zaproponowany wlew poszczególnych amin katecholowych jest adekwatny na początku leczenia (wybierz najmniejszą dawkę zalecaną) u pacjenta z przedstawionym rozpoznaniem?</t></is></c><c r="F617" s="2" t="inlineStr"><is><t>pacjent = 50 kg z ostrą niewydolnością serca i ciśnieniem skurczowym 85 mmHg – dopamina 200 mg/40 ml 0,9% NaCl → wlew = 3 ml/h</t></is></c><c r="G617" s="2" t="inlineStr"><is><t>pacjent = 100 kg we wstrząsie septycznym z ciśnieniem skurczowym 60 mmHg – noradrenalina 4 mg/40 ml 0,9% NaCl → wlew = 12 ml/h</t></is></c><c r="H617" s="2" t="inlineStr"><is><t>pacjent = 50 kg z zaostrzeniem przewlekłej niewydolności serca skurczowym 105 mmHg – dobutamina 250 mg/50 ml 0,9% NaCl → wlew =1,2 ml/h</t></is></c><c r="I617" s="2" t="inlineStr" /><c r="J617" s="2" t="inlineStr" /><c r="K617" s="2" t="inlineStr"><is><t>pacjent = 100 kg z ostrą niewydolnością serca i ciśnieniem skurczowym 80 mmHg – dobutamina 250 mg/50 ml 0,9% NaCl → wlew = 2,4 ml/h</t></is></c><c r="L617" s="2" t="inlineStr" /><c r="M617" s="2" t="inlineStr" /><c r="N617" s="2" t="inlineStr" /><c r="O617" s="2" t="inlineStr" /><c r="P617" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2018/19</t></is></c><c r="Q617" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="618"><c r="A618" s="2" t="inlineStr"><is><t>ZABURZENIA RYTMU SERCA</t></is></c><c r="B618" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C618" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D618" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E618" s="2" t="inlineStr"><is><t>Wskaż lek o bardzo krótkim okresie półtrwania (&lt;5 min), który z tego powodu wymaga stosowania we wlewie dożylnym lub jest wykorzystywany w celu osiągnięcia błyskawicznego krótkotrwałego efektu terapeutycznego:</t></is></c><c r="F618" s="2" t="inlineStr"><is><t>esmolol</t></is></c><c r="G618" s="2" t="inlineStr"><is><t>sukcynylocholina</t></is></c><c r="H618" s="2" t="inlineStr"><is><t>adenozyna</t></is></c><c r="I618" s="2" t="inlineStr" /><c r="J618" s="2" t="inlineStr" /><c r="K618" s="2" t="inlineStr"><is><t>diazepam</t></is></c><c r="L618" s="2" t="inlineStr" /><c r="M618" s="2" t="inlineStr" /><c r="N618" s="2" t="inlineStr" /><c r="O618" s="2" t="inlineStr" /><c r="P618" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2018/19</t></is></c><c r="Q618" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="619"><c r="A619" s="2" t="inlineStr"><is><t>UKŁAD ODDECHOWY</t></is></c><c r="B619" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C619" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D619" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E619" s="2" t="inlineStr"><is><t>Wskaż poprawną kombinację terapeutyczną w leczeniu zapalnego kaszlu w infekcji oskrzeli:</t></is></c><c r="F619" s="2" t="inlineStr"><is><t>ambroksol w nebulizacji + acetylocysteina doustnie</t></is></c><c r="G619" s="2" t="inlineStr" /><c r="H619" s="2" t="inlineStr" /><c r="I619" s="2" t="inlineStr" /><c r="J619" s="2" t="inlineStr" /><c r="K619" s="2" t="inlineStr"><is><t>wazycyna doustnie + 10% NaCl w nebulizacji</t></is></c><c r="L619" s="2" t="inlineStr"><is><t>sulfagwajakol + kodeina w doustnym preparacie złożonym</t></is></c><c r="M619" s="2" t="inlineStr"><is><t>dornaza alfa w inhalacjach + erdosteina doustnie</t></is></c><c r="N619" s="2" t="inlineStr" /><c r="O619" s="2" t="inlineStr" /><c r="P619" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2018/19</t></is></c><c r="Q619" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="620"><c r="A620" s="2" t="inlineStr"><is><t>UKŁAD ODDECHOWY</t></is></c><c r="B620" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C620" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D620" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E620" s="2" t="inlineStr"><is><t>W napadzie duszności u osoby z cechami skurczu oskrzeli (cichy szmer pęcherzykowy, głośne świsty, wydłużona faza wydechu) w celu przerwania napadu zasadne jest zastosowanie:</t></is></c><c r="F620" s="2" t="inlineStr"><is><t>salbutamolu wziewnie w nebulizacji</t></is></c><c r="G620" s="2" t="inlineStr"><is><t>bromku ipratropium wziewnie w nebulizacji</t></is></c><c r="H620" s="2" t="inlineStr" /><c r="I620" s="2" t="inlineStr" /><c r="J620" s="2" t="inlineStr" /><c r="K620" s="2" t="inlineStr"><is><t>triazotanu glicerolu w aerozolu na błonę śluzową jamy ustnej</t></is></c><c r="L620" s="2" t="inlineStr"><is><t>cyklezonidu wziewnie z inhalatora aerozolowego</t></is></c><c r="M620" s="2" t="inlineStr" /><c r="N620" s="2" t="inlineStr" /><c r="O620" s="2" t="inlineStr" /><c r="P620" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2018/19</t></is></c><c r="Q620" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="621"><c r="A621" s="2" t="inlineStr"><is><t>NADCIŚNIENIE TĘTNICZE</t></is></c><c r="B621" s="2" t="inlineStr"><is><t>Farmakokinetyka</t></is></c><c r="C621" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D621" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E621" s="2" t="inlineStr"><is><t>Który lek ma w swojej grupie farmakologicznej nietypową, wyróżniającą go farmakokinetykę:</t></is></c><c r="F621" s="2" t="inlineStr"><is><t>cyklezonid</t></is></c><c r="G621" s="2" t="inlineStr"><is><t>amlodypina</t></is></c><c r="H621" s="2" t="inlineStr" /><c r="I621" s="2" t="inlineStr" /><c r="J621" s="2" t="inlineStr" /><c r="K621" s="2" t="inlineStr"><is><t>metoprolol</t></is></c><c r="L621" s="2" t="inlineStr"><is><t>iwabradyna</t></is></c><c r="M621" s="2" t="inlineStr" /><c r="N621" s="2" t="inlineStr" /><c r="O621" s="2" t="inlineStr" /><c r="P621" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2018/19</t></is></c><c r="Q621" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="622"><c r="A622" s="2" t="inlineStr"><is><t>UKŁAD WSPÓŁCZULNY</t></is></c><c r="B622" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C622" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D622" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E622" s="2" t="inlineStr"><is><t>Lekiem stosowanym „ratunkowo” w poważnych powikłaniach polekowych jest:</t></is></c><c r="F622" s="2" t="inlineStr"><is><t>adrenalina</t></is></c><c r="G622" s="2" t="inlineStr"><is><t>półbursztynian hydrokortyzonu</t></is></c><c r="H622" s="2" t="inlineStr"><is><t>dantrolen</t></is></c><c r="I622" s="2" t="inlineStr"><is><t>acetylocysteina</t></is></c><c r="J622" s="2" t="inlineStr" /><c r="K622" s="2" t="inlineStr" /><c r="L622" s="2" t="inlineStr" /><c r="M622" s="2" t="inlineStr" /><c r="N622" s="2" t="inlineStr" /><c r="O622" s="2" t="inlineStr" /><c r="P622" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2018/19</t></is></c><c r="Q622" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="623"><c r="A623" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B623" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C623" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D623" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E623" s="2" t="inlineStr"><is><t>Do leków zmniejszających obciążenie wstępne należy:</t></is></c><c r="F623" s="2" t="inlineStr"><is><t>diazotan izosorbidu</t></is></c><c r="G623" s="2" t="inlineStr"><is><t>furosemid</t></is></c><c r="H623" s="2" t="inlineStr" /><c r="I623" s="2" t="inlineStr" /><c r="J623" s="2" t="inlineStr" /><c r="K623" s="2" t="inlineStr"><is><t>diosmina</t></is></c><c r="L623" s="2" t="inlineStr"><is><t>pentoksyfilina</t></is></c><c r="M623" s="2" t="inlineStr" /><c r="N623" s="2" t="inlineStr" /><c r="O623" s="2" t="inlineStr" /><c r="P623" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2018/19</t></is></c><c r="Q623" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="624"><c r="A624" s="2" t="inlineStr"><is><t>LEKI PRZECIWDEPRESYJNE</t></is></c><c r="B624" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C624" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D624" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E624" s="2" t="inlineStr"><is><t>Pacjentka z zespołem depresyjnym stosująca tryptany ma zwiększone ryzyko zespołu serotoninowego po włączeniu:</t></is></c><c r="F624" s="2" t="inlineStr"><is><t>fluoksetyny</t></is></c><c r="G624" s="2" t="inlineStr"><is><t>wenlafaksyny</t></is></c><c r="H624" s="2" t="inlineStr"><is><t>klomipraminy</t></is></c><c r="I624" s="2" t="inlineStr"><is><t>duloksetyny</t></is></c><c r="J624" s="2" t="inlineStr" /><c r="K624" s="2" t="inlineStr" /><c r="L624" s="2" t="inlineStr" /><c r="M624" s="2" t="inlineStr" /><c r="N624" s="2" t="inlineStr" /><c r="O624" s="2" t="inlineStr" /><c r="P624" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2018/19</t></is></c><c r="Q624" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="625"><c r="A625" s="2" t="inlineStr"><is><t>LEKI PRZECIWPSYCHOTYCZNE</t></is></c><c r="B625" s="2" t="inlineStr"><is><t>Sposób podania</t></is></c><c r="C625" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D625" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E625" s="2" t="inlineStr"><is><t>Jeśli splątany i agresywny pacjent odmawia przyjmowania leków doustnie to po zastosowaniu krótkotrwałego unieruchomienia kończyn można mu podać dożylnie lek uspokajający, którym jest:</t></is></c><c r="F625" s="2" t="inlineStr"><is><t>midazolam</t></is></c><c r="G625" s="2" t="inlineStr" /><c r="H625" s="2" t="inlineStr" /><c r="I625" s="2" t="inlineStr" /><c r="J625" s="2" t="inlineStr" /><c r="K625" s="2" t="inlineStr"><is><t>piracetam</t></is></c><c r="L625" s="2" t="inlineStr"><is><t>haloperydol</t></is></c><c r="M625" s="2" t="inlineStr"><is><t>rysperydon</t></is></c><c r="N625" s="2" t="inlineStr" /><c r="O625" s="2" t="inlineStr" /><c r="P625" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2018/19</t></is></c><c r="Q625" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="626"><c r="A626" s="2" t="inlineStr"><is><t>LEKI PRZECIWDEPRESYJNE</t></is></c><c r="B626" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C626" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D626" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E626" s="2" t="inlineStr"><is><t>Jako lek normotymiczny w chorobie afektywnej dwubiegunowej można zastosować:</t></is></c><c r="F626" s="2" t="inlineStr"><is><t>lamotryginę</t></is></c><c r="G626" s="2" t="inlineStr"><is><t>olanzapinę</t></is></c><c r="H626" s="2" t="inlineStr" /><c r="I626" s="2" t="inlineStr" /><c r="J626" s="2" t="inlineStr" /><c r="K626" s="2" t="inlineStr"><is><t>fluoksetynę</t></is></c><c r="L626" s="2" t="inlineStr"><is><t>haloperydol</t></is></c><c r="M626" s="2" t="inlineStr" /><c r="N626" s="2" t="inlineStr" /><c r="O626" s="2" t="inlineStr" /><c r="P626" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2018/19</t></is></c><c r="Q626" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="627"><c r="A627" s="2" t="inlineStr"><is><t>PADACZKA</t></is></c><c r="B627" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C627" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D627" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E627" s="2" t="inlineStr"><is><t>Który lek jest stosowany jedynie we wskazaniu wymienionym przy tym leku?</t></is></c><c r="F627" s="2" t="inlineStr"><is><t>netupitant – terapia wspomagająca stosowanie wysoce emetogennej chemioterapii przeciwnowotworowej</t></is></c><c r="G627" s="2" t="inlineStr"><is><t>memantyna – choroba Alzheimera</t></is></c><c r="H627" s="2" t="inlineStr" /><c r="I627" s="2" t="inlineStr" /><c r="J627" s="2" t="inlineStr" /><c r="K627" s="2" t="inlineStr"><is><t>karbamazepina – padaczka</t></is></c><c r="L627" s="2" t="inlineStr"><is><t>pregabalina – polineuropatia cukrzycowa</t></is></c><c r="M627" s="2" t="inlineStr" /><c r="N627" s="2" t="inlineStr" /><c r="O627" s="2" t="inlineStr" /><c r="P627" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2018/19</t></is></c><c r="Q627" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="628"><c r="A628" s="2" t="inlineStr"><is><t>ZNIECZULENIA OGÓLNE</t></is></c><c r="B628" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C628" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D628" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E628" s="2" t="inlineStr"><is><t>Idealny lek znieczulenia ogólnego:</t></is></c><c r="F628" s="2" t="inlineStr"><is><t>jest skuteczny we wszystkich grupach pacjentów</t></is></c><c r="G628" s="2" t="inlineStr"><is><t>działa przeciwbólowo</t></is></c><c r="H628" s="2" t="inlineStr"><is><t>jest bezpieczny dla wszystkich grup pacjentów</t></is></c><c r="I628" s="2" t="inlineStr"><is><t>jest tani</t></is></c><c r="J628" s="2" t="inlineStr" /><c r="K628" s="2" t="inlineStr" /><c r="L628" s="2" t="inlineStr" /><c r="M628" s="2" t="inlineStr" /><c r="N628" s="2" t="inlineStr" /><c r="O628" s="2" t="inlineStr" /><c r="P628" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2018/19</t></is></c><c r="Q628" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="629"><c r="A629" s="2" t="inlineStr"><is><t>CHOROBA PARKINSONA</t></is></c><c r="B629" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C629" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D629" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E629" s="2" t="inlineStr"><is><t>Cholinolityki:</t></is></c><c r="F629" s="2" t="inlineStr"><is><t>są lekami z wyboru w polekowym zespole parkinsonowskim</t></is></c><c r="G629" s="2" t="inlineStr"><is><t>zmniejszają drżenie w chorobie Parkinsona</t></is></c><c r="H629" s="2" t="inlineStr"><is><t>nie różnią się skutecznością w chorobie Parkinsona</t></is></c><c r="I629" s="2" t="inlineStr"><is><t>można podawać w połączeniu z lewodopą</t></is></c><c r="J629" s="2" t="inlineStr" /><c r="K629" s="2" t="inlineStr" /><c r="L629" s="2" t="inlineStr" /><c r="M629" s="2" t="inlineStr" /><c r="N629" s="2" t="inlineStr" /><c r="O629" s="2" t="inlineStr" /><c r="P629" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2018/19</t></is></c><c r="Q629" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="630"><c r="A630" s="2" t="inlineStr"><is><t>LEKI PRZECIWNOWOTWOROWE</t></is></c><c r="B630" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C630" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D630" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E630" s="2" t="inlineStr"><is><t>Wskaż prawidłowe połączenie mykotoksyny z zagrożeniem poekspozycyjnym:</t></is></c><c r="F630" s="2" t="inlineStr"><is><t>zearaleon – działanie estrogenne i anaboliczne</t></is></c><c r="G630" s="2" t="inlineStr"><is><t>aflatoksyna – ryzyko nowotworów wątroby</t></is></c><c r="H630" s="2" t="inlineStr" /><c r="I630" s="2" t="inlineStr" /><c r="J630" s="2" t="inlineStr" /><c r="K630" s="2" t="inlineStr"><is><t>patulina – ryzyko nowotworów dróg moczowych</t></is></c><c r="L630" s="2" t="inlineStr"><is><t>ochratoksyna – silne działanie alergizujące</t></is></c><c r="M630" s="2" t="inlineStr" /><c r="N630" s="2" t="inlineStr" /><c r="O630" s="2" t="inlineStr" /><c r="P630" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2018/19</t></is></c><c r="Q630" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="631"><c r="A631" s="2" t="inlineStr"><is><t>LEKI PRZECIWHISTAMINOWE</t></is></c><c r="B631" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C631" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D631" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E631" s="2" t="inlineStr"><is><t>Leki przeciwhistaminowe drugiej generacji blokujące receptor H1 w odróżnieniu od leków pierwszej generacji:</t></is></c><c r="F631" s="2" t="inlineStr"><is><t>są w znaczącym stopniu pozbawione działania sedatywnego</t></is></c><c r="G631" s="2" t="inlineStr" /><c r="H631" s="2" t="inlineStr" /><c r="I631" s="2" t="inlineStr" /><c r="J631" s="2" t="inlineStr" /><c r="K631" s="2" t="inlineStr"><is><t>mają istotne działanie cholinolityczne</t></is></c><c r="L631" s="2" t="inlineStr"><is><t>mogą być stosowane w postaci wstrzyknięć</t></is></c><c r="M631" s="2" t="inlineStr"><is><t>są skuteczne w profilaktyce choroby lokomocyjnej</t></is></c><c r="N631" s="2" t="inlineStr" /><c r="O631" s="2" t="inlineStr" /><c r="P631" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2018/19</t></is></c><c r="Q631" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="632"><c r="A632" s="2" t="inlineStr"><is><t>GLIKOKORTYKOSTEROIDY</t></is></c><c r="B632" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C632" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D632" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E632" s="2" t="inlineStr"><is><t>W leczeniu ostrego napadu dny moczanowej stosuje się:</t></is></c><c r="F632" s="2" t="inlineStr"><is><t>kolchicynę</t></is></c><c r="G632" s="2" t="inlineStr"><is><t>glikokortykosteroidy</t></is></c><c r="H632" s="2" t="inlineStr"><is><t>niesteroidowe leki przeciwzapalne</t></is></c><c r="I632" s="2" t="inlineStr" /><c r="J632" s="2" t="inlineStr" /><c r="K632" s="2" t="inlineStr"><is><t>allopurynol</t></is></c><c r="L632" s="2" t="inlineStr" /><c r="M632" s="2" t="inlineStr" /><c r="N632" s="2" t="inlineStr" /><c r="O632" s="2" t="inlineStr" /><c r="P632" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2018/19</t></is></c><c r="Q632" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="633"><c r="A633" s="2" t="inlineStr"><is><t>LEKI MOCZOPĘDNE</t></is></c><c r="B633" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C633" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D633" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E633" s="2" t="inlineStr"><is><t>Diuretyki pętlowe:</t></is></c><c r="F633" s="2" t="inlineStr"><is><t>zwiększają filtrację kłębuszkową też przez korzystny wpływ na syntezę prostaglandyn w nerkach</t></is></c><c r="G633" s="2" t="inlineStr"><is><t>ulegają wydzielaniu cewkowemu w kanalikach proksymalnych</t></is></c><c r="H633" s="2" t="inlineStr"><is><t>tworzą wysoki ładunek sodowy w kanaliku dalszym aktywując układ reninowo￾angiotensynowy</t></is></c><c r="I633" s="2" t="inlineStr"><is><t>zwiększają pojemność łożyska żylnego jeszcze przed wystąpieniem efektu diuretycznego</t></is></c><c r="J633" s="2" t="inlineStr" /><c r="K633" s="2" t="inlineStr" /><c r="L633" s="2" t="inlineStr" /><c r="M633" s="2" t="inlineStr" /><c r="N633" s="2" t="inlineStr" /><c r="O633" s="2" t="inlineStr" /><c r="P633" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2018/19</t></is></c><c r="Q633" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="634"><c r="A634" s="2" t="inlineStr"><is><t>LEKI MOCZOPĘDNE</t></is></c><c r="B634" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C634" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D634" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E634" s="2" t="inlineStr"><is><t>Który lek może być zastosowany u chorego z nadwrażliwością na sulfonamidy?</t></is></c><c r="F634" s="2" t="inlineStr"><is><t>torasemid</t></is></c><c r="G634" s="2" t="inlineStr"><is><t>eplerenon</t></is></c><c r="H634" s="2" t="inlineStr" /><c r="I634" s="2" t="inlineStr" /><c r="J634" s="2" t="inlineStr" /><c r="K634" s="2" t="inlineStr"><is><t>furosemid</t></is></c><c r="L634" s="2" t="inlineStr"><is><t>hydrochlorotiazyd</t></is></c><c r="M634" s="2" t="inlineStr" /><c r="N634" s="2" t="inlineStr" /><c r="O634" s="2" t="inlineStr" /><c r="P634" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2018/19</t></is></c><c r="Q634" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="635"><c r="A635" s="2" t="inlineStr"><is><t>UKŁAD WSPÓŁCZULNY</t></is></c><c r="B635" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C635" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D635" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E635" s="2" t="inlineStr"><is><t>Wskaż prawdziwe stwierdzenie dotyczące metoprololu:</t></is></c><c r="F635" s="2" t="inlineStr"><is><t>ma działanie hipotensyjne związane ze zmniejszeniem aktywności reninowej osocza</t></is></c><c r="G635" s="2" t="inlineStr"><is><t>zmienia działanie układu współczulnego na poziomie ośrodkowego układu nerwowego</t></is></c><c r="H635" s="2" t="inlineStr"><is><t>jest niebezpieczny w naczynioskurczowych chorobach tętnic</t></is></c><c r="I635" s="2" t="inlineStr" /><c r="J635" s="2" t="inlineStr" /><c r="K635" s="2" t="inlineStr"><is><t>w terapii przewlekłej powoduje down-regulację receptorów beta-adrenergicznych</t></is></c><c r="L635" s="2" t="inlineStr" /><c r="M635" s="2" t="inlineStr" /><c r="N635" s="2" t="inlineStr" /><c r="O635" s="2" t="inlineStr" /><c r="P635" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2018/19</t></is></c><c r="Q635" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="636"><c r="A636" s="2" t="inlineStr"><is><t>LEKI PRZECIWPSYCHOTYCZNE</t></is></c><c r="B636" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C636" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D636" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E636" s="2" t="inlineStr"><is><t>W filmie „Piękny umysł” Alicia, żona chorego na schizofrenię Johna Nasha, pyta go: „Czy to przez lek?”, a on odpowiada: „Tak”. O którym działaniu niepożądanym chloropromazyny mogli rozmawiać?</t></is></c><c r="F636" s="2" t="inlineStr"><is><t>zmniejszeniu libido</t></is></c><c r="G636" s="2" t="inlineStr" /><c r="H636" s="2" t="inlineStr" /><c r="I636" s="2" t="inlineStr" /><c r="J636" s="2" t="inlineStr" /><c r="K636" s="2" t="inlineStr"><is><t>nadciśnieniu tętniczym</t></is></c><c r="L636" s="2" t="inlineStr"><is><t>ślinotoku</t></is></c><c r="M636" s="2" t="inlineStr"><is><t>przymusie robienia notatek na ścianach</t></is></c><c r="N636" s="2" t="inlineStr" /><c r="O636" s="2" t="inlineStr" /><c r="P636" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2018/19</t></is></c><c r="Q636" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="637"><c r="A637" s="2" t="inlineStr"><is><t>LEKI PRZECIWDEPRESYJNE</t></is></c><c r="B637" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C637" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D637" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E637" s="2" t="inlineStr"><is><t>W arcydziele „Sto lat samotności” Gabriela Garcii Marqueza wioskę Macondo nawiedza zaraza bezsenności i zapomnienia. Wskaż uzasadnioną opcję terapeutyczną do zaproponowania w leczeniu krótkotrwałej bezsenności, gdyby wydarzenia opisane przez Marqueza działy się współcześnie:</t></is></c><c r="F637" s="2" t="inlineStr"><is><t>trazodon</t></is></c><c r="G637" s="2" t="inlineStr" /><c r="H637" s="2" t="inlineStr" /><c r="I637" s="2" t="inlineStr" /><c r="J637" s="2" t="inlineStr" /><c r="K637" s="2" t="inlineStr"><is><t>triazolam</t></is></c><c r="L637" s="2" t="inlineStr"><is><t>dezimipramina</t></is></c><c r="M637" s="2" t="inlineStr"><is><t>hydroksyzyna</t></is></c><c r="N637" s="2" t="inlineStr" /><c r="O637" s="2" t="inlineStr" /><c r="P637" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2018/19</t></is></c><c r="Q637" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="638"><c r="A638" s="2" t="inlineStr"><is><t>LEKI PRZECIWDEPRESYJNE</t></is></c><c r="B638" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C638" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D638" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E638" s="2" t="inlineStr"><is><t>Amitryptylina w przeciwieństwie do wenlafaksyny:</t></is></c><c r="F638" s="2" t="inlineStr"><is><t>działa antagonistycznie wobec receptora muskarynowego (M1)</t></is></c><c r="G638" s="2" t="inlineStr" /><c r="H638" s="2" t="inlineStr" /><c r="I638" s="2" t="inlineStr" /><c r="J638" s="2" t="inlineStr" /><c r="K638" s="2" t="inlineStr"><is><t>jest skuteczna w bólach neuropatycznych</t></is></c><c r="L638" s="2" t="inlineStr"><is><t>zmniejsza wychwyt zwrotny noradrenaliny i serotoniny</t></is></c><c r="M638" s="2" t="inlineStr"><is><t>jest agonistą receptora dopaminowego (D2)</t></is></c><c r="N638" s="2" t="inlineStr" /><c r="O638" s="2" t="inlineStr" /><c r="P638" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2018/19</t></is></c><c r="Q638" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="639"><c r="A639" s="2" t="inlineStr"><is><t>UKŁAD WSPÓŁCZULNY</t></is></c><c r="B639" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C639" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D639" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E639" s="2" t="inlineStr"><is><t>Za reakcję paradoksalną uznasz:</t></is></c><c r="F639" s="2" t="inlineStr"><is><t>zwiększenie ciśnienia krwi po metoprololu</t></is></c><c r="G639" s="2" t="inlineStr"><is><t>pobudzenie i agresję po alprazolamie</t></is></c><c r="H639" s="2" t="inlineStr" /><c r="I639" s="2" t="inlineStr" /><c r="J639" s="2" t="inlineStr" /><c r="K639" s="2" t="inlineStr"><is><t>drgawki po amitryptylinie</t></is></c><c r="L639" s="2" t="inlineStr"><is><t>zaburzenia koordynacji ruchowej po zopiklonie</t></is></c><c r="M639" s="2" t="inlineStr" /><c r="N639" s="2" t="inlineStr" /><c r="O639" s="2" t="inlineStr" /><c r="P639" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2018/19</t></is></c><c r="Q639" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="640"><c r="A640" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B640" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C640" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D640" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E640" s="2" t="inlineStr"><is><t>Który lek ma zastosowanie w wymiotach związanych z chemioterapią przeciwnowotworową?</t></is></c><c r="F640" s="2" t="inlineStr"><is><t>deksametazon</t></is></c><c r="G640" s="2" t="inlineStr"><is><t>palonosetron</t></is></c><c r="H640" s="2" t="inlineStr"><is><t>aprepitant</t></is></c><c r="I640" s="2" t="inlineStr"><is><t>metoklopramid</t></is></c><c r="J640" s="2" t="inlineStr" /><c r="K640" s="2" t="inlineStr" /><c r="L640" s="2" t="inlineStr" /><c r="M640" s="2" t="inlineStr" /><c r="N640" s="2" t="inlineStr" /><c r="O640" s="2" t="inlineStr" /><c r="P640" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2018/19</t></is></c><c r="Q640" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="641"><c r="A641" s="2" t="inlineStr"><is><t>LEKI PRZECIWDEPRESYJNE</t></is></c><c r="B641" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C641" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D641" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E641" s="2" t="inlineStr"><is><t>Pacjentka od wielu lat otrzymuje perazynę, mianserynę i lorazepam. Na tej podstawie można rozpoznać (możliwe jest więcej niż jedno rozpoznanie):</t></is></c><c r="F641" s="2" t="inlineStr"><is><t>zaburzenia depresyjno-urojeniowe</t></is></c><c r="G641" s="2" t="inlineStr"><is><t>uzależnienie lekowe</t></is></c><c r="H641" s="2" t="inlineStr" /><c r="I641" s="2" t="inlineStr" /><c r="J641" s="2" t="inlineStr" /><c r="K641" s="2" t="inlineStr"><is><t>dwubiegunową chorobę afektywną</t></is></c><c r="L641" s="2" t="inlineStr"><is><t>fobię społeczną</t></is></c><c r="M641" s="2" t="inlineStr" /><c r="N641" s="2" t="inlineStr" /><c r="O641" s="2" t="inlineStr" /><c r="P641" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2018/19</t></is></c><c r="Q641" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="642"><c r="A642" s="2" t="inlineStr"><is><t>LEKI PRZECIWPSYCHOTYCZNE</t></is></c><c r="B642" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C642" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D642" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E642" s="2" t="inlineStr"><is><t>Podczas stosowania kwetiapiny, bardzo popularnej w psychotycznych zaburzeniach zachowania u pacjentów oddziałów somatycznych, trzeba pamiętać, że zwiększa się ryzyko:</t></is></c><c r="F642" s="2" t="inlineStr"><is><t>hipertriglicerydemii</t></is></c><c r="G642" s="2" t="inlineStr"><is><t>zespołu pozapiramidowego</t></is></c><c r="H642" s="2" t="inlineStr"><is><t>hiperglikemii</t></is></c><c r="I642" s="2" t="inlineStr"><is><t>zakrzepowego zapalenia żył</t></is></c><c r="J642" s="2" t="inlineStr" /><c r="K642" s="2" t="inlineStr" /><c r="L642" s="2" t="inlineStr" /><c r="M642" s="2" t="inlineStr" /><c r="N642" s="2" t="inlineStr" /><c r="O642" s="2" t="inlineStr" /><c r="P642" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2018/19</t></is></c><c r="Q642" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="643"><c r="A643" s="2" t="inlineStr"><is><t>CHOROBA NIEDOKRWIENNA SERCA</t></is></c><c r="B643" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C643" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D643" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E643" s="2" t="inlineStr"><is><t>Która z poniższych informacji znajduje się w charakterystyce produktu leczniczego:</t></is></c><c r="F643" s="2" t="inlineStr"><is><t>informacja o warunkach przechowywania produktu leczniczego</t></is></c><c r="G643" s="2" t="inlineStr"><is><t>data wydania pierwszego pozwolenia na dopuszczenie do obrotu produktu leczniczego</t></is></c><c r="H643" s="2" t="inlineStr" /><c r="I643" s="2" t="inlineStr" /><c r="J643" s="2" t="inlineStr" /><c r="K643" s="2" t="inlineStr"><is><t>cena produktu leczniczego</t></is></c><c r="L643" s="2" t="inlineStr"><is><t>informacja o okresowym wstrzymaniu produktu leczniczego w obrocie</t></is></c><c r="M643" s="2" t="inlineStr" /><c r="N643" s="2" t="inlineStr" /><c r="O643" s="2" t="inlineStr" /><c r="P643" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2017/18 - 1 termin</t></is></c><c r="Q643" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="644"><c r="A644" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B644" s="2" t="inlineStr"><is><t>Farmakokinetyka</t></is></c><c r="C644" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D644" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E644" s="2" t="inlineStr"><is><t>Do określenia biodostępności leku po podaniu doustnym konieczna jest znajomość:</t></is></c><c r="F644" s="2" t="inlineStr"><is><t>AUC0→t po podaniu dożylnym</t></is></c><c r="G644" s="2" t="inlineStr"><is><t>AUC0→t po podaniu doustnym</t></is></c><c r="H644" s="2" t="inlineStr" /><c r="I644" s="2" t="inlineStr" /><c r="J644" s="2" t="inlineStr" /><c r="K644" s="2" t="inlineStr"><is><t>stopnia wchłaniania ksylozy z przewodu pokarmowego</t></is></c><c r="L644" s="2" t="inlineStr"><is><t>Cmax leku po podaniu dożylnym</t></is></c><c r="M644" s="2" t="inlineStr" /><c r="N644" s="2" t="inlineStr" /><c r="O644" s="2" t="inlineStr" /><c r="P644" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2017/18 - 1 termin</t></is></c><c r="Q644" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="645"><c r="A645" s="2" t="inlineStr"><is><t>FARMAKOKINETYKA</t></is></c><c r="B645" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C645" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D645" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E645" s="2" t="inlineStr"><is><t>W stanie stacjonarnym objętość dystrybucji leku A = 6 l, a leku B = 206 l. Na podstawie tych danych można stwierdzić, że w stanie stacjonarnym lek A:</t></is></c><c r="F645" s="2" t="inlineStr"><is><t>osiąga większe stężenie we krwi niż lek B po podaniu takiej samej dawki obu leków i.v</t></is></c><c r="G645" s="2" t="inlineStr"><is><t>jest rozmieszczony nierównomiernie w przestrzeniach płynowych organizmu</t></is></c><c r="H645" s="2" t="inlineStr" /><c r="I645" s="2" t="inlineStr" /><c r="J645" s="2" t="inlineStr" /><c r="K645" s="2" t="inlineStr"><is><t>działa w kompartmencie obwodowym</t></is></c><c r="L645" s="2" t="inlineStr"><is><t>jest eliminowany zgodnie z kinetyką 0 rzędu</t></is></c><c r="M645" s="2" t="inlineStr"><is><t>Która z poniższych par lek-zagrażające życiu działanie niepożądane jest prawdziwa?</t></is></c><c r="N645" s="2" t="inlineStr" /><c r="O645" s="2" t="inlineStr" /><c r="P645" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2017/18 - 1 termin</t></is></c><c r="Q645" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="646"><c r="A646" s="2" t="inlineStr"><is><t>CUKRZYCA</t></is></c><c r="B646" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C646" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D646" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E646" s="2" t="inlineStr"><is><t>W celu obniżenia glikemii przed posiłkiem można podać:</t></is></c><c r="F646" s="2" t="inlineStr"><is><t>glulizynę</t></is></c><c r="G646" s="2" t="inlineStr" /><c r="H646" s="2" t="inlineStr" /><c r="I646" s="2" t="inlineStr" /><c r="J646" s="2" t="inlineStr" /><c r="K646" s="2" t="inlineStr"><is><t>degludec</t></is></c><c r="L646" s="2" t="inlineStr"><is><t>detemir</t></is></c><c r="M646" s="2" t="inlineStr"><is><t>glarginę</t></is></c><c r="N646" s="2" t="inlineStr" /><c r="O646" s="2" t="inlineStr" /><c r="P646" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2017/18 - 1 termin</t></is></c><c r="Q646" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="647"><c r="A647" s="2" t="inlineStr"><is><t>LEKI PRZECIWGRZYBICZE</t></is></c><c r="B647" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C647" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D647" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E647" s="2" t="inlineStr"><is><t>W leczeniu hiperprolaktynemii (prolaktynoma to najczęstszy typ gruczolaka przysadki) uzasadnione jest zastosowanie:</t></is></c><c r="F647" s="2" t="inlineStr"><is><t>bromokryptyny</t></is></c><c r="G647" s="2" t="inlineStr" /><c r="H647" s="2" t="inlineStr" /><c r="I647" s="2" t="inlineStr" /><c r="J647" s="2" t="inlineStr" /><c r="K647" s="2" t="inlineStr"><is><t>ketokonazolu</t></is></c><c r="L647" s="2" t="inlineStr"><is><t>eplerenonu</t></is></c><c r="M647" s="2" t="inlineStr"><is><t>klomifenu</t></is></c><c r="N647" s="2" t="inlineStr" /><c r="O647" s="2" t="inlineStr" /><c r="P647" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2017/18 - 1 termin</t></is></c><c r="Q647" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="648"><c r="A648" s="2" t="inlineStr"><is><t>FARMAKOKINETYKA</t></is></c><c r="B648" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C648" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D648" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E648" s="2" t="inlineStr"><is><t>Odtwórczy (generyczny) produkt leczniczy to produkt leczniczy :</t></is></c><c r="F648" s="2" t="inlineStr"><is><t>zawierający tę samą substancję aktywną co produkt oryginalny (innowacyjny)</t></is></c><c r="G648" s="2" t="inlineStr"><is><t>biorównoważny z produktem oryginalnym (innowacyjnym)</t></is></c><c r="H648" s="2" t="inlineStr" /><c r="I648" s="2" t="inlineStr" /><c r="J648" s="2" t="inlineStr" /><c r="K648" s="2" t="inlineStr"><is><t>mający ten sam skład co produkt oryginalny (innowacyjny)</t></is></c><c r="L648" s="2" t="inlineStr"><is><t>zarejestrowany także w innych wskazaniach niż produkt oryginalny (innowacyjny)</t></is></c><c r="M648" s="2" t="inlineStr" /><c r="N648" s="2" t="inlineStr" /><c r="O648" s="2" t="inlineStr" /><c r="P648" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2017/18 - 1 termin</t></is></c><c r="Q648" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="649"><c r="A649" s="2" t="inlineStr"><is><t>ANTYKONCEPCJA</t></is></c><c r="B649" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C649" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D649" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E649" s="2" t="inlineStr"><is><t>„Lekiem” o nieudokumentowanej skuteczności (de facto bezwartościowym) jest:</t></is></c><c r="F649" s="2" t="inlineStr"><is><t>beta-glukan</t></is></c><c r="G649" s="2" t="inlineStr" /><c r="H649" s="2" t="inlineStr" /><c r="I649" s="2" t="inlineStr" /><c r="J649" s="2" t="inlineStr" /><c r="K649" s="2" t="inlineStr"><is><t>drospirenon</t></is></c><c r="L649" s="2" t="inlineStr"><is><t>metamizol</t></is></c><c r="M649" s="2" t="inlineStr"><is><t>aprotynina</t></is></c><c r="N649" s="2" t="inlineStr" /><c r="O649" s="2" t="inlineStr" /><c r="P649" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2017/18 - 1 termin</t></is></c><c r="Q649" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="650"><c r="A650" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B650" s="2" t="inlineStr"><is><t>Przeciwwskazania</t></is></c><c r="C650" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D650" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E650" s="2" t="inlineStr"><is><t>U chorych obciążonych dodatnią historią krwawienia z wrzodów żołądka w przypadku planowanego przewlekłego leczenia NLPZ należy:</t></is></c><c r="F650" s="2" t="inlineStr"><is><t>przepisać dodatkowo pantoprazol</t></is></c><c r="G650" s="2" t="inlineStr"><is><t>wykonać test na nosicielstwo Helicobacter pylori w celu ewentualnej eradykacji</t></is></c><c r="H650" s="2" t="inlineStr"><is><t>przy braku innych przeciwwskazań wybrać lek z grupy koksybów</t></is></c><c r="I650" s="2" t="inlineStr" /><c r="J650" s="2" t="inlineStr" /><c r="K650" s="2" t="inlineStr"><is><t>bezwzględnie odstąpić od terapii klasycznymi (nieselektywnymi) NLPZ</t></is></c><c r="L650" s="2" t="inlineStr" /><c r="M650" s="2" t="inlineStr" /><c r="N650" s="2" t="inlineStr" /><c r="O650" s="2" t="inlineStr" /><c r="P650" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2017/18 - 1 termin</t></is></c><c r="Q650" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="651"><c r="A651" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B651" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C651" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D651" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E651" s="2" t="inlineStr"><is><t>Do leków zwiększających niekorzystny wpływ NLPZ na przewód pokarmowy zaliczysz:</t></is></c><c r="F651" s="2" t="inlineStr"><is><t>warfarynę</t></is></c><c r="G651" s="2" t="inlineStr"><is><t>prednizon</t></is></c><c r="H651" s="2" t="inlineStr" /><c r="I651" s="2" t="inlineStr" /><c r="J651" s="2" t="inlineStr" /><c r="K651" s="2" t="inlineStr"><is><t>etamsylat</t></is></c><c r="L651" s="2" t="inlineStr"><is><t>sukralfat</t></is></c><c r="M651" s="2" t="inlineStr" /><c r="N651" s="2" t="inlineStr" /><c r="O651" s="2" t="inlineStr" /><c r="P651" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2017/18 - 1 termin</t></is></c><c r="Q651" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="652"><c r="A652" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B652" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C652" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D652" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E652" s="2" t="inlineStr"><is><t>Czynniki stymulujące erytropoezę:</t></is></c><c r="F652" s="2" t="inlineStr"><is><t>powodują przemijające objawy grypopodobne</t></is></c><c r="G652" s="2" t="inlineStr"><is><t>zwiększają ciśnienie tętnicze krwi</t></is></c><c r="H652" s="2" t="inlineStr"><is><t>rzadko powodują wybiórczą aplazję czerwonokrwinkową</t></is></c><c r="I652" s="2" t="inlineStr"><is><t>predysponują do powikłań zakrzepowych</t></is></c><c r="J652" s="2" t="inlineStr" /><c r="K652" s="2" t="inlineStr" /><c r="L652" s="2" t="inlineStr" /><c r="M652" s="2" t="inlineStr" /><c r="N652" s="2" t="inlineStr" /><c r="O652" s="2" t="inlineStr" /><c r="P652" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2017/18 - 1 termin</t></is></c><c r="Q652" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="653"><c r="A653" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B653" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C653" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D653" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E653" s="2" t="inlineStr"><is><t>Którego/których leków może dotyczyć poniższy opis: pośrednio hamuje aktywność czynnika krzepnięcia Xa:</t></is></c><c r="F653" s="2" t="inlineStr"><is><t>enoksaparyna</t></is></c><c r="G653" s="2" t="inlineStr"><is><t>fondaparyna</t></is></c><c r="H653" s="2" t="inlineStr" /><c r="I653" s="2" t="inlineStr" /><c r="J653" s="2" t="inlineStr" /><c r="K653" s="2" t="inlineStr"><is><t>edoksaban</t></is></c><c r="L653" s="2" t="inlineStr"><is><t>biwalirudyna</t></is></c><c r="M653" s="2" t="inlineStr" /><c r="N653" s="2" t="inlineStr" /><c r="O653" s="2" t="inlineStr" /><c r="P653" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2017/18 - 1 termin</t></is></c><c r="Q653" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="654"><c r="A654" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B654" s="2" t="inlineStr"><is><t>Farmakokinetyka</t></is></c><c r="C654" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D654" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E654" s="2" t="inlineStr"><is><t>Którego/których leków może dotyczyć poniższy opis: prolek, nieodwracalnie blokujący receptory P2Y12:</t></is></c><c r="F654" s="2" t="inlineStr"><is><t>prasugrel</t></is></c><c r="G654" s="2" t="inlineStr" /><c r="H654" s="2" t="inlineStr" /><c r="I654" s="2" t="inlineStr" /><c r="J654" s="2" t="inlineStr" /><c r="K654" s="2" t="inlineStr"><is><t>dipyrydamol</t></is></c><c r="L654" s="2" t="inlineStr"><is><t>tikagrelor</t></is></c><c r="M654" s="2" t="inlineStr"><is><t>cilostazol</t></is></c><c r="N654" s="2" t="inlineStr" /><c r="O654" s="2" t="inlineStr" /><c r="P654" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2017/18 - 1 termin</t></is></c><c r="Q654" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="655"><c r="A655" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B655" s="2" t="inlineStr"><is><t>Monitorowanie</t></is></c><c r="C655" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D655" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E655" s="2" t="inlineStr"><is><t>Wadą heparyny niefrakcjonowanej w porównaniu z drobnocząsteczkowymi jest:</t></is></c><c r="F655" s="2" t="inlineStr"><is><t>wymaga monitorowania APTT</t></is></c><c r="G655" s="2" t="inlineStr"><is><t>silniej indukuje powstawanie przeciwciał p-kompleksowi PF4 z heparyną</t></is></c><c r="H655" s="2" t="inlineStr" /><c r="I655" s="2" t="inlineStr" /><c r="J655" s="2" t="inlineStr" /><c r="K655" s="2" t="inlineStr"><is><t>jest mniej bezpieczna w niewydolności nerek</t></is></c><c r="L655" s="2" t="inlineStr"><is><t>trudniej jest zneutralizować jej działanie siarczanem protaminy</t></is></c><c r="M655" s="2" t="inlineStr" /><c r="N655" s="2" t="inlineStr" /><c r="O655" s="2" t="inlineStr" /><c r="P655" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2017/18 - 1 termin</t></is></c><c r="Q655" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="656"><c r="A656" s="2" t="inlineStr"><is><t>LEKI HIPOLIPEMIZUJĄCE</t></is></c><c r="B656" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C656" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D656" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E656" s="2" t="inlineStr"><is><t>Rosuwastatyna zmniejsza:</t></is></c><c r="F656" s="2" t="inlineStr"><is><t>syntezę cholesterolu w wątrobie poprzez konkurencyjne hamowanie aktywności reduktazy HMG-CoA</t></is></c><c r="G656" s="2" t="inlineStr"><is><t>stężenie cholesterolu LDL</t></is></c><c r="H656" s="2" t="inlineStr"><is><t>stężenie lipoprotein zawierających apoB, w tym cząsteczek o dużej zawartości triglicerydów</t></is></c><c r="I656" s="2" t="inlineStr" /><c r="J656" s="2" t="inlineStr" /><c r="K656" s="2" t="inlineStr"><is><t>ekspresję receptorów dla LDL na powierzchni hepatocytów</t></is></c><c r="L656" s="2" t="inlineStr" /><c r="M656" s="2" t="inlineStr" /><c r="N656" s="2" t="inlineStr" /><c r="O656" s="2" t="inlineStr" /><c r="P656" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2017/18 - 1 termin</t></is></c><c r="Q656" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="657"><c r="A657" s="2" t="inlineStr"><is><t>LEKI HIPOLIPEMIZUJĄCE</t></is></c><c r="B657" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C657" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D657" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E657" s="2" t="inlineStr"><is><t>W prawidłowo prowadzonej profilaktyce sercowo-naczyniowej (czyli profilaktyce miażdżycy) należy osiągnąć następujące cele terapeutyczne:</t></is></c><c r="F657" s="2" t="inlineStr"><is><t>w grupie osób dużego ryzyka zmniejszenie stężenia cholesterolu LDL w surowicy poniżej 70 mg/dl</t></is></c><c r="G657" s="2" t="inlineStr" /><c r="H657" s="2" t="inlineStr" /><c r="I657" s="2" t="inlineStr" /><c r="J657" s="2" t="inlineStr" /><c r="K657" s="2" t="inlineStr"><is><t>obniżenie stężenia trójglicerydów w surowicy poniżej 115 mg/dl</t></is></c><c r="L657" s="2" t="inlineStr"><is><t>zmniejszenie masy ciała do wartości BMI poniżej 27 kg/m2</t></is></c><c r="M657" s="2" t="inlineStr"><is><t>podwyższenie stężenia cholesterolu HDL w surowicy u mężczyzn powyżej 30 mg/dl</t></is></c><c r="N657" s="2" t="inlineStr" /><c r="O657" s="2" t="inlineStr" /><c r="P657" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2017/18 - 1 termin</t></is></c><c r="Q657" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="658"><c r="A658" s="2" t="inlineStr"><is><t>LEKI IMMUNOSUPRESYJNE</t></is></c><c r="B658" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C658" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D658" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E658" s="2" t="inlineStr"><is><t>Wskaż prawidłowe stwierdzenie:</t></is></c><c r="F658" s="2" t="inlineStr"><is><t>ofatumumab to ludzkie przeciwciało skierowane przeciw receptorowi CD20 limfocytów B</t></is></c><c r="G658" s="2" t="inlineStr"><is><t>bazyliksymab to chimeryczne przeciwciało skierowane przeciw receptorowi CD25 na powierzchni limfocytów T</t></is></c><c r="H658" s="2" t="inlineStr" /><c r="I658" s="2" t="inlineStr" /><c r="J658" s="2" t="inlineStr" /><c r="K658" s="2" t="inlineStr"><is><t>rituksymab to chimeryczne przeciwciało skierowane przeciw receptorowi CD52 limfocytów B</t></is></c><c r="L658" s="2" t="inlineStr"><is><t>natalizumab to humanizowane przeciwciało monoklonalne przeciw CD11a limfocytów B</t></is></c><c r="M658" s="2" t="inlineStr" /><c r="N658" s="2" t="inlineStr" /><c r="O658" s="2" t="inlineStr" /><c r="P658" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2017/18 - 1 termin</t></is></c><c r="Q658" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="659"><c r="A659" s="2" t="inlineStr"><is><t>LEKI IMMUNOSUPRESYJNE</t></is></c><c r="B659" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C659" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D659" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E659" s="2" t="inlineStr"><is><t>W leczeniu immunosupresyjnym jest/są stosowana/-e:</t></is></c><c r="F659" s="2" t="inlineStr"><is><t>przeciwciała przeciwtymocytarne królicze</t></is></c><c r="G659" s="2" t="inlineStr" /><c r="H659" s="2" t="inlineStr" /><c r="I659" s="2" t="inlineStr" /><c r="J659" s="2" t="inlineStr" /><c r="K659" s="2" t="inlineStr"><is><t>cyklofilina</t></is></c><c r="L659" s="2" t="inlineStr"><is><t>inozyna</t></is></c><c r="M659" s="2" t="inlineStr"><is><t>kolchicyna</t></is></c><c r="N659" s="2" t="inlineStr" /><c r="O659" s="2" t="inlineStr" /><c r="P659" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2017/18 - 1 termin</t></is></c><c r="Q659" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="660"><c r="A660" s="2" t="inlineStr"><is><t>FARMAKOLOGIA OGÓLNA I EBM</t></is></c><c r="B660" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C660" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D660" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E660" s="2" t="inlineStr"><is><t>Lekiem terapii genowej jest:</t></is></c><c r="F660" s="2" t="inlineStr"><is><t>fomiwirsen</t></is></c><c r="G660" s="2" t="inlineStr"><is><t>mipomersen</t></is></c><c r="H660" s="2" t="inlineStr"><is><t>typarwowek alipogenu</t></is></c><c r="I660" s="2" t="inlineStr" /><c r="J660" s="2" t="inlineStr" /><c r="K660" s="2" t="inlineStr"><is><t>OKT3</t></is></c><c r="L660" s="2" t="inlineStr" /><c r="M660" s="2" t="inlineStr" /><c r="N660" s="2" t="inlineStr" /><c r="O660" s="2" t="inlineStr" /><c r="P660" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2017/18 - 1 termin</t></is></c><c r="Q660" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="661"><c r="A661" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B661" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C661" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D661" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E661" s="2" t="inlineStr"><is><t>Długotrwałe stosowanie pantoprazolu może być przyczyną:</t></is></c><c r="F661" s="2" t="inlineStr"><is><t>zakażeń dolnego odcinka układu oddechowego</t></is></c><c r="G661" s="2" t="inlineStr"><is><t>zwyrodnienia tylnosznurowego z powodu zmniejszonego wchłaniania witaminy B12</t></is></c><c r="H661" s="2" t="inlineStr"><is><t>osteoporozy</t></is></c><c r="I661" s="2" t="inlineStr"><is><t>zakażeń przewodu pokarmowego</t></is></c><c r="J661" s="2" t="inlineStr" /><c r="K661" s="2" t="inlineStr" /><c r="L661" s="2" t="inlineStr" /><c r="M661" s="2" t="inlineStr" /><c r="N661" s="2" t="inlineStr" /><c r="O661" s="2" t="inlineStr" /><c r="P661" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2017/18 - 1 termin</t></is></c><c r="Q661" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="662"><c r="A662" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B662" s="2" t="inlineStr"><is><t>Interakcje</t></is></c><c r="C662" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D662" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E662" s="2" t="inlineStr"><is><t>Wskaż prawidłowe stwierdzenie dotyczące inhibitorów pompy protonowej (IPP):</t></is></c><c r="F662" s="2" t="inlineStr"><is><t>są lekami prekursorowymi</t></is></c><c r="G662" s="2" t="inlineStr"><is><t>aktywność osiągają w komórkach okładzinowych w fazie czynnej=wydzielniczej</t></is></c><c r="H662" s="2" t="inlineStr"><is><t>powodują nieodwracalne zablokowanie pompy protonowej</t></is></c><c r="I662" s="2" t="inlineStr"><is><t>w różnym stopniu hamują izoenzymy CYP (CYP2C19 i CYP3A4)</t></is></c><c r="J662" s="2" t="inlineStr" /><c r="K662" s="2" t="inlineStr" /><c r="L662" s="2" t="inlineStr" /><c r="M662" s="2" t="inlineStr" /><c r="N662" s="2" t="inlineStr" /><c r="O662" s="2" t="inlineStr" /><c r="P662" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2017/18 - 1 termin</t></is></c><c r="Q662" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="663"><c r="A663" s="2" t="inlineStr"><is><t>NARKOTYCZNE LEKI PRZECIWBÓLOWE</t></is></c><c r="B663" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C663" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D663" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E663" s="2" t="inlineStr"><is><t>W leczeniu zaparć będących działaniem niepożądanym agonistów receptorów opioidowych zastosowanie ma:</t></is></c><c r="F663" s="2" t="inlineStr"><is><t>alwimopan</t></is></c><c r="G663" s="2" t="inlineStr"><is><t>metylnaltrekson</t></is></c><c r="H663" s="2" t="inlineStr" /><c r="I663" s="2" t="inlineStr" /><c r="J663" s="2" t="inlineStr" /><c r="K663" s="2" t="inlineStr"><is><t>papaweryna</t></is></c><c r="L663" s="2" t="inlineStr"><is><t>metadon</t></is></c><c r="M663" s="2" t="inlineStr" /><c r="N663" s="2" t="inlineStr" /><c r="O663" s="2" t="inlineStr" /><c r="P663" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2017/18 - 1 termin</t></is></c><c r="Q663" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="664"><c r="A664" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B664" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C664" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D664" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E664" s="2" t="inlineStr"><is><t>Wybierz stwierdzenie opisujące 20% roztwór albumin:</t></is></c><c r="F664" s="2" t="inlineStr"><is><t>powoduje ponad 100% przyrost objętości osocza</t></is></c><c r="G664" s="2" t="inlineStr"><is><t>działa objętościowo do 6 h</t></is></c><c r="H664" s="2" t="inlineStr" /><c r="I664" s="2" t="inlineStr" /><c r="J664" s="2" t="inlineStr" /><c r="K664" s="2" t="inlineStr"><is><t>może spowodować uszkodzenie nerek</t></is></c><c r="L664" s="2" t="inlineStr"><is><t>ma istotny wpływ na krzepnięcie krwi</t></is></c><c r="M664" s="2" t="inlineStr" /><c r="N664" s="2" t="inlineStr" /><c r="O664" s="2" t="inlineStr" /><c r="P664" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2017/18 - 1 termin</t></is></c><c r="Q664" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="665"><c r="A665" s="2" t="inlineStr"><is><t>LEKI PRZECIWNOWOTWOROWE</t></is></c><c r="B665" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C665" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D665" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E665" s="2" t="inlineStr"><is><t>Lekiem genotoksycznym jest:</t></is></c><c r="F665" s="2" t="inlineStr"><is><t>cyklofosfamid</t></is></c><c r="G665" s="2" t="inlineStr"><is><t>cisplatyna</t></is></c><c r="H665" s="2" t="inlineStr"><is><t>doksorubicyna</t></is></c><c r="I665" s="2" t="inlineStr"><is><t>irinotekan</t></is></c><c r="J665" s="2" t="inlineStr" /><c r="K665" s="2" t="inlineStr" /><c r="L665" s="2" t="inlineStr" /><c r="M665" s="2" t="inlineStr" /><c r="N665" s="2" t="inlineStr" /><c r="O665" s="2" t="inlineStr" /><c r="P665" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2017/18 - 1 termin</t></is></c><c r="Q665" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="666"><c r="A666" s="2" t="inlineStr"><is><t>FARMAKOLOGIA OGÓLNA I EBM</t></is></c><c r="B666" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C666" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D666" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E666" s="2" t="inlineStr"><is><t>Psychoaktywne substancje uzależniające aktywują:</t></is></c><c r="F666" s="2" t="inlineStr"><is><t>obszar brzuszny nakrywki</t></is></c><c r="G666" s="2" t="inlineStr"><is><t>jądro półleżące</t></is></c><c r="H666" s="2" t="inlineStr"><is><t>korę przedczołową</t></is></c><c r="I666" s="2" t="inlineStr"><is><t>mezolimbiczny układ dopaminowy</t></is></c><c r="J666" s="2" t="inlineStr" /><c r="K666" s="2" t="inlineStr" /><c r="L666" s="2" t="inlineStr" /><c r="M666" s="2" t="inlineStr" /><c r="N666" s="2" t="inlineStr" /><c r="O666" s="2" t="inlineStr" /><c r="P666" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2017/18 - 1 termin</t></is></c><c r="Q666" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="667"><c r="A667" s="2" t="inlineStr"><is><t>LEKI PRZECIWNOWOTWOROWE</t></is></c><c r="B667" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C667" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D667" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E667" s="2" t="inlineStr"><is><t>Patulina:</t></is></c><c r="F667" s="2" t="inlineStr"><is><t>ma działanie mutagenne</t></is></c><c r="G667" s="2" t="inlineStr"><is><t>w warunkach naturalnych znana jest jako substancja skażająca jabłka i powodująca brązową zgniliznę innych owoców</t></is></c><c r="H667" s="2" t="inlineStr" /><c r="I667" s="2" t="inlineStr" /><c r="J667" s="2" t="inlineStr" /><c r="K667" s="2" t="inlineStr"><is><t>powoduje endemiczną epidemię bałkańską</t></is></c><c r="L667" s="2" t="inlineStr"><is><t>jest związkiem, który zwiększa ryzyko nowotworu wątroby</t></is></c><c r="M667" s="2" t="inlineStr" /><c r="N667" s="2" t="inlineStr" /><c r="O667" s="2" t="inlineStr" /><c r="P667" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2017/18 - 1 termin</t></is></c><c r="Q667" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="668"><c r="A668" s="2" t="inlineStr"><is><t>LEKI HIPOLIPEMIZUJĄCE</t></is></c><c r="B668" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C668" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D668" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E668" s="2" t="inlineStr"><is><t>Blaszki miażdżycowe w naczyniach wieńcowych stabilizuje:</t></is></c><c r="F668" s="2" t="inlineStr"><is><t>atorwastatyna</t></is></c><c r="G668" s="2" t="inlineStr" /><c r="H668" s="2" t="inlineStr" /><c r="I668" s="2" t="inlineStr" /><c r="J668" s="2" t="inlineStr" /><c r="K668" s="2" t="inlineStr"><is><t>fondaparyna</t></is></c><c r="L668" s="2" t="inlineStr"><is><t>gliklazyd</t></is></c><c r="M668" s="2" t="inlineStr"><is><t>kwasy omega 6</t></is></c><c r="N668" s="2" t="inlineStr" /><c r="O668" s="2" t="inlineStr" /><c r="P668" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2017/18 - 1 termin</t></is></c><c r="Q668" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="669"><c r="A669" s="2" t="inlineStr"><is><t>FARMAKOLOGIA OGÓLNA I EBM</t></is></c><c r="B669" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C669" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D669" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E669" s="2" t="inlineStr"><is><t>Wyrób medyczny to narzędzie, przyrząd, aparat, sprzęt, materiał lub inny artykuł, który może służyć do:</t></is></c><c r="F669" s="2" t="inlineStr"><is><t>regulacji poczęć</t></is></c><c r="G669" s="2" t="inlineStr"><is><t>diagnozowania chorób</t></is></c><c r="H669" s="2" t="inlineStr"><is><t>modyfikowania procesów fizjologicznych</t></is></c><c r="I669" s="2" t="inlineStr" /><c r="J669" s="2" t="inlineStr" /><c r="K669" s="2" t="inlineStr"><is><t>leczenia farmakologicznego</t></is></c><c r="L669" s="2" t="inlineStr" /><c r="M669" s="2" t="inlineStr" /><c r="N669" s="2" t="inlineStr" /><c r="O669" s="2" t="inlineStr" /><c r="P669" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2017/18 - 2 termin</t></is></c><c r="Q669" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="670"><c r="A670" s="2" t="inlineStr"><is><t>FARMAKOKINETYKA</t></is></c><c r="B670" s="2" t="inlineStr"><is><t>Interakcje</t></is></c><c r="C670" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D670" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E670" s="2" t="inlineStr"><is><t>Które stwierdzenie jest prawdziwe:</t></is></c><c r="F670" s="2" t="inlineStr"><is><t>dyfuzja bierna to główny mechanizm transportu leków przez błony półprzepuszczalne</t></is></c><c r="G670" s="2" t="inlineStr"><is><t>P-glikoproteina (P-gp) usuwa leki z komórki do środowiska pozakomórkowego w sposób zależny od ATP</t></is></c><c r="H670" s="2" t="inlineStr"><is><t>CYP3A4 jest głównym izoenzymem uczestniczącym w metabolizmie 1 fazy leków</t></is></c><c r="I670" s="2" t="inlineStr" /><c r="J670" s="2" t="inlineStr" /><c r="K670" s="2" t="inlineStr"><is><t>istotne klinicznie jest wiązanie leku z białkami transportującymi we krwi ≥ 60%</t></is></c><c r="L670" s="2" t="inlineStr" /><c r="M670" s="2" t="inlineStr" /><c r="N670" s="2" t="inlineStr" /><c r="O670" s="2" t="inlineStr" /><c r="P670" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2017/18 - 2 termin</t></is></c><c r="Q670" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="671"><c r="A671" s="2" t="inlineStr"><is><t>STANY NAGŁE</t></is></c><c r="B671" s="2" t="inlineStr"><is><t>Dawkowanie</t></is></c><c r="C671" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D671" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E671" s="2" t="inlineStr"><is><t>W stosowanej do korekty dawkowania leków skali Childa-Turcotte’a-Pugh należy uwzględnić m.in. następujący parametr:</t></is></c><c r="F671" s="2" t="inlineStr"><is><t>stężenie albumin w surowicy</t></is></c><c r="G671" s="2" t="inlineStr"><is><t>stężenie bilirubiny w surowicy</t></is></c><c r="H671" s="2" t="inlineStr"><is><t>ocenę neurologiczną (zmiany osobowości, zaburzenia nastroju, spowolnienie myślenia, zaburzenia koncentracji uwagi, drżenia grubofaliste kończyn, zaburzenia mowy)</t></is></c><c r="I671" s="2" t="inlineStr" /><c r="J671" s="2" t="inlineStr" /><c r="K671" s="2" t="inlineStr"><is><t>stężenie kreatyniny w surowicy</t></is></c><c r="L671" s="2" t="inlineStr" /><c r="M671" s="2" t="inlineStr" /><c r="N671" s="2" t="inlineStr" /><c r="O671" s="2" t="inlineStr" /><c r="P671" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2017/18 - 2 termin</t></is></c><c r="Q671" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="672"><c r="A672" s="2" t="inlineStr"><is><t>FARMAKOKINETYKA</t></is></c><c r="B672" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C672" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D672" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E672" s="2" t="inlineStr"><is><t>Lek L jest metabolizowany w wątrobie przy udziale enzymów CYP do nieaktywnych i nietoksycznych metabolitów, które następnie wydalane są przez nerki. Można się zatem spodziewać, że wystąpienie działań toksycznych tego leku jest:</t></is></c><c r="F672" s="2" t="inlineStr"><is><t>bardziej prawdopodobne u osób pijących regularnie soki owocowe, zwłaszcza grejfrutowy</t></is></c><c r="G672" s="2" t="inlineStr" /><c r="H672" s="2" t="inlineStr" /><c r="I672" s="2" t="inlineStr" /><c r="J672" s="2" t="inlineStr" /><c r="K672" s="2" t="inlineStr"><is><t>zależne głównie od stopnia wydolności nerek</t></is></c><c r="L672" s="2" t="inlineStr"><is><t>częstsze podczas stosowania induktorów enzymów CYP</t></is></c><c r="M672" s="2" t="inlineStr"><is><t>związane ze stosowaniem leków wiążących kwasy żółciowe w przewodzie pokarmowym</t></is></c><c r="N672" s="2" t="inlineStr"><is><t>Glikokortykosteroidy są stosowane w:</t></is></c><c r="O672" s="2" t="inlineStr" /><c r="P672" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2017/18 - 2 termin</t></is></c><c r="Q672" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="673"><c r="A673" s="2" t="inlineStr"><is><t>CUKRZYCA</t></is></c><c r="B673" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C673" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D673" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E673" s="2" t="inlineStr"><is><t>Przyrost masy ciała powoduje:</t></is></c><c r="F673" s="2" t="inlineStr"><is><t>gliklazyd</t></is></c><c r="G673" s="2" t="inlineStr"><is><t>insulina izofanowa</t></is></c><c r="H673" s="2" t="inlineStr" /><c r="I673" s="2" t="inlineStr" /><c r="J673" s="2" t="inlineStr" /><c r="K673" s="2" t="inlineStr"><is><t>liraglutyd</t></is></c><c r="L673" s="2" t="inlineStr"><is><t>metformina</t></is></c><c r="M673" s="2" t="inlineStr" /><c r="N673" s="2" t="inlineStr" /><c r="O673" s="2" t="inlineStr" /><c r="P673" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2017/18 - 2 termin</t></is></c><c r="Q673" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="674"><c r="A674" s="2" t="inlineStr"><is><t>GLIKOKORTYKOSTEROIDY</t></is></c><c r="B674" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C674" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D674" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E674" s="2" t="inlineStr"><is><t>Glikokortykosteroidy dzieli się na słabo i silnie działające na podstawie:</t></is></c><c r="F674" s="2" t="inlineStr"><is><t>testu wazokonstrykcji naczyń (zblednięcia skóry)</t></is></c><c r="G674" s="2" t="inlineStr"><is><t>działania przeciwzapalnego</t></is></c><c r="H674" s="2" t="inlineStr" /><c r="I674" s="2" t="inlineStr" /><c r="J674" s="2" t="inlineStr" /><c r="K674" s="2" t="inlineStr"><is><t>działania mineralokortykoidowego</t></is></c><c r="L674" s="2" t="inlineStr"><is><t>działania immunosupresyjnego</t></is></c><c r="M674" s="2" t="inlineStr" /><c r="N674" s="2" t="inlineStr" /><c r="O674" s="2" t="inlineStr" /><c r="P674" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2017/18 - 2 termin</t></is></c><c r="Q674" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="675"><c r="A675" s="2" t="inlineStr"><is><t>LEKI MOCZOPĘDNE</t></is></c><c r="B675" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C675" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D675" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E675" s="2" t="inlineStr"><is><t>Za typowe polekowe działanie niepożądane podczas stosowania niesteroidowych leków przeciwzapalnych uznasz:</t></is></c><c r="F675" s="2" t="inlineStr"><is><t>krwawienie z wrzodu dwunastnicy</t></is></c><c r="G675" s="2" t="inlineStr"><is><t>skurcz oskrzeli u chorego z polipami nosa i przewlekłym zapaleniem zatok</t></is></c><c r="H675" s="2" t="inlineStr"><is><t>hipernatremię (zwiększenie stężenia sodu w surowicy)</t></is></c><c r="I675" s="2" t="inlineStr" /><c r="J675" s="2" t="inlineStr" /><c r="K675" s="2" t="inlineStr"><is><t>hipokaliemię (obniżenie stężenia potasu w surowicy)</t></is></c><c r="L675" s="2" t="inlineStr" /><c r="M675" s="2" t="inlineStr" /><c r="N675" s="2" t="inlineStr" /><c r="O675" s="2" t="inlineStr" /><c r="P675" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2017/18 - 2 termin</t></is></c><c r="Q675" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="676"><c r="A676" s="2" t="inlineStr"><is><t>FARMAKOLOGIA OGÓLNA I EBM</t></is></c><c r="B676" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C676" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D676" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E676" s="2" t="inlineStr"><is><t>Wskaż poprawną definicję:</t></is></c><c r="F676" s="2" t="inlineStr"><is><t>wpółczynnik (indeks) terapeutyczny leku – zakres między najmniejszą dawką skuteczną a maksymalną nie powodującą efektów toksycznych, im większy tym korzystniej</t></is></c><c r="G676" s="2" t="inlineStr"><is><t>placebo - interwencja pozbawiona bezpośredniego działania biologicznego, mająca stworzyć u pacjenta wrażenie, że otrzymuje on leczenie</t></is></c><c r="H676" s="2" t="inlineStr" /><c r="I676" s="2" t="inlineStr" /><c r="J676" s="2" t="inlineStr" /><c r="K676" s="2" t="inlineStr"><is><t>polekowe działanie niepożądane – każde niepożądane i niezamierzone zdarzenie podczas stosowania leku, bez konieczności ustalenia związku przyczynowo-skutkowego</t></is></c><c r="L676" s="2" t="inlineStr"><is><t>metaanaliza - badanie wieloośrodkowe, w którym grupa eksperymentalna porównywana jest do grupy kontrolne</t></is></c><c r="M676" s="2" t="inlineStr" /><c r="N676" s="2" t="inlineStr" /><c r="O676" s="2" t="inlineStr" /><c r="P676" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2017/18 - 2 termin</t></is></c><c r="Q676" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="677"><c r="A677" s="2" t="inlineStr"><is><t>UKŁAD PRZYWSPÓŁCZULNY</t></is></c><c r="B677" s="2" t="inlineStr"><is><t>Antidotum</t></is></c><c r="C677" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D677" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E677" s="2" t="inlineStr"><is><t>Objawy przedawkowania oksykodonu to:</t></is></c><c r="F677" s="2" t="inlineStr"><is><t>zmniejszenie częstości oddechów</t></is></c><c r="G677" s="2" t="inlineStr" /><c r="H677" s="2" t="inlineStr" /><c r="I677" s="2" t="inlineStr" /><c r="J677" s="2" t="inlineStr" /><c r="K677" s="2" t="inlineStr"><is><t>rozszerzone źrenice</t></is></c><c r="L677" s="2" t="inlineStr"><is><t>pobudzenie psychoruchowe</t></is></c><c r="M677" s="2" t="inlineStr"><is><t>gorączka obwodowa</t></is></c><c r="N677" s="2" t="inlineStr" /><c r="O677" s="2" t="inlineStr" /><c r="P677" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2017/18 - 2 termin</t></is></c><c r="Q677" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="678"><c r="A678" s="2" t="inlineStr"><is><t>NARKOTYCZNE LEKI PRZECIWBÓLOWE</t></is></c><c r="B678" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C678" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D678" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E678" s="2" t="inlineStr"><is><t>Szybki efekt przeciwbólowy można osiągnąć, stosując:</t></is></c><c r="F678" s="2" t="inlineStr"><is><t>fentanyl w postaci donosowej</t></is></c><c r="G678" s="2" t="inlineStr"><is><t>buprenorfinę w tabletkach podjęzykowych</t></is></c><c r="H678" s="2" t="inlineStr" /><c r="I678" s="2" t="inlineStr" /><c r="J678" s="2" t="inlineStr" /><c r="K678" s="2" t="inlineStr"><is><t>tramadol w systemie transdermalnym</t></is></c><c r="L678" s="2" t="inlineStr"><is><t>nalokson we wlewie dożylnym</t></is></c><c r="M678" s="2" t="inlineStr" /><c r="N678" s="2" t="inlineStr" /><c r="O678" s="2" t="inlineStr" /><c r="P678" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2017/18 - 2 termin</t></is></c><c r="Q678" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="679"><c r="A679" s="2" t="inlineStr"><is><t>NIEOPIOIDOWE LEKI PRZECIWBÓLOWE</t></is></c><c r="B679" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C679" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D679" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E679" s="2" t="inlineStr"><is><t>Działanie przeciwgorączkowe ma:</t></is></c><c r="F679" s="2" t="inlineStr"><is><t>metamizol</t></is></c><c r="G679" s="2" t="inlineStr"><is><t>paracetamol</t></is></c><c r="H679" s="2" t="inlineStr"><is><t>kwas acetylosalicylowy</t></is></c><c r="I679" s="2" t="inlineStr"><is><t>ibuprofen</t></is></c><c r="J679" s="2" t="inlineStr" /><c r="K679" s="2" t="inlineStr" /><c r="L679" s="2" t="inlineStr" /><c r="M679" s="2" t="inlineStr" /><c r="N679" s="2" t="inlineStr" /><c r="O679" s="2" t="inlineStr" /><c r="P679" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2017/18 - 2 termin</t></is></c><c r="Q679" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="680"><c r="A680" s="2" t="inlineStr"><is><t>NIEOPIOIDOWE LEKI PRZECIWBÓLOWE</t></is></c><c r="B680" s="2" t="inlineStr"><is><t>Przeciwwskazania</t></is></c><c r="C680" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D680" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E680" s="2" t="inlineStr"><is><t>Popularna aspiryna, czyli poprawnie kwas acetylosalicylowy:</t></is></c><c r="F680" s="2" t="inlineStr"><is><t>jest przeciwwskazana u dzieci do 12 r.ż</t></is></c><c r="G680" s="2" t="inlineStr"><is><t>konkuruje o miejsce wiązania z ibuprofenem</t></is></c><c r="H680" s="2" t="inlineStr" /><c r="I680" s="2" t="inlineStr" /><c r="J680" s="2" t="inlineStr" /><c r="K680" s="2" t="inlineStr"><is><t>działa odwracalnie antyagregacyjnie</t></is></c><c r="L680" s="2" t="inlineStr"><is><t>w małych dawkach preferencyjnie hamuje cyklooksygenazę 2</t></is></c><c r="M680" s="2" t="inlineStr" /><c r="N680" s="2" t="inlineStr" /><c r="O680" s="2" t="inlineStr" /><c r="P680" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2017/18 - 2 termin</t></is></c><c r="Q680" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="681"><c r="A681" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B681" s="2" t="inlineStr"><is><t>Antidotum</t></is></c><c r="C681" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D681" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E681" s="2" t="inlineStr"><is><t>Wskaż prawidłowy zestaw lek – antidotum:</t></is></c><c r="F681" s="2" t="inlineStr"><is><t>heparyna – siarczan protaminy</t></is></c><c r="G681" s="2" t="inlineStr"><is><t>warfaryna - fitomenadion</t></is></c><c r="H681" s="2" t="inlineStr"><is><t>dabigatraban – idarucizumab</t></is></c><c r="I681" s="2" t="inlineStr"><is><t>acenokumarol – koncentrat zespołu czynników protrombiny</t></is></c><c r="J681" s="2" t="inlineStr" /><c r="K681" s="2" t="inlineStr" /><c r="L681" s="2" t="inlineStr" /><c r="M681" s="2" t="inlineStr" /><c r="N681" s="2" t="inlineStr" /><c r="O681" s="2" t="inlineStr" /><c r="P681" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2017/18 - 2 termin</t></is></c><c r="Q681" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="682"><c r="A682" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B682" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C682" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D682" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E682" s="2" t="inlineStr"><is><t>U pacjentów z mechaniczną zastawką serca potwierdzono skuteczność przeciwzakrzepową:</t></is></c><c r="F682" s="2" t="inlineStr"><is><t>warfaryny</t></is></c><c r="G682" s="2" t="inlineStr" /><c r="H682" s="2" t="inlineStr" /><c r="I682" s="2" t="inlineStr" /><c r="J682" s="2" t="inlineStr" /><c r="K682" s="2" t="inlineStr"><is><t>fondaparyny</t></is></c><c r="L682" s="2" t="inlineStr"><is><t>kwasu acetylosalicylowego + klopidogrelu</t></is></c><c r="M682" s="2" t="inlineStr"><is><t>dabigatranu</t></is></c><c r="N682" s="2" t="inlineStr" /><c r="O682" s="2" t="inlineStr" /><c r="P682" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2017/18 - 2 termin</t></is></c><c r="Q682" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="683"><c r="A683" s="2" t="inlineStr"><is><t>LEKI PRZECIWNOWOTWOROWE</t></is></c><c r="B683" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C683" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D683" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E683" s="2" t="inlineStr"><is><t>Hematopoetycznymi czynnikami wzrostu, które znalazły zastosowanie kliniczne są:</t></is></c><c r="F683" s="2" t="inlineStr"><is><t>darbepoetyna</t></is></c><c r="G683" s="2" t="inlineStr"><is><t>filgrastym</t></is></c><c r="H683" s="2" t="inlineStr"><is><t>lenograstym</t></is></c><c r="I683" s="2" t="inlineStr"><is><t>interleukina-11</t></is></c><c r="J683" s="2" t="inlineStr" /><c r="K683" s="2" t="inlineStr" /><c r="L683" s="2" t="inlineStr" /><c r="M683" s="2" t="inlineStr" /><c r="N683" s="2" t="inlineStr" /><c r="O683" s="2" t="inlineStr" /><c r="P683" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2017/18 - 2 termin</t></is></c><c r="Q683" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="684"><c r="A684" s="2" t="inlineStr"><is><t>NIEOPIOIDOWE LEKI PRZECIWBÓLOWE</t></is></c><c r="B684" s="2" t="inlineStr"><is><t>Przeciwwskazania</t></is></c><c r="C684" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D684" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E684" s="2" t="inlineStr"><is><t>Przeciwwskazaniem do stosowania kwasu acetylosalicylowego w dawce antyagregacyjnej jest:</t></is></c><c r="F684" s="2" t="inlineStr"><is><t>nadwrażliwość na NLPZ (niesteroidowe leki przeciwzapalne)</t></is></c><c r="G684" s="2" t="inlineStr" /><c r="H684" s="2" t="inlineStr" /><c r="I684" s="2" t="inlineStr" /><c r="J684" s="2" t="inlineStr" /><c r="K684" s="2" t="inlineStr"><is><t>choroba wrzodowa górnego odcinka przewodu pokarmowego w wywiadach</t></is></c><c r="L684" s="2" t="inlineStr"><is><t>zespół zależności alkoholowej</t></is></c><c r="M684" s="2" t="inlineStr"><is><t>niewydolność nerek</t></is></c><c r="N684" s="2" t="inlineStr" /><c r="O684" s="2" t="inlineStr" /><c r="P684" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2017/18 - 2 termin</t></is></c><c r="Q684" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="685"><c r="A685" s="2" t="inlineStr"><is><t>LEKI HIPOLIPEMIZUJĄCE</t></is></c><c r="B685" s="2" t="inlineStr"><is><t>Interakcje</t></is></c><c r="C685" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D685" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E685" s="2" t="inlineStr"><is><t>Istotnemu metabolizmowi wątrobowemu za pośrednictwem izoenzymów CYP podlega:</t></is></c><c r="F685" s="2" t="inlineStr"><is><t>atorwastatyna</t></is></c><c r="G685" s="2" t="inlineStr"><is><t>symwastatyna</t></is></c><c r="H685" s="2" t="inlineStr" /><c r="I685" s="2" t="inlineStr" /><c r="J685" s="2" t="inlineStr" /><c r="K685" s="2" t="inlineStr"><is><t>rosuwastatyna</t></is></c><c r="L685" s="2" t="inlineStr"><is><t>prawastayna</t></is></c><c r="M685" s="2" t="inlineStr" /><c r="N685" s="2" t="inlineStr" /><c r="O685" s="2" t="inlineStr" /><c r="P685" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2017/18 - 2 termin</t></is></c><c r="Q685" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="686"><c r="A686" s="2" t="inlineStr"><is><t>LEKI HIPOLIPEMIZUJĄCE</t></is></c><c r="B686" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C686" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D686" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E686" s="2" t="inlineStr"><is><t>Inhibitory reduktazy HMG-CoA:</t></is></c><c r="F686" s="2" t="inlineStr"><is><t>w większym stopniu zmniejszają stężenie cholesterolu LDL w surowicy w porównaniu z fibratami</t></is></c><c r="G686" s="2" t="inlineStr" /><c r="H686" s="2" t="inlineStr" /><c r="I686" s="2" t="inlineStr" /><c r="J686" s="2" t="inlineStr" /><c r="K686" s="2" t="inlineStr"><is><t>w większym stopniu zmniejszają stężenie triglicerydów w surowicy w porównaniu z fibratami</t></is></c><c r="L686" s="2" t="inlineStr"><is><t>mają istotny wpływ na stężenie Lp(a) = lipoproteiny a</t></is></c><c r="M686" s="2" t="inlineStr"><is><t>nie powinny być łączone z inhibitorami PCSK9</t></is></c><c r="N686" s="2" t="inlineStr" /><c r="O686" s="2" t="inlineStr" /><c r="P686" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2017/18 - 2 termin</t></is></c><c r="Q686" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="687"><c r="A687" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B687" s="2" t="inlineStr"><is><t>Monitorowanie</t></is></c><c r="C687" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D687" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E687" s="2" t="inlineStr"><is><t>Wskaż prawidłowy zestaw lek – akceptowany sposób monitorowania działania:</t></is></c><c r="F687" s="2" t="inlineStr"><is><t>rywaroksaban – aktywność czynnika anty - Xa</t></is></c><c r="G687" s="2" t="inlineStr"><is><t>dabigatran - APTT</t></is></c><c r="H687" s="2" t="inlineStr"><is><t>acenokumarol – INR</t></is></c><c r="I687" s="2" t="inlineStr" /><c r="J687" s="2" t="inlineStr" /><c r="K687" s="2" t="inlineStr"><is><t>heparyna niefrakcjonowana – czas protrombinowy</t></is></c><c r="L687" s="2" t="inlineStr" /><c r="M687" s="2" t="inlineStr" /><c r="N687" s="2" t="inlineStr" /><c r="O687" s="2" t="inlineStr" /><c r="P687" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2017/18 - 2 termin</t></is></c><c r="Q687" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="688"><c r="A688" s="2" t="inlineStr"><is><t>LEKI IMMUNOSUPRESYJNE</t></is></c><c r="B688" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C688" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D688" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E688" s="2" t="inlineStr"><is><t>Wskaż zestaw zawierający inhibitory kalcyneuryny:</t></is></c><c r="F688" s="2" t="inlineStr"><is><t>pimekrolimus, takrolimus, cyklosporyna</t></is></c><c r="G688" s="2" t="inlineStr" /><c r="H688" s="2" t="inlineStr" /><c r="I688" s="2" t="inlineStr" /><c r="J688" s="2" t="inlineStr" /><c r="K688" s="2" t="inlineStr"><is><t>cyklosporyna, pimekrolimus, sirolimus</t></is></c><c r="L688" s="2" t="inlineStr"><is><t>ewerolimus, takrolimus, cyklosporyna</t></is></c><c r="M688" s="2" t="inlineStr"><is><t>takrolimus, azatiopryna, pimekrolimus</t></is></c><c r="N688" s="2" t="inlineStr" /><c r="O688" s="2" t="inlineStr" /><c r="P688" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2017/18 - 2 termin</t></is></c><c r="Q688" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="689"><c r="A689" s="2" t="inlineStr"><is><t>LEKI ROŚLINNE I SUPLEMENTY</t></is></c><c r="B689" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C689" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D689" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E689" s="2" t="inlineStr"><is><t>W Europie dopuszczono do obrotu biopodobne produkty zawierające infliksymab. Oznacza to, że:</t></is></c><c r="F689" s="2" t="inlineStr"><is><t>wykazano ich podobieństwo farmaceutyczne z produktem oryginalnym</t></is></c><c r="G689" s="2" t="inlineStr"><is><t>wykazano ich podobieństwo z produktem oryginalnym w modelach przedklinicznych</t></is></c><c r="H689" s="2" t="inlineStr"><is><t>wykazano jego podobieństwo z produktem oryginalnym w badaniach klinicznych</t></is></c><c r="I689" s="2" t="inlineStr"><is><t>wykazano ich podobną immunogenność z produktem oryginalnym w badaniach klinicznych</t></is></c><c r="J689" s="2" t="inlineStr" /><c r="K689" s="2" t="inlineStr" /><c r="L689" s="2" t="inlineStr" /><c r="M689" s="2" t="inlineStr" /><c r="N689" s="2" t="inlineStr" /><c r="O689" s="2" t="inlineStr" /><c r="P689" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2017/18 - 2 termin</t></is></c><c r="Q689" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="690"><c r="A690" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B690" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C690" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D690" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E690" s="2" t="inlineStr"><is><t>Rozkurczający wpływ na mięśniówkę przewodu pokarmowego wywiera:</t></is></c><c r="F690" s="2" t="inlineStr"><is><t>mebeweryna</t></is></c><c r="G690" s="2" t="inlineStr" /><c r="H690" s="2" t="inlineStr" /><c r="I690" s="2" t="inlineStr" /><c r="J690" s="2" t="inlineStr" /><c r="K690" s="2" t="inlineStr"><is><t>racekadotryl</t></is></c><c r="L690" s="2" t="inlineStr"><is><t>mesalazyna</t></is></c><c r="M690" s="2" t="inlineStr"><is><t>ryfaksymina</t></is></c><c r="N690" s="2" t="inlineStr" /><c r="O690" s="2" t="inlineStr" /><c r="P690" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2017/18 - 2 termin</t></is></c><c r="Q690" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="691"><c r="A691" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B691" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C691" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D691" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E691" s="2" t="inlineStr"><is><t>Metoklopramid:</t></is></c><c r="F691" s="2" t="inlineStr"><is><t>to lek przeciwwymiotny</t></is></c><c r="G691" s="2" t="inlineStr"><is><t>może spowodować hiperprolaktynemię</t></is></c><c r="H691" s="2" t="inlineStr"><is><t>to lek prokinetyczny</t></is></c><c r="I691" s="2" t="inlineStr"><is><t>może spowodować objawy pozapiramidowe</t></is></c><c r="J691" s="2" t="inlineStr" /><c r="K691" s="2" t="inlineStr" /><c r="L691" s="2" t="inlineStr" /><c r="M691" s="2" t="inlineStr" /><c r="N691" s="2" t="inlineStr" /><c r="O691" s="2" t="inlineStr" /><c r="P691" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2017/18 - 2 termin</t></is></c><c r="Q691" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="692"><c r="A692" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B692" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C692" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D692" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E692" s="2" t="inlineStr"><is><t>W skojarzonej terapii eradykacyjnej H. pylori zastosujesz zgodnie z aktualną wiedzą medyczną:</t></is></c><c r="F692" s="2" t="inlineStr"><is><t>omeprazol</t></is></c><c r="G692" s="2" t="inlineStr"><is><t>pantoprazol</t></is></c><c r="H692" s="2" t="inlineStr"><is><t>cytrynian bizmutu</t></is></c><c r="I692" s="2" t="inlineStr" /><c r="J692" s="2" t="inlineStr" /><c r="K692" s="2" t="inlineStr"><is><t>ranitydynę</t></is></c><c r="L692" s="2" t="inlineStr" /><c r="M692" s="2" t="inlineStr" /><c r="N692" s="2" t="inlineStr" /><c r="O692" s="2" t="inlineStr" /><c r="P692" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2017/18 - 2 termin</t></is></c><c r="Q692" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="693"><c r="A693" s="2" t="inlineStr"><is><t>STANY NAGŁE</t></is></c><c r="B693" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C693" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D693" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E693" s="2" t="inlineStr"><is><t>Izotonicznym krystaloidem do uzupełnienie płynów jest:</t></is></c><c r="F693" s="2" t="inlineStr"><is><t>0,9% NaCl</t></is></c><c r="G693" s="2" t="inlineStr"><is><t>płyn wieloelektrolitowy</t></is></c><c r="H693" s="2" t="inlineStr"><is><t>płyn 2 : 1 (5% glukoza + 0,9% NaCl)</t></is></c><c r="I693" s="2" t="inlineStr" /><c r="J693" s="2" t="inlineStr" /><c r="K693" s="2" t="inlineStr"><is><t>4% roztw. żelatyny</t></is></c><c r="L693" s="2" t="inlineStr" /><c r="M693" s="2" t="inlineStr" /><c r="N693" s="2" t="inlineStr" /><c r="O693" s="2" t="inlineStr" /><c r="P693" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2017/18 - 2 termin</t></is></c><c r="Q693" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="694"><c r="A694" s="2" t="inlineStr"><is><t>LEKI PRZECIWNOWOTWOROWE</t></is></c><c r="B694" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C694" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D694" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E694" s="2" t="inlineStr"><is><t>Lekiem genotoksycznym jest:</t></is></c><c r="F694" s="2" t="inlineStr"><is><t>busulfan</t></is></c><c r="G694" s="2" t="inlineStr"><is><t>mitomycyna</t></is></c><c r="H694" s="2" t="inlineStr"><is><t>daktynomycyna</t></is></c><c r="I694" s="2" t="inlineStr"><is><t>etopozyd</t></is></c><c r="J694" s="2" t="inlineStr" /><c r="K694" s="2" t="inlineStr" /><c r="L694" s="2" t="inlineStr" /><c r="M694" s="2" t="inlineStr" /><c r="N694" s="2" t="inlineStr" /><c r="O694" s="2" t="inlineStr" /><c r="P694" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2017/18 - 2 termin</t></is></c><c r="Q694" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="695"><c r="A695" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B695" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C695" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D695" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E695" s="2" t="inlineStr"><is><t>Dysforia, nudności, wymioty, biegunka, bóle mięśni, łzawienie, wyciek z nosa, pocenie, rozszerzenie źrenic, piloerekcja, ziewanie i gorączka to cechy zespołu odstawiennego u uzależnionych od:</t></is></c><c r="F695" s="2" t="inlineStr"><is><t>heroiny</t></is></c><c r="G695" s="2" t="inlineStr" /><c r="H695" s="2" t="inlineStr" /><c r="I695" s="2" t="inlineStr" /><c r="J695" s="2" t="inlineStr" /><c r="K695" s="2" t="inlineStr"><is><t>etanolu</t></is></c><c r="L695" s="2" t="inlineStr"><is><t>nikotyny</t></is></c><c r="M695" s="2" t="inlineStr"><is><t>kokainy</t></is></c><c r="N695" s="2" t="inlineStr" /><c r="O695" s="2" t="inlineStr" /><c r="P695" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2017/18 - 2 termin</t></is></c><c r="Q695" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="696"><c r="A696" s="2" t="inlineStr"><is><t>LEKI TOKSYCZNE W CIĄŻY</t></is></c><c r="B696" s="2" t="inlineStr"><is><t>Ciąża</t></is></c><c r="C696" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D696" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E696" s="2" t="inlineStr"><is><t>Mykotoksyny:</t></is></c><c r="F696" s="2" t="inlineStr"><is><t>to produkty wtórnego metabolizmu różnych rodzajów grzybów pleśniowych</t></is></c><c r="G696" s="2" t="inlineStr"><is><t>są wytwarzane jako produkt uboczny w procesach metabolicznych lub są produktem wytwarzanym w celach obronnych</t></is></c><c r="H696" s="2" t="inlineStr"><is><t>mogą mieć silne właściwości mutagenne lub teratogenne</t></is></c><c r="I696" s="2" t="inlineStr"><is><t>są potencjalnie toksyczne dla ludzi i zwierząt</t></is></c><c r="J696" s="2" t="inlineStr" /><c r="K696" s="2" t="inlineStr" /><c r="L696" s="2" t="inlineStr" /><c r="M696" s="2" t="inlineStr" /><c r="N696" s="2" t="inlineStr" /><c r="O696" s="2" t="inlineStr" /><c r="P696" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2017/18 - 2 termin</t></is></c><c r="Q696" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="697"><c r="A697" s="2" t="inlineStr"><is><t>FARMAKOKINETYKA</t></is></c><c r="B697" s="2" t="inlineStr"><is><t>Farmakokinetyka</t></is></c><c r="C697" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D697" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E697" s="2" t="inlineStr"><is><t>Wskaż korzystne cechy leku:</t></is></c><c r="F697" s="2" t="inlineStr"><is><t>biodostępność po podaniu p.o. dorównująca biodostępności po podaniu i.v</t></is></c><c r="G697" s="2" t="inlineStr"><is><t>dostępne swoiste antidotum</t></is></c><c r="H697" s="2" t="inlineStr" /><c r="I697" s="2" t="inlineStr" /><c r="J697" s="2" t="inlineStr" /><c r="K697" s="2" t="inlineStr"><is><t>procesy kinetyczne zgodne z kinetyką 0 rzędu</t></is></c><c r="L697" s="2" t="inlineStr"><is><t>duża kumulacja w tkankach – wiązanie z biomolekułami</t></is></c><c r="M697" s="2" t="inlineStr" /><c r="N697" s="2" t="inlineStr" /><c r="O697" s="2" t="inlineStr" /><c r="P697" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2017/18 - 2 termin</t></is></c><c r="Q697" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="698"><c r="A698" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B698" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C698" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D698" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E698" s="2" t="inlineStr"><is><t>Jaki lek przeciwbakteryjny może odpowiadać poniższej charakterystyce? Ma dobrą biodostępność po podaniu doustnym i jest skuteczny w zakażeniach Streptococcus pneumoniae przy obecnym profilu oporności tego gatunku pod warunkiem właściwego schematu ekspozycji na lek:</t></is></c><c r="F698" s="2" t="inlineStr"><is><t>lewofloksacyna</t></is></c><c r="G698" s="2" t="inlineStr"><is><t>amoksycylina</t></is></c><c r="H698" s="2" t="inlineStr" /><c r="I698" s="2" t="inlineStr" /><c r="J698" s="2" t="inlineStr" /><c r="K698" s="2" t="inlineStr"><is><t>doksycyklina</t></is></c><c r="L698" s="2" t="inlineStr"><is><t>ceftriakson</t></is></c><c r="M698" s="2" t="inlineStr" /><c r="N698" s="2" t="inlineStr" /><c r="O698" s="2" t="inlineStr" /><c r="P698" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2017/18 - 1 termin</t></is></c><c r="Q698" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="699"><c r="A699" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B699" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C699" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D699" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E699" s="2" t="inlineStr"><is><t>Co jest zasadniczym warunkiem skuteczności cefadroksylu w leczeniu niepowikłanych zakażeń układu moczowego?</t></is></c><c r="F699" s="2" t="inlineStr"><is><t>przestrzeganie stałego interwału dawkowania zgodnie z parametrami farmakokinetycznymi leku</t></is></c><c r="G699" s="2" t="inlineStr"><is><t>fT%&gt;MIC ≥ 60%</t></is></c><c r="H699" s="2" t="inlineStr" /><c r="I699" s="2" t="inlineStr" /><c r="J699" s="2" t="inlineStr" /><c r="K699" s="2" t="inlineStr"><is><t>stały 10-dniowy cykl leczenia</t></is></c><c r="L699" s="2" t="inlineStr"><is><t>podanie jak największej bezpiecznej dawki jednorazowej, czyli uzyskanie maksymalnego bezpiecznego stężenia leku w surowicy</t></is></c><c r="M699" s="2" t="inlineStr" /><c r="N699" s="2" t="inlineStr" /><c r="O699" s="2" t="inlineStr" /><c r="P699" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2017/18 - 1 termin</t></is></c><c r="Q699" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="700"><c r="A700" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B700" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C700" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D700" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E700" s="2" t="inlineStr"><is><t>Wskaż prawdziwe stwierdzenia dotyczące kwasu klawulanowego:</t></is></c><c r="F700" s="2" t="inlineStr"><is><t>kwas klawulanowy powoduje niezależnie działania niepożądane, np. Polekowe zapalenie wątroby</t></is></c><c r="G700" s="2" t="inlineStr"><is><t>zmniejszona wrażliwość Streptococcus pneumoniae na beta-laktamy ma mechanizm nieenzymatyczny, zatem stosowanie połączeń z kwasem klawulanowym w zakażeniach o tej etiologii nie ma uzasadnienia</t></is></c><c r="H700" s="2" t="inlineStr"><is><t>amoksycylina + kwas klawulanowy powodują znaczną dysbakteriozę i skłonność do nadkażeń florą szpitalną</t></is></c><c r="I700" s="2" t="inlineStr" /><c r="J700" s="2" t="inlineStr" /><c r="K700" s="2" t="inlineStr"><is><t>kwas klawulanowy jest przeciwwskazany w ciąży</t></is></c><c r="L700" s="2" t="inlineStr" /><c r="M700" s="2" t="inlineStr" /><c r="N700" s="2" t="inlineStr" /><c r="O700" s="2" t="inlineStr" /><c r="P700" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2017/18 - 1 termin</t></is></c><c r="Q700" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="701"><c r="A701" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B701" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C701" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D701" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E701" s="2" t="inlineStr"><is><t>Podaj prawidłową interpretację sytuacji klinicznej:</t></is></c><c r="F701" s="2" t="inlineStr"><is><t>w 1 h po zakończeniu dożylnego podania piperacyliny + tazobaktamu (pip + taz) wystąpiła pokrzywka i duszność, ciśnienie skurczowe = 80 mmHg → nadwrażliwość typu natychmiastowego na penicyliny → zakaz leczenia wszystkimi penicylinami</t></is></c><c r="G701" s="2" t="inlineStr"><is><t>po 1 tygodniu leczenia ceftriaksonem + azytromycyną domowego zapalenia płuc w szpitalu wystąpiła małopłytkowość PLT = 60 G/l → nadwrażliwość typu cytotoksycznego najprawdopodobniej po ceftriaksonie → zakaz leczenia wszystkimi cefalosporynami</t></is></c><c r="H701" s="2" t="inlineStr"><is><t>po 5 dniach leczenia ceftriaksonem z metronidazolem w ramach leczenia powikłanego zapalenia wyrostka robaczkowego po operacji apendektomii wystąpił atak kolki żółciowej, w USG złogi w pęcherzyku żółciowym → prawdopodobnie wzrost gęstości żółci z powodu wydzielania ceftriaksonu → zakaz kontynuacji ceftriaksonu</t></is></c><c r="I701" s="2" t="inlineStr" /><c r="J701" s="2" t="inlineStr" /><c r="K701" s="2" t="inlineStr"><is><t>po 1 tygodniu leczenia pip + taz z powodu powikłanego zakażenia jamy brzusznej wystąpiły uogólnione obrzęki, w bad. laboratoryjnych hipernatremia = 153 mmol/l → bez związku z antybiotykoterapią, należy szukać innej przyczyny → kontynuacja leczenia pip + taz</t></is></c><c r="L701" s="2" t="inlineStr"><is><t>W zakażeniach o etiologii metycylinooporne Staphylococcus spp. uzasadnione może być zastosowanie:</t></is></c><c r="M701" s="2" t="inlineStr" /><c r="N701" s="2" t="inlineStr" /><c r="O701" s="2" t="inlineStr" /><c r="P701" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2017/18 - 1 termin</t></is></c><c r="Q701" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="702"><c r="A702" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B702" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C702" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D702" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E702" s="2" t="inlineStr"><is><t>Łatwo jest prowadzić leczenie sekwencyjne w przypadku:</t></is></c><c r="F702" s="2" t="inlineStr"><is><t>kloksacyliny</t></is></c><c r="G702" s="2" t="inlineStr"><is><t>amoksycyliny + kwasu klawulanowego</t></is></c><c r="H702" s="2" t="inlineStr"><is><t>cefuroksymu</t></is></c><c r="I702" s="2" t="inlineStr" /><c r="J702" s="2" t="inlineStr" /><c r="K702" s="2" t="inlineStr"><is><t>ceftazydymu</t></is></c><c r="L702" s="2" t="inlineStr" /><c r="M702" s="2" t="inlineStr" /><c r="N702" s="2" t="inlineStr" /><c r="O702" s="2" t="inlineStr" /><c r="P702" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2017/18 - 1 termin</t></is></c><c r="Q702" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="703"><c r="A703" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B703" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C703" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D703" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E703" s="2" t="inlineStr"><is><t>Prawdziwe jest stwierdzenie:</t></is></c><c r="F703" s="2" t="inlineStr"><is><t>cefazolina i cefuroksym i.v. są lekami z wyboru w p-infekcyjnej profilaktyce okołozabiegowej</t></is></c><c r="G703" s="2" t="inlineStr"><is><t>amoksycylina + kwas klawulanowy p.o. jest lekiem z wyboru w leczeniu z wyprzedzeniem po pogryzieniu przez psa</t></is></c><c r="H703" s="2" t="inlineStr" /><c r="I703" s="2" t="inlineStr" /><c r="J703" s="2" t="inlineStr" /><c r="K703" s="2" t="inlineStr"><is><t>ampicylina i.v. jest lekiem z wyboru w p-infekcyjnej profilaktyce rany skórnej spowodowanej ostrym przedmiotem</t></is></c><c r="L703" s="2" t="inlineStr"><is><t>aksetyl cefuroksymu jest lekiem z wyboru w leczeniu z wyprzedzeniem asymptomatycznej bakteriurii u 75-letniej kobiety z nietrzymaniem moczu</t></is></c><c r="M703" s="2" t="inlineStr" /><c r="N703" s="2" t="inlineStr" /><c r="O703" s="2" t="inlineStr" /><c r="P703" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2017/18 - 1 termin</t></is></c><c r="Q703" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="704"><c r="A704" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B704" s="2" t="inlineStr"><is><t>Interakcje</t></is></c><c r="C704" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D704" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E704" s="2" t="inlineStr"><is><t>W którym przypadku decyzja dotycząca racjonalnego leczenia początkowego domowego zakażenia jest prawidłowa u pacjenta bez nadwrażliwości na leki w wywiadach?</t></is></c><c r="F704" s="2" t="inlineStr"><is><t>grypa u nieszczepionego 80-letniego mężczyzny z POChP – oseltamiwir</t></is></c><c r="G704" s="2" t="inlineStr"><is><t>zapalenie płuc u osoby bez chorób współtowarzyszących – amoksycylina w dawce 3-4 g/24 h</t></is></c><c r="H704" s="2" t="inlineStr" /><c r="I704" s="2" t="inlineStr" /><c r="J704" s="2" t="inlineStr" /><c r="K704" s="2" t="inlineStr"><is><t>angina paciorkowcowa – azytromycyna</t></is></c><c r="L704" s="2" t="inlineStr"><is><t>niezapalna ostra biegunka – cyprofloksacyna</t></is></c><c r="M704" s="2" t="inlineStr" /><c r="N704" s="2" t="inlineStr" /><c r="O704" s="2" t="inlineStr" /><c r="P704" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2017/18 - 1 termin</t></is></c><c r="Q704" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="705"><c r="A705" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B705" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C705" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D705" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E705" s="2" t="inlineStr"><is><t>Linezolid jest wskazany w terapii zakażeń o etiologii:</t></is></c><c r="F705" s="2" t="inlineStr"><is><t>wankomycynooporny Enterococcus faecium (WRE)</t></is></c><c r="G705" s="2" t="inlineStr"><is><t>Streptococcus pneumoniae opornej na penicylinę</t></is></c><c r="H705" s="2" t="inlineStr"><is><t>metycylinooporny gronkowiec złocisty (MRSA)</t></is></c><c r="I705" s="2" t="inlineStr" /><c r="J705" s="2" t="inlineStr" /><c r="K705" s="2" t="inlineStr"><is><t>Klebsiella pneumonae oporna na karbapenemy</t></is></c><c r="L705" s="2" t="inlineStr" /><c r="M705" s="2" t="inlineStr" /><c r="N705" s="2" t="inlineStr" /><c r="O705" s="2" t="inlineStr" /><c r="P705" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2017/18 - 1 termin</t></is></c><c r="Q705" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="706"><c r="A706" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B706" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C706" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D706" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E706" s="2" t="inlineStr"><is><t>Który zestaw przedstawia leki od najwęższego do najszerszego spektrum działania przeciwbakteryjnego:</t></is></c><c r="F706" s="2" t="inlineStr"><is><t>ampicylina – piperacylina – piperacylina + tazobaktam</t></is></c><c r="G706" s="2" t="inlineStr"><is><t>ertapenem – imipenem – meropenem + waborbaktam</t></is></c><c r="H706" s="2" t="inlineStr" /><c r="I706" s="2" t="inlineStr" /><c r="J706" s="2" t="inlineStr" /><c r="K706" s="2" t="inlineStr"><is><t>ceftazydym – cefotaksym – cefepim</t></is></c><c r="L706" s="2" t="inlineStr"><is><t>ampicylina – fenoksymetylopenicylina – kloksacylina</t></is></c><c r="M706" s="2" t="inlineStr" /><c r="N706" s="2" t="inlineStr" /><c r="O706" s="2" t="inlineStr" /><c r="P706" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2017/18 - 1 termin</t></is></c><c r="Q706" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="707"><c r="A707" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B707" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C707" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D707" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E707" s="2" t="inlineStr"><is><t>W leczeniu zakażenia bakteriami atypowymi u chorego z pierwotnym wydłużeniem QTc racjonalne jest zastosowanie:</t></is></c><c r="F707" s="2" t="inlineStr"><is><t>doksycykliny</t></is></c><c r="G707" s="2" t="inlineStr" /><c r="H707" s="2" t="inlineStr" /><c r="I707" s="2" t="inlineStr" /><c r="J707" s="2" t="inlineStr" /><c r="K707" s="2" t="inlineStr"><is><t>moksyfloksacyny</t></is></c><c r="L707" s="2" t="inlineStr"><is><t>klarytromycyny</t></is></c><c r="M707" s="2" t="inlineStr"><is><t>klindamycyny</t></is></c><c r="N707" s="2" t="inlineStr" /><c r="O707" s="2" t="inlineStr" /><c r="P707" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2017/18 - 1 termin</t></is></c><c r="Q707" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="708"><c r="A708" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B708" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C708" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D708" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E708" s="2" t="inlineStr"><is><t>Wskazaniem do zastosowania metronidazolu jest:</t></is></c><c r="F708" s="2" t="inlineStr"><is><t>biegunka o etiologii Clostridium difficile o nieciężkim przebiegu</t></is></c><c r="G708" s="2" t="inlineStr"><is><t>lamblioza</t></is></c><c r="H708" s="2" t="inlineStr" /><c r="I708" s="2" t="inlineStr" /><c r="J708" s="2" t="inlineStr" /><c r="K708" s="2" t="inlineStr"><is><t>eradykacja nosicielstwa Bacteroides fragilis z przewodu pokarmowego przed wszystkimi operacjami w polu czystym-skażonym</t></is></c><c r="L708" s="2" t="inlineStr"><is><t>toksoplazmoza</t></is></c><c r="M708" s="2" t="inlineStr" /><c r="N708" s="2" t="inlineStr" /><c r="O708" s="2" t="inlineStr" /><c r="P708" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2017/18 - 1 termin</t></is></c><c r="Q708" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="709"><c r="A709" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B709" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C709" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D709" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E709" s="2" t="inlineStr"><is><t>Kolistymetat sodu:</t></is></c><c r="F709" s="2" t="inlineStr"><is><t>jest prolekiem, który po przekształceniu w aktywną postać powoduje lizę błony komórek bakteryjnych</t></is></c><c r="G709" s="2" t="inlineStr"><is><t>może spowodować zaburzenia ruchowe (ataksja) i zaburzenia czuciowe (parestezje)</t></is></c><c r="H709" s="2" t="inlineStr"><is><t>jest stosowany w zakażeniach pałeczkami Gram (-) przy ograniczonych opcjach terapeutycznych</t></is></c><c r="I709" s="2" t="inlineStr" /><c r="J709" s="2" t="inlineStr" /><c r="K709" s="2" t="inlineStr"><is><t>jest stosowany wyłącznie dożylnie</t></is></c><c r="L709" s="2" t="inlineStr" /><c r="M709" s="2" t="inlineStr" /><c r="N709" s="2" t="inlineStr" /><c r="O709" s="2" t="inlineStr" /><c r="P709" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2017/18 - 1 termin</t></is></c><c r="Q709" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="710"><c r="A710" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B710" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C710" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D710" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E710" s="2" t="inlineStr"><is><t>Ze względu na podobieństwo w farmakologicznym mechanizmie działania nie należy łączyć:</t></is></c><c r="F710" s="2" t="inlineStr"><is><t>kotrymoksazolu i trimetoprimu</t></is></c><c r="G710" s="2" t="inlineStr"><is><t>erytromycyny i klindamycyny</t></is></c><c r="H710" s="2" t="inlineStr" /><c r="I710" s="2" t="inlineStr" /><c r="J710" s="2" t="inlineStr" /><c r="K710" s="2" t="inlineStr"><is><t>ampicyliny i gentamycyny</t></is></c><c r="L710" s="2" t="inlineStr"><is><t>wankomycyny i aztreonamu</t></is></c><c r="M710" s="2" t="inlineStr" /><c r="N710" s="2" t="inlineStr" /><c r="O710" s="2" t="inlineStr" /><c r="P710" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2017/18 - 1 termin</t></is></c><c r="Q710" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="711"><c r="A711" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B711" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C711" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D711" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E711" s="2" t="inlineStr"><is><t>Nadwrażliwość na promieniowanie ultrafioletowe (UV) może być związana ze stosowaniem:</t></is></c><c r="F711" s="2" t="inlineStr"><is><t>doksycykliny</t></is></c><c r="G711" s="2" t="inlineStr"><is><t>lewofloksacyny</t></is></c><c r="H711" s="2" t="inlineStr"><is><t>kotrymoksazolu</t></is></c><c r="I711" s="2" t="inlineStr" /><c r="J711" s="2" t="inlineStr" /><c r="K711" s="2" t="inlineStr"><is><t>amoksycyliny</t></is></c><c r="L711" s="2" t="inlineStr" /><c r="M711" s="2" t="inlineStr" /><c r="N711" s="2" t="inlineStr" /><c r="O711" s="2" t="inlineStr" /><c r="P711" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2017/18 - 1 termin</t></is></c><c r="Q711" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="712"><c r="A712" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B712" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C712" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D712" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E712" s="2" t="inlineStr"><is><t>Za uzasadnione uznasz dodanie metronidazolu do:</t></is></c><c r="F712" s="2" t="inlineStr"><is><t>cyprofloksacyny w leczeniu zakażenia mieszanego dróg żółciowych z udziałem beztlenowców</t></is></c><c r="G712" s="2" t="inlineStr" /><c r="H712" s="2" t="inlineStr" /><c r="I712" s="2" t="inlineStr" /><c r="J712" s="2" t="inlineStr" /><c r="K712" s="2" t="inlineStr"><is><t>amoksycyliny + kwasu klawulanowego w leczeniu zakażenia mieszanego zatok szczękowych z udziałem beztlenowców</t></is></c><c r="L712" s="2" t="inlineStr"><is><t>piperacyliny + tazobaktamu w leczeniu zachłystowego zapalenia płuc (zakażenie florą przewodu pokarmowego)</t></is></c><c r="M712" s="2" t="inlineStr"><is><t>imipenemu + cilastatyny w leczeniu kałowego zapalenia otrzewnej po perforacji jelita grubego (zakażenie florą przewodu pokarmowego)</t></is></c><c r="N712" s="2" t="inlineStr" /><c r="O712" s="2" t="inlineStr" /><c r="P712" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2017/18 - 1 termin</t></is></c><c r="Q712" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="713"><c r="A713" s="2" t="inlineStr"><is><t>LEKI PRZECIWPASOŻYTNICZE</t></is></c><c r="B713" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C713" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D713" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E713" s="2" t="inlineStr"><is><t>Właściwy wybór leku w infestacji pasożytniczej to:</t></is></c><c r="F713" s="2" t="inlineStr"><is><t>wszawica - permetryna</t></is></c><c r="G713" s="2" t="inlineStr"><is><t>rzęsistkowica - metronidazol</t></is></c><c r="H713" s="2" t="inlineStr"><is><t>toksoplazmoza – kotrymoksazol</t></is></c><c r="I713" s="2" t="inlineStr"><is><t>infestacja owsikiem - pyrantel</t></is></c><c r="J713" s="2" t="inlineStr" /><c r="K713" s="2" t="inlineStr" /><c r="L713" s="2" t="inlineStr" /><c r="M713" s="2" t="inlineStr" /><c r="N713" s="2" t="inlineStr" /><c r="O713" s="2" t="inlineStr" /><c r="P713" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2017/18 - 1 termin</t></is></c><c r="Q713" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="714"><c r="A714" s="2" t="inlineStr"><is><t>LEKI PRZECIWWIRUSOWE</t></is></c><c r="B714" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C714" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D714" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E714" s="2" t="inlineStr"><is><t>Właściwy wybór leku przeciwwirusowego w zakażeniu wirusowym to:</t></is></c><c r="F714" s="2" t="inlineStr"><is><t>wirus półpaśca – acyklowir</t></is></c><c r="G714" s="2" t="inlineStr"><is><t>przewlekłe wirusowe zapalenie wątroby typu C - bezpośrednio działające ledipaswir + sofosbuwir –</t></is></c><c r="H714" s="2" t="inlineStr" /><c r="I714" s="2" t="inlineStr" /><c r="J714" s="2" t="inlineStr" /><c r="K714" s="2" t="inlineStr"><is><t>rotawirus – loperamid</t></is></c><c r="L714" s="2" t="inlineStr"><is><t>kłykciny kończyste – pranobeks inozyny</t></is></c><c r="M714" s="2" t="inlineStr" /><c r="N714" s="2" t="inlineStr" /><c r="O714" s="2" t="inlineStr" /><c r="P714" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2017/18 - 1 termin</t></is></c><c r="Q714" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="715"><c r="A715" s="2" t="inlineStr"><is><t>LEKI PRZECIWGRZYBICZE</t></is></c><c r="B715" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C715" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D715" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E715" s="2" t="inlineStr"><is><t>W dermatofitozach skuteczne jest miejscowe użycie:</t></is></c><c r="F715" s="2" t="inlineStr"><is><t>naftyfiny</t></is></c><c r="G715" s="2" t="inlineStr"><is><t>klotrimazolu</t></is></c><c r="H715" s="2" t="inlineStr" /><c r="I715" s="2" t="inlineStr" /><c r="J715" s="2" t="inlineStr" /><c r="K715" s="2" t="inlineStr"><is><t>natamycyny</t></is></c><c r="L715" s="2" t="inlineStr"><is><t>imikwimodu</t></is></c><c r="M715" s="2" t="inlineStr" /><c r="N715" s="2" t="inlineStr" /><c r="O715" s="2" t="inlineStr" /><c r="P715" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2017/18 - 1 termin</t></is></c><c r="Q715" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="716"><c r="A716" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B716" s="2" t="inlineStr"><is><t>Sposób podania</t></is></c><c r="C716" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D716" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E716" s="2" t="inlineStr"><is><t>W przypadku biegunki o etiologii Clostridium difficile uzasadnione może być stosowanie:</t></is></c><c r="F716" s="2" t="inlineStr"><is><t>fidaksomycyny doustnie</t></is></c><c r="G716" s="2" t="inlineStr"><is><t>wankomycyny doustnie</t></is></c><c r="H716" s="2" t="inlineStr" /><c r="I716" s="2" t="inlineStr" /><c r="J716" s="2" t="inlineStr" /><c r="K716" s="2" t="inlineStr"><is><t>nifuroksazydu doustnie</t></is></c><c r="L716" s="2" t="inlineStr"><is><t>kotrymoksazolu doustnie</t></is></c><c r="M716" s="2" t="inlineStr" /><c r="N716" s="2" t="inlineStr" /><c r="O716" s="2" t="inlineStr" /><c r="P716" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2017/18 - 1 termin</t></is></c><c r="Q716" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="717"><c r="A717" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B717" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C717" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D717" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E717" s="2" t="inlineStr"><is><t>W leczeniu gruźlicy wielolekoopornej (MDR-TB) do leków podstawowych (grupa A, B i C wg wytycznych WHO) należy:</t></is></c><c r="F717" s="2" t="inlineStr"><is><t>moksyfloksacyna</t></is></c><c r="G717" s="2" t="inlineStr"><is><t>amikacyna</t></is></c><c r="H717" s="2" t="inlineStr"><is><t>linezolid</t></is></c><c r="I717" s="2" t="inlineStr"><is><t>kapreomycyna</t></is></c><c r="J717" s="2" t="inlineStr" /><c r="K717" s="2" t="inlineStr" /><c r="L717" s="2" t="inlineStr" /><c r="M717" s="2" t="inlineStr" /><c r="N717" s="2" t="inlineStr" /><c r="O717" s="2" t="inlineStr" /><c r="P717" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2017/18 - 1 termin</t></is></c><c r="Q717" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="718"><c r="A718" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B718" s="2" t="inlineStr"><is><t>Farmakokinetyka</t></is></c><c r="C718" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D718" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E718" s="2" t="inlineStr"><is><t>Opis farmakokinetyki leku A: lek A dobrze wchłania się z przewodu pokarmowego, dobrze przenika przez barierę krew – mózg, podlega metabolizmowi wątrobowemu. Lekiem A może być:</t></is></c><c r="F718" s="2" t="inlineStr"><is><t>worykonazol</t></is></c><c r="G718" s="2" t="inlineStr" /><c r="H718" s="2" t="inlineStr" /><c r="I718" s="2" t="inlineStr" /><c r="J718" s="2" t="inlineStr" /><c r="K718" s="2" t="inlineStr"><is><t>amoksycylina</t></is></c><c r="L718" s="2" t="inlineStr"><is><t>klindamycyna</t></is></c><c r="M718" s="2" t="inlineStr"><is><t>wankomycyna</t></is></c><c r="N718" s="2" t="inlineStr" /><c r="O718" s="2" t="inlineStr" /><c r="P718" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2017/18 - 1 termin</t></is></c><c r="Q718" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="719"><c r="A719" s="2" t="inlineStr"><is><t>LEKI PRZECIWGRZYBICZE</t></is></c><c r="B719" s="2" t="inlineStr"><is><t>Sposób podania</t></is></c><c r="C719" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D719" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E719" s="2" t="inlineStr"><is><t>Zmiany na płytkach paznokciowych polegające na ich zgrubieniu, przebarwieniu, łamliwości, nadmiernym rogowaceniu i pobruzdowaniu można leczyć:</t></is></c><c r="F719" s="2" t="inlineStr"><is><t>amorolfiną miejscowo</t></is></c><c r="G719" s="2" t="inlineStr"><is><t>terbinafiną doustnie</t></is></c><c r="H719" s="2" t="inlineStr"><is><t>itrakonazolem doustnie</t></is></c><c r="I719" s="2" t="inlineStr"><is><t>cyklopiroksolaminą miejscowo</t></is></c><c r="J719" s="2" t="inlineStr" /><c r="K719" s="2" t="inlineStr" /><c r="L719" s="2" t="inlineStr" /><c r="M719" s="2" t="inlineStr" /><c r="N719" s="2" t="inlineStr" /><c r="O719" s="2" t="inlineStr" /><c r="P719" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2017/18 - 1 termin</t></is></c><c r="Q719" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="720"><c r="A720" s="2" t="inlineStr"><is><t>LEKI PRZECIWGRZYBICZE</t></is></c><c r="B720" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C720" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D720" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E720" s="2" t="inlineStr"><is><t>Wskaż prawdziwe połączenie lek – wrażliwy drobnoustrój:</t></is></c><c r="F720" s="2" t="inlineStr"><is><t>kaspofungina _ Candida spp</t></is></c><c r="G720" s="2" t="inlineStr"><is><t>amfoterycyna B – Cryptococcus neoformans</t></is></c><c r="H720" s="2" t="inlineStr"><is><t>worykonazol - Candida crusei</t></is></c><c r="I720" s="2" t="inlineStr" /><c r="J720" s="2" t="inlineStr" /><c r="K720" s="2" t="inlineStr"><is><t>flukonazol – Aspergillus fumigatus</t></is></c><c r="L720" s="2" t="inlineStr" /><c r="M720" s="2" t="inlineStr" /><c r="N720" s="2" t="inlineStr" /><c r="O720" s="2" t="inlineStr" /><c r="P720" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2017/18 - 1 termin</t></is></c><c r="Q720" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="721"><c r="A721" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B721" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C721" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D721" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E721" s="2" t="inlineStr"><is><t>Aktualnie wg komunikatu WHO krytyczny problem wielolekooporności na większość leków p-bakteryjnych dotyczy:</t></is></c><c r="F721" s="2" t="inlineStr"><is><t>Acinetobacter baumani z opornością na karbapenemy</t></is></c><c r="G721" s="2" t="inlineStr"><is><t>Pseudomonas aeruginosa z opornością na karbapenemy</t></is></c><c r="H721" s="2" t="inlineStr"><is><t>Enterobacteriacae z opornością na karbapenemy</t></is></c><c r="I721" s="2" t="inlineStr" /><c r="J721" s="2" t="inlineStr" /><c r="K721" s="2" t="inlineStr"><is><t>Stenotrophomonas maltophilia z opornością na karbapenemy</t></is></c><c r="L721" s="2" t="inlineStr" /><c r="M721" s="2" t="inlineStr" /><c r="N721" s="2" t="inlineStr" /><c r="O721" s="2" t="inlineStr" /><c r="P721" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2017/18 - 1 termin</t></is></c><c r="Q721" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="722"><c r="A722" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B722" s="2" t="inlineStr"><is><t>Dawkowanie</t></is></c><c r="C722" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D722" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E722" s="2" t="inlineStr"><is><t>Dla leków p-infekcyjnych dla których celem farmakodynamicznym jest wysoka wartość fAUC : MIC, np. fluorochinolonów zasadne jest:</t></is></c><c r="F722" s="2" t="inlineStr"><is><t>zwiększenie w bezpiecznych granicach skumulowanej dobowej dawki leku</t></is></c><c r="G722" s="2" t="inlineStr" /><c r="H722" s="2" t="inlineStr" /><c r="I722" s="2" t="inlineStr" /><c r="J722" s="2" t="inlineStr" /><c r="K722" s="2" t="inlineStr"><is><t>precyzyjne ustalenie jak najczęstszego dawkowania leku</t></is></c><c r="L722" s="2" t="inlineStr"><is><t>monitorowanie stężenia maksymalnego (peak) w celu modyfikacji dawki</t></is></c><c r="M722" s="2" t="inlineStr"><is><t>osiągnięcie zdefiniowanej wartości fCmin : MIC</t></is></c><c r="N722" s="2" t="inlineStr" /><c r="O722" s="2" t="inlineStr" /><c r="P722" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2017/18 - 1 termin</t></is></c><c r="Q722" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="723"><c r="A723" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B723" s="2" t="inlineStr"><is><t>Dawkowanie</t></is></c><c r="C723" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D723" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E723" s="2" t="inlineStr"><is><t>U pacjenta z eGFR &lt; 30 ml/min (wyliczony z wzoru Cockcrofta-Gaulta) należy zmodyfikować dawkowanie:</t></is></c><c r="F723" s="2" t="inlineStr"><is><t>gentamycyny</t></is></c><c r="G723" s="2" t="inlineStr"><is><t>wankomycyny</t></is></c><c r="H723" s="2" t="inlineStr"><is><t>imipenemu</t></is></c><c r="I723" s="2" t="inlineStr" /><c r="J723" s="2" t="inlineStr" /><c r="K723" s="2" t="inlineStr"><is><t>klindamycyny</t></is></c><c r="L723" s="2" t="inlineStr" /><c r="M723" s="2" t="inlineStr" /><c r="N723" s="2" t="inlineStr" /><c r="O723" s="2" t="inlineStr" /><c r="P723" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2017/18 - 1 termin</t></is></c><c r="Q723" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="724"><c r="A724" s="2" t="inlineStr"><is><t>CUKRZYCA</t></is></c><c r="B724" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C724" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D724" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E724" s="2" t="inlineStr"><is><t>Do długoterminowych działań niepożądanych terapii HAART należy:</t></is></c><c r="F724" s="2" t="inlineStr"><is><t>uszkodzenie wątroby</t></is></c><c r="G724" s="2" t="inlineStr"><is><t>zespół lipodystrofii</t></is></c><c r="H724" s="2" t="inlineStr"><is><t>kwasica mleczanowa</t></is></c><c r="I724" s="2" t="inlineStr"><is><t>insulinooporność</t></is></c><c r="J724" s="2" t="inlineStr" /><c r="K724" s="2" t="inlineStr" /><c r="L724" s="2" t="inlineStr" /><c r="M724" s="2" t="inlineStr" /><c r="N724" s="2" t="inlineStr" /><c r="O724" s="2" t="inlineStr" /><c r="P724" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2017/18 - 1 termin</t></is></c><c r="Q724" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="725"><c r="A725" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B725" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C725" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D725" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E725" s="2" t="inlineStr"><is><t>Do jakiego związku może się odnosić następujący opis: ma słabe działanie antyseptyczne, po wchłonięciu może powodować ciężkie powikłania tj. Uszkodzenia wątroby i nerek, niewydolność serca, splątanie, a nawet zgon:</t></is></c><c r="F725" s="2" t="inlineStr"><is><t>boran sodu</t></is></c><c r="G725" s="2" t="inlineStr" /><c r="H725" s="2" t="inlineStr" /><c r="I725" s="2" t="inlineStr" /><c r="J725" s="2" t="inlineStr" /><c r="K725" s="2" t="inlineStr"><is><t>oktenidyna</t></is></c><c r="L725" s="2" t="inlineStr"><is><t>woda utleniona</t></is></c><c r="M725" s="2" t="inlineStr"><is><t>jodopowidon</t></is></c><c r="N725" s="2" t="inlineStr" /><c r="O725" s="2" t="inlineStr" /><c r="P725" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2017/18 - 1 termin</t></is></c><c r="Q725" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="726"><c r="A726" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B726" s="2" t="inlineStr"><is><t>Dawkowanie</t></is></c><c r="C726" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D726" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E726" s="2" t="inlineStr"><is><t>U pacjenta leczonego antagonistą witaminy K (warfaryną, acenokumarolem) zmianę efektu przeciwzakrzepowego bez adekwatnej modyfikacji dawki tego leku może spowodować:</t></is></c><c r="F726" s="2" t="inlineStr"><is><t>flukonazol</t></is></c><c r="G726" s="2" t="inlineStr"><is><t>klarytromycyna</t></is></c><c r="H726" s="2" t="inlineStr"><is><t>ryfampicyna</t></is></c><c r="I726" s="2" t="inlineStr"><is><t>cyprofloksacyna</t></is></c><c r="J726" s="2" t="inlineStr" /><c r="K726" s="2" t="inlineStr" /><c r="L726" s="2" t="inlineStr" /><c r="M726" s="2" t="inlineStr" /><c r="N726" s="2" t="inlineStr" /><c r="O726" s="2" t="inlineStr" /><c r="P726" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2017/18 - 1 termin</t></is></c><c r="Q726" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="727"><c r="A727" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B727" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C727" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D727" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E727" s="2" t="inlineStr"><is><t>W zakażeniach o etiologii Streptococcus pneumoniae skuteczny/a może być:</t></is></c><c r="F727" s="2" t="inlineStr"><is><t>ceftriakson</t></is></c><c r="G727" s="2" t="inlineStr"><is><t>klarytromycyna</t></is></c><c r="H727" s="2" t="inlineStr"><is><t>amoksycylina</t></is></c><c r="I727" s="2" t="inlineStr"><is><t>lewofloksacyna</t></is></c><c r="J727" s="2" t="inlineStr" /><c r="K727" s="2" t="inlineStr" /><c r="L727" s="2" t="inlineStr" /><c r="M727" s="2" t="inlineStr" /><c r="N727" s="2" t="inlineStr" /><c r="O727" s="2" t="inlineStr" /><c r="P727" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2017/18 - 2 termin</t></is></c><c r="Q727" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="728"><c r="A728" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B728" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C728" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D728" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E728" s="2" t="inlineStr"><is><t>W zakażeniach o etiologii Escherichia coli skuteczny/a może być:</t></is></c><c r="F728" s="2" t="inlineStr"><is><t>cefuroksym</t></is></c><c r="G728" s="2" t="inlineStr"><is><t>kotrymoksazol</t></is></c><c r="H728" s="2" t="inlineStr"><is><t>fosfomycyna</t></is></c><c r="I728" s="2" t="inlineStr" /><c r="J728" s="2" t="inlineStr" /><c r="K728" s="2" t="inlineStr"><is><t>metronidazol</t></is></c><c r="L728" s="2" t="inlineStr" /><c r="M728" s="2" t="inlineStr" /><c r="N728" s="2" t="inlineStr" /><c r="O728" s="2" t="inlineStr" /><c r="P728" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2017/18 - 2 termin</t></is></c><c r="Q728" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="729"><c r="A729" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B729" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C729" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D729" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E729" s="2" t="inlineStr"><is><t>W zakażeniach o etiologii Staphylococcus aureus metycylinowrażliwy (MSSA) skuteczny/a może być:</t></is></c><c r="F729" s="2" t="inlineStr"><is><t>cefadroksyl</t></is></c><c r="G729" s="2" t="inlineStr"><is><t>klindamycyna</t></is></c><c r="H729" s="2" t="inlineStr"><is><t>kloksacylina</t></is></c><c r="I729" s="2" t="inlineStr" /><c r="J729" s="2" t="inlineStr" /><c r="K729" s="2" t="inlineStr"><is><t>fenoksymetylopenicylina</t></is></c><c r="L729" s="2" t="inlineStr" /><c r="M729" s="2" t="inlineStr" /><c r="N729" s="2" t="inlineStr" /><c r="O729" s="2" t="inlineStr" /><c r="P729" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2017/18 - 2 termin</t></is></c><c r="Q729" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="730"><c r="A730" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B730" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C730" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D730" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E730" s="2" t="inlineStr"><is><t>W zakażeniu o etiologii Streptococcus pyogenes skuteczny/a może być:</t></is></c><c r="F730" s="2" t="inlineStr"><is><t>penicylina benzylowa</t></is></c><c r="G730" s="2" t="inlineStr"><is><t>erytromycyna</t></is></c><c r="H730" s="2" t="inlineStr"><is><t>fenoksymetylopenicylina</t></is></c><c r="I730" s="2" t="inlineStr" /><c r="J730" s="2" t="inlineStr" /><c r="K730" s="2" t="inlineStr"><is><t>aztreonam</t></is></c><c r="L730" s="2" t="inlineStr"><is><t>W zakażeniu o etiologii Pseudomonas aeruginosa skuteczny/a może być:</t></is></c><c r="M730" s="2" t="inlineStr" /><c r="N730" s="2" t="inlineStr" /><c r="O730" s="2" t="inlineStr" /><c r="P730" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2017/18 - 2 termin</t></is></c><c r="Q730" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="731"><c r="A731" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B731" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C731" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D731" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E731" s="2" t="inlineStr"><is><t>W zakażeniach wywołanych przez beztlenowce (w tym Bacteroides fragilis) skuteczny/a może być:</t></is></c><c r="F731" s="2" t="inlineStr"><is><t>amoksycylina + kwas klawulanowy</t></is></c><c r="G731" s="2" t="inlineStr"><is><t>imipenem + cilastatyna</t></is></c><c r="H731" s="2" t="inlineStr"><is><t>klindamycyna</t></is></c><c r="I731" s="2" t="inlineStr" /><c r="J731" s="2" t="inlineStr" /><c r="K731" s="2" t="inlineStr"><is><t>cyprofloksacyna</t></is></c><c r="L731" s="2" t="inlineStr" /><c r="M731" s="2" t="inlineStr" /><c r="N731" s="2" t="inlineStr" /><c r="O731" s="2" t="inlineStr" /><c r="P731" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2017/18 - 2 termin</t></is></c><c r="Q731" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="732"><c r="A732" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B732" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C732" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D732" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E732" s="2" t="inlineStr"><is><t>W zakażeniach o etiologii Mycoplasma pneumoniae skuteczny/a może być:</t></is></c><c r="F732" s="2" t="inlineStr"><is><t>azytromycyna</t></is></c><c r="G732" s="2" t="inlineStr"><is><t>doksycyklina</t></is></c><c r="H732" s="2" t="inlineStr"><is><t>moksyfloksacyna</t></is></c><c r="I732" s="2" t="inlineStr" /><c r="J732" s="2" t="inlineStr" /><c r="K732" s="2" t="inlineStr"><is><t>amikacyna</t></is></c><c r="L732" s="2" t="inlineStr" /><c r="M732" s="2" t="inlineStr" /><c r="N732" s="2" t="inlineStr" /><c r="O732" s="2" t="inlineStr" /><c r="P732" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2017/18 - 2 termin</t></is></c><c r="Q732" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="733"><c r="A733" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B733" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C733" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D733" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E733" s="2" t="inlineStr"><is><t>W eradykacji Helicobacter pylori można zastosować:</t></is></c><c r="F733" s="2" t="inlineStr"><is><t>tetracyklina</t></is></c><c r="G733" s="2" t="inlineStr"><is><t>amoksycylina</t></is></c><c r="H733" s="2" t="inlineStr"><is><t>cytrynian bizmutu</t></is></c><c r="I733" s="2" t="inlineStr"><is><t>metronidazol</t></is></c><c r="J733" s="2" t="inlineStr" /><c r="K733" s="2" t="inlineStr" /><c r="L733" s="2" t="inlineStr" /><c r="M733" s="2" t="inlineStr" /><c r="N733" s="2" t="inlineStr" /><c r="O733" s="2" t="inlineStr" /><c r="P733" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2017/18 - 2 termin</t></is></c><c r="Q733" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="734"><c r="A734" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B734" s="2" t="inlineStr"><is><t>Ciąża</t></is></c><c r="C734" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D734" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E734" s="2" t="inlineStr"><is><t>Ciężarna kobieta leczona była z konieczności gentamycyną z powodu powikłanego zapalenia nerek. Na jakie ryzyka narażone zostało jej dziecko w czasie takiej terapii?</t></is></c><c r="F734" s="2" t="inlineStr"><is><t>głuchotę</t></is></c><c r="G734" s="2" t="inlineStr" /><c r="H734" s="2" t="inlineStr" /><c r="I734" s="2" t="inlineStr" /><c r="J734" s="2" t="inlineStr" /><c r="K734" s="2" t="inlineStr"><is><t>powstanie deformacji kostnych</t></is></c><c r="L734" s="2" t="inlineStr"><is><t>utratę wzroku</t></is></c><c r="M734" s="2" t="inlineStr"><is><t>zahamowanie rozwoju chrząstek</t></is></c><c r="N734" s="2" t="inlineStr" /><c r="O734" s="2" t="inlineStr" /><c r="P734" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2017/18 - 2 termin</t></is></c><c r="Q734" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="735"><c r="A735" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B735" s="2" t="inlineStr"><is><t>Interakcje</t></is></c><c r="C735" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D735" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E735" s="2" t="inlineStr"><is><t>Wskaż prawidłowe skojarzenie lek przeciwbakteryjny – mechanizm działania</t></is></c><c r="F735" s="2" t="inlineStr"><is><t>kolistyna – uszkadza błonę komórkową</t></is></c><c r="G735" s="2" t="inlineStr" /><c r="H735" s="2" t="inlineStr" /><c r="I735" s="2" t="inlineStr" /><c r="J735" s="2" t="inlineStr" /><c r="K735" s="2" t="inlineStr"><is><t>cyprofloksacyna – działa cytotoksycznie uszkadzając DNA</t></is></c><c r="L735" s="2" t="inlineStr"><is><t>azytromycyna – hamuje syntezę ściany bakteryjnej</t></is></c><c r="M735" s="2" t="inlineStr"><is><t>metronidazol – hamuje syntezę DNA</t></is></c><c r="N735" s="2" t="inlineStr" /><c r="O735" s="2" t="inlineStr" /><c r="P735" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2017/18 - 2 termin</t></is></c><c r="Q735" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="736"><c r="A736" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B736" s="2" t="inlineStr"><is><t>Sposób podania</t></is></c><c r="C736" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D736" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E736" s="2" t="inlineStr"><is><t>Aby uzyskać działanie ogólnoustrojowe, doustnie można podać:</t></is></c><c r="F736" s="2" t="inlineStr"><is><t>lewofloksacynę</t></is></c><c r="G736" s="2" t="inlineStr" /><c r="H736" s="2" t="inlineStr" /><c r="I736" s="2" t="inlineStr" /><c r="J736" s="2" t="inlineStr" /><c r="K736" s="2" t="inlineStr"><is><t>wankomycynę</t></is></c><c r="L736" s="2" t="inlineStr"><is><t>fidaksomycynę</t></is></c><c r="M736" s="2" t="inlineStr"><is><t>ryfaksyminę</t></is></c><c r="N736" s="2" t="inlineStr" /><c r="O736" s="2" t="inlineStr" /><c r="P736" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2017/18 - 2 termin</t></is></c><c r="Q736" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="737"><c r="A737" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B737" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C737" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D737" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E737" s="2" t="inlineStr"><is><t>Do antybiotyków o szerokim zakresie działania przeciwbakteryjnego na bakterie Gram (+) i Gram (-) należy:</t></is></c><c r="F737" s="2" t="inlineStr"><is><t>tygecyklina</t></is></c><c r="G737" s="2" t="inlineStr"><is><t>piperacylina + tazobaktam</t></is></c><c r="H737" s="2" t="inlineStr" /><c r="I737" s="2" t="inlineStr" /><c r="J737" s="2" t="inlineStr" /><c r="K737" s="2" t="inlineStr"><is><t>kolistyna</t></is></c><c r="L737" s="2" t="inlineStr"><is><t>linezolid</t></is></c><c r="M737" s="2" t="inlineStr" /><c r="N737" s="2" t="inlineStr" /><c r="O737" s="2" t="inlineStr" /><c r="P737" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2017/18 - 2 termin</t></is></c><c r="Q737" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="738"><c r="A738" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B738" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C738" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D738" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E738" s="2" t="inlineStr"><is><t>Do leków do stosowania wyłącznie miejscowego należy:</t></is></c><c r="F738" s="2" t="inlineStr"><is><t>bacytracyna</t></is></c><c r="G738" s="2" t="inlineStr"><is><t>mupirocyna</t></is></c><c r="H738" s="2" t="inlineStr"><is><t>nystatyna</t></is></c><c r="I738" s="2" t="inlineStr" /><c r="J738" s="2" t="inlineStr" /><c r="K738" s="2" t="inlineStr"><is><t>fosfomycyna</t></is></c><c r="L738" s="2" t="inlineStr" /><c r="M738" s="2" t="inlineStr" /><c r="N738" s="2" t="inlineStr" /><c r="O738" s="2" t="inlineStr" /><c r="P738" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2017/18 - 2 termin</t></is></c><c r="Q738" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="739"><c r="A739" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B739" s="2" t="inlineStr"><is><t>Interakcje</t></is></c><c r="C739" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D739" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E739" s="2" t="inlineStr"><is><t>Leki przeciwbakteryjne o wysokim potencjale selekcji szczepów Clostridium difficile to:</t></is></c><c r="F739" s="2" t="inlineStr"><is><t>amoksycylina + kwas klawulanowy</t></is></c><c r="G739" s="2" t="inlineStr"><is><t>klindamycyna</t></is></c><c r="H739" s="2" t="inlineStr"><is><t>cyprofloksacyna</t></is></c><c r="I739" s="2" t="inlineStr" /><c r="J739" s="2" t="inlineStr" /><c r="K739" s="2" t="inlineStr"><is><t>teikoplanina</t></is></c><c r="L739" s="2" t="inlineStr" /><c r="M739" s="2" t="inlineStr" /><c r="N739" s="2" t="inlineStr" /><c r="O739" s="2" t="inlineStr" /><c r="P739" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2017/18 - 2 termin</t></is></c><c r="Q739" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="740"><c r="A740" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B740" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C740" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D740" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E740" s="2" t="inlineStr"><is><t>Wskaż właściwe połączenia: mechanizm oporności na lek przeciwbakteryjny – lek unieczynniany w tym mechanizmie:</t></is></c><c r="F740" s="2" t="inlineStr"><is><t>wytwarzanie β-laktamaz – amoksycylina</t></is></c><c r="G740" s="2" t="inlineStr" /><c r="H740" s="2" t="inlineStr" /><c r="I740" s="2" t="inlineStr" /><c r="J740" s="2" t="inlineStr" /><c r="K740" s="2" t="inlineStr"><is><t>wytwarzanie karbapenemaz – tazobaktam</t></is></c><c r="L740" s="2" t="inlineStr"><is><t>metylacja podjednostki 50S rybosomu - fosfomycyna</t></is></c><c r="M740" s="2" t="inlineStr"><is><t>modyfikacja/ochrona topoizomerazy II – metronidazol</t></is></c><c r="N740" s="2" t="inlineStr" /><c r="O740" s="2" t="inlineStr" /><c r="P740" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2017/18 - 2 termin</t></is></c><c r="Q740" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="741"><c r="A741" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B741" s="2" t="inlineStr"><is><t>Interakcje</t></is></c><c r="C741" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D741" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E741" s="2" t="inlineStr"><is><t>Cel farmakodynamiczny, jakim jest zależność efektu od czasu w jakim stężenie leku przekracza MIC (fT&gt;MIC) należy osiągnąć w trakcie stosowania:</t></is></c><c r="F741" s="2" t="inlineStr"><is><t>linezolidu</t></is></c><c r="G741" s="2" t="inlineStr"><is><t>ceftriaksonu</t></is></c><c r="H741" s="2" t="inlineStr" /><c r="I741" s="2" t="inlineStr" /><c r="J741" s="2" t="inlineStr" /><c r="K741" s="2" t="inlineStr"><is><t>metronidazolu</t></is></c><c r="L741" s="2" t="inlineStr"><is><t>cyprofloksacyny</t></is></c><c r="M741" s="2" t="inlineStr" /><c r="N741" s="2" t="inlineStr" /><c r="O741" s="2" t="inlineStr" /><c r="P741" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2017/18 - 2 termin</t></is></c><c r="Q741" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="742"><c r="A742" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B742" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C742" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D742" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E742" s="2" t="inlineStr"><is><t>Który z poniższych leków hamuje podjędnostkę 30S rybosomów?</t></is></c><c r="F742" s="2" t="inlineStr"><is><t>tygecyklina</t></is></c><c r="G742" s="2" t="inlineStr"><is><t>streptomycyna</t></is></c><c r="H742" s="2" t="inlineStr" /><c r="I742" s="2" t="inlineStr" /><c r="J742" s="2" t="inlineStr" /><c r="K742" s="2" t="inlineStr"><is><t>chinuprystyna-dalfoprystyna</t></is></c><c r="L742" s="2" t="inlineStr"><is><t>linezolid</t></is></c><c r="M742" s="2" t="inlineStr" /><c r="N742" s="2" t="inlineStr" /><c r="O742" s="2" t="inlineStr" /><c r="P742" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2017/18 - 2 termin</t></is></c><c r="Q742" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="743"><c r="A743" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B743" s="2" t="inlineStr"><is><t>Przeciwwskazania</t></is></c><c r="C743" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D743" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E743" s="2" t="inlineStr"><is><t>Antybiotyki beta-laktamowe:</t></is></c><c r="F743" s="2" t="inlineStr"><is><t>cechują się bardzo dobrym profilem bezpieczeństwa</t></is></c><c r="G743" s="2" t="inlineStr"><is><t>są praktycznie pozbawione istotnych interakcji lekowych</t></is></c><c r="H743" s="2" t="inlineStr" /><c r="I743" s="2" t="inlineStr" /><c r="J743" s="2" t="inlineStr" /><c r="K743" s="2" t="inlineStr"><is><t>bardzo dobrze dystrybuują do płynu mózgowo rdzeniowego</t></is></c><c r="L743" s="2" t="inlineStr"><is><t>są przeciwwskazane w umiarkowanej i ciężkiej niewydolności wątroby</t></is></c><c r="M743" s="2" t="inlineStr" /><c r="N743" s="2" t="inlineStr" /><c r="O743" s="2" t="inlineStr" /><c r="P743" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2017/18 - 2 termin</t></is></c><c r="Q743" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="744"><c r="A744" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B744" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C744" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D744" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E744" s="2" t="inlineStr"><is><t>Fluorochinolony:</t></is></c><c r="F744" s="2" t="inlineStr"><is><t>mogą powodować zapalenie więzadeł</t></is></c><c r="G744" s="2" t="inlineStr" /><c r="H744" s="2" t="inlineStr" /><c r="I744" s="2" t="inlineStr" /><c r="J744" s="2" t="inlineStr" /><c r="K744" s="2" t="inlineStr"><is><t>słabo wchłaniają się z przewodu pokarmowego</t></is></c><c r="L744" s="2" t="inlineStr"><is><t>są grupą, na którą rzadko stwierdza się oporność bakteryjną</t></is></c><c r="M744" s="2" t="inlineStr"><is><t>niezależnie od generacji wykazują aktywność wyłącznie wobec bakterii tlenowych</t></is></c><c r="N744" s="2" t="inlineStr" /><c r="O744" s="2" t="inlineStr" /><c r="P744" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2017/18 - 2 termin</t></is></c><c r="Q744" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="745"><c r="A745" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B745" s="2" t="inlineStr"><is><t>Przeciwwskazania</t></is></c><c r="C745" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D745" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E745" s="2" t="inlineStr"><is><t>Tetracykliny:</t></is></c><c r="F745" s="2" t="inlineStr"><is><t>są przeciwwskazane u dzieci</t></is></c><c r="G745" s="2" t="inlineStr"><is><t>działają także na bakterie atypowe</t></is></c><c r="H745" s="2" t="inlineStr"><is><t>mogą być przyczyną fotosensytyzacji</t></is></c><c r="I745" s="2" t="inlineStr" /><c r="J745" s="2" t="inlineStr" /><c r="K745" s="2" t="inlineStr"><is><t>mają nadal szeroki zakres działania przeciwbakteryjnego wobec bakterii tlenowych i mogą być stosowane w empirycznym leczeniu wielu zespołów klinicznych</t></is></c><c r="L745" s="2" t="inlineStr" /><c r="M745" s="2" t="inlineStr" /><c r="N745" s="2" t="inlineStr" /><c r="O745" s="2" t="inlineStr" /><c r="P745" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2017/18 - 2 termin</t></is></c><c r="Q745" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="746"><c r="A746" s="2" t="inlineStr"><is><t>LEKI PRZECIWWIRUSOWE</t></is></c><c r="B746" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C746" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D746" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E746" s="2" t="inlineStr"><is><t>Oseltamiwir należy stosować u nieszczepionych osób z grup ryzyka ciężkiego przebiegu grypy, do których należą:</t></is></c><c r="F746" s="2" t="inlineStr"><is><t>kobiety w ciąży i w 2 tyg. po porodzie</t></is></c><c r="G746" s="2" t="inlineStr"><is><t>dzieci do 2 roku życia</t></is></c><c r="H746" s="2" t="inlineStr"><is><t>osoby z wieku podeszłym &gt;= 65 lat</t></is></c><c r="I746" s="2" t="inlineStr" /><c r="J746" s="2" t="inlineStr" /><c r="K746" s="2" t="inlineStr"><is><t>kobiety karmiące piersią</t></is></c><c r="L746" s="2" t="inlineStr" /><c r="M746" s="2" t="inlineStr" /><c r="N746" s="2" t="inlineStr" /><c r="O746" s="2" t="inlineStr" /><c r="P746" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2017/18 - 2 termin</t></is></c><c r="Q746" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="747"><c r="A747" s="2" t="inlineStr"><is><t>LEKI PRZECIWWIRUSOWE</t></is></c><c r="B747" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C747" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D747" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E747" s="2" t="inlineStr"><is><t>Acyklowir służy do leczenia:</t></is></c><c r="F747" s="2" t="inlineStr"><is><t>opryszczki pospolitej (HSV)</t></is></c><c r="G747" s="2" t="inlineStr"><is><t>ospy wietrznej i półpaśca (VZV)</t></is></c><c r="H747" s="2" t="inlineStr" /><c r="I747" s="2" t="inlineStr" /><c r="J747" s="2" t="inlineStr" /><c r="K747" s="2" t="inlineStr"><is><t>mononukleozy zakaźnej (EBV)</t></is></c><c r="L747" s="2" t="inlineStr"><is><t>cytomegalii (CMV)</t></is></c><c r="M747" s="2" t="inlineStr" /><c r="N747" s="2" t="inlineStr" /><c r="O747" s="2" t="inlineStr" /><c r="P747" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2017/18 - 2 termin</t></is></c><c r="Q747" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="748"><c r="A748" s="2" t="inlineStr"><is><t>LEKI PRZECIWWIRUSOWE</t></is></c><c r="B748" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C748" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D748" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E748" s="2" t="inlineStr"><is><t>W bezinterferonowej terapii przewlekłego wirusowego zapalenia wątroby typu C zastosowanie mają leki przeciwwirusowe działające bezpośrednio (DAA) na wirusa typu C, do których należy:</t></is></c><c r="F748" s="2" t="inlineStr"><is><t>symeprewir</t></is></c><c r="G748" s="2" t="inlineStr"><is><t>ledipaswir</t></is></c><c r="H748" s="2" t="inlineStr" /><c r="I748" s="2" t="inlineStr" /><c r="J748" s="2" t="inlineStr" /><c r="K748" s="2" t="inlineStr"><is><t>zydowudyna</t></is></c><c r="L748" s="2" t="inlineStr"><is><t>lamiwudyna</t></is></c><c r="M748" s="2" t="inlineStr" /><c r="N748" s="2" t="inlineStr" /><c r="O748" s="2" t="inlineStr" /><c r="P748" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2017/18 - 2 termin</t></is></c><c r="Q748" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="749"><c r="A749" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B749" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C749" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D749" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E749" s="2" t="inlineStr"><is><t>Metronidazol służy do leczenia:</t></is></c><c r="F749" s="2" t="inlineStr"><is><t>rzęsistkowicy (Trichomonas vaginalis)</t></is></c><c r="G749" s="2" t="inlineStr"><is><t>lambliozy (Giargia lamblia)</t></is></c><c r="H749" s="2" t="inlineStr" /><c r="I749" s="2" t="inlineStr" /><c r="J749" s="2" t="inlineStr" /><c r="K749" s="2" t="inlineStr"><is><t>toksoplazmozy (Toxoplasma godi)</t></is></c><c r="L749" s="2" t="inlineStr"><is><t>pneumocystozy (Pneumocystis jirovecii)</t></is></c><c r="M749" s="2" t="inlineStr" /><c r="N749" s="2" t="inlineStr" /><c r="O749" s="2" t="inlineStr" /><c r="P749" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2017/18 - 2 termin</t></is></c><c r="Q749" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="750"><c r="A750" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B750" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C750" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D750" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E750" s="2" t="inlineStr"><is><t>Do leków 2 fazy (kontynuacji) w leczeniu gruźlicy należą:</t></is></c><c r="F750" s="2" t="inlineStr"><is><t>izoniazyd</t></is></c><c r="G750" s="2" t="inlineStr"><is><t>ryfampicyna</t></is></c><c r="H750" s="2" t="inlineStr" /><c r="I750" s="2" t="inlineStr" /><c r="J750" s="2" t="inlineStr" /><c r="K750" s="2" t="inlineStr"><is><t>etambutol</t></is></c><c r="L750" s="2" t="inlineStr"><is><t>pirazynamid</t></is></c><c r="M750" s="2" t="inlineStr" /><c r="N750" s="2" t="inlineStr" /><c r="O750" s="2" t="inlineStr" /><c r="P750" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2017/18 - 2 termin</t></is></c><c r="Q750" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="751"><c r="A751" s="2" t="inlineStr"><is><t>LEKI PRZECIWGRZYBICZE</t></is></c><c r="B751" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C751" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D751" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E751" s="2" t="inlineStr"><is><t>Aktywność wobec dermatofitów ma:</t></is></c><c r="F751" s="2" t="inlineStr"><is><t>flukonazol</t></is></c><c r="G751" s="2" t="inlineStr"><is><t>amorolfina</t></is></c><c r="H751" s="2" t="inlineStr"><is><t>klotrymazol</t></is></c><c r="I751" s="2" t="inlineStr"><is><t>terbinafina</t></is></c><c r="J751" s="2" t="inlineStr" /><c r="K751" s="2" t="inlineStr" /><c r="L751" s="2" t="inlineStr" /><c r="M751" s="2" t="inlineStr" /><c r="N751" s="2" t="inlineStr" /><c r="O751" s="2" t="inlineStr" /><c r="P751" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2017/18 - 2 termin</t></is></c><c r="Q751" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="752"><c r="A752" s="2" t="inlineStr"><is><t>FARMAKOKINETYKA</t></is></c><c r="B752" s="2" t="inlineStr"><is><t>Interakcje</t></is></c><c r="C752" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D752" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E752" s="2" t="inlineStr"><is><t>Cechą charakterystyczną dla azoli jest:</t></is></c><c r="F752" s="2" t="inlineStr"><is><t>hamowanie syntezy ergosterolu</t></is></c><c r="G752" s="2" t="inlineStr"><is><t>hamowanie izoenzymów CYP</t></is></c><c r="H752" s="2" t="inlineStr" /><c r="I752" s="2" t="inlineStr" /><c r="J752" s="2" t="inlineStr" /><c r="K752" s="2" t="inlineStr"><is><t>duże podobieństwo parametrów farmakokinetycznych leków tej grupy</t></is></c><c r="L752" s="2" t="inlineStr"><is><t>zależność ekspozycja-efekt typu fT&gt;MIC</t></is></c><c r="M752" s="2" t="inlineStr" /><c r="N752" s="2" t="inlineStr" /><c r="O752" s="2" t="inlineStr" /><c r="P752" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2017/18 - 2 termin</t></is></c><c r="Q752" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="753"><c r="A753" s="2" t="inlineStr"><is><t>LEKI PRZECIWGRZYBICZE</t></is></c><c r="B753" s="2" t="inlineStr"><is><t>Dawkowanie</t></is></c><c r="C753" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D753" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E753" s="2" t="inlineStr"><is><t>U pacjenta z eGFR &lt; 30 ml/min (wyliczony z wzoru Cockcrofta-Gaulta) należy zmodyfikować dawkowanie:</t></is></c><c r="F753" s="2" t="inlineStr"><is><t>oseltamiwiru</t></is></c><c r="G753" s="2" t="inlineStr"><is><t>flukonazolu</t></is></c><c r="H753" s="2" t="inlineStr" /><c r="I753" s="2" t="inlineStr" /><c r="J753" s="2" t="inlineStr" /><c r="K753" s="2" t="inlineStr"><is><t>ryfampicyny</t></is></c><c r="L753" s="2" t="inlineStr"><is><t>kaspofunginy</t></is></c><c r="M753" s="2" t="inlineStr" /><c r="N753" s="2" t="inlineStr" /><c r="O753" s="2" t="inlineStr" /><c r="P753" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2017/18 - 2 termin</t></is></c><c r="Q753" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="754"><c r="A754" s="2" t="inlineStr"><is><t>LEKI PRZECIWGRZYBICZE</t></is></c><c r="B754" s="2" t="inlineStr"><is><t>Farmakokinetyka</t></is></c><c r="C754" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D754" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E754" s="2" t="inlineStr"><is><t>Dobrą biodostępność po podaniu doustnym ma:</t></is></c><c r="F754" s="2" t="inlineStr"><is><t>flukonazol</t></is></c><c r="G754" s="2" t="inlineStr"><is><t>worykonazol</t></is></c><c r="H754" s="2" t="inlineStr" /><c r="I754" s="2" t="inlineStr" /><c r="J754" s="2" t="inlineStr" /><c r="K754" s="2" t="inlineStr"><is><t>amfoterycyna B</t></is></c><c r="L754" s="2" t="inlineStr"><is><t>pozakonazol</t></is></c><c r="M754" s="2" t="inlineStr" /><c r="N754" s="2" t="inlineStr" /><c r="O754" s="2" t="inlineStr" /><c r="P754" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2017/18 - 2 termin</t></is></c><c r="Q754" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="755"><c r="A755" s="2" t="inlineStr"><is><t>LEKI PRZECIWGRZYBICZE</t></is></c><c r="B755" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C755" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D755" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E755" s="2" t="inlineStr"><is><t>W kandydozie jamy ustnej (pleśniawkach) zastosować można:</t></is></c><c r="F755" s="2" t="inlineStr"><is><t>flukonazol</t></is></c><c r="G755" s="2" t="inlineStr"><is><t>nystatynę</t></is></c><c r="H755" s="2" t="inlineStr" /><c r="I755" s="2" t="inlineStr" /><c r="J755" s="2" t="inlineStr" /><c r="K755" s="2" t="inlineStr"><is><t>kwas borowy z gliceryną</t></is></c><c r="L755" s="2" t="inlineStr"><is><t>kaspofunginę</t></is></c><c r="M755" s="2" t="inlineStr" /><c r="N755" s="2" t="inlineStr" /><c r="O755" s="2" t="inlineStr" /><c r="P755" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2017/18 - 2 termin</t></is></c><c r="Q755" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="756"><c r="A756" s="2" t="inlineStr"><is><t>UKŁAD ODDECHOWY</t></is></c><c r="B756" s="2" t="inlineStr"><is><t>Sposób podania</t></is></c><c r="C756" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D756" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E756" s="2" t="inlineStr"><is><t>Spośród wymienionych glikokortykosteroidów stosowanych wziewnie w leczeniu chorób układu oddechowego w formie proleku dostępny jest:</t></is></c><c r="F756" s="2" t="inlineStr"><is><t>dipropionian beklometazonu</t></is></c><c r="G756" s="2" t="inlineStr"><is><t>cyklezonid</t></is></c><c r="H756" s="2" t="inlineStr" /><c r="I756" s="2" t="inlineStr" /><c r="J756" s="2" t="inlineStr" /><c r="K756" s="2" t="inlineStr"><is><t>budezonid</t></is></c><c r="L756" s="2" t="inlineStr"><is><t>propionian flutykazonu</t></is></c><c r="M756" s="2" t="inlineStr" /><c r="N756" s="2" t="inlineStr" /><c r="O756" s="2" t="inlineStr" /><c r="P756" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2017/18 - 1 termin</t></is></c><c r="Q756" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="757"><c r="A757" s="2" t="inlineStr"><is><t>UKŁAD ODDECHOWY</t></is></c><c r="B757" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C757" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D757" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E757" s="2" t="inlineStr"><is><t>Długodziałającym lekiem o wpływie na receptory komórkowe jest:</t></is></c><c r="F757" s="2" t="inlineStr"><is><t>bromek umeklidynium</t></is></c><c r="G757" s="2" t="inlineStr" /><c r="H757" s="2" t="inlineStr" /><c r="I757" s="2" t="inlineStr" /><c r="J757" s="2" t="inlineStr" /><c r="K757" s="2" t="inlineStr"><is><t>dornaza alfa</t></is></c><c r="L757" s="2" t="inlineStr"><is><t>nedokromil</t></is></c><c r="M757" s="2" t="inlineStr"><is><t>roflumilast</t></is></c><c r="N757" s="2" t="inlineStr" /><c r="O757" s="2" t="inlineStr" /><c r="P757" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2017/18 - 1 termin</t></is></c><c r="Q757" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="758"><c r="A758" s="2" t="inlineStr"><is><t>UKŁAD WSPÓŁCZULNY</t></is></c><c r="B758" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C758" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D758" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E758" s="2" t="inlineStr"><is><t>Unikalny profil działania klinicznego w swojej grupie farmakologicznej ma:</t></is></c><c r="F758" s="2" t="inlineStr"><is><t>formoterol</t></is></c><c r="G758" s="2" t="inlineStr"><is><t>celiprolol</t></is></c><c r="H758" s="2" t="inlineStr"><is><t>dekstrometorfan</t></is></c><c r="I758" s="2" t="inlineStr" /><c r="J758" s="2" t="inlineStr" /><c r="K758" s="2" t="inlineStr"><is><t>poraktant alfa</t></is></c><c r="L758" s="2" t="inlineStr" /><c r="M758" s="2" t="inlineStr" /><c r="N758" s="2" t="inlineStr" /><c r="O758" s="2" t="inlineStr" /><c r="P758" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2017/18 - 1 termin</t></is></c><c r="Q758" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="759"><c r="A759" s="2" t="inlineStr"><is><t>NADCIŚNIENIE TĘTNICZE</t></is></c><c r="B759" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C759" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D759" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E759" s="2" t="inlineStr"><is><t>Do groźnych powikłań po podaniu ramiprylu może dojść w przypadku zastosowania leku u:</t></is></c><c r="F759" s="2" t="inlineStr"><is><t>20-letniej kobiety w ciąży</t></is></c><c r="G759" s="2" t="inlineStr"><is><t>35-letniej kobiety z obustronnym istotnym zwężeniem tętnic nerkowych w przebiegu dysplazji włóknistej</t></is></c><c r="H759" s="2" t="inlineStr" /><c r="I759" s="2" t="inlineStr" /><c r="J759" s="2" t="inlineStr" /><c r="K759" s="2" t="inlineStr"><is><t>70-letniego mężczyzny z POChP</t></is></c><c r="L759" s="2" t="inlineStr"><is><t>50-letniego mężczyzny ze źle kontrolowanym zespołem metabolicznym (otyłość, cukrzyca, nadciśnienie tętnicze, dyslipidemia), aktywnego palacza nikotyny b</t></is></c><c r="M759" s="2" t="inlineStr"><is><t>Wskaż prawdziwe stwierdzenie dotyczące współczynnika T/P (trough-to-peak ratio):</t></is></c><c r="N759" s="2" t="inlineStr" /><c r="O759" s="2" t="inlineStr" /><c r="P759" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2017/18 - 1 termin</t></is></c><c r="Q759" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="760"><c r="A760" s="2" t="inlineStr"><is><t>NADCIŚNIENIE TĘTNICZE</t></is></c><c r="B760" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C760" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D760" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E760" s="2" t="inlineStr"><is><t>Które pary leków mających ten sam zasadniczy mechanizm działania różnią się istotnie profilem działań klinicznych?</t></is></c><c r="F760" s="2" t="inlineStr"><is><t>werapamil i nitrendypina</t></is></c><c r="G760" s="2" t="inlineStr"><is><t>doksazosyna i tamsulozyna</t></is></c><c r="H760" s="2" t="inlineStr" /><c r="I760" s="2" t="inlineStr" /><c r="J760" s="2" t="inlineStr" /><c r="K760" s="2" t="inlineStr"><is><t>moksonidyna i rylmenidyna</t></is></c><c r="L760" s="2" t="inlineStr"><is><t>spironolakton i kanrenon</t></is></c><c r="M760" s="2" t="inlineStr" /><c r="N760" s="2" t="inlineStr" /><c r="O760" s="2" t="inlineStr" /><c r="P760" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2017/18 - 1 termin</t></is></c><c r="Q760" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="761"><c r="A761" s="2" t="inlineStr"><is><t>UKŁAD ODDECHOWY</t></is></c><c r="B761" s="2" t="inlineStr"><is><t>Przeciwwskazania</t></is></c><c r="C761" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D761" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E761" s="2" t="inlineStr"><is><t>β – adrenolityki:</t></is></c><c r="F761" s="2" t="inlineStr"><is><t>zwalniają częstość rytmu serca, a przez to zapotrzebowanie serca na tlen</t></is></c><c r="G761" s="2" t="inlineStr" /><c r="H761" s="2" t="inlineStr" /><c r="I761" s="2" t="inlineStr" /><c r="J761" s="2" t="inlineStr" /><c r="K761" s="2" t="inlineStr"><is><t>zmniejszają ciśnienie tętnicze i w efekcie powodują spadek przepływu wieńcowego</t></is></c><c r="L761" s="2" t="inlineStr"><is><t>powodują wzrost stężenia glukozy we krwi i dlatego maskują objawy hipoglikemii</t></is></c><c r="M761" s="2" t="inlineStr"><is><t>powodują skurcz oskrzeli i dlatego są bezwzględnie przeciwwskazane w POChP</t></is></c><c r="N761" s="2" t="inlineStr" /><c r="O761" s="2" t="inlineStr" /><c r="P761" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2017/18 - 1 termin</t></is></c><c r="Q761" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="762"><c r="A762" s="2" t="inlineStr"><is><t>NIEWYDOLNOŚĆ SERCA</t></is></c><c r="B762" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C762" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D762" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E762" s="2" t="inlineStr"><is><t>Zaburzenia widzenia powoduje:</t></is></c><c r="F762" s="2" t="inlineStr"><is><t>digoksyna</t></is></c><c r="G762" s="2" t="inlineStr"><is><t>sildenafil</t></is></c><c r="H762" s="2" t="inlineStr"><is><t>iwabradyna</t></is></c><c r="I762" s="2" t="inlineStr" /><c r="J762" s="2" t="inlineStr" /><c r="K762" s="2" t="inlineStr"><is><t>piracetam</t></is></c><c r="L762" s="2" t="inlineStr" /><c r="M762" s="2" t="inlineStr" /><c r="N762" s="2" t="inlineStr" /><c r="O762" s="2" t="inlineStr" /><c r="P762" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2017/18 - 1 termin</t></is></c><c r="Q762" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="763"><c r="A763" s="2" t="inlineStr"><is><t>ZABURZENIA RYTMU SERCA</t></is></c><c r="B763" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C763" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D763" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E763" s="2" t="inlineStr"><is><t>Do kardiowersji farmakologicznej w migotaniu przedsionków stosuje się:</t></is></c><c r="F763" s="2" t="inlineStr"><is><t>amiodaron</t></is></c><c r="G763" s="2" t="inlineStr"><is><t>propafenon</t></is></c><c r="H763" s="2" t="inlineStr" /><c r="I763" s="2" t="inlineStr" /><c r="J763" s="2" t="inlineStr" /><c r="K763" s="2" t="inlineStr"><is><t>adenozynę</t></is></c><c r="L763" s="2" t="inlineStr"><is><t>lidokainę</t></is></c><c r="M763" s="2" t="inlineStr" /><c r="N763" s="2" t="inlineStr" /><c r="O763" s="2" t="inlineStr" /><c r="P763" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2017/18 - 1 termin</t></is></c><c r="Q763" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="764"><c r="A764" s="2" t="inlineStr"><is><t>NADCIŚNIENIE TĘTNICZE</t></is></c><c r="B764" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C764" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D764" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E764" s="2" t="inlineStr"><is><t>Poprzez aktywację białkowej kinazy G via cGMP działa:</t></is></c><c r="F764" s="2" t="inlineStr"><is><t>nitroprusydek sodu</t></is></c><c r="G764" s="2" t="inlineStr"><is><t>sakubitryl</t></is></c><c r="H764" s="2" t="inlineStr"><is><t>riocyguat</t></is></c><c r="I764" s="2" t="inlineStr"><is><t>nesirytyd</t></is></c><c r="J764" s="2" t="inlineStr" /><c r="K764" s="2" t="inlineStr" /><c r="L764" s="2" t="inlineStr" /><c r="M764" s="2" t="inlineStr" /><c r="N764" s="2" t="inlineStr" /><c r="O764" s="2" t="inlineStr" /><c r="P764" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2017/18 - 1 termin</t></is></c><c r="Q764" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="765"><c r="A765" s="2" t="inlineStr"><is><t>ZABURZENIA RYTMU SERCA</t></is></c><c r="B765" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C765" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D765" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E765" s="2" t="inlineStr"><is><t>Na kanały sodowe ma wpływ:</t></is></c><c r="F765" s="2" t="inlineStr"><is><t>propafenon</t></is></c><c r="G765" s="2" t="inlineStr"><is><t>ranolazyna</t></is></c><c r="H765" s="2" t="inlineStr"><is><t>bupiwakaina</t></is></c><c r="I765" s="2" t="inlineStr" /><c r="J765" s="2" t="inlineStr" /><c r="K765" s="2" t="inlineStr"><is><t>adenozyna</t></is></c><c r="L765" s="2" t="inlineStr" /><c r="M765" s="2" t="inlineStr" /><c r="N765" s="2" t="inlineStr" /><c r="O765" s="2" t="inlineStr" /><c r="P765" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2017/18 - 1 termin</t></is></c><c r="Q765" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="766"><c r="A766" s="2" t="inlineStr"><is><t>LEKI PRZECIWDEPRESYJNE</t></is></c><c r="B766" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C766" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D766" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E766" s="2" t="inlineStr"><is><t>Wybierz prawidłowy zestaw lek – wskazanie do stosowania:</t></is></c><c r="F766" s="2" t="inlineStr"><is><t>bupropion – uzależnienie od nikotyny</t></is></c><c r="G766" s="2" t="inlineStr"><is><t>atomoksetyna – ADHD (zespół nadpobudliwości z deficytem uwagi)</t></is></c><c r="H766" s="2" t="inlineStr"><is><t>lamotrygina - profilaktyka zaburzeń afektywnych dwubiegunowych</t></is></c><c r="I766" s="2" t="inlineStr" /><c r="J766" s="2" t="inlineStr" /><c r="K766" s="2" t="inlineStr"><is><t>agomelatyna – bezsenność krótkotrwała</t></is></c><c r="L766" s="2" t="inlineStr" /><c r="M766" s="2" t="inlineStr" /><c r="N766" s="2" t="inlineStr" /><c r="O766" s="2" t="inlineStr" /><c r="P766" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2017/18 - 1 termin</t></is></c><c r="Q766" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="767"><c r="A767" s="2" t="inlineStr"><is><t>LEKI PRZECIWLĘKOWE</t></is></c><c r="B767" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C767" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D767" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E767" s="2" t="inlineStr"><is><t>Meghan skarżącej się na bezsenność, która związana jest ze stresem wywołanym planowanym wydarzeniem z jej udziałem emitowanym we wszystkich telewizjach świata za 2 tygodnie, przepiszesz:</t></is></c><c r="F767" s="2" t="inlineStr"><is><t>zaleplon</t></is></c><c r="G767" s="2" t="inlineStr" /><c r="H767" s="2" t="inlineStr" /><c r="I767" s="2" t="inlineStr" /><c r="J767" s="2" t="inlineStr" /><c r="K767" s="2" t="inlineStr"><is><t>diazepam</t></is></c><c r="L767" s="2" t="inlineStr"><is><t>mirtazapinę</t></is></c><c r="M767" s="2" t="inlineStr"><is><t>hydroksyzynę</t></is></c><c r="N767" s="2" t="inlineStr" /><c r="O767" s="2" t="inlineStr" /><c r="P767" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2017/18 - 1 termin</t></is></c><c r="Q767" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="768"><c r="A768" s="2" t="inlineStr"><is><t>OTĘPIENIE</t></is></c><c r="B768" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C768" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D768" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E768" s="2" t="inlineStr"><is><t>Pozapsychiatryczne zastosowania leków przeciwdepresyjnych obejmują:</t></is></c><c r="F768" s="2" t="inlineStr"><is><t>ból neuropatyczny</t></is></c><c r="G768" s="2" t="inlineStr"><is><t>bezsenność przewlekłą po niepowodzeniu wprowadzenia zasad higieny snu</t></is></c><c r="H768" s="2" t="inlineStr" /><c r="I768" s="2" t="inlineStr" /><c r="J768" s="2" t="inlineStr" /><c r="K768" s="2" t="inlineStr"><is><t>otępienie naczyniopochodne</t></is></c><c r="L768" s="2" t="inlineStr"><is><t>przerywanie napadów migren</t></is></c><c r="M768" s="2" t="inlineStr" /><c r="N768" s="2" t="inlineStr" /><c r="O768" s="2" t="inlineStr" /><c r="P768" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2017/18 - 1 termin</t></is></c><c r="Q768" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="769"><c r="A769" s="2" t="inlineStr"><is><t>LEKI PRZECIWLĘKOWE</t></is></c><c r="B769" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C769" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D769" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E769" s="2" t="inlineStr"><is><t>W leczeniu lęku uogólnionego zastosowanie ma:</t></is></c><c r="F769" s="2" t="inlineStr"><is><t>sertralina</t></is></c><c r="G769" s="2" t="inlineStr"><is><t>pregabalina</t></is></c><c r="H769" s="2" t="inlineStr"><is><t>buspiron</t></is></c><c r="I769" s="2" t="inlineStr" /><c r="J769" s="2" t="inlineStr" /><c r="K769" s="2" t="inlineStr"><is><t>klorazepat</t></is></c><c r="L769" s="2" t="inlineStr" /><c r="M769" s="2" t="inlineStr" /><c r="N769" s="2" t="inlineStr" /><c r="O769" s="2" t="inlineStr" /><c r="P769" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2017/18 - 1 termin</t></is></c><c r="Q769" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="770"><c r="A770" s="2" t="inlineStr"><is><t>LEKI PRZECIWDEPRESYJNE</t></is></c><c r="B770" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C770" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D770" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E770" s="2" t="inlineStr"><is><t>Za reakcję paradoksalną uznasz:</t></is></c><c r="F770" s="2" t="inlineStr"><is><t>agresję po lorazepamie</t></is></c><c r="G770" s="2" t="inlineStr" /><c r="H770" s="2" t="inlineStr" /><c r="I770" s="2" t="inlineStr" /><c r="J770" s="2" t="inlineStr" /><c r="K770" s="2" t="inlineStr"><is><t>drgawki po amitryptylinie</t></is></c><c r="L770" s="2" t="inlineStr"><is><t>niepamięć następczą po zopiklonie</t></is></c><c r="M770" s="2" t="inlineStr"><is><t>jadłowstręt po fluoksetynie</t></is></c><c r="N770" s="2" t="inlineStr" /><c r="O770" s="2" t="inlineStr" /><c r="P770" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2017/18 - 1 termin</t></is></c><c r="Q770" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="771"><c r="A771" s="2" t="inlineStr"><is><t>PADACZKA</t></is></c><c r="B771" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C771" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D771" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E771" s="2" t="inlineStr"><is><t>W początkowym okresie leczenia depresji selektywnymi inhibitorami wychwytu zwrotnego serotoniny:</t></is></c><c r="F771" s="2" t="inlineStr"><is><t>mogą nasilać lęk, choć są uważane za leki przeciwlękowe podczas długotrwałej terapii</t></is></c><c r="G771" s="2" t="inlineStr"><is><t>częściej niż w późniejszym okresie terapii dochodzi do myśli lub prób samobójczych</t></is></c><c r="H771" s="2" t="inlineStr" /><c r="I771" s="2" t="inlineStr" /><c r="J771" s="2" t="inlineStr" /><c r="K771" s="2" t="inlineStr"><is><t>występują fluktuacje nastroju polegające na szybkiej poprawie, ale z okresami gwałtownych pogorszeń</t></is></c><c r="L771" s="2" t="inlineStr"><is><t>stosuje się równocześnie karbamazepinę aby zapobiec przejściu depresji w manię</t></is></c><c r="M771" s="2" t="inlineStr" /><c r="N771" s="2" t="inlineStr" /><c r="O771" s="2" t="inlineStr" /><c r="P771" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2017/18 - 1 termin</t></is></c><c r="Q771" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="772"><c r="A772" s="2" t="inlineStr"><is><t>LEKI PRZECIWDEPRESYJNE</t></is></c><c r="B772" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C772" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D772" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E772" s="2" t="inlineStr"><is><t>Pacjentka od wielu lat otrzymuje perazynę, mianseryną i lorazepam. Na tej podstawie można rozpoznać:</t></is></c><c r="F772" s="2" t="inlineStr"><is><t>zaburzenia depresyjno-urojeniowe</t></is></c><c r="G772" s="2" t="inlineStr"><is><t>uzależnienie lekowe</t></is></c><c r="H772" s="2" t="inlineStr" /><c r="I772" s="2" t="inlineStr" /><c r="J772" s="2" t="inlineStr" /><c r="K772" s="2" t="inlineStr"><is><t>dwubiegunową chorobę afektywną</t></is></c><c r="L772" s="2" t="inlineStr"><is><t>fobię społeczną</t></is></c><c r="M772" s="2" t="inlineStr" /><c r="N772" s="2" t="inlineStr" /><c r="O772" s="2" t="inlineStr" /><c r="P772" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2017/18 - 1 termin</t></is></c><c r="Q772" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="773"><c r="A773" s="2" t="inlineStr"><is><t>UKŁAD WSPÓŁCZULNY</t></is></c><c r="B773" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C773" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D773" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E773" s="2" t="inlineStr"><is><t>Układ dopaminowy OUN aktywuje bezpośrednio:</t></is></c><c r="F773" s="2" t="inlineStr"><is><t>ropinirol</t></is></c><c r="G773" s="2" t="inlineStr"><is><t>metylfenidat</t></is></c><c r="H773" s="2" t="inlineStr" /><c r="I773" s="2" t="inlineStr" /><c r="J773" s="2" t="inlineStr" /><c r="K773" s="2" t="inlineStr"><is><t>piracetam</t></is></c><c r="L773" s="2" t="inlineStr"><is><t>kofeina</t></is></c><c r="M773" s="2" t="inlineStr" /><c r="N773" s="2" t="inlineStr" /><c r="O773" s="2" t="inlineStr" /><c r="P773" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2017/18 - 1 termin</t></is></c><c r="Q773" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="774"><c r="A774" s="2" t="inlineStr"><is><t>LEKI PRZECIWPSYCHOTYCZNE</t></is></c><c r="B774" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C774" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D774" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E774" s="2" t="inlineStr"><is><t>Przy stosowaniu neuroleptyków największe ryzyko przyrostu masy ciała dotyczy:</t></is></c><c r="F774" s="2" t="inlineStr"><is><t>chlorpromazyny</t></is></c><c r="G774" s="2" t="inlineStr"><is><t>olanzapiny</t></is></c><c r="H774" s="2" t="inlineStr" /><c r="I774" s="2" t="inlineStr" /><c r="J774" s="2" t="inlineStr" /><c r="K774" s="2" t="inlineStr"><is><t>arypiprazolu</t></is></c><c r="L774" s="2" t="inlineStr"><is><t>haloperidolu</t></is></c><c r="M774" s="2" t="inlineStr" /><c r="N774" s="2" t="inlineStr" /><c r="O774" s="2" t="inlineStr" /><c r="P774" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2017/18 - 1 termin</t></is></c><c r="Q774" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="775"><c r="A775" s="2" t="inlineStr"><is><t>UKŁAD PRZYWSPÓŁCZULNY</t></is></c><c r="B775" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C775" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D775" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E775" s="2" t="inlineStr"><is><t>Na acetylocholinestarazę ma wpływ:</t></is></c><c r="F775" s="2" t="inlineStr"><is><t>neostygmina</t></is></c><c r="G775" s="2" t="inlineStr"><is><t>donepezil</t></is></c><c r="H775" s="2" t="inlineStr" /><c r="I775" s="2" t="inlineStr" /><c r="J775" s="2" t="inlineStr" /><c r="K775" s="2" t="inlineStr"><is><t>suksametonium</t></is></c><c r="L775" s="2" t="inlineStr"><is><t>tropikamid</t></is></c><c r="M775" s="2" t="inlineStr" /><c r="N775" s="2" t="inlineStr" /><c r="O775" s="2" t="inlineStr" /><c r="P775" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2017/18 - 1 termin</t></is></c><c r="Q775" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="776"><c r="A776" s="2" t="inlineStr"><is><t>LEKI MOCZOPĘDNE</t></is></c><c r="B776" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C776" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D776" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E776" s="2" t="inlineStr"><is><t>Hiponatremia polekowa może być rozpoznana podczas stosowania:</t></is></c><c r="F776" s="2" t="inlineStr"><is><t>torasemidu</t></is></c><c r="G776" s="2" t="inlineStr"><is><t>indapamidu</t></is></c><c r="H776" s="2" t="inlineStr"><is><t>karbamazepiny</t></is></c><c r="I776" s="2" t="inlineStr" /><c r="J776" s="2" t="inlineStr" /><c r="K776" s="2" t="inlineStr"><is><t>tolwaptanu</t></is></c><c r="L776" s="2" t="inlineStr" /><c r="M776" s="2" t="inlineStr" /><c r="N776" s="2" t="inlineStr" /><c r="O776" s="2" t="inlineStr" /><c r="P776" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2017/18 - 1 termin</t></is></c><c r="Q776" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="777"><c r="A777" s="2" t="inlineStr"><is><t>PADACZKA</t></is></c><c r="B777" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C777" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D777" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E777" s="2" t="inlineStr"><is><t>Czy na podstawie informacji o stosowaniu leku można jednoznacznie postawić wymienione rozpoznanie?</t></is></c><c r="F777" s="2" t="inlineStr"><is><t>fingolimod – stwardnienie rozsiane</t></is></c><c r="G777" s="2" t="inlineStr"><is><t>memantyna – choroba Alzheimera</t></is></c><c r="H777" s="2" t="inlineStr" /><c r="I777" s="2" t="inlineStr" /><c r="J777" s="2" t="inlineStr" /><c r="K777" s="2" t="inlineStr"><is><t>kwas walproinowy – padaczka</t></is></c><c r="L777" s="2" t="inlineStr"><is><t>pregabalina – polineuropatia cukrzycowa</t></is></c><c r="M777" s="2" t="inlineStr" /><c r="N777" s="2" t="inlineStr" /><c r="O777" s="2" t="inlineStr" /><c r="P777" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2017/18 - 1 termin</t></is></c><c r="Q777" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="778"><c r="A778" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B778" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C778" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D778" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E778" s="2" t="inlineStr"><is><t>Które z powyższych stwierdzeń jest prawdziwe?</t></is></c><c r="F778" s="2" t="inlineStr"><is><t>podczas leczenia takalcytolem należy monitorować stężenie wapnia w moczu</t></is></c><c r="G778" s="2" t="inlineStr"><is><t>metoksalen powinno się podawać 1-2 h przed planowaną ekspozycją na promieniowanie UVA</t></is></c><c r="H778" s="2" t="inlineStr"><is><t>nadtlenek benzoilu ma zastosowanie w leczeniu trądziku</t></is></c><c r="I778" s="2" t="inlineStr" /><c r="J778" s="2" t="inlineStr" /><c r="K778" s="2" t="inlineStr"><is><t>podczas stosowania acytretyny skuteczną antykoncepcję należy stosować przez miesiąc po zakończeniu terapii</t></is></c><c r="L778" s="2" t="inlineStr" /><c r="M778" s="2" t="inlineStr" /><c r="N778" s="2" t="inlineStr" /><c r="O778" s="2" t="inlineStr" /><c r="P778" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2017/18 - 1 termin</t></is></c><c r="Q778" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="779"><c r="A779" s="2" t="inlineStr"><is><t>LEKI ROŚLINNE I SUPLEMENTY</t></is></c><c r="B779" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C779" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D779" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E779" s="2" t="inlineStr"><is><t>Doping genetyczny może dotyczyć genu kodującego:</t></is></c><c r="F779" s="2" t="inlineStr"><is><t>enzym konwertujący angiotensynę</t></is></c><c r="G779" s="2" t="inlineStr"><is><t>erytropoetynę</t></is></c><c r="H779" s="2" t="inlineStr"><is><t>kolagen</t></is></c><c r="I779" s="2" t="inlineStr"><is><t>hormon wzrostu</t></is></c><c r="J779" s="2" t="inlineStr" /><c r="K779" s="2" t="inlineStr" /><c r="L779" s="2" t="inlineStr" /><c r="M779" s="2" t="inlineStr" /><c r="N779" s="2" t="inlineStr" /><c r="O779" s="2" t="inlineStr" /><c r="P779" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2017/18 - 1 termin</t></is></c><c r="Q779" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="780"><c r="A780" s="2" t="inlineStr"><is><t>CHOROBA PARKINSONA</t></is></c><c r="B780" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C780" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D780" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E780" s="2" t="inlineStr"><is><t>Cholinolityki</t></is></c><c r="F780" s="2" t="inlineStr"><is><t>są lekami z wyboru w polekowym zespole parkinsonowskim</t></is></c><c r="G780" s="2" t="inlineStr"><is><t>nie ma istotnych różnic w skuteczności leków tej grupy stosowanych w chorobie Parkinsona</t></is></c><c r="H780" s="2" t="inlineStr"><is><t>zmniejszają drżenie w chorobie Parkinsona</t></is></c><c r="I780" s="2" t="inlineStr"><is><t>można podawać w połączeniu z lewodopą</t></is></c><c r="J780" s="2" t="inlineStr" /><c r="K780" s="2" t="inlineStr" /><c r="L780" s="2" t="inlineStr" /><c r="M780" s="2" t="inlineStr" /><c r="N780" s="2" t="inlineStr" /><c r="O780" s="2" t="inlineStr" /><c r="P780" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2017/18 - 1 termin</t></is></c><c r="Q780" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="781"><c r="A781" s="2" t="inlineStr"><is><t>UKŁAD PRZYWSPÓŁCZULNY</t></is></c><c r="B781" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C781" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D781" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E781" s="2" t="inlineStr"><is><t>Terapia genowa w okulistyce ma zastosowanie w leczeniu:</t></is></c><c r="F781" s="2" t="inlineStr"><is><t>zwyrodnienia barwnikowego siatkówki (retinitis pigmentosa)</t></is></c><c r="G781" s="2" t="inlineStr" /><c r="H781" s="2" t="inlineStr" /><c r="I781" s="2" t="inlineStr" /><c r="J781" s="2" t="inlineStr" /><c r="K781" s="2" t="inlineStr"><is><t>jaskry</t></is></c><c r="L781" s="2" t="inlineStr"><is><t>zapalenia współczulnego oka</t></is></c><c r="M781" s="2" t="inlineStr"><is><t>choroby Besta</t></is></c><c r="N781" s="2" t="inlineStr" /><c r="O781" s="2" t="inlineStr" /><c r="P781" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2017/18 - 1 termin</t></is></c><c r="Q781" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="782"><c r="A782" s="2" t="inlineStr"><is><t>OSTEOPOROZA</t></is></c><c r="B782" s="2" t="inlineStr"><is><t>Interakcje</t></is></c><c r="C782" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D782" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E782" s="2" t="inlineStr"><is><t>Wskaż prawdziwe stwierdzenie:</t></is></c><c r="F782" s="2" t="inlineStr"><is><t>bisfosfoniany hamują resorpcję kości przez nasilenie działania osteoprotegeryny na RANKL</t></is></c><c r="G782" s="2" t="inlineStr"><is><t>teryparatyd w małych przerywanych dawkach paradoksalnie zwiększa tworzenie kości</t></is></c><c r="H782" s="2" t="inlineStr"><is><t>ranelinian strontu przez podwójnie korzystne działanie (zwiększa tworzenie i hamuje resorpcję kości) jest lekiem pierwszego wyboru w leczeniu osteoporozy</t></is></c><c r="I782" s="2" t="inlineStr"><is><t>denosumab hamuje resorpcję kości przez zablokowanie interakcji RANK-RANKL</t></is></c><c r="J782" s="2" t="inlineStr" /><c r="K782" s="2" t="inlineStr" /><c r="L782" s="2" t="inlineStr" /><c r="M782" s="2" t="inlineStr" /><c r="N782" s="2" t="inlineStr" /><c r="O782" s="2" t="inlineStr" /><c r="P782" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2017/18 - 1 termin</t></is></c><c r="Q782" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="783"><c r="A783" s="2" t="inlineStr"><is><t>LEKI PRZECIWHISTAMINOWE</t></is></c><c r="B783" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C783" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D783" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E783" s="2" t="inlineStr"><is><t>Rupatadyna:</t></is></c><c r="F783" s="2" t="inlineStr"><is><t>jest selektywnym niesedatywnym antagonistą receptorów H1</t></is></c><c r="G783" s="2" t="inlineStr"><is><t>hamuje degranulację komórek tucznych in vitro</t></is></c><c r="H783" s="2" t="inlineStr"><is><t>ma aktywny metabolit – desloratadynę zaliczaną do 3 generacji leków przeciwhistaminowych</t></is></c><c r="I783" s="2" t="inlineStr"><is><t>w dawkach zalecanych nie wydłuża odstępu QTc</t></is></c><c r="J783" s="2" t="inlineStr" /><c r="K783" s="2" t="inlineStr" /><c r="L783" s="2" t="inlineStr" /><c r="M783" s="2" t="inlineStr" /><c r="N783" s="2" t="inlineStr" /><c r="O783" s="2" t="inlineStr" /><c r="P783" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2017/18 - 1 termin</t></is></c><c r="Q783" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="784"><c r="A784" s="2" t="inlineStr"><is><t>UKŁAD ODDECHOWY</t></is></c><c r="B784" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C784" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D784" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E784" s="2" t="inlineStr"><is><t>W leczeniu astmy używane są wziewne postaci:</t></is></c><c r="F784" s="2" t="inlineStr"><is><t>propionianu flutykazonu</t></is></c><c r="G784" s="2" t="inlineStr"><is><t>indakaterolu</t></is></c><c r="H784" s="2" t="inlineStr" /><c r="I784" s="2" t="inlineStr" /><c r="J784" s="2" t="inlineStr" /><c r="K784" s="2" t="inlineStr"><is><t>montelukastu</t></is></c><c r="L784" s="2" t="inlineStr"><is><t>acetylocysteiny</t></is></c><c r="M784" s="2" t="inlineStr" /><c r="N784" s="2" t="inlineStr" /><c r="O784" s="2" t="inlineStr" /><c r="P784" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2017/18 - 2 termin</t></is></c><c r="Q784" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="785"><c r="A785" s="2" t="inlineStr"><is><t>UKŁAD ODDECHOWY</t></is></c><c r="B785" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C785" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D785" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E785" s="2" t="inlineStr"><is><t>U małego dziecka wygodną formą podania leku wziewnego jest:</t></is></c><c r="F785" s="2" t="inlineStr"><is><t>pomocnicze użycie komory inhalacyjnej, tzw. spacera</t></is></c><c r="G785" s="2" t="inlineStr"><is><t>nebulizacja</t></is></c><c r="H785" s="2" t="inlineStr" /><c r="I785" s="2" t="inlineStr" /><c r="J785" s="2" t="inlineStr" /><c r="K785" s="2" t="inlineStr"><is><t>inhalacja z inhalatora suchego proszku</t></is></c><c r="L785" s="2" t="inlineStr"><is><t>inhalacja z dozownika ciśnieniowego</t></is></c><c r="M785" s="2" t="inlineStr" /><c r="N785" s="2" t="inlineStr" /><c r="O785" s="2" t="inlineStr" /><c r="P785" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2017/18 - 2 termin</t></is></c><c r="Q785" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="786"><c r="A786" s="2" t="inlineStr"><is><t>UKŁAD ODDECHOWY</t></is></c><c r="B786" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C786" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D786" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E786" s="2" t="inlineStr"><is><t>Wskaż prawdziwe połączenie lek – działania niepożądane:</t></is></c><c r="F786" s="2" t="inlineStr"><is><t>bromek glikopironium - tachykardia</t></is></c><c r="G786" s="2" t="inlineStr"><is><t>budezonid – kandydoza jamy ustnej</t></is></c><c r="H786" s="2" t="inlineStr"><is><t>teofilina – zaburzenia rytmu serca</t></is></c><c r="I786" s="2" t="inlineStr"><is><t>omalizumab – reakcje w miejscu podskórnego podania leku, takie jak ból, zaczerwienienie, świąd, obrzęk</t></is></c><c r="J786" s="2" t="inlineStr" /><c r="K786" s="2" t="inlineStr" /><c r="L786" s="2" t="inlineStr" /><c r="M786" s="2" t="inlineStr" /><c r="N786" s="2" t="inlineStr" /><c r="O786" s="2" t="inlineStr" /><c r="P786" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2017/18 - 2 termin</t></is></c><c r="Q786" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="787"><c r="A787" s="2" t="inlineStr"><is><t>NADCIŚNIENIE TĘTNICZE</t></is></c><c r="B787" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C787" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D787" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E787" s="2" t="inlineStr"><is><t>Chorzy na pierwotne nadciśnienie tętnicze z towarzyszącą cukrzycą największe korzyści osiągają z zastosowania:</t></is></c><c r="F787" s="2" t="inlineStr"><is><t>ramiprylu</t></is></c><c r="G787" s="2" t="inlineStr"><is><t>telmisartanu</t></is></c><c r="H787" s="2" t="inlineStr" /><c r="I787" s="2" t="inlineStr" /><c r="J787" s="2" t="inlineStr" /><c r="K787" s="2" t="inlineStr"><is><t>metoprololu</t></is></c><c r="L787" s="2" t="inlineStr"><is><t>hydrochlorotiazydu</t></is></c><c r="M787" s="2" t="inlineStr"><is><t>Istotnym działaniem niepożądanym inhibitorów konwertazy angiotensyny jest:</t></is></c><c r="N787" s="2" t="inlineStr" /><c r="O787" s="2" t="inlineStr" /><c r="P787" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2017/18 - 2 termin</t></is></c><c r="Q787" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="788"><c r="A788" s="2" t="inlineStr"><is><t>LEKI MOCZOPĘDNE</t></is></c><c r="B788" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C788" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D788" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E788" s="2" t="inlineStr"><is><t>Wybierz prawidłowe pary lek – efekt działania:</t></is></c><c r="F788" s="2" t="inlineStr"><is><t>torasemid - hiperurykemia</t></is></c><c r="G788" s="2" t="inlineStr"><is><t>indapamid - hiponatremia</t></is></c><c r="H788" s="2" t="inlineStr" /><c r="I788" s="2" t="inlineStr" /><c r="J788" s="2" t="inlineStr" /><c r="K788" s="2" t="inlineStr"><is><t>mannitol – hiperglikemia</t></is></c><c r="L788" s="2" t="inlineStr"><is><t>eplerenon - hipokaliemia</t></is></c><c r="M788" s="2" t="inlineStr" /><c r="N788" s="2" t="inlineStr" /><c r="O788" s="2" t="inlineStr" /><c r="P788" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2017/18 - 2 termin</t></is></c><c r="Q788" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="789"><c r="A789" s="2" t="inlineStr"><is><t>NIEWYDOLNOŚĆ SERCA</t></is></c><c r="B789" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C789" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D789" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E789" s="2" t="inlineStr"><is><t>Wskaż prawdziwe stwierdzenie dotyczące digoksyny:</t></is></c><c r="F789" s="2" t="inlineStr"><is><t>jest wskazana u pacjentów z niewydolnością serca i migotaniem przedsionków</t></is></c><c r="G789" s="2" t="inlineStr"><is><t>zmniejsza chorobowość pacjentów z niewydolnością serca</t></is></c><c r="H789" s="2" t="inlineStr" /><c r="I789" s="2" t="inlineStr" /><c r="J789" s="2" t="inlineStr" /><c r="K789" s="2" t="inlineStr"><is><t>poprawia przeżycie chorych z niewydolnością serca</t></is></c><c r="L789" s="2" t="inlineStr"><is><t>jest pozbawiona działania proarytmicznego</t></is></c><c r="M789" s="2" t="inlineStr" /><c r="N789" s="2" t="inlineStr" /><c r="O789" s="2" t="inlineStr" /><c r="P789" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2017/18 - 2 termin</t></is></c><c r="Q789" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="790"><c r="A790" s="2" t="inlineStr"><is><t>NADCIŚNIENIE TĘTNICZE</t></is></c><c r="B790" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C790" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D790" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E790" s="2" t="inlineStr"><is><t>Wskaż prawdziwe zdanie dotyczące leczenia niewydolności serca:</t></is></c><c r="F790" s="2" t="inlineStr"><is><t>enalapryl przez zniesienie niekorzystnej adaptacji zmniejsza umieralność chorych ze skurczową niewydolnością serca</t></is></c><c r="G790" s="2" t="inlineStr"><is><t>karwedilol przez zniesienie niekorzystnej adaptacji zmniejsza umieralność chorych ze skurczową niewydolnością serca</t></is></c><c r="H790" s="2" t="inlineStr"><is><t>leki moczopędne są zalecane w celu zmniejszenia objawów i poprawy wydolności wysiłkowej u pacjentów z objawami zastoju</t></is></c><c r="I790" s="2" t="inlineStr" /><c r="J790" s="2" t="inlineStr" /><c r="K790" s="2" t="inlineStr"><is><t>statyny powinny być stosowane rutynowo u wszystkich chorych z niewydolnością mięśnia sercowego</t></is></c><c r="L790" s="2" t="inlineStr" /><c r="M790" s="2" t="inlineStr" /><c r="N790" s="2" t="inlineStr" /><c r="O790" s="2" t="inlineStr" /><c r="P790" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2017/18 - 2 termin</t></is></c><c r="Q790" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="791"><c r="A791" s="2" t="inlineStr"><is><t>NIEWYDOLNOŚĆ SERCA</t></is></c><c r="B791" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C791" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D791" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E791" s="2" t="inlineStr"><is><t>Do leków przeciwskazanych u pacjentów z niewydolnością serca należy:</t></is></c><c r="F791" s="2" t="inlineStr"><is><t>werapamil</t></is></c><c r="G791" s="2" t="inlineStr"><is><t>ketoprofen</t></is></c><c r="H791" s="2" t="inlineStr" /><c r="I791" s="2" t="inlineStr" /><c r="J791" s="2" t="inlineStr" /><c r="K791" s="2" t="inlineStr"><is><t>nebiwolol</t></is></c><c r="L791" s="2" t="inlineStr"><is><t>iwabradyna</t></is></c><c r="M791" s="2" t="inlineStr" /><c r="N791" s="2" t="inlineStr" /><c r="O791" s="2" t="inlineStr" /><c r="P791" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2017/18 - 2 termin</t></is></c><c r="Q791" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="792"><c r="A792" s="2" t="inlineStr"><is><t>CHOROBA NIEDOKRWIENNA SERCA</t></is></c><c r="B792" s="2" t="inlineStr"><is><t>Przeciwwskazania</t></is></c><c r="C792" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D792" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E792" s="2" t="inlineStr"><is><t>W postaci naczynioskurczowej choroby niedokrwiennej serca przeciwwskazane jest stosowanie:</t></is></c><c r="F792" s="2" t="inlineStr"><is><t>metoprololu</t></is></c><c r="G792" s="2" t="inlineStr" /><c r="H792" s="2" t="inlineStr" /><c r="I792" s="2" t="inlineStr" /><c r="J792" s="2" t="inlineStr" /><c r="K792" s="2" t="inlineStr"><is><t>diltiazemu</t></is></c><c r="L792" s="2" t="inlineStr"><is><t>diazotanu izosorbidu</t></is></c><c r="M792" s="2" t="inlineStr"><is><t>werapamilu</t></is></c><c r="N792" s="2" t="inlineStr" /><c r="O792" s="2" t="inlineStr" /><c r="P792" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2017/18 - 2 termin</t></is></c><c r="Q792" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="793"><c r="A793" s="2" t="inlineStr"><is><t>ZABURZENIA RYTMU SERCA</t></is></c><c r="B793" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C793" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D793" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E793" s="2" t="inlineStr"><is><t>Do działań niepożądanych amiodaronu należy:</t></is></c><c r="F793" s="2" t="inlineStr"><is><t>hipotonia</t></is></c><c r="G793" s="2" t="inlineStr"><is><t>fotosensytyzacja</t></is></c><c r="H793" s="2" t="inlineStr"><is><t>śródmiąższowe zapalenie płuc</t></is></c><c r="I793" s="2" t="inlineStr" /><c r="J793" s="2" t="inlineStr" /><c r="K793" s="2" t="inlineStr"><is><t>tachykardia</t></is></c><c r="L793" s="2" t="inlineStr" /><c r="M793" s="2" t="inlineStr" /><c r="N793" s="2" t="inlineStr" /><c r="O793" s="2" t="inlineStr" /><c r="P793" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2017/18 - 2 termin</t></is></c><c r="Q793" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="794"><c r="A794" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B794" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C794" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D794" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E794" s="2" t="inlineStr"><is><t>Lekiem rozkurczającym tętnice pozawieńcowe jest:</t></is></c><c r="F794" s="2" t="inlineStr"><is><t>nicergolina</t></is></c><c r="G794" s="2" t="inlineStr"><is><t>alprostadyl</t></is></c><c r="H794" s="2" t="inlineStr"><is><t>fentolamina</t></is></c><c r="I794" s="2" t="inlineStr"><is><t>cilostazol</t></is></c><c r="J794" s="2" t="inlineStr" /><c r="K794" s="2" t="inlineStr" /><c r="L794" s="2" t="inlineStr" /><c r="M794" s="2" t="inlineStr" /><c r="N794" s="2" t="inlineStr" /><c r="O794" s="2" t="inlineStr" /><c r="P794" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2017/18 - 2 termin</t></is></c><c r="Q794" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="795"><c r="A795" s="2" t="inlineStr"><is><t>LEKI PRZECIWLĘKOWE</t></is></c><c r="B795" s="2" t="inlineStr"><is><t>Sposób podania</t></is></c><c r="C795" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D795" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E795" s="2" t="inlineStr"><is><t>Midazolam może być stosowany zgodnie z aktualną wiedzą:</t></is></c><c r="F795" s="2" t="inlineStr"><is><t>doustnie do sedacji w premedykacji przed zabiegami chirurgicznymi</t></is></c><c r="G795" s="2" t="inlineStr"><is><t>dożylnie w sedacji do nieprzyjemnych zabiegów diagnostycznych</t></is></c><c r="H795" s="2" t="inlineStr"><is><t>dożylnie w długotrwałej sedacji na oddziale intensywnej opieki medycznej</t></is></c><c r="I795" s="2" t="inlineStr" /><c r="J795" s="2" t="inlineStr" /><c r="K795" s="2" t="inlineStr"><is><t>doustnie w przewlekłym leczeniu bezsenności</t></is></c><c r="L795" s="2" t="inlineStr" /><c r="M795" s="2" t="inlineStr" /><c r="N795" s="2" t="inlineStr" /><c r="O795" s="2" t="inlineStr" /><c r="P795" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2017/18 - 2 termin</t></is></c><c r="Q795" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="796"><c r="A796" s="2" t="inlineStr"><is><t>LEKI PRZECIWDEPRESYJNE</t></is></c><c r="B796" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C796" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D796" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E796" s="2" t="inlineStr"><is><t>W zaburzeniach lękowych można racjonalnie zastosować:</t></is></c><c r="F796" s="2" t="inlineStr"><is><t>escitalopram</t></is></c><c r="G796" s="2" t="inlineStr"><is><t>alprazolam</t></is></c><c r="H796" s="2" t="inlineStr" /><c r="I796" s="2" t="inlineStr" /><c r="J796" s="2" t="inlineStr" /><c r="K796" s="2" t="inlineStr"><is><t>baklofen</t></is></c><c r="L796" s="2" t="inlineStr"><is><t>moklobemid</t></is></c><c r="M796" s="2" t="inlineStr" /><c r="N796" s="2" t="inlineStr" /><c r="O796" s="2" t="inlineStr" /><c r="P796" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2017/18 - 2 termin</t></is></c><c r="Q796" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="797"><c r="A797" s="2" t="inlineStr"><is><t>LEKI PRZECIWDEPRESYJNE</t></is></c><c r="B797" s="2" t="inlineStr"><is><t>Antidotum</t></is></c><c r="C797" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D797" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E797" s="2" t="inlineStr"><is><t>Flumazenil to:</t></is></c><c r="F797" s="2" t="inlineStr"><is><t>antagonista receptora benzodiazepinowego</t></is></c><c r="G797" s="2" t="inlineStr"><is><t>antidotum w przedawkowaniu benzodiazepin</t></is></c><c r="H797" s="2" t="inlineStr" /><c r="I797" s="2" t="inlineStr" /><c r="J797" s="2" t="inlineStr" /><c r="K797" s="2" t="inlineStr"><is><t>odwrotny agonista receptora GABA-A</t></is></c><c r="L797" s="2" t="inlineStr"><is><t>antidotum w przedawkowaniu trójpierścieniowych leków przeciwdepresyjnych</t></is></c><c r="M797" s="2" t="inlineStr" /><c r="N797" s="2" t="inlineStr" /><c r="O797" s="2" t="inlineStr" /><c r="P797" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2017/18 - 2 termin</t></is></c><c r="Q797" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="798"><c r="A798" s="2" t="inlineStr"><is><t>LEKI PRZECIWLĘKOWE</t></is></c><c r="B798" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C798" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D798" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E798" s="2" t="inlineStr"><is><t>Do krótkodziałających benzodiazepin należy:</t></is></c><c r="F798" s="2" t="inlineStr"><is><t>midazolam</t></is></c><c r="G798" s="2" t="inlineStr"><is><t>triazolam</t></is></c><c r="H798" s="2" t="inlineStr" /><c r="I798" s="2" t="inlineStr" /><c r="J798" s="2" t="inlineStr" /><c r="K798" s="2" t="inlineStr"><is><t>diazepam</t></is></c><c r="L798" s="2" t="inlineStr"><is><t>flunitrazepam</t></is></c><c r="M798" s="2" t="inlineStr" /><c r="N798" s="2" t="inlineStr" /><c r="O798" s="2" t="inlineStr" /><c r="P798" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2017/18 - 2 termin</t></is></c><c r="Q798" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="799"><c r="A799" s="2" t="inlineStr"><is><t>UKŁAD WSPÓŁCZULNY</t></is></c><c r="B799" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C799" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D799" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E799" s="2" t="inlineStr"><is><t>Wskaż prawidłowe połączenie lek-mechanizm działania:</t></is></c><c r="F799" s="2" t="inlineStr"><is><t>mirtazapina – antagonista receptorów adrenergicznych alfa2 i serotoninowych 5HT2a, 5HT2c, 5HT3</t></is></c><c r="G799" s="2" t="inlineStr" /><c r="H799" s="2" t="inlineStr" /><c r="I799" s="2" t="inlineStr" /><c r="J799" s="2" t="inlineStr" /><c r="K799" s="2" t="inlineStr"><is><t>reboksetyna – hamowanie wychwytu zwrotnego serotoniny i noradrenaliny</t></is></c><c r="L799" s="2" t="inlineStr"><is><t>tianeptyna – selektywne hamowanie wychwytu zwrotnego noradrenaliny</t></is></c><c r="M799" s="2" t="inlineStr"><is><t>wenlafaksyna – nasilanie presynaptycznego wychwytu zwrotnego serotoniny</t></is></c><c r="N799" s="2" t="inlineStr" /><c r="O799" s="2" t="inlineStr" /><c r="P799" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2017/18 - 2 termin</t></is></c><c r="Q799" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="800"><c r="A800" s="2" t="inlineStr"><is><t>CHOROBA PARKINSONA</t></is></c><c r="B800" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C800" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D800" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E800" s="2" t="inlineStr"><is><t>Do działań niepożądanych neuroleptyków zalicza się:</t></is></c><c r="F800" s="2" t="inlineStr"><is><t>dyskinezy</t></is></c><c r="G800" s="2" t="inlineStr"><is><t>dysfunkcje seksualne</t></is></c><c r="H800" s="2" t="inlineStr" /><c r="I800" s="2" t="inlineStr" /><c r="J800" s="2" t="inlineStr" /><c r="K800" s="2" t="inlineStr"><is><t>skłonność do hazardu</t></is></c><c r="L800" s="2" t="inlineStr"><is><t>somnambulizm (sennowłóctwo)</t></is></c><c r="M800" s="2" t="inlineStr" /><c r="N800" s="2" t="inlineStr" /><c r="O800" s="2" t="inlineStr" /><c r="P800" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2017/18 - 2 termin</t></is></c><c r="Q800" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="801"><c r="A801" s="2" t="inlineStr"><is><t>LEKI PRZECIWPSYCHOTYCZNE</t></is></c><c r="B801" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C801" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D801" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E801" s="2" t="inlineStr"><is><t>Stężenie cholesterolu LDL w surowicy zwiększa:</t></is></c><c r="F801" s="2" t="inlineStr"><is><t>olanzapina</t></is></c><c r="G801" s="2" t="inlineStr"><is><t>rysperydon</t></is></c><c r="H801" s="2" t="inlineStr"><is><t>kwetiapina</t></is></c><c r="I801" s="2" t="inlineStr" /><c r="J801" s="2" t="inlineStr" /><c r="K801" s="2" t="inlineStr"><is><t>zyprazydon</t></is></c><c r="L801" s="2" t="inlineStr" /><c r="M801" s="2" t="inlineStr" /><c r="N801" s="2" t="inlineStr" /><c r="O801" s="2" t="inlineStr" /><c r="P801" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2017/18 - 2 termin</t></is></c><c r="Q801" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="802"><c r="A802" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B802" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C802" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D802" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E802" s="2" t="inlineStr"><is><t>Działanie przeciwwymiotne ma:</t></is></c><c r="F802" s="2" t="inlineStr"><is><t>metoklopramid</t></is></c><c r="G802" s="2" t="inlineStr"><is><t>prometazyna</t></is></c><c r="H802" s="2" t="inlineStr"><is><t>tietylperazyna</t></is></c><c r="I802" s="2" t="inlineStr"><is><t>palonosetron</t></is></c><c r="J802" s="2" t="inlineStr" /><c r="K802" s="2" t="inlineStr" /><c r="L802" s="2" t="inlineStr" /><c r="M802" s="2" t="inlineStr" /><c r="N802" s="2" t="inlineStr" /><c r="O802" s="2" t="inlineStr" /><c r="P802" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2017/18 - 2 termin</t></is></c><c r="Q802" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="803"><c r="A803" s="2" t="inlineStr"><is><t>PADACZKA</t></is></c><c r="B803" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C803" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D803" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E803" s="2" t="inlineStr"><is><t>Przez wpływ na prąd sodowy działa:</t></is></c><c r="F803" s="2" t="inlineStr"><is><t>okskarbazepina</t></is></c><c r="G803" s="2" t="inlineStr"><is><t>kwas walproinowy</t></is></c><c r="H803" s="2" t="inlineStr"><is><t>lamotrygina</t></is></c><c r="I803" s="2" t="inlineStr" /><c r="J803" s="2" t="inlineStr" /><c r="K803" s="2" t="inlineStr"><is><t>pregabalina</t></is></c><c r="L803" s="2" t="inlineStr" /><c r="M803" s="2" t="inlineStr" /><c r="N803" s="2" t="inlineStr" /><c r="O803" s="2" t="inlineStr" /><c r="P803" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2017/18 - 2 termin</t></is></c><c r="Q803" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="804"><c r="A804" s="2" t="inlineStr"><is><t>UKŁAD WSPÓŁCZULNY</t></is></c><c r="B804" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C804" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D804" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E804" s="2" t="inlineStr"><is><t>W profilaktyce migreny wykazano skuteczność:</t></is></c><c r="F804" s="2" t="inlineStr"><is><t>kwasu walproinowego</t></is></c><c r="G804" s="2" t="inlineStr"><is><t>toksyny botulinowej (w migrenie występującej co najmniej 14 dni w miesiącu)</t></is></c><c r="H804" s="2" t="inlineStr"><is><t>topiramatu</t></is></c><c r="I804" s="2" t="inlineStr"><is><t>propranololu</t></is></c><c r="J804" s="2" t="inlineStr" /><c r="K804" s="2" t="inlineStr" /><c r="L804" s="2" t="inlineStr" /><c r="M804" s="2" t="inlineStr" /><c r="N804" s="2" t="inlineStr" /><c r="O804" s="2" t="inlineStr" /><c r="P804" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2017/18 - 2 termin</t></is></c><c r="Q804" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="805"><c r="A805" s="2" t="inlineStr"><is><t>LEKI PRZECIWDEPRESYJNE</t></is></c><c r="B805" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C805" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D805" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E805" s="2" t="inlineStr"><is><t>W leczeniu bólu neuropatycznego stosuje się:</t></is></c><c r="F805" s="2" t="inlineStr"><is><t>wenlafaksynę</t></is></c><c r="G805" s="2" t="inlineStr"><is><t>duloksetynę</t></is></c><c r="H805" s="2" t="inlineStr"><is><t>amitryptylinę</t></is></c><c r="I805" s="2" t="inlineStr" /><c r="J805" s="2" t="inlineStr" /><c r="K805" s="2" t="inlineStr"><is><t>tianeptynę</t></is></c><c r="L805" s="2" t="inlineStr" /><c r="M805" s="2" t="inlineStr" /><c r="N805" s="2" t="inlineStr" /><c r="O805" s="2" t="inlineStr" /><c r="P805" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2017/18 - 2 termin</t></is></c><c r="Q805" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="806"><c r="A806" s="2" t="inlineStr"><is><t>LEKI IMMUNOSUPRESYJNE</t></is></c><c r="B806" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C806" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D806" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E806" s="2" t="inlineStr"><is><t>W leczeniu łuszczycy stosuje się:</t></is></c><c r="F806" s="2" t="inlineStr"><is><t>preparaty dziegciowe</t></is></c><c r="G806" s="2" t="inlineStr"><is><t>adapalen</t></is></c><c r="H806" s="2" t="inlineStr"><is><t>adalimumab</t></is></c><c r="I806" s="2" t="inlineStr" /><c r="J806" s="2" t="inlineStr" /><c r="K806" s="2" t="inlineStr"><is><t>kwas azelainowy</t></is></c><c r="L806" s="2" t="inlineStr" /><c r="M806" s="2" t="inlineStr" /><c r="N806" s="2" t="inlineStr" /><c r="O806" s="2" t="inlineStr" /><c r="P806" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2017/18 - 2 termin</t></is></c><c r="Q806" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="807"><c r="A807" s="2" t="inlineStr"><is><t>HORMONY PŁCIOWE</t></is></c><c r="B807" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C807" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D807" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E807" s="2" t="inlineStr"><is><t>Działanie niepożądane sterydów anabolicznych to:</t></is></c><c r="F807" s="2" t="inlineStr"><is><t>uszkodzenie ścięgien</t></is></c><c r="G807" s="2" t="inlineStr"><is><t>wzrost hematokrytu</t></is></c><c r="H807" s="2" t="inlineStr"><is><t>łysienie</t></is></c><c r="I807" s="2" t="inlineStr"><is><t>ginekomastia</t></is></c><c r="J807" s="2" t="inlineStr" /><c r="K807" s="2" t="inlineStr" /><c r="L807" s="2" t="inlineStr" /><c r="M807" s="2" t="inlineStr" /><c r="N807" s="2" t="inlineStr" /><c r="O807" s="2" t="inlineStr" /><c r="P807" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2017/18 - 2 termin</t></is></c><c r="Q807" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="808"><c r="A808" s="2" t="inlineStr"><is><t>FARMAKOKINETYKA</t></is></c><c r="B808" s="2" t="inlineStr"><is><t>Interakcje</t></is></c><c r="C808" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D808" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E808" s="2" t="inlineStr"><is><t>Kwas walproinowy:</t></is></c><c r="F808" s="2" t="inlineStr"><is><t>może powodować zwiększenie masy ciała</t></is></c><c r="G808" s="2" t="inlineStr"><is><t>nie powinien być stosowany u ciężarnych</t></is></c><c r="H808" s="2" t="inlineStr"><is><t>może być zastosowany w profilaktyce dwubiegunowej choroby afektywnej</t></is></c><c r="I808" s="2" t="inlineStr" /><c r="J808" s="2" t="inlineStr" /><c r="K808" s="2" t="inlineStr"><is><t>jest induktorem izoenzymów CYP</t></is></c><c r="L808" s="2" t="inlineStr" /><c r="M808" s="2" t="inlineStr" /><c r="N808" s="2" t="inlineStr" /><c r="O808" s="2" t="inlineStr" /><c r="P808" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2017/18 - 2 termin</t></is></c><c r="Q808" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="809"><c r="A809" s="2" t="inlineStr"><is><t>UKŁAD WSPÓŁCZULNY</t></is></c><c r="B809" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C809" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D809" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E809" s="2" t="inlineStr"><is><t>W terapii jaskry pierwotnej otwartego kąta można zastosować:</t></is></c><c r="F809" s="2" t="inlineStr"><is><t>timolol</t></is></c><c r="G809" s="2" t="inlineStr"><is><t>dorzolamid</t></is></c><c r="H809" s="2" t="inlineStr"><is><t>betaksolol</t></is></c><c r="I809" s="2" t="inlineStr"><is><t>latanoprost</t></is></c><c r="J809" s="2" t="inlineStr" /><c r="K809" s="2" t="inlineStr" /><c r="L809" s="2" t="inlineStr" /><c r="M809" s="2" t="inlineStr" /><c r="N809" s="2" t="inlineStr" /><c r="O809" s="2" t="inlineStr" /><c r="P809" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2017/18 - 2 termin</t></is></c><c r="Q809" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="810"><c r="A810" s="2" t="inlineStr"><is><t>OSTEOPOROZA</t></is></c><c r="B810" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C810" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D810" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E810" s="2" t="inlineStr"><is><t>Wskazaniem do stosowania bisfosfonianów jest:</t></is></c><c r="F810" s="2" t="inlineStr"><is><t>osteoporoza posteroidowa</t></is></c><c r="G810" s="2" t="inlineStr"><is><t>ból z powodu osteolitycznych przerzutów nowotworowych do kości</t></is></c><c r="H810" s="2" t="inlineStr" /><c r="I810" s="2" t="inlineStr" /><c r="J810" s="2" t="inlineStr" /><c r="K810" s="2" t="inlineStr"><is><t>ciężka hiperkaliemia</t></is></c><c r="L810" s="2" t="inlineStr"><is><t>ciężka hipokalcemia</t></is></c><c r="M810" s="2" t="inlineStr" /><c r="N810" s="2" t="inlineStr" /><c r="O810" s="2" t="inlineStr" /><c r="P810" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2017/18 - 2 termin</t></is></c><c r="Q810" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="811"><c r="A811" s="2" t="inlineStr"><is><t>LEKI PRZECIWHISTAMINOWE</t></is></c><c r="B811" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C811" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D811" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E811" s="2" t="inlineStr"><is><t>Korzystne cechy leku przeciwhistaminowego stosowanego do leczenia przewlekłego alergicznego nieżytu nosa to:</t></is></c><c r="F811" s="2" t="inlineStr"><is><t>utrudnione przechodzenie do ośrodkowego układu nerwowego</t></is></c><c r="G811" s="2" t="inlineStr" /><c r="H811" s="2" t="inlineStr" /><c r="I811" s="2" t="inlineStr" /><c r="J811" s="2" t="inlineStr" /><c r="K811" s="2" t="inlineStr"><is><t>krótki czas działania 3-6 godzin</t></is></c><c r="L811" s="2" t="inlineStr"><is><t>działanie cholinolityczne</t></is></c><c r="M811" s="2" t="inlineStr"><is><t>zdolność do kumulacji w tkankach obwodowych</t></is></c><c r="N811" s="2" t="inlineStr" /><c r="O811" s="2" t="inlineStr" /><c r="P811" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2017/18 - 2 termin</t></is></c><c r="Q811" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="812"><c r="A812" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B812" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C812" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D812" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E812" s="2" t="inlineStr"><is><t>Wskaż prawidłowe ordynacje lekarskie:</t></is></c><c r="F812" s="2" t="inlineStr"><is><t>biegunka o etiologii Clostridium difficile o nieciężkim przebiegu – metronidazol przez 10 dni</t></is></c><c r="G812" s="2" t="inlineStr" /><c r="H812" s="2" t="inlineStr" /><c r="I812" s="2" t="inlineStr" /><c r="J812" s="2" t="inlineStr" /><c r="K812" s="2" t="inlineStr"><is><t>nosicielstwo Klebsiella pneumoniae ESBL (+) w przewodzie pokarmowym – meropenem przez 5 dni</t></is></c><c r="L812" s="2" t="inlineStr"><is><t>posiew krwi Streptococcus epidermidis oporny na metycylinę (MR) w butelce tlenowej i beztlenowej u pacjenta niegorączkującego, leukocyty = 8,9 G/l (N 4-10 G/L), CRP – 100 mg/l (N do 10 mg/l), prokalcytonina = 0,01 ng/ml (N do 0,5ng/ml) – wankomycyna przez 3 tygodnie</t></is></c><c r="M812" s="2" t="inlineStr"><is><t>posiew moczu Escherichia coli &gt; 10 5 jtk/ml (cfu/ml) u pacjentki z objawami dysurycznymi – imipenem + cilastatyna z powodu najniższej wartości MIC wg antybiogramu przez 3 dni</t></is></c><c r="N812" s="2" t="inlineStr" /><c r="O812" s="2" t="inlineStr" /><c r="P812" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2016/17 - 1 termin</t></is></c><c r="Q812" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="813"><c r="A813" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B813" s="2" t="inlineStr"><is><t>Interakcje</t></is></c><c r="C813" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D813" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E813" s="2" t="inlineStr"><is><t>Kobieta z zakażeniem Enteroccocus faecium opornym na glikopeptydy (VRE) jest leczona lekiem przeciwbakteryjnym wiążącym się z jednostką 50S rybosomu bakteryjnego. Zaznacz prawdziwe informacje dotyczące tego leku:</t></is></c><c r="F813" s="2" t="inlineStr"><is><t>podczas jego stosowania &gt;10 dni może dojść do rozwoju trombocytopenii</t></is></c><c r="G813" s="2" t="inlineStr"><is><t>może być bezpiecznie stosowany u pacjentów leczonych lekami blokującymi CYP3A4, ponieważ nie wchodzi z nimi w interakcje</t></is></c><c r="H813" s="2" t="inlineStr" /><c r="I813" s="2" t="inlineStr" /><c r="J813" s="2" t="inlineStr" /><c r="K813" s="2" t="inlineStr"><is><t>jego działanie przeciwbakteryjne zależy od stężenia maksymalnego</t></is></c><c r="L813" s="2" t="inlineStr"><is><t>może być bezpiecznie zastosowany w trakcie leczenia inhibitorami wychwytu zwrotnego serotoniny, ponieważ nie wchodzi z nimi w interakcje</t></is></c><c r="M813" s="2" t="inlineStr" /><c r="N813" s="2" t="inlineStr" /><c r="O813" s="2" t="inlineStr" /><c r="P813" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2016/17 - 1 termin</t></is></c><c r="Q813" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="814"><c r="A814" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B814" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C814" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D814" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E814" s="2" t="inlineStr"><is><t>60-letnia kobieta z domowym zapaleniem płuc, w skali CURB-65 = 0 pkt jest leczona zgodnie ze standardem postępowania uwzględniającym dominującą etiologię tego zakażenia u osób dorosłych. Zaznacz prawdziwe informacje dotyczące tego leczenia:</t></is></c><c r="F814" s="2" t="inlineStr"><is><t>wymaga stałych optymalnych przedziałów dawkowania w ciągu całej doby</t></is></c><c r="G814" s="2" t="inlineStr"><is><t>w razie nadwrażliwości na leczenie początkowe w wywiadach wskazane jest zastosowanie lewofloksacyny lub moksyfloksacyny</t></is></c><c r="H814" s="2" t="inlineStr" /><c r="I814" s="2" t="inlineStr" /><c r="J814" s="2" t="inlineStr" /><c r="K814" s="2" t="inlineStr"><is><t>konieczne jest leczenie skojarzone 2 lekami przeciwbakteryjnymi o różnych mechanizmach działania</t></is></c><c r="L814" s="2" t="inlineStr"><is><t>powinno trwać co najmniej 21 dni</t></is></c><c r="M814" s="2" t="inlineStr" /><c r="N814" s="2" t="inlineStr" /><c r="O814" s="2" t="inlineStr" /><c r="P814" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2016/17 - 1 termin</t></is></c><c r="Q814" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="815"><c r="A815" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B815" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C815" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D815" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E815" s="2" t="inlineStr"><is><t>Amoksycylina z kwasem klawulanowym jest powszechnie stosowanym połączeniem antybiotykowym, które ma jednak ograniczenia. Wskaż istotne wady tego połączenia:</t></is></c><c r="F815" s="2" t="inlineStr"><is><t>aktywność wobec fizjologicznego mikrobiomu przewodu pokarmowego człowieka</t></is></c><c r="G815" s="2" t="inlineStr"><is><t>zależne od kwasu klawulanowego biegunka i uszkodzenie wątroby</t></is></c><c r="H815" s="2" t="inlineStr"><is><t>konieczność korekty dawki proporcjonalnie do eGFR (wskaźnika filtracji kłębuszkowej)</t></is></c><c r="I815" s="2" t="inlineStr" /><c r="J815" s="2" t="inlineStr" /><c r="K815" s="2" t="inlineStr"><is><t>ograniczona biodostępność po podaniu doustnym</t></is></c><c r="L815" s="2" t="inlineStr"><is><t>W zakażeniach dermatofitami stosuje się:</t></is></c><c r="M815" s="2" t="inlineStr" /><c r="N815" s="2" t="inlineStr" /><c r="O815" s="2" t="inlineStr" /><c r="P815" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2016/17 - 1 termin</t></is></c><c r="Q815" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="816"><c r="A816" s="2" t="inlineStr"><is><t>LEKI PRZECIWGRZYBICZE</t></is></c><c r="B816" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C816" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D816" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E816" s="2" t="inlineStr"><is><t>Anidulafungina w odróżnieniu od amfoterycyny B:</t></is></c><c r="F816" s="2" t="inlineStr"><is><t>ma wąskie spektrum działania przeciwgrzybiczego</t></is></c><c r="G816" s="2" t="inlineStr"><is><t>działa poprzez zahamowanie syntezy ściany komórkowej grzyba</t></is></c><c r="H816" s="2" t="inlineStr"><is><t>nie powoduje uszkodzenia nerek</t></is></c><c r="I816" s="2" t="inlineStr" /><c r="J816" s="2" t="inlineStr" /><c r="K816" s="2" t="inlineStr"><is><t>w leczeniu inwazyjnej kandydozy podawana jest drogą dożylną</t></is></c><c r="L816" s="2" t="inlineStr" /><c r="M816" s="2" t="inlineStr" /><c r="N816" s="2" t="inlineStr" /><c r="O816" s="2" t="inlineStr" /><c r="P816" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2016/17 - 1 termin</t></is></c><c r="Q816" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="817"><c r="A817" s="2" t="inlineStr"><is><t>LEKI PRZECIWWIRUSOWE</t></is></c><c r="B817" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C817" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D817" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E817" s="2" t="inlineStr"><is><t>Wskaż prawdziwe stwierdzenia dotyczące inhibitorów neuraminidazy:</t></is></c><c r="F817" s="2" t="inlineStr"><is><t>są skuteczne wobec wirusa grypy A i B</t></is></c><c r="G817" s="2" t="inlineStr"><is><t>leczenie lekami tej grupy powinno być wdrożone do 48 h od początku objawów u nieszczepionych osób z grup ryzyka ciężkiego przebiegu grypy</t></is></c><c r="H817" s="2" t="inlineStr" /><c r="I817" s="2" t="inlineStr" /><c r="J817" s="2" t="inlineStr" /><c r="K817" s="2" t="inlineStr"><is><t>oseltamiwir ma działanie tylko w drogach oddechowych, a zanamiwir ogólnoustrojowe, co wiąże się ze sposobem podania tych leków</t></is></c><c r="L817" s="2" t="inlineStr"><is><t>są nieskuteczne wobec wirusa świńskiej grypy H1N1</t></is></c><c r="M817" s="2" t="inlineStr" /><c r="N817" s="2" t="inlineStr" /><c r="O817" s="2" t="inlineStr" /><c r="P817" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2016/17 - 1 termin</t></is></c><c r="Q817" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="818"><c r="A818" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B818" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C818" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D818" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E818" s="2" t="inlineStr"><is><t>Flukonazol zgodnie z aktualną widzą medyczną można zastosować w profilaktyce medycznej u:</t></is></c><c r="F818" s="2" t="inlineStr"><is><t>pacjentów z agranulocytozą przez czas jej trwania</t></is></c><c r="G818" s="2" t="inlineStr"><is><t>biorców przeszczepów wątroby w okresie okołoprzeszczepiennym</t></is></c><c r="H818" s="2" t="inlineStr" /><c r="I818" s="2" t="inlineStr" /><c r="J818" s="2" t="inlineStr" /><c r="K818" s="2" t="inlineStr"><is><t>pacjentów leczonych szerokospektralnymi lekami przeciwbakteryjnymi przez czas takiej antybiotykoterapii</t></is></c><c r="L818" s="2" t="inlineStr"><is><t>wszystkich pacjentów oddziałów intensywnej terapii</t></is></c><c r="M818" s="2" t="inlineStr" /><c r="N818" s="2" t="inlineStr" /><c r="O818" s="2" t="inlineStr" /><c r="P818" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2016/17 - 1 termin</t></is></c><c r="Q818" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="819"><c r="A819" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B819" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C819" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D819" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E819" s="2" t="inlineStr"><is><t>Intrygujące konsekwencje stosowania leków to:</t></is></c><c r="F819" s="2" t="inlineStr"><is><t>pomarańczowe łzy i pot podczas stosowania ryfampicyny</t></is></c><c r="G819" s="2" t="inlineStr"><is><t>widzenie przedmiotów w żółtych obwódkach, tzw. „halo”, podczas stosowania digoksyny</t></is></c><c r="H819" s="2" t="inlineStr"><is><t>lepsze wyniki sportowe podczas stosowania meldonium u zawodowych sportowców</t></is></c><c r="I819" s="2" t="inlineStr" /><c r="J819" s="2" t="inlineStr" /><c r="K819" s="2" t="inlineStr"><is><t>poprawa IQ podczas stosowania piracetamu u licealistów i studentów</t></is></c><c r="L819" s="2" t="inlineStr" /><c r="M819" s="2" t="inlineStr" /><c r="N819" s="2" t="inlineStr" /><c r="O819" s="2" t="inlineStr" /><c r="P819" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2016/17 - 1 termin</t></is></c><c r="Q819" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="820"><c r="A820" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B820" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C820" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D820" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E820" s="2" t="inlineStr"><is><t>Do antyseptyki na ranę zastosujesz:</t></is></c><c r="F820" s="2" t="inlineStr"><is><t>jodopowidon</t></is></c><c r="G820" s="2" t="inlineStr"><is><t>oktenidynę</t></is></c><c r="H820" s="2" t="inlineStr" /><c r="I820" s="2" t="inlineStr" /><c r="J820" s="2" t="inlineStr" /><c r="K820" s="2" t="inlineStr"><is><t>wodę utlenioną</t></is></c><c r="L820" s="2" t="inlineStr"><is><t>0,9% roztwór NaCl</t></is></c><c r="M820" s="2" t="inlineStr" /><c r="N820" s="2" t="inlineStr" /><c r="O820" s="2" t="inlineStr" /><c r="P820" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2016/17 - 1 termin</t></is></c><c r="Q820" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="821"><c r="A821" s="2" t="inlineStr"><is><t>UKŁAD ODDECHOWY</t></is></c><c r="B821" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C821" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D821" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E821" s="2" t="inlineStr"><is><t>W leczeniu astmy są stosowane leki z grupy:</t></is></c><c r="F821" s="2" t="inlineStr"><is><t>agonistów receptora glikokortykosteroidowego</t></is></c><c r="G821" s="2" t="inlineStr"><is><t>antagonistów receptora M 3</t></is></c><c r="H821" s="2" t="inlineStr" /><c r="I821" s="2" t="inlineStr" /><c r="J821" s="2" t="inlineStr" /><c r="K821" s="2" t="inlineStr"><is><t>przeciwciał monoklonalnych przeciwko receptorowi dla interleukiny 1 (IL-1)</t></is></c><c r="L821" s="2" t="inlineStr"><is><t>agonistów recepta leukotrienowego CysLT 1 (B)</t></is></c><c r="M821" s="2" t="inlineStr" /><c r="N821" s="2" t="inlineStr" /><c r="O821" s="2" t="inlineStr" /><c r="P821" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2016/17 - 1 termin</t></is></c><c r="Q821" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="822"><c r="A822" s="2" t="inlineStr"><is><t>UKŁAD ODDECHOWY</t></is></c><c r="B822" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C822" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D822" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E822" s="2" t="inlineStr"><is><t>Wskaż zestaw leków o identycznym molekularnym mechanizmie działania:</t></is></c><c r="F822" s="2" t="inlineStr"><is><t>acetylocysteina, mesna, erdosteina</t></is></c><c r="G822" s="2" t="inlineStr"><is><t>indekaterol, wilanterol, salbutamol</t></is></c><c r="H822" s="2" t="inlineStr"><is><t>tiotropium, glikopironium, umeklidynium</t></is></c><c r="I822" s="2" t="inlineStr" /><c r="J822" s="2" t="inlineStr" /><c r="K822" s="2" t="inlineStr"><is><t>zileuton, zafirlukast, cyklezonid</t></is></c><c r="L822" s="2" t="inlineStr" /><c r="M822" s="2" t="inlineStr" /><c r="N822" s="2" t="inlineStr" /><c r="O822" s="2" t="inlineStr" /><c r="P822" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2016/17 - 1 termin</t></is></c><c r="Q822" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="823"><c r="A823" s="2" t="inlineStr"><is><t>NADCIŚNIENIE TĘTNICZE</t></is></c><c r="B823" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C823" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D823" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E823" s="2" t="inlineStr"><is><t>Obciążenie wstępne serca zmniejsza:</t></is></c><c r="F823" s="2" t="inlineStr"><is><t>triazotan izosorbidu</t></is></c><c r="G823" s="2" t="inlineStr"><is><t>torasemid</t></is></c><c r="H823" s="2" t="inlineStr" /><c r="I823" s="2" t="inlineStr" /><c r="J823" s="2" t="inlineStr" /><c r="K823" s="2" t="inlineStr"><is><t>amlodypina</t></is></c><c r="L823" s="2" t="inlineStr"><is><t>bisoprolol</t></is></c><c r="M823" s="2" t="inlineStr" /><c r="N823" s="2" t="inlineStr" /><c r="O823" s="2" t="inlineStr" /><c r="P823" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2016/17 - 1 termin</t></is></c><c r="Q823" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="824"><c r="A824" s="2" t="inlineStr"><is><t>LEKI MOCZOPĘDNE</t></is></c><c r="B824" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C824" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D824" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E824" s="2" t="inlineStr"><is><t>Wskaż prawdziwe stwierdzenie:</t></is></c><c r="F824" s="2" t="inlineStr"><is><t>furosemid bezpośrednio rozkurcza naczynia krwionośne</t></is></c><c r="G824" s="2" t="inlineStr"><is><t>mannitol redukuje ciśnienie osmotyczne w rdzeniu nerki</t></is></c><c r="H824" s="2" t="inlineStr" /><c r="I824" s="2" t="inlineStr" /><c r="J824" s="2" t="inlineStr" /><c r="K824" s="2" t="inlineStr"><is><t>hydrochlorotiazyd działa natiuretycznie niezależnie od eGFR (wskaźnika filtracji kłębuszkowej)</t></is></c><c r="L824" s="2" t="inlineStr"><is><t>sporonolakton zwiększa objętość krwi krążącej</t></is></c><c r="M824" s="2" t="inlineStr" /><c r="N824" s="2" t="inlineStr" /><c r="O824" s="2" t="inlineStr" /><c r="P824" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2016/17 - 1 termin</t></is></c><c r="Q824" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="825"><c r="A825" s="2" t="inlineStr"><is><t>ZABURZENIA RYTMU SERCA</t></is></c><c r="B825" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C825" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D825" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E825" s="2" t="inlineStr"><is><t>Pacjent z objawową bradykardią = 35 uderzeń/min jest leczony poniższym zestawem leków. Który z nich należy niezwłocznie odstawić?</t></is></c><c r="F825" s="2" t="inlineStr"><is><t>digoksyna</t></is></c><c r="G825" s="2" t="inlineStr"><is><t>amiodaron</t></is></c><c r="H825" s="2" t="inlineStr"><is><t>betaksolol</t></is></c><c r="I825" s="2" t="inlineStr" /><c r="J825" s="2" t="inlineStr" /><c r="K825" s="2" t="inlineStr"><is><t>losartan</t></is></c><c r="L825" s="2" t="inlineStr" /><c r="M825" s="2" t="inlineStr" /><c r="N825" s="2" t="inlineStr" /><c r="O825" s="2" t="inlineStr" /><c r="P825" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2016/17 - 1 termin</t></is></c><c r="Q825" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="826"><c r="A826" s="2" t="inlineStr"><is><t>ZABURZENIA RYTMU SERCA</t></is></c><c r="B826" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C826" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D826" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E826" s="2" t="inlineStr"><is><t>Wskaż prawidłowe pary lek - działanie niepożądane:</t></is></c><c r="F826" s="2" t="inlineStr"><is><t>propafenon - epizody nieutrwalonego częstoskurczu komorowego</t></is></c><c r="G826" s="2" t="inlineStr"><is><t>adenozyna - ból w klatce piersiowej</t></is></c><c r="H826" s="2" t="inlineStr" /><c r="I826" s="2" t="inlineStr" /><c r="J826" s="2" t="inlineStr" /><c r="K826" s="2" t="inlineStr"><is><t>wernakalant - migotanie przedsionków</t></is></c><c r="L826" s="2" t="inlineStr"><is><t>sotalol – zwiększenie progu defibrylacji</t></is></c><c r="M826" s="2" t="inlineStr" /><c r="N826" s="2" t="inlineStr" /><c r="O826" s="2" t="inlineStr" /><c r="P826" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2016/17 - 1 termin</t></is></c><c r="Q826" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="827"><c r="A827" s="2" t="inlineStr"><is><t>NIEWYDOLNOŚĆ SERCA</t></is></c><c r="B827" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C827" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D827" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E827" s="2" t="inlineStr"><is><t>Działanie inotropowe dodatnie i rozkurczające naczynia ma:</t></is></c><c r="F827" s="2" t="inlineStr"><is><t>lewosimendan</t></is></c><c r="G827" s="2" t="inlineStr"><is><t>dobutamina</t></is></c><c r="H827" s="2" t="inlineStr" /><c r="I827" s="2" t="inlineStr" /><c r="J827" s="2" t="inlineStr" /><c r="K827" s="2" t="inlineStr"><is><t>nebiwolol</t></is></c><c r="L827" s="2" t="inlineStr"><is><t>efedryna</t></is></c><c r="M827" s="2" t="inlineStr" /><c r="N827" s="2" t="inlineStr" /><c r="O827" s="2" t="inlineStr" /><c r="P827" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2016/17 - 1 termin</t></is></c><c r="Q827" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="828"><c r="A828" s="2" t="inlineStr"><is><t>ZABURZENIA RYTMU SERCA</t></is></c><c r="B828" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C828" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D828" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E828" s="2" t="inlineStr"><is><t>Wskaż minusy leczenia lipofilnym beta-adrenolitykiem:</t></is></c><c r="F828" s="2" t="inlineStr"><is><t>zaburzenia potencji</t></is></c><c r="G828" s="2" t="inlineStr"><is><t>ograniczenie wydolności fizycznej</t></is></c><c r="H828" s="2" t="inlineStr"><is><t>zaburzenia lipidowe</t></is></c><c r="I828" s="2" t="inlineStr" /><c r="J828" s="2" t="inlineStr" /><c r="K828" s="2" t="inlineStr"><is><t>działanie proarytmiczne, w tym obniżenie progu migotania komór</t></is></c><c r="L828" s="2" t="inlineStr" /><c r="M828" s="2" t="inlineStr" /><c r="N828" s="2" t="inlineStr" /><c r="O828" s="2" t="inlineStr" /><c r="P828" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2016/17 - 1 termin</t></is></c><c r="Q828" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="829"><c r="A829" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B829" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C829" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D829" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E829" s="2" t="inlineStr"><is><t>U 70-letniego mężczyzny z przewlekłą niewydolnością żylną wspomagająco do kompresjoterapii zastosujesz:</t></is></c><c r="F829" s="2" t="inlineStr"><is><t>mikronizowaną diosminę + hesperydynę</t></is></c><c r="G829" s="2" t="inlineStr" /><c r="H829" s="2" t="inlineStr" /><c r="I829" s="2" t="inlineStr" /><c r="J829" s="2" t="inlineStr" /><c r="K829" s="2" t="inlineStr"><is><t>kwas acetylosalicylowy w dawce antyagregacyjnej</t></is></c><c r="L829" s="2" t="inlineStr"><is><t>enoksaparynę w dawce profilaktycznej</t></is></c><c r="M829" s="2" t="inlineStr"><is><t>furosemid w dawce leczniczej</t></is></c><c r="N829" s="2" t="inlineStr" /><c r="O829" s="2" t="inlineStr" /><c r="P829" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2016/17 - 1 termin</t></is></c><c r="Q829" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="830"><c r="A830" s="2" t="inlineStr"><is><t>LEKI PRZECIWLĘKOWE</t></is></c><c r="B830" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C830" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D830" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E830" s="2" t="inlineStr"><is><t>80-letniemu mężczyźnie przesypiającemu w nocy 5 h, uskarżającemu na trudności z zasypianiem należy zalecić:</t></is></c><c r="F830" s="2" t="inlineStr"><is><t>zasady higieny snu</t></is></c><c r="G830" s="2" t="inlineStr" /><c r="H830" s="2" t="inlineStr" /><c r="I830" s="2" t="inlineStr" /><c r="J830" s="2" t="inlineStr" /><c r="K830" s="2" t="inlineStr"><is><t>alprazolam</t></is></c><c r="L830" s="2" t="inlineStr"><is><t>zolpidem</t></is></c><c r="M830" s="2" t="inlineStr"><is><t>hydroksyzynę</t></is></c><c r="N830" s="2" t="inlineStr" /><c r="O830" s="2" t="inlineStr" /><c r="P830" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2016/17 - 1 termin</t></is></c><c r="Q830" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="831"><c r="A831" s="2" t="inlineStr"><is><t>ZABURZENIA RYTMU SERCA</t></is></c><c r="B831" s="2" t="inlineStr"><is><t>Przeciwwskazania</t></is></c><c r="C831" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D831" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E831" s="2" t="inlineStr"><is><t>Zyprazydonu, leku istotnie wydłużającego odstęp QT nie należy stosować:</t></is></c><c r="F831" s="2" t="inlineStr"><is><t>w hipokaliemii</t></is></c><c r="G831" s="2" t="inlineStr"><is><t>łącznie z moksyfloksacyną</t></is></c><c r="H831" s="2" t="inlineStr"><is><t>w objawowej bradykardii</t></is></c><c r="I831" s="2" t="inlineStr"><is><t>łącznie z amiodaronem</t></is></c><c r="J831" s="2" t="inlineStr" /><c r="K831" s="2" t="inlineStr" /><c r="L831" s="2" t="inlineStr" /><c r="M831" s="2" t="inlineStr" /><c r="N831" s="2" t="inlineStr" /><c r="O831" s="2" t="inlineStr" /><c r="P831" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2016/17 - 1 termin</t></is></c><c r="Q831" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="832"><c r="A832" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B832" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C832" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D832" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E832" s="2" t="inlineStr"><is><t>Zaburzenia pozapiramidowe mogą wystąpić w przebiegu stosowania:</t></is></c><c r="F832" s="2" t="inlineStr"><is><t>flunaryzyny</t></is></c><c r="G832" s="2" t="inlineStr"><is><t>metoklopramidu</t></is></c><c r="H832" s="2" t="inlineStr" /><c r="I832" s="2" t="inlineStr" /><c r="J832" s="2" t="inlineStr" /><c r="K832" s="2" t="inlineStr"><is><t>betahistyny</t></is></c><c r="L832" s="2" t="inlineStr"><is><t>rywastygminy</t></is></c><c r="M832" s="2" t="inlineStr" /><c r="N832" s="2" t="inlineStr" /><c r="O832" s="2" t="inlineStr" /><c r="P832" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2016/17 - 1 termin</t></is></c><c r="Q832" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="833"><c r="A833" s="2" t="inlineStr"><is><t>LEKI PRZECIWPSYCHOTYCZNE</t></is></c><c r="B833" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C833" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D833" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E833" s="2" t="inlineStr"><is><t>Parkinsonizm polekowy w przebiegu leczenia lekami przeciwpsychotycznymi wynika z:</t></is></c><c r="F833" s="2" t="inlineStr"><is><t>zmniejszania działania dopaminy w układzie nigrostriatalnym</t></is></c><c r="G833" s="2" t="inlineStr" /><c r="H833" s="2" t="inlineStr" /><c r="I833" s="2" t="inlineStr" /><c r="J833" s="2" t="inlineStr" /><c r="K833" s="2" t="inlineStr"><is><t>patogenezy schizofrenii</t></is></c><c r="L833" s="2" t="inlineStr"><is><t>zmniejszania działania dopaminy w obszarze mezokortykalnym</t></is></c><c r="M833" s="2" t="inlineStr"><is><t>blokowania receptorów muskarynowych</t></is></c><c r="N833" s="2" t="inlineStr" /><c r="O833" s="2" t="inlineStr" /><c r="P833" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2016/17 - 1 termin</t></is></c><c r="Q833" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="834"><c r="A834" s="2" t="inlineStr"><is><t>PADACZKA</t></is></c><c r="B834" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C834" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D834" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E834" s="2" t="inlineStr"><is><t>Napływ sodu do komórki hamuje:</t></is></c><c r="F834" s="2" t="inlineStr"><is><t>ranolzyna</t></is></c><c r="G834" s="2" t="inlineStr"><is><t>iwabradyna</t></is></c><c r="H834" s="2" t="inlineStr"><is><t>okskarbamazepina</t></is></c><c r="I834" s="2" t="inlineStr" /><c r="J834" s="2" t="inlineStr" /><c r="K834" s="2" t="inlineStr"><is><t>gabapentyna</t></is></c><c r="L834" s="2" t="inlineStr" /><c r="M834" s="2" t="inlineStr" /><c r="N834" s="2" t="inlineStr" /><c r="O834" s="2" t="inlineStr" /><c r="P834" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2016/17 - 1 termin</t></is></c><c r="Q834" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="835"><c r="A835" s="2" t="inlineStr"><is><t>OTĘPIENIE</t></is></c><c r="B835" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C835" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D835" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E835" s="2" t="inlineStr"><is><t>W ramach badania geriatrycznego u 80-letniej kobiety ze średnim wykształceniem wynik MMSE = 25 pkt. Za niezgodne z aktualną wiedzą medyczną uznasz zastosowanie u niej:</t></is></c><c r="F835" s="2" t="inlineStr"><is><t>piracetamu</t></is></c><c r="G835" s="2" t="inlineStr"><is><t>winpocetyny</t></is></c><c r="H835" s="2" t="inlineStr"><is><t>suplementacji cynku</t></is></c><c r="I835" s="2" t="inlineStr" /><c r="J835" s="2" t="inlineStr" /><c r="K835" s="2" t="inlineStr"><is><t>treningu mózgu (np. zgadnij co to za zawód: arlzek)</t></is></c><c r="L835" s="2" t="inlineStr" /><c r="M835" s="2" t="inlineStr" /><c r="N835" s="2" t="inlineStr" /><c r="O835" s="2" t="inlineStr" /><c r="P835" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2016/17 - 1 termin</t></is></c><c r="Q835" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="836"><c r="A836" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B836" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C836" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D836" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E836" s="2" t="inlineStr"><is><t>W zapobieganiu wymiotom w przebiegu chemioterapii należy zastosować:</t></is></c><c r="F836" s="2" t="inlineStr"><is><t>aprepitant</t></is></c><c r="G836" s="2" t="inlineStr"><is><t>ondansetron</t></is></c><c r="H836" s="2" t="inlineStr" /><c r="I836" s="2" t="inlineStr" /><c r="J836" s="2" t="inlineStr" /><c r="K836" s="2" t="inlineStr"><is><t>skopolaminę</t></is></c><c r="L836" s="2" t="inlineStr"><is><t>dimenhydrinat</t></is></c><c r="M836" s="2" t="inlineStr" /><c r="N836" s="2" t="inlineStr" /><c r="O836" s="2" t="inlineStr" /><c r="P836" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2016/17 - 1 termin</t></is></c><c r="Q836" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="837"><c r="A837" s="2" t="inlineStr"><is><t>HORMONY PŁCIOWE</t></is></c><c r="B837" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C837" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D837" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E837" s="2" t="inlineStr"><is><t>Wg Światowej Agencji Antydopingowej (WADA) za doping uważa się:</t></is></c><c r="F837" s="2" t="inlineStr"><is><t>użycie przez sportowców czynników stymulujących erytropoezę</t></is></c><c r="G837" s="2" t="inlineStr"><is><t>podanie sportowcowi autopreparatu krwinek czerwonych</t></is></c><c r="H837" s="2" t="inlineStr"><is><t>obecność we krwi sportowca egzogennych substancji o działaniu agonistycznym w stosunku do receptorów androgenowych i dla IGF-1</t></is></c><c r="I837" s="2" t="inlineStr"><is><t>podanie sportowcowi polimerów kwasów nukleinowych lub analogów kwasu nukleinowego</t></is></c><c r="J837" s="2" t="inlineStr" /><c r="K837" s="2" t="inlineStr" /><c r="L837" s="2" t="inlineStr" /><c r="M837" s="2" t="inlineStr" /><c r="N837" s="2" t="inlineStr" /><c r="O837" s="2" t="inlineStr" /><c r="P837" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2016/17 - 1 termin</t></is></c><c r="Q837" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="838"><c r="A838" s="2" t="inlineStr"><is><t>UKŁAD ODDECHOWY</t></is></c><c r="B838" s="2" t="inlineStr"><is><t>Antidotum</t></is></c><c r="C838" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D838" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E838" s="2" t="inlineStr"><is><t>U chorego z zaburzeniami świadomości, sennością, zaburzeniami równowagi, mowy, widzenia, omamy, pobudzeniem psychoruchowym, drgawkami, hipotonia z nieutrwalonymi częstoskurczami komorowymi będziesz podejrzewał zatrucie i podasz:</t></is></c><c r="F838" s="2" t="inlineStr"><is><t>imipraminą - fizostygminę</t></is></c><c r="G838" s="2" t="inlineStr" /><c r="H838" s="2" t="inlineStr" /><c r="I838" s="2" t="inlineStr" /><c r="J838" s="2" t="inlineStr" /><c r="K838" s="2" t="inlineStr"><is><t>paracetamolem- N-acetylocysteinę</t></is></c><c r="L838" s="2" t="inlineStr"><is><t>kodeiną - naltrekson</t></is></c><c r="M838" s="2" t="inlineStr"><is><t>litem - fizostygminę</t></is></c><c r="N838" s="2" t="inlineStr" /><c r="O838" s="2" t="inlineStr" /><c r="P838" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2016/17 - 1 termin</t></is></c><c r="Q838" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="839"><c r="A839" s="2" t="inlineStr"><is><t>LEKI PRZECIWHISTAMINOWE</t></is></c><c r="B839" s="2" t="inlineStr"><is><t>Sposób podania</t></is></c><c r="C839" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D839" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E839" s="2" t="inlineStr"><is><t>Klemastyna:</t></is></c><c r="F839" s="2" t="inlineStr"><is><t>może być podawana dożylnie</t></is></c><c r="G839" s="2" t="inlineStr"><is><t>powoduje senność i zaburzenia koordynacji ruchów</t></is></c><c r="H839" s="2" t="inlineStr" /><c r="I839" s="2" t="inlineStr" /><c r="J839" s="2" t="inlineStr" /><c r="K839" s="2" t="inlineStr"><is><t>jest selektywnym długodziałającym antagonistą receptorów histaminowych H1</t></is></c><c r="L839" s="2" t="inlineStr"><is><t>jest stosowana doustnie jako lek z wyboru w leczeniu przewlekłym alergii sezonowych</t></is></c><c r="M839" s="2" t="inlineStr" /><c r="N839" s="2" t="inlineStr" /><c r="O839" s="2" t="inlineStr" /><c r="P839" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2016/17 - 1 termin</t></is></c><c r="Q839" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="840"><c r="A840" s="2" t="inlineStr"><is><t>STANY NAGŁE</t></is></c><c r="B840" s="2" t="inlineStr"><is><t>Antidotum</t></is></c><c r="C840" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D840" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E840" s="2" t="inlineStr"><is><t>Wskaż prawdziwe stwierdzenie dotyczące przedawkowania leków znieczulenia miejscowego:</t></is></c><c r="F840" s="2" t="inlineStr"><is><t>Powodują drgawki, bradykardię i hipotonię</t></is></c><c r="G840" s="2" t="inlineStr"><is><t>Parestezje (drętwienie) języka i ust są wczesnym charakterystycznym objawem zwiastunowym</t></is></c><c r="H840" s="2" t="inlineStr"><is><t>W resuscytacji krążeniowo oddechowej, oprócz typowego algorytmu, stosuje się wlew emulsji tłuszczowej</t></is></c><c r="I840" s="2" t="inlineStr"><is><t>Na wystąpienie objawów nie ma wpływu miejscu wstrzyknięcia leku, a jedynie jego dawka</t></is></c><c r="J840" s="2" t="inlineStr" /><c r="K840" s="2" t="inlineStr" /><c r="L840" s="2" t="inlineStr" /><c r="M840" s="2" t="inlineStr" /><c r="N840" s="2" t="inlineStr" /><c r="O840" s="2" t="inlineStr" /><c r="P840" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2016/17 - 2 termin</t></is></c><c r="Q840" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="841"><c r="A841" s="2" t="inlineStr"><is><t>LEKI MOCZOPĘDNE</t></is></c><c r="B841" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C841" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D841" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E841" s="2" t="inlineStr"><is><t>Do leczenia ostrego zamknięcia kąta przesączania (potocznie ataku jaskry) można zastosować:</t></is></c><c r="F841" s="2" t="inlineStr"><is><t>Timolol</t></is></c><c r="G841" s="2" t="inlineStr"><is><t>Acetazolamid</t></is></c><c r="H841" s="2" t="inlineStr"><is><t>Mannitol</t></is></c><c r="I841" s="2" t="inlineStr" /><c r="J841" s="2" t="inlineStr" /><c r="K841" s="2" t="inlineStr"><is><t>Zydowudynę</t></is></c><c r="L841" s="2" t="inlineStr" /><c r="M841" s="2" t="inlineStr" /><c r="N841" s="2" t="inlineStr" /><c r="O841" s="2" t="inlineStr" /><c r="P841" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2016/17 - 2 termin</t></is></c><c r="Q841" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="842"><c r="A842" s="2" t="inlineStr"><is><t>LEKI PRZECIWHISTAMINOWE</t></is></c><c r="B842" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C842" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D842" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E842" s="2" t="inlineStr"><is><t>Do leków przeciwhistaminowych stosowanych wyłącznie miejscowo na błony śluzowe należą:</t></is></c><c r="F842" s="2" t="inlineStr"><is><t>Emedastyna</t></is></c><c r="G842" s="2" t="inlineStr"><is><t>Azelastyna</t></is></c><c r="H842" s="2" t="inlineStr" /><c r="I842" s="2" t="inlineStr" /><c r="J842" s="2" t="inlineStr" /><c r="K842" s="2" t="inlineStr"><is><t>Desforatadyna</t></is></c><c r="L842" s="2" t="inlineStr"><is><t>Bilastyna</t></is></c><c r="M842" s="2" t="inlineStr" /><c r="N842" s="2" t="inlineStr" /><c r="O842" s="2" t="inlineStr" /><c r="P842" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2016/17 - 2 termin</t></is></c><c r="Q842" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="843"><c r="A843" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B843" s="2" t="inlineStr"><is><t>Antidotum</t></is></c><c r="C843" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D843" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E843" s="2" t="inlineStr"><is><t>Dorosły pacjent trafił do szpitala 3 godziny po samobójczym przedawkowaniu fenobarbitalu (pochodna kwasu barbiturowego). Należy zastosować:</t></is></c><c r="F843" s="2" t="inlineStr"><is><t>Rozcienczenie trucizny przez podanie do wypicia dużej ilości wody pitnej</t></is></c><c r="G843" s="2" t="inlineStr"><is><t>Alkalizację moczu do pH co najmniej 7,5 przez dodanie wodorowęglanu sodu do dożylnych płynów infuzyjnych</t></is></c><c r="H843" s="2" t="inlineStr" /><c r="I843" s="2" t="inlineStr" /><c r="J843" s="2" t="inlineStr" /><c r="K843" s="2" t="inlineStr"><is><t>Płukanie żołądka z zastosowaniem wody pitnej przez sondę ustno-żołądkową w małych porcjach jedna po drugiej</t></is></c><c r="L843" s="2" t="inlineStr"><is><t>Irygację całego jelita przez doustne podanie płynów elektrolitowych z polietylenoglikolem (tzw. makrogolami)</t></is></c><c r="M843" s="2" t="inlineStr" /><c r="N843" s="2" t="inlineStr" /><c r="O843" s="2" t="inlineStr" /><c r="P843" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2016/17 - 2 termin</t></is></c><c r="Q843" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="844"><c r="A844" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B844" s="2" t="inlineStr"><is><t>Antidotum</t></is></c><c r="C844" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D844" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E844" s="2" t="inlineStr"><is><t>Wskaż prawidłowe połączenie trucizna – antidotum – mechanizm działania antidotum:</t></is></c><c r="F844" s="2" t="inlineStr"><is><t>Paracetamol – acetylocysteina – neutralizacja metaboliczna</t></is></c><c r="G844" s="2" t="inlineStr"><is><t>Amitryptylina - fizostygmina - antagonizm fizjologiczny</t></is></c><c r="H844" s="2" t="inlineStr"><is><t>Dabigatran – idarucyzumab - neutralizujące przeciwciało</t></is></c><c r="I844" s="2" t="inlineStr"><is><t>Diazepam – flomazenil – antagonizm receptorowy</t></is></c><c r="J844" s="2" t="inlineStr" /><c r="K844" s="2" t="inlineStr" /><c r="L844" s="2" t="inlineStr" /><c r="M844" s="2" t="inlineStr" /><c r="N844" s="2" t="inlineStr" /><c r="O844" s="2" t="inlineStr" /><c r="P844" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2016/17 - 2 termin</t></is></c><c r="Q844" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="845"><c r="A845" s="2" t="inlineStr"><is><t>PADACZKA</t></is></c><c r="B845" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C845" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D845" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E845" s="2" t="inlineStr"><is><t>Który z leków działa przeciwdrgawkowo głównie poprzez nasilenie transmisji GABA￾ergicznej:</t></is></c><c r="F845" s="2" t="inlineStr"><is><t>Tiagabina</t></is></c><c r="G845" s="2" t="inlineStr" /><c r="H845" s="2" t="inlineStr" /><c r="I845" s="2" t="inlineStr" /><c r="J845" s="2" t="inlineStr" /><c r="K845" s="2" t="inlineStr"><is><t>Lamotrygina</t></is></c><c r="L845" s="2" t="inlineStr"><is><t>Lewetriacetam</t></is></c><c r="M845" s="2" t="inlineStr"><is><t>Zonisamid</t></is></c><c r="N845" s="2" t="inlineStr" /><c r="O845" s="2" t="inlineStr" /><c r="P845" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2016/17 - 2 termin</t></is></c><c r="Q845" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="846"><c r="A846" s="2" t="inlineStr"><is><t>OTĘPIENIE</t></is></c><c r="B846" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C846" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D846" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E846" s="2" t="inlineStr"><is><t>Które leki mogą zaostrzyć objawy otępienia u osoby z chorobą Alzheimera?</t></is></c><c r="F846" s="2" t="inlineStr"><is><t>Olanzapina</t></is></c><c r="G846" s="2" t="inlineStr"><is><t>Memantyna</t></is></c><c r="H846" s="2" t="inlineStr"><is><t>Biperiden</t></is></c><c r="I846" s="2" t="inlineStr" /><c r="J846" s="2" t="inlineStr" /><c r="K846" s="2" t="inlineStr"><is><t>Piracetam</t></is></c><c r="L846" s="2" t="inlineStr" /><c r="M846" s="2" t="inlineStr" /><c r="N846" s="2" t="inlineStr" /><c r="O846" s="2" t="inlineStr" /><c r="P846" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2016/17 - 2 termin</t></is></c><c r="Q846" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="847"><c r="A847" s="2" t="inlineStr"><is><t>CHOROBA PARKINSONA</t></is></c><c r="B847" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C847" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D847" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E847" s="2" t="inlineStr"><is><t>Skłonność do hazardu, kompulsywne objadanie i obsesje seksualne to działania niepożądane obserwowane w terapii:</t></is></c><c r="F847" s="2" t="inlineStr"><is><t>L-dopą</t></is></c><c r="G847" s="2" t="inlineStr"><is><t>Pramipeksolem</t></is></c><c r="H847" s="2" t="inlineStr" /><c r="I847" s="2" t="inlineStr" /><c r="J847" s="2" t="inlineStr" /><c r="K847" s="2" t="inlineStr"><is><t>Metylofenidatem</t></is></c><c r="L847" s="2" t="inlineStr"><is><t>Zolpidemem</t></is></c><c r="M847" s="2" t="inlineStr" /><c r="N847" s="2" t="inlineStr" /><c r="O847" s="2" t="inlineStr" /><c r="P847" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2016/17 - 2 termin</t></is></c><c r="Q847" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="848"><c r="A848" s="2" t="inlineStr"><is><t>LEKI PRZECIWNOWOTWOROWE</t></is></c><c r="B848" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C848" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D848" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E848" s="2" t="inlineStr"><is><t>Zolendronian:</t></is></c><c r="F848" s="2" t="inlineStr"><is><t>Z dużym powinowactwem wiąże się ze zmineralizowaną kością</t></is></c><c r="G848" s="2" t="inlineStr"><is><t>Hamuje resorbcję kości</t></is></c><c r="H848" s="2" t="inlineStr" /><c r="I848" s="2" t="inlineStr" /><c r="J848" s="2" t="inlineStr" /><c r="K848" s="2" t="inlineStr"><is><t>Koryguje hiperkalcemię w chorobach nowotworowych zwiększając jednoczeście kalcurię</t></is></c><c r="L848" s="2" t="inlineStr"><is><t>Może spowodować martwicę szczęki szczególnie w przypadku złego stanu uzębienia</t></is></c><c r="M848" s="2" t="inlineStr" /><c r="N848" s="2" t="inlineStr" /><c r="O848" s="2" t="inlineStr" /><c r="P848" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2016/17 - 2 termin</t></is></c><c r="Q848" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="849"><c r="A849" s="2" t="inlineStr"><is><t>LEKI IMMUNOSUPRESYJNE</t></is></c><c r="B849" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C849" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D849" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E849" s="2" t="inlineStr"><is><t>Leki stosowane przewlekle w stwardnieniu rozsianym w celu modyfikacji przebiegu choroby to:</t></is></c><c r="F849" s="2" t="inlineStr"><is><t>PEG-interferon-beta</t></is></c><c r="G849" s="2" t="inlineStr"><is><t>Natalizumab</t></is></c><c r="H849" s="2" t="inlineStr"><is><t>Adalimumab</t></is></c><c r="I849" s="2" t="inlineStr" /><c r="J849" s="2" t="inlineStr" /><c r="K849" s="2" t="inlineStr"><is><t>Interferon-gamma</t></is></c><c r="L849" s="2" t="inlineStr" /><c r="M849" s="2" t="inlineStr" /><c r="N849" s="2" t="inlineStr" /><c r="O849" s="2" t="inlineStr" /><c r="P849" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2016/17 - 2 termin</t></is></c><c r="Q849" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="850"><c r="A850" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B850" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C850" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D850" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E850" s="2" t="inlineStr"><is><t>Który mechanizm opisuje działanie aprepitantu:</t></is></c><c r="F850" s="2" t="inlineStr"><is><t>Stymulowanie receptora neurokininy (NK1) w strefie chemoreceptorowej mózgu</t></is></c><c r="G850" s="2" t="inlineStr" /><c r="H850" s="2" t="inlineStr" /><c r="I850" s="2" t="inlineStr" /><c r="J850" s="2" t="inlineStr" /><c r="K850" s="2" t="inlineStr"><is><t>Stymulowanie receptora O2 w strefie chemoreceptorowej mózgu</t></is></c><c r="L850" s="2" t="inlineStr"><is><t>Stymulowanie receptora 5-HT3 na włóknach aferentnych nerwu błędnego</t></is></c><c r="M850" s="2" t="inlineStr"><is><t>Blokowanie receptora muskarynowego w ośrodku wymiotnym w rdzeniu przedłużonym</t></is></c><c r="N850" s="2" t="inlineStr" /><c r="O850" s="2" t="inlineStr" /><c r="P850" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2016/17 - 2 termin</t></is></c><c r="Q850" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="851"><c r="A851" s="2" t="inlineStr"><is><t>LEKI PRZECIWDEPRESYJNE</t></is></c><c r="B851" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C851" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D851" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E851" s="2" t="inlineStr"><is><t>Amitryptylina ma zastosowanie w leczeniu:</t></is></c><c r="F851" s="2" t="inlineStr"><is><t>Bólu neuropatycznego</t></is></c><c r="G851" s="2" t="inlineStr"><is><t>Choroby afektywnej jednobiegunowej</t></is></c><c r="H851" s="2" t="inlineStr" /><c r="I851" s="2" t="inlineStr" /><c r="J851" s="2" t="inlineStr" /><c r="K851" s="2" t="inlineStr"><is><t>Bezsenności</t></is></c><c r="L851" s="2" t="inlineStr"><is><t>Padaczki</t></is></c><c r="M851" s="2" t="inlineStr" /><c r="N851" s="2" t="inlineStr" /><c r="O851" s="2" t="inlineStr" /><c r="P851" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2016/17 - 2 termin</t></is></c><c r="Q851" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="852"><c r="A852" s="2" t="inlineStr"><is><t>LEKI PRZECIWDEPRESYJNE</t></is></c><c r="B852" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C852" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D852" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E852" s="2" t="inlineStr"><is><t>Zespół serotoninowy może być wynikiem podawania:</t></is></c><c r="F852" s="2" t="inlineStr"><is><t>Tramadolu</t></is></c><c r="G852" s="2" t="inlineStr"><is><t>Escitalopramu</t></is></c><c r="H852" s="2" t="inlineStr" /><c r="I852" s="2" t="inlineStr" /><c r="J852" s="2" t="inlineStr" /><c r="K852" s="2" t="inlineStr"><is><t>Litu</t></is></c><c r="L852" s="2" t="inlineStr"><is><t>Buspironu</t></is></c><c r="M852" s="2" t="inlineStr" /><c r="N852" s="2" t="inlineStr" /><c r="O852" s="2" t="inlineStr" /><c r="P852" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2016/17 - 2 termin</t></is></c><c r="Q852" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="853"><c r="A853" s="2" t="inlineStr"><is><t>LEKI PRZECIWLĘKOWE</t></is></c><c r="B853" s="2" t="inlineStr"><is><t>Farmakokinetyka</t></is></c><c r="C853" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D853" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E853" s="2" t="inlineStr"><is><t>Benzodiazepiną nie mającą wątrobowego metabolizmu jest:</t></is></c><c r="F853" s="2" t="inlineStr"><is><t>Lorazepam</t></is></c><c r="G853" s="2" t="inlineStr"><is><t>Oksazepam</t></is></c><c r="H853" s="2" t="inlineStr" /><c r="I853" s="2" t="inlineStr" /><c r="J853" s="2" t="inlineStr" /><c r="K853" s="2" t="inlineStr"><is><t>Nitrazepam</t></is></c><c r="L853" s="2" t="inlineStr"><is><t>Diazepam</t></is></c><c r="M853" s="2" t="inlineStr" /><c r="N853" s="2" t="inlineStr" /><c r="O853" s="2" t="inlineStr" /><c r="P853" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2016/17 - 2 termin</t></is></c><c r="Q853" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="854"><c r="A854" s="2" t="inlineStr"><is><t>UKŁAD ODDECHOWY</t></is></c><c r="B854" s="2" t="inlineStr"><is><t>Antidotum</t></is></c><c r="C854" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D854" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E854" s="2" t="inlineStr"><is><t>Acetylocysteina:</t></is></c><c r="F854" s="2" t="inlineStr"><is><t>Jest odtrutką w zatruciu paracetamolem ze względu na udział w detoksykacji toksycznego metabolitu N-acetylo-4-benzochinoiminy (NAPO)</t></is></c><c r="G854" s="2" t="inlineStr" /><c r="H854" s="2" t="inlineStr" /><c r="I854" s="2" t="inlineStr" /><c r="J854" s="2" t="inlineStr" /><c r="K854" s="2" t="inlineStr"><is><t>Może być stosowana doustnie, dożylnie i wziewnie</t></is></c><c r="L854" s="2" t="inlineStr"><is><t>W dużej dawce pobudza ruchomość rzęsek nabłonka oddechowego</t></is></c><c r="M854" s="2" t="inlineStr"><is><t>Rozrzedza śluz poprzez zmniejszenie oddziaływania ładunków elektrycznych występujących w sieci mucyn (działanie niedestrukcyjne)</t></is></c><c r="N854" s="2" t="inlineStr" /><c r="O854" s="2" t="inlineStr" /><c r="P854" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2016/17 - 2 termin</t></is></c><c r="Q854" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="855"><c r="A855" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B855" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C855" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D855" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E855" s="2" t="inlineStr"><is><t>Przewlekłe stosowanie pantoprazolu może prowadzić do:</t></is></c><c r="F855" s="2" t="inlineStr"><is><t>Zmniejszonego wchłaniania witaminy B12, Mg2+, Ca2+</t></is></c><c r="G855" s="2" t="inlineStr"><is><t>Zwiększonego ryzyka zakażenia przewodu pokarmowego, np. biegunka Clostridium difficile</t></is></c><c r="H855" s="2" t="inlineStr"><is><t>Zwiększonego ryzyka złamania kościu udowej</t></is></c><c r="I855" s="2" t="inlineStr" /><c r="J855" s="2" t="inlineStr" /><c r="K855" s="2" t="inlineStr"><is><t>Zwiększonego ryzyka zakażenia układu oddechowego</t></is></c><c r="L855" s="2" t="inlineStr" /><c r="M855" s="2" t="inlineStr" /><c r="N855" s="2" t="inlineStr" /><c r="O855" s="2" t="inlineStr" /><c r="P855" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2016/17 - 2 termin</t></is></c><c r="Q855" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="856"><c r="A856" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B856" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C856" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D856" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E856" s="2" t="inlineStr"><is><t>Wybierz prawidłowe połączenie - lek prokinetyczny / mechanizm działania:</t></is></c><c r="F856" s="2" t="inlineStr"><is><t>Erytromycyna - agonista rec. Motylinowego</t></is></c><c r="G856" s="2" t="inlineStr"><is><t>Cizapryd – agonista rec. 5-HT4</t></is></c><c r="H856" s="2" t="inlineStr" /><c r="I856" s="2" t="inlineStr" /><c r="J856" s="2" t="inlineStr" /><c r="K856" s="2" t="inlineStr"><is><t>Metoklopramid – agonista rec. 5-HT3 i rec. D2</t></is></c><c r="L856" s="2" t="inlineStr"><is><t>Itopryd – agonista rec. 5-HT4 i rec. D2</t></is></c><c r="M856" s="2" t="inlineStr" /><c r="N856" s="2" t="inlineStr" /><c r="O856" s="2" t="inlineStr" /><c r="P856" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2016/17 - 2 termin</t></is></c><c r="Q856" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="857"><c r="A857" s="2" t="inlineStr"><is><t>LEKI PRZECIWNOWOTWOROWE</t></is></c><c r="B857" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C857" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D857" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E857" s="2" t="inlineStr"><is><t>Kwerolimus jest stosowany w:</t></is></c><c r="F857" s="2" t="inlineStr"><is><t>Kardiologii (stenty wiecowe)</t></is></c><c r="G857" s="2" t="inlineStr"><is><t>Onkologii (wybrane zaawansowane nowotwory piersi i nerki)</t></is></c><c r="H857" s="2" t="inlineStr" /><c r="I857" s="2" t="inlineStr" /><c r="J857" s="2" t="inlineStr" /><c r="K857" s="2" t="inlineStr"><is><t>Neurologii (stwardnieni rozsiane)</t></is></c><c r="L857" s="2" t="inlineStr"><is><t>Dermatologii (łuszczyca)</t></is></c><c r="M857" s="2" t="inlineStr" /><c r="N857" s="2" t="inlineStr" /><c r="O857" s="2" t="inlineStr" /><c r="P857" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2016/17 - 2 termin</t></is></c><c r="Q857" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="858"><c r="A858" s="2" t="inlineStr"><is><t>LEKI IMMUNOSUPRESYJNE</t></is></c><c r="B858" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C858" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D858" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E858" s="2" t="inlineStr"><is><t>Mykofenolan mofetylu (MMF):</t></is></c><c r="F858" s="2" t="inlineStr"><is><t>Jest odwracalnym inhibitorem dehydrogenazy inozynomonofosforanu hamującym syntezę de novo nukleotydów guaninowych</t></is></c><c r="G858" s="2" t="inlineStr"><is><t>Działa silniej na limfocyty niż na inne komórki</t></is></c><c r="H858" s="2" t="inlineStr" /><c r="I858" s="2" t="inlineStr" /><c r="J858" s="2" t="inlineStr" /><c r="K858" s="2" t="inlineStr"><is><t>Bezpośrednio hamuje wytwarzanie interleukiny 2 (IL-2)</t></is></c><c r="L858" s="2" t="inlineStr"><is><t>Jest inhibitorem sygnału po pobudzeniu receptorów dla IL-2</t></is></c><c r="M858" s="2" t="inlineStr" /><c r="N858" s="2" t="inlineStr" /><c r="O858" s="2" t="inlineStr" /><c r="P858" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2016/17 - 2 termin</t></is></c><c r="Q858" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="859"><c r="A859" s="2" t="inlineStr"><is><t>ZABURZENIA RYTMU SERCA</t></is></c><c r="B859" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C859" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D859" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E859" s="2" t="inlineStr"><is><t>Adenozyna</t></is></c><c r="F859" s="2" t="inlineStr"><is><t>To nukleotyd purynowy występujący we wszystkich komórkach organizmu</t></is></c><c r="G859" s="2" t="inlineStr" /><c r="H859" s="2" t="inlineStr" /><c r="I859" s="2" t="inlineStr" /><c r="J859" s="2" t="inlineStr" /><c r="K859" s="2" t="inlineStr"><is><t>Aktywuje kanały potasowe i powoduje depolaryzację komórek</t></is></c><c r="L859" s="2" t="inlineStr"><is><t>Działa dromotropowo ujemnie w węźle przedsionkowo-komorowym</t></is></c><c r="M859" s="2" t="inlineStr"><is><t>Jest skuteczna kardiowersji farmakologicznej częstoskurczów komorowych</t></is></c><c r="N859" s="2" t="inlineStr" /><c r="O859" s="2" t="inlineStr" /><c r="P859" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2016/17 - 2 termin</t></is></c><c r="Q859" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="860"><c r="A860" s="2" t="inlineStr"><is><t>LEKI HIPOLIPEMIZUJĄCE</t></is></c><c r="B860" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C860" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D860" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E860" s="2" t="inlineStr"><is><t>Ewolokumab:</t></is></c><c r="F860" s="2" t="inlineStr"><is><t>Jest ludzkim przeciwciałem poliklonalnym</t></is></c><c r="G860" s="2" t="inlineStr"><is><t>Hamuje aktywność konwertazy białkowej subtylizyna/keksyna typu 9 (PCSK9) - enzymu biorącego udział w degradacji receptorów dla LDL</t></is></c><c r="H860" s="2" t="inlineStr" /><c r="I860" s="2" t="inlineStr" /><c r="J860" s="2" t="inlineStr" /><c r="K860" s="2" t="inlineStr"><is><t>Jest stosowany dożylnie</t></is></c><c r="L860" s="2" t="inlineStr"><is><t>Zwiększa stęężenie cholesterolu HDL o ponad 100%</t></is></c><c r="M860" s="2" t="inlineStr" /><c r="N860" s="2" t="inlineStr" /><c r="O860" s="2" t="inlineStr" /><c r="P860" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2016/17 - 2 termin</t></is></c><c r="Q860" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="861"><c r="A861" s="2" t="inlineStr"><is><t>UKŁAD WSPÓŁCZULNY</t></is></c><c r="B861" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C861" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D861" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E861" s="2" t="inlineStr"><is><t>Przyczyną wzrostu masy ciała może być:</t></is></c><c r="F861" s="2" t="inlineStr"><is><t>Klemastyny</t></is></c><c r="G861" s="2" t="inlineStr"><is><t>Kwetiapiny</t></is></c><c r="H861" s="2" t="inlineStr"><is><t>Citalopramu</t></is></c><c r="I861" s="2" t="inlineStr" /><c r="J861" s="2" t="inlineStr" /><c r="K861" s="2" t="inlineStr"><is><t>Liraglutydu</t></is></c><c r="L861" s="2" t="inlineStr" /><c r="M861" s="2" t="inlineStr" /><c r="N861" s="2" t="inlineStr" /><c r="O861" s="2" t="inlineStr" /><c r="P861" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2016/17 - 2 termin</t></is></c><c r="Q861" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="862"><c r="A862" s="2" t="inlineStr"><is><t>LEKI HIPOLIPEMIZUJĄCE</t></is></c><c r="B862" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C862" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D862" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E862" s="2" t="inlineStr"><is><t>Reguła Robertsa mówi o:</t></is></c><c r="F862" s="2" t="inlineStr"><is><t>Podwajaniu dawki statyny</t></is></c><c r="G862" s="2" t="inlineStr"><is><t>Obniżeniu stężenia cholesterolu LDL o dodatkowe 7% po odpowiednim zwiększeniu dawki statyny</t></is></c><c r="H862" s="2" t="inlineStr" /><c r="I862" s="2" t="inlineStr" /><c r="J862" s="2" t="inlineStr" /><c r="K862" s="2" t="inlineStr"><is><t>Obniżeniu stężenia cholesterolu LDL o dodatkowe 5% po odpowiednim zwiększeniu dawki statyny</t></is></c><c r="L862" s="2" t="inlineStr"><is><t>Potrajaniu dawki statyny</t></is></c><c r="M862" s="2" t="inlineStr" /><c r="N862" s="2" t="inlineStr" /><c r="O862" s="2" t="inlineStr" /><c r="P862" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2016/17 - 2 termin</t></is></c><c r="Q862" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="863"><c r="A863" s="2" t="inlineStr"><is><t>UKŁAD WSPÓŁCZULNY</t></is></c><c r="B863" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C863" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D863" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E863" s="2" t="inlineStr"><is><t>Wskaż prawidłowe połączenie lek – mechanizm działania:</t></is></c><c r="F863" s="2" t="inlineStr"><is><t>Roflumilast – inhibitor fosfodiestrazy 4</t></is></c><c r="G863" s="2" t="inlineStr" /><c r="H863" s="2" t="inlineStr" /><c r="I863" s="2" t="inlineStr" /><c r="J863" s="2" t="inlineStr" /><c r="K863" s="2" t="inlineStr"><is><t>Indakaterol – nieselektywny agonista receptorów beta-adrenergicznych</t></is></c><c r="L863" s="2" t="inlineStr"><is><t>Tiotropium - długodziałający gonista receptorów M3</t></is></c><c r="M863" s="2" t="inlineStr"><is><t>Omalizumab - przeciwciało monoklonalne przeciw ludzkim przeciwciałom klasy IgA</t></is></c><c r="N863" s="2" t="inlineStr" /><c r="O863" s="2" t="inlineStr" /><c r="P863" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2016/17 - 2 termin</t></is></c><c r="Q863" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="864"><c r="A864" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B864" s="2" t="inlineStr"><is><t>Przeciwwskazania</t></is></c><c r="C864" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D864" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E864" s="2" t="inlineStr"><is><t>Wskaż prawdziwe stwierdzenie dotyczące małopłytkowości indukowanej heparyną (HIT) typu II:</t></is></c><c r="F864" s="2" t="inlineStr"><is><t>Występuje typowo między 5. a 10. dniem ekspozycji na heparyny ze znacznym nadmiarem liczby płytek (30 000-50 000/mikrolitr)</t></is></c><c r="G864" s="2" t="inlineStr"><is><t>Stwarza istotne ryzyko powikła zakrzepowo-zatorowych</t></is></c><c r="H864" s="2" t="inlineStr"><is><t>Jest potwierdzana identyfikacją przeciwciał przeciw kompleksom heparyna-PF4 w surowicy</t></is></c><c r="I864" s="2" t="inlineStr"><is><t>Jest bezterminowym przeciwwskazaniem do reekspozycji chorego na heparyny</t></is></c><c r="J864" s="2" t="inlineStr" /><c r="K864" s="2" t="inlineStr" /><c r="L864" s="2" t="inlineStr" /><c r="M864" s="2" t="inlineStr" /><c r="N864" s="2" t="inlineStr" /><c r="O864" s="2" t="inlineStr" /><c r="P864" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2016/17 - 2 termin</t></is></c><c r="Q864" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="865"><c r="A865" s="2" t="inlineStr"><is><t>NIEWYDOLNOŚĆ SERCA</t></is></c><c r="B865" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C865" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D865" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E865" s="2" t="inlineStr"><is><t>Wskaż prawidłowe połączenie lek – mechanizm działania:</t></is></c><c r="F865" s="2" t="inlineStr"><is><t>Iwabradyna – zahamowanie prądu potasowego w węźle przedsionkowo￾komorowym</t></is></c><c r="G865" s="2" t="inlineStr"><is><t>Sakubitril – zahamowanie aktywności neprylizyny</t></is></c><c r="H865" s="2" t="inlineStr"><is><t>Riociguat – aktywacja cyklazy adenylowej</t></is></c><c r="I865" s="2" t="inlineStr"><is><t>Digoksyna – aktywacja wymiennika sodowo-wapniowego</t></is></c><c r="J865" s="2" t="inlineStr" /><c r="K865" s="2" t="inlineStr" /><c r="L865" s="2" t="inlineStr" /><c r="M865" s="2" t="inlineStr" /><c r="N865" s="2" t="inlineStr" /><c r="O865" s="2" t="inlineStr" /><c r="P865" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2016/17 - 2 termin</t></is></c><c r="Q865" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="866"><c r="A866" s="2" t="inlineStr"><is><t>NADCIŚNIENIE TĘTNICZE</t></is></c><c r="B866" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C866" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D866" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E866" s="2" t="inlineStr"><is><t>Do leków hamujących układ RAA należy:</t></is></c><c r="F866" s="2" t="inlineStr"><is><t>Zofenopryl</t></is></c><c r="G866" s="2" t="inlineStr"><is><t>Eplerenon</t></is></c><c r="H866" s="2" t="inlineStr" /><c r="I866" s="2" t="inlineStr" /><c r="J866" s="2" t="inlineStr" /><c r="K866" s="2" t="inlineStr"><is><t>Aliskiren</t></is></c><c r="L866" s="2" t="inlineStr"><is><t>Nebiwolol</t></is></c><c r="M866" s="2" t="inlineStr" /><c r="N866" s="2" t="inlineStr" /><c r="O866" s="2" t="inlineStr" /><c r="P866" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2016/17 - 2 termin</t></is></c><c r="Q866" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="867"><c r="A867" s="2" t="inlineStr"><is><t>LEKI MOCZOPĘDNE</t></is></c><c r="B867" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C867" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D867" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E867" s="2" t="inlineStr"><is><t>Wskaż prawidłowe stwierdzenie dotyczące torasemidu:</t></is></c><c r="F867" s="2" t="inlineStr"><is><t>Hamuje symporter sodowo-potasowo-chlorkowy części grubościennej ramienia wstępującego pętli Henlego</t></is></c><c r="G867" s="2" t="inlineStr"><is><t>Zwiększa aktywność reninową osocza</t></is></c><c r="H867" s="2" t="inlineStr" /><c r="I867" s="2" t="inlineStr" /><c r="J867" s="2" t="inlineStr" /><c r="K867" s="2" t="inlineStr"><is><t>Powoduje słabszy efekt natiuretyczny niż furosemid</t></is></c><c r="L867" s="2" t="inlineStr"><is><t>Jest nieskuteczny jeśli eGFR (wskaźnik filtracji kłębuszkowej) &lt; 30 ml/min</t></is></c><c r="M867" s="2" t="inlineStr" /><c r="N867" s="2" t="inlineStr" /><c r="O867" s="2" t="inlineStr" /><c r="P867" s="2" t="inlineStr"><is><t>KOLOKWIUM 3 – 2016/17 - 2 termin</t></is></c><c r="Q867" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="868"><c r="A868" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B868" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C868" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D868" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E868" s="2" t="inlineStr"><is><t>W zakażeniach Mycoplasama pneumoniae można zastosować</t></is></c><c r="F868" s="2" t="inlineStr"><is><t>Doksycykline</t></is></c><c r="G868" s="2" t="inlineStr"><is><t>Klarytromycyne</t></is></c><c r="H868" s="2" t="inlineStr" /><c r="I868" s="2" t="inlineStr" /><c r="J868" s="2" t="inlineStr" /><c r="K868" s="2" t="inlineStr"><is><t>Amoksycyline</t></is></c><c r="L868" s="2" t="inlineStr"><is><t>Ceftriakson + linezoild , chloramfenikol, makrolidy wgl, tetracyklina, tygecyklina, chinolony 2 gen : cyproflokascyna ofloksacyna pflokascyna norfloksacyna</t></is></c><c r="M868" s="2" t="inlineStr" /><c r="N868" s="2" t="inlineStr" /><c r="O868" s="2" t="inlineStr" /><c r="P868" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2015/16 - 2 termin</t></is></c><c r="Q868" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="869"><c r="A869" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B869" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C869" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D869" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E869" s="2" t="inlineStr"><is><t>W zakazeniu Clostridium diff. skuteczne sa:</t></is></c><c r="F869" s="2" t="inlineStr"><is><t>Metronidazol</t></is></c><c r="G869" s="2" t="inlineStr"><is><t>Wankomycyna</t></is></c><c r="H869" s="2" t="inlineStr" /><c r="I869" s="2" t="inlineStr" /><c r="J869" s="2" t="inlineStr" /><c r="K869" s="2" t="inlineStr"><is><t>Amoksycylina</t></is></c><c r="L869" s="2" t="inlineStr"><is><t>Klindamycyna Fidaksomycyna tygecyklina (off label) ryfaksymina</t></is></c><c r="M869" s="2" t="inlineStr" /><c r="N869" s="2" t="inlineStr" /><c r="O869" s="2" t="inlineStr" /><c r="P869" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2015/16 - 2 termin</t></is></c><c r="Q869" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="870"><c r="A870" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B870" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C870" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D870" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E870" s="2" t="inlineStr"><is><t>Do leków i rzutu w gruźlicy należy</t></is></c><c r="F870" s="2" t="inlineStr"><is><t>Ryfampicyna</t></is></c><c r="G870" s="2" t="inlineStr"><is><t>Izoniazyd</t></is></c><c r="H870" s="2" t="inlineStr"><is><t>Pyryzynamid streptomycyna etambutol</t></is></c><c r="I870" s="2" t="inlineStr" /><c r="J870" s="2" t="inlineStr" /><c r="K870" s="2" t="inlineStr"><is><t>Kanamycna</t></is></c><c r="L870" s="2" t="inlineStr" /><c r="M870" s="2" t="inlineStr" /><c r="N870" s="2" t="inlineStr" /><c r="O870" s="2" t="inlineStr" /><c r="P870" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2015/16 - 2 termin</t></is></c><c r="Q870" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="871"><c r="A871" s="2" t="inlineStr"><is><t>NARKOTYCZNE LEKI PRZECIWBÓLOWE</t></is></c><c r="B871" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C871" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D871" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E871" s="2" t="inlineStr"><is><t>Efekt pułapowy wykazuje</t></is></c><c r="F871" s="2" t="inlineStr"><is><t>Buprenorfina pentazoccyna</t></is></c><c r="G871" s="2" t="inlineStr" /><c r="H871" s="2" t="inlineStr" /><c r="I871" s="2" t="inlineStr" /><c r="J871" s="2" t="inlineStr" /><c r="K871" s="2" t="inlineStr"><is><t>Morfina</t></is></c><c r="L871" s="2" t="inlineStr"><is><t>Kodeina</t></is></c><c r="M871" s="2" t="inlineStr"><is><t>Metadon</t></is></c><c r="N871" s="2" t="inlineStr" /><c r="O871" s="2" t="inlineStr" /><c r="P871" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2015/16 - 2 termin</t></is></c><c r="Q871" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="872"><c r="A872" s="2" t="inlineStr"><is><t>HORMONY PŁCIOWE</t></is></c><c r="B872" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C872" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D872" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E872" s="2" t="inlineStr"><is><t>Hiperprolaktynemia</t></is></c><c r="F872" s="2" t="inlineStr"><is><t>Karbegolina</t></is></c><c r="G872" s="2" t="inlineStr"><is><t>Bromokryptyna hinagolid</t></is></c><c r="H872" s="2" t="inlineStr" /><c r="I872" s="2" t="inlineStr" /><c r="J872" s="2" t="inlineStr" /><c r="K872" s="2" t="inlineStr"><is><t>Gorserelina</t></is></c><c r="L872" s="2" t="inlineStr"><is><t>Finasteryd</t></is></c><c r="M872" s="2" t="inlineStr" /><c r="N872" s="2" t="inlineStr" /><c r="O872" s="2" t="inlineStr" /><c r="P872" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2015/16 - 2 termin</t></is></c><c r="Q872" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="873"><c r="A873" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B873" s="2" t="inlineStr"><is><t>Interakcje</t></is></c><c r="C873" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D873" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E873" s="2" t="inlineStr"><is><t>Azytromycyna: makrolid, aktywny wobec h.influenzae, bakterie atypowe, leczenie boreliozy</t></is></c><c r="F873" s="2" t="inlineStr"><is><t>jest stosowana w nierzeżączkowym zapaleniu cewki moczowej</t></is></c><c r="G873" s="2" t="inlineStr" /><c r="H873" s="2" t="inlineStr" /><c r="I873" s="2" t="inlineStr" /><c r="J873" s="2" t="inlineStr" /><c r="K873" s="2" t="inlineStr"><is><t>jest słabo wchłaniana z przewodu pokarmowego</t></is></c><c r="L873" s="2" t="inlineStr"><is><t>ma bardzo krótki okres półtrwania → długi okres półtrwania (50-60h)</t></is></c><c r="M873" s="2" t="inlineStr"><is><t>istotnie klinicznie hamuje aktywność izoenzymu CYP3A4 → nie daje interakcji</t></is></c><c r="N873" s="2" t="inlineStr" /><c r="O873" s="2" t="inlineStr" /><c r="P873" s="2" t="inlineStr"><is><t>EGZAMIN IWL 1 lutego 2016</t></is></c><c r="Q873" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="874"><c r="A874" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B874" s="2" t="inlineStr"><is><t>Sposób podania</t></is></c><c r="C874" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D874" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E874" s="2" t="inlineStr"><is><t>Ceftriakson:</t></is></c><c r="F874" s="2" t="inlineStr"><is><t>należy do cefalosporyn III generacji</t></is></c><c r="G874" s="2" t="inlineStr"><is><t>może być podawany dożylnie</t></is></c><c r="H874" s="2" t="inlineStr"><is><t>nie wykazuje aktywności wobec Borrelia burgdorferi</t></is></c><c r="I874" s="2" t="inlineStr" /><c r="J874" s="2" t="inlineStr" /><c r="K874" s="2" t="inlineStr"><is><t>wykazuje aktywność wobec MRSA</t></is></c><c r="L874" s="2" t="inlineStr"><is><t>stosowany w zakażeniach OUN</t></is></c><c r="M874" s="2" t="inlineStr" /><c r="N874" s="2" t="inlineStr" /><c r="O874" s="2" t="inlineStr" /><c r="P874" s="2" t="inlineStr"><is><t>EGZAMIN IWL 1 lutego 2016</t></is></c><c r="Q874" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="875"><c r="A875" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B875" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C875" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D875" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E875" s="2" t="inlineStr"><is><t>Pseudomonas aeruginosa jest wrażliwy na działanie:</t></is></c><c r="F875" s="2" t="inlineStr"><is><t>kolistyny</t></is></c><c r="G875" s="2" t="inlineStr"><is><t>tobramycyny</t></is></c><c r="H875" s="2" t="inlineStr" /><c r="I875" s="2" t="inlineStr" /><c r="J875" s="2" t="inlineStr" /><c r="K875" s="2" t="inlineStr"><is><t>telawancyny</t></is></c><c r="L875" s="2" t="inlineStr"><is><t>cefazoliny</t></is></c><c r="M875" s="2" t="inlineStr"><is><t>pipercylina, cefalosporyny IIIb: ceftazym, cefoperazon, IV generacji: cefepim, V generacja: ceftarolina, ceftobiprol, caftalozan/tazobaktam, , aztreonam, aminoglikozydy (tobramycyna) chinolony od II gen. , gramicydyna</t></is></c><c r="N875" s="2" t="inlineStr" /><c r="O875" s="2" t="inlineStr" /><c r="P875" s="2" t="inlineStr"><is><t>EGZAMIN IWL 1 lutego 2016</t></is></c><c r="Q875" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="876"><c r="A876" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B876" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C876" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D876" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E876" s="2" t="inlineStr"><is><t>W terapii empirycznej bakteryjnego zapalenia opon mózgowo-rdzeniowych u osób dorosłych zalecane są:</t></is></c><c r="F876" s="2" t="inlineStr"><is><t>cefotaksym z wankomycyną</t></is></c><c r="G876" s="2" t="inlineStr"><is><t>ceftriakson z wankomycyną ewentualnie + ampicylina a – prawdziwe odpowiedzi 1, 3 i 4 b – prawdziwe odpowiedzi 1 i 3 c – prawdziwe odpowiedzi 2 i 4 d – prawdziwa odpowiedź 4 e – wszystkie odpowiedzi prawdziwe</t></is></c><c r="H876" s="2" t="inlineStr" /><c r="I876" s="2" t="inlineStr" /><c r="J876" s="2" t="inlineStr" /><c r="K876" s="2" t="inlineStr"><is><t>ampicylina z gentamycyną</t></is></c><c r="L876" s="2" t="inlineStr"><is><t>ampicylina z deksametazonem</t></is></c><c r="M876" s="2" t="inlineStr" /><c r="N876" s="2" t="inlineStr" /><c r="O876" s="2" t="inlineStr" /><c r="P876" s="2" t="inlineStr"><is><t>EGZAMIN IWL 1 lutego 2016</t></is></c><c r="Q876" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="877"><c r="A877" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B877" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C877" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D877" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E877" s="2" t="inlineStr"><is><t>Efekt bakteriobójczy zależny od czasu, w którym stężenie leku jest większe od MIC wykazują:</t></is></c><c r="F877" s="2" t="inlineStr"><is><t>amoksycylina z kwasem klawulanowym</t></is></c><c r="G877" s="2" t="inlineStr"><is><t>ceftriakson</t></is></c><c r="H877" s="2" t="inlineStr" /><c r="I877" s="2" t="inlineStr" /><c r="J877" s="2" t="inlineStr" /><c r="K877" s="2" t="inlineStr"><is><t>lewofloksacyna → chinolony</t></is></c><c r="L877" s="2" t="inlineStr"><is><t>amikacyna beta-laktamy, erytromycyna, klarytromycyna</t></is></c><c r="M877" s="2" t="inlineStr" /><c r="N877" s="2" t="inlineStr" /><c r="O877" s="2" t="inlineStr" /><c r="P877" s="2" t="inlineStr"><is><t>EGZAMIN IWL 1 lutego 2016</t></is></c><c r="Q877" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="878"><c r="A878" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B878" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C878" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D878" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E878" s="2" t="inlineStr"><is><t>Leki przeciwdrobnoustrojowe, których mechanizm działania polega na hamowaniu biosyntezy ściany komórkowej bakterii to:</t></is></c><c r="F878" s="2" t="inlineStr"><is><t>cefadroksyl</t></is></c><c r="G878" s="2" t="inlineStr"><is><t>wankomycyna</t></is></c><c r="H878" s="2" t="inlineStr"><is><t>bacytracyna penicyliny, cefalosporyny, karbapenemy, aztreonam, wankomycyna, teikoplanina, telawancyna, dalbawancyna, fosfomycyna, bacytracyna, sulfonamidy</t></is></c><c r="I878" s="2" t="inlineStr" /><c r="J878" s="2" t="inlineStr" /><c r="K878" s="2" t="inlineStr"><is><t>klindamycyna</t></is></c><c r="L878" s="2" t="inlineStr" /><c r="M878" s="2" t="inlineStr" /><c r="N878" s="2" t="inlineStr" /><c r="O878" s="2" t="inlineStr" /><c r="P878" s="2" t="inlineStr"><is><t>EGZAMIN IWL 1 lutego 2016</t></is></c><c r="Q878" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="879"><c r="A879" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B879" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C879" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D879" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E879" s="2" t="inlineStr"><is><t>Aktywność przeciwbakteryjną względem Legionella spp. ma:</t></is></c><c r="F879" s="2" t="inlineStr"><is><t>moksyfloksacyna</t></is></c><c r="G879" s="2" t="inlineStr"><is><t>azytromycyna</t></is></c><c r="H879" s="2" t="inlineStr" /><c r="I879" s="2" t="inlineStr" /><c r="J879" s="2" t="inlineStr" /><c r="K879" s="2" t="inlineStr"><is><t>metronidazol</t></is></c><c r="L879" s="2" t="inlineStr"><is><t>tygecyklina makrolidy, chinolony, kolistyna</t></is></c><c r="M879" s="2" t="inlineStr" /><c r="N879" s="2" t="inlineStr" /><c r="O879" s="2" t="inlineStr" /><c r="P879" s="2" t="inlineStr"><is><t>EGZAMIN IWL 1 lutego 2016</t></is></c><c r="Q879" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="880"><c r="A880" s="2" t="inlineStr"><is><t>LEKI PRZECIWWIRUSOWE</t></is></c><c r="B880" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C880" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D880" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E880" s="2" t="inlineStr"><is><t>Inhibitory neuraminidazy:</t></is></c><c r="F880" s="2" t="inlineStr"><is><t>hamują uwalnianie wirusów z zakażonych komórek → agregacja wirusów na powierzchni komórek oraz zmniejszenie namnażania wirusów w drogach oddechowych</t></is></c><c r="G880" s="2" t="inlineStr"><is><t>można je stosować w leczeniu grypy typu A i B</t></is></c><c r="H880" s="2" t="inlineStr" /><c r="I880" s="2" t="inlineStr" /><c r="J880" s="2" t="inlineStr" /><c r="K880" s="2" t="inlineStr"><is><t>nie różnią się między sobą pod względem skuteczności i działań niepożądanych</t></is></c><c r="L880" s="2" t="inlineStr"><is><t>nie są skuteczne w profilaktyce grypy ostelamiwir (dzieci od 1r.ż.) skrócenie czasu objawów o 1-2 dni, zastosować 6- 48h od wystąpienia objawów, zanaiwir, panamiwir a – prawdziwe odpowiedzi 1, 3 i 4 b – prawdziwe odpowiedzi 1 i 3 c – prawdziwe odpowiedzi 2 i 4 d – prawdziwa odpowiedź 4 e – wszystkie odpowiedzi prawdziwe</t></is></c><c r="M880" s="2" t="inlineStr" /><c r="N880" s="2" t="inlineStr" /><c r="O880" s="2" t="inlineStr" /><c r="P880" s="2" t="inlineStr"><is><t>EGZAMIN IWL 1 lutego 2016</t></is></c><c r="Q880" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="881"><c r="A881" s="2" t="inlineStr"><is><t>LEKI PRZECIWGRZYBICZE</t></is></c><c r="B881" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C881" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D881" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E881" s="2" t="inlineStr"><is><t>W grzybiczym zakażeniu paznokci zastosowanie ma:</t></is></c><c r="F881" s="2" t="inlineStr"><is><t>itrakonazol</t></is></c><c r="G881" s="2" t="inlineStr"><is><t>terbinafina</t></is></c><c r="H881" s="2" t="inlineStr" /><c r="I881" s="2" t="inlineStr" /><c r="J881" s="2" t="inlineStr" /><c r="K881" s="2" t="inlineStr"><is><t>natamycyna</t></is></c><c r="L881" s="2" t="inlineStr"><is><t>kaspofungina</t></is></c><c r="M881" s="2" t="inlineStr"><is><t>amorolfina (lakier do paznokci)</t></is></c><c r="N881" s="2" t="inlineStr" /><c r="O881" s="2" t="inlineStr" /><c r="P881" s="2" t="inlineStr"><is><t>EGZAMIN IWL 1 lutego 2016</t></is></c><c r="Q881" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="882"><c r="A882" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B882" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C882" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D882" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E882" s="2" t="inlineStr"><is><t>Po ugryzieniu przez kleszcza, gdy obserwujemy rumień wędrujący, racjonalne jest zastosowanie:</t></is></c><c r="F882" s="2" t="inlineStr"><is><t>doksycykliny</t></is></c><c r="G882" s="2" t="inlineStr"><is><t>azytromycyny a – prawdziwe odpowiedzi 1, 3 i 4 b – prawdziwe odpowiedzi 1 i 3 c – prawdziwe odpowiedzi 2 i 4 d – prawdziwa odpowiedź 4 e – wszystkie odpowiedzi prawdziwe</t></is></c><c r="H882" s="2" t="inlineStr" /><c r="I882" s="2" t="inlineStr" /><c r="J882" s="2" t="inlineStr" /><c r="K882" s="2" t="inlineStr"><is><t>Amoksycyliny (borelioza)</t></is></c><c r="L882" s="2" t="inlineStr"><is><t>cefuroksymu (borelioza)</t></is></c><c r="M882" s="2" t="inlineStr" /><c r="N882" s="2" t="inlineStr" /><c r="O882" s="2" t="inlineStr" /><c r="P882" s="2" t="inlineStr"><is><t>EGZAMIN IWL 1 lutego 2016</t></is></c><c r="Q882" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="883"><c r="A883" s="2" t="inlineStr"><is><t>LEKI PRZECIWWIRUSOWE</t></is></c><c r="B883" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C883" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D883" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E883" s="2" t="inlineStr"><is><t>W leczeniu zakażenia wirusem opryszczki (Herpes) stosuje się:</t></is></c><c r="F883" s="2" t="inlineStr"><is><t>foskarnet</t></is></c><c r="G883" s="2" t="inlineStr"><is><t>acyklowir (HBV)</t></is></c><c r="H883" s="2" t="inlineStr" /><c r="I883" s="2" t="inlineStr" /><c r="J883" s="2" t="inlineStr" /><c r="K883" s="2" t="inlineStr"><is><t>Rymantadynę (grypa A)</t></is></c><c r="L883" s="2" t="inlineStr"><is><t>lamiwudynę</t></is></c><c r="M883" s="2" t="inlineStr" /><c r="N883" s="2" t="inlineStr" /><c r="O883" s="2" t="inlineStr" /><c r="P883" s="2" t="inlineStr"><is><t>EGZAMIN IWL 1 lutego 2016</t></is></c><c r="Q883" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="884"><c r="A884" s="2" t="inlineStr"><is><t>TARCZYCA</t></is></c><c r="B884" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C884" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D884" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E884" s="2" t="inlineStr"><is><t>Liotyronina: T3, nie ma preparatu w Polsce zawierającego tylko T3, jest preparat zawierający T3 i T4 1:5</t></is></c><c r="F884" s="2" t="inlineStr"><is><t>odpowiada ona naturalnemu hormonowi T3</t></is></c><c r="G884" s="2" t="inlineStr"><is><t>ma krótszy okres półtrwania niż lewotyroksyna</t></is></c><c r="H884" s="2" t="inlineStr" /><c r="I884" s="2" t="inlineStr" /><c r="J884" s="2" t="inlineStr" /><c r="K884" s="2" t="inlineStr"><is><t>jest lekiem z wyboru w niedoczynności tarczycy → lekiem z wyboru jest lewotyroksyna</t></is></c><c r="L884" s="2" t="inlineStr"><is><t>jest przeciwwskazana w leczeniu śpiączki hipometabolicznej</t></is></c><c r="M884" s="2" t="inlineStr" /><c r="N884" s="2" t="inlineStr" /><c r="O884" s="2" t="inlineStr" /><c r="P884" s="2" t="inlineStr"><is><t>EGZAMIN IWL 1 lutego 2016</t></is></c><c r="Q884" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="885"><c r="A885" s="2" t="inlineStr"><is><t>TARCZYCA</t></is></c><c r="B885" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C885" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D885" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E885" s="2" t="inlineStr"><is><t>Wskazaniem do zastosowania jodku potasu może być:</t></is></c><c r="F885" s="2" t="inlineStr"><is><t>ochrona tarczycy przed jodem radioaktywnym</t></is></c><c r="G885" s="2" t="inlineStr"><is><t>przygotowanie do usunięcia tarczycy</t></is></c><c r="H885" s="2" t="inlineStr"><is><t>przełom tyreotoksyczny</t></is></c><c r="I885" s="2" t="inlineStr"><is><t>zapobieganie powstawaniu wola z niedoboru jodu a – prawdziwe odpowiedzi 1, 3 i 4 b – prawdziwe odpowiedzi 1 i 3 c – prawdziwe odpowiedzi 2 i 4 d – prawdziwa odpowiedź 4 e – wszystkie odpowiedzi prawdziwe</t></is></c><c r="J885" s="2" t="inlineStr" /><c r="K885" s="2" t="inlineStr" /><c r="L885" s="2" t="inlineStr" /><c r="M885" s="2" t="inlineStr" /><c r="N885" s="2" t="inlineStr" /><c r="O885" s="2" t="inlineStr" /><c r="P885" s="2" t="inlineStr"><is><t>EGZAMIN IWL 1 lutego 2016</t></is></c><c r="Q885" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="886"><c r="A886" s="2" t="inlineStr"><is><t>LEKI HIPOLIPEMIZUJĄCE</t></is></c><c r="B886" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C886" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D886" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E886" s="2" t="inlineStr"><is><t>W leczeniu hiperprolaktynemii stosuje się:</t></is></c><c r="F886" s="2" t="inlineStr"><is><t>bromokryptynę</t></is></c><c r="G886" s="2" t="inlineStr"><is><t>karbegolinę</t></is></c><c r="H886" s="2" t="inlineStr" /><c r="I886" s="2" t="inlineStr" /><c r="J886" s="2" t="inlineStr" /><c r="K886" s="2" t="inlineStr"><is><t>somatostatynę</t></is></c><c r="L886" s="2" t="inlineStr"><is><t>terlipresynę chinagolid</t></is></c><c r="M886" s="2" t="inlineStr" /><c r="N886" s="2" t="inlineStr" /><c r="O886" s="2" t="inlineStr" /><c r="P886" s="2" t="inlineStr"><is><t>EGZAMIN IWL 1 lutego 2016</t></is></c><c r="Q886" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="887"><c r="A887" s="2" t="inlineStr"><is><t>HORMONY PŁCIOWE</t></is></c><c r="B887" s="2" t="inlineStr"><is><t>Interakcje</t></is></c><c r="C887" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D887" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E887" s="2" t="inlineStr"><is><t>Działanie antyandrogenne wykazuje:</t></is></c><c r="F887" s="2" t="inlineStr"><is><t>octan cyproteronu</t></is></c><c r="G887" s="2" t="inlineStr"><is><t>finasteryd</t></is></c><c r="H887" s="2" t="inlineStr"><is><t>bikalutamid flutamid, cyproteron, dutasteryd, abirateron, spironolakton</t></is></c><c r="I887" s="2" t="inlineStr" /><c r="J887" s="2" t="inlineStr" /><c r="K887" s="2" t="inlineStr"><is><t>ketokonazol</t></is></c><c r="L887" s="2" t="inlineStr" /><c r="M887" s="2" t="inlineStr" /><c r="N887" s="2" t="inlineStr" /><c r="O887" s="2" t="inlineStr" /><c r="P887" s="2" t="inlineStr"><is><t>EGZAMIN IWL 1 lutego 2016</t></is></c><c r="Q887" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="888"><c r="A888" s="2" t="inlineStr"><is><t>GLIKOKORTYKOSTEROIDY</t></is></c><c r="B888" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C888" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D888" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E888" s="2" t="inlineStr"><is><t>Glikokortykosteroidy zwiększają:</t></is></c><c r="F888" s="2" t="inlineStr"><is><t>produkcję surfaktantu ciśnienie krwi, ciśnienie śródgałkowe, glukoneogenezę</t></is></c><c r="G888" s="2" t="inlineStr" /><c r="H888" s="2" t="inlineStr" /><c r="I888" s="2" t="inlineStr" /><c r="J888" s="2" t="inlineStr" /><c r="K888" s="2" t="inlineStr"><is><t>ekspresję genu osteokalcyny (obniża)</t></is></c><c r="L888" s="2" t="inlineStr"><is><t>stężenie wapnia w surowicy krwi</t></is></c><c r="M888" s="2" t="inlineStr"><is><t>syntezę testosteronu</t></is></c><c r="N888" s="2" t="inlineStr" /><c r="O888" s="2" t="inlineStr" /><c r="P888" s="2" t="inlineStr"><is><t>EGZAMIN IWL 1 lutego 2016</t></is></c><c r="Q888" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="889"><c r="A889" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B889" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C889" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D889" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E889" s="2" t="inlineStr"><is><t>Efektem nadmiaru gestagenów może być:</t></is></c><c r="F889" s="2" t="inlineStr"><is><t>depresja</t></is></c><c r="G889" s="2" t="inlineStr"><is><t>łojotok skóry</t></is></c><c r="H889" s="2" t="inlineStr"><is><t>przyrost masy ciała</t></is></c><c r="I889" s="2" t="inlineStr"><is><t>hirsutyzm trądzik, zmęczenie, zmiany libido</t></is></c><c r="J889" s="2" t="inlineStr" /><c r="K889" s="2" t="inlineStr" /><c r="L889" s="2" t="inlineStr" /><c r="M889" s="2" t="inlineStr" /><c r="N889" s="2" t="inlineStr" /><c r="O889" s="2" t="inlineStr" /><c r="P889" s="2" t="inlineStr"><is><t>EGZAMIN IWL 1 lutego 2016</t></is></c><c r="Q889" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="890"><c r="A890" s="2" t="inlineStr"><is><t>LEKI PRZECIWPASOŻYTNICZE</t></is></c><c r="B890" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C890" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D890" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E890" s="2" t="inlineStr"><is><t>W leczeniu wągrzycy (cysticerkozy) stosujemy:</t></is></c><c r="F890" s="2" t="inlineStr"><is><t>Prazykwantel→ tasiemczyca, bąblowica</t></is></c><c r="G890" s="2" t="inlineStr"><is><t>albendazol → wągrzyca a – prawdziwe odpowiedzi 1, 3 i 4 b – prawdziwe odpowiedzi 1 i 3 c – prawdziwe odpowiedzi 2 i 4 d – prawdziwa odpowiedź 4 e – wszystkie odpowiedzi prawdziwe</t></is></c><c r="H890" s="2" t="inlineStr" /><c r="I890" s="2" t="inlineStr" /><c r="J890" s="2" t="inlineStr" /><c r="K890" s="2" t="inlineStr"><is><t>Metronidazol → trichomonas vaginalis, lambdia intestinalis</t></is></c><c r="L890" s="2" t="inlineStr"><is><t>iwermektynę→ węgorek jelitowy, włosogłówka</t></is></c><c r="M890" s="2" t="inlineStr" /><c r="N890" s="2" t="inlineStr" /><c r="O890" s="2" t="inlineStr" /><c r="P890" s="2" t="inlineStr"><is><t>EGZAMIN IWL 1 lutego 2016</t></is></c><c r="Q890" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="891"><c r="A891" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B891" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C891" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D891" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E891" s="2" t="inlineStr"><is><t>Działanie zapierające wykazuje:</t></is></c><c r="F891" s="2" t="inlineStr"><is><t>werapamil</t></is></c><c r="G891" s="2" t="inlineStr"><is><t>węglan wapnia</t></is></c><c r="H891" s="2" t="inlineStr"><is><t>odwar z suchych owoców borówki czernicy loperamid, opioidy, difenokslat, oktreotyd, gatbniki (kora dębu, borówka czernicy), smektyn, racekadotryl, związki wapnia, antagoiści kanałów wapniowych, cholinolityki, niektóre neuroleptyki, leki przeciwhistaminowe (działanie atroinowe)</t></is></c><c r="I891" s="2" t="inlineStr" /><c r="J891" s="2" t="inlineStr" /><c r="K891" s="2" t="inlineStr"><is><t>erytromycyna</t></is></c><c r="L891" s="2" t="inlineStr" /><c r="M891" s="2" t="inlineStr" /><c r="N891" s="2" t="inlineStr" /><c r="O891" s="2" t="inlineStr" /><c r="P891" s="2" t="inlineStr"><is><t>EGZAMIN IWL 1 lutego 2016</t></is></c><c r="Q891" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="892"><c r="A892" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B892" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C892" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D892" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E892" s="2" t="inlineStr"><is><t>Efekty gastrotoksyczne związane ze stosowaniem niesteroidowych leków przeciwzapalnych może nasilać:</t></is></c><c r="F892" s="2" t="inlineStr"><is><t>zolendronian</t></is></c><c r="G892" s="2" t="inlineStr"><is><t>fluoksetyna</t></is></c><c r="H892" s="2" t="inlineStr"><is><t>acenokumarol</t></is></c><c r="I892" s="2" t="inlineStr"><is><t>prednizon gks, ssri, bisfosfoniany, leki przeciwzakrzepowe, mukolityki, leki wykrztuśne, spironolakton</t></is></c><c r="J892" s="2" t="inlineStr" /><c r="K892" s="2" t="inlineStr" /><c r="L892" s="2" t="inlineStr" /><c r="M892" s="2" t="inlineStr" /><c r="N892" s="2" t="inlineStr" /><c r="O892" s="2" t="inlineStr" /><c r="P892" s="2" t="inlineStr"><is><t>EGZAMIN IWL 1 lutego 2016</t></is></c><c r="Q892" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="893"><c r="A893" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B893" s="2" t="inlineStr"><is><t>Ciąża</t></is></c><c r="C893" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D893" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E893" s="2" t="inlineStr"><is><t>Zastosowanie ibuprofenu w 3 trymestrze ciąży może spowodować:</t></is></c><c r="F893" s="2" t="inlineStr"><is><t>przedwczesne zamknięcie przewodu Botalla</t></is></c><c r="G893" s="2" t="inlineStr"><is><t>zwiększone ryzyko krwawienia u matki</t></is></c><c r="H893" s="2" t="inlineStr" /><c r="I893" s="2" t="inlineStr" /><c r="J893" s="2" t="inlineStr" /><c r="K893" s="2" t="inlineStr"><is><t>zwiększenie czynności skurczowej macicy → opóźnienie porodu</t></is></c><c r="L893" s="2" t="inlineStr"><is><t>zwiększone ryzyko obrzęków u matki zmniejszają ilość płynu owodniowego, stany przed rzucawkowe → leczenie małymi dawkami ASA</t></is></c><c r="M893" s="2" t="inlineStr" /><c r="N893" s="2" t="inlineStr" /><c r="O893" s="2" t="inlineStr" /><c r="P893" s="2" t="inlineStr"><is><t>EGZAMIN IWL 1 lutego 2016</t></is></c><c r="Q893" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="894"><c r="A894" s="2" t="inlineStr"><is><t>BÓLE GŁOWY</t></is></c><c r="B894" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C894" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D894" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E894" s="2" t="inlineStr"><is><t>Napad migreny przerywa:</t></is></c><c r="F894" s="2" t="inlineStr"><is><t>winian ergotaminy</t></is></c><c r="G894" s="2" t="inlineStr"><is><t>sumatryptan</t></is></c><c r="H894" s="2" t="inlineStr"><is><t>ibuprofen Tryptany, alkaloidy sporysz, nlzp a – prawdziwe odpowiedzi 1, 3 i 4 b – prawdziwe odpowiedzi 1 i 3 c – prawdziwe odpowiedzi 2 i 4 d – prawdziwa odpowiedź 4 e – wszystkie odpowiedzi prawdziwe</t></is></c><c r="I894" s="2" t="inlineStr" /><c r="J894" s="2" t="inlineStr" /><c r="K894" s="2" t="inlineStr"><is><t>metoklopramid</t></is></c><c r="L894" s="2" t="inlineStr" /><c r="M894" s="2" t="inlineStr" /><c r="N894" s="2" t="inlineStr" /><c r="O894" s="2" t="inlineStr" /><c r="P894" s="2" t="inlineStr"><is><t>EGZAMIN IWL 1 lutego 2016</t></is></c><c r="Q894" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="895"><c r="A895" s="2" t="inlineStr"><is><t>NIEOPIOIDOWE LEKI PRZECIWBÓLOWE</t></is></c><c r="B895" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C895" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D895" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E895" s="2" t="inlineStr"><is><t>Nefopam:→ działa chronotopowo dodatnio i inotropowo dodatnio</t></is></c><c r="F895" s="2" t="inlineStr"><is><t>jest inhibitorem wychwytu zwrotnego serotoniny i noradrenaliny</t></is></c><c r="G895" s="2" t="inlineStr"><is><t>u osób starszych może wywoływać omamy</t></is></c><c r="H895" s="2" t="inlineStr" /><c r="I895" s="2" t="inlineStr" /><c r="J895" s="2" t="inlineStr" /><c r="K895" s="2" t="inlineStr"><is><t>hamuje wybiórczo cyklooksygenazę typu 2</t></is></c><c r="L895" s="2" t="inlineStr"><is><t>u dzieci może być stosowany w profilaktyce drgawek gorączkowych → nie stosujemy go do 12 roku życia</t></is></c><c r="M895" s="2" t="inlineStr" /><c r="N895" s="2" t="inlineStr" /><c r="O895" s="2" t="inlineStr" /><c r="P895" s="2" t="inlineStr"><is><t>EGZAMIN IWL 1 lutego 2016</t></is></c><c r="Q895" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="896"><c r="A896" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B896" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C896" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D896" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E896" s="2" t="inlineStr"><is><t>W zespole abstynencyjnym w uzależnieniu od opioidów występują:</t></is></c><c r="F896" s="2" t="inlineStr"><is><t>rozszerzenie źrenic</t></is></c><c r="G896" s="2" t="inlineStr"><is><t>wymioty i biegunka</t></is></c><c r="H896" s="2" t="inlineStr"><is><t>bezsenność</t></is></c><c r="I896" s="2" t="inlineStr"><is><t>łzawienie i wyciek z nosa dysforia, nudności, bóle mięśni, pocenie, piloerekcja (gęsia skórka), ziewanie, gorączka a – prawdziwe odpowiedzi 1, 3 i 4 b – prawdziwe odpowiedzi 1 i 3 c – prawdziwe odpowiedzi 2 i 4 d – prawdziwa odpowiedź 4 e – wszystkie odpowiedzi prawdziwe</t></is></c><c r="J896" s="2" t="inlineStr" /><c r="K896" s="2" t="inlineStr" /><c r="L896" s="2" t="inlineStr" /><c r="M896" s="2" t="inlineStr" /><c r="N896" s="2" t="inlineStr" /><c r="O896" s="2" t="inlineStr" /><c r="P896" s="2" t="inlineStr"><is><t>EGZAMIN IWL 1 lutego 2016</t></is></c><c r="Q896" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="897"><c r="A897" s="2" t="inlineStr"><is><t>CUKRZYCA</t></is></c><c r="B897" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C897" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D897" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E897" s="2" t="inlineStr"><is><t>Redukcję masy ciała może powodować stosowanie:</t></is></c><c r="F897" s="2" t="inlineStr"><is><t>fluoksetyny</t></is></c><c r="G897" s="2" t="inlineStr"><is><t>metforminy</t></is></c><c r="H897" s="2" t="inlineStr"><is><t>liraglutydu orlistat, flozyny, akarboza, leki inkretynowe, hormony tarczycy, ssri, zonisamid, roflumilast</t></is></c><c r="I897" s="2" t="inlineStr" /><c r="J897" s="2" t="inlineStr" /><c r="K897" s="2" t="inlineStr"><is><t>insuliny</t></is></c><c r="L897" s="2" t="inlineStr" /><c r="M897" s="2" t="inlineStr" /><c r="N897" s="2" t="inlineStr" /><c r="O897" s="2" t="inlineStr" /><c r="P897" s="2" t="inlineStr"><is><t>EGZAMIN IWL 1 lutego 2016</t></is></c><c r="Q897" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="898"><c r="A898" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B898" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C898" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D898" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E898" s="2" t="inlineStr"><is><t>W udarze niedokrwiennym mózgu możesz zastosować tkankowy aktywator plazminogenu jeśli stwierdzisz, że pacjent:</t></is></c><c r="F898" s="2" t="inlineStr"><is><t>otrzymuje doustne leczenie przeciwkrzepliwe (INR=1.5)</t></is></c><c r="G898" s="2" t="inlineStr"><is><t>jest w podeszłym wieku (&gt; 80 lat)</t></is></c><c r="H898" s="2" t="inlineStr"><is><t>ma wartości ciśnienia tętniczego: SBP ≤ 185 mm Hg lub DBP ≤ 110 mm Hg</t></is></c><c r="I898" s="2" t="inlineStr"><is><t>ma czas od wystąpienia objawów udaru mózgu nie przekraczający 4.5h</t></is></c><c r="J898" s="2" t="inlineStr" /><c r="K898" s="2" t="inlineStr" /><c r="L898" s="2" t="inlineStr" /><c r="M898" s="2" t="inlineStr" /><c r="N898" s="2" t="inlineStr" /><c r="O898" s="2" t="inlineStr" /><c r="P898" s="2" t="inlineStr"><is><t>EGZAMIN IWL 1 lutego 2016</t></is></c><c r="Q898" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="899"><c r="A899" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B899" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C899" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D899" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E899" s="2" t="inlineStr"><is><t>Do leków działających na receptor P2Y12 zaliczamy:</t></is></c><c r="F899" s="2" t="inlineStr"><is><t>prasugrel → tiklopidyna, klopidrel, tikagrelor, kangrelor a – prawdziwe odpowiedzi 1, 3 i 4 b – prawdziwe odpowiedzi 1 i 3 c – prawdziwe odpowiedzi 2 i 4 d – prawdziwa odpowiedź 4 e – wszystkie odpowiedzi prawdziwe</t></is></c><c r="G899" s="2" t="inlineStr" /><c r="H899" s="2" t="inlineStr" /><c r="I899" s="2" t="inlineStr" /><c r="J899" s="2" t="inlineStr" /><c r="K899" s="2" t="inlineStr"><is><t>apiksaban</t></is></c><c r="L899" s="2" t="inlineStr"><is><t>worapaksar</t></is></c><c r="M899" s="2" t="inlineStr"><is><t>dypirydamol</t></is></c><c r="N899" s="2" t="inlineStr" /><c r="O899" s="2" t="inlineStr" /><c r="P899" s="2" t="inlineStr"><is><t>EGZAMIN IWL 1 lutego 2016</t></is></c><c r="Q899" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="900"><c r="A900" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B900" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C900" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D900" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E900" s="2" t="inlineStr"><is><t>Do częstych działań niepożądanych atorwastatyny należy:</t></is></c><c r="F900" s="2" t="inlineStr"><is><t>miopatia</t></is></c><c r="G900" s="2" t="inlineStr"><is><t>uszkodzenie wątroby objawy ze strony układu pokarmowego: bóle brzucha, wzdęcia, zaparcia, biegunki, nudności, wymioty, wysypka, świąd, wypadanie włosów, zawroty głowy, skurcze mięśni, reakcje nadwrażliwości, obrzęk naczynioruchowy, rekacja anafilaktyczna, zapalenie trzustki, rambdomioliza</t></is></c><c r="H900" s="2" t="inlineStr" /><c r="I900" s="2" t="inlineStr" /><c r="J900" s="2" t="inlineStr" /><c r="K900" s="2" t="inlineStr"><is><t>rogowacenie ciemne</t></is></c><c r="L900" s="2" t="inlineStr"><is><t>uderzenia gorąca</t></is></c><c r="M900" s="2" t="inlineStr" /><c r="N900" s="2" t="inlineStr" /><c r="O900" s="2" t="inlineStr" /><c r="P900" s="2" t="inlineStr"><is><t>EGZAMIN IWL 1 lutego 2016</t></is></c><c r="Q900" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="901"><c r="A901" s="2" t="inlineStr"><is><t>FARMAKOKINETYKA</t></is></c><c r="B901" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C901" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D901" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E901" s="2" t="inlineStr"><is><t>Orlistat:</t></is></c><c r="F901" s="2" t="inlineStr"><is><t>może być przyczyną wystąpienia tłuszczowych stolców</t></is></c><c r="G901" s="2" t="inlineStr"><is><t>może być stosowany u osób z chorobami układu krążenia</t></is></c><c r="H901" s="2" t="inlineStr" /><c r="I901" s="2" t="inlineStr" /><c r="J901" s="2" t="inlineStr" /><c r="K901" s="2" t="inlineStr"><is><t>ma wysoką biodostępność po podaniu doustnym</t></is></c><c r="L901" s="2" t="inlineStr"><is><t>zwiększa wchłanianie witaminy D → może powodować niedobór (A,D,E,K)</t></is></c><c r="M901" s="2" t="inlineStr" /><c r="N901" s="2" t="inlineStr" /><c r="O901" s="2" t="inlineStr" /><c r="P901" s="2" t="inlineStr"><is><t>EGZAMIN IWL 1 lutego 2016</t></is></c><c r="Q901" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="902"><c r="A902" s="2" t="inlineStr"><is><t>NADCIŚNIENIE TĘTNICZE</t></is></c><c r="B902" s="2" t="inlineStr"><is><t>Farmakokinetyka</t></is></c><c r="C902" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D902" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E902" s="2" t="inlineStr"><is><t>Wybierz właściwe zestawienia lek prekursorowy – jego aktywny metabolit:</t></is></c><c r="F902" s="2" t="inlineStr"><is><t>cileksetyl kandesartanu → kandesartan</t></is></c><c r="G902" s="2" t="inlineStr" /><c r="H902" s="2" t="inlineStr" /><c r="I902" s="2" t="inlineStr" /><c r="J902" s="2" t="inlineStr" /><c r="K902" s="2" t="inlineStr"><is><t>eplerenon → kanrenon (jest on metabolitem spironolaktonu)</t></is></c><c r="L902" s="2" t="inlineStr"><is><t>lizynopryl → lizynoprylat</t></is></c><c r="M902" s="2" t="inlineStr"><is><t>nebiwolol → tlenek azotu</t></is></c><c r="N902" s="2" t="inlineStr" /><c r="O902" s="2" t="inlineStr" /><c r="P902" s="2" t="inlineStr"><is><t>EGZAMIN IWL 1 lutego 2016</t></is></c><c r="Q902" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="903"><c r="A903" s="2" t="inlineStr"><is><t>LEKI MOCZOPĘDNE</t></is></c><c r="B903" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C903" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D903" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E903" s="2" t="inlineStr"><is><t>Hiponatremię z dużym stężeniem Na+ w moczu (&gt; 20 mmol/l) może spowodować:</t></is></c><c r="F903" s="2" t="inlineStr"><is><t>karbamazepina</t></is></c><c r="G903" s="2" t="inlineStr"><is><t>prednizon</t></is></c><c r="H903" s="2" t="inlineStr"><is><t>fluoksetyna</t></is></c><c r="I903" s="2" t="inlineStr"><is><t>indapamid tiazydy moczopędne, tiazydopodobne, diuretyki pętlowe, diuretyki osmotycznee, karbamazepina, gancyklowir, SSRI, SNRI, a – prawdziwe odpowiedzi 1, 3 i 4 b – prawdziwe odpowiedzi 1 i 3 c – prawdziwe odpowiedzi 2 i 4 d – prawdziwa odpowiedź 4 e – wszystkie odpowiedzi prawdziwe</t></is></c><c r="J903" s="2" t="inlineStr" /><c r="K903" s="2" t="inlineStr" /><c r="L903" s="2" t="inlineStr" /><c r="M903" s="2" t="inlineStr" /><c r="N903" s="2" t="inlineStr" /><c r="O903" s="2" t="inlineStr" /><c r="P903" s="2" t="inlineStr"><is><t>EGZAMIN IWL 1 lutego 2016</t></is></c><c r="Q903" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="904"><c r="A904" s="2" t="inlineStr"><is><t>LEKI IMMUNOSUPRESYJNE</t></is></c><c r="B904" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C904" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D904" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E904" s="2" t="inlineStr"><is><t>Wskaż prawidłowe połączenie lek-wskazanie:</t></is></c><c r="F904" s="2" t="inlineStr"><is><t>omalizumab – astma</t></is></c><c r="G904" s="2" t="inlineStr"><is><t>denosumab – osteoporoza</t></is></c><c r="H904" s="2" t="inlineStr" /><c r="I904" s="2" t="inlineStr" /><c r="J904" s="2" t="inlineStr" /><c r="K904" s="2" t="inlineStr"><is><t>natalizumab – reumatoidalne zapalenie stawów → stwardnienie rozsiane</t></is></c><c r="L904" s="2" t="inlineStr"><is><t>infliksymab – stwardnienie rozsiane zwyrodnienie plamki związane z wiekiem – ranibizumab, ustekinumab → czynna choroba</t></is></c><c r="M904" s="2" t="inlineStr" /><c r="N904" s="2" t="inlineStr" /><c r="O904" s="2" t="inlineStr" /><c r="P904" s="2" t="inlineStr"><is><t>EGZAMIN IWL 1 lutego 2016</t></is></c><c r="Q904" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="905"><c r="A905" s="2" t="inlineStr"><is><t>UKŁAD ODDECHOWY</t></is></c><c r="B905" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C905" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D905" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E905" s="2" t="inlineStr"><is><t>Działanie wykrztuśne ma:</t></is></c><c r="F905" s="2" t="inlineStr"><is><t>wyciąg z prawoślazu lekarskiego</t></is></c><c r="G905" s="2" t="inlineStr"><is><t>gwajafenazyna a – prawdziwe odpowiedzi 1, 3 i 4 b – prawdziwe odpowiedzi 1 i 3 c – prawdziwe odpowiedzi 2 i 4 d – prawdziwa odpowiedź 4 e – wszystkie odpowiedzi prawdziwe</t></is></c><c r="H905" s="2" t="inlineStr" /><c r="I905" s="2" t="inlineStr" /><c r="J905" s="2" t="inlineStr" /><c r="K905" s="2" t="inlineStr"><is><t>oksykodon</t></is></c><c r="L905" s="2" t="inlineStr"><is><t>mesna</t></is></c><c r="M905" s="2" t="inlineStr" /><c r="N905" s="2" t="inlineStr" /><c r="O905" s="2" t="inlineStr" /><c r="P905" s="2" t="inlineStr"><is><t>EGZAMIN IWL 1 lutego 2016</t></is></c><c r="Q905" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="906"><c r="A906" s="2" t="inlineStr"><is><t>LEKI ROŚLINNE I SUPLEMENTY</t></is></c><c r="B906" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C906" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D906" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E906" s="2" t="inlineStr"><is><t>URPL - Urząd Rejestracji Produktów Leczniczych, Wyrobów Medycznych i Produktów Biobójczych ocenia działania niepożądane zarejestrowanych:</t></is></c><c r="F906" s="2" t="inlineStr"><is><t>leków homeopatycznych</t></is></c><c r="G906" s="2" t="inlineStr"><is><t>leków dostępnych bez recepty</t></is></c><c r="H906" s="2" t="inlineStr"><is><t>leków pochodzenia roślinnego a – prawdziwe odpowiedzi 1, 3 i 4 b – prawdziwe odpowiedzi 1 i 3 c – prawdziwe odpowiedzi 2 i 4 d – prawdziwa odpowiedź 4 e – wszystkie odpowiedzi prawdziwe</t></is></c><c r="I906" s="2" t="inlineStr" /><c r="J906" s="2" t="inlineStr" /><c r="K906" s="2" t="inlineStr"><is><t>suplementów diety</t></is></c><c r="L906" s="2" t="inlineStr" /><c r="M906" s="2" t="inlineStr" /><c r="N906" s="2" t="inlineStr" /><c r="O906" s="2" t="inlineStr" /><c r="P906" s="2" t="inlineStr"><is><t>EGZAMIN IWL 1 lutego 2016</t></is></c><c r="Q906" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="907"><c r="A907" s="2" t="inlineStr"><is><t>LEKI PRZECIWNOWOTWOROWE</t></is></c><c r="B907" s="2" t="inlineStr"><is><t>Ciąża</t></is></c><c r="C907" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D907" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E907" s="2" t="inlineStr"><is><t>Teratogenem człowieka o udokumentowanym działaniu jest:</t></is></c><c r="F907" s="2" t="inlineStr"><is><t>metotreksat</t></is></c><c r="G907" s="2" t="inlineStr"><is><t>tiamazol</t></is></c><c r="H907" s="2" t="inlineStr"><is><t>kwas walproinowy</t></is></c><c r="I907" s="2" t="inlineStr"><is><t>lit</t></is></c><c r="J907" s="2" t="inlineStr" /><c r="K907" s="2" t="inlineStr" /><c r="L907" s="2" t="inlineStr" /><c r="M907" s="2" t="inlineStr" /><c r="N907" s="2" t="inlineStr" /><c r="O907" s="2" t="inlineStr" /><c r="P907" s="2" t="inlineStr"><is><t>EGZAMIN IWL 1 lutego 2016</t></is></c><c r="Q907" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="908"><c r="A908" s="2" t="inlineStr"><is><t>LEKI PRZECIWHISTAMINOWE</t></is></c><c r="B908" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C908" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D908" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E908" s="2" t="inlineStr"><is><t>Klemastyna:</t></is></c><c r="F908" s="2" t="inlineStr"><is><t>selektywnie działa na rec. H1</t></is></c><c r="G908" s="2" t="inlineStr"><is><t>dobrze przenika przez barierę krew- mózg</t></is></c><c r="H908" s="2" t="inlineStr"><is><t>jest lekiem z wyboru w leczeniu przewlekłego alergicznego nieżytu nosa</t></is></c><c r="I908" s="2" t="inlineStr"><is><t>może być stosowana od 2 r. ż. a – prawdziwe odpowiedzi 1, 3 i 4 b – prawdziwe odpowiedzi 1 i 3 c – prawdziwe odpowiedzi 2 i 4 d – prawdziwa odpowiedź 4 e – wszystkie odpowiedzi prawdziwe</t></is></c><c r="J908" s="2" t="inlineStr" /><c r="K908" s="2" t="inlineStr" /><c r="L908" s="2" t="inlineStr" /><c r="M908" s="2" t="inlineStr" /><c r="N908" s="2" t="inlineStr" /><c r="O908" s="2" t="inlineStr" /><c r="P908" s="2" t="inlineStr"><is><t>EGZAMIN IWL 1 lutego 2016</t></is></c><c r="Q908" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="909"><c r="A909" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B909" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C909" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D909" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E909" s="2" t="inlineStr"><is><t>Skuteczne leczenie w owrzodzeniach żylnych obejmuje:</t></is></c><c r="F909" s="2" t="inlineStr"><is><t>opatrunki hydrokoloidowe uzupełniające: opatrunki ze srebrem, pentoksyfilina, filgrastym, lenogrstym, hydrożele, alginiany, opatrunki poliuretanowe, oczyszczona frakacja flawonoidów, diosmina, hesperydyna a – prawdziwe odpowiedzi 1, 3 i 4 b – prawdziwe odpowiedzi 1 i 3 c – prawdziwe odpowiedzi 2 i 4 d – prawdziwa odpowiedź 4 e – wszystkie odpowiedzi prawdziwe</t></is></c><c r="G909" s="2" t="inlineStr" /><c r="H909" s="2" t="inlineStr" /><c r="I909" s="2" t="inlineStr" /><c r="J909" s="2" t="inlineStr" /><c r="K909" s="2" t="inlineStr"><is><t>wyciągi zawierające glikozydy kasztanowca</t></is></c><c r="L909" s="2" t="inlineStr"><is><t>heparynoidy do stosowania miejscowego</t></is></c><c r="M909" s="2" t="inlineStr"><is><t>dobesylan wapnia</t></is></c><c r="N909" s="2" t="inlineStr" /><c r="O909" s="2" t="inlineStr" /><c r="P909" s="2" t="inlineStr"><is><t>EGZAMIN IWL 1 lutego 2016</t></is></c><c r="Q909" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="910"><c r="A910" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B910" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C910" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D910" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E910" s="2" t="inlineStr"><is><t>Działanie przeciwwymiotne ma:</t></is></c><c r="F910" s="2" t="inlineStr"><is><t>dimenhydrinat] Setrony, metoklopramid, neurroleptyki: chlorprometazyna, prometazyna, tietylperazyna, prochlorperazyna, haloperydol, droperydol, dimenhydrant, deksametazon, metyloprednizolon, kanabinoidy, aprepitantfosaprepitant, netupitant</t></is></c><c r="G910" s="2" t="inlineStr" /><c r="H910" s="2" t="inlineStr" /><c r="I910" s="2" t="inlineStr" /><c r="J910" s="2" t="inlineStr" /><c r="K910" s="2" t="inlineStr"><is><t>lewetyracetam</t></is></c><c r="L910" s="2" t="inlineStr"><is><t>skopolamina</t></is></c><c r="M910" s="2" t="inlineStr"><is><t>wortioksetyna</t></is></c><c r="N910" s="2" t="inlineStr" /><c r="O910" s="2" t="inlineStr" /><c r="P910" s="2" t="inlineStr"><is><t>EGZAMIN IWL 1 lutego 2016</t></is></c><c r="Q910" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="911"><c r="A911" s="2" t="inlineStr"><is><t>CHOROBA PARKINSONA</t></is></c><c r="B911" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C911" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D911" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E911" s="2" t="inlineStr"><is><t>W chorobie Parkinsona lewodopę można podawać jednocześnie z:</t></is></c><c r="F911" s="2" t="inlineStr"><is><t>benserazydem</t></is></c><c r="G911" s="2" t="inlineStr"><is><t>bromokryptyną</t></is></c><c r="H911" s="2" t="inlineStr"><is><t>rotygotyną</t></is></c><c r="I911" s="2" t="inlineStr"><is><t>entekaponem lewodopa + agoniści receptora dopaminergiczneho (bromokryptyna, kabergolina, pergoli, piribedyl,ropinirol, pramipeksol, rotygotyna, apomorfina + cholinolityki (benzatropina, triheksyfenidyl, biperiden, procyklidyna, orfenadryna + inhibitor dekarboksylazy (benserazyd, karbidodopa) + inhibitor COMt (entakapon, tolkapon) a – prawdziwe odpowiedzi 1, 3 i 4 b – prawdziwe odpowiedzi 1 i 3 c – prawdziwe odpowiedzi 2 i 4 d – prawdziwa odpowiedź 4 e – wszystkie odpowiedzi prawdziwe</t></is></c><c r="J911" s="2" t="inlineStr" /><c r="K911" s="2" t="inlineStr" /><c r="L911" s="2" t="inlineStr" /><c r="M911" s="2" t="inlineStr" /><c r="N911" s="2" t="inlineStr" /><c r="O911" s="2" t="inlineStr" /><c r="P911" s="2" t="inlineStr"><is><t>EGZAMIN IWL 1 lutego 2016</t></is></c><c r="Q911" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="912"><c r="A912" s="2" t="inlineStr"><is><t>LEKI PRZECIWDEPRESYJNE</t></is></c><c r="B912" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C912" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D912" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E912" s="2" t="inlineStr"><is><t>U chorego leczonego escitalopramem ryzyko wystąpienia zespołu serotoninergicznego rośnie gdy dołączymy do terapii:</t></is></c><c r="F912" s="2" t="inlineStr"><is><t>linezolid</t></is></c><c r="G912" s="2" t="inlineStr"><is><t>tramadol</t></is></c><c r="H912" s="2" t="inlineStr"><is><t>ziele dziurawca</t></is></c><c r="I912" s="2" t="inlineStr"><is><t>korzeń żeń-szenia MAO, tryptofan, tapentadol, tramadol,linezolid, fentanyl, klomipramina, lit, wenlafaksyna, mirta zapina, tradozon</t></is></c><c r="J912" s="2" t="inlineStr" /><c r="K912" s="2" t="inlineStr" /><c r="L912" s="2" t="inlineStr" /><c r="M912" s="2" t="inlineStr" /><c r="N912" s="2" t="inlineStr" /><c r="O912" s="2" t="inlineStr" /><c r="P912" s="2" t="inlineStr"><is><t>EGZAMIN IWL 1 lutego 2016</t></is></c><c r="Q912" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="913"><c r="A913" s="2" t="inlineStr"><is><t>LEKI PRZECIWLĘKOWE</t></is></c><c r="B913" s="2" t="inlineStr"><is><t>Antidotum</t></is></c><c r="C913" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D913" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E913" s="2" t="inlineStr"><is><t>Podanie węgla aktywowanego nie przyniesie efektu w przypadku zatrucia:</t></is></c><c r="F913" s="2" t="inlineStr"><is><t>etanolem</t></is></c><c r="G913" s="2" t="inlineStr"><is><t>ołowiem</t></is></c><c r="H913" s="2" t="inlineStr"><is><t>benzyną nie podajemy gdy: chory nieprzytomny, zamroczony, zatrucie kwasami, zasadami, metalami ciężkimi, alkoholami,węglowodanami (benzyna, nafta)</t></is></c><c r="I913" s="2" t="inlineStr" /><c r="J913" s="2" t="inlineStr" /><c r="K913" s="2" t="inlineStr"><is><t>benzodiazepinami</t></is></c><c r="L913" s="2" t="inlineStr" /><c r="M913" s="2" t="inlineStr" /><c r="N913" s="2" t="inlineStr" /><c r="O913" s="2" t="inlineStr" /><c r="P913" s="2" t="inlineStr"><is><t>EGZAMIN IWL 1 lutego 2016</t></is></c><c r="Q913" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="914"><c r="A914" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B914" s="2" t="inlineStr"><is><t>Farmakokinetyka</t></is></c><c r="C914" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D914" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E914" s="2" t="inlineStr"><is><t>U osób w starszym wieku na zmiany farmakokinetyki leków mogą wpływać:</t></is></c><c r="F914" s="2" t="inlineStr"><is><t>hipoproteinemia</t></is></c><c r="G914" s="2" t="inlineStr"><is><t>spadek masy wątroby</t></is></c><c r="H914" s="2" t="inlineStr" /><c r="I914" s="2" t="inlineStr" /><c r="J914" s="2" t="inlineStr" /><c r="K914" s="2" t="inlineStr"><is><t>zanik kosmków jelitowych</t></is></c><c r="L914" s="2" t="inlineStr"><is><t>obniżenie stężenia kwaśnej alfa-1 glikoproteiny a – prawdziwe odpowiedzi 1, 3 i 4 b – prawdziwe odpowiedzi 1 i 3 c – prawdziwe odpowiedzi 2 i 4 d – prawdziwa odpowiedź 4 e – wszystkie odpowiedzi prawdziwe</t></is></c><c r="M914" s="2" t="inlineStr" /><c r="N914" s="2" t="inlineStr" /><c r="O914" s="2" t="inlineStr" /><c r="P914" s="2" t="inlineStr"><is><t>EGZAMIN IWL 1 lutego 2016</t></is></c><c r="Q914" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="915"><c r="A915" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B915" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C915" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D915" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E915" s="2" t="inlineStr"><is><t>Przewlekłe stosowanie pantoprazolu:</t></is></c><c r="F915" s="2" t="inlineStr"><is><t>zwiększa ryzyko zakażeń dróg oddechowych</t></is></c><c r="G915" s="2" t="inlineStr"><is><t>zaburza wchłanianie wapnia z przewodu pokarmowego</t></is></c><c r="H915" s="2" t="inlineStr" /><c r="I915" s="2" t="inlineStr" /><c r="J915" s="2" t="inlineStr" /><c r="K915" s="2" t="inlineStr"><is><t>zmniejsza ryzyko złamania szyjki kości udowej</t></is></c><c r="L915" s="2" t="inlineStr"><is><t>zmniejsza działanie klopidogrelu → omeprazol inne działania po przewlekłym stosowaniu: wzrost ryzyka zakażeń układu pokarmowego, Clostrioides difficile,zapalenie jelita cienkiego, zaburzenia wchłaniania (Mg, Ca,Fe, Wit. B12), ostre śródmiąższowe zapalenie nerek, toczeń rumieniowaty, zanikowe zapalenie błony śluzowej żołądka</t></is></c><c r="M915" s="2" t="inlineStr" /><c r="N915" s="2" t="inlineStr" /><c r="O915" s="2" t="inlineStr" /><c r="P915" s="2" t="inlineStr"><is><t>EGZAMIN IWL 1 lutego 2016</t></is></c><c r="Q915" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="916"><c r="A916" s="2" t="inlineStr"><is><t>NADCIŚNIENIE TĘTNICZE</t></is></c><c r="B916" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C916" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D916" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E916" s="2" t="inlineStr"><is><t>W profilaktyce krwawienia z żylaków przełyku w przebiegu nadciśnienia wrotnego stosuje się:</t></is></c><c r="F916" s="2" t="inlineStr"><is><t>propranolol</t></is></c><c r="G916" s="2" t="inlineStr"><is><t>karwedilol a – prawdziwe odpowiedzi 1, 3 i 4 b – prawdziwe odpowiedzi 1 i 3 c – prawdziwe odpowiedzi 2 i 4 d – prawdziwa odpowiedź 4 e – wszystkie odpowiedzi prawdziwe</t></is></c><c r="H916" s="2" t="inlineStr" /><c r="I916" s="2" t="inlineStr" /><c r="J916" s="2" t="inlineStr" /><c r="K916" s="2" t="inlineStr"><is><t>doksazosynę</t></is></c><c r="L916" s="2" t="inlineStr"><is><t>klonidynę</t></is></c><c r="M916" s="2" t="inlineStr" /><c r="N916" s="2" t="inlineStr" /><c r="O916" s="2" t="inlineStr" /><c r="P916" s="2" t="inlineStr"><is><t>EGZAMIN IWL 1 lutego 2016</t></is></c><c r="Q916" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="917"><c r="A917" s="2" t="inlineStr"><is><t>NIEWYDOLNOŚĆ SERCA</t></is></c><c r="B917" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C917" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D917" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E917" s="2" t="inlineStr"><is><t>Digoksyna:</t></is></c><c r="F917" s="2" t="inlineStr"><is><t>zmniejsza aktywację układu współczulnego u osób z niewydolnością serca</t></is></c><c r="G917" s="2" t="inlineStr"><is><t>może sprzyjać wystąpieniu depresji</t></is></c><c r="H917" s="2" t="inlineStr"><is><t>jest stosowana w celu kontroli rytmu serca w utrwalonym migotaniu przedsionków</t></is></c><c r="I917" s="2" t="inlineStr"><is><t>może być nieskuteczna z powodu dezaktywacji przez bakterie jelitowe a – prawdziwe odpowiedzi 1, 3 i 4 b – prawdziwe odpowiedzi 1 i 3 c – prawdziwe odpowiedzi 2 i 4 d – prawdziwa odpowiedź 4 e – wszystkie odpowiedzi prawdziwe</t></is></c><c r="J917" s="2" t="inlineStr" /><c r="K917" s="2" t="inlineStr" /><c r="L917" s="2" t="inlineStr" /><c r="M917" s="2" t="inlineStr" /><c r="N917" s="2" t="inlineStr" /><c r="O917" s="2" t="inlineStr" /><c r="P917" s="2" t="inlineStr"><is><t>EGZAMIN IWL 1 lutego 2016</t></is></c><c r="Q917" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="918"><c r="A918" s="2" t="inlineStr"><is><t>NIEWYDOLNOŚĆ SERCA</t></is></c><c r="B918" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C918" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D918" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E918" s="2" t="inlineStr"><is><t>W niewydolności serca przeżycie chorych poprawia:</t></is></c><c r="F918" s="2" t="inlineStr"><is><t>eplerenon RAA z beta-adrenolitykami eplerenon/spironolakton</t></is></c><c r="G918" s="2" t="inlineStr" /><c r="H918" s="2" t="inlineStr" /><c r="I918" s="2" t="inlineStr" /><c r="J918" s="2" t="inlineStr" /><c r="K918" s="2" t="inlineStr"><is><t>atenolol</t></is></c><c r="L918" s="2" t="inlineStr"><is><t>tolwaptan</t></is></c><c r="M918" s="2" t="inlineStr"><is><t>digoksyna</t></is></c><c r="N918" s="2" t="inlineStr" /><c r="O918" s="2" t="inlineStr" /><c r="P918" s="2" t="inlineStr"><is><t>EGZAMIN IWL 1 lutego 2016</t></is></c><c r="Q918" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="919"><c r="A919" s="2" t="inlineStr"><is><t>ZABURZENIA RYTMU SERCA</t></is></c><c r="B919" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C919" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D919" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E919" s="2" t="inlineStr"><is><t>Amiodaron:</t></is></c><c r="F919" s="2" t="inlineStr"><is><t>obniża energię potrzebną do skutecznej defibrylacji elektrycznej</t></is></c><c r="G919" s="2" t="inlineStr"><is><t>jest stosowany alternatywnie z lidokainą w resuscytacji krążeniowo￾oddechowej</t></is></c><c r="H919" s="2" t="inlineStr"><is><t>może być rozpuszczany w 5% glukozie a – prawdziwe odpowiedzi 1, 3 i 4 b – prawdziwe odpowiedzi 1 i 3 c – prawdziwe odpowiedzi 2 i 4 d – prawdziwa odpowiedź 4 e – wszystkie odpowiedzi prawdziwe</t></is></c><c r="I919" s="2" t="inlineStr" /><c r="J919" s="2" t="inlineStr" /><c r="K919" s="2" t="inlineStr"><is><t>jest antagonistą sercowych kanałów potasowych z wyjątkiem Ikr</t></is></c><c r="L919" s="2" t="inlineStr" /><c r="M919" s="2" t="inlineStr" /><c r="N919" s="2" t="inlineStr" /><c r="O919" s="2" t="inlineStr" /><c r="P919" s="2" t="inlineStr"><is><t>EGZAMIN IWL 1 lutego 2016</t></is></c><c r="Q919" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="920"><c r="A920" s="2" t="inlineStr"><is><t>NADCIŚNIENIE TĘTNICZE</t></is></c><c r="B920" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C920" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D920" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E920" s="2" t="inlineStr"><is><t>W leczeniu nadciśnienia tętniczego przeciwwskazane jest połączenie:</t></is></c><c r="F920" s="2" t="inlineStr"><is><t>ramipryl + telmisartan inhibitory neprylizyny +inhibitory ACE inhibitory ACE + sartanami azotany +sandenafil/wardenafil Beta-adrenolityki + atagoniści kanałów wapniowych</t></is></c><c r="G920" s="2" t="inlineStr" /><c r="H920" s="2" t="inlineStr" /><c r="I920" s="2" t="inlineStr" /><c r="J920" s="2" t="inlineStr" /><c r="K920" s="2" t="inlineStr"><is><t>amlodypina + chlortalidon</t></is></c><c r="L920" s="2" t="inlineStr"><is><t>amlodypina + peryndopryl</t></is></c><c r="M920" s="2" t="inlineStr"><is><t>peryndopryl + indapamid</t></is></c><c r="N920" s="2" t="inlineStr" /><c r="O920" s="2" t="inlineStr" /><c r="P920" s="2" t="inlineStr"><is><t>EGZAMIN IWL 1 lutego 2016</t></is></c><c r="Q920" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="921"><c r="A921" s="2" t="inlineStr"><is><t>NADCIŚNIENIE TĘTNICZE</t></is></c><c r="B921" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C921" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D921" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E921" s="2" t="inlineStr"><is><t>Teoretyczną przesłanką stosowania inhibitorów konwertazy angiotensyny w przewlekłej skurczowej niewydolności serca jest:</t></is></c><c r="F921" s="2" t="inlineStr"><is><t>odwracanie włóknienia miokardium</t></is></c><c r="G921" s="2" t="inlineStr"><is><t>odwracanie przerostu kardiomiocytów</t></is></c><c r="H921" s="2" t="inlineStr"><is><t>korzystne bezpośrednie działanie hemodynamiczne Własnoręczny podpis Numer indeksu</t></is></c><c r="I921" s="2" t="inlineStr" /><c r="J921" s="2" t="inlineStr" /><c r="K921" s="2" t="inlineStr"><is><t>zwiększenie naprężenia ściany lewej komory</t></is></c><c r="L921" s="2" t="inlineStr" /><c r="M921" s="2" t="inlineStr" /><c r="N921" s="2" t="inlineStr" /><c r="O921" s="2" t="inlineStr" /><c r="P921" s="2" t="inlineStr"><is><t>EGZAMIN IWL 1 lutego 2016</t></is></c><c r="Q921" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="922"><c r="A922" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B922" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C922" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D922" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E922" s="2" t="inlineStr"><is><t>Klindamycyna:</t></is></c><c r="F922" s="2" t="inlineStr"><is><t>jest aktywna wobec beztlenowców I TLENOWE G +/// NA TLENOWE G- NIE! Oporność na nią to MLB – makrolidy Linozamidy i Streptogramin Często łączy się z betalaktamami, na infekcje, które produkują toksyny np. pyogenes/ zakażenia stawów i kości / trądzik / róża Na rzeżączkę – penicyliny naturalne/cefalosporyny III (ceftrazycym/ceftriakson) Zapalenie gardła rzeżączkowe – azytromycyna po i ceftriakson im</t></is></c><c r="G922" s="2" t="inlineStr" /><c r="H922" s="2" t="inlineStr" /><c r="I922" s="2" t="inlineStr" /><c r="J922" s="2" t="inlineStr" /><c r="K922" s="2" t="inlineStr"><is><t>dobrze przenika do płynu mózgowo-rdzeniowego wszędzie dobrze tylko nie do OUN</t></is></c><c r="L922" s="2" t="inlineStr"><is><t>słabo selekcjonuje szczepy Clostridium difficile w jelicie</t></is></c><c r="M922" s="2" t="inlineStr"><is><t>stosowana jest jako lek z wyboru w nierzeżączkowym zapaleniu cewki moczowej</t></is></c><c r="N922" s="2" t="inlineStr" /><c r="O922" s="2" t="inlineStr" /><c r="P922" s="2" t="inlineStr"><is><t>EGZAMIN IWL 25 stycznia 2017</t></is></c><c r="Q922" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="923"><c r="A923" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B923" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C923" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D923" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E923" s="2" t="inlineStr"><is><t>Wskaż prawdziwe połączenie lek – działania niepożądane:</t></is></c><c r="F923" s="2" t="inlineStr"><is><t>lewofloksacyna – drgawki/ zak clostridium difficile/ pęknięcia ścięgien/ wysypki /wydłużenia QT/fotosentyzacja/ zab oun / zaburzenia glikemii / zaburzenia szpiku</t></is></c><c r="G923" s="2" t="inlineStr"><is><t>ceftriakson – zagęszczenie żółci</t></is></c><c r="H923" s="2" t="inlineStr"><is><t>wankomycyna – zespół czerwonego karku/ niedościśnienie/ histamina/ nefrotoksyczność monitorowanie jeśli złe nerki/ słuchu/ szpiku</t></is></c><c r="I923" s="2" t="inlineStr"><is><t>linezolid – trombocytopenia/ zespół serotoninowy/neuropatie obwodowe/WASKIE SPEKTRUM/</t></is></c><c r="J923" s="2" t="inlineStr" /><c r="K923" s="2" t="inlineStr"><is><t>W celu zwiększenia bezpieczeństwa leczenia amikacyną mężczyzny z powikłanym zakażeniem układu moczowego należy:</t></is></c><c r="L923" s="2" t="inlineStr" /><c r="M923" s="2" t="inlineStr" /><c r="N923" s="2" t="inlineStr" /><c r="O923" s="2" t="inlineStr" /><c r="P923" s="2" t="inlineStr"><is><t>EGZAMIN IWL 25 stycznia 2017</t></is></c><c r="Q923" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="924"><c r="A924" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B924" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C924" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D924" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E924" s="2" t="inlineStr"><is><t>W leczeniu pacjentki z niepowikłanym zapaleniem pęcherza moczowego można zastosować:</t></is></c><c r="F924" s="2" t="inlineStr"><is><t>amoksycylinę z inhibitorem beta-laktamazy</t></is></c><c r="G924" s="2" t="inlineStr"><is><t>fosfomycynę</t></is></c><c r="H924" s="2" t="inlineStr"><is><t>cyprofloksacynę</t></is></c><c r="I924" s="2" t="inlineStr"><is><t>furazydynę + kotrimoksazol</t></is></c><c r="J924" s="2" t="inlineStr" /><c r="K924" s="2" t="inlineStr" /><c r="L924" s="2" t="inlineStr" /><c r="M924" s="2" t="inlineStr" /><c r="N924" s="2" t="inlineStr" /><c r="O924" s="2" t="inlineStr" /><c r="P924" s="2" t="inlineStr"><is><t>EGZAMIN IWL 25 stycznia 2017</t></is></c><c r="Q924" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="925"><c r="A925" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B925" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C925" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D925" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E925" s="2" t="inlineStr"><is><t>Lekiem przeciwbakteryjnym o wąskim zakresie działania przeciwbakteryjnego jest:</t></is></c><c r="F925" s="2" t="inlineStr"><is><t>fenoksymetylopenicylina</t></is></c><c r="G925" s="2" t="inlineStr"><is><t>nystatyna</t></is></c><c r="H925" s="2" t="inlineStr"><is><t>chloramfenikol WĄSKIE SPEKTRUM – • aminoglikozycy (tobramycyna/amikacyna) • linezolid/ • polimyksyny • daptomycyna • fidaksomycyna • nadtlenek benzoilu • flucytozyna • nystatyna SZEROKIE – • chinolony (-floksacyna) • Ryfaksymina • pochodne triazolowe (Azole) • amfoterycyna b • cyklopiroksoamina • iwermektyna(p-pasożytniczy) • ryfampicyna • Aminopenicyliny (ampi/amoksy) • Ureidopenicyliny – piperacylina • Karboksypenicyliny – tykarcylina – brak w PL</t></is></c><c r="I925" s="2" t="inlineStr" /><c r="J925" s="2" t="inlineStr" /><c r="K925" s="2" t="inlineStr"><is><t>aksetyl cefuroksymu</t></is></c><c r="L925" s="2" t="inlineStr" /><c r="M925" s="2" t="inlineStr" /><c r="N925" s="2" t="inlineStr" /><c r="O925" s="2" t="inlineStr" /><c r="P925" s="2" t="inlineStr"><is><t>EGZAMIN IWL 25 stycznia 2017</t></is></c><c r="Q925" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="926"><c r="A926" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B926" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C926" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D926" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E926" s="2" t="inlineStr"><is><t>Aktywność przeciwbakteryjną względem opornych na metycylinę szczepów Staphylococcus aureus (MRSA) ma:</t></is></c><c r="F926" s="2" t="inlineStr"><is><t>linezolid</t></is></c><c r="G926" s="2" t="inlineStr"><is><t>mupirocyna</t></is></c><c r="H926" s="2" t="inlineStr"><is><t>wankomycyna</t></is></c><c r="I926" s="2" t="inlineStr"><is><t>dalfoprystyna/chinuprystyna • cefalosporyny V generacji Ceftarolina Ceftobiprol Ceftolozan/tazobaktam • glikopeptydy – wankomycyna teikoplanina • glikolipopeptydy -dalbawancyna i oritowancyna – zakażenia skórne i tkanek miękkich nie laczyc z wanko • fosfomycyna • streptograminy • oksazolidynony – linezolid i tedyzolid • tygecyklina • kwas fusydowy i mupirocyna • delafloksacyna i ozenoksacyna • daptomycyna – off label • kotrimoksazol</t></is></c><c r="J926" s="2" t="inlineStr" /><c r="K926" s="2" t="inlineStr" /><c r="L926" s="2" t="inlineStr" /><c r="M926" s="2" t="inlineStr" /><c r="N926" s="2" t="inlineStr" /><c r="O926" s="2" t="inlineStr" /><c r="P926" s="2" t="inlineStr"><is><t>EGZAMIN IWL 25 stycznia 2017</t></is></c><c r="Q926" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="927"><c r="A927" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B927" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C927" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D927" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E927" s="2" t="inlineStr"><is><t>Profilaktyka infekcyjnego zapalenia wsierdzia (IZW) jest wskazana u osób z grup wysokiego ryzyka IZW w przypadku procedur:</t></is></c><c r="F927" s="2" t="inlineStr"><is><t>dentystycznych z manipulacją w obrębie dziąseł lub okolicy około￾wierzchołkowej zębów</t></is></c><c r="G927" s="2" t="inlineStr"><is><t>inwazyjnych w obrębie górnych dróg oddechowych, tj. usunięcie migdałka</t></is></c><c r="H927" s="2" t="inlineStr" /><c r="I927" s="2" t="inlineStr" /><c r="J927" s="2" t="inlineStr" /><c r="K927" s="2" t="inlineStr"><is><t>inwazyjnych w obrębie układu moczowo-płciowego</t></is></c><c r="L927" s="2" t="inlineStr"><is><t>inwazyjnych w obrębie przewodu pokarmowego LECZENIE IZW – aminoglikozydy – tobramycyna wankomycyna i teikopanina</t></is></c><c r="M927" s="2" t="inlineStr" /><c r="N927" s="2" t="inlineStr" /><c r="O927" s="2" t="inlineStr" /><c r="P927" s="2" t="inlineStr"><is><t>EGZAMIN IWL 25 stycznia 2017</t></is></c><c r="Q927" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="928"><c r="A928" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B928" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C928" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D928" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E928" s="2" t="inlineStr"><is><t>W standardowej profilaktyce okołooperacyjnej wskazane jeststosowanie:</t></is></c><c r="F928" s="2" t="inlineStr"><is><t>wankomycyny</t></is></c><c r="G928" s="2" t="inlineStr"><is><t>metronidazolu</t></is></c><c r="H928" s="2" t="inlineStr"><is><t>cyprofloksacyny</t></is></c><c r="I928" s="2" t="inlineStr"><is><t>cefazoliny • cefuroksym • klindamycyna • wankomycyna • gentamycyna • metronidazol</t></is></c><c r="J928" s="2" t="inlineStr" /><c r="K928" s="2" t="inlineStr" /><c r="L928" s="2" t="inlineStr" /><c r="M928" s="2" t="inlineStr" /><c r="N928" s="2" t="inlineStr" /><c r="O928" s="2" t="inlineStr" /><c r="P928" s="2" t="inlineStr"><is><t>EGZAMIN IWL 25 stycznia 2017</t></is></c><c r="Q928" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="929"><c r="A929" s="2" t="inlineStr"><is><t>LEKI PRZECIWGRZYBICZE</t></is></c><c r="B929" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C929" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D929" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E929" s="2" t="inlineStr"><is><t>W grzybiczym zakażeniu skóry gładkiej można zastosować miejscowo:</t></is></c><c r="F929" s="2" t="inlineStr"><is><t>cyklopiroksolaminę</t></is></c><c r="G929" s="2" t="inlineStr"><is><t>natamycynę</t></is></c><c r="H929" s="2" t="inlineStr"><is><t>klotrimazol • terbinafina • kwas undecylenowy</t></is></c><c r="I929" s="2" t="inlineStr" /><c r="J929" s="2" t="inlineStr" /><c r="K929" s="2" t="inlineStr"><is><t>kaspofunginę</t></is></c><c r="L929" s="2" t="inlineStr" /><c r="M929" s="2" t="inlineStr" /><c r="N929" s="2" t="inlineStr" /><c r="O929" s="2" t="inlineStr" /><c r="P929" s="2" t="inlineStr"><is><t>EGZAMIN IWL 25 stycznia 2017</t></is></c><c r="Q929" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="930"><c r="A930" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B930" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C930" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D930" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E930" s="2" t="inlineStr"><is><t>Wskaż poprawną strategię postępowania w zakresie leczenia zakażeń:</t></is></c><c r="F930" s="2" t="inlineStr"><is><t>leczenie empiryczne powinno uwzględniać miejsce powstania zakażenia: domowe lub związane z kontaktem ze służbą zdrowia</t></is></c><c r="G930" s="2" t="inlineStr"><is><t>na podstawie antybiogramu należy dokonać deeskalacji leczenia</t></is></c><c r="H930" s="2" t="inlineStr"><is><t>zasadą jest doustne leczenie przeciwinfekcyjne poza uzasadnionymi wyjątkami dekolonizacją MRSA przed operacjami</t></is></c><c r="I930" s="2" t="inlineStr" /><c r="J930" s="2" t="inlineStr" /><c r="K930" s="2" t="inlineStr" /><c r="L930" s="2" t="inlineStr" /><c r="M930" s="2" t="inlineStr" /><c r="N930" s="2" t="inlineStr" /><c r="O930" s="2" t="inlineStr" /><c r="P930" s="2" t="inlineStr"><is><t>EGZAMIN IWL 25 stycznia 2017</t></is></c><c r="Q930" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="931"><c r="A931" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B931" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C931" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D931" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E931" s="2" t="inlineStr"><is><t>W leczeniu trądziku młodzieńczego racjonalne jestzastosowanie:</t></is></c><c r="F931" s="2" t="inlineStr"><is><t>klindamycyny</t></is></c><c r="G931" s="2" t="inlineStr"><is><t>doksycykliny</t></is></c><c r="H931" s="2" t="inlineStr"><is><t>izotretinoiny • Makrolidy • Linkozamidy • Tetracykliny - CIĘŻKA POSTAĆ TRĄDZIKU POSPOLITEGO, WYWOŁYWANE PRZEZ WRAŻLIWE DROBNOUSTROJE (PROPIONIBACTERIUM ACNES, S. AUREUS) • Flutamid Bikalutamid Cyproteron – CIĘŻKA POSTAĆ ! • KERATOLITYCZNE : Kwas salicylowy 2-6% , Kwas mlekowy, glikolowy i związki siarki, mocznik 2-30% • retinol, tretinoina i jej izomer izotretinoina • etretinat i jego metabolit acitretyna • tazaroten retinoidy • adapalen</t></is></c><c r="I931" s="2" t="inlineStr" /><c r="J931" s="2" t="inlineStr" /><c r="K931" s="2" t="inlineStr"><is><t>norfloksacyny</t></is></c><c r="L931" s="2" t="inlineStr" /><c r="M931" s="2" t="inlineStr" /><c r="N931" s="2" t="inlineStr" /><c r="O931" s="2" t="inlineStr" /><c r="P931" s="2" t="inlineStr"><is><t>EGZAMIN IWL 25 stycznia 2017</t></is></c><c r="Q931" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="932"><c r="A932" s="2" t="inlineStr"><is><t>NIEOPIOIDOWE LEKI PRZECIWBÓLOWE</t></is></c><c r="B932" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C932" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D932" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E932" s="2" t="inlineStr"><is><t>Istotne genetycznie uwarunkowane różnice działania stwierdzono dla:</t></is></c><c r="F932" s="2" t="inlineStr"><is><t>abakawiru</t></is></c><c r="G932" s="2" t="inlineStr"><is><t>karbamazepiny</t></is></c><c r="H932" s="2" t="inlineStr"><is><t>warfaryny • kropidogrel • Celekoksyb • Diklofenak • Ibuprofen • Indometacyna • Ketoprofen • Meloksykam • Naproksen • Piroksykam • Kodeina •</t></is></c><c r="I932" s="2" t="inlineStr" /><c r="J932" s="2" t="inlineStr" /><c r="K932" s="2" t="inlineStr"><is><t>diltiazemu</t></is></c><c r="L932" s="2" t="inlineStr" /><c r="M932" s="2" t="inlineStr" /><c r="N932" s="2" t="inlineStr" /><c r="O932" s="2" t="inlineStr" /><c r="P932" s="2" t="inlineStr"><is><t>EGZAMIN IWL 25 stycznia 2017</t></is></c><c r="Q932" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="933"><c r="A933" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B933" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C933" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D933" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E933" s="2" t="inlineStr"><is><t>Inhibitory dipeptydylopeptydazy IV (DPP IV):</t></is></c><c r="F933" s="2" t="inlineStr"><is><t>mogą być stosowane łącznie z insuliną</t></is></c><c r="G933" s="2" t="inlineStr"><is><t>zwiększają ryzyko wystąpienia dolegliwości ze strony przewodu pokarmowego</t></is></c><c r="H933" s="2" t="inlineStr" /><c r="I933" s="2" t="inlineStr" /><c r="J933" s="2" t="inlineStr" /><c r="K933" s="2" t="inlineStr"><is><t>powodują przyrost masy ciała</t></is></c><c r="L933" s="2" t="inlineStr"><is><t>są podawane podskórnie • NIE hamują opróżniania żołądka</t></is></c><c r="M933" s="2" t="inlineStr" /><c r="N933" s="2" t="inlineStr" /><c r="O933" s="2" t="inlineStr" /><c r="P933" s="2" t="inlineStr"><is><t>EGZAMIN IWL 25 stycznia 2017</t></is></c><c r="Q933" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="934"><c r="A934" s="2" t="inlineStr"><is><t>CUKRZYCA</t></is></c><c r="B934" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C934" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D934" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E934" s="2" t="inlineStr"><is><t>Wskaż zdanie/zdania prawdziwe:</t></is></c><c r="F934" s="2" t="inlineStr"><is><t>empagliflozyna – zmniejsza ryzyko śmierci z przyczyn sercowo-naczyniowych u chorych z cukrzycą typu 2</t></is></c><c r="G934" s="2" t="inlineStr"><is><t>metformina – zmniejsza ryzyko powikłań makroangiopatycznych</t></is></c><c r="H934" s="2" t="inlineStr" /><c r="I934" s="2" t="inlineStr" /><c r="J934" s="2" t="inlineStr" /><c r="K934" s="2" t="inlineStr"><is><t>sitagliptyna - pomimo euglikemii może spowodować kwasicę ketonową TO FLOZYNY</t></is></c><c r="L934" s="2" t="inlineStr"><is><t>gliklazyd – powoduje redukcję masy ciała</t></is></c><c r="M934" s="2" t="inlineStr" /><c r="N934" s="2" t="inlineStr" /><c r="O934" s="2" t="inlineStr" /><c r="P934" s="2" t="inlineStr"><is><t>EGZAMIN IWL 25 stycznia 2017</t></is></c><c r="Q934" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="935"><c r="A935" s="2" t="inlineStr"><is><t>TARCZYCA</t></is></c><c r="B935" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C935" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D935" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E935" s="2" t="inlineStr"><is><t>Stosowanie tiamazolu może być przyczyną:</t></is></c><c r="F935" s="2" t="inlineStr"><is><t>żółtaczki cholestatycznej</t></is></c><c r="G935" s="2" t="inlineStr"><is><t>agranulocytozy</t></is></c><c r="H935" s="2" t="inlineStr"><is><t>wysypki skórnej</t></is></c><c r="I935" s="2" t="inlineStr"><is><t>niedoczynności tarczycy • Artralgia, • agranulocytoza (występuje w około 0,3-0,6% przypadków), • małopłytkowość, • pancytopenia ś • wiąd, wysypka, pokrzywka, • gorączka polekowa, • zaburzenia smaku, • ciężkie reakcje skórne, • toczeń rumieniowaty polekowy, • łysienie, • żółtaczka cholestatyczna, • toksyczne zapalenie wątrob</t></is></c><c r="J935" s="2" t="inlineStr" /><c r="K935" s="2" t="inlineStr" /><c r="L935" s="2" t="inlineStr" /><c r="M935" s="2" t="inlineStr" /><c r="N935" s="2" t="inlineStr" /><c r="O935" s="2" t="inlineStr" /><c r="P935" s="2" t="inlineStr"><is><t>EGZAMIN IWL 25 stycznia 2017</t></is></c><c r="Q935" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="936"><c r="A936" s="2" t="inlineStr"><is><t>GLIKOKORTYKOSTEROIDY</t></is></c><c r="B936" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C936" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D936" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E936" s="2" t="inlineStr"><is><t>Leczenie triamcynolonem może pogorszyć przebieg: - GKS</t></is></c><c r="F936" s="2" t="inlineStr"><is><t>jaskry</t></is></c><c r="G936" s="2" t="inlineStr"><is><t>zaburzeń nastroju</t></is></c><c r="H936" s="2" t="inlineStr"><is><t>zaćmy</t></is></c><c r="I936" s="2" t="inlineStr"><is><t>osteoporozy</t></is></c><c r="J936" s="2" t="inlineStr" /><c r="K936" s="2" t="inlineStr" /><c r="L936" s="2" t="inlineStr" /><c r="M936" s="2" t="inlineStr" /><c r="N936" s="2" t="inlineStr" /><c r="O936" s="2" t="inlineStr" /><c r="P936" s="2" t="inlineStr"><is><t>EGZAMIN IWL 25 stycznia 2017</t></is></c><c r="Q936" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="937"><c r="A937" s="2" t="inlineStr"><is><t>OSTEOPOROZA</t></is></c><c r="B937" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C937" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D937" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E937" s="2" t="inlineStr"><is><t>Potwierdzone klinicznie zmniejszenie ryzyka złamania kości udowej w przebiegu osteoporozy występuje w wyniku leczenia:</t></is></c><c r="F937" s="2" t="inlineStr"><is><t>ranelinianem strontu</t></is></c><c r="G937" s="2" t="inlineStr"><is><t>kwasem ibandronowym</t></is></c><c r="H937" s="2" t="inlineStr" /><c r="I937" s="2" t="inlineStr" /><c r="J937" s="2" t="inlineStr" /><c r="K937" s="2" t="inlineStr"><is><t>Raloksyfenem</t></is></c><c r="L937" s="2" t="inlineStr"><is><t>kalcytoniną</t></is></c><c r="M937" s="2" t="inlineStr" /><c r="N937" s="2" t="inlineStr" /><c r="O937" s="2" t="inlineStr" /><c r="P937" s="2" t="inlineStr"><is><t>EGZAMIN IWL 25 stycznia 2017</t></is></c><c r="Q937" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="938"><c r="A938" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B938" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C938" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D938" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E938" s="2" t="inlineStr"><is><t>Witamina D3 (cholekalcyferol):</t></is></c><c r="F938" s="2" t="inlineStr"><is><t>może być stosowana w niedoczynności przytarczyc</t></is></c><c r="G938" s="2" t="inlineStr"><is><t>w nadmiarze hamuje wzrost kości</t></is></c><c r="H938" s="2" t="inlineStr" /><c r="I938" s="2" t="inlineStr" /><c r="J938" s="2" t="inlineStr" /><c r="K938" s="2" t="inlineStr"><is><t>mimo stosowania w dużych dawkach nie chroni przed osteoporotycznymi złamaniami kości</t></is></c><c r="L938" s="2" t="inlineStr"><is><t>jest nieaktywna u chorych z niewydolnością nerek – chyba chodziło o wątrobę</t></is></c><c r="M938" s="2" t="inlineStr" /><c r="N938" s="2" t="inlineStr" /><c r="O938" s="2" t="inlineStr" /><c r="P938" s="2" t="inlineStr"><is><t>EGZAMIN IWL 25 stycznia 2017</t></is></c><c r="Q938" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="939"><c r="A939" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B939" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C939" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D939" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E939" s="2" t="inlineStr"><is><t>Aby zmniejszyć efekty gastrotoksyczne naproksenu zalecane jeststosowanie:</t></is></c><c r="F939" s="2" t="inlineStr"><is><t>omeprazolu</t></is></c><c r="G939" s="2" t="inlineStr" /><c r="H939" s="2" t="inlineStr" /><c r="I939" s="2" t="inlineStr" /><c r="J939" s="2" t="inlineStr" /><c r="K939" s="2" t="inlineStr"><is><t>laktulozy</t></is></c><c r="L939" s="2" t="inlineStr"><is><t>cytrynianu potasowo-bizmutowego</t></is></c><c r="M939" s="2" t="inlineStr"><is><t>węglanu wapnia</t></is></c><c r="N939" s="2" t="inlineStr" /><c r="O939" s="2" t="inlineStr" /><c r="P939" s="2" t="inlineStr"><is><t>EGZAMIN IWL 25 stycznia 2017</t></is></c><c r="Q939" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="940"><c r="A940" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B940" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C940" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D940" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E940" s="2" t="inlineStr"><is><t>W zespole abstynencji w zależności od opioidów występują:</t></is></c><c r="F940" s="2" t="inlineStr"><is><t>wyciek z nosa i łzawienie</t></is></c><c r="G940" s="2" t="inlineStr"><is><t>bóle mięśniowe</t></is></c><c r="H940" s="2" t="inlineStr"><is><t>wymioty i biegunka • dysforia • nudności, wymioty, biegunka • bóle mięśni • łzawienie, wyciek z nosa, pocenie • rozszerzenie źrenic • piloerekcja • ziewanie • gorączka</t></is></c><c r="I940" s="2" t="inlineStr" /><c r="J940" s="2" t="inlineStr" /><c r="K940" s="2" t="inlineStr"><is><t>zwężenie źrenic</t></is></c><c r="L940" s="2" t="inlineStr" /><c r="M940" s="2" t="inlineStr" /><c r="N940" s="2" t="inlineStr" /><c r="O940" s="2" t="inlineStr" /><c r="P940" s="2" t="inlineStr"><is><t>EGZAMIN IWL 25 stycznia 2017</t></is></c><c r="Q940" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="941"><c r="A941" s="2" t="inlineStr"><is><t>NIEOPIOIDOWE LEKI PRZECIWBÓLOWE</t></is></c><c r="B941" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C941" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D941" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E941" s="2" t="inlineStr"><is><t>Tryptany w leczeniu migreny:</t></is></c><c r="F941" s="2" t="inlineStr"><is><t>mogą być stosowane doustnie</t></is></c><c r="G941" s="2" t="inlineStr"><is><t>różnią się szybkością działania</t></is></c><c r="H941" s="2" t="inlineStr"><is><t>mogą być łączone z niesteroidowymi lekami przeciwzapalnymi o Można stosować max 9 dni w miesciącu - potem ryzyko bólu głowy o Połązcenie z NLPZ daje dobrą poprawę o Skuteczna jest 2 dawka</t></is></c><c r="I941" s="2" t="inlineStr" /><c r="J941" s="2" t="inlineStr" /><c r="K941" s="2" t="inlineStr"><is><t>należy podawać wyłącznie w fazie aury</t></is></c><c r="L941" s="2" t="inlineStr" /><c r="M941" s="2" t="inlineStr" /><c r="N941" s="2" t="inlineStr" /><c r="O941" s="2" t="inlineStr" /><c r="P941" s="2" t="inlineStr"><is><t>EGZAMIN IWL 25 stycznia 2017</t></is></c><c r="Q941" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="942"><c r="A942" s="2" t="inlineStr"><is><t>ZNIECZULENIA MIEJSCOWE</t></is></c><c r="B942" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C942" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D942" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E942" s="2" t="inlineStr"><is><t>Do leków znieczulających miejscowo stosowanych na błony śluzowe należy:</t></is></c><c r="F942" s="2" t="inlineStr"><is><t>prylokaina</t></is></c><c r="G942" s="2" t="inlineStr"><is><t>lidokaina ZNIECZULENIE MIEJSCOWE aminoestry – • tetrakaina, • prokaina, • chloroprokaina aminoamidy • (lidokaina, • prylokaina, • mepiwakaina • bupiwakaina, • etydokaina, • ropiwakaina</t></is></c><c r="H942" s="2" t="inlineStr" /><c r="I942" s="2" t="inlineStr" /><c r="J942" s="2" t="inlineStr" /><c r="K942" s="2" t="inlineStr"><is><t>chlorek etylu</t></is></c><c r="L942" s="2" t="inlineStr"><is><t>kapsaicyna</t></is></c><c r="M942" s="2" t="inlineStr" /><c r="N942" s="2" t="inlineStr" /><c r="O942" s="2" t="inlineStr" /><c r="P942" s="2" t="inlineStr"><is><t>EGZAMIN IWL 25 stycznia 2017</t></is></c><c r="Q942" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="943"><c r="A943" s="2" t="inlineStr"><is><t>LEKI PRZECIWDEPRESYJNE</t></is></c><c r="B943" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C943" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D943" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E943" s="2" t="inlineStr"><is><t>Lekiem stosowanym w neuropatii popółpaścowej jest:</t></is></c><c r="F943" s="2" t="inlineStr"><is><t>amitryptylina</t></is></c><c r="G943" s="2" t="inlineStr"><is><t>pregabalina</t></is></c><c r="H943" s="2" t="inlineStr"><is><t>lidokaina</t></is></c><c r="I943" s="2" t="inlineStr"><is><t>gabapentyna BÓLE NEUROPATYCZNE : • przeciwdepresyjne (wenlafaksyna, duloksetyna, amitryptylina) • przeciwpadaczkowe (gabapentyna, pregabalina) • Lidokaina (ból związany z przeczulicą) • Kapsaicyna • Opioidy (w dużych dawkach)</t></is></c><c r="J943" s="2" t="inlineStr" /><c r="K943" s="2" t="inlineStr" /><c r="L943" s="2" t="inlineStr" /><c r="M943" s="2" t="inlineStr" /><c r="N943" s="2" t="inlineStr" /><c r="O943" s="2" t="inlineStr" /><c r="P943" s="2" t="inlineStr"><is><t>EGZAMIN IWL 25 stycznia 2017</t></is></c><c r="Q943" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="944"><c r="A944" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B944" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C944" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D944" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E944" s="2" t="inlineStr"><is><t>Wskaż prawidłowy lek przeciwzakrzepowego u osoby z:</t></is></c><c r="F944" s="2" t="inlineStr"><is><t>zapaleniem żył głębokich – rywaroksaban i zatorowość płucna wgl noac to są refundowane w tych wskazaniach wszystkie i gatran i ksabany</t></is></c><c r="G944" s="2" t="inlineStr"><is><t>ciążą - enoksaparyna</t></is></c><c r="H944" s="2" t="inlineStr"><is><t>mechaniczną zastawką serca – warfaryna</t></is></c><c r="I944" s="2" t="inlineStr" /><c r="J944" s="2" t="inlineStr" /><c r="K944" s="2" t="inlineStr"><is><t>niewydolnością nerek (CCr &lt;30ml/min) – dabigatran – NIE</t></is></c><c r="L944" s="2" t="inlineStr" /><c r="M944" s="2" t="inlineStr" /><c r="N944" s="2" t="inlineStr" /><c r="O944" s="2" t="inlineStr" /><c r="P944" s="2" t="inlineStr"><is><t>EGZAMIN IWL 25 stycznia 2017</t></is></c><c r="Q944" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="945"><c r="A945" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B945" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C945" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D945" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E945" s="2" t="inlineStr"><is><t>Na istotnie zmniejszoną skuteczność doustnych antagonistów witaminy K może mieć wpływ spożywanie:</t></is></c><c r="F945" s="2" t="inlineStr"><is><t>szpina</t></is></c><c r="G945" s="2" t="inlineStr" /><c r="H945" s="2" t="inlineStr" /><c r="I945" s="2" t="inlineStr" /><c r="J945" s="2" t="inlineStr" /><c r="K945" s="2" t="inlineStr"><is><t>oleju rybnego zawierającego nienasycone kwasy tłuszczowe omega -3</t></is></c><c r="L945" s="2" t="inlineStr"><is><t>witaminy E – nasila</t></is></c><c r="M945" s="2" t="inlineStr"><is><t>czosnku – nasila</t></is></c><c r="N945" s="2" t="inlineStr" /><c r="O945" s="2" t="inlineStr" /><c r="P945" s="2" t="inlineStr"><is><t>EGZAMIN IWL 25 stycznia 2017</t></is></c><c r="Q945" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="946"><c r="A946" s="2" t="inlineStr"><is><t>LEKI HIPOLIPEMIZUJĄCE</t></is></c><c r="B946" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C946" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D946" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E946" s="2" t="inlineStr"><is><t>Fenofibrat:</t></is></c><c r="F946" s="2" t="inlineStr"><is><t>zmniejsza stężenie trójglicerydów i zwiększa stężenie cholesterolu HDL</t></is></c><c r="G946" s="2" t="inlineStr"><is><t>zwiększa ryzyko kamicy pęcherzyka żółciowego</t></is></c><c r="H946" s="2" t="inlineStr" /><c r="I946" s="2" t="inlineStr" /><c r="J946" s="2" t="inlineStr" /><c r="K946" s="2" t="inlineStr"><is><t>hamuje reduktazę 3-hydroksy-3-metyloglutarylo-CoA (HMG-CoA)</t></is></c><c r="L946" s="2" t="inlineStr"><is><t>nie może być stosowany w połączeniu ze statyną – fenofibrat i bezafibrat można, zwykłych fibratów nie można</t></is></c><c r="M946" s="2" t="inlineStr" /><c r="N946" s="2" t="inlineStr" /><c r="O946" s="2" t="inlineStr" /><c r="P946" s="2" t="inlineStr"><is><t>EGZAMIN IWL 25 stycznia 2017</t></is></c><c r="Q946" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="947"><c r="A947" s="2" t="inlineStr"><is><t>NADCIŚNIENIE TĘTNICZE</t></is></c><c r="B947" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C947" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D947" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E947" s="2" t="inlineStr"><is><t>Hiperurykemię może spowodować:</t></is></c><c r="F947" s="2" t="inlineStr"><is><t>torasemid</t></is></c><c r="G947" s="2" t="inlineStr"><is><t>kwas acetylosalicylowy HIPERURYKEMIA – powodują • Diuretyki • Inh reniny - aliskiren • Cyklosporyna – inh kalcyneuryny • Statyny – przy rabdomiolizie • Cytotoksyczne bo zespół lizy guza • Pyrazynamid – na gruźlice</t></is></c><c r="H947" s="2" t="inlineStr" /><c r="I947" s="2" t="inlineStr" /><c r="J947" s="2" t="inlineStr" /><c r="K947" s="2" t="inlineStr"><is><t>Losartan – jedyny z sartanów zmniejsza stężenie kwasu moczowego ! inne nic nie robią</t></is></c><c r="L947" s="2" t="inlineStr"><is><t>allopurynol</t></is></c><c r="M947" s="2" t="inlineStr" /><c r="N947" s="2" t="inlineStr" /><c r="O947" s="2" t="inlineStr" /><c r="P947" s="2" t="inlineStr"><is><t>EGZAMIN IWL 25 stycznia 2017</t></is></c><c r="Q947" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="948"><c r="A948" s="2" t="inlineStr"><is><t>LEKI PRZECIWPSYCHOTYCZNE</t></is></c><c r="B948" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C948" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D948" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E948" s="2" t="inlineStr"><is><t>Odstęp QT mogą wydłużać:</t></is></c><c r="F948" s="2" t="inlineStr"><is><t>propranolol</t></is></c><c r="G948" s="2" t="inlineStr"><is><t>diltiazem • metadon • atomoksetyna • modafinil • Leki p/c histaminowe Hydroksyzyna Difenhydramina • Neuroleptyki Typowe: Chlorpromazyna Fenotiazyna Tiorydazyna Flufenazyna Tioksanten Butyrofenon Haloperidol • Atypowe: SDA–antagoniści dopaminy i serotoniny Risperidon, Sertindol, Ziprasidon • MARTA –multiacting –receptortargetedantipsychotics Klozapina, Kwetiapina, Olanzapina • Antagoniści receptorów D2 i D3 Amisulpryd, Sulpiryd • Częściowy agonista receptora D2 Arypiprazol • P- wymiotne Antagoniści receptorów 5 HT3 Ondasetron Palonosetron • Klarytromycyna • Chinolony I generacja Kwas nalidyksowy (brak w Polsce) • II generacja Norfloksacyna Ofloksacyna Pefloksacyna Cyprofloksacyna • III generacja Lewofloksacyna • IV generacja Moksyfloksacyna Prulifloksacyna Delafloksacyna Ozenoksacyna • Azole • Metoklopramid • Cyzapryd • Beta – andrenomimetyki Długodziałające, wziewne: Salmeterol Formoterol Indakaterol (POChP) Wilanterol • Ranolazyna • Amiodaron/ Sotalol / Bretylium III generacja antyarytmiczne • II GENERACJA P-ALERGICZNYCH : Loratadyna Cetyryzyna Lewokabastyna Bilastyna Rupatadyna • Bedakilina lek na gruźlice</t></is></c><c r="H948" s="2" t="inlineStr" /><c r="I948" s="2" t="inlineStr" /><c r="J948" s="2" t="inlineStr" /><c r="K948" s="2" t="inlineStr"><is><t>amiodaron</t></is></c><c r="L948" s="2" t="inlineStr"><is><t>sotalol</t></is></c><c r="M948" s="2" t="inlineStr" /><c r="N948" s="2" t="inlineStr" /><c r="O948" s="2" t="inlineStr" /><c r="P948" s="2" t="inlineStr"><is><t>EGZAMIN IWL 25 stycznia 2017</t></is></c><c r="Q948" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="949"><c r="A949" s="2" t="inlineStr"><is><t>LEKI PRZECIWPASOŻYTNICZE</t></is></c><c r="B949" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C949" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D949" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E949" s="2" t="inlineStr"><is><t>W leczeniu zarażenia glistą ludzką stosujemy:</t></is></c><c r="F949" s="2" t="inlineStr"><is><t>pyrantel</t></is></c><c r="G949" s="2" t="inlineStr"><is><t>albendazol PASOŻYTY WESZ LUDZKA i ŁONOWA Pediculus humanus Phthirius pubis • • Heksachlorocykloheksan (Lindan – kontaktowy środek owado- i roztoczobójczy, nie niszczy gnid, znaczna toksyczność, neuro!) • Tiocyjanooktan izobornylu – niszczy wszy i gnidy (miejscowo 5% emulsja) • Benzoesan benzyl • Permetryna (insektycyd działający na kanały sodowe, należący do grupy piretroidów) • Syntetyczny olej silikonowy (dimetikon) Toxoplasma gondii • pirymetamina + sulfadiazyna + kwas folinowy (P+S+KF), sulfadoksyna, klindamycyna • kotrymoksazol - nie stosować pirymetaminy razem z kotrymoksazolem (depresja szpiku kostnego) • spiramycyna profilaktycznie (ostra toksoplazma w ciąży) • inwazja płodu: po 12-14 tygodniu ciąży P+S+KF (też u noworodka po urodzeniu) Trichomonas vaginalis – rzęsistek pochwowy ▪ Metronidazol ▪ Tinidazol glista ludzka, tęgoryjec: • albendazol, • mebendazol, • pyrantel, • iwermektyna węgorek jelitowy: ▪ iwermektyna, ▪ tiabendazol, ▪ albendazol owsik: • pyrantel, • mebendazol, • albendazo Tasiemce – • prazykwantel, • niklozamid</t></is></c><c r="H949" s="2" t="inlineStr" /><c r="I949" s="2" t="inlineStr" /><c r="J949" s="2" t="inlineStr" /><c r="K949" s="2" t="inlineStr"><is><t>tynidazol</t></is></c><c r="L949" s="2" t="inlineStr"><is><t>krotamiton</t></is></c><c r="M949" s="2" t="inlineStr" /><c r="N949" s="2" t="inlineStr" /><c r="O949" s="2" t="inlineStr" /><c r="P949" s="2" t="inlineStr"><is><t>EGZAMIN IWL 25 stycznia 2017</t></is></c><c r="Q949" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="950"><c r="A950" s="2" t="inlineStr"><is><t>LEKI PRZECIWWIRUSOWE</t></is></c><c r="B950" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C950" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D950" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E950" s="2" t="inlineStr"><is><t>W leczeniu grypy zaleca się:</t></is></c><c r="F950" s="2" t="inlineStr"><is><t>zanamiwir</t></is></c><c r="G950" s="2" t="inlineStr"><is><t>oseltamiwir</t></is></c><c r="H950" s="2" t="inlineStr"><is><t>foskarnet GRYPA • Inhibitory neuraminidazy: oseltamiwir, zanamiwir, panamiwir • amantadyna, rymantadyna • rybawiryna</t></is></c><c r="I950" s="2" t="inlineStr" /><c r="J950" s="2" t="inlineStr" /><c r="K950" s="2" t="inlineStr"><is><t>acyklowir</t></is></c><c r="L950" s="2" t="inlineStr" /><c r="M950" s="2" t="inlineStr" /><c r="N950" s="2" t="inlineStr" /><c r="O950" s="2" t="inlineStr" /><c r="P950" s="2" t="inlineStr"><is><t>EGZAMIN IWL 25 stycznia 2017</t></is></c><c r="Q950" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="951"><c r="A951" s="2" t="inlineStr"><is><t>UKŁAD PRZYWSPÓŁCZULNY</t></is></c><c r="B951" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C951" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D951" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E951" s="2" t="inlineStr"><is><t>Bromek glikopironium :</t></is></c><c r="F951" s="2" t="inlineStr"><is><t>wykazuje synergizm działania bronchodylatacyjnego z indakaterolem</t></is></c><c r="G951" s="2" t="inlineStr"><is><t>jest stosowany w leczeniu podtrzymującym w POChP Cholinolityki Bromek ipratropium (doraźnie) Bromek tiotropium (astma/POChP) Bromek glikopironium (POChP) Bromek umeklidynium (POChP) Bromek aklidynium</t></is></c><c r="H951" s="2" t="inlineStr" /><c r="I951" s="2" t="inlineStr" /><c r="J951" s="2" t="inlineStr" /><c r="K951" s="2" t="inlineStr"><is><t>jest wziewnym agonistą receptorów muskarynowych</t></is></c><c r="L951" s="2" t="inlineStr"><is><t>rozszczepia wiązania disiarczkowe w glikoproteinach śluzu</t></is></c><c r="M951" s="2" t="inlineStr" /><c r="N951" s="2" t="inlineStr" /><c r="O951" s="2" t="inlineStr" /><c r="P951" s="2" t="inlineStr"><is><t>EGZAMIN IWL 25 stycznia 2017</t></is></c><c r="Q951" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="952"><c r="A952" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B952" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C952" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D952" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E952" s="2" t="inlineStr"><is><t>W leczeniu przewlekłego zapalenia trzustki celowe może być zastosowanie:</t></is></c><c r="F952" s="2" t="inlineStr"><is><t>suplementacji enzymów trzustkowych</t></is></c><c r="G952" s="2" t="inlineStr"><is><t>pantoprazolu</t></is></c><c r="H952" s="2" t="inlineStr"><is><t>fluoksetyny Pankreatyna</t></is></c><c r="I952" s="2" t="inlineStr" /><c r="J952" s="2" t="inlineStr" /><c r="K952" s="2" t="inlineStr"><is><t>tramadolu</t></is></c><c r="L952" s="2" t="inlineStr" /><c r="M952" s="2" t="inlineStr" /><c r="N952" s="2" t="inlineStr" /><c r="O952" s="2" t="inlineStr" /><c r="P952" s="2" t="inlineStr"><is><t>EGZAMIN IWL 25 stycznia 2017</t></is></c><c r="Q952" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="953"><c r="A953" s="2" t="inlineStr"><is><t>LEKI PRZECIWPASOŻYTNICZE</t></is></c><c r="B953" s="2" t="inlineStr"><is><t>Sposób podania</t></is></c><c r="C953" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D953" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E953" s="2" t="inlineStr"><is><t>Profilaktyka przeciwmalaryczna w warunkach wysokiego ryzyka zakażenia Plasmodium falciparum obejmuje stosowanie:</t></is></c><c r="F953" s="2" t="inlineStr"><is><t>repelentów</t></is></c><c r="G953" s="2" t="inlineStr"><is><t>atowakwonu/proguanilu</t></is></c><c r="H953" s="2" t="inlineStr"><is><t>doksycykliny Profilaktyka Bardzo małe/małe ryzyko: (1) Chemioprofilaktyka nie jest rekomendowana, ale zaleca się ochronę przeciwkomarową i rozważenie leczenia przeciwmalarycznego w razie wystąpienia gorączki Małe ryzyko: (2) • Chlorochina Umiarkowane ryzyko: (3) • proguanil z chlorochiną Wysokie ryzyko: (4) • proguanil z atowakwonem lub • doksycyklina lub • meflochina Wysokie ryzyko z opornością na meflochinę: (5) (Kambodża, Laos, Myanmar, Wietnam) • proguanil z atowakwonem lub • doksycyklina Wysokie ryzyko i duża oporność na chlorochinę: • proguanil z atowakwonem (Malarone) lub • doksycyklina lub • meflochina Leczenie malarii Leczenie rozpocząć jak najwcześniej Poszukiwać pomocy lekarskiej w czasie pobytu na terenie endemicznym (nie czekać na powrót do kraju) Zalecane terapie: • Atowakwon-proguanil (doustnie) • Artemeter-lumefantrin (doustnie) • Chinina – głównie parenteralnie jako leczenie ciężkiej malarii powikłanej</t></is></c><c r="I953" s="2" t="inlineStr" /><c r="J953" s="2" t="inlineStr" /><c r="K953" s="2" t="inlineStr"><is><t>artemetru/lumefantryny</t></is></c><c r="L953" s="2" t="inlineStr" /><c r="M953" s="2" t="inlineStr" /><c r="N953" s="2" t="inlineStr" /><c r="O953" s="2" t="inlineStr" /><c r="P953" s="2" t="inlineStr"><is><t>EGZAMIN IWL 25 stycznia 2017</t></is></c><c r="Q953" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="954"><c r="A954" s="2" t="inlineStr"><is><t>CUKRZYCA</t></is></c><c r="B954" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C954" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D954" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E954" s="2" t="inlineStr"><is><t>Farmakoterapię otyłości należy rozważyć, gdy:</t></is></c><c r="F954" s="2" t="inlineStr"><is><t>BMI&gt; 27 kg/m2 i glikemia na czczo &gt;100mg/dl</t></is></c><c r="G954" s="2" t="inlineStr"><is><t>BMI≥ 30 kg/m2 i stwierdzono ponowny wzrost masy ciała pomimo wdrożonych procedur niefarmakologicznych</t></is></c><c r="H954" s="2" t="inlineStr"><is><t>BMI&gt; 27 kg/m2 i SBP ≥160 mmHg Kiedy rozpocząć? • BMI≥ 30 kg/m2 a terapia dietetyczna skojarzona z behawioralną i ćwiczeniami fizycznymi spowodowała redukcję masy ciała mniejszą niż 5 kg lub też występuje ponowny wzrost masy ciała. • BMI &gt; 27 kg/m2 wraz z dodatkowymi czynnikami ryzyka związanymi z otyłością Czynniki ryzyka: nadciśnienie, cukrzyca typ 2, dyslipidemia, choroby układu krążenia, zespół bezdechu sennego</t></is></c><c r="I954" s="2" t="inlineStr" /><c r="J954" s="2" t="inlineStr" /><c r="K954" s="2" t="inlineStr"><is><t>BMI≥ 30 kg/m2, a wcześniejsze procedury niefarmakologiczne spowodowały redukcję masy ciała w przedziale 7-10 kg</t></is></c><c r="L954" s="2" t="inlineStr" /><c r="M954" s="2" t="inlineStr" /><c r="N954" s="2" t="inlineStr" /><c r="O954" s="2" t="inlineStr" /><c r="P954" s="2" t="inlineStr"><is><t>EGZAMIN IWL 25 stycznia 2017</t></is></c><c r="Q954" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="955"><c r="A955" s="2" t="inlineStr"><is><t>LEKI PRZECIWPSYCHOTYCZNE</t></is></c><c r="B955" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C955" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D955" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E955" s="2" t="inlineStr"><is><t>Wzrost masy ciała mogą spowodować:</t></is></c><c r="F955" s="2" t="inlineStr"><is><t>chlorpromazyna</t></is></c><c r="G955" s="2" t="inlineStr"><is><t>insulina</t></is></c><c r="H955" s="2" t="inlineStr"><is><t>kwas walproinowy • neuroleptyki: pochodne fenotiazyny (chlorpromazyna) i butyrofenonu (haloperidol), klozapina, olanzapina, rysperydon, kwetiapina • leki przeciwdepresyjne: sole litu, TLPD, IMAO, mirtazapina, paroksetyna • leki przeciwpadaczkowe: pochodne kwasu walproinowego, karbamazepina, gabapentyna, • steroidy: glikokortykosteroidy, • leki hipoglikemizujące: insulina, pochodne sulfonylomocznika, - • leki przeciwhistaminowe: difenhydramina</t></is></c><c r="I955" s="2" t="inlineStr" /><c r="J955" s="2" t="inlineStr" /><c r="K955" s="2" t="inlineStr"><is><t>liraglutyd</t></is></c><c r="L955" s="2" t="inlineStr" /><c r="M955" s="2" t="inlineStr" /><c r="N955" s="2" t="inlineStr" /><c r="O955" s="2" t="inlineStr" /><c r="P955" s="2" t="inlineStr"><is><t>EGZAMIN IWL 25 stycznia 2017</t></is></c><c r="Q955" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="956"><c r="A956" s="2" t="inlineStr"><is><t>NARKOTYCZNE LEKI PRZECIWBÓLOWE</t></is></c><c r="B956" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C956" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D956" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E956" s="2" t="inlineStr"><is><t>Który z leków istotnie zwiększa ryzyko napadów drgawkowych:</t></is></c><c r="F956" s="2" t="inlineStr"><is><t>tramadol</t></is></c><c r="G956" s="2" t="inlineStr"><is><t>amitryptylina</t></is></c><c r="H956" s="2" t="inlineStr"><is><t>prometazyna • izoniazyd • rezerpina • karbapenemy • penicyliny naturalne i cefalosporyny I gen – w dużych dawkach • chinolony (-floksacyna) • worykonazol • Echinokandyny Kaspofungina (iv) Anidulafungina (iv) Mykafungina (iv) • Flucytozyna • Buflomedyl – już nie stosujemy choroby obwodowych naczyń krwionoś. • Ranelinian strontu • Inhibitory acetylocholinesterazy Donepezil Rywastygmina Galantamina • Acyklowir • Cholinomimetyki jeśli zrobią przełom • Silne opioidy: Morfina, oksykodon, fentanyl, metadon, buprenorfina, tapentadol • Słabe opioidy: Tramadol, dihydrokodeina, kodeina • Inhibitory kalcyneuryny Cyklosporyna (CsA) Takrolimus (TAC) Pimekrolimus • TLPD - Nieselektywne inhibitory wychwytu zwrotnego NA, 5-HT i DA - Klomipramina (Anafranil) - Nortryptylina (Pamelor) - Imipramina (Tofranil) - Amitryptylina (Elavil) - Desipramina (Norpramin) - Doksepina (Sinequan) - Protryptylina (Vivactil) - Maprotylina (Ludiomil) - Amoksapina (Ascendin) - Trimipramina (Surmontil) - Dibenzepina – Lofepramina • NASSA – leki działające głównie receptorowo na układ NA i 5-HT Mirtazapina Mianseryna • SOLE LITU • Neuroleptyki Typowe: Chlorpromazyna Fenotiazyna Tiorydazyna Flufenazyna Tioksanten Butyrofenon Haloperidol • KLOZAPINA Leki przeciwhistaminowe doustne I generacja • Cyproheptadyna-tabletki • Hydroksyzyna-syrop, tabletki, roztwór do inj. • Prometazyna- drażetki, syrop tietylperazyna tabletki, roztwór do inj., czopki • klemastyna tabletki, syrop, roztwór do inj. • dimetynden - krople doustne, żel, z fenylefryną aerozol do nosa • chlorfenamina- preparat z paracetamolem i pseudoefryną - tabletki • difenhydramina – tabletki, preparat z nafazolinąkrople do oczu/nosa lub paracetamolem tabletki antazolina –roztwór do inj • ketotifen-tabletki, syrop, krople do oczu</t></is></c><c r="I956" s="2" t="inlineStr" /><c r="J956" s="2" t="inlineStr" /><c r="K956" s="2" t="inlineStr"><is><t>klorazepan</t></is></c><c r="L956" s="2" t="inlineStr" /><c r="M956" s="2" t="inlineStr" /><c r="N956" s="2" t="inlineStr" /><c r="O956" s="2" t="inlineStr" /><c r="P956" s="2" t="inlineStr"><is><t>EGZAMIN IWL 25 stycznia 2017</t></is></c><c r="Q956" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="957"><c r="A957" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B957" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C957" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D957" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E957" s="2" t="inlineStr"><is><t>Wskazaniem do stosowania retinolu jest:</t></is></c><c r="F957" s="2" t="inlineStr"><is><t>łuszczyca</t></is></c><c r="G957" s="2" t="inlineStr"><is><t>niedowidzenie o zmierzchu • Łuszczyca • Trądzik • Rybia łuska • Rogowacenie przymieszkowe • Brodawki płaskie</t></is></c><c r="H957" s="2" t="inlineStr" /><c r="I957" s="2" t="inlineStr" /><c r="J957" s="2" t="inlineStr" /><c r="K957" s="2" t="inlineStr"><is><t>polineuropatia obwodowa</t></is></c><c r="L957" s="2" t="inlineStr"><is><t>osteomalacja</t></is></c><c r="M957" s="2" t="inlineStr" /><c r="N957" s="2" t="inlineStr" /><c r="O957" s="2" t="inlineStr" /><c r="P957" s="2" t="inlineStr"><is><t>EGZAMIN IWL 25 stycznia 2017</t></is></c><c r="Q957" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="958"><c r="A958" s="2" t="inlineStr"><is><t>LEKI PRZECIWHISTAMINOWE</t></is></c><c r="B958" s="2" t="inlineStr"><is><t>Przeciwwskazania</t></is></c><c r="C958" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D958" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E958" s="2" t="inlineStr"><is><t>Feksofenadyna: - II generacja przeciwhistaminowych</t></is></c><c r="F958" s="2" t="inlineStr"><is><t>jest podawana doustnie</t></is></c><c r="G958" s="2" t="inlineStr" /><c r="H958" s="2" t="inlineStr" /><c r="I958" s="2" t="inlineStr" /><c r="J958" s="2" t="inlineStr" /><c r="K958" s="2" t="inlineStr"><is><t>działa nieselektywnie na rec. H1</t></is></c><c r="L958" s="2" t="inlineStr"><is><t>przenika w znacznym stopniu przez barierę krew- mózg</t></is></c><c r="M958" s="2" t="inlineStr"><is><t>działa kardiotoksycznie i jest przeciwwskazana w chorobie niedokrwiennej serca</t></is></c><c r="N958" s="2" t="inlineStr" /><c r="O958" s="2" t="inlineStr" /><c r="P958" s="2" t="inlineStr"><is><t>EGZAMIN IWL 25 stycznia 2017</t></is></c><c r="Q958" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="959"><c r="A959" s="2" t="inlineStr"><is><t>OTĘPIENIE</t></is></c><c r="B959" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C959" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D959" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E959" s="2" t="inlineStr"><is><t>Podanie rywastygminy jest uzasadnione u pacjentów z - CHOLINOMIMETYK</t></is></c><c r="F959" s="2" t="inlineStr"><is><t>otępieniem w przebiegu choroby Parkinsona</t></is></c><c r="G959" s="2" t="inlineStr"><is><t>chorobą Alzheimera • TLPD MAJĄCE CHOLINOLITYCZNE DZIALANIE SĄ SILNIE PRZECIWSKAZANE w ALZHEIMERZE ! • Neuroleptyki tylko atypowe można w alzheimerze</t></is></c><c r="H959" s="2" t="inlineStr" /><c r="I959" s="2" t="inlineStr" /><c r="J959" s="2" t="inlineStr" /><c r="K959" s="2" t="inlineStr"><is><t>otępieniem naczyniopochodnym</t></is></c><c r="L959" s="2" t="inlineStr"><is><t>otępieniem czołowo-skroniowym</t></is></c><c r="M959" s="2" t="inlineStr" /><c r="N959" s="2" t="inlineStr" /><c r="O959" s="2" t="inlineStr" /><c r="P959" s="2" t="inlineStr"><is><t>EGZAMIN IWL 25 stycznia 2017</t></is></c><c r="Q959" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="960"><c r="A960" s="2" t="inlineStr"><is><t>LEKI PRZECIWLĘKOWE</t></is></c><c r="B960" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C960" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D960" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E960" s="2" t="inlineStr"><is><t>W alkoholowym zespole odstawiennym celowe może być zastosowanie:</t></is></c><c r="F960" s="2" t="inlineStr"><is><t>tiaminy</t></is></c><c r="G960" s="2" t="inlineStr"><is><t>diazepamu</t></is></c><c r="H960" s="2" t="inlineStr"><is><t>płynoterapia z suplementacją elektrolitów Zespół abstynencyjny • drżenie (głownie dłoni) • nudności, wymioty • nadmierne pocenie • pobudzenie ruchowe LEKI • Klometiazol – na majaczenie • Chlormetiazol • Neuroleptyki • KARBAMAZEPINA • Baklofen – wydaje się być skuteczny • Topiramat – tez na kokainę • benzodiazepiny: oksazepam i lorazepam – skuteczne tez na majaczenie Farmakoterapia uzależnienia od etanolu • • Akamprozat • Disufiram • naltrekson Zapobieganie nawrotom i utrzymanie abstynencji</t></is></c><c r="I960" s="2" t="inlineStr" /><c r="J960" s="2" t="inlineStr" /><c r="K960" s="2" t="inlineStr"><is><t>akamprozatu</t></is></c><c r="L960" s="2" t="inlineStr" /><c r="M960" s="2" t="inlineStr" /><c r="N960" s="2" t="inlineStr" /><c r="O960" s="2" t="inlineStr" /><c r="P960" s="2" t="inlineStr"><is><t>EGZAMIN IWL 25 stycznia 2017</t></is></c><c r="Q960" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="961"><c r="A961" s="2" t="inlineStr"><is><t>NARKOTYCZNE LEKI PRZECIWBÓLOWE</t></is></c><c r="B961" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C961" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D961" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E961" s="2" t="inlineStr"><is><t>W terapii substytucyjnej uzależnienia od opioidów celowe może być zastosowanie:</t></is></c><c r="F961" s="2" t="inlineStr"><is><t>buprenorfiny</t></is></c><c r="G961" s="2" t="inlineStr"><is><t>metadonu - buprenorfina + nalokson - metadon -naltrekson</t></is></c><c r="H961" s="2" t="inlineStr" /><c r="I961" s="2" t="inlineStr" /><c r="J961" s="2" t="inlineStr" /><c r="K961" s="2" t="inlineStr"><is><t>nalokson</t></is></c><c r="L961" s="2" t="inlineStr"><is><t>warenikliny</t></is></c><c r="M961" s="2" t="inlineStr" /><c r="N961" s="2" t="inlineStr" /><c r="O961" s="2" t="inlineStr" /><c r="P961" s="2" t="inlineStr"><is><t>EGZAMIN IWL 25 stycznia 2017</t></is></c><c r="Q961" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="962"><c r="A962" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B962" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C962" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D962" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E962" s="2" t="inlineStr"><is><t>Silnie hepatotoksycznie działa:</t></is></c><c r="F962" s="2" t="inlineStr"><is><t>Izoniazyd</t></is></c><c r="G962" s="2" t="inlineStr"><is><t>pirazynamid</t></is></c><c r="H962" s="2" t="inlineStr"><is><t>ryfampicyna • tetracykliny • środki przeczyszczające – roślinne też Liście senesu strączyńca Kora kruszyny Korzeń rzewienia Aloes • rapaholin • nlpz • steroidy anaboliczne • Kwas walproinowy Walproinian sodu • Retinoidy • Paarcetamol</t></is></c><c r="I962" s="2" t="inlineStr" /><c r="J962" s="2" t="inlineStr" /><c r="K962" s="2" t="inlineStr"><is><t>streptomycyna</t></is></c><c r="L962" s="2" t="inlineStr" /><c r="M962" s="2" t="inlineStr" /><c r="N962" s="2" t="inlineStr" /><c r="O962" s="2" t="inlineStr" /><c r="P962" s="2" t="inlineStr"><is><t>EGZAMIN IWL 25 stycznia 2017</t></is></c><c r="Q962" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="963"><c r="A963" s="2" t="inlineStr"><is><t>UKŁAD PRZYWSPÓŁCZULNY</t></is></c><c r="B963" s="2" t="inlineStr"><is><t>Antidotum</t></is></c><c r="C963" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D963" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E963" s="2" t="inlineStr"><is><t>Atropina jest stosowana w przypadku zatrucia:</t></is></c><c r="F963" s="2" t="inlineStr"><is><t>grzybami strzępiakami i lejkówkami</t></is></c><c r="G963" s="2" t="inlineStr"><is><t>glikozydami naparstnicy</t></is></c><c r="H963" s="2" t="inlineStr"><is><t>związkami fosforoorganicznymi • inhibitory acetylocholinesterazy • zw. fosforoorganiczne</t></is></c><c r="I963" s="2" t="inlineStr" /><c r="J963" s="2" t="inlineStr" /><c r="K963" s="2" t="inlineStr"><is><t>pokrzykiem wilczą jagodą</t></is></c><c r="L963" s="2" t="inlineStr" /><c r="M963" s="2" t="inlineStr" /><c r="N963" s="2" t="inlineStr" /><c r="O963" s="2" t="inlineStr" /><c r="P963" s="2" t="inlineStr"><is><t>EGZAMIN IWL 25 stycznia 2017</t></is></c><c r="Q963" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="964"><c r="A964" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B964" s="2" t="inlineStr"><is><t>Ciąża</t></is></c><c r="C964" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D964" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E964" s="2" t="inlineStr"><is><t>Udokumentowane działanie teratogenne wykazuje:</t></is></c><c r="F964" s="2" t="inlineStr"><is><t>trimetoprim-sulfametoksazol</t></is></c><c r="G964" s="2" t="inlineStr"><is><t>warfaryna</t></is></c><c r="H964" s="2" t="inlineStr"><is><t>kwas walproinowy</t></is></c><c r="I964" s="2" t="inlineStr"><is><t>gentamycyna o Streptomycyna o kapreomycyny, o kanamycyny o etionamidu o Inhibitory ACE – najlepiej wcale nie stosować w okresie rozrodczym kobiet o Sartany o LORKAZERYNA o FENTERMINA/TOPIRAMAT o SOLE LITU o SSRI – małe ryzyko o Retinoidy o Kwas walproinowy o Metotreksat o Leflunomid a – prawdziwe odpowiedzi 1, 3 i 4 b – prawdziwe odpowiedzi 1 i 3 c – prawdziwe odpowiedzi 2 i 4 d – prawdziwa odpowiedź 4 e – wszystkie odpowiedzi prawdziwe</t></is></c><c r="J964" s="2" t="inlineStr" /><c r="K964" s="2" t="inlineStr" /><c r="L964" s="2" t="inlineStr" /><c r="M964" s="2" t="inlineStr" /><c r="N964" s="2" t="inlineStr" /><c r="O964" s="2" t="inlineStr" /><c r="P964" s="2" t="inlineStr"><is><t>EGZAMIN IWL 25 stycznia 2017</t></is></c><c r="Q964" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="965"><c r="A965" s="2" t="inlineStr"><is><t>NADCIŚNIENIE TĘTNICZE</t></is></c><c r="B965" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C965" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D965" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E965" s="2" t="inlineStr"><is><t>Wskaż prawdziwe połączenie lek – wskazanie:</t></is></c><c r="F965" s="2" t="inlineStr"><is><t>ranolazyna - stabilna choroba niedokrwienna serca</t></is></c><c r="G965" s="2" t="inlineStr" /><c r="H965" s="2" t="inlineStr" /><c r="I965" s="2" t="inlineStr" /><c r="J965" s="2" t="inlineStr" /><c r="K965" s="2" t="inlineStr"><is><t>cilostazol - ostra niewydolność mięśnia sercowego – chromanie</t></is></c><c r="L965" s="2" t="inlineStr"><is><t>milrynon - migotanie przedsionków – krótkotrwawle w niewydolności serca</t></is></c><c r="M965" s="2" t="inlineStr"><is><t>riocyguat - nadciśnienie tętnicze</t></is></c><c r="N965" s="2" t="inlineStr" /><c r="O965" s="2" t="inlineStr" /><c r="P965" s="2" t="inlineStr"><is><t>EGZAMIN IWL 25 stycznia 2017</t></is></c><c r="Q965" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="966"><c r="A966" s="2" t="inlineStr"><is><t>LEKI MOCZOPĘDNE</t></is></c><c r="B966" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C966" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D966" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E966" s="2" t="inlineStr"><is><t>W leczeniu zagrażającej życiu hiperkaliemii można zastosować:</t></is></c><c r="F966" s="2" t="inlineStr"><is><t>10 ml 10% chlorku lub glukonianu wapnia i.v. w 10 min bolusie</t></is></c><c r="G966" s="2" t="inlineStr"><is><t>500 ml 20% glukozy z 20 j.m. insuliny krótkodziałającej i.v. przez 1-2 godziny</t></is></c><c r="H966" s="2" t="inlineStr"><is><t>Hemodializę HIPERKALIEMIA • podanie preparatu wapnia obligatoryjne przy [K]=&gt;7 mmol/l lub poszerzeniu zespołów QRS lub zaniku czynności przedsionków w EKG • • 10-20 ml 10% glukonianu wapnia w WOLNYM podaniu IV 5-15 min • • (Glukonian wapnia 10%, 0,23 mmol Ca/1 ml; chlorek wapnia 10%, ok. 6 mmol Ca/1 ml) • • stężenie potasu zmniejsza glukoza z insuliną: 500 ml 20% glukozy + 20 j insuliny krótkodziałąjącej IV przez 2-4 h (1 g glukozy/5 j.m. insuliny) • • żywice jonowymienne (sól sodowa/wapniowa sulfonianu polistyrenu, patiromer, sól sodowa cyklokrzemianu cyrkonu) HIPOKALIEMIA o Nie wolno podawać stężonych roztworów potasu!!! o W 1000 ml 0,9% NaCl maksymalnie 40 mmol potasu (nie wolno przekraczać stężenia 40 mmol/l) w WOLNYM wlewie IV (2 h, nie wolno przekraczać szybkości wlewu 20 mmol/h); nie wolno przekraczać ładunku 200 mmol/24 o Kalium chloratum 15%, amp. a 10 ml/20 ml, czyli 1 amp. = 1,5 g/3,0 g KCl = 20 mmol/40 mmol o Aby podwyższyć stężenie potasu w surowicy o 1 mmol/l należy podać ▪ przy stężeniu wyjściowym &gt; 3 mmol/l – 100-200 mmol ▪ przy stężeniu wyjściowym &lt; 3 mmol/l – 200-400 mmol</t></is></c><c r="I966" s="2" t="inlineStr" /><c r="J966" s="2" t="inlineStr" /><c r="K966" s="2" t="inlineStr"><is><t>diuretyki pętlowe i.v</t></is></c><c r="L966" s="2" t="inlineStr" /><c r="M966" s="2" t="inlineStr" /><c r="N966" s="2" t="inlineStr" /><c r="O966" s="2" t="inlineStr" /><c r="P966" s="2" t="inlineStr"><is><t>EGZAMIN IWL 25 stycznia 2017</t></is></c><c r="Q966" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="967"><c r="A967" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B967" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C967" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D967" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E967" s="2" t="inlineStr"><is><t>Apiksaban jest substratem dla P-gp. Co to oznacza?</t></is></c><c r="F967" s="2" t="inlineStr"><is><t>silne induktory P-gp o działaniu ogólnoustrojowym zmniejszają skuteczność apiksabanu Własnoręczny podpis Numer indeksu</t></is></c><c r="G967" s="2" t="inlineStr" /><c r="H967" s="2" t="inlineStr" /><c r="I967" s="2" t="inlineStr" /><c r="J967" s="2" t="inlineStr" /><c r="K967" s="2" t="inlineStr"><is><t>lek jest wchłaniany z p. pokarmowego z wykorzystaniem transportu ułatwionego</t></is></c><c r="L967" s="2" t="inlineStr"><is><t>jest metabolizowany w wątrobie i nie powinien być stosowany u osób z 10-15 pkt wg skali Childa-Pugha</t></is></c><c r="M967" s="2" t="inlineStr"><is><t>jest prawdopodobne, że hemodializa byłaby skutecznym środkiem zaradczym podczas przedawkowania apiksabanu</t></is></c><c r="N967" s="2" t="inlineStr" /><c r="O967" s="2" t="inlineStr" /><c r="P967" s="2" t="inlineStr"><is><t>EGZAMIN IWL 25 stycznia 2017</t></is></c><c r="Q967" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="968"><c r="A968" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B968" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C968" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D968" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E968" s="2" t="inlineStr"><is><t>Kolistyna:</t></is></c><c r="F968" s="2" t="inlineStr"><is><t>może być podawana wziewnie u osób z mukowiscydozą</t></is></c><c r="G968" s="2" t="inlineStr"><is><t>może być zastosowana w leczeniu ciężkich zakażeń uogólnionych wywołanych przez Klebsiella pneumoniae wytwarzającą karbapenemazy</t></is></c><c r="H968" s="2" t="inlineStr"><is><t>wykazuje aktywność wobec Pseudomonas aeruginosa</t></is></c><c r="I968" s="2" t="inlineStr" /><c r="J968" s="2" t="inlineStr" /><c r="K968" s="2" t="inlineStr"><is><t>jest skuteczna w neuroinfekcjach</t></is></c><c r="L968" s="2" t="inlineStr" /><c r="M968" s="2" t="inlineStr" /><c r="N968" s="2" t="inlineStr" /><c r="O968" s="2" t="inlineStr" /><c r="P968" s="2" t="inlineStr"><is><t>EGZAMIN IWL 20 czerwca 2018</t></is></c><c r="Q968" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="969"><c r="A969" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B969" s="2" t="inlineStr"><is><t>Ciąża</t></is></c><c r="C969" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D969" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E969" s="2" t="inlineStr"><is><t>Doksycyklina:</t></is></c><c r="F969" s="2" t="inlineStr"><is><t>działa na bakterie atypowe</t></is></c><c r="G969" s="2" t="inlineStr" /><c r="H969" s="2" t="inlineStr" /><c r="I969" s="2" t="inlineStr" /><c r="J969" s="2" t="inlineStr" /><c r="K969" s="2" t="inlineStr"><is><t>może być bezpiecznie stosowana u dzieci powyżej 2 r.ż</t></is></c><c r="L969" s="2" t="inlineStr"><is><t>jest agonistą receptorów GABA-A wywołując efektsedatywny</t></is></c><c r="M969" s="2" t="inlineStr"><is><t>jest bezpieczna w terapii kobiet w ciąży</t></is></c><c r="N969" s="2" t="inlineStr" /><c r="O969" s="2" t="inlineStr" /><c r="P969" s="2" t="inlineStr"><is><t>EGZAMIN IWL 20 czerwca 2018</t></is></c><c r="Q969" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="970"><c r="A970" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B970" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C970" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D970" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E970" s="2" t="inlineStr"><is><t>Wskaż prawdziwe połączenie lek – działania niepożądane:</t></is></c><c r="F970" s="2" t="inlineStr"><is><t>amoksycylina – leukopenia w mechanizmie nadwrażliwości immunologicznej</t></is></c><c r="G970" s="2" t="inlineStr"><is><t>tynidazol - neuropatia obwodowa</t></is></c><c r="H970" s="2" t="inlineStr"><is><t>amikacyna – zaburzenia słuchu i równowagi</t></is></c><c r="I970" s="2" t="inlineStr" /><c r="J970" s="2" t="inlineStr" /><c r="K970" s="2" t="inlineStr"><is><t>roksytromycyna – uszkodzenie nerek</t></is></c><c r="L970" s="2" t="inlineStr"><is><t>Właściwy wybór leku przeciwwirusowego w zakażeniu to:</t></is></c><c r="M970" s="2" t="inlineStr" /><c r="N970" s="2" t="inlineStr" /><c r="O970" s="2" t="inlineStr" /><c r="P970" s="2" t="inlineStr"><is><t>EGZAMIN IWL 20 czerwca 2018</t></is></c><c r="Q970" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="971"><c r="A971" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B971" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C971" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D971" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E971" s="2" t="inlineStr"><is><t>Wyłącznie na drobnoustroje Gram dodatnie działa:</t></is></c><c r="F971" s="2" t="inlineStr"><is><t>mupirocyna</t></is></c><c r="G971" s="2" t="inlineStr" /><c r="H971" s="2" t="inlineStr" /><c r="I971" s="2" t="inlineStr" /><c r="J971" s="2" t="inlineStr" /><c r="K971" s="2" t="inlineStr"><is><t>metronidazol</t></is></c><c r="L971" s="2" t="inlineStr"><is><t>fosfomycyna</t></is></c><c r="M971" s="2" t="inlineStr"><is><t>gentamycyna</t></is></c><c r="N971" s="2" t="inlineStr" /><c r="O971" s="2" t="inlineStr" /><c r="P971" s="2" t="inlineStr"><is><t>EGZAMIN IWL 20 czerwca 2018</t></is></c><c r="Q971" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="972"><c r="A972" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B972" s="2" t="inlineStr"><is><t>Monitorowanie</t></is></c><c r="C972" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D972" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E972" s="2" t="inlineStr"><is><t>Jeśli celem farmakodynamicznym dla stosowanego antybiotyku jest wysoka wartość T&gt;MIC, to powinno się:</t></is></c><c r="F972" s="2" t="inlineStr"><is><t>monitorować stężenie leku we krwi w celu modyfikowania dawkowania</t></is></c><c r="G972" s="2" t="inlineStr"><is><t>podawać leki w przedłużonym wlewie dożylnym</t></is></c><c r="H972" s="2" t="inlineStr"><is><t>zwiększyć częstość podawania leku w ciągu doby</t></is></c><c r="I972" s="2" t="inlineStr" /><c r="J972" s="2" t="inlineStr" /><c r="K972" s="2" t="inlineStr"><is><t>podawać lek w pojedynczej skumulowanej dawce dobowej</t></is></c><c r="L972" s="2" t="inlineStr" /><c r="M972" s="2" t="inlineStr" /><c r="N972" s="2" t="inlineStr" /><c r="O972" s="2" t="inlineStr" /><c r="P972" s="2" t="inlineStr"><is><t>EGZAMIN IWL 20 czerwca 2018</t></is></c><c r="Q972" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="973"><c r="A973" s="2" t="inlineStr"><is><t>LEKI PRZECIWPASOŻYTNICZE</t></is></c><c r="B973" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C973" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D973" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E973" s="2" t="inlineStr"><is><t>Wskaż prawidłowe stwierdzenia dotyczące profilaktyki i leczenia malarii:</t></is></c><c r="F973" s="2" t="inlineStr"><is><t>lumefantryna w połączeniu z artemeterem może być skuteczna w zakażeniu Plasmodium falciparum</t></is></c><c r="G973" s="2" t="inlineStr"><is><t>w przypadkach wymagających profilaktyki długoterminowej można zastosować chlorochinę</t></is></c><c r="H973" s="2" t="inlineStr" /><c r="I973" s="2" t="inlineStr" /><c r="J973" s="2" t="inlineStr" /><c r="K973" s="2" t="inlineStr"><is><t>pochodne artemizyniny zalecane są tylko do profilaktyki malarii</t></is></c><c r="L973" s="2" t="inlineStr"><is><t>atowakwon z proguanilem może być stosowany u osób z upośledzoną czynnością nerek (klirens kreatyniny &lt;30 ml/min)</t></is></c><c r="M973" s="2" t="inlineStr" /><c r="N973" s="2" t="inlineStr" /><c r="O973" s="2" t="inlineStr" /><c r="P973" s="2" t="inlineStr"><is><t>EGZAMIN IWL 20 czerwca 2018</t></is></c><c r="Q973" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="974"><c r="A974" s="2" t="inlineStr"><is><t>CUKRZYCA</t></is></c><c r="B974" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C974" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D974" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E974" s="2" t="inlineStr"><is><t>Wskazaniem do insulinoterapii jest:</t></is></c><c r="F974" s="2" t="inlineStr"><is><t>cukrzyca typu LADA</t></is></c><c r="G974" s="2" t="inlineStr"><is><t>ostry zespół wieńcowy u osoby z cukrzycą typu II</t></is></c><c r="H974" s="2" t="inlineStr"><is><t>znaczna hiperglikemia (&gt;300 mg/dl) w przebiegu cukrzycy typu II</t></is></c><c r="I974" s="2" t="inlineStr"><is><t>cukrzyca ciężarnych Insilinoterapia : ZAWSZE W CUKRZYCY TYPU 1 , Cukrzyca typu 3 – po pankreatotomii lub jak wcale trzustka nie działa</t></is></c><c r="J974" s="2" t="inlineStr" /><c r="K974" s="2" t="inlineStr" /><c r="L974" s="2" t="inlineStr" /><c r="M974" s="2" t="inlineStr" /><c r="N974" s="2" t="inlineStr" /><c r="O974" s="2" t="inlineStr" /><c r="P974" s="2" t="inlineStr"><is><t>EGZAMIN IWL 20 czerwca 2018</t></is></c><c r="Q974" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="975"><c r="A975" s="2" t="inlineStr"><is><t>CUKRZYCA</t></is></c><c r="B975" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C975" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D975" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E975" s="2" t="inlineStr"><is><t>Długodziałające analogi insuliny w porównaniu do insuliny protaminowo-cynkowej (NPH) charakteryzują się:</t></is></c><c r="F975" s="2" t="inlineStr"><is><t>mniejszym ryzykiem hipoglikemii</t></is></c><c r="G975" s="2" t="inlineStr" /><c r="H975" s="2" t="inlineStr" /><c r="I975" s="2" t="inlineStr" /><c r="J975" s="2" t="inlineStr" /><c r="K975" s="2" t="inlineStr"><is><t>mniejszym ryzykiem onkologicznym</t></is></c><c r="L975" s="2" t="inlineStr"><is><t>większym ryzykiem zjawiska brzasku</t></is></c><c r="M975" s="2" t="inlineStr"><is><t>działaniem anorektycznym</t></is></c><c r="N975" s="2" t="inlineStr" /><c r="O975" s="2" t="inlineStr" /><c r="P975" s="2" t="inlineStr"><is><t>EGZAMIN IWL 20 czerwca 2018</t></is></c><c r="Q975" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="976"><c r="A976" s="2" t="inlineStr"><is><t>TARCZYCA</t></is></c><c r="B976" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C976" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D976" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E976" s="2" t="inlineStr"><is><t>Zmniejszenie obwodowej konwersji tyroksyny do trójjodotyroniny jest efektem stosowania :</t></is></c><c r="F976" s="2" t="inlineStr"><is><t>hydrokortyzonu</t></is></c><c r="G976" s="2" t="inlineStr"><is><t>propylotiouracylu</t></is></c><c r="H976" s="2" t="inlineStr" /><c r="I976" s="2" t="inlineStr" /><c r="J976" s="2" t="inlineStr" /><c r="K976" s="2" t="inlineStr"><is><t>płynu Lugola – on bazuje na efekcie wolfa czaichofa – przeladowanie jodem tarczycy nagle nie do końca wiadomo czemu tarczyca przestaje syntetyzować hormony. Dlatego się podawało po Czarnobylu</t></is></c><c r="L976" s="2" t="inlineStr"><is><t>propranololu Tyreostatyczne zwykle blokują tarczyce tylko pochodne tiouracylu i gks i beta adrenolityki blokują konwersje</t></is></c><c r="M976" s="2" t="inlineStr" /><c r="N976" s="2" t="inlineStr" /><c r="O976" s="2" t="inlineStr" /><c r="P976" s="2" t="inlineStr"><is><t>EGZAMIN IWL 20 czerwca 2018</t></is></c><c r="Q976" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="977"><c r="A977" s="2" t="inlineStr"><is><t>HORMONY PŁCIOWE</t></is></c><c r="B977" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C977" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D977" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E977" s="2" t="inlineStr"><is><t>Wskazaniem do stosowania hormonalnej terapii zastępczej u kobiet po menopauzie jest:</t></is></c><c r="F977" s="2" t="inlineStr"><is><t>obecność objawów wypadowych To miał być super pomysł na menopauzę, ale to WIELKA PORAŻKA bo choroby układu krążenia i otępienia miały ustąpić i miało nie być osteoporozy, ale nie jest. Przybywa wykrzepien zawałów udarów i nowotwory estrogeno zeleżne – rak TRZONU a nie szyjki macicy i rak SUTKA , można dać gestagen i wtedy mniejsze ryzyko ale wciąż nie ma sensu. HTZ TYLKO KRÓTKOTRWALE W DOPOCHOWYCH – objawowo i krótkoterminowo zdażenia okołomenopauzalne no i po resekcji</t></is></c><c r="G977" s="2" t="inlineStr" /><c r="H977" s="2" t="inlineStr" /><c r="I977" s="2" t="inlineStr" /><c r="J977" s="2" t="inlineStr" /><c r="K977" s="2" t="inlineStr"><is><t>wtórna profilaktyka chorób układu krążenia</t></is></c><c r="L977" s="2" t="inlineStr"><is><t>profilaktyka osteoporozy</t></is></c><c r="M977" s="2" t="inlineStr"><is><t>zapobieganie chorobie Alzheimera</t></is></c><c r="N977" s="2" t="inlineStr" /><c r="O977" s="2" t="inlineStr" /><c r="P977" s="2" t="inlineStr"><is><t>EGZAMIN IWL 20 czerwca 2018</t></is></c><c r="Q977" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="978"><c r="A978" s="2" t="inlineStr"><is><t>NARKOTYCZNE LEKI PRZECIWBÓLOWE</t></is></c><c r="B978" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C978" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D978" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E978" s="2" t="inlineStr"><is><t>Przeciwbólowy efekt pułapowy wykazuje:</t></is></c><c r="F978" s="2" t="inlineStr"><is><t>naproksen</t></is></c><c r="G978" s="2" t="inlineStr"><is><t>buprenorfina – jest agoantaginistą wiec tak !</t></is></c><c r="H978" s="2" t="inlineStr"><is><t>ibuprofen Zwiększenie dawki już nic nie da Ten efekt maja wszystkie leki poza opioidami, ale tylko tymi pełnymi agonistami</t></is></c><c r="I978" s="2" t="inlineStr" /><c r="J978" s="2" t="inlineStr" /><c r="K978" s="2" t="inlineStr"><is><t>oksykodon – czysty agonista wiec nie</t></is></c><c r="L978" s="2" t="inlineStr" /><c r="M978" s="2" t="inlineStr" /><c r="N978" s="2" t="inlineStr" /><c r="O978" s="2" t="inlineStr" /><c r="P978" s="2" t="inlineStr"><is><t>EGZAMIN IWL 20 czerwca 2018</t></is></c><c r="Q978" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="979"><c r="A979" s="2" t="inlineStr"><is><t>ZABURZENIA RYTMU SERCA</t></is></c><c r="B979" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C979" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D979" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E979" s="2" t="inlineStr"><is><t>Teofilina: - METYLOKSANTYNA</t></is></c><c r="F979" s="2" t="inlineStr"><is><t>jest antagonistą receptora adenozynowego</t></is></c><c r="G979" s="2" t="inlineStr"><is><t>hamuje aktywność fosfodiesteraz</t></is></c><c r="H979" s="2" t="inlineStr"><is><t>zwiększa przepływ nerkowy</t></is></c><c r="I979" s="2" t="inlineStr"><is><t>pobudza ośrodek oddechowy w rdzeniu przedłużonym BARDZO NIEBEZPIECZNY LEK – stymulują miokardium PROARYTMIE I TACHYKARDIA Słabo albo wcale nie podowuje poprawe spirometrycznego badania. Wielu pacjentów subiektywnie uważa, że ma poprawę w POCHP po włączeniu do ich leczenia teofiliny. Pewnie dlatego, że to psychostymulat , robi dobrze na głowę poprawia vigor człowiekowi i ma wpływ na mięśnie szkieletowe</t></is></c><c r="J979" s="2" t="inlineStr" /><c r="K979" s="2" t="inlineStr" /><c r="L979" s="2" t="inlineStr" /><c r="M979" s="2" t="inlineStr" /><c r="N979" s="2" t="inlineStr" /><c r="O979" s="2" t="inlineStr" /><c r="P979" s="2" t="inlineStr"><is><t>EGZAMIN IWL 20 czerwca 2018</t></is></c><c r="Q979" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="980"><c r="A980" s="2" t="inlineStr"><is><t>FARMAKOKINETYKA</t></is></c><c r="B980" s="2" t="inlineStr"><is><t>Farmakokinetyka</t></is></c><c r="C980" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D980" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E980" s="2" t="inlineStr"><is><t>Idealny glikokortykosteroid wziewny:</t></is></c><c r="F980" s="2" t="inlineStr"><is><t>połknięty charakteryzuje się niewielką biodostępnością</t></is></c><c r="G980" s="2" t="inlineStr" /><c r="H980" s="2" t="inlineStr" /><c r="I980" s="2" t="inlineStr" /><c r="J980" s="2" t="inlineStr" /><c r="K980" s="2" t="inlineStr"><is><t>dobrze wchłania się z pęcherzyków płucnych</t></is></c><c r="L980" s="2" t="inlineStr"><is><t>nie podlega efektowi pierwszego przejścia przez wątrobę</t></is></c><c r="M980" s="2" t="inlineStr"><is><t>ma krótki okres półtrwania kompleksu glikokortykosteroidu zreceptorem (t1/2 = 2 – 3 godz) – nie bo by musiał cały czas psikac</t></is></c><c r="N980" s="2" t="inlineStr" /><c r="O980" s="2" t="inlineStr" /><c r="P980" s="2" t="inlineStr"><is><t>EGZAMIN IWL 20 czerwca 2018</t></is></c><c r="Q980" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="981"><c r="A981" s="2" t="inlineStr"><is><t>LEKI PRZECIWDEPRESYJNE</t></is></c><c r="B981" s="2" t="inlineStr"><is><t>Antidotum</t></is></c><c r="C981" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D981" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E981" s="2" t="inlineStr"><is><t>W zatruciu solami litu:</t></is></c><c r="F981" s="2" t="inlineStr"><is><t>należy natychmiast zakończyć podawanie litu</t></is></c><c r="G981" s="2" t="inlineStr"><is><t>w leczeniu ostrego zatrucia istotne znaczenie na intensywne wyrównywanie zaburzeń gospodarki wodno-elektrolitowej, a zwłaszcza uzupełnianie niedoboru sodu poprzez przetaczanie roztworu 0,9% NaCl dożylnie</t></is></c><c r="H981" s="2" t="inlineStr"><is><t>podstawową metodą eliminacji leku jest hemodializa</t></is></c><c r="I981" s="2" t="inlineStr" /><c r="J981" s="2" t="inlineStr" /><c r="K981" s="2" t="inlineStr"><is><t>korzystne działanie ma stosowanie węgla aktywowanego</t></is></c><c r="L981" s="2" t="inlineStr" /><c r="M981" s="2" t="inlineStr" /><c r="N981" s="2" t="inlineStr" /><c r="O981" s="2" t="inlineStr" /><c r="P981" s="2" t="inlineStr"><is><t>EGZAMIN IWL 20 czerwca 2018</t></is></c><c r="Q981" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="982"><c r="A982" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B982" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C982" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D982" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E982" s="2" t="inlineStr"><is><t>Czarne zabarwienie stolca powoduje podawanie preparatów:</t></is></c><c r="F982" s="2" t="inlineStr"><is><t>bizmutu</t></is></c><c r="G982" s="2" t="inlineStr"><is><t>żelaza</t></is></c><c r="H982" s="2" t="inlineStr" /><c r="I982" s="2" t="inlineStr" /><c r="J982" s="2" t="inlineStr" /><c r="K982" s="2" t="inlineStr"><is><t>wapnia</t></is></c><c r="L982" s="2" t="inlineStr"><is><t>glinu</t></is></c><c r="M982" s="2" t="inlineStr" /><c r="N982" s="2" t="inlineStr" /><c r="O982" s="2" t="inlineStr" /><c r="P982" s="2" t="inlineStr"><is><t>EGZAMIN IWL 20 czerwca 2018</t></is></c><c r="Q982" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="983"><c r="A983" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B983" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C983" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D983" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E983" s="2" t="inlineStr"><is><t>Uzasadnionym wskazaniem do przewlekłego stosowania inhibitorów pompy protonowej jest:</t></is></c><c r="F983" s="2" t="inlineStr"><is><t>choroba refluksowa przełyku</t></is></c><c r="G983" s="2" t="inlineStr"><is><t>profilaktyka gastropatii u osób leczonych niesteroidowymi lekami przeciwzapalnymi powyżej 65 r.ż</t></is></c><c r="H983" s="2" t="inlineStr"><is><t>eradykacja Helicobacter pylori</t></is></c><c r="I983" s="2" t="inlineStr" /><c r="J983" s="2" t="inlineStr" /><c r="K983" s="2" t="inlineStr"><is><t>profilaktyka wrzodów stresowych</t></is></c><c r="L983" s="2" t="inlineStr" /><c r="M983" s="2" t="inlineStr" /><c r="N983" s="2" t="inlineStr" /><c r="O983" s="2" t="inlineStr" /><c r="P983" s="2" t="inlineStr"><is><t>EGZAMIN IWL 20 czerwca 2018</t></is></c><c r="Q983" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="984"><c r="A984" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B984" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C984" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D984" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E984" s="2" t="inlineStr"><is><t>Ryzyko uszkodzenia wątroby przez paracetamol rośnie w przypadku:</t></is></c><c r="F984" s="2" t="inlineStr"><is><t>zespołu zależności alkoholowej (ZZA)</t></is></c><c r="G984" s="2" t="inlineStr"><is><t>wygłodzenia (kacheksji)</t></is></c><c r="H984" s="2" t="inlineStr"><is><t>indukcji enzymów mikrosomalnych wątroby</t></is></c><c r="I984" s="2" t="inlineStr"><is><t>przedawkowania</t></is></c><c r="J984" s="2" t="inlineStr" /><c r="K984" s="2" t="inlineStr" /><c r="L984" s="2" t="inlineStr" /><c r="M984" s="2" t="inlineStr" /><c r="N984" s="2" t="inlineStr" /><c r="O984" s="2" t="inlineStr" /><c r="P984" s="2" t="inlineStr"><is><t>EGZAMIN IWL 20 czerwca 2018</t></is></c><c r="Q984" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="985"><c r="A985" s="2" t="inlineStr"><is><t>BÓLE GŁOWY</t></is></c><c r="B985" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C985" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D985" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E985" s="2" t="inlineStr"><is><t>W przerywaniu bólów migrenowych stosuje się:</t></is></c><c r="F985" s="2" t="inlineStr"><is><t>kwas acetylosalicylowy</t></is></c><c r="G985" s="2" t="inlineStr"><is><t>dihydroergotaminę –ALKALOID SPORYSZU rzadko tylko wtedy gdy pacjent ma często napady, żeby nie dawać non stop tryptanów</t></is></c><c r="H985" s="2" t="inlineStr"><is><t>zolmitryptan</t></is></c><c r="I985" s="2" t="inlineStr" /><c r="J985" s="2" t="inlineStr" /><c r="K985" s="2" t="inlineStr"><is><t>morfinę</t></is></c><c r="L985" s="2" t="inlineStr" /><c r="M985" s="2" t="inlineStr" /><c r="N985" s="2" t="inlineStr" /><c r="O985" s="2" t="inlineStr" /><c r="P985" s="2" t="inlineStr"><is><t>EGZAMIN IWL 20 czerwca 2018</t></is></c><c r="Q985" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="986"><c r="A986" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B986" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C986" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D986" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E986" s="2" t="inlineStr"><is><t>Analogi prostaglandyny E1 mogą powodować: - TO MIZOPROSTOL ( ABORTYWNY)</t></is></c><c r="F986" s="2" t="inlineStr"><is><t>rozszerzenie naczyń krwionośnych tętniczych</t></is></c><c r="G986" s="2" t="inlineStr"><is><t>hamowanie wydzielania soku żołądkowego reszta odpowiedzi odnosi się do innych prostaglandyn</t></is></c><c r="H986" s="2" t="inlineStr" /><c r="I986" s="2" t="inlineStr" /><c r="J986" s="2" t="inlineStr" /><c r="K986" s="2" t="inlineStr"><is><t>poprawę odpływu cieczy wodnistej z oka</t></is></c><c r="L986" s="2" t="inlineStr"><is><t>hamowanie agregacji płytek krwi</t></is></c><c r="M986" s="2" t="inlineStr" /><c r="N986" s="2" t="inlineStr" /><c r="O986" s="2" t="inlineStr" /><c r="P986" s="2" t="inlineStr"><is><t>EGZAMIN IWL 20 czerwca 2018</t></is></c><c r="Q986" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="987"><c r="A987" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B987" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C987" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D987" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E987" s="2" t="inlineStr"><is><t>Substytucja enzymów trzustkowych jest wskazana:</t></is></c><c r="F987" s="2" t="inlineStr"><is><t>w mukowiscydozie to przewlekla niewydolność trzustki</t></is></c><c r="G987" s="2" t="inlineStr"><is><t>po resekcji trzustki</t></is></c><c r="H987" s="2" t="inlineStr" /><c r="I987" s="2" t="inlineStr" /><c r="J987" s="2" t="inlineStr" /><c r="K987" s="2" t="inlineStr"><is><t>w cukrzycy typu I</t></is></c><c r="L987" s="2" t="inlineStr"><is><t>w anoreksji</t></is></c><c r="M987" s="2" t="inlineStr" /><c r="N987" s="2" t="inlineStr" /><c r="O987" s="2" t="inlineStr" /><c r="P987" s="2" t="inlineStr"><is><t>EGZAMIN IWL 20 czerwca 2018</t></is></c><c r="Q987" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="988"><c r="A988" s="2" t="inlineStr"><is><t>PADACZKA</t></is></c><c r="B988" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C988" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D988" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E988" s="2" t="inlineStr"><is><t>Wybierz prawidłowe połączenie lek – wskazanie do podania:</t></is></c><c r="F988" s="2" t="inlineStr"><is><t>haloperydol – agresja u pacjentów z organicznym uszkodzeniem mózgu – jeśli pacjent nie ma schizofrenii ale ogolnie cos z nimi nie tak, np. somatyczna choroba uszkodzenie mózgu to się stosuje NEUROLEPTYKI ! i klasyczne i atypowe</t></is></c><c r="G988" s="2" t="inlineStr"><is><t>betahistya – zawroty głowy w przebiegu choroby Méniére'a – setki ludzi przyjmują niepotrzebnie to aktywuje rec dla histaminy w stanach uznali że nieskuteczne. Ta choroba to nadciśnienie endolimy w uchu wewnętrznym – nudności i wymioty występują. NA INNE NIE MA WPŁYWU POZA MENIEREM</t></is></c><c r="H988" s="2" t="inlineStr"><is><t>topiramat – profilaktyka migreny lub KWAS WALPROINOWY FLUNARYZYNA LAMOTRYGINA</t></is></c><c r="I988" s="2" t="inlineStr"><is><t>lamotrygina – profilaktyka choroby afektywnej dwubiegunowej – albo LITEM(węglan litu) nie pozwala wejść ani w depresje ani w manie, karbamazepina i kwas walproinowy</t></is></c><c r="J988" s="2" t="inlineStr" /><c r="K988" s="2" t="inlineStr" /><c r="L988" s="2" t="inlineStr" /><c r="M988" s="2" t="inlineStr" /><c r="N988" s="2" t="inlineStr" /><c r="O988" s="2" t="inlineStr" /><c r="P988" s="2" t="inlineStr"><is><t>EGZAMIN IWL 20 czerwca 2018</t></is></c><c r="Q988" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="989"><c r="A989" s="2" t="inlineStr"><is><t>FARMAKOKINETYKA</t></is></c><c r="B989" s="2" t="inlineStr"><is><t>Farmakokinetyka</t></is></c><c r="C989" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D989" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E989" s="2" t="inlineStr"><is><t>Kwas acetylosalicylowy:</t></is></c><c r="F989" s="2" t="inlineStr"><is><t>może być przyczyną zapalenia jelita cienkiego</t></is></c><c r="G989" s="2" t="inlineStr"><is><t>po przedawkowaniu szybciej wydala się przez nerki po dożylnym podaniu wodorowęglanu sodu</t></is></c><c r="H989" s="2" t="inlineStr" /><c r="I989" s="2" t="inlineStr" /><c r="J989" s="2" t="inlineStr" /><c r="K989" s="2" t="inlineStr"><is><t>ma eliminację metabolitów zgodnie z kinetyką I rzędu po podaniu małych dawek kardiologicznych – o ile małe dawki to kinetyka I, ALE jak duże dawki &gt;100mg na dobę to kinetyka 0 i jest nieprzywidywalna</t></is></c><c r="L989" s="2" t="inlineStr"><is><t>słabiej zapobiega powstaniu zakrzepu na blaszce miażdżycowej niż w układzie żylnym</t></is></c><c r="M989" s="2" t="inlineStr" /><c r="N989" s="2" t="inlineStr" /><c r="O989" s="2" t="inlineStr" /><c r="P989" s="2" t="inlineStr"><is><t>EGZAMIN IWL 20 czerwca 2018</t></is></c><c r="Q989" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="990"><c r="A990" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B990" s="2" t="inlineStr"><is><t>Antidotum</t></is></c><c r="C990" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D990" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E990" s="2" t="inlineStr"><is><t>Wskaż prawdziwe stwierdzenie dotyczące leczenia heparyną niefrakcjonowaną:</t></is></c><c r="F990" s="2" t="inlineStr"><is><t>może być podawana podskórnie, ale jej biodostępność jest wtedy mała i zmienna osobniczo</t></is></c><c r="G990" s="2" t="inlineStr"><is><t>białka osoczowe mogą zmniejszać jej działanie przeciwkrzepliwe i być przyczyną oporności na leczenie</t></is></c><c r="H990" s="2" t="inlineStr"><is><t>przedłużenie aPTT 1,5–2 razy w stosunku do wartości wyjściowej jes pożądanym efektem terapeutycznym</t></is></c><c r="I990" s="2" t="inlineStr"><is><t>jej antidotum jest siarczan protaminy</t></is></c><c r="J990" s="2" t="inlineStr" /><c r="K990" s="2" t="inlineStr" /><c r="L990" s="2" t="inlineStr" /><c r="M990" s="2" t="inlineStr" /><c r="N990" s="2" t="inlineStr" /><c r="O990" s="2" t="inlineStr" /><c r="P990" s="2" t="inlineStr"><is><t>EGZAMIN IWL 20 czerwca 2018</t></is></c><c r="Q990" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="991"><c r="A991" s="2" t="inlineStr"><is><t>UKŁAD PRZYWSPÓŁCZULNY</t></is></c><c r="B991" s="2" t="inlineStr"><is><t>Przeciwwskazania</t></is></c><c r="C991" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D991" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E991" s="2" t="inlineStr"><is><t>Przeciwwskazaniem do podania cholinolityków jest:</t></is></c><c r="F991" s="2" t="inlineStr"><is><t>rozrost gruczołu krokowego</t></is></c><c r="G991" s="2" t="inlineStr"><is><t>jaskra Upośledzają funkcje ośrodkowe – starsi mogą wejść w demencje bo szlaki kognitywne sa na acetylkocholinie Podowują suchość w ustach Gdzie cholinolityki ? Dimenchydryna/ skopolamina – w KINETOZACH 46min Bronchodylatacyjne wziewne</t></is></c><c r="H991" s="2" t="inlineStr" /><c r="I991" s="2" t="inlineStr" /><c r="J991" s="2" t="inlineStr" /><c r="K991" s="2" t="inlineStr"><is><t>choroba wrzodowa żołądka i dwunastnicy -</t></is></c><c r="L991" s="2" t="inlineStr"><is><t>choroba lokomocyjna</t></is></c><c r="M991" s="2" t="inlineStr" /><c r="N991" s="2" t="inlineStr" /><c r="O991" s="2" t="inlineStr" /><c r="P991" s="2" t="inlineStr"><is><t>EGZAMIN IWL 20 czerwca 2018</t></is></c><c r="Q991" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="992"><c r="A992" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B992" s="2" t="inlineStr"><is><t>Monitorowanie</t></is></c><c r="C992" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D992" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E992" s="2" t="inlineStr"><is><t>Warfaryna:</t></is></c><c r="F992" s="2" t="inlineStr"><is><t>jest stosowana w profilaktyce i leczeniu żylnej choroby zakrzepowo- zatorowej</t></is></c><c r="G992" s="2" t="inlineStr"><is><t>może być przyczyną zespołu purpurowego palucha</t></is></c><c r="H992" s="2" t="inlineStr" /><c r="I992" s="2" t="inlineStr" /><c r="J992" s="2" t="inlineStr" /><c r="K992" s="2" t="inlineStr"><is><t>wymaga utrzymania wartości INR powyżej 4</t></is></c><c r="L992" s="2" t="inlineStr"><is><t>jest eliminowana niezmieniona przez nerki – kompletna bzdura bo jest nawet polimorfizm między ludzmi jak szybko ją metabolizują cyp2y9 enzym</t></is></c><c r="M992" s="2" t="inlineStr" /><c r="N992" s="2" t="inlineStr" /><c r="O992" s="2" t="inlineStr" /><c r="P992" s="2" t="inlineStr"><is><t>EGZAMIN IWL 20 czerwca 2018</t></is></c><c r="Q992" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="993"><c r="A993" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B993" s="2" t="inlineStr"><is><t>Monitorowanie</t></is></c><c r="C993" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D993" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E993" s="2" t="inlineStr"><is><t>Fondaparynuks:</t></is></c><c r="F993" s="2" t="inlineStr"><is><t>jest stosowany u osób z zawałem serca z przetrwałym uniesieniem odcinka ST (STEMI) oraz bez jego uniesienia (NSTEMI)</t></is></c><c r="G993" s="2" t="inlineStr" /><c r="H993" s="2" t="inlineStr" /><c r="I993" s="2" t="inlineStr" /><c r="J993" s="2" t="inlineStr" /><c r="K993" s="2" t="inlineStr"><is><t>wybiórczo hamuje czynnik IIa – 10</t></is></c><c r="L993" s="2" t="inlineStr"><is><t>w zalecanych dawkach istotnie wydłuża aPTT – bezpieczny bez monitorowania</t></is></c><c r="M993" s="2" t="inlineStr"><is><t>nie jest wydalany przez nerki i może być stosowany u pacjentów z klirensem kreatyniny poniżej 30 ml/min – wręcz przeciwnie, frakcjonowane są głównie eliminowane przez nerki jest zakaz, którego nikt nie przestrzega podawania ich poniżej 30 GFR . w stacjach dializ jak ktoś ma rozpoznana nadkrzepliwosc poheparynowa HIT – to nawet bez działających nerek się fondaparyne daje</t></is></c><c r="N993" s="2" t="inlineStr" /><c r="O993" s="2" t="inlineStr" /><c r="P993" s="2" t="inlineStr"><is><t>EGZAMIN IWL 20 czerwca 2018</t></is></c><c r="Q993" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="994"><c r="A994" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B994" s="2" t="inlineStr"><is><t>Sposób podania</t></is></c><c r="C994" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D994" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E994" s="2" t="inlineStr"><is><t>Bezpośrednim inhibitorem trombiny podawanym dożylnie jest:</t></is></c><c r="F994" s="2" t="inlineStr"><is><t>argatroban</t></is></c><c r="G994" s="2" t="inlineStr"><is><t>dabigatran – nie bo jest podawany doustnie</t></is></c><c r="H994" s="2" t="inlineStr"><is><t>biwalirudyna</t></is></c><c r="I994" s="2" t="inlineStr" /><c r="J994" s="2" t="inlineStr" /><c r="K994" s="2" t="inlineStr"><is><t>dalteparyna</t></is></c><c r="L994" s="2" t="inlineStr" /><c r="M994" s="2" t="inlineStr" /><c r="N994" s="2" t="inlineStr" /><c r="O994" s="2" t="inlineStr" /><c r="P994" s="2" t="inlineStr"><is><t>EGZAMIN IWL 20 czerwca 2018</t></is></c><c r="Q994" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="995"><c r="A995" s="2" t="inlineStr"><is><t>UKŁAD PRZYWSPÓŁCZULNY</t></is></c><c r="B995" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C995" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D995" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E995" s="2" t="inlineStr"><is><t>Odwracalne inhibitory acetylocholinesterazy są stosowane w leczeniu:</t></is></c><c r="F995" s="2" t="inlineStr"><is><t>nużliwości mięśni – tak ale musi być odwracalny (-stygmina)</t></is></c><c r="G995" s="2" t="inlineStr"><is><t>pooperacyjnej niedrożności jelit- można by próbować cholinolitykami np. kawa działa taka zwykla do picia</t></is></c><c r="H995" s="2" t="inlineStr"><is><t>choroby Alzheimera CHOLINOMIMETYKI</t></is></c><c r="I995" s="2" t="inlineStr" /><c r="J995" s="2" t="inlineStr" /><c r="K995" s="2" t="inlineStr"><is><t>zatruć związkami fosforoorganicznymi – powinny być cholinolityki</t></is></c><c r="L995" s="2" t="inlineStr" /><c r="M995" s="2" t="inlineStr" /><c r="N995" s="2" t="inlineStr" /><c r="O995" s="2" t="inlineStr" /><c r="P995" s="2" t="inlineStr"><is><t>EGZAMIN IWL 20 czerwca 2018</t></is></c><c r="Q995" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="996"><c r="A996" s="2" t="inlineStr"><is><t>NARKOTYCZNE LEKI PRZECIWBÓLOWE</t></is></c><c r="B996" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C996" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D996" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E996" s="2" t="inlineStr"><is><t>Zaznacz prawidłowe pary dotyczące leczenia uzależnień i wybranego leku:</t></is></c><c r="F996" s="2" t="inlineStr"><is><t>uzależnienie od alkoholu – nalmefen –</t></is></c><c r="G996" s="2" t="inlineStr"><is><t>uzależnienie od heroiny – metadon abstynencja od opioidów dożylnych zmiana na po, to jest preferowany rodzaj ekspozycji</t></is></c><c r="H996" s="2" t="inlineStr" /><c r="I996" s="2" t="inlineStr" /><c r="J996" s="2" t="inlineStr" /><c r="K996" s="2" t="inlineStr"><is><t>uzależnienie od nikotyny – klonidyna nie, tylko BUPROPION albo syntetyczny agoaganistyczne rec nikotynowe</t></is></c><c r="L996" s="2" t="inlineStr"><is><t>uzależnienie od amfetaminy – wareniklina</t></is></c><c r="M996" s="2" t="inlineStr" /><c r="N996" s="2" t="inlineStr" /><c r="O996" s="2" t="inlineStr" /><c r="P996" s="2" t="inlineStr"><is><t>EGZAMIN IWL 20 czerwca 2018</t></is></c><c r="Q996" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="997"><c r="A997" s="2" t="inlineStr"><is><t>STANY NAGŁE</t></is></c><c r="B997" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C997" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D997" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E997" s="2" t="inlineStr"><is><t>Wskaż prawidłowe pary płyn infuzyjny – możliwe działanie niepożądane:</t></is></c><c r="F997" s="2" t="inlineStr"><is><t>5% roztwór glukozy – hiponatremia</t></is></c><c r="G997" s="2" t="inlineStr"><is><t>HES (hydroksyetylowana skrobia) – ostre uszkodzenie nerek</t></is></c><c r="H997" s="2" t="inlineStr"><is><t>5% roztwór albuminy – anafilaksja</t></is></c><c r="I997" s="2" t="inlineStr"><is><t>dekstran 70 000 – działanie przeciwkrzepliwe i jeszcze większa podatność na wstrząsy Najlepszy wybór to albuminy 20%, ale trudne do pozyskania i drogie Ewentualnie żelatyna 3,4-4,5%</t></is></c><c r="J997" s="2" t="inlineStr" /><c r="K997" s="2" t="inlineStr" /><c r="L997" s="2" t="inlineStr" /><c r="M997" s="2" t="inlineStr" /><c r="N997" s="2" t="inlineStr" /><c r="O997" s="2" t="inlineStr" /><c r="P997" s="2" t="inlineStr"><is><t>EGZAMIN IWL 20 czerwca 2018</t></is></c><c r="Q997" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="998"><c r="A998" s="2" t="inlineStr"><is><t>NADCIŚNIENIE TĘTNICZE</t></is></c><c r="B998" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C998" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D998" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E998" s="2" t="inlineStr"><is><t>Wskaż prawidłowe stwierdzenie dotyczące leczenia hipotensyjnego tiazydowymi lekami moczopędnymi:</t></is></c><c r="F998" s="2" t="inlineStr"><is><t>tiazydy mogą bezpośrednio oddziaływać na ścianę naczyń i zmniejszać systemowy opór naczyniowy</t></is></c><c r="G998" s="2" t="inlineStr"><is><t>pełny efekt hipotensyjny występuje po kilkunastu dniach leczenia</t></is></c><c r="H998" s="2" t="inlineStr"><is><t>blokada kotransportera Na-Cl w kanaliku dystalnym prowadzi do zwiększenia natriurezy</t></is></c><c r="I998" s="2" t="inlineStr" /><c r="J998" s="2" t="inlineStr" /><c r="K998" s="2" t="inlineStr"><is><t>ich skuteczność w leczeniu przewlekłym wynika przede wszystkim ze zmniejszenia objętości osocza i rzutu serca</t></is></c><c r="L998" s="2" t="inlineStr" /><c r="M998" s="2" t="inlineStr" /><c r="N998" s="2" t="inlineStr" /><c r="O998" s="2" t="inlineStr" /><c r="P998" s="2" t="inlineStr"><is><t>EGZAMIN IWL 20 czerwca 2018</t></is></c><c r="Q998" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="999"><c r="A999" s="2" t="inlineStr"><is><t>UKŁAD PRZYWSPÓŁCZULNY</t></is></c><c r="B999" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C999" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D999" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E999" s="2" t="inlineStr"><is><t>Suksametonium może być przyczyną:</t></is></c><c r="F999" s="2" t="inlineStr"><is><t>drżenia włókienkowego mięśni szkieletowych</t></is></c><c r="G999" s="2" t="inlineStr"><is><t>zaburzeń oddychania</t></is></c><c r="H999" s="2" t="inlineStr"><is><t>zespołu hipertermii złośliwej</t></is></c><c r="I999" s="2" t="inlineStr"><is><t>długotrwałego efektu zwiotczającego u osób z dysfunkcją acetylcholinesterazy</t></is></c><c r="J999" s="2" t="inlineStr" /><c r="K999" s="2" t="inlineStr" /><c r="L999" s="2" t="inlineStr" /><c r="M999" s="2" t="inlineStr" /><c r="N999" s="2" t="inlineStr" /><c r="O999" s="2" t="inlineStr" /><c r="P999" s="2" t="inlineStr"><is><t>EGZAMIN IWL 20 czerwca 2018</t></is></c><c r="Q999" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="1000"><c r="A1000" s="2" t="inlineStr"><is><t>UKŁAD ODDECHOWY</t></is></c><c r="B1000" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C1000" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1000" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1000" s="2" t="inlineStr"><is><t>W celu łagodzenia suchego kaszlu można wybrać:</t></is></c><c r="F1000" s="2" t="inlineStr"><is><t>dekstrometorfan</t></is></c><c r="G1000" s="2" t="inlineStr"><is><t>kodeinę</t></is></c><c r="H1000" s="2" t="inlineStr"><is><t>butamirat Powinniśmy stosować zwykle stosować coś co wzmaga kaszel jeśli jest mokry. Jak suchy to chronimy oskrzela, żeby się nie namęczyły bo to już nie jest żadna funkcja ochronna</t></is></c><c r="I1000" s="2" t="inlineStr" /><c r="J1000" s="2" t="inlineStr" /><c r="K1000" s="2" t="inlineStr"><is><t>bromheksynę – ze swoim metabolitem ambroksolem jest MUKOKINETYCZNA</t></is></c><c r="L1000" s="2" t="inlineStr" /><c r="M1000" s="2" t="inlineStr" /><c r="N1000" s="2" t="inlineStr" /><c r="O1000" s="2" t="inlineStr" /><c r="P1000" s="2" t="inlineStr"><is><t>EGZAMIN IWL 20 czerwca 2018</t></is></c><c r="Q1000" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="1001"><c r="A1001" s="2" t="inlineStr"><is><t>LEKI PRZECIWPASOŻYTNICZE</t></is></c><c r="B1001" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C1001" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1001" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1001" s="2" t="inlineStr"><is><t>Albendazol stosowany jest w jelitowej infestacji:1:30</t></is></c><c r="F1001" s="2" t="inlineStr"><is><t>glistą ludzką</t></is></c><c r="G1001" s="2" t="inlineStr"><is><t>tasiemcem uzbrojonym</t></is></c><c r="H1001" s="2" t="inlineStr"><is><t>owsikami PERMETRYNA (1%) WSZAWICA (5%) ŚWIEŻB Pasożyty przewodu pokarmowego są mega częste na całym świecie, w Polsce mniej ale ogólnie dużo</t></is></c><c r="I1001" s="2" t="inlineStr" /><c r="J1001" s="2" t="inlineStr" /><c r="K1001" s="2" t="inlineStr"><is><t>lambliami</t></is></c><c r="L1001" s="2" t="inlineStr" /><c r="M1001" s="2" t="inlineStr" /><c r="N1001" s="2" t="inlineStr" /><c r="O1001" s="2" t="inlineStr" /><c r="P1001" s="2" t="inlineStr"><is><t>EGZAMIN IWL 20 czerwca 2018</t></is></c><c r="Q1001" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="1002"><c r="A1002" s="2" t="inlineStr"><is><t>LEKI PRZECIWDEPRESYJNE</t></is></c><c r="B1002" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C1002" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1002" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1002" s="2" t="inlineStr"><is><t>Napad paniki należy leczyć stosując doraźnie:</t></is></c><c r="F1002" s="2" t="inlineStr"><is><t>techniki relaksacyjne</t></is></c><c r="G1002" s="2" t="inlineStr"><is><t>alprazolam</t></is></c><c r="H1002" s="2" t="inlineStr"><is><t>fluoksetynę – też długi lęk LĘK – główna grupa przewlekłego to aktywujące układ serotoninowy najpierw były TLPD – KLOMIPRANINA ( w Polsce już nie ma ) teraz dominują SSRI – fluoksetyne – rozwijają powoli swoje działania ALE DORAŹNIE – Benzodiazepiny – fatalne ale dobre do szybkiego efektu alprazolam</t></is></c><c r="I1002" s="2" t="inlineStr" /><c r="J1002" s="2" t="inlineStr" /><c r="K1002" s="2" t="inlineStr"><is><t>pregabalinę</t></is></c><c r="L1002" s="2" t="inlineStr" /><c r="M1002" s="2" t="inlineStr" /><c r="N1002" s="2" t="inlineStr" /><c r="O1002" s="2" t="inlineStr" /><c r="P1002" s="2" t="inlineStr"><is><t>EGZAMIN IWL 20 czerwca 2018</t></is></c><c r="Q1002" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="1003"><c r="A1003" s="2" t="inlineStr"><is><t>GLIKOKORTYKOSTEROIDY</t></is></c><c r="B1003" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C1003" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1003" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1003" s="2" t="inlineStr"><is><t>Fenoterol może być przyczyną: - niezbyt ulubiona grupa szybko działających bronchodylatacyjnych</t></is></c><c r="F1003" s="2" t="inlineStr"><is><t>Tachykardii – zwiększenie siły skurczu zwiększenie zapotrzebowanie na tlen</t></is></c><c r="G1003" s="2" t="inlineStr"><is><t>drżenia mięśni – wygląda tak jakby miał dreszcze</t></is></c><c r="H1003" s="2" t="inlineStr"><is><t>hiperglikemii – tak bo b2 jest w wątrobie i powoduje glikogenolizę</t></is></c><c r="I1003" s="2" t="inlineStr"><is><t>hamowania skurczów ciężarnej macicy – stosowane jako TOKOLIZA – wygaszanie skurczu u ciężarnej wtedy są iv tylko po to żeby podać betametazon lub deksametazon, żeby dziecko sobie wypracowalo surfaktant. Do bani bo SABA -</t></is></c><c r="J1003" s="2" t="inlineStr" /><c r="K1003" s="2" t="inlineStr" /><c r="L1003" s="2" t="inlineStr" /><c r="M1003" s="2" t="inlineStr" /><c r="N1003" s="2" t="inlineStr" /><c r="O1003" s="2" t="inlineStr" /><c r="P1003" s="2" t="inlineStr"><is><t>EGZAMIN IWL 20 czerwca 2018</t></is></c><c r="Q1003" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="1004"><c r="A1004" s="2" t="inlineStr"><is><t>UKŁAD WSPÓŁCZULNY</t></is></c><c r="B1004" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C1004" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1004" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1004" s="2" t="inlineStr"><is><t>Długo działające beta2-mimetyki (LABA):</t></is></c><c r="F1004" s="2" t="inlineStr"><is><t>podawane przewlekle powodują down-regulację receptorów beta2 adrenergicznych w oskrzelach - klasyczne zjawisko jak któryś z układów jest niedopieszczony albo obładowany ! tu jest ciągle atakowany bo mimetyk wiec naturalny mechanizm adaptacji to zmniejszenie liczby receptorów</t></is></c><c r="G1004" s="2" t="inlineStr" /><c r="H1004" s="2" t="inlineStr" /><c r="I1004" s="2" t="inlineStr" /><c r="J1004" s="2" t="inlineStr" /><c r="K1004" s="2" t="inlineStr"><is><t>nie powinny być podawane razem z glikokortykosteroidami , które blokują wytwarzanie białek receptorów beta2-adrenergicznych – powinny być, to jest bardzo dobre połączenie w ASTMIE w jednym inhalatorze</t></is></c><c r="L1004" s="2" t="inlineStr"><is><t>mogą być przyczyną istotnej klinicznie hiperkaliemii - 18 min ZABURZENIA ELEKTROLITOWE TO HIPERGLIKEMIA a drugie to HIPOKALIEMIA</t></is></c><c r="M1004" s="2" t="inlineStr"><is><t>wykazują działanie przeciwzapalne – Nie dlatego zasadne jest łączenie z GKS</t></is></c><c r="N1004" s="2" t="inlineStr" /><c r="O1004" s="2" t="inlineStr" /><c r="P1004" s="2" t="inlineStr"><is><t>EGZAMIN IWL 20 czerwca 2018</t></is></c><c r="Q1004" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="1005"><c r="A1005" s="2" t="inlineStr"><is><t>NIEOPIOIDOWE LEKI PRZECIWBÓLOWE</t></is></c><c r="B1005" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C1005" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1005" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1005" s="2" t="inlineStr"><is><t>Wskaż prawidłowe stwierdzenie dotyczące niesteroidowych leków przeciwzapalnych:</t></is></c><c r="F1005" s="2" t="inlineStr"><is><t>ketoprofen powoduje większe ryzyko występowania krwawienia z górnego odcinka przewodu pokarmowego niżibuprofen – wszystkie badania wskazują że najmniej gastroszkodliwy jest ibuprofen !, ale jest dość szkodliwy kardio więc średniawka. Doodbytniczo • dajemy tylko jak choroba dotyczy jelita np. – wrzodziejące zapalenie jelita – można też dawać po, ale ma sens podanie czopek albo wlewke tego samego leku np. MESALAZYNA albo SALAZYNE z SULFAPIRYDYNĄ. • Drgawki gorączkowe u dzieci – paracetamol czy diazepam (relanium) – ale to dlatego, że to brak innej drogi. NLPZ nie można podawać doodbytniczo ! – jedyny skutek to uszkodzenie błony dolnego p.p</t></is></c><c r="G1005" s="2" t="inlineStr" /><c r="H1005" s="2" t="inlineStr" /><c r="I1005" s="2" t="inlineStr" /><c r="J1005" s="2" t="inlineStr" /><c r="K1005" s="2" t="inlineStr"><is><t>meloksykam jest preferencyjnym inhibitorem COX-1 – oczywiście, że nie bo on i nimesulid i diklofenak to preferencyjne cox-2 . ASA jest preferencyjny w COX-1</t></is></c><c r="L1005" s="2" t="inlineStr"><is><t>zastąpienie drogi doustnej podania diklofenaku drogą doodbytniczą zmniejsza ryzyko wystąpienia działań niepożądanych – zawsze na takie pytania można odpowiadać, ze to nie prawda, bo droga doodbytnicza to fatalna droga podawania leków. PRZECHODZI TEŻ EFEKT PIERWSZEGO PRZEJŚCIA – czopki wlewki itp. A na dodatek diklofenak to słaby kwas i jak włożymy do zasadowego środowiska odbytnicy to wgł zły pomysł bo się szybko zjonizuje i może silnie uszkodzić enterocyty</t></is></c><c r="M1005" s="2" t="inlineStr"><is><t>nimesulid należy do najmniej hepatotoksycznych NLPZ – on i diklofenat są najbardziej</t></is></c><c r="N1005" s="2" t="inlineStr" /><c r="O1005" s="2" t="inlineStr" /><c r="P1005" s="2" t="inlineStr"><is><t>EGZAMIN IWL 20 czerwca 2018</t></is></c><c r="Q1005" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="1006"><c r="A1006" s="2" t="inlineStr"><is><t>NADCIŚNIENIE TĘTNICZE</t></is></c><c r="B1006" s="2" t="inlineStr"><is><t>Farmakokinetyka</t></is></c><c r="C1006" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1006" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1006" s="2" t="inlineStr"><is><t>Lekiem prekursorowym jest:</t></is></c><c r="F1006" s="2" t="inlineStr"><is><t>Enalapryl -</t></is></c><c r="G1006" s="2" t="inlineStr"><is><t>Cyklezonid – To ten unikalny gks który się przekształca tylko oskrzalach do leków, połkiety wcale nie działa</t></is></c><c r="H1006" s="2" t="inlineStr"><is><t>Lewodopa – klasyczny prekursor dopaminy w Parkinsonie bo dopamina nie przechodzi przez bariere krew mózg. - Pryl co się kończą to zawsze proleki bo są przekształcane tylko KAPTOPRYL I LIZYNOPRYL są aktywnie działające</t></is></c><c r="I1006" s="2" t="inlineStr" /><c r="J1006" s="2" t="inlineStr" /><c r="K1006" s="2" t="inlineStr"><is><t>Furosemid – z diuretyków wszystkie są aktywne POZA SPIRONOLAKTONEM</t></is></c><c r="L1006" s="2" t="inlineStr" /><c r="M1006" s="2" t="inlineStr" /><c r="N1006" s="2" t="inlineStr" /><c r="O1006" s="2" t="inlineStr" /><c r="P1006" s="2" t="inlineStr"><is><t>EGZAMIN IWL 20 czerwca 2018</t></is></c><c r="Q1006" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="1007"><c r="A1007" s="2" t="inlineStr"><is><t>LEKI IMMUNOSUPRESYJNE</t></is></c><c r="B1007" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C1007" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1007" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1007" s="2" t="inlineStr"><is><t>Cyklosporyna: - obszar immunosuperesyjny</t></is></c><c r="F1007" s="2" t="inlineStr"><is><t>jest stosowana w zapobieganiu odrzucania przeszczepu po alogenicznym przeszczepieniu narządów unaczynionych – to jej główne zalecenie, ale też się stosuje w autoagresji takich jak toczeń rumieniowaty układowy. TAKROLIMUS ją wypiera bo jest bardziej przewidywalny ale też jest inh kalcyneuryny</t></is></c><c r="G1007" s="2" t="inlineStr"><is><t>zwiększa ryzyko chorób rozrostowych układu chłonnego – WSZYSTKIE IMMUNOSUPRESYJNE m.in. prednizon sirolimus – 2 podstawowe DN • Zwiększa szanse infekcji - reaktywacja cytomegalii/ gruźlicy i de novo • Zwiększa ryzyko chorób rozrostowych Niezbyt umiemy spacyfikować odpowiedz humoralna czyli limf B , wiec jak są odrzucenia humoralne z atakiem przeciwciałami to, źle idzie nam wygaszanie. ROBI SIĘ PLAZMAFEREZE zamieniając jego osocze na preparaty albuminowe albo osocze dawców</t></is></c><c r="H1007" s="2" t="inlineStr" /><c r="I1007" s="2" t="inlineStr" /><c r="J1007" s="2" t="inlineStr" /><c r="K1007" s="2" t="inlineStr"><is><t>jest rekombinowanym w pełni ludzkim przeciwciałem monoklonalnym –</t></is></c><c r="L1007" s="2" t="inlineStr"><is><t>neutralizuje biologiczną aktywność TNF – to typowe leki na RZS gro terapii monoklonalne przeciwciał ADALIMUMAM ETANERCEPT – to białko fuzyjne</t></is></c><c r="M1007" s="2" t="inlineStr" /><c r="N1007" s="2" t="inlineStr" /><c r="O1007" s="2" t="inlineStr" /><c r="P1007" s="2" t="inlineStr"><is><t>EGZAMIN IWL 20 czerwca 2018</t></is></c><c r="Q1007" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="1008"><c r="A1008" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B1008" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C1008" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1008" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1008" s="2" t="inlineStr"><is><t>Do leków o udowodnionym korzystnym działaniu w profilaktyce wtórnej niedokrwiennego udaru mózgu należy:</t></is></c><c r="F1008" s="2" t="inlineStr"><is><t>kwas acetylosalicylowy – bo antyagregacyjny</t></is></c><c r="G1008" s="2" t="inlineStr"><is><t>atorwastatyna – dobra w miażdżycy max dawka 80 rosuwastatyna to 40mg/d</t></is></c><c r="H1008" s="2" t="inlineStr"><is><t>klopidogrel – bo antyagregacyjny udar mózgu profilaktyka – głównie chcemy się pozbyć miażdżycy i migotania przedsionków! GRUPA EKSTREMALNEGO RYZYKA to ldl powinno być poniżej 40mg/dl !!! THE LOWER THE BETTER !!!</t></is></c><c r="I1008" s="2" t="inlineStr" /><c r="J1008" s="2" t="inlineStr" /><c r="K1008" s="2" t="inlineStr"><is><t>kwas traneksamowy – nie to antidotum na zbyt aktywną fibrynolizę to inh t-PA, nie bezpośrednio, ale zmienia konformacje</t></is></c><c r="L1008" s="2" t="inlineStr" /><c r="M1008" s="2" t="inlineStr" /><c r="N1008" s="2" t="inlineStr" /><c r="O1008" s="2" t="inlineStr" /><c r="P1008" s="2" t="inlineStr"><is><t>EGZAMIN IWL 20 czerwca 2018</t></is></c><c r="Q1008" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="1009"><c r="A1009" s="2" t="inlineStr"><is><t>CHOROBA PARKINSONA</t></is></c><c r="B1009" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C1009" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1009" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1009" s="2" t="inlineStr"><is><t>Lewodopa:</t></is></c><c r="F1009" s="2" t="inlineStr"><is><t>jest jednym z najskuteczniejszych leków stosowanych w terapii choroby Parkinsona – tak dlatego nie lubimy od niej zaczynać, bo chcemy zatrzymać sobie na gorszy czas</t></is></c><c r="G1009" s="2" t="inlineStr"><is><t>ma krótki okres półtrwania i dlatego wymaga wielokrotnego podawania w ciągu doby – dlatego są preparaty o zmodyfikowanym uwalnianiu</t></is></c><c r="H1009" s="2" t="inlineStr"><is><t>podczas długotrwałego leczenia może wywołać fluktuacje ruchowe i dyskinezy – mogą też pojawiać się bradykinezje</t></is></c><c r="I1009" s="2" t="inlineStr"><is><t>może wywoływać działania niepożądane ze strony przewodu pokarmowego – tak bo to lek o działaniu dopaminowym, teraz dajemy jej małe dawki bo ZAWSZE DAJEMY Z INHIBITORAMI OBWODOWEGO PRZEKSZTAŁĆANIA Zespół on-off - takie dziwne niewyjaśnione zjawisko, że lek nagle super działa a potem nagle przestaje działać</t></is></c><c r="J1009" s="2" t="inlineStr" /><c r="K1009" s="2" t="inlineStr" /><c r="L1009" s="2" t="inlineStr" /><c r="M1009" s="2" t="inlineStr" /><c r="N1009" s="2" t="inlineStr" /><c r="O1009" s="2" t="inlineStr" /><c r="P1009" s="2" t="inlineStr"><is><t>EGZAMIN IWL 20 czerwca 2018</t></is></c><c r="Q1009" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="1010"><c r="A1010" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B1010" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C1010" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1010" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1010" s="2" t="inlineStr"><is><t>Kokaina:</t></is></c><c r="F1010" s="2" t="inlineStr"><is><t>hamuje wychwyt zwrotny dopaminy w szczelinie synaptycznej</t></is></c><c r="G1010" s="2" t="inlineStr"><is><t>może powodować wystąpienie zawału mięśnia sercowego – tak nawet u 20 latka może wywołać zawał jak serce nie ma zwężonych naczyń</t></is></c><c r="H1010" s="2" t="inlineStr"><is><t>może powodować krwawienia wewnątrzczaszkowe – każdy kto zwiększa ciśnienie krwi może takie spowodować</t></is></c><c r="I1010" s="2" t="inlineStr" /><c r="J1010" s="2" t="inlineStr" /><c r="K1010" s="2" t="inlineStr"><is><t>hamuje aktywność receptorów dla kwasu glutaminowego</t></is></c><c r="L1010" s="2" t="inlineStr" /><c r="M1010" s="2" t="inlineStr" /><c r="N1010" s="2" t="inlineStr" /><c r="O1010" s="2" t="inlineStr" /><c r="P1010" s="2" t="inlineStr"><is><t>EGZAMIN IWL 20 czerwca 2018</t></is></c><c r="Q1010" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="1011"><c r="A1011" s="2" t="inlineStr"><is><t>LEKI PRZECIWHISTAMINOWE</t></is></c><c r="B1011" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C1011" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1011" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1011" s="2" t="inlineStr"><is><t>W alergicznym zapaleniu spojówek można zastosować dospojówkowo:</t></is></c><c r="F1011" s="2" t="inlineStr"><is><t>Antazolinę – jest do przerywania napadów w migotaniu. Tylko leki p￾histaminowe 1 generacji są iv !! klemastyna – najlepszy lek 1- generacji to ratunek w ciężkich stanach anafilaksji !! łącznie z adrenaliną im</t></is></c><c r="G1011" s="2" t="inlineStr"><is><t>azelastynę</t></is></c><c r="H1011" s="2" t="inlineStr"><is><t>kromoglikan sodowy – lek stabilizujący mastocyt i nie ma zdolności już uwalniania jakiejkolwiek mediatorów</t></is></c><c r="I1011" s="2" t="inlineStr"><is><t>olopatadynę ANAFILAKSJA ! STAN NAGŁY • Klemastyna iv , z 1 generacji p-histaminowych wyjątkowa bo działa 12 h, a te reakcje się długo rozkręcają, wiec jak się uratuje a anfilaksjii trzeba zatrzymać w szpitalu czekając na drugą fazę • Adrenalina im KARDIOWERSJA FARMAKOLOGICZNA Antazolina</t></is></c><c r="J1011" s="2" t="inlineStr" /><c r="K1011" s="2" t="inlineStr" /><c r="L1011" s="2" t="inlineStr" /><c r="M1011" s="2" t="inlineStr" /><c r="N1011" s="2" t="inlineStr" /><c r="O1011" s="2" t="inlineStr" /><c r="P1011" s="2" t="inlineStr"><is><t>EGZAMIN IWL 20 czerwca 2018</t></is></c><c r="Q1011" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="1012"><c r="A1012" s="2" t="inlineStr"><is><t>NARKOTYCZNE LEKI PRZECIWBÓLOWE</t></is></c><c r="B1012" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C1012" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1012" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1012" s="2" t="inlineStr"><is><t>Stosowanie preparatu złożonego bupropionu z naltreksonem w leczeniu otyłości:</t></is></c><c r="F1012" s="2" t="inlineStr"><is><t>ma wpływ na ośrodkowy układ nagrody – głównie bupropion bo działa dopaminowo</t></is></c><c r="G1012" s="2" t="inlineStr"><is><t>zwiększa i wydłuża uczucie sytości</t></is></c><c r="H1012" s="2" t="inlineStr"><is><t>ma zwiększoną skuteczność kliniczną ze względu na efektsynergistyczny bupropionu i naltreksonu – dlatego połączenie a nie monoterapia Nie wierzymy, że się utrzymają • bupropion – lek zmniejszający wychwyt zwrotny dopaminy i NIKOTYNA . • Naltrekson tylko PO. ( nalokson tylko iv ) – nieselektywny opioid !</t></is></c><c r="I1012" s="2" t="inlineStr" /><c r="J1012" s="2" t="inlineStr" /><c r="K1012" s="2" t="inlineStr"><is><t>jest wskazane dla wszystkich osób z wyjściową wartością BMI wynoszącą ≥27 kg/m2 – nie bo otyłość to 30 lub więcej. A u tych 27 to tylko jak są współistniejące</t></is></c><c r="L1012" s="2" t="inlineStr" /><c r="M1012" s="2" t="inlineStr" /><c r="N1012" s="2" t="inlineStr" /><c r="O1012" s="2" t="inlineStr" /><c r="P1012" s="2" t="inlineStr"><is><t>EGZAMIN IWL 20 czerwca 2018</t></is></c><c r="Q1012" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="1013"><c r="A1013" s="2" t="inlineStr"><is><t>UKŁAD WSPÓŁCZULNY</t></is></c><c r="B1013" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C1013" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1013" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1013" s="2" t="inlineStr"><is><t>Dodatek adrenaliny do lidokainy w lekach do znieczulenia miejscowego może powodować:</t></is></c><c r="F1013" s="2" t="inlineStr"><is><t>zwiększone ryzyko martwicy tkanek po podaniach obwodowych – oj może, dlatego nie można podawać do palców czy innych dystalnie leżących partii ciała</t></is></c><c r="G1013" s="2" t="inlineStr"><is><t>wydłużenie czasu działania lidokainy – tak bo trzyma w jednym miejscu i to spowalnia jej metabolizm ogólnoustrojowy Adrenalina powoduje obkurczenie naczyń krwionośnych, więc lek nie ma jak uciec z danego miejsca</t></is></c><c r="H1013" s="2" t="inlineStr" /><c r="I1013" s="2" t="inlineStr" /><c r="J1013" s="2" t="inlineStr" /><c r="K1013" s="2" t="inlineStr"><is><t>zwiększone niebezpieczeństwo zatrzymania oddechu – adrenalina wgl nie zatrzymuje oddechu bo stymuluje układ wspolczulny wiec w drugą strone</t></is></c><c r="L1013" s="2" t="inlineStr"><is><t>zahamowanie metabolizmu lidokainy – nie ona hamuje wchłanianie lidokainy do systemowego działania</t></is></c><c r="M1013" s="2" t="inlineStr" /><c r="N1013" s="2" t="inlineStr" /><c r="O1013" s="2" t="inlineStr" /><c r="P1013" s="2" t="inlineStr"><is><t>EGZAMIN IWL 20 czerwca 2018</t></is></c><c r="Q1013" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="1014"><c r="A1014" s="2" t="inlineStr"><is><t>NIEWYDOLNOŚĆ SERCA</t></is></c><c r="B1014" s="2" t="inlineStr"><is><t>Sposób podania</t></is></c><c r="C1014" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1014" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1014" s="2" t="inlineStr"><is><t>Digoksyna: - nie lubimy</t></is></c><c r="F1014" s="2" t="inlineStr"><is><t>podtrzymuje aktywację baroreceptorów zatoki szyjnej przy obniżeniu ciśnienia krwi u osób z niewydolnością serca – bardzo ważna cecha</t></is></c><c r="G1014" s="2" t="inlineStr"><is><t>podana doustnie może być nieskuteczna z powodu dezaktywacji przez bakterie jelitowe – 10% ma takie bakterie które KOMPLETNIE JA DYZAKTYWUJĄ</t></is></c><c r="H1014" s="2" t="inlineStr" /><c r="I1014" s="2" t="inlineStr" /><c r="J1014" s="2" t="inlineStr" /><c r="K1014" s="2" t="inlineStr"><is><t>powoduje kardiowersję migotania przedsionków do rytmu zatokowego – nie po to żeby umiarowić rytm tylko żeby zwolnić przewodzenie między przedsionkiem a komorą, wiec uporządkowuje czynność komór. ALE to nie kardiowersja</t></is></c><c r="L1014" s="2" t="inlineStr"><is><t>jest lekiem o korzystnym działaniu rokowniczym w skurczowej niewydolności serca – NIE MA DOWODÓW, ŻE JEST KORZYSTNA ROKOWNICZO JASNE STRONY CIEMNIEJ MOCY ! W małych dawakach korzystnie moduluje odpowiedz baroreceptorów, tak że nie wszczynają alarmu przy niskim ciśnieniu !</t></is></c><c r="M1014" s="2" t="inlineStr" /><c r="N1014" s="2" t="inlineStr" /><c r="O1014" s="2" t="inlineStr" /><c r="P1014" s="2" t="inlineStr"><is><t>EGZAMIN IWL 20 czerwca 2018</t></is></c><c r="Q1014" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="1015"><c r="A1015" s="2" t="inlineStr"><is><t>UKŁAD PRZYWSPÓŁCZULNY</t></is></c><c r="B1015" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C1015" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1015" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1015" s="2" t="inlineStr"><is><t>Skopolamina (hioscyna): - TO CHOLINOLITYK</t></is></c><c r="F1015" s="2" t="inlineStr"><is><t>dobrze przenika przez barierę krew- mózg – tak , butylobromek skopolaminy używany w kolce nerkowej czy żółciowej szybko rozkurcza mm gładkie</t></is></c><c r="G1015" s="2" t="inlineStr"><is><t>zwalnia czynność serca</t></is></c><c r="H1015" s="2" t="inlineStr" /><c r="I1015" s="2" t="inlineStr" /><c r="J1015" s="2" t="inlineStr" /><c r="K1015" s="2" t="inlineStr"><is><t>selektywnie blokuje receptory H1 – antagonista muskarynowych</t></is></c><c r="L1015" s="2" t="inlineStr"><is><t>zwiększa motorykę przewodu pokarmowego – blokuje układ przywspolczulny wiec działa spazmolitycznie !</t></is></c><c r="M1015" s="2" t="inlineStr" /><c r="N1015" s="2" t="inlineStr" /><c r="O1015" s="2" t="inlineStr" /><c r="P1015" s="2" t="inlineStr"><is><t>EGZAMIN IWL 20 czerwca 2018</t></is></c><c r="Q1015" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="1016"><c r="A1016" s="2" t="inlineStr"><is><t>UKŁAD WSPÓŁCZULNY</t></is></c><c r="B1016" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C1016" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1016" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1016" s="2" t="inlineStr"><is><t>Teoretyczną przesłanką stosowania beta-adrenolityków w przewlekłej skurczowej niewydolności serca jest:</t></is></c><c r="F1016" s="2" t="inlineStr"><is><t>odwracanie beta-down regulacji – bardzo ważny mechanizm w niewydolności serca</t></is></c><c r="G1016" s="2" t="inlineStr"><is><t>korzystny bezpośredni wpływ hemodynamiczny – owszem odciążają bo spowalniają rytm , odciążają z siły skurczu i zmniejszają afterload</t></is></c><c r="H1016" s="2" t="inlineStr"><is><t>zapobieganie proarytmicznemu działaniu katecholamin – w chorym sercu najważniejsze co mogą zrobić to zablokowanie proarytmiczne działania katecholamin</t></is></c><c r="I1016" s="2" t="inlineStr" /><c r="J1016" s="2" t="inlineStr" /><c r="K1016" s="2" t="inlineStr"><is><t>zwiększenie naprężenia ściany lewej komory</t></is></c><c r="L1016" s="2" t="inlineStr" /><c r="M1016" s="2" t="inlineStr" /><c r="N1016" s="2" t="inlineStr" /><c r="O1016" s="2" t="inlineStr" /><c r="P1016" s="2" t="inlineStr"><is><t>EGZAMIN IWL 20 czerwca 2018</t></is></c><c r="Q1016" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="1017"><c r="A1017" s="2" t="inlineStr"><is><t>LEKI PRZECIWHISTAMINOWE</t></is></c><c r="B1017" s="2" t="inlineStr"><is><t>Farmakokinetyka</t></is></c><c r="C1017" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1017" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1017" s="2" t="inlineStr"><is><t>Rupatadyna: - lek przeciwhistaminowy 2 generacji</t></is></c><c r="F1017" s="2" t="inlineStr"><is><t>ma minimalny potencjał sedatywny – tak bo to 2 generacja</t></is></c><c r="G1017" s="2" t="inlineStr"><is><t>oprócz antagonizmu wobec receptora H1 wykazuje przeciwzapalną aktywność pozareceptorową – faktycznie niektóre leki 2 generacji mają taką cechę, to jest ich plus bo każda alergia ma podłoże zapalne</t></is></c><c r="H1017" s="2" t="inlineStr"><is><t>w znacznym stopniu ulega efektowi pierwszego przejścia z powstaniem aktywnych metabolitów</t></is></c><c r="I1017" s="2" t="inlineStr"><is><t>w dawkach zalecanych nie wydłuża skorygowanego odstępu cQT – wszystkie które wydłużały zostały wyeliminowane TYLKO EBASTYNA WYDŁUŻA</t></is></c><c r="J1017" s="2" t="inlineStr" /><c r="K1017" s="2" t="inlineStr" /><c r="L1017" s="2" t="inlineStr" /><c r="M1017" s="2" t="inlineStr" /><c r="N1017" s="2" t="inlineStr" /><c r="O1017" s="2" t="inlineStr" /><c r="P1017" s="2" t="inlineStr"><is><t>EGZAMIN IWL 20 czerwca 2018</t></is></c><c r="Q1017" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="1018"><c r="A1018" s="2" t="inlineStr"><is><t>NADCIŚNIENIE TĘTNICZE</t></is></c><c r="B1018" s="2" t="inlineStr"><is><t>Przeciwwskazania</t></is></c><c r="C1018" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1018" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1018" s="2" t="inlineStr"><is><t>U pacjentów z eGFR&lt;30 ml/min należy zrezygnować ze stosowania:</t></is></c><c r="F1018" s="2" t="inlineStr"><is><t>metforminy</t></is></c><c r="G1018" s="2" t="inlineStr"><is><t>hydrochlorotiazydu To 4 stadium niewydolności nerek ! następne stadium to DIALIZA METFORMINA ! – poniżej nie można TIAZYDY DIURETYKI – nie działają</t></is></c><c r="H1018" s="2" t="inlineStr" /><c r="I1018" s="2" t="inlineStr" /><c r="J1018" s="2" t="inlineStr" /><c r="K1018" s="2" t="inlineStr"><is><t>metoprololu</t></is></c><c r="L1018" s="2" t="inlineStr"><is><t>amlodypiny – całkowicie wątrobowa</t></is></c><c r="M1018" s="2" t="inlineStr" /><c r="N1018" s="2" t="inlineStr" /><c r="O1018" s="2" t="inlineStr" /><c r="P1018" s="2" t="inlineStr"><is><t>EGZAMIN IWL 20 czerwca 2018</t></is></c><c r="Q1018" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="1019"><c r="A1019" s="2" t="inlineStr"><is><t>LEKI PRZECIWDEPRESYJNE</t></is></c><c r="B1019" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C1019" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1019" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1019" s="2" t="inlineStr"><is><t>Wenlafaksyna: i w tej samej grupie z DULOKSETYNĄ</t></is></c><c r="F1019" s="2" t="inlineStr"><is><t>może być podawana w uogólnionych zaburzeniach lękowych</t></is></c><c r="G1019" s="2" t="inlineStr"><is><t>stosowana razem z tryptanami może powodować wystąpienie zespołu serotoninowego Działają podobnie jak TLPD , ale nie ma złego panelu postsynaptycznego wskazania o depresja o Bóle neuropatyczne – polineutopatia cukrzycowe, neuropatia toczeniowa o Uogólnione zaburzenia lękowe ZESPÓŁ SEROTONINOWY ! – może być mylony z neuroinfekcją • Głównie zaburzenia świadomości • Drzenia mięśniowe • Wysoka gorączka • Pobudzenie zachowania ZESPÓŁ CHOLINOLITYCZNY - starszy pacjent jest bardziej narażony Wpada w otępienie – nie wie gdzie jest Zaburzenia zachowania</t></is></c><c r="H1019" s="2" t="inlineStr" /><c r="I1019" s="2" t="inlineStr" /><c r="J1019" s="2" t="inlineStr" /><c r="K1019" s="2" t="inlineStr"><is><t>ma istotne działanie cholinolityczne – nie bo właśnie brakiem tych działań różni się od TLPD</t></is></c><c r="L1019" s="2" t="inlineStr"><is><t>można ją bezpiecznie stosować w terapii skojarzonej z inhibitorami MAO – UWAGA ZESPÓŁ SEROTONINOWY</t></is></c><c r="M1019" s="2" t="inlineStr" /><c r="N1019" s="2" t="inlineStr" /><c r="O1019" s="2" t="inlineStr" /><c r="P1019" s="2" t="inlineStr"><is><t>EGZAMIN IWL 20 czerwca 2018</t></is></c><c r="Q1019" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="1020"><c r="A1020" s="2" t="inlineStr"><is><t>LEKI PRZECIWNOWOTWOROWE</t></is></c><c r="B1020" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C1020" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1020" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1020" s="2" t="inlineStr"><is><t>Czy słuszna jest przedstawiona interpretacja działania leku na podstawie nazwy międzynarodowej:</t></is></c><c r="F1020" s="2" t="inlineStr"><is><t>paliwizumab – humanizowane przeciwciało monoklonalne o działaniu p-wirusowym</t></is></c><c r="G1020" s="2" t="inlineStr"><is><t>ekulizumab – humanizowane przeciwciało monoklonalne o wpływie na układ odpornościowy mab – zawsze przeciwciało monoklonalne mid – to jakas dziwna końcówka tum – przeciwnowotworowy li(m) – limfatyczny – wpływ na układ odporonościowy wi(r) – wirusowy jeżeli jest o – mysi jeżeli jest ksi – himeryzkowany jeżeli jest zu – humanizowane jeżeli jest u – całkowicie ludzkie</t></is></c><c r="H1020" s="2" t="inlineStr" /><c r="I1020" s="2" t="inlineStr" /><c r="J1020" s="2" t="inlineStr" /><c r="K1020" s="2" t="inlineStr"><is><t>ofatumumab – mysie przeciwciało monoklonalne o wpływie p-nowotworowym</t></is></c><c r="L1020" s="2" t="inlineStr"><is><t>pomalidomid – mysie przeciwciało monoklonalne o wpływie na układ odpornościowy</t></is></c><c r="M1020" s="2" t="inlineStr" /><c r="N1020" s="2" t="inlineStr" /><c r="O1020" s="2" t="inlineStr" /><c r="P1020" s="2" t="inlineStr"><is><t>EGZAMIN IWL 20 czerwca 2018</t></is></c><c r="Q1020" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="1021"><c r="A1021" s="2" t="inlineStr"><is><t>LEKI PRZECIWNOWOTWOROWE</t></is></c><c r="B1021" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C1021" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1021" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1021" s="2" t="inlineStr"><is><t>Do przeciwciał monoklonalnych anty-TNF należy:</t></is></c><c r="F1021" s="2" t="inlineStr"><is><t>Adalimumab tnf inflyksymab adalimumab golimumab entelizumab</t></is></c><c r="G1021" s="2" t="inlineStr" /><c r="H1021" s="2" t="inlineStr" /><c r="I1021" s="2" t="inlineStr" /><c r="J1021" s="2" t="inlineStr" /><c r="K1021" s="2" t="inlineStr"><is><t>Omalizumab ige</t></is></c><c r="L1021" s="2" t="inlineStr"><is><t>Trastuzumab cd52</t></is></c><c r="M1021" s="2" t="inlineStr"><is><t>Rytuksymab cd20</t></is></c><c r="N1021" s="2" t="inlineStr" /><c r="O1021" s="2" t="inlineStr" /><c r="P1021" s="2" t="inlineStr"><is><t>EGZAMIN IWL 20 czerwca 2018</t></is></c><c r="Q1021" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="1022"><c r="A1022" s="2" t="inlineStr"><is><t>ZABURZENIA RYTMU SERCA</t></is></c><c r="B1022" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C1022" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1022" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1022" s="2" t="inlineStr"><is><t>Werapamil można stosować w:</t></is></c><c r="F1022" s="2" t="inlineStr"><is><t>postaci naczynioskurczowej choroby niedokrwiennej serca – tak jak najbardziej</t></is></c><c r="G1022" s="2" t="inlineStr"><is><t>napadowym częstoskurczu z łącza przedsionkowo-komorowego – werapamil diltiazem i adenozyna bardzo dobrze</t></is></c><c r="H1022" s="2" t="inlineStr" /><c r="I1022" s="2" t="inlineStr" /><c r="J1022" s="2" t="inlineStr" /><c r="K1022" s="2" t="inlineStr"><is><t>bradykardii – nie i nie można łączyc z beta adrenolitykami bo się boimy bradykardii</t></is></c><c r="L1022" s="2" t="inlineStr"><is><t>migotaniu przedsionków u osób z zespołem preekscytacji – słynne NIE</t></is></c><c r="M1022" s="2" t="inlineStr" /><c r="N1022" s="2" t="inlineStr" /><c r="O1022" s="2" t="inlineStr" /><c r="P1022" s="2" t="inlineStr"><is><t>EGZAMIN IWL 20 czerwca 2018</t></is></c><c r="Q1022" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="1023"><c r="A1023" s="2" t="inlineStr"><is><t>NADCIŚNIENIE TĘTNICZE</t></is></c><c r="B1023" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C1023" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1023" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1023" s="2" t="inlineStr"><is><t>Inhibitory neprylizyny:</t></is></c><c r="F1023" s="2" t="inlineStr"><is><t>zmniejszają przebudowę mięśnia sercowego – tak</t></is></c><c r="G1023" s="2" t="inlineStr"><is><t>zwiększają stężenie angiotensyny II – tak dlatego zawsze trzeba dawać z sartanem</t></is></c><c r="H1023" s="2" t="inlineStr"><is><t>są stosowane w przewlekłej niewydolności serca z upośledzoną frakcją wyrzutową – ich główne wskazanie do stosowania</t></is></c><c r="I1023" s="2" t="inlineStr" /><c r="J1023" s="2" t="inlineStr" /><c r="K1023" s="2" t="inlineStr"><is><t>rozkładają peptydy natriuretyczne – nie , ich stężenie wzrasta</t></is></c><c r="L1023" s="2" t="inlineStr" /><c r="M1023" s="2" t="inlineStr" /><c r="N1023" s="2" t="inlineStr" /><c r="O1023" s="2" t="inlineStr" /><c r="P1023" s="2" t="inlineStr"><is><t>EGZAMIN IWL 20 czerwca 2018</t></is></c><c r="Q1023" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="1024"><c r="A1024" s="2" t="inlineStr"><is><t>FARMAKOKINETYKA</t></is></c><c r="B1024" s="2" t="inlineStr"><is><t>Farmakokinetyka</t></is></c><c r="C1024" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1024" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1024" s="2" t="inlineStr"><is><t>Biodostępność leku A po jednorazowym podaniu doustnym wynosi 50%. Tmax wynosi 30 min, a Cmax 2μg/dl. Oznacza to, że:</t></is></c><c r="F1024" s="2" t="inlineStr"><is><t>lek A może podlegać nawet w 50% efektowi pierwszego przejścia przez wątrobę – możliwe bo radykalnie spadla jego biodostępność</t></is></c><c r="G1024" s="2" t="inlineStr" /><c r="H1024" s="2" t="inlineStr" /><c r="I1024" s="2" t="inlineStr" /><c r="J1024" s="2" t="inlineStr" /><c r="K1024" s="2" t="inlineStr"><is><t>dawka wynosiła 4 μg – leków w takiej dawce się nie podaje i wgl nie ma takiego wzoru</t></is></c><c r="L1024" s="2" t="inlineStr"><is><t>lek A słabo wiąże się z białkami krwi – nie wiemy tez nic na ten tamat</t></is></c><c r="M1024" s="2" t="inlineStr"><is><t>okres półtrwania leku A wynosi również około 30 minut – też nic na ten temat nie wiemy</t></is></c><c r="N1024" s="2" t="inlineStr" /><c r="O1024" s="2" t="inlineStr" /><c r="P1024" s="2" t="inlineStr"><is><t>EGZAMIN IWL 20 czerwca 2018</t></is></c><c r="Q1024" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="1025"><c r="A1025" s="2" t="inlineStr"><is><t>LEKI PRZECIWNOWOTWOROWE</t></is></c><c r="B1025" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C1025" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1025" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1025" s="2" t="inlineStr"><is><t>Przez hamowanie działania VEGF (naczyniowego śródbłonkowego czynnika wzrostu) działa:</t></is></c><c r="F1025" s="2" t="inlineStr"><is><t>bewacyzumab</t></is></c><c r="G1025" s="2" t="inlineStr"><is><t>sunitynib</t></is></c><c r="H1025" s="2" t="inlineStr"><is><t>aflibercept VEGF – to bum w okulistyce – zapobieganie zwydonieniu plamki zółtek</t></is></c><c r="I1025" s="2" t="inlineStr" /><c r="J1025" s="2" t="inlineStr" /><c r="K1025" s="2" t="inlineStr"><is><t>bortezomib – inh proteosomu onkologiczny lek</t></is></c><c r="L1025" s="2" t="inlineStr" /><c r="M1025" s="2" t="inlineStr" /><c r="N1025" s="2" t="inlineStr" /><c r="O1025" s="2" t="inlineStr" /><c r="P1025" s="2" t="inlineStr"><is><t>EGZAMIN IWL 20 czerwca 2018</t></is></c><c r="Q1025" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="1026"><c r="A1026" s="2" t="inlineStr"><is><t>FARMAKOKINETYKA</t></is></c><c r="B1026" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C1026" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1026" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1026" s="2" t="inlineStr"><is><t>Podanie doodbytnicze leku:</t></is></c><c r="F1026" s="2" t="inlineStr"><is><t>może łatwo doprowadzić do miejscowego uszkodzenia błony śluzowej odbytnicy – to na pewno</t></is></c><c r="G1026" s="2" t="inlineStr" /><c r="H1026" s="2" t="inlineStr" /><c r="I1026" s="2" t="inlineStr" /><c r="J1026" s="2" t="inlineStr" /><c r="K1026" s="2" t="inlineStr"><is><t>zwiększa efekt pierwszego przejścia – nic z nim nie robi</t></is></c><c r="L1026" s="2" t="inlineStr"><is><t>jest metodą z wyboru u dzieci – to leki w postaci płynnej do 6 roku życia</t></is></c><c r="M1026" s="2" t="inlineStr"><is><t>wymaga podania większej dawki leku w porównaniu do podania doustnego – nie ma takiej reguły</t></is></c><c r="N1026" s="2" t="inlineStr" /><c r="O1026" s="2" t="inlineStr" /><c r="P1026" s="2" t="inlineStr"><is><t>EGZAMIN IWL 20 czerwca 2018</t></is></c><c r="Q1026" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="1027"><c r="A1027" s="2" t="inlineStr"><is><t>LEKI PRZECIWDEPRESYJNE</t></is></c><c r="B1027" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C1027" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1027" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1027" s="2" t="inlineStr"><is><t>Doneuronalny wychwyt monoamin jest hamowany przez:</t></is></c><c r="F1027" s="2" t="inlineStr"><is><t>citalopram</t></is></c><c r="G1027" s="2" t="inlineStr"><is><t>reboksetynę</t></is></c><c r="H1027" s="2" t="inlineStr"><is><t>mirtazapinę</t></is></c><c r="I1027" s="2" t="inlineStr" /><c r="J1027" s="2" t="inlineStr" /><c r="K1027" s="2" t="inlineStr"><is><t>tianeptynę – to jest jedyny lek p-depresyjny który nasila wychwyt monoamin ZWIEKSZA WYCHWYT ZWROTNY – IKR sądzi, że nie działa</t></is></c><c r="L1027" s="2" t="inlineStr" /><c r="M1027" s="2" t="inlineStr" /><c r="N1027" s="2" t="inlineStr" /><c r="O1027" s="2" t="inlineStr" /><c r="P1027" s="2" t="inlineStr"><is><t>EGZAMIN IWL 20 czerwca 2018</t></is></c><c r="Q1027" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="1028"><c r="A1028" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B1028" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C1028" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1028" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1028" s="2" t="inlineStr"><is><t>W leczeniu gruźlicy płucnej lekowrażliwej:</t></is></c><c r="F1028" s="2" t="inlineStr"><is><t>leczenie wyjaławiające powinno trwać co najmniej 4 miesiące</t></is></c><c r="G1028" s="2" t="inlineStr"><is><t>u kobiet ciężarnych podaje się leki według zwykłego schematu z wyłączeniem streptomycyny</t></is></c><c r="H1028" s="2" t="inlineStr" /><c r="I1028" s="2" t="inlineStr" /><c r="J1028" s="2" t="inlineStr" /><c r="K1028" s="2" t="inlineStr"><is><t>w intensywnej fazie leczenia przez 2 miesiące podaje się 2 leki - ryfampicynę i izoniazyd</t></is></c><c r="L1028" s="2" t="inlineStr"><is><t>w fazie kontynuacji każdy pacjent powinien otrzymać etambutol</t></is></c><c r="M1028" s="2" t="inlineStr" /><c r="N1028" s="2" t="inlineStr" /><c r="O1028" s="2" t="inlineStr" /><c r="P1028" s="2" t="inlineStr"><is><t>EGZAMIN IWL 20 czerwca 2018</t></is></c><c r="Q1028" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="1029"><c r="A1029" s="2" t="inlineStr"><is><t>LEKI PRZECIWDEPRESYJNE</t></is></c><c r="B1029" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C1029" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1029" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1029" s="2" t="inlineStr"><is><t>Wskaż prawdziwe połączenie lek – wskazanie:</t></is></c><c r="F1029" s="2" t="inlineStr"><is><t>sulpiryd - schizofrenia</t></is></c><c r="G1029" s="2" t="inlineStr"><is><t>metylofenidat - zespół nadpobudliwości ruchowej z deficytem uwagi (ADHD)</t></is></c><c r="H1029" s="2" t="inlineStr" /><c r="I1029" s="2" t="inlineStr" /><c r="J1029" s="2" t="inlineStr" /><c r="K1029" s="2" t="inlineStr"><is><t>moklobemid - bezsenność</t></is></c><c r="L1029" s="2" t="inlineStr"><is><t>sertindol - depresja</t></is></c><c r="M1029" s="2" t="inlineStr" /><c r="N1029" s="2" t="inlineStr" /><c r="O1029" s="2" t="inlineStr" /><c r="P1029" s="2" t="inlineStr"><is><t>EGZAMIN IWL 20 czerwca 2018</t></is></c><c r="Q1029" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="1030"><c r="A1030" s="2" t="inlineStr"><is><t>NIEOPIOIDOWE LEKI PRZECIWBÓLOWE</t></is></c><c r="B1030" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C1030" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1030" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1030" s="2" t="inlineStr"><is><t>Wskaż prawdziwe stwierdzenie dotyczące metamizolu:</t></is></c><c r="F1030" s="2" t="inlineStr"><is><t>podczas szybkiego wstrzykiwania dożylnego leku może dojść do gwałtownych spadków ciśnienia krwi</t></is></c><c r="G1030" s="2" t="inlineStr"><is><t>może powodować ciężkie uszkodzenia szpiku w mechanizmie nadwrażliwości</t></is></c><c r="H1030" s="2" t="inlineStr"><is><t>zwiększa częstość występowania guzów Wilmsa (nerczak zarodkowy, nephroblastoma)</t></is></c><c r="I1030" s="2" t="inlineStr" /><c r="J1030" s="2" t="inlineStr" /><c r="K1030" s="2" t="inlineStr"><is><t>ma silne działanie przeciwzapalne</t></is></c><c r="L1030" s="2" t="inlineStr" /><c r="M1030" s="2" t="inlineStr" /><c r="N1030" s="2" t="inlineStr" /><c r="O1030" s="2" t="inlineStr" /><c r="P1030" s="2" t="inlineStr"><is><t>EGZAMIN IWL 20 czerwca 2018</t></is></c><c r="Q1030" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="1031"><c r="A1031" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B1031" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C1031" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1031" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1031" s="2" t="inlineStr"><is><t>Które połączenie lekowe jest bezwzględnie konieczne w wymienionejsytuacji klinicznej:</t></is></c><c r="F1031" s="2" t="inlineStr"><is><t>sartan + sakubitryl w skurczowej niewydolnościserca</t></is></c><c r="G1031" s="2" t="inlineStr"><is><t>kwas acetylosalicylowy + antagonista receptorów P2Y12 poangioplastyce wieńcowej z implantacją stentu</t></is></c><c r="H1031" s="2" t="inlineStr" /><c r="I1031" s="2" t="inlineStr" /><c r="J1031" s="2" t="inlineStr" /><c r="K1031" s="2" t="inlineStr"><is><t>heparyna drobnocząsteczkowa + ksaban w początkowym okresie leczenia żylnej choroby zakrzepowo-zatorowej</t></is></c><c r="L1031" s="2" t="inlineStr"><is><t>adrenalina + atropina w resuscytacji krążeniowo-oddechowej w NZK w przebiegu asystolii</t></is></c><c r="M1031" s="2" t="inlineStr" /><c r="N1031" s="2" t="inlineStr" /><c r="O1031" s="2" t="inlineStr" /><c r="P1031" s="2" t="inlineStr"><is><t>EGZAMIN IWL 20 czerwca 2018</t></is></c><c r="Q1031" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="1032"><c r="A1032" s="2" t="inlineStr"><is><t>CUKRZYCA</t></is></c><c r="B1032" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C1032" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1032" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1032" s="2" t="inlineStr"><is><t>Glukagon:</t></is></c><c r="F1032" s="2" t="inlineStr"><is><t>stosowany jest w leczeniu ciężkiej hipoglikemii gdy nie można podać dożylnie glukozy</t></is></c><c r="G1032" s="2" t="inlineStr"><is><t>jest podawany parenteralnie</t></is></c><c r="H1032" s="2" t="inlineStr"><is><t>ma zastosowanie w zatruciach lekami ß-adrenolitycznymi</t></is></c><c r="I1032" s="2" t="inlineStr"><is><t>jest nieskuteczny w przypadku hipoglikemii wywołanej spożyciem alkoholu</t></is></c><c r="J1032" s="2" t="inlineStr" /><c r="K1032" s="2" t="inlineStr" /><c r="L1032" s="2" t="inlineStr" /><c r="M1032" s="2" t="inlineStr" /><c r="N1032" s="2" t="inlineStr" /><c r="O1032" s="2" t="inlineStr" /><c r="P1032" s="2" t="inlineStr"><is><t>EGZAMIN IWL 20 czerwca 2018</t></is></c><c r="Q1032" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="1033"><c r="A1033" s="2" t="inlineStr"><is><t>UKŁAD ODDECHOWY</t></is></c><c r="B1033" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C1033" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1033" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1033" s="2" t="inlineStr"><is><t>W celu przerwania ataku duszności uzasadnione jest podanie wziewnie:</t></is></c><c r="F1033" s="2" t="inlineStr"><is><t>bromku ipratriopium</t></is></c><c r="G1033" s="2" t="inlineStr"><is><t>salbutamolu</t></is></c><c r="H1033" s="2" t="inlineStr" /><c r="I1033" s="2" t="inlineStr" /><c r="J1033" s="2" t="inlineStr" /><c r="K1033" s="2" t="inlineStr"><is><t>roflumilastu</t></is></c><c r="L1033" s="2" t="inlineStr"><is><t>flutykazonu</t></is></c><c r="M1033" s="2" t="inlineStr" /><c r="N1033" s="2" t="inlineStr" /><c r="O1033" s="2" t="inlineStr" /><c r="P1033" s="2" t="inlineStr"><is><t>EGZAMIN IWL 20 czerwca 2018</t></is></c><c r="Q1033" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="1034"><c r="A1034" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B1034" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C1034" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1034" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1034" s="2" t="inlineStr"><is><t>Wskaż prawdziwe zdanie:</t></is></c><c r="F1034" s="2" t="inlineStr"><is><t>w chromaniu przestankowym znaczenie kliniczne ma leczenie przeciwpłytkowe i hipolipemizujące</t></is></c><c r="G1034" s="2" t="inlineStr"><is><t>zaleca się podanie inhibitora P2Y12 przed przezskórną interwencją wieńcową u osoby z ostrym zespołem wieńcowym, a następnie kontynuację tego leczenia przez co najmniej 12 miesięcy</t></is></c><c r="H1034" s="2" t="inlineStr"><is><t>po rozpoczęciu leczenia inhibitorami konwertazy angiotensyny należy się spodziewać niewielkiego wzrostu stężenia kreatyniny we krwi</t></is></c><c r="I1034" s="2" t="inlineStr" /><c r="J1034" s="2" t="inlineStr" /><c r="K1034" s="2" t="inlineStr"><is><t>niedihydropirydynowi antagoniści wapnia są wskazani w leczeniu pacjentów z niewydolnością serca z obniżoną frakcją wyrzutową</t></is></c><c r="L1034" s="2" t="inlineStr" /><c r="M1034" s="2" t="inlineStr" /><c r="N1034" s="2" t="inlineStr" /><c r="O1034" s="2" t="inlineStr" /><c r="P1034" s="2" t="inlineStr"><is><t>EGZAMIN IWL 20 czerwca 2018</t></is></c><c r="Q1034" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="1035"><c r="A1035" s="2" t="inlineStr"><is><t>ZABURZENIA RYTMU SERCA</t></is></c><c r="B1035" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C1035" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1035" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1035" s="2" t="inlineStr"><is><t>U osoby z pierwotnym wydłużeniem QTc bezpieczne jestzastosowanie:</t></is></c><c r="F1035" s="2" t="inlineStr"><is><t>propranololu</t></is></c><c r="G1035" s="2" t="inlineStr" /><c r="H1035" s="2" t="inlineStr" /><c r="I1035" s="2" t="inlineStr" /><c r="J1035" s="2" t="inlineStr" /><c r="K1035" s="2" t="inlineStr"><is><t>digoksyny</t></is></c><c r="L1035" s="2" t="inlineStr"><is><t>sotalolu</t></is></c><c r="M1035" s="2" t="inlineStr"><is><t>amiodaronu</t></is></c><c r="N1035" s="2" t="inlineStr" /><c r="O1035" s="2" t="inlineStr" /><c r="P1035" s="2" t="inlineStr"><is><t>EGZAMIN IWL 20 czerwca 2018</t></is></c><c r="Q1035" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="1036"><c r="A1036" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B1036" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C1036" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1036" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1036" s="2" t="inlineStr"><is><t>Lidokaina:</t></is></c><c r="F1036" s="2" t="inlineStr"><is><t>jest skuteczna w znieczuleniu nasiękowym</t></is></c><c r="G1036" s="2" t="inlineStr"><is><t>jest metabolizowana w wątrobie</t></is></c><c r="H1036" s="2" t="inlineStr"><is><t>może powodować drgawki</t></is></c><c r="I1036" s="2" t="inlineStr" /><c r="J1036" s="2" t="inlineStr" /><c r="K1036" s="2" t="inlineStr"><is><t>silnie blokuje kanały potasowe</t></is></c><c r="L1036" s="2" t="inlineStr" /><c r="M1036" s="2" t="inlineStr" /><c r="N1036" s="2" t="inlineStr" /><c r="O1036" s="2" t="inlineStr" /><c r="P1036" s="2" t="inlineStr"><is><t>EGZAMIN IWL 20 czerwca 2018</t></is></c><c r="Q1036" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="1037"><c r="A1037" s="2" t="inlineStr"><is><t>NADCIŚNIENIE TĘTNICZE</t></is></c><c r="B1037" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C1037" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1037" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1037" s="2" t="inlineStr"><is><t>Koangiokardianem, czyli lekiem działającym bezpośrednio na serce i na naczynia jest:</t></is></c><c r="F1037" s="2" t="inlineStr"><is><t>lewosymendan</t></is></c><c r="G1037" s="2" t="inlineStr" /><c r="H1037" s="2" t="inlineStr" /><c r="I1037" s="2" t="inlineStr" /><c r="J1037" s="2" t="inlineStr" /><c r="K1037" s="2" t="inlineStr"><is><t>midodryna</t></is></c><c r="L1037" s="2" t="inlineStr"><is><t>epoprostenol</t></is></c><c r="M1037" s="2" t="inlineStr"><is><t>riocyguat</t></is></c><c r="N1037" s="2" t="inlineStr" /><c r="O1037" s="2" t="inlineStr" /><c r="P1037" s="2" t="inlineStr"><is><t>EGZAMIN IWL 20 czerwca 2018</t></is></c><c r="Q1037" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="1038"><c r="A1038" s="2" t="inlineStr"><is><t>OSTEOPOROZA</t></is></c><c r="B1038" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C1038" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1038" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1038" s="2" t="inlineStr"><is><t>Wskaż prawdziwe zdanie dotyczące bisfosfonianów:</t></is></c><c r="F1038" s="2" t="inlineStr"><is><t>są lekami pierwszego rzutu w profilaktyce i leczeniu osteoporozy pomenopauzalnej u kobiet</t></is></c><c r="G1038" s="2" t="inlineStr"><is><t>mogą być stosowane w zapobieganiu i leczeniu osteoporozy posteroidowej</t></is></c><c r="H1038" s="2" t="inlineStr"><is><t>u osób z przerzutami nowotworowymi do układu kostnego łagodzą bóle kostne</t></is></c><c r="I1038" s="2" t="inlineStr"><is><t>przeciwwskazaniem do ich podawania jest ciężka niewydolność nerek (klirens kreatyniny &lt; 35–30 ml/min)</t></is></c><c r="J1038" s="2" t="inlineStr" /><c r="K1038" s="2" t="inlineStr" /><c r="L1038" s="2" t="inlineStr" /><c r="M1038" s="2" t="inlineStr" /><c r="N1038" s="2" t="inlineStr" /><c r="O1038" s="2" t="inlineStr" /><c r="P1038" s="2" t="inlineStr"><is><t>EGZAMIN IWL 20 czerwca 2018</t></is></c><c r="Q1038" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="1039"><c r="A1039" s="2" t="inlineStr"><is><t>LEKI HIPOLIPEMIZUJĄCE</t></is></c><c r="B1039" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C1039" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1039" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1039" s="2" t="inlineStr"><is><t>Zmniejszenie hipertriglicerydemii można osiągnąć stosując:</t></is></c><c r="F1039" s="2" t="inlineStr"><is><t>atorwastatynę</t></is></c><c r="G1039" s="2" t="inlineStr"><is><t>fenofibrat</t></is></c><c r="H1039" s="2" t="inlineStr"><is><t>PUFA – wielonienasycone kwasy tłuszczowe</t></is></c><c r="I1039" s="2" t="inlineStr" /><c r="J1039" s="2" t="inlineStr" /><c r="K1039" s="2" t="inlineStr"><is><t>kolesewelam</t></is></c><c r="L1039" s="2" t="inlineStr" /><c r="M1039" s="2" t="inlineStr" /><c r="N1039" s="2" t="inlineStr" /><c r="O1039" s="2" t="inlineStr" /><c r="P1039" s="2" t="inlineStr"><is><t>EGZAMIN IWL 20 czerwca 2018</t></is></c><c r="Q1039" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="1040"><c r="A1040" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B1040" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C1040" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1040" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1040" s="2" t="inlineStr"><is><t>Lekiem wydłużającym dystans chromania przestankowego jest:</t></is></c><c r="F1040" s="2" t="inlineStr"><is><t>naftydrofuryl</t></is></c><c r="G1040" s="2" t="inlineStr"><is><t>cilostazol</t></is></c><c r="H1040" s="2" t="inlineStr" /><c r="I1040" s="2" t="inlineStr" /><c r="J1040" s="2" t="inlineStr" /><c r="K1040" s="2" t="inlineStr"><is><t>pentoksyfilina</t></is></c><c r="L1040" s="2" t="inlineStr"><is><t>diosmina mikronizowana</t></is></c><c r="M1040" s="2" t="inlineStr" /><c r="N1040" s="2" t="inlineStr" /><c r="O1040" s="2" t="inlineStr" /><c r="P1040" s="2" t="inlineStr"><is><t>EGZAMIN IWL 20 czerwca 2018</t></is></c><c r="Q1040" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="1041"><c r="A1041" s="2" t="inlineStr"><is><t>LEKI HIPOLIPEMIZUJĄCE</t></is></c><c r="B1041" s="2" t="inlineStr"><is><t>Monitorowanie</t></is></c><c r="C1041" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1041" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1041" s="2" t="inlineStr"><is><t>W prawidłowo prowadzonym leczeniu statynami należy:</t></is></c><c r="F1041" s="2" t="inlineStr"><is><t>oznaczyć aktywność ALAT i CK w surowicy przed rozpoczęciem leczenia</t></is></c><c r="G1041" s="2" t="inlineStr"><is><t>odstawić statynę jeśli aktywność ALAT przekroczy w surowicy 3- krotnie górną granicę wartości prawidłowych</t></is></c><c r="H1041" s="2" t="inlineStr" /><c r="I1041" s="2" t="inlineStr" /><c r="J1041" s="2" t="inlineStr" /><c r="K1041" s="2" t="inlineStr"><is><t>ocenić skuteczność leczenia hipolipemizującego po 2 tygodniach odjego rozpoczęcia</t></is></c><c r="L1041" s="2" t="inlineStr"><is><t>monitorować aktywność CK u każdego pacjenta</t></is></c><c r="M1041" s="2" t="inlineStr" /><c r="N1041" s="2" t="inlineStr" /><c r="O1041" s="2" t="inlineStr" /><c r="P1041" s="2" t="inlineStr"><is><t>EGZAMIN IWL 20 czerwca 2018</t></is></c><c r="Q1041" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="1042"><c r="A1042" s="2" t="inlineStr"><is><t>FARMAKOKINETYKA</t></is></c><c r="B1042" s="2" t="inlineStr"><is><t>Interakcje</t></is></c><c r="C1042" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1042" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1042" s="2" t="inlineStr"><is><t>Interakcją farmakokinetyczną jest:</t></is></c><c r="F1042" s="2" t="inlineStr"><is><t>hamowanie wchłaniania z przewodu pokarmowego leków podawanych jednocześnie</t></is></c><c r="G1042" s="2" t="inlineStr"><is><t>zwiększenie metabolizmu leków podawanych jednocześnie</t></is></c><c r="H1042" s="2" t="inlineStr" /><c r="I1042" s="2" t="inlineStr" /><c r="J1042" s="2" t="inlineStr" /><c r="K1042" s="2" t="inlineStr"><is><t>wytrącenie się osadu po zmieszaniu dwóch leków w jednym roztworzedo wstrzyknięcia</t></is></c><c r="L1042" s="2" t="inlineStr"><is><t>nasilenie sedacji po skojarzeniu opioidów z etanolem</t></is></c><c r="M1042" s="2" t="inlineStr" /><c r="N1042" s="2" t="inlineStr" /><c r="O1042" s="2" t="inlineStr" /><c r="P1042" s="2" t="inlineStr"><is><t>EGZAMIN IWL 20 czerwca 2018</t></is></c><c r="Q1042" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="1043"><c r="A1043" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B1043" s="2" t="inlineStr"><is><t>Farmakokinetyka</t></is></c><c r="C1043" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1043" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1043" s="2" t="inlineStr"><is><t>Właściwości farmakodynamiczne i parametry farmakokinetyczne leków mają wpływna podejmowanie decyzji klinicznych. Czy słuszne jest wobec tego:</t></is></c><c r="F1043" s="2" t="inlineStr"><is><t>wielokrotne powtórzenie dawki naloksonu (t0,5 = 63 min ± 12 min) po przedawkowaniu metadonu? – antidota często dzialaja krócej niż substancja zatruwająca Własnoręczny podpis Numer indeksu</t></is></c><c r="G1043" s="2" t="inlineStr" /><c r="H1043" s="2" t="inlineStr" /><c r="I1043" s="2" t="inlineStr" /><c r="J1043" s="2" t="inlineStr" /><c r="K1043" s="2" t="inlineStr"><is><t>przetoczenie koncentratu płytek krwi 13 h po podaniu tikagreloru (tikagrelor ze swoim czynnym metabolitem mają łączny czas półtrwania eliminacji (t0,5) = 12h)?</t></is></c><c r="L1043" s="2" t="inlineStr"><is><t>odstawienie suplementacji potasu w hiperaldosteronizmie pierwotnym po 16-17 h po włączeniu spironolaktonu (Cmax kanrenonu = 16,5 h po podaniu spironolaktonu)?</t></is></c><c r="M1043" s="2" t="inlineStr"><is><t>przeprowadzenie operacji neurochirurgicznej po 36 h po odstawieniu klopidogrelu (t0,5 klopidogrelu = 6 h, jego aktywne metabolity mają pomijalnie krótki czas t0,5)? – nie możńa bo od NIEODWRACALNIE w przeciwieństwie do TIKAGRELORU</t></is></c><c r="N1043" s="2" t="inlineStr" /><c r="O1043" s="2" t="inlineStr" /><c r="P1043" s="2" t="inlineStr"><is><t>EGZAMIN IWL 20 czerwca 2018</t></is></c><c r="Q1043" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="1044"><c r="A1044" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B1044" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C1044" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1044" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1044" s="2" t="inlineStr"><is><t>Wskaż prawidłowe zestawienia lek - spektrum działania:</t></is></c><c r="F1044" s="2" t="inlineStr"><is><t>lewofloksacyna – Pseudomonas aeruginosa, Streptococcus pneumoniae</t></is></c><c r="G1044" s="2" t="inlineStr"><is><t>penicylina G – Fusobacterium spp., Streptococcus pyogenes</t></is></c><c r="H1044" s="2" t="inlineStr" /><c r="I1044" s="2" t="inlineStr" /><c r="J1044" s="2" t="inlineStr" /><c r="K1044" s="2" t="inlineStr"><is><t>amikacyna – Clostridium spp., Helicobacter pylori</t></is></c><c r="L1044" s="2" t="inlineStr"><is><t>teikoplanina – Escherichia coli, Bacteroides fragilis</t></is></c><c r="M1044" s="2" t="inlineStr" /><c r="N1044" s="2" t="inlineStr" /><c r="O1044" s="2" t="inlineStr" /><c r="P1044" s="2" t="inlineStr"><is><t>EGZAMIN IWL 21 czerwca 2019</t></is></c><c r="Q1044" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="1045"><c r="A1045" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B1045" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C1045" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1045" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1045" s="2" t="inlineStr"><is><t>Linezolid może być skuteczny w zakażeniach szczepami:</t></is></c><c r="F1045" s="2" t="inlineStr"><is><t>MRSA (methicyllin-resistant Staphylococcus aureus)</t></is></c><c r="G1045" s="2" t="inlineStr"><is><t>MSSA (methicillin-sensitive Staphylococcus aureus)</t></is></c><c r="H1045" s="2" t="inlineStr"><is><t>VRE (Vancomycin-Resistant Enterococcus)</t></is></c><c r="I1045" s="2" t="inlineStr" /><c r="J1045" s="2" t="inlineStr" /><c r="K1045" s="2" t="inlineStr"><is><t>CPE (Carbapenemase-producing Enterobacteriaceae)</t></is></c><c r="L1045" s="2" t="inlineStr" /><c r="M1045" s="2" t="inlineStr" /><c r="N1045" s="2" t="inlineStr" /><c r="O1045" s="2" t="inlineStr" /><c r="P1045" s="2" t="inlineStr"><is><t>EGZAMIN IWL 21 czerwca 2019</t></is></c><c r="Q1045" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="1046"><c r="A1046" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B1046" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C1046" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1046" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1046" s="2" t="inlineStr"><is><t>Wskaż prawdziwe połączenie lek – mechanizm działania:</t></is></c><c r="F1046" s="2" t="inlineStr"><is><t>fosfomycyna- blokowanie syntezy ściany komórkowej bakterii</t></is></c><c r="G1046" s="2" t="inlineStr"><is><t>moksyfloksacyna - hamowanie tworzenia kompleksów topoizomerazy typu II i IV z kwasem DNA</t></is></c><c r="H1046" s="2" t="inlineStr" /><c r="I1046" s="2" t="inlineStr" /><c r="J1046" s="2" t="inlineStr" /><c r="K1046" s="2" t="inlineStr"><is><t>kolistyna - hamowanie biosyntezy białka w komórkach bakterii poprzez wiązanie się z podjednostką 30 S rybosomu</t></is></c><c r="L1046" s="2" t="inlineStr"><is><t>klindamycyna - zmniejszanie aktywności dinukleotydu nikotynoamidoadeninowego (NAD) w komórce bakterii</t></is></c><c r="M1046" s="2" t="inlineStr" /><c r="N1046" s="2" t="inlineStr" /><c r="O1046" s="2" t="inlineStr" /><c r="P1046" s="2" t="inlineStr"><is><t>EGZAMIN IWL 21 czerwca 2019</t></is></c><c r="Q1046" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="1047"><c r="A1047" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B1047" s="2" t="inlineStr"><is><t>Dawkowanie</t></is></c><c r="C1047" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1047" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1047" s="2" t="inlineStr"><is><t>U osoby z istotnie upośledzoną czynnością nerek (eGFR &lt;30ml/min wg wzoru Cockcrofta- Gaulta) i wskazaniem do leczenia zakażenia o etiologii bakteryjnej, należy zmodyfikować dawkowanie:</t></is></c><c r="F1047" s="2" t="inlineStr"><is><t>amoksycyliny</t></is></c><c r="G1047" s="2" t="inlineStr"><is><t>cefepimu</t></is></c><c r="H1047" s="2" t="inlineStr" /><c r="I1047" s="2" t="inlineStr" /><c r="J1047" s="2" t="inlineStr" /><c r="K1047" s="2" t="inlineStr"><is><t>cefoperazonu</t></is></c><c r="L1047" s="2" t="inlineStr"><is><t>ceftriaksonu</t></is></c><c r="M1047" s="2" t="inlineStr"><is><t>U kobiety w ciąży z anginą paciorkowcową i nadwrażliwością na antybiotyki beta￾laktamowe, można zastosować:</t></is></c><c r="N1047" s="2" t="inlineStr" /><c r="O1047" s="2" t="inlineStr" /><c r="P1047" s="2" t="inlineStr"><is><t>EGZAMIN IWL 21 czerwca 2019</t></is></c><c r="Q1047" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="1048"><c r="A1048" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B1048" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C1048" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1048" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1048" s="2" t="inlineStr"><is><t>Zaznacz twierdzenie prawdziwe:</t></is></c><c r="F1048" s="2" t="inlineStr"><is><t>w leczeniu pacjentki z niepowikłanym zakażeniem układu moczowego można zastosować empirycznie fosfomycynę</t></is></c><c r="G1048" s="2" t="inlineStr"><is><t>mupirocyna jest stosowana przed operacjami chirurgicznymi w eradykacji gronkowców opornych na metycylinę kolonizujących jamę nosową</t></is></c><c r="H1048" s="2" t="inlineStr" /><c r="I1048" s="2" t="inlineStr" /><c r="J1048" s="2" t="inlineStr" /><c r="K1048" s="2" t="inlineStr"><is><t>cyprofloksacyna jest skutecznym lekiem w zakażeniach dolnych dróg oddechowych wywołanych przez Streptococcus pneumoniae</t></is></c><c r="L1048" s="2" t="inlineStr"><is><t>kolistymetat sodowy jest nieskuteczny w zakażeniach o etiologii Pseudomonas aeruginosa</t></is></c><c r="M1048" s="2" t="inlineStr" /><c r="N1048" s="2" t="inlineStr" /><c r="O1048" s="2" t="inlineStr" /><c r="P1048" s="2" t="inlineStr"><is><t>EGZAMIN IWL 21 czerwca 2019</t></is></c><c r="Q1048" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="1049"><c r="A1049" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B1049" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C1049" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1049" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1049" s="2" t="inlineStr"><is><t>Co można zastosować u pacjenta z boreliozą (rumień skórny wędrujący)?</t></is></c><c r="F1049" s="2" t="inlineStr"><is><t>amoksycylinę</t></is></c><c r="G1049" s="2" t="inlineStr"><is><t>aksetyl cefuroksymu</t></is></c><c r="H1049" s="2" t="inlineStr"><is><t>doksycyklinę</t></is></c><c r="I1049" s="2" t="inlineStr" /><c r="J1049" s="2" t="inlineStr" /><c r="K1049" s="2" t="inlineStr"><is><t>kotrymoksazol</t></is></c><c r="L1049" s="2" t="inlineStr" /><c r="M1049" s="2" t="inlineStr" /><c r="N1049" s="2" t="inlineStr" /><c r="O1049" s="2" t="inlineStr" /><c r="P1049" s="2" t="inlineStr"><is><t>EGZAMIN IWL 21 czerwca 2019</t></is></c><c r="Q1049" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="1050"><c r="A1050" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B1050" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C1050" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1050" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1050" s="2" t="inlineStr"><is><t>Aktywność przeciwbakteryjną względem Haemophilus influenzae wykazuje:</t></is></c><c r="F1050" s="2" t="inlineStr"><is><t>klarytromycyna</t></is></c><c r="G1050" s="2" t="inlineStr"><is><t>ceftriakson</t></is></c><c r="H1050" s="2" t="inlineStr"><is><t>moksyfloksacyna</t></is></c><c r="I1050" s="2" t="inlineStr"><is><t>amoksycylina z kwasem klawulanowym</t></is></c><c r="J1050" s="2" t="inlineStr" /><c r="K1050" s="2" t="inlineStr" /><c r="L1050" s="2" t="inlineStr" /><c r="M1050" s="2" t="inlineStr" /><c r="N1050" s="2" t="inlineStr" /><c r="O1050" s="2" t="inlineStr" /><c r="P1050" s="2" t="inlineStr"><is><t>EGZAMIN IWL 21 czerwca 2019</t></is></c><c r="Q1050" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="1051"><c r="A1051" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B1051" s="2" t="inlineStr"><is><t>Interakcje</t></is></c><c r="C1051" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1051" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1051" s="2" t="inlineStr"><is><t>Chemioprofilaktyka zakażenia zgodna z aktualną wiedzą medyczną to:</t></is></c><c r="F1051" s="2" t="inlineStr"><is><t>podanie ceftriaksonu lub cyprofloksacyny osobie z bliskiego kontaktu z chorym na inwazyjną chorobę meningokokową</t></is></c><c r="G1051" s="2" t="inlineStr" /><c r="H1051" s="2" t="inlineStr" /><c r="I1051" s="2" t="inlineStr" /><c r="J1051" s="2" t="inlineStr" /><c r="K1051" s="2" t="inlineStr"><is><t>3-dniowe podawanie cefazoliny po planowej operacji w polu czystym￾skażonym</t></is></c><c r="L1051" s="2" t="inlineStr"><is><t>dołączenie flukonazolu do szerokospektralnej antybiotykoterapii przeciwbakteryjnej po tygodniu jej stosowania</t></is></c><c r="M1051" s="2" t="inlineStr"><is><t>codzienne podawanie furazydyny w jednej dawce przez 6 miesięcy kobiecie w wieku pomenopauzalnym z bezobjawową bakteriurią</t></is></c><c r="N1051" s="2" t="inlineStr" /><c r="O1051" s="2" t="inlineStr" /><c r="P1051" s="2" t="inlineStr"><is><t>EGZAMIN IWL 21 czerwca 2019</t></is></c><c r="Q1051" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="1052"><c r="A1052" s="2" t="inlineStr"><is><t>LEKI PRZECIWWIRUSOWE</t></is></c><c r="B1052" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C1052" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1052" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1052" s="2" t="inlineStr"><is><t>Oseltamiwir:</t></is></c><c r="F1052" s="2" t="inlineStr"><is><t>jest inhibitorem neuraminidazy wirusowej</t></is></c><c r="G1052" s="2" t="inlineStr"><is><t>występuje w postaci doustnej</t></is></c><c r="H1052" s="2" t="inlineStr" /><c r="I1052" s="2" t="inlineStr" /><c r="J1052" s="2" t="inlineStr" /><c r="K1052" s="2" t="inlineStr"><is><t>nie indukuje oporności wirusów grypy A</t></is></c><c r="L1052" s="2" t="inlineStr"><is><t>nie jest skuteczny w profilaktyce grypy po ekspozycji</t></is></c><c r="M1052" s="2" t="inlineStr" /><c r="N1052" s="2" t="inlineStr" /><c r="O1052" s="2" t="inlineStr" /><c r="P1052" s="2" t="inlineStr"><is><t>EGZAMIN IWL 21 czerwca 2019</t></is></c><c r="Q1052" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="1053"><c r="A1053" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B1053" s="2" t="inlineStr"><is><t>Interakcje</t></is></c><c r="C1053" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1053" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1053" s="2" t="inlineStr"><is><t>Jakie leki mają uzasadnienie w opisanym przypadku: 18-letnia aktywna seksualnie kobieta z niepowikłanym zakażeniem układu moczowego objawiającym się częstomoczem, parciami naglącymi i dolegliwościami bólowymi cewki moczowej w czasie mikcji, planująca wyjazd na wakacje z opalaniem na Teneryfie za 2 dni?</t></is></c><c r="F1053" s="2" t="inlineStr"><is><t>cefadroksyl</t></is></c><c r="G1053" s="2" t="inlineStr" /><c r="H1053" s="2" t="inlineStr" /><c r="I1053" s="2" t="inlineStr" /><c r="J1053" s="2" t="inlineStr" /><c r="K1053" s="2" t="inlineStr"><is><t>ko-trymoksazol</t></is></c><c r="L1053" s="2" t="inlineStr"><is><t>amoksycylina</t></is></c><c r="M1053" s="2" t="inlineStr"><is><t>cyprofloksacyna</t></is></c><c r="N1053" s="2" t="inlineStr" /><c r="O1053" s="2" t="inlineStr" /><c r="P1053" s="2" t="inlineStr"><is><t>EGZAMIN IWL 21 czerwca 2019</t></is></c><c r="Q1053" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="1054"><c r="A1054" s="2" t="inlineStr"><is><t>LEKI PRZECIWGRZYBICZE</t></is></c><c r="B1054" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C1054" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1054" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1054" s="2" t="inlineStr"><is><t>W leczeniu zakażeń grzybiczych:</t></is></c><c r="F1054" s="2" t="inlineStr"><is><t>w przypadku niepowikłanej kandydozy sromu i pochwy może być skuteczne jednorazowe doustne podanie flukonazolu</t></is></c><c r="G1054" s="2" t="inlineStr"><is><t>paznokci można rozważyć zastosowanie cyklopiroksolaminy w lakierze</t></is></c><c r="H1054" s="2" t="inlineStr" /><c r="I1054" s="2" t="inlineStr" /><c r="J1054" s="2" t="inlineStr" /><c r="K1054" s="2" t="inlineStr"><is><t>skóry gładkiej leki stosuje się wyłącznie miejscowo</t></is></c><c r="L1054" s="2" t="inlineStr"><is><t>ośrodkowego układu nerwowego o etiologii Aspergillus spp. można zastosować kaspofunginę</t></is></c><c r="M1054" s="2" t="inlineStr" /><c r="N1054" s="2" t="inlineStr" /><c r="O1054" s="2" t="inlineStr" /><c r="P1054" s="2" t="inlineStr"><is><t>EGZAMIN IWL 21 czerwca 2019</t></is></c><c r="Q1054" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="1055"><c r="A1055" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B1055" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C1055" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1055" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1055" s="2" t="inlineStr"><is><t>Azytromycyna:</t></is></c><c r="F1055" s="2" t="inlineStr"><is><t>po podaniu doustnym nie osiąga stężenia terapeutycznego w OUN</t></is></c><c r="G1055" s="2" t="inlineStr"><is><t>ma długi okres połowicznego półtrwania (powyżej 24 godzin)</t></is></c><c r="H1055" s="2" t="inlineStr" /><c r="I1055" s="2" t="inlineStr" /><c r="J1055" s="2" t="inlineStr" /><c r="K1055" s="2" t="inlineStr"><is><t>ma istotny wpływ na enzymy układu cytochromu P-450</t></is></c><c r="L1055" s="2" t="inlineStr"><is><t>jest wydalana wyłącznie przez nerki</t></is></c><c r="M1055" s="2" t="inlineStr" /><c r="N1055" s="2" t="inlineStr" /><c r="O1055" s="2" t="inlineStr" /><c r="P1055" s="2" t="inlineStr"><is><t>EGZAMIN IWL 21 czerwca 2019</t></is></c><c r="Q1055" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="1056"><c r="A1056" s="2" t="inlineStr"><is><t>LEKI PRZECIWWIRUSOWE</t></is></c><c r="B1056" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C1056" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1056" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1056" s="2" t="inlineStr"><is><t>W leczeniu przewlekłego wirusowego zapalenia wątroby typu B zaleca się:</t></is></c><c r="F1056" s="2" t="inlineStr"><is><t>adefowir</t></is></c><c r="G1056" s="2" t="inlineStr"><is><t>lamiwudynę</t></is></c><c r="H1056" s="2" t="inlineStr" /><c r="I1056" s="2" t="inlineStr" /><c r="J1056" s="2" t="inlineStr" /><c r="K1056" s="2" t="inlineStr"><is><t>acyklowir</t></is></c><c r="L1056" s="2" t="inlineStr"><is><t>foskarnet</t></is></c><c r="M1056" s="2" t="inlineStr" /><c r="N1056" s="2" t="inlineStr" /><c r="O1056" s="2" t="inlineStr" /><c r="P1056" s="2" t="inlineStr"><is><t>EGZAMIN IWL 21 czerwca 2019</t></is></c><c r="Q1056" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="1057"><c r="A1057" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B1057" s="2" t="inlineStr"><is><t>Sposób podania</t></is></c><c r="C1057" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1057" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1057" s="2" t="inlineStr"><is><t>W pierwszym leczeniu nowego przypadku gruźlicy płuc:</t></is></c><c r="F1057" s="2" t="inlineStr"><is><t>streptomycyna nie jest lekiem pierwszego wyboru</t></is></c><c r="G1057" s="2" t="inlineStr" /><c r="H1057" s="2" t="inlineStr" /><c r="I1057" s="2" t="inlineStr" /><c r="J1057" s="2" t="inlineStr" /><c r="K1057" s="2" t="inlineStr"><is><t>etambutol jest włączany do terapii w fazie kontynuacji leczenia, która ma na celu wyjałowienie organizmu z Mycobacterium tuberculosis</t></is></c><c r="L1057" s="2" t="inlineStr"><is><t>czas standardowego leczenia nie może być krótszy niż 9 miesięcy</t></is></c><c r="M1057" s="2" t="inlineStr"><is><t>izoniazyd musi być podawany dożylnie</t></is></c><c r="N1057" s="2" t="inlineStr" /><c r="O1057" s="2" t="inlineStr" /><c r="P1057" s="2" t="inlineStr"><is><t>EGZAMIN IWL 21 czerwca 2019</t></is></c><c r="Q1057" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="1058"><c r="A1058" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B1058" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C1058" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1058" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1058" s="2" t="inlineStr"><is><t>Krytyczna potrzeba opracowania nowych leków przeciwbakteryjnych wynika z selekcji:</t></is></c><c r="F1058" s="2" t="inlineStr"><is><t>Pseudomonas aeruginosa opornych na karbapenemy (CPPA)</t></is></c><c r="G1058" s="2" t="inlineStr"><is><t>Klebsiella pneumoniae opornych na karbapenemy (CPE)</t></is></c><c r="H1058" s="2" t="inlineStr" /><c r="I1058" s="2" t="inlineStr" /><c r="J1058" s="2" t="inlineStr" /><c r="K1058" s="2" t="inlineStr"><is><t>Staphylococcus aureus opornych na metycylinę (MRSA)</t></is></c><c r="L1058" s="2" t="inlineStr"><is><t>Streptococcus pneumoniae opornych na tetracykliny (TRSP)</t></is></c><c r="M1058" s="2" t="inlineStr" /><c r="N1058" s="2" t="inlineStr" /><c r="O1058" s="2" t="inlineStr" /><c r="P1058" s="2" t="inlineStr"><is><t>EGZAMIN IWL 21 czerwca 2019</t></is></c><c r="Q1058" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="1059"><c r="A1059" s="2" t="inlineStr"><is><t>CUKRZYCA</t></is></c><c r="B1059" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C1059" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1059" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1059" s="2" t="inlineStr"><is><t>Metformina:</t></is></c><c r="F1059" s="2" t="inlineStr"><is><t>zmniejsza ryzyko powikłań makroangiopatycznych cukrzycy • nei powoduje hiperglikemia • zapobiega przejściu stanu przedcukrzycowego w cukrzyce wiec i w zlej glukozie na czczko i złej tolerancji • nie wiemy jak działa na poziomie tkankowym • SPOKO NA MIKROANGIO , ale gorzej makroangio. • Ma dobry wpływ na profil lipidowy jak statyny • ZMNIEJSZA RYZYKO ZAWAŁU U OTYŁYCH KTÓRZY DOPIERO ZACZYNAJA LIRAGLUTYD(glp1) I FLOZYNY chronią przed udarami i zawałami !</t></is></c><c r="G1059" s="2" t="inlineStr" /><c r="H1059" s="2" t="inlineStr" /><c r="I1059" s="2" t="inlineStr" /><c r="J1059" s="2" t="inlineStr" /><c r="K1059" s="2" t="inlineStr"><is><t>powoduje przyrost masy ciała</t></is></c><c r="L1059" s="2" t="inlineStr"><is><t>może spowodować kwasicę ketonową</t></is></c><c r="M1059" s="2" t="inlineStr"><is><t>może być stosowana bezpiecznie jedynie u osób ze wskaźnikiem filtracji nerkowej eGFR &gt; 60 ml/mi</t></is></c><c r="N1059" s="2" t="inlineStr" /><c r="O1059" s="2" t="inlineStr" /><c r="P1059" s="2" t="inlineStr"><is><t>EGZAMIN IWL 21 czerwca 2019</t></is></c><c r="Q1059" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="1060"><c r="A1060" s="2" t="inlineStr"><is><t>CUKRZYCA</t></is></c><c r="B1060" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C1060" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1060" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1060" s="2" t="inlineStr"><is><t>Pacjent z cukrzycą typu II leczony metforminą w monoterapii, nie uzyskuje zadowalającej korekty HbA1C. Do leczenia można dołączyć:</t></is></c><c r="F1060" s="2" t="inlineStr"><is><t>Gliklazyd – pochodna sulfynylomocznika</t></is></c><c r="G1060" s="2" t="inlineStr"><is><t>empagliflozynę</t></is></c><c r="H1060" s="2" t="inlineStr"><is><t>liraglutyd</t></is></c><c r="I1060" s="2" t="inlineStr"><is><t>insulinę</t></is></c><c r="J1060" s="2" t="inlineStr" /><c r="K1060" s="2" t="inlineStr" /><c r="L1060" s="2" t="inlineStr" /><c r="M1060" s="2" t="inlineStr" /><c r="N1060" s="2" t="inlineStr" /><c r="O1060" s="2" t="inlineStr" /><c r="P1060" s="2" t="inlineStr"><is><t>EGZAMIN IWL 21 czerwca 2019</t></is></c><c r="Q1060" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="1061"><c r="A1061" s="2" t="inlineStr"><is><t>TARCZYCA</t></is></c><c r="B1061" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C1061" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1061" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1061" s="2" t="inlineStr"><is><t>W leczeniu przewlekłej niedoczynności tarczycy, głownie Hashimoto</t></is></c><c r="F1061" s="2" t="inlineStr"><is><t>dawkę hormonu tarczycy należy podawać 1x dziennie na czczo suplementujemy tyroksynę a nie trójjodotyronine w POLSCE , bo raz dziennie na czczo !</t></is></c><c r="G1061" s="2" t="inlineStr" /><c r="H1061" s="2" t="inlineStr" /><c r="I1061" s="2" t="inlineStr" /><c r="J1061" s="2" t="inlineStr" /><c r="K1061" s="2" t="inlineStr"><is><t>preferuje się preparaty złożone LT3 i LT4 – nie mamy w Polsce ! tylko tyrozyna, nawet nie ma iv do operacji i trzeba import docelowy</t></is></c><c r="L1061" s="2" t="inlineStr"><is><t>tyroksyna powinna być podawana razem z beta-adrenolitykiem</t></is></c><c r="M1061" s="2" t="inlineStr"><is><t>stosowanie inhibitora pompy protonowej poprawia wchłanianie hormonów tarczycy</t></is></c><c r="N1061" s="2" t="inlineStr" /><c r="O1061" s="2" t="inlineStr" /><c r="P1061" s="2" t="inlineStr"><is><t>EGZAMIN IWL 21 czerwca 2019</t></is></c><c r="Q1061" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="1062"><c r="A1062" s="2" t="inlineStr"><is><t>CUKRZYCA</t></is></c><c r="B1062" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C1062" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1062" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1062" s="2" t="inlineStr"><is><t>Do doustnych leków przeciwcukrzycowych istotnie zwiększających ryzyko hipoglikemii należy:</t></is></c><c r="F1062" s="2" t="inlineStr"><is><t>pochodna sulfonylomocznika już insulina bezpieczniejsaz bo krótkodziałająca meglitynidy też podowują GKUKAGON jak się poda na hipoglikemie</t></is></c><c r="G1062" s="2" t="inlineStr" /><c r="H1062" s="2" t="inlineStr" /><c r="I1062" s="2" t="inlineStr" /><c r="J1062" s="2" t="inlineStr" /><c r="K1062" s="2" t="inlineStr"><is><t>inhibitor alfa-glukozydazy (AKARBOZA)</t></is></c><c r="L1062" s="2" t="inlineStr"><is><t>pochodna biguanidu</t></is></c><c r="M1062" s="2" t="inlineStr"><is><t>glitazon</t></is></c><c r="N1062" s="2" t="inlineStr" /><c r="O1062" s="2" t="inlineStr" /><c r="P1062" s="2" t="inlineStr"><is><t>EGZAMIN IWL 21 czerwca 2019</t></is></c><c r="Q1062" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="1063"><c r="A1063" s="2" t="inlineStr"><is><t>LEKI PRZECIWNOWOTWOROWE</t></is></c><c r="B1063" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C1063" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1063" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1063" s="2" t="inlineStr"><is><t>W leczeniu choroby na tle autoimmunizacji prednizonem (gks) konieczne są szczególne środki nadzoru i terapia wspomagająca w przypadku współwystępowania:</t></is></c><c r="F1063" s="2" t="inlineStr"><is><t>zaćmy starczej</t></is></c><c r="G1063" s="2" t="inlineStr"><is><t>osteoporozy</t></is></c><c r="H1063" s="2" t="inlineStr" /><c r="I1063" s="2" t="inlineStr" /><c r="J1063" s="2" t="inlineStr" /><c r="K1063" s="2" t="inlineStr"><is><t>hiperkalcemii nowotworowej</t></is></c><c r="L1063" s="2" t="inlineStr"><is><t>małopłytkowości idiopatycznej</t></is></c><c r="M1063" s="2" t="inlineStr" /><c r="N1063" s="2" t="inlineStr" /><c r="O1063" s="2" t="inlineStr" /><c r="P1063" s="2" t="inlineStr"><is><t>EGZAMIN IWL 21 czerwca 2019</t></is></c><c r="Q1063" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="1064"><c r="A1064" s="2" t="inlineStr"><is><t>OSTEOPOROZA</t></is></c><c r="B1064" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C1064" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1064" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1064" s="2" t="inlineStr"><is><t>Bisfosfoniany są stosowane w:</t></is></c><c r="F1064" s="2" t="inlineStr"><is><t>leczeniu osteoporozy posteroidowej DO KAŻDEJ JAKO PIERWSZA LINIA</t></is></c><c r="G1064" s="2" t="inlineStr"><is><t>zapobieganiu skutkom ciężkiej hiperkalcemii</t></is></c><c r="H1064" s="2" t="inlineStr" /><c r="I1064" s="2" t="inlineStr" /><c r="J1064" s="2" t="inlineStr" /><c r="K1064" s="2" t="inlineStr"><is><t>przyspieszaniu zrostu kości po złamaniach</t></is></c><c r="L1064" s="2" t="inlineStr"><is><t>przeciwbólowej terapii choroby zwyrodnieniowej stawów</t></is></c><c r="M1064" s="2" t="inlineStr" /><c r="N1064" s="2" t="inlineStr" /><c r="O1064" s="2" t="inlineStr" /><c r="P1064" s="2" t="inlineStr"><is><t>EGZAMIN IWL 21 czerwca 2019</t></is></c><c r="Q1064" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="1065"><c r="A1065" s="2" t="inlineStr"><is><t>UKŁAD ODDECHOWY</t></is></c><c r="B1065" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C1065" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1065" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1065" s="2" t="inlineStr"><is><t>Wskaż prawidłowe połączenie lek - wskazanie do stosowania:</t></is></c><c r="F1065" s="2" t="inlineStr"><is><t>klobetazol – atopowe zapalenie skóry</t></is></c><c r="G1065" s="2" t="inlineStr"><is><t>betametazon – stymulowanie dojrzewania płuc płodu</t></is></c><c r="H1065" s="2" t="inlineStr"><is><t>cyklezonid – astma nadzwyczajny bo ulega aktywacji tylko w drzewie oskrzelowym i nie ma systemowych oddzialywan PROLEK</t></is></c><c r="I1065" s="2" t="inlineStr"><is><t>hydrokortyzon – ostra niedoczynność kory nadnerczy</t></is></c><c r="J1065" s="2" t="inlineStr" /><c r="K1065" s="2" t="inlineStr" /><c r="L1065" s="2" t="inlineStr" /><c r="M1065" s="2" t="inlineStr" /><c r="N1065" s="2" t="inlineStr" /><c r="O1065" s="2" t="inlineStr" /><c r="P1065" s="2" t="inlineStr"><is><t>EGZAMIN IWL 21 czerwca 2019</t></is></c><c r="Q1065" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="1066"><c r="A1066" s="2" t="inlineStr"><is><t>LEKI PRZECIWPSYCHOTYCZNE</t></is></c><c r="B1066" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C1066" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1066" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1066" s="2" t="inlineStr"><is><t>Hiperprolaktynemia może być powikłaniem leczenia:</t></is></c><c r="F1066" s="2" t="inlineStr"><is><t>rysperydonem</t></is></c><c r="G1066" s="2" t="inlineStr"><is><t>chlorpromazyną</t></is></c><c r="H1066" s="2" t="inlineStr"><is><t>arypiprazolem DOPAMINA HAMUJE WYDZIELANIE PROLAKTYNY Leki neuroleptyki zaznaczone one powodują hiperprolaktynemie</t></is></c><c r="I1066" s="2" t="inlineStr" /><c r="J1066" s="2" t="inlineStr" /><c r="K1066" s="2" t="inlineStr"><is><t>bromokryptyną- agonista receptora jako lek hamujący wydzielanie prolaktyny w gruczolakach przysadki</t></is></c><c r="L1066" s="2" t="inlineStr" /><c r="M1066" s="2" t="inlineStr" /><c r="N1066" s="2" t="inlineStr" /><c r="O1066" s="2" t="inlineStr" /><c r="P1066" s="2" t="inlineStr"><is><t>EGZAMIN IWL 21 czerwca 2019</t></is></c><c r="Q1066" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="1067"><c r="A1067" s="2" t="inlineStr"><is><t>NADCIŚNIENIE TĘTNICZE</t></is></c><c r="B1067" s="2" t="inlineStr"><is><t>Sposób podania</t></is></c><c r="C1067" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1067" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1067" s="2" t="inlineStr"><is><t>W hipokalcemii:</t></is></c><c r="F1067" s="2" t="inlineStr"><is><t>przewlekłej, której przyczyna nie może być usunięta, stosujemy doustnie węglan wapnia</t></is></c><c r="G1067" s="2" t="inlineStr"><is><t>witamina D powinna być podawana pod postacią aktywnych metabolitów – alfakalcydolu lub kalcytriolu</t></is></c><c r="H1067" s="2" t="inlineStr"><is><t>objawowej należy zastosować dożylnie chlorek wapnia albo glukonian wapnia, ale on jest niespodziankowy wiec preferujemy chlorek wapnia ( jest w nim 3 razy więcej jonów wapnia) TRZEBA PODAWAC BARDZO WOLNO BO ZATRZYMANIE AKCJI SERCA</t></is></c><c r="I1067" s="2" t="inlineStr"><is><t>spowodowanej nadmierną utratą wapnia z moczem skuteczne mogą być diuretyki tiazydowe</t></is></c><c r="J1067" s="2" t="inlineStr" /><c r="K1067" s="2" t="inlineStr" /><c r="L1067" s="2" t="inlineStr" /><c r="M1067" s="2" t="inlineStr" /><c r="N1067" s="2" t="inlineStr" /><c r="O1067" s="2" t="inlineStr" /><c r="P1067" s="2" t="inlineStr"><is><t>EGZAMIN IWL 21 czerwca 2019</t></is></c><c r="Q1067" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="1068"><c r="A1068" s="2" t="inlineStr"><is><t>GLIKOKORTYKOSTEROIDY</t></is></c><c r="B1068" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C1068" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1068" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1068" s="2" t="inlineStr"><is><t>Do przerwania napadu dny moczanowej można zastosować:</t></is></c><c r="F1068" s="2" t="inlineStr"><is><t>ibuprofen</t></is></c><c r="G1068" s="2" t="inlineStr"><is><t>hydrokortyzon</t></is></c><c r="H1068" s="2" t="inlineStr"><is><t>kolchicynę to jedyne wskazanie, jak się ja poda i ustąpi to wiadomo ze dna LEK JEDNEJ CHOROBY nlpz – jeżeli ból do 3 w skali was, ale jeśli dna na podlozu zapalnym to super gks SULFINPIRAZON benzomaron</t></is></c><c r="I1068" s="2" t="inlineStr" /><c r="J1068" s="2" t="inlineStr" /><c r="K1068" s="2" t="inlineStr"><is><t>allopurinol</t></is></c><c r="L1068" s="2" t="inlineStr" /><c r="M1068" s="2" t="inlineStr" /><c r="N1068" s="2" t="inlineStr" /><c r="O1068" s="2" t="inlineStr" /><c r="P1068" s="2" t="inlineStr"><is><t>EGZAMIN IWL 21 czerwca 2019</t></is></c><c r="Q1068" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="1069"><c r="A1069" s="2" t="inlineStr"><is><t>LEKI PRZECIWPASOŻYTNICZE</t></is></c><c r="B1069" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C1069" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1069" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1069" s="2" t="inlineStr"><is><t>W zarażeniach pasożytniczych:</t></is></c><c r="F1069" s="2" t="inlineStr"><is><t>pyrantel wykazuje skuteczność wobec glisty ludzkiej</t></is></c><c r="G1069" s="2" t="inlineStr"><is><t>Trichomonas vaginalis stosuje się metronidazol = tymidazol</t></is></c><c r="H1069" s="2" t="inlineStr"><is><t>permetrynę stosuje się we wszawicy</t></is></c><c r="I1069" s="2" t="inlineStr"><is><t>albendazol zabija pasożyty uniemożliwiając im wchłanianie glukozy permetryna 1%wszawica</t></is></c><c r="J1069" s="2" t="inlineStr" /><c r="K1069" s="2" t="inlineStr" /><c r="L1069" s="2" t="inlineStr" /><c r="M1069" s="2" t="inlineStr" /><c r="N1069" s="2" t="inlineStr" /><c r="O1069" s="2" t="inlineStr" /><c r="P1069" s="2" t="inlineStr"><is><t>EGZAMIN IWL 21 czerwca 2019</t></is></c><c r="Q1069" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="1070"><c r="A1070" s="2" t="inlineStr"><is><t>NIEOPIOIDOWE LEKI PRZECIWBÓLOWE</t></is></c><c r="B1070" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C1070" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1070" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1070" s="2" t="inlineStr"><is><t>Do możliwych działań niepożądanych paracetamolu można zaliczyć:</t></is></c><c r="F1070" s="2" t="inlineStr"><is><t>uszkodzenie wątroby pochodne kwasu propionowego : naproksen / ketoprofen / ibuprofen są jakby najbezpieczniejsze z NLPZ NLPZ działają PROZAKRZEPOWO jedyny jego mankament to nadmierne zbieranie si jego metabolitu np. w kaheksji alkoholikow po ciężkich schorzeniach wątroby</t></is></c><c r="G1070" s="2" t="inlineStr" /><c r="H1070" s="2" t="inlineStr" /><c r="I1070" s="2" t="inlineStr" /><c r="J1070" s="2" t="inlineStr" /><c r="K1070" s="2" t="inlineStr"><is><t>wzrost ryzyka wystąpienia choroby układu oddechowego nasilanej przez aspirynę (astmy indukowanej)</t></is></c><c r="L1070" s="2" t="inlineStr"><is><t>uszkodzenie chrząstek nasadowych u dzieci</t></is></c><c r="M1070" s="2" t="inlineStr"><is><t>działanie antyagregacyjne</t></is></c><c r="N1070" s="2" t="inlineStr" /><c r="O1070" s="2" t="inlineStr" /><c r="P1070" s="2" t="inlineStr"><is><t>EGZAMIN IWL 21 czerwca 2019</t></is></c><c r="Q1070" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="1071"><c r="A1071" s="2" t="inlineStr"><is><t>NARKOTYCZNE LEKI PRZECIWBÓLOWE</t></is></c><c r="B1071" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C1071" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1071" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1071" s="2" t="inlineStr"><is><t>W farmakoterapii silnego bólu przebijającego można zastosować:</t></is></c><c r="F1071" s="2" t="inlineStr"><is><t>fentanyl na błonę śluzową jamy ustnej</t></is></c><c r="G1071" s="2" t="inlineStr"><is><t>buprenorfinę podjęzykowo</t></is></c><c r="H1071" s="2" t="inlineStr"><is><t>fentanyl donosowo</t></is></c><c r="I1071" s="2" t="inlineStr"><is><t>morfinę doustnie Przebijajacy to taki co wystepuje mimo terapii p-bólowej FENTANYLÓW jest dużo Morfina nie może być o zmodyfikowanym uwalbnianiu • Jeżeli stosujemy czystego agonistę opioidowego, to w przebijającym też musimy dać czystego agonistę. • Jeżeli ma agoantagoniste w podstawowej to w przebijającym musimy też podać agoantagoniste. – żeby nie zniosły swoich działań</t></is></c><c r="J1071" s="2" t="inlineStr" /><c r="K1071" s="2" t="inlineStr" /><c r="L1071" s="2" t="inlineStr" /><c r="M1071" s="2" t="inlineStr" /><c r="N1071" s="2" t="inlineStr" /><c r="O1071" s="2" t="inlineStr" /><c r="P1071" s="2" t="inlineStr"><is><t>EGZAMIN IWL 21 czerwca 2019</t></is></c><c r="Q1071" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="1072"><c r="A1072" s="2" t="inlineStr"><is><t>ZNIECZULENIA OGÓLNE</t></is></c><c r="B1072" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C1072" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1072" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1072" s="2" t="inlineStr"><is><t>Do leków stosowanych miejscowo przeciwbólowo należy/ą:</t></is></c><c r="F1072" s="2" t="inlineStr"><is><t>Ketoprofen jak najbardziej można</t></is></c><c r="G1072" s="2" t="inlineStr"><is><t>kapsaicyna tylko do miejscowego znieczulenia</t></is></c><c r="H1072" s="2" t="inlineStr" /><c r="I1072" s="2" t="inlineStr" /><c r="J1072" s="2" t="inlineStr" /><c r="K1072" s="2" t="inlineStr"><is><t>izofluran</t></is></c><c r="L1072" s="2" t="inlineStr"><is><t>propofol</t></is></c><c r="M1072" s="2" t="inlineStr" /><c r="N1072" s="2" t="inlineStr" /><c r="O1072" s="2" t="inlineStr" /><c r="P1072" s="2" t="inlineStr"><is><t>EGZAMIN IWL 21 czerwca 2019</t></is></c><c r="Q1072" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="1073"><c r="A1073" s="2" t="inlineStr"><is><t>NARKOTYCZNE LEKI PRZECIWBÓLOWE</t></is></c><c r="B1073" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C1073" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1073" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1073" s="2" t="inlineStr"><is><t>Metadon jest:</t></is></c><c r="F1073" s="2" t="inlineStr"><is><t>agonistą receptorów opioidowych typu μ</t></is></c><c r="G1073" s="2" t="inlineStr"><is><t>antagonistą receptorów NMDA – receptory dla aminokwasów pobudzających czyli glutaminowego w oun są 2 uklady ten układ aktywujący a drugi to układ hamujący gabaregiczny</t></is></c><c r="H1073" s="2" t="inlineStr" /><c r="I1073" s="2" t="inlineStr" /><c r="J1073" s="2" t="inlineStr" /><c r="K1073" s="2" t="inlineStr"><is><t>inhibitorem COX-2</t></is></c><c r="L1073" s="2" t="inlineStr"><is><t>inhibitorem wychwytu dopaminy Całkiem spoko opioidów jest antagonista nmda – destrometorfan i metadon</t></is></c><c r="M1073" s="2" t="inlineStr" /><c r="N1073" s="2" t="inlineStr" /><c r="O1073" s="2" t="inlineStr" /><c r="P1073" s="2" t="inlineStr"><is><t>EGZAMIN IWL 21 czerwca 2019</t></is></c><c r="Q1073" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="1074"><c r="A1074" s="2" t="inlineStr"><is><t>NIEOPIOIDOWE LEKI PRZECIWBÓLOWE</t></is></c><c r="B1074" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C1074" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1074" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1074" s="2" t="inlineStr"><is><t>Diklofenak:</t></is></c><c r="F1074" s="2" t="inlineStr"><is><t>istotnie klinicznie zwiększa ryzyko sercowo – naczyniowe</t></is></c><c r="G1074" s="2" t="inlineStr" /><c r="H1074" s="2" t="inlineStr" /><c r="I1074" s="2" t="inlineStr" /><c r="J1074" s="2" t="inlineStr" /><c r="K1074" s="2" t="inlineStr"><is><t>ma nieznaczne działanie hepatotoksyczne</t></is></c><c r="L1074" s="2" t="inlineStr"><is><t>w największym stopniu wśród klasycznych NLPZ zwiększa ryzyko uszkodzeń błony śluzowej górnego odcinka p. pokarmowego – właśnie odwtornie IBUPROFEN JESZCZE LEPIEJ</t></is></c><c r="M1074" s="2" t="inlineStr"><is><t>może być podawany jednoczasowo z antyagregacyjnymi dawkami kwasu acetylosalicylowego</t></is></c><c r="N1074" s="2" t="inlineStr" /><c r="O1074" s="2" t="inlineStr" /><c r="P1074" s="2" t="inlineStr"><is><t>EGZAMIN IWL 21 czerwca 2019</t></is></c><c r="Q1074" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="1075"><c r="A1075" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B1075" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C1075" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1075" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1075" s="2" t="inlineStr"><is><t>Skuteczny w profilaktyce wymiotów po chemioterapii przeciwnowotworowej jest:</t></is></c><c r="F1075" s="2" t="inlineStr"><is><t>ondansetron</t></is></c><c r="G1075" s="2" t="inlineStr"><is><t>metoklopramid</t></is></c><c r="H1075" s="2" t="inlineStr"><is><t>skopolamina – KINETOZY chilinolityk działa na muskarynowe CHEMIOTERAPIA : najgorsze to późne wymioty czyli po 24 h od podania leku, im najtrudniej zapobiec. Platyna mega wywołuje wymioty TYLKO JEDNA GRUPA działa na wymioty typu późnego prwewncyjnie i skutecznie – antagoniści receptora 5ht3 – SETRONY najpotężniejszy jest PALONOSETRON (40x silniej niż inne) i dłużej METOKLOPRAMID – antagonista rec dopaminowych – klasyczny neuroleptyk, ale nie str. stosowany w psychiatri – też PROKINETYK w gastro i PRZECIWWYMIOTNY GKS Sterydy – deksametazon – uzupełnienie jako 2 lub 3 lek PRZEWLEKŁE WYMIOTY Antagoniści NK1 – aprepitant Podaje się 3 dni przed chemioterapią</t></is></c><c r="I1075" s="2" t="inlineStr" /><c r="J1075" s="2" t="inlineStr" /><c r="K1075" s="2" t="inlineStr"><is><t>dimenhydrynat – aviomarin KINETOZY przeciwhistaminowy</t></is></c><c r="L1075" s="2" t="inlineStr" /><c r="M1075" s="2" t="inlineStr" /><c r="N1075" s="2" t="inlineStr" /><c r="O1075" s="2" t="inlineStr" /><c r="P1075" s="2" t="inlineStr"><is><t>EGZAMIN IWL 21 czerwca 2019</t></is></c><c r="Q1075" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="1076"><c r="A1076" s="2" t="inlineStr"><is><t>UKŁAD PRZYWSPÓŁCZULNY</t></is></c><c r="B1076" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C1076" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1076" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1076" s="2" t="inlineStr"><is><t>Pirydostygmina jest: lek na układ przywspółczulny stosowany w neurologii POŚREDNI CHOLINOMIMETYK BO BLOKUJE ACETYLOCHILISTERAZE , te bezpośrednie to gazy bojowe. ! bo to nieodwracalne gazy uśmiercają</t></is></c><c r="F1076" s="2" t="inlineStr"><is><t>wskazana w leczeniu nużliwości mięśni (miasthenia gravis)</t></is></c><c r="G1076" s="2" t="inlineStr"><is><t>objawy przedawkowania związane są z oddziaływaniem na receptory muskarynowe i nikotynowe</t></is></c><c r="H1076" s="2" t="inlineStr" /><c r="I1076" s="2" t="inlineStr" /><c r="J1076" s="2" t="inlineStr" /><c r="K1076" s="2" t="inlineStr"><is><t>nieodwracalnym inhibitorem acetylocholinesterazy</t></is></c><c r="L1076" s="2" t="inlineStr"><is><t>stosowana w przypadku zatrucia grzybami strzępiakami i lejkówkami -To grzyb cholinomimetyczny</t></is></c><c r="M1076" s="2" t="inlineStr" /><c r="N1076" s="2" t="inlineStr" /><c r="O1076" s="2" t="inlineStr" /><c r="P1076" s="2" t="inlineStr"><is><t>EGZAMIN IWL 21 czerwca 2019</t></is></c><c r="Q1076" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="1077"><c r="A1077" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B1077" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C1077" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1077" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1077" s="2" t="inlineStr"><is><t>Do działań niepożądanych warfaryny należy/należą:</t></is></c><c r="F1077" s="2" t="inlineStr"><is><t>martwica skóry - wyłączają też antykoagulamty białko C i białko wspomagające S, jak włączamy je go zanim padnie krzepnięcie to pada antykoagulacja wiec to powoduje zakrzepice a to może doprowadzić do martwicy skóry</t></is></c><c r="G1077" s="2" t="inlineStr"><is><t>krwioplucie – każdy przeciwzakrzepowy może spowodować !</t></is></c><c r="H1077" s="2" t="inlineStr"><is><t>wady rozwojowe płodu</t></is></c><c r="I1077" s="2" t="inlineStr" /><c r="J1077" s="2" t="inlineStr" /><c r="K1077" s="2" t="inlineStr"><is><t>małopłytkowość – to TYLKO HEPARYNY - HIT niefrakcjonowana i frankcjonowane – FONDAPARYNUS NIE POWODUJE WCALE HIT</t></is></c><c r="L1077" s="2" t="inlineStr" /><c r="M1077" s="2" t="inlineStr" /><c r="N1077" s="2" t="inlineStr" /><c r="O1077" s="2" t="inlineStr" /><c r="P1077" s="2" t="inlineStr"><is><t>EGZAMIN IWL 21 czerwca 2019</t></is></c><c r="Q1077" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="1078"><c r="A1078" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B1078" s="2" t="inlineStr"><is><t>Sposób podania</t></is></c><c r="C1078" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1078" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1078" s="2" t="inlineStr"><is><t>Wskaż prawidłowe zdanie na temat leków antyagregacyjnych:</t></is></c><c r="F1078" s="2" t="inlineStr"><is><t>klopidogrel jest prolekiem</t></is></c><c r="G1078" s="2" t="inlineStr"><is><t>abcyksymab bywa stosowany w przypadku przezskórnych zabiegów na naczyniach wieńcowych</t></is></c><c r="H1078" s="2" t="inlineStr" /><c r="I1078" s="2" t="inlineStr" /><c r="J1078" s="2" t="inlineStr" /><c r="K1078" s="2" t="inlineStr"><is><t>tikagrelor nieodwracalnie wiąże się z receptorami P2Y12</t></is></c><c r="L1078" s="2" t="inlineStr"><is><t>kangrelor należy odstawić na minimum 3 dni przed planowanym zabiegiem chirurgicznym</t></is></c><c r="M1078" s="2" t="inlineStr" /><c r="N1078" s="2" t="inlineStr" /><c r="O1078" s="2" t="inlineStr" /><c r="P1078" s="2" t="inlineStr"><is><t>EGZAMIN IWL 21 czerwca 2019</t></is></c><c r="Q1078" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="1079"><c r="A1079" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B1079" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C1079" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1079" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1079" s="2" t="inlineStr"><is><t>U chorego leczonego heparyną niefrakcjonowaną wysunięto mocne podejrzenie małopłytkowości typu 2 wywołanej przez heparynę (HIT-2). W takiej sytuacji racjonalne jest:</t></is></c><c r="F1079" s="2" t="inlineStr"><is><t>oznaczenie poziomu przeciwciał przeciwko kompleksowi heparyny z czynnikiem płytkowym 4 (PF4) w surowicy</t></is></c><c r="G1079" s="2" t="inlineStr"><is><t>natychmiastowe odstawienie heparyny</t></is></c><c r="H1079" s="2" t="inlineStr"><is><t>kontynuacja leczenia przeciwzakrzepowego biwalirudyną HIT 2 zagraża życiu – przeciwciała z heparyna i z płytkami się zlepiają jest obraz maloplytkowosci a to jest zakrzepica. ROZWIJA SIĘ PO 5-10 DNIACH , może się utrzymywać tyle ile przeciwciała śmigają ok 28 dni ! Nie można zmienić frakcjonowanej na nie frakcjonowana bo i tak rozpozna, ale fondaparynuks się podaje</t></is></c><c r="I1079" s="2" t="inlineStr" /><c r="J1079" s="2" t="inlineStr" /><c r="K1079" s="2" t="inlineStr"><is><t>zastosowanie antagonisty witaminy K</t></is></c><c r="L1079" s="2" t="inlineStr" /><c r="M1079" s="2" t="inlineStr" /><c r="N1079" s="2" t="inlineStr" /><c r="O1079" s="2" t="inlineStr" /><c r="P1079" s="2" t="inlineStr"><is><t>EGZAMIN IWL 21 czerwca 2019</t></is></c><c r="Q1079" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="1080"><c r="A1080" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B1080" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C1080" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1080" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1080" s="2" t="inlineStr"><is><t>W celu zniesienia efektu przeciwkrzepliwego heparyny niefrakcjonowanej jako antidotum stosuje się:</t></is></c><c r="F1080" s="2" t="inlineStr"><is><t>siarczan protaminy Dla drobnocząsteczkowych średnio Na fondaparynę wcale nie działa Andeksenat alfa jest antidotum na ksabany, ale też się chce używać dla fonda</t></is></c><c r="G1080" s="2" t="inlineStr" /><c r="H1080" s="2" t="inlineStr" /><c r="I1080" s="2" t="inlineStr" /><c r="J1080" s="2" t="inlineStr" /><c r="K1080" s="2" t="inlineStr"><is><t>kwas traneksamowy</t></is></c><c r="L1080" s="2" t="inlineStr"><is><t>świeżo mrożone osocze str</t></is></c><c r="M1080" s="2" t="inlineStr"><is><t>fitomenadion</t></is></c><c r="N1080" s="2" t="inlineStr" /><c r="O1080" s="2" t="inlineStr" /><c r="P1080" s="2" t="inlineStr"><is><t>EGZAMIN IWL 21 czerwca 2019</t></is></c><c r="Q1080" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="1081"><c r="A1081" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B1081" s="2" t="inlineStr"><is><t>Monitorowanie</t></is></c><c r="C1081" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1081" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1081" s="2" t="inlineStr"><is><t>Wartości APTT rosną w trakcie leczenia:</t></is></c><c r="F1081" s="2" t="inlineStr"><is><t>heparyną niefrakcjonowaną – tylko ona jest tym monitorowana, frankcjonowana nie wymaga POWINNO BYĆ WYDŁUŻONE DO 2,5 monitorujemy drobnocząsteczkowe - określanie aktywności anty Xa to takie stężenie leku we krwi 4 godziny po podaniu podskórynym. NIE APTT o - skrajności w masie ciala – pediatryczne poniżej 40kg o - gfr poniżej 30 o - kobiety w ciąży Problemem jest fondaparyna bo ona też powinna być w tych 3 grupach monitorowana, ale nie ma dobrego wystandaryzowanego testu i labolatoria nie chcą oznaczac . Niefrakcjonowana trzeba MONITOROWAC ZAWSZE</t></is></c><c r="G1081" s="2" t="inlineStr" /><c r="H1081" s="2" t="inlineStr" /><c r="I1081" s="2" t="inlineStr" /><c r="J1081" s="2" t="inlineStr" /><c r="K1081" s="2" t="inlineStr"><is><t>heparyną drobnocząsteczkową</t></is></c><c r="L1081" s="2" t="inlineStr"><is><t>agonistą receptora GPIIb/IIIa – nie monitorujemy</t></is></c><c r="M1081" s="2" t="inlineStr"><is><t>bezpośrednim inhibitorem czynnika X – ksabany nie monitorujemy</t></is></c><c r="N1081" s="2" t="inlineStr" /><c r="O1081" s="2" t="inlineStr" /><c r="P1081" s="2" t="inlineStr"><is><t>EGZAMIN IWL 21 czerwca 2019</t></is></c><c r="Q1081" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="1082"><c r="A1082" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B1082" s="2" t="inlineStr"><is><t>Monitorowanie</t></is></c><c r="C1082" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1082" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1082" s="2" t="inlineStr"><is><t>Doustne leki przeciwzakrzepowe nie będące antagonistami witaminy K (NOAC):</t></is></c><c r="F1082" s="2" t="inlineStr"><is><t>mogą być stosowane w profilaktyce i w leczeniu zakrzepicy żył głębokich</t></is></c><c r="G1082" s="2" t="inlineStr"><is><t>nie są zalecane u pacjentów z mechanicznymi zastawkami serca</t></is></c><c r="H1082" s="2" t="inlineStr"><is><t>mają wspólne antidotum – idarucyzumab – tylko do dabigatanu KSABANY – 3 zarejestrowane rywalo api i edo – ksaban GATRANY – jeden dabigartan ZALECANE ( zapobieganie kardiogennej zatorowości / migotanie trzepotanie przedsionków / profilaktyka i leczenie zakrzepicy żył głębokich ) NIE SĄ ZALECANE Mechaniczne zastawki – tutaj tylko antagoniści witaminy K Patologia w obrębie zastawki MITRALNEJ = zylna zastawka lewego serca stenoza/ niedomylaność Występowanie zastawkowe migotanie na zastawce MITRALNEJ Zespół antyfosfolipidowy</t></is></c><c r="I1082" s="2" t="inlineStr" /><c r="J1082" s="2" t="inlineStr" /><c r="K1082" s="2" t="inlineStr"><is><t>wymagają terapii monitorowanej oznaczeniami INR</t></is></c><c r="L1082" s="2" t="inlineStr" /><c r="M1082" s="2" t="inlineStr" /><c r="N1082" s="2" t="inlineStr" /><c r="O1082" s="2" t="inlineStr" /><c r="P1082" s="2" t="inlineStr"><is><t>EGZAMIN IWL 21 czerwca 2019</t></is></c><c r="Q1082" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="1083"><c r="A1083" s="2" t="inlineStr"><is><t>CUKRZYCA</t></is></c><c r="B1083" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C1083" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1083" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1083" s="2" t="inlineStr"><is><t>Do strategii o udokumentowanym działaniu zmniejszającym ryzyko udaru niedokrwiennego mózgu (profilaktyka pierwotna) należy leczenie:</t></is></c><c r="F1083" s="2" t="inlineStr"><is><t>hipotensyjne</t></is></c><c r="G1083" s="2" t="inlineStr"><is><t>normoglikemizujące w cukrzycy typu II</t></is></c><c r="H1083" s="2" t="inlineStr"><is><t>nikotynizmu</t></is></c><c r="I1083" s="2" t="inlineStr"><is><t>przeciwkrzepliwe w migotaniu przedsionków Czynniki ryzyka Migotanie/trzepotanie przedsionków – główny problem kardiogennego ryzyka śmierci MIAŻDZYCA – ryzyko i neuro i kardio</t></is></c><c r="J1083" s="2" t="inlineStr" /><c r="K1083" s="2" t="inlineStr" /><c r="L1083" s="2" t="inlineStr" /><c r="M1083" s="2" t="inlineStr" /><c r="N1083" s="2" t="inlineStr" /><c r="O1083" s="2" t="inlineStr" /><c r="P1083" s="2" t="inlineStr"><is><t>EGZAMIN IWL 21 czerwca 2019</t></is></c><c r="Q1083" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="1084"><c r="A1084" s="2" t="inlineStr"><is><t>CUKRZYCA</t></is></c><c r="B1084" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C1084" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1084" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1084" s="2" t="inlineStr"><is><t>Orlistat:</t></is></c><c r="F1084" s="2" t="inlineStr"><is><t>jest wybiórczym długodziałającym inhibitorem lipaz obecnych w przewodzie pokarmowym – trochę podobny do akarbozy ona cukry xd</t></is></c><c r="G1084" s="2" t="inlineStr"><is><t>bez zastosowania diety o zmniejszonej zawartości tłuszczu charakteryzuje się złą tolerancją leczenia</t></is></c><c r="H1084" s="2" t="inlineStr" /><c r="I1084" s="2" t="inlineStr" /><c r="J1084" s="2" t="inlineStr" /><c r="K1084" s="2" t="inlineStr"><is><t>nie może być stosowany w połączeniu ze statyną – MOŻE</t></is></c><c r="L1084" s="2" t="inlineStr"><is><t>zwiększa ryzyko hipoglikemii częste niepożądane u pacjentów z cukrzycą typu II, ale nie przez jego bezpośrednie działanie, ale bo mają biegunke i źle przyswają KLASYCZNIE BEHAWIORALNIE KARA PACJENTA – jak źle jesz to biegunka ból brzucha</t></is></c><c r="M1084" s="2" t="inlineStr" /><c r="N1084" s="2" t="inlineStr" /><c r="O1084" s="2" t="inlineStr" /><c r="P1084" s="2" t="inlineStr"><is><t>EGZAMIN IWL 21 czerwca 2019</t></is></c><c r="Q1084" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="1085"><c r="A1085" s="2" t="inlineStr"><is><t>NADCIŚNIENIE TĘTNICZE</t></is></c><c r="B1085" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C1085" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1085" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1085" s="2" t="inlineStr"><is><t>Stężenie kwasu moczowego w surowicy zmniejsza się po zastosowaniu: 2:04</t></is></c><c r="F1085" s="2" t="inlineStr"><is><t>losartanu TYLKO ON JEDYNY ZMNIEJSZA inne sartany nie</t></is></c><c r="G1085" s="2" t="inlineStr"><is><t>allopurynolu • cebuksostat • razburykaza – lek biotechnologiczny rozkładający kwas moczowy stosowany tylko w onkologii urykozuryczne sulfinpirazon benzbromaron</t></is></c><c r="H1085" s="2" t="inlineStr" /><c r="I1085" s="2" t="inlineStr" /><c r="J1085" s="2" t="inlineStr" /><c r="K1085" s="2" t="inlineStr"><is><t>torasemidu</t></is></c><c r="L1085" s="2" t="inlineStr"><is><t>kwasu acetylosalicylowego w małej dawce (&lt; 2g/dobę) byłoby dobrze – W DUŻEJ zmniejsza !</t></is></c><c r="M1085" s="2" t="inlineStr" /><c r="N1085" s="2" t="inlineStr" /><c r="O1085" s="2" t="inlineStr" /><c r="P1085" s="2" t="inlineStr"><is><t>EGZAMIN IWL 21 czerwca 2019</t></is></c><c r="Q1085" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="1086"><c r="A1086" s="2" t="inlineStr"><is><t>LEKI HIPOLIPEMIZUJĄCE</t></is></c><c r="B1086" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C1086" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1086" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1086" s="2" t="inlineStr"><is><t>W leczeniu zaburzeń lipidowych:</t></is></c><c r="F1086" s="2" t="inlineStr"><is><t>fibraty są lekami pierwszego wyboru w ciężkiej hipertrójglicerydemii – grozi zapaleniem trzustki !! albo plazmafereza i się płucze surowice z tłuszczu</t></is></c><c r="G1086" s="2" t="inlineStr"><is><t>można rozważyć zastosowanie ezetymibu w monoterapii u pacjentów, którzy nie tolerują statyn, aby uzyskać docelowe stężenia cholesterolu LDL w surowicy – no można ale średnie</t></is></c><c r="H1086" s="2" t="inlineStr"><is><t>po zastosowaniu kolesewelamu może dojść do zwiększenia stężenia trójglicerydów w surowicy to grupa żywic jonowymiennych ich nie ma one odbiżają ldl ale zwiekszaja tg , bez sensu wiec. Maja duży mankament – łączą kwasy zółciowe i dużo leków które pacjent przyjmuje wiec trzeba by było robic przerwę 6 h miedzy lekiem a tą żywicą . W POLCE NIE MA ŻADNEJ STATYN NIE MOŻNA GDY Kinaza keratynowa powyżej 5 razy powyżej normy i rabdomioliza Gdy 3 razy wzrasta stężenie ASPAT ALAT aminotransferaz – przerwany</t></is></c><c r="I1086" s="2" t="inlineStr" /><c r="J1086" s="2" t="inlineStr" /><c r="K1086" s="2" t="inlineStr"><is><t>łączne stosowanie statyn i wielonienasyconych kwasów tłuszczowych (PUFA omega-3) zalecane jest u pacjentów z bardzo wysokim stężeniem cholesterolu LDL w surowicy – nie prawda bo statyny są ekstra ale pufa nie obniża ldl wiec jak statyna nie starcza to trzeba dać ezetymib – tani lub z drogimi refundowane tylko w rodzinnej hipercholesterolemii inh pcsk9 (eworokumab)</t></is></c><c r="L1086" s="2" t="inlineStr" /><c r="M1086" s="2" t="inlineStr" /><c r="N1086" s="2" t="inlineStr" /><c r="O1086" s="2" t="inlineStr" /><c r="P1086" s="2" t="inlineStr"><is><t>EGZAMIN IWL 21 czerwca 2019</t></is></c><c r="Q1086" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="1087"><c r="A1087" s="2" t="inlineStr"><is><t>NADCIŚNIENIE TĘTNICZE</t></is></c><c r="B1087" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C1087" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1087" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1087" s="2" t="inlineStr"><is><t>Polekowe upośledzenie funkcji nerek może wystąpić podczas stosowania w dawkach terapeutycznych:</t></is></c><c r="F1087" s="2" t="inlineStr"><is><t>kolistymetatu</t></is></c><c r="G1087" s="2" t="inlineStr" /><c r="H1087" s="2" t="inlineStr" /><c r="I1087" s="2" t="inlineStr" /><c r="J1087" s="2" t="inlineStr" /><c r="K1087" s="2" t="inlineStr"><is><t>węglanu litu</t></is></c><c r="L1087" s="2" t="inlineStr"><is><t>ketoprofenu</t></is></c><c r="M1087" s="2" t="inlineStr"><is><t>peryndoprylu</t></is></c><c r="N1087" s="2" t="inlineStr" /><c r="O1087" s="2" t="inlineStr" /><c r="P1087" s="2" t="inlineStr"><is><t>EGZAMIN IWL 21 czerwca 2019</t></is></c><c r="Q1087" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="1088"><c r="A1088" s="2" t="inlineStr"><is><t>FARMAKOKINETYKA</t></is></c><c r="B1088" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C1088" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1088" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1088" s="2" t="inlineStr"><is><t>Wskaż prawdziwe twierdzenie dotyczące oddziaływania leku na receptory:</t></is></c><c r="F1088" s="2" t="inlineStr"><is><t>antagonista konkurencyjny przesuwa krzywą dawka-odpowiedź agonisty (dose- response curve) na prawo</t></is></c><c r="G1088" s="2" t="inlineStr"><is><t>agonista wiąże się w miejscu allosterycznej modulacji receptora dla endogennego liganda</t></is></c><c r="H1088" s="2" t="inlineStr"><is><t>odwrotny agonista wiąże się z receptorem w miejscu wiązania endogennego liganda, ale wywołuje odwrotny efekt biologiczny</t></is></c><c r="I1088" s="2" t="inlineStr"><is><t>antagonista funkcjonalny hamuje efekt biologiczny innego leku - agonisty poprzez działanie agonistyczne na odmienne receptory</t></is></c><c r="J1088" s="2" t="inlineStr" /><c r="K1088" s="2" t="inlineStr" /><c r="L1088" s="2" t="inlineStr" /><c r="M1088" s="2" t="inlineStr" /><c r="N1088" s="2" t="inlineStr" /><c r="O1088" s="2" t="inlineStr" /><c r="P1088" s="2" t="inlineStr"><is><t>EGZAMIN IWL 21 czerwca 2019</t></is></c><c r="Q1088" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="1089"><c r="A1089" s="2" t="inlineStr"><is><t>UKŁAD ODDECHOWY</t></is></c><c r="B1089" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C1089" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1089" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1089" s="2" t="inlineStr"><is><t>W nebulizacji można podać:</t></is></c><c r="F1089" s="2" t="inlineStr"><is><t>budezonid</t></is></c><c r="G1089" s="2" t="inlineStr"><is><t>tobramycynę</t></is></c><c r="H1089" s="2" t="inlineStr"><is><t>salbutamol</t></is></c><c r="I1089" s="2" t="inlineStr"><is><t>ambroksol ABSOLUTNIE NIE MOŻNA ACC !</t></is></c><c r="J1089" s="2" t="inlineStr" /><c r="K1089" s="2" t="inlineStr" /><c r="L1089" s="2" t="inlineStr" /><c r="M1089" s="2" t="inlineStr" /><c r="N1089" s="2" t="inlineStr" /><c r="O1089" s="2" t="inlineStr" /><c r="P1089" s="2" t="inlineStr"><is><t>EGZAMIN IWL 21 czerwca 2019</t></is></c><c r="Q1089" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="1090"><c r="A1090" s="2" t="inlineStr"><is><t>UKŁAD ODDECHOWY</t></is></c><c r="B1090" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C1090" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1090" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1090" s="2" t="inlineStr"><is><t>Wskazaniem do podania mukolityków jest:</t></is></c><c r="F1090" s="2" t="inlineStr"><is><t>przewlekła obturacyjna choroba płuc (POChP)</t></is></c><c r="G1090" s="2" t="inlineStr"><is><t>mukowiscydoza</t></is></c><c r="H1090" s="2" t="inlineStr" /><c r="I1090" s="2" t="inlineStr" /><c r="J1090" s="2" t="inlineStr" /><c r="K1090" s="2" t="inlineStr"><is><t>suchy, uporczywy kaszel o nieustalonej przyczynie</t></is></c><c r="L1090" s="2" t="inlineStr"><is><t>profilaktyka złamań żeber u osób z osteoporozą</t></is></c><c r="M1090" s="2" t="inlineStr" /><c r="N1090" s="2" t="inlineStr" /><c r="O1090" s="2" t="inlineStr" /><c r="P1090" s="2" t="inlineStr"><is><t>EGZAMIN IWL 21 czerwca 2019</t></is></c><c r="Q1090" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="1091"><c r="A1091" s="2" t="inlineStr"><is><t>UKŁAD ODDECHOWY</t></is></c><c r="B1091" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C1091" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1091" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1091" s="2" t="inlineStr"><is><t>W leczeniu ciężkich zaostrzeń astmy niekorzystna jest ekspozycja pacjenta na:</t></is></c><c r="F1091" s="2" t="inlineStr"><is><t>beta-adrenolityki</t></is></c><c r="G1091" s="2" t="inlineStr"><is><t>leki przeciwkaszlowe</t></is></c><c r="H1091" s="2" t="inlineStr" /><c r="I1091" s="2" t="inlineStr" /><c r="J1091" s="2" t="inlineStr" /><c r="K1091" s="2" t="inlineStr"><is><t>teofilinę</t></is></c><c r="L1091" s="2" t="inlineStr"><is><t>doustne glikokortykosteroidy</t></is></c><c r="M1091" s="2" t="inlineStr" /><c r="N1091" s="2" t="inlineStr" /><c r="O1091" s="2" t="inlineStr" /><c r="P1091" s="2" t="inlineStr"><is><t>EGZAMIN IWL 21 czerwca 2019</t></is></c><c r="Q1091" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="1092"><c r="A1092" s="2" t="inlineStr"><is><t>UKŁAD ODDECHOWY</t></is></c><c r="B1092" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C1092" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1092" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1092" s="2" t="inlineStr"><is><t>Bromek tiotropium:</t></is></c><c r="F1092" s="2" t="inlineStr"><is><t>jest stosowany w leczeniu przewlekłej obturacyjnej choroby płuc (POChP)</t></is></c><c r="G1092" s="2" t="inlineStr" /><c r="H1092" s="2" t="inlineStr" /><c r="I1092" s="2" t="inlineStr" /><c r="J1092" s="2" t="inlineStr" /><c r="K1092" s="2" t="inlineStr"><is><t>jest wziewnym agonistą receptorów muskarynowych</t></is></c><c r="L1092" s="2" t="inlineStr"><is><t>może być stosowany do przerywania ostrej duszności w astmie</t></is></c><c r="M1092" s="2" t="inlineStr"><is><t>rozszczepia wiązania disiarczkowe w glikoproteinach śluzu</t></is></c><c r="N1092" s="2" t="inlineStr" /><c r="O1092" s="2" t="inlineStr" /><c r="P1092" s="2" t="inlineStr"><is><t>EGZAMIN IWL 21 czerwca 2019</t></is></c><c r="Q1092" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="1093"><c r="A1093" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B1093" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C1093" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1093" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1093" s="2" t="inlineStr"><is><t>W leczeniu refluksu żołądkowo-przełykowego można zastosować:</t></is></c><c r="F1093" s="2" t="inlineStr"><is><t>lanzoprazol</t></is></c><c r="G1093" s="2" t="inlineStr" /><c r="H1093" s="2" t="inlineStr" /><c r="I1093" s="2" t="inlineStr" /><c r="J1093" s="2" t="inlineStr" /><c r="K1093" s="2" t="inlineStr"><is><t>suplementację enzymów trzustkowych</t></is></c><c r="L1093" s="2" t="inlineStr"><is><t>ryfaksyminę</t></is></c><c r="M1093" s="2" t="inlineStr"><is><t>mizoprostol</t></is></c><c r="N1093" s="2" t="inlineStr" /><c r="O1093" s="2" t="inlineStr" /><c r="P1093" s="2" t="inlineStr"><is><t>EGZAMIN IWL 21 czerwca 2019</t></is></c><c r="Q1093" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="1094"><c r="A1094" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B1094" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C1094" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1094" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1094" s="2" t="inlineStr"><is><t>Wskaż prawdziwe twierdzenie na temat leczenia zaparć:</t></is></c><c r="F1094" s="2" t="inlineStr"><is><t>bisakodyl wykazuje bezpośrednie działanie na sploty nerwowe błony śluzowej w jelicie grubym</t></is></c><c r="G1094" s="2" t="inlineStr"><is><t>dokusan sodowy działa rozmiękczająco na masy kałowe</t></is></c><c r="H1094" s="2" t="inlineStr" /><c r="I1094" s="2" t="inlineStr" /><c r="J1094" s="2" t="inlineStr" /><c r="K1094" s="2" t="inlineStr"><is><t>racekadotryl zwiększa poślizg mas kałowych w obrębie jelita grubego</t></is></c><c r="L1094" s="2" t="inlineStr"><is><t>siarczan magnezu ma działanie adsorpcyjne</t></is></c><c r="M1094" s="2" t="inlineStr" /><c r="N1094" s="2" t="inlineStr" /><c r="O1094" s="2" t="inlineStr" /><c r="P1094" s="2" t="inlineStr"><is><t>EGZAMIN IWL 21 czerwca 2019</t></is></c><c r="Q1094" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="1095"><c r="A1095" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B1095" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C1095" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1095" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1095" s="2" t="inlineStr"><is><t>Mesalazyna:</t></is></c><c r="F1095" s="2" t="inlineStr"><is><t>jest pochodną kwasu 5-aminosalicylowego</t></is></c><c r="G1095" s="2" t="inlineStr"><is><t>może powodować biegunkę, wzdęcia i bóle brzucha</t></is></c><c r="H1095" s="2" t="inlineStr"><is><t>jest stosowana we wrzodziejącym zapaleniu jelita grubego</t></is></c><c r="I1095" s="2" t="inlineStr" /><c r="J1095" s="2" t="inlineStr" /><c r="K1095" s="2" t="inlineStr"><is><t>zasięg jej działania w przewodzie pokarmowym po podaniu doustnym nie zależy od zastosowanego preparatu</t></is></c><c r="L1095" s="2" t="inlineStr" /><c r="M1095" s="2" t="inlineStr" /><c r="N1095" s="2" t="inlineStr" /><c r="O1095" s="2" t="inlineStr" /><c r="P1095" s="2" t="inlineStr"><is><t>EGZAMIN IWL 21 czerwca 2019</t></is></c><c r="Q1095" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="1096"><c r="A1096" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B1096" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C1096" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1096" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1096" s="2" t="inlineStr"><is><t>Pantoprazol:</t></is></c><c r="F1096" s="2" t="inlineStr"><is><t>zmniejsza wchłanianie witaminy B12 z przewodu pokarmowego</t></is></c><c r="G1096" s="2" t="inlineStr"><is><t>zwiększa ryzyko zakażeń przewodu pokarmowego</t></is></c><c r="H1096" s="2" t="inlineStr" /><c r="I1096" s="2" t="inlineStr" /><c r="J1096" s="2" t="inlineStr" /><c r="K1096" s="2" t="inlineStr"><is><t>zmniejsza przekształcanie klopidogrelu do aktywnych pochodnych</t></is></c><c r="L1096" s="2" t="inlineStr"><is><t>zwiększa wydzielanie gastryny bez konsekwencji klinicznych</t></is></c><c r="M1096" s="2" t="inlineStr" /><c r="N1096" s="2" t="inlineStr" /><c r="O1096" s="2" t="inlineStr" /><c r="P1096" s="2" t="inlineStr"><is><t>EGZAMIN IWL 21 czerwca 2019</t></is></c><c r="Q1096" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="1097"><c r="A1097" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B1097" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C1097" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1097" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1097" s="2" t="inlineStr"><is><t>Prokinetyki znalazły zastosowanie w leczeniu:</t></is></c><c r="F1097" s="2" t="inlineStr"><is><t>gastroparezy cukrzycowej (spowolnienia opróżniania żołądka wywołanego neuropatią autonomiczną)</t></is></c><c r="G1097" s="2" t="inlineStr"><is><t>atonicznego zaparcia nawykowego</t></is></c><c r="H1097" s="2" t="inlineStr" /><c r="I1097" s="2" t="inlineStr" /><c r="J1097" s="2" t="inlineStr" /><c r="K1097" s="2" t="inlineStr"><is><t>choroby lokomocyjnej</t></is></c><c r="L1097" s="2" t="inlineStr"><is><t>niedrożności mechanicznej jelita cienkiego</t></is></c><c r="M1097" s="2" t="inlineStr" /><c r="N1097" s="2" t="inlineStr" /><c r="O1097" s="2" t="inlineStr" /><c r="P1097" s="2" t="inlineStr"><is><t>EGZAMIN IWL 21 czerwca 2019</t></is></c><c r="Q1097" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="1098"><c r="A1098" s="2" t="inlineStr"><is><t>LEKI PRZECIWPSYCHOTYCZNE</t></is></c><c r="B1098" s="2" t="inlineStr"><is><t>Monitorowanie</t></is></c><c r="C1098" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1098" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1098" s="2" t="inlineStr"><is><t>Klozapina:</t></is></c><c r="F1098" s="2" t="inlineStr"><is><t>może być skuteczna w lekoopornej schizofrenii</t></is></c><c r="G1098" s="2" t="inlineStr"><is><t>wymaga monitorowania morfologii krwi</t></is></c><c r="H1098" s="2" t="inlineStr" /><c r="I1098" s="2" t="inlineStr" /><c r="J1098" s="2" t="inlineStr" /><c r="K1098" s="2" t="inlineStr"><is><t>jest przeciwwskazana u pacjentów agresywnych i pobudzonych</t></is></c><c r="L1098" s="2" t="inlineStr"><is><t>jest neutralna metabolicznie</t></is></c><c r="M1098" s="2" t="inlineStr" /><c r="N1098" s="2" t="inlineStr" /><c r="O1098" s="2" t="inlineStr" /><c r="P1098" s="2" t="inlineStr"><is><t>EGZAMIN IWL 21 czerwca 2019</t></is></c><c r="Q1098" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="1099"><c r="A1099" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B1099" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C1099" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1099" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1099" s="2" t="inlineStr"><is><t>Wskaż prawidłowe zestawienie roślina lecznicza – wskazanie:</t></is></c><c r="F1099" s="2" t="inlineStr"><is><t>kozłek lekarski (valeriana officinalis) – łagodne stany lękowe</t></is></c><c r="G1099" s="2" t="inlineStr"><is><t>dziurawiec zwyczajny (hypericum perforatum) – łagodna depresja</t></is></c><c r="H1099" s="2" t="inlineStr" /><c r="I1099" s="2" t="inlineStr" /><c r="J1099" s="2" t="inlineStr" /><c r="K1099" s="2" t="inlineStr"><is><t>miłorząb japoński (ginkgo biloba) – zaburzenia krzepnięcia</t></is></c><c r="L1099" s="2" t="inlineStr"><is><t>borówka czernica (vaccinium myrtillus) - zaparcie</t></is></c><c r="M1099" s="2" t="inlineStr" /><c r="N1099" s="2" t="inlineStr" /><c r="O1099" s="2" t="inlineStr" /><c r="P1099" s="2" t="inlineStr"><is><t>EGZAMIN IWL 21 czerwca 2019</t></is></c><c r="Q1099" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="1100"><c r="A1100" s="2" t="inlineStr"><is><t>PADACZKA</t></is></c><c r="B1100" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C1100" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1100" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1100" s="2" t="inlineStr"><is><t>Pregabalina:</t></is></c><c r="F1100" s="2" t="inlineStr"><is><t>wiąże się z kanałem wapniowym w OUN</t></is></c><c r="G1100" s="2" t="inlineStr"><is><t>należy do leków przeciwpadaczkowych</t></is></c><c r="H1100" s="2" t="inlineStr"><is><t>może być stosowana przewlekle w leczeniu bólu neuropatycznego</t></is></c><c r="I1100" s="2" t="inlineStr" /><c r="J1100" s="2" t="inlineStr" /><c r="K1100" s="2" t="inlineStr"><is><t>zmniejsza uwalnianie kwasu glutaminowego z części presynapytycznej neuronu</t></is></c><c r="L1100" s="2" t="inlineStr" /><c r="M1100" s="2" t="inlineStr" /><c r="N1100" s="2" t="inlineStr" /><c r="O1100" s="2" t="inlineStr" /><c r="P1100" s="2" t="inlineStr"><is><t>EGZAMIN IWL 21 czerwca 2019</t></is></c><c r="Q1100" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="1101"><c r="A1101" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B1101" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C1101" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1101" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1101" s="2" t="inlineStr"><is><t>Laktuloza:</t></is></c><c r="F1101" s="2" t="inlineStr"><is><t>jest syntetycznym dwucukrem nie podlegającym trawieniu w p. pokarmowym</t></is></c><c r="G1101" s="2" t="inlineStr"><is><t>zakwasza treść jelita grubego</t></is></c><c r="H1101" s="2" t="inlineStr" /><c r="I1101" s="2" t="inlineStr" /><c r="J1101" s="2" t="inlineStr" /><c r="K1101" s="2" t="inlineStr"><is><t>działa maksymalnie po 6 godzinach od podania</t></is></c><c r="L1101" s="2" t="inlineStr"><is><t>zwiększa wchłanianie amoniaku z jelit</t></is></c><c r="M1101" s="2" t="inlineStr" /><c r="N1101" s="2" t="inlineStr" /><c r="O1101" s="2" t="inlineStr" /><c r="P1101" s="2" t="inlineStr"><is><t>EGZAMIN IWL 21 czerwca 2019</t></is></c><c r="Q1101" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="1102"><c r="A1102" s="2" t="inlineStr"><is><t>CHOROBA PARKINSONA</t></is></c><c r="B1102" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C1102" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1102" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1102" s="2" t="inlineStr"><is><t>Do bezpośrednich agonistów receptorów dopaminowych stosowanych w chorobie Parkinsona należy:</t></is></c><c r="F1102" s="2" t="inlineStr"><is><t>ropinirol</t></is></c><c r="G1102" s="2" t="inlineStr"><is><t>pramipeksol</t></is></c><c r="H1102" s="2" t="inlineStr" /><c r="I1102" s="2" t="inlineStr" /><c r="J1102" s="2" t="inlineStr" /><c r="K1102" s="2" t="inlineStr"><is><t>entakapon</t></is></c><c r="L1102" s="2" t="inlineStr"><is><t>rasagilina</t></is></c><c r="M1102" s="2" t="inlineStr" /><c r="N1102" s="2" t="inlineStr" /><c r="O1102" s="2" t="inlineStr" /><c r="P1102" s="2" t="inlineStr"><is><t>EGZAMIN IWL 21 czerwca 2019</t></is></c><c r="Q1102" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="1103"><c r="A1103" s="2" t="inlineStr"><is><t>CHOROBA NIEDOKRWIENNA SERCA</t></is></c><c r="B1103" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C1103" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1103" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1103" s="2" t="inlineStr"><is><t>Wskaż prawdziwe stwierdzenie dotyczące benzodiazepin:</t></is></c><c r="F1103" s="2" t="inlineStr"><is><t>leki długodziałające w przeciwieństwie do leków krótkodziałających wywołują niepamięć następczą</t></is></c><c r="G1103" s="2" t="inlineStr"><is><t>mogą spowodować nawrót dolegliwości w nasileniu większym, niż przed ich podaniem (efekt z odbicia)</t></is></c><c r="H1103" s="2" t="inlineStr"><is><t>leki krótkodziałające są bezpieczniejsze od leków o długim czasie działania ze względu na mniejsze ryzyko rozwoju tolerancji i uzależnienia</t></is></c><c r="I1103" s="2" t="inlineStr"><is><t>znalazły zastosowanie w leczeniu napadów paniki w krótkotrwałym użyciu</t></is></c><c r="J1103" s="2" t="inlineStr" /><c r="K1103" s="2" t="inlineStr" /><c r="L1103" s="2" t="inlineStr" /><c r="M1103" s="2" t="inlineStr" /><c r="N1103" s="2" t="inlineStr" /><c r="O1103" s="2" t="inlineStr" /><c r="P1103" s="2" t="inlineStr"><is><t>EGZAMIN IWL 21 czerwca 2019</t></is></c><c r="Q1103" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="1104"><c r="A1104" s="2" t="inlineStr"><is><t>LEKI PRZECIWLĘKOWE</t></is></c><c r="B1104" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C1104" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1104" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1104" s="2" t="inlineStr"><is><t>Niebenzodiazepinowe leki nasenne z grupy cyklopironów:</t></is></c><c r="F1104" s="2" t="inlineStr"><is><t>nie zmniejszają latencji snu</t></is></c><c r="G1104" s="2" t="inlineStr" /><c r="H1104" s="2" t="inlineStr" /><c r="I1104" s="2" t="inlineStr" /><c r="J1104" s="2" t="inlineStr" /><c r="K1104" s="2" t="inlineStr"><is><t>łączą się w obrębie kompleksu receptora GABA-A</t></is></c><c r="L1104" s="2" t="inlineStr"><is><t>mają istotne klinicznie działanie anksjolityczne</t></is></c><c r="M1104" s="2" t="inlineStr"><is><t>mogą być przyczyną niepamięci następczej</t></is></c><c r="N1104" s="2" t="inlineStr" /><c r="O1104" s="2" t="inlineStr" /><c r="P1104" s="2" t="inlineStr"><is><t>EGZAMIN IWL 21 czerwca 2019</t></is></c><c r="Q1104" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="1105"><c r="A1105" s="2" t="inlineStr"><is><t>OTĘPIENIE</t></is></c><c r="B1105" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C1105" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1105" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1105" s="2" t="inlineStr"><is><t>W leczeniu zaawansowanej choroby Alzheimera skuteczne są:</t></is></c><c r="F1105" s="2" t="inlineStr"><is><t>rywastygmina</t></is></c><c r="G1105" s="2" t="inlineStr"><is><t>piracetam</t></is></c><c r="H1105" s="2" t="inlineStr"><is><t>memantyna</t></is></c><c r="I1105" s="2" t="inlineStr" /><c r="J1105" s="2" t="inlineStr" /><c r="K1105" s="2" t="inlineStr"><is><t>amitryptylina – nie można bo cholinolityk</t></is></c><c r="L1105" s="2" t="inlineStr" /><c r="M1105" s="2" t="inlineStr" /><c r="N1105" s="2" t="inlineStr" /><c r="O1105" s="2" t="inlineStr" /><c r="P1105" s="2" t="inlineStr"><is><t>EGZAMIN IWL 21 czerwca 2019</t></is></c><c r="Q1105" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="1106"><c r="A1106" s="2" t="inlineStr"><is><t>LEKI PRZECIWDEPRESYJNE</t></is></c><c r="B1106" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C1106" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1106" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1106" s="2" t="inlineStr"><is><t>Chorobę afektywną jednobiegunową (endogenny zespół depresyjny), współistniejącą z bólem przewlekłym można optymalnie leczyć:</t></is></c><c r="F1106" s="2" t="inlineStr"><is><t>duloksetyną</t></is></c><c r="G1106" s="2" t="inlineStr"><is><t>amitryptyliną</t></is></c><c r="H1106" s="2" t="inlineStr" /><c r="I1106" s="2" t="inlineStr" /><c r="J1106" s="2" t="inlineStr" /><c r="K1106" s="2" t="inlineStr"><is><t>wortioksetyną</t></is></c><c r="L1106" s="2" t="inlineStr"><is><t>tasimelteonem</t></is></c><c r="M1106" s="2" t="inlineStr" /><c r="N1106" s="2" t="inlineStr" /><c r="O1106" s="2" t="inlineStr" /><c r="P1106" s="2" t="inlineStr"><is><t>EGZAMIN IWL 21 czerwca 2019</t></is></c><c r="Q1106" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="1107"><c r="A1107" s="2" t="inlineStr"><is><t>NADCIŚNIENIE TĘTNICZE</t></is></c><c r="B1107" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C1107" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1107" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1107" s="2" t="inlineStr"><is><t>Nadciśnienie płucne zmniejszają:</t></is></c><c r="F1107" s="2" t="inlineStr"><is><t>syntetyczne analogi prostacykliny PROSTANOIDY – jedyne miejsce tych leków epoprostenol iloprost</t></is></c><c r="G1107" s="2" t="inlineStr"><is><t>inhibitory fosfodiesterazy 5 – SILDENAFIL ( WIAGRA) – nie można łączyć z AZOTANAMI</t></is></c><c r="H1107" s="2" t="inlineStr"><is><t>aktywatory rozpuszczalnej cyklazy guanylowej (sGC) – nowsze riocyguat</t></is></c><c r="I1107" s="2" t="inlineStr"><is><t>antagoniści receptora dla endoteliny BOSENTAN, ABRYSENTAN, MACYTENTAN</t></is></c><c r="J1107" s="2" t="inlineStr" /><c r="K1107" s="2" t="inlineStr" /><c r="L1107" s="2" t="inlineStr" /><c r="M1107" s="2" t="inlineStr" /><c r="N1107" s="2" t="inlineStr" /><c r="O1107" s="2" t="inlineStr" /><c r="P1107" s="2" t="inlineStr"><is><t>EGZAMIN IWL 21 czerwca 2019</t></is></c><c r="Q1107" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="1108"><c r="A1108" s="2" t="inlineStr"><is><t>ZNIECZULENIA OGÓLNE</t></is></c><c r="B1108" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C1108" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1108" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1108" s="2" t="inlineStr"><is><t>Propofol:</t></is></c><c r="F1108" s="2" t="inlineStr"><is><t>może być stosowany we wprowadzaniu do znieczulenia ogólnego</t></is></c><c r="G1108" s="2" t="inlineStr"><is><t>jest stosowany w celu sedacji osób wentylowanych mechanicznie w intensywnej opiece medycznej</t></is></c><c r="H1108" s="2" t="inlineStr" /><c r="I1108" s="2" t="inlineStr" /><c r="J1108" s="2" t="inlineStr" /><c r="K1108" s="2" t="inlineStr"><is><t>należy do grupy długodziałających anestetyków dożylnych</t></is></c><c r="L1108" s="2" t="inlineStr"><is><t>często powoduje wzrost ciśnienia tętniczego</t></is></c><c r="M1108" s="2" t="inlineStr" /><c r="N1108" s="2" t="inlineStr" /><c r="O1108" s="2" t="inlineStr" /><c r="P1108" s="2" t="inlineStr"><is><t>EGZAMIN IWL 21 czerwca 2019</t></is></c><c r="Q1108" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="1109"><c r="A1109" s="2" t="inlineStr"><is><t>PADACZKA</t></is></c><c r="B1109" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C1109" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1109" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1109" s="2" t="inlineStr"><is><t>Do leków normotymicznych należy:</t></is></c><c r="F1109" s="2" t="inlineStr"><is><t>węglan litu</t></is></c><c r="G1109" s="2" t="inlineStr"><is><t>karbamazepina</t></is></c><c r="H1109" s="2" t="inlineStr"><is><t>kwas walproinowy</t></is></c><c r="I1109" s="2" t="inlineStr"><is><t>lamotrygina</t></is></c><c r="J1109" s="2" t="inlineStr" /><c r="K1109" s="2" t="inlineStr" /><c r="L1109" s="2" t="inlineStr" /><c r="M1109" s="2" t="inlineStr" /><c r="N1109" s="2" t="inlineStr" /><c r="O1109" s="2" t="inlineStr" /><c r="P1109" s="2" t="inlineStr"><is><t>EGZAMIN IWL 21 czerwca 2019</t></is></c><c r="Q1109" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="1110"><c r="A1110" s="2" t="inlineStr"><is><t>NADCIŚNIENIE TĘTNICZE</t></is></c><c r="B1110" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C1110" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1110" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1110" s="2" t="inlineStr"><is><t>Uwalnianie noradrenaliny z zakończeń presynaptycznych powoduje:</t></is></c><c r="F1110" s="2" t="inlineStr"><is><t>amfetamina</t></is></c><c r="G1110" s="2" t="inlineStr" /><c r="H1110" s="2" t="inlineStr" /><c r="I1110" s="2" t="inlineStr" /><c r="J1110" s="2" t="inlineStr" /><c r="K1110" s="2" t="inlineStr"><is><t>klonidyna</t></is></c><c r="L1110" s="2" t="inlineStr"><is><t>reboksetyna</t></is></c><c r="M1110" s="2" t="inlineStr"><is><t>moksonidyna</t></is></c><c r="N1110" s="2" t="inlineStr" /><c r="O1110" s="2" t="inlineStr" /><c r="P1110" s="2" t="inlineStr"><is><t>EGZAMIN IWL 21 czerwca 2019</t></is></c><c r="Q1110" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="1111"><c r="A1111" s="2" t="inlineStr"><is><t>FARMAKOKINETYKA</t></is></c><c r="B1111" s="2" t="inlineStr"><is><t>Farmakokinetyka</t></is></c><c r="C1111" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1111" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1111" s="2" t="inlineStr"><is><t>Kinetykę liniową charakteryzuje:</t></is></c><c r="F1111" s="2" t="inlineStr"><is><t>stały okres półtrwania procesu</t></is></c><c r="G1111" s="2" t="inlineStr"><is><t>stały skład metabolitów</t></is></c><c r="H1111" s="2" t="inlineStr" /><c r="I1111" s="2" t="inlineStr" /><c r="J1111" s="2" t="inlineStr" /><c r="K1111" s="2" t="inlineStr"><is><t>taka sama wielkość AUC niezależne od dawki</t></is></c><c r="L1111" s="2" t="inlineStr"><is><t>takie samo stężenie w stanie stacjonarnym niezależnie od dawki</t></is></c><c r="M1111" s="2" t="inlineStr" /><c r="N1111" s="2" t="inlineStr" /><c r="O1111" s="2" t="inlineStr" /><c r="P1111" s="2" t="inlineStr"><is><t>EGZAMIN IWL 21 czerwca 2019</t></is></c><c r="Q1111" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="1112"><c r="A1112" s="2" t="inlineStr"><is><t>LEKI PRZECIWDEPRESYJNE</t></is></c><c r="B1112" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C1112" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1112" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1112" s="2" t="inlineStr"><is><t>W leczeniu uzależnienia od nikotyny celowe może być zastosowanie:</t></is></c><c r="F1112" s="2" t="inlineStr"><is><t>warenikliny</t></is></c><c r="G1112" s="2" t="inlineStr"><is><t>cytyzyny</t></is></c><c r="H1112" s="2" t="inlineStr" /><c r="I1112" s="2" t="inlineStr" /><c r="J1112" s="2" t="inlineStr" /><c r="K1112" s="2" t="inlineStr"><is><t>akamprozatu</t></is></c><c r="L1112" s="2" t="inlineStr"><is><t>naltreksonu z bupropionem</t></is></c><c r="M1112" s="2" t="inlineStr" /><c r="N1112" s="2" t="inlineStr" /><c r="O1112" s="2" t="inlineStr" /><c r="P1112" s="2" t="inlineStr"><is><t>EGZAMIN IWL 21 czerwca 2019</t></is></c><c r="Q1112" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="1113"><c r="A1113" s="2" t="inlineStr"><is><t>LEKI PRZECIWPSYCHOTYCZNE</t></is></c><c r="B1113" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C1113" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1113" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1113" s="2" t="inlineStr"><is><t>Złośliwy zespół neuroleptyczny:</t></is></c><c r="F1113" s="2" t="inlineStr"><is><t>może wystąpić u osób przyjmujących neuroleptyki atypowe</t></is></c><c r="G1113" s="2" t="inlineStr"><is><t>może być przyczyną ilościowych i jakościowych zaburzeń świadomości</t></is></c><c r="H1113" s="2" t="inlineStr" /><c r="I1113" s="2" t="inlineStr" /><c r="J1113" s="2" t="inlineStr" /><c r="K1113" s="2" t="inlineStr"><is><t>cechuje się osłabieniem napięcia mięśniowego i gorączką</t></is></c><c r="L1113" s="2" t="inlineStr"><is><t>o dużym nasileniu może wymagać podania agonistów receptorów dopaminowych</t></is></c><c r="M1113" s="2" t="inlineStr" /><c r="N1113" s="2" t="inlineStr" /><c r="O1113" s="2" t="inlineStr" /><c r="P1113" s="2" t="inlineStr"><is><t>EGZAMIN IWL 21 czerwca 2019</t></is></c><c r="Q1113" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="1114"><c r="A1114" s="2" t="inlineStr"><is><t>UKŁAD PRZYWSPÓŁCZULNY</t></is></c><c r="B1114" s="2" t="inlineStr"><is><t>Antidotum</t></is></c><c r="C1114" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1114" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1114" s="2" t="inlineStr"><is><t>Rozszerzenie źrenic (mydriasis) może wystąpić w zatruciu:</t></is></c><c r="F1114" s="2" t="inlineStr"><is><t>Skopolaminą i atropina tez</t></is></c><c r="G1114" s="2" t="inlineStr"><is><t>amfetaminą</t></is></c><c r="H1114" s="2" t="inlineStr"><is><t>doksepiną - tlpd</t></is></c><c r="I1114" s="2" t="inlineStr" /><c r="J1114" s="2" t="inlineStr" /><c r="K1114" s="2" t="inlineStr"><is><t>tapentadolem</t></is></c><c r="L1114" s="2" t="inlineStr" /><c r="M1114" s="2" t="inlineStr" /><c r="N1114" s="2" t="inlineStr" /><c r="O1114" s="2" t="inlineStr" /><c r="P1114" s="2" t="inlineStr"><is><t>EGZAMIN IWL 21 czerwca 2019</t></is></c><c r="Q1114" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="1115"><c r="A1115" s="2" t="inlineStr"><is><t>HORMONY PŁCIOWE</t></is></c><c r="B1115" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C1115" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1115" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1115" s="2" t="inlineStr"><is><t>Finasteryd:</t></is></c><c r="F1115" s="2" t="inlineStr"><is><t>jest stosowany w leczeniu łagodnego rozrostu gruczołu krokowego</t></is></c><c r="G1115" s="2" t="inlineStr"><is><t>hamuje łysienie typu męskiego</t></is></c><c r="H1115" s="2" t="inlineStr" /><c r="I1115" s="2" t="inlineStr" /><c r="J1115" s="2" t="inlineStr" /><c r="K1115" s="2" t="inlineStr"><is><t>zwiększa wytwarzanie 5-alfa-dihydrotestosteronu – inhibitor</t></is></c><c r="L1115" s="2" t="inlineStr"><is><t>jest stosowany w leczeniu zaburzeń wzwodu</t></is></c><c r="M1115" s="2" t="inlineStr" /><c r="N1115" s="2" t="inlineStr" /><c r="O1115" s="2" t="inlineStr" /><c r="P1115" s="2" t="inlineStr"><is><t>EGZAMIN IWL 21 czerwca 2019</t></is></c><c r="Q1115" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="1116"><c r="A1116" s="2" t="inlineStr"><is><t>UKŁAD PRZYWSPÓŁCZULNY</t></is></c><c r="B1116" s="2" t="inlineStr"><is><t>Antidotum</t></is></c><c r="C1116" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1116" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1116" s="2" t="inlineStr"><is><t>Zatrucie związkami fosforoorganicznymi może wymagać zastosowania:</t></is></c><c r="F1116" s="2" t="inlineStr"><is><t>pralidoksymu</t></is></c><c r="G1116" s="2" t="inlineStr"><is><t>atropiny</t></is></c><c r="H1116" s="2" t="inlineStr" /><c r="I1116" s="2" t="inlineStr" /><c r="J1116" s="2" t="inlineStr" /><c r="K1116" s="2" t="inlineStr"><is><t>morfiny</t></is></c><c r="L1116" s="2" t="inlineStr"><is><t>diazepamu</t></is></c><c r="M1116" s="2" t="inlineStr" /><c r="N1116" s="2" t="inlineStr" /><c r="O1116" s="2" t="inlineStr" /><c r="P1116" s="2" t="inlineStr"><is><t>EGZAMIN IWL 21 czerwca 2019</t></is></c><c r="Q1116" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="1117"><c r="A1117" s="2" t="inlineStr"><is><t>LEKI PRZECIWNOWOTWOROWE</t></is></c><c r="B1117" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C1117" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1117" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1117" s="2" t="inlineStr"><is><t>Inhibitory immunologicznych punktów kontrolnych:</t></is></c><c r="F1117" s="2" t="inlineStr"><is><t>są przeciwciałami monoklonalnymi przeciw CLTA-4, PD-1 i PDL-1</t></is></c><c r="G1117" s="2" t="inlineStr"><is><t>znoszą negatywną regulację aktywności układu odpornościowego w mikrośrodowisku nowotworów</t></is></c><c r="H1117" s="2" t="inlineStr"><is><t>są skuteczne w leczeniu różnych typów nowotworów</t></is></c><c r="I1117" s="2" t="inlineStr"><is><t>indukują zjawiska autoimmunologiczne</t></is></c><c r="J1117" s="2" t="inlineStr" /><c r="K1117" s="2" t="inlineStr" /><c r="L1117" s="2" t="inlineStr" /><c r="M1117" s="2" t="inlineStr" /><c r="N1117" s="2" t="inlineStr" /><c r="O1117" s="2" t="inlineStr" /><c r="P1117" s="2" t="inlineStr"><is><t>EGZAMIN IWL 21 czerwca 2019</t></is></c><c r="Q1117" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="1118"><c r="A1118" s="2" t="inlineStr"><is><t>LEKI ROŚLINNE I SUPLEMENTY</t></is></c><c r="B1118" s="2" t="inlineStr"><is><t>Sposób podania</t></is></c><c r="C1118" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1118" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1118" s="2" t="inlineStr"><is><t>Wskaż prawdziwe stwierdzenia dotyczące suplementacji żelaza:</t></is></c><c r="F1118" s="2" t="inlineStr"><is><t>witamina C poprawia wchłanianie preparatów żelaza z przewodu pokarmowego</t></is></c><c r="G1118" s="2" t="inlineStr"><is><t>w przypadku nietolerancji doustnych preparatów żelaza może dojść do konieczności podawania żelaza dożylnie</t></is></c><c r="H1118" s="2" t="inlineStr"><is><t>suplementacja żelaza jest niezbędna w diecie wegańskiej (wykluczenie spożywania mięsa i innych produktów pochodzenia zwierzęcego)</t></is></c><c r="I1118" s="2" t="inlineStr" /><c r="J1118" s="2" t="inlineStr" /><c r="K1118" s="2" t="inlineStr"><is><t>żelazo wchłania się lepiej po posiłku</t></is></c><c r="L1118" s="2" t="inlineStr" /><c r="M1118" s="2" t="inlineStr" /><c r="N1118" s="2" t="inlineStr" /><c r="O1118" s="2" t="inlineStr" /><c r="P1118" s="2" t="inlineStr"><is><t>EGZAMIN IWL 21 czerwca 2019</t></is></c><c r="Q1118" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="1119"><c r="A1119" s="2" t="inlineStr"><is><t>UKŁAD WSPÓŁCZULNY</t></is></c><c r="B1119" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C1119" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1119" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1119" s="2" t="inlineStr"><is><t>Wskaż prawidłowe połączenie lek – mechanizm działania:</t></is></c><c r="F1119" s="2" t="inlineStr"><is><t>bupropion – hamowanie wychwytu zwrotnego noradrenaliny i dopaminy</t></is></c><c r="G1119" s="2" t="inlineStr"><is><t>akamprozat – antagonista receptora NMDA</t></is></c><c r="H1119" s="2" t="inlineStr" /><c r="I1119" s="2" t="inlineStr" /><c r="J1119" s="2" t="inlineStr" /><c r="K1119" s="2" t="inlineStr"><is><t>wareniklina – antagonizm względem receptora dopaminowego</t></is></c><c r="L1119" s="2" t="inlineStr"><is><t>disulfiram – pobudzenie receptora GABA-B</t></is></c><c r="M1119" s="2" t="inlineStr" /><c r="N1119" s="2" t="inlineStr" /><c r="O1119" s="2" t="inlineStr" /><c r="P1119" s="2" t="inlineStr"><is><t>EGZAMIN IWL 21 czerwca 2019</t></is></c><c r="Q1119" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="1120"><c r="A1120" s="2" t="inlineStr"><is><t>NADCIŚNIENIE TĘTNICZE</t></is></c><c r="B1120" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C1120" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1120" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1120" s="2" t="inlineStr"><is><t>Paradoksalny efekt leku został wykorzystany w leczeniu:</t></is></c><c r="F1120" s="2" t="inlineStr"><is><t>nefrogennej moczówki prostej hydrochlorotiazydem</t></is></c><c r="G1120" s="2" t="inlineStr" /><c r="H1120" s="2" t="inlineStr" /><c r="I1120" s="2" t="inlineStr" /><c r="J1120" s="2" t="inlineStr" /><c r="K1120" s="2" t="inlineStr"><is><t>objawowego bloku przewodzenia przedsionkowo-komorowego izoprenaliną (izoproterenolem)</t></is></c><c r="L1120" s="2" t="inlineStr"><is><t>ciężkiej hiperkalcemii furosemidem</t></is></c><c r="M1120" s="2" t="inlineStr"><is><t>hipotonii ortostatycznej midodryną</t></is></c><c r="N1120" s="2" t="inlineStr" /><c r="O1120" s="2" t="inlineStr" /><c r="P1120" s="2" t="inlineStr"><is><t>EGZAMIN IWL 21 czerwca 2019</t></is></c><c r="Q1120" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="1121"><c r="A1121" s="2" t="inlineStr"><is><t>STANY NAGŁE</t></is></c><c r="B1121" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C1121" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1121" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1121" s="2" t="inlineStr"><is><t>Wskaż prawdziwe stwierdzenie:</t></is></c><c r="F1121" s="2" t="inlineStr"><is><t>0,9% roztwór NaCl jest optymalnym płynem do pokrycia zapotrzebowania na sód i wodę przy zwykłych stratach</t></is></c><c r="G1121" s="2" t="inlineStr" /><c r="H1121" s="2" t="inlineStr" /><c r="I1121" s="2" t="inlineStr" /><c r="J1121" s="2" t="inlineStr" /><c r="K1121" s="2" t="inlineStr"><is><t>po przetoczeniu 0,9% roztworu NaCl przyrost objętości osocza odpowiada ok. 18-31% przetoczonego płynu</t></is></c><c r="L1121" s="2" t="inlineStr"><is><t>zabronione jest stosowanie hipotonicznych roztworów NaCl</t></is></c><c r="M1121" s="2" t="inlineStr"><is><t>stosowanie 0,9% roztworu NaCl zagraża znacznym przewodnieniem, w tym obrzękiem płuc</t></is></c><c r="N1121" s="2" t="inlineStr" /><c r="O1121" s="2" t="inlineStr" /><c r="P1121" s="2" t="inlineStr"><is><t>EGZAMIN IWL 21 czerwca 2019</t></is></c><c r="Q1121" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="1122"><c r="A1122" s="2" t="inlineStr"><is><t>LEKI PRZECIWHISTAMINOWE</t></is></c><c r="B1122" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C1122" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1122" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1122" s="2" t="inlineStr"><is><t>Bilastyna:</t></is></c><c r="F1122" s="2" t="inlineStr"><is><t>ma zastosowanie w leczeniu przewlekłego alergicznego nieżytu nosa</t></is></c><c r="G1122" s="2" t="inlineStr" /><c r="H1122" s="2" t="inlineStr" /><c r="I1122" s="2" t="inlineStr" /><c r="J1122" s="2" t="inlineStr" /><c r="K1122" s="2" t="inlineStr"><is><t>działa nieselektywnie na rec. H1</t></is></c><c r="L1122" s="2" t="inlineStr"><is><t>przenika w znacznym stopniu przez barierę krew- mózg</t></is></c><c r="M1122" s="2" t="inlineStr"><is><t>silnie wpływa na aktywność izoenzymów cytochromu P450, dlatego ryzyko jej interakcji z innymi lekami jest duże</t></is></c><c r="N1122" s="2" t="inlineStr" /><c r="O1122" s="2" t="inlineStr" /><c r="P1122" s="2" t="inlineStr"><is><t>EGZAMIN IWL 21 czerwca 2019</t></is></c><c r="Q1122" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="1123"><c r="A1123" s="2" t="inlineStr"><is><t>CHOROBA NIEDOKRWIENNA SERCA</t></is></c><c r="B1123" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C1123" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1123" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1123" s="2" t="inlineStr"><is><t>Kanały potasowe są aktywowane przez:</t></is></c><c r="F1123" s="2" t="inlineStr"><is><t>Nikorandil jest we wszystkich standardach choroby wieńcowej tylko nie w polsce , agonista kanałów</t></is></c><c r="G1123" s="2" t="inlineStr"><is><t>diazoksyd aktywator kanałów potasowych</t></is></c><c r="H1123" s="2" t="inlineStr" /><c r="I1123" s="2" t="inlineStr" /><c r="J1123" s="2" t="inlineStr" /><c r="K1123" s="2" t="inlineStr"><is><t>glibenklamid</t></is></c><c r="L1123" s="2" t="inlineStr"><is><t>sotalol ANTAGONISTA Sotalol Glibenklamid</t></is></c><c r="M1123" s="2" t="inlineStr" /><c r="N1123" s="2" t="inlineStr" /><c r="O1123" s="2" t="inlineStr" /><c r="P1123" s="2" t="inlineStr"><is><t>EGZAMIN IWL 21 czerwca 2019</t></is></c><c r="Q1123" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="1124"><c r="A1124" s="2" t="inlineStr"><is><t>NADCIŚNIENIE TĘTNICZE</t></is></c><c r="B1124" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C1124" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1124" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1124" s="2" t="inlineStr"><is><t>Hydralazyna: - NADCIŚNIENIE TETNICZE trochę przeszłość bo teraz się liczą moczopędne z wyboru tiazyd/tiazydopodobne – świetnie przepadane – wazodylatacyjne, a nie dlatego, że woda się wylewa tylko do dopieto po 4 tygodniach . super są antagoniści Ca , krótkodziałające są NIEDOBRE bo wachaja ciśnienie i denerwują baroreceptowy i serce szalaje bo nie wie co ma robić. AMLODYPINA JEST SUPER - mały efekt 1 przejścia, długo działająca dobre T/P LEKI BLOKUJĄCE raa Dziadowo ale trochę beta adrenolityki</t></is></c><c r="F1124" s="2" t="inlineStr"><is><t>stymuluje odruch z baroreceptorów</t></is></c><c r="G1124" s="2" t="inlineStr"><is><t>jest bezpośrednim wazodylatatorem</t></is></c><c r="H1124" s="2" t="inlineStr"><is><t>zmniejsza obciążenie następcze bo jest bezpośrednim wazodylatatorem wiec zmniejsza opór</t></is></c><c r="I1124" s="2" t="inlineStr"><is><t>może prowadzić do polekowego tocznia układowego – tylko 2 leki to powodują PROKAINAMID (arytmie ) i HYDRALAZYNA Rozkurcza naczynia na maxa Stymuluje mega nerkę</t></is></c><c r="J1124" s="2" t="inlineStr" /><c r="K1124" s="2" t="inlineStr" /><c r="L1124" s="2" t="inlineStr" /><c r="M1124" s="2" t="inlineStr" /><c r="N1124" s="2" t="inlineStr" /><c r="O1124" s="2" t="inlineStr" /><c r="P1124" s="2" t="inlineStr"><is><t>EGZAMIN IWL 21 czerwca 2019</t></is></c><c r="Q1124" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="1125"><c r="A1125" s="2" t="inlineStr"><is><t>NIEWYDOLNOŚĆ SERCA</t></is></c><c r="B1125" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C1125" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1125" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1125" s="2" t="inlineStr"><is><t>Inhibitory fosfodiesterazy typu 3:</t></is></c><c r="F1125" s="2" t="inlineStr"><is><t>wydłużają dystans marszu bez bólu u pacjentów z chromaniem przestankowym</t></is></c><c r="G1125" s="2" t="inlineStr"><is><t>mają działanie inotropowe dodatnie leki o działaniu inotropowym dodatnim, ale to ich minus bo milrinon inamrinon cilostazol ich systematyczne stosowanie działa objawowo, ale SKRACA PRZEŻYCIE . 4 LEKI DO KRÓTKIEGO PODAWANIA – tylko cilostazol ma antyagregacyjne i rozszerzające naczynia poszedł do chromania przystankowego ING PDE5 – ANGIOFOSFODIESTERAZA – NACZYNIOWE ODDZIALYWANIA. Zwiększamy cGMP</t></is></c><c r="H1125" s="2" t="inlineStr" /><c r="I1125" s="2" t="inlineStr" /><c r="J1125" s="2" t="inlineStr" /><c r="K1125" s="2" t="inlineStr"><is><t>są skuteczne w leczeniu zaburzeń erekcji</t></is></c><c r="L1125" s="2" t="inlineStr"><is><t>są stosowane długoterminowo w leczeniu niewydolności serca</t></is></c><c r="M1125" s="2" t="inlineStr" /><c r="N1125" s="2" t="inlineStr" /><c r="O1125" s="2" t="inlineStr" /><c r="P1125" s="2" t="inlineStr"><is><t>EGZAMIN IWL 21 czerwca 2019</t></is></c><c r="Q1125" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="1126"><c r="A1126" s="2" t="inlineStr"><is><t>CHOROBA NIEDOKRWIENNA SERCA</t></is></c><c r="B1126" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C1126" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1126" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1126" s="2" t="inlineStr"><is><t>Do działań niepożądanych azotanów można zaliczyć:</t></is></c><c r="F1126" s="2" t="inlineStr"><is><t>rozwój tolerancji</t></is></c><c r="G1126" s="2" t="inlineStr"><is><t>bóle głowy – klasyka dla leków rozszerzających</t></is></c><c r="H1126" s="2" t="inlineStr"><is><t>hipotensję ortostatyczną – klasyka dla leków rozszerzających Margines medycyny ale są 3 mega ważne zastosowanie • Przerywanie bólów dławicowych !</t></is></c><c r="I1126" s="2" t="inlineStr" /><c r="J1126" s="2" t="inlineStr" /><c r="K1126" s="2" t="inlineStr"><is><t>nasilenie deficytu tlenowego mięśnia sercowego w stabilnej chorobie wieńcowej – właśnie je stosujemy w tej chorobie i to jest totalnie na odwrót – zmniejszają deficyt tlenowy jak wszystkie leki, które są objawowo w bólach wieńcowych</t></is></c><c r="L1126" s="2" t="inlineStr" /><c r="M1126" s="2" t="inlineStr" /><c r="N1126" s="2" t="inlineStr" /><c r="O1126" s="2" t="inlineStr" /><c r="P1126" s="2" t="inlineStr"><is><t>EGZAMIN IWL 21 czerwca 2019</t></is></c><c r="Q1126" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="1127"><c r="A1127" s="2" t="inlineStr"><is><t>ZABURZENIA RYTMU SERCA</t></is></c><c r="B1127" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C1127" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1127" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1127" s="2" t="inlineStr"><is><t>U pacjentów z zespołem preekscytacji (Wolfa-Parkinsona-White’a, w którym występują dodatkowe patologiczne drogi przewodzenia przedsionkowo￾komorowego) w profilaktyce tachyarytmii przeciwwskazane jest stosowanie:</t></is></c><c r="F1127" s="2" t="inlineStr"><is><t>werapamilu • NAJLEPIEJ ZROBIĆ ABLACJE, PONISZCZENIE PRZEZSKURNE LECZENIE ARTYMII Zespół WPW to zespół preekscytacji, powodują artymie w tych artymiach NIE MOŻNA STOSOWAĆ ANTAGONISTÓW KANAŁÓW WAPNIOWYCH !!!! werapamilu i diltiazemu W artymiach nadkomorowych – częstoskurcz i wąskie QRS, też by był gruby błąd z ANTAGONISTAMI KANAŁÓW WAPNIOWYCH Adenozyna werapamil diltiazem – jest avrt częstoskurcz napadowy ONE SĄ WSKAZANE</t></is></c><c r="G1127" s="2" t="inlineStr" /><c r="H1127" s="2" t="inlineStr" /><c r="I1127" s="2" t="inlineStr" /><c r="J1127" s="2" t="inlineStr" /><c r="K1127" s="2" t="inlineStr"><is><t>Amiodaronu III klasa – ma cechy antagonisty wapniowego , to jest dirty drug ale można</t></is></c><c r="L1127" s="2" t="inlineStr"><is><t>sotalolu – III klasa</t></is></c><c r="M1127" s="2" t="inlineStr"><is><t>flekainidu – Ib</t></is></c><c r="N1127" s="2" t="inlineStr" /><c r="O1127" s="2" t="inlineStr" /><c r="P1127" s="2" t="inlineStr"><is><t>EGZAMIN IWL 21 czerwca 2019</t></is></c><c r="Q1127" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="1128"><c r="A1128" s="2" t="inlineStr"><is><t>CHOROBA NIEDOKRWIENNA SERCA</t></is></c><c r="B1128" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C1128" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1128" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1128" s="2" t="inlineStr"><is><t>Beta-adrenolityki w chorobie niedokrwiennej serca: - typowa choroba z deficytem</t></is></c><c r="F1128" s="2" t="inlineStr"><is><t>podnoszą próg migotania komór przez zapobieganie proarytmicznemu działaniu katecholamin taaak ! bardzo prawdziwe i dobre - PODNOSZĄ PRÓG MIGOTANIA KOMÓR bo zmniejszają wpływ amin katecholowoych BATOMOTROPOWO UJEMNIE = ANTYARTYMICZNIE</t></is></c><c r="G1128" s="2" t="inlineStr"><is><t>działają chronotropowo ujemnie, przez co zmniejszają zapotrzebowanie mięśnia sercowego na tlen – ŚWIĘTA PRAWDA – zwalnia rozrusznik przez to wolniej bije serce</t></is></c><c r="H1128" s="2" t="inlineStr"><is><t>w prewencji wtórnej po zawale mięśnia sercowego powinny być kardioselektywne, lipofilne i pozbawione wewnętrznej aktywności sympatykomimetycznej – nie koniecznie muszą być lipofilne ale ABSOLUTNIE POZBAWIONE AKTYWNOSCI WEWNETRZNEJ I KARDIOSELEKTYWNE B2 SELEKTYWNE ANTAGONISCI Niesamowite właściwości Zmniejszają zapotrzebowanie mięśnia sercowego na tlen NIE ROZKURCZAJĄ naczyń wieńcowych POPRAWIAJĄ UKRWIENIE serca nie bezpośrednio wydłużają faze rozkurczu w warstwie PODWSIERDZIOWEJ – to tylko wtedy płynie krew przez wieńcówki bo ona jest najgłębiej i jak się zaciska mięsień to sa takie cieniutkie naczynia, że zaciska je. ! DZIAŁAJĄ GŁOWNIE PRZEZ zmniejszenie tropizmów i obniżają ciśnienie 3 głowne składowe tropiznów, które pochłaniają tlen ! • Czestość • Napręzenie ściany • Akt skurczu</t></is></c><c r="I1128" s="2" t="inlineStr" /><c r="J1128" s="2" t="inlineStr" /><c r="K1128" s="2" t="inlineStr"><is><t>zmniejszają wartości ciśnienia tętniczego, co powoduje spadek przepływu przez tętnice wieńcowe – to by było niedobrze, jakbyśmy indukowali spadek przez tetnice wieńcowe, ale prawda jest, że zmniejszają wartości się ciśnienia. Ok czasem się zdarz, że jest tak małe ciśnienei, że zawał ale zwykle wieńcówka się samoreguluje</t></is></c><c r="L1128" s="2" t="inlineStr" /><c r="M1128" s="2" t="inlineStr" /><c r="N1128" s="2" t="inlineStr" /><c r="O1128" s="2" t="inlineStr" /><c r="P1128" s="2" t="inlineStr"><is><t>EGZAMIN IWL 21 czerwca 2019</t></is></c><c r="Q1128" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="1129"><c r="A1129" s="2" t="inlineStr"><is><t>ZABURZENIA RYTMU SERCA</t></is></c><c r="B1129" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C1129" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1129" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1129" s="2" t="inlineStr"><is><t>Wskaż prawdziwe stwierdzenie dotyczące digoksyny: - NIE FAJNY LEK / ZMARGILIZOWANY</t></is></c><c r="F1129" s="2" t="inlineStr"><is><t>powoduje bloki przewodzenia przedsionkowo-komorowego -chrono i dromotropowo ujemnie zwalnia przewodzenie przedsionkowo komorowe</t></is></c><c r="G1129" s="2" t="inlineStr"><is><t>jest coraz rzadziej stosowana w celu kontroli częstotliwości rytmu komór u chorych z migotaniem przedsionków - w spoczynku jest ok, ale jak pacjent się zaczyna ruszać to pojawia się niekontrolowana szybkość częstoś komór. • Lepszy wybór to antagoniści wapnia – werapamil i diltiazem lub beta adrenolityki • Mankament digoksyny u osob z migotaniem przednionków, źle wpływa na przeżycie bo on permamentnie działa inotropowo i blokuje atpaze na kardiomiocytow i neutonach. KONTROLA JEST ALE PRZEŻYCIE SIĘ SKRACA Jesteśmy w stanie go zaakceptować bo korzystnie koryguje niestabilność w układzie współczulnym i przywspółczujnym. Digoksyna modyfikuje działanie baroreceptorów tak, że lepiej znoszą spadki ciśnienia i nie odpalają mega współczulnego W małych dawakach stężonkach jest super wlasnie na promowanie przywspółczulnego a – prawdziwe odpowiedzi 1, 3 i 4 b – prawdziwe odpowiedzi 1 i 3 c – prawdziwe odpowiedzi 2 i 4 d – prawdziwa odpowiedź 4 e – wszystkie odpowiedzi prawdziwe</t></is></c><c r="H1129" s="2" t="inlineStr" /><c r="I1129" s="2" t="inlineStr" /><c r="J1129" s="2" t="inlineStr" /><c r="K1129" s="2" t="inlineStr"><is><t>hamuje układ przywspółczulny – PROMUJE PRZYWSPÓŁCZULNY</t></is></c><c r="L1129" s="2" t="inlineStr"><is><t>hiperkaliemia zwiększa toksyczność digoksyny – blokuje atpaze sodowo potasową łaczy się z nia tam gdzie łączy się potas. HIPOKALIEMIA usposabnia do toksyczności</t></is></c><c r="M1129" s="2" t="inlineStr" /><c r="N1129" s="2" t="inlineStr" /><c r="O1129" s="2" t="inlineStr" /><c r="P1129" s="2" t="inlineStr"><is><t>EGZAMIN IWL 21 czerwca 2019</t></is></c><c r="Q1129" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="1130"><c r="A1130" s="2" t="inlineStr"><is><t>ZABURZENIA RYTMU SERCA</t></is></c><c r="B1130" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C1130" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1130" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1130" s="2" t="inlineStr"><is><t>Jaki lek powoduje bradykardię zatokową i wydłużenie odstępu QTc?</t></is></c><c r="F1130" s="2" t="inlineStr"><is><t>Sotalol – wszystkie leki klasy I powodują bradykardie</t></is></c><c r="G1130" s="2" t="inlineStr"><is><t>Amiodaron – III klasa partymicznych – bradykardia Wszystkie antyartymiczne powodują bradykardie Tylko III klasa antyarytmicznych powoduje wydluzenie QT</t></is></c><c r="H1130" s="2" t="inlineStr" /><c r="I1130" s="2" t="inlineStr" /><c r="J1130" s="2" t="inlineStr" /><c r="K1130" s="2" t="inlineStr"><is><t>Lidokaina – bradykardia</t></is></c><c r="L1130" s="2" t="inlineStr"><is><t>Esmolol – wszystkie beta- adrenolityki powodują bradykardie</t></is></c><c r="M1130" s="2" t="inlineStr" /><c r="N1130" s="2" t="inlineStr" /><c r="O1130" s="2" t="inlineStr" /><c r="P1130" s="2" t="inlineStr"><is><t>EGZAMIN IWL 21 czerwca 2019</t></is></c><c r="Q1130" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="1131"><c r="A1131" s="2" t="inlineStr"><is><t>NIEWYDOLNOŚĆ SERCA</t></is></c><c r="B1131" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C1131" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1131" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1131" s="2" t="inlineStr"><is><t>Korzystny wpływ na przeżycie ma:</t></is></c><c r="F1131" s="2" t="inlineStr"><is><t>Apiksaban NOAC w napadowym migotaniu przedsionków</t></is></c><c r="G1131" s="2" t="inlineStr"><is><t>atorwastatyna w stabilnej chorobie wieńcowej</t></is></c><c r="H1131" s="2" t="inlineStr"><is><t>milrynon w przewlekłej niewydolności serca z upośledzoną frakcją wyrzutową – niepożądane jest działanie inotropowe dodatnie wiec one szkodzą. Tutaj blok RAA i beta adrenolityki POŁĄCZONE ZE SOBĄ , oferują komfort funkcjonowania źle bijącemu sercu KORZYSTNY WPŁYW NA PRZEŻYCIE ! 45 min Gks – astma Statyny – miażdżyca | atorwa – chore nerki / rosuwa – chora wątroba Blok RAA z beta adrenolitykami – Niewydolnośc serca Antagoniści dla receptora dla aldosteronu – eplerenon &gt; spironolakton – Niewydolnośc serca Klopidogrel / asa NIE SĄ TAK DOBRE</t></is></c><c r="I1131" s="2" t="inlineStr" /><c r="J1131" s="2" t="inlineStr" /><c r="K1131" s="2" t="inlineStr"><is><t>flekainid w arytmiach komorowych po zawale serca</t></is></c><c r="L1131" s="2" t="inlineStr" /><c r="M1131" s="2" t="inlineStr" /><c r="N1131" s="2" t="inlineStr" /><c r="O1131" s="2" t="inlineStr" /><c r="P1131" s="2" t="inlineStr"><is><t>EGZAMIN IWL 21 czerwca 2019</t></is></c><c r="Q1131" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="1132"><c r="A1132" s="2" t="inlineStr"><is><t>FARMAKOKINETYKA</t></is></c><c r="B1132" s="2" t="inlineStr"><is><t>Farmakokinetyka</t></is></c><c r="C1132" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1132" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1132" s="2" t="inlineStr"><is><t>Po dożylnym podaniu 600 mg leku oznaczone stężenie początkowe (C0) leku we krwi wynosi 3 mg/l, zatem prawdą jest, że:</t></is></c><c r="F1132" s="2" t="inlineStr"><is><t>objętość dystrybucji wynosi Vd = 200 l to stężenie podane podzielone przez stężenie leku we krwi</t></is></c><c r="G1132" s="2" t="inlineStr"><is><t>lek występuje we krwi, płynie zewnątrz- i wewnątrzkomórkowym – wiadomo, bo dużo leku itp. I musi się gdzieś rozchodzić</t></is></c><c r="H1132" s="2" t="inlineStr"><is><t>lek rozmieszcza się w kompartmencie głębokim – tak duże objętości dystrybucji, świadczy, że się magazunuje</t></is></c><c r="I1132" s="2" t="inlineStr" /><c r="J1132" s="2" t="inlineStr" /><c r="K1132" s="2" t="inlineStr"><is><t>lek występuje w płynie mózgowo- rdzeniowym - nie można tego stwierdzić na podstawie objętości dystrubucji i na dodatek jest tam bariera wiec trudno przewidzieć. Trzeba sprawdzić nawet przy olbrzymiej objętości dystrybucji . BADANIA RADIOIZOTOPOWE U ZWIERZĄT PODCZAS BADAŃ</t></is></c><c r="L1132" s="2" t="inlineStr" /><c r="M1132" s="2" t="inlineStr" /><c r="N1132" s="2" t="inlineStr" /><c r="O1132" s="2" t="inlineStr" /><c r="P1132" s="2" t="inlineStr"><is><t>EGZAMIN IWL 21 czerwca 2019</t></is></c><c r="Q1132" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="1133"><c r="A1133" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B1133" s="2" t="inlineStr"><is><t>Przeciwwskazania</t></is></c><c r="C1133" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1133" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1133" s="2" t="inlineStr"><is><t>Wskaż które połączenia lekowe stanowią zagrożenie życia, a zatem są bezwzględne przeciwskazane?</t></is></c><c r="F1133" s="2" t="inlineStr"><is><t>ramipryl i sakubitryl – nie wolno łączyć inh neprylizyny z inh konwertazy bo to prowadzi do MEGA HIPOTONII ! jak się odstawi ing konwertazy nawet krótkodziałającego to trzeba czekać 36h przed podaniem sakubitrylu ! A sakubitryl MUSI BYĆ podany z SARTANEM !</t></is></c><c r="G1133" s="2" t="inlineStr"><is><t>diazotan izosorbidu i wardenafil AZOTANY I ANTAGONIŚCI WAPNIA BO MEGA HIPOTONIA • ZŁE INTERAKCJE ZABIJA ! • BETA ADRENOLITYK I AGONISTA KANAŁÓW WAPNIOWYCH • Antyagregacyjne się mega łaczy to jest DAPT dual antypalatte treatment jest mega wstazana ASA</t></is></c><c r="H1133" s="2" t="inlineStr" /><c r="I1133" s="2" t="inlineStr" /><c r="J1133" s="2" t="inlineStr" /><c r="K1133" s="2" t="inlineStr"><is><t>kwas acetylosalicylowy i tykagrelor ASA + P2Y12 koniecznie łączymy !</t></is></c><c r="L1133" s="2" t="inlineStr"><is><t>dobutamina i noradrenalina – doskonałe połączenie nawzajem się uzupełniają jak pacjentowi pada kardiogennie i ma ciśnienie niskie skurczowe poniżej 100 to trzeba wspomóc serce dobutaminą która jest mega lepsze niż dopamina, ona dodatkowo rozkurcza naczynia płucne. DOBUTAMINA LEPSZA OD DOPAMINY, ale ciśnienie jest przeszkoda bo ona rozkurcza naczynia bo działa na rec B2, to może zrobić kwas wiec jest potrzebna NORADRENALINA LEPSZA OD ADRENALINY ! • ANGIO – adrenalina i noradrenalina • KARDIO – dobutamina i dopamina</t></is></c><c r="M1133" s="2" t="inlineStr" /><c r="N1133" s="2" t="inlineStr" /><c r="O1133" s="2" t="inlineStr" /><c r="P1133" s="2" t="inlineStr"><is><t>EGZAMIN IWL 21 czerwca 2019</t></is></c><c r="Q1133" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="1134"><c r="A1134" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B1134" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C1134" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1134" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1134" s="2" t="inlineStr"><is><t>Oktenidyna: - Środek odkażający</t></is></c><c r="F1134" s="2" t="inlineStr"><is><t>działa bakteriobójczo w stosunku do MRSA – nadaje się do warunków szpitalnych</t></is></c><c r="G1134" s="2" t="inlineStr"><is><t>może być stosowana na błony śluzowe – jasne, że mogła Skóra nie uszkodzona ! – alkohole 70% Skóra uszkodzona – związki nie działające probólowo i nie zaburzają gojenia się rany ( czyli nie dajemy cytotoksycznych ) nie mogą mieć systemowych działań, bo z rany się wchłoną . MAŁY WYBÓR NA RANE Kiedyś do 09.19r był o Jodopowidon – nowoczesny preparat jodowy, ale zabarwiał na żółto wiec, źle oceniało się rane</t></is></c><c r="H1134" s="2" t="inlineStr" /><c r="I1134" s="2" t="inlineStr" /><c r="J1134" s="2" t="inlineStr" /><c r="K1134" s="2" t="inlineStr"><is><t>nie nadaje się do stosowania u dzieci poniżej 3 roku życia – można</t></is></c><c r="L1134" s="2" t="inlineStr"><is><t>powoduje zmianę zabarwienia tkanek – nie bo tylko związki jodu</t></is></c><c r="M1134" s="2" t="inlineStr" /><c r="N1134" s="2" t="inlineStr" /><c r="O1134" s="2" t="inlineStr" /><c r="P1134" s="2" t="inlineStr"><is><t>EGZAMIN IWL 21 czerwca 2019</t></is></c><c r="Q1134" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="1135"><c r="A1135" s="2" t="inlineStr"><is><t>ZABURZENIA RYTMU SERCA</t></is></c><c r="B1135" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C1135" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1135" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1135" s="2" t="inlineStr"><is><t>Bezwzględnym przeciwwskazaniem do podania beta-adrenolityków jest:</t></is></c><c r="F1135" s="2" t="inlineStr"><is><t>objawowa hipotensja Na maksa przeciwskazania - sytuacja z astmą jest do wyjaśnienia -nebiwolol hybryda z rozkurczającym oskrzela wazodylatacyjny -BRADYKARDIA OBJAWOWA -CHOROBA RAYNO – w żadnej naczynioskurczowej, np. w chorobie wieńcowej zależnej od skurczu! - BLOK PRZEWODZENIA II STOPNIA – typu Mobitz Jeżeli pacjent ma stymulator to może dostawac nawet z blokami przewodzenia i bradykardią</t></is></c><c r="G1135" s="2" t="inlineStr" /><c r="H1135" s="2" t="inlineStr" /><c r="I1135" s="2" t="inlineStr" /><c r="J1135" s="2" t="inlineStr" /><c r="K1135" s="2" t="inlineStr"><is><t>migotanie przedsionków z szybką czynnością komór – to wskazanie</t></is></c><c r="L1135" s="2" t="inlineStr"><is><t>przewlekła obturacyjna choroba płucna – to absolutnie nie jest przeciwskazanie</t></is></c><c r="M1135" s="2" t="inlineStr"><is><t>nadczynność tarczycy – leczymy nimi</t></is></c><c r="N1135" s="2" t="inlineStr" /><c r="O1135" s="2" t="inlineStr" /><c r="P1135" s="2" t="inlineStr"><is><t>EGZAMIN IWL 21 czerwca 2019</t></is></c><c r="Q1135" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="1136"><c r="A1136" s="2" t="inlineStr"><is><t>UKŁAD WSPÓŁCZULNY</t></is></c><c r="B1136" s="2" t="inlineStr"><is><t>Antidotum</t></is></c><c r="C1136" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1136" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1136" s="2" t="inlineStr"><is><t>Wskaż prawdziwe zestawienie lek – efekt działania:</t></is></c><c r="F1136" s="2" t="inlineStr"><is><t>propranolol - upośledzenie konwersji obwodowej lewotyroksyny</t></is></c><c r="G1136" s="2" t="inlineStr"><is><t>celiprolol – możliwość maskowania objawów hipoglikemii</t></is></c><c r="H1136" s="2" t="inlineStr"><is><t>metoprolol – możliwość zmniejszenia terapeutycznego działania adrenaliny Przedawkowanie beta adrenolityków – podajemy glukagon !</t></is></c><c r="I1136" s="2" t="inlineStr" /><c r="J1136" s="2" t="inlineStr" /><c r="K1136" s="2" t="inlineStr"><is><t>nebiwolol - zmniejszenie uwalniania endogennego tlenku azotu</t></is></c><c r="L1136" s="2" t="inlineStr" /><c r="M1136" s="2" t="inlineStr" /><c r="N1136" s="2" t="inlineStr" /><c r="O1136" s="2" t="inlineStr" /><c r="P1136" s="2" t="inlineStr"><is><t>EGZAMIN IWL 21 czerwca 2019</t></is></c><c r="Q1136" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="1137"><c r="A1137" s="2" t="inlineStr"><is><t>BÓLE GŁOWY</t></is></c><c r="B1137" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C1137" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1137" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1137" s="2" t="inlineStr"><is><t>W leczeniu migrenowych bólów głowy:</t></is></c><c r="F1137" s="2" t="inlineStr"><is><t>sumatryptan po podaniu podskórnym zaczyna działać po 10 minutach</t></is></c><c r="G1137" s="2" t="inlineStr"><is><t>w profilaktyce migreny można zastosować kwas walproinowy</t></is></c><c r="H1137" s="2" t="inlineStr"><is><t>naratryptan działa wolniej od sumatryptanu, ale jego zastosowanie związane jest z mniejszym ryzykiem nawrotu bólu</t></is></c><c r="I1137" s="2" t="inlineStr" /><c r="J1137" s="2" t="inlineStr" /><c r="K1137" s="2" t="inlineStr"><is><t>zwiększone ryzyko wystąpienia bólów głowy z nadużywania leków jest związane z przyjmowaniem tryptanów częściej niż 3 razy w miesiącu</t></is></c><c r="L1137" s="2" t="inlineStr" /><c r="M1137" s="2" t="inlineStr" /><c r="N1137" s="2" t="inlineStr" /><c r="O1137" s="2" t="inlineStr" /><c r="P1137" s="2" t="inlineStr"><is><t>EGZAMIN IWL 21 czerwca 2019</t></is></c><c r="Q1137" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="1138"><c r="A1138" s="2" t="inlineStr"><is><t>NADCIŚNIENIE TĘTNICZE</t></is></c><c r="B1138" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C1138" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1138" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1138" s="2" t="inlineStr"><is><t>Wskaż prawdziwe zestawienie lek – wskazanie: - alfa adrenolityki</t></is></c><c r="F1138" s="2" t="inlineStr"><is><t>urapidyl – przełom nadciśnieniowy</t></is></c><c r="G1138" s="2" t="inlineStr"><is><t>doksazosyna – rozrost gruczołu krokowego</t></is></c><c r="H1138" s="2" t="inlineStr" /><c r="I1138" s="2" t="inlineStr" /><c r="J1138" s="2" t="inlineStr" /><c r="K1138" s="2" t="inlineStr"><is><t>tamsulozyna – łagodne nadciśnienie tętnicze – kłamsto i oszustro jest uroselektywna i idealna do rozrostu gruczołu krokowego – mieśnie wypieracza pęcherza moczowego zmniejsza problemy z mikcją</t></is></c><c r="L1138" s="2" t="inlineStr"><is><t>alfuzosyna – naglące nietrzymanie moczu</t></is></c><c r="M1138" s="2" t="inlineStr" /><c r="N1138" s="2" t="inlineStr" /><c r="O1138" s="2" t="inlineStr" /><c r="P1138" s="2" t="inlineStr"><is><t>EGZAMIN IWL 21 czerwca 2019</t></is></c><c r="Q1138" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="1139"><c r="A1139" s="2" t="inlineStr"><is><t>LEKI PRZECIWWIRUSOWE</t></is></c><c r="B1139" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C1139" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1139" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1139" s="2" t="inlineStr"><is><t>Wskaż prawdziwe stwierdzenia dotyczące inhibitorów konwertazy angiotensyny:</t></is></c><c r="F1139" s="2" t="inlineStr"><is><t>mogą spowodować ostrą niewydolność nerek ze względu na zaburzenie filtracji kłębuszkowej</t></is></c><c r="G1139" s="2" t="inlineStr"><is><t>nie powinny być stosowane jeśli u pacjenta rozpoznano obrzęk naczyniopochodny</t></is></c><c r="H1139" s="2" t="inlineStr"><is><t>wykazują działanie nefroprotekcyjne poprzez zmniejszenie ciśnienia w kłębuszkach nerkowych NIE ODSTAWIAMY ICH W COVID !</t></is></c><c r="I1139" s="2" t="inlineStr" /><c r="J1139" s="2" t="inlineStr" /><c r="K1139" s="2" t="inlineStr"><is><t>w razie wywołania kaszlu powinny być łączone z dekstrometorfanem</t></is></c><c r="L1139" s="2" t="inlineStr" /><c r="M1139" s="2" t="inlineStr" /><c r="N1139" s="2" t="inlineStr" /><c r="O1139" s="2" t="inlineStr" /><c r="P1139" s="2" t="inlineStr"><is><t>EGZAMIN IWL 21 czerwca 2019</t></is></c><c r="Q1139" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="1140"><c r="A1140" s="2" t="inlineStr"><is><t>GLIKOKORTYKOSTEROIDY</t></is></c><c r="B1140" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C1140" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1140" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1140" s="2" t="inlineStr"><is><t>Glikokortykosteroidy o długim czasie działania to:</t></is></c><c r="F1140" s="2" t="inlineStr"><is><t>betametazon</t></is></c><c r="G1140" s="2" t="inlineStr"><is><t>deksametazon</t></is></c><c r="H1140" s="2" t="inlineStr" /><c r="I1140" s="2" t="inlineStr" /><c r="J1140" s="2" t="inlineStr" /><c r="K1140" s="2" t="inlineStr"><is><t>hydrokortyzon</t></is></c><c r="L1140" s="2" t="inlineStr"><is><t>prednizon</t></is></c><c r="M1140" s="2" t="inlineStr" /><c r="N1140" s="2" t="inlineStr" /><c r="O1140" s="2" t="inlineStr" /><c r="P1140" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1140" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="1141"><c r="A1141" s="2" t="inlineStr"><is><t>LEKI PRZECIWDEPRESYJNE</t></is></c><c r="B1141" s="2" t="inlineStr"><is><t>Antidotum</t></is></c><c r="C1141" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1141" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1141" s="2" t="inlineStr"><is><t>Rozszerzenie źrenic, suchość w ustach, osłabienie lub porażenie perystaltyki jelit obserwowane jest w przebiegu zatrucia:</t></is></c><c r="F1141" s="2" t="inlineStr"><is><t>imipraminą</t></is></c><c r="G1141" s="2" t="inlineStr" /><c r="H1141" s="2" t="inlineStr" /><c r="I1141" s="2" t="inlineStr" /><c r="J1141" s="2" t="inlineStr" /><c r="K1141" s="2" t="inlineStr"><is><t>kokainą</t></is></c><c r="L1141" s="2" t="inlineStr"><is><t>escitalopramem</t></is></c><c r="M1141" s="2" t="inlineStr"><is><t>zolpidemem</t></is></c><c r="N1141" s="2" t="inlineStr" /><c r="O1141" s="2" t="inlineStr" /><c r="P1141" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1141" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="1142"><c r="A1142" s="2" t="inlineStr"><is><t>LEKI IMMUNOSUPRESYJNE</t></is></c><c r="B1142" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C1142" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1142" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1142" s="2" t="inlineStr"><is><t>Wskaż prawidłowe połączenie lek-mechanizm działania immunosupresyjnego:</t></is></c><c r="F1142" s="2" t="inlineStr"><is><t>leflunomid – hamuje syntezę pirymidyny</t></is></c><c r="G1142" s="2" t="inlineStr"><is><t>mykofenolan mofetylu – hamuje syntezę puryn de novo</t></is></c><c r="H1142" s="2" t="inlineStr" /><c r="I1142" s="2" t="inlineStr" /><c r="J1142" s="2" t="inlineStr" /><c r="K1142" s="2" t="inlineStr"><is><t>cyklosporyna – hamuje kinazę serynowo-treoninową (mTOR)</t></is></c><c r="L1142" s="2" t="inlineStr"><is><t>sirolimus – tworzy kompleks z cyklofiliną i hamuje kalcyneurynę</t></is></c><c r="M1142" s="2" t="inlineStr" /><c r="N1142" s="2" t="inlineStr" /><c r="O1142" s="2" t="inlineStr" /><c r="P1142" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1142" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="1143"><c r="A1143" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B1143" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C1143" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1143" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1143" s="2" t="inlineStr"><is><t>Stosowanie których leków jest związane z ryzykiem wzrostu stężenia kwasu moczowego w surowicy:</t></is></c><c r="F1143" s="2" t="inlineStr"><is><t>doksorubicyny</t></is></c><c r="G1143" s="2" t="inlineStr"><is><t>furosemidu</t></is></c><c r="H1143" s="2" t="inlineStr"><is><t>etambutolu</t></is></c><c r="I1143" s="2" t="inlineStr" /><c r="J1143" s="2" t="inlineStr" /><c r="K1143" s="2" t="inlineStr"><is><t>losartanu</t></is></c><c r="L1143" s="2" t="inlineStr"><is><t>W leczeniu zależności nikotynowej wskazane są:</t></is></c><c r="M1143" s="2" t="inlineStr" /><c r="N1143" s="2" t="inlineStr" /><c r="O1143" s="2" t="inlineStr" /><c r="P1143" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1143" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="1144"><c r="A1144" s="2" t="inlineStr"><is><t>CHOROBA PARKINSONA</t></is></c><c r="B1144" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C1144" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1144" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1144" s="2" t="inlineStr"><is><t>Złośliwy zespół neuroleptyczny:</t></is></c><c r="F1144" s="2" t="inlineStr"><is><t>w leczeniu stosuje się bromokryptynę</t></is></c><c r="G1144" s="2" t="inlineStr" /><c r="H1144" s="2" t="inlineStr" /><c r="I1144" s="2" t="inlineStr" /><c r="J1144" s="2" t="inlineStr" /><c r="K1144" s="2" t="inlineStr"><is><t>występuje tylko przy stosowaniu klasycznych leków przeciwpsychotycznych</t></is></c><c r="L1144" s="2" t="inlineStr"><is><t>charakteryzuje się występowaniem hipotermii</t></is></c><c r="M1144" s="2" t="inlineStr"><is><t>nie wymaga odstawiania stosowanych leków przeciwpsychotycznych</t></is></c><c r="N1144" s="2" t="inlineStr" /><c r="O1144" s="2" t="inlineStr" /><c r="P1144" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1144" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="1145"><c r="A1145" s="2" t="inlineStr"><is><t>LEKI PRZECIWPSYCHOTYCZNE</t></is></c><c r="B1145" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C1145" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1145" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1145" s="2" t="inlineStr"><is><t>Olanzapina:</t></is></c><c r="F1145" s="2" t="inlineStr"><is><t>powoduje przyrost masy ciała</t></is></c><c r="G1145" s="2" t="inlineStr"><is><t>może być stosowana jako lek stabilizujący nastrój</t></is></c><c r="H1145" s="2" t="inlineStr"><is><t>ma silne działanie hipotensyjne a – prawidłowe 1, 3 i 4 b – prawidłowe 1 i 3 c – prawidłowe 2 i 4 d – prawidłowa 4 e – wszystkie prawidłowe</t></is></c><c r="I1145" s="2" t="inlineStr" /><c r="J1145" s="2" t="inlineStr" /><c r="K1145" s="2" t="inlineStr"><is><t>równie często jak klasyczne neuroleptyki powoduje zaburzenia układu pozapiramidowego</t></is></c><c r="L1145" s="2" t="inlineStr" /><c r="M1145" s="2" t="inlineStr" /><c r="N1145" s="2" t="inlineStr" /><c r="O1145" s="2" t="inlineStr" /><c r="P1145" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1145" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="1146"><c r="A1146" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B1146" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C1146" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1146" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1146" s="2" t="inlineStr"><is><t>Preparaty zawierające pankreatynę stosuje się w:</t></is></c><c r="F1146" s="2" t="inlineStr"><is><t>przewlekłym zapaleniu trzustki</t></is></c><c r="G1146" s="2" t="inlineStr"><is><t>leczeniu mukowiscydozy z zajęciem trzustki</t></is></c><c r="H1146" s="2" t="inlineStr"><is><t>po resekcji trzustki</t></is></c><c r="I1146" s="2" t="inlineStr" /><c r="J1146" s="2" t="inlineStr" /><c r="K1146" s="2" t="inlineStr"><is><t>leczeniu otyłości skojarzonej z insulinoopornością</t></is></c><c r="L1146" s="2" t="inlineStr" /><c r="M1146" s="2" t="inlineStr" /><c r="N1146" s="2" t="inlineStr" /><c r="O1146" s="2" t="inlineStr" /><c r="P1146" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1146" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="1147"><c r="A1147" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B1147" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C1147" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1147" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1147" s="2" t="inlineStr"><is><t>Leczenie objawowe w ostrej biegunce może obejmować:</t></is></c><c r="F1147" s="2" t="inlineStr"><is><t>dietę kleikową</t></is></c><c r="G1147" s="2" t="inlineStr"><is><t>nawodnienie doustne z zastosowaniem doustnych preparatów nawadniających</t></is></c><c r="H1147" s="2" t="inlineStr"><is><t>nawodnienie dożylne 0,9% NaCl</t></is></c><c r="I1147" s="2" t="inlineStr" /><c r="J1147" s="2" t="inlineStr" /><c r="K1147" s="2" t="inlineStr"><is><t>stosowanie leków hamujących perystaltykę jelit</t></is></c><c r="L1147" s="2" t="inlineStr" /><c r="M1147" s="2" t="inlineStr" /><c r="N1147" s="2" t="inlineStr" /><c r="O1147" s="2" t="inlineStr" /><c r="P1147" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1147" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="1148"><c r="A1148" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B1148" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C1148" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1148" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1148" s="2" t="inlineStr"><is><t>Papaweryna:</t></is></c><c r="F1148" s="2" t="inlineStr"><is><t>podana dożylnie może powodować spadek ciśnienia krwi</t></is></c><c r="G1148" s="2" t="inlineStr"><is><t>podana dożylnie może powodować zaburzenia rytmu serca</t></is></c><c r="H1148" s="2" t="inlineStr"><is><t>powoduje rozkurcz mięśniówki gładkiej przewodu pokarmowego</t></is></c><c r="I1148" s="2" t="inlineStr"><is><t>powoduje rozkurcz mięśniówki gładkiej dróg żółciowych</t></is></c><c r="J1148" s="2" t="inlineStr" /><c r="K1148" s="2" t="inlineStr" /><c r="L1148" s="2" t="inlineStr" /><c r="M1148" s="2" t="inlineStr" /><c r="N1148" s="2" t="inlineStr" /><c r="O1148" s="2" t="inlineStr" /><c r="P1148" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1148" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="1149"><c r="A1149" s="2" t="inlineStr"><is><t>UKŁAD PRZYWSPÓŁCZULNY</t></is></c><c r="B1149" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C1149" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1149" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1149" s="2" t="inlineStr"><is><t>Spazmolitykiem bezpośrednim jest:</t></is></c><c r="F1149" s="2" t="inlineStr"><is><t>drotaweryna</t></is></c><c r="G1149" s="2" t="inlineStr"><is><t>alweryna</t></is></c><c r="H1149" s="2" t="inlineStr" /><c r="I1149" s="2" t="inlineStr" /><c r="J1149" s="2" t="inlineStr" /><c r="K1149" s="2" t="inlineStr"><is><t>solifenacyna</t></is></c><c r="L1149" s="2" t="inlineStr"><is><t>metoklopramid</t></is></c><c r="M1149" s="2" t="inlineStr" /><c r="N1149" s="2" t="inlineStr" /><c r="O1149" s="2" t="inlineStr" /><c r="P1149" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1149" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="1150"><c r="A1150" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B1150" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C1150" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1150" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1150" s="2" t="inlineStr"><is><t>W leczeniu rzekomobłoniastego zapalenia jelita grubego celowe jest zastosowanie:</t></is></c><c r="F1150" s="2" t="inlineStr"><is><t>metronidazolu</t></is></c><c r="G1150" s="2" t="inlineStr"><is><t>wankomycyny</t></is></c><c r="H1150" s="2" t="inlineStr" /><c r="I1150" s="2" t="inlineStr" /><c r="J1150" s="2" t="inlineStr" /><c r="K1150" s="2" t="inlineStr"><is><t>erytromycyny</t></is></c><c r="L1150" s="2" t="inlineStr"><is><t>Sacharomyces boulardi</t></is></c><c r="M1150" s="2" t="inlineStr" /><c r="N1150" s="2" t="inlineStr" /><c r="O1150" s="2" t="inlineStr" /><c r="P1150" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1150" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="1151"><c r="A1151" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B1151" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C1151" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1151" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1151" s="2" t="inlineStr"><is><t>Omeprazol:</t></is></c><c r="F1151" s="2" t="inlineStr"><is><t>hamuje podstawowe i stymulowane posiłkiem wydzielanie kwasu solnego</t></is></c><c r="G1151" s="2" t="inlineStr"><is><t>przewlekle stosowany może powodować niedobór magnezu</t></is></c><c r="H1151" s="2" t="inlineStr" /><c r="I1151" s="2" t="inlineStr" /><c r="J1151" s="2" t="inlineStr" /><c r="K1151" s="2" t="inlineStr"><is><t>jest równie skuteczny jak ranitydyna w leczeniu wrzodu żołądka</t></is></c><c r="L1151" s="2" t="inlineStr"><is><t>jest selektywnym i odwracalnym inhibitorem pompy protonowej</t></is></c><c r="M1151" s="2" t="inlineStr" /><c r="N1151" s="2" t="inlineStr" /><c r="O1151" s="2" t="inlineStr" /><c r="P1151" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1151" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="1152"><c r="A1152" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B1152" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C1152" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1152" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1152" s="2" t="inlineStr"><is><t>W leczeniu eradykacyjnym Helicobacter pylori obowiązują schematy:</t></is></c><c r="F1152" s="2" t="inlineStr"><is><t>omeprazol, amoksycylina, metronidazol</t></is></c><c r="G1152" s="2" t="inlineStr"><is><t>pantoprazol, metronidazol, amoksycylina, tetracyklina</t></is></c><c r="H1152" s="2" t="inlineStr" /><c r="I1152" s="2" t="inlineStr" /><c r="J1152" s="2" t="inlineStr" /><c r="K1152" s="2" t="inlineStr"><is><t>lanzoprazol, ampicylina, wankomycyna</t></is></c><c r="L1152" s="2" t="inlineStr"><is><t>omeprazol, amoksycylina, klindamycyna a – prawidłowe 1, 3 i 4 b – prawidłowe 1 i 3 c – prawidłowe 2 i 4 d – prawidłowa 4 e – wszystkie prawidłowe</t></is></c><c r="M1152" s="2" t="inlineStr" /><c r="N1152" s="2" t="inlineStr" /><c r="O1152" s="2" t="inlineStr" /><c r="P1152" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1152" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="1153"><c r="A1153" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B1153" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C1153" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1153" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1153" s="2" t="inlineStr"><is><t>Mizoprostol:</t></is></c><c r="F1153" s="2" t="inlineStr"><is><t>przyspiesza regenerację błony śluzowej żołądka po zastosowaniu niesteroidowych leków przeciwzapalnych</t></is></c><c r="G1153" s="2" t="inlineStr"><is><t>jest przeciwwskazany u kobiet w ciąży z powodu ryzyka poronienia</t></is></c><c r="H1153" s="2" t="inlineStr"><is><t>powoduje biegunkę</t></is></c><c r="I1153" s="2" t="inlineStr" /><c r="J1153" s="2" t="inlineStr" /><c r="K1153" s="2" t="inlineStr"><is><t>powoduje ginekomastię</t></is></c><c r="L1153" s="2" t="inlineStr" /><c r="M1153" s="2" t="inlineStr" /><c r="N1153" s="2" t="inlineStr" /><c r="O1153" s="2" t="inlineStr" /><c r="P1153" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1153" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="1154"><c r="A1154" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B1154" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C1154" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1154" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1154" s="2" t="inlineStr"><is><t>Syntezę ściany komórkowej hamuje:</t></is></c><c r="F1154" s="2" t="inlineStr"><is><t>fosfomycyna</t></is></c><c r="G1154" s="2" t="inlineStr"><is><t>aztreonam</t></is></c><c r="H1154" s="2" t="inlineStr"><is><t>aksetyl cefuroksymu</t></is></c><c r="I1154" s="2" t="inlineStr"><is><t>wankomycyna</t></is></c><c r="J1154" s="2" t="inlineStr" /><c r="K1154" s="2" t="inlineStr" /><c r="L1154" s="2" t="inlineStr" /><c r="M1154" s="2" t="inlineStr" /><c r="N1154" s="2" t="inlineStr" /><c r="O1154" s="2" t="inlineStr" /><c r="P1154" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1154" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="1155"><c r="A1155" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B1155" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C1155" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1155" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1155" s="2" t="inlineStr"><is><t>Tetracykliny:</t></is></c><c r="F1155" s="2" t="inlineStr"><is><t>hamują syntezę białek</t></is></c><c r="G1155" s="2" t="inlineStr"><is><t>powodują przebarwienia i deformacje szkliwa</t></is></c><c r="H1155" s="2" t="inlineStr"><is><t>osłabiają działanie doustnych środków antykoncepcyjnych</t></is></c><c r="I1155" s="2" t="inlineStr" /><c r="J1155" s="2" t="inlineStr" /><c r="K1155" s="2" t="inlineStr"><is><t>powodują zespół czerwonego karku po szybkim podaniu i.v</t></is></c><c r="L1155" s="2" t="inlineStr" /><c r="M1155" s="2" t="inlineStr" /><c r="N1155" s="2" t="inlineStr" /><c r="O1155" s="2" t="inlineStr" /><c r="P1155" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1155" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="1156"><c r="A1156" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B1156" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C1156" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1156" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1156" s="2" t="inlineStr"><is><t>Erytromycyna:</t></is></c><c r="F1156" s="2" t="inlineStr"><is><t>jest metabolizowana z udziałem enzymów cytochromu P-450</t></is></c><c r="G1156" s="2" t="inlineStr"><is><t>bezpośrednio stymuluje motorykę przewodu pokarmowego</t></is></c><c r="H1156" s="2" t="inlineStr" /><c r="I1156" s="2" t="inlineStr" /><c r="J1156" s="2" t="inlineStr" /><c r="K1156" s="2" t="inlineStr"><is><t>jest oporna na działanie soku żołądkowego</t></is></c><c r="L1156" s="2" t="inlineStr"><is><t>osiąga wysokie stężenie wewnątrzkomórkowe</t></is></c><c r="M1156" s="2" t="inlineStr" /><c r="N1156" s="2" t="inlineStr" /><c r="O1156" s="2" t="inlineStr" /><c r="P1156" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1156" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="1157"><c r="A1157" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B1157" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C1157" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1157" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1157" s="2" t="inlineStr"><is><t>Klindamycyna:</t></is></c><c r="F1157" s="2" t="inlineStr"><is><t>może indukować powstawanie oporności krzyżowej z makrolidami</t></is></c><c r="G1157" s="2" t="inlineStr"><is><t>jest aktywna w stosunku do beztlenowców</t></is></c><c r="H1157" s="2" t="inlineStr"><is><t>jest stosowana miejscowo w leczeniu trądziku</t></is></c><c r="I1157" s="2" t="inlineStr"><is><t>ma silne działanie selekcjonujące Clostridium difficile</t></is></c><c r="J1157" s="2" t="inlineStr" /><c r="K1157" s="2" t="inlineStr" /><c r="L1157" s="2" t="inlineStr" /><c r="M1157" s="2" t="inlineStr" /><c r="N1157" s="2" t="inlineStr" /><c r="O1157" s="2" t="inlineStr" /><c r="P1157" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1157" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="1158"><c r="A1158" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B1158" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C1158" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1158" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1158" s="2" t="inlineStr"><is><t>Azytromycyna wykazuje aktywność w stosunku do:</t></is></c><c r="F1158" s="2" t="inlineStr"><is><t>Mycoplasma pneumoniae</t></is></c><c r="G1158" s="2" t="inlineStr"><is><t>Haemophilusinfluenzae</t></is></c><c r="H1158" s="2" t="inlineStr"><is><t>Chlamydia pneumophila</t></is></c><c r="I1158" s="2" t="inlineStr"><is><t>Borrelia burgdorferi</t></is></c><c r="J1158" s="2" t="inlineStr" /><c r="K1158" s="2" t="inlineStr" /><c r="L1158" s="2" t="inlineStr" /><c r="M1158" s="2" t="inlineStr" /><c r="N1158" s="2" t="inlineStr" /><c r="O1158" s="2" t="inlineStr" /><c r="P1158" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1158" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="1159"><c r="A1159" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B1159" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C1159" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1159" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1159" s="2" t="inlineStr"><is><t>W leczeniu zakażeń wywołanych szczepami Staphylococcus aureus opornymi na metycylinę (MRSA ) celowe jest zastosowanie:</t></is></c><c r="F1159" s="2" t="inlineStr"><is><t>wankomycyny</t></is></c><c r="G1159" s="2" t="inlineStr"><is><t>linezolidu</t></is></c><c r="H1159" s="2" t="inlineStr" /><c r="I1159" s="2" t="inlineStr" /><c r="J1159" s="2" t="inlineStr" /><c r="K1159" s="2" t="inlineStr"><is><t>cyprofloksacyny</t></is></c><c r="L1159" s="2" t="inlineStr"><is><t>imipenemu a – prawidłowe 1, 3 i 4 b – prawidłowe 1 i 3 c – prawidłowe 2 i 4 d – prawidłowa 4 e – wszystkie prawidłowe</t></is></c><c r="M1159" s="2" t="inlineStr" /><c r="N1159" s="2" t="inlineStr" /><c r="O1159" s="2" t="inlineStr" /><c r="P1159" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1159" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="1160"><c r="A1160" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B1160" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C1160" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1160" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1160" s="2" t="inlineStr"><is><t>Lewofloksacyna jest skuteczna w zakażeniach o etiologii:</t></is></c><c r="F1160" s="2" t="inlineStr"><is><t>Streptococcus pneumoniae</t></is></c><c r="G1160" s="2" t="inlineStr"><is><t>Legionella pneumophila</t></is></c><c r="H1160" s="2" t="inlineStr" /><c r="I1160" s="2" t="inlineStr" /><c r="J1160" s="2" t="inlineStr" /><c r="K1160" s="2" t="inlineStr"><is><t>Bacteroides fragilis</t></is></c><c r="L1160" s="2" t="inlineStr"><is><t>Clostridium difficile</t></is></c><c r="M1160" s="2" t="inlineStr" /><c r="N1160" s="2" t="inlineStr" /><c r="O1160" s="2" t="inlineStr" /><c r="P1160" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1160" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="1161"><c r="A1161" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B1161" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C1161" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1161" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1161" s="2" t="inlineStr"><is><t>W leczeniu zapalenia opon mózgowo-rdzeniowych celowe jest zastosowanie:</t></is></c><c r="F1161" s="2" t="inlineStr"><is><t>ceftriaksonu</t></is></c><c r="G1161" s="2" t="inlineStr"><is><t>cefotaksymu</t></is></c><c r="H1161" s="2" t="inlineStr" /><c r="I1161" s="2" t="inlineStr" /><c r="J1161" s="2" t="inlineStr" /><c r="K1161" s="2" t="inlineStr"><is><t>cefoperazonu</t></is></c><c r="L1161" s="2" t="inlineStr"><is><t>cefazoliny</t></is></c><c r="M1161" s="2" t="inlineStr" /><c r="N1161" s="2" t="inlineStr" /><c r="O1161" s="2" t="inlineStr" /><c r="P1161" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1161" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="1162"><c r="A1162" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B1162" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C1162" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1162" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1162" s="2" t="inlineStr"><is><t>Mupirocyna:</t></is></c><c r="F1162" s="2" t="inlineStr"><is><t>jest stosowana w postaci maści</t></is></c><c r="G1162" s="2" t="inlineStr"><is><t>hamuje syntetazę izoleucynową t-RNA</t></is></c><c r="H1162" s="2" t="inlineStr"><is><t>nie wykazuje oporności krzyżowej z innymi dostępnymi antybiotykami</t></is></c><c r="I1162" s="2" t="inlineStr"><is><t>jest stosowana w liszaju wywołanym gronkowcem złocistym</t></is></c><c r="J1162" s="2" t="inlineStr" /><c r="K1162" s="2" t="inlineStr" /><c r="L1162" s="2" t="inlineStr" /><c r="M1162" s="2" t="inlineStr" /><c r="N1162" s="2" t="inlineStr" /><c r="O1162" s="2" t="inlineStr" /><c r="P1162" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1162" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="1163"><c r="A1163" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B1163" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C1163" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1163" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1163" s="2" t="inlineStr"><is><t>Fenoksymetylpenicylina jest wskazana w leczeniu:</t></is></c><c r="F1163" s="2" t="inlineStr"><is><t>anginy paciorkowcowej</t></is></c><c r="G1163" s="2" t="inlineStr" /><c r="H1163" s="2" t="inlineStr" /><c r="I1163" s="2" t="inlineStr" /><c r="J1163" s="2" t="inlineStr" /><c r="K1163" s="2" t="inlineStr"><is><t>przewlekłego zapalenia zatok</t></is></c><c r="L1163" s="2" t="inlineStr"><is><t>zapalenia płuc o etiologii Mycoplasma pneumoniae</t></is></c><c r="M1163" s="2" t="inlineStr"><is><t>zapalenia ucha środkowego</t></is></c><c r="N1163" s="2" t="inlineStr" /><c r="O1163" s="2" t="inlineStr" /><c r="P1163" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1163" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="1164"><c r="A1164" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B1164" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C1164" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1164" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1164" s="2" t="inlineStr"><is><t>Metronidazol:</t></is></c><c r="F1164" s="2" t="inlineStr"><is><t>jest lekiem przeciwpierwotniakowym</t></is></c><c r="G1164" s="2" t="inlineStr"><is><t>powoduje reakcję disulfiramopodobną</t></is></c><c r="H1164" s="2" t="inlineStr"><is><t>jest skuteczny wobec bakterii beztlenowych</t></is></c><c r="I1164" s="2" t="inlineStr"><is><t>dobrze przenika do większości tkanek</t></is></c><c r="J1164" s="2" t="inlineStr" /><c r="K1164" s="2" t="inlineStr" /><c r="L1164" s="2" t="inlineStr" /><c r="M1164" s="2" t="inlineStr" /><c r="N1164" s="2" t="inlineStr" /><c r="O1164" s="2" t="inlineStr" /><c r="P1164" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1164" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="1165"><c r="A1165" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B1165" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C1165" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1165" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1165" s="2" t="inlineStr"><is><t>Betahistyna:</t></is></c><c r="F1165" s="2" t="inlineStr"><is><t>jest skuteczna w terapii choroby Ménière’a</t></is></c><c r="G1165" s="2" t="inlineStr" /><c r="H1165" s="2" t="inlineStr" /><c r="I1165" s="2" t="inlineStr" /><c r="J1165" s="2" t="inlineStr" /><c r="K1165" s="2" t="inlineStr"><is><t>jest antagonistą receptora histaminowego typu 2 (H2)</t></is></c><c r="L1165" s="2" t="inlineStr"><is><t>znalazła zastosowanie w leczeniu chorobywrzodowej</t></is></c><c r="M1165" s="2" t="inlineStr"><is><t>może być stosowana u dzieci</t></is></c><c r="N1165" s="2" t="inlineStr" /><c r="O1165" s="2" t="inlineStr" /><c r="P1165" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1165" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="1166"><c r="A1166" s="2" t="inlineStr"><is><t>LEKI PRZECIWWIRUSOWE</t></is></c><c r="B1166" s="2" t="inlineStr"><is><t>Przeciwwskazania</t></is></c><c r="C1166" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1166" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1166" s="2" t="inlineStr"><is><t>Filgrastim:</t></is></c><c r="F1166" s="2" t="inlineStr"><is><t>może zwiększać ryzyko pęknięcia śledziony a – prawidłowe 1, 3 i 4 b – prawidłowe 1 i 3 c – prawidłowe 2 i 4 d – prawidłowa 4 e – wszystkie prawidłowe</t></is></c><c r="G1166" s="2" t="inlineStr" /><c r="H1166" s="2" t="inlineStr" /><c r="I1166" s="2" t="inlineStr" /><c r="J1166" s="2" t="inlineStr" /><c r="K1166" s="2" t="inlineStr"><is><t>stymuluje wzrost płytek krwi</t></is></c><c r="L1166" s="2" t="inlineStr"><is><t>jest stosowany doustnie</t></is></c><c r="M1166" s="2" t="inlineStr"><is><t>jest przeciwwskazany u pacjentów z HIV</t></is></c><c r="N1166" s="2" t="inlineStr" /><c r="O1166" s="2" t="inlineStr" /><c r="P1166" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1166" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="1167"><c r="A1167" s="2" t="inlineStr"><is><t>LEKI PRZECIWGRZYBICZE</t></is></c><c r="B1167" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C1167" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1167" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1167" s="2" t="inlineStr"><is><t>Posakonazol:</t></is></c><c r="F1167" s="2" t="inlineStr"><is><t>jest aktywny wobec Candida</t></is></c><c r="G1167" s="2" t="inlineStr"><is><t>hamuje biosyntezę ergosterolu</t></is></c><c r="H1167" s="2" t="inlineStr"><is><t>może być przyczyną uszkodzenia wątroby</t></is></c><c r="I1167" s="2" t="inlineStr" /><c r="J1167" s="2" t="inlineStr" /><c r="K1167" s="2" t="inlineStr"><is><t>ma wysoką biodostępność po podaniu doustnym</t></is></c><c r="L1167" s="2" t="inlineStr" /><c r="M1167" s="2" t="inlineStr" /><c r="N1167" s="2" t="inlineStr" /><c r="O1167" s="2" t="inlineStr" /><c r="P1167" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1167" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="1168"><c r="A1168" s="2" t="inlineStr"><is><t>LEKI PRZECIWWIRUSOWE</t></is></c><c r="B1168" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C1168" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1168" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1168" s="2" t="inlineStr"><is><t>Acyklowir:</t></is></c><c r="F1168" s="2" t="inlineStr"><is><t>jest używany w leczeniu półpaśca</t></is></c><c r="G1168" s="2" t="inlineStr"><is><t>może powodować upośledzenie czynności nerek</t></is></c><c r="H1168" s="2" t="inlineStr" /><c r="I1168" s="2" t="inlineStr" /><c r="J1168" s="2" t="inlineStr" /><c r="K1168" s="2" t="inlineStr"><is><t>nie może być podawany dożylnie</t></is></c><c r="L1168" s="2" t="inlineStr"><is><t>stosuje się go w terapii grypy</t></is></c><c r="M1168" s="2" t="inlineStr" /><c r="N1168" s="2" t="inlineStr" /><c r="O1168" s="2" t="inlineStr" /><c r="P1168" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1168" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="1169"><c r="A1169" s="2" t="inlineStr"><is><t>LEKI PRZECIWWIRUSOWE</t></is></c><c r="B1169" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C1169" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1169" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1169" s="2" t="inlineStr"><is><t>W leczeniu przewlekłego wirusowego zapalenia wątroby typu C można zastosować:</t></is></c><c r="F1169" s="2" t="inlineStr"><is><t>interferon alfa</t></is></c><c r="G1169" s="2" t="inlineStr"><is><t>rybawirynę</t></is></c><c r="H1169" s="2" t="inlineStr"><is><t>telaprewir</t></is></c><c r="I1169" s="2" t="inlineStr" /><c r="J1169" s="2" t="inlineStr" /><c r="K1169" s="2" t="inlineStr"><is><t>boceprewir</t></is></c><c r="L1169" s="2" t="inlineStr" /><c r="M1169" s="2" t="inlineStr" /><c r="N1169" s="2" t="inlineStr" /><c r="O1169" s="2" t="inlineStr" /><c r="P1169" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1169" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="1170"><c r="A1170" s="2" t="inlineStr"><is><t>CUKRZYCA</t></is></c><c r="B1170" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C1170" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1170" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1170" s="2" t="inlineStr"><is><t>Glibenklamid:</t></is></c><c r="F1170" s="2" t="inlineStr"><is><t>hamuje kanały potasowe zależne od ATP w komórkach beta trzustki</t></is></c><c r="G1170" s="2" t="inlineStr"><is><t>może powodować hipoglikemię</t></is></c><c r="H1170" s="2" t="inlineStr"><is><t>może być stosowany w skojarzeniu z insuliną</t></is></c><c r="I1170" s="2" t="inlineStr" /><c r="J1170" s="2" t="inlineStr" /><c r="K1170" s="2" t="inlineStr"><is><t>jest lekiem pierwszego rzutu w leczeniu cukrzycy typu 2 chroniącym przed powikłaniami makroangiopatycznymi</t></is></c><c r="L1170" s="2" t="inlineStr" /><c r="M1170" s="2" t="inlineStr" /><c r="N1170" s="2" t="inlineStr" /><c r="O1170" s="2" t="inlineStr" /><c r="P1170" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1170" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="1171"><c r="A1171" s="2" t="inlineStr"><is><t>CUKRZYCA</t></is></c><c r="B1171" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C1171" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1171" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1171" s="2" t="inlineStr"><is><t>Który z wymienionych poniżej leków przeciwcukrzycowych stymuluje wydzielanie insuliny:</t></is></c><c r="F1171" s="2" t="inlineStr"><is><t>repaglinid</t></is></c><c r="G1171" s="2" t="inlineStr"><is><t>gliklazyd</t></is></c><c r="H1171" s="2" t="inlineStr" /><c r="I1171" s="2" t="inlineStr" /><c r="J1171" s="2" t="inlineStr" /><c r="K1171" s="2" t="inlineStr"><is><t>metformina</t></is></c><c r="L1171" s="2" t="inlineStr"><is><t>kanagliflozyna</t></is></c><c r="M1171" s="2" t="inlineStr" /><c r="N1171" s="2" t="inlineStr" /><c r="O1171" s="2" t="inlineStr" /><c r="P1171" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1171" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="1172"><c r="A1172" s="2" t="inlineStr"><is><t>TARCZYCA</t></is></c><c r="B1172" s="2" t="inlineStr"><is><t>Monitorowanie</t></is></c><c r="C1172" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1172" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1172" s="2" t="inlineStr"><is><t>Lewotyroksyna:</t></is></c><c r="F1172" s="2" t="inlineStr"><is><t>jest lekiem z wyboru w niedoczynności tarczycy</t></is></c><c r="G1172" s="2" t="inlineStr"><is><t>w trakcie jej podawania obowiązkowe jest monitorowanie stężenia TSH</t></is></c><c r="H1172" s="2" t="inlineStr" /><c r="I1172" s="2" t="inlineStr" /><c r="J1172" s="2" t="inlineStr" /><c r="K1172" s="2" t="inlineStr"><is><t>odpowiada ona naturalnemu hormonowi T3</t></is></c><c r="L1172" s="2" t="inlineStr"><is><t>nasila działanie acenokumarolu</t></is></c><c r="M1172" s="2" t="inlineStr" /><c r="N1172" s="2" t="inlineStr" /><c r="O1172" s="2" t="inlineStr" /><c r="P1172" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1172" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="1173"><c r="A1173" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B1173" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C1173" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1173" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1173" s="2" t="inlineStr"><is><t>Działaniem niepożądanym tiamazolu jest/są:</t></is></c><c r="F1173" s="2" t="inlineStr"><is><t>wysypka plamisto-grudkowa</t></is></c><c r="G1173" s="2" t="inlineStr"><is><t>bóle stawów</t></is></c><c r="H1173" s="2" t="inlineStr"><is><t>zaburzenia czynności wątroby</t></is></c><c r="I1173" s="2" t="inlineStr"><is><t>agranulocytoza a – prawidłowe 1, 3 i 4 b – prawidłowe 1 i 3 c – prawidłowe 2 i 4 d – prawidłowa 4 e – wszystkie prawidłowe</t></is></c><c r="J1173" s="2" t="inlineStr" /><c r="K1173" s="2" t="inlineStr" /><c r="L1173" s="2" t="inlineStr" /><c r="M1173" s="2" t="inlineStr" /><c r="N1173" s="2" t="inlineStr" /><c r="O1173" s="2" t="inlineStr" /><c r="P1173" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1173" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="1174"><c r="A1174" s="2" t="inlineStr"><is><t>NADCIŚNIENIE TĘTNICZE</t></is></c><c r="B1174" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C1174" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1174" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1174" s="2" t="inlineStr"><is><t>Działaniem niepożądanym progestagenów jest:</t></is></c><c r="F1174" s="2" t="inlineStr"><is><t>wzrost ciśnienia tętniczego</t></is></c><c r="G1174" s="2" t="inlineStr"><is><t>depresja</t></is></c><c r="H1174" s="2" t="inlineStr"><is><t>hirsutyzm</t></is></c><c r="I1174" s="2" t="inlineStr"><is><t>zaburzenia libido</t></is></c><c r="J1174" s="2" t="inlineStr" /><c r="K1174" s="2" t="inlineStr" /><c r="L1174" s="2" t="inlineStr" /><c r="M1174" s="2" t="inlineStr" /><c r="N1174" s="2" t="inlineStr" /><c r="O1174" s="2" t="inlineStr" /><c r="P1174" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1174" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="1175"><c r="A1175" s="2" t="inlineStr"><is><t>LEKI PRZECIWNOWOTWOROWE</t></is></c><c r="B1175" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C1175" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1175" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1175" s="2" t="inlineStr"><is><t>Tamoksyfen:</t></is></c><c r="F1175" s="2" t="inlineStr"><is><t>to selektywny modulator receptora estrogenowego</t></is></c><c r="G1175" s="2" t="inlineStr"><is><t>jest wskazany w leczeniu raka sutka</t></is></c><c r="H1175" s="2" t="inlineStr" /><c r="I1175" s="2" t="inlineStr" /><c r="J1175" s="2" t="inlineStr" /><c r="K1175" s="2" t="inlineStr"><is><t>zwiększa ryzyko zakrzepicy żylnej</t></is></c><c r="L1175" s="2" t="inlineStr"><is><t>powoduje uderzenia gorąca</t></is></c><c r="M1175" s="2" t="inlineStr" /><c r="N1175" s="2" t="inlineStr" /><c r="O1175" s="2" t="inlineStr" /><c r="P1175" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1175" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="1176"><c r="A1176" s="2" t="inlineStr"><is><t>HORMONY PŁCIOWE</t></is></c><c r="B1176" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C1176" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1176" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1176" s="2" t="inlineStr"><is><t>Działaniem niepożądanym steroidów anabolicznych jest:</t></is></c><c r="F1176" s="2" t="inlineStr"><is><t>żółtaczka cholestatyczna</t></is></c><c r="G1176" s="2" t="inlineStr"><is><t>pęknięcie ścięgna</t></is></c><c r="H1176" s="2" t="inlineStr"><is><t>bezpłodność</t></is></c><c r="I1176" s="2" t="inlineStr"><is><t>maskulinizacja u kobiet</t></is></c><c r="J1176" s="2" t="inlineStr" /><c r="K1176" s="2" t="inlineStr" /><c r="L1176" s="2" t="inlineStr" /><c r="M1176" s="2" t="inlineStr" /><c r="N1176" s="2" t="inlineStr" /><c r="O1176" s="2" t="inlineStr" /><c r="P1176" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1176" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="1177"><c r="A1177" s="2" t="inlineStr"><is><t>HORMONY PŁCIOWE</t></is></c><c r="B1177" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C1177" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1177" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1177" s="2" t="inlineStr"><is><t>Finasteryd:</t></is></c><c r="F1177" s="2" t="inlineStr"><is><t>zmniejsza wytwarzanie dihydrotestosteronu</t></is></c><c r="G1177" s="2" t="inlineStr"><is><t>jest stosowany w leczeniu łagodnego rozrostu gruczołu krokowego</t></is></c><c r="H1177" s="2" t="inlineStr"><is><t>może powodować ginekomastię</t></is></c><c r="I1177" s="2" t="inlineStr" /><c r="J1177" s="2" t="inlineStr" /><c r="K1177" s="2" t="inlineStr"><is><t>jest stosowany w leczeniu zaburzeń wzwodu</t></is></c><c r="L1177" s="2" t="inlineStr" /><c r="M1177" s="2" t="inlineStr" /><c r="N1177" s="2" t="inlineStr" /><c r="O1177" s="2" t="inlineStr" /><c r="P1177" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1177" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="1178"><c r="A1178" s="2" t="inlineStr"><is><t>HORMONY PŁCIOWE</t></is></c><c r="B1178" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C1178" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1178" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1178" s="2" t="inlineStr"><is><t>W leczeniu łysienia androgenowego u mężczyzn celowe jest zastosowanie:</t></is></c><c r="F1178" s="2" t="inlineStr"><is><t>minoksydylu</t></is></c><c r="G1178" s="2" t="inlineStr" /><c r="H1178" s="2" t="inlineStr" /><c r="I1178" s="2" t="inlineStr" /><c r="J1178" s="2" t="inlineStr" /><c r="K1178" s="2" t="inlineStr"><is><t>etynyloestradiolu</t></is></c><c r="L1178" s="2" t="inlineStr"><is><t>klobetazolu</t></is></c><c r="M1178" s="2" t="inlineStr"><is><t>tamsulozyny</t></is></c><c r="N1178" s="2" t="inlineStr" /><c r="O1178" s="2" t="inlineStr" /><c r="P1178" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1178" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="1179"><c r="A1179" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B1179" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C1179" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1179" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1179" s="2" t="inlineStr"><is><t>Metoklopramid:</t></is></c><c r="F1179" s="2" t="inlineStr"><is><t>może powodować objawy pozapiramidowe</t></is></c><c r="G1179" s="2" t="inlineStr"><is><t>ma działanie przeciwwymiotne</t></is></c><c r="H1179" s="2" t="inlineStr" /><c r="I1179" s="2" t="inlineStr" /><c r="J1179" s="2" t="inlineStr" /><c r="K1179" s="2" t="inlineStr"><is><t>jest agonistą receptorów opioidowych</t></is></c><c r="L1179" s="2" t="inlineStr"><is><t>powoduje wzrost wydzielania prolaktyny</t></is></c><c r="M1179" s="2" t="inlineStr" /><c r="N1179" s="2" t="inlineStr" /><c r="O1179" s="2" t="inlineStr" /><c r="P1179" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1179" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="1180"><c r="A1180" s="2" t="inlineStr"><is><t>NADCIŚNIENIE TĘTNICZE</t></is></c><c r="B1180" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C1180" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1180" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1180" s="2" t="inlineStr"><is><t>Niesteroidowe leki przeciwzapalne:</t></is></c><c r="F1180" s="2" t="inlineStr"><is><t>zmniejszają skuteczność hipotensyjną beta-adrenolityków</t></is></c><c r="G1180" s="2" t="inlineStr"><is><t>mogą być przyczyną zaostrzenia niewydolności serca</t></is></c><c r="H1180" s="2" t="inlineStr"><is><t>mogą powodować zaostrzenie objawów astmy</t></is></c><c r="I1180" s="2" t="inlineStr"><is><t>u noworodków ułatwiają zamknięcie przetrwałego przewodu tętniczego (Botalla) a – prawidłowe 1, 3 i 4 b – prawidłowe 1 i 3 c – prawidłowe 2 i 4 d – prawidłowa 4 e – wszystkie prawidłowe</t></is></c><c r="J1180" s="2" t="inlineStr" /><c r="K1180" s="2" t="inlineStr" /><c r="L1180" s="2" t="inlineStr" /><c r="M1180" s="2" t="inlineStr" /><c r="N1180" s="2" t="inlineStr" /><c r="O1180" s="2" t="inlineStr" /><c r="P1180" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1180" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="1181"><c r="A1181" s="2" t="inlineStr"><is><t>NIEOPIOIDOWE LEKI PRZECIWBÓLOWE</t></is></c><c r="B1181" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C1181" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1181" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1181" s="2" t="inlineStr"><is><t>Wskaż prawidłowe połączenie leku i jego zastosowania:</t></is></c><c r="F1181" s="2" t="inlineStr"><is><t>kwas acetylosalicylowy - profilaktyka wtórna zawału serca</t></is></c><c r="G1181" s="2" t="inlineStr"><is><t>ibuprofen - bolesne miesiączkowanie</t></is></c><c r="H1181" s="2" t="inlineStr" /><c r="I1181" s="2" t="inlineStr" /><c r="J1181" s="2" t="inlineStr" /><c r="K1181" s="2" t="inlineStr"><is><t>kwas acetylosalicylowy - gorączka w grypie u 4-letniego dziecka</t></is></c><c r="L1181" s="2" t="inlineStr"><is><t>paracetamol - ból głowy po nadużyciu etanolu</t></is></c><c r="M1181" s="2" t="inlineStr" /><c r="N1181" s="2" t="inlineStr" /><c r="O1181" s="2" t="inlineStr" /><c r="P1181" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1181" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="1182"><c r="A1182" s="2" t="inlineStr"><is><t>ZNIECZULENIA MIEJSCOWE</t></is></c><c r="B1182" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C1182" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1182" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1182" s="2" t="inlineStr"><is><t>Do leków działających miejscowo przeciwbólowo należy/ą:</t></is></c><c r="F1182" s="2" t="inlineStr"><is><t>kapsaicyna</t></is></c><c r="G1182" s="2" t="inlineStr"><is><t>lidokaina</t></is></c><c r="H1182" s="2" t="inlineStr" /><c r="I1182" s="2" t="inlineStr" /><c r="J1182" s="2" t="inlineStr" /><c r="K1182" s="2" t="inlineStr"><is><t>propofol</t></is></c><c r="L1182" s="2" t="inlineStr"><is><t>izofluran</t></is></c><c r="M1182" s="2" t="inlineStr" /><c r="N1182" s="2" t="inlineStr" /><c r="O1182" s="2" t="inlineStr" /><c r="P1182" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1182" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="1183"><c r="A1183" s="2" t="inlineStr"><is><t>UKŁAD PRZYWSPÓŁCZULNY</t></is></c><c r="B1183" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C1183" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1183" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1183" s="2" t="inlineStr"><is><t>W kolce nerkowej uzasadnione jest podanie:</t></is></c><c r="F1183" s="2" t="inlineStr"><is><t>butylobromku skopolaminy doodbytniczo</t></is></c><c r="G1183" s="2" t="inlineStr" /><c r="H1183" s="2" t="inlineStr" /><c r="I1183" s="2" t="inlineStr" /><c r="J1183" s="2" t="inlineStr" /><c r="K1183" s="2" t="inlineStr"><is><t>metamizolu dożylnie</t></is></c><c r="L1183" s="2" t="inlineStr"><is><t>papaweryny doustnie</t></is></c><c r="M1183" s="2" t="inlineStr"><is><t>oksyfenonium doustnie</t></is></c><c r="N1183" s="2" t="inlineStr" /><c r="O1183" s="2" t="inlineStr" /><c r="P1183" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1183" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="1184"><c r="A1184" s="2" t="inlineStr"><is><t>NARKOTYCZNE LEKI PRZECIWBÓLOWE</t></is></c><c r="B1184" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C1184" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1184" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1184" s="2" t="inlineStr"><is><t>Ból przebijający można skutecznie opanować stosując lek opioidowy w postaci:</t></is></c><c r="F1184" s="2" t="inlineStr"><is><t>podskórnej</t></is></c><c r="G1184" s="2" t="inlineStr"><is><t>systemu transdermalnego (TTS)</t></is></c><c r="H1184" s="2" t="inlineStr"><is><t>podjęzykowej</t></is></c><c r="I1184" s="2" t="inlineStr"><is><t>doustnej o natychmiastowym uwalnianiu</t></is></c><c r="J1184" s="2" t="inlineStr" /><c r="K1184" s="2" t="inlineStr" /><c r="L1184" s="2" t="inlineStr" /><c r="M1184" s="2" t="inlineStr" /><c r="N1184" s="2" t="inlineStr" /><c r="O1184" s="2" t="inlineStr" /><c r="P1184" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1184" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="1185"><c r="A1185" s="2" t="inlineStr"><is><t>NARKOTYCZNE LEKI PRZECIWBÓLOWE</t></is></c><c r="B1185" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C1185" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1185" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1185" s="2" t="inlineStr"><is><t>Tramadol:</t></is></c><c r="F1185" s="2" t="inlineStr"><is><t>może być stosowany parenteralnie</t></is></c><c r="G1185" s="2" t="inlineStr"><is><t>jest przeciwwskazany u pacjentów z padaczką</t></is></c><c r="H1185" s="2" t="inlineStr"><is><t>jest stosowany w bólach kolkowych</t></is></c><c r="I1185" s="2" t="inlineStr"><is><t>podawany łącznie z fluoksetyną może prowadzić do wystąpienia zespołu serotoninowego</t></is></c><c r="J1185" s="2" t="inlineStr" /><c r="K1185" s="2" t="inlineStr" /><c r="L1185" s="2" t="inlineStr" /><c r="M1185" s="2" t="inlineStr" /><c r="N1185" s="2" t="inlineStr" /><c r="O1185" s="2" t="inlineStr" /><c r="P1185" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1185" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="1186"><c r="A1186" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B1186" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C1186" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1186" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1186" s="2" t="inlineStr"><is><t>Petydyna:</t></is></c><c r="F1186" s="2" t="inlineStr"><is><t>może wywoływać zaparcia</t></is></c><c r="G1186" s="2" t="inlineStr"><is><t>działa neurotoksycznie</t></is></c><c r="H1186" s="2" t="inlineStr"><is><t>hamuje ośrodek oddechowy</t></is></c><c r="I1186" s="2" t="inlineStr"><is><t>może powodować tachykardię</t></is></c><c r="J1186" s="2" t="inlineStr" /><c r="K1186" s="2" t="inlineStr" /><c r="L1186" s="2" t="inlineStr" /><c r="M1186" s="2" t="inlineStr" /><c r="N1186" s="2" t="inlineStr" /><c r="O1186" s="2" t="inlineStr" /><c r="P1186" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1186" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="1187"><c r="A1187" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B1187" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C1187" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1187" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1187" s="2" t="inlineStr"><is><t>Objawy zespołu abstynencyjnego w przebiegu uzależnienia od opioidów to:</t></is></c><c r="F1187" s="2" t="inlineStr"><is><t>ziewanie</t></is></c><c r="G1187" s="2" t="inlineStr"><is><t>biegunka</t></is></c><c r="H1187" s="2" t="inlineStr"><is><t>piloerekcja („gęsia skóra”) a – prawidłowe 1, 3 i 4 b – prawidłowe 1 i 3 c – prawidłowe 2 i 4 d – prawidłowa 4 e – wszystkie prawidłowe</t></is></c><c r="I1187" s="2" t="inlineStr" /><c r="J1187" s="2" t="inlineStr" /><c r="K1187" s="2" t="inlineStr"><is><t>senność</t></is></c><c r="L1187" s="2" t="inlineStr" /><c r="M1187" s="2" t="inlineStr" /><c r="N1187" s="2" t="inlineStr" /><c r="O1187" s="2" t="inlineStr" /><c r="P1187" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1187" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="1188"><c r="A1188" s="2" t="inlineStr"><is><t>NADCIŚNIENIE TĘTNICZE</t></is></c><c r="B1188" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C1188" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1188" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1188" s="2" t="inlineStr"><is><t>Klonidyna:</t></is></c><c r="F1188" s="2" t="inlineStr"><is><t>jest agonistą receptora alfa-2 adrenergicznego</t></is></c><c r="G1188" s="2" t="inlineStr"><is><t>działa hipotensyjnie</t></is></c><c r="H1188" s="2" t="inlineStr" /><c r="I1188" s="2" t="inlineStr" /><c r="J1188" s="2" t="inlineStr" /><c r="K1188" s="2" t="inlineStr"><is><t>jest przeciwwskazana w leczeniu spastyczności</t></is></c><c r="L1188" s="2" t="inlineStr"><is><t>jest stosowana w terapii choroby afektywnej jednobiegunowej</t></is></c><c r="M1188" s="2" t="inlineStr" /><c r="N1188" s="2" t="inlineStr" /><c r="O1188" s="2" t="inlineStr" /><c r="P1188" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1188" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="1189"><c r="A1189" s="2" t="inlineStr"><is><t>UKŁAD WSPÓŁCZULNY</t></is></c><c r="B1189" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C1189" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1189" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1189" s="2" t="inlineStr"><is><t>Receptory beta-adrenergiczne aktywuje:</t></is></c><c r="F1189" s="2" t="inlineStr"><is><t>dopamina</t></is></c><c r="G1189" s="2" t="inlineStr"><is><t>efedryna</t></is></c><c r="H1189" s="2" t="inlineStr"><is><t>indakaterol</t></is></c><c r="I1189" s="2" t="inlineStr" /><c r="J1189" s="2" t="inlineStr" /><c r="K1189" s="2" t="inlineStr"><is><t>moksonidyna</t></is></c><c r="L1189" s="2" t="inlineStr" /><c r="M1189" s="2" t="inlineStr" /><c r="N1189" s="2" t="inlineStr" /><c r="O1189" s="2" t="inlineStr" /><c r="P1189" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1189" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="1190"><c r="A1190" s="2" t="inlineStr"><is><t>UKŁAD WSPÓŁCZULNY</t></is></c><c r="B1190" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C1190" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1190" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1190" s="2" t="inlineStr"><is><t>Receptory alfa-1 adrenergiczne blokuje:</t></is></c><c r="F1190" s="2" t="inlineStr"><is><t>labetalol</t></is></c><c r="G1190" s="2" t="inlineStr"><is><t>haloperydol</t></is></c><c r="H1190" s="2" t="inlineStr"><is><t>doksazosyna</t></is></c><c r="I1190" s="2" t="inlineStr" /><c r="J1190" s="2" t="inlineStr" /><c r="K1190" s="2" t="inlineStr"><is><t>nafazolina</t></is></c><c r="L1190" s="2" t="inlineStr" /><c r="M1190" s="2" t="inlineStr" /><c r="N1190" s="2" t="inlineStr" /><c r="O1190" s="2" t="inlineStr" /><c r="P1190" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1190" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="1191"><c r="A1191" s="2" t="inlineStr"><is><t>UKŁAD WSPÓŁCZULNY</t></is></c><c r="B1191" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C1191" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1191" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1191" s="2" t="inlineStr"><is><t>Długotrwałe stosowanie którego leku/ów wymaga wolnego odstawiania:</t></is></c><c r="F1191" s="2" t="inlineStr"><is><t>atenololu</t></is></c><c r="G1191" s="2" t="inlineStr"><is><t>fluoksetyny</t></is></c><c r="H1191" s="2" t="inlineStr"><is><t>prednizonu</t></is></c><c r="I1191" s="2" t="inlineStr" /><c r="J1191" s="2" t="inlineStr" /><c r="K1191" s="2" t="inlineStr"><is><t>paracetamolu</t></is></c><c r="L1191" s="2" t="inlineStr" /><c r="M1191" s="2" t="inlineStr" /><c r="N1191" s="2" t="inlineStr" /><c r="O1191" s="2" t="inlineStr" /><c r="P1191" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1191" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="1192"><c r="A1192" s="2" t="inlineStr"><is><t>UKŁAD WSPÓŁCZULNY</t></is></c><c r="B1192" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C1192" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1192" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1192" s="2" t="inlineStr"><is><t>Działaniem niepożądanym antagonistów receptora beta-adrenergicznego jest:</t></is></c><c r="F1192" s="2" t="inlineStr"><is><t>bradykardia</t></is></c><c r="G1192" s="2" t="inlineStr"><is><t>bloki przewodzenia przedsionkowo-komorowego</t></is></c><c r="H1192" s="2" t="inlineStr" /><c r="I1192" s="2" t="inlineStr" /><c r="J1192" s="2" t="inlineStr" /><c r="K1192" s="2" t="inlineStr"><is><t>wzrost ciśnienia śródgałkowego</t></is></c><c r="L1192" s="2" t="inlineStr"><is><t>zakrzepowe zapalenie żył</t></is></c><c r="M1192" s="2" t="inlineStr" /><c r="N1192" s="2" t="inlineStr" /><c r="O1192" s="2" t="inlineStr" /><c r="P1192" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1192" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="1193"><c r="A1193" s="2" t="inlineStr"><is><t>STANY NAGŁE</t></is></c><c r="B1193" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C1193" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1193" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1193" s="2" t="inlineStr"><is><t>Adrenalina znalazła zastosowanie:</t></is></c><c r="F1193" s="2" t="inlineStr"><is><t>w terapii wstrząsu anafilaktycznego</t></is></c><c r="G1193" s="2" t="inlineStr"><is><t>w resuscytacji krążeniowo-oddechowej bez względu na mechanizm zatrzymania krążenia</t></is></c><c r="H1193" s="2" t="inlineStr"><is><t>jako dodatek do leków miejscowo znieczulających</t></is></c><c r="I1193" s="2" t="inlineStr" /><c r="J1193" s="2" t="inlineStr" /><c r="K1193" s="2" t="inlineStr"><is><t>w terapii arytmii nadkomorowych</t></is></c><c r="L1193" s="2" t="inlineStr" /><c r="M1193" s="2" t="inlineStr" /><c r="N1193" s="2" t="inlineStr" /><c r="O1193" s="2" t="inlineStr" /><c r="P1193" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1193" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="1194"><c r="A1194" s="2" t="inlineStr"><is><t>CHOROBA PARKINSONA</t></is></c><c r="B1194" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C1194" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1194" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1194" s="2" t="inlineStr"><is><t>Bromokryptyna może być stosowana w leczeniu:</t></is></c><c r="F1194" s="2" t="inlineStr"><is><t>akromegalii</t></is></c><c r="G1194" s="2" t="inlineStr"><is><t>mlekotoku</t></is></c><c r="H1194" s="2" t="inlineStr"><is><t>zaburzeń cyklu miesiączkowego</t></is></c><c r="I1194" s="2" t="inlineStr"><is><t>hipogonadyzmu a – prawidłowe 1, 3 i 4 b – prawidłowe 1 i 3 c – prawidłowe 2 i 4 d – prawidłowa 4 e – wszystkie prawidłowe</t></is></c><c r="J1194" s="2" t="inlineStr" /><c r="K1194" s="2" t="inlineStr" /><c r="L1194" s="2" t="inlineStr" /><c r="M1194" s="2" t="inlineStr" /><c r="N1194" s="2" t="inlineStr" /><c r="O1194" s="2" t="inlineStr" /><c r="P1194" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1194" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="1195"><c r="A1195" s="2" t="inlineStr"><is><t>NADCIŚNIENIE TĘTNICZE</t></is></c><c r="B1195" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C1195" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1195" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1195" s="2" t="inlineStr"><is><t>Długodziałającą pochodną dihydropirydyny jest:</t></is></c><c r="F1195" s="2" t="inlineStr"><is><t>lerkanidypina</t></is></c><c r="G1195" s="2" t="inlineStr"><is><t>amlodypina</t></is></c><c r="H1195" s="2" t="inlineStr" /><c r="I1195" s="2" t="inlineStr" /><c r="J1195" s="2" t="inlineStr" /><c r="K1195" s="2" t="inlineStr"><is><t>nifedypina</t></is></c><c r="L1195" s="2" t="inlineStr"><is><t>nimodypina</t></is></c><c r="M1195" s="2" t="inlineStr" /><c r="N1195" s="2" t="inlineStr" /><c r="O1195" s="2" t="inlineStr" /><c r="P1195" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1195" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="1196"><c r="A1196" s="2" t="inlineStr"><is><t>ZABURZENIA RYTMU SERCA</t></is></c><c r="B1196" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C1196" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1196" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1196" s="2" t="inlineStr"><is><t>W resuscytacji krążeniowo-oddechowej u osoby z zaburzeniami rytmu serca do defibrylacji zastosujesz dodatkowo:</t></is></c><c r="F1196" s="2" t="inlineStr"><is><t>amiodaron 300 mg w krótkim 10-minutowym wlewie i.v</t></is></c><c r="G1196" s="2" t="inlineStr" /><c r="H1196" s="2" t="inlineStr" /><c r="I1196" s="2" t="inlineStr" /><c r="J1196" s="2" t="inlineStr" /><c r="K1196" s="2" t="inlineStr"><is><t>lidokainę 100 mg w bolusie i.v., a następnie wlewie ciągłym i.v</t></is></c><c r="L1196" s="2" t="inlineStr"><is><t>propafenon 70 mg w krótkim wstrzyknięciu i.v</t></is></c><c r="M1196" s="2" t="inlineStr"><is><t>adenozynę co 2 min w trzech kolejnych szybkich wstrzyknięciach i.v. 3 mg-6 mg-12mg</t></is></c><c r="N1196" s="2" t="inlineStr" /><c r="O1196" s="2" t="inlineStr" /><c r="P1196" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1196" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="1197"><c r="A1197" s="2" t="inlineStr"><is><t>ZABURZENIA RYTMU SERCA</t></is></c><c r="B1197" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C1197" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1197" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1197" s="2" t="inlineStr"><is><t>Amiodaron jest lekiem, który:</t></is></c><c r="F1197" s="2" t="inlineStr"><is><t>działa słabo adrenolitycznie</t></is></c><c r="G1197" s="2" t="inlineStr"><is><t>jest słabym antagonistą kanałów wapniowych</t></is></c><c r="H1197" s="2" t="inlineStr"><is><t>wydłuża odstęp QT przez blokowanie kanałów potasowych Ikr</t></is></c><c r="I1197" s="2" t="inlineStr" /><c r="J1197" s="2" t="inlineStr" /><c r="K1197" s="2" t="inlineStr"><is><t>w istotny sposób blokuje kanały sodowe</t></is></c><c r="L1197" s="2" t="inlineStr" /><c r="M1197" s="2" t="inlineStr" /><c r="N1197" s="2" t="inlineStr" /><c r="O1197" s="2" t="inlineStr" /><c r="P1197" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1197" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="1198"><c r="A1198" s="2" t="inlineStr"><is><t>NIEOPIOIDOWE LEKI PRZECIWBÓLOWE</t></is></c><c r="B1198" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C1198" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1198" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1198" s="2" t="inlineStr"><is><t>Ryzyko sercowo-naczyniowe zwiększają:</t></is></c><c r="F1198" s="2" t="inlineStr"><is><t>diklofenak</t></is></c><c r="G1198" s="2" t="inlineStr"><is><t>celekoksyb</t></is></c><c r="H1198" s="2" t="inlineStr" /><c r="I1198" s="2" t="inlineStr" /><c r="J1198" s="2" t="inlineStr" /><c r="K1198" s="2" t="inlineStr"><is><t>naproksen</t></is></c><c r="L1198" s="2" t="inlineStr"><is><t>paracetamol</t></is></c><c r="M1198" s="2" t="inlineStr" /><c r="N1198" s="2" t="inlineStr" /><c r="O1198" s="2" t="inlineStr" /><c r="P1198" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1198" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="1199"><c r="A1199" s="2" t="inlineStr"><is><t>NADCIŚNIENIE TĘTNICZE</t></is></c><c r="B1199" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C1199" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1199" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1199" s="2" t="inlineStr"><is><t>Enzymem, którego blokowanie może być przydatne w leczeniu nadciśnienia tętniczego jest:</t></is></c><c r="F1199" s="2" t="inlineStr"><is><t>endotelina</t></is></c><c r="G1199" s="2" t="inlineStr"><is><t>konwertaza angiotensyny a – prawidłowe 1, 3 i 4 b – prawidłowe 1 i 3 c – prawidłowe 2 i 4 d – prawidłowa 4 e – wszystkie prawidłowe</t></is></c><c r="H1199" s="2" t="inlineStr" /><c r="I1199" s="2" t="inlineStr" /><c r="J1199" s="2" t="inlineStr" /><c r="K1199" s="2" t="inlineStr"><is><t>syntaza aldosteronu</t></is></c><c r="L1199" s="2" t="inlineStr"><is><t>neprylizyna</t></is></c><c r="M1199" s="2" t="inlineStr" /><c r="N1199" s="2" t="inlineStr" /><c r="O1199" s="2" t="inlineStr" /><c r="P1199" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1199" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="1200"><c r="A1200" s="2" t="inlineStr"><is><t>UKŁAD WSPÓŁCZULNY</t></is></c><c r="B1200" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C1200" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1200" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1200" s="2" t="inlineStr"><is><t>Charakterystycznym działaniem związanym ze stosowaniem beta-adrenolityków w chorobie wieńcowej jest:</t></is></c><c r="F1200" s="2" t="inlineStr"><is><t>zwiększenie oporu obwodowego</t></is></c><c r="G1200" s="2" t="inlineStr" /><c r="H1200" s="2" t="inlineStr" /><c r="I1200" s="2" t="inlineStr" /><c r="J1200" s="2" t="inlineStr" /><c r="K1200" s="2" t="inlineStr"><is><t>zwiększenie objętości późnorozkurczowej</t></is></c><c r="L1200" s="2" t="inlineStr"><is><t>zwiększenie kurczliwości mięśnia serca</t></is></c><c r="M1200" s="2" t="inlineStr"><is><t>zmniejszenie zapotrzebowania serca na tlen</t></is></c><c r="N1200" s="2" t="inlineStr" /><c r="O1200" s="2" t="inlineStr" /><c r="P1200" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1200" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="1201"><c r="A1201" s="2" t="inlineStr"><is><t>UKŁAD WSPÓŁCZULNY</t></is></c><c r="B1201" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C1201" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1201" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1201" s="2" t="inlineStr"><is><t>Nebiwolol:</t></is></c><c r="F1201" s="2" t="inlineStr"><is><t>aktywuje receptory beta-3 adrenergiczne</t></is></c><c r="G1201" s="2" t="inlineStr"><is><t>jest szczególnie przydatny u pacjentów z cukrzycą</t></is></c><c r="H1201" s="2" t="inlineStr" /><c r="I1201" s="2" t="inlineStr" /><c r="J1201" s="2" t="inlineStr" /><c r="K1201" s="2" t="inlineStr"><is><t>równie często jak inne beta-adrenolityki powoduje zaburzenia erekcji</t></is></c><c r="L1201" s="2" t="inlineStr"><is><t>wykazuje działanie antyoksydacyjne</t></is></c><c r="M1201" s="2" t="inlineStr" /><c r="N1201" s="2" t="inlineStr" /><c r="O1201" s="2" t="inlineStr" /><c r="P1201" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1201" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="1202"><c r="A1202" s="2" t="inlineStr"><is><t>NADCIŚNIENIE TĘTNICZE</t></is></c><c r="B1202" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C1202" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1202" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1202" s="2" t="inlineStr"><is><t>Nefroprotekcyjne działanie inhibitorów ACE wynika z:</t></is></c><c r="F1202" s="2" t="inlineStr"><is><t>rozkurczu naczyń odprowadzających kłębuszka nerkowego</t></is></c><c r="G1202" s="2" t="inlineStr"><is><t>zmniejszenia hiperfiltracji kłębuszkowej</t></is></c><c r="H1202" s="2" t="inlineStr" /><c r="I1202" s="2" t="inlineStr" /><c r="J1202" s="2" t="inlineStr" /><c r="K1202" s="2" t="inlineStr"><is><t>rozkurczu naczyń doprowadzających kłębuszka nerkowego</t></is></c><c r="L1202" s="2" t="inlineStr"><is><t>zahamowania aktywności współczulnej</t></is></c><c r="M1202" s="2" t="inlineStr" /><c r="N1202" s="2" t="inlineStr" /><c r="O1202" s="2" t="inlineStr" /><c r="P1202" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1202" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="1203"><c r="A1203" s="2" t="inlineStr"><is><t>NADCIŚNIENIE TĘTNICZE</t></is></c><c r="B1203" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C1203" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1203" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1203" s="2" t="inlineStr"><is><t>Do leków hamujących układ RAA należy:</t></is></c><c r="F1203" s="2" t="inlineStr"><is><t>metoprolol</t></is></c><c r="G1203" s="2" t="inlineStr"><is><t>eplerenon</t></is></c><c r="H1203" s="2" t="inlineStr" /><c r="I1203" s="2" t="inlineStr" /><c r="J1203" s="2" t="inlineStr" /><c r="K1203" s="2" t="inlineStr"><is><t>doksazosyna</t></is></c><c r="L1203" s="2" t="inlineStr"><is><t>urapidil</t></is></c><c r="M1203" s="2" t="inlineStr" /><c r="N1203" s="2" t="inlineStr" /><c r="O1203" s="2" t="inlineStr" /><c r="P1203" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1203" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="1204"><c r="A1204" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B1204" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C1204" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1204" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1204" s="2" t="inlineStr"><is><t>Do leków działających za pośrednictwem czynnika Xa należy:</t></is></c><c r="F1204" s="2" t="inlineStr"><is><t>enoksaparyna</t></is></c><c r="G1204" s="2" t="inlineStr"><is><t>fondaparynuks</t></is></c><c r="H1204" s="2" t="inlineStr"><is><t>rywaroksaban</t></is></c><c r="I1204" s="2" t="inlineStr" /><c r="J1204" s="2" t="inlineStr" /><c r="K1204" s="2" t="inlineStr"><is><t>dabigatran</t></is></c><c r="L1204" s="2" t="inlineStr" /><c r="M1204" s="2" t="inlineStr" /><c r="N1204" s="2" t="inlineStr" /><c r="O1204" s="2" t="inlineStr" /><c r="P1204" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1204" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="1205"><c r="A1205" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B1205" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C1205" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1205" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1205" s="2" t="inlineStr"><is><t>Jako profilaktykę przeciwzakrzepową udaru niedokrwiennego mózgu u pacjenta zmigotaniem przedsionków dopuszczalne jest zastosowanie:</t></is></c><c r="F1205" s="2" t="inlineStr"><is><t>fondaparynuksu</t></is></c><c r="G1205" s="2" t="inlineStr" /><c r="H1205" s="2" t="inlineStr" /><c r="I1205" s="2" t="inlineStr" /><c r="J1205" s="2" t="inlineStr" /><c r="K1205" s="2" t="inlineStr"><is><t>warfaryny</t></is></c><c r="L1205" s="2" t="inlineStr"><is><t>biwalirudyny</t></is></c><c r="M1205" s="2" t="inlineStr"><is><t>dabigatranu</t></is></c><c r="N1205" s="2" t="inlineStr" /><c r="O1205" s="2" t="inlineStr" /><c r="P1205" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1205" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="1206"><c r="A1206" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B1206" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C1206" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1206" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1206" s="2" t="inlineStr"><is><t>Tikagrelor:</t></is></c><c r="F1206" s="2" t="inlineStr"><is><t>odwracalnie blokuje receptor purynergiczny P2Y12</t></is></c><c r="G1206" s="2" t="inlineStr"><is><t>działa 3-4 dni</t></is></c><c r="H1206" s="2" t="inlineStr" /><c r="I1206" s="2" t="inlineStr" /><c r="J1206" s="2" t="inlineStr" /><c r="K1206" s="2" t="inlineStr"><is><t>jest lekiem prekursorowym</t></is></c><c r="L1206" s="2" t="inlineStr"><is><t>wymaga redukcji dawki w niewydolności nerek a – prawidłowe 1, 3 i 4 b – prawidłowe 1 i 3 c – prawidłowe 2 i 4 d – prawidłowa 4 e – wszystkie prawidłowe</t></is></c><c r="M1206" s="2" t="inlineStr" /><c r="N1206" s="2" t="inlineStr" /><c r="O1206" s="2" t="inlineStr" /><c r="P1206" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1206" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="1207"><c r="A1207" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B1207" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C1207" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1207" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1207" s="2" t="inlineStr"><is><t>Alteplaza:</t></is></c><c r="F1207" s="2" t="inlineStr"><is><t>może spowodować zaburzenia rytmu serca jako wynik reperfuzji w zawale serca</t></is></c><c r="G1207" s="2" t="inlineStr" /><c r="H1207" s="2" t="inlineStr" /><c r="I1207" s="2" t="inlineStr" /><c r="J1207" s="2" t="inlineStr" /><c r="K1207" s="2" t="inlineStr"><is><t>hamuje bezpośrednio plazminogen</t></is></c><c r="L1207" s="2" t="inlineStr"><is><t>jest silnie immunogenna</t></is></c><c r="M1207" s="2" t="inlineStr"><is><t>ma długi czas działania</t></is></c><c r="N1207" s="2" t="inlineStr" /><c r="O1207" s="2" t="inlineStr" /><c r="P1207" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1207" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="1208"><c r="A1208" s="2" t="inlineStr"><is><t>LEKI HIPOLIPEMIZUJĄCE</t></is></c><c r="B1208" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C1208" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1208" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1208" s="2" t="inlineStr"><is><t>Po zastosowaniu statyn obserwuje się:</t></is></c><c r="F1208" s="2" t="inlineStr"><is><t>zwiększenie liczby receptorów LDL</t></is></c><c r="G1208" s="2" t="inlineStr"><is><t>zwiększenie katabolizmu LDL</t></is></c><c r="H1208" s="2" t="inlineStr"><is><t>nasilenie wątrobowego wychwytu prekursorów LDL</t></is></c><c r="I1208" s="2" t="inlineStr"><is><t>zwiększenie stężenia HDL</t></is></c><c r="J1208" s="2" t="inlineStr" /><c r="K1208" s="2" t="inlineStr" /><c r="L1208" s="2" t="inlineStr" /><c r="M1208" s="2" t="inlineStr" /><c r="N1208" s="2" t="inlineStr" /><c r="O1208" s="2" t="inlineStr" /><c r="P1208" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1208" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="1209"><c r="A1209" s="2" t="inlineStr"><is><t>LEKI HIPOLIPEMIZUJĄCE</t></is></c><c r="B1209" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C1209" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1209" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1209" s="2" t="inlineStr"><is><t>Ezetymib:</t></is></c><c r="F1209" s="2" t="inlineStr"><is><t>zmniejsza stężenie cholesterolu LDL</t></is></c><c r="G1209" s="2" t="inlineStr"><is><t>hamuje wchłanianie cholesterolu z przewodu pokarmowego</t></is></c><c r="H1209" s="2" t="inlineStr" /><c r="I1209" s="2" t="inlineStr" /><c r="J1209" s="2" t="inlineStr" /><c r="K1209" s="2" t="inlineStr"><is><t>zmniejsza stężenie glukozy</t></is></c><c r="L1209" s="2" t="inlineStr"><is><t>zmniejsza stężenia triglicerydów</t></is></c><c r="M1209" s="2" t="inlineStr" /><c r="N1209" s="2" t="inlineStr" /><c r="O1209" s="2" t="inlineStr" /><c r="P1209" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1209" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="1210"><c r="A1210" s="2" t="inlineStr"><is><t>NIEWYDOLNOŚĆ SERCA</t></is></c><c r="B1210" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C1210" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1210" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1210" s="2" t="inlineStr"><is><t>Eplerenon jest:</t></is></c><c r="F1210" s="2" t="inlineStr"><is><t>diuretykiem oszczędzającym potas</t></is></c><c r="G1210" s="2" t="inlineStr"><is><t>bardziej selektywnym antagonistą aldosteronu niż spironolakton</t></is></c><c r="H1210" s="2" t="inlineStr" /><c r="I1210" s="2" t="inlineStr" /><c r="J1210" s="2" t="inlineStr" /><c r="K1210" s="2" t="inlineStr"><is><t>wskazany w leczeniu migotania przedsionków</t></is></c><c r="L1210" s="2" t="inlineStr"><is><t>przekształcany do aktywnego metabolitu – kanrenonu</t></is></c><c r="M1210" s="2" t="inlineStr" /><c r="N1210" s="2" t="inlineStr" /><c r="O1210" s="2" t="inlineStr" /><c r="P1210" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1210" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="1211"><c r="A1211" s="2" t="inlineStr"><is><t>NADCIŚNIENIE TĘTNICZE</t></is></c><c r="B1211" s="2" t="inlineStr"><is><t>Farmakokinetyka</t></is></c><c r="C1211" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1211" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1211" s="2" t="inlineStr"><is><t>Hydrochlorotiazyd:</t></is></c><c r="F1211" s="2" t="inlineStr"><is><t>zmniejsza wydalanie wapnia z moczem</t></is></c><c r="G1211" s="2" t="inlineStr"><is><t>może być stosowany w nerkopochodnej moczówce prostej</t></is></c><c r="H1211" s="2" t="inlineStr" /><c r="I1211" s="2" t="inlineStr" /><c r="J1211" s="2" t="inlineStr" /><c r="K1211" s="2" t="inlineStr"><is><t>jest lekiem podawanym dożylnie</t></is></c><c r="L1211" s="2" t="inlineStr"><is><t>zmniejsza wydalanie magnezu z moczem</t></is></c><c r="M1211" s="2" t="inlineStr" /><c r="N1211" s="2" t="inlineStr" /><c r="O1211" s="2" t="inlineStr" /><c r="P1211" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1211" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="1212"><c r="A1212" s="2" t="inlineStr"><is><t>LEKI MOCZOPĘDNE</t></is></c><c r="B1212" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C1212" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1212" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1212" s="2" t="inlineStr"><is><t>Zasadowicę metaboliczną mogą powodować:</t></is></c><c r="F1212" s="2" t="inlineStr"><is><t>tiazydy</t></is></c><c r="G1212" s="2" t="inlineStr" /><c r="H1212" s="2" t="inlineStr" /><c r="I1212" s="2" t="inlineStr" /><c r="J1212" s="2" t="inlineStr" /><c r="K1212" s="2" t="inlineStr"><is><t>inhibitory anhydrazy węglanowej</t></is></c><c r="L1212" s="2" t="inlineStr"><is><t>diuretyki pętlowe</t></is></c><c r="M1212" s="2" t="inlineStr"><is><t>diuretyki oszczędzające potas</t></is></c><c r="N1212" s="2" t="inlineStr" /><c r="O1212" s="2" t="inlineStr" /><c r="P1212" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1212" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="1213"><c r="A1213" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B1213" s="2" t="inlineStr"><is><t>Farmakokinetyka</t></is></c><c r="C1213" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1213" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1213" s="2" t="inlineStr"><is><t>W schyłkowej niewydolności wątroby dochodzi do zaburzeń:</t></is></c><c r="F1213" s="2" t="inlineStr"><is><t>wiązania leków z białkami</t></is></c><c r="G1213" s="2" t="inlineStr"><is><t>klirensu leków a – prawidłowe 1, 3 i 4 b – prawidłowe 1 i 3 c – prawidłowe 2 i 4 d – prawidłowa 4 e – wszystkie prawidłowe</t></is></c><c r="H1213" s="2" t="inlineStr" /><c r="I1213" s="2" t="inlineStr" /><c r="J1213" s="2" t="inlineStr" /><c r="K1213" s="2" t="inlineStr"><is><t>wchłaniania leków z przewodu pokarmowego</t></is></c><c r="L1213" s="2" t="inlineStr"><is><t>dystrybucji leków</t></is></c><c r="M1213" s="2" t="inlineStr" /><c r="N1213" s="2" t="inlineStr" /><c r="O1213" s="2" t="inlineStr" /><c r="P1213" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1213" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="1214"><c r="A1214" s="2" t="inlineStr"><is><t>STANY NAGŁE</t></is></c><c r="B1214" s="2" t="inlineStr"><is><t>Antidotum</t></is></c><c r="C1214" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1214" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1214" s="2" t="inlineStr"><is><t>Jeśli eGFR ≥ 60 ml/min to nastąpi kumulacja (przedawkowanie):</t></is></c><c r="F1214" s="2" t="inlineStr"><is><t>żadnego z wyżej wymienionych typów leków</t></is></c><c r="G1214" s="2" t="inlineStr" /><c r="H1214" s="2" t="inlineStr" /><c r="I1214" s="2" t="inlineStr" /><c r="J1214" s="2" t="inlineStr" /><c r="K1214" s="2" t="inlineStr"><is><t>leków wydalanych w &gt; 90% przez nerki</t></is></c><c r="L1214" s="2" t="inlineStr"><is><t>leków wymagających podawania dawki wysycającej</t></is></c><c r="M1214" s="2" t="inlineStr"><is><t>leków o bardzo wąskim wskaźniku terapeutycznym</t></is></c><c r="N1214" s="2" t="inlineStr" /><c r="O1214" s="2" t="inlineStr" /><c r="P1214" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1214" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="1215"><c r="A1215" s="2" t="inlineStr"><is><t>FARMAKOKINETYKA</t></is></c><c r="B1215" s="2" t="inlineStr"><is><t>Monitorowanie</t></is></c><c r="C1215" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1215" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1215" s="2" t="inlineStr"><is><t>Wskaż prawidłowe zasady prowadzenia terapii monitorowanej stężeniami leku:</t></is></c><c r="F1215" s="2" t="inlineStr"><is><t>oznaczenia należy wykonywać po osiągnięciu przez lek stanu stacjonarnego</t></is></c><c r="G1215" s="2" t="inlineStr"><is><t>w większości przypadków wystarczy oznaczenie całkowitego stężenia leku</t></is></c><c r="H1215" s="2" t="inlineStr"><is><t>w przypadku leków o kinetyce liniowej można wyliczyć modyfikację dawki na podstawie poprawnych pomiarów stężeń leku we krwi</t></is></c><c r="I1215" s="2" t="inlineStr" /><c r="J1215" s="2" t="inlineStr" /><c r="K1215" s="2" t="inlineStr"><is><t>pomiary należy wykonywać w połowie czasu między Cmax a Cmin</t></is></c><c r="L1215" s="2" t="inlineStr" /><c r="M1215" s="2" t="inlineStr" /><c r="N1215" s="2" t="inlineStr" /><c r="O1215" s="2" t="inlineStr" /><c r="P1215" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1215" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="1216"><c r="A1216" s="2" t="inlineStr"><is><t>UKŁAD WSPÓŁCZULNY</t></is></c><c r="B1216" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C1216" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1216" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1216" s="2" t="inlineStr"><is><t>Bromek ipratropium:</t></is></c><c r="F1216" s="2" t="inlineStr"><is><t>jest antagonistą receptora muskarynowego (M3)</t></is></c><c r="G1216" s="2" t="inlineStr"><is><t>rozkurcza mięśniówkę oskrzeli</t></is></c><c r="H1216" s="2" t="inlineStr" /><c r="I1216" s="2" t="inlineStr" /><c r="J1216" s="2" t="inlineStr" /><c r="K1216" s="2" t="inlineStr"><is><t>jest agonistą receptora beta 2 adrenergicznego</t></is></c><c r="L1216" s="2" t="inlineStr"><is><t>działa silnie przeciwzapalnie</t></is></c><c r="M1216" s="2" t="inlineStr" /><c r="N1216" s="2" t="inlineStr" /><c r="O1216" s="2" t="inlineStr" /><c r="P1216" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1216" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="1217"><c r="A1217" s="2" t="inlineStr"><is><t>UKŁAD ODDECHOWY</t></is></c><c r="B1217" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C1217" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1217" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1217" s="2" t="inlineStr"><is><t>Dekstrometorfan:</t></is></c><c r="F1217" s="2" t="inlineStr"><is><t>ma mały potencjał uzależniający</t></is></c><c r="G1217" s="2" t="inlineStr"><is><t>hamuje odruch kaszlowy</t></is></c><c r="H1217" s="2" t="inlineStr" /><c r="I1217" s="2" t="inlineStr" /><c r="J1217" s="2" t="inlineStr" /><c r="K1217" s="2" t="inlineStr"><is><t>jest lekiem wykrztuśnym</t></is></c><c r="L1217" s="2" t="inlineStr"><is><t>działa przeciwwymiotnie</t></is></c><c r="M1217" s="2" t="inlineStr" /><c r="N1217" s="2" t="inlineStr" /><c r="O1217" s="2" t="inlineStr" /><c r="P1217" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1217" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="1218"><c r="A1218" s="2" t="inlineStr"><is><t>UKŁAD ODDECHOWY</t></is></c><c r="B1218" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C1218" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1218" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1218" s="2" t="inlineStr"><is><t>N-acetylocysteina:</t></is></c><c r="F1218" s="2" t="inlineStr"><is><t>jest stosowana w zatruciu paracetamolem</t></is></c><c r="G1218" s="2" t="inlineStr"><is><t>może być stosowana dożylnie</t></is></c><c r="H1218" s="2" t="inlineStr"><is><t>działa mukolitycznie</t></is></c><c r="I1218" s="2" t="inlineStr" /><c r="J1218" s="2" t="inlineStr" /><c r="K1218" s="2" t="inlineStr"><is><t>jest przeciwwskazana w mukowiscydozie</t></is></c><c r="L1218" s="2" t="inlineStr" /><c r="M1218" s="2" t="inlineStr" /><c r="N1218" s="2" t="inlineStr" /><c r="O1218" s="2" t="inlineStr" /><c r="P1218" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1218" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="1219"><c r="A1219" s="2" t="inlineStr"><is><t>LEKI MOCZOPĘDNE</t></is></c><c r="B1219" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C1219" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1219" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1219" s="2" t="inlineStr"><is><t>W leczeniu jaskry ma zastosowanie:</t></is></c><c r="F1219" s="2" t="inlineStr"><is><t>tymolol</t></is></c><c r="G1219" s="2" t="inlineStr"><is><t>latanoprost</t></is></c><c r="H1219" s="2" t="inlineStr"><is><t>brymonidyna</t></is></c><c r="I1219" s="2" t="inlineStr"><is><t>dorzolamid</t></is></c><c r="J1219" s="2" t="inlineStr" /><c r="K1219" s="2" t="inlineStr" /><c r="L1219" s="2" t="inlineStr" /><c r="M1219" s="2" t="inlineStr" /><c r="N1219" s="2" t="inlineStr" /><c r="O1219" s="2" t="inlineStr" /><c r="P1219" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1219" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="1220"><c r="A1220" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B1220" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C1220" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1220" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1220" s="2" t="inlineStr"><is><t>Pozagałkowe zapalenie nerwu wzrokowego, grożące zanikiem nerwu wzrokowego i utratą wzroku, może być następstwem terapii:</t></is></c><c r="F1220" s="2" t="inlineStr"><is><t>etambutolem a – prawidłowe 1, 3 i 4 b – prawidłowe 1 i 3 c – prawidłowe 2 i 4 d – prawidłowa 4 e – wszystkie prawidłowe</t></is></c><c r="G1220" s="2" t="inlineStr" /><c r="H1220" s="2" t="inlineStr" /><c r="I1220" s="2" t="inlineStr" /><c r="J1220" s="2" t="inlineStr" /><c r="K1220" s="2" t="inlineStr"><is><t>ryfamipicyną</t></is></c><c r="L1220" s="2" t="inlineStr"><is><t>pirazynamidem</t></is></c><c r="M1220" s="2" t="inlineStr"><is><t>ofloksacyną</t></is></c><c r="N1220" s="2" t="inlineStr" /><c r="O1220" s="2" t="inlineStr" /><c r="P1220" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1220" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="1221"><c r="A1221" s="2" t="inlineStr"><is><t>LEKI PRZECIWPASOŻYTNICZE</t></is></c><c r="B1221" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C1221" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1221" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1221" s="2" t="inlineStr"><is><t>Dla korzystających z ofert last– minute, udających się w rejony endemiczne malarii w ramach tzw. szybkiej profilaktyki zalecana jest:</t></is></c><c r="F1221" s="2" t="inlineStr"><is><t>meflochina</t></is></c><c r="G1221" s="2" t="inlineStr"><is><t>chlorochina</t></is></c><c r="H1221" s="2" t="inlineStr" /><c r="I1221" s="2" t="inlineStr" /><c r="J1221" s="2" t="inlineStr" /><c r="K1221" s="2" t="inlineStr"><is><t>doksycyklina</t></is></c><c r="L1221" s="2" t="inlineStr"><is><t>atowakwon + proguanil</t></is></c><c r="M1221" s="2" t="inlineStr" /><c r="N1221" s="2" t="inlineStr" /><c r="O1221" s="2" t="inlineStr" /><c r="P1221" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1221" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="1222"><c r="A1222" s="2" t="inlineStr"><is><t>LEKI PRZECIWNOWOTWOROWE</t></is></c><c r="B1222" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C1222" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1222" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1222" s="2" t="inlineStr"><is><t>Zamiana automatyczna = substytucja, którą może przeprowadzić farmaceuta przy realizacji recepty, obejmuje preparaty zawierające:</t></is></c><c r="F1222" s="2" t="inlineStr"><is><t>ondansetron</t></is></c><c r="G1222" s="2" t="inlineStr" /><c r="H1222" s="2" t="inlineStr" /><c r="I1222" s="2" t="inlineStr" /><c r="J1222" s="2" t="inlineStr" /><c r="K1222" s="2" t="inlineStr"><is><t>epoetynę alfa</t></is></c><c r="L1222" s="2" t="inlineStr"><is><t>L-tyroksynę</t></is></c><c r="M1222" s="2" t="inlineStr"><is><t>filgrastym</t></is></c><c r="N1222" s="2" t="inlineStr" /><c r="O1222" s="2" t="inlineStr" /><c r="P1222" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1222" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="1223"><c r="A1223" s="2" t="inlineStr"><is><t>LEKI PRZECIWNOWOTWOROWE</t></is></c><c r="B1223" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C1223" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1223" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1223" s="2" t="inlineStr"><is><t>Inhibitorem kinazy białkowej BCR-ABL o przełomowym znaczeniu w leczeniu przewlekłej białaczki szpikowej jest/są:</t></is></c><c r="F1223" s="2" t="inlineStr"><is><t>imatinib</t></is></c><c r="G1223" s="2" t="inlineStr" /><c r="H1223" s="2" t="inlineStr" /><c r="I1223" s="2" t="inlineStr" /><c r="J1223" s="2" t="inlineStr" /><c r="K1223" s="2" t="inlineStr"><is><t>bortezomib</t></is></c><c r="L1223" s="2" t="inlineStr"><is><t>talidomid</t></is></c><c r="M1223" s="2" t="inlineStr"><is><t>azacytydyna</t></is></c><c r="N1223" s="2" t="inlineStr" /><c r="O1223" s="2" t="inlineStr" /><c r="P1223" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1223" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="1224"><c r="A1224" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B1224" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C1224" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1224" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1224" s="2" t="inlineStr"><is><t>Gentamicyna:</t></is></c><c r="F1224" s="2" t="inlineStr"><is><t>słabo wchłania się z przewodu pokarmowego</t></is></c><c r="G1224" s="2" t="inlineStr"><is><t>jest transportowana do wnętrza komórek w procesie zależnym od tlenu</t></is></c><c r="H1224" s="2" t="inlineStr"><is><t>wykazuje zależną od stężenia aktywność bakteriobójczą</t></is></c><c r="I1224" s="2" t="inlineStr"><is><t>może spowodować ostrą niewydolność nerek</t></is></c><c r="J1224" s="2" t="inlineStr" /><c r="K1224" s="2" t="inlineStr" /><c r="L1224" s="2" t="inlineStr" /><c r="M1224" s="2" t="inlineStr" /><c r="N1224" s="2" t="inlineStr" /><c r="O1224" s="2" t="inlineStr" /><c r="P1224" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1224" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="1225"><c r="A1225" s="2" t="inlineStr"><is><t>FARMAKOKINETYKA</t></is></c><c r="B1225" s="2" t="inlineStr"><is><t>Farmakokinetyka</t></is></c><c r="C1225" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1225" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1225" s="2" t="inlineStr"><is><t>Do określenia biodostępności leku po podaniu doustnym konieczna jestznajomość:</t></is></c><c r="F1225" s="2" t="inlineStr"><is><t>AUC 0→t po podaniu dożylnym</t></is></c><c r="G1225" s="2" t="inlineStr" /><c r="H1225" s="2" t="inlineStr" /><c r="I1225" s="2" t="inlineStr" /><c r="J1225" s="2" t="inlineStr" /><c r="K1225" s="2" t="inlineStr"><is><t>Cmax po podaniu dożylnym</t></is></c><c r="L1225" s="2" t="inlineStr"><is><t>radioaktywności tkankowej po podaniu leku znakowanego izotopem zdrowym ochotnikom</t></is></c><c r="M1225" s="2" t="inlineStr"><is><t>stopnia wchłaniania ksylozy</t></is></c><c r="N1225" s="2" t="inlineStr" /><c r="O1225" s="2" t="inlineStr" /><c r="P1225" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1225" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="1226"><c r="A1226" s="2" t="inlineStr"><is><t>FARMAKOKINETYKA</t></is></c><c r="B1226" s="2" t="inlineStr"><is><t>Farmakokinetyka</t></is></c><c r="C1226" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1226" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1226" s="2" t="inlineStr"><is><t>Kinetykę liniową charakteryzuje:</t></is></c><c r="F1226" s="2" t="inlineStr"><is><t>stały okres półtrwania procesu</t></is></c><c r="G1226" s="2" t="inlineStr"><is><t>stały skład metabolitów</t></is></c><c r="H1226" s="2" t="inlineStr" /><c r="I1226" s="2" t="inlineStr" /><c r="J1226" s="2" t="inlineStr" /><c r="K1226" s="2" t="inlineStr"><is><t>stałe AUC niezależne od dawki</t></is></c><c r="L1226" s="2" t="inlineStr"><is><t>stałe stężenie w stanie stacjonarnym niezależnie od dawki a – prawidłowe 1, 3 i 4 b – prawidłowe 1 i 3 c – prawidłowe 2 i 4 d – prawidłowa 4 e – wszystkie prawidłowe</t></is></c><c r="M1226" s="2" t="inlineStr" /><c r="N1226" s="2" t="inlineStr" /><c r="O1226" s="2" t="inlineStr" /><c r="P1226" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1226" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="1227"><c r="A1227" s="2" t="inlineStr"><is><t>LEKI MOCZOPĘDNE</t></is></c><c r="B1227" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C1227" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1227" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1227" s="2" t="inlineStr"><is><t>Wskazaniem do zastosowania wapnia jest:</t></is></c><c r="F1227" s="2" t="inlineStr"><is><t>ciężka hiperkaliemia</t></is></c><c r="G1227" s="2" t="inlineStr"><is><t>osteopenia</t></is></c><c r="H1227" s="2" t="inlineStr"><is><t>tężyczka</t></is></c><c r="I1227" s="2" t="inlineStr"><is><t>przewlekła niewydolność nerek ze skłonnością do hiperfosfatemii</t></is></c><c r="J1227" s="2" t="inlineStr" /><c r="K1227" s="2" t="inlineStr" /><c r="L1227" s="2" t="inlineStr" /><c r="M1227" s="2" t="inlineStr" /><c r="N1227" s="2" t="inlineStr" /><c r="O1227" s="2" t="inlineStr" /><c r="P1227" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1227" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="1228"><c r="A1228" s="2" t="inlineStr"><is><t>OSTEOPOROZA</t></is></c><c r="B1228" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C1228" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1228" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1228" s="2" t="inlineStr"><is><t>Witamina D:</t></is></c><c r="F1228" s="2" t="inlineStr"><is><t>ma działanie endokrynne</t></is></c><c r="G1228" s="2" t="inlineStr"><is><t>powszechne są jej pierwotne niedobory związane z małą ekspozycjąna promieniowanie UV</t></is></c><c r="H1228" s="2" t="inlineStr"><is><t>jej niedobór powoduje zwiększenie stężenia PTH</t></is></c><c r="I1228" s="2" t="inlineStr"><is><t>w monoterapii w dużych dawkach jest skuteczna w zapobieganiu osteoporotycznym złamaniom kości</t></is></c><c r="J1228" s="2" t="inlineStr" /><c r="K1228" s="2" t="inlineStr" /><c r="L1228" s="2" t="inlineStr" /><c r="M1228" s="2" t="inlineStr" /><c r="N1228" s="2" t="inlineStr" /><c r="O1228" s="2" t="inlineStr" /><c r="P1228" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1228" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="1229"><c r="A1229" s="2" t="inlineStr"><is><t>OSTEOPOROZA</t></is></c><c r="B1229" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C1229" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1229" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1229" s="2" t="inlineStr"><is><t>Zolendronian:</t></is></c><c r="F1229" s="2" t="inlineStr"><is><t>hamuje rekrutację i aktywność osteoklastów</t></is></c><c r="G1229" s="2" t="inlineStr"><is><t>wbudowuje się w kość i hamuje jej resorpcję</t></is></c><c r="H1229" s="2" t="inlineStr" /><c r="I1229" s="2" t="inlineStr" /><c r="J1229" s="2" t="inlineStr" /><c r="K1229" s="2" t="inlineStr"><is><t>jest antagonistą RANK (receptora aktywatora jądrowego czynnika kappa B)</t></is></c><c r="L1229" s="2" t="inlineStr"><is><t>pobudza replikację preosteoblastów</t></is></c><c r="M1229" s="2" t="inlineStr" /><c r="N1229" s="2" t="inlineStr" /><c r="O1229" s="2" t="inlineStr" /><c r="P1229" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1229" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="1230"><c r="A1230" s="2" t="inlineStr"><is><t>UKŁAD PRZYWSPÓŁCZULNY</t></is></c><c r="B1230" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C1230" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1230" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1230" s="2" t="inlineStr"><is><t>Przez barierę krew-mózg przenika:</t></is></c><c r="F1230" s="2" t="inlineStr"><is><t>atropina</t></is></c><c r="G1230" s="2" t="inlineStr"><is><t>skopolamina</t></is></c><c r="H1230" s="2" t="inlineStr" /><c r="I1230" s="2" t="inlineStr" /><c r="J1230" s="2" t="inlineStr" /><c r="K1230" s="2" t="inlineStr"><is><t>butylobromek hioscyny</t></is></c><c r="L1230" s="2" t="inlineStr"><is><t>ipratropium</t></is></c><c r="M1230" s="2" t="inlineStr" /><c r="N1230" s="2" t="inlineStr" /><c r="O1230" s="2" t="inlineStr" /><c r="P1230" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1230" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="1231"><c r="A1231" s="2" t="inlineStr"><is><t>UKŁAD WSPÓŁCZULNY</t></is></c><c r="B1231" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C1231" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1231" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1231" s="2" t="inlineStr"><is><t>W celu zahamowania czynności skurczowej macicy stosuje się:</t></is></c><c r="F1231" s="2" t="inlineStr"><is><t>fenoterol</t></is></c><c r="G1231" s="2" t="inlineStr" /><c r="H1231" s="2" t="inlineStr" /><c r="I1231" s="2" t="inlineStr" /><c r="J1231" s="2" t="inlineStr" /><c r="K1231" s="2" t="inlineStr"><is><t>ergometrynę</t></is></c><c r="L1231" s="2" t="inlineStr"><is><t>siarczan magnezu</t></is></c><c r="M1231" s="2" t="inlineStr"><is><t>atomoksetynę</t></is></c><c r="N1231" s="2" t="inlineStr" /><c r="O1231" s="2" t="inlineStr" /><c r="P1231" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1231" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="1232"><c r="A1232" s="2" t="inlineStr"><is><t>LEKI PRZECIWHISTAMINOWE</t></is></c><c r="B1232" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C1232" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1232" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1232" s="2" t="inlineStr"><is><t>Cetyryzyna:</t></is></c><c r="F1232" s="2" t="inlineStr"><is><t>selektywnie blokuje receptory H1</t></is></c><c r="G1232" s="2" t="inlineStr"><is><t>ma zastosowanie w leczeniu przewlekłego alergicznego nieżytu nosa</t></is></c><c r="H1232" s="2" t="inlineStr" /><c r="I1232" s="2" t="inlineStr" /><c r="J1232" s="2" t="inlineStr" /><c r="K1232" s="2" t="inlineStr"><is><t>dobrze przenika przez barierę krew- mózg</t></is></c><c r="L1232" s="2" t="inlineStr"><is><t>może być stosowana od 2 r. ż</t></is></c><c r="M1232" s="2" t="inlineStr" /><c r="N1232" s="2" t="inlineStr" /><c r="O1232" s="2" t="inlineStr" /><c r="P1232" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1232" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="1233"><c r="A1233" s="2" t="inlineStr"><is><t>LEKI PRZECIWHISTAMINOWE</t></is></c><c r="B1233" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C1233" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1233" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1233" s="2" t="inlineStr"><is><t>Leki drugiej generacji blokujące receptor H1 w porównaniu z lekami pierwszej generacji:</t></is></c><c r="F1233" s="2" t="inlineStr"><is><t>są w znaczącym stopniu pozbawione działania sedatywnego a – prawidłowe 1, 3 i 4 b – prawidłowe 1 i 3 c – prawidłowe 2 i 4 d – prawidłowa 4 e – wszystkie prawidłowe</t></is></c><c r="G1233" s="2" t="inlineStr" /><c r="H1233" s="2" t="inlineStr" /><c r="I1233" s="2" t="inlineStr" /><c r="J1233" s="2" t="inlineStr" /><c r="K1233" s="2" t="inlineStr"><is><t>działają dłużej</t></is></c><c r="L1233" s="2" t="inlineStr"><is><t>mogą być stosowane w postaci wstrzyknięć</t></is></c><c r="M1233" s="2" t="inlineStr"><is><t>są skuteczne w leczeniu pokrzywki idiopatycznej</t></is></c><c r="N1233" s="2" t="inlineStr" /><c r="O1233" s="2" t="inlineStr" /><c r="P1233" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1233" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="1234"><c r="A1234" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B1234" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C1234" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1234" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1234" s="2" t="inlineStr"><is><t>Uwalnianie histaminy zwiększa/ją:</t></is></c><c r="F1234" s="2" t="inlineStr"><is><t>wankomycyna</t></is></c><c r="G1234" s="2" t="inlineStr"><is><t>tubokuraryna</t></is></c><c r="H1234" s="2" t="inlineStr" /><c r="I1234" s="2" t="inlineStr" /><c r="J1234" s="2" t="inlineStr" /><c r="K1234" s="2" t="inlineStr"><is><t>środki cieniujące zawierające jod</t></is></c><c r="L1234" s="2" t="inlineStr"><is><t>morfina</t></is></c><c r="M1234" s="2" t="inlineStr" /><c r="N1234" s="2" t="inlineStr" /><c r="O1234" s="2" t="inlineStr" /><c r="P1234" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1234" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="1235"><c r="A1235" s="2" t="inlineStr"><is><t>UKŁAD PRZYWSPÓŁCZULNY</t></is></c><c r="B1235" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C1235" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1235" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1235" s="2" t="inlineStr"><is><t>Działanie cholinolityczne występuje po podaniu:</t></is></c><c r="F1235" s="2" t="inlineStr"><is><t>hydroksyzyny</t></is></c><c r="G1235" s="2" t="inlineStr" /><c r="H1235" s="2" t="inlineStr" /><c r="I1235" s="2" t="inlineStr" /><c r="J1235" s="2" t="inlineStr" /><c r="K1235" s="2" t="inlineStr"><is><t>haloperydolu</t></is></c><c r="L1235" s="2" t="inlineStr"><is><t>bilastyny</t></is></c><c r="M1235" s="2" t="inlineStr"><is><t>imipraminy</t></is></c><c r="N1235" s="2" t="inlineStr" /><c r="O1235" s="2" t="inlineStr" /><c r="P1235" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1235" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="1236"><c r="A1236" s="2" t="inlineStr"><is><t>LEKI PRZECIWNOWOTWOROWE</t></is></c><c r="B1236" s="2" t="inlineStr"><is><t>Farmakokinetyka</t></is></c><c r="C1236" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1236" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1236" s="2" t="inlineStr"><is><t>Metotreksat:</t></is></c><c r="F1236" s="2" t="inlineStr"><is><t>jest antymetabolitem</t></is></c><c r="G1236" s="2" t="inlineStr"><is><t>wykazuje działanie immunosupresyjne</t></is></c><c r="H1236" s="2" t="inlineStr"><is><t>jest wskazany do stosowania w łuszczycy</t></is></c><c r="I1236" s="2" t="inlineStr"><is><t>jest wskazany do stosowania w skojarzonym leczeniu wielolekowym ostrych białaczek</t></is></c><c r="J1236" s="2" t="inlineStr" /><c r="K1236" s="2" t="inlineStr" /><c r="L1236" s="2" t="inlineStr" /><c r="M1236" s="2" t="inlineStr" /><c r="N1236" s="2" t="inlineStr" /><c r="O1236" s="2" t="inlineStr" /><c r="P1236" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1236" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="1237"><c r="A1237" s="2" t="inlineStr"><is><t>LEKI IMMUNOSUPRESYJNE</t></is></c><c r="B1237" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C1237" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1237" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1237" s="2" t="inlineStr"><is><t>Humanizowanym przeciwciałem monoklonalnym, czyli przeciwciałem mającym w 90% sekwencję ludzką, jest:</t></is></c><c r="F1237" s="2" t="inlineStr"><is><t>daklizumab LEKI PRZECIWGRZYBICZE</t></is></c><c r="G1237" s="2" t="inlineStr" /><c r="H1237" s="2" t="inlineStr" /><c r="I1237" s="2" t="inlineStr" /><c r="J1237" s="2" t="inlineStr" /><c r="K1237" s="2" t="inlineStr"><is><t>rytuksymab</t></is></c><c r="L1237" s="2" t="inlineStr"><is><t>etanercept</t></is></c><c r="M1237" s="2" t="inlineStr"><is><t>adalimumab</t></is></c><c r="N1237" s="2" t="inlineStr" /><c r="O1237" s="2" t="inlineStr" /><c r="P1237" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1237" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="1238"><c r="A1238" s="2" t="inlineStr"><is><t>LEKI PRZECIWGRZYBICZE</t></is></c><c r="B1238" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C1238" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1238" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1238" s="2" t="inlineStr"><is><t>Flucytozyna</t></is></c><c r="F1238" s="2" t="inlineStr"><is><t>Ma ograniczone zastosowanie w monoterapi</t></is></c><c r="G1238" s="2" t="inlineStr"><is><t>Jest stosowana w s kojarzeniu z lekami wypływającymi na intergralność błony komótkowej</t></is></c><c r="H1238" s="2" t="inlineStr"><is><t>Przekształcona jest do 5- fluorouracylu, który jest wbudowywany w miejsce uracylu w rna co zaburza syntezę białek</t></is></c><c r="I1238" s="2" t="inlineStr"><is><t>Dobrze penetruje do oun</t></is></c><c r="J1238" s="2" t="inlineStr" /><c r="K1238" s="2" t="inlineStr"><is><t>Ma bardzo szeroki zakres działania</t></is></c><c r="L1238" s="2" t="inlineStr" /><c r="M1238" s="2" t="inlineStr" /><c r="N1238" s="2" t="inlineStr" /><c r="O1238" s="2" t="inlineStr" /><c r="P1238" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1238" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="1239"><c r="A1239" s="2" t="inlineStr"><is><t>LEKI PRZECIWGRZYBICZE</t></is></c><c r="B1239" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C1239" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1239" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1239" s="2" t="inlineStr"><is><t>Lekiem który zastosujesz w leczeniu doustnej grzybicy paznikciowej jest</t></is></c><c r="F1239" s="2" t="inlineStr"><is><t>Flukonazol</t></is></c><c r="G1239" s="2" t="inlineStr"><is><t>Terbinafina</t></is></c><c r="H1239" s="2" t="inlineStr"><is><t>Itrakonazol</t></is></c><c r="I1239" s="2" t="inlineStr" /><c r="J1239" s="2" t="inlineStr" /><c r="K1239" s="2" t="inlineStr"><is><t>Amorolfina</t></is></c><c r="L1239" s="2" t="inlineStr" /><c r="M1239" s="2" t="inlineStr" /><c r="N1239" s="2" t="inlineStr" /><c r="O1239" s="2" t="inlineStr" /><c r="P1239" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1239" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="1240"><c r="A1240" s="2" t="inlineStr"><is><t>LEKI PRZECIWGRZYBICZE</t></is></c><c r="B1240" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C1240" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1240" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1240" s="2" t="inlineStr"><is><t>W leczeniu zakażenia OUN zastosujesz</t></is></c><c r="F1240" s="2" t="inlineStr"><is><t>Amfoterycyne B w kompleksach lipidowych</t></is></c><c r="G1240" s="2" t="inlineStr"><is><t>Liposomalną amfoterycynę B</t></is></c><c r="H1240" s="2" t="inlineStr" /><c r="I1240" s="2" t="inlineStr" /><c r="J1240" s="2" t="inlineStr" /><c r="K1240" s="2" t="inlineStr"><is><t>Klasyczną amfoterycynę B</t></is></c><c r="L1240" s="2" t="inlineStr"><is><t>Kaspofunginę</t></is></c><c r="M1240" s="2" t="inlineStr" /><c r="N1240" s="2" t="inlineStr" /><c r="O1240" s="2" t="inlineStr" /><c r="P1240" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1240" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="1241"><c r="A1241" s="2" t="inlineStr"><is><t>LEKI PRZECIWGRZYBICZE</t></is></c><c r="B1241" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C1241" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1241" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1241" s="2" t="inlineStr"><is><t>Wskazaniem do doustnej terapii p-grzybiczej jest</t></is></c><c r="F1241" s="2" t="inlineStr"><is><t>Rozległe zmiany skórne</t></is></c><c r="G1241" s="2" t="inlineStr"><is><t>Nieskuteczność leczenia miejscowego</t></is></c><c r="H1241" s="2" t="inlineStr"><is><t>Grzybica inwazyjna</t></is></c><c r="I1241" s="2" t="inlineStr" /><c r="J1241" s="2" t="inlineStr" /><c r="K1241" s="2" t="inlineStr"><is><t>Grzybica paznokci pojedynczych płytek paznokciowych zlokalizowanych na powierzchni płytki paznokciowej i ograniczonej do dystalnej płytki paznokcia</t></is></c><c r="L1241" s="2" t="inlineStr" /><c r="M1241" s="2" t="inlineStr" /><c r="N1241" s="2" t="inlineStr" /><c r="O1241" s="2" t="inlineStr" /><c r="P1241" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1241" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="1242"><c r="A1242" s="2" t="inlineStr"><is><t>LEKI PRZECIWGRZYBICZE</t></is></c><c r="B1242" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C1242" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1242" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1242" s="2" t="inlineStr"><is><t>Liposomalna postać amfoterycyny b w porównaniu do konwencjonalnej</t></is></c><c r="F1242" s="2" t="inlineStr"><is><t>Może być stosowana w grzybiczych zakażeniach oun</t></is></c><c r="G1242" s="2" t="inlineStr"><is><t>W mniejszym stopniu zaburza czynność nerek</t></is></c><c r="H1242" s="2" t="inlineStr"><is><t>Może być stosowana w większych dawakach</t></is></c><c r="I1242" s="2" t="inlineStr" /><c r="J1242" s="2" t="inlineStr" /><c r="K1242" s="2" t="inlineStr"><is><t>W miniejszym stopniu zaburza czynność wątroby</t></is></c><c r="L1242" s="2" t="inlineStr"><is><t>Ma szeresze spektrum</t></is></c><c r="M1242" s="2" t="inlineStr" /><c r="N1242" s="2" t="inlineStr" /><c r="O1242" s="2" t="inlineStr" /><c r="P1242" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1242" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="1243"><c r="A1243" s="2" t="inlineStr"><is><t>LEKI PRZECIWGRZYBICZE</t></is></c><c r="B1243" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C1243" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1243" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1243" s="2" t="inlineStr"><is><t>Który z azoli nie wymaga korekcji w niewydolności nerek gfr</t></is></c><c r="F1243" s="2" t="inlineStr"><is><t>Izawukonazol</t></is></c><c r="G1243" s="2" t="inlineStr"><is><t>Worykonazol</t></is></c><c r="H1243" s="2" t="inlineStr"><is><t>Pozakonazol</t></is></c><c r="I1243" s="2" t="inlineStr" /><c r="J1243" s="2" t="inlineStr" /><c r="K1243" s="2" t="inlineStr"><is><t>Flukonazol</t></is></c><c r="L1243" s="2" t="inlineStr" /><c r="M1243" s="2" t="inlineStr" /><c r="N1243" s="2" t="inlineStr" /><c r="O1243" s="2" t="inlineStr" /><c r="P1243" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1243" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="1244"><c r="A1244" s="2" t="inlineStr"><is><t>LEKI PRZECIWGRZYBICZE</t></is></c><c r="B1244" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C1244" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1244" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1244" s="2" t="inlineStr"><is><t>W leczeniu zakażenia układu moczowego Candida Crusei</t></is></c><c r="F1244" s="2" t="inlineStr"><is><t>Klasyczyna amfoterycyna b</t></is></c><c r="G1244" s="2" t="inlineStr" /><c r="H1244" s="2" t="inlineStr" /><c r="I1244" s="2" t="inlineStr" /><c r="J1244" s="2" t="inlineStr" /><c r="K1244" s="2" t="inlineStr"><is><t>Kaspofungine</t></is></c><c r="L1244" s="2" t="inlineStr"><is><t>Amfoterycyne b w kompleksach lipidowych</t></is></c><c r="M1244" s="2" t="inlineStr"><is><t>Liposomalna amfoterycyne b</t></is></c><c r="N1244" s="2" t="inlineStr" /><c r="O1244" s="2" t="inlineStr" /><c r="P1244" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1244" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="1245"><c r="A1245" s="2" t="inlineStr"><is><t>LEKI PRZECIWGRZYBICZE</t></is></c><c r="B1245" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C1245" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1245" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1245" s="2" t="inlineStr"><is><t>Które z leków ma zastosowanie w leczeniu grzybicy głębokiej aspergillus</t></is></c><c r="F1245" s="2" t="inlineStr"><is><t>Worykonazol</t></is></c><c r="G1245" s="2" t="inlineStr"><is><t>kaspofungina PRZEWÓD POKARMOWY</t></is></c><c r="H1245" s="2" t="inlineStr" /><c r="I1245" s="2" t="inlineStr" /><c r="J1245" s="2" t="inlineStr" /><c r="K1245" s="2" t="inlineStr"><is><t>Flukonazol</t></is></c><c r="L1245" s="2" t="inlineStr"><is><t>Ketokonazol</t></is></c><c r="M1245" s="2" t="inlineStr"><is><t>Nystatyna</t></is></c><c r="N1245" s="2" t="inlineStr" /><c r="O1245" s="2" t="inlineStr" /><c r="P1245" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1245" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="1246"><c r="A1246" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B1246" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C1246" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1246" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1246" s="2" t="inlineStr"><is><t>Schemat eradykacji helocobacter pylori</t></is></c><c r="F1246" s="2" t="inlineStr"><is><t>Przynajmniej 2 leków przeciwbakteryjnych</t></is></c><c r="G1246" s="2" t="inlineStr"><is><t>IPP w podwójnej dawce</t></is></c><c r="H1246" s="2" t="inlineStr"><is><t>Soli bizmutu</t></is></c><c r="I1246" s="2" t="inlineStr" /><c r="J1246" s="2" t="inlineStr" /><c r="K1246" s="2" t="inlineStr"><is><t>Leku neutralizaującego</t></is></c><c r="L1246" s="2" t="inlineStr"><is><t>Antagonisty recptora histaminowego H2</t></is></c><c r="M1246" s="2" t="inlineStr"><is><t>Neomycyny</t></is></c><c r="N1246" s="2" t="inlineStr"><is><t>Sukralfatu</t></is></c><c r="O1246" s="2" t="inlineStr" /><c r="P1246" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1246" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="1247"><c r="A1247" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B1247" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C1247" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1247" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1247" s="2" t="inlineStr"><is><t>Właściwe dla pankreatyny</t></is></c><c r="F1247" s="2" t="inlineStr"><is><t>Nie powinna być stosowana w ostrym zap trzustku</t></is></c><c r="G1247" s="2" t="inlineStr"><is><t>Zawiera lipazę amylazę i proteazę</t></is></c><c r="H1247" s="2" t="inlineStr" /><c r="I1247" s="2" t="inlineStr" /><c r="J1247" s="2" t="inlineStr" /><c r="K1247" s="2" t="inlineStr"><is><t>Jest stosowana w niewydolności trzustki w przebiegu mukowiscydozy</t></is></c><c r="L1247" s="2" t="inlineStr"><is><t>Jest podawana doustnie i parenteralnie</t></is></c><c r="M1247" s="2" t="inlineStr"><is><t>Dawkowanie należy ustalić indywidualnie zależnie od masy ciała pacjenta</t></is></c><c r="N1247" s="2" t="inlineStr" /><c r="O1247" s="2" t="inlineStr" /><c r="P1247" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1247" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="1248"><c r="A1248" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B1248" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C1248" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1248" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1248" s="2" t="inlineStr"><is><t>Wskaż prawidłowe połączenie lek – mechanizm</t></is></c><c r="F1248" s="2" t="inlineStr"><is><t>Itopryd – antagonista D2</t></is></c><c r="G1248" s="2" t="inlineStr"><is><t>Cyzapryd – agonista 5-HT4</t></is></c><c r="H1248" s="2" t="inlineStr" /><c r="I1248" s="2" t="inlineStr" /><c r="J1248" s="2" t="inlineStr" /><c r="K1248" s="2" t="inlineStr"><is><t>Loperamid – antagonista opioidowych</t></is></c><c r="L1248" s="2" t="inlineStr"><is><t>Famotydyna – agonista H2</t></is></c><c r="M1248" s="2" t="inlineStr" /><c r="N1248" s="2" t="inlineStr" /><c r="O1248" s="2" t="inlineStr" /><c r="P1248" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1248" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="1249"><c r="A1249" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B1249" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C1249" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1249" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1249" s="2" t="inlineStr"><is><t>Wskaż prawidłowe</t></is></c><c r="F1249" s="2" t="inlineStr"><is><t>Leczenie zaparć większości przypadków polega na zastosowaniu własciewej diety i stylu życia</t></is></c><c r="G1249" s="2" t="inlineStr"><is><t>Środki przeczyszczające różnią się między sobą miejscem działania</t></is></c><c r="H1249" s="2" t="inlineStr" /><c r="I1249" s="2" t="inlineStr" /><c r="J1249" s="2" t="inlineStr" /><c r="K1249" s="2" t="inlineStr"><is><t>Przwelekłe stosowanie opiodów to przeciwskazanie do leków przeczyszczających</t></is></c><c r="L1249" s="2" t="inlineStr"><is><t>Zaparcia nawykowe są wskazaniem do leków przeczyszczających</t></is></c><c r="M1249" s="2" t="inlineStr"><is><t>Leki przeczyszczające działają przyczynowo</t></is></c><c r="N1249" s="2" t="inlineStr" /><c r="O1249" s="2" t="inlineStr" /><c r="P1249" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1249" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="1250"><c r="A1250" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B1250" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C1250" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1250" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1250" s="2" t="inlineStr"><is><t>Wskaż prawdziwe</t></is></c><c r="F1250" s="2" t="inlineStr"><is><t>Odwar z kory dębu stosowany do płukania jamy ustnej działa ściągająco</t></is></c><c r="G1250" s="2" t="inlineStr" /><c r="H1250" s="2" t="inlineStr" /><c r="I1250" s="2" t="inlineStr" /><c r="J1250" s="2" t="inlineStr" /><c r="K1250" s="2" t="inlineStr"><is><t>Odwar z kory kruszyny działa zapierająco</t></is></c><c r="L1250" s="2" t="inlineStr"><is><t>Wyciąg z czarnej rzodkwi łagodzi dolegliwości w zaostrzeniu kamnicy żółciowej</t></is></c><c r="M1250" s="2" t="inlineStr"><is><t>Wyciag z karczocha działa regenerująco na hepatocyty</t></is></c><c r="N1250" s="2" t="inlineStr" /><c r="O1250" s="2" t="inlineStr" /><c r="P1250" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1250" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="1251"><c r="A1251" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B1251" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C1251" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1251" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1251" s="2" t="inlineStr"><is><t>Leki osłaniające nie nadają się do ambulatoryjnego leczenia owrzodzenia żołądka</t></is></c><c r="F1251" s="2" t="inlineStr"><is><t>Wymagają ścisłego reżimu dawkowania powyżej 4 razy na dobę, na czczo</t></is></c><c r="G1251" s="2" t="inlineStr" /><c r="H1251" s="2" t="inlineStr" /><c r="I1251" s="2" t="inlineStr" /><c r="J1251" s="2" t="inlineStr" /><c r="K1251" s="2" t="inlineStr"><is><t>Są silnie toksyczne nawet u pacjentów z prawidłową czynnościa nerek</t></is></c><c r="L1251" s="2" t="inlineStr"><is><t>Są nieskuteczne</t></is></c><c r="M1251" s="2" t="inlineStr"><is><t>Za drogie</t></is></c><c r="N1251" s="2" t="inlineStr"><is><t>Powodują kolonializację przez helicobacter</t></is></c><c r="O1251" s="2" t="inlineStr" /><c r="P1251" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1251" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="1252"><c r="A1252" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B1252" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C1252" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1252" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1252" s="2" t="inlineStr"><is><t>Wskaż wskazania do wyższych niż standarowe dawki ipp</t></is></c><c r="F1252" s="2" t="inlineStr"><is><t>Gastinoma</t></is></c><c r="G1252" s="2" t="inlineStr"><is><t>Krawaienie z przewodu pokarmowego</t></is></c><c r="H1252" s="2" t="inlineStr"><is><t>Eradykacja helicobacter</t></is></c><c r="I1252" s="2" t="inlineStr" /><c r="J1252" s="2" t="inlineStr" /><c r="K1252" s="2" t="inlineStr"><is><t>Zapalenie przełyku</t></is></c><c r="L1252" s="2" t="inlineStr"><is><t>Dyspepsja</t></is></c><c r="M1252" s="2" t="inlineStr" /><c r="N1252" s="2" t="inlineStr" /><c r="O1252" s="2" t="inlineStr" /><c r="P1252" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1252" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="1253"><c r="A1253" s="2" t="inlineStr"><is><t>LEKI HIPOLIPEMIZUJĄCE</t></is></c><c r="B1253" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C1253" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1253" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1253" s="2" t="inlineStr"><is><t>Ryzyko miopatii i rabdomiolizy w stosowaniu symwastatyny wzzrasta w przypadku</t></is></c><c r="F1253" s="2" t="inlineStr"><is><t>Jednoczesnego stosowania klarytomycyny</t></is></c><c r="G1253" s="2" t="inlineStr"><is><t>Stosowaniu max dawki terepeutycznej</t></is></c><c r="H1253" s="2" t="inlineStr"><is><t>Jednoczesne stosowanie posakonazolu</t></is></c><c r="I1253" s="2" t="inlineStr"><is><t>Nadużywanie alkoholu</t></is></c><c r="J1253" s="2" t="inlineStr" /><c r="K1253" s="2" t="inlineStr"><is><t>Nadczynoości tarczycy</t></is></c><c r="L1253" s="2" t="inlineStr"><is><t>Palenia tytoniu</t></is></c><c r="M1253" s="2" t="inlineStr"><is><t>Młodych mężczyzn</t></is></c><c r="N1253" s="2" t="inlineStr" /><c r="O1253" s="2" t="inlineStr" /><c r="P1253" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1253" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="1254"><c r="A1254" s="2" t="inlineStr"><is><t>LEKI HIPOLIPEMIZUJĄCE</t></is></c><c r="B1254" s="2" t="inlineStr"><is><t>Monitorowanie</t></is></c><c r="C1254" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1254" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1254" s="2" t="inlineStr"><is><t>Prawidłowe stwierdzenie</t></is></c><c r="F1254" s="2" t="inlineStr"><is><t>Maksymalny wpływ statyny w określonej dawce na stężenie ldl-c w surowicy zostaje osiągnięty po 7-10 dniach jej stosowania</t></is></c><c r="G1254" s="2" t="inlineStr"><is><t>Ryzyko uszkodzenia mięśni szkieletowych przez statyny zwiększa się wraz ze stosowaną dawką</t></is></c><c r="H1254" s="2" t="inlineStr"><is><t>Przed włączeniem statyny należy oznaczyć aktywność aminotranswerazy alaninowej alat w surowicy, ale potem monitorowanie wątrobowych testów nie jest zalecane</t></is></c><c r="I1254" s="2" t="inlineStr" /><c r="J1254" s="2" t="inlineStr" /><c r="K1254" s="2" t="inlineStr"><is><t>Statyny działają równie skurczenie u wszystkich chorych w tym także u pacjentów z homozygotyczną postacią rodzinnej hipercholesterolemii</t></is></c><c r="L1254" s="2" t="inlineStr"><is><t>Dołączenie fibratów lub pochodnych niacyny do statyn zmniejsza ryzyko powikłań sercowo naczyniowych w porównaniu z monoterapią statyną</t></is></c><c r="M1254" s="2" t="inlineStr" /><c r="N1254" s="2" t="inlineStr" /><c r="O1254" s="2" t="inlineStr" /><c r="P1254" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1254" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="1255"><c r="A1255" s="2" t="inlineStr"><is><t>LEKI HIPOLIPEMIZUJĄCE</t></is></c><c r="B1255" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C1255" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1255" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1255" s="2" t="inlineStr"><is><t>Wskaż prawdziwe na temat inhibitorów pcsk9</t></is></c><c r="F1255" s="2" t="inlineStr"><is><t>Stanowią istotną opcję terapeutyczną u pacjentów z hipercholesterolemią, którzy nie mogą statyn</t></is></c><c r="G1255" s="2" t="inlineStr"><is><t>Powodują zwiększanie gęstości rec dla ldl na hepatocytach</t></is></c><c r="H1255" s="2" t="inlineStr"><is><t>Sa przeciwciałami monoklonalnymi</t></is></c><c r="I1255" s="2" t="inlineStr" /><c r="J1255" s="2" t="inlineStr" /><c r="K1255" s="2" t="inlineStr"><is><t>Wchodzą w wiele interakcji</t></is></c><c r="L1255" s="2" t="inlineStr"><is><t>Najskuteczniej wśród leków hipolipomiczujących zmniejszają stężenie TG w surowicy</t></is></c><c r="M1255" s="2" t="inlineStr" /><c r="N1255" s="2" t="inlineStr" /><c r="O1255" s="2" t="inlineStr" /><c r="P1255" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1255" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="1256"><c r="A1256" s="2" t="inlineStr"><is><t>LEKI HIPOLIPEMIZUJĄCE</t></is></c><c r="B1256" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C1256" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1256" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1256" s="2" t="inlineStr"><is><t>Spadek ldl o 50% tg o 25% i hdl wzsot o 10 % można się spodziewać po zastosowaniu odpowiedniej dawki</t></is></c><c r="F1256" s="2" t="inlineStr"><is><t>Rozuwastatyny</t></is></c><c r="G1256" s="2" t="inlineStr" /><c r="H1256" s="2" t="inlineStr" /><c r="I1256" s="2" t="inlineStr" /><c r="J1256" s="2" t="inlineStr" /><c r="K1256" s="2" t="inlineStr"><is><t>DHA + EPA</t></is></c><c r="L1256" s="2" t="inlineStr"><is><t>Ezetymib</t></is></c><c r="M1256" s="2" t="inlineStr"><is><t>Fenofibratu</t></is></c><c r="N1256" s="2" t="inlineStr"><is><t>Kolesewelamu</t></is></c><c r="O1256" s="2" t="inlineStr" /><c r="P1256" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1256" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="1257"><c r="A1257" s="2" t="inlineStr"><is><t>LEKI HIPOLIPEMIZUJĄCE</t></is></c><c r="B1257" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C1257" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1257" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1257" s="2" t="inlineStr"><is><t>Łączne zastosowanie symwastatyny i flukonazolu</t></is></c><c r="F1257" s="2" t="inlineStr"><is><t>Wpływa istitnie na ryzyko wystąpienie działań niepożądach statyny</t></is></c><c r="G1257" s="2" t="inlineStr" /><c r="H1257" s="2" t="inlineStr" /><c r="I1257" s="2" t="inlineStr" /><c r="J1257" s="2" t="inlineStr" /><c r="K1257" s="2" t="inlineStr"><is><t>Może spowodować niebezpieczne dla życia zaburzenia rytmu serca</t></is></c><c r="L1257" s="2" t="inlineStr"><is><t>Wiąże się ze zmniejszeniem skutecznego leczenia przeciwgrzybiczego w wyniku zmniejszania działania flukonazolu</t></is></c><c r="M1257" s="2" t="inlineStr"><is><t>Wiąże się ze zwiększonym ryzykiem rabdomiolizy w wyniku indukcji metabolizmu statyny do aktywnych metabolitów</t></is></c><c r="N1257" s="2" t="inlineStr" /><c r="O1257" s="2" t="inlineStr" /><c r="P1257" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1257" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="1258"><c r="A1258" s="2" t="inlineStr"><is><t>LEKI PRZECIWDEPRESYJNE</t></is></c><c r="B1258" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C1258" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1258" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1258" s="2" t="inlineStr"><is><t>Zmniejszenia masy ciała można się spodziewać w trakcie stosowania</t></is></c><c r="F1258" s="2" t="inlineStr"><is><t>Bupropionu</t></is></c><c r="G1258" s="2" t="inlineStr"><is><t>Marihuany leczniczej</t></is></c><c r="H1258" s="2" t="inlineStr"><is><t>Metforminy</t></is></c><c r="I1258" s="2" t="inlineStr" /><c r="J1258" s="2" t="inlineStr" /><c r="K1258" s="2" t="inlineStr"><is><t>Prednizonu</t></is></c><c r="L1258" s="2" t="inlineStr"><is><t>L- karnityny</t></is></c><c r="M1258" s="2" t="inlineStr"><is><t>Rysperydonu</t></is></c><c r="N1258" s="2" t="inlineStr"><is><t>Sertraliny</t></is></c><c r="O1258" s="2" t="inlineStr" /><c r="P1258" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1258" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="1259"><c r="A1259" s="2" t="inlineStr"><is><t>LEKI HIPOLIPEMIZUJĄCE</t></is></c><c r="B1259" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C1259" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1259" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1259" s="2" t="inlineStr"><is><t>Ezetymib zastosujesz w hipercholesterolemii</t></is></c><c r="F1259" s="2" t="inlineStr"><is><t>W skojarzeniu ze statynami</t></is></c><c r="G1259" s="2" t="inlineStr"><is><t>W monoterapii jak nie można statyn</t></is></c><c r="H1259" s="2" t="inlineStr"><is><t>Jeśli stosowanie statyny w maxymalnej dawce nie daje pożądanego efektu</t></is></c><c r="I1259" s="2" t="inlineStr" /><c r="J1259" s="2" t="inlineStr" /><c r="K1259" s="2" t="inlineStr"><is><t>Jako lek pierwszego rzutu</t></is></c><c r="L1259" s="2" t="inlineStr"><is><t>W skojarzeniu z fibratami</t></is></c><c r="M1259" s="2" t="inlineStr"><is><t>Jeśli stosowanie 2 statyn nie daje pożądanego efektu</t></is></c><c r="N1259" s="2" t="inlineStr" /><c r="O1259" s="2" t="inlineStr" /><c r="P1259" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1259" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="1260"><c r="A1260" s="2" t="inlineStr"><is><t>FARMAKOKINETYKA</t></is></c><c r="B1260" s="2" t="inlineStr"><is><t>Interakcje</t></is></c><c r="C1260" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1260" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1260" s="2" t="inlineStr"><is><t>Statyny istonie różnią się farmakologicznie i klinicznie</t></is></c><c r="F1260" s="2" t="inlineStr"><is><t>T1/2 co ma wpływ na chronofarmakoterapię – wieczorem lub bez względu na porę dnia</t></is></c><c r="G1260" s="2" t="inlineStr"><is><t>Eliminacją przez nerki w postaci niezmienionej co ma wpływ na wybór w przewlekłej chorobie nerek</t></is></c><c r="H1260" s="2" t="inlineStr"><is><t>Metabolizmem przez cyp3a4 co ma wpływ na interakcje lekowe prowadzącej do miopatii</t></is></c><c r="I1260" s="2" t="inlineStr" /><c r="J1260" s="2" t="inlineStr" /><c r="K1260" s="2" t="inlineStr"><is><t>Lipofilnościa co ma wpływ na ich biodostępność</t></is></c><c r="L1260" s="2" t="inlineStr"><is><t>Wiązaniem z białkami krwi co ma wpływ na rozwój cukrzycy polekowej</t></is></c><c r="M1260" s="2" t="inlineStr" /><c r="N1260" s="2" t="inlineStr" /><c r="O1260" s="2" t="inlineStr" /><c r="P1260" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1260" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="1261"><c r="A1261" s="2" t="inlineStr"><is><t>TARCZYCA</t></is></c><c r="B1261" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C1261" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1261" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1261" s="2" t="inlineStr"><is><t>Farmakologiczne leczenie otyłości</t></is></c><c r="F1261" s="2" t="inlineStr"><is><t>Miraglutyd</t></is></c><c r="G1261" s="2" t="inlineStr"><is><t>Orlistat</t></is></c><c r="H1261" s="2" t="inlineStr" /><c r="I1261" s="2" t="inlineStr" /><c r="J1261" s="2" t="inlineStr" /><c r="K1261" s="2" t="inlineStr"><is><t>Deksfenfluraminę</t></is></c><c r="L1261" s="2" t="inlineStr"><is><t>Sibutraminę</t></is></c><c r="M1261" s="2" t="inlineStr"><is><t>Lewotyroksynę</t></is></c><c r="N1261" s="2" t="inlineStr" /><c r="O1261" s="2" t="inlineStr" /><c r="P1261" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1261" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="1262"><c r="A1262" s="2" t="inlineStr"><is><t>LEKI HIPOLIPEMIZUJĄCE</t></is></c><c r="B1262" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C1262" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1262" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1262" s="2" t="inlineStr"><is><t>Działanie plejotropowe statyn wynika z</t></is></c><c r="F1262" s="2" t="inlineStr"><is><t>Zwiększenie stntezty NO</t></is></c><c r="G1262" s="2" t="inlineStr"><is><t>Korzystny wpływ na hemostazę</t></is></c><c r="H1262" s="2" t="inlineStr"><is><t>Hamowanie syntezty IL – 6 I TNFalfa ODDECHOWE</t></is></c><c r="I1262" s="2" t="inlineStr" /><c r="J1262" s="2" t="inlineStr" /><c r="K1262" s="2" t="inlineStr"><is><t>Zwiększenie stęż białka c reaktywnego</t></is></c><c r="L1262" s="2" t="inlineStr"><is><t>Zwiększenie aktywności NK</t></is></c><c r="M1262" s="2" t="inlineStr" /><c r="N1262" s="2" t="inlineStr" /><c r="O1262" s="2" t="inlineStr" /><c r="P1262" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1262" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="1263"><c r="A1263" s="2" t="inlineStr"><is><t>UKŁAD ODDECHOWY</t></is></c><c r="B1263" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C1263" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1263" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1263" s="2" t="inlineStr"><is><t>Wskaż prawdziwe omalizumab</t></is></c><c r="F1263" s="2" t="inlineStr"><is><t>To rekombinowane humanizowane przeciwciało monoklonalne przeciwko ige</t></is></c><c r="G1263" s="2" t="inlineStr"><is><t>Zmniejsza liczbę zaostrzeń i hospitalizacji w ciężkiej astmie alergicznej</t></is></c><c r="H1263" s="2" t="inlineStr" /><c r="I1263" s="2" t="inlineStr" /><c r="J1263" s="2" t="inlineStr" /><c r="K1263" s="2" t="inlineStr"><is><t>To rekombinowane ludzkie przeciwciało przeciwko IL-5</t></is></c><c r="L1263" s="2" t="inlineStr"><is><t>Jest podawany w nebulizacji</t></is></c><c r="M1263" s="2" t="inlineStr"><is><t>Jest stosowany u osob z astmą niealergiczna</t></is></c><c r="N1263" s="2" t="inlineStr" /><c r="O1263" s="2" t="inlineStr" /><c r="P1263" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1263" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="1264"><c r="A1264" s="2" t="inlineStr"><is><t>ZABURZENIA RYTMU SERCA</t></is></c><c r="B1264" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C1264" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1264" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1264" s="2" t="inlineStr"><is><t>Do działań niepożądanych indakaterolu należy</t></is></c><c r="F1264" s="2" t="inlineStr"><is><t>Zwiększone ryzyko wydłużenia QT przy przedawkowaniu</t></is></c><c r="G1264" s="2" t="inlineStr"><is><t>Hiperglikemia</t></is></c><c r="H1264" s="2" t="inlineStr" /><c r="I1264" s="2" t="inlineStr" /><c r="J1264" s="2" t="inlineStr" /><c r="K1264" s="2" t="inlineStr"><is><t>Bradykardia</t></is></c><c r="L1264" s="2" t="inlineStr"><is><t>Hiperkaliemia</t></is></c><c r="M1264" s="2" t="inlineStr"><is><t>Nasilenie działania gks</t></is></c><c r="N1264" s="2" t="inlineStr" /><c r="O1264" s="2" t="inlineStr" /><c r="P1264" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1264" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="1265"><c r="A1265" s="2" t="inlineStr"><is><t>UKŁAD ODDECHOWY</t></is></c><c r="B1265" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C1265" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1265" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1265" s="2" t="inlineStr"><is><t>Działanie p- kaszlowe wykazuje</t></is></c><c r="F1265" s="2" t="inlineStr"><is><t>Butamirat</t></is></c><c r="G1265" s="2" t="inlineStr"><is><t>Dekstrometorfan</t></is></c><c r="H1265" s="2" t="inlineStr"><is><t>Dihydrokodeina</t></is></c><c r="I1265" s="2" t="inlineStr" /><c r="J1265" s="2" t="inlineStr" /><c r="K1265" s="2" t="inlineStr"><is><t>Loperamid</t></is></c><c r="L1265" s="2" t="inlineStr"><is><t>Ambroksol</t></is></c><c r="M1265" s="2" t="inlineStr"><is><t>Lewopromazyna</t></is></c><c r="N1265" s="2" t="inlineStr" /><c r="O1265" s="2" t="inlineStr" /><c r="P1265" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1265" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="1266"><c r="A1266" s="2" t="inlineStr"><is><t>UKŁAD ODDECHOWY</t></is></c><c r="B1266" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C1266" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D1266" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E1266" s="2" t="inlineStr"><is><t>Gks w leczeniu astmy oskrzelowej</t></is></c><c r="F1266" s="2" t="inlineStr"><is><t>działają przeciwzapalnie +/</t></is></c><c r="G1266" s="2" t="inlineStr"><is><t>zapobiegają rozwojowi tolerancji na B2-adrenomimetyki +/</t></is></c><c r="H1266" s="2" t="inlineStr"><is><t>są stosowane w stanie astmatyczny</t></is></c><c r="I1266" s="2" t="inlineStr" /><c r="J1266" s="2" t="inlineStr" /><c r="K1266" s="2" t="inlineStr"><is><t>zmniejszają niebezpieczeństwo wystąpienia zapalenia płuc</t></is></c><c r="L1266" s="2" t="inlineStr"><is><t>zwiększają efektywność cholinolityków</t></is></c><c r="M1266" s="2" t="inlineStr" /><c r="N1266" s="2" t="inlineStr" /><c r="O1266" s="2" t="inlineStr" /><c r="P1266" s="2" t="inlineStr"><is><t>EGZAMIN IWL</t></is></c><c r="Q1266" s="2" t="inlineStr"><is><t>srednia</t></is></c></row></sheetData><autoFilter ref="A1:Q1266" /><pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5" /></worksheet>
+<file path=xl/worksheets/sheet1.xml><worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"><sheetPr><outlinePr summaryBelow="1" summaryRight="1" /><pageSetUpPr /></sheetPr><dimension ref="A1:Q1106" /><sheetFormatPr baseColWidth="8" defaultRowHeight="15" /><cols><col width="30" customWidth="1" min="1" max="1" /><col width="21" customWidth="1" min="2" max="2" /><col width="9" customWidth="1" min="3" max="3" /><col width="9" customWidth="1" min="4" max="4" /><col width="60" customWidth="1" min="5" max="5" /><col width="32" customWidth="1" min="6" max="6" /><col width="32" customWidth="1" min="7" max="7" /><col width="32" customWidth="1" min="8" max="8" /><col width="32" customWidth="1" min="9" max="9" /><col width="32" customWidth="1" min="10" max="10" /><col width="32" customWidth="1" min="11" max="11" /><col width="32" customWidth="1" min="12" max="12" /><col width="32" customWidth="1" min="13" max="13" /><col width="32" customWidth="1" min="14" max="14" /><col width="32" customWidth="1" min="15" max="15" /><col width="26" customWidth="1" min="16" max="16" /><col width="10" customWidth="1" min="17" max="17" /></cols><sheetData><row r="1"><c r="A1" s="1" t="inlineStr"><is><t>Section</t></is></c><c r="B1" s="1" t="inlineStr"><is><t>Category</t></is></c><c r="C1" s="1" t="inlineStr"><is><t>Poziom</t></is></c><c r="D1" s="1" t="inlineStr"><is><t>Type</t></is></c><c r="E1" s="1" t="inlineStr"><is><t>Question</t></is></c><c r="F1" s="1" t="inlineStr"><is><t>True 1</t></is></c><c r="G1" s="1" t="inlineStr"><is><t>True 2</t></is></c><c r="H1" s="1" t="inlineStr"><is><t>True 3</t></is></c><c r="I1" s="1" t="inlineStr"><is><t>True 4</t></is></c><c r="J1" s="1" t="inlineStr"><is><t>True 5</t></is></c><c r="K1" s="1" t="inlineStr"><is><t>False 1</t></is></c><c r="L1" s="1" t="inlineStr"><is><t>False 2</t></is></c><c r="M1" s="1" t="inlineStr"><is><t>False 3</t></is></c><c r="N1" s="1" t="inlineStr"><is><t>False 4</t></is></c><c r="O1" s="1" t="inlineStr"><is><t>False 5</t></is></c><c r="P1" s="1" t="inlineStr"><is><t>Zrodlo</t></is></c><c r="Q1" s="1" t="inlineStr"><is><t>Pewnosc</t></is></c></row><row r="2"><c r="A2" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B2" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C2" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D2" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E2" s="2" t="inlineStr"><is><t>Czarne zabarwienie stolca powoduje podanie preparatów:</t></is></c><c r="F2" s="2" t="inlineStr"><is><t>Bizmutu</t></is></c><c r="G2" s="2" t="inlineStr"><is><t>Żelaza</t></is></c><c r="H2" s="2" t="inlineStr" /><c r="I2" s="2" t="inlineStr" /><c r="J2" s="2" t="inlineStr" /><c r="K2" s="2" t="inlineStr"><is><t>Wapnia</t></is></c><c r="L2" s="2" t="inlineStr"><is><t>Glinu</t></is></c><c r="M2" s="2" t="inlineStr" /><c r="N2" s="2" t="inlineStr" /><c r="O2" s="2" t="inlineStr" /><c r="P2" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q2" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="3"><c r="A3" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B3" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C3" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D3" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E3" s="2" t="inlineStr"><is><t>Uzasadnionym wskazaniem do przewlekłego stosowania inhibitorów pompy protonowej jest:</t></is></c><c r="F3" s="2" t="inlineStr"><is><t>Choroba refluksowa żołądka</t></is></c><c r="G3" s="2" t="inlineStr"><is><t>Profilaktyka gastropatii u osób leczonych niesteroidowymi lekami przeciwzapalnymi powyżej 65 r.ż</t></is></c><c r="H3" s="2" t="inlineStr"><is><t>Eradykacja Helicobacter Pylori</t></is></c><c r="I3" s="2" t="inlineStr" /><c r="J3" s="2" t="inlineStr" /><c r="K3" s="2" t="inlineStr"><is><t>Profilaktyka wrzodów stresowych</t></is></c><c r="L3" s="2" t="inlineStr" /><c r="M3" s="2" t="inlineStr" /><c r="N3" s="2" t="inlineStr" /><c r="O3" s="2" t="inlineStr" /><c r="P3" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q3" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="4"><c r="A4" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B4" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C4" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D4" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E4" s="2" t="inlineStr"><is><t>Wybierz prawidłowe połączenie lek – wskazanie</t></is></c><c r="F4" s="2" t="inlineStr"><is><t>Mesalazyna – choroba Leśniowskiego crohna</t></is></c><c r="G4" s="2" t="inlineStr"><is><t>Rifaksymina – biegunka podróżnych</t></is></c><c r="H4" s="2" t="inlineStr"><is><t>Metylonaltrekson – zaparcia w trakcie terapii opioidami</t></is></c><c r="I4" s="2" t="inlineStr" /><c r="J4" s="2" t="inlineStr" /><c r="K4" s="2" t="inlineStr"><is><t>Racekadotryl – śpiączka wątrobowa</t></is></c><c r="L4" s="2" t="inlineStr" /><c r="M4" s="2" t="inlineStr" /><c r="N4" s="2" t="inlineStr" /><c r="O4" s="2" t="inlineStr" /><c r="P4" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q4" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="5"><c r="A5" s="2" t="inlineStr"><is><t>ZNIECZULENIA OGÓLNE</t></is></c><c r="B5" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C5" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D5" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E5" s="2" t="inlineStr"><is><t>Do leków które wykazują miejscowe działanie przeciwbólowe po podaniu na skórę należy:</t></is></c><c r="F5" s="2" t="inlineStr"><is><t>Kapsaicyna</t></is></c><c r="G5" s="2" t="inlineStr"><is><t>Ketoprofen</t></is></c><c r="H5" s="2" t="inlineStr" /><c r="I5" s="2" t="inlineStr" /><c r="J5" s="2" t="inlineStr" /><c r="K5" s="2" t="inlineStr"><is><t>Propofol</t></is></c><c r="L5" s="2" t="inlineStr"><is><t>Tiopental</t></is></c><c r="M5" s="2" t="inlineStr" /><c r="N5" s="2" t="inlineStr" /><c r="O5" s="2" t="inlineStr" /><c r="P5" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q5" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="6"><c r="A6" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B6" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C6" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D6" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E6" s="2" t="inlineStr"><is><t>Ryzyko uszkodzenia wątroby przez paracetamol rośnie w przypadku:</t></is></c><c r="F6" s="2" t="inlineStr"><is><t>Zespołu zależności alkoholowej (ZAA)</t></is></c><c r="G6" s="2" t="inlineStr"><is><t>Wygłodzenia (kacheksji)</t></is></c><c r="H6" s="2" t="inlineStr"><is><t>Indukcji enzymów mikrosomalnych wątroby</t></is></c><c r="I6" s="2" t="inlineStr"><is><t>Przedawkowania</t></is></c><c r="J6" s="2" t="inlineStr" /><c r="K6" s="2" t="inlineStr" /><c r="L6" s="2" t="inlineStr" /><c r="M6" s="2" t="inlineStr" /><c r="N6" s="2" t="inlineStr" /><c r="O6" s="2" t="inlineStr" /><c r="P6" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q6" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="7"><c r="A7" s="2" t="inlineStr"><is><t>BÓLE GŁOWY</t></is></c><c r="B7" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C7" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D7" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E7" s="2" t="inlineStr"><is><t>W przerywaniu bólów migrenowych stosuje się:</t></is></c><c r="F7" s="2" t="inlineStr"><is><t>Kwas acetylosalicylowy</t></is></c><c r="G7" s="2" t="inlineStr"><is><t>Dihydroergotaminę</t></is></c><c r="H7" s="2" t="inlineStr"><is><t>Zolmitryptan</t></is></c><c r="I7" s="2" t="inlineStr" /><c r="J7" s="2" t="inlineStr" /><c r="K7" s="2" t="inlineStr"><is><t>Morfinę</t></is></c><c r="L7" s="2" t="inlineStr" /><c r="M7" s="2" t="inlineStr" /><c r="N7" s="2" t="inlineStr" /><c r="O7" s="2" t="inlineStr" /><c r="P7" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q7" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="8"><c r="A8" s="2" t="inlineStr"><is><t>JASKRA</t></is></c><c r="B8" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C8" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D8" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E8" s="2" t="inlineStr"><is><t>Analogi prostaglandyny E1 mogą powodować</t></is></c><c r="F8" s="2" t="inlineStr"><is><t>Hamowanie wydzielania soku żołądkowego</t></is></c><c r="G8" s="2" t="inlineStr" /><c r="H8" s="2" t="inlineStr" /><c r="I8" s="2" t="inlineStr" /><c r="J8" s="2" t="inlineStr" /><c r="K8" s="2" t="inlineStr"><is><t>Poprawę odpływu cieczy wodnistej z oka</t></is></c><c r="L8" s="2" t="inlineStr"><is><t>Rozszerzanie naczyń krwionośnych tętniczych</t></is></c><c r="M8" s="2" t="inlineStr"><is><t>Hamowanie agregacji płytek krwi</t></is></c><c r="N8" s="2" t="inlineStr" /><c r="O8" s="2" t="inlineStr" /><c r="P8" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q8" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="9"><c r="A9" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B9" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C9" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D9" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E9" s="2" t="inlineStr"><is><t>Substytucja enzymów trzustkowych jest wskazana:</t></is></c><c r="F9" s="2" t="inlineStr"><is><t>W mukowiscydozie</t></is></c><c r="G9" s="2" t="inlineStr"><is><t>Po resekcji trzustki</t></is></c><c r="H9" s="2" t="inlineStr" /><c r="I9" s="2" t="inlineStr" /><c r="J9" s="2" t="inlineStr" /><c r="K9" s="2" t="inlineStr"><is><t>W cukrzycy typu 1</t></is></c><c r="L9" s="2" t="inlineStr"><is><t>W anoreksji</t></is></c><c r="M9" s="2" t="inlineStr" /><c r="N9" s="2" t="inlineStr" /><c r="O9" s="2" t="inlineStr" /><c r="P9" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q9" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="10"><c r="A10" s="2" t="inlineStr"><is><t>PADACZKA</t></is></c><c r="B10" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C10" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D10" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E10" s="2" t="inlineStr"><is><t>Wybierz prawidłowe połączenie lek – wskazanie do podania:</t></is></c><c r="F10" s="2" t="inlineStr"><is><t>Haloperydol – agresja u pacjentów z ograniczonym uszkodzeniem mózgu</t></is></c><c r="G10" s="2" t="inlineStr"><is><t>Betahistyna – zawroty głowy w przebiegu choroby Meniere’a</t></is></c><c r="H10" s="2" t="inlineStr"><is><t>Topiramat – profilaktyka migreny</t></is></c><c r="I10" s="2" t="inlineStr"><is><t>Lamotrygina – profilaktyka choroby afektywnej dwubiegunowej</t></is></c><c r="J10" s="2" t="inlineStr" /><c r="K10" s="2" t="inlineStr" /><c r="L10" s="2" t="inlineStr" /><c r="M10" s="2" t="inlineStr" /><c r="N10" s="2" t="inlineStr" /><c r="O10" s="2" t="inlineStr" /><c r="P10" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q10" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="11"><c r="A11" s="2" t="inlineStr"><is><t>FARMAKOKINETYKA</t></is></c><c r="B11" s="2" t="inlineStr"><is><t>Farmakokinetyka</t></is></c><c r="C11" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D11" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E11" s="2" t="inlineStr"><is><t>Kwas acetylosalicylowy:</t></is></c><c r="F11" s="2" t="inlineStr"><is><t>Ma eliminację metabolitów zgodnie z kinetyką I rzędu po podaniu małych dawek kardiologicznych</t></is></c><c r="G11" s="2" t="inlineStr"><is><t>Może być przyczyną zapalenia jelita cienkiego</t></is></c><c r="H11" s="2" t="inlineStr"><is><t>Po przedawkowaniu szybciej wydala się przez nerki po dożylnym podaniu wodorowęglanu sodu</t></is></c><c r="I11" s="2" t="inlineStr" /><c r="J11" s="2" t="inlineStr" /><c r="K11" s="2" t="inlineStr"><is><t>Słabiej zapobiega powstawaniu zakrzepu na blaszce miażdżycowej</t></is></c><c r="L11" s="2" t="inlineStr" /><c r="M11" s="2" t="inlineStr" /><c r="N11" s="2" t="inlineStr" /><c r="O11" s="2" t="inlineStr" /><c r="P11" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q11" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="12"><c r="A12" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B12" s="2" t="inlineStr"><is><t>Antidotum</t></is></c><c r="C12" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D12" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E12" s="2" t="inlineStr"><is><t>Wskaż prawdziwe stwierdzenie dotyczące leczenia heparyną niefrakcjonowaną:</t></is></c><c r="F12" s="2" t="inlineStr"><is><t>Może być podawana podskórnie ale jej biodostępność jest wtedy mała i zmienna osobniczo</t></is></c><c r="G12" s="2" t="inlineStr"><is><t>Białka osoczowe mogą zmniejszać jej działanie przeciwkrzepliwe i być przyczyną oporności na leczenie</t></is></c><c r="H12" s="2" t="inlineStr"><is><t>Przedłużenie aPTT 1,5-2 razy w stosunku do wartości wyjściowej jest pożądanym efektem terapeutycznym</t></is></c><c r="I12" s="2" t="inlineStr"><is><t>Jej antidotum jest siarczan protaminy</t></is></c><c r="J12" s="2" t="inlineStr" /><c r="K12" s="2" t="inlineStr" /><c r="L12" s="2" t="inlineStr" /><c r="M12" s="2" t="inlineStr" /><c r="N12" s="2" t="inlineStr" /><c r="O12" s="2" t="inlineStr" /><c r="P12" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q12" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="13"><c r="A13" s="2" t="inlineStr"><is><t>UKŁAD PRZYWSPÓŁCZULNY</t></is></c><c r="B13" s="2" t="inlineStr"><is><t>Przeciwwskazania</t></is></c><c r="C13" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D13" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E13" s="2" t="inlineStr"><is><t>Przeciwwskazaniem do podania cholinolityków jest:</t></is></c><c r="F13" s="2" t="inlineStr"><is><t>Rozrost gruczołu krokowego</t></is></c><c r="G13" s="2" t="inlineStr"><is><t>Jaskra</t></is></c><c r="H13" s="2" t="inlineStr" /><c r="I13" s="2" t="inlineStr" /><c r="J13" s="2" t="inlineStr" /><c r="K13" s="2" t="inlineStr"><is><t>Choroba wrzodowa żołądka i dwunastnicy</t></is></c><c r="L13" s="2" t="inlineStr"><is><t>Choroba lokomocyjna</t></is></c><c r="M13" s="2" t="inlineStr" /><c r="N13" s="2" t="inlineStr" /><c r="O13" s="2" t="inlineStr" /><c r="P13" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q13" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="14"><c r="A14" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B14" s="2" t="inlineStr"><is><t>Monitorowanie</t></is></c><c r="C14" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D14" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E14" s="2" t="inlineStr"><is><t>Warfaryna:</t></is></c><c r="F14" s="2" t="inlineStr"><is><t>Jest sotosowana w profilaktyce i leczeniu żylnej choroby zakrzepowo-zatorowej</t></is></c><c r="G14" s="2" t="inlineStr"><is><t>Może być przyczyną zespołu purpurowego palucha</t></is></c><c r="H14" s="2" t="inlineStr" /><c r="I14" s="2" t="inlineStr" /><c r="J14" s="2" t="inlineStr" /><c r="K14" s="2" t="inlineStr"><is><t>Wymaga utrzymania INR&gt;4</t></is></c><c r="L14" s="2" t="inlineStr"><is><t>Jest eliminowana niezmieniona przez nerki</t></is></c><c r="M14" s="2" t="inlineStr" /><c r="N14" s="2" t="inlineStr" /><c r="O14" s="2" t="inlineStr" /><c r="P14" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q14" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="15"><c r="A15" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B15" s="2" t="inlineStr"><is><t>Monitorowanie</t></is></c><c r="C15" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D15" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E15" s="2" t="inlineStr"><is><t>Fondaparynuks:</t></is></c><c r="F15" s="2" t="inlineStr"><is><t>Jest stosowana u osób z zawałem serca z przetrwałym uniesieniem odcinka ST (STEMI) oraz bez jego uniesienia (NSTEMI)</t></is></c><c r="G15" s="2" t="inlineStr" /><c r="H15" s="2" t="inlineStr" /><c r="I15" s="2" t="inlineStr" /><c r="J15" s="2" t="inlineStr" /><c r="K15" s="2" t="inlineStr"><is><t>Wybiórczo hamuje czynnik IIa</t></is></c><c r="L15" s="2" t="inlineStr"><is><t>W zalecanych dawkach hamuje istotnie wydłuża aPTT</t></is></c><c r="M15" s="2" t="inlineStr"><is><t>Nie jest wydalany przez nerki i może być stosowany u pacjentów z klirensem kreatyniny poniżej 30ml/min</t></is></c><c r="N15" s="2" t="inlineStr" /><c r="O15" s="2" t="inlineStr" /><c r="P15" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q15" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="16"><c r="A16" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B16" s="2" t="inlineStr"><is><t>Sposób podania</t></is></c><c r="C16" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D16" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E16" s="2" t="inlineStr"><is><t>Bezpośrednim inhibitorem trombiny podawanym dożylnie jest:</t></is></c><c r="F16" s="2" t="inlineStr"><is><t>Argatroban</t></is></c><c r="G16" s="2" t="inlineStr"><is><t>Biwalirudyna</t></is></c><c r="H16" s="2" t="inlineStr" /><c r="I16" s="2" t="inlineStr" /><c r="J16" s="2" t="inlineStr" /><c r="K16" s="2" t="inlineStr"><is><t>Dabigatran</t></is></c><c r="L16" s="2" t="inlineStr"><is><t>Dalteparyna</t></is></c><c r="M16" s="2" t="inlineStr" /><c r="N16" s="2" t="inlineStr" /><c r="O16" s="2" t="inlineStr" /><c r="P16" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q16" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="17"><c r="A17" s="2" t="inlineStr"><is><t>UKŁAD PRZYWSPÓŁCZULNY</t></is></c><c r="B17" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C17" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D17" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E17" s="2" t="inlineStr"><is><t>Odwracalne inhibitory acetylocholinesterazy są stosowane w leczeniu:</t></is></c><c r="F17" s="2" t="inlineStr"><is><t>Nużliwości mięśni</t></is></c><c r="G17" s="2" t="inlineStr"><is><t>Pooperacyjnej niedrożności jelit</t></is></c><c r="H17" s="2" t="inlineStr"><is><t>Choroby Alzheimera</t></is></c><c r="I17" s="2" t="inlineStr" /><c r="J17" s="2" t="inlineStr" /><c r="K17" s="2" t="inlineStr"><is><t>Zatruć związakmi fosfoorganicznymi</t></is></c><c r="L17" s="2" t="inlineStr" /><c r="M17" s="2" t="inlineStr" /><c r="N17" s="2" t="inlineStr" /><c r="O17" s="2" t="inlineStr" /><c r="P17" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q17" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="18"><c r="A18" s="2" t="inlineStr"><is><t>NADCIŚNIENIE TĘTNICZE</t></is></c><c r="B18" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C18" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D18" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E18" s="2" t="inlineStr"><is><t>Zaznacza prawidłowe pary dotyczące leczenia uzależnień i wybranego leku:</t></is></c><c r="F18" s="2" t="inlineStr"><is><t>Uzależnienie od alkoholu – nalmefen</t></is></c><c r="G18" s="2" t="inlineStr"><is><t>Uzależnienie od heroiny – metadon</t></is></c><c r="H18" s="2" t="inlineStr" /><c r="I18" s="2" t="inlineStr" /><c r="J18" s="2" t="inlineStr" /><c r="K18" s="2" t="inlineStr"><is><t>Uzależnienie od nikotyny – klonidyna</t></is></c><c r="L18" s="2" t="inlineStr"><is><t>Uzależnienie od amfetaminy – wereniklina</t></is></c><c r="M18" s="2" t="inlineStr" /><c r="N18" s="2" t="inlineStr" /><c r="O18" s="2" t="inlineStr" /><c r="P18" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q18" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="19"><c r="A19" s="2" t="inlineStr"><is><t>STANY NAGŁE</t></is></c><c r="B19" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C19" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D19" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E19" s="2" t="inlineStr"><is><t>Wskaż prawidłowe pary płyn infuzyjny – możliwe działania niepożądane:</t></is></c><c r="F19" s="2" t="inlineStr"><is><t>5% roztwór glukozy – hiponatremia</t></is></c><c r="G19" s="2" t="inlineStr"><is><t>HES (hydroksyetylowana skrobia) – ostre uszkodzenie nerek</t></is></c><c r="H19" s="2" t="inlineStr"><is><t>5% roztwór albuminy – anafilaksja</t></is></c><c r="I19" s="2" t="inlineStr"><is><t>Dekstran 70000 – działanie przeciwkrzepliwe</t></is></c><c r="J19" s="2" t="inlineStr" /><c r="K19" s="2" t="inlineStr" /><c r="L19" s="2" t="inlineStr" /><c r="M19" s="2" t="inlineStr" /><c r="N19" s="2" t="inlineStr" /><c r="O19" s="2" t="inlineStr" /><c r="P19" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q19" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="20"><c r="A20" s="2" t="inlineStr"><is><t>NADCIŚNIENIE TĘTNICZE</t></is></c><c r="B20" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C20" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D20" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E20" s="2" t="inlineStr"><is><t>Wskaż prawidłowe stwierdzenie dotyczące leczenia hipotensyjnego:</t></is></c><c r="F20" s="2" t="inlineStr"><is><t>Tiazydy mogą bezpośrednio oddziaływać na ścianę naczyń i zmniejszać systemowy opór naczyniowy</t></is></c><c r="G20" s="2" t="inlineStr"><is><t>Pełny efekt hipotensyjny występuje po kilkunastu dniach leczenia</t></is></c><c r="H20" s="2" t="inlineStr"><is><t>Blokada kotransportera Na-Cl w kanaliku dystalnym prowadzi do zwiększeniu natriurezy</t></is></c><c r="I20" s="2" t="inlineStr" /><c r="J20" s="2" t="inlineStr" /><c r="K20" s="2" t="inlineStr"><is><t>Ich skuteczność w leczeniu przewlekłym wynika przede wszystkim ze zmniejszenia objętości osocza i rzutu serca</t></is></c><c r="L20" s="2" t="inlineStr" /><c r="M20" s="2" t="inlineStr" /><c r="N20" s="2" t="inlineStr" /><c r="O20" s="2" t="inlineStr" /><c r="P20" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q20" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="21"><c r="A21" s="2" t="inlineStr"><is><t>UKŁAD PRZYWSPÓŁCZULNY</t></is></c><c r="B21" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C21" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D21" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E21" s="2" t="inlineStr"><is><t>Suksametonium może być przyczyną:</t></is></c><c r="F21" s="2" t="inlineStr"><is><t>Drżenia włókienkowego mięśni szkieletowych</t></is></c><c r="G21" s="2" t="inlineStr"><is><t>Zaburzeń oddychania</t></is></c><c r="H21" s="2" t="inlineStr"><is><t>Zespołu hipertermii złośliwej</t></is></c><c r="I21" s="2" t="inlineStr"><is><t>Długotrwałego efektu zwiotczającego u osób z dysfunkcją acetylocholinesterazy</t></is></c><c r="J21" s="2" t="inlineStr" /><c r="K21" s="2" t="inlineStr" /><c r="L21" s="2" t="inlineStr" /><c r="M21" s="2" t="inlineStr" /><c r="N21" s="2" t="inlineStr" /><c r="O21" s="2" t="inlineStr" /><c r="P21" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q21" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="22"><c r="A22" s="2" t="inlineStr"><is><t>UKŁAD ODDECHOWY</t></is></c><c r="B22" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C22" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D22" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E22" s="2" t="inlineStr"><is><t>W celu łagodzenia suchego kaszlu można wybrać:</t></is></c><c r="F22" s="2" t="inlineStr"><is><t>Dekstrometorfan</t></is></c><c r="G22" s="2" t="inlineStr"><is><t>Kodeinę</t></is></c><c r="H22" s="2" t="inlineStr"><is><t>Butamirat</t></is></c><c r="I22" s="2" t="inlineStr" /><c r="J22" s="2" t="inlineStr" /><c r="K22" s="2" t="inlineStr"><is><t>Bromheksynę</t></is></c><c r="L22" s="2" t="inlineStr" /><c r="M22" s="2" t="inlineStr" /><c r="N22" s="2" t="inlineStr" /><c r="O22" s="2" t="inlineStr" /><c r="P22" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q22" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="23"><c r="A23" s="2" t="inlineStr"><is><t>LEKI PRZECIWPASOŻYTNICZE</t></is></c><c r="B23" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C23" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D23" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E23" s="2" t="inlineStr"><is><t>Albendazol stosowany jest w jelitowej infestacji:</t></is></c><c r="F23" s="2" t="inlineStr"><is><t>Glistą ludzką</t></is></c><c r="G23" s="2" t="inlineStr"><is><t>Tasiemcem uzbrojonym</t></is></c><c r="H23" s="2" t="inlineStr"><is><t>Owsikami</t></is></c><c r="I23" s="2" t="inlineStr" /><c r="J23" s="2" t="inlineStr" /><c r="K23" s="2" t="inlineStr"><is><t>Lambliami</t></is></c><c r="L23" s="2" t="inlineStr" /><c r="M23" s="2" t="inlineStr" /><c r="N23" s="2" t="inlineStr" /><c r="O23" s="2" t="inlineStr" /><c r="P23" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q23" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="24"><c r="A24" s="2" t="inlineStr"><is><t>PADACZKA</t></is></c><c r="B24" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C24" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D24" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E24" s="2" t="inlineStr"><is><t>Napad paniki należy leczyć stosując doraźnie:</t></is></c><c r="F24" s="2" t="inlineStr"><is><t>Techniki relaksacyjne</t></is></c><c r="G24" s="2" t="inlineStr"><is><t>Alprazolam</t></is></c><c r="H24" s="2" t="inlineStr" /><c r="I24" s="2" t="inlineStr" /><c r="J24" s="2" t="inlineStr" /><c r="K24" s="2" t="inlineStr"><is><t>Pregabalinę</t></is></c><c r="L24" s="2" t="inlineStr"><is><t>Fluoksetynę</t></is></c><c r="M24" s="2" t="inlineStr" /><c r="N24" s="2" t="inlineStr" /><c r="O24" s="2" t="inlineStr" /><c r="P24" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q24" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="25"><c r="A25" s="2" t="inlineStr"><is><t>UKŁAD WSPÓŁCZULNY</t></is></c><c r="B25" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C25" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D25" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E25" s="2" t="inlineStr"><is><t>Fenoterol może być przyczyną:</t></is></c><c r="F25" s="2" t="inlineStr"><is><t>Tachykardii</t></is></c><c r="G25" s="2" t="inlineStr"><is><t>Drżenia mięśni</t></is></c><c r="H25" s="2" t="inlineStr"><is><t>Hiperglikemii</t></is></c><c r="I25" s="2" t="inlineStr"><is><t>Hamowania skurczów ciężarnej macicy</t></is></c><c r="J25" s="2" t="inlineStr" /><c r="K25" s="2" t="inlineStr" /><c r="L25" s="2" t="inlineStr" /><c r="M25" s="2" t="inlineStr" /><c r="N25" s="2" t="inlineStr" /><c r="O25" s="2" t="inlineStr" /><c r="P25" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q25" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="26"><c r="A26" s="2" t="inlineStr"><is><t>UKŁAD WSPÓŁCZULNY</t></is></c><c r="B26" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C26" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D26" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E26" s="2" t="inlineStr"><is><t>Długo działające beta2-mimetyki (LABA):</t></is></c><c r="F26" s="2" t="inlineStr"><is><t>Podawane przewlekle powodują down-regulację receptorów beta2-adrenergicznych w oskrzelach</t></is></c><c r="G26" s="2" t="inlineStr" /><c r="H26" s="2" t="inlineStr" /><c r="I26" s="2" t="inlineStr" /><c r="J26" s="2" t="inlineStr" /><c r="K26" s="2" t="inlineStr"><is><t>Nie powinny być podawane razem z glikokortykosteroidami które blokują wytwarzanie białek receptorów beta2-adrenergicznych</t></is></c><c r="L26" s="2" t="inlineStr"><is><t>Mogą być przyczyną istotnej klinicznie hieprkaliemi</t></is></c><c r="M26" s="2" t="inlineStr"><is><t>Wykazują działanie przeciwzapalne</t></is></c><c r="N26" s="2" t="inlineStr" /><c r="O26" s="2" t="inlineStr" /><c r="P26" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q26" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="27"><c r="A27" s="2" t="inlineStr"><is><t>NIEOPIOIDOWE LEKI PRZECIWBÓLOWE</t></is></c><c r="B27" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C27" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D27" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E27" s="2" t="inlineStr"><is><t>Wskaż prawidłowe stwierdzenie dotyczące NLPZ:</t></is></c><c r="F27" s="2" t="inlineStr"><is><t>Ketoprofen powoduje większe ryzyko krwawienia z górnego odcinka przewodu pokarmowego niż ibuprofen</t></is></c><c r="G27" s="2" t="inlineStr" /><c r="H27" s="2" t="inlineStr" /><c r="I27" s="2" t="inlineStr" /><c r="J27" s="2" t="inlineStr" /><c r="K27" s="2" t="inlineStr"><is><t>Meloksykam jest preferencyjnym inhibitorem COX-1</t></is></c><c r="L27" s="2" t="inlineStr"><is><t>Zastąpienie drogi doustnej podania diklofenaku drogą doodbytniczą zmniejsza ryzyko wystąpienia działań niepożądanych</t></is></c><c r="M27" s="2" t="inlineStr"><is><t>Nimesulid należy do najmniej hepatotoksycznych NLPZ</t></is></c><c r="N27" s="2" t="inlineStr" /><c r="O27" s="2" t="inlineStr" /><c r="P27" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q27" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="28"><c r="A28" s="2" t="inlineStr"><is><t>NADCIŚNIENIE TĘTNICZE</t></is></c><c r="B28" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C28" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D28" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E28" s="2" t="inlineStr"><is><t>Lekiem prkeursorowym jest:</t></is></c><c r="F28" s="2" t="inlineStr"><is><t>Enalapryl</t></is></c><c r="G28" s="2" t="inlineStr"><is><t>Cyklezonid</t></is></c><c r="H28" s="2" t="inlineStr"><is><t>Lewodopa</t></is></c><c r="I28" s="2" t="inlineStr" /><c r="J28" s="2" t="inlineStr" /><c r="K28" s="2" t="inlineStr"><is><t>Furosemid</t></is></c><c r="L28" s="2" t="inlineStr" /><c r="M28" s="2" t="inlineStr" /><c r="N28" s="2" t="inlineStr" /><c r="O28" s="2" t="inlineStr" /><c r="P28" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q28" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="29"><c r="A29" s="2" t="inlineStr"><is><t>LEKI IMMUNOSUPRESYJNE</t></is></c><c r="B29" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C29" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D29" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E29" s="2" t="inlineStr"><is><t>Cyklosporyna:</t></is></c><c r="F29" s="2" t="inlineStr"><is><t>Jest stosowana w zapobieganiu odrzucania przeszczepu allogenicznego narządów unaczynionych</t></is></c><c r="G29" s="2" t="inlineStr"><is><t>Zwiększa ryzyko chorób rozrostowych układu chłonnego</t></is></c><c r="H29" s="2" t="inlineStr" /><c r="I29" s="2" t="inlineStr" /><c r="J29" s="2" t="inlineStr" /><c r="K29" s="2" t="inlineStr"><is><t>Jest rekombinowanym w pełni ludzkim przeciwciałem monoklonalnym</t></is></c><c r="L29" s="2" t="inlineStr"><is><t>Neutralizuje biologiczną aktywność TNF</t></is></c><c r="M29" s="2" t="inlineStr" /><c r="N29" s="2" t="inlineStr" /><c r="O29" s="2" t="inlineStr" /><c r="P29" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q29" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="30"><c r="A30" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B30" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C30" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D30" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E30" s="2" t="inlineStr"><is><t>Do leków o udowodnionym korzystnym działaniu w profilaktyce wtórnej niedokrwiennego udaru mózgu należy:</t></is></c><c r="F30" s="2" t="inlineStr"><is><t>Kwas acetylosalicylowy</t></is></c><c r="G30" s="2" t="inlineStr"><is><t>Atorwastatyna</t></is></c><c r="H30" s="2" t="inlineStr"><is><t>Klopidogrel</t></is></c><c r="I30" s="2" t="inlineStr" /><c r="J30" s="2" t="inlineStr" /><c r="K30" s="2" t="inlineStr"><is><t>Kwas traneksamowy</t></is></c><c r="L30" s="2" t="inlineStr" /><c r="M30" s="2" t="inlineStr" /><c r="N30" s="2" t="inlineStr" /><c r="O30" s="2" t="inlineStr" /><c r="P30" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q30" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="31"><c r="A31" s="2" t="inlineStr"><is><t>CHOROBA PARKINSONA</t></is></c><c r="B31" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C31" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D31" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E31" s="2" t="inlineStr"><is><t>Lewodopa:</t></is></c><c r="F31" s="2" t="inlineStr"><is><t>Jest jednym z najskuteczniejszych leków stosowanych w terapii choroby Parkinsona</t></is></c><c r="G31" s="2" t="inlineStr"><is><t>Ma krótki okres półtrwania i dlatego wymaga wielokrotnego podawania w ciągu doby</t></is></c><c r="H31" s="2" t="inlineStr"><is><t>Podczas długotrwałego leczenia może wywołać fluktuacje ruchowe i dyskinezy</t></is></c><c r="I31" s="2" t="inlineStr"><is><t>Może wywoływać działania niepożądane ze strony przewodu pokarmowego</t></is></c><c r="J31" s="2" t="inlineStr" /><c r="K31" s="2" t="inlineStr" /><c r="L31" s="2" t="inlineStr" /><c r="M31" s="2" t="inlineStr" /><c r="N31" s="2" t="inlineStr" /><c r="O31" s="2" t="inlineStr" /><c r="P31" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q31" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="32"><c r="A32" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B32" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C32" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D32" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E32" s="2" t="inlineStr"><is><t>Kokaina:</t></is></c><c r="F32" s="2" t="inlineStr"><is><t>Hamuje wychwyt zwrotny dopaminy w szczelinie synaptycznej</t></is></c><c r="G32" s="2" t="inlineStr"><is><t>Może powodować wystąpienie zawału mięśnia sercowego</t></is></c><c r="H32" s="2" t="inlineStr"><is><t>Może powodować krwawienia wewnątrzczaszkowe</t></is></c><c r="I32" s="2" t="inlineStr" /><c r="J32" s="2" t="inlineStr" /><c r="K32" s="2" t="inlineStr"><is><t>Hamuje aktywność receptora dla kwasu glutaminowego</t></is></c><c r="L32" s="2" t="inlineStr" /><c r="M32" s="2" t="inlineStr" /><c r="N32" s="2" t="inlineStr" /><c r="O32" s="2" t="inlineStr" /><c r="P32" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q32" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="33"><c r="A33" s="2" t="inlineStr"><is><t>LEKI PRZECIWHISTAMINOWE</t></is></c><c r="B33" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C33" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D33" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E33" s="2" t="inlineStr"><is><t>W alergicznym zapaleniu spojówek może stosować dospojówkowo:</t></is></c><c r="F33" s="2" t="inlineStr"><is><t>Antazolinę</t></is></c><c r="G33" s="2" t="inlineStr"><is><t>Azelastynę</t></is></c><c r="H33" s="2" t="inlineStr"><is><t>Kromoglikan sodowy</t></is></c><c r="I33" s="2" t="inlineStr"><is><t>Olopatadynę</t></is></c><c r="J33" s="2" t="inlineStr" /><c r="K33" s="2" t="inlineStr" /><c r="L33" s="2" t="inlineStr" /><c r="M33" s="2" t="inlineStr" /><c r="N33" s="2" t="inlineStr" /><c r="O33" s="2" t="inlineStr" /><c r="P33" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q33" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="34"><c r="A34" s="2" t="inlineStr"><is><t>NARKOTYCZNE LEKI PRZECIWBÓLOWE</t></is></c><c r="B34" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C34" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D34" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E34" s="2" t="inlineStr"><is><t>Stosowanie preparatu złożonego bupropionu z naltreksonem w leczeniu otyłości:</t></is></c><c r="F34" s="2" t="inlineStr"><is><t>Ma wpływ na ośrodkowy układ nagrody</t></is></c><c r="G34" s="2" t="inlineStr"><is><t>Zwiększa i wydłuża uczucie sytości</t></is></c><c r="H34" s="2" t="inlineStr"><is><t>Ma zwiększoną skuteczność kliniczną ze względu na efekt synergistyczny bupropionu i naltreksonu</t></is></c><c r="I34" s="2" t="inlineStr" /><c r="J34" s="2" t="inlineStr" /><c r="K34" s="2" t="inlineStr"><is><t>Jest wskazane dla wszystkich osób z wyjściową wartością BMI wynoszącą ≥27</t></is></c><c r="L34" s="2" t="inlineStr" /><c r="M34" s="2" t="inlineStr" /><c r="N34" s="2" t="inlineStr" /><c r="O34" s="2" t="inlineStr" /><c r="P34" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q34" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="35"><c r="A35" s="2" t="inlineStr"><is><t>UKŁAD WSPÓŁCZULNY</t></is></c><c r="B35" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C35" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D35" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E35" s="2" t="inlineStr"><is><t>Dodatek adrenaliny do lidokainy w lekach do znieczulania miejscowego może powodować:</t></is></c><c r="F35" s="2" t="inlineStr"><is><t>Zwiększone ryzyko martwicy tkanek po podaniach obwodowych</t></is></c><c r="G35" s="2" t="inlineStr"><is><t>Wydłużenie czasu działania lidokainy</t></is></c><c r="H35" s="2" t="inlineStr" /><c r="I35" s="2" t="inlineStr" /><c r="J35" s="2" t="inlineStr" /><c r="K35" s="2" t="inlineStr"><is><t>Zwiększone niebezpieczeństwo zatrzymania oddechu</t></is></c><c r="L35" s="2" t="inlineStr"><is><t>Zahamowanie metabolizmu lidokainy</t></is></c><c r="M35" s="2" t="inlineStr" /><c r="N35" s="2" t="inlineStr" /><c r="O35" s="2" t="inlineStr" /><c r="P35" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q35" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="36"><c r="A36" s="2" t="inlineStr"><is><t>NIEWYDOLNOŚĆ SERCA</t></is></c><c r="B36" s="2" t="inlineStr"><is><t>Sposób podania</t></is></c><c r="C36" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D36" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E36" s="2" t="inlineStr"><is><t>Digoksyna</t></is></c><c r="F36" s="2" t="inlineStr"><is><t>Podtrzymuje aktywację baroreceptorów zatoki szyjnej przy obniżeniu ciśnienia krwi u osób z niewydolnością serca</t></is></c><c r="G36" s="2" t="inlineStr"><is><t>Podana doustnie może być nieskuteczna z powodu dezaktywacji przez bakterie jelitowe</t></is></c><c r="H36" s="2" t="inlineStr" /><c r="I36" s="2" t="inlineStr" /><c r="J36" s="2" t="inlineStr" /><c r="K36" s="2" t="inlineStr"><is><t>Powoduje kardiowersję migotania przedsionków do rytmu zatokowego</t></is></c><c r="L36" s="2" t="inlineStr"><is><t>Jest lekiem o korzystnym działaniu rokowniczym w skurczowej niewydolności serca</t></is></c><c r="M36" s="2" t="inlineStr" /><c r="N36" s="2" t="inlineStr" /><c r="O36" s="2" t="inlineStr" /><c r="P36" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q36" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="37"><c r="A37" s="2" t="inlineStr"><is><t>UKŁAD WSPÓŁCZULNY</t></is></c><c r="B37" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C37" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D37" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E37" s="2" t="inlineStr"><is><t>Teoretyczną przesłanką stosowania beta-adrenolityków w przewlekłej skurczowej niewydolności serca jest:</t></is></c><c r="F37" s="2" t="inlineStr"><is><t>Odwracanie beta-down regulacji</t></is></c><c r="G37" s="2" t="inlineStr"><is><t>Zapobieganie proarytmicznemu działaniu katecholamin</t></is></c><c r="H37" s="2" t="inlineStr" /><c r="I37" s="2" t="inlineStr" /><c r="J37" s="2" t="inlineStr" /><c r="K37" s="2" t="inlineStr"><is><t>Korzystny bezpośredni wpływ hemodynamiczny</t></is></c><c r="L37" s="2" t="inlineStr"><is><t>Zwiększenie naprężenia ściany lewej komory</t></is></c><c r="M37" s="2" t="inlineStr" /><c r="N37" s="2" t="inlineStr" /><c r="O37" s="2" t="inlineStr" /><c r="P37" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q37" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="38"><c r="A38" s="2" t="inlineStr"><is><t>LEKI PRZECIWHISTAMINOWE</t></is></c><c r="B38" s="2" t="inlineStr"><is><t>Farmakokinetyka</t></is></c><c r="C38" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D38" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E38" s="2" t="inlineStr"><is><t>Rupatadyna:</t></is></c><c r="F38" s="2" t="inlineStr"><is><t>Ma minimalny potencjał sedatywny</t></is></c><c r="G38" s="2" t="inlineStr"><is><t>Oprócz antagonizmu wobec receptora H1 wykazuje przeciwzapalną aktywność pozareceptorową</t></is></c><c r="H38" s="2" t="inlineStr"><is><t>W znacznym stopniu ulega efektowi pierwszego przejścia z powstaniem aktywnych metabolitów</t></is></c><c r="I38" s="2" t="inlineStr"><is><t>W dawkach zalecanych nie wydłuża skorygowanego odstępu cQT</t></is></c><c r="J38" s="2" t="inlineStr" /><c r="K38" s="2" t="inlineStr" /><c r="L38" s="2" t="inlineStr" /><c r="M38" s="2" t="inlineStr" /><c r="N38" s="2" t="inlineStr" /><c r="O38" s="2" t="inlineStr" /><c r="P38" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q38" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="39"><c r="A39" s="2" t="inlineStr"><is><t>NADCIŚNIENIE TĘTNICZE</t></is></c><c r="B39" s="2" t="inlineStr"><is><t>Przeciwwskazania</t></is></c><c r="C39" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D39" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E39" s="2" t="inlineStr"><is><t>U pacjentów z eGFR&lt;30ml/min należy rezygnować ze stosowania:</t></is></c><c r="F39" s="2" t="inlineStr"><is><t>Metyforminy</t></is></c><c r="G39" s="2" t="inlineStr"><is><t>Hydrochlorotiazydu</t></is></c><c r="H39" s="2" t="inlineStr" /><c r="I39" s="2" t="inlineStr" /><c r="J39" s="2" t="inlineStr" /><c r="K39" s="2" t="inlineStr"><is><t>Metoprololu</t></is></c><c r="L39" s="2" t="inlineStr"><is><t>Amlodypiny</t></is></c><c r="M39" s="2" t="inlineStr" /><c r="N39" s="2" t="inlineStr" /><c r="O39" s="2" t="inlineStr" /><c r="P39" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q39" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="40"><c r="A40" s="2" t="inlineStr"><is><t>UKŁAD PRZYWSPÓŁCZULNY</t></is></c><c r="B40" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C40" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D40" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E40" s="2" t="inlineStr"><is><t>Wenlafaksyna:</t></is></c><c r="F40" s="2" t="inlineStr"><is><t>Może być podawana w uogólnionych zaburzeniach lękowych</t></is></c><c r="G40" s="2" t="inlineStr"><is><t>Stosowana razem z tryptanami może powodować wystąpienie zespołu serotoninowego</t></is></c><c r="H40" s="2" t="inlineStr" /><c r="I40" s="2" t="inlineStr" /><c r="J40" s="2" t="inlineStr" /><c r="K40" s="2" t="inlineStr"><is><t>Ma istotne działanie cholinolityczne</t></is></c><c r="L40" s="2" t="inlineStr"><is><t>Można ją bezpiecznie stosować w terapii skojarzonej z inhibitorami MAO</t></is></c><c r="M40" s="2" t="inlineStr" /><c r="N40" s="2" t="inlineStr" /><c r="O40" s="2" t="inlineStr" /><c r="P40" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q40" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="41"><c r="A41" s="2" t="inlineStr"><is><t>LEKI IMMUNOSUPRESYJNE</t></is></c><c r="B41" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C41" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D41" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E41" s="2" t="inlineStr"><is><t>Czy słuszna jest przedstawiona interpretacja działania leku na podstawie nazwy międzynarodowej:</t></is></c><c r="F41" s="2" t="inlineStr"><is><t>Paliwizumab – humanizowane przeciwciało monoklonalne o działaniu p￾wirusowym</t></is></c><c r="G41" s="2" t="inlineStr"><is><t>Ekulizumab – humanizowane przeciwciało monoklonalne o wpływie na układ odpornościowy</t></is></c><c r="H41" s="2" t="inlineStr" /><c r="I41" s="2" t="inlineStr" /><c r="J41" s="2" t="inlineStr" /><c r="K41" s="2" t="inlineStr"><is><t>Ofatumumab – mysie przeciwciało monoklonalne o wpływie p-nowotworowym</t></is></c><c r="L41" s="2" t="inlineStr"><is><t>Pomalidomid – mysie przeciwciało monoklonalne o wpływie na układ odpornościowy</t></is></c><c r="M41" s="2" t="inlineStr" /><c r="N41" s="2" t="inlineStr" /><c r="O41" s="2" t="inlineStr" /><c r="P41" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q41" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="42"><c r="A42" s="2" t="inlineStr"><is><t>LEKI PRZECIWNOWOTWOROWE</t></is></c><c r="B42" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C42" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D42" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E42" s="2" t="inlineStr"><is><t>Do przeciwciał monoklonalnych anty-TNF należy:</t></is></c><c r="F42" s="2" t="inlineStr"><is><t>Adalimumab</t></is></c><c r="G42" s="2" t="inlineStr" /><c r="H42" s="2" t="inlineStr" /><c r="I42" s="2" t="inlineStr" /><c r="J42" s="2" t="inlineStr" /><c r="K42" s="2" t="inlineStr"><is><t>Omalizumab</t></is></c><c r="L42" s="2" t="inlineStr"><is><t>Trastuzumab</t></is></c><c r="M42" s="2" t="inlineStr"><is><t>Rytuksymab</t></is></c><c r="N42" s="2" t="inlineStr" /><c r="O42" s="2" t="inlineStr" /><c r="P42" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q42" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="43"><c r="A43" s="2" t="inlineStr"><is><t>ZABURZENIA RYTMU SERCA</t></is></c><c r="B43" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C43" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D43" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E43" s="2" t="inlineStr"><is><t>Werapamil można stosować w:</t></is></c><c r="F43" s="2" t="inlineStr"><is><t>Postaci naczynioskurczowej choroby niedokrwiennej serca</t></is></c><c r="G43" s="2" t="inlineStr"><is><t>Napadowym częstoskurczu z łącza przedsionkowo-komorowego</t></is></c><c r="H43" s="2" t="inlineStr" /><c r="I43" s="2" t="inlineStr" /><c r="J43" s="2" t="inlineStr" /><c r="K43" s="2" t="inlineStr"><is><t>Bradykardii</t></is></c><c r="L43" s="2" t="inlineStr"><is><t>Migotaniu przedsionków u osób z zespołem preekscytacji</t></is></c><c r="M43" s="2" t="inlineStr" /><c r="N43" s="2" t="inlineStr" /><c r="O43" s="2" t="inlineStr" /><c r="P43" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q43" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="44"><c r="A44" s="2" t="inlineStr"><is><t>NIEWYDOLNOŚĆ SERCA</t></is></c><c r="B44" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C44" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D44" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E44" s="2" t="inlineStr"><is><t>Inhibitory neprylizyny:</t></is></c><c r="F44" s="2" t="inlineStr"><is><t>Zmniejszają przebudowę mięśnia sercowego</t></is></c><c r="G44" s="2" t="inlineStr"><is><t>Zwiększają stężenie angiotensyny II</t></is></c><c r="H44" s="2" t="inlineStr"><is><t>Są stosowane w przewlekłej niewydolności serca z upośledzoną frakcją wyrzutową</t></is></c><c r="I44" s="2" t="inlineStr" /><c r="J44" s="2" t="inlineStr" /><c r="K44" s="2" t="inlineStr"><is><t>Rozkładają peptydy natriuretyczne</t></is></c><c r="L44" s="2" t="inlineStr" /><c r="M44" s="2" t="inlineStr" /><c r="N44" s="2" t="inlineStr" /><c r="O44" s="2" t="inlineStr" /><c r="P44" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q44" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="45"><c r="A45" s="2" t="inlineStr"><is><t>FARMAKOKINETYKA</t></is></c><c r="B45" s="2" t="inlineStr"><is><t>Farmakokinetyka</t></is></c><c r="C45" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D45" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E45" s="2" t="inlineStr"><is><t>Biodostępność leku A po jednorazowym podaniu doustnym wynosi 50%. Tmax wynosi 30min, Cmax 2µg/dl. Oznacza to, że:</t></is></c><c r="F45" s="2" t="inlineStr"><is><t>Lek A może podlegać nawet w 50% efektowi pierwszego przejścia</t></is></c><c r="G45" s="2" t="inlineStr" /><c r="H45" s="2" t="inlineStr" /><c r="I45" s="2" t="inlineStr" /><c r="J45" s="2" t="inlineStr" /><c r="K45" s="2" t="inlineStr"><is><t>Dawka wynosiła 4µg</t></is></c><c r="L45" s="2" t="inlineStr"><is><t>Lek A słabo się wiąże z białkami krwi</t></is></c><c r="M45" s="2" t="inlineStr"><is><t>Okres półtrwania leku A wynosi również około 30min</t></is></c><c r="N45" s="2" t="inlineStr" /><c r="O45" s="2" t="inlineStr" /><c r="P45" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q45" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="46"><c r="A46" s="2" t="inlineStr"><is><t>FARMAKOKINETYKA</t></is></c><c r="B46" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C46" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D46" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E46" s="2" t="inlineStr"><is><t>Podanie doodbytnicze leku:</t></is></c><c r="F46" s="2" t="inlineStr"><is><t>Może łatwo doprowadzić do miejscowego uszkodzenia błony śluzowej odbytnicy</t></is></c><c r="G46" s="2" t="inlineStr" /><c r="H46" s="2" t="inlineStr" /><c r="I46" s="2" t="inlineStr" /><c r="J46" s="2" t="inlineStr" /><c r="K46" s="2" t="inlineStr"><is><t>Zwiększa efekt pierwszego przejścia</t></is></c><c r="L46" s="2" t="inlineStr"><is><t>Jest metodą z wyboru u dzieci</t></is></c><c r="M46" s="2" t="inlineStr"><is><t>Wymaga podania większej dawki leku w porównaniu do podania doustnego</t></is></c><c r="N46" s="2" t="inlineStr" /><c r="O46" s="2" t="inlineStr" /><c r="P46" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q46" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="47"><c r="A47" s="2" t="inlineStr"><is><t>NADCIŚNIENIE TĘTNICZE</t></is></c><c r="B47" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C47" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D47" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E47" s="2" t="inlineStr"><is><t>Zaburzenia erekcji mogą być spowodowane stosowaniem:</t></is></c><c r="F47" s="2" t="inlineStr"><is><t>Inhibitorów 5-alfa reduktazy</t></is></c><c r="G47" s="2" t="inlineStr"><is><t>Tiazydów moczopędnych</t></is></c><c r="H47" s="2" t="inlineStr"><is><t>Beta-adrenolityków niekardioselektywnych</t></is></c><c r="I47" s="2" t="inlineStr"><is><t>Inhibitorów wychwytu zwrotnego serotoniny</t></is></c><c r="J47" s="2" t="inlineStr" /><c r="K47" s="2" t="inlineStr" /><c r="L47" s="2" t="inlineStr" /><c r="M47" s="2" t="inlineStr" /><c r="N47" s="2" t="inlineStr" /><c r="O47" s="2" t="inlineStr" /><c r="P47" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q47" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="48"><c r="A48" s="2" t="inlineStr"><is><t>LEKI PRZECIWDEPRESYJNE</t></is></c><c r="B48" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C48" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D48" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E48" s="2" t="inlineStr"><is><t>Doneuronalny wychwyt monoamin jest hamowany przez:</t></is></c><c r="F48" s="2" t="inlineStr"><is><t>Citalopram</t></is></c><c r="G48" s="2" t="inlineStr"><is><t>Reboksetynę</t></is></c><c r="H48" s="2" t="inlineStr" /><c r="I48" s="2" t="inlineStr" /><c r="J48" s="2" t="inlineStr" /><c r="K48" s="2" t="inlineStr"><is><t>Tianeptynę</t></is></c><c r="L48" s="2" t="inlineStr"><is><t>Mirtazapinę</t></is></c><c r="M48" s="2" t="inlineStr" /><c r="N48" s="2" t="inlineStr" /><c r="O48" s="2" t="inlineStr" /><c r="P48" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q48" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="49"><c r="A49" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B49" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C49" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D49" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E49" s="2" t="inlineStr"><is><t>W leczeniu gruźlicy płucnej lekowrażliwej:</t></is></c><c r="F49" s="2" t="inlineStr"><is><t>Leczenie wyjaławiające powinno trwać co najmniej 4 miesiące</t></is></c><c r="G49" s="2" t="inlineStr"><is><t>U kobiet ciężarnych podaje się leki według zwykłego schematu z wyłączeniem streptomycyny</t></is></c><c r="H49" s="2" t="inlineStr" /><c r="I49" s="2" t="inlineStr" /><c r="J49" s="2" t="inlineStr" /><c r="K49" s="2" t="inlineStr"><is><t>W intensywnej fazie leczenia przez 2 miesiące podaje się 2 leki – rifampicynę i izoniazyd</t></is></c><c r="L49" s="2" t="inlineStr"><is><t>W fazie kontynuacji każdy pacjent powinien otrzymać etambutol</t></is></c><c r="M49" s="2" t="inlineStr" /><c r="N49" s="2" t="inlineStr" /><c r="O49" s="2" t="inlineStr" /><c r="P49" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q49" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="50"><c r="A50" s="2" t="inlineStr"><is><t>LEKI PRZECIWDEPRESYJNE</t></is></c><c r="B50" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C50" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D50" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E50" s="2" t="inlineStr"><is><t>Wskaż prawdziwe połączenie lek-wskazanie:</t></is></c><c r="F50" s="2" t="inlineStr"><is><t>Sulpiryd – schizofrenia</t></is></c><c r="G50" s="2" t="inlineStr"><is><t>Metylofenidat – ADHD</t></is></c><c r="H50" s="2" t="inlineStr" /><c r="I50" s="2" t="inlineStr" /><c r="J50" s="2" t="inlineStr" /><c r="K50" s="2" t="inlineStr"><is><t>Moklobemid – bezsenność</t></is></c><c r="L50" s="2" t="inlineStr"><is><t>Sertindol – depresja</t></is></c><c r="M50" s="2" t="inlineStr" /><c r="N50" s="2" t="inlineStr" /><c r="O50" s="2" t="inlineStr" /><c r="P50" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q50" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="51"><c r="A51" s="2" t="inlineStr"><is><t>LEKI PRZECIWPSYCHOTYCZNE</t></is></c><c r="B51" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C51" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D51" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E51" s="2" t="inlineStr"><is><t>Hiperprolaktynemia może wiązać się z leczeniem:</t></is></c><c r="F51" s="2" t="inlineStr"><is><t>Promazyną</t></is></c><c r="G51" s="2" t="inlineStr"><is><t>Rysperydonem</t></is></c><c r="H51" s="2" t="inlineStr"><is><t>Metoklopramidem</t></is></c><c r="I51" s="2" t="inlineStr" /><c r="J51" s="2" t="inlineStr" /><c r="K51" s="2" t="inlineStr"><is><t>Bromokryptyną</t></is></c><c r="L51" s="2" t="inlineStr" /><c r="M51" s="2" t="inlineStr" /><c r="N51" s="2" t="inlineStr" /><c r="O51" s="2" t="inlineStr" /><c r="P51" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q51" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="52"><c r="A52" s="2" t="inlineStr"><is><t>UKŁAD WSPÓŁCZULNY</t></is></c><c r="B52" s="2" t="inlineStr"><is><t>Antidotum</t></is></c><c r="C52" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D52" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E52" s="2" t="inlineStr"><is><t>Ośrodkowy zespół cholinolityczny może wystąpić w wyniku ostrego przedawkowania:</t></is></c><c r="F52" s="2" t="inlineStr"><is><t>Doksepiny</t></is></c><c r="G52" s="2" t="inlineStr"><is><t>Olanzapiny</t></is></c><c r="H52" s="2" t="inlineStr"><is><t>Perfenazyny</t></is></c><c r="I52" s="2" t="inlineStr"><is><t>Klemastyny</t></is></c><c r="J52" s="2" t="inlineStr" /><c r="K52" s="2" t="inlineStr" /><c r="L52" s="2" t="inlineStr" /><c r="M52" s="2" t="inlineStr" /><c r="N52" s="2" t="inlineStr" /><c r="O52" s="2" t="inlineStr" /><c r="P52" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q52" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="53"><c r="A53" s="2" t="inlineStr"><is><t>NIEOPIOIDOWE LEKI PRZECIWBÓLOWE</t></is></c><c r="B53" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C53" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D53" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E53" s="2" t="inlineStr"><is><t>Wskaż prawdziwe stwierdzenie dotyczące metamizolu:</t></is></c><c r="F53" s="2" t="inlineStr"><is><t>Podczas szybkiego wstrzykiwania dożylnego leku może dojść do gwałtownych spadków ciśnienia krwi</t></is></c><c r="G53" s="2" t="inlineStr"><is><t>Może powodować ciężkie uszkodzenia szpiku w mechanizmie nadwrażliwości</t></is></c><c r="H53" s="2" t="inlineStr"><is><t>Zwiększa częstość występowania guzów Wilmsa (nephroblastoma, nerczak zarodkowy)</t></is></c><c r="I53" s="2" t="inlineStr" /><c r="J53" s="2" t="inlineStr" /><c r="K53" s="2" t="inlineStr"><is><t>Ma silne działanie przeciwzapalne</t></is></c><c r="L53" s="2" t="inlineStr" /><c r="M53" s="2" t="inlineStr" /><c r="N53" s="2" t="inlineStr" /><c r="O53" s="2" t="inlineStr" /><c r="P53" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q53" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="54"><c r="A54" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B54" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C54" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D54" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E54" s="2" t="inlineStr"><is><t>Które połączenie lekowe jest bezwzględnie konieczne w wymienionej sytuacji klinicznej:</t></is></c><c r="F54" s="2" t="inlineStr"><is><t>Sartan + sakubitryl w skurczowej niewydolności serca</t></is></c><c r="G54" s="2" t="inlineStr"><is><t>Kwas acetylosalicylowy + antagonista receptorów P2Y12 po angioplastyce wieńcowej z implantacją stentu</t></is></c><c r="H54" s="2" t="inlineStr" /><c r="I54" s="2" t="inlineStr" /><c r="J54" s="2" t="inlineStr" /><c r="K54" s="2" t="inlineStr"><is><t>Heparyna drobnocząsteczkowa + ksaban w początkowym okresie leczenia żylnej choroby zakrzepowo zatorowej</t></is></c><c r="L54" s="2" t="inlineStr"><is><t>Adrenalina + atropina w resuscytacji krążeniowo-oddechowej w przebiegu NZK z asystolią</t></is></c><c r="M54" s="2" t="inlineStr" /><c r="N54" s="2" t="inlineStr" /><c r="O54" s="2" t="inlineStr" /><c r="P54" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q54" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="55"><c r="A55" s="2" t="inlineStr"><is><t>UKŁAD PRZYWSPÓŁCZULNY</t></is></c><c r="B55" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C55" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D55" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E55" s="2" t="inlineStr"><is><t>Efekt prokinetyczny można uzyskać:</t></is></c><c r="F55" s="2" t="inlineStr"><is><t>Pobudzając receptory 5-HT4</t></is></c><c r="G55" s="2" t="inlineStr"><is><t>Blokując receptory dopaminowe D2</t></is></c><c r="H55" s="2" t="inlineStr"><is><t>Hamując aktywność acetylocholinoesterazy</t></is></c><c r="I55" s="2" t="inlineStr"><is><t>Pobudzając receptory motylinowe</t></is></c><c r="J55" s="2" t="inlineStr" /><c r="K55" s="2" t="inlineStr" /><c r="L55" s="2" t="inlineStr" /><c r="M55" s="2" t="inlineStr" /><c r="N55" s="2" t="inlineStr" /><c r="O55" s="2" t="inlineStr" /><c r="P55" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q55" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="56"><c r="A56" s="2" t="inlineStr"><is><t>CUKRZYCA</t></is></c><c r="B56" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C56" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D56" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E56" s="2" t="inlineStr"><is><t>Glukagon:</t></is></c><c r="F56" s="2" t="inlineStr"><is><t>Stosowany jest w leczeniu ciężkiej hipoglikemii gdy nie można podać dożylnie glukozy</t></is></c><c r="G56" s="2" t="inlineStr"><is><t>Jest podawany parenteralnie</t></is></c><c r="H56" s="2" t="inlineStr"><is><t>Ma zastosowanie w zatruciach lekami beta-adrenolitycznymi</t></is></c><c r="I56" s="2" t="inlineStr"><is><t>Jest nieskuteczny w przypadku glikemii</t></is></c><c r="J56" s="2" t="inlineStr" /><c r="K56" s="2" t="inlineStr" /><c r="L56" s="2" t="inlineStr" /><c r="M56" s="2" t="inlineStr" /><c r="N56" s="2" t="inlineStr" /><c r="O56" s="2" t="inlineStr" /><c r="P56" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q56" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="57"><c r="A57" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B57" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C57" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D57" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E57" s="2" t="inlineStr"><is><t>Ryzyko encefalopatii w przebiegu marskości wątroby zmniejsza stosowanie:</t></is></c><c r="F57" s="2" t="inlineStr"><is><t>Ryfaksyminy</t></is></c><c r="G57" s="2" t="inlineStr"><is><t>Asparaginianu ornityny</t></is></c><c r="H57" s="2" t="inlineStr"><is><t>Laktulozy</t></is></c><c r="I57" s="2" t="inlineStr" /><c r="J57" s="2" t="inlineStr" /><c r="K57" s="2" t="inlineStr"><is><t>Benzodiazepin</t></is></c><c r="L57" s="2" t="inlineStr" /><c r="M57" s="2" t="inlineStr" /><c r="N57" s="2" t="inlineStr" /><c r="O57" s="2" t="inlineStr" /><c r="P57" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q57" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="58"><c r="A58" s="2" t="inlineStr"><is><t>UKŁAD ODDECHOWY</t></is></c><c r="B58" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C58" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D58" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E58" s="2" t="inlineStr"><is><t>W celu przerwania ataku duszności uzasadnione jest podanie wziewne:</t></is></c><c r="F58" s="2" t="inlineStr"><is><t>Bromku ipratriopium</t></is></c><c r="G58" s="2" t="inlineStr"><is><t>Salbutamolu</t></is></c><c r="H58" s="2" t="inlineStr" /><c r="I58" s="2" t="inlineStr" /><c r="J58" s="2" t="inlineStr" /><c r="K58" s="2" t="inlineStr"><is><t>Roflumilastu</t></is></c><c r="L58" s="2" t="inlineStr"><is><t>flutykazonu</t></is></c><c r="M58" s="2" t="inlineStr" /><c r="N58" s="2" t="inlineStr" /><c r="O58" s="2" t="inlineStr" /><c r="P58" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q58" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="59"><c r="A59" s="2" t="inlineStr"><is><t>GLIKOKORTYKOSTEROIDY</t></is></c><c r="B59" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C59" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D59" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E59" s="2" t="inlineStr"><is><t>W leczeniu małopłytkowości stosuje się:</t></is></c><c r="F59" s="2" t="inlineStr"><is><t>Preparaty immunoglobulin poliwalentnych</t></is></c><c r="G59" s="2" t="inlineStr"><is><t>Eltrombopag</t></is></c><c r="H59" s="2" t="inlineStr"><is><t>Romiplostym</t></is></c><c r="I59" s="2" t="inlineStr"><is><t>Prednizon</t></is></c><c r="J59" s="2" t="inlineStr" /><c r="K59" s="2" t="inlineStr" /><c r="L59" s="2" t="inlineStr" /><c r="M59" s="2" t="inlineStr" /><c r="N59" s="2" t="inlineStr" /><c r="O59" s="2" t="inlineStr" /><c r="P59" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q59" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="60"><c r="A60" s="2" t="inlineStr"><is><t>LEKI PRZECIWNOWOTWOROWE</t></is></c><c r="B60" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C60" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D60" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E60" s="2" t="inlineStr"><is><t>Ewerolimus jest stosowany w:</t></is></c><c r="F60" s="2" t="inlineStr"><is><t>Kardiologii (stenty wieńcowe)</t></is></c><c r="G60" s="2" t="inlineStr"><is><t>Onkologii (wybrane zaawansowane nowotwory piersi i nerki)</t></is></c><c r="H60" s="2" t="inlineStr" /><c r="I60" s="2" t="inlineStr" /><c r="J60" s="2" t="inlineStr" /><c r="K60" s="2" t="inlineStr"><is><t>Neurologii (stwardnienie rozsiane)</t></is></c><c r="L60" s="2" t="inlineStr"><is><t>Dermatologii (łuszczyca)</t></is></c><c r="M60" s="2" t="inlineStr" /><c r="N60" s="2" t="inlineStr" /><c r="O60" s="2" t="inlineStr" /><c r="P60" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q60" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="61"><c r="A61" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B61" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C61" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D61" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E61" s="2" t="inlineStr"><is><t>Wskaż prawdziwe zdanie:</t></is></c><c r="F61" s="2" t="inlineStr"><is><t>W chromaniu przestankowym znaczenie kliniczne ma leczenie przeciwpłytkowe i hipolipemizujące</t></is></c><c r="G61" s="2" t="inlineStr"><is><t>Zaleca się podawanie inhibitora P2Y12 przed przezskórną interwencją wieńcową u osoby z ostrym zespołem wieńcowym, a następnie kontynuację tego leczenia przez co najmniej 12 miesięcy</t></is></c><c r="H61" s="2" t="inlineStr"><is><t>Po rozpoczęciu leczenia inhibitorami konwertazy angiotensyny należy się spodziewać niewielkiego wzrostu stężenia kreatyniny we krwi</t></is></c><c r="I61" s="2" t="inlineStr" /><c r="J61" s="2" t="inlineStr" /><c r="K61" s="2" t="inlineStr"><is><t>Niedihydropirydynowi antagoniści wapnia są wskazani w leczeniu pacjentów z niewydolnością serca z obniżoną frakcją wyrzutową</t></is></c><c r="L61" s="2" t="inlineStr" /><c r="M61" s="2" t="inlineStr" /><c r="N61" s="2" t="inlineStr" /><c r="O61" s="2" t="inlineStr" /><c r="P61" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q61" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="62"><c r="A62" s="2" t="inlineStr"><is><t>ZABURZENIA RYTMU SERCA</t></is></c><c r="B62" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C62" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D62" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E62" s="2" t="inlineStr"><is><t>U osób z pierwotnym wydłużenie QTc bezpieczne jest zastosowanie:</t></is></c><c r="F62" s="2" t="inlineStr"><is><t>Propranololu</t></is></c><c r="G62" s="2" t="inlineStr" /><c r="H62" s="2" t="inlineStr" /><c r="I62" s="2" t="inlineStr" /><c r="J62" s="2" t="inlineStr" /><c r="K62" s="2" t="inlineStr"><is><t>Digoksyny</t></is></c><c r="L62" s="2" t="inlineStr"><is><t>Sotalolu</t></is></c><c r="M62" s="2" t="inlineStr"><is><t>Amiodaronu</t></is></c><c r="N62" s="2" t="inlineStr" /><c r="O62" s="2" t="inlineStr" /><c r="P62" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q62" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="63"><c r="A63" s="2" t="inlineStr"><is><t>CHOROBA NIEDOKRWIENNA SERCA</t></is></c><c r="B63" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C63" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D63" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E63" s="2" t="inlineStr"><is><t>Beta-adrenolityki można zastosować w:</t></is></c><c r="F63" s="2" t="inlineStr"><is><t>Tachykardii zatokowej</t></is></c><c r="G63" s="2" t="inlineStr"><is><t>Niewydolności mięśnia serca z upośledzoną frakcją wyrzutową</t></is></c><c r="H63" s="2" t="inlineStr"><is><t>W kontroli rytmu komór w migotaniu przedsionków</t></is></c><c r="I63" s="2" t="inlineStr" /><c r="J63" s="2" t="inlineStr" /><c r="K63" s="2" t="inlineStr"><is><t>Naczynioskurczowym wariancie choroby niedokrwiennej serca</t></is></c><c r="L63" s="2" t="inlineStr" /><c r="M63" s="2" t="inlineStr" /><c r="N63" s="2" t="inlineStr" /><c r="O63" s="2" t="inlineStr" /><c r="P63" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q63" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="64"><c r="A64" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B64" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C64" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D64" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E64" s="2" t="inlineStr"><is><t>Lidokaina:</t></is></c><c r="F64" s="2" t="inlineStr"><is><t>Jest skuteczna w znieczulaniu nasiękowym</t></is></c><c r="G64" s="2" t="inlineStr"><is><t>Jest metabolizowana w wątrobie</t></is></c><c r="H64" s="2" t="inlineStr"><is><t>Może powodować drgawki</t></is></c><c r="I64" s="2" t="inlineStr" /><c r="J64" s="2" t="inlineStr" /><c r="K64" s="2" t="inlineStr"><is><t>Silnie blokuje kanały potasowe</t></is></c><c r="L64" s="2" t="inlineStr" /><c r="M64" s="2" t="inlineStr" /><c r="N64" s="2" t="inlineStr" /><c r="O64" s="2" t="inlineStr" /><c r="P64" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q64" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="65"><c r="A65" s="2" t="inlineStr"><is><t>NADCIŚNIENIE TĘTNICZE</t></is></c><c r="B65" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C65" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D65" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E65" s="2" t="inlineStr"><is><t>Wskaż prawdziwe połączenie lek-działanie niepożądane:</t></is></c><c r="F65" s="2" t="inlineStr"><is><t>Ramipryl-obrzęk naczynioruchowy</t></is></c><c r="G65" s="2" t="inlineStr"><is><t>Metoprolol-zasłabnięcie lub omdlenie</t></is></c><c r="H65" s="2" t="inlineStr" /><c r="I65" s="2" t="inlineStr" /><c r="J65" s="2" t="inlineStr" /><c r="K65" s="2" t="inlineStr"><is><t>Losartan-zwiększenie stężenia kwasu moczowego</t></is></c><c r="L65" s="2" t="inlineStr"><is><t>Simwastatyna-poprawa tolerancji glukozy</t></is></c><c r="M65" s="2" t="inlineStr" /><c r="N65" s="2" t="inlineStr" /><c r="O65" s="2" t="inlineStr" /><c r="P65" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q65" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="66"><c r="A66" s="2" t="inlineStr"><is><t>LEKI MOCZOPĘDNE</t></is></c><c r="B66" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C66" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D66" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E66" s="2" t="inlineStr"><is><t>Która ordynacja jest błędna i wymaga korekty?</t></is></c><c r="F66" s="2" t="inlineStr"><is><t>Furosemid p.o. 1xd w obrzękach pochodzenia sercowego</t></is></c><c r="G66" s="2" t="inlineStr"><is><t>Hydrochlorotiazyd p.o. 1xd w obrzękach kończyn dolnych w przebiegu zespołu pozakrzepowego podudzi</t></is></c><c r="H66" s="2" t="inlineStr" /><c r="I66" s="2" t="inlineStr" /><c r="J66" s="2" t="inlineStr" /><c r="K66" s="2" t="inlineStr"><is><t>Torasemid p.o. 1xd w obrzękach pochodzenia nerkowego</t></is></c><c r="L66" s="2" t="inlineStr"><is><t>Spironolakton p.o. 1xd w wodobrzuszu w przebiegu niewydolności wątroby</t></is></c><c r="M66" s="2" t="inlineStr" /><c r="N66" s="2" t="inlineStr" /><c r="O66" s="2" t="inlineStr" /><c r="P66" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q66" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="67"><c r="A67" s="2" t="inlineStr"><is><t>NADCIŚNIENIE TĘTNICZE</t></is></c><c r="B67" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C67" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D67" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E67" s="2" t="inlineStr"><is><t>Koangiokardianem, czyli lekiem działającym bezpośrednio na serce i naczynia jest:</t></is></c><c r="F67" s="2" t="inlineStr"><is><t>Lewosymendan</t></is></c><c r="G67" s="2" t="inlineStr" /><c r="H67" s="2" t="inlineStr" /><c r="I67" s="2" t="inlineStr" /><c r="J67" s="2" t="inlineStr" /><c r="K67" s="2" t="inlineStr"><is><t>Midodryna</t></is></c><c r="L67" s="2" t="inlineStr"><is><t>Epoprostenol</t></is></c><c r="M67" s="2" t="inlineStr"><is><t>Riocyguat</t></is></c><c r="N67" s="2" t="inlineStr" /><c r="O67" s="2" t="inlineStr" /><c r="P67" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q67" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="68"><c r="A68" s="2" t="inlineStr"><is><t>OSTEOPOROZA</t></is></c><c r="B68" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C68" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D68" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E68" s="2" t="inlineStr"><is><t>Wskaż prawdziwe stwierdzenie dotyczące bisfosfonianów:</t></is></c><c r="F68" s="2" t="inlineStr"><is><t>Są lekami pierwszego rzutu w profilaktyce i leczeniu osteoporozy pomenopauzalnej u kobiet</t></is></c><c r="G68" s="2" t="inlineStr"><is><t>Mogą być stosowane w zapobieganiu i leczeniu osteoporozy posteroidowej</t></is></c><c r="H68" s="2" t="inlineStr"><is><t>U osób z przerzutami nowotworowymi do układu kostnego łagodzą bóle kostne</t></is></c><c r="I68" s="2" t="inlineStr"><is><t>Przeciwwskazaniem do ich podawania jest ciężka niewydolność nerek (GFR&lt;30)</t></is></c><c r="J68" s="2" t="inlineStr" /><c r="K68" s="2" t="inlineStr" /><c r="L68" s="2" t="inlineStr" /><c r="M68" s="2" t="inlineStr" /><c r="N68" s="2" t="inlineStr" /><c r="O68" s="2" t="inlineStr" /><c r="P68" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q68" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="69"><c r="A69" s="2" t="inlineStr"><is><t>LEKI HIPOLIPEMIZUJĄCE</t></is></c><c r="B69" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C69" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D69" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E69" s="2" t="inlineStr"><is><t>Zmniejszenie hipertriglicerydemii można osiągnąć stosując:</t></is></c><c r="F69" s="2" t="inlineStr"><is><t>Atorwastatynę</t></is></c><c r="G69" s="2" t="inlineStr"><is><t>Fenofibrat</t></is></c><c r="H69" s="2" t="inlineStr"><is><t>PUFA-wielonienasycone kwasy tłuszczowe</t></is></c><c r="I69" s="2" t="inlineStr" /><c r="J69" s="2" t="inlineStr" /><c r="K69" s="2" t="inlineStr"><is><t>Koleswelam</t></is></c><c r="L69" s="2" t="inlineStr" /><c r="M69" s="2" t="inlineStr" /><c r="N69" s="2" t="inlineStr" /><c r="O69" s="2" t="inlineStr" /><c r="P69" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q69" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="70"><c r="A70" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B70" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C70" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D70" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E70" s="2" t="inlineStr"><is><t>Lekiem wydłużającym dystans chromania przestankowego jest:</t></is></c><c r="F70" s="2" t="inlineStr"><is><t>Natydrofuryl</t></is></c><c r="G70" s="2" t="inlineStr"><is><t>Cilostazol</t></is></c><c r="H70" s="2" t="inlineStr" /><c r="I70" s="2" t="inlineStr" /><c r="J70" s="2" t="inlineStr" /><c r="K70" s="2" t="inlineStr"><is><t>Pentoksyfilina</t></is></c><c r="L70" s="2" t="inlineStr"><is><t>Diosmina mikronizowana</t></is></c><c r="M70" s="2" t="inlineStr" /><c r="N70" s="2" t="inlineStr" /><c r="O70" s="2" t="inlineStr" /><c r="P70" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q70" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="71"><c r="A71" s="2" t="inlineStr"><is><t>LEKI HIPOLIPEMIZUJĄCE</t></is></c><c r="B71" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C71" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D71" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E71" s="2" t="inlineStr"><is><t>W prawidłowo przeprowadzonym leczeniu statynami należy:</t></is></c><c r="F71" s="2" t="inlineStr"><is><t>Oznaczyć aktywność ALAT i CK w surowicy przed rozpoczęciem leczenia</t></is></c><c r="G71" s="2" t="inlineStr"><is><t>Odstawić statynę jeśli aktywność ALAT przekroczy w surowicy 3-krotnie górną granicę wartości prawidłowych</t></is></c><c r="H71" s="2" t="inlineStr" /><c r="I71" s="2" t="inlineStr" /><c r="J71" s="2" t="inlineStr" /><c r="K71" s="2" t="inlineStr"><is><t>Ocenić skuteczność leczenia hipolipemizującego po 2 tygodniach od jego rozpoczęcia</t></is></c><c r="L71" s="2" t="inlineStr"><is><t>Mintorować aktywność CK u każdego pacjenta</t></is></c><c r="M71" s="2" t="inlineStr" /><c r="N71" s="2" t="inlineStr" /><c r="O71" s="2" t="inlineStr" /><c r="P71" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q71" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="72"><c r="A72" s="2" t="inlineStr"><is><t>NADCIŚNIENIE TĘTNICZE</t></is></c><c r="B72" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C72" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D72" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E72" s="2" t="inlineStr"><is><t>Na kanały sodowe ma wpływ:</t></is></c><c r="F72" s="2" t="inlineStr"><is><t>Ranolazyna</t></is></c><c r="G72" s="2" t="inlineStr"><is><t>Iwabradyna</t></is></c><c r="H72" s="2" t="inlineStr" /><c r="I72" s="2" t="inlineStr" /><c r="J72" s="2" t="inlineStr" /><c r="K72" s="2" t="inlineStr"><is><t>Adenozyna</t></is></c><c r="L72" s="2" t="inlineStr"><is><t>Nitrendypina</t></is></c><c r="M72" s="2" t="inlineStr" /><c r="N72" s="2" t="inlineStr" /><c r="O72" s="2" t="inlineStr" /><c r="P72" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q72" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="73"><c r="A73" s="2" t="inlineStr"><is><t>FARMAKOKINETYKA</t></is></c><c r="B73" s="2" t="inlineStr"><is><t>Interakcje</t></is></c><c r="C73" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D73" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E73" s="2" t="inlineStr"><is><t>Interakcją farmakokinetyczną jest:</t></is></c><c r="F73" s="2" t="inlineStr"><is><t>Hamowanie wchłaniania z przewodu pokarmowego leków podawanych jednocześnie</t></is></c><c r="G73" s="2" t="inlineStr"><is><t>Zwiększanie metabolizmu leków podawanych jednocześnie</t></is></c><c r="H73" s="2" t="inlineStr" /><c r="I73" s="2" t="inlineStr" /><c r="J73" s="2" t="inlineStr" /><c r="K73" s="2" t="inlineStr"><is><t>Wytrącanie się osadu po zmieszaniu dwóch leków w jednym roztworze do wstrzyknięcia</t></is></c><c r="L73" s="2" t="inlineStr"><is><t>Nasilenie sedacji po skojarzeniu opioidów z etanolem</t></is></c><c r="M73" s="2" t="inlineStr" /><c r="N73" s="2" t="inlineStr" /><c r="O73" s="2" t="inlineStr" /><c r="P73" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q73" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="74"><c r="A74" s="2" t="inlineStr"><is><t>NARKOTYCZNE LEKI PRZECIWBÓLOWE</t></is></c><c r="B74" s="2" t="inlineStr"><is><t>Antidotum</t></is></c><c r="C74" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D74" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E74" s="2" t="inlineStr"><is><t>Właściwości farmakodynamiczne i parametry farmakokinetyczne leków mają wpływ na podejmowanie decyzji klinicznych. Czy słuszne jest wobec tego:</t></is></c><c r="F74" s="2" t="inlineStr"><is><t>Wielokrotne powtórzenie dawki naloksonu(t1/2=63min+/-12min) po przedawkowaniu metadonu</t></is></c><c r="G74" s="2" t="inlineStr" /><c r="H74" s="2" t="inlineStr" /><c r="I74" s="2" t="inlineStr" /><c r="J74" s="2" t="inlineStr" /><c r="K74" s="2" t="inlineStr"><is><t>Przetoczenie koncentratu płytek krwi 13h po podaniu tikagrelolu (tikagrelol ze swoim czynnym metabolitem mają łączny czas półtrwania eliminacji 12h)</t></is></c><c r="L74" s="2" t="inlineStr"><is><t>Odstawienie suplementacji potasu w hiperaldosteronizmie pierwotnym po 16-17h po włączeniu spironolaktonu (Cmax karnenonu=16,5h po podaniu spironolaktonu)</t></is></c><c r="M74" s="2" t="inlineStr"><is><t>Przeprowadzenie operacji neurochirurgicznej po 36h po odstawieniu klopidogrelu(t1/2=6h, jego aktywne mają pomijalnie krótki t1/2)</t></is></c><c r="N74" s="2" t="inlineStr" /><c r="O74" s="2" t="inlineStr" /><c r="P74" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q74" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="75"><c r="A75" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B75" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C75" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D75" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E75" s="2" t="inlineStr"><is><t>Kolistyna:</t></is></c><c r="F75" s="2" t="inlineStr"><is><t>Może być podawana wziewnie u osób z mukowiscydozą</t></is></c><c r="G75" s="2" t="inlineStr"><is><t>Może być stosowana w leczeniu ciężkich zakażeń uogólnionych wywołanych prze Klebsiella pneumoniae wytwarzającą karbapenemazy</t></is></c><c r="H75" s="2" t="inlineStr"><is><t>Wykazuje aktywność wobec Pseudomonas aeruginosa</t></is></c><c r="I75" s="2" t="inlineStr" /><c r="J75" s="2" t="inlineStr" /><c r="K75" s="2" t="inlineStr"><is><t>Jest skuteczna w neuroinfekcjach</t></is></c><c r="L75" s="2" t="inlineStr" /><c r="M75" s="2" t="inlineStr" /><c r="N75" s="2" t="inlineStr" /><c r="O75" s="2" t="inlineStr" /><c r="P75" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q75" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="76"><c r="A76" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B76" s="2" t="inlineStr"><is><t>Ciąża</t></is></c><c r="C76" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D76" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E76" s="2" t="inlineStr"><is><t>Doksycyklina</t></is></c><c r="F76" s="2" t="inlineStr"><is><t>Działa na bakterie atypowe</t></is></c><c r="G76" s="2" t="inlineStr" /><c r="H76" s="2" t="inlineStr" /><c r="I76" s="2" t="inlineStr" /><c r="J76" s="2" t="inlineStr" /><c r="K76" s="2" t="inlineStr"><is><t>Może być bezpiecznie stosowana u dzieci powyżej 2r.ż</t></is></c><c r="L76" s="2" t="inlineStr"><is><t>Jest anatgonistą receptorów GABA-A wywołujących efekt sedatywny</t></is></c><c r="M76" s="2" t="inlineStr"><is><t>Jest bezpieczna w terapii kobiet w ciąży</t></is></c><c r="N76" s="2" t="inlineStr" /><c r="O76" s="2" t="inlineStr" /><c r="P76" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q76" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="77"><c r="A77" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B77" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C77" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D77" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E77" s="2" t="inlineStr"><is><t>Wskaż prawdziwe połączenie lek-mechanizm działania:</t></is></c><c r="F77" s="2" t="inlineStr"><is><t>Fosfomycyna-blokowanie syntezy ściany komórkowej bakterii</t></is></c><c r="G77" s="2" t="inlineStr" /><c r="H77" s="2" t="inlineStr" /><c r="I77" s="2" t="inlineStr" /><c r="J77" s="2" t="inlineStr" /><c r="K77" s="2" t="inlineStr"><is><t>Cefepim-hamowanie topoizomerazy II</t></is></c><c r="L77" s="2" t="inlineStr"><is><t>Pefloksacyna-hamowanie biosyntezy białka w komórkach bakterii poprzez wiązanie się z podjednostką 50S rybosomu</t></is></c><c r="M77" s="2" t="inlineStr"><is><t>Trimetoprim-bezpośrednie uszkodzenie DNA</t></is></c><c r="N77" s="2" t="inlineStr" /><c r="O77" s="2" t="inlineStr" /><c r="P77" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q77" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="78"><c r="A78" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B78" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C78" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D78" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E78" s="2" t="inlineStr"><is><t>Wskaż prawdziwe połączenie lek-działania niepożądane:</t></is></c><c r="F78" s="2" t="inlineStr"><is><t>Amoksycylina-leukopenia w mechanizmie nadwrażliwości immunologicznej</t></is></c><c r="G78" s="2" t="inlineStr"><is><t>Tynidazol-neuropatia obwodowa</t></is></c><c r="H78" s="2" t="inlineStr"><is><t>Amikacyna-zaburzenia słuchu i równowagi</t></is></c><c r="I78" s="2" t="inlineStr" /><c r="J78" s="2" t="inlineStr" /><c r="K78" s="2" t="inlineStr"><is><t>Roksytromycyna-uszkodzenie nerek</t></is></c><c r="L78" s="2" t="inlineStr" /><c r="M78" s="2" t="inlineStr" /><c r="N78" s="2" t="inlineStr" /><c r="O78" s="2" t="inlineStr" /><c r="P78" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q78" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="79"><c r="A79" s="2" t="inlineStr"><is><t>LEKI PRZECIWWIRUSOWE</t></is></c><c r="B79" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C79" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D79" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E79" s="2" t="inlineStr"><is><t>Właściwy wybór leku przeciwwirusowego w zakażeniu to:</t></is></c><c r="F79" s="2" t="inlineStr"><is><t>Wirus HBV-lamiwudyna</t></is></c><c r="G79" s="2" t="inlineStr"><is><t>Cytomegalowirus-walgancyklowir</t></is></c><c r="H79" s="2" t="inlineStr" /><c r="I79" s="2" t="inlineStr" /><c r="J79" s="2" t="inlineStr" /><c r="K79" s="2" t="inlineStr"><is><t>Norowirus-sakwinawir</t></is></c><c r="L79" s="2" t="inlineStr"><is><t>Wirus opryszczki-rybawiryna</t></is></c><c r="M79" s="2" t="inlineStr" /><c r="N79" s="2" t="inlineStr" /><c r="O79" s="2" t="inlineStr" /><c r="P79" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q79" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="80"><c r="A80" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B80" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C80" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D80" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E80" s="2" t="inlineStr"><is><t>Wskaż prawdziwe połączenie lek-wrażliwy drobnoustrój:</t></is></c><c r="F80" s="2" t="inlineStr"><is><t>Lewofloksacyna-Streptococcus pneumoniae</t></is></c><c r="G80" s="2" t="inlineStr"><is><t>Aksetyl cefuroksymu-Hemophilus influenzae</t></is></c><c r="H80" s="2" t="inlineStr" /><c r="I80" s="2" t="inlineStr" /><c r="J80" s="2" t="inlineStr" /><c r="K80" s="2" t="inlineStr"><is><t>Fenoksymetylopenicylina-Staphylococcus aureus MSSA</t></is></c><c r="L80" s="2" t="inlineStr"><is><t>Fidaksomycyna-Bacteroides fragilis</t></is></c><c r="M80" s="2" t="inlineStr" /><c r="N80" s="2" t="inlineStr" /><c r="O80" s="2" t="inlineStr" /><c r="P80" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q80" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="81"><c r="A81" s="2" t="inlineStr"><is><t>LEKI PRZECIWGRZYBICZE</t></is></c><c r="B81" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C81" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D81" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E81" s="2" t="inlineStr"><is><t>Flukonazol:</t></is></c><c r="F81" s="2" t="inlineStr"><is><t>W leczeniu kandydozy jamy ustnej nie jest skuteczny po podaniu dawki jednorazowej</t></is></c><c r="G81" s="2" t="inlineStr" /><c r="H81" s="2" t="inlineStr" /><c r="I81" s="2" t="inlineStr" /><c r="J81" s="2" t="inlineStr" /><c r="K81" s="2" t="inlineStr"><is><t>Ma małą biodostępność po podaniu doustnym</t></is></c><c r="L81" s="2" t="inlineStr"><is><t>Powinien być podawany profilaktycznie pacjentom leczonym szerokospektralnymi lekami przeciwbakteryjnymi z powodu zakażenia układu oddechowego</t></is></c><c r="M81" s="2" t="inlineStr"><is><t>Istotnie hamuje syntezę hormonów steroidowych</t></is></c><c r="N81" s="2" t="inlineStr" /><c r="O81" s="2" t="inlineStr" /><c r="P81" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q81" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="82"><c r="A82" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B82" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C82" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D82" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E82" s="2" t="inlineStr"><is><t>Wyłącznie na ustroje gram dodatnie działa:</t></is></c><c r="F82" s="2" t="inlineStr"><is><t>Mupriocyna</t></is></c><c r="G82" s="2" t="inlineStr" /><c r="H82" s="2" t="inlineStr" /><c r="I82" s="2" t="inlineStr" /><c r="J82" s="2" t="inlineStr" /><c r="K82" s="2" t="inlineStr"><is><t>Metronidazol</t></is></c><c r="L82" s="2" t="inlineStr"><is><t>Fosfomycyna</t></is></c><c r="M82" s="2" t="inlineStr"><is><t>Gentamycyna</t></is></c><c r="N82" s="2" t="inlineStr" /><c r="O82" s="2" t="inlineStr" /><c r="P82" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q82" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="83"><c r="A83" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B83" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C83" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D83" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E83" s="2" t="inlineStr"><is><t>W leczeniu rzęsistkowicy (Trichomonas Vaginalis) wykorzystuje się:</t></is></c><c r="F83" s="2" t="inlineStr"><is><t>Tynidazol</t></is></c><c r="G83" s="2" t="inlineStr"><is><t>Metronidazol</t></is></c><c r="H83" s="2" t="inlineStr" /><c r="I83" s="2" t="inlineStr" /><c r="J83" s="2" t="inlineStr" /><c r="K83" s="2" t="inlineStr"><is><t>Sulfametoksazol+trymetoprym</t></is></c><c r="L83" s="2" t="inlineStr"><is><t>Spiramycynę</t></is></c><c r="M83" s="2" t="inlineStr" /><c r="N83" s="2" t="inlineStr" /><c r="O83" s="2" t="inlineStr" /><c r="P83" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q83" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="84"><c r="A84" s="2" t="inlineStr"><is><t>LEKI PRZECIWWIRUSOWE</t></is></c><c r="B84" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C84" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D84" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E84" s="2" t="inlineStr"><is><t>Do charakterystycznych działań niepożądanych inhibitorów proteazy HIV należy/należą:</t></is></c><c r="F84" s="2" t="inlineStr"><is><t>Liczne interakcje lekowe</t></is></c><c r="G84" s="2" t="inlineStr"><is><t>Cukrzyca</t></is></c><c r="H84" s="2" t="inlineStr"><is><t>Uszkodzenie wątroby</t></is></c><c r="I84" s="2" t="inlineStr"><is><t>Hipertriglicerydemia</t></is></c><c r="J84" s="2" t="inlineStr" /><c r="K84" s="2" t="inlineStr" /><c r="L84" s="2" t="inlineStr" /><c r="M84" s="2" t="inlineStr" /><c r="N84" s="2" t="inlineStr" /><c r="O84" s="2" t="inlineStr" /><c r="P84" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q84" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="85"><c r="A85" s="2" t="inlineStr"><is><t>LEKI PRZECIWGRZYBICZE</t></is></c><c r="B85" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C85" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D85" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E85" s="2" t="inlineStr"><is><t>W zakażeniu o etiologii Candida albicans można zastosować miejscowo:</t></is></c><c r="F85" s="2" t="inlineStr"><is><t>Natamycynę</t></is></c><c r="G85" s="2" t="inlineStr"><is><t>Mykonazol</t></is></c><c r="H85" s="2" t="inlineStr" /><c r="I85" s="2" t="inlineStr" /><c r="J85" s="2" t="inlineStr" /><c r="K85" s="2" t="inlineStr"><is><t>Mykafunginę</t></is></c><c r="L85" s="2" t="inlineStr"><is><t>Izawukonazol</t></is></c><c r="M85" s="2" t="inlineStr" /><c r="N85" s="2" t="inlineStr" /><c r="O85" s="2" t="inlineStr" /><c r="P85" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q85" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="86"><c r="A86" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B86" s="2" t="inlineStr"><is><t>Monitorowanie</t></is></c><c r="C86" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D86" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E86" s="2" t="inlineStr"><is><t>Jeśli celem farmakodynamicznym dla stosowanego antybiotyku jest wysoka wartość T&gt;MIC to powinno się:</t></is></c><c r="F86" s="2" t="inlineStr"><is><t>Monitorować stężenie leku we krwi w celu modyfikacji dawkowania</t></is></c><c r="G86" s="2" t="inlineStr"><is><t>Podawać lek w przedłużonym wlewie dożylnym</t></is></c><c r="H86" s="2" t="inlineStr"><is><t>Zwiększać częstość podawania leku w ciągu doby</t></is></c><c r="I86" s="2" t="inlineStr" /><c r="J86" s="2" t="inlineStr" /><c r="K86" s="2" t="inlineStr"><is><t>Podać lek w pojedynczej skumulowanej dawce dobowej</t></is></c><c r="L86" s="2" t="inlineStr" /><c r="M86" s="2" t="inlineStr" /><c r="N86" s="2" t="inlineStr" /><c r="O86" s="2" t="inlineStr" /><c r="P86" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q86" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="87"><c r="A87" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B87" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C87" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D87" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E87" s="2" t="inlineStr"><is><t>Do przestarzałych środków odkażających, które z powodu braku skuteczności lub istotnych działań niepożądanych nie powinny być obecnie stosowane należy:</t></is></c><c r="F87" s="2" t="inlineStr"><is><t>Nadmanganian potasu</t></is></c><c r="G87" s="2" t="inlineStr"><is><t>Tetraboran sodowy</t></is></c><c r="H87" s="2" t="inlineStr" /><c r="I87" s="2" t="inlineStr" /><c r="J87" s="2" t="inlineStr" /><c r="K87" s="2" t="inlineStr"><is><t>Oktenidyna</t></is></c><c r="L87" s="2" t="inlineStr"><is><t>Jodopowidon</t></is></c><c r="M87" s="2" t="inlineStr" /><c r="N87" s="2" t="inlineStr" /><c r="O87" s="2" t="inlineStr" /><c r="P87" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q87" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="88"><c r="A88" s="2" t="inlineStr"><is><t>LEKI PRZECIWPASOŻYTNICZE</t></is></c><c r="B88" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C88" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D88" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E88" s="2" t="inlineStr"><is><t>Wskaż prawidłowe stwierdzenia dotyczące profilaktyki i leczenia malarii:</t></is></c><c r="F88" s="2" t="inlineStr"><is><t>Lumefantryna w połączeniu z artemeterem może być skuteczna w zakażeniu Plasmodium falciparum</t></is></c><c r="G88" s="2" t="inlineStr"><is><t>W przypadkach wymagających profilaktyki długoterminowej można zastosować chlorochinę</t></is></c><c r="H88" s="2" t="inlineStr" /><c r="I88" s="2" t="inlineStr" /><c r="J88" s="2" t="inlineStr" /><c r="K88" s="2" t="inlineStr"><is><t>Pochodne artemizyniny zalecane są tylko do profilaktyki malarii</t></is></c><c r="L88" s="2" t="inlineStr"><is><t>Atowakwon z proguanilem może być stosowany u osób z upośledzoną czynnością nerek (GFR&lt;30)</t></is></c><c r="M88" s="2" t="inlineStr" /><c r="N88" s="2" t="inlineStr" /><c r="O88" s="2" t="inlineStr" /><c r="P88" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q88" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="89"><c r="A89" s="2" t="inlineStr"><is><t>NADCIŚNIENIE TĘTNICZE</t></is></c><c r="B89" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C89" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D89" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E89" s="2" t="inlineStr"><is><t>Do przyczyn jatrogennej nefropatii można zaliczyć stosowanie:</t></is></c><c r="F89" s="2" t="inlineStr"><is><t>Jodowych środków kontrastowych podczas koronarografii</t></is></c><c r="G89" s="2" t="inlineStr"><is><t>Ibuprofenu przewlekle w reumatoidalnym zapaleniu stawów</t></is></c><c r="H89" s="2" t="inlineStr"><is><t>Ramiprylu w niewydolności serca</t></is></c><c r="I89" s="2" t="inlineStr" /><c r="J89" s="2" t="inlineStr" /><c r="K89" s="2" t="inlineStr"><is><t>Loratadyny przewlekle w alergicznym zapaleniu błony śluzowej nosa</t></is></c><c r="L89" s="2" t="inlineStr" /><c r="M89" s="2" t="inlineStr" /><c r="N89" s="2" t="inlineStr" /><c r="O89" s="2" t="inlineStr" /><c r="P89" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q89" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="90"><c r="A90" s="2" t="inlineStr"><is><t>FARMAKOKINETYKA</t></is></c><c r="B90" s="2" t="inlineStr"><is><t>Farmakokinetyka</t></is></c><c r="C90" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D90" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E90" s="2" t="inlineStr"><is><t>Wskaż prawdziwe zdania dotyczące leczenia morfiną:</t></is></c><c r="F90" s="2" t="inlineStr"><is><t>Metabolity morfiny wydalane są przez nerki</t></is></c><c r="G90" s="2" t="inlineStr"><is><t>Przy przewlekłym stosowaniu morfiny powstaje morfino-6-glukuronian – metabolit, którego siła działania analgetycznego przewyższa siłę działania związku macierzystego</t></is></c><c r="H90" s="2" t="inlineStr"><is><t>Morfina może być podawana zewnątrzoponowo</t></is></c><c r="I90" s="2" t="inlineStr" /><c r="J90" s="2" t="inlineStr" /><c r="K90" s="2" t="inlineStr"><is><t>Morfina ma dużą biodostępność po podaniu doustnym</t></is></c><c r="L90" s="2" t="inlineStr" /><c r="M90" s="2" t="inlineStr" /><c r="N90" s="2" t="inlineStr" /><c r="O90" s="2" t="inlineStr" /><c r="P90" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q90" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="91"><c r="A91" s="2" t="inlineStr"><is><t>CUKRZYCA</t></is></c><c r="B91" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C91" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D91" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E91" s="2" t="inlineStr"><is><t>Wskazanie do insulinoterapii jest:</t></is></c><c r="F91" s="2" t="inlineStr"><is><t>Cukrzyca typu LADA</t></is></c><c r="G91" s="2" t="inlineStr"><is><t>Ostry zespół wieńcowy u osoby z cukrzycą typu II</t></is></c><c r="H91" s="2" t="inlineStr"><is><t>Znaczna hiperglikemia (&gt;300) w przebiegu cukrzycy typu II</t></is></c><c r="I91" s="2" t="inlineStr"><is><t>Cukrzyca ciężarnych</t></is></c><c r="J91" s="2" t="inlineStr" /><c r="K91" s="2" t="inlineStr" /><c r="L91" s="2" t="inlineStr" /><c r="M91" s="2" t="inlineStr" /><c r="N91" s="2" t="inlineStr" /><c r="O91" s="2" t="inlineStr" /><c r="P91" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q91" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="92"><c r="A92" s="2" t="inlineStr"><is><t>CUKRZYCA</t></is></c><c r="B92" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C92" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D92" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E92" s="2" t="inlineStr"><is><t>Długodziałające analogii insuliny w porównaniu do insuliny protaminowo-cynkowej (NPH) charakteryzują się:</t></is></c><c r="F92" s="2" t="inlineStr"><is><t>Mniejszym ryzykiem hipoglikemii</t></is></c><c r="G92" s="2" t="inlineStr" /><c r="H92" s="2" t="inlineStr" /><c r="I92" s="2" t="inlineStr" /><c r="J92" s="2" t="inlineStr" /><c r="K92" s="2" t="inlineStr"><is><t>Mniejszym ryzykiem onkologicznym</t></is></c><c r="L92" s="2" t="inlineStr"><is><t>Większym ryzykiem zjawiska brzasku</t></is></c><c r="M92" s="2" t="inlineStr"><is><t>Działaniem anorektycznym</t></is></c><c r="N92" s="2" t="inlineStr" /><c r="O92" s="2" t="inlineStr" /><c r="P92" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q92" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="93"><c r="A93" s="2" t="inlineStr"><is><t>TARCZYCA</t></is></c><c r="B93" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C93" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D93" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E93" s="2" t="inlineStr"><is><t>Zmniejszenie obwodowej konwersji tyroksyny do trójjodotyroniny jest efektem stosowania:</t></is></c><c r="F93" s="2" t="inlineStr"><is><t>Hydrokortyzonu</t></is></c><c r="G93" s="2" t="inlineStr"><is><t>Propylotiouracylu</t></is></c><c r="H93" s="2" t="inlineStr"><is><t>Propanololu</t></is></c><c r="I93" s="2" t="inlineStr" /><c r="J93" s="2" t="inlineStr" /><c r="K93" s="2" t="inlineStr"><is><t>Płynu Lugola</t></is></c><c r="L93" s="2" t="inlineStr" /><c r="M93" s="2" t="inlineStr" /><c r="N93" s="2" t="inlineStr" /><c r="O93" s="2" t="inlineStr" /><c r="P93" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q93" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="94"><c r="A94" s="2" t="inlineStr"><is><t>OSTEOPOROZA</t></is></c><c r="B94" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C94" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D94" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E94" s="2" t="inlineStr"><is><t>Wskazaniem do stosowania hormonalnej terapii zastępczej u kobiet po menopauzie jest:</t></is></c><c r="F94" s="2" t="inlineStr"><is><t>Obecność objawów wypadowych</t></is></c><c r="G94" s="2" t="inlineStr" /><c r="H94" s="2" t="inlineStr" /><c r="I94" s="2" t="inlineStr" /><c r="J94" s="2" t="inlineStr" /><c r="K94" s="2" t="inlineStr"><is><t>Wtórna profilaktyka chorób układu krążenia</t></is></c><c r="L94" s="2" t="inlineStr"><is><t>Profilaktyka osteoporozy</t></is></c><c r="M94" s="2" t="inlineStr"><is><t>Zapobieganie chorobie Alzheimera</t></is></c><c r="N94" s="2" t="inlineStr" /><c r="O94" s="2" t="inlineStr" /><c r="P94" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q94" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="95"><c r="A95" s="2" t="inlineStr"><is><t>NIEOPIOIDOWE LEKI PRZECIWBÓLOWE</t></is></c><c r="B95" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C95" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D95" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E95" s="2" t="inlineStr"><is><t>Przeciwbólowy efekt pułapowy wykazuje:</t></is></c><c r="F95" s="2" t="inlineStr"><is><t>Naproksen</t></is></c><c r="G95" s="2" t="inlineStr"><is><t>Buprenorfina</t></is></c><c r="H95" s="2" t="inlineStr"><is><t>Ibuprofen</t></is></c><c r="I95" s="2" t="inlineStr" /><c r="J95" s="2" t="inlineStr" /><c r="K95" s="2" t="inlineStr"><is><t>Oksykodon</t></is></c><c r="L95" s="2" t="inlineStr" /><c r="M95" s="2" t="inlineStr" /><c r="N95" s="2" t="inlineStr" /><c r="O95" s="2" t="inlineStr" /><c r="P95" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q95" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="96"><c r="A96" s="2" t="inlineStr"><is><t>ZABURZENIA RYTMU SERCA</t></is></c><c r="B96" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C96" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D96" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E96" s="2" t="inlineStr"><is><t>Teofilina:</t></is></c><c r="F96" s="2" t="inlineStr"><is><t>Jest anatgonistą receptora adenozynowego</t></is></c><c r="G96" s="2" t="inlineStr"><is><t>Hamuje aktywność fosfodiesteraz</t></is></c><c r="H96" s="2" t="inlineStr"><is><t>Zwiększa przepływ nerkowy</t></is></c><c r="I96" s="2" t="inlineStr"><is><t>Pobudza ośrodek oddechowy w rdzeniu przedłużonym</t></is></c><c r="J96" s="2" t="inlineStr" /><c r="K96" s="2" t="inlineStr" /><c r="L96" s="2" t="inlineStr" /><c r="M96" s="2" t="inlineStr" /><c r="N96" s="2" t="inlineStr" /><c r="O96" s="2" t="inlineStr" /><c r="P96" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q96" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="97"><c r="A97" s="2" t="inlineStr"><is><t>FARMAKOKINETYKA</t></is></c><c r="B97" s="2" t="inlineStr"><is><t>Farmakokinetyka</t></is></c><c r="C97" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D97" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E97" s="2" t="inlineStr"><is><t>Idealny glikokortykosteroid wziewny:</t></is></c><c r="F97" s="2" t="inlineStr"><is><t>Połknięty charakteryzuje się niewielką biodostępnością</t></is></c><c r="G97" s="2" t="inlineStr" /><c r="H97" s="2" t="inlineStr" /><c r="I97" s="2" t="inlineStr" /><c r="J97" s="2" t="inlineStr" /><c r="K97" s="2" t="inlineStr"><is><t>Dobrze wchłania się z pęcherzyków płucnych</t></is></c><c r="L97" s="2" t="inlineStr"><is><t>Nie podlega efektowi pierwszego przejścia przez wątrobę</t></is></c><c r="M97" s="2" t="inlineStr"><is><t>Ma krótki okres półtrwania kompleksu glikokortkosteroidu z receptorem t1/2=2-3h</t></is></c><c r="N97" s="2" t="inlineStr" /><c r="O97" s="2" t="inlineStr" /><c r="P97" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q97" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="98"><c r="A98" s="2" t="inlineStr"><is><t>NIEOPIOIDOWE LEKI PRZECIWBÓLOWE</t></is></c><c r="B98" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C98" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D98" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E98" s="2" t="inlineStr"><is><t>Działanie keratolityczne wykazuje:</t></is></c><c r="F98" s="2" t="inlineStr"><is><t>Mocznik</t></is></c><c r="G98" s="2" t="inlineStr"><is><t>Kwas salicylowy</t></is></c><c r="H98" s="2" t="inlineStr"><is><t>Nadtlenek benzoilu</t></is></c><c r="I98" s="2" t="inlineStr" /><c r="J98" s="2" t="inlineStr" /><c r="K98" s="2" t="inlineStr"><is><t>Metoksalen</t></is></c><c r="L98" s="2" t="inlineStr" /><c r="M98" s="2" t="inlineStr" /><c r="N98" s="2" t="inlineStr" /><c r="O98" s="2" t="inlineStr" /><c r="P98" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q98" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="99"><c r="A99" s="2" t="inlineStr"><is><t>LEKI PRZECIWDEPRESYJNE</t></is></c><c r="B99" s="2" t="inlineStr"><is><t>Antidotum</t></is></c><c r="C99" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D99" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E99" s="2" t="inlineStr"><is><t>W zatruciu solami litu:</t></is></c><c r="F99" s="2" t="inlineStr"><is><t>Należy natychmiast zakończyć podawanie litu</t></is></c><c r="G99" s="2" t="inlineStr"><is><t>W leczeniu ostrego zatrucia istotne znaczenie ma intensywne wyrównanie zaburzeń gospodarki wodno-elektrolitowej, zwłaszcza uzupełnianie niedoboru sodu poprzez przetaczanie roztworu 0,9% NaCl dożylnie</t></is></c><c r="H99" s="2" t="inlineStr"><is><t>Podstawową metodą eliminacji leku jest hemodializa</t></is></c><c r="I99" s="2" t="inlineStr" /><c r="J99" s="2" t="inlineStr" /><c r="K99" s="2" t="inlineStr"><is><t>Korzystne działanie ma stosowanie węgla aktywowanego</t></is></c><c r="L99" s="2" t="inlineStr" /><c r="M99" s="2" t="inlineStr" /><c r="N99" s="2" t="inlineStr" /><c r="O99" s="2" t="inlineStr" /><c r="P99" s="2" t="inlineStr"><is><t>EGZ 2019 I termin</t></is></c><c r="Q99" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="100"><c r="A100" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B100" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C100" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D100" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E100" s="2" t="inlineStr"><is><t>Doksycyklina:</t></is></c><c r="F100" s="2" t="inlineStr"><is><t>w niewielkim stopniu penetruje do ośrodkowego układu nerwowego</t></is></c><c r="G100" s="2" t="inlineStr"><is><t>tworzy chelaty z solami żelaza</t></is></c><c r="H100" s="2" t="inlineStr"><is><t>jest stosowana w leczeniu zakażeń układu moczowego o etiologii Chlamydia trachomatis</t></is></c><c r="I100" s="2" t="inlineStr"><is><t>nie wykazuje aktywności wobec Pseudomonas aeruginosa</t></is></c><c r="J100" s="2" t="inlineStr" /><c r="K100" s="2" t="inlineStr" /><c r="L100" s="2" t="inlineStr" /><c r="M100" s="2" t="inlineStr" /><c r="N100" s="2" t="inlineStr" /><c r="O100" s="2" t="inlineStr" /><c r="P100" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q100" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="101"><c r="A101" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B101" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C101" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D101" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E101" s="2" t="inlineStr"><is><t>Fluorochinolony:</t></is></c><c r="F101" s="2" t="inlineStr"><is><t>mogą spowodować zapalenie ścięgien</t></is></c><c r="G101" s="2" t="inlineStr"><is><t>mogą być przyczyną zaburzeń rytmu serca</t></is></c><c r="H101" s="2" t="inlineStr" /><c r="I101" s="2" t="inlineStr" /><c r="J101" s="2" t="inlineStr" /><c r="K101" s="2" t="inlineStr"><is><t>wszystkie generacje mają zbliżoną skuteczność przeciwko Gram ujemnym pałeczkom niefermentującym</t></is></c><c r="L101" s="2" t="inlineStr"><is><t>są agonistami receptorów GABA-A wywołując efekt sedatywny</t></is></c><c r="M101" s="2" t="inlineStr" /><c r="N101" s="2" t="inlineStr" /><c r="O101" s="2" t="inlineStr" /><c r="P101" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q101" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="102"><c r="A102" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B102" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C102" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D102" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E102" s="2" t="inlineStr"><is><t>Wskaż prawdziwe połączenie lek – mechanizm działania:</t></is></c><c r="F102" s="2" t="inlineStr"><is><t>linezolid- hamowanie biosyntezy białka w komórkach bakterii poprzez wiązanie się z podjednostką 50 S rybosomu</t></is></c><c r="G102" s="2" t="inlineStr" /><c r="H102" s="2" t="inlineStr" /><c r="I102" s="2" t="inlineStr" /><c r="J102" s="2" t="inlineStr" /><c r="K102" s="2" t="inlineStr"><is><t>cefuroksym – hamowanie topoizomerazy II</t></is></c><c r="L102" s="2" t="inlineStr"><is><t>moksyfloksacyna - blokowanie syntezy ściany komórkowej bakterii</t></is></c><c r="M102" s="2" t="inlineStr"><is><t>wankomycyna - uszkodzenie DNA</t></is></c><c r="N102" s="2" t="inlineStr" /><c r="O102" s="2" t="inlineStr" /><c r="P102" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q102" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="103"><c r="A103" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B103" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C103" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D103" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E103" s="2" t="inlineStr"><is><t>Wskaż prawdziwe połączenie lek – działania niepożądane:</t></is></c><c r="F103" s="2" t="inlineStr"><is><t>tygecyklina - nadwrażliwość na światło</t></is></c><c r="G103" s="2" t="inlineStr"><is><t>metronidazol - neuropatia obwodowa</t></is></c><c r="H103" s="2" t="inlineStr"><is><t>wankomycyna – uwalnianie histaminy</t></is></c><c r="I103" s="2" t="inlineStr" /><c r="J103" s="2" t="inlineStr" /><c r="K103" s="2" t="inlineStr"><is><t>azytromycyna – blokowanie wątrobowych enzymów mikrosomalnych (CYP)</t></is></c><c r="L103" s="2" t="inlineStr" /><c r="M103" s="2" t="inlineStr" /><c r="N103" s="2" t="inlineStr" /><c r="O103" s="2" t="inlineStr" /><c r="P103" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q103" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="104"><c r="A104" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B104" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C104" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D104" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E104" s="2" t="inlineStr"><is><t>Błędny schemat terapeutyczny to zastosowanie:</t></is></c><c r="F104" s="2" t="inlineStr"><is><t>loperamidu w zapalnej biegunce poantybiotykowej przez 10 dni</t></is></c><c r="G104" s="2" t="inlineStr" /><c r="H104" s="2" t="inlineStr" /><c r="I104" s="2" t="inlineStr" /><c r="J104" s="2" t="inlineStr" /><c r="K104" s="2" t="inlineStr"><is><t>azytromycyny w krztuścu przez 5 dni</t></is></c><c r="L104" s="2" t="inlineStr"><is><t>kotrymoksazolu w niepowikłanym zakażeniu układu moczowego przez 3 dni</t></is></c><c r="M104" s="2" t="inlineStr"><is><t>fenoksymetylpenicyliny w anginie paciorkowcowej przez 10 dni</t></is></c><c r="N104" s="2" t="inlineStr" /><c r="O104" s="2" t="inlineStr" /><c r="P104" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q104" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="105"><c r="A105" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B105" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C105" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D105" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E105" s="2" t="inlineStr"><is><t>W leczeniu 60-letniego pacjenta z pozaszpitalnym zapaleniem płuc (skala CURB-0pkt) uwzględniającym typową etiologię zakażenia u dorosłych należy:</t></is></c><c r="F105" s="2" t="inlineStr"><is><t>stosować stałe optymalne przedziały dawkowania w ciągu całej doby</t></is></c><c r="G105" s="2" t="inlineStr"><is><t>w razie nadwrażliwości na leczenie początkowe w wywiadach zastosować lewofloksacynę lub moksyfloksacynę</t></is></c><c r="H105" s="2" t="inlineStr" /><c r="I105" s="2" t="inlineStr" /><c r="J105" s="2" t="inlineStr" /><c r="K105" s="2" t="inlineStr"><is><t>leczyć 2 lekami przeciwbakteryjnymi o różnych mechanizmach działania</t></is></c><c r="L105" s="2" t="inlineStr"><is><t>prowadzić terapię co najmniej 21 dni</t></is></c><c r="M105" s="2" t="inlineStr" /><c r="N105" s="2" t="inlineStr" /><c r="O105" s="2" t="inlineStr" /><c r="P105" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q105" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="106"><c r="A106" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B106" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C106" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D106" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E106" s="2" t="inlineStr"><is><t>W leczeniu zapalenia opon mózgowo-rdzeniowych uzasadnione jest zastosowanie:</t></is></c><c r="F106" s="2" t="inlineStr"><is><t>ceftriaksonu</t></is></c><c r="G106" s="2" t="inlineStr"><is><t>acyklowiru</t></is></c><c r="H106" s="2" t="inlineStr"><is><t>meropenemu</t></is></c><c r="I106" s="2" t="inlineStr"><is><t>flukonazol</t></is></c><c r="J106" s="2" t="inlineStr" /><c r="K106" s="2" t="inlineStr" /><c r="L106" s="2" t="inlineStr" /><c r="M106" s="2" t="inlineStr" /><c r="N106" s="2" t="inlineStr" /><c r="O106" s="2" t="inlineStr" /><c r="P106" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q106" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="107"><c r="A107" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B107" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C107" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D107" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E107" s="2" t="inlineStr"><is><t>Wyłącznie na drobnoustroje Gram ujemne działa:</t></is></c><c r="F107" s="2" t="inlineStr"><is><t>aztreonam</t></is></c><c r="G107" s="2" t="inlineStr" /><c r="H107" s="2" t="inlineStr" /><c r="I107" s="2" t="inlineStr" /><c r="J107" s="2" t="inlineStr" /><c r="K107" s="2" t="inlineStr"><is><t>mupirocyna</t></is></c><c r="L107" s="2" t="inlineStr"><is><t>kwas fusydowy</t></is></c><c r="M107" s="2" t="inlineStr"><is><t>metronidazol</t></is></c><c r="N107" s="2" t="inlineStr" /><c r="O107" s="2" t="inlineStr" /><c r="P107" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q107" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="108"><c r="A108" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B108" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C108" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D108" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E108" s="2" t="inlineStr"><is><t>W leczeniu toksoplazmozy wykorzystuje się:</t></is></c><c r="F108" s="2" t="inlineStr"><is><t>pirymetaminę z sulfadiazyną</t></is></c><c r="G108" s="2" t="inlineStr"><is><t>spiramycynę</t></is></c><c r="H108" s="2" t="inlineStr" /><c r="I108" s="2" t="inlineStr" /><c r="J108" s="2" t="inlineStr" /><c r="K108" s="2" t="inlineStr"><is><t>dalfoprystynę/chinuprystynę</t></is></c><c r="L108" s="2" t="inlineStr"><is><t>oksytetracyklinę</t></is></c><c r="M108" s="2" t="inlineStr" /><c r="N108" s="2" t="inlineStr" /><c r="O108" s="2" t="inlineStr" /><c r="P108" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q108" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="109"><c r="A109" s="2" t="inlineStr"><is><t>CUKRZYCA</t></is></c><c r="B109" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C109" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D109" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E109" s="2" t="inlineStr"><is><t>Do odległych działań niepożądanych terapii HAART (Highly Active Antiretroviral Therapy) należy:</t></is></c><c r="F109" s="2" t="inlineStr"><is><t>uszkodzenie wątroby</t></is></c><c r="G109" s="2" t="inlineStr"><is><t>lipodystrofia</t></is></c><c r="H109" s="2" t="inlineStr"><is><t>kwasica mleczanowa</t></is></c><c r="I109" s="2" t="inlineStr"><is><t>insulinooporność</t></is></c><c r="J109" s="2" t="inlineStr" /><c r="K109" s="2" t="inlineStr" /><c r="L109" s="2" t="inlineStr" /><c r="M109" s="2" t="inlineStr" /><c r="N109" s="2" t="inlineStr" /><c r="O109" s="2" t="inlineStr" /><c r="P109" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q109" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="110"><c r="A110" s="2" t="inlineStr"><is><t>LEKI PRZECIWGRZYBICZE</t></is></c><c r="B110" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C110" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D110" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E110" s="2" t="inlineStr"><is><t>W grzybiczym zakażeniu paznokci można zastosować</t></is></c><c r="F110" s="2" t="inlineStr"><is><t>amorolfinę</t></is></c><c r="G110" s="2" t="inlineStr" /><c r="H110" s="2" t="inlineStr" /><c r="I110" s="2" t="inlineStr" /><c r="J110" s="2" t="inlineStr" /><c r="K110" s="2" t="inlineStr"><is><t>natamycynę</t></is></c><c r="L110" s="2" t="inlineStr"><is><t>klotrymazol</t></is></c><c r="M110" s="2" t="inlineStr"><is><t>kaspofunginę</t></is></c><c r="N110" s="2" t="inlineStr" /><c r="O110" s="2" t="inlineStr" /><c r="P110" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q110" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="111"><c r="A111" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B111" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C111" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D111" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E111" s="2" t="inlineStr"><is><t>Efekt bakteriobójczy zależny od skumulowanej ekspozycji (AUC24/MIC) wykazuje:</t></is></c><c r="F111" s="2" t="inlineStr"><is><t>lewofloksacyna</t></is></c><c r="G111" s="2" t="inlineStr"><is><t>azytromycyna</t></is></c><c r="H111" s="2" t="inlineStr" /><c r="I111" s="2" t="inlineStr" /><c r="J111" s="2" t="inlineStr" /><c r="K111" s="2" t="inlineStr"><is><t>amoksycylina z kwasem klawulanowym</t></is></c><c r="L111" s="2" t="inlineStr"><is><t>amikacyna</t></is></c><c r="M111" s="2" t="inlineStr" /><c r="N111" s="2" t="inlineStr" /><c r="O111" s="2" t="inlineStr" /><c r="P111" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q111" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="112"><c r="A112" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B112" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C112" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D112" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E112" s="2" t="inlineStr"><is><t>Do odkażania rany w obrębie skóry można zastosować:</t></is></c><c r="F112" s="2" t="inlineStr"><is><t>oktenidynę</t></is></c><c r="G112" s="2" t="inlineStr"><is><t>jodopowidon</t></is></c><c r="H112" s="2" t="inlineStr" /><c r="I112" s="2" t="inlineStr" /><c r="J112" s="2" t="inlineStr" /><c r="K112" s="2" t="inlineStr"><is><t>wodę do wstrzyknięć</t></is></c><c r="L112" s="2" t="inlineStr"><is><t>kwas borowy</t></is></c><c r="M112" s="2" t="inlineStr" /><c r="N112" s="2" t="inlineStr" /><c r="O112" s="2" t="inlineStr" /><c r="P112" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q112" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="113"><c r="A113" s="2" t="inlineStr"><is><t>FARMAKOLOGIA OGÓLNA I EBM</t></is></c><c r="B113" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C113" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D113" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E113" s="2" t="inlineStr"><is><t>Koszt dodatkowego roku życia skorygowanego o jakość (ang. QALY – quality adjusted life year):</t></is></c><c r="F113" s="2" t="inlineStr"><is><t>stanowi formalne kryterium refundacyjne zgodnie z obowiązującymi regulacjami prawnymi</t></is></c><c r="G113" s="2" t="inlineStr"><is><t>jest wynikiem analizy kosztów użyteczności</t></is></c><c r="H113" s="2" t="inlineStr"><is><t>jego wartość progowa, czyli maksymalna dla procedur uznanych za kosztowo efektywne, stanowi 3-krotność produktu krajowego brutto per capita zgodnie z obowiązującymi regulacjami prawnymi</t></is></c><c r="I113" s="2" t="inlineStr" /><c r="J113" s="2" t="inlineStr" /><c r="K113" s="2" t="inlineStr"><is><t>możliwy jest do oszacowania tylko w przypadku procedur zmniejszających umieralność całkowitą</t></is></c><c r="L113" s="2" t="inlineStr" /><c r="M113" s="2" t="inlineStr" /><c r="N113" s="2" t="inlineStr" /><c r="O113" s="2" t="inlineStr" /><c r="P113" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q113" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="114"><c r="A114" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B114" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C114" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D114" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E114" s="2" t="inlineStr"><is><t>U pacjenta z niewydolnością nerek należy dokonać modyfikacji dawek:</t></is></c><c r="F114" s="2" t="inlineStr"><is><t>wankomycyny</t></is></c><c r="G114" s="2" t="inlineStr"><is><t>cyprofloksacyny</t></is></c><c r="H114" s="2" t="inlineStr"><is><t>gentamycyny</t></is></c><c r="I114" s="2" t="inlineStr" /><c r="J114" s="2" t="inlineStr" /><c r="K114" s="2" t="inlineStr"><is><t>erytromycyny</t></is></c><c r="L114" s="2" t="inlineStr" /><c r="M114" s="2" t="inlineStr" /><c r="N114" s="2" t="inlineStr" /><c r="O114" s="2" t="inlineStr" /><c r="P114" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q114" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="115"><c r="A115" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B115" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C115" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D115" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E115" s="2" t="inlineStr"><is><t>Rotacja opioidów jest uzasadniona w przypadku:</t></is></c><c r="F115" s="2" t="inlineStr"><is><t>nudności</t></is></c><c r="G115" s="2" t="inlineStr"><is><t>zaburzeń świadomości</t></is></c><c r="H115" s="2" t="inlineStr"><is><t>długotrwałej (bezterminowej) terapii w celu ułatwienia jej prowadzenia</t></is></c><c r="I115" s="2" t="inlineStr" /><c r="J115" s="2" t="inlineStr" /><c r="K115" s="2" t="inlineStr"><is><t>zaparć</t></is></c><c r="L115" s="2" t="inlineStr" /><c r="M115" s="2" t="inlineStr" /><c r="N115" s="2" t="inlineStr" /><c r="O115" s="2" t="inlineStr" /><c r="P115" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q115" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="116"><c r="A116" s="2" t="inlineStr"><is><t>CUKRZYCA</t></is></c><c r="B116" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C116" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D116" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E116" s="2" t="inlineStr"><is><t>Dapagliflozyna:</t></is></c><c r="F116" s="2" t="inlineStr"><is><t>zwiększa ryzyko zakażeń układu moczowo-płciowego</t></is></c><c r="G116" s="2" t="inlineStr"><is><t>może spowodować kwasicę ketonową</t></is></c><c r="H116" s="2" t="inlineStr" /><c r="I116" s="2" t="inlineStr" /><c r="J116" s="2" t="inlineStr" /><c r="K116" s="2" t="inlineStr"><is><t>zmniejsza glukozurię</t></is></c><c r="L116" s="2" t="inlineStr"><is><t>nie może być stosowana łącznie z insuliną</t></is></c><c r="M116" s="2" t="inlineStr" /><c r="N116" s="2" t="inlineStr" /><c r="O116" s="2" t="inlineStr" /><c r="P116" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q116" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="117"><c r="A117" s="2" t="inlineStr"><is><t>CUKRZYCA</t></is></c><c r="B117" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C117" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D117" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E117" s="2" t="inlineStr"><is><t>Wskaż zdanie prawdziwe:</t></is></c><c r="F117" s="2" t="inlineStr"><is><t>zwiększenie stężenia glukozy w godzinach porannych poprzedzone hipoglikemią nocną może być wskazaniem do zmniejszenia dawki insuliny bazowej</t></is></c><c r="G117" s="2" t="inlineStr"><is><t>efekt brzasku może zmniejszyć zastosowanie długodziałających bezszczytowych analogów insuliny</t></is></c><c r="H117" s="2" t="inlineStr"><is><t>kardioprotekcyjne działanie empagliflozyny może mieć związek z usprawnieniem procesów energetycznych w komórkach mięśnia sercowego</t></is></c><c r="I117" s="2" t="inlineStr" /><c r="J117" s="2" t="inlineStr" /><c r="K117" s="2" t="inlineStr"><is><t>insulina izofanowa (NPH) jest przeznaczona do stosowana przed głównymi posiłkami</t></is></c><c r="L117" s="2" t="inlineStr" /><c r="M117" s="2" t="inlineStr" /><c r="N117" s="2" t="inlineStr" /><c r="O117" s="2" t="inlineStr" /><c r="P117" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q117" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="118"><c r="A118" s="2" t="inlineStr"><is><t>TARCZYCA</t></is></c><c r="B118" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C118" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D118" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E118" s="2" t="inlineStr"><is><t>W leczeniu nadczynności tarczycy można zastosować:</t></is></c><c r="F118" s="2" t="inlineStr"><is><t>jod promieniotwórczy 131 I</t></is></c><c r="G118" s="2" t="inlineStr"><is><t>płyn Lugola</t></is></c><c r="H118" s="2" t="inlineStr"><is><t>tiamazol</t></is></c><c r="I118" s="2" t="inlineStr"><is><t>propranolol</t></is></c><c r="J118" s="2" t="inlineStr" /><c r="K118" s="2" t="inlineStr" /><c r="L118" s="2" t="inlineStr" /><c r="M118" s="2" t="inlineStr" /><c r="N118" s="2" t="inlineStr" /><c r="O118" s="2" t="inlineStr" /><c r="P118" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q118" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="119"><c r="A119" s="2" t="inlineStr"><is><t>HORMONY PŁCIOWE</t></is></c><c r="B119" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C119" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D119" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E119" s="2" t="inlineStr"><is><t>Do progestagenów należy:</t></is></c><c r="F119" s="2" t="inlineStr"><is><t>megestrol</t></is></c><c r="G119" s="2" t="inlineStr"><is><t>noretysteron</t></is></c><c r="H119" s="2" t="inlineStr" /><c r="I119" s="2" t="inlineStr" /><c r="J119" s="2" t="inlineStr" /><c r="K119" s="2" t="inlineStr"><is><t>dutasteryd</t></is></c><c r="L119" s="2" t="inlineStr"><is><t>anastrozol</t></is></c><c r="M119" s="2" t="inlineStr" /><c r="N119" s="2" t="inlineStr" /><c r="O119" s="2" t="inlineStr" /><c r="P119" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q119" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="120"><c r="A120" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B120" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C120" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D120" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E120" s="2" t="inlineStr"><is><t>Do leków antyagregacyjnych stosowanych w profilaktyce wtórnej udaru niedokrwiennego mózgu na podłożu miażdżycy naczyń do- i mózgowych należą:</t></is></c><c r="F120" s="2" t="inlineStr"><is><t>klopidogrel</t></is></c><c r="G120" s="2" t="inlineStr"><is><t>kwas acetylosalicylowy</t></is></c><c r="H120" s="2" t="inlineStr" /><c r="I120" s="2" t="inlineStr" /><c r="J120" s="2" t="inlineStr" /><c r="K120" s="2" t="inlineStr"><is><t>tikagrelor</t></is></c><c r="L120" s="2" t="inlineStr"><is><t>prasugrel</t></is></c><c r="M120" s="2" t="inlineStr" /><c r="N120" s="2" t="inlineStr" /><c r="O120" s="2" t="inlineStr" /><c r="P120" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q120" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="121"><c r="A121" s="2" t="inlineStr"><is><t>LEKI MOCZOPĘDNE</t></is></c><c r="B121" s="2" t="inlineStr"><is><t>Sposób podania</t></is></c><c r="C121" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D121" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E121" s="2" t="inlineStr"><is><t>W ciężkiej hiperkalcemii (&gt;15mg/dl) można zastosować dożylnie:</t></is></c><c r="F121" s="2" t="inlineStr"><is><t>kalcytoninę</t></is></c><c r="G121" s="2" t="inlineStr"><is><t>pamidronian</t></is></c><c r="H121" s="2" t="inlineStr"><is><t>hydrokortyzon</t></is></c><c r="I121" s="2" t="inlineStr"><is><t>furosemid</t></is></c><c r="J121" s="2" t="inlineStr" /><c r="K121" s="2" t="inlineStr" /><c r="L121" s="2" t="inlineStr" /><c r="M121" s="2" t="inlineStr" /><c r="N121" s="2" t="inlineStr" /><c r="O121" s="2" t="inlineStr" /><c r="P121" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q121" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="122"><c r="A122" s="2" t="inlineStr"><is><t>GLIKOKORTYKOSTEROIDY</t></is></c><c r="B122" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C122" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D122" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E122" s="2" t="inlineStr"><is><t>Immunosupresyjne działanie glikokortykosteroidów jest spowodowane:</t></is></c><c r="F122" s="2" t="inlineStr"><is><t>redukcją liczby limfocytów T</t></is></c><c r="G122" s="2" t="inlineStr"><is><t>zahamowaniem funkcji makrofagów tkankowych</t></is></c><c r="H122" s="2" t="inlineStr" /><c r="I122" s="2" t="inlineStr" /><c r="J122" s="2" t="inlineStr" /><c r="K122" s="2" t="inlineStr"><is><t>zwiększeniem syntezy IL-2</t></is></c><c r="L122" s="2" t="inlineStr"><is><t>aktywacją fosfolipazy A2 i zmniejszeniem syntezy prostaglandyn</t></is></c><c r="M122" s="2" t="inlineStr" /><c r="N122" s="2" t="inlineStr" /><c r="O122" s="2" t="inlineStr" /><c r="P122" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q122" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="123"><c r="A123" s="2" t="inlineStr"><is><t>OSTEOPOROZA</t></is></c><c r="B123" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C123" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D123" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E123" s="2" t="inlineStr"><is><t>91-letni mężczyzna jest leczony od co najmniej 6 miesięcy tamsulozyną, finasterydem, diosminą, piracetamem, zolpidemem, witaminą D3 w dużej dawce i węglanem wapnia. Na tej podstawie można powiedzieć, że:</t></is></c><c r="F123" s="2" t="inlineStr"><is><t>choruje na rozrost gruczołu krokowego</t></is></c><c r="G123" s="2" t="inlineStr"><is><t>jest uzależniony od zolpidemu</t></is></c><c r="H123" s="2" t="inlineStr"><is><t>można bez konsekwencji odstawić piracetam</t></is></c><c r="I123" s="2" t="inlineStr"><is><t>terapia zmniejsza ryzyko osteoporotycznych złamań kości</t></is></c><c r="J123" s="2" t="inlineStr" /><c r="K123" s="2" t="inlineStr" /><c r="L123" s="2" t="inlineStr" /><c r="M123" s="2" t="inlineStr" /><c r="N123" s="2" t="inlineStr" /><c r="O123" s="2" t="inlineStr" /><c r="P123" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q123" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="124"><c r="A124" s="2" t="inlineStr"><is><t>STANY NAGŁE</t></is></c><c r="B124" s="2" t="inlineStr"><is><t>Antidotum</t></is></c><c r="C124" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D124" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E124" s="2" t="inlineStr"><is><t>Witamina K1 (fitomenadion):</t></is></c><c r="F124" s="2" t="inlineStr"><is><t>może być wskazana u osób ze spontanicznym zwiększeniem INR&gt;GGN (górnej granicy normy) spowodowanym antybiotykami niszczącymi fizjologiczną florę jelit</t></is></c><c r="G124" s="2" t="inlineStr"><is><t>nie antagonizuje działania heparyny</t></is></c><c r="H124" s="2" t="inlineStr"><is><t>może spowodować reakcję rzekomoanafilaktyczną</t></is></c><c r="I124" s="2" t="inlineStr"><is><t>jest antidotum w przedawkowaniu pochodnych hydroksykumaryny</t></is></c><c r="J124" s="2" t="inlineStr" /><c r="K124" s="2" t="inlineStr" /><c r="L124" s="2" t="inlineStr" /><c r="M124" s="2" t="inlineStr" /><c r="N124" s="2" t="inlineStr" /><c r="O124" s="2" t="inlineStr" /><c r="P124" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q124" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="125"><c r="A125" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B125" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C125" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D125" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E125" s="2" t="inlineStr"><is><t>Działanie zapierające wykazuje:</t></is></c><c r="F125" s="2" t="inlineStr"><is><t>oksykodon</t></is></c><c r="G125" s="2" t="inlineStr"><is><t>werapamil</t></is></c><c r="H125" s="2" t="inlineStr"><is><t>oktreotyd</t></is></c><c r="I125" s="2" t="inlineStr" /><c r="J125" s="2" t="inlineStr" /><c r="K125" s="2" t="inlineStr"><is><t>fosforan sodu</t></is></c><c r="L125" s="2" t="inlineStr" /><c r="M125" s="2" t="inlineStr" /><c r="N125" s="2" t="inlineStr" /><c r="O125" s="2" t="inlineStr" /><c r="P125" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q125" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="126"><c r="A126" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B126" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C126" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D126" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E126" s="2" t="inlineStr"><is><t>W leczeniu ostrej biegunki u dzieci uzasadnione jest zastosowanie:</t></is></c><c r="F126" s="2" t="inlineStr"><is><t>probiotyku S. boulardi</t></is></c><c r="G126" s="2" t="inlineStr"><is><t>racekadotrylu</t></is></c><c r="H126" s="2" t="inlineStr"><is><t>doustnego płynu nawadniającego</t></is></c><c r="I126" s="2" t="inlineStr" /><c r="J126" s="2" t="inlineStr" /><c r="K126" s="2" t="inlineStr"><is><t>loperamidu</t></is></c><c r="L126" s="2" t="inlineStr" /><c r="M126" s="2" t="inlineStr" /><c r="N126" s="2" t="inlineStr" /><c r="O126" s="2" t="inlineStr" /><c r="P126" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q126" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="127"><c r="A127" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B127" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C127" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D127" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E127" s="2" t="inlineStr"><is><t>Wybierz prawidłowe połączenie lek - mechanizm działania:</t></is></c><c r="F127" s="2" t="inlineStr"><is><t>itopryd - antagonista receptora D2</t></is></c><c r="G127" s="2" t="inlineStr"><is><t>alwimopan - antagonista receptora μ</t></is></c><c r="H127" s="2" t="inlineStr" /><c r="I127" s="2" t="inlineStr" /><c r="J127" s="2" t="inlineStr" /><c r="K127" s="2" t="inlineStr"><is><t>alweryna - agonista receptora motylinowego</t></is></c><c r="L127" s="2" t="inlineStr"><is><t>simetykon - agonista receptora 5-HT4</t></is></c><c r="M127" s="2" t="inlineStr" /><c r="N127" s="2" t="inlineStr" /><c r="O127" s="2" t="inlineStr" /><c r="P127" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q127" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="128"><c r="A128" s="2" t="inlineStr"><is><t>UKŁAD PRZYWSPÓŁCZULNY</t></is></c><c r="B128" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C128" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D128" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E128" s="2" t="inlineStr"><is><t>W kolce wątrobowej uzasadnione jest podanie:</t></is></c><c r="F128" s="2" t="inlineStr"><is><t>ketoprofenu i.v</t></is></c><c r="G128" s="2" t="inlineStr"><is><t>papaweryny i.m</t></is></c><c r="H128" s="2" t="inlineStr"><is><t>butylobromku skopolaminy p.r</t></is></c><c r="I128" s="2" t="inlineStr"><is><t>buprenorfiny i.m</t></is></c><c r="J128" s="2" t="inlineStr" /><c r="K128" s="2" t="inlineStr" /><c r="L128" s="2" t="inlineStr" /><c r="M128" s="2" t="inlineStr" /><c r="N128" s="2" t="inlineStr" /><c r="O128" s="2" t="inlineStr" /><c r="P128" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q128" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="129"><c r="A129" s="2" t="inlineStr"><is><t>BÓLE GŁOWY</t></is></c><c r="B129" s="2" t="inlineStr"><is><t>Ciąża</t></is></c><c r="C129" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D129" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E129" s="2" t="inlineStr"><is><t>Sumatryptan:</t></is></c><c r="F129" s="2" t="inlineStr"><is><t>pobudzając receptory 5-HT1D wywołuje wybiórczy skurcz naczyń i przerywa napad migreny</t></is></c><c r="G129" s="2" t="inlineStr"><is><t>jest niezalecany u pacjentów z chorobą niedokrwienną serca</t></is></c><c r="H129" s="2" t="inlineStr" /><c r="I129" s="2" t="inlineStr" /><c r="J129" s="2" t="inlineStr" /><c r="K129" s="2" t="inlineStr"><is><t>może być stosowany jedynie podskórnie</t></is></c><c r="L129" s="2" t="inlineStr"><is><t>może być podawany w czasie ciąży</t></is></c><c r="M129" s="2" t="inlineStr" /><c r="N129" s="2" t="inlineStr" /><c r="O129" s="2" t="inlineStr" /><c r="P129" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q129" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="130"><c r="A130" s="2" t="inlineStr"><is><t>UKŁAD WSPÓŁCZULNY</t></is></c><c r="B130" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C130" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D130" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E130" s="2" t="inlineStr"><is><t>W profilaktyce bólów migrenowych znalazł zastosowanie:</t></is></c><c r="F130" s="2" t="inlineStr"><is><t>topiramat</t></is></c><c r="G130" s="2" t="inlineStr"><is><t>erenumab</t></is></c><c r="H130" s="2" t="inlineStr"><is><t>propranolol</t></is></c><c r="I130" s="2" t="inlineStr"><is><t>toksyna botulinowa</t></is></c><c r="J130" s="2" t="inlineStr" /><c r="K130" s="2" t="inlineStr" /><c r="L130" s="2" t="inlineStr" /><c r="M130" s="2" t="inlineStr" /><c r="N130" s="2" t="inlineStr" /><c r="O130" s="2" t="inlineStr" /><c r="P130" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q130" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="131"><c r="A131" s="2" t="inlineStr"><is><t>NADCIŚNIENIE TĘTNICZE</t></is></c><c r="B131" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C131" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D131" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E131" s="2" t="inlineStr"><is><t>Erytropoetyna może zwiększyć:</t></is></c><c r="F131" s="2" t="inlineStr"><is><t>wartości ciśnienia tętniczego</t></is></c><c r="G131" s="2" t="inlineStr"><is><t>krzepliwość krwi</t></is></c><c r="H131" s="2" t="inlineStr"><is><t>maksymalną wydolność wysiłkową</t></is></c><c r="I131" s="2" t="inlineStr" /><c r="J131" s="2" t="inlineStr" /><c r="K131" s="2" t="inlineStr"><is><t>aktywność amylazy w surowicy</t></is></c><c r="L131" s="2" t="inlineStr" /><c r="M131" s="2" t="inlineStr" /><c r="N131" s="2" t="inlineStr" /><c r="O131" s="2" t="inlineStr" /><c r="P131" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q131" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="132"><c r="A132" s="2" t="inlineStr"><is><t>UKŁAD PRZYWSPÓŁCZULNY</t></is></c><c r="B132" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C132" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D132" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E132" s="2" t="inlineStr"><is><t>W profilaktyce wymiotów w przebiegu kinetoz stosuje się:</t></is></c><c r="F132" s="2" t="inlineStr"><is><t>skopolaminę</t></is></c><c r="G132" s="2" t="inlineStr"><is><t>dimenhydrinat</t></is></c><c r="H132" s="2" t="inlineStr" /><c r="I132" s="2" t="inlineStr" /><c r="J132" s="2" t="inlineStr" /><c r="K132" s="2" t="inlineStr"><is><t>haloperydol</t></is></c><c r="L132" s="2" t="inlineStr"><is><t>betahistynę</t></is></c><c r="M132" s="2" t="inlineStr" /><c r="N132" s="2" t="inlineStr" /><c r="O132" s="2" t="inlineStr" /><c r="P132" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q132" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="133"><c r="A133" s="2" t="inlineStr"><is><t>UKŁAD WSPÓŁCZULNY</t></is></c><c r="B133" s="2" t="inlineStr"><is><t>Sposób podania</t></is></c><c r="C133" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D133" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E133" s="2" t="inlineStr"><is><t>Oksymetazolina:</t></is></c><c r="F133" s="2" t="inlineStr"><is><t>może doprowadzić do wystąpienia tzw. efektu „ z odbicia”</t></is></c><c r="G133" s="2" t="inlineStr" /><c r="H133" s="2" t="inlineStr" /><c r="I133" s="2" t="inlineStr" /><c r="J133" s="2" t="inlineStr" /><c r="K133" s="2" t="inlineStr"><is><t>jest antagonistą receptorów adrenergicznych alfa</t></is></c><c r="L133" s="2" t="inlineStr"><is><t>wykazuje skuteczność kliniczną po 5. dniach terapii</t></is></c><c r="M133" s="2" t="inlineStr"><is><t>jest podawana doustnie</t></is></c><c r="N133" s="2" t="inlineStr" /><c r="O133" s="2" t="inlineStr" /><c r="P133" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q133" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="134"><c r="A134" s="2" t="inlineStr"><is><t>UKŁAD PRZYWSPÓŁCZULNY</t></is></c><c r="B134" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C134" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D134" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E134" s="2" t="inlineStr"><is><t>Petydyna:</t></is></c><c r="F134" s="2" t="inlineStr"><is><t>ma działanie zapierające</t></is></c><c r="G134" s="2" t="inlineStr"><is><t>nietypowo dla swojej grupy farmakologicznej rozszerza źrenice</t></is></c><c r="H134" s="2" t="inlineStr"><is><t>hamuje ośrodek oddechowy</t></is></c><c r="I134" s="2" t="inlineStr"><is><t>stosowana długotrwale działa neurotoksycznie przez kumulujący się metabolit</t></is></c><c r="J134" s="2" t="inlineStr" /><c r="K134" s="2" t="inlineStr" /><c r="L134" s="2" t="inlineStr" /><c r="M134" s="2" t="inlineStr" /><c r="N134" s="2" t="inlineStr" /><c r="O134" s="2" t="inlineStr" /><c r="P134" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q134" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="135"><c r="A135" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B135" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C135" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D135" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E135" s="2" t="inlineStr"><is><t>Wskaż prawdziwe stwierdzenie dotyczące małopłytkowości typu II wywołanej heparyną:</t></is></c><c r="F135" s="2" t="inlineStr"><is><t>stwierdzenie małopłytkowości immunologicznej w przebiegu leczenia heparyną jest wskazaniem do jej natychmiastowego odstawienia</t></is></c><c r="G135" s="2" t="inlineStr"><is><t>HIT II wiąże się z 20–40-krotnym zwiększeniem ryzyka zakrzepicy żylnej</t></is></c><c r="H135" s="2" t="inlineStr" /><c r="I135" s="2" t="inlineStr" /><c r="J135" s="2" t="inlineStr" /><c r="K135" s="2" t="inlineStr"><is><t>HIT II występuje najczęściej po 3 tygodniach od rozpoczęcia terapii heparyną</t></is></c><c r="L135" s="2" t="inlineStr"><is><t>heparyny drobnocząsteczkowe nie stwarzają ryzyka wystąpienia trombocytopenii immunologicznej</t></is></c><c r="M135" s="2" t="inlineStr" /><c r="N135" s="2" t="inlineStr" /><c r="O135" s="2" t="inlineStr" /><c r="P135" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q135" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="136"><c r="A136" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B136" s="2" t="inlineStr"><is><t>Ciąża</t></is></c><c r="C136" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D136" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E136" s="2" t="inlineStr"><is><t>U kobiet w trzecim trymestrze ciąży przeciwwskazany/-a jest:</t></is></c><c r="F136" s="2" t="inlineStr"><is><t>ketoprofen</t></is></c><c r="G136" s="2" t="inlineStr"><is><t>walsartan</t></is></c><c r="H136" s="2" t="inlineStr"><is><t>acenokumarol</t></is></c><c r="I136" s="2" t="inlineStr" /><c r="J136" s="2" t="inlineStr" /><c r="K136" s="2" t="inlineStr"><is><t>enoksaparyna</t></is></c><c r="L136" s="2" t="inlineStr" /><c r="M136" s="2" t="inlineStr" /><c r="N136" s="2" t="inlineStr" /><c r="O136" s="2" t="inlineStr" /><c r="P136" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q136" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="137"><c r="A137" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B137" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C137" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D137" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E137" s="2" t="inlineStr"><is><t>U pacjenta leczonego przeciwzakrzepowo dabigatranem ze stwierdzonym umiarkowanym aktywnym krwawieniem należy:</t></is></c><c r="F137" s="2" t="inlineStr"><is><t>odroczyć podanie kolejnej dawki leku</t></is></c><c r="G137" s="2" t="inlineStr"><is><t>zapewnić podaż płynów</t></is></c><c r="H137" s="2" t="inlineStr"><is><t>rozważyć podanie węgla aktywowanego jeśli dabigatran był podany niedawno</t></is></c><c r="I137" s="2" t="inlineStr" /><c r="J137" s="2" t="inlineStr" /><c r="K137" s="2" t="inlineStr"><is><t>zastosować siarczan protaminy</t></is></c><c r="L137" s="2" t="inlineStr" /><c r="M137" s="2" t="inlineStr" /><c r="N137" s="2" t="inlineStr" /><c r="O137" s="2" t="inlineStr" /><c r="P137" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q137" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="138"><c r="A138" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B138" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C138" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D138" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E138" s="2" t="inlineStr"><is><t>Nadroparyna:</t></is></c><c r="F138" s="2" t="inlineStr"><is><t>może być podawana dożylnie</t></is></c><c r="G138" s="2" t="inlineStr"><is><t>jest skuteczna w leczeniu zakrzepicy żył głębokich</t></is></c><c r="H138" s="2" t="inlineStr" /><c r="I138" s="2" t="inlineStr" /><c r="J138" s="2" t="inlineStr" /><c r="K138" s="2" t="inlineStr"><is><t>jest antagonistą receptora PAR-1</t></is></c><c r="L138" s="2" t="inlineStr"><is><t>w profilaktyce zakrzepicy żylnej powinna być podana nie później niż 36 godzin przed zabiegiem chirurgicznym</t></is></c><c r="M138" s="2" t="inlineStr" /><c r="N138" s="2" t="inlineStr" /><c r="O138" s="2" t="inlineStr" /><c r="P138" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q138" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="139"><c r="A139" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B139" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C139" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D139" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E139" s="2" t="inlineStr"><is><t>Wskazaniem do podania tkankowego aktywatora plazminogenu (t-PA) może być:</t></is></c><c r="F139" s="2" t="inlineStr"><is><t>zatorowość płucna wysokiego ryzyka (czyli z niestabilnością hemodynamiczną)</t></is></c><c r="G139" s="2" t="inlineStr"><is><t>ostry zator tętnicy kończyny dolnej</t></is></c><c r="H139" s="2" t="inlineStr"><is><t>ostry udar niedokrwienny mózgu</t></is></c><c r="I139" s="2" t="inlineStr" /><c r="J139" s="2" t="inlineStr" /><c r="K139" s="2" t="inlineStr"><is><t>ostry zespół wieńcowy bez uniesienia odcinka ST</t></is></c><c r="L139" s="2" t="inlineStr" /><c r="M139" s="2" t="inlineStr" /><c r="N139" s="2" t="inlineStr" /><c r="O139" s="2" t="inlineStr" /><c r="P139" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q139" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="140"><c r="A140" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B140" s="2" t="inlineStr"><is><t>Sposób podania</t></is></c><c r="C140" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D140" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E140" s="2" t="inlineStr"><is><t>W udarze niedokrwiennym mózgu należy:</t></is></c><c r="F140" s="2" t="inlineStr"><is><t>obniżać ciśnienie tętnicze jeśli przekracza wartości 220/120 mmHg</t></is></c><c r="G140" s="2" t="inlineStr"><is><t>podać doustnie kwas acetylosalicylowy jeżeli nie można zastosować leczenia trombolitycznego</t></is></c><c r="H140" s="2" t="inlineStr" /><c r="I140" s="2" t="inlineStr" /><c r="J140" s="2" t="inlineStr" /><c r="K140" s="2" t="inlineStr"><is><t>stosować duże dawki heparyny niefrakcjonowanej</t></is></c><c r="L140" s="2" t="inlineStr"><is><t>profilaktycznie podawać antybiotyki β-laktamowe ze względu na bardzo częste występowanie infekcji dróg oddechowych</t></is></c><c r="M140" s="2" t="inlineStr" /><c r="N140" s="2" t="inlineStr" /><c r="O140" s="2" t="inlineStr" /><c r="P140" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q140" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="141"><c r="A141" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B141" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C141" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D141" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E141" s="2" t="inlineStr"><is><t>Inhibitory reduktazy HMG-CoA zwiększają produkcję:</t></is></c><c r="F141" s="2" t="inlineStr"><is><t>tkankowego aktywatora plazminogenu</t></is></c><c r="G141" s="2" t="inlineStr"><is><t>tlenku azotu</t></is></c><c r="H141" s="2" t="inlineStr" /><c r="I141" s="2" t="inlineStr" /><c r="J141" s="2" t="inlineStr" /><c r="K141" s="2" t="inlineStr"><is><t>metaloproteinaz</t></is></c><c r="L141" s="2" t="inlineStr"><is><t>tromboksanu A2</t></is></c><c r="M141" s="2" t="inlineStr" /><c r="N141" s="2" t="inlineStr" /><c r="O141" s="2" t="inlineStr" /><c r="P141" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q141" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="142"><c r="A142" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B142" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C142" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D142" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E142" s="2" t="inlineStr"><is><t>20% roztwór albumin:</t></is></c><c r="F142" s="2" t="inlineStr"><is><t>powoduje ponad 100% przyrost objętości osocza</t></is></c><c r="G142" s="2" t="inlineStr"><is><t>działa objętościowo do 6 h</t></is></c><c r="H142" s="2" t="inlineStr" /><c r="I142" s="2" t="inlineStr" /><c r="J142" s="2" t="inlineStr" /><c r="K142" s="2" t="inlineStr"><is><t>może spowodować uszkodzenie nerek</t></is></c><c r="L142" s="2" t="inlineStr"><is><t>ma istotny wpływ na krzepnięcie krwi</t></is></c><c r="M142" s="2" t="inlineStr" /><c r="N142" s="2" t="inlineStr" /><c r="O142" s="2" t="inlineStr" /><c r="P142" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q142" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="143"><c r="A143" s="2" t="inlineStr"><is><t>UKŁAD PRZYWSPÓŁCZULNY</t></is></c><c r="B143" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C143" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D143" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E143" s="2" t="inlineStr"><is><t>Zastosowanie atrakurium może być przyczyną:</t></is></c><c r="F143" s="2" t="inlineStr"><is><t>długotrwałego efektu zwiotczającego</t></is></c><c r="G143" s="2" t="inlineStr" /><c r="H143" s="2" t="inlineStr" /><c r="I143" s="2" t="inlineStr" /><c r="J143" s="2" t="inlineStr" /><c r="K143" s="2" t="inlineStr"><is><t>drżenia włókienkowego mięśni szkieletowych</t></is></c><c r="L143" s="2" t="inlineStr"><is><t>anestezji</t></is></c><c r="M143" s="2" t="inlineStr"><is><t>hipertermii złośliwej</t></is></c><c r="N143" s="2" t="inlineStr" /><c r="O143" s="2" t="inlineStr" /><c r="P143" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q143" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="144"><c r="A144" s="2" t="inlineStr"><is><t>LEKI MOCZOPĘDNE</t></is></c><c r="B144" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C144" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D144" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E144" s="2" t="inlineStr"><is><t>Torasemid:</t></is></c><c r="F144" s="2" t="inlineStr"><is><t>hamuje symporter sodowo-potasowo-chlorkowy części grubościennej ramienia wstępującego pętli Henlego</t></is></c><c r="G144" s="2" t="inlineStr"><is><t>zwiększa aktywność reninową osocza</t></is></c><c r="H144" s="2" t="inlineStr" /><c r="I144" s="2" t="inlineStr" /><c r="J144" s="2" t="inlineStr" /><c r="K144" s="2" t="inlineStr"><is><t>zmniejsza wydalanie wapnia z moczem</t></is></c><c r="L144" s="2" t="inlineStr"><is><t>jest nieskuteczny, jeśli eGFRr &lt; 30 ml/min</t></is></c><c r="M144" s="2" t="inlineStr" /><c r="N144" s="2" t="inlineStr" /><c r="O144" s="2" t="inlineStr" /><c r="P144" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q144" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="145"><c r="A145" s="2" t="inlineStr"><is><t>FARMAKOLOGIA OGÓLNA I EBM</t></is></c><c r="B145" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C145" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D145" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E145" s="2" t="inlineStr"><is><t>Formularz świadomej zgody uczestnika na udział w badaniu klinicznym powinien zostać podpisany:</t></is></c><c r="F145" s="2" t="inlineStr"><is><t>przez uczestnika badania</t></is></c><c r="G145" s="2" t="inlineStr"><is><t>przez badacza</t></is></c><c r="H145" s="2" t="inlineStr"><is><t>w dwóch egzemplarzach</t></is></c><c r="I145" s="2" t="inlineStr" /><c r="J145" s="2" t="inlineStr" /><c r="K145" s="2" t="inlineStr"><is><t>bezpośrednio po badaniach oceniających czy pacjent spełnia kryteria włączenia do badania</t></is></c><c r="L145" s="2" t="inlineStr" /><c r="M145" s="2" t="inlineStr" /><c r="N145" s="2" t="inlineStr" /><c r="O145" s="2" t="inlineStr" /><c r="P145" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q145" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="146"><c r="A146" s="2" t="inlineStr"><is><t>LEKI PRZECIWPASOŻYTNICZE</t></is></c><c r="B146" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C146" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D146" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E146" s="2" t="inlineStr"><is><t>W leczeniu zarażenia owsikiem skuteczny jest:</t></is></c><c r="F146" s="2" t="inlineStr"><is><t>mebendazol</t></is></c><c r="G146" s="2" t="inlineStr"><is><t>albendazol</t></is></c><c r="H146" s="2" t="inlineStr"><is><t>pyrantel</t></is></c><c r="I146" s="2" t="inlineStr" /><c r="J146" s="2" t="inlineStr" /><c r="K146" s="2" t="inlineStr"><is><t>tynidazol</t></is></c><c r="L146" s="2" t="inlineStr" /><c r="M146" s="2" t="inlineStr" /><c r="N146" s="2" t="inlineStr" /><c r="O146" s="2" t="inlineStr" /><c r="P146" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q146" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="147"><c r="A147" s="2" t="inlineStr"><is><t>LEKI PRZECIWWIRUSOWE</t></is></c><c r="B147" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C147" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D147" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E147" s="2" t="inlineStr"><is><t>Cytomegalię u osób z niedoborami odporności należy leczyć stosując:</t></is></c><c r="F147" s="2" t="inlineStr"><is><t>gancyklowir</t></is></c><c r="G147" s="2" t="inlineStr" /><c r="H147" s="2" t="inlineStr" /><c r="I147" s="2" t="inlineStr" /><c r="J147" s="2" t="inlineStr" /><c r="K147" s="2" t="inlineStr"><is><t>zanamiwir</t></is></c><c r="L147" s="2" t="inlineStr"><is><t>acyklowir</t></is></c><c r="M147" s="2" t="inlineStr"><is><t>oseltamiwir</t></is></c><c r="N147" s="2" t="inlineStr" /><c r="O147" s="2" t="inlineStr" /><c r="P147" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q147" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="148"><c r="A148" s="2" t="inlineStr"><is><t>UKŁAD ODDECHOWY</t></is></c><c r="B148" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C148" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D148" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E148" s="2" t="inlineStr"><is><t>W terapii POChP u osób o wysokim ryzyku zaostrzeń i dużym nasileniu objawów (grupa</t></is></c><c r="F148" s="2" t="inlineStr"><is><t>bromek tiotropium z formoterolem i cyklezonidem</t></is></c><c r="G148" s="2" t="inlineStr"><is><t>budezonid z formoterolem</t></is></c><c r="H148" s="2" t="inlineStr"><is><t>bromek aklidynium z salmeterolem i flutikazonem</t></is></c><c r="I148" s="2" t="inlineStr"><is><t>bromek glikopironium z roflumilastem</t></is></c><c r="J148" s="2" t="inlineStr" /><c r="K148" s="2" t="inlineStr"><is><t>można zastosować:</t></is></c><c r="L148" s="2" t="inlineStr" /><c r="M148" s="2" t="inlineStr" /><c r="N148" s="2" t="inlineStr" /><c r="O148" s="2" t="inlineStr" /><c r="P148" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q148" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="149"><c r="A149" s="2" t="inlineStr"><is><t>UKŁAD ODDECHOWY</t></is></c><c r="B149" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C149" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D149" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E149" s="2" t="inlineStr"><is><t>Wskaż prawidłowe twierdzenie dotyczące farmakoterapii astmy oskrzelowej :</t></is></c><c r="F149" s="2" t="inlineStr"><is><t>wziewne glikokortykosteroidy zmniejszają częstość/liczbę hospitalizacji i umieralność z powodu astmy</t></is></c><c r="G149" s="2" t="inlineStr"><is><t>długodziałające wziewne betaadrenomimetyki w monoterapii mogą zwiększać ryzyko zgonu z powodu astmy</t></is></c><c r="H149" s="2" t="inlineStr"><is><t>kromony mogą być skuteczne u chorych ze skurczem oskrzeli wywoływanym przez wysiłek fizyczny</t></is></c><c r="I149" s="2" t="inlineStr" /><c r="J149" s="2" t="inlineStr" /><c r="K149" s="2" t="inlineStr"><is><t>leki przeciwleukotrienowe w monoterapii są bardziej skuteczne od wziewnych glikokortykosteroidów w małych dawkach</t></is></c><c r="L149" s="2" t="inlineStr" /><c r="M149" s="2" t="inlineStr" /><c r="N149" s="2" t="inlineStr" /><c r="O149" s="2" t="inlineStr" /><c r="P149" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q149" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="150"><c r="A150" s="2" t="inlineStr"><is><t>NADCIŚNIENIE TĘTNICZE</t></is></c><c r="B150" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C150" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D150" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E150" s="2" t="inlineStr"><is><t>W leczeniu wodobrzusza w przebiegu marskości wątroby wskazane jest stosowanie:</t></is></c><c r="F150" s="2" t="inlineStr"><is><t>furosemidu</t></is></c><c r="G150" s="2" t="inlineStr"><is><t>spironolaktonu</t></is></c><c r="H150" s="2" t="inlineStr"><is><t>karwedilolu</t></is></c><c r="I150" s="2" t="inlineStr" /><c r="J150" s="2" t="inlineStr" /><c r="K150" s="2" t="inlineStr"><is><t>ramiprylu</t></is></c><c r="L150" s="2" t="inlineStr" /><c r="M150" s="2" t="inlineStr" /><c r="N150" s="2" t="inlineStr" /><c r="O150" s="2" t="inlineStr" /><c r="P150" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q150" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="151"><c r="A151" s="2" t="inlineStr"><is><t>LEKI MOCZOPĘDNE</t></is></c><c r="B151" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C151" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D151" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E151" s="2" t="inlineStr"><is><t>W leczeniu dny moczanowej należy:</t></is></c><c r="F151" s="2" t="inlineStr"><is><t>stosować dietę z ograniczeniem podaży mięs, podrobów i fruktozy</t></is></c><c r="G151" s="2" t="inlineStr"><is><t>objawowo stosować leki z grupy NLPZ</t></is></c><c r="H151" s="2" t="inlineStr" /><c r="I151" s="2" t="inlineStr" /><c r="J151" s="2" t="inlineStr" /><c r="K151" s="2" t="inlineStr"><is><t>podać jak najszybciej allopurynol przy podejrzeniu ostrego napadu</t></is></c><c r="L151" s="2" t="inlineStr"><is><t>w każdym przypadku bezobjawowej hiperurykemii stosować kolchicynę</t></is></c><c r="M151" s="2" t="inlineStr" /><c r="N151" s="2" t="inlineStr" /><c r="O151" s="2" t="inlineStr" /><c r="P151" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q151" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="152"><c r="A152" s="2" t="inlineStr"><is><t>NIEOPIOIDOWE LEKI PRZECIWBÓLOWE</t></is></c><c r="B152" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C152" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D152" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E152" s="2" t="inlineStr"><is><t>Zotarolimus:</t></is></c><c r="F152" s="2" t="inlineStr"><is><t>jest stosowany w stentach wieńcowych uwalniających lek</t></is></c><c r="G152" s="2" t="inlineStr" /><c r="H152" s="2" t="inlineStr" /><c r="I152" s="2" t="inlineStr" /><c r="J152" s="2" t="inlineStr" /><c r="K152" s="2" t="inlineStr"><is><t>jest rekombinowanym w pełni ludzkim przeciwciałem monoklonalnym</t></is></c><c r="L152" s="2" t="inlineStr"><is><t>nie może być stosowany łącznie z kwasem acetylosalicylowym</t></is></c><c r="M152" s="2" t="inlineStr"><is><t>neutralizuje biologiczną aktywność TNF</t></is></c><c r="N152" s="2" t="inlineStr" /><c r="O152" s="2" t="inlineStr" /><c r="P152" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q152" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="153"><c r="A153" s="2" t="inlineStr"><is><t>OTĘPIENIE</t></is></c><c r="B153" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C153" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D153" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E153" s="2" t="inlineStr"><is><t>W leczeniu choroby Alzheimera:</t></is></c><c r="F153" s="2" t="inlineStr"><is><t>w zaawansowanych przypadkach wskazane jest włączenie do leczenia antagonisty receptorów NMDA</t></is></c><c r="G153" s="2" t="inlineStr"><is><t>donepezil korzystnie wpływa na globalne zdolności intelektualne w łagodnych stadiach choroby</t></is></c><c r="H153" s="2" t="inlineStr" /><c r="I153" s="2" t="inlineStr" /><c r="J153" s="2" t="inlineStr" /><c r="K153" s="2" t="inlineStr"><is><t>stosuje się leki cholinolityczne</t></is></c><c r="L153" s="2" t="inlineStr"><is><t>istotną rolę odgrywa zastosowanie piracetamu</t></is></c><c r="M153" s="2" t="inlineStr" /><c r="N153" s="2" t="inlineStr" /><c r="O153" s="2" t="inlineStr" /><c r="P153" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q153" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="154"><c r="A154" s="2" t="inlineStr"><is><t>PADACZKA</t></is></c><c r="B154" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C154" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D154" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E154" s="2" t="inlineStr"><is><t>Przewlekłe stosowanie lorazepamu może spowodować:</t></is></c><c r="F154" s="2" t="inlineStr"><is><t>otępienie</t></is></c><c r="G154" s="2" t="inlineStr"><is><t>tolerancję na jego działanie</t></is></c><c r="H154" s="2" t="inlineStr"><is><t>uzależnienie psychiczne i fizyczne</t></is></c><c r="I154" s="2" t="inlineStr" /><c r="J154" s="2" t="inlineStr" /><c r="K154" s="2" t="inlineStr"><is><t>stan padaczkowy</t></is></c><c r="L154" s="2" t="inlineStr" /><c r="M154" s="2" t="inlineStr" /><c r="N154" s="2" t="inlineStr" /><c r="O154" s="2" t="inlineStr" /><c r="P154" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q154" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="155"><c r="A155" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B155" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C155" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D155" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E155" s="2" t="inlineStr"><is><t>Wybierz prawidłowe połączenie lek - mechanizm działania:</t></is></c><c r="F155" s="2" t="inlineStr"><is><t>orlistat - blokowanie lipaz wytwarzanych w przewodzie pokarmowym</t></is></c><c r="G155" s="2" t="inlineStr"><is><t>tramadol – blokowanie zwrotnego wychwytu noradrenaliny i serotoniny w synapsach zstępującego układu analgetycznego</t></is></c><c r="H155" s="2" t="inlineStr"><is><t>ezetymib – hamowanie aktywności białka NPC1L1 w nabłonku błony śluzowej jelita</t></is></c><c r="I155" s="2" t="inlineStr"><is><t>celekoksyb -wybiórcze zablokowanie COX-2</t></is></c><c r="J155" s="2" t="inlineStr" /><c r="K155" s="2" t="inlineStr" /><c r="L155" s="2" t="inlineStr" /><c r="M155" s="2" t="inlineStr" /><c r="N155" s="2" t="inlineStr" /><c r="O155" s="2" t="inlineStr" /><c r="P155" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q155" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="156"><c r="A156" s="2" t="inlineStr"><is><t>LEKI MOCZOPĘDNE</t></is></c><c r="B156" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C156" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D156" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E156" s="2" t="inlineStr"><is><t>Do leczenia ostrego zamknięcia kąta przesączania (potocznie ataku jaskry) można zastosować:</t></is></c><c r="F156" s="2" t="inlineStr"><is><t>tymolol</t></is></c><c r="G156" s="2" t="inlineStr"><is><t>acetazolamid</t></is></c><c r="H156" s="2" t="inlineStr"><is><t>mannitol</t></is></c><c r="I156" s="2" t="inlineStr" /><c r="J156" s="2" t="inlineStr" /><c r="K156" s="2" t="inlineStr"><is><t>zydowudynę</t></is></c><c r="L156" s="2" t="inlineStr" /><c r="M156" s="2" t="inlineStr" /><c r="N156" s="2" t="inlineStr" /><c r="O156" s="2" t="inlineStr" /><c r="P156" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q156" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="157"><c r="A157" s="2" t="inlineStr"><is><t>PADACZKA</t></is></c><c r="B157" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C157" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D157" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E157" s="2" t="inlineStr"><is><t>W leczeniu stanu padaczkowego:</t></is></c><c r="F157" s="2" t="inlineStr"><is><t>lekiem pierwszego rzutu jest diazepam i.v</t></is></c><c r="G157" s="2" t="inlineStr"><is><t>w przypadku postaci opornej na leczenie można zastosować wlew dożylny midazolamu</t></is></c><c r="H157" s="2" t="inlineStr" /><c r="I157" s="2" t="inlineStr" /><c r="J157" s="2" t="inlineStr" /><c r="K157" s="2" t="inlineStr"><is><t>nie powinno się stosować fenytoiny we wlewie dożylnym</t></is></c><c r="L157" s="2" t="inlineStr"><is><t>należy stosować duże dawki steroidów i.v</t></is></c><c r="M157" s="2" t="inlineStr" /><c r="N157" s="2" t="inlineStr" /><c r="O157" s="2" t="inlineStr" /><c r="P157" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q157" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="158"><c r="A158" s="2" t="inlineStr"><is><t>FARMAKOLOGIA OGÓLNA I EBM</t></is></c><c r="B158" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C158" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D158" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E158" s="2" t="inlineStr"><is><t>Charakterystyka Produktu Leczniczego (ChPL) zawiera informacje o:</t></is></c><c r="F158" s="2" t="inlineStr"><is><t>specjalnych środkach ostrożności podczas przechowywania produktu leczniczego</t></is></c><c r="G158" s="2" t="inlineStr"><is><t>właściwościach farmakokinetycznych leku</t></is></c><c r="H158" s="2" t="inlineStr"><is><t>dacie wydania pierwszego pozwolenia na dopuszczenie do obrotu</t></is></c><c r="I158" s="2" t="inlineStr" /><c r="J158" s="2" t="inlineStr" /><c r="K158" s="2" t="inlineStr"><is><t>cenie produktu leczniczego</t></is></c><c r="L158" s="2" t="inlineStr" /><c r="M158" s="2" t="inlineStr" /><c r="N158" s="2" t="inlineStr" /><c r="O158" s="2" t="inlineStr" /><c r="P158" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q158" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="159"><c r="A159" s="2" t="inlineStr"><is><t>FARMAKOLOGIA OGÓLNA I EBM</t></is></c><c r="B159" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C159" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D159" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E159" s="2" t="inlineStr"><is><t>Agencja Oceny Technologii Medycznych i Taryfikacji:</t></is></c><c r="F159" s="2" t="inlineStr"><is><t>wycenia procedury medyczne</t></is></c><c r="G159" s="2" t="inlineStr"><is><t>zajmuje stanowisko w sprawie skuteczności i bezpieczeństwa leków</t></is></c><c r="H159" s="2" t="inlineStr"><is><t>rekomenduje leki do refundacji</t></is></c><c r="I159" s="2" t="inlineStr" /><c r="J159" s="2" t="inlineStr" /><c r="K159" s="2" t="inlineStr"><is><t>rejestruje leki</t></is></c><c r="L159" s="2" t="inlineStr" /><c r="M159" s="2" t="inlineStr" /><c r="N159" s="2" t="inlineStr" /><c r="O159" s="2" t="inlineStr" /><c r="P159" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q159" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="160"><c r="A160" s="2" t="inlineStr"><is><t>FARMAKOLOGIA OGÓLNA I EBM</t></is></c><c r="B160" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C160" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D160" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E160" s="2" t="inlineStr"><is><t>W hierarchii badań naukowych:</t></is></c><c r="F160" s="2" t="inlineStr"><is><t>badania kohortowe mają wyższą pozycję niż serie przypadków</t></is></c><c r="G160" s="2" t="inlineStr" /><c r="H160" s="2" t="inlineStr" /><c r="I160" s="2" t="inlineStr" /><c r="J160" s="2" t="inlineStr" /><c r="K160" s="2" t="inlineStr"><is><t>metaanalizy są na tym samym poziomie co randomizowane badania kontrolowane</t></is></c><c r="L160" s="2" t="inlineStr"><is><t>najwyższą pozycję mają randomizowane badania kontrolowane</t></is></c><c r="M160" s="2" t="inlineStr"><is><t>badania kohortowe są na tym samym poziomie co randomizowane badania kliniczne</t></is></c><c r="N160" s="2" t="inlineStr" /><c r="O160" s="2" t="inlineStr" /><c r="P160" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q160" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="161"><c r="A161" s="2" t="inlineStr"><is><t>LEKI PRZECIWHISTAMINOWE</t></is></c><c r="B161" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C161" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D161" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E161" s="2" t="inlineStr"><is><t>Desloratadyna:</t></is></c><c r="F161" s="2" t="inlineStr"><is><t>selektywnie blokuje receptory H1</t></is></c><c r="G161" s="2" t="inlineStr"><is><t>ma zastosowanie w leczeniu przewlekłego alergicznego nieżytu nosa</t></is></c><c r="H161" s="2" t="inlineStr" /><c r="I161" s="2" t="inlineStr" /><c r="J161" s="2" t="inlineStr" /><c r="K161" s="2" t="inlineStr"><is><t>dobrze przenika przez barierę krew- mózg</t></is></c><c r="L161" s="2" t="inlineStr"><is><t>ma znaczące działanie proarytmiczne</t></is></c><c r="M161" s="2" t="inlineStr" /><c r="N161" s="2" t="inlineStr" /><c r="O161" s="2" t="inlineStr" /><c r="P161" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q161" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="162"><c r="A162" s="2" t="inlineStr"><is><t>LEKI MOCZOPĘDNE</t></is></c><c r="B162" s="2" t="inlineStr"><is><t>Farmakokinetyka</t></is></c><c r="C162" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D162" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E162" s="2" t="inlineStr"><is><t>Mannitol podany iv. zmniejsza:</t></is></c><c r="F162" s="2" t="inlineStr"><is><t>ciśnienie wewnątrzczaszkowe</t></is></c><c r="G162" s="2" t="inlineStr" /><c r="H162" s="2" t="inlineStr" /><c r="I162" s="2" t="inlineStr" /><c r="J162" s="2" t="inlineStr" /><c r="K162" s="2" t="inlineStr"><is><t>ciśnienie osmotyczne płynu zewnątrzkomórkowego</t></is></c><c r="L162" s="2" t="inlineStr"><is><t>wydalanie sodu i chlorków</t></is></c><c r="M162" s="2" t="inlineStr"><is><t>filtrację nerkową</t></is></c><c r="N162" s="2" t="inlineStr" /><c r="O162" s="2" t="inlineStr" /><c r="P162" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q162" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="163"><c r="A163" s="2" t="inlineStr"><is><t>LEKI PRZECIWDEPRESYJNE</t></is></c><c r="B163" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C163" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D163" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E163" s="2" t="inlineStr"><is><t>Podanie inhibitorów wychwytu zwrotnego serotoniny (SSRI) jest uzasadnione u pacjentów z:</t></is></c><c r="F163" s="2" t="inlineStr"><is><t>lękiem uogólnionym</t></is></c><c r="G163" s="2" t="inlineStr"><is><t>chorobą afektywną dwubiegunową</t></is></c><c r="H163" s="2" t="inlineStr"><is><t>nerwicą natręctw</t></is></c><c r="I163" s="2" t="inlineStr"><is><t>chorobą afektywną jednobiegunową</t></is></c><c r="J163" s="2" t="inlineStr" /><c r="K163" s="2" t="inlineStr" /><c r="L163" s="2" t="inlineStr" /><c r="M163" s="2" t="inlineStr" /><c r="N163" s="2" t="inlineStr" /><c r="O163" s="2" t="inlineStr" /><c r="P163" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q163" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="164"><c r="A164" s="2" t="inlineStr"><is><t>LEKI PRZECIWDEPRESYJNE</t></is></c><c r="B164" s="2" t="inlineStr"><is><t>Struktura chemiczna</t></is></c><c r="C164" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D164" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E164" s="2" t="inlineStr"><is><t>Do wspólnych cech wenlafaksyny i amitryptyliny należy:</t></is></c><c r="F164" s="2" t="inlineStr"><is><t>hamowanie wychwytu zwrotnego serotoniny i noradrenaliny</t></is></c><c r="G164" s="2" t="inlineStr" /><c r="H164" s="2" t="inlineStr" /><c r="I164" s="2" t="inlineStr" /><c r="J164" s="2" t="inlineStr" /><c r="K164" s="2" t="inlineStr"><is><t>trójpierścieniowa budowa chemiczna</t></is></c><c r="L164" s="2" t="inlineStr"><is><t>konieczność znacznych ograniczeń dietetycznych podczas ich stosowania ze względu na ryzyko wystąpienia tzw. zespołu serowego (cheese effect)</t></is></c><c r="M164" s="2" t="inlineStr"><is><t>antagonizm wobec receptorów muskarynowych M1</t></is></c><c r="N164" s="2" t="inlineStr" /><c r="O164" s="2" t="inlineStr" /><c r="P164" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q164" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="165"><c r="A165" s="2" t="inlineStr"><is><t>LEKI IMMUNOSUPRESYJNE</t></is></c><c r="B165" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C165" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D165" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E165" s="2" t="inlineStr"><is><t>Leki, które hamują kompleks kalcyneuryny to:</t></is></c><c r="F165" s="2" t="inlineStr"><is><t>cyklosporyna</t></is></c><c r="G165" s="2" t="inlineStr"><is><t>takrolimus</t></is></c><c r="H165" s="2" t="inlineStr" /><c r="I165" s="2" t="inlineStr" /><c r="J165" s="2" t="inlineStr" /><c r="K165" s="2" t="inlineStr"><is><t>talidomid</t></is></c><c r="L165" s="2" t="inlineStr"><is><t>mykofenolan mofetylu</t></is></c><c r="M165" s="2" t="inlineStr" /><c r="N165" s="2" t="inlineStr" /><c r="O165" s="2" t="inlineStr" /><c r="P165" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q165" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="166"><c r="A166" s="2" t="inlineStr"><is><t>ZABURZENIA RYTMU SERCA</t></is></c><c r="B166" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C166" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D166" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E166" s="2" t="inlineStr"><is><t>Lacydypina:</t></is></c><c r="F166" s="2" t="inlineStr"><is><t>zmniejsza obciążenie następcze serca</t></is></c><c r="G166" s="2" t="inlineStr" /><c r="H166" s="2" t="inlineStr" /><c r="I166" s="2" t="inlineStr" /><c r="J166" s="2" t="inlineStr" /><c r="K166" s="2" t="inlineStr"><is><t>ma silne działanie inotropowe ujemne</t></is></c><c r="L166" s="2" t="inlineStr"><is><t>ma działanie dromotropowe ujemne</t></is></c><c r="M166" s="2" t="inlineStr"><is><t>ma działanie chronotropowe dodatnie</t></is></c><c r="N166" s="2" t="inlineStr" /><c r="O166" s="2" t="inlineStr" /><c r="P166" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q166" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="167"><c r="A167" s="2" t="inlineStr"><is><t>CHOROBA NIEDOKRWIENNA SERCA</t></is></c><c r="B167" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C167" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D167" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E167" s="2" t="inlineStr"><is><t>Do donorów tlenku azotu należy:</t></is></c><c r="F167" s="2" t="inlineStr"><is><t>nikorandil</t></is></c><c r="G167" s="2" t="inlineStr"><is><t>molsidomina</t></is></c><c r="H167" s="2" t="inlineStr"><is><t>diazotan izosorbitolu</t></is></c><c r="I167" s="2" t="inlineStr" /><c r="J167" s="2" t="inlineStr" /><c r="K167" s="2" t="inlineStr"><is><t>trimetazydyna</t></is></c><c r="L167" s="2" t="inlineStr" /><c r="M167" s="2" t="inlineStr" /><c r="N167" s="2" t="inlineStr" /><c r="O167" s="2" t="inlineStr" /><c r="P167" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q167" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="168"><c r="A168" s="2" t="inlineStr"><is><t>FARMAKOKINETYKA</t></is></c><c r="B168" s="2" t="inlineStr"><is><t>Sposób podania</t></is></c><c r="C168" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D168" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E168" s="2" t="inlineStr"><is><t>Względna dostępność biologiczna leku (biorównoważność) może być określona przez porównanie AUC:</t></is></c><c r="F168" s="2" t="inlineStr"><is><t>leku wzorcowego podanego drogą pozanaczyniową i dożylnie</t></is></c><c r="G168" s="2" t="inlineStr"><is><t>leku wzorcowego i badanego podanych tą samą drogą</t></is></c><c r="H168" s="2" t="inlineStr" /><c r="I168" s="2" t="inlineStr" /><c r="J168" s="2" t="inlineStr" /><c r="K168" s="2" t="inlineStr"><is><t>tylko leków podawanych drogą dożylną</t></is></c><c r="L168" s="2" t="inlineStr"><is><t>leku badanego podanego drogą pozanaczyniową i wzorcowego podanego dożylnie</t></is></c><c r="M168" s="2" t="inlineStr" /><c r="N168" s="2" t="inlineStr" /><c r="O168" s="2" t="inlineStr" /><c r="P168" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q168" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="169"><c r="A169" s="2" t="inlineStr"><is><t>LEKI PRZECIWLĘKOWE</t></is></c><c r="B169" s="2" t="inlineStr"><is><t>Farmakokinetyka</t></is></c><c r="C169" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D169" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E169" s="2" t="inlineStr"><is><t>Benzodiazepiną, która nie podlega metabolizmowi wątrobowemu jest:</t></is></c><c r="F169" s="2" t="inlineStr"><is><t>lorazepam</t></is></c><c r="G169" s="2" t="inlineStr"><is><t>oksazepam</t></is></c><c r="H169" s="2" t="inlineStr" /><c r="I169" s="2" t="inlineStr" /><c r="J169" s="2" t="inlineStr" /><c r="K169" s="2" t="inlineStr"><is><t>nitrazepam</t></is></c><c r="L169" s="2" t="inlineStr"><is><t>diazepam</t></is></c><c r="M169" s="2" t="inlineStr" /><c r="N169" s="2" t="inlineStr" /><c r="O169" s="2" t="inlineStr" /><c r="P169" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q169" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="170"><c r="A170" s="2" t="inlineStr"><is><t>FARMAKOKINETYKA</t></is></c><c r="B170" s="2" t="inlineStr"><is><t>Farmakokinetyka</t></is></c><c r="C170" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D170" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E170" s="2" t="inlineStr"><is><t>Objętość dystrybucji ma znaczenie w określeniu wielkości dawki:</t></is></c><c r="F170" s="2" t="inlineStr"><is><t>nasycającej</t></is></c><c r="G170" s="2" t="inlineStr"><is><t>podtrzymującej</t></is></c><c r="H170" s="2" t="inlineStr" /><c r="I170" s="2" t="inlineStr" /><c r="J170" s="2" t="inlineStr" /><c r="K170" s="2" t="inlineStr"><is><t>śmiertelnej</t></is></c><c r="L170" s="2" t="inlineStr"><is><t>toksycznej</t></is></c><c r="M170" s="2" t="inlineStr" /><c r="N170" s="2" t="inlineStr" /><c r="O170" s="2" t="inlineStr" /><c r="P170" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q170" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="171"><c r="A171" s="2" t="inlineStr"><is><t>NIEOPIOIDOWE LEKI PRZECIWBÓLOWE</t></is></c><c r="B171" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C171" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D171" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E171" s="2" t="inlineStr"><is><t>Do obniżenia gorączki u 2-letniego dziecka można zastosować:</t></is></c><c r="F171" s="2" t="inlineStr"><is><t>czopek doodbytniczy zawierający paracetamol</t></is></c><c r="G171" s="2" t="inlineStr"><is><t>zawiesinę doustną zawierającą ibuprofen</t></is></c><c r="H171" s="2" t="inlineStr" /><c r="I171" s="2" t="inlineStr" /><c r="J171" s="2" t="inlineStr" /><c r="K171" s="2" t="inlineStr"><is><t>tabletki o natychmiastowym uwalnianiu w jamie ustnej zawierające kwas acetylosalicylowy</t></is></c><c r="L171" s="2" t="inlineStr"><is><t>wstrzyknięcie domięśniowe metamizolu</t></is></c><c r="M171" s="2" t="inlineStr" /><c r="N171" s="2" t="inlineStr" /><c r="O171" s="2" t="inlineStr" /><c r="P171" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q171" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="172"><c r="A172" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B172" s="2" t="inlineStr"><is><t>Monitorowanie</t></is></c><c r="C172" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D172" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E172" s="2" t="inlineStr"><is><t>Typowe leki podlegające monitorowaniu stężeń to:</t></is></c><c r="F172" s="2" t="inlineStr"><is><t>cyklosporyna</t></is></c><c r="G172" s="2" t="inlineStr"><is><t>fenytoina</t></is></c><c r="H172" s="2" t="inlineStr"><is><t>gentamycyna</t></is></c><c r="I172" s="2" t="inlineStr"><is><t>Digoksyna</t></is></c><c r="J172" s="2" t="inlineStr" /><c r="K172" s="2" t="inlineStr" /><c r="L172" s="2" t="inlineStr" /><c r="M172" s="2" t="inlineStr" /><c r="N172" s="2" t="inlineStr" /><c r="O172" s="2" t="inlineStr" /><c r="P172" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q172" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="173"><c r="A173" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B173" s="2" t="inlineStr"><is><t>Ciąża</t></is></c><c r="C173" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D173" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E173" s="2" t="inlineStr"><is><t>Izoniazyd:</t></is></c><c r="F173" s="2" t="inlineStr"><is><t>działa bakteriobójczo na prątki szybko namnażające się</t></is></c><c r="G173" s="2" t="inlineStr" /><c r="H173" s="2" t="inlineStr" /><c r="I173" s="2" t="inlineStr" /><c r="J173" s="2" t="inlineStr" /><c r="K173" s="2" t="inlineStr"><is><t>nie powinien być stosowany przez kobiety w ciąży</t></is></c><c r="L173" s="2" t="inlineStr"><is><t>nie jest stosowany w leczeniu gruźlicy pozapłucnej</t></is></c><c r="M173" s="2" t="inlineStr"><is><t>może spowodować neuropatię obwodową</t></is></c><c r="N173" s="2" t="inlineStr" /><c r="O173" s="2" t="inlineStr" /><c r="P173" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q173" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="174"><c r="A174" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B174" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C174" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D174" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E174" s="2" t="inlineStr"><is><t>Wskaż prawdziwe połączenie lek-działanie niepożądne:</t></is></c><c r="F174" s="2" t="inlineStr"><is><t>zolpidem – niepamięć następcza</t></is></c><c r="G174" s="2" t="inlineStr"><is><t>rotygotyna – nudności i wymioty</t></is></c><c r="H174" s="2" t="inlineStr"><is><t>alprazolam - senność</t></is></c><c r="I174" s="2" t="inlineStr"><is><t>fluoksetyna – zaburzenia libido i funkcji seksualnych</t></is></c><c r="J174" s="2" t="inlineStr" /><c r="K174" s="2" t="inlineStr" /><c r="L174" s="2" t="inlineStr" /><c r="M174" s="2" t="inlineStr" /><c r="N174" s="2" t="inlineStr" /><c r="O174" s="2" t="inlineStr" /><c r="P174" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q174" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="175"><c r="A175" s="2" t="inlineStr"><is><t>LEKI PRZECIWPSYCHOTYCZNE</t></is></c><c r="B175" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C175" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D175" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E175" s="2" t="inlineStr"><is><t>Do leczenia zaburzeń psychotycznych z nasilonymi objawami negatywnymi należy wybrać:</t></is></c><c r="F175" s="2" t="inlineStr"><is><t>amisulpiryd</t></is></c><c r="G175" s="2" t="inlineStr"><is><t>olanzapinę</t></is></c><c r="H175" s="2" t="inlineStr" /><c r="I175" s="2" t="inlineStr" /><c r="J175" s="2" t="inlineStr" /><c r="K175" s="2" t="inlineStr"><is><t>haloperydol</t></is></c><c r="L175" s="2" t="inlineStr"><is><t>chlorpromazynę</t></is></c><c r="M175" s="2" t="inlineStr" /><c r="N175" s="2" t="inlineStr" /><c r="O175" s="2" t="inlineStr" /><c r="P175" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q175" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="176"><c r="A176" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B176" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C176" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D176" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E176" s="2" t="inlineStr"><is><t>Działanie przeciwwymiotne metoklopramidu wynika z blokady receptorów:</t></is></c><c r="F176" s="2" t="inlineStr"><is><t>dopaminowych (D2)</t></is></c><c r="G176" s="2" t="inlineStr"><is><t>serotoninowych (5-HT3)</t></is></c><c r="H176" s="2" t="inlineStr" /><c r="I176" s="2" t="inlineStr" /><c r="J176" s="2" t="inlineStr" /><c r="K176" s="2" t="inlineStr"><is><t>neurokininowych (NK1)</t></is></c><c r="L176" s="2" t="inlineStr"><is><t>kannabinoidowych (CB1)</t></is></c><c r="M176" s="2" t="inlineStr" /><c r="N176" s="2" t="inlineStr" /><c r="O176" s="2" t="inlineStr" /><c r="P176" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q176" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="177"><c r="A177" s="2" t="inlineStr"><is><t>UKŁAD PRZYWSPÓŁCZULNY</t></is></c><c r="B177" s="2" t="inlineStr"><is><t>Antidotum</t></is></c><c r="C177" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D177" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E177" s="2" t="inlineStr"><is><t>Rozszerzenie źrenic, suchość w ustach, osłabienie lub porażenie perystaltyki jelit obserwowane jest w przebiegu zatrucia:</t></is></c><c r="F177" s="2" t="inlineStr"><is><t>amitryptyliną</t></is></c><c r="G177" s="2" t="inlineStr" /><c r="H177" s="2" t="inlineStr" /><c r="I177" s="2" t="inlineStr" /><c r="J177" s="2" t="inlineStr" /><c r="K177" s="2" t="inlineStr"><is><t>escitalopramem</t></is></c><c r="L177" s="2" t="inlineStr"><is><t>pestycydami fosforoorganicznymi</t></is></c><c r="M177" s="2" t="inlineStr"><is><t>glikozydami naparstnicy</t></is></c><c r="N177" s="2" t="inlineStr" /><c r="O177" s="2" t="inlineStr" /><c r="P177" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q177" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="178"><c r="A178" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B178" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C178" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D178" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E178" s="2" t="inlineStr"><is><t>U 70-letniego mężczyzny z przewlekłą niewydolnością żylną wspomagająco do kompresjoterapii należy zastosować:</t></is></c><c r="F178" s="2" t="inlineStr"><is><t>mikronizowaną diosminę + hesperydynę</t></is></c><c r="G178" s="2" t="inlineStr" /><c r="H178" s="2" t="inlineStr" /><c r="I178" s="2" t="inlineStr" /><c r="J178" s="2" t="inlineStr" /><c r="K178" s="2" t="inlineStr"><is><t>kwas acetylosalicylowy w dawce antyagregacyjnej</t></is></c><c r="L178" s="2" t="inlineStr"><is><t>enoksaparynę w dawce profilaktycznej</t></is></c><c r="M178" s="2" t="inlineStr"><is><t>furosemid w dawce leczniczej</t></is></c><c r="N178" s="2" t="inlineStr" /><c r="O178" s="2" t="inlineStr" /><c r="P178" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q178" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="179"><c r="A179" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B179" s="2" t="inlineStr"><is><t>Antidotum</t></is></c><c r="C179" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D179" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E179" s="2" t="inlineStr"><is><t>Nie powinno się zwalniać pasażu jelitowego w przebiegu:</t></is></c><c r="F179" s="2" t="inlineStr"><is><t>zatrucia z objawami ogólnymi</t></is></c><c r="G179" s="2" t="inlineStr"><is><t>biegunki z krwią w stolcu i gorączką</t></is></c><c r="H179" s="2" t="inlineStr"><is><t>ostrej biegunki o niewielkim nasileniu</t></is></c><c r="I179" s="2" t="inlineStr" /><c r="J179" s="2" t="inlineStr" /><c r="K179" s="2" t="inlineStr"><is><t>przewlekłej biegunki związanej z chorobą zapalną jelit</t></is></c><c r="L179" s="2" t="inlineStr" /><c r="M179" s="2" t="inlineStr" /><c r="N179" s="2" t="inlineStr" /><c r="O179" s="2" t="inlineStr" /><c r="P179" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q179" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="180"><c r="A180" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B180" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C180" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D180" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E180" s="2" t="inlineStr"><is><t>Związki bizmutu:</t></is></c><c r="F180" s="2" t="inlineStr"><is><t>tworzą nierozpuszczalne kompleksy z białkami wysiękowymi na powierzchni owrzodzenia, działając osłaniająco wobec kwasu solnego i pepsyny na uszkodzoną błonę śluzową żołądka i dwunastnicy</t></is></c><c r="G180" s="2" t="inlineStr"><is><t>wchłaniają się z przewodu pokarmowego</t></is></c><c r="H180" s="2" t="inlineStr"><is><t>bezpośrednio niszczą komórki Helicobacter pylori</t></is></c><c r="I180" s="2" t="inlineStr"><is><t>mogą spowodować czarne zabarwienie języka i kału</t></is></c><c r="J180" s="2" t="inlineStr" /><c r="K180" s="2" t="inlineStr" /><c r="L180" s="2" t="inlineStr" /><c r="M180" s="2" t="inlineStr" /><c r="N180" s="2" t="inlineStr" /><c r="O180" s="2" t="inlineStr" /><c r="P180" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q180" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="181"><c r="A181" s="2" t="inlineStr"><is><t>UKŁAD WSPÓŁCZULNY</t></is></c><c r="B181" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C181" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D181" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E181" s="2" t="inlineStr"><is><t>Wskaż prawidłowe połączenie lek – wskazanie - dawka:</t></is></c><c r="F181" s="2" t="inlineStr"><is><t>dobutamina – diagnostyka niedokrwienia mięśnia serca –wlew 2-20 mcg/kg m.c./min</t></is></c><c r="G181" s="2" t="inlineStr"><is><t>adrenalina – resuscytacja krążeniowo-oddechowa– w dawkach frakcjonowanych i.v. po 1 mg w rozcieńczeniu w 10 ml 0,9% NaCl</t></is></c><c r="H181" s="2" t="inlineStr" /><c r="I181" s="2" t="inlineStr" /><c r="J181" s="2" t="inlineStr" /><c r="K181" s="2" t="inlineStr"><is><t>noradrenalina – ciężka hipotonia – wlew 2-10 mcg/kg m.c./min</t></is></c><c r="L181" s="2" t="inlineStr"><is><t>dopamina – ostra niewydolność mięśnia sercowego – wlew 1-3 mcg/kg m.c./min</t></is></c><c r="M181" s="2" t="inlineStr" /><c r="N181" s="2" t="inlineStr" /><c r="O181" s="2" t="inlineStr" /><c r="P181" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q181" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="182"><c r="A182" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B182" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C182" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D182" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E182" s="2" t="inlineStr"><is><t>Skala HAS-BLED określa ryzyko krwawienia u osób z migotaniem przedsionków stosujących leczenie przeciwkrzepliwe na podstawie oceny:</t></is></c><c r="F182" s="2" t="inlineStr"><is><t>wartości skurczowego ciśnienia tętniczego</t></is></c><c r="G182" s="2" t="inlineStr"><is><t>czynności wątroby</t></is></c><c r="H182" s="2" t="inlineStr"><is><t>stężenia kreatyniny</t></is></c><c r="I182" s="2" t="inlineStr" /><c r="J182" s="2" t="inlineStr" /><c r="K182" s="2" t="inlineStr"><is><t>glikemii</t></is></c><c r="L182" s="2" t="inlineStr" /><c r="M182" s="2" t="inlineStr" /><c r="N182" s="2" t="inlineStr" /><c r="O182" s="2" t="inlineStr" /><c r="P182" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q182" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="183"><c r="A183" s="2" t="inlineStr"><is><t>UKŁAD WSPÓŁCZULNY</t></is></c><c r="B183" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C183" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D183" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E183" s="2" t="inlineStr"><is><t>Wskaż prawdziwe połączenie substancja uzależniająca - lek stosowany w terapii uzależnienia:</t></is></c><c r="F183" s="2" t="inlineStr"><is><t>heroina - metadon</t></is></c><c r="G183" s="2" t="inlineStr"><is><t>nikotyna – wareniklina</t></is></c><c r="H183" s="2" t="inlineStr"><is><t>alkohol - nalmefen</t></is></c><c r="I183" s="2" t="inlineStr" /><c r="J183" s="2" t="inlineStr" /><c r="K183" s="2" t="inlineStr"><is><t>amfetamina - deferoksamina</t></is></c><c r="L183" s="2" t="inlineStr" /><c r="M183" s="2" t="inlineStr" /><c r="N183" s="2" t="inlineStr" /><c r="O183" s="2" t="inlineStr" /><c r="P183" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q183" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="184"><c r="A184" s="2" t="inlineStr"><is><t>LEKI MOCZOPĘDNE</t></is></c><c r="B184" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C184" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D184" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E184" s="2" t="inlineStr"><is><t>Peptydy natriuretyczne zwiększają:</t></is></c><c r="F184" s="2" t="inlineStr"><is><t>filtrację kłębuszkową</t></is></c><c r="G184" s="2" t="inlineStr" /><c r="H184" s="2" t="inlineStr" /><c r="I184" s="2" t="inlineStr" /><c r="J184" s="2" t="inlineStr" /><c r="K184" s="2" t="inlineStr"><is><t>wydzielanie aldosteronu</t></is></c><c r="L184" s="2" t="inlineStr"><is><t>glikemię</t></is></c><c r="M184" s="2" t="inlineStr"><is><t>aktywność układu współczulnego</t></is></c><c r="N184" s="2" t="inlineStr" /><c r="O184" s="2" t="inlineStr" /><c r="P184" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q184" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="185"><c r="A185" s="2" t="inlineStr"><is><t>ZABURZENIA RYTMU SERCA</t></is></c><c r="B185" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C185" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D185" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E185" s="2" t="inlineStr"><is><t>Pacjent z objawową bradykardią = 35 uderzeń/min jest leczony poniższym zestawem leków. Który z nich należy niezwłocznie odstawić?</t></is></c><c r="F185" s="2" t="inlineStr"><is><t>digoksynę</t></is></c><c r="G185" s="2" t="inlineStr"><is><t>amiodaron</t></is></c><c r="H185" s="2" t="inlineStr"><is><t>betaksolol</t></is></c><c r="I185" s="2" t="inlineStr" /><c r="J185" s="2" t="inlineStr" /><c r="K185" s="2" t="inlineStr"><is><t>losartan</t></is></c><c r="L185" s="2" t="inlineStr" /><c r="M185" s="2" t="inlineStr" /><c r="N185" s="2" t="inlineStr" /><c r="O185" s="2" t="inlineStr" /><c r="P185" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q185" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="186"><c r="A186" s="2" t="inlineStr"><is><t>NADCIŚNIENIE TĘTNICZE</t></is></c><c r="B186" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C186" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D186" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E186" s="2" t="inlineStr"><is><t>Irbesartan zwiększa w osoczu stężenie:</t></is></c><c r="F186" s="2" t="inlineStr"><is><t>reniny</t></is></c><c r="G186" s="2" t="inlineStr"><is><t>potasu</t></is></c><c r="H186" s="2" t="inlineStr" /><c r="I186" s="2" t="inlineStr" /><c r="J186" s="2" t="inlineStr" /><c r="K186" s="2" t="inlineStr"><is><t>bradykininy</t></is></c><c r="L186" s="2" t="inlineStr"><is><t>aldosteronu</t></is></c><c r="M186" s="2" t="inlineStr" /><c r="N186" s="2" t="inlineStr" /><c r="O186" s="2" t="inlineStr" /><c r="P186" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q186" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="187"><c r="A187" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B187" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C187" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D187" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E187" s="2" t="inlineStr"><is><t>70-letnia kobieta od miesiąca po wypisie ze szpitala otrzymuje kwas acetylosalicylowy + klopidogrel. Na tej podstawie można sądzić, że przebyła:</t></is></c><c r="F187" s="2" t="inlineStr"><is><t>angioplastykę wieńcową z wszczepieniem stentu</t></is></c><c r="G187" s="2" t="inlineStr"><is><t>zawał serca</t></is></c><c r="H187" s="2" t="inlineStr" /><c r="I187" s="2" t="inlineStr" /><c r="J187" s="2" t="inlineStr" /><c r="K187" s="2" t="inlineStr"><is><t>udar niedokrwienny mózgu</t></is></c><c r="L187" s="2" t="inlineStr"><is><t>zatorowość płucną niewysokiego ryzyka</t></is></c><c r="M187" s="2" t="inlineStr" /><c r="N187" s="2" t="inlineStr" /><c r="O187" s="2" t="inlineStr" /><c r="P187" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q187" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="188"><c r="A188" s="2" t="inlineStr"><is><t>ZABURZENIA RYTMU SERCA</t></is></c><c r="B188" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C188" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D188" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E188" s="2" t="inlineStr"><is><t>Wskaż prawdziwe połączenie lek – działanie niepożądane:</t></is></c><c r="F188" s="2" t="inlineStr"><is><t>metoprolol – blok przedsionkowo-komorowy I stopnia</t></is></c><c r="G188" s="2" t="inlineStr"><is><t>sotalol - wydłużenie odstępu QT</t></is></c><c r="H188" s="2" t="inlineStr"><is><t>propafenon - zaburzenia hematopoezy</t></is></c><c r="I188" s="2" t="inlineStr"><is><t>adenozyna - ból w klatce piersiowej</t></is></c><c r="J188" s="2" t="inlineStr" /><c r="K188" s="2" t="inlineStr" /><c r="L188" s="2" t="inlineStr" /><c r="M188" s="2" t="inlineStr" /><c r="N188" s="2" t="inlineStr" /><c r="O188" s="2" t="inlineStr" /><c r="P188" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q188" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="189"><c r="A189" s="2" t="inlineStr"><is><t>NADCIŚNIENIE TĘTNICZE</t></is></c><c r="B189" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C189" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D189" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E189" s="2" t="inlineStr"><is><t>59-letni mężczyzna z pozawałową niewydolnością serca (EF ok. 30%), z implantowanym ICD (kardiowerterem defibrylatorem) w prewencji pierwotnej NZK, z eGFR = 95%, z bólami pleców na skutek wielopoziomowej dyskopatii jest leczony: ramiprylem, karwedilolem, eplerenonem, indapamidem, preparatami chlorku potasu, magnezu z witaminą B6 i węglanu wapnia oraz paracetamolem i ketoprofenem. Które stwierdzenie jest prawdziwe?</t></is></c><c r="F189" s="2" t="inlineStr"><is><t>opisana terapia stwarza zagrożenie hiperkaliemią, co trzeba monitorować</t></is></c><c r="G189" s="2" t="inlineStr"><is><t>należy odstawić ketoprofen, bo może on osłabiać działanie leków w niewydolności serca</t></is></c><c r="H189" s="2" t="inlineStr" /><c r="I189" s="2" t="inlineStr" /><c r="J189" s="2" t="inlineStr" /><c r="K189" s="2" t="inlineStr"><is><t>ze względu na lepszą kontrolę choroby zamiast ramiprylu należy podać walsartan</t></is></c><c r="L189" s="2" t="inlineStr"><is><t>indapamid jako lek potencjalnie nieskuteczny powinien zostać zastąpiony torasemidem</t></is></c><c r="M189" s="2" t="inlineStr" /><c r="N189" s="2" t="inlineStr" /><c r="O189" s="2" t="inlineStr" /><c r="P189" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q189" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="190"><c r="A190" s="2" t="inlineStr"><is><t>NADCIŚNIENIE TĘTNICZE</t></is></c><c r="B190" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C190" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D190" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E190" s="2" t="inlineStr"><is><t>Wartości ciśnienia tętniczego może zwiększyć stosowanie:</t></is></c><c r="F190" s="2" t="inlineStr"><is><t>piroksykamu</t></is></c><c r="G190" s="2" t="inlineStr"><is><t>prednizonu</t></is></c><c r="H190" s="2" t="inlineStr" /><c r="I190" s="2" t="inlineStr" /><c r="J190" s="2" t="inlineStr" /><c r="K190" s="2" t="inlineStr"><is><t>eplerenonu</t></is></c><c r="L190" s="2" t="inlineStr"><is><t>morfiny</t></is></c><c r="M190" s="2" t="inlineStr" /><c r="N190" s="2" t="inlineStr" /><c r="O190" s="2" t="inlineStr" /><c r="P190" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q190" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="191"><c r="A191" s="2" t="inlineStr"><is><t>OSTEOPOROZA</t></is></c><c r="B191" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C191" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D191" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E191" s="2" t="inlineStr"><is><t>Kwas ibandronowy:</t></is></c><c r="F191" s="2" t="inlineStr"><is><t>z dużym powinowactwem wiąże się ze zmineralizowaną kością</t></is></c><c r="G191" s="2" t="inlineStr"><is><t>zmniejsza ryzyko złamania kręgów kręgosłupa u kobiet po menopauzie</t></is></c><c r="H191" s="2" t="inlineStr"><is><t>hamuje aktywację osteoklastów</t></is></c><c r="I191" s="2" t="inlineStr"><is><t>może spowodować martwicę szczęki</t></is></c><c r="J191" s="2" t="inlineStr" /><c r="K191" s="2" t="inlineStr" /><c r="L191" s="2" t="inlineStr" /><c r="M191" s="2" t="inlineStr" /><c r="N191" s="2" t="inlineStr" /><c r="O191" s="2" t="inlineStr" /><c r="P191" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q191" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="192"><c r="A192" s="2" t="inlineStr"><is><t>LEKI HIPOLIPEMIZUJĄCE</t></is></c><c r="B192" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C192" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D192" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E192" s="2" t="inlineStr"><is><t>Dodatkowe zmniejszenie stężenia cholesterolu LDL w surowicy można osiągnąć przez dodanie do statyn:</t></is></c><c r="F192" s="2" t="inlineStr"><is><t>kolesewelamu</t></is></c><c r="G192" s="2" t="inlineStr"><is><t>ewolokumabu</t></is></c><c r="H192" s="2" t="inlineStr"><is><t>ezetymibu</t></is></c><c r="I192" s="2" t="inlineStr" /><c r="J192" s="2" t="inlineStr" /><c r="K192" s="2" t="inlineStr"><is><t>PUFA – wielonienasyconych kwasów tłuszczowych</t></is></c><c r="L192" s="2" t="inlineStr" /><c r="M192" s="2" t="inlineStr" /><c r="N192" s="2" t="inlineStr" /><c r="O192" s="2" t="inlineStr" /><c r="P192" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q192" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="193"><c r="A193" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B193" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C193" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D193" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E193" s="2" t="inlineStr"><is><t>Które stwierdzenie jest prawdziwe:</t></is></c><c r="F193" s="2" t="inlineStr"><is><t>cilostazol wydłuża dystans marszu bez bólu u pacjentów z chromaniem przestankowym</t></is></c><c r="G193" s="2" t="inlineStr"><is><t>stosowanie serelaksyny może przynieść korzyści pacjentom z ostrą niewydolnością mięśnia sercowego</t></is></c><c r="H193" s="2" t="inlineStr"><is><t>do działań niepożądanych milrynonu należą zaburzenia rytmu serca</t></is></c><c r="I193" s="2" t="inlineStr" /><c r="J193" s="2" t="inlineStr" /><c r="K193" s="2" t="inlineStr"><is><t>inhibitory fosfodiesterazy 5 mogą być podane łącznie z azotanami</t></is></c><c r="L193" s="2" t="inlineStr" /><c r="M193" s="2" t="inlineStr" /><c r="N193" s="2" t="inlineStr" /><c r="O193" s="2" t="inlineStr" /><c r="P193" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q193" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="194"><c r="A194" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B194" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C194" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D194" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E194" s="2" t="inlineStr"><is><t>Fibraty (pochodne kwasu fibrynowego):</t></is></c><c r="F194" s="2" t="inlineStr"><is><t>hamują uwalnianie frakcji lipidowej VLDL z wątroby</t></is></c><c r="G194" s="2" t="inlineStr"><is><t>nasilają aktywność lipazy lipoproteinowej</t></is></c><c r="H194" s="2" t="inlineStr" /><c r="I194" s="2" t="inlineStr" /><c r="J194" s="2" t="inlineStr" /><c r="K194" s="2" t="inlineStr"><is><t>hamują wchłanianie tłuszczów złożonych z przewodu pokarmowego</t></is></c><c r="L194" s="2" t="inlineStr"><is><t>zmniejszają stężenie frakcji HDL poprzez spadek syntezy Apo-A1 i Apo-AII</t></is></c><c r="M194" s="2" t="inlineStr" /><c r="N194" s="2" t="inlineStr" /><c r="O194" s="2" t="inlineStr" /><c r="P194" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q194" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="195"><c r="A195" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B195" s="2" t="inlineStr"><is><t>Farmakokinetyka</t></is></c><c r="C195" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D195" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E195" s="2" t="inlineStr"><is><t>U chorych ze zdekompensowaną obukomorową niewydolnością serca:</t></is></c><c r="F195" s="2" t="inlineStr"><is><t>znacznie opóźnione jest wchłanianie leków z przewodu pokarmowego</t></is></c><c r="G195" s="2" t="inlineStr"><is><t>leki hydrofilne dystrybuują się do płynu obrzękowego, co dodatkowo negatywnie wpływa na ich dystrybucję do narządów docelowych</t></is></c><c r="H195" s="2" t="inlineStr"><is><t>zmniejsza się klirens wątrobowy wszystkich leków metabolizowanych w wątrobie niezależnie od stopnia ich ekstrakcji wątrobowej</t></is></c><c r="I195" s="2" t="inlineStr" /><c r="J195" s="2" t="inlineStr" /><c r="K195" s="2" t="inlineStr"><is><t>stosunkowo mało zmniejsza się klirens nerkowy leków</t></is></c><c r="L195" s="2" t="inlineStr" /><c r="M195" s="2" t="inlineStr" /><c r="N195" s="2" t="inlineStr" /><c r="O195" s="2" t="inlineStr" /><c r="P195" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q195" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="196"><c r="A196" s="2" t="inlineStr"><is><t>FARMAKOKINETYKA</t></is></c><c r="B196" s="2" t="inlineStr"><is><t>Interakcje</t></is></c><c r="C196" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D196" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E196" s="2" t="inlineStr"><is><t>Interakcją farmakodynamiczną jest:</t></is></c><c r="F196" s="2" t="inlineStr"><is><t>nasilenie depresji OUN po skojarzeniu opioidów z etanolem</t></is></c><c r="G196" s="2" t="inlineStr" /><c r="H196" s="2" t="inlineStr" /><c r="I196" s="2" t="inlineStr" /><c r="J196" s="2" t="inlineStr" /><c r="K196" s="2" t="inlineStr"><is><t>hamowanie wchłaniania z przewodu pokarmowego leków podawanych jednocześnie</t></is></c><c r="L196" s="2" t="inlineStr"><is><t>wytrącenie się osadu po zmieszaniu dwóch leków w jednym roztworze do wstrzyknięcia</t></is></c><c r="M196" s="2" t="inlineStr"><is><t>zwiększenie metabolizmu leków podawanych jednocześnie</t></is></c><c r="N196" s="2" t="inlineStr" /><c r="O196" s="2" t="inlineStr" /><c r="P196" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q196" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="197"><c r="A197" s="2" t="inlineStr"><is><t>LEKI MOCZOPĘDNE</t></is></c><c r="B197" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C197" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D197" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E197" s="2" t="inlineStr"><is><t>Kwasicę metaboliczną mogą powodować:</t></is></c><c r="F197" s="2" t="inlineStr"><is><t>metformina</t></is></c><c r="G197" s="2" t="inlineStr"><is><t>kwas acetylosalicylowy</t></is></c><c r="H197" s="2" t="inlineStr" /><c r="I197" s="2" t="inlineStr" /><c r="J197" s="2" t="inlineStr" /><c r="K197" s="2" t="inlineStr"><is><t>diuretyki pętlowe</t></is></c><c r="L197" s="2" t="inlineStr"><is><t>etanol</t></is></c><c r="M197" s="2" t="inlineStr" /><c r="N197" s="2" t="inlineStr" /><c r="O197" s="2" t="inlineStr" /><c r="P197" s="2" t="inlineStr"><is><t>EGZ 2018 I termin</t></is></c><c r="Q197" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="198"><c r="A198" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B198" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C198" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D198" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E198" s="2" t="inlineStr"><is><t>Klindamycyna:</t></is></c><c r="F198" s="2" t="inlineStr"><is><t>jest aktywna wobec beztlenowców</t></is></c><c r="G198" s="2" t="inlineStr" /><c r="H198" s="2" t="inlineStr" /><c r="I198" s="2" t="inlineStr" /><c r="J198" s="2" t="inlineStr" /><c r="K198" s="2" t="inlineStr"><is><t>dobrze przenika do płynu mózgowo-rdzeniowego</t></is></c><c r="L198" s="2" t="inlineStr"><is><t>słabo selekcjonuje szczepy Clostridium difficile w jelicie</t></is></c><c r="M198" s="2" t="inlineStr"><is><t>stosowana jest jako lek z wyboru w nierzeżączkowym zapaleniu cewki moczowej</t></is></c><c r="N198" s="2" t="inlineStr" /><c r="O198" s="2" t="inlineStr" /><c r="P198" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q198" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="199"><c r="A199" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B199" s="2" t="inlineStr"><is><t>Struktura chemiczna</t></is></c><c r="C199" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D199" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E199" s="2" t="inlineStr"><is><t>Pierścień beta-laktamowy znajduje się w cząsteczce:</t></is></c><c r="F199" s="2" t="inlineStr"><is><t>kloksacyliny</t></is></c><c r="G199" s="2" t="inlineStr"><is><t>ceftazydymu</t></is></c><c r="H199" s="2" t="inlineStr"><is><t>meropenemu</t></is></c><c r="I199" s="2" t="inlineStr" /><c r="J199" s="2" t="inlineStr" /><c r="K199" s="2" t="inlineStr"><is><t>wankomycyny</t></is></c><c r="L199" s="2" t="inlineStr" /><c r="M199" s="2" t="inlineStr" /><c r="N199" s="2" t="inlineStr" /><c r="O199" s="2" t="inlineStr" /><c r="P199" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q199" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="200"><c r="A200" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B200" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C200" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D200" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E200" s="2" t="inlineStr"><is><t>Wskaż prawdziwe połączenie lek – mechanizm działania:</t></is></c><c r="F200" s="2" t="inlineStr"><is><t>tygecyklina - hamowanie biosyntezy białka w komórkach bakterii poprzez wiązanie się z podjednostką 30 S rybosomu</t></is></c><c r="G200" s="2" t="inlineStr"><is><t>trimetoprim - inhibicja reduktazy kwasu dihydrofoliowego (DHFR)</t></is></c><c r="H200" s="2" t="inlineStr" /><c r="I200" s="2" t="inlineStr" /><c r="J200" s="2" t="inlineStr" /><c r="K200" s="2" t="inlineStr"><is><t>metronidazol - blokowanie syntezy ściany komórkowej bakterii</t></is></c><c r="L200" s="2" t="inlineStr"><is><t>teikoplanina - uszkodzenie DNA</t></is></c><c r="M200" s="2" t="inlineStr" /><c r="N200" s="2" t="inlineStr" /><c r="O200" s="2" t="inlineStr" /><c r="P200" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q200" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="201"><c r="A201" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B201" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C201" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D201" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E201" s="2" t="inlineStr"><is><t>Wskaż prawdziwe połączenie lek – działania niepożądane:</t></is></c><c r="F201" s="2" t="inlineStr"><is><t>lewofloksacyna - drgawki</t></is></c><c r="G201" s="2" t="inlineStr"><is><t>ceftriakson – zagęszczenie żółci</t></is></c><c r="H201" s="2" t="inlineStr"><is><t>wankomycyna – zespół czerwonego karku</t></is></c><c r="I201" s="2" t="inlineStr"><is><t>linezolid – trombocytopenia</t></is></c><c r="J201" s="2" t="inlineStr" /><c r="K201" s="2" t="inlineStr"><is><t>W celu zwiększenia bezpieczeństwa leczenia amikacyną mężczyzny z powikłanym zakażeniem układu moczowego należy:</t></is></c><c r="L201" s="2" t="inlineStr" /><c r="M201" s="2" t="inlineStr" /><c r="N201" s="2" t="inlineStr" /><c r="O201" s="2" t="inlineStr" /><c r="P201" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q201" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="202"><c r="A202" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B202" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C202" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D202" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E202" s="2" t="inlineStr"><is><t>W leczeniu pacjentki z niepowikłanym zapaleniem pęcherza moczowego można zastosować:</t></is></c><c r="F202" s="2" t="inlineStr"><is><t>amoksycylinę z inhibitorem beta-laktamazy</t></is></c><c r="G202" s="2" t="inlineStr"><is><t>fosfomycynę</t></is></c><c r="H202" s="2" t="inlineStr"><is><t>cyprofloksacynę</t></is></c><c r="I202" s="2" t="inlineStr"><is><t>furazydynę</t></is></c><c r="J202" s="2" t="inlineStr" /><c r="K202" s="2" t="inlineStr" /><c r="L202" s="2" t="inlineStr" /><c r="M202" s="2" t="inlineStr" /><c r="N202" s="2" t="inlineStr" /><c r="O202" s="2" t="inlineStr" /><c r="P202" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q202" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="203"><c r="A203" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B203" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C203" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D203" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E203" s="2" t="inlineStr"><is><t>Lekiem przeciwbakteryjnym o wąskim zakresie działania przeciwbakteryjnego jest:</t></is></c><c r="F203" s="2" t="inlineStr"><is><t>fenoksymetylopenicylina</t></is></c><c r="G203" s="2" t="inlineStr"><is><t>nystatyna</t></is></c><c r="H203" s="2" t="inlineStr" /><c r="I203" s="2" t="inlineStr" /><c r="J203" s="2" t="inlineStr" /><c r="K203" s="2" t="inlineStr"><is><t>aksetyl cefuroksymu</t></is></c><c r="L203" s="2" t="inlineStr"><is><t>chloramfenikol</t></is></c><c r="M203" s="2" t="inlineStr" /><c r="N203" s="2" t="inlineStr" /><c r="O203" s="2" t="inlineStr" /><c r="P203" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q203" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="204"><c r="A204" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B204" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C204" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D204" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E204" s="2" t="inlineStr"><is><t>Aktywność przeciwbakteryjną względem opornych na metycylinę szczepów Staphylococcus aureus (MRSA) ma:</t></is></c><c r="F204" s="2" t="inlineStr"><is><t>linezolid</t></is></c><c r="G204" s="2" t="inlineStr"><is><t>mupirocyna</t></is></c><c r="H204" s="2" t="inlineStr"><is><t>wankomycyna</t></is></c><c r="I204" s="2" t="inlineStr"><is><t>dalfoprystyna/chinuprystyna</t></is></c><c r="J204" s="2" t="inlineStr" /><c r="K204" s="2" t="inlineStr" /><c r="L204" s="2" t="inlineStr" /><c r="M204" s="2" t="inlineStr" /><c r="N204" s="2" t="inlineStr" /><c r="O204" s="2" t="inlineStr" /><c r="P204" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q204" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="205"><c r="A205" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B205" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C205" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D205" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E205" s="2" t="inlineStr"><is><t>Profilaktyka infekcyjnego zapalenia wsierdzia (IZW) jest wskazana u osób z grup wysokiego ryzyka IZW w przypadku procedur:</t></is></c><c r="F205" s="2" t="inlineStr"><is><t>dentystycznych z manipulacją w obrębie dziąseł lub okolicy około-wierzchołkowej zębów</t></is></c><c r="G205" s="2" t="inlineStr"><is><t>inwazyjnych w obrębie górnych dróg oddechowych, tj. usunięcie migdałka</t></is></c><c r="H205" s="2" t="inlineStr" /><c r="I205" s="2" t="inlineStr" /><c r="J205" s="2" t="inlineStr" /><c r="K205" s="2" t="inlineStr"><is><t>inwazyjnych w obrębie układu moczowo-płciowego</t></is></c><c r="L205" s="2" t="inlineStr"><is><t>inwazyjnych w obrębie przewodu pokarmowego</t></is></c><c r="M205" s="2" t="inlineStr" /><c r="N205" s="2" t="inlineStr" /><c r="O205" s="2" t="inlineStr" /><c r="P205" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q205" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="206"><c r="A206" s="2" t="inlineStr"><is><t>LEKI PRZECIWWIRUSOWE</t></is></c><c r="B206" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C206" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D206" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E206" s="2" t="inlineStr"><is><t>Gancyklowir:</t></is></c><c r="F206" s="2" t="inlineStr"><is><t>może powodować uszkodzenie szpiku</t></is></c><c r="G206" s="2" t="inlineStr" /><c r="H206" s="2" t="inlineStr" /><c r="I206" s="2" t="inlineStr" /><c r="J206" s="2" t="inlineStr" /><c r="K206" s="2" t="inlineStr"><is><t>jest inhibitorem proteazy wirusowej</t></is></c><c r="L206" s="2" t="inlineStr"><is><t>bezpośrednio hamuje uwalnianie wirusów z zakażonych komórek</t></is></c><c r="M206" s="2" t="inlineStr"><is><t>nie przenika do ośrodkowego układu nerwowego</t></is></c><c r="N206" s="2" t="inlineStr" /><c r="O206" s="2" t="inlineStr" /><c r="P206" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q206" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="207"><c r="A207" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B207" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C207" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D207" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E207" s="2" t="inlineStr"><is><t>W standardowej profilaktyce okołooperacyjnej wskazane jest stosowanie:</t></is></c><c r="F207" s="2" t="inlineStr"><is><t>wankomycyny</t></is></c><c r="G207" s="2" t="inlineStr"><is><t>metronidazolu</t></is></c><c r="H207" s="2" t="inlineStr"><is><t>cyprofloksacyny</t></is></c><c r="I207" s="2" t="inlineStr"><is><t>cefazoliny</t></is></c><c r="J207" s="2" t="inlineStr" /><c r="K207" s="2" t="inlineStr" /><c r="L207" s="2" t="inlineStr" /><c r="M207" s="2" t="inlineStr" /><c r="N207" s="2" t="inlineStr" /><c r="O207" s="2" t="inlineStr" /><c r="P207" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q207" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="208"><c r="A208" s="2" t="inlineStr"><is><t>LEKI PRZECIWGRZYBICZE</t></is></c><c r="B208" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C208" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D208" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E208" s="2" t="inlineStr"><is><t>W grzybiczym zakażeniu skóry gładkiej można zastosować miejscowo:</t></is></c><c r="F208" s="2" t="inlineStr"><is><t>cyklopiroksolaminę</t></is></c><c r="G208" s="2" t="inlineStr"><is><t>natamycynę</t></is></c><c r="H208" s="2" t="inlineStr"><is><t>klotrimazol</t></is></c><c r="I208" s="2" t="inlineStr" /><c r="J208" s="2" t="inlineStr" /><c r="K208" s="2" t="inlineStr"><is><t>kaspofunginę</t></is></c><c r="L208" s="2" t="inlineStr" /><c r="M208" s="2" t="inlineStr" /><c r="N208" s="2" t="inlineStr" /><c r="O208" s="2" t="inlineStr" /><c r="P208" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q208" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="209"><c r="A209" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B209" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C209" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D209" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E209" s="2" t="inlineStr"><is><t>Wskaż poprawną strategię postępowania w zakresie leczenia zakażeń:</t></is></c><c r="F209" s="2" t="inlineStr"><is><t>leczenie empiryczne powinno uwzględniać miejsce powstania zakażenia: domowe lub związane z kontaktem ze służbą zdrowia</t></is></c><c r="G209" s="2" t="inlineStr"><is><t>na podstawie antybiogramu należy dokonać deeskalacji leczenia</t></is></c><c r="H209" s="2" t="inlineStr"><is><t>zasadą jest doustne leczenie przeciwinfekcyjne poza uzasadnionymi wyjątkami poza dekolonizacją MRSA przed operacjami</t></is></c><c r="I209" s="2" t="inlineStr" /><c r="J209" s="2" t="inlineStr" /><c r="K209" s="2" t="inlineStr" /><c r="L209" s="2" t="inlineStr" /><c r="M209" s="2" t="inlineStr" /><c r="N209" s="2" t="inlineStr" /><c r="O209" s="2" t="inlineStr" /><c r="P209" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q209" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="210"><c r="A210" s="2" t="inlineStr"><is><t>LEKI PRZECIWNOWOTWOROWE</t></is></c><c r="B210" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C210" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D210" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E210" s="2" t="inlineStr"><is><t>W Polsce granica opłacalności procedur medycznych jest:</t></is></c><c r="F210" s="2" t="inlineStr"><is><t>wykorzystywanym i usankcjonowanym prawnie kryterium refundacyjnym</t></is></c><c r="G210" s="2" t="inlineStr"><is><t>ustalona w oparciu o roczny koszt dializoterapii – przewlekłej, powszechnej i jednej z najdroższych procedur medycznych</t></is></c><c r="H210" s="2" t="inlineStr"><is><t>ustalona w oparciu o 3 krotność produktu krajowego brutto per capita</t></is></c><c r="I210" s="2" t="inlineStr"><is><t>odmienna dla leków stosowanych w chorobach onkologicznych</t></is></c><c r="J210" s="2" t="inlineStr" /><c r="K210" s="2" t="inlineStr" /><c r="L210" s="2" t="inlineStr" /><c r="M210" s="2" t="inlineStr" /><c r="N210" s="2" t="inlineStr" /><c r="O210" s="2" t="inlineStr" /><c r="P210" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q210" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="211"><c r="A211" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B211" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C211" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D211" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E211" s="2" t="inlineStr"><is><t>W leczeniu trądziku młodzieńczego racjonalne jest zastosowanie:</t></is></c><c r="F211" s="2" t="inlineStr"><is><t>klindamycyny</t></is></c><c r="G211" s="2" t="inlineStr"><is><t>doksycykliny</t></is></c><c r="H211" s="2" t="inlineStr"><is><t>izotretinoiny</t></is></c><c r="I211" s="2" t="inlineStr" /><c r="J211" s="2" t="inlineStr" /><c r="K211" s="2" t="inlineStr"><is><t>norfloksacyny</t></is></c><c r="L211" s="2" t="inlineStr" /><c r="M211" s="2" t="inlineStr" /><c r="N211" s="2" t="inlineStr" /><c r="O211" s="2" t="inlineStr" /><c r="P211" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q211" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="212"><c r="A212" s="2" t="inlineStr"><is><t>LEKI PRZECIWWIRUSOWE</t></is></c><c r="B212" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C212" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D212" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E212" s="2" t="inlineStr"><is><t>Istotne genetycznie uwarunkowane różnice działania stwierdzono dla:</t></is></c><c r="F212" s="2" t="inlineStr"><is><t>abakawiru</t></is></c><c r="G212" s="2" t="inlineStr"><is><t>karbamazepiny</t></is></c><c r="H212" s="2" t="inlineStr"><is><t>warfaryny</t></is></c><c r="I212" s="2" t="inlineStr" /><c r="J212" s="2" t="inlineStr" /><c r="K212" s="2" t="inlineStr"><is><t>diltiazemu</t></is></c><c r="L212" s="2" t="inlineStr" /><c r="M212" s="2" t="inlineStr" /><c r="N212" s="2" t="inlineStr" /><c r="O212" s="2" t="inlineStr" /><c r="P212" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q212" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="213"><c r="A213" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B213" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C213" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D213" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E213" s="2" t="inlineStr"><is><t>Inhibitory dipeptydylopeptydazy IV (DPP IV):</t></is></c><c r="F213" s="2" t="inlineStr"><is><t>mogą być stosowane łącznie z insuliną</t></is></c><c r="G213" s="2" t="inlineStr"><is><t>zwiększają ryzyko wystąpienia dolegliwości ze strony przewodu pokarmowego</t></is></c><c r="H213" s="2" t="inlineStr" /><c r="I213" s="2" t="inlineStr" /><c r="J213" s="2" t="inlineStr" /><c r="K213" s="2" t="inlineStr"><is><t>powodują przyrost masy ciała</t></is></c><c r="L213" s="2" t="inlineStr"><is><t>są podawane podskórnie</t></is></c><c r="M213" s="2" t="inlineStr" /><c r="N213" s="2" t="inlineStr" /><c r="O213" s="2" t="inlineStr" /><c r="P213" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q213" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="214"><c r="A214" s="2" t="inlineStr"><is><t>CUKRZYCA</t></is></c><c r="B214" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C214" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D214" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E214" s="2" t="inlineStr"><is><t>Wskaż zdanie/zdania prawdziwe:</t></is></c><c r="F214" s="2" t="inlineStr"><is><t>empagliflozyna – zmniejsza ryzyko śmierci z przyczyn sercowo￾naczyniowych u chorych z cukrzycą typu 2</t></is></c><c r="G214" s="2" t="inlineStr"><is><t>metformina – zmniejsza ryzyko powikłań makroangiopatycznych</t></is></c><c r="H214" s="2" t="inlineStr" /><c r="I214" s="2" t="inlineStr" /><c r="J214" s="2" t="inlineStr" /><c r="K214" s="2" t="inlineStr"><is><t>sitagliptyna - pomimo euglikemii może spowodować kwasicę ketonową</t></is></c><c r="L214" s="2" t="inlineStr"><is><t>gliklazyd – powoduje redukcję masy ciała</t></is></c><c r="M214" s="2" t="inlineStr" /><c r="N214" s="2" t="inlineStr" /><c r="O214" s="2" t="inlineStr" /><c r="P214" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q214" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="215"><c r="A215" s="2" t="inlineStr"><is><t>TARCZYCA</t></is></c><c r="B215" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C215" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D215" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E215" s="2" t="inlineStr"><is><t>Stosowanie tiamazolu może być przyczyną:</t></is></c><c r="F215" s="2" t="inlineStr"><is><t>żółtaczki cholestatycznej</t></is></c><c r="G215" s="2" t="inlineStr"><is><t>agranulocytozy</t></is></c><c r="H215" s="2" t="inlineStr"><is><t>wysypki skórnej</t></is></c><c r="I215" s="2" t="inlineStr"><is><t>niedoczynności tarczycy</t></is></c><c r="J215" s="2" t="inlineStr" /><c r="K215" s="2" t="inlineStr" /><c r="L215" s="2" t="inlineStr" /><c r="M215" s="2" t="inlineStr" /><c r="N215" s="2" t="inlineStr" /><c r="O215" s="2" t="inlineStr" /><c r="P215" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q215" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="216"><c r="A216" s="2" t="inlineStr"><is><t>UKŁAD PRZYWSPÓŁCZULNY</t></is></c><c r="B216" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C216" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D216" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E216" s="2" t="inlineStr"><is><t>Leczenie triamcynolonem może pogorszyć przebieg:</t></is></c><c r="F216" s="2" t="inlineStr"><is><t>jaskry</t></is></c><c r="G216" s="2" t="inlineStr"><is><t>zaburzeń nastroju</t></is></c><c r="H216" s="2" t="inlineStr"><is><t>zaćmy</t></is></c><c r="I216" s="2" t="inlineStr"><is><t>osteoporozy</t></is></c><c r="J216" s="2" t="inlineStr" /><c r="K216" s="2" t="inlineStr" /><c r="L216" s="2" t="inlineStr" /><c r="M216" s="2" t="inlineStr" /><c r="N216" s="2" t="inlineStr" /><c r="O216" s="2" t="inlineStr" /><c r="P216" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q216" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="217"><c r="A217" s="2" t="inlineStr"><is><t>CUKRZYCA</t></is></c><c r="B217" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C217" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D217" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E217" s="2" t="inlineStr"><is><t>Pacjent nieprzytomny, z hipoglikemią po spożyciu alkoholu, powinien otrzymać:</t></is></c><c r="F217" s="2" t="inlineStr"><is><t>20% roztwór glukozy i.v</t></is></c><c r="G217" s="2" t="inlineStr" /><c r="H217" s="2" t="inlineStr" /><c r="I217" s="2" t="inlineStr" /><c r="J217" s="2" t="inlineStr" /><c r="K217" s="2" t="inlineStr"><is><t>glukagon i.m</t></is></c><c r="L217" s="2" t="inlineStr"><is><t>glukozę p.o</t></is></c><c r="M217" s="2" t="inlineStr"><is><t>glukagon s.c</t></is></c><c r="N217" s="2" t="inlineStr" /><c r="O217" s="2" t="inlineStr" /><c r="P217" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q217" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="218"><c r="A218" s="2" t="inlineStr"><is><t>OSTEOPOROZA</t></is></c><c r="B218" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C218" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D218" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E218" s="2" t="inlineStr"><is><t>Potwierdzone klinicznie zmniejszenie ryzyka złamania kości udowej w przebiegu osteoporozy występuje w wyniku leczenia:</t></is></c><c r="F218" s="2" t="inlineStr"><is><t>ranelinianem strontu</t></is></c><c r="G218" s="2" t="inlineStr"><is><t>kwasem ibandronowy</t></is></c><c r="H218" s="2" t="inlineStr" /><c r="I218" s="2" t="inlineStr" /><c r="J218" s="2" t="inlineStr" /><c r="K218" s="2" t="inlineStr"><is><t>raloksyfenem</t></is></c><c r="L218" s="2" t="inlineStr"><is><t>kalcytoniną</t></is></c><c r="M218" s="2" t="inlineStr" /><c r="N218" s="2" t="inlineStr" /><c r="O218" s="2" t="inlineStr" /><c r="P218" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q218" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="219"><c r="A219" s="2" t="inlineStr"><is><t>GLIKOKORTYKOSTEROIDY</t></is></c><c r="B219" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C219" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D219" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E219" s="2" t="inlineStr"><is><t>Wskaż prawidłowe połączenie - wskazanie do stosowania glikokortykosteroidów - uzasadnienie zastosowania:</t></is></c><c r="F219" s="2" t="inlineStr"><is><t>poród przedwczesny – stymulowanie dojrzewania płuc płodu</t></is></c><c r="G219" s="2" t="inlineStr"><is><t>astma – ograniczenie procesu zapalnego</t></is></c><c r="H219" s="2" t="inlineStr"><is><t>przełom nadnerczowy – leczenie substytucyjne</t></is></c><c r="I219" s="2" t="inlineStr" /><c r="J219" s="2" t="inlineStr" /><c r="K219" s="2" t="inlineStr"><is><t>mononukleoza zakaźna – efekt immunosupresyjny</t></is></c><c r="L219" s="2" t="inlineStr" /><c r="M219" s="2" t="inlineStr" /><c r="N219" s="2" t="inlineStr" /><c r="O219" s="2" t="inlineStr" /><c r="P219" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q219" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="220"><c r="A220" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B220" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C220" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D220" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E220" s="2" t="inlineStr"><is><t>Do działań niepożądanych środków antykoncepcyjnych zalicza się:</t></is></c><c r="F220" s="2" t="inlineStr"><is><t>trądzik</t></is></c><c r="G220" s="2" t="inlineStr"><is><t>depresję</t></is></c><c r="H220" s="2" t="inlineStr"><is><t>zwiększenie ryzyka udaru mózgu</t></is></c><c r="I220" s="2" t="inlineStr" /><c r="J220" s="2" t="inlineStr" /><c r="K220" s="2" t="inlineStr"><is><t>zwiększenie ryzyka raka jajnika</t></is></c><c r="L220" s="2" t="inlineStr" /><c r="M220" s="2" t="inlineStr" /><c r="N220" s="2" t="inlineStr" /><c r="O220" s="2" t="inlineStr" /><c r="P220" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q220" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="221"><c r="A221" s="2" t="inlineStr"><is><t>TARCZYCA</t></is></c><c r="B221" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C221" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D221" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E221" s="2" t="inlineStr"><is><t>Witamina D3 (cholekalcyferol):</t></is></c><c r="F221" s="2" t="inlineStr"><is><t>może być stosowana w niedoczynności przytarczyc</t></is></c><c r="G221" s="2" t="inlineStr"><is><t>w nadmiarze hamuje wzrost kości</t></is></c><c r="H221" s="2" t="inlineStr" /><c r="I221" s="2" t="inlineStr" /><c r="J221" s="2" t="inlineStr" /><c r="K221" s="2" t="inlineStr"><is><t>mimo stosowania w dużych dawkach nie chroni przed osteoporotycznymi złamaniami kości</t></is></c><c r="L221" s="2" t="inlineStr"><is><t>jest nieaktywna u chorych z niewydolnością nerek</t></is></c><c r="M221" s="2" t="inlineStr" /><c r="N221" s="2" t="inlineStr" /><c r="O221" s="2" t="inlineStr" /><c r="P221" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q221" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="222"><c r="A222" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B222" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C222" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D222" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E222" s="2" t="inlineStr"><is><t>Działanie przeczyszczające wykazuje:</t></is></c><c r="F222" s="2" t="inlineStr"><is><t>siarczan magnezu</t></is></c><c r="G222" s="2" t="inlineStr"><is><t>dokusan sodowy</t></is></c><c r="H222" s="2" t="inlineStr" /><c r="I222" s="2" t="inlineStr" /><c r="J222" s="2" t="inlineStr" /><c r="K222" s="2" t="inlineStr"><is><t>werapamil</t></is></c><c r="L222" s="2" t="inlineStr"><is><t>racekadotryl</t></is></c><c r="M222" s="2" t="inlineStr" /><c r="N222" s="2" t="inlineStr" /><c r="O222" s="2" t="inlineStr" /><c r="P222" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q222" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="223"><c r="A223" s="2" t="inlineStr"><is><t>LEKI PRZECIWNOWOTWOROWE</t></is></c><c r="B223" s="2" t="inlineStr"><is><t>Antidotum</t></is></c><c r="C223" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D223" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E223" s="2" t="inlineStr"><is><t>Mesna :</t></is></c><c r="F223" s="2" t="inlineStr"><is><t>powoduje upłynnienie wydzieliny w drzewie oskrzelowym</t></is></c><c r="G223" s="2" t="inlineStr"><is><t>jest antidotum przeciw metabolitowi cyklofosfamidu drażniącemu błonę śluzową dróg moczowych</t></is></c><c r="H223" s="2" t="inlineStr"><is><t>jest stosowana miejscowo w postaci inhalacji</t></is></c><c r="I223" s="2" t="inlineStr"><is><t>może wywołać skurcz oskrzeli</t></is></c><c r="J223" s="2" t="inlineStr" /><c r="K223" s="2" t="inlineStr" /><c r="L223" s="2" t="inlineStr" /><c r="M223" s="2" t="inlineStr" /><c r="N223" s="2" t="inlineStr" /><c r="O223" s="2" t="inlineStr" /><c r="P223" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q223" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="224"><c r="A224" s="2" t="inlineStr"><is><t>ZNIECZULENIA MIEJSCOWE</t></is></c><c r="B224" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C224" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D224" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E224" s="2" t="inlineStr"><is><t>Do leków znieczulających miejscowo stosowanych na błony śluzowe należy:</t></is></c><c r="F224" s="2" t="inlineStr"><is><t>prylokaina</t></is></c><c r="G224" s="2" t="inlineStr"><is><t>lidokaina</t></is></c><c r="H224" s="2" t="inlineStr" /><c r="I224" s="2" t="inlineStr" /><c r="J224" s="2" t="inlineStr" /><c r="K224" s="2" t="inlineStr"><is><t>chlorek etylu</t></is></c><c r="L224" s="2" t="inlineStr"><is><t>kapsaicyna</t></is></c><c r="M224" s="2" t="inlineStr" /><c r="N224" s="2" t="inlineStr" /><c r="O224" s="2" t="inlineStr" /><c r="P224" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q224" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="225"><c r="A225" s="2" t="inlineStr"><is><t>LEKI PRZECIWNOWOTWOROWE</t></is></c><c r="B225" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C225" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D225" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E225" s="2" t="inlineStr"><is><t>Inhibitorem kinaz białkowych jest:</t></is></c><c r="F225" s="2" t="inlineStr"><is><t>rapamycyna</t></is></c><c r="G225" s="2" t="inlineStr"><is><t>imatynib</t></is></c><c r="H225" s="2" t="inlineStr" /><c r="I225" s="2" t="inlineStr" /><c r="J225" s="2" t="inlineStr" /><c r="K225" s="2" t="inlineStr"><is><t>bortezomib</t></is></c><c r="L225" s="2" t="inlineStr"><is><t>lenalidomid</t></is></c><c r="M225" s="2" t="inlineStr" /><c r="N225" s="2" t="inlineStr" /><c r="O225" s="2" t="inlineStr" /><c r="P225" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q225" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="226"><c r="A226" s="2" t="inlineStr"><is><t>LEKI PRZECIWHISTAMINOWE</t></is></c><c r="B226" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C226" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D226" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E226" s="2" t="inlineStr"><is><t>Betahistyna:</t></is></c><c r="F226" s="2" t="inlineStr"><is><t>zwiększa przepływ krwi w uchu wewnętrznym</t></is></c><c r="G226" s="2" t="inlineStr"><is><t>jest stosowana w leczeniu choroby Méniére'a</t></is></c><c r="H226" s="2" t="inlineStr" /><c r="I226" s="2" t="inlineStr" /><c r="J226" s="2" t="inlineStr" /><c r="K226" s="2" t="inlineStr"><is><t>jest agonistą receptorów H3</t></is></c><c r="L226" s="2" t="inlineStr"><is><t>jest lekiem z wyboru w przedsionkowych zawrotach głowy</t></is></c><c r="M226" s="2" t="inlineStr" /><c r="N226" s="2" t="inlineStr" /><c r="O226" s="2" t="inlineStr" /><c r="P226" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q226" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="227"><c r="A227" s="2" t="inlineStr"><is><t>PADACZKA</t></is></c><c r="B227" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C227" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D227" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E227" s="2" t="inlineStr"><is><t>Lekiem stosowanym w neuropatii popółpaścowej jest:</t></is></c><c r="F227" s="2" t="inlineStr"><is><t>amitryptylina</t></is></c><c r="G227" s="2" t="inlineStr"><is><t>pregabalina</t></is></c><c r="H227" s="2" t="inlineStr"><is><t>lidokaina</t></is></c><c r="I227" s="2" t="inlineStr"><is><t>gabapentyna</t></is></c><c r="J227" s="2" t="inlineStr" /><c r="K227" s="2" t="inlineStr" /><c r="L227" s="2" t="inlineStr" /><c r="M227" s="2" t="inlineStr" /><c r="N227" s="2" t="inlineStr" /><c r="O227" s="2" t="inlineStr" /><c r="P227" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q227" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="228"><c r="A228" s="2" t="inlineStr"><is><t>NARKOTYCZNE LEKI PRZECIWBÓLOWE</t></is></c><c r="B228" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C228" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D228" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E228" s="2" t="inlineStr"><is><t>Na drugim stopniu drabiny analgetycznej wg WHO znajduje się:</t></is></c><c r="F228" s="2" t="inlineStr"><is><t>morfina w dawce ≤ 30 mg/dobę</t></is></c><c r="G228" s="2" t="inlineStr"><is><t>kodeina w dawce ≤360 mg/dobę</t></is></c><c r="H228" s="2" t="inlineStr"><is><t>oksykodon w dawce ≤20 mg/dobę</t></is></c><c r="I228" s="2" t="inlineStr" /><c r="J228" s="2" t="inlineStr" /><c r="K228" s="2" t="inlineStr"><is><t>fentanyl w dawce ≤ 10 mg/dobę</t></is></c><c r="L228" s="2" t="inlineStr" /><c r="M228" s="2" t="inlineStr" /><c r="N228" s="2" t="inlineStr" /><c r="O228" s="2" t="inlineStr" /><c r="P228" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q228" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="229"><c r="A229" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B229" s="2" t="inlineStr"><is><t>Farmakokinetyka</t></is></c><c r="C229" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D229" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E229" s="2" t="inlineStr"><is><t>Wskaż prawidłowe zdanie:</t></is></c><c r="F229" s="2" t="inlineStr"><is><t>czas odstawienia rywaroksabanu przed planowanym zabiegiem chirurgicznym zależy od ryzyka krwawienia</t></is></c><c r="G229" s="2" t="inlineStr"><is><t>jeśli uzyskano stabilną hemostazę antagonisty witaminy K włącza się w 1. dobie po zabiegu chirurgicznym</t></is></c><c r="H229" s="2" t="inlineStr" /><c r="I229" s="2" t="inlineStr" /><c r="J229" s="2" t="inlineStr" /><c r="K229" s="2" t="inlineStr"><is><t>warfaryny nie należy odstawiać wcześniej niż na 2 dni przed planowanym zabiegiem chirurgicznym</t></is></c><c r="L229" s="2" t="inlineStr"><is><t>czas odstawienia edoksabanu przed zabiegiem chirurgicznym nie zależy od wartości klirensu kreatyniny</t></is></c><c r="M229" s="2" t="inlineStr" /><c r="N229" s="2" t="inlineStr" /><c r="O229" s="2" t="inlineStr" /><c r="P229" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q229" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="230"><c r="A230" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B230" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C230" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D230" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E230" s="2" t="inlineStr"><is><t>Wskaż prawidłowy lek przeciwzakrzepowego u osoby z:</t></is></c><c r="F230" s="2" t="inlineStr"><is><t>zapaleniem żył głębokich - rywaroksaban</t></is></c><c r="G230" s="2" t="inlineStr"><is><t>ciążą - enoksaparyna</t></is></c><c r="H230" s="2" t="inlineStr"><is><t>mechaniczną zastawką serca – warfaryna</t></is></c><c r="I230" s="2" t="inlineStr" /><c r="J230" s="2" t="inlineStr" /><c r="K230" s="2" t="inlineStr"><is><t>niewydolnością nerek (CCr &lt;30ml/min) – dabigatran</t></is></c><c r="L230" s="2" t="inlineStr" /><c r="M230" s="2" t="inlineStr" /><c r="N230" s="2" t="inlineStr" /><c r="O230" s="2" t="inlineStr" /><c r="P230" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q230" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="231"><c r="A231" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B231" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C231" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D231" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E231" s="2" t="inlineStr"><is><t>Podczas leczenia przeciwzakrzepowego z zastosowaniem nadroparyny należy:</t></is></c><c r="F231" s="2" t="inlineStr"><is><t>kontrolować liczbę płytek</t></is></c><c r="G231" s="2" t="inlineStr"><is><t>rozważyć korektę dawek u osób otyłych</t></is></c><c r="H231" s="2" t="inlineStr" /><c r="I231" s="2" t="inlineStr" /><c r="J231" s="2" t="inlineStr" /><c r="K231" s="2" t="inlineStr"><is><t>monitorować dawki za pomocą oznaczenia APTT</t></is></c><c r="L231" s="2" t="inlineStr"><is><t>zmniejszyć dawkę w każdym przypadku, jeśli eGFR osiąga wartość mniejszą niż 90 ml/min</t></is></c><c r="M231" s="2" t="inlineStr" /><c r="N231" s="2" t="inlineStr" /><c r="O231" s="2" t="inlineStr" /><c r="P231" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q231" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="232"><c r="A232" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B232" s="2" t="inlineStr"><is><t>Sposób podania</t></is></c><c r="C232" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D232" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E232" s="2" t="inlineStr"><is><t>Kangrelor:</t></is></c><c r="F232" s="2" t="inlineStr"><is><t>jest wskazany podczas przezskórnych interwencji wieńcowych łącznie z kwasem acetylosalicylowym</t></is></c><c r="G232" s="2" t="inlineStr" /><c r="H232" s="2" t="inlineStr" /><c r="I232" s="2" t="inlineStr" /><c r="J232" s="2" t="inlineStr" /><c r="K232" s="2" t="inlineStr"><is><t>jest agonistą receptora P2Y12</t></is></c><c r="L232" s="2" t="inlineStr"><is><t>wymaga aktywacji w przewodzie pokarmowym</t></is></c><c r="M232" s="2" t="inlineStr"><is><t>działa przez 1-2 doby</t></is></c><c r="N232" s="2" t="inlineStr" /><c r="O232" s="2" t="inlineStr" /><c r="P232" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q232" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="233"><c r="A233" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B233" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C233" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D233" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E233" s="2" t="inlineStr"><is><t>Na istotnie zmniejszoną skuteczność doustnych antagonistów witaminy K może mieć wpływ spożywanie:</t></is></c><c r="F233" s="2" t="inlineStr"><is><t>szpinaku</t></is></c><c r="G233" s="2" t="inlineStr" /><c r="H233" s="2" t="inlineStr" /><c r="I233" s="2" t="inlineStr" /><c r="J233" s="2" t="inlineStr" /><c r="K233" s="2" t="inlineStr"><is><t>oleju rybnego zawierającego nienasycone kwasy tłuszczowe omega -3</t></is></c><c r="L233" s="2" t="inlineStr"><is><t>witaminy E</t></is></c><c r="M233" s="2" t="inlineStr"><is><t>czosnku</t></is></c><c r="N233" s="2" t="inlineStr" /><c r="O233" s="2" t="inlineStr" /><c r="P233" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q233" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="234"><c r="A234" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B234" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C234" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D234" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E234" s="2" t="inlineStr"><is><t>Pacjentom, którzy przebyli udar niedokrwienny mózgu należy zalecić profilaktykę wtórną. Do leków o udokumentowanym działaniu zmniejszających ryzyko następnego udaru należy:</t></is></c><c r="F234" s="2" t="inlineStr"><is><t>simwastatyna</t></is></c><c r="G234" s="2" t="inlineStr"><is><t>klopidogrel</t></is></c><c r="H234" s="2" t="inlineStr"><is><t>lizynopryl</t></is></c><c r="I234" s="2" t="inlineStr"><is><t>kwas acetylosalicylowy</t></is></c><c r="J234" s="2" t="inlineStr" /><c r="K234" s="2" t="inlineStr" /><c r="L234" s="2" t="inlineStr" /><c r="M234" s="2" t="inlineStr" /><c r="N234" s="2" t="inlineStr" /><c r="O234" s="2" t="inlineStr" /><c r="P234" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q234" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="235"><c r="A235" s="2" t="inlineStr"><is><t>LEKI HIPOLIPEMIZUJĄCE</t></is></c><c r="B235" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C235" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D235" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E235" s="2" t="inlineStr"><is><t>Fenofibrat:</t></is></c><c r="F235" s="2" t="inlineStr"><is><t>zmniejsza stężenie trójglicerydów i zwiększa stężenie cholesterolu HDL</t></is></c><c r="G235" s="2" t="inlineStr"><is><t>zwiększa ryzyko kamicy pęcherzyka żółciowego</t></is></c><c r="H235" s="2" t="inlineStr" /><c r="I235" s="2" t="inlineStr" /><c r="J235" s="2" t="inlineStr" /><c r="K235" s="2" t="inlineStr"><is><t>hamuje reduktazę 3-hydroksy-3-metyloglutarylo-CoA (HMG-CoA)</t></is></c><c r="L235" s="2" t="inlineStr"><is><t>nie może być stosowany w połączeniu ze statyną</t></is></c><c r="M235" s="2" t="inlineStr" /><c r="N235" s="2" t="inlineStr" /><c r="O235" s="2" t="inlineStr" /><c r="P235" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q235" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="236"><c r="A236" s="2" t="inlineStr"><is><t>LEKI MOCZOPĘDNE</t></is></c><c r="B236" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C236" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D236" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E236" s="2" t="inlineStr"><is><t>Hiperurykemię może spowodować:</t></is></c><c r="F236" s="2" t="inlineStr"><is><t>torasemid</t></is></c><c r="G236" s="2" t="inlineStr"><is><t>kwas acetylosalicylowy</t></is></c><c r="H236" s="2" t="inlineStr" /><c r="I236" s="2" t="inlineStr" /><c r="J236" s="2" t="inlineStr" /><c r="K236" s="2" t="inlineStr"><is><t>losartan</t></is></c><c r="L236" s="2" t="inlineStr"><is><t>allopurynol</t></is></c><c r="M236" s="2" t="inlineStr" /><c r="N236" s="2" t="inlineStr" /><c r="O236" s="2" t="inlineStr" /><c r="P236" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q236" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="237"><c r="A237" s="2" t="inlineStr"><is><t>ZABURZENIA RYTMU SERCA</t></is></c><c r="B237" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C237" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D237" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E237" s="2" t="inlineStr"><is><t>Odstęp QT mogą wydłużać:</t></is></c><c r="F237" s="2" t="inlineStr"><is><t>amiodaron</t></is></c><c r="G237" s="2" t="inlineStr"><is><t>sotalol</t></is></c><c r="H237" s="2" t="inlineStr" /><c r="I237" s="2" t="inlineStr" /><c r="J237" s="2" t="inlineStr" /><c r="K237" s="2" t="inlineStr"><is><t>propranolol</t></is></c><c r="L237" s="2" t="inlineStr"><is><t>diltiazem</t></is></c><c r="M237" s="2" t="inlineStr" /><c r="N237" s="2" t="inlineStr" /><c r="O237" s="2" t="inlineStr" /><c r="P237" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q237" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="238"><c r="A238" s="2" t="inlineStr"><is><t>NADCIŚNIENIE TĘTNICZE</t></is></c><c r="B238" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C238" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D238" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E238" s="2" t="inlineStr"><is><t>Indapamid:</t></is></c><c r="F238" s="2" t="inlineStr"><is><t>ma działanie naczyniorozszerzające</t></is></c><c r="G238" s="2" t="inlineStr"><is><t>może spowodować hiponatremię</t></is></c><c r="H238" s="2" t="inlineStr"><is><t>zmniejsza wydalanie wapnia z moczem</t></is></c><c r="I238" s="2" t="inlineStr"><is><t>jest chętnie stosowany w przewlekłej terapii nadciśnienia tętniczego u osób po 80 roku życia</t></is></c><c r="J238" s="2" t="inlineStr" /><c r="K238" s="2" t="inlineStr" /><c r="L238" s="2" t="inlineStr" /><c r="M238" s="2" t="inlineStr" /><c r="N238" s="2" t="inlineStr" /><c r="O238" s="2" t="inlineStr" /><c r="P238" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q238" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="239"><c r="A239" s="2" t="inlineStr"><is><t>LEKI ROŚLINNE I SUPLEMENTY</t></is></c><c r="B239" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C239" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D239" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E239" s="2" t="inlineStr"><is><t>Produkty biopodobne:</t></is></c><c r="F239" s="2" t="inlineStr"><is><t>są automatycznie zamienne (substytucja)</t></is></c><c r="G239" s="2" t="inlineStr"><is><t>muszą mieć potwierdzoną podobną immunogenność</t></is></c><c r="H239" s="2" t="inlineStr" /><c r="I239" s="2" t="inlineStr" /><c r="J239" s="2" t="inlineStr" /><c r="K239" s="2" t="inlineStr"><is><t>są rejestrowane w procedurze zdecentralizowanej</t></is></c><c r="L239" s="2" t="inlineStr"><is><t>po dopuszczeniu do obrotu mogą być stosowane we wszystkich wskazaniach zamiennie</t></is></c><c r="M239" s="2" t="inlineStr" /><c r="N239" s="2" t="inlineStr" /><c r="O239" s="2" t="inlineStr" /><c r="P239" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q239" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="240"><c r="A240" s="2" t="inlineStr"><is><t>LEKI PRZECIWPASOŻYTNICZE</t></is></c><c r="B240" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C240" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D240" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E240" s="2" t="inlineStr"><is><t>W leczeniu zarażenia glistą ludzką stosujemy:</t></is></c><c r="F240" s="2" t="inlineStr"><is><t>pyrantel</t></is></c><c r="G240" s="2" t="inlineStr"><is><t>albendazol</t></is></c><c r="H240" s="2" t="inlineStr" /><c r="I240" s="2" t="inlineStr" /><c r="J240" s="2" t="inlineStr" /><c r="K240" s="2" t="inlineStr"><is><t>tynidazol</t></is></c><c r="L240" s="2" t="inlineStr"><is><t>krotamiton</t></is></c><c r="M240" s="2" t="inlineStr" /><c r="N240" s="2" t="inlineStr" /><c r="O240" s="2" t="inlineStr" /><c r="P240" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q240" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="241"><c r="A241" s="2" t="inlineStr"><is><t>LEKI PRZECIWWIRUSOWE</t></is></c><c r="B241" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C241" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D241" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E241" s="2" t="inlineStr"><is><t>W leczeniu grypy zaleca się:</t></is></c><c r="F241" s="2" t="inlineStr"><is><t>zanamiwir</t></is></c><c r="G241" s="2" t="inlineStr"><is><t>oseltamiwir</t></is></c><c r="H241" s="2" t="inlineStr" /><c r="I241" s="2" t="inlineStr" /><c r="J241" s="2" t="inlineStr" /><c r="K241" s="2" t="inlineStr"><is><t>acyklowir</t></is></c><c r="L241" s="2" t="inlineStr"><is><t>foskarnet</t></is></c><c r="M241" s="2" t="inlineStr" /><c r="N241" s="2" t="inlineStr" /><c r="O241" s="2" t="inlineStr" /><c r="P241" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q241" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="242"><c r="A242" s="2" t="inlineStr"><is><t>UKŁAD ODDECHOWY</t></is></c><c r="B242" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C242" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D242" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E242" s="2" t="inlineStr"><is><t>W przypadku dotychczas nieleczonych chorych, u których objawy astmy oskrzelowej w ciągu dnia występują sporadycznie (&lt;2 razy w miesiącu), objawy nocne nie występują, nie ma czynników ryzyka zaostrzeń (także w wywiadzie), a czynność płuc jest prawidłowa należy zastosować:</t></is></c><c r="F242" s="2" t="inlineStr"><is><t>fenoterol doraźnie</t></is></c><c r="G242" s="2" t="inlineStr" /><c r="H242" s="2" t="inlineStr" /><c r="I242" s="2" t="inlineStr" /><c r="J242" s="2" t="inlineStr" /><c r="K242" s="2" t="inlineStr"><is><t>montelukast przewlekle</t></is></c><c r="L242" s="2" t="inlineStr"><is><t>regularnie małe dawki cyklezonidu</t></is></c><c r="M242" s="2" t="inlineStr"><is><t>teofilinę krótkodziałającą</t></is></c><c r="N242" s="2" t="inlineStr" /><c r="O242" s="2" t="inlineStr" /><c r="P242" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q242" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="243"><c r="A243" s="2" t="inlineStr"><is><t>UKŁAD PRZYWSPÓŁCZULNY</t></is></c><c r="B243" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C243" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D243" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E243" s="2" t="inlineStr"><is><t>Bromek glikopironium :</t></is></c><c r="F243" s="2" t="inlineStr"><is><t>wykazuje synergizm działania bronchodylatacyjnego z indakaterolem</t></is></c><c r="G243" s="2" t="inlineStr"><is><t>jest stosowany w leczeniu podtrzymującym w POChP</t></is></c><c r="H243" s="2" t="inlineStr" /><c r="I243" s="2" t="inlineStr" /><c r="J243" s="2" t="inlineStr" /><c r="K243" s="2" t="inlineStr"><is><t>jest wziewnym agonistą receptorów muskarynowych</t></is></c><c r="L243" s="2" t="inlineStr"><is><t>rozszczepia wiązania disiarczkowe w glikoproteinach śluzu</t></is></c><c r="M243" s="2" t="inlineStr" /><c r="N243" s="2" t="inlineStr" /><c r="O243" s="2" t="inlineStr" /><c r="P243" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q243" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="244"><c r="A244" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B244" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C244" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D244" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E244" s="2" t="inlineStr"><is><t>W leczeniu przewlekłego zapalenia trzustki celowe może być zastosowanie:</t></is></c><c r="F244" s="2" t="inlineStr"><is><t>suplementacji enzymów trzustkowych</t></is></c><c r="G244" s="2" t="inlineStr"><is><t>tramadolu</t></is></c><c r="H244" s="2" t="inlineStr"><is><t>pantoprazolu</t></is></c><c r="I244" s="2" t="inlineStr"><is><t>fluoksetyny</t></is></c><c r="J244" s="2" t="inlineStr" /><c r="K244" s="2" t="inlineStr" /><c r="L244" s="2" t="inlineStr" /><c r="M244" s="2" t="inlineStr" /><c r="N244" s="2" t="inlineStr" /><c r="O244" s="2" t="inlineStr" /><c r="P244" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q244" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="245"><c r="A245" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B245" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C245" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D245" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E245" s="2" t="inlineStr"><is><t>Profilaktyka przeciwmalaryczna w warunkach wysokiego ryzyka zakażenia Plasmodium falciparum obejmuje stosowanie:</t></is></c><c r="F245" s="2" t="inlineStr"><is><t>repelentów</t></is></c><c r="G245" s="2" t="inlineStr"><is><t>atowakwonu/proguanilu</t></is></c><c r="H245" s="2" t="inlineStr"><is><t>doksycykliny</t></is></c><c r="I245" s="2" t="inlineStr" /><c r="J245" s="2" t="inlineStr" /><c r="K245" s="2" t="inlineStr"><is><t>artemetru/lumefantryny</t></is></c><c r="L245" s="2" t="inlineStr" /><c r="M245" s="2" t="inlineStr" /><c r="N245" s="2" t="inlineStr" /><c r="O245" s="2" t="inlineStr" /><c r="P245" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q245" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="246"><c r="A246" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B246" s="2" t="inlineStr"><is><t>Przeciwwskazania</t></is></c><c r="C246" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D246" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E246" s="2" t="inlineStr"><is><t>Adalimumab:</t></is></c><c r="F246" s="2" t="inlineStr"><is><t>jest rekombinowanym w pełni ludzkim przeciwciałem monoklonalnym</t></is></c><c r="G246" s="2" t="inlineStr"><is><t>neutralizuje biologiczną czynność TNF</t></is></c><c r="H246" s="2" t="inlineStr"><is><t>jest przeciwwskazany w ciężkich zakażeniach</t></is></c><c r="I246" s="2" t="inlineStr" /><c r="J246" s="2" t="inlineStr" /><c r="K246" s="2" t="inlineStr"><is><t>jest wytwarzany z użyciem komórek zwierzęcych, co wiadomo na podstawie ujednoliconych zasad nadawania nazw przeciwciałom monoklonalnym</t></is></c><c r="L246" s="2" t="inlineStr" /><c r="M246" s="2" t="inlineStr" /><c r="N246" s="2" t="inlineStr" /><c r="O246" s="2" t="inlineStr" /><c r="P246" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q246" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="247"><c r="A247" s="2" t="inlineStr"><is><t>CUKRZYCA</t></is></c><c r="B247" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C247" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D247" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E247" s="2" t="inlineStr"><is><t>Dla insuliny aspart u pacjentów z umiarkowaną i ciężką niewydolnością wątroby stwierdzono: t max = ok. 85 min (tmax = ok. 40 minut u pacjentów z prawidłową czynnością wątroby); AUC, Cmax i CL/F były podobne do pacjentów z prawidłową czynnością wątroby. Na tej podstawie u osób z niewydolnością wątroby uzasadnione jest:</t></is></c><c r="F247" s="2" t="inlineStr"><is><t>wcześniejsze podanie leku przed posiłkiem</t></is></c><c r="G247" s="2" t="inlineStr"><is><t>stosowanie leku u osób z 7-15 pkt wg skali Childa-Pugha</t></is></c><c r="H247" s="2" t="inlineStr" /><c r="I247" s="2" t="inlineStr" /><c r="J247" s="2" t="inlineStr" /><c r="K247" s="2" t="inlineStr"><is><t>wyłącznie dożylne podawanie leku</t></is></c><c r="L247" s="2" t="inlineStr"><is><t>redukcja dawki początkowej o ½ oszacowanej na podstawie m.c. i wyjściowej glikemii</t></is></c><c r="M247" s="2" t="inlineStr" /><c r="N247" s="2" t="inlineStr" /><c r="O247" s="2" t="inlineStr" /><c r="P247" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q247" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="248"><c r="A248" s="2" t="inlineStr"><is><t>NADCIŚNIENIE TĘTNICZE</t></is></c><c r="B248" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C248" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D248" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E248" s="2" t="inlineStr"><is><t>Wartości ciśnienia tętniczego mogą się zwiększyć po włączeniu:</t></is></c><c r="F248" s="2" t="inlineStr"><is><t>metyloprednizolonu</t></is></c><c r="G248" s="2" t="inlineStr"><is><t>diklofenaku</t></is></c><c r="H248" s="2" t="inlineStr" /><c r="I248" s="2" t="inlineStr" /><c r="J248" s="2" t="inlineStr" /><c r="K248" s="2" t="inlineStr"><is><t>eplerenonu</t></is></c><c r="L248" s="2" t="inlineStr"><is><t>urapidylu</t></is></c><c r="M248" s="2" t="inlineStr" /><c r="N248" s="2" t="inlineStr" /><c r="O248" s="2" t="inlineStr" /><c r="P248" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q248" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="249"><c r="A249" s="2" t="inlineStr"><is><t>CHOROBA NIEDOKRWIENNA SERCA</t></is></c><c r="B249" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C249" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D249" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E249" s="2" t="inlineStr"><is><t>Farmakoterapię otyłości należy rozważyć, gdy:</t></is></c><c r="F249" s="2" t="inlineStr"><is><t>BMI&gt; 27 kg/m2 i glikemia na czczo &gt;100mg/dl</t></is></c><c r="G249" s="2" t="inlineStr"><is><t>BMI≥ 30 kg/m2 i stwierdzono ponowny wzrost masy ciała pomimo wdrożonych procedur niefarmakologicznych</t></is></c><c r="H249" s="2" t="inlineStr"><is><t>BMI&gt; 27 kg/m2 i SBP ≥160 mmHg</t></is></c><c r="I249" s="2" t="inlineStr" /><c r="J249" s="2" t="inlineStr" /><c r="K249" s="2" t="inlineStr"><is><t>BMI≥ 30 kg/m2, a wcześniejsze procedury niefarmakologiczne spowodowały redukcję masy ciała w przedziale 7-10 kg</t></is></c><c r="L249" s="2" t="inlineStr" /><c r="M249" s="2" t="inlineStr" /><c r="N249" s="2" t="inlineStr" /><c r="O249" s="2" t="inlineStr" /><c r="P249" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q249" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="250"><c r="A250" s="2" t="inlineStr"><is><t>CUKRZYCA</t></is></c><c r="B250" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C250" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D250" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E250" s="2" t="inlineStr"><is><t>Wzrost masy ciała mogą spowodować:</t></is></c><c r="F250" s="2" t="inlineStr"><is><t>chlorpromazyna</t></is></c><c r="G250" s="2" t="inlineStr"><is><t>insulina</t></is></c><c r="H250" s="2" t="inlineStr"><is><t>kwas walproinowy</t></is></c><c r="I250" s="2" t="inlineStr" /><c r="J250" s="2" t="inlineStr" /><c r="K250" s="2" t="inlineStr"><is><t>liraglutyd</t></is></c><c r="L250" s="2" t="inlineStr" /><c r="M250" s="2" t="inlineStr" /><c r="N250" s="2" t="inlineStr" /><c r="O250" s="2" t="inlineStr" /><c r="P250" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q250" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="251"><c r="A251" s="2" t="inlineStr"><is><t>NARKOTYCZNE LEKI PRZECIWBÓLOWE</t></is></c><c r="B251" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C251" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D251" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E251" s="2" t="inlineStr"><is><t>Który z leków istotnie zwiększa ryzyko napadów drgawkowych:</t></is></c><c r="F251" s="2" t="inlineStr"><is><t>tramadol</t></is></c><c r="G251" s="2" t="inlineStr"><is><t>amitryptylina</t></is></c><c r="H251" s="2" t="inlineStr"><is><t>prometazyna</t></is></c><c r="I251" s="2" t="inlineStr" /><c r="J251" s="2" t="inlineStr" /><c r="K251" s="2" t="inlineStr"><is><t>klorazepan</t></is></c><c r="L251" s="2" t="inlineStr" /><c r="M251" s="2" t="inlineStr" /><c r="N251" s="2" t="inlineStr" /><c r="O251" s="2" t="inlineStr" /><c r="P251" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q251" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="252"><c r="A252" s="2" t="inlineStr"><is><t>FARMAKOLOGIA OGÓLNA I EBM</t></is></c><c r="B252" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C252" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D252" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E252" s="2" t="inlineStr"><is><t>Zgoda komisji bioetycznej jest niezbędna, gdy planowane jest przeprowadzenie:</t></is></c><c r="F252" s="2" t="inlineStr"><is><t>badania klinicznego fazy III</t></is></c><c r="G252" s="2" t="inlineStr"><is><t>eksperymentu leczniczego</t></is></c><c r="H252" s="2" t="inlineStr"><is><t>badania klinicznego niekomercyjnego</t></is></c><c r="I252" s="2" t="inlineStr" /><c r="J252" s="2" t="inlineStr" /><c r="K252" s="2" t="inlineStr"><is><t>zastosowania leku off-label, ale zgodnie z aktualną wiedzą medyczną</t></is></c><c r="L252" s="2" t="inlineStr" /><c r="M252" s="2" t="inlineStr" /><c r="N252" s="2" t="inlineStr" /><c r="O252" s="2" t="inlineStr" /><c r="P252" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q252" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="253"><c r="A253" s="2" t="inlineStr"><is><t>LEKI PRZECIWWIRUSOWE</t></is></c><c r="B253" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C253" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D253" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E253" s="2" t="inlineStr"><is><t>W procedurze centralnej rejestruje się leki stosowane w:</t></is></c><c r="F253" s="2" t="inlineStr"><is><t>chorobach rzadkich</t></is></c><c r="G253" s="2" t="inlineStr"><is><t>terapii HIV</t></is></c><c r="H253" s="2" t="inlineStr"><is><t>terapii genowej</t></is></c><c r="I253" s="2" t="inlineStr" /><c r="J253" s="2" t="inlineStr" /><c r="K253" s="2" t="inlineStr"><is><t>populacji geriatrycznej</t></is></c><c r="L253" s="2" t="inlineStr" /><c r="M253" s="2" t="inlineStr" /><c r="N253" s="2" t="inlineStr" /><c r="O253" s="2" t="inlineStr" /><c r="P253" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q253" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="254"><c r="A254" s="2" t="inlineStr"><is><t>FARMAKOLOGIA OGÓLNA I EBM</t></is></c><c r="B254" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C254" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D254" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E254" s="2" t="inlineStr"><is><t>Pierwotnym źródłem wiedzy o lekach są:</t></is></c><c r="F254" s="2" t="inlineStr"><is><t>publikacje wyników badań klinicznych</t></is></c><c r="G254" s="2" t="inlineStr" /><c r="H254" s="2" t="inlineStr" /><c r="I254" s="2" t="inlineStr" /><c r="J254" s="2" t="inlineStr" /><c r="K254" s="2" t="inlineStr"><is><t>wytyczne praktyki klinicznej</t></is></c><c r="L254" s="2" t="inlineStr"><is><t>charakterystyki produktów leczniczych</t></is></c><c r="M254" s="2" t="inlineStr"><is><t>podręczniki farmakologii i indeksy leków</t></is></c><c r="N254" s="2" t="inlineStr" /><c r="O254" s="2" t="inlineStr" /><c r="P254" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q254" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="255"><c r="A255" s="2" t="inlineStr"><is><t>LEKI ROŚLINNE I SUPLEMENTY</t></is></c><c r="B255" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C255" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D255" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E255" s="2" t="inlineStr"><is><t>Wskazaniem do stosowania retinolu jest:</t></is></c><c r="F255" s="2" t="inlineStr"><is><t>łuszczyca</t></is></c><c r="G255" s="2" t="inlineStr"><is><t>niedowidzenie o zmierzchu</t></is></c><c r="H255" s="2" t="inlineStr" /><c r="I255" s="2" t="inlineStr" /><c r="J255" s="2" t="inlineStr" /><c r="K255" s="2" t="inlineStr"><is><t>polineuropatia obwodowa</t></is></c><c r="L255" s="2" t="inlineStr"><is><t>osteomalacja</t></is></c><c r="M255" s="2" t="inlineStr" /><c r="N255" s="2" t="inlineStr" /><c r="O255" s="2" t="inlineStr" /><c r="P255" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q255" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="256"><c r="A256" s="2" t="inlineStr"><is><t>CHOROBA NIEDOKRWIENNA SERCA</t></is></c><c r="B256" s="2" t="inlineStr"><is><t>Przeciwwskazania</t></is></c><c r="C256" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D256" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E256" s="2" t="inlineStr"><is><t>Feksofenadyna:</t></is></c><c r="F256" s="2" t="inlineStr"><is><t>jest podawana doustnie</t></is></c><c r="G256" s="2" t="inlineStr" /><c r="H256" s="2" t="inlineStr" /><c r="I256" s="2" t="inlineStr" /><c r="J256" s="2" t="inlineStr" /><c r="K256" s="2" t="inlineStr"><is><t>działa nieselektywnie na rec. H1</t></is></c><c r="L256" s="2" t="inlineStr"><is><t>przenika w znacznym stopniu przez barierę krew- mózg</t></is></c><c r="M256" s="2" t="inlineStr"><is><t>działa kardiotoksycznie i jest przeciwwskazana w chorobie niedokrwiennej serca</t></is></c><c r="N256" s="2" t="inlineStr" /><c r="O256" s="2" t="inlineStr" /><c r="P256" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q256" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="257"><c r="A257" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B257" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C257" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D257" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E257" s="2" t="inlineStr"><is><t>Wskaż wady dekstranów:</t></is></c><c r="F257" s="2" t="inlineStr"><is><t>utrudniają wiarygodne oznaczenie grupy krwi i próby krzyżowej</t></is></c><c r="G257" s="2" t="inlineStr"><is><t>są immunogenne</t></is></c><c r="H257" s="2" t="inlineStr" /><c r="I257" s="2" t="inlineStr" /><c r="J257" s="2" t="inlineStr" /><c r="K257" s="2" t="inlineStr"><is><t>powodują przyrost objętości wewnątrznaczyniowej przekraczający ich objętość</t></is></c><c r="L257" s="2" t="inlineStr"><is><t>działają prozakrzepowo</t></is></c><c r="M257" s="2" t="inlineStr" /><c r="N257" s="2" t="inlineStr" /><c r="O257" s="2" t="inlineStr" /><c r="P257" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q257" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="258"><c r="A258" s="2" t="inlineStr"><is><t>OTĘPIENIE</t></is></c><c r="B258" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C258" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D258" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E258" s="2" t="inlineStr"><is><t>Podanie rywastygminy jest uzasadnione u pacjentów z:</t></is></c><c r="F258" s="2" t="inlineStr"><is><t>otępieniem w przebiegu choroby Parkinsona</t></is></c><c r="G258" s="2" t="inlineStr"><is><t>chorobą Alzheimera</t></is></c><c r="H258" s="2" t="inlineStr" /><c r="I258" s="2" t="inlineStr" /><c r="J258" s="2" t="inlineStr" /><c r="K258" s="2" t="inlineStr"><is><t>otępieniem naczyniopochodnym</t></is></c><c r="L258" s="2" t="inlineStr"><is><t>otępieniem czołowo-skroniowym</t></is></c><c r="M258" s="2" t="inlineStr" /><c r="N258" s="2" t="inlineStr" /><c r="O258" s="2" t="inlineStr" /><c r="P258" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q258" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="259"><c r="A259" s="2" t="inlineStr"><is><t>LEKI PRZECIWLĘKOWE</t></is></c><c r="B259" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C259" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D259" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E259" s="2" t="inlineStr"><is><t>W alkoholowym zespole odstawiennym celowe może być zastosowanie:</t></is></c><c r="F259" s="2" t="inlineStr"><is><t>tiaminy</t></is></c><c r="G259" s="2" t="inlineStr"><is><t>diazepamu</t></is></c><c r="H259" s="2" t="inlineStr"><is><t>płynoterapia z suplementacją elektrolitów</t></is></c><c r="I259" s="2" t="inlineStr" /><c r="J259" s="2" t="inlineStr" /><c r="K259" s="2" t="inlineStr"><is><t>akamprozatu</t></is></c><c r="L259" s="2" t="inlineStr" /><c r="M259" s="2" t="inlineStr" /><c r="N259" s="2" t="inlineStr" /><c r="O259" s="2" t="inlineStr" /><c r="P259" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q259" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="260"><c r="A260" s="2" t="inlineStr"><is><t>LEKI IMMUNOSUPRESYJNE</t></is></c><c r="B260" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C260" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D260" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E260" s="2" t="inlineStr"><is><t>Mykofenolan mofetylu:</t></is></c><c r="F260" s="2" t="inlineStr"><is><t>jest wskazany w profilaktyce ostrego odrzucania przeszczepu serca</t></is></c><c r="G260" s="2" t="inlineStr"><is><t>zwiększa ryzyko wystąpienia nowotworów</t></is></c><c r="H260" s="2" t="inlineStr" /><c r="I260" s="2" t="inlineStr" /><c r="J260" s="2" t="inlineStr" /><c r="K260" s="2" t="inlineStr"><is><t>należy do inhibitorów mTOR</t></is></c><c r="L260" s="2" t="inlineStr"><is><t>stosowany w czasie ciąży jest bezpieczny dla płodu</t></is></c><c r="M260" s="2" t="inlineStr" /><c r="N260" s="2" t="inlineStr" /><c r="O260" s="2" t="inlineStr" /><c r="P260" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q260" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="261"><c r="A261" s="2" t="inlineStr"><is><t>NIEWYDOLNOŚĆ SERCA</t></is></c><c r="B261" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C261" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D261" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E261" s="2" t="inlineStr"><is><t>Iwabradyna:</t></is></c><c r="F261" s="2" t="inlineStr"><is><t>może powodować zaburzenia widzenia</t></is></c><c r="G261" s="2" t="inlineStr"><is><t>wybiórczo i swoiście wpływa na na prąd If rozrusznika serca</t></is></c><c r="H261" s="2" t="inlineStr" /><c r="I261" s="2" t="inlineStr" /><c r="J261" s="2" t="inlineStr" /><c r="K261" s="2" t="inlineStr"><is><t>obniża kurczliwość mięśnia sercowego</t></is></c><c r="L261" s="2" t="inlineStr"><is><t>wydłuża czas repolaryzacji komór</t></is></c><c r="M261" s="2" t="inlineStr" /><c r="N261" s="2" t="inlineStr" /><c r="O261" s="2" t="inlineStr" /><c r="P261" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q261" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="262"><c r="A262" s="2" t="inlineStr"><is><t>CHOROBA NIEDOKRWIENNA SERCA</t></is></c><c r="B262" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C262" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D262" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E262" s="2" t="inlineStr"><is><t>Monoazotan izosorbidu:</t></is></c><c r="F262" s="2" t="inlineStr"><is><t>jest skuteczny po podaniu doustnym</t></is></c><c r="G262" s="2" t="inlineStr"><is><t>poprawia ukrwienie obszarów podwsierdziowych serca</t></is></c><c r="H262" s="2" t="inlineStr" /><c r="I262" s="2" t="inlineStr" /><c r="J262" s="2" t="inlineStr" /><c r="K262" s="2" t="inlineStr"><is><t>podlega istotnemu efektowi pierwszego przejścia przez wątrobę</t></is></c><c r="L262" s="2" t="inlineStr"><is><t>jest przeciwwskazany w naczynioskurczowej postaci choroby wieńcowej</t></is></c><c r="M262" s="2" t="inlineStr" /><c r="N262" s="2" t="inlineStr" /><c r="O262" s="2" t="inlineStr" /><c r="P262" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q262" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="263"><c r="A263" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B263" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C263" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D263" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E263" s="2" t="inlineStr"><is><t>W leczeniu owrzodzeń żylnych, jako leczenie uzupełniające, skuteczne są:</t></is></c><c r="F263" s="2" t="inlineStr"><is><t>mikronizowana diosmina</t></is></c><c r="G263" s="2" t="inlineStr"><is><t>opatrunki ze srebrem</t></is></c><c r="H263" s="2" t="inlineStr"><is><t>pentoksyfilina</t></is></c><c r="I263" s="2" t="inlineStr"><is><t>filgrastym</t></is></c><c r="J263" s="2" t="inlineStr" /><c r="K263" s="2" t="inlineStr" /><c r="L263" s="2" t="inlineStr" /><c r="M263" s="2" t="inlineStr" /><c r="N263" s="2" t="inlineStr" /><c r="O263" s="2" t="inlineStr" /><c r="P263" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q263" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="264"><c r="A264" s="2" t="inlineStr"><is><t>OTĘPIENIE</t></is></c><c r="B264" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C264" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D264" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E264" s="2" t="inlineStr"><is><t>Funkcje kognitywne u osób bez zaburzeń poznawczych poprawiają:</t></is></c><c r="F264" s="2" t="inlineStr"><is><t>piracetam</t></is></c><c r="G264" s="2" t="inlineStr"><is><t>winpocetyna</t></is></c><c r="H264" s="2" t="inlineStr"><is><t>nicergolina</t></is></c><c r="I264" s="2" t="inlineStr"><is><t>metylfenidat</t></is></c><c r="J264" s="2" t="inlineStr" /><c r="K264" s="2" t="inlineStr" /><c r="L264" s="2" t="inlineStr" /><c r="M264" s="2" t="inlineStr" /><c r="N264" s="2" t="inlineStr" /><c r="O264" s="2" t="inlineStr" /><c r="P264" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q264" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="265"><c r="A265" s="2" t="inlineStr"><is><t>LEKI PRZECIWPSYCHOTYCZNE</t></is></c><c r="B265" s="2" t="inlineStr"><is><t>Monitorowanie</t></is></c><c r="C265" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D265" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E265" s="2" t="inlineStr"><is><t>Klozapina:</t></is></c><c r="F265" s="2" t="inlineStr"><is><t>może być skuteczna w lekoopornej schizofrenii</t></is></c><c r="G265" s="2" t="inlineStr"><is><t>wymaga monitorowania morfologii krwi</t></is></c><c r="H265" s="2" t="inlineStr"><is><t>nasila objawy zespołu metabolicznego</t></is></c><c r="I265" s="2" t="inlineStr" /><c r="J265" s="2" t="inlineStr" /><c r="K265" s="2" t="inlineStr"><is><t>w małych dawkach zalecana jest do leczenia bezsenności</t></is></c><c r="L265" s="2" t="inlineStr" /><c r="M265" s="2" t="inlineStr" /><c r="N265" s="2" t="inlineStr" /><c r="O265" s="2" t="inlineStr" /><c r="P265" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q265" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="266"><c r="A266" s="2" t="inlineStr"><is><t>NARKOTYCZNE LEKI PRZECIWBÓLOWE</t></is></c><c r="B266" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C266" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D266" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E266" s="2" t="inlineStr"><is><t>W terapii substytucyjnej uzależnienia od opioidów celowe może być zastosowanie:</t></is></c><c r="F266" s="2" t="inlineStr"><is><t>buprenorfiny</t></is></c><c r="G266" s="2" t="inlineStr"><is><t>metadonu</t></is></c><c r="H266" s="2" t="inlineStr" /><c r="I266" s="2" t="inlineStr" /><c r="J266" s="2" t="inlineStr" /><c r="K266" s="2" t="inlineStr"><is><t>nalokson</t></is></c><c r="L266" s="2" t="inlineStr"><is><t>warenikliny</t></is></c><c r="M266" s="2" t="inlineStr" /><c r="N266" s="2" t="inlineStr" /><c r="O266" s="2" t="inlineStr" /><c r="P266" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q266" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="267"><c r="A267" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B267" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C267" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D267" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E267" s="2" t="inlineStr"><is><t>Silnie hepatotoksycznie działa:</t></is></c><c r="F267" s="2" t="inlineStr"><is><t>izoniazyd</t></is></c><c r="G267" s="2" t="inlineStr"><is><t>pirazynamid</t></is></c><c r="H267" s="2" t="inlineStr"><is><t>ryfampicyna</t></is></c><c r="I267" s="2" t="inlineStr" /><c r="J267" s="2" t="inlineStr" /><c r="K267" s="2" t="inlineStr"><is><t>streptomycyna</t></is></c><c r="L267" s="2" t="inlineStr" /><c r="M267" s="2" t="inlineStr" /><c r="N267" s="2" t="inlineStr" /><c r="O267" s="2" t="inlineStr" /><c r="P267" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q267" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="268"><c r="A268" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B268" s="2" t="inlineStr"><is><t>Ciąża</t></is></c><c r="C268" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D268" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E268" s="2" t="inlineStr"><is><t>Etambutol:</t></is></c><c r="F268" s="2" t="inlineStr"><is><t>zapobiega powstawaniu lekooporności na inne leki przeciwprątkowe</t></is></c><c r="G268" s="2" t="inlineStr"><is><t>może spowodować zaburzenia widzenia barwnego</t></is></c><c r="H268" s="2" t="inlineStr" /><c r="I268" s="2" t="inlineStr" /><c r="J268" s="2" t="inlineStr" /><c r="K268" s="2" t="inlineStr"><is><t>nie powinien być stosowany przez kobiety w ciąży</t></is></c><c r="L268" s="2" t="inlineStr"><is><t>nie jest stosowany w leczeniu gruźlicy pozapłucnej</t></is></c><c r="M268" s="2" t="inlineStr" /><c r="N268" s="2" t="inlineStr" /><c r="O268" s="2" t="inlineStr" /><c r="P268" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q268" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="269"><c r="A269" s="2" t="inlineStr"><is><t>LEKI NASENNE</t></is></c><c r="B269" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C269" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D269" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E269" s="2" t="inlineStr"><is><t>Wskaż prawdziwe połączenie lek – wskazanie:</t></is></c><c r="F269" s="2" t="inlineStr"><is><t>zolpidem - bezsenność</t></is></c><c r="G269" s="2" t="inlineStr"><is><t>rotygotyna – zespół niespokojnych nóg</t></is></c><c r="H269" s="2" t="inlineStr"><is><t>alprazolam - napady paniki</t></is></c><c r="I269" s="2" t="inlineStr"><is><t>fluoksetyna – zaburzenia kompulsywne</t></is></c><c r="J269" s="2" t="inlineStr" /><c r="K269" s="2" t="inlineStr" /><c r="L269" s="2" t="inlineStr" /><c r="M269" s="2" t="inlineStr" /><c r="N269" s="2" t="inlineStr" /><c r="O269" s="2" t="inlineStr" /><c r="P269" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q269" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="270"><c r="A270" s="2" t="inlineStr"><is><t>LEKI PRZECIWDEPRESYJNE</t></is></c><c r="B270" s="2" t="inlineStr"><is><t>Struktura chemiczna</t></is></c><c r="C270" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D270" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E270" s="2" t="inlineStr"><is><t>Jeśli leczymy depresję, to:</t></is></c><c r="F270" s="2" t="inlineStr"><is><t>u pacjentów z niewydolnością nerek lekiem pierwszego wyboru może być sertralina</t></is></c><c r="G270" s="2" t="inlineStr"><is><t>istnieje zwiększone ryzyko zachowań samobójczych u pacjentów w wieku poniżej 25 lat w okresie rozpoczynania leczenia przeciwdepresyjnego</t></is></c><c r="H270" s="2" t="inlineStr" /><c r="I270" s="2" t="inlineStr" /><c r="J270" s="2" t="inlineStr" /><c r="K270" s="2" t="inlineStr"><is><t>u osób starszych preferujemy trójpierścieniowe laki przeciwdepresyjne</t></is></c><c r="L270" s="2" t="inlineStr"><is><t>brak poprawy po 4 tygodniach leczenia sugeruje rozpoznanie depresji lekoopornej</t></is></c><c r="M270" s="2" t="inlineStr" /><c r="N270" s="2" t="inlineStr" /><c r="O270" s="2" t="inlineStr" /><c r="P270" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q270" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="271"><c r="A271" s="2" t="inlineStr"><is><t>UKŁAD ODDECHOWY</t></is></c><c r="B271" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C271" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D271" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E271" s="2" t="inlineStr"><is><t>Działanie przeciwkaszlowe wykazuje:</t></is></c><c r="F271" s="2" t="inlineStr"><is><t>dekstrometorfan</t></is></c><c r="G271" s="2" t="inlineStr"><is><t>kodeina</t></is></c><c r="H271" s="2" t="inlineStr" /><c r="I271" s="2" t="inlineStr" /><c r="J271" s="2" t="inlineStr" /><c r="K271" s="2" t="inlineStr"><is><t>loperamid</t></is></c><c r="L271" s="2" t="inlineStr"><is><t>prometazyna</t></is></c><c r="M271" s="2" t="inlineStr" /><c r="N271" s="2" t="inlineStr" /><c r="O271" s="2" t="inlineStr" /><c r="P271" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q271" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="272"><c r="A272" s="2" t="inlineStr"><is><t>NIEWYDOLNOŚĆ SERCA</t></is></c><c r="B272" s="2" t="inlineStr"><is><t>Antidotum</t></is></c><c r="C272" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D272" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E272" s="2" t="inlineStr"><is><t>Atropina jest stosowana w przypadku zatrucia:</t></is></c><c r="F272" s="2" t="inlineStr"><is><t>grzybami strzępiakami i lejkówkami</t></is></c><c r="G272" s="2" t="inlineStr"><is><t>glikozydami naparstnicy</t></is></c><c r="H272" s="2" t="inlineStr"><is><t>związkami fosforoorganicznymi</t></is></c><c r="I272" s="2" t="inlineStr" /><c r="J272" s="2" t="inlineStr" /><c r="K272" s="2" t="inlineStr"><is><t>pokrzykiem wilczą jagodą</t></is></c><c r="L272" s="2" t="inlineStr" /><c r="M272" s="2" t="inlineStr" /><c r="N272" s="2" t="inlineStr" /><c r="O272" s="2" t="inlineStr" /><c r="P272" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q272" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="273"><c r="A273" s="2" t="inlineStr"><is><t>TARCZYCA</t></is></c><c r="B273" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C273" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D273" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E273" s="2" t="inlineStr"><is><t>W porównaniu do osób dorosłych w populacji pediatrycznej:</t></is></c><c r="F273" s="2" t="inlineStr"><is><t>zmieniona reakcja na leki jest uwarunkowana przede wszystkim zmianami w farmakokinetyce leków</t></is></c><c r="G273" s="2" t="inlineStr"><is><t>do osiągnięcia stężenia terapeutycznego leku mogą wystarczyć w pierwszym kwartale życia (w przeliczeniu na masę ciała) mniejsze dawki leku</t></is></c><c r="H273" s="2" t="inlineStr"><is><t>w pierwszym półroczu życia leki wydalane przez nerki są eliminowane wolniej, a ich biologiczny okres półtrwania jest dłuższy</t></is></c><c r="I273" s="2" t="inlineStr"><is><t>w pierwszym roku życia frakcja wolna leku może być większa</t></is></c><c r="J273" s="2" t="inlineStr" /><c r="K273" s="2" t="inlineStr" /><c r="L273" s="2" t="inlineStr" /><c r="M273" s="2" t="inlineStr" /><c r="N273" s="2" t="inlineStr" /><c r="O273" s="2" t="inlineStr" /><c r="P273" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q273" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="274"><c r="A274" s="2" t="inlineStr"><is><t>NIEWYDOLNOŚĆ SERCA</t></is></c><c r="B274" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C274" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D274" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E274" s="2" t="inlineStr"><is><t>Inhibitory fosfodiesterazy typu 5:</t></is></c><c r="F274" s="2" t="inlineStr"><is><t>są skuteczne w leczeniu zaburzeń erekcji</t></is></c><c r="G274" s="2" t="inlineStr"><is><t>nie mogą być przyjmowane jednocześnie z azotanami z uwagi na duże ryzyko wystąpienia ciężkiej, niekorygowalnej hipotonii</t></is></c><c r="H274" s="2" t="inlineStr" /><c r="I274" s="2" t="inlineStr" /><c r="J274" s="2" t="inlineStr" /><c r="K274" s="2" t="inlineStr"><is><t>wydłużają dystans marszu bez bólu u pacjentów z chromaniem przestankowym</t></is></c><c r="L274" s="2" t="inlineStr"><is><t>mają działanie inotropowe dodatnie</t></is></c><c r="M274" s="2" t="inlineStr" /><c r="N274" s="2" t="inlineStr" /><c r="O274" s="2" t="inlineStr" /><c r="P274" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q274" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="275"><c r="A275" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B275" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C275" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D275" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E275" s="2" t="inlineStr"><is><t>Wpływ rozkurczający na mięśniówkę przewodu pokarmowego ma:</t></is></c><c r="F275" s="2" t="inlineStr"><is><t>drotaweryna</t></is></c><c r="G275" s="2" t="inlineStr" /><c r="H275" s="2" t="inlineStr" /><c r="I275" s="2" t="inlineStr" /><c r="J275" s="2" t="inlineStr" /><c r="K275" s="2" t="inlineStr"><is><t>itopryd</t></is></c><c r="L275" s="2" t="inlineStr"><is><t>mesalazyna</t></is></c><c r="M275" s="2" t="inlineStr"><is><t>ryfaksymina</t></is></c><c r="N275" s="2" t="inlineStr" /><c r="O275" s="2" t="inlineStr" /><c r="P275" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q275" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="276"><c r="A276" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B276" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C276" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D276" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E276" s="2" t="inlineStr"><is><t>Lanzoprazol stosowany przewlekle powoduje:</t></is></c><c r="F276" s="2" t="inlineStr"><is><t>wzrost ryzyka zakażenia Clostridum difficile</t></is></c><c r="G276" s="2" t="inlineStr"><is><t>wzrost ryzyka infekcji dróg oddechowych</t></is></c><c r="H276" s="2" t="inlineStr"><is><t>zmniejszenie wchłaniania wapnia z przewodu pokarmowego</t></is></c><c r="I276" s="2" t="inlineStr"><is><t>zmniejszenie przekształcania klopidogrelu do aktywnych pochodnych</t></is></c><c r="J276" s="2" t="inlineStr" /><c r="K276" s="2" t="inlineStr" /><c r="L276" s="2" t="inlineStr" /><c r="M276" s="2" t="inlineStr" /><c r="N276" s="2" t="inlineStr" /><c r="O276" s="2" t="inlineStr" /><c r="P276" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q276" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="277"><c r="A277" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B277" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C277" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D277" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E277" s="2" t="inlineStr"><is><t>Sposób eradykacji Helicobacter pylori zalecany w Polsce to:</t></is></c><c r="F277" s="2" t="inlineStr"><is><t>podwójna dawka IPP, metronidazol, tetracyklina, cytrynian bizmutu przez 14 dni</t></is></c><c r="G277" s="2" t="inlineStr" /><c r="H277" s="2" t="inlineStr" /><c r="I277" s="2" t="inlineStr" /><c r="J277" s="2" t="inlineStr" /><c r="K277" s="2" t="inlineStr"><is><t>terapia sekwencyjna przez 10 dni - podwójna dawka IPP (inhibitora pompy protonowej) z amoksycyliną (dni 1-5), a następnie z klarytromycyną i metronidazolem (dni 6-10)</t></is></c><c r="L277" s="2" t="inlineStr"><is><t>podwójna dawka IPP, amoksycylina, klarytromycyna przez 10 dni</t></is></c><c r="M277" s="2" t="inlineStr"><is><t>podwójna dawka IPP, amoksycylina, klarytromycyna, metronidazol przez 14 dni</t></is></c><c r="N277" s="2" t="inlineStr" /><c r="O277" s="2" t="inlineStr" /><c r="P277" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q277" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="278"><c r="A278" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B278" s="2" t="inlineStr"><is><t>Ciąża</t></is></c><c r="C278" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D278" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E278" s="2" t="inlineStr"><is><t>Udokumentowane działanie teratogenne wykazuje:</t></is></c><c r="F278" s="2" t="inlineStr"><is><t>trimetoprim-sulfametoksazol</t></is></c><c r="G278" s="2" t="inlineStr"><is><t>warfaryna</t></is></c><c r="H278" s="2" t="inlineStr"><is><t>kwas walproinowy</t></is></c><c r="I278" s="2" t="inlineStr"><is><t>gentamycyna</t></is></c><c r="J278" s="2" t="inlineStr" /><c r="K278" s="2" t="inlineStr" /><c r="L278" s="2" t="inlineStr" /><c r="M278" s="2" t="inlineStr" /><c r="N278" s="2" t="inlineStr" /><c r="O278" s="2" t="inlineStr" /><c r="P278" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q278" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="279"><c r="A279" s="2" t="inlineStr"><is><t>LEKI PRZECIWDEPRESYJNE</t></is></c><c r="B279" s="2" t="inlineStr"><is><t>Antidotum</t></is></c><c r="C279" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D279" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E279" s="2" t="inlineStr"><is><t>Wskaż prawdziwe połączenie lek – odtrutka:</t></is></c><c r="F279" s="2" t="inlineStr"><is><t>oksazepam - flumazenil</t></is></c><c r="G279" s="2" t="inlineStr"><is><t>trójpierścieniowe leki przeciwdepresyjne – wodorowęglan sodu</t></is></c><c r="H279" s="2" t="inlineStr"><is><t>żelazo - deferoksamina</t></is></c><c r="I279" s="2" t="inlineStr"><is><t>warfaryna - fitomenadion</t></is></c><c r="J279" s="2" t="inlineStr" /><c r="K279" s="2" t="inlineStr" /><c r="L279" s="2" t="inlineStr" /><c r="M279" s="2" t="inlineStr" /><c r="N279" s="2" t="inlineStr" /><c r="O279" s="2" t="inlineStr" /><c r="P279" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q279" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="280"><c r="A280" s="2" t="inlineStr"><is><t>CHOROBA NIEDOKRWIENNA SERCA</t></is></c><c r="B280" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C280" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D280" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E280" s="2" t="inlineStr"><is><t>Wazodylatacyjny mechanizm działania azotanów zależy od:</t></is></c><c r="F280" s="2" t="inlineStr"><is><t>wzrostu stężenia cGMP</t></is></c><c r="G280" s="2" t="inlineStr"><is><t>defosforylacji łańcuchów lekkich miozyny</t></is></c><c r="H280" s="2" t="inlineStr" /><c r="I280" s="2" t="inlineStr" /><c r="J280" s="2" t="inlineStr" /><c r="K280" s="2" t="inlineStr"><is><t>hamowania aktywności cyklazy guanylowej</t></is></c><c r="L280" s="2" t="inlineStr"><is><t>pobudzania kanałów potasowych</t></is></c><c r="M280" s="2" t="inlineStr" /><c r="N280" s="2" t="inlineStr" /><c r="O280" s="2" t="inlineStr" /><c r="P280" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q280" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="281"><c r="A281" s="2" t="inlineStr"><is><t>ZABURZENIA RYTMU SERCA</t></is></c><c r="B281" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C281" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D281" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E281" s="2" t="inlineStr"><is><t>Bradykardia może wystąpić po zastosowaniu:</t></is></c><c r="F281" s="2" t="inlineStr"><is><t>werapamilu</t></is></c><c r="G281" s="2" t="inlineStr" /><c r="H281" s="2" t="inlineStr" /><c r="I281" s="2" t="inlineStr" /><c r="J281" s="2" t="inlineStr" /><c r="K281" s="2" t="inlineStr"><is><t>nifedypiny</t></is></c><c r="L281" s="2" t="inlineStr"><is><t>trimetazydyny</t></is></c><c r="M281" s="2" t="inlineStr"><is><t>spironolaktonu</t></is></c><c r="N281" s="2" t="inlineStr" /><c r="O281" s="2" t="inlineStr" /><c r="P281" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q281" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="282"><c r="A282" s="2" t="inlineStr"><is><t>UKŁAD WSPÓŁCZULNY</t></is></c><c r="B282" s="2" t="inlineStr"><is><t>Farmakokinetyka</t></is></c><c r="C282" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D282" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E282" s="2" t="inlineStr"><is><t>Teoretyczną przesłanką stosowania beta-adrenolityków w chorobie wieńcowej serca jest:</t></is></c><c r="F282" s="2" t="inlineStr"><is><t>usprawnienie metabolizmu kardiomiocytów</t></is></c><c r="G282" s="2" t="inlineStr"><is><t>zapobieganie proarytmicznemu działaniu katecholamin</t></is></c><c r="H282" s="2" t="inlineStr"><is><t>poprawa perfuzji warstwy podwsierdziowej</t></is></c><c r="I282" s="2" t="inlineStr"><is><t>korzystny wpływ hemodynamiczny zmniejszający zapotrzebowanie mięśnia sercowego na tlen</t></is></c><c r="J282" s="2" t="inlineStr" /><c r="K282" s="2" t="inlineStr" /><c r="L282" s="2" t="inlineStr" /><c r="M282" s="2" t="inlineStr" /><c r="N282" s="2" t="inlineStr" /><c r="O282" s="2" t="inlineStr" /><c r="P282" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q282" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="283"><c r="A283" s="2" t="inlineStr"><is><t>NIEWYDOLNOŚĆ SERCA</t></is></c><c r="B283" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C283" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D283" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E283" s="2" t="inlineStr"><is><t>Digoksyna:</t></is></c><c r="F283" s="2" t="inlineStr"><is><t>aktywuje układ przywspółczulny</t></is></c><c r="G283" s="2" t="inlineStr"><is><t>wywiera arytmie i zaburzenia przewodzenia</t></is></c><c r="H283" s="2" t="inlineStr"><is><t>jest stosowana w celu kontroli częstotliwości rytmu komór u chorych z migotaniem przedsionków</t></is></c><c r="I283" s="2" t="inlineStr"><is><t>w zatruciu można zastosować fragmenty Fab przeciwciał wiążących</t></is></c><c r="J283" s="2" t="inlineStr" /><c r="K283" s="2" t="inlineStr" /><c r="L283" s="2" t="inlineStr" /><c r="M283" s="2" t="inlineStr" /><c r="N283" s="2" t="inlineStr" /><c r="O283" s="2" t="inlineStr" /><c r="P283" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q283" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="284"><c r="A284" s="2" t="inlineStr"><is><t>NADCIŚNIENIE TĘTNICZE</t></is></c><c r="B284" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C284" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D284" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E284" s="2" t="inlineStr"><is><t>Wskaż prawdziwe połączenie lek – wskazanie:</t></is></c><c r="F284" s="2" t="inlineStr"><is><t>ranolazyna - stabilna choroba niedokrwienna serca</t></is></c><c r="G284" s="2" t="inlineStr" /><c r="H284" s="2" t="inlineStr" /><c r="I284" s="2" t="inlineStr" /><c r="J284" s="2" t="inlineStr" /><c r="K284" s="2" t="inlineStr"><is><t>cilostazol - ostra niewydolność mięśnia sercowego</t></is></c><c r="L284" s="2" t="inlineStr"><is><t>milrynon - migotanie przedsionków</t></is></c><c r="M284" s="2" t="inlineStr"><is><t>riocyguat - nadciśnienie tętnicze</t></is></c><c r="N284" s="2" t="inlineStr" /><c r="O284" s="2" t="inlineStr" /><c r="P284" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q284" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="285"><c r="A285" s="2" t="inlineStr"><is><t>NADCIŚNIENIE TĘTNICZE</t></is></c><c r="B285" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C285" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D285" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E285" s="2" t="inlineStr"><is><t>Do leków stosowanych w leczeniu nadciśnienia tętniczego ze wskazań naglących (RR&gt;180/120 mmHg z powikłaniami narządowymi) należą:</t></is></c><c r="F285" s="2" t="inlineStr"><is><t>esmolol</t></is></c><c r="G285" s="2" t="inlineStr"><is><t>urapidyl</t></is></c><c r="H285" s="2" t="inlineStr" /><c r="I285" s="2" t="inlineStr" /><c r="J285" s="2" t="inlineStr" /><c r="K285" s="2" t="inlineStr"><is><t>doksazosyna</t></is></c><c r="L285" s="2" t="inlineStr"><is><t>kaptopryl</t></is></c><c r="M285" s="2" t="inlineStr" /><c r="N285" s="2" t="inlineStr" /><c r="O285" s="2" t="inlineStr" /><c r="P285" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q285" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="286"><c r="A286" s="2" t="inlineStr"><is><t>NIEWYDOLNOŚĆ SERCA</t></is></c><c r="B286" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C286" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D286" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E286" s="2" t="inlineStr"><is><t>Do leków zmniejszających ryzyko zgonu sercowo-naczyniowego w przebiegu skurczowej niewydolności serca należy:</t></is></c><c r="F286" s="2" t="inlineStr"><is><t>bisoprolol</t></is></c><c r="G286" s="2" t="inlineStr"><is><t>eplerenon</t></is></c><c r="H286" s="2" t="inlineStr"><is><t>sakubitril w skojarzeniu z walsartanem</t></is></c><c r="I286" s="2" t="inlineStr" /><c r="J286" s="2" t="inlineStr" /><c r="K286" s="2" t="inlineStr"><is><t>digoksyna</t></is></c><c r="L286" s="2" t="inlineStr" /><c r="M286" s="2" t="inlineStr" /><c r="N286" s="2" t="inlineStr" /><c r="O286" s="2" t="inlineStr" /><c r="P286" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q286" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="287"><c r="A287" s="2" t="inlineStr"><is><t>CHOROBA NIEDOKRWIENNA SERCA</t></is></c><c r="B287" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C287" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D287" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E287" s="2" t="inlineStr"><is><t>U 67-letniej kobiety z dyskomfortem zamostkowym występującym przy wchodzeniu na 3 piętro i ustępującym w spoczynku, z blokiem przedsionkowo-komorowym II stopnia typu Mobitza w badaniu met. Holtera należy zastosować:</t></is></c><c r="F287" s="2" t="inlineStr"><is><t>rosuwastatynę</t></is></c><c r="G287" s="2" t="inlineStr"><is><t>kwas acetylosalicylowy</t></is></c><c r="H287" s="2" t="inlineStr"><is><t>triazotan glicerolu w aerozolu</t></is></c><c r="I287" s="2" t="inlineStr" /><c r="J287" s="2" t="inlineStr" /><c r="K287" s="2" t="inlineStr"><is><t>nebiwolol</t></is></c><c r="L287" s="2" t="inlineStr" /><c r="M287" s="2" t="inlineStr" /><c r="N287" s="2" t="inlineStr" /><c r="O287" s="2" t="inlineStr" /><c r="P287" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q287" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="288"><c r="A288" s="2" t="inlineStr"><is><t>FARMAKOKINETYKA</t></is></c><c r="B288" s="2" t="inlineStr"><is><t>Monitorowanie</t></is></c><c r="C288" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D288" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E288" s="2" t="inlineStr"><is><t>Wskaż prawidłowe zasady prowadzenia terapii monitorowanej stężeniami leku:</t></is></c><c r="F288" s="2" t="inlineStr"><is><t>oznaczenia należy wykonywać po osiągnięciu przez lek stanu stacjonarnego</t></is></c><c r="G288" s="2" t="inlineStr"><is><t>pomiary należy wykonywać w momencie Cmin, czyli tuż przed podaniem kolejnej, zwykle porannej dawki leku</t></is></c><c r="H288" s="2" t="inlineStr"><is><t>w większości przypadków wystarczy oznaczenie całkowitego stężenia leku</t></is></c><c r="I288" s="2" t="inlineStr"><is><t>w przypadku leków o kinetyce liniowej można wyliczyć modyfikację dawki na podstawie pomiarów aktualnych i znajomości docelowych stężeń leku we krwi</t></is></c><c r="J288" s="2" t="inlineStr" /><c r="K288" s="2" t="inlineStr" /><c r="L288" s="2" t="inlineStr" /><c r="M288" s="2" t="inlineStr" /><c r="N288" s="2" t="inlineStr" /><c r="O288" s="2" t="inlineStr" /><c r="P288" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q288" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="289"><c r="A289" s="2" t="inlineStr"><is><t>ZABURZENIA RYTMU SERCA</t></is></c><c r="B289" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C289" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D289" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E289" s="2" t="inlineStr"><is><t>Które stwierdzenie jest prawdziwe:</t></is></c><c r="F289" s="2" t="inlineStr"><is><t>propafenon nie jest zalecany u pacjentów z chorobą wieńcową</t></is></c><c r="G289" s="2" t="inlineStr"><is><t>amiodaron można stosować w celu zwiększenia skuteczności kardiowersji elektrycznej</t></is></c><c r="H289" s="2" t="inlineStr" /><c r="I289" s="2" t="inlineStr" /><c r="J289" s="2" t="inlineStr" /><c r="K289" s="2" t="inlineStr"><is><t>dronedaron zmniejsza umieralność u pacjentów z niewydolnością serca w klasie III/IV NYHA</t></is></c><c r="L289" s="2" t="inlineStr"><is><t>beta-adrenolityki stosuje się w celu kardiowersji farmakologicznej</t></is></c><c r="M289" s="2" t="inlineStr" /><c r="N289" s="2" t="inlineStr" /><c r="O289" s="2" t="inlineStr" /><c r="P289" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q289" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="290"><c r="A290" s="2" t="inlineStr"><is><t>LEKI HIPOLIPEMIZUJĄCE</t></is></c><c r="B290" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C290" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D290" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E290" s="2" t="inlineStr"><is><t>W celu oceny działań niepożądanych w trakcie leczenia atorwastatyną należy sprawdzić:</t></is></c><c r="F290" s="2" t="inlineStr"><is><t>aktywność kinazy fosfokreatynowej (CPK)</t></is></c><c r="G290" s="2" t="inlineStr"><is><t>aktywność enzymów wątrobowych (AST/ALT)</t></is></c><c r="H290" s="2" t="inlineStr" /><c r="I290" s="2" t="inlineStr" /><c r="J290" s="2" t="inlineStr" /><c r="K290" s="2" t="inlineStr"><is><t>stężenie glukozy</t></is></c><c r="L290" s="2" t="inlineStr"><is><t>stężenie peptydu natriuretycznego typu B (BNP)</t></is></c><c r="M290" s="2" t="inlineStr" /><c r="N290" s="2" t="inlineStr" /><c r="O290" s="2" t="inlineStr" /><c r="P290" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q290" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="291"><c r="A291" s="2" t="inlineStr"><is><t>LEKI MOCZOPĘDNE</t></is></c><c r="B291" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C291" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D291" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E291" s="2" t="inlineStr"><is><t>W leczeniu zagrażającej życiu hiperkaliemii można zastosować:</t></is></c><c r="F291" s="2" t="inlineStr"><is><t>10 ml 10% chlorku lub glukonianu wapnia i.v. w 10 min bolusie</t></is></c><c r="G291" s="2" t="inlineStr"><is><t>500 ml 20% glukozy z 20 j.m. insuliny krótkodziałającej i.v. przez 1-2 godziny</t></is></c><c r="H291" s="2" t="inlineStr"><is><t>hemodializę</t></is></c><c r="I291" s="2" t="inlineStr" /><c r="J291" s="2" t="inlineStr" /><c r="K291" s="2" t="inlineStr"><is><t>diuretyki pętlowe i.v</t></is></c><c r="L291" s="2" t="inlineStr" /><c r="M291" s="2" t="inlineStr" /><c r="N291" s="2" t="inlineStr" /><c r="O291" s="2" t="inlineStr" /><c r="P291" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q291" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="292"><c r="A292" s="2" t="inlineStr"><is><t>UKŁAD WSPÓŁCZULNY</t></is></c><c r="B292" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C292" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D292" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E292" s="2" t="inlineStr"><is><t>Powinowactwo do receptorów alfa-1-adrenergicznych wykazuje:</t></is></c><c r="F292" s="2" t="inlineStr"><is><t>doksazosyna</t></is></c><c r="G292" s="2" t="inlineStr"><is><t>labetalol</t></is></c><c r="H292" s="2" t="inlineStr"><is><t>adrenalina</t></is></c><c r="I292" s="2" t="inlineStr"><is><t>karwedilol</t></is></c><c r="J292" s="2" t="inlineStr" /><c r="K292" s="2" t="inlineStr" /><c r="L292" s="2" t="inlineStr" /><c r="M292" s="2" t="inlineStr" /><c r="N292" s="2" t="inlineStr" /><c r="O292" s="2" t="inlineStr" /><c r="P292" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q292" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="293"><c r="A293" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B293" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C293" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D293" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E293" s="2" t="inlineStr"><is><t>Apiksaban jest substratem dla P-gp. Co to oznacza?</t></is></c><c r="F293" s="2" t="inlineStr"><is><t>silne induktory P-gp o działaniu ogólnoustrojowym zmniejszają skuteczność apiksabanu</t></is></c><c r="G293" s="2" t="inlineStr" /><c r="H293" s="2" t="inlineStr" /><c r="I293" s="2" t="inlineStr" /><c r="J293" s="2" t="inlineStr" /><c r="K293" s="2" t="inlineStr"><is><t>lek jest wchłaniany z p. pokarmowego z wykorzystaniem transportu ułatwionego</t></is></c><c r="L293" s="2" t="inlineStr"><is><t>jest metabolizowany w wątrobie i nie powinien być stosowany u osób z 10- 15 pkt wg skali Childa-Pugha</t></is></c><c r="M293" s="2" t="inlineStr"><is><t>jest prawdopodobne, że hemodializa byłaby skutecznym środkiem zaradczym podczas przedawkowania apiksabanu</t></is></c><c r="N293" s="2" t="inlineStr" /><c r="O293" s="2" t="inlineStr" /><c r="P293" s="2" t="inlineStr"><is><t>EGZ 2017 I termin</t></is></c><c r="Q293" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="294"><c r="A294" s="2" t="inlineStr"><is><t>FARMAKOKINETYKA</t></is></c><c r="B294" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C294" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D294" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E294" s="2" t="inlineStr"><is><t>Opis rzedowości procesu:</t></is></c><c r="F294" s="2" t="inlineStr"><is><t>Dotyczy wszystkich etapów farmakokinetycznych</t></is></c><c r="G294" s="2" t="inlineStr"><is><t>Definiuje dynamiki zmian w układzie stężenie-czas w zależności od budowy chemicznej leku</t></is></c><c r="H294" s="2" t="inlineStr"><is><t>Może się zmienić dla leku w trakcie pojedynczej ekspozycji</t></is></c><c r="I294" s="2" t="inlineStr"><is><t>Powstaje ostatecznie w badaniach w medelu zwierzęcym</t></is></c><c r="J294" s="2" t="inlineStr" /><c r="K294" s="2" t="inlineStr" /><c r="L294" s="2" t="inlineStr" /><c r="M294" s="2" t="inlineStr" /><c r="N294" s="2" t="inlineStr" /><c r="O294" s="2" t="inlineStr" /><c r="P294" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q294" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="295"><c r="A295" s="2" t="inlineStr"><is><t>FARMAKOKINETYKA</t></is></c><c r="B295" s="2" t="inlineStr"><is><t>Farmakokinetyka</t></is></c><c r="C295" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D295" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E295" s="2" t="inlineStr"><is><t>Jeśli proces eliminacji leku przez nerki jest opisany kinetyką zerowego rzędu to:</t></is></c><c r="F295" s="2" t="inlineStr"><is><t>Procesy wchłaniania i dystrybucji również opisane są kinetyką zerowego rzędu</t></is></c><c r="G295" s="2" t="inlineStr"><is><t>Szybkość procesu eliminacji nerkowej jest stała</t></is></c><c r="H295" s="2" t="inlineStr" /><c r="I295" s="2" t="inlineStr" /><c r="J295" s="2" t="inlineStr" /><c r="K295" s="2" t="inlineStr"><is><t>Stężenie leku w moczu jest odwrotnie proporocjonalne do stężenia leku we krwi</t></is></c><c r="L295" s="2" t="inlineStr"><is><t>Klirens nerkowy leku jest wprost proporcjonalny do stężeniu leku</t></is></c><c r="M295" s="2" t="inlineStr" /><c r="N295" s="2" t="inlineStr" /><c r="O295" s="2" t="inlineStr" /><c r="P295" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q295" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="296"><c r="A296" s="2" t="inlineStr"><is><t>FARMAKOKINETYKA</t></is></c><c r="B296" s="2" t="inlineStr"><is><t>Farmakokinetyka</t></is></c><c r="C296" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D296" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E296" s="2" t="inlineStr"><is><t>Wskaż właściwie zdefiniowane parametry farmakokinetyczne</t></is></c><c r="F296" s="2" t="inlineStr"><is><t>AUC – pole pod krzywą zmian stężenia leku we krwi w czasie</t></is></c><c r="G296" s="2" t="inlineStr" /><c r="H296" s="2" t="inlineStr" /><c r="I296" s="2" t="inlineStr" /><c r="J296" s="2" t="inlineStr" /><c r="K296" s="2" t="inlineStr"><is><t>T1/2 – czas po którym stężenie leku we krwi jest równe stężeniu leku gdyby biodostępność wynosiła 50%</t></is></c><c r="L296" s="2" t="inlineStr"><is><t>Tmax – maksymalny czas w którym stężeniu leku we krwi jest wykrywalne</t></is></c><c r="M296" s="2" t="inlineStr"><is><t>Cmax – stężenie leku we krwi osiągane po podaniu dożylnym</t></is></c><c r="N296" s="2" t="inlineStr" /><c r="O296" s="2" t="inlineStr" /><c r="P296" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q296" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="297"><c r="A297" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B297" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C297" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D297" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E297" s="2" t="inlineStr"><is><t>Do zwiększenia przepuszczalności bariery krew mózg dla leków dochodzi w przypadku</t></is></c><c r="F297" s="2" t="inlineStr"><is><t>Zapalenia opon mózgowo-rdzeniowych</t></is></c><c r="G297" s="2" t="inlineStr"><is><t>Niedokrwienia mózgu</t></is></c><c r="H297" s="2" t="inlineStr" /><c r="I297" s="2" t="inlineStr" /><c r="J297" s="2" t="inlineStr" /><c r="K297" s="2" t="inlineStr"><is><t>Chorób neurodegeneracyjnych</t></is></c><c r="L297" s="2" t="inlineStr"><is><t>Chorób autoimmunologicznych</t></is></c><c r="M297" s="2" t="inlineStr"><is><t>Wskaż prawidłowe połączenie antybiotyk – mechanizm działania</t></is></c><c r="N297" s="2" t="inlineStr" /><c r="O297" s="2" t="inlineStr" /><c r="P297" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q297" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="298"><c r="A298" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B298" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C298" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D298" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E298" s="2" t="inlineStr"><is><t>Azytromycyna</t></is></c><c r="F298" s="2" t="inlineStr"><is><t>Kumuluje się w makrofagach</t></is></c><c r="G298" s="2" t="inlineStr"><is><t>Ma długi okres półtrwania</t></is></c><c r="H298" s="2" t="inlineStr" /><c r="I298" s="2" t="inlineStr" /><c r="J298" s="2" t="inlineStr" /><c r="K298" s="2" t="inlineStr"><is><t>Słabo wchłania się z PP</t></is></c><c r="L298" s="2" t="inlineStr"><is><t>Hamuje enzymy cytochromu P-450</t></is></c><c r="M298" s="2" t="inlineStr" /><c r="N298" s="2" t="inlineStr" /><c r="O298" s="2" t="inlineStr" /><c r="P298" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q298" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="299"><c r="A299" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B299" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C299" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D299" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E299" s="2" t="inlineStr"><is><t>Działanie ototoksyczne wskazują</t></is></c><c r="F299" s="2" t="inlineStr"><is><t>Salicylany</t></is></c><c r="G299" s="2" t="inlineStr"><is><t>Aminoglikozydy</t></is></c><c r="H299" s="2" t="inlineStr" /><c r="I299" s="2" t="inlineStr" /><c r="J299" s="2" t="inlineStr" /><c r="K299" s="2" t="inlineStr"><is><t>Glitazony</t></is></c><c r="L299" s="2" t="inlineStr"><is><t>Penicyliny</t></is></c><c r="M299" s="2" t="inlineStr" /><c r="N299" s="2" t="inlineStr" /><c r="O299" s="2" t="inlineStr" /><c r="P299" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q299" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="300"><c r="A300" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B300" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C300" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D300" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E300" s="2" t="inlineStr"><is><t>W leczeniu boreliozy można użyć</t></is></c><c r="F300" s="2" t="inlineStr"><is><t>Amoksycyliny</t></is></c><c r="G300" s="2" t="inlineStr"><is><t>Cefuroksymu aksetylu</t></is></c><c r="H300" s="2" t="inlineStr"><is><t>Azytromycyny</t></is></c><c r="I300" s="2" t="inlineStr"><is><t>Doksycykliny</t></is></c><c r="J300" s="2" t="inlineStr" /><c r="K300" s="2" t="inlineStr" /><c r="L300" s="2" t="inlineStr" /><c r="M300" s="2" t="inlineStr" /><c r="N300" s="2" t="inlineStr" /><c r="O300" s="2" t="inlineStr" /><c r="P300" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q300" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="301"><c r="A301" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B301" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C301" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D301" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E301" s="2" t="inlineStr"><is><t>Syntezę ściany komórkowej hamuje</t></is></c><c r="F301" s="2" t="inlineStr"><is><t>Imipenem</t></is></c><c r="G301" s="2" t="inlineStr"><is><t>Wankomycyna</t></is></c><c r="H301" s="2" t="inlineStr" /><c r="I301" s="2" t="inlineStr" /><c r="J301" s="2" t="inlineStr" /><c r="K301" s="2" t="inlineStr"><is><t>Erytromycyna</t></is></c><c r="L301" s="2" t="inlineStr"><is><t>Mupirocyna</t></is></c><c r="M301" s="2" t="inlineStr" /><c r="N301" s="2" t="inlineStr" /><c r="O301" s="2" t="inlineStr" /><c r="P301" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q301" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="302"><c r="A302" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B302" s="2" t="inlineStr"><is><t>Interakcje</t></is></c><c r="C302" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D302" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E302" s="2" t="inlineStr"><is><t>Reakcje disulfiramową może spowodować spożycie alkoholu podczas terapii</t></is></c><c r="F302" s="2" t="inlineStr"><is><t>Metronidazol</t></is></c><c r="G302" s="2" t="inlineStr" /><c r="H302" s="2" t="inlineStr" /><c r="I302" s="2" t="inlineStr" /><c r="J302" s="2" t="inlineStr" /><c r="K302" s="2" t="inlineStr"><is><t>Klindamycyną</t></is></c><c r="L302" s="2" t="inlineStr"><is><t>Piperalicyna</t></is></c><c r="M302" s="2" t="inlineStr"><is><t>Cyprofloksacyna</t></is></c><c r="N302" s="2" t="inlineStr" /><c r="O302" s="2" t="inlineStr" /><c r="P302" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q302" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="303"><c r="A303" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B303" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C303" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D303" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E303" s="2" t="inlineStr"><is><t>W zakażeniach Mycoplasama pneumoniae można zastosować</t></is></c><c r="F303" s="2" t="inlineStr"><is><t>Doksycykline</t></is></c><c r="G303" s="2" t="inlineStr"><is><t>Klarytromycyne</t></is></c><c r="H303" s="2" t="inlineStr" /><c r="I303" s="2" t="inlineStr" /><c r="J303" s="2" t="inlineStr" /><c r="K303" s="2" t="inlineStr"><is><t>Amoksycyline</t></is></c><c r="L303" s="2" t="inlineStr"><is><t>Ceftriakson</t></is></c><c r="M303" s="2" t="inlineStr" /><c r="N303" s="2" t="inlineStr" /><c r="O303" s="2" t="inlineStr" /><c r="P303" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q303" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="304"><c r="A304" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B304" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C304" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D304" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E304" s="2" t="inlineStr"><is><t>Makrolidy mogą być skuteczne w zakażeniach</t></is></c><c r="F304" s="2" t="inlineStr"><is><t>H. influenza</t></is></c><c r="G304" s="2" t="inlineStr"><is><t>L. pneumophila</t></is></c><c r="H304" s="2" t="inlineStr"><is><t>H. pylori</t></is></c><c r="I304" s="2" t="inlineStr"><is><t>T. gondi</t></is></c><c r="J304" s="2" t="inlineStr" /><c r="K304" s="2" t="inlineStr" /><c r="L304" s="2" t="inlineStr" /><c r="M304" s="2" t="inlineStr" /><c r="N304" s="2" t="inlineStr" /><c r="O304" s="2" t="inlineStr" /><c r="P304" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q304" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="305"><c r="A305" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B305" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C305" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D305" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E305" s="2" t="inlineStr"><is><t>W zakazeniu Clostridium diff. skuteczne sa:</t></is></c><c r="F305" s="2" t="inlineStr"><is><t>Metronidazol</t></is></c><c r="G305" s="2" t="inlineStr"><is><t>Wankomycyna</t></is></c><c r="H305" s="2" t="inlineStr" /><c r="I305" s="2" t="inlineStr" /><c r="J305" s="2" t="inlineStr" /><c r="K305" s="2" t="inlineStr"><is><t>Amoksycylina</t></is></c><c r="L305" s="2" t="inlineStr"><is><t>Klindamycyna</t></is></c><c r="M305" s="2" t="inlineStr" /><c r="N305" s="2" t="inlineStr" /><c r="O305" s="2" t="inlineStr" /><c r="P305" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q305" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="306"><c r="A306" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B306" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C306" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D306" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E306" s="2" t="inlineStr"><is><t>Na MRSA działa</t></is></c><c r="F306" s="2" t="inlineStr"><is><t>Wankomycyna</t></is></c><c r="G306" s="2" t="inlineStr"><is><t>Linezolid</t></is></c><c r="H306" s="2" t="inlineStr" /><c r="I306" s="2" t="inlineStr" /><c r="J306" s="2" t="inlineStr" /><c r="K306" s="2" t="inlineStr"><is><t>Cefazolina</t></is></c><c r="L306" s="2" t="inlineStr"><is><t>Meropenem</t></is></c><c r="M306" s="2" t="inlineStr" /><c r="N306" s="2" t="inlineStr" /><c r="O306" s="2" t="inlineStr" /><c r="P306" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q306" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="307"><c r="A307" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B307" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C307" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D307" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E307" s="2" t="inlineStr"><is><t>Kolistyna</t></is></c><c r="F307" s="2" t="inlineStr"><is><t>Działa nefrotoksycznie</t></is></c><c r="G307" s="2" t="inlineStr" /><c r="H307" s="2" t="inlineStr" /><c r="I307" s="2" t="inlineStr" /><c r="J307" s="2" t="inlineStr" /><c r="K307" s="2" t="inlineStr"><is><t>Działa głównie na bakterie Gram+</t></is></c><c r="L307" s="2" t="inlineStr"><is><t>Dobrze wchłania się po podaniu PO</t></is></c><c r="M307" s="2" t="inlineStr"><is><t>Jest wydalana głównie z kałem</t></is></c><c r="N307" s="2" t="inlineStr" /><c r="O307" s="2" t="inlineStr" /><c r="P307" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q307" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="308"><c r="A308" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B308" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C308" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D308" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E308" s="2" t="inlineStr"><is><t>Zagrożenia dla płodu jest mało prawdopodobne po</t></is></c><c r="F308" s="2" t="inlineStr"><is><t>Amoksycyliny z kwasem klawulanowym</t></is></c><c r="G308" s="2" t="inlineStr"><is><t>Erytromycyny</t></is></c><c r="H308" s="2" t="inlineStr"><is><t>Cefuroksymu</t></is></c><c r="I308" s="2" t="inlineStr" /><c r="J308" s="2" t="inlineStr" /><c r="K308" s="2" t="inlineStr"><is><t>Amikacyny</t></is></c><c r="L308" s="2" t="inlineStr" /><c r="M308" s="2" t="inlineStr" /><c r="N308" s="2" t="inlineStr" /><c r="O308" s="2" t="inlineStr" /><c r="P308" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q308" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="309"><c r="A309" s="2" t="inlineStr"><is><t>LEKI PRZECIWGRZYBICZE</t></is></c><c r="B309" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C309" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D309" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E309" s="2" t="inlineStr"><is><t>Ketokonazol</t></is></c><c r="F309" s="2" t="inlineStr"><is><t>Jest dostępny w postaci szamponu</t></is></c><c r="G309" s="2" t="inlineStr"><is><t>Ma zostosowanie w zespole Cushinga</t></is></c><c r="H309" s="2" t="inlineStr"><is><t>Wykazuje działanie hepatotoksyczne</t></is></c><c r="I309" s="2" t="inlineStr" /><c r="J309" s="2" t="inlineStr" /><c r="K309" s="2" t="inlineStr"><is><t>Nie wchłania się po podaniu doustnym</t></is></c><c r="L309" s="2" t="inlineStr" /><c r="M309" s="2" t="inlineStr" /><c r="N309" s="2" t="inlineStr" /><c r="O309" s="2" t="inlineStr" /><c r="P309" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q309" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="310"><c r="A310" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B310" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C310" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D310" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E310" s="2" t="inlineStr"><is><t>Do leków i rzutu w gruźlicy należy</t></is></c><c r="F310" s="2" t="inlineStr"><is><t>Ryfampicyna</t></is></c><c r="G310" s="2" t="inlineStr"><is><t>Izoniazyd</t></is></c><c r="H310" s="2" t="inlineStr"><is><t>Pyryzynamid</t></is></c><c r="I310" s="2" t="inlineStr" /><c r="J310" s="2" t="inlineStr" /><c r="K310" s="2" t="inlineStr"><is><t>Kanamycna</t></is></c><c r="L310" s="2" t="inlineStr" /><c r="M310" s="2" t="inlineStr" /><c r="N310" s="2" t="inlineStr" /><c r="O310" s="2" t="inlineStr" /><c r="P310" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q310" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="311"><c r="A311" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B311" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C311" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D311" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E311" s="2" t="inlineStr"><is><t>Podczas stosowania morfiny nie rozwija się tolerancja na TYLKO NA TE!!!</t></is></c><c r="F311" s="2" t="inlineStr"><is><t>Zaparcia</t></is></c><c r="G311" s="2" t="inlineStr"><is><t>Zwężenie źrenic</t></is></c><c r="H311" s="2" t="inlineStr" /><c r="I311" s="2" t="inlineStr" /><c r="J311" s="2" t="inlineStr" /><c r="K311" s="2" t="inlineStr"><is><t>Wymioty</t></is></c><c r="L311" s="2" t="inlineStr"><is><t>Depresję oddechową</t></is></c><c r="M311" s="2" t="inlineStr" /><c r="N311" s="2" t="inlineStr" /><c r="O311" s="2" t="inlineStr" /><c r="P311" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q311" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="312"><c r="A312" s="2" t="inlineStr"><is><t>NARKOTYCZNE LEKI PRZECIWBÓLOWE</t></is></c><c r="B312" s="2" t="inlineStr"><is><t>Sposób podania</t></is></c><c r="C312" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D312" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E312" s="2" t="inlineStr"><is><t>W farmakoterapii silnego bólu przebijającego stosujemy</t></is></c><c r="F312" s="2" t="inlineStr"><is><t>Morfinę doustnie w dawkach ratunkowych</t></is></c><c r="G312" s="2" t="inlineStr"><is><t>Fentanyl w postaci dopoliczkowej</t></is></c><c r="H312" s="2" t="inlineStr"><is><t>Buprenorfinę podjęzykowo</t></is></c><c r="I312" s="2" t="inlineStr"><is><t>Fentanyl w postaci donosowej</t></is></c><c r="J312" s="2" t="inlineStr" /><c r="K312" s="2" t="inlineStr" /><c r="L312" s="2" t="inlineStr" /><c r="M312" s="2" t="inlineStr" /><c r="N312" s="2" t="inlineStr" /><c r="O312" s="2" t="inlineStr" /><c r="P312" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q312" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="313"><c r="A313" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B313" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C313" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D313" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E313" s="2" t="inlineStr"><is><t>Ośrodkowe działania opioidów obejmują</t></is></c><c r="F313" s="2" t="inlineStr"><is><t>Działanie przeciwkaszlowe</t></is></c><c r="G313" s="2" t="inlineStr"><is><t>Wymioty</t></is></c><c r="H313" s="2" t="inlineStr" /><c r="I313" s="2" t="inlineStr" /><c r="J313" s="2" t="inlineStr" /><c r="K313" s="2" t="inlineStr"><is><t>Zwiększenie ciśnienia w drogach żółciowych</t></is></c><c r="L313" s="2" t="inlineStr"><is><t>Zaparcia</t></is></c><c r="M313" s="2" t="inlineStr" /><c r="N313" s="2" t="inlineStr" /><c r="O313" s="2" t="inlineStr" /><c r="P313" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q313" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="314"><c r="A314" s="2" t="inlineStr"><is><t>NARKOTYCZNE LEKI PRZECIWBÓLOWE</t></is></c><c r="B314" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C314" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D314" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E314" s="2" t="inlineStr"><is><t>Efekt pułapowy wykazuje</t></is></c><c r="F314" s="2" t="inlineStr"><is><t>Buprenorfina</t></is></c><c r="G314" s="2" t="inlineStr" /><c r="H314" s="2" t="inlineStr" /><c r="I314" s="2" t="inlineStr" /><c r="J314" s="2" t="inlineStr" /><c r="K314" s="2" t="inlineStr"><is><t>Morfina</t></is></c><c r="L314" s="2" t="inlineStr"><is><t>Kodeina</t></is></c><c r="M314" s="2" t="inlineStr"><is><t>Metadon</t></is></c><c r="N314" s="2" t="inlineStr" /><c r="O314" s="2" t="inlineStr" /><c r="P314" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q314" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="315"><c r="A315" s="2" t="inlineStr"><is><t>CUKRZYCA</t></is></c><c r="B315" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C315" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D315" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E315" s="2" t="inlineStr"><is><t>Metformina</t></is></c><c r="F315" s="2" t="inlineStr"><is><t>Zaburza wchłanianie witaminy B12</t></is></c><c r="G315" s="2" t="inlineStr"><is><t>Może powodować kwasicę metaboliczną</t></is></c><c r="H315" s="2" t="inlineStr" /><c r="I315" s="2" t="inlineStr" /><c r="J315" s="2" t="inlineStr" /><c r="K315" s="2" t="inlineStr"><is><t>Stymuluje wydzielanie insuliny</t></is></c><c r="L315" s="2" t="inlineStr"><is><t>Powoduje przyrost masy ciała</t></is></c><c r="M315" s="2" t="inlineStr" /><c r="N315" s="2" t="inlineStr" /><c r="O315" s="2" t="inlineStr" /><c r="P315" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q315" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="316"><c r="A316" s="2" t="inlineStr"><is><t>CUKRZYCA</t></is></c><c r="B316" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C316" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D316" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E316" s="2" t="inlineStr"><is><t>Szybkie analogi insuliny</t></is></c><c r="F316" s="2" t="inlineStr"><is><t>Lispro</t></is></c><c r="G316" s="2" t="inlineStr"><is><t>Aspart</t></is></c><c r="H316" s="2" t="inlineStr" /><c r="I316" s="2" t="inlineStr" /><c r="J316" s="2" t="inlineStr" /><c r="K316" s="2" t="inlineStr"><is><t>Glargina</t></is></c><c r="L316" s="2" t="inlineStr"><is><t>Detemir</t></is></c><c r="M316" s="2" t="inlineStr" /><c r="N316" s="2" t="inlineStr" /><c r="O316" s="2" t="inlineStr" /><c r="P316" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q316" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="317"><c r="A317" s="2" t="inlineStr"><is><t>ANTYKONCEPCJA</t></is></c><c r="B317" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C317" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D317" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E317" s="2" t="inlineStr"><is><t>Działania niepożądane hormonalnych środków antykoncepcyjnych z powodu obecności gestagenu</t></is></c><c r="F317" s="2" t="inlineStr"><is><t>Przyrost masy ciała</t></is></c><c r="G317" s="2" t="inlineStr"><is><t>Obniżenie libido</t></is></c><c r="H317" s="2" t="inlineStr"><is><t>Depresja</t></is></c><c r="I317" s="2" t="inlineStr"><is><t>Hirsutyzm</t></is></c><c r="J317" s="2" t="inlineStr" /><c r="K317" s="2" t="inlineStr" /><c r="L317" s="2" t="inlineStr" /><c r="M317" s="2" t="inlineStr" /><c r="N317" s="2" t="inlineStr" /><c r="O317" s="2" t="inlineStr" /><c r="P317" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q317" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="318"><c r="A318" s="2" t="inlineStr"><is><t>HORMONY PŁCIOWE</t></is></c><c r="B318" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C318" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D318" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E318" s="2" t="inlineStr"><is><t>Hiperprolaktynemia</t></is></c><c r="F318" s="2" t="inlineStr"><is><t>Karbegolina</t></is></c><c r="G318" s="2" t="inlineStr"><is><t>Bromokryptyna</t></is></c><c r="H318" s="2" t="inlineStr" /><c r="I318" s="2" t="inlineStr" /><c r="J318" s="2" t="inlineStr" /><c r="K318" s="2" t="inlineStr"><is><t>Gorserelina</t></is></c><c r="L318" s="2" t="inlineStr"><is><t>Finasteryd</t></is></c><c r="M318" s="2" t="inlineStr" /><c r="N318" s="2" t="inlineStr" /><c r="O318" s="2" t="inlineStr" /><c r="P318" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q318" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="319"><c r="A319" s="2" t="inlineStr"><is><t>CUKRZYCA</t></is></c><c r="B319" s="2" t="inlineStr"><is><t>Sposób podania</t></is></c><c r="C319" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D319" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E319" s="2" t="inlineStr"><is><t>Terapia cukrzycy typu 2 podskórnie</t></is></c><c r="F319" s="2" t="inlineStr"><is><t>Detemir</t></is></c><c r="G319" s="2" t="inlineStr" /><c r="H319" s="2" t="inlineStr" /><c r="I319" s="2" t="inlineStr" /><c r="J319" s="2" t="inlineStr" /><c r="K319" s="2" t="inlineStr"><is><t>Glipizyd</t></is></c><c r="L319" s="2" t="inlineStr"><is><t>Liraglutyd</t></is></c><c r="M319" s="2" t="inlineStr"><is><t>Linagliptyna</t></is></c><c r="N319" s="2" t="inlineStr" /><c r="O319" s="2" t="inlineStr" /><c r="P319" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q319" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="320"><c r="A320" s="2" t="inlineStr"><is><t>TARCZYCA</t></is></c><c r="B320" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C320" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D320" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E320" s="2" t="inlineStr"><is><t>Terapia nadczynności tarczycy</t></is></c><c r="F320" s="2" t="inlineStr"><is><t>Jod radioaktywny</t></is></c><c r="G320" s="2" t="inlineStr"><is><t>Bisoprolol</t></is></c><c r="H320" s="2" t="inlineStr"><is><t>Tiamazol</t></is></c><c r="I320" s="2" t="inlineStr"><is><t>Propylotiouracyl</t></is></c><c r="J320" s="2" t="inlineStr" /><c r="K320" s="2" t="inlineStr" /><c r="L320" s="2" t="inlineStr" /><c r="M320" s="2" t="inlineStr" /><c r="N320" s="2" t="inlineStr" /><c r="O320" s="2" t="inlineStr" /><c r="P320" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q320" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="321"><c r="A321" s="2" t="inlineStr"><is><t>LEKI IMMUNOSUPRESYJNE</t></is></c><c r="B321" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C321" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D321" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E321" s="2" t="inlineStr"><is><t>Cyklosporyna</t></is></c><c r="F321" s="2" t="inlineStr"><is><t>Jest eliminowana przez wątrobę</t></is></c><c r="G321" s="2" t="inlineStr"><is><t>Jest stosowana w celu zapobiegania odrzucania przeszczepów</t></is></c><c r="H321" s="2" t="inlineStr" /><c r="I321" s="2" t="inlineStr" /><c r="J321" s="2" t="inlineStr" /><c r="K321" s="2" t="inlineStr"><is><t>Jest aktywatorem kalcyneuryny</t></is></c><c r="L321" s="2" t="inlineStr"><is><t>Może powodować atrofię dziąseł</t></is></c><c r="M321" s="2" t="inlineStr" /><c r="N321" s="2" t="inlineStr" /><c r="O321" s="2" t="inlineStr" /><c r="P321" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q321" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="322"><c r="A322" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B322" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C322" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D322" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E322" s="2" t="inlineStr"><is><t>Podczas terapii GKS może dojsć do pogorszenia przebiegu</t></is></c><c r="F322" s="2" t="inlineStr"><is><t>Cukrzycy</t></is></c><c r="G322" s="2" t="inlineStr"><is><t>Gruźlicy</t></is></c><c r="H322" s="2" t="inlineStr"><is><t>Osteoporozy</t></is></c><c r="I322" s="2" t="inlineStr" /><c r="J322" s="2" t="inlineStr" /><c r="K322" s="2" t="inlineStr"><is><t>Małopłytkowości idiopatycznej</t></is></c><c r="L322" s="2" t="inlineStr" /><c r="M322" s="2" t="inlineStr" /><c r="N322" s="2" t="inlineStr" /><c r="O322" s="2" t="inlineStr" /><c r="P322" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q322" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="323"><c r="A323" s="2" t="inlineStr"><is><t>NIEOPIOIDOWE LEKI PRZECIWBÓLOWE</t></is></c><c r="B323" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C323" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D323" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E323" s="2" t="inlineStr"><is><t>Wzrostu ryzyka sercowo-naczyniowego NIE powoduje</t></is></c><c r="F323" s="2" t="inlineStr"><is><t>Kwas acetylosalicylowy</t></is></c><c r="G323" s="2" t="inlineStr" /><c r="H323" s="2" t="inlineStr" /><c r="I323" s="2" t="inlineStr" /><c r="J323" s="2" t="inlineStr" /><c r="K323" s="2" t="inlineStr"><is><t>Celekoksyb</t></is></c><c r="L323" s="2" t="inlineStr"><is><t>Indometacyna</t></is></c><c r="M323" s="2" t="inlineStr"><is><t>Ketoprofen</t></is></c><c r="N323" s="2" t="inlineStr" /><c r="O323" s="2" t="inlineStr" /><c r="P323" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q323" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="324"><c r="A324" s="2" t="inlineStr"><is><t>NIEOPIOIDOWE LEKI PRZECIWBÓLOWE</t></is></c><c r="B324" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C324" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D324" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E324" s="2" t="inlineStr"><is><t>Zmniejszenie ryzyka gastrotoksyczności NLPZ – co możemy</t></is></c><c r="F324" s="2" t="inlineStr"><is><t>Analogi PGE1</t></is></c><c r="G324" s="2" t="inlineStr"><is><t>IPP</t></is></c><c r="H324" s="2" t="inlineStr" /><c r="I324" s="2" t="inlineStr" /><c r="J324" s="2" t="inlineStr" /><c r="K324" s="2" t="inlineStr"><is><t>GKS</t></is></c><c r="L324" s="2" t="inlineStr"><is><t>Preparaty o wybiórczym powinowactwie do COX1</t></is></c><c r="M324" s="2" t="inlineStr" /><c r="N324" s="2" t="inlineStr" /><c r="O324" s="2" t="inlineStr" /><c r="P324" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q324" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="325"><c r="A325" s="2" t="inlineStr"><is><t>NIEOPIOIDOWE LEKI PRZECIWBÓLOWE</t></is></c><c r="B325" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C325" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D325" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E325" s="2" t="inlineStr"><is><t>Paracetamol</t></is></c><c r="F325" s="2" t="inlineStr"><is><t>Jest metabolizowany przez enzymy cytochromu P-450</t></is></c><c r="G325" s="2" t="inlineStr" /><c r="H325" s="2" t="inlineStr" /><c r="I325" s="2" t="inlineStr" /><c r="J325" s="2" t="inlineStr" /><c r="K325" s="2" t="inlineStr"><is><t>Działa silnie przeciwzapalnie</t></is></c><c r="L325" s="2" t="inlineStr"><is><t>Hamuje COX2 w OUN</t></is></c><c r="M325" s="2" t="inlineStr"><is><t>Wykazuje działanie gastrotoksyczne</t></is></c><c r="N325" s="2" t="inlineStr" /><c r="O325" s="2" t="inlineStr" /><c r="P325" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q325" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="326"><c r="A326" s="2" t="inlineStr"><is><t>LEKI PRZECIWNOWOTWOROWE</t></is></c><c r="B326" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C326" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D326" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E326" s="2" t="inlineStr"><is><t>Leki immunosupresyjne</t></is></c><c r="F326" s="2" t="inlineStr"><is><t>Powodują upośledzenie odporności komórkowej</t></is></c><c r="G326" s="2" t="inlineStr"><is><t>Są lekami o wąskim wskaźniku terapeutycznym</t></is></c><c r="H326" s="2" t="inlineStr" /><c r="I326" s="2" t="inlineStr" /><c r="J326" s="2" t="inlineStr" /><c r="K326" s="2" t="inlineStr"><is><t>Zapobiegają rozwojowi nowotworów</t></is></c><c r="L326" s="2" t="inlineStr"><is><t>Znajdują zastosowanie w terapii chorób neurodegeneracyjnych</t></is></c><c r="M326" s="2" t="inlineStr" /><c r="N326" s="2" t="inlineStr" /><c r="O326" s="2" t="inlineStr" /><c r="P326" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q326" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="327"><c r="A327" s="2" t="inlineStr"><is><t>UKŁAD ODDECHOWY</t></is></c><c r="B327" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C327" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D327" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E327" s="2" t="inlineStr"><is><t>Wskaż prawidłowe pary lek – wskazanie</t></is></c><c r="F327" s="2" t="inlineStr"><is><t>Bromoheksyna – astma oskrzelowa</t></is></c><c r="G327" s="2" t="inlineStr" /><c r="H327" s="2" t="inlineStr" /><c r="I327" s="2" t="inlineStr" /><c r="J327" s="2" t="inlineStr" /><c r="K327" s="2" t="inlineStr"><is><t>Acetylocysteina – ostre zapalenie zatok obocznych nosa</t></is></c><c r="L327" s="2" t="inlineStr"><is><t>Dornaza alfa – sarkoidoza</t></is></c><c r="M327" s="2" t="inlineStr"><is><t>Ambroksol – infekcyjne zaostrzenie POChP</t></is></c><c r="N327" s="2" t="inlineStr" /><c r="O327" s="2" t="inlineStr" /><c r="P327" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q327" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="328"><c r="A328" s="2" t="inlineStr"><is><t>UKŁAD WSPÓŁCZULNY</t></is></c><c r="B328" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C328" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D328" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E328" s="2" t="inlineStr"><is><t>W celu przerwania ataku duszności Zależy jakiej dusznosći. Duszności przygodnej będą same SABA, jak mamy zaostrzenie astmy to GKS też</t></is></c><c r="F328" s="2" t="inlineStr"><is><t>Fenoterol</t></is></c><c r="G328" s="2" t="inlineStr"><is><t>Salbutamol</t></is></c><c r="H328" s="2" t="inlineStr" /><c r="I328" s="2" t="inlineStr" /><c r="J328" s="2" t="inlineStr" /><c r="K328" s="2" t="inlineStr"><is><t>Salmeterol</t></is></c><c r="L328" s="2" t="inlineStr"><is><t>Flutikazon</t></is></c><c r="M328" s="2" t="inlineStr" /><c r="N328" s="2" t="inlineStr" /><c r="O328" s="2" t="inlineStr" /><c r="P328" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q328" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="329"><c r="A329" s="2" t="inlineStr"><is><t>UKŁAD ODDECHOWY</t></is></c><c r="B329" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C329" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D329" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E329" s="2" t="inlineStr"><is><t>Omalizumab</t></is></c><c r="F329" s="2" t="inlineStr"><is><t>Blokuje łączenie IgE z komórkami tucznymi</t></is></c><c r="G329" s="2" t="inlineStr"><is><t>Zmniejsza liczbę zaostrzeń astmy</t></is></c><c r="H329" s="2" t="inlineStr" /><c r="I329" s="2" t="inlineStr" /><c r="J329" s="2" t="inlineStr" /><c r="K329" s="2" t="inlineStr"><is><t>Stosowany jest w astmie o umiarkowanej ciężkości</t></is></c><c r="L329" s="2" t="inlineStr"><is><t>Zwiększa zapotrzebowanie na GKS</t></is></c><c r="M329" s="2" t="inlineStr" /><c r="N329" s="2" t="inlineStr" /><c r="O329" s="2" t="inlineStr" /><c r="P329" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q329" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="330"><c r="A330" s="2" t="inlineStr"><is><t>UKŁAD WSPÓŁCZULNY</t></is></c><c r="B330" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C330" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D330" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E330" s="2" t="inlineStr"><is><t>Farmakoterapia POChP kategoria A i B</t></is></c><c r="F330" s="2" t="inlineStr"><is><t>Krótko i długo działające cholinolityki</t></is></c><c r="G330" s="2" t="inlineStr"><is><t>Krótko i długo działające beta2 adrenomimetyki</t></is></c><c r="H330" s="2" t="inlineStr" /><c r="I330" s="2" t="inlineStr" /><c r="J330" s="2" t="inlineStr" /><c r="K330" s="2" t="inlineStr"><is><t>GKS</t></is></c><c r="L330" s="2" t="inlineStr"><is><t>Inhibitory fosfodiesterazy 4</t></is></c><c r="M330" s="2" t="inlineStr" /><c r="N330" s="2" t="inlineStr" /><c r="O330" s="2" t="inlineStr" /><c r="P330" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q330" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="331"><c r="A331" s="2" t="inlineStr"><is><t>FARMAKOKINETYKA</t></is></c><c r="B331" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C331" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D331" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E331" s="2" t="inlineStr"><is><t>Omeprazol</t></is></c><c r="F331" s="2" t="inlineStr"><is><t>Powoduje nieodwracalne zablokowanie pompy protonowej</t></is></c><c r="G331" s="2" t="inlineStr"><is><t>Jest inhibitorem enzymów cytochromu P-450</t></is></c><c r="H331" s="2" t="inlineStr" /><c r="I331" s="2" t="inlineStr" /><c r="J331" s="2" t="inlineStr" /><c r="K331" s="2" t="inlineStr"><is><t>Hamuje wydzielanie kwasu solnego przez 6-12h</t></is></c><c r="L331" s="2" t="inlineStr"><is><t>Jest aktywowany przez pepsynę</t></is></c><c r="M331" s="2" t="inlineStr" /><c r="N331" s="2" t="inlineStr" /><c r="O331" s="2" t="inlineStr" /><c r="P331" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q331" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="332"><c r="A332" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B332" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C332" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D332" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E332" s="2" t="inlineStr"><is><t>Metoklopramid</t></is></c><c r="F332" s="2" t="inlineStr"><is><t>Jest agonistą receptorów dopaminowych</t></is></c><c r="G332" s="2" t="inlineStr"><is><t>Działa przeciwwymiotnie</t></is></c><c r="H332" s="2" t="inlineStr" /><c r="I332" s="2" t="inlineStr" /><c r="J332" s="2" t="inlineStr" /><c r="K332" s="2" t="inlineStr"><is><t>Zmniejsza objawy pozapiramidowe</t></is></c><c r="L332" s="2" t="inlineStr"><is><t>Zmniejsza stężenie prolaktyny</t></is></c><c r="M332" s="2" t="inlineStr" /><c r="N332" s="2" t="inlineStr" /><c r="O332" s="2" t="inlineStr" /><c r="P332" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q332" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="333"><c r="A333" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B333" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C333" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D333" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E333" s="2" t="inlineStr"><is><t>Przewlekłe zapalenie trzustki z alkoholu</t></is></c><c r="F333" s="2" t="inlineStr"><is><t>Preparaty enzymów trzustkowych</t></is></c><c r="G333" s="2" t="inlineStr"><is><t>Leki przeciwbólowe</t></is></c><c r="H333" s="2" t="inlineStr" /><c r="I333" s="2" t="inlineStr" /><c r="J333" s="2" t="inlineStr" /><c r="K333" s="2" t="inlineStr"><is><t>GKS</t></is></c><c r="L333" s="2" t="inlineStr"><is><t>Leki przeciwbakteryjne</t></is></c><c r="M333" s="2" t="inlineStr" /><c r="N333" s="2" t="inlineStr" /><c r="O333" s="2" t="inlineStr" /><c r="P333" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q333" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="334"><c r="A334" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B334" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C334" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D334" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E334" s="2" t="inlineStr"><is><t>Chory z encefalopatią wątrobową, możemy</t></is></c><c r="F334" s="2" t="inlineStr"><is><t>Asparaginian ornityny</t></is></c><c r="G334" s="2" t="inlineStr"><is><t>Laktuloza</t></is></c><c r="H334" s="2" t="inlineStr"><is><t>Ryfaksymina</t></is></c><c r="I334" s="2" t="inlineStr" /><c r="J334" s="2" t="inlineStr" /><c r="K334" s="2" t="inlineStr"><is><t>Piracetam</t></is></c><c r="L334" s="2" t="inlineStr" /><c r="M334" s="2" t="inlineStr" /><c r="N334" s="2" t="inlineStr" /><c r="O334" s="2" t="inlineStr" /><c r="P334" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q334" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="335"><c r="A335" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B335" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C335" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D335" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E335" s="2" t="inlineStr"><is><t>Schematy eradykacji H. Pylori (rekomendowane)</t></is></c><c r="F335" s="2" t="inlineStr"><is><t>Pantoprazol/cytrynian bizmutu/tetracyklina/metronidazol</t></is></c><c r="G335" s="2" t="inlineStr" /><c r="H335" s="2" t="inlineStr" /><c r="I335" s="2" t="inlineStr" /><c r="J335" s="2" t="inlineStr" /><c r="K335" s="2" t="inlineStr"><is><t>Cytrynian bizmutu/metronidazol</t></is></c><c r="L335" s="2" t="inlineStr"><is><t>Mizoprostol/metronidazol/klarytromycyna</t></is></c><c r="M335" s="2" t="inlineStr"><is><t>Ranitydyna/amoksycylina/metronidazol</t></is></c><c r="N335" s="2" t="inlineStr" /><c r="O335" s="2" t="inlineStr" /><c r="P335" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q335" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="336"><c r="A336" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B336" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C336" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D336" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E336" s="2" t="inlineStr"><is><t>Lek przeciwzakrzepowy – czas odstawienia (planowa, duże ryzyko krwawienia, nerki prawidłowe)</t></is></c><c r="F336" s="2" t="inlineStr"><is><t>Dabigatran – 1 dzień</t></is></c><c r="G336" s="2" t="inlineStr" /><c r="H336" s="2" t="inlineStr" /><c r="I336" s="2" t="inlineStr" /><c r="J336" s="2" t="inlineStr" /><c r="K336" s="2" t="inlineStr"><is><t>Warfaryna – 2 dni</t></is></c><c r="L336" s="2" t="inlineStr"><is><t>Acenokumarol – 10 dni</t></is></c><c r="M336" s="2" t="inlineStr"><is><t>Kwas acetylosalicylowy – 5 dni</t></is></c><c r="N336" s="2" t="inlineStr" /><c r="O336" s="2" t="inlineStr" /><c r="P336" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q336" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="337"><c r="A337" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B337" s="2" t="inlineStr"><is><t>Monitorowanie</t></is></c><c r="C337" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D337" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E337" s="2" t="inlineStr"><is><t>Lek – monitorowanie</t></is></c><c r="F337" s="2" t="inlineStr"><is><t>Heparyna niefrakcjonowana – APTT</t></is></c><c r="G337" s="2" t="inlineStr" /><c r="H337" s="2" t="inlineStr" /><c r="I337" s="2" t="inlineStr" /><c r="J337" s="2" t="inlineStr" /><c r="K337" s="2" t="inlineStr"><is><t>Dabigatran – INR</t></is></c><c r="L337" s="2" t="inlineStr"><is><t>Acenokumarol – czas ekarynowy</t></is></c><c r="M337" s="2" t="inlineStr"><is><t>Rywaroksaban – czas trombinowy</t></is></c><c r="N337" s="2" t="inlineStr" /><c r="O337" s="2" t="inlineStr" /><c r="P337" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q337" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="338"><c r="A338" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B338" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C338" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D338" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E338" s="2" t="inlineStr"><is><t>Działanie antyagregacyjne</t></is></c><c r="F338" s="2" t="inlineStr"><is><t>Antagoniści receptorów P2Y12</t></is></c><c r="G338" s="2" t="inlineStr" /><c r="H338" s="2" t="inlineStr" /><c r="I338" s="2" t="inlineStr" /><c r="J338" s="2" t="inlineStr" /><c r="K338" s="2" t="inlineStr"><is><t>Agoniści receptorów GP IIb/IIIa</t></is></c><c r="L338" s="2" t="inlineStr"><is><t>Inhibitory COX2</t></is></c><c r="M338" s="2" t="inlineStr"><is><t>Agoniści receptorów TXA2</t></is></c><c r="N338" s="2" t="inlineStr" /><c r="O338" s="2" t="inlineStr" /><c r="P338" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q338" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="339"><c r="A339" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B339" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C339" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D339" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E339" s="2" t="inlineStr"><is><t>Zahamowanie agregacji płytek zależne od ADP po</t></is></c><c r="F339" s="2" t="inlineStr"><is><t>Klopidogrelu</t></is></c><c r="G339" s="2" t="inlineStr"><is><t>Tikagreloru</t></is></c><c r="H339" s="2" t="inlineStr" /><c r="I339" s="2" t="inlineStr" /><c r="J339" s="2" t="inlineStr" /><c r="K339" s="2" t="inlineStr"><is><t>Enoksaparyny</t></is></c><c r="L339" s="2" t="inlineStr"><is><t>Dipyridamolu</t></is></c><c r="M339" s="2" t="inlineStr" /><c r="N339" s="2" t="inlineStr" /><c r="O339" s="2" t="inlineStr" /><c r="P339" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q339" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="340"><c r="A340" s="2" t="inlineStr"><is><t>LEKI HIPOLIPEMIZUJĄCE</t></is></c><c r="B340" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C340" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D340" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E340" s="2" t="inlineStr"><is><t>Statyny</t></is></c><c r="F340" s="2" t="inlineStr"><is><t>Zmniejszają stężenie cholesterolu LDL</t></is></c><c r="G340" s="2" t="inlineStr"><is><t>Zmniejszą stężenie triglicerydów</t></is></c><c r="H340" s="2" t="inlineStr" /><c r="I340" s="2" t="inlineStr" /><c r="J340" s="2" t="inlineStr" /><c r="K340" s="2" t="inlineStr"><is><t>Nie wpływają na stężenie cholesterolu wewnątrzkomórkowego</t></is></c><c r="L340" s="2" t="inlineStr"><is><t>Zmniejszają stężęnie cholesterolu HDL</t></is></c><c r="M340" s="2" t="inlineStr" /><c r="N340" s="2" t="inlineStr" /><c r="O340" s="2" t="inlineStr" /><c r="P340" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q340" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="341"><c r="A341" s="2" t="inlineStr"><is><t>LEKI HIPOLIPEMIZUJĄCE</t></is></c><c r="B341" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C341" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D341" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E341" s="2" t="inlineStr"><is><t>Wielokierunkowe działanie statyn</t></is></c><c r="F341" s="2" t="inlineStr"><is><t>Poprawę funkcji śródbłonka</t></is></c><c r="G341" s="2" t="inlineStr"><is><t>Efekt przeciwzapalny</t></is></c><c r="H341" s="2" t="inlineStr"><is><t>Wpływ na fibrynolizę</t></is></c><c r="I341" s="2" t="inlineStr"><is><t>Stabilizację blaszki miażdżycowej</t></is></c><c r="J341" s="2" t="inlineStr" /><c r="K341" s="2" t="inlineStr" /><c r="L341" s="2" t="inlineStr" /><c r="M341" s="2" t="inlineStr" /><c r="N341" s="2" t="inlineStr" /><c r="O341" s="2" t="inlineStr" /><c r="P341" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q341" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="342"><c r="A342" s="2" t="inlineStr"><is><t>CUKRZYCA</t></is></c><c r="B342" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C342" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D342" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E342" s="2" t="inlineStr"><is><t>Farmakoterapia otyłości</t></is></c><c r="F342" s="2" t="inlineStr"><is><t>Liraglutyd</t></is></c><c r="G342" s="2" t="inlineStr"><is><t>Orlistat</t></is></c><c r="H342" s="2" t="inlineStr" /><c r="I342" s="2" t="inlineStr" /><c r="J342" s="2" t="inlineStr" /><c r="K342" s="2" t="inlineStr"><is><t>Paroksetyna</t></is></c><c r="L342" s="2" t="inlineStr"><is><t>Naltrekson</t></is></c><c r="M342" s="2" t="inlineStr" /><c r="N342" s="2" t="inlineStr" /><c r="O342" s="2" t="inlineStr" /><c r="P342" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q342" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="343"><c r="A343" s="2" t="inlineStr"><is><t>UKŁAD WSPÓŁCZULNY</t></is></c><c r="B343" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C343" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D343" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E343" s="2" t="inlineStr"><is><t>Do beta adrenolityków zmniejszających śmiertelność w skurczowej niewydolności serca</t></is></c><c r="F343" s="2" t="inlineStr"><is><t>Nebiwolol</t></is></c><c r="G343" s="2" t="inlineStr" /><c r="H343" s="2" t="inlineStr" /><c r="I343" s="2" t="inlineStr" /><c r="J343" s="2" t="inlineStr" /><c r="K343" s="2" t="inlineStr"><is><t>Atenolol</t></is></c><c r="L343" s="2" t="inlineStr"><is><t>Esmolol</t></is></c><c r="M343" s="2" t="inlineStr"><is><t>Acebutolol</t></is></c><c r="N343" s="2" t="inlineStr" /><c r="O343" s="2" t="inlineStr" /><c r="P343" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q343" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="344"><c r="A344" s="2" t="inlineStr"><is><t>CHOROBA NIEDOKRWIENNA SERCA</t></is></c><c r="B344" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C344" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D344" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E344" s="2" t="inlineStr"><is><t>Donory NO</t></is></c><c r="F344" s="2" t="inlineStr"><is><t>Nikorandil</t></is></c><c r="G344" s="2" t="inlineStr"><is><t>Molsidomina</t></is></c><c r="H344" s="2" t="inlineStr"><is><t>Diazontanizosorbitol</t></is></c><c r="I344" s="2" t="inlineStr" /><c r="J344" s="2" t="inlineStr" /><c r="K344" s="2" t="inlineStr"><is><t>Trimetazydyna</t></is></c><c r="L344" s="2" t="inlineStr" /><c r="M344" s="2" t="inlineStr" /><c r="N344" s="2" t="inlineStr" /><c r="O344" s="2" t="inlineStr" /><c r="P344" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q344" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="345"><c r="A345" s="2" t="inlineStr"><is><t>UKŁAD WSPÓŁCZULNY</t></is></c><c r="B345" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C345" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D345" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E345" s="2" t="inlineStr"><is><t>Leki I wyborou w monoterapii NT</t></is></c><c r="F345" s="2" t="inlineStr"><is><t>Antagoniści receptora angiotensynowego</t></is></c><c r="G345" s="2" t="inlineStr"><is><t>Antagoniści kanałów wapniowych</t></is></c><c r="H345" s="2" t="inlineStr" /><c r="I345" s="2" t="inlineStr" /><c r="J345" s="2" t="inlineStr" /><c r="K345" s="2" t="inlineStr"><is><t>Alfa1 adrenolityki</t></is></c><c r="L345" s="2" t="inlineStr"><is><t>Inhibitory reniny</t></is></c><c r="M345" s="2" t="inlineStr" /><c r="N345" s="2" t="inlineStr" /><c r="O345" s="2" t="inlineStr" /><c r="P345" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q345" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="346"><c r="A346" s="2" t="inlineStr"><is><t>LEKI MOCZOPĘDNE</t></is></c><c r="B346" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C346" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D346" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E346" s="2" t="inlineStr"><is><t>Zmniejszenie śmiertnelności w skurczowej niewydolności serca</t></is></c><c r="F346" s="2" t="inlineStr"><is><t>Inhibitory konwertazy angiotensyny</t></is></c><c r="G346" s="2" t="inlineStr"><is><t>Antagoniści aldosteronu</t></is></c><c r="H346" s="2" t="inlineStr" /><c r="I346" s="2" t="inlineStr" /><c r="J346" s="2" t="inlineStr" /><c r="K346" s="2" t="inlineStr"><is><t>Waptany</t></is></c><c r="L346" s="2" t="inlineStr"><is><t>Diuretyki pętlowe</t></is></c><c r="M346" s="2" t="inlineStr" /><c r="N346" s="2" t="inlineStr" /><c r="O346" s="2" t="inlineStr" /><c r="P346" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q346" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="347"><c r="A347" s="2" t="inlineStr"><is><t>NADCIŚNIENIE TĘTNICZE</t></is></c><c r="B347" s="2" t="inlineStr"><is><t>Interakcje</t></is></c><c r="C347" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D347" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E347" s="2" t="inlineStr"><is><t>Przeciwskane jest jednoczesne stosowanie beta adrenolityków i</t></is></c><c r="F347" s="2" t="inlineStr"><is><t>Werapamilu</t></is></c><c r="G347" s="2" t="inlineStr" /><c r="H347" s="2" t="inlineStr" /><c r="I347" s="2" t="inlineStr" /><c r="J347" s="2" t="inlineStr" /><c r="K347" s="2" t="inlineStr"><is><t>Kaptoprylu</t></is></c><c r="L347" s="2" t="inlineStr"><is><t>Torasemidu</t></is></c><c r="M347" s="2" t="inlineStr"><is><t>Irbesartanu</t></is></c><c r="N347" s="2" t="inlineStr" /><c r="O347" s="2" t="inlineStr" /><c r="P347" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q347" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="348"><c r="A348" s="2" t="inlineStr"><is><t>NADCIŚNIENIE TĘTNICZE</t></is></c><c r="B348" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C348" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D348" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E348" s="2" t="inlineStr"><is><t>Stan kliniczny – lek nadciśnieniowy</t></is></c><c r="F348" s="2" t="inlineStr"><is><t>Mikroalbuminuria – peryndopryl</t></is></c><c r="G348" s="2" t="inlineStr"><is><t>Tętniak aorty – bisoprolol</t></is></c><c r="H348" s="2" t="inlineStr"><is><t>Ciąża – metyldopa</t></is></c><c r="I348" s="2" t="inlineStr"><is><t>Chory po 80 rż. – indapamid</t></is></c><c r="J348" s="2" t="inlineStr" /><c r="K348" s="2" t="inlineStr" /><c r="L348" s="2" t="inlineStr" /><c r="M348" s="2" t="inlineStr" /><c r="N348" s="2" t="inlineStr" /><c r="O348" s="2" t="inlineStr" /><c r="P348" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q348" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="349"><c r="A349" s="2" t="inlineStr"><is><t>NIEWYDOLNOŚĆ SERCA</t></is></c><c r="B349" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C349" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D349" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E349" s="2" t="inlineStr"><is><t>Inotropowe dodatnie</t></is></c><c r="F349" s="2" t="inlineStr"><is><t>Lewosymendan</t></is></c><c r="G349" s="2" t="inlineStr"><is><t>Milrinon</t></is></c><c r="H349" s="2" t="inlineStr" /><c r="I349" s="2" t="inlineStr" /><c r="J349" s="2" t="inlineStr" /><c r="K349" s="2" t="inlineStr"><is><t>Nesirytyd</t></is></c><c r="L349" s="2" t="inlineStr"><is><t>Sakubitryl</t></is></c><c r="M349" s="2" t="inlineStr" /><c r="N349" s="2" t="inlineStr" /><c r="O349" s="2" t="inlineStr" /><c r="P349" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q349" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="350"><c r="A350" s="2" t="inlineStr"><is><t>NADCIŚNIENIE TĘTNICZE</t></is></c><c r="B350" s="2" t="inlineStr"><is><t>Interakcje</t></is></c><c r="C350" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D350" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E350" s="2" t="inlineStr"><is><t>Skojarzenia leków w nadciśnieniu</t></is></c><c r="F350" s="2" t="inlineStr"><is><t>Inhibitor konwertazy angiotensyny + diuretyk tiazydowy</t></is></c><c r="G350" s="2" t="inlineStr"><is><t>Inhibitor konwertazy angiotensyny + antagonista wapnia</t></is></c><c r="H350" s="2" t="inlineStr"><is><t>Diuretyk tiazydowy + antagonista wapnia</t></is></c><c r="I350" s="2" t="inlineStr" /><c r="J350" s="2" t="inlineStr" /><c r="K350" s="2" t="inlineStr"><is><t>Sartan + inhibitor konwertazy angiotensyny</t></is></c><c r="L350" s="2" t="inlineStr" /><c r="M350" s="2" t="inlineStr" /><c r="N350" s="2" t="inlineStr" /><c r="O350" s="2" t="inlineStr" /><c r="P350" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q350" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="351"><c r="A351" s="2" t="inlineStr"><is><t>ZABURZENIA RYTMU SERCA</t></is></c><c r="B351" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C351" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D351" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E351" s="2" t="inlineStr"><is><t>Amlodypina – działanie</t></is></c><c r="F351" s="2" t="inlineStr"><is><t>Zmniejszające opór obwodowy</t></is></c><c r="G351" s="2" t="inlineStr" /><c r="H351" s="2" t="inlineStr" /><c r="I351" s="2" t="inlineStr" /><c r="J351" s="2" t="inlineStr" /><c r="K351" s="2" t="inlineStr"><is><t>Chronotropowe dodatnie</t></is></c><c r="L351" s="2" t="inlineStr"><is><t>Inotropowe ujemne</t></is></c><c r="M351" s="2" t="inlineStr"><is><t>Dromotropowe ujemne</t></is></c><c r="N351" s="2" t="inlineStr" /><c r="O351" s="2" t="inlineStr" /><c r="P351" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q351" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="352"><c r="A352" s="2" t="inlineStr"><is><t>ZABURZENIA RYTMU SERCA</t></is></c><c r="B352" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C352" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D352" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E352" s="2" t="inlineStr"><is><t>Dławica naczynioskurczowa (Prinzmetala)</t></is></c><c r="F352" s="2" t="inlineStr"><is><t>Diltiazem</t></is></c><c r="G352" s="2" t="inlineStr"><is><t>Werapamil</t></is></c><c r="H352" s="2" t="inlineStr" /><c r="I352" s="2" t="inlineStr" /><c r="J352" s="2" t="inlineStr" /><c r="K352" s="2" t="inlineStr"><is><t>Atenolol</t></is></c><c r="L352" s="2" t="inlineStr"><is><t>Prazosyna</t></is></c><c r="M352" s="2" t="inlineStr" /><c r="N352" s="2" t="inlineStr" /><c r="O352" s="2" t="inlineStr" /><c r="P352" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q352" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="353"><c r="A353" s="2" t="inlineStr"><is><t>NADCIŚNIENIE TĘTNICZE</t></is></c><c r="B353" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C353" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D353" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E353" s="2" t="inlineStr"><is><t>Hiperkaliemia przy stosowaniu</t></is></c><c r="F353" s="2" t="inlineStr"><is><t>Kaptoprylu</t></is></c><c r="G353" s="2" t="inlineStr"><is><t>Amilorlydu</t></is></c><c r="H353" s="2" t="inlineStr" /><c r="I353" s="2" t="inlineStr" /><c r="J353" s="2" t="inlineStr" /><c r="K353" s="2" t="inlineStr"><is><t>Torasemidu</t></is></c><c r="L353" s="2" t="inlineStr"><is><t>Hydrochlortiazydu</t></is></c><c r="M353" s="2" t="inlineStr" /><c r="N353" s="2" t="inlineStr" /><c r="O353" s="2" t="inlineStr" /><c r="P353" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q353" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="354"><c r="A354" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B354" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C354" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D354" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E354" s="2" t="inlineStr"><is><t>OZW – postepowanie</t></is></c><c r="F354" s="2" t="inlineStr"><is><t>Furasemidu i.m</t></is></c><c r="G354" s="2" t="inlineStr"><is><t>Tikaglerolu p.o Klopidogrel bardziej, ale powiedzmy ze tak</t></is></c><c r="H354" s="2" t="inlineStr"><is><t>Morfiny s.c</t></is></c><c r="I354" s="2" t="inlineStr"><is><t>Kwasu acetylosalicylowego p.o</t></is></c><c r="J354" s="2" t="inlineStr" /><c r="K354" s="2" t="inlineStr" /><c r="L354" s="2" t="inlineStr" /><c r="M354" s="2" t="inlineStr" /><c r="N354" s="2" t="inlineStr" /><c r="O354" s="2" t="inlineStr" /><c r="P354" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q354" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="355"><c r="A355" s="2" t="inlineStr"><is><t>ZABURZENIA RYTMU SERCA</t></is></c><c r="B355" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C355" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D355" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E355" s="2" t="inlineStr"><is><t>Amiodaron ???</t></is></c><c r="F355" s="2" t="inlineStr"><is><t>Jest stosowany w arytmiach opornych na inne leki</t></is></c><c r="G355" s="2" t="inlineStr" /><c r="H355" s="2" t="inlineStr" /><c r="I355" s="2" t="inlineStr" /><c r="J355" s="2" t="inlineStr" /><c r="K355" s="2" t="inlineStr"><is><t>Działa inotropowo ujemnie</t></is></c><c r="L355" s="2" t="inlineStr"><is><t>Jest skuteczny wyłącznie w arytmiach komorowych</t></is></c><c r="M355" s="2" t="inlineStr"><is><t>Jest agonistą kanałów potasowych</t></is></c><c r="N355" s="2" t="inlineStr" /><c r="O355" s="2" t="inlineStr" /><c r="P355" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q355" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="356"><c r="A356" s="2" t="inlineStr"><is><t>LEKI MOCZOPĘDNE</t></is></c><c r="B356" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C356" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D356" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E356" s="2" t="inlineStr"><is><t>Eplerenon</t></is></c><c r="F356" s="2" t="inlineStr"><is><t>Selektywnie wiąże się z receptorem dla mineralokortykoidów</t></is></c><c r="G356" s="2" t="inlineStr" /><c r="H356" s="2" t="inlineStr" /><c r="I356" s="2" t="inlineStr" /><c r="J356" s="2" t="inlineStr" /><c r="K356" s="2" t="inlineStr"><is><t>Nie powoduje hiperkaliemii</t></is></c><c r="L356" s="2" t="inlineStr"><is><t>Jest agonistą receptorów dla androgenów</t></is></c><c r="M356" s="2" t="inlineStr"><is><t>Powoduje hipernatremię</t></is></c><c r="N356" s="2" t="inlineStr" /><c r="O356" s="2" t="inlineStr" /><c r="P356" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q356" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="357"><c r="A357" s="2" t="inlineStr"><is><t>PADACZKA</t></is></c><c r="B357" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C357" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D357" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E357" s="2" t="inlineStr"><is><t>TLPD – działania niepożądane</t></is></c><c r="F357" s="2" t="inlineStr"><is><t>Zwiększenie masy ciała</t></is></c><c r="G357" s="2" t="inlineStr"><is><t>Obniżenie progu drgawkowego</t></is></c><c r="H357" s="2" t="inlineStr"><is><t>Suchowść w ustach</t></is></c><c r="I357" s="2" t="inlineStr"><is><t>Nad lub niedociśnienie tętnicze</t></is></c><c r="J357" s="2" t="inlineStr" /><c r="K357" s="2" t="inlineStr" /><c r="L357" s="2" t="inlineStr" /><c r="M357" s="2" t="inlineStr" /><c r="N357" s="2" t="inlineStr" /><c r="O357" s="2" t="inlineStr" /><c r="P357" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q357" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="358"><c r="A358" s="2" t="inlineStr"><is><t>PADACZKA</t></is></c><c r="B358" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C358" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D358" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E358" s="2" t="inlineStr"><is><t>Lek przeciwpadaczkowy – mechanizm</t></is></c><c r="F358" s="2" t="inlineStr"><is><t>Gabapentyna – nasilenie transmisji GABA</t></is></c><c r="G358" s="2" t="inlineStr"><is><t>Karbamazepina – blokokowanie kanałów sodowych</t></is></c><c r="H358" s="2" t="inlineStr"><is><t>Etosuksymid – blokowanie kanałów wapniowych</t></is></c><c r="I358" s="2" t="inlineStr" /><c r="J358" s="2" t="inlineStr" /><c r="K358" s="2" t="inlineStr"><is><t>Lamotrygina – pobudzenie synaptycznego uwalniania aminokwasów</t></is></c><c r="L358" s="2" t="inlineStr" /><c r="M358" s="2" t="inlineStr" /><c r="N358" s="2" t="inlineStr" /><c r="O358" s="2" t="inlineStr" /><c r="P358" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q358" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="359"><c r="A359" s="2" t="inlineStr"><is><t>LEKI HIPOLIPEMIZUJĄCE</t></is></c><c r="B359" s="2" t="inlineStr"><is><t>Monitorowanie</t></is></c><c r="C359" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D359" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E359" s="2" t="inlineStr"><is><t>Klozapina wymaga monitorowania Wszystkie wymagają LPP</t></is></c><c r="F359" s="2" t="inlineStr"><is><t>Morfologii</t></is></c><c r="G359" s="2" t="inlineStr"><is><t>Masy ciała</t></is></c><c r="H359" s="2" t="inlineStr"><is><t>Lipidogramu</t></is></c><c r="I359" s="2" t="inlineStr"><is><t>Glikemii</t></is></c><c r="J359" s="2" t="inlineStr" /><c r="K359" s="2" t="inlineStr" /><c r="L359" s="2" t="inlineStr" /><c r="M359" s="2" t="inlineStr" /><c r="N359" s="2" t="inlineStr" /><c r="O359" s="2" t="inlineStr" /><c r="P359" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q359" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="360"><c r="A360" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B360" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C360" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D360" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E360" s="2" t="inlineStr"><is><t>Fluoksetyna</t></is></c><c r="F360" s="2" t="inlineStr"><is><t>Hamuje wychwyt zwrotny serotoniny</t></is></c><c r="G360" s="2" t="inlineStr" /><c r="H360" s="2" t="inlineStr" /><c r="I360" s="2" t="inlineStr" /><c r="J360" s="2" t="inlineStr" /><c r="K360" s="2" t="inlineStr"><is><t>Ma istotny wpływ na układ krążenia</t></is></c><c r="L360" s="2" t="inlineStr"><is><t>Często powoduje zaparcia</t></is></c><c r="M360" s="2" t="inlineStr"><is><t>Nie działa na enzymy cytochromu P-450</t></is></c><c r="N360" s="2" t="inlineStr" /><c r="O360" s="2" t="inlineStr" /><c r="P360" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q360" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="361"><c r="A361" s="2" t="inlineStr"><is><t>LEKI PRZECIWDEPRESYJNE</t></is></c><c r="B361" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C361" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D361" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E361" s="2" t="inlineStr"><is><t>Zespoł serotoninowy – fluoksetyna i… MAO A i = 5-HT, NA, A, DA, tyramina.... MAO B i = DA i 5-HT</t></is></c><c r="F361" s="2" t="inlineStr"><is><t>Klomipramina</t></is></c><c r="G361" s="2" t="inlineStr"><is><t>Linezolid</t></is></c><c r="H361" s="2" t="inlineStr"><is><t>Wenlafaksyna</t></is></c><c r="I361" s="2" t="inlineStr"><is><t>Moklobemid</t></is></c><c r="J361" s="2" t="inlineStr" /><c r="K361" s="2" t="inlineStr" /><c r="L361" s="2" t="inlineStr" /><c r="M361" s="2" t="inlineStr" /><c r="N361" s="2" t="inlineStr" /><c r="O361" s="2" t="inlineStr" /><c r="P361" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q361" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="362"><c r="A362" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B362" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C362" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D362" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E362" s="2" t="inlineStr"><is><t>Choroba Wilsona</t></is></c><c r="F362" s="2" t="inlineStr"><is><t>Siarczan cynku</t></is></c><c r="G362" s="2" t="inlineStr"><is><t>D-penicylamina</t></is></c><c r="H362" s="2" t="inlineStr" /><c r="I362" s="2" t="inlineStr" /><c r="J362" s="2" t="inlineStr" /><c r="K362" s="2" t="inlineStr"><is><t>Ropinirol</t></is></c><c r="L362" s="2" t="inlineStr"><is><t>Siarczan magnezu</t></is></c><c r="M362" s="2" t="inlineStr" /><c r="N362" s="2" t="inlineStr" /><c r="O362" s="2" t="inlineStr" /><c r="P362" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q362" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="363"><c r="A363" s="2" t="inlineStr"><is><t>PADACZKA</t></is></c><c r="B363" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C363" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D363" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E363" s="2" t="inlineStr"><is><t>Farmakoterapia bólu neuropatycznego jakiego? :D Tako to wszystkie LPD i przeciwpadaczkowe</t></is></c><c r="F363" s="2" t="inlineStr"><is><t>Gabapentyna</t></is></c><c r="G363" s="2" t="inlineStr"><is><t>Amitryptylina</t></is></c><c r="H363" s="2" t="inlineStr"><is><t>Duloksetyna</t></is></c><c r="I363" s="2" t="inlineStr" /><c r="J363" s="2" t="inlineStr" /><c r="K363" s="2" t="inlineStr"><is><t>Ibuprofen</t></is></c><c r="L363" s="2" t="inlineStr" /><c r="M363" s="2" t="inlineStr" /><c r="N363" s="2" t="inlineStr" /><c r="O363" s="2" t="inlineStr" /><c r="P363" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q363" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="364"><c r="A364" s="2" t="inlineStr"><is><t>UKŁAD WSPÓŁCZULNY</t></is></c><c r="B364" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C364" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D364" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E364" s="2" t="inlineStr"><is><t>Profilaktyka migreny</t></is></c><c r="F364" s="2" t="inlineStr"><is><t>Metoprolol</t></is></c><c r="G364" s="2" t="inlineStr"><is><t>Flunaryzyna</t></is></c><c r="H364" s="2" t="inlineStr" /><c r="I364" s="2" t="inlineStr" /><c r="J364" s="2" t="inlineStr" /><c r="K364" s="2" t="inlineStr"><is><t>Indometacyna to w hemikranii</t></is></c><c r="L364" s="2" t="inlineStr"><is><t>Toksyna botulinowa</t></is></c><c r="M364" s="2" t="inlineStr" /><c r="N364" s="2" t="inlineStr" /><c r="O364" s="2" t="inlineStr" /><c r="P364" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q364" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="365"><c r="A365" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B365" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C365" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D365" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E365" s="2" t="inlineStr"><is><t>Alteplaza</t></is></c><c r="F365" s="2" t="inlineStr"><is><t>W udarze niedokrwiennym mózgu</t></is></c><c r="G365" s="2" t="inlineStr" /><c r="H365" s="2" t="inlineStr" /><c r="I365" s="2" t="inlineStr" /><c r="J365" s="2" t="inlineStr" /><c r="K365" s="2" t="inlineStr"><is><t>Przed planowaną kardiowersją</t></is></c><c r="L365" s="2" t="inlineStr"><is><t>W zatorowości płucnej niewysokiego ryzyka</t></is></c><c r="M365" s="2" t="inlineStr"><is><t>W TIA</t></is></c><c r="N365" s="2" t="inlineStr" /><c r="O365" s="2" t="inlineStr" /><c r="P365" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q365" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="366"><c r="A366" s="2" t="inlineStr"><is><t>LEKI HIPOLIPEMIZUJĄCE</t></is></c><c r="B366" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C366" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D366" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E366" s="2" t="inlineStr"><is><t>Profilaktyka wtórna udaru mózgu</t></is></c><c r="F366" s="2" t="inlineStr"><is><t>Dipirydamol</t></is></c><c r="G366" s="2" t="inlineStr"><is><t>Atorwastatyna</t></is></c><c r="H366" s="2" t="inlineStr"><is><t>Enoksapyrana</t></is></c><c r="I366" s="2" t="inlineStr"><is><t>Kwas acetylosalicylowy</t></is></c><c r="J366" s="2" t="inlineStr" /><c r="K366" s="2" t="inlineStr" /><c r="L366" s="2" t="inlineStr" /><c r="M366" s="2" t="inlineStr" /><c r="N366" s="2" t="inlineStr" /><c r="O366" s="2" t="inlineStr" /><c r="P366" s="2" t="inlineStr"><is><t>EGZ 2017 II termin</t></is></c><c r="Q366" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="367"><c r="A367" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B367" s="2" t="inlineStr"><is><t>Interakcje</t></is></c><c r="C367" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D367" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E367" s="2" t="inlineStr"><is><t>Azytromycyna:</t></is></c><c r="F367" s="2" t="inlineStr"><is><t>jest stosowana w nierzeżączkowym zapaleniu cewki moczowej</t></is></c><c r="G367" s="2" t="inlineStr" /><c r="H367" s="2" t="inlineStr" /><c r="I367" s="2" t="inlineStr" /><c r="J367" s="2" t="inlineStr" /><c r="K367" s="2" t="inlineStr"><is><t>jest słabo wchłaniana z przewodu pokarmowego</t></is></c><c r="L367" s="2" t="inlineStr"><is><t>ma bardzo krótki okres półtrwania</t></is></c><c r="M367" s="2" t="inlineStr"><is><t>istotnie klinicznie hamuje aktywność izoenzymu CYP3A4</t></is></c><c r="N367" s="2" t="inlineStr" /><c r="O367" s="2" t="inlineStr" /><c r="P367" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q367" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="368"><c r="A368" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B368" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C368" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D368" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E368" s="2" t="inlineStr"><is><t>Do działań niepożądanych doksycykliny zaliczamy:</t></is></c><c r="F368" s="2" t="inlineStr"><is><t>fotodermatozy</t></is></c><c r="G368" s="2" t="inlineStr"><is><t>zaburzenia czynności cewek nerkowych wywołane przez jej produkty rozpadu</t></is></c><c r="H368" s="2" t="inlineStr"><is><t>zapalenie wątroby</t></is></c><c r="I368" s="2" t="inlineStr"><is><t>zaburzenia rozwoju zębów i kości</t></is></c><c r="J368" s="2" t="inlineStr" /><c r="K368" s="2" t="inlineStr" /><c r="L368" s="2" t="inlineStr" /><c r="M368" s="2" t="inlineStr" /><c r="N368" s="2" t="inlineStr" /><c r="O368" s="2" t="inlineStr" /><c r="P368" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q368" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="369"><c r="A369" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B369" s="2" t="inlineStr"><is><t>Sposób podania</t></is></c><c r="C369" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D369" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E369" s="2" t="inlineStr"><is><t>Ceftriakson:</t></is></c><c r="F369" s="2" t="inlineStr"><is><t>należy do cefalosporyn III generacji</t></is></c><c r="G369" s="2" t="inlineStr"><is><t>może być podawany dożylnie</t></is></c><c r="H369" s="2" t="inlineStr" /><c r="I369" s="2" t="inlineStr" /><c r="J369" s="2" t="inlineStr" /><c r="K369" s="2" t="inlineStr"><is><t>wykazuje aktywność wobec MRSA</t></is></c><c r="L369" s="2" t="inlineStr"><is><t>nie wykazuje aktywności wobec Borrelia burgdorferi</t></is></c><c r="M369" s="2" t="inlineStr" /><c r="N369" s="2" t="inlineStr" /><c r="O369" s="2" t="inlineStr" /><c r="P369" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q369" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="370"><c r="A370" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B370" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C370" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D370" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E370" s="2" t="inlineStr"><is><t>Pseudomonas aeruginosa jest wrażliwy na działanie:</t></is></c><c r="F370" s="2" t="inlineStr"><is><t>kolistyny</t></is></c><c r="G370" s="2" t="inlineStr"><is><t>tobramycyn</t></is></c><c r="H370" s="2" t="inlineStr" /><c r="I370" s="2" t="inlineStr" /><c r="J370" s="2" t="inlineStr" /><c r="K370" s="2" t="inlineStr"><is><t>telawancyny</t></is></c><c r="L370" s="2" t="inlineStr"><is><t>cefazoliny</t></is></c><c r="M370" s="2" t="inlineStr" /><c r="N370" s="2" t="inlineStr" /><c r="O370" s="2" t="inlineStr" /><c r="P370" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q370" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="371"><c r="A371" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B371" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C371" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D371" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E371" s="2" t="inlineStr"><is><t>W terapii empirycznej bakteryjnego zapalenia opon mózgowo-rdzeniowych u osób dorosłych zalecane są:</t></is></c><c r="F371" s="2" t="inlineStr"><is><t>cefotaksym z wankomycyną</t></is></c><c r="G371" s="2" t="inlineStr"><is><t>ceftriakson z wankomycyną</t></is></c><c r="H371" s="2" t="inlineStr" /><c r="I371" s="2" t="inlineStr" /><c r="J371" s="2" t="inlineStr" /><c r="K371" s="2" t="inlineStr"><is><t>ampicylina z gentamycyną</t></is></c><c r="L371" s="2" t="inlineStr"><is><t>ampicylina z deksametazonem</t></is></c><c r="M371" s="2" t="inlineStr" /><c r="N371" s="2" t="inlineStr" /><c r="O371" s="2" t="inlineStr" /><c r="P371" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q371" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="372"><c r="A372" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B372" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C372" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D372" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E372" s="2" t="inlineStr"><is><t>Efekt bakteriobójczy zależny od czasu, w którym stężenie leku jest większe od MIC wykazują:</t></is></c><c r="F372" s="2" t="inlineStr"><is><t>amoksycylina z kwasem klawulanowym</t></is></c><c r="G372" s="2" t="inlineStr"><is><t>ceftriakson</t></is></c><c r="H372" s="2" t="inlineStr" /><c r="I372" s="2" t="inlineStr" /><c r="J372" s="2" t="inlineStr" /><c r="K372" s="2" t="inlineStr"><is><t>lewofloksacyna</t></is></c><c r="L372" s="2" t="inlineStr"><is><t>amikacyna</t></is></c><c r="M372" s="2" t="inlineStr" /><c r="N372" s="2" t="inlineStr" /><c r="O372" s="2" t="inlineStr" /><c r="P372" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q372" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="373"><c r="A373" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B373" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C373" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D373" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E373" s="2" t="inlineStr"><is><t>Leki przeciwdrobnoustrojowe, których mechanizm działania polega na hamowaniu biosyntezy ściany komórkowej bakterii to:</t></is></c><c r="F373" s="2" t="inlineStr"><is><t>cefadroksyl</t></is></c><c r="G373" s="2" t="inlineStr"><is><t>wankomycyna</t></is></c><c r="H373" s="2" t="inlineStr"><is><t>bacytracyna</t></is></c><c r="I373" s="2" t="inlineStr" /><c r="J373" s="2" t="inlineStr" /><c r="K373" s="2" t="inlineStr"><is><t>klindamycyna</t></is></c><c r="L373" s="2" t="inlineStr" /><c r="M373" s="2" t="inlineStr" /><c r="N373" s="2" t="inlineStr" /><c r="O373" s="2" t="inlineStr" /><c r="P373" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q373" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="374"><c r="A374" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B374" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C374" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D374" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E374" s="2" t="inlineStr"><is><t>Aktywność przeciwbakteryjną względem Legionella spp. ma:</t></is></c><c r="F374" s="2" t="inlineStr"><is><t>moksyfloksacyna</t></is></c><c r="G374" s="2" t="inlineStr"><is><t>azytromycyna</t></is></c><c r="H374" s="2" t="inlineStr"><is><t>tygecyklina</t></is></c><c r="I374" s="2" t="inlineStr" /><c r="J374" s="2" t="inlineStr" /><c r="K374" s="2" t="inlineStr"><is><t>metronidazol</t></is></c><c r="L374" s="2" t="inlineStr" /><c r="M374" s="2" t="inlineStr" /><c r="N374" s="2" t="inlineStr" /><c r="O374" s="2" t="inlineStr" /><c r="P374" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q374" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="375"><c r="A375" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B375" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C375" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D375" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E375" s="2" t="inlineStr"><is><t>Jodopowidon znalazł zastosowanie w:</t></is></c><c r="F375" s="2" t="inlineStr"><is><t>dezynfekcji skóry przed nakłuciem</t></is></c><c r="G375" s="2" t="inlineStr"><is><t>leczeniu zakażeń pochwy florą mieszaną</t></is></c><c r="H375" s="2" t="inlineStr"><is><t>profilaktyce zakażeń ran</t></is></c><c r="I375" s="2" t="inlineStr"><is><t>leczeniu zakażeń błony śluzowej jamy ustnej</t></is></c><c r="J375" s="2" t="inlineStr" /><c r="K375" s="2" t="inlineStr" /><c r="L375" s="2" t="inlineStr" /><c r="M375" s="2" t="inlineStr" /><c r="N375" s="2" t="inlineStr" /><c r="O375" s="2" t="inlineStr" /><c r="P375" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q375" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="376"><c r="A376" s="2" t="inlineStr"><is><t>LEKI PRZECIWWIRUSOWE</t></is></c><c r="B376" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C376" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D376" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E376" s="2" t="inlineStr"><is><t>Inhibitory neuraminidazy:</t></is></c><c r="F376" s="2" t="inlineStr"><is><t>hamują uwalnianie wirusów z zakażonych komórek</t></is></c><c r="G376" s="2" t="inlineStr"><is><t>można je stosować w leczeniu grypy typu A i B</t></is></c><c r="H376" s="2" t="inlineStr" /><c r="I376" s="2" t="inlineStr" /><c r="J376" s="2" t="inlineStr" /><c r="K376" s="2" t="inlineStr"><is><t>nie różnią się między sobą pod względem skuteczności i działań niepożądanych</t></is></c><c r="L376" s="2" t="inlineStr"><is><t>nie są skuteczne w profilaktyce grypy</t></is></c><c r="M376" s="2" t="inlineStr" /><c r="N376" s="2" t="inlineStr" /><c r="O376" s="2" t="inlineStr" /><c r="P376" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q376" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="377"><c r="A377" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B377" s="2" t="inlineStr"><is><t>Interakcje</t></is></c><c r="C377" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D377" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E377" s="2" t="inlineStr"><is><t>Cyprofloksacyna:</t></is></c><c r="F377" s="2" t="inlineStr"><is><t>ma efekt działania zależny od skumulowanej ekspozycji</t></is></c><c r="G377" s="2" t="inlineStr"><is><t>jest stosowana w leczeniu empirycznym niepowikłanego ostrego odmiedniczkowego zapalenia nerek</t></is></c><c r="H377" s="2" t="inlineStr"><is><t>może być podawana dożylnie</t></is></c><c r="I377" s="2" t="inlineStr" /><c r="J377" s="2" t="inlineStr" /><c r="K377" s="2" t="inlineStr"><is><t>nie wydłuża odstępu QT</t></is></c><c r="L377" s="2" t="inlineStr" /><c r="M377" s="2" t="inlineStr" /><c r="N377" s="2" t="inlineStr" /><c r="O377" s="2" t="inlineStr" /><c r="P377" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q377" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="378"><c r="A378" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B378" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C378" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D378" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E378" s="2" t="inlineStr"><is><t>Leczenie przeciwbakteryjne powinno być zlecone, jeśli w badaniu mikrobiologicznym zostanie stwierdzone:</t></is></c><c r="F378" s="2" t="inlineStr"><is><t>obecność Escherichia coli w dwóch posiewach krwi obwodowej</t></is></c><c r="G378" s="2" t="inlineStr"><is><t>brak wzrostu bakterii we krwi u osoby z klinicznymi i radiologicznymi cechami zapalenia płuc</t></is></c><c r="H378" s="2" t="inlineStr" /><c r="I378" s="2" t="inlineStr" /><c r="J378" s="2" t="inlineStr" /><c r="K378" s="2" t="inlineStr"><is><t>nosicielstwo szczepu alarmowego w przewodzie pokarmowym</t></is></c><c r="L378" s="2" t="inlineStr"><is><t>trzy gatunki bakterii w posiewie moczu</t></is></c><c r="M378" s="2" t="inlineStr" /><c r="N378" s="2" t="inlineStr" /><c r="O378" s="2" t="inlineStr" /><c r="P378" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q378" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="379"><c r="A379" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B379" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C379" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D379" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E379" s="2" t="inlineStr"><is><t>Przeciwinfekcyjna farmakoprofilaktyka medyczna jest zalecana:</t></is></c><c r="F379" s="2" t="inlineStr"><is><t>w ciężkiej neutropenii trwającej &gt; 7 dni u osób z ostrymi białaczkami</t></is></c><c r="G379" s="2" t="inlineStr"><is><t>nieszczepionym osobom z grup ryzyka ciężkiego przebiegu choroby po kontakcie z chorym na grypę</t></is></c><c r="H379" s="2" t="inlineStr" /><c r="I379" s="2" t="inlineStr" /><c r="J379" s="2" t="inlineStr" /><c r="K379" s="2" t="inlineStr"><is><t>po implantacji stentów wieńcowych przez 12 miesięcy</t></is></c><c r="L379" s="2" t="inlineStr"><is><t>podczas przewlekłego cewnikowania pęcherza moczowego</t></is></c><c r="M379" s="2" t="inlineStr" /><c r="N379" s="2" t="inlineStr" /><c r="O379" s="2" t="inlineStr" /><c r="P379" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q379" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="380"><c r="A380" s="2" t="inlineStr"><is><t>LEKI PRZECIWGRZYBICZE</t></is></c><c r="B380" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C380" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D380" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E380" s="2" t="inlineStr"><is><t>W grzybiczym zakażeniu paznokci zastosowanie ma:</t></is></c><c r="F380" s="2" t="inlineStr"><is><t>itrakonazol</t></is></c><c r="G380" s="2" t="inlineStr"><is><t>terbinafina</t></is></c><c r="H380" s="2" t="inlineStr" /><c r="I380" s="2" t="inlineStr" /><c r="J380" s="2" t="inlineStr" /><c r="K380" s="2" t="inlineStr"><is><t>natamycyna</t></is></c><c r="L380" s="2" t="inlineStr"><is><t>kaspofungina</t></is></c><c r="M380" s="2" t="inlineStr" /><c r="N380" s="2" t="inlineStr" /><c r="O380" s="2" t="inlineStr" /><c r="P380" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q380" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="381"><c r="A381" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B381" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C381" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D381" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E381" s="2" t="inlineStr"><is><t>Po ugryzieniu przez kleszcza, gdy obserwujemy rumień wędrujący, racjonalne jest zastosowanie:</t></is></c><c r="F381" s="2" t="inlineStr"><is><t>amoksycyliny</t></is></c><c r="G381" s="2" t="inlineStr"><is><t>doksycykliny</t></is></c><c r="H381" s="2" t="inlineStr"><is><t>cefuroksymu</t></is></c><c r="I381" s="2" t="inlineStr"><is><t>azytromycyny</t></is></c><c r="J381" s="2" t="inlineStr" /><c r="K381" s="2" t="inlineStr" /><c r="L381" s="2" t="inlineStr" /><c r="M381" s="2" t="inlineStr" /><c r="N381" s="2" t="inlineStr" /><c r="O381" s="2" t="inlineStr" /><c r="P381" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q381" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="382"><c r="A382" s="2" t="inlineStr"><is><t>LEKI PRZECIWWIRUSOWE</t></is></c><c r="B382" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C382" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D382" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E382" s="2" t="inlineStr"><is><t>W leczeniu zakażenia wirusem opryszczki (Herpes) stosuje się:</t></is></c><c r="F382" s="2" t="inlineStr"><is><t>foskarnet</t></is></c><c r="G382" s="2" t="inlineStr"><is><t>acyklowir</t></is></c><c r="H382" s="2" t="inlineStr" /><c r="I382" s="2" t="inlineStr" /><c r="J382" s="2" t="inlineStr" /><c r="K382" s="2" t="inlineStr"><is><t>rymantadynę</t></is></c><c r="L382" s="2" t="inlineStr"><is><t>lamiwudynę</t></is></c><c r="M382" s="2" t="inlineStr" /><c r="N382" s="2" t="inlineStr" /><c r="O382" s="2" t="inlineStr" /><c r="P382" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q382" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="383"><c r="A383" s="2" t="inlineStr"><is><t>CUKRZYCA</t></is></c><c r="B383" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C383" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D383" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E383" s="2" t="inlineStr"><is><t>Metformina:</t></is></c><c r="F383" s="2" t="inlineStr"><is><t>jest wskazana w stanie przedcukrzycowym</t></is></c><c r="G383" s="2" t="inlineStr"><is><t>zmniejsza śmiertelność w cukrzycy typu 2</t></is></c><c r="H383" s="2" t="inlineStr" /><c r="I383" s="2" t="inlineStr" /><c r="J383" s="2" t="inlineStr" /><c r="K383" s="2" t="inlineStr"><is><t>hamuje kanały potasowe zależne od ATP w komórkach B trzustki</t></is></c><c r="L383" s="2" t="inlineStr"><is><t>nie może być stosowana w skojarzeniu z insuliną</t></is></c><c r="M383" s="2" t="inlineStr" /><c r="N383" s="2" t="inlineStr" /><c r="O383" s="2" t="inlineStr" /><c r="P383" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q383" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="384"><c r="A384" s="2" t="inlineStr"><is><t>CUKRZYCA</t></is></c><c r="B384" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C384" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D384" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E384" s="2" t="inlineStr"><is><t>W leczeniu hipoglikemii stosuje się:</t></is></c><c r="F384" s="2" t="inlineStr"><is><t>węglowodany proste doustnie</t></is></c><c r="G384" s="2" t="inlineStr"><is><t>glukozę dożylnie</t></is></c><c r="H384" s="2" t="inlineStr"><is><t>węglowodany złożone doustnie</t></is></c><c r="I384" s="2" t="inlineStr" /><c r="J384" s="2" t="inlineStr" /><c r="K384" s="2" t="inlineStr"><is><t>glukagon doustnie</t></is></c><c r="L384" s="2" t="inlineStr" /><c r="M384" s="2" t="inlineStr" /><c r="N384" s="2" t="inlineStr" /><c r="O384" s="2" t="inlineStr" /><c r="P384" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q384" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="385"><c r="A385" s="2" t="inlineStr"><is><t>TARCZYCA</t></is></c><c r="B385" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C385" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D385" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E385" s="2" t="inlineStr"><is><t>Liotyronina:</t></is></c><c r="F385" s="2" t="inlineStr"><is><t>odpowiada ona naturalnemu hormonowi T3</t></is></c><c r="G385" s="2" t="inlineStr"><is><t>ma krótszy okres półtrwania niż lewotyroksyna</t></is></c><c r="H385" s="2" t="inlineStr" /><c r="I385" s="2" t="inlineStr" /><c r="J385" s="2" t="inlineStr" /><c r="K385" s="2" t="inlineStr"><is><t>jest lekiem z wyboru w niedoczynności tarczycy</t></is></c><c r="L385" s="2" t="inlineStr"><is><t>jest przeciwwskazana w leczeniu śpiączki hipometabolicznej</t></is></c><c r="M385" s="2" t="inlineStr" /><c r="N385" s="2" t="inlineStr" /><c r="O385" s="2" t="inlineStr" /><c r="P385" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q385" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="386"><c r="A386" s="2" t="inlineStr"><is><t>TARCZYCA</t></is></c><c r="B386" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C386" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D386" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E386" s="2" t="inlineStr"><is><t>Wskazaniem do zastosowania jodku potasu może być:</t></is></c><c r="F386" s="2" t="inlineStr"><is><t>ochrona tarczycy przed jodem radioaktywnym</t></is></c><c r="G386" s="2" t="inlineStr"><is><t>przygotowanie do usunięcia tarczycy</t></is></c><c r="H386" s="2" t="inlineStr"><is><t>przełom tyreotoksyczny</t></is></c><c r="I386" s="2" t="inlineStr"><is><t>zapobieganie powstawaniu wola z niedoboru jodu</t></is></c><c r="J386" s="2" t="inlineStr" /><c r="K386" s="2" t="inlineStr" /><c r="L386" s="2" t="inlineStr" /><c r="M386" s="2" t="inlineStr" /><c r="N386" s="2" t="inlineStr" /><c r="O386" s="2" t="inlineStr" /><c r="P386" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q386" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="387"><c r="A387" s="2" t="inlineStr"><is><t>LEKI HIPOLIPEMIZUJĄCE</t></is></c><c r="B387" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C387" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D387" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E387" s="2" t="inlineStr"><is><t>W leczeniu hiperprolaktynemii stosuje się:</t></is></c><c r="F387" s="2" t="inlineStr"><is><t>bromokryptynę</t></is></c><c r="G387" s="2" t="inlineStr"><is><t>karbegolinę</t></is></c><c r="H387" s="2" t="inlineStr" /><c r="I387" s="2" t="inlineStr" /><c r="J387" s="2" t="inlineStr" /><c r="K387" s="2" t="inlineStr"><is><t>somatostatynę</t></is></c><c r="L387" s="2" t="inlineStr"><is><t>terlipresynę</t></is></c><c r="M387" s="2" t="inlineStr" /><c r="N387" s="2" t="inlineStr" /><c r="O387" s="2" t="inlineStr" /><c r="P387" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q387" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="388"><c r="A388" s="2" t="inlineStr"><is><t>HORMONY PŁCIOWE</t></is></c><c r="B388" s="2" t="inlineStr"><is><t>Interakcje</t></is></c><c r="C388" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D388" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E388" s="2" t="inlineStr"><is><t>Działanie antyandrogenne wykazuje:</t></is></c><c r="F388" s="2" t="inlineStr"><is><t>octan cyproteronu</t></is></c><c r="G388" s="2" t="inlineStr"><is><t>ketokonazol</t></is></c><c r="H388" s="2" t="inlineStr"><is><t>finasteryd</t></is></c><c r="I388" s="2" t="inlineStr"><is><t>bikalutamid</t></is></c><c r="J388" s="2" t="inlineStr" /><c r="K388" s="2" t="inlineStr" /><c r="L388" s="2" t="inlineStr" /><c r="M388" s="2" t="inlineStr" /><c r="N388" s="2" t="inlineStr" /><c r="O388" s="2" t="inlineStr" /><c r="P388" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q388" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="389"><c r="A389" s="2" t="inlineStr"><is><t>GLIKOKORTYKOSTEROIDY</t></is></c><c r="B389" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C389" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D389" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E389" s="2" t="inlineStr"><is><t>Glikokortykosteroidy zwiększają:</t></is></c><c r="F389" s="2" t="inlineStr"><is><t>produkcję surfaktantu</t></is></c><c r="G389" s="2" t="inlineStr" /><c r="H389" s="2" t="inlineStr" /><c r="I389" s="2" t="inlineStr" /><c r="J389" s="2" t="inlineStr" /><c r="K389" s="2" t="inlineStr"><is><t>ekspresję genu osteokalcyny</t></is></c><c r="L389" s="2" t="inlineStr"><is><t>stężenie wapnia w surowicy krwi</t></is></c><c r="M389" s="2" t="inlineStr"><is><t>syntezę testosteronu</t></is></c><c r="N389" s="2" t="inlineStr" /><c r="O389" s="2" t="inlineStr" /><c r="P389" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q389" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="390"><c r="A390" s="2" t="inlineStr"><is><t>HORMONY PŁCIOWE</t></is></c><c r="B390" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C390" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D390" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E390" s="2" t="inlineStr"><is><t>Efektem nadmiaru gestagenów może być:</t></is></c><c r="F390" s="2" t="inlineStr"><is><t>depresja</t></is></c><c r="G390" s="2" t="inlineStr"><is><t>łojotok skóry</t></is></c><c r="H390" s="2" t="inlineStr"><is><t>przyrost masy ciała</t></is></c><c r="I390" s="2" t="inlineStr"><is><t>hirsutyzm</t></is></c><c r="J390" s="2" t="inlineStr" /><c r="K390" s="2" t="inlineStr" /><c r="L390" s="2" t="inlineStr" /><c r="M390" s="2" t="inlineStr" /><c r="N390" s="2" t="inlineStr" /><c r="O390" s="2" t="inlineStr" /><c r="P390" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q390" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="391"><c r="A391" s="2" t="inlineStr"><is><t>LEKI PRZECIWPASOŻYTNICZE</t></is></c><c r="B391" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C391" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D391" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E391" s="2" t="inlineStr"><is><t>W leczeniu wągrzycy (cysticerkozy) stosujemy:</t></is></c><c r="F391" s="2" t="inlineStr"><is><t>prazykwantel</t></is></c><c r="G391" s="2" t="inlineStr"><is><t>albendazol</t></is></c><c r="H391" s="2" t="inlineStr" /><c r="I391" s="2" t="inlineStr" /><c r="J391" s="2" t="inlineStr" /><c r="K391" s="2" t="inlineStr"><is><t>metronidazol</t></is></c><c r="L391" s="2" t="inlineStr"><is><t>iwermektynę bo</t></is></c><c r="M391" s="2" t="inlineStr" /><c r="N391" s="2" t="inlineStr" /><c r="O391" s="2" t="inlineStr" /><c r="P391" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q391" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="392"><c r="A392" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B392" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C392" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D392" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E392" s="2" t="inlineStr"><is><t>Działanie zapierające wykazuje:</t></is></c><c r="F392" s="2" t="inlineStr"><is><t>werapamil</t></is></c><c r="G392" s="2" t="inlineStr"><is><t>węglan wapnia</t></is></c><c r="H392" s="2" t="inlineStr"><is><t>odwar z suchych owoców borówki czernicy</t></is></c><c r="I392" s="2" t="inlineStr" /><c r="J392" s="2" t="inlineStr" /><c r="K392" s="2" t="inlineStr"><is><t>erytromycyna</t></is></c><c r="L392" s="2" t="inlineStr" /><c r="M392" s="2" t="inlineStr" /><c r="N392" s="2" t="inlineStr" /><c r="O392" s="2" t="inlineStr" /><c r="P392" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q392" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="393"><c r="A393" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B393" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C393" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D393" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E393" s="2" t="inlineStr"><is><t>Stosowanie kwasu acetylosalicylowego może być przyczyną:</t></is></c><c r="F393" s="2" t="inlineStr"><is><t>zaostrzenia astmy</t></is></c><c r="G393" s="2" t="inlineStr"><is><t>retencji sodu i wody</t></is></c><c r="H393" s="2" t="inlineStr"><is><t>niedokrwistości</t></is></c><c r="I393" s="2" t="inlineStr" /><c r="J393" s="2" t="inlineStr" /><c r="K393" s="2" t="inlineStr"><is><t>zakrzepicy żył głębokich</t></is></c><c r="L393" s="2" t="inlineStr" /><c r="M393" s="2" t="inlineStr" /><c r="N393" s="2" t="inlineStr" /><c r="O393" s="2" t="inlineStr" /><c r="P393" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q393" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="394"><c r="A394" s="2" t="inlineStr"><is><t>LEKI PRZECIWDEPRESYJNE</t></is></c><c r="B394" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C394" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D394" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E394" s="2" t="inlineStr"><is><t>Efekty gastrotoksyczne związane ze stosowaniem niesteroidowych leków przeciwzapalnych może nasilać:</t></is></c><c r="F394" s="2" t="inlineStr"><is><t>zolendronian</t></is></c><c r="G394" s="2" t="inlineStr"><is><t>fluoksetyna tak, SSRI też</t></is></c><c r="H394" s="2" t="inlineStr"><is><t>acenokumarol</t></is></c><c r="I394" s="2" t="inlineStr"><is><t>prednizon</t></is></c><c r="J394" s="2" t="inlineStr" /><c r="K394" s="2" t="inlineStr" /><c r="L394" s="2" t="inlineStr" /><c r="M394" s="2" t="inlineStr" /><c r="N394" s="2" t="inlineStr" /><c r="O394" s="2" t="inlineStr" /><c r="P394" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q394" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="395"><c r="A395" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B395" s="2" t="inlineStr"><is><t>Ciąża</t></is></c><c r="C395" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D395" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E395" s="2" t="inlineStr"><is><t>Zastosowanie ibuprofenu w 3 trymestrze ciąży może spowodować:</t></is></c><c r="F395" s="2" t="inlineStr"><is><t>przedwczesne zamknięcie przewodu Botalla</t></is></c><c r="G395" s="2" t="inlineStr"><is><t>zwiększone ryzyko krwawienia u matki</t></is></c><c r="H395" s="2" t="inlineStr"><is><t>zwiększone ryzyko obrzęków u matki</t></is></c><c r="I395" s="2" t="inlineStr" /><c r="J395" s="2" t="inlineStr" /><c r="K395" s="2" t="inlineStr"><is><t>zwiększenie czynności skurczowej macicy</t></is></c><c r="L395" s="2" t="inlineStr" /><c r="M395" s="2" t="inlineStr" /><c r="N395" s="2" t="inlineStr" /><c r="O395" s="2" t="inlineStr" /><c r="P395" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q395" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="396"><c r="A396" s="2" t="inlineStr"><is><t>BÓLE GŁOWY</t></is></c><c r="B396" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C396" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D396" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E396" s="2" t="inlineStr"><is><t>Napad migreny przerywa:</t></is></c><c r="F396" s="2" t="inlineStr"><is><t>winian ergotaminy</t></is></c><c r="G396" s="2" t="inlineStr"><is><t>sumatryptan</t></is></c><c r="H396" s="2" t="inlineStr"><is><t>ibuprofen</t></is></c><c r="I396" s="2" t="inlineStr" /><c r="J396" s="2" t="inlineStr" /><c r="K396" s="2" t="inlineStr"><is><t>metoklopramid</t></is></c><c r="L396" s="2" t="inlineStr" /><c r="M396" s="2" t="inlineStr" /><c r="N396" s="2" t="inlineStr" /><c r="O396" s="2" t="inlineStr" /><c r="P396" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q396" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="397"><c r="A397" s="2" t="inlineStr"><is><t>ZNIECZULENIA MIEJSCOWE</t></is></c><c r="B397" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C397" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D397" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E397" s="2" t="inlineStr"><is><t>W leczeniu neuralgii popółpaśćcowej można zastosować:</t></is></c><c r="F397" s="2" t="inlineStr"><is><t>8% kapsaicynę w kremie</t></is></c><c r="G397" s="2" t="inlineStr"><is><t>5% lidokainę w plastrach</t></is></c><c r="H397" s="2" t="inlineStr"><is><t>amitryptylinę</t></is></c><c r="I397" s="2" t="inlineStr" /><c r="J397" s="2" t="inlineStr" /><c r="K397" s="2" t="inlineStr"><is><t>metamizol</t></is></c><c r="L397" s="2" t="inlineStr" /><c r="M397" s="2" t="inlineStr" /><c r="N397" s="2" t="inlineStr" /><c r="O397" s="2" t="inlineStr" /><c r="P397" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q397" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="398"><c r="A398" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B398" s="2" t="inlineStr"><is><t>Przeciwwskazania</t></is></c><c r="C398" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D398" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E398" s="2" t="inlineStr"><is><t>Loperamid:</t></is></c><c r="F398" s="2" t="inlineStr"><is><t>w dawkach terapeutycznych nie działa ośrodkowo</t></is></c><c r="G398" s="2" t="inlineStr"><is><t>jest przeciwwskazany we wrzodziejącym zapaleniu jelita grubego</t></is></c><c r="H398" s="2" t="inlineStr" /><c r="I398" s="2" t="inlineStr" /><c r="J398" s="2" t="inlineStr" /><c r="K398" s="2" t="inlineStr"><is><t>jest agonistą receptorów serotoninowych w jelicie</t></is></c><c r="L398" s="2" t="inlineStr"><is><t>wykazuje działanie przeciwbólowe</t></is></c><c r="M398" s="2" t="inlineStr" /><c r="N398" s="2" t="inlineStr" /><c r="O398" s="2" t="inlineStr" /><c r="P398" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q398" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="399"><c r="A399" s="2" t="inlineStr"><is><t>NARKOTYCZNE LEKI PRZECIWBÓLOWE</t></is></c><c r="B399" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C399" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D399" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E399" s="2" t="inlineStr"><is><t>Fentanyl:</t></is></c><c r="F399" s="2" t="inlineStr"><is><t>hamuje ośrodek oddechowy</t></is></c><c r="G399" s="2" t="inlineStr" /><c r="H399" s="2" t="inlineStr" /><c r="I399" s="2" t="inlineStr" /><c r="J399" s="2" t="inlineStr" /><c r="K399" s="2" t="inlineStr"><is><t>działa neurotoksycznie</t></is></c><c r="L399" s="2" t="inlineStr"><is><t>ma aktywne metabolity</t></is></c><c r="M399" s="2" t="inlineStr"><is><t>uwalnia histaminę</t></is></c><c r="N399" s="2" t="inlineStr" /><c r="O399" s="2" t="inlineStr" /><c r="P399" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q399" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="400"><c r="A400" s="2" t="inlineStr"><is><t>NIEOPIOIDOWE LEKI PRZECIWBÓLOWE</t></is></c><c r="B400" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C400" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D400" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E400" s="2" t="inlineStr"><is><t>Nefopam</t></is></c><c r="F400" s="2" t="inlineStr"><is><t>jest inhibitorem wychwytu zwrotnego serotoniny i noradrenaliny</t></is></c><c r="G400" s="2" t="inlineStr"><is><t>u osób starszych może wywoływać omamy</t></is></c><c r="H400" s="2" t="inlineStr" /><c r="I400" s="2" t="inlineStr" /><c r="J400" s="2" t="inlineStr" /><c r="K400" s="2" t="inlineStr"><is><t>hamuje wybiórczo cyklooksygenazę typu 2</t></is></c><c r="L400" s="2" t="inlineStr"><is><t>u dzieci może być stosowany w profilaktyce drgawek gorączkowych</t></is></c><c r="M400" s="2" t="inlineStr" /><c r="N400" s="2" t="inlineStr" /><c r="O400" s="2" t="inlineStr" /><c r="P400" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q400" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="401"><c r="A401" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B401" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C401" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D401" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E401" s="2" t="inlineStr"><is><t>W zespole abstynencyjnym w uzależnieniu od opioidów występują:</t></is></c><c r="F401" s="2" t="inlineStr"><is><t>rozszerzenie źrenic</t></is></c><c r="G401" s="2" t="inlineStr"><is><t>wymioty i biegunka</t></is></c><c r="H401" s="2" t="inlineStr"><is><t>bezsenność</t></is></c><c r="I401" s="2" t="inlineStr"><is><t>łzawienie i wyciek z nosa</t></is></c><c r="J401" s="2" t="inlineStr" /><c r="K401" s="2" t="inlineStr" /><c r="L401" s="2" t="inlineStr" /><c r="M401" s="2" t="inlineStr" /><c r="N401" s="2" t="inlineStr" /><c r="O401" s="2" t="inlineStr" /><c r="P401" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q401" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="402"><c r="A402" s="2" t="inlineStr"><is><t>CUKRZYCA</t></is></c><c r="B402" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C402" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D402" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E402" s="2" t="inlineStr"><is><t>Redukcję masy ciała może powodować stosowanie:</t></is></c><c r="F402" s="2" t="inlineStr"><is><t>fluoksetyny</t></is></c><c r="G402" s="2" t="inlineStr"><is><t>metforminy</t></is></c><c r="H402" s="2" t="inlineStr"><is><t>liraglutydu</t></is></c><c r="I402" s="2" t="inlineStr" /><c r="J402" s="2" t="inlineStr" /><c r="K402" s="2" t="inlineStr"><is><t>insuliny</t></is></c><c r="L402" s="2" t="inlineStr" /><c r="M402" s="2" t="inlineStr" /><c r="N402" s="2" t="inlineStr" /><c r="O402" s="2" t="inlineStr" /><c r="P402" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q402" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="403"><c r="A403" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B403" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C403" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D403" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E403" s="2" t="inlineStr"><is><t>W udarze niedokrwiennym mózgu możesz zastosować tkankowy aktywator plazminogenu jeśli stwierdzisz, że pacjent:</t></is></c><c r="F403" s="2" t="inlineStr"><is><t>doustne leczenie przeciwkrzepliwe (INR=1.5)</t></is></c><c r="G403" s="2" t="inlineStr"><is><t>ma wartości ciśnienia tętniczego: SBP ≤ 185 mm Hg lub DBP ≤ 110 mm Hg</t></is></c><c r="H403" s="2" t="inlineStr"><is><t>ma czas od wystąpienia objawów udaru mózgu nie przekraczający 4.5h</t></is></c><c r="I403" s="2" t="inlineStr" /><c r="J403" s="2" t="inlineStr" /><c r="K403" s="2" t="inlineStr"><is><t>jest w podeszłym wieku (&gt; 80 lat)</t></is></c><c r="L403" s="2" t="inlineStr" /><c r="M403" s="2" t="inlineStr" /><c r="N403" s="2" t="inlineStr" /><c r="O403" s="2" t="inlineStr" /><c r="P403" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q403" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="404"><c r="A404" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B404" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C404" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D404" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E404" s="2" t="inlineStr"><is><t>U 76 letniej kobiety z napadowym migotaniem przedsionków, cukrzycą i nadciśnieniem tętniczym (Cha2DS2VASc = 5 pkt) i niskim ryzykiem krwawienia (HAS-BLED = 2 pkt) wskazane w przewlekłej profilaktyce są:</t></is></c><c r="F404" s="2" t="inlineStr"><is><t>warfaryna</t></is></c><c r="G404" s="2" t="inlineStr"><is><t>eteksylan dabigatranu</t></is></c><c r="H404" s="2" t="inlineStr" /><c r="I404" s="2" t="inlineStr" /><c r="J404" s="2" t="inlineStr" /><c r="K404" s="2" t="inlineStr"><is><t>kwas acetylosalicylowy</t></is></c><c r="L404" s="2" t="inlineStr"><is><t>fondaparynuks</t></is></c><c r="M404" s="2" t="inlineStr" /><c r="N404" s="2" t="inlineStr" /><c r="O404" s="2" t="inlineStr" /><c r="P404" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q404" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="405"><c r="A405" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B405" s="2" t="inlineStr"><is><t>Ciąża</t></is></c><c r="C405" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D405" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E405" s="2" t="inlineStr"><is><t>Rywaroksaban:</t></is></c><c r="F405" s="2" t="inlineStr"><is><t>wymaga redukcji dawki w niewydolności nerek</t></is></c><c r="G405" s="2" t="inlineStr" /><c r="H405" s="2" t="inlineStr" /><c r="I405" s="2" t="inlineStr" /><c r="J405" s="2" t="inlineStr" /><c r="K405" s="2" t="inlineStr"><is><t>odwracalnie blokuje receptor GP IIb/IIIa</t></is></c><c r="L405" s="2" t="inlineStr"><is><t>występuje w postaci proleku</t></is></c><c r="M405" s="2" t="inlineStr"><is><t>jest stosowany w profilaktyce choroby zakrzepowo-zatorowej w czasie ciąży</t></is></c><c r="N405" s="2" t="inlineStr" /><c r="O405" s="2" t="inlineStr" /><c r="P405" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q405" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="406"><c r="A406" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B406" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C406" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D406" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E406" s="2" t="inlineStr"><is><t>Do leków działających na receptor P2Y12 zaliczamy:</t></is></c><c r="F406" s="2" t="inlineStr"><is><t>prasugrel</t></is></c><c r="G406" s="2" t="inlineStr" /><c r="H406" s="2" t="inlineStr" /><c r="I406" s="2" t="inlineStr" /><c r="J406" s="2" t="inlineStr" /><c r="K406" s="2" t="inlineStr"><is><t>apiksaban</t></is></c><c r="L406" s="2" t="inlineStr"><is><t>worapaksar</t></is></c><c r="M406" s="2" t="inlineStr"><is><t>dypirydamol</t></is></c><c r="N406" s="2" t="inlineStr" /><c r="O406" s="2" t="inlineStr" /><c r="P406" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q406" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="407"><c r="A407" s="2" t="inlineStr"><is><t>LEKI HIPOLIPEMIZUJĄCE</t></is></c><c r="B407" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C407" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D407" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E407" s="2" t="inlineStr"><is><t>Do częstych działań niepożądanych atorwastatyny należy:</t></is></c><c r="F407" s="2" t="inlineStr"><is><t>uszkodzenie wątroby</t></is></c><c r="G407" s="2" t="inlineStr" /><c r="H407" s="2" t="inlineStr" /><c r="I407" s="2" t="inlineStr" /><c r="J407" s="2" t="inlineStr" /><c r="K407" s="2" t="inlineStr"><is><t>rogowacenie ciemne</t></is></c><c r="L407" s="2" t="inlineStr"><is><t>miopatia</t></is></c><c r="M407" s="2" t="inlineStr"><is><t>uderzenia gorąca</t></is></c><c r="N407" s="2" t="inlineStr" /><c r="O407" s="2" t="inlineStr" /><c r="P407" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q407" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="408"><c r="A408" s="2" t="inlineStr"><is><t>FARMAKOKINETYKA</t></is></c><c r="B408" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C408" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D408" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E408" s="2" t="inlineStr"><is><t>Orlistat:</t></is></c><c r="F408" s="2" t="inlineStr"><is><t>może być przyczyną wystąpienia tłuszczowych stolców</t></is></c><c r="G408" s="2" t="inlineStr"><is><t>może być stosowany u osób z chorobami układu krążenia</t></is></c><c r="H408" s="2" t="inlineStr" /><c r="I408" s="2" t="inlineStr" /><c r="J408" s="2" t="inlineStr" /><c r="K408" s="2" t="inlineStr"><is><t>ma wysoką biodostępność po podaniu doustnym</t></is></c><c r="L408" s="2" t="inlineStr"><is><t>zwiększa wchłanianie witaminy D</t></is></c><c r="M408" s="2" t="inlineStr" /><c r="N408" s="2" t="inlineStr" /><c r="O408" s="2" t="inlineStr" /><c r="P408" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q408" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="409"><c r="A409" s="2" t="inlineStr"><is><t>NADCIŚNIENIE TĘTNICZE</t></is></c><c r="B409" s="2" t="inlineStr"><is><t>Farmakokinetyka</t></is></c><c r="C409" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D409" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E409" s="2" t="inlineStr"><is><t>Wybierz właściwe zestawienia lek prekursorowy – jego aktywny metabolit:</t></is></c><c r="F409" s="2" t="inlineStr"><is><t>cileksetyl kandesartanu → kandesartan</t></is></c><c r="G409" s="2" t="inlineStr" /><c r="H409" s="2" t="inlineStr" /><c r="I409" s="2" t="inlineStr" /><c r="J409" s="2" t="inlineStr" /><c r="K409" s="2" t="inlineStr"><is><t>eplerenon → kanrenon</t></is></c><c r="L409" s="2" t="inlineStr"><is><t>lizynopryl → lizynoprylat</t></is></c><c r="M409" s="2" t="inlineStr"><is><t>nebiwolol → tlenek azotu</t></is></c><c r="N409" s="2" t="inlineStr" /><c r="O409" s="2" t="inlineStr" /><c r="P409" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q409" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="410"><c r="A410" s="2" t="inlineStr"><is><t>LEKI MOCZOPĘDNE</t></is></c><c r="B410" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C410" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D410" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E410" s="2" t="inlineStr"><is><t>Torasemid w przeciwieństwie do furosemidu nie powoduje:</t></is></c><c r="F410" s="2" t="inlineStr"><is><t>retencji sodu po efekcie natiuretycznym przy podaniu 1 x 24 h</t></is></c><c r="G410" s="2" t="inlineStr" /><c r="H410" s="2" t="inlineStr" /><c r="I410" s="2" t="inlineStr" /><c r="J410" s="2" t="inlineStr" /><c r="K410" s="2" t="inlineStr"><is><t>efektu natiuretycznego po podaniu doustnym</t></is></c><c r="L410" s="2" t="inlineStr"><is><t>reakcji alergicznych w nadwrażliwości na związki sulfonamidowe</t></is></c><c r="M410" s="2" t="inlineStr"><is><t>hiperkalcemii</t></is></c><c r="N410" s="2" t="inlineStr" /><c r="O410" s="2" t="inlineStr" /><c r="P410" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q410" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="411"><c r="A411" s="2" t="inlineStr"><is><t>NADCIŚNIENIE TĘTNICZE</t></is></c><c r="B411" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C411" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D411" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E411" s="2" t="inlineStr"><is><t>Hiponatremię z dużym stężeniem Na+ w moczu (&gt; 20 mmol/l) może spowodować:</t></is></c><c r="F411" s="2" t="inlineStr"><is><t>karbamazepina</t></is></c><c r="G411" s="2" t="inlineStr"><is><t>fluoksetyna</t></is></c><c r="H411" s="2" t="inlineStr"><is><t>indapamid</t></is></c><c r="I411" s="2" t="inlineStr" /><c r="J411" s="2" t="inlineStr" /><c r="K411" s="2" t="inlineStr"><is><t>prednizon</t></is></c><c r="L411" s="2" t="inlineStr" /><c r="M411" s="2" t="inlineStr" /><c r="N411" s="2" t="inlineStr" /><c r="O411" s="2" t="inlineStr" /><c r="P411" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q411" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="412"><c r="A412" s="2" t="inlineStr"><is><t>LEKI IMMUNOSUPRESYJNE</t></is></c><c r="B412" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C412" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D412" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E412" s="2" t="inlineStr"><is><t>Wskaż prawidłowe połączenie lek-wskazanie:</t></is></c><c r="F412" s="2" t="inlineStr"><is><t>omalizumab – astma</t></is></c><c r="G412" s="2" t="inlineStr"><is><t>denosumab – osteoporoza</t></is></c><c r="H412" s="2" t="inlineStr" /><c r="I412" s="2" t="inlineStr" /><c r="J412" s="2" t="inlineStr" /><c r="K412" s="2" t="inlineStr"><is><t>natalizumab – reumatoidalne zapalenie stawów</t></is></c><c r="L412" s="2" t="inlineStr"><is><t>infliksymab – stwardnienie rozsiane</t></is></c><c r="M412" s="2" t="inlineStr" /><c r="N412" s="2" t="inlineStr" /><c r="O412" s="2" t="inlineStr" /><c r="P412" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q412" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="413"><c r="A413" s="2" t="inlineStr"><is><t>FARMAKOKINETYKA</t></is></c><c r="B413" s="2" t="inlineStr"><is><t>Farmakokinetyka</t></is></c><c r="C413" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D413" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E413" s="2" t="inlineStr"><is><t>Jeśli wartość AUC leku oceniona w badaniach przedklinicznych jest większa po podaniu dożylnym niż po podaniu doustnym, to oznacza, że:</t></is></c><c r="F413" s="2" t="inlineStr"><is><t>brak jest wystarczających danych do określenia przyczyny mniejszej wartości AUC leku po podaniu p.o</t></is></c><c r="G413" s="2" t="inlineStr"><is><t>biodostępność leku po podaniu i.v. jest większa niż po podaniu p.o</t></is></c><c r="H413" s="2" t="inlineStr" /><c r="I413" s="2" t="inlineStr" /><c r="J413" s="2" t="inlineStr" /><c r="K413" s="2" t="inlineStr"><is><t>AUC leku ocenione w badaniach klinicznych będzie podobne</t></is></c><c r="L413" s="2" t="inlineStr"><is><t>lek powinien być stosowany na czczo</t></is></c><c r="M413" s="2" t="inlineStr" /><c r="N413" s="2" t="inlineStr" /><c r="O413" s="2" t="inlineStr" /><c r="P413" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q413" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="414"><c r="A414" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B414" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C414" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D414" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E414" s="2" t="inlineStr"><is><t>Daptomycyna ma dwukompartmentowy model rozmieszczenia w organizmie (t 1/2 α= 7 min i t 1/2β = 5 h). Na tej podstawie uzasadniony jest następujący wniosek:</t></is></c><c r="F414" s="2" t="inlineStr"><is><t>po szybkiej fazie dystrybucji następuje wolniejsza faza eliminacji</t></is></c><c r="G414" s="2" t="inlineStr"><is><t>występuje utrudnienie w redystrybucji leku z tkanek do krążenia ogólnego</t></is></c><c r="H414" s="2" t="inlineStr" /><c r="I414" s="2" t="inlineStr" /><c r="J414" s="2" t="inlineStr" /><c r="K414" s="2" t="inlineStr"><is><t>lek wchłania się na dużej długości przewodu pokarmowego</t></is></c><c r="L414" s="2" t="inlineStr"><is><t>lek rozmieszcza się głównie w obszarach hydrofilnych</t></is></c><c r="M414" s="2" t="inlineStr" /><c r="N414" s="2" t="inlineStr" /><c r="O414" s="2" t="inlineStr" /><c r="P414" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q414" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="415"><c r="A415" s="2" t="inlineStr"><is><t>UKŁAD ODDECHOWY</t></is></c><c r="B415" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C415" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D415" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E415" s="2" t="inlineStr"><is><t>W terapii POChP u osób o niewielkim ryzyku i nasilonych objawach (kategoria B) stosuje się:</t></is></c><c r="F415" s="2" t="inlineStr"><is><t>salmeterol</t></is></c><c r="G415" s="2" t="inlineStr"><is><t>bromek aklidynium</t></is></c><c r="H415" s="2" t="inlineStr" /><c r="I415" s="2" t="inlineStr" /><c r="J415" s="2" t="inlineStr" /><c r="K415" s="2" t="inlineStr"><is><t>wziewne glikokortykosteroidy</t></is></c><c r="L415" s="2" t="inlineStr"><is><t>roflumilast</t></is></c><c r="M415" s="2" t="inlineStr" /><c r="N415" s="2" t="inlineStr" /><c r="O415" s="2" t="inlineStr" /><c r="P415" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q415" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="416"><c r="A416" s="2" t="inlineStr"><is><t>UKŁAD ODDECHOWY</t></is></c><c r="B416" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C416" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D416" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E416" s="2" t="inlineStr"><is><t>Działanie wykrztuśne ma:</t></is></c><c r="F416" s="2" t="inlineStr"><is><t>wyciąg z prawoślazu lekarskiego</t></is></c><c r="G416" s="2" t="inlineStr"><is><t>gwajafenazyna</t></is></c><c r="H416" s="2" t="inlineStr" /><c r="I416" s="2" t="inlineStr" /><c r="J416" s="2" t="inlineStr" /><c r="K416" s="2" t="inlineStr"><is><t>oksykodon</t></is></c><c r="L416" s="2" t="inlineStr"><is><t>mesna</t></is></c><c r="M416" s="2" t="inlineStr" /><c r="N416" s="2" t="inlineStr" /><c r="O416" s="2" t="inlineStr" /><c r="P416" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q416" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="417"><c r="A417" s="2" t="inlineStr"><is><t>UKŁAD WSPÓŁCZULNY</t></is></c><c r="B417" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C417" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D417" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E417" s="2" t="inlineStr"><is><t>Indakaterol:</t></is></c><c r="F417" s="2" t="inlineStr"><is><t>zwiększa aktywność ruchową rzęsek</t></is></c><c r="G417" s="2" t="inlineStr"><is><t>wykazuje synergizm działania z glikokortykosteroidami</t></is></c><c r="H417" s="2" t="inlineStr" /><c r="I417" s="2" t="inlineStr" /><c r="J417" s="2" t="inlineStr" /><c r="K417" s="2" t="inlineStr"><is><t>jest beta-adrenomimetykiem wziewnym o krótkim czasie działania (SABA)</t></is></c><c r="L417" s="2" t="inlineStr"><is><t>rozszczepia wiązania disiarczkowe w glikoproteinach śluzu</t></is></c><c r="M417" s="2" t="inlineStr" /><c r="N417" s="2" t="inlineStr" /><c r="O417" s="2" t="inlineStr" /><c r="P417" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q417" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="418"><c r="A418" s="2" t="inlineStr"><is><t>CHOROBA NIEDOKRWIENNA SERCA</t></is></c><c r="B418" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C418" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D418" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E418" s="2" t="inlineStr"><is><t>Meta-analiza badań klinicznych:</t></is></c><c r="F418" s="2" t="inlineStr"><is><t>jest uzupełnieniem przeglądu systematycznego</t></is></c><c r="G418" s="2" t="inlineStr"><is><t>może przynieść zupełnie nowe - odmienne wyniki niż badania, na których jest oparta</t></is></c><c r="H418" s="2" t="inlineStr"><is><t>pozwala zwiększyć precyzję oszacowania efektu klinicznego</t></is></c><c r="I418" s="2" t="inlineStr"><is><t>charakteryzuje się heterogenicznością statystyczną, która istotnie wpływa na interpretację wyników</t></is></c><c r="J418" s="2" t="inlineStr" /><c r="K418" s="2" t="inlineStr" /><c r="L418" s="2" t="inlineStr" /><c r="M418" s="2" t="inlineStr" /><c r="N418" s="2" t="inlineStr" /><c r="O418" s="2" t="inlineStr" /><c r="P418" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q418" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="419"><c r="A419" s="2" t="inlineStr"><is><t>LEKI PRZECIWWIRUSOWE</t></is></c><c r="B419" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C419" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D419" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E419" s="2" t="inlineStr"><is><t>Mieloidalne czynniki wzrostu (G-CSF oraz GM-CSF) znalazły zastosowanie u pacjentów:</t></is></c><c r="F419" s="2" t="inlineStr"><is><t>z ciężką przewlekłą neutropenią</t></is></c><c r="G419" s="2" t="inlineStr"><is><t>po przeszczepieniu komórek macierzystych szpiku kostnego</t></is></c><c r="H419" s="2" t="inlineStr" /><c r="I419" s="2" t="inlineStr" /><c r="J419" s="2" t="inlineStr" /><c r="K419" s="2" t="inlineStr"><is><t>zakażonych wirusem HIV</t></is></c><c r="L419" s="2" t="inlineStr"><is><t>z idiopatyczną plamicą małopłytkową</t></is></c><c r="M419" s="2" t="inlineStr" /><c r="N419" s="2" t="inlineStr" /><c r="O419" s="2" t="inlineStr" /><c r="P419" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q419" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="420"><c r="A420" s="2" t="inlineStr"><is><t>LEKI PRZECIWPASOŻYTNICZE</t></is></c><c r="B420" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C420" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D420" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E420" s="2" t="inlineStr"><is><t>Które stwierdzenie dotyczące profilaktyki malarii jest prawdziwe?</t></is></c><c r="F420" s="2" t="inlineStr"><is><t>dla większości leków standardowy czas rozpoczynania stosowania leku w profilaktyce wynosi tydzień przed planowaną podróżą</t></is></c><c r="G420" s="2" t="inlineStr"><is><t>nie dysponujemy uniwersalnym lekiem stosowanym w profilaktyce</t></is></c><c r="H420" s="2" t="inlineStr"><is><t>profilaktyka farmakologiczna stanowi uzupełnienie profilaktyki barierowej (odpowiednie ubrania, moskitiery i siatki nasączone DEET)</t></is></c><c r="I420" s="2" t="inlineStr" /><c r="J420" s="2" t="inlineStr" /><c r="K420" s="2" t="inlineStr"><is><t>leki stosuje się profilaktycznie tylko przez tydzień w czasie pobytu na terenie endemicznym</t></is></c><c r="L420" s="2" t="inlineStr" /><c r="M420" s="2" t="inlineStr" /><c r="N420" s="2" t="inlineStr" /><c r="O420" s="2" t="inlineStr" /><c r="P420" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q420" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="421"><c r="A421" s="2" t="inlineStr"><is><t>FARMAKOLOGIA OGÓLNA I EBM</t></is></c><c r="B421" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C421" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D421" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E421" s="2" t="inlineStr"><is><t>Przeprowadzenie eksperymentu leczniczego:</t></is></c><c r="F421" s="2" t="inlineStr"><is><t>jest możliwe, jeśli dostępne metody leczenia okazały się nieskuteczne</t></is></c><c r="G421" s="2" t="inlineStr"><is><t>wymaga świadomej zgody pacjenta</t></is></c><c r="H421" s="2" t="inlineStr" /><c r="I421" s="2" t="inlineStr" /><c r="J421" s="2" t="inlineStr" /><c r="K421" s="2" t="inlineStr"><is><t>ma na celu głównie poszerzenie wiedzy medycznej</t></is></c><c r="L421" s="2" t="inlineStr"><is><t>nie wymaga pozytywnej opinii Komisji Bioetycznej</t></is></c><c r="M421" s="2" t="inlineStr" /><c r="N421" s="2" t="inlineStr" /><c r="O421" s="2" t="inlineStr" /><c r="P421" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q421" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="422"><c r="A422" s="2" t="inlineStr"><is><t>LEKI ROŚLINNE I SUPLEMENTY</t></is></c><c r="B422" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C422" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D422" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E422" s="2" t="inlineStr"><is><t>W leczeniu niedokrwistości megaloblastycznej zastosowanie ma:</t></is></c><c r="F422" s="2" t="inlineStr"><is><t>cyjanokobalamina</t></is></c><c r="G422" s="2" t="inlineStr"><is><t>kwas foliowy</t></is></c><c r="H422" s="2" t="inlineStr" /><c r="I422" s="2" t="inlineStr" /><c r="J422" s="2" t="inlineStr" /><c r="K422" s="2" t="inlineStr"><is><t>siarczan żelaza</t></is></c><c r="L422" s="2" t="inlineStr"><is><t>erytropoetyna</t></is></c><c r="M422" s="2" t="inlineStr" /><c r="N422" s="2" t="inlineStr" /><c r="O422" s="2" t="inlineStr" /><c r="P422" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q422" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="423"><c r="A423" s="2" t="inlineStr"><is><t>NARKOTYCZNE LEKI PRZECIWBÓLOWE</t></is></c><c r="B423" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C423" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D423" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E423" s="2" t="inlineStr"><is><t>Preparat złożony naltreksonu z bupropionem:</t></is></c><c r="F423" s="2" t="inlineStr"><is><t>istotnie obniża masę ciała w porównaniu z placebo</t></is></c><c r="G423" s="2" t="inlineStr"><is><t>jest zarejestrowany w Europie do leczenia otyłości</t></is></c><c r="H423" s="2" t="inlineStr"><is><t>sprzyja pojawianiu się myśli samobójczych</t></is></c><c r="I423" s="2" t="inlineStr"><is><t>działa antagonistycznie na receptory 5HT2c</t></is></c><c r="J423" s="2" t="inlineStr" /><c r="K423" s="2" t="inlineStr" /><c r="L423" s="2" t="inlineStr" /><c r="M423" s="2" t="inlineStr" /><c r="N423" s="2" t="inlineStr" /><c r="O423" s="2" t="inlineStr" /><c r="P423" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q423" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="424"><c r="A424" s="2" t="inlineStr"><is><t>LEKI PRZECIWDEPRESYJNE</t></is></c><c r="B424" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C424" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D424" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E424" s="2" t="inlineStr"><is><t>W leczeniu uzależnienia od nikotyny wykazano skuteczność:</t></is></c><c r="F424" s="2" t="inlineStr"><is><t>warenikliny</t></is></c><c r="G424" s="2" t="inlineStr"><is><t>cytyzyny</t></is></c><c r="H424" s="2" t="inlineStr"><is><t>nikotynowej terapii zastępczej</t></is></c><c r="I424" s="2" t="inlineStr" /><c r="J424" s="2" t="inlineStr" /><c r="K424" s="2" t="inlineStr"><is><t>benzodiazepin</t></is></c><c r="L424" s="2" t="inlineStr" /><c r="M424" s="2" t="inlineStr" /><c r="N424" s="2" t="inlineStr" /><c r="O424" s="2" t="inlineStr" /><c r="P424" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q424" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="425"><c r="A425" s="2" t="inlineStr"><is><t>FARMAKOLOGIA OGÓLNA I EBM</t></is></c><c r="B425" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C425" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D425" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E425" s="2" t="inlineStr"><is><t>Elementami nadzoru nad bezpieczeństwem farmakoterapii jest:</t></is></c><c r="F425" s="2" t="inlineStr"><is><t>plan Zarządzania Ryzykiem</t></is></c><c r="G425" s="2" t="inlineStr"><is><t>strona internetowa Urzędu Rejestracji Produktów Leczniczych, Wyrobów Medycznych i Produktów Biobójczych</t></is></c><c r="H425" s="2" t="inlineStr"><is><t>raport PSUR</t></is></c><c r="I425" s="2" t="inlineStr"><is><t>baza zarejestrowanych produktów leczniczych prowadzona przez Europejską Agencję Leków</t></is></c><c r="J425" s="2" t="inlineStr" /><c r="K425" s="2" t="inlineStr" /><c r="L425" s="2" t="inlineStr" /><c r="M425" s="2" t="inlineStr" /><c r="N425" s="2" t="inlineStr" /><c r="O425" s="2" t="inlineStr" /><c r="P425" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q425" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="426"><c r="A426" s="2" t="inlineStr"><is><t>LEKI ROŚLINNE I SUPLEMENTY</t></is></c><c r="B426" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C426" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D426" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E426" s="2" t="inlineStr"><is><t>URPL - Urząd Rejestracji Produktów Leczniczych, Wyrobów Medycznych i Produktów Biobójczych ocenia działania niepożądane zarejestrowanych:</t></is></c><c r="F426" s="2" t="inlineStr"><is><t>leków homeopatycznych</t></is></c><c r="G426" s="2" t="inlineStr"><is><t>leków dostępnych bez recepty</t></is></c><c r="H426" s="2" t="inlineStr"><is><t>leków pochodzenia roślinnego</t></is></c><c r="I426" s="2" t="inlineStr" /><c r="J426" s="2" t="inlineStr" /><c r="K426" s="2" t="inlineStr"><is><t>suplementów diety</t></is></c><c r="L426" s="2" t="inlineStr" /><c r="M426" s="2" t="inlineStr" /><c r="N426" s="2" t="inlineStr" /><c r="O426" s="2" t="inlineStr" /><c r="P426" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q426" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="427"><c r="A427" s="2" t="inlineStr"><is><t>LEKI PRZECIWNOWOTWOROWE</t></is></c><c r="B427" s="2" t="inlineStr"><is><t>Ciąża</t></is></c><c r="C427" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D427" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E427" s="2" t="inlineStr"><is><t>Teratogenem człowieka o udokumentowanym działaniu jest:</t></is></c><c r="F427" s="2" t="inlineStr"><is><t>metotreksat</t></is></c><c r="G427" s="2" t="inlineStr"><is><t>kwas walproinowy</t></is></c><c r="H427" s="2" t="inlineStr"><is><t>lit</t></is></c><c r="I427" s="2" t="inlineStr" /><c r="J427" s="2" t="inlineStr" /><c r="K427" s="2" t="inlineStr"><is><t>tiamazol tiamazol ma kategorię D</t></is></c><c r="L427" s="2" t="inlineStr" /><c r="M427" s="2" t="inlineStr" /><c r="N427" s="2" t="inlineStr" /><c r="O427" s="2" t="inlineStr" /><c r="P427" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q427" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="428"><c r="A428" s="2" t="inlineStr"><is><t>LEKI PRZECIWWIRUSOWE</t></is></c><c r="B428" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C428" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D428" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E428" s="2" t="inlineStr"><is><t>Alfakalcydol:</t></is></c><c r="F428" s="2" t="inlineStr"><is><t>koryguje zaburzenia wapniowe w przewlekłej chorobie nerek</t></is></c><c r="G428" s="2" t="inlineStr"><is><t>koryguje zaburzenia wapniowe w niedoczynności przytarczyc</t></is></c><c r="H428" s="2" t="inlineStr"><is><t>zmniejsza ryzyko osteoporotycznych złamań kości</t></is></c><c r="I428" s="2" t="inlineStr" /><c r="J428" s="2" t="inlineStr" /><c r="K428" s="2" t="inlineStr"><is><t>chroni przed chorobami wirusowymi</t></is></c><c r="L428" s="2" t="inlineStr" /><c r="M428" s="2" t="inlineStr" /><c r="N428" s="2" t="inlineStr" /><c r="O428" s="2" t="inlineStr" /><c r="P428" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q428" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="429"><c r="A429" s="2" t="inlineStr"><is><t>LEKI MOCZOPĘDNE</t></is></c><c r="B429" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C429" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D429" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E429" s="2" t="inlineStr"><is><t>Wskaż prawdziwe stwierdzenie:</t></is></c><c r="F429" s="2" t="inlineStr"><is><t>5% roztwór glukozy jest izotoniczny in vitro i hipotoniczny in vivo</t></is></c><c r="G429" s="2" t="inlineStr"><is><t>15% roztwór mannitolu jest hipertonicznym płynem stosowanym do leczenia obrzęku mózgu</t></is></c><c r="H429" s="2" t="inlineStr" /><c r="I429" s="2" t="inlineStr" /><c r="J429" s="2" t="inlineStr" /><c r="K429" s="2" t="inlineStr"><is><t>stosowanie roztworów hipotonicznych grozi dehydratacją komórek i plazmolizą</t></is></c><c r="L429" s="2" t="inlineStr"><is><t>stosowanie roztworów hipertonicznych grozi obrzękiem komórek i ich lizą</t></is></c><c r="M429" s="2" t="inlineStr" /><c r="N429" s="2" t="inlineStr" /><c r="O429" s="2" t="inlineStr" /><c r="P429" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q429" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="430"><c r="A430" s="2" t="inlineStr"><is><t>OTĘPIENIE</t></is></c><c r="B430" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C430" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D430" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E430" s="2" t="inlineStr"><is><t>Podanie rywastygminy jest uzasadnione u pacjentów z:</t></is></c><c r="F430" s="2" t="inlineStr"><is><t>otępieniem w przebiegu choroby Parkinsona</t></is></c><c r="G430" s="2" t="inlineStr"><is><t>chorobą Alzheimera</t></is></c><c r="H430" s="2" t="inlineStr" /><c r="I430" s="2" t="inlineStr" /><c r="J430" s="2" t="inlineStr" /><c r="K430" s="2" t="inlineStr"><is><t>otępieniem naczyniopochodnym</t></is></c><c r="L430" s="2" t="inlineStr"><is><t>łagodnymi zaburzeniami poznawczymi</t></is></c><c r="M430" s="2" t="inlineStr" /><c r="N430" s="2" t="inlineStr" /><c r="O430" s="2" t="inlineStr" /><c r="P430" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q430" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="431"><c r="A431" s="2" t="inlineStr"><is><t>LEKI PRZECIWHISTAMINOWE</t></is></c><c r="B431" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C431" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D431" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E431" s="2" t="inlineStr"><is><t>Klemastyna:</t></is></c><c r="F431" s="2" t="inlineStr"><is><t>dobrze przenika przez barierę krew- mózg 22</t></is></c><c r="G431" s="2" t="inlineStr"><is><t>może być stosowana od 2 r. ż</t></is></c><c r="H431" s="2" t="inlineStr" /><c r="I431" s="2" t="inlineStr" /><c r="J431" s="2" t="inlineStr" /><c r="K431" s="2" t="inlineStr"><is><t>selektywnie działa na rec. H1</t></is></c><c r="L431" s="2" t="inlineStr"><is><t>jest lekiem z wyboru w leczeniu przewlekłego alergicznego nieżytu nosa</t></is></c><c r="M431" s="2" t="inlineStr" /><c r="N431" s="2" t="inlineStr" /><c r="O431" s="2" t="inlineStr" /><c r="P431" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q431" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="432"><c r="A432" s="2" t="inlineStr"><is><t>PADACZKA</t></is></c><c r="B432" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C432" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D432" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E432" s="2" t="inlineStr"><is><t>W stanie padaczkowym zalecane jest zastosowanie:</t></is></c><c r="F432" s="2" t="inlineStr"><is><t>lorazepamu dożylnie</t></is></c><c r="G432" s="2" t="inlineStr"><is><t>fenytoiny we wlewie dożylnym</t></is></c><c r="H432" s="2" t="inlineStr" /><c r="I432" s="2" t="inlineStr" /><c r="J432" s="2" t="inlineStr" /><c r="K432" s="2" t="inlineStr"><is><t>diazepamu domięśniowo</t></is></c><c r="L432" s="2" t="inlineStr"><is><t>fenobarbitalu podskórnie</t></is></c><c r="M432" s="2" t="inlineStr" /><c r="N432" s="2" t="inlineStr" /><c r="O432" s="2" t="inlineStr" /><c r="P432" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q432" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="433"><c r="A433" s="2" t="inlineStr"><is><t>LEKI PRZECIWNOWOTWOROWE</t></is></c><c r="B433" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C433" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D433" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E433" s="2" t="inlineStr"><is><t>Inhibitorem kinazy tyrozynowej o działaniu przeciwnowotworowym jest:</t></is></c><c r="F433" s="2" t="inlineStr"><is><t>imatynib</t></is></c><c r="G433" s="2" t="inlineStr"><is><t>sunitynib</t></is></c><c r="H433" s="2" t="inlineStr" /><c r="I433" s="2" t="inlineStr" /><c r="J433" s="2" t="inlineStr" /><c r="K433" s="2" t="inlineStr"><is><t>ewerolimus</t></is></c><c r="L433" s="2" t="inlineStr"><is><t>bortezomib</t></is></c><c r="M433" s="2" t="inlineStr" /><c r="N433" s="2" t="inlineStr" /><c r="O433" s="2" t="inlineStr" /><c r="P433" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q433" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="434"><c r="A434" s="2" t="inlineStr"><is><t>PADACZKA</t></is></c><c r="B434" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C434" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D434" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E434" s="2" t="inlineStr"><is><t>Wskaż prawidłowe połączenie lek – wskazanie:</t></is></c><c r="F434" s="2" t="inlineStr"><is><t>drżenie samoistne – propranolol</t></is></c><c r="G434" s="2" t="inlineStr"><is><t>zespół niespokojnych nóg – pramipeksol</t></is></c><c r="H434" s="2" t="inlineStr"><is><t>padaczka z napadami uogólnionymi toniczno-klonicznymi – kwas walproinowy</t></is></c><c r="I434" s="2" t="inlineStr"><is><t>immunologiczny obrzęk mózgu – deksametazon</t></is></c><c r="J434" s="2" t="inlineStr" /><c r="K434" s="2" t="inlineStr" /><c r="L434" s="2" t="inlineStr" /><c r="M434" s="2" t="inlineStr" /><c r="N434" s="2" t="inlineStr" /><c r="O434" s="2" t="inlineStr" /><c r="P434" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q434" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="435"><c r="A435" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B435" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C435" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D435" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E435" s="2" t="inlineStr"><is><t>Skuteczne leczenie w owrzodzeniach żylnych obejmuje:</t></is></c><c r="F435" s="2" t="inlineStr"><is><t>opatrunki hydrokoloidowe</t></is></c><c r="G435" s="2" t="inlineStr" /><c r="H435" s="2" t="inlineStr" /><c r="I435" s="2" t="inlineStr" /><c r="J435" s="2" t="inlineStr" /><c r="K435" s="2" t="inlineStr"><is><t>wyciągi zawierające glikozydy kasztanowca</t></is></c><c r="L435" s="2" t="inlineStr"><is><t>heparynoidy do stosowania miejscowego</t></is></c><c r="M435" s="2" t="inlineStr"><is><t>dobesylan wapnia</t></is></c><c r="N435" s="2" t="inlineStr" /><c r="O435" s="2" t="inlineStr" /><c r="P435" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q435" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="436"><c r="A436" s="2" t="inlineStr"><is><t>LEKI PRZECIWPSYCHOTYCZNE</t></is></c><c r="B436" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C436" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D436" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E436" s="2" t="inlineStr"><is><t>W leczeniu zaburzeń lękowych z napadami paniki można zastosować:</t></is></c><c r="F436" s="2" t="inlineStr"><is><t>doksepinę</t></is></c><c r="G436" s="2" t="inlineStr"><is><t>alprazolam</t></is></c><c r="H436" s="2" t="inlineStr" /><c r="I436" s="2" t="inlineStr" /><c r="J436" s="2" t="inlineStr" /><c r="K436" s="2" t="inlineStr"><is><t>rysperydon</t></is></c><c r="L436" s="2" t="inlineStr"><is><t>haloperydol</t></is></c><c r="M436" s="2" t="inlineStr" /><c r="N436" s="2" t="inlineStr" /><c r="O436" s="2" t="inlineStr" /><c r="P436" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q436" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="437"><c r="A437" s="2" t="inlineStr"><is><t>UKŁAD PRZYWSPÓŁCZULNY</t></is></c><c r="B437" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C437" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D437" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E437" s="2" t="inlineStr"><is><t>Działanie przeciwwymiotne ma:</t></is></c><c r="F437" s="2" t="inlineStr"><is><t>skopolamina</t></is></c><c r="G437" s="2" t="inlineStr"><is><t>dimenhydrinat</t></is></c><c r="H437" s="2" t="inlineStr" /><c r="I437" s="2" t="inlineStr" /><c r="J437" s="2" t="inlineStr" /><c r="K437" s="2" t="inlineStr"><is><t>lewetyracetam</t></is></c><c r="L437" s="2" t="inlineStr"><is><t>wortioksetyna</t></is></c><c r="M437" s="2" t="inlineStr" /><c r="N437" s="2" t="inlineStr" /><c r="O437" s="2" t="inlineStr" /><c r="P437" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q437" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="438"><c r="A438" s="2" t="inlineStr"><is><t>UKŁAD WSPÓŁCZULNY</t></is></c><c r="B438" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C438" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D438" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E438" s="2" t="inlineStr"><is><t>Amfetamina:</t></is></c><c r="F438" s="2" t="inlineStr"><is><t>może działać neurotoksycznie</t></is></c><c r="G438" s="2" t="inlineStr" /><c r="H438" s="2" t="inlineStr" /><c r="I438" s="2" t="inlineStr" /><c r="J438" s="2" t="inlineStr" /><c r="K438" s="2" t="inlineStr"><is><t>bezpośrednio pobudza receptory dopaminergiczne</t></is></c><c r="L438" s="2" t="inlineStr"><is><t>wzmaga apetyt</t></is></c><c r="M438" s="2" t="inlineStr"><is><t>obniża ciśnienie tętnicze krwi</t></is></c><c r="N438" s="2" t="inlineStr" /><c r="O438" s="2" t="inlineStr" /><c r="P438" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q438" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="439"><c r="A439" s="2" t="inlineStr"><is><t>UKŁAD PRZYWSPÓŁCZULNY</t></is></c><c r="B439" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C439" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D439" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E439" s="2" t="inlineStr"><is><t>Kwetiapina:</t></is></c><c r="F439" s="2" t="inlineStr"><is><t>zwiększa ryzyko wystąpienia zespołu metabolicznego</t></is></c><c r="G439" s="2" t="inlineStr"><is><t>może być stosowana jako lek normotymiczny</t></is></c><c r="H439" s="2" t="inlineStr" /><c r="I439" s="2" t="inlineStr" /><c r="J439" s="2" t="inlineStr" /><c r="K439" s="2" t="inlineStr"><is><t>nie powoduje złośliwego zespołu neuroleptycznego</t></is></c><c r="L439" s="2" t="inlineStr"><is><t>nie wykazuje aktywności cholinolitycznej</t></is></c><c r="M439" s="2" t="inlineStr" /><c r="N439" s="2" t="inlineStr" /><c r="O439" s="2" t="inlineStr" /><c r="P439" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q439" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="440"><c r="A440" s="2" t="inlineStr"><is><t>CHOROBA PARKINSONA</t></is></c><c r="B440" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C440" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D440" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E440" s="2" t="inlineStr"><is><t>W chorobie Parkinsona lewodopę można podawać jednocześnie z:</t></is></c><c r="F440" s="2" t="inlineStr"><is><t>benserazydem</t></is></c><c r="G440" s="2" t="inlineStr"><is><t>bromokryptyną</t></is></c><c r="H440" s="2" t="inlineStr"><is><t>rotygotyną</t></is></c><c r="I440" s="2" t="inlineStr"><is><t>entekaponem</t></is></c><c r="J440" s="2" t="inlineStr" /><c r="K440" s="2" t="inlineStr" /><c r="L440" s="2" t="inlineStr" /><c r="M440" s="2" t="inlineStr" /><c r="N440" s="2" t="inlineStr" /><c r="O440" s="2" t="inlineStr" /><c r="P440" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q440" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="441"><c r="A441" s="2" t="inlineStr"><is><t>LEKI PRZECIWPSYCHOTYCZNE</t></is></c><c r="B441" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C441" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D441" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E441" s="2" t="inlineStr"><is><t>Wystąpienie objawów pozapiramidowych w przebiegu leczenia lekami przeciwpsychotycznymi:</t></is></c><c r="F441" s="2" t="inlineStr"><is><t>jest wskazaniem do modyfikacji dawki leku</t></is></c><c r="G441" s="2" t="inlineStr"><is><t>zależy od procentu zablokowania receptorów D2 w układzie nigrostriatalnym</t></is></c><c r="H441" s="2" t="inlineStr" /><c r="I441" s="2" t="inlineStr" /><c r="J441" s="2" t="inlineStr" /><c r="K441" s="2" t="inlineStr"><is><t>jest wskazaniem do natychmiastowej zmiany leku</t></is></c><c r="L441" s="2" t="inlineStr"><is><t>jest nieodłącznym elementem leczenia przeciwpsychotycznego, obserwowanym u wszystkich leczonych pacjentów</t></is></c><c r="M441" s="2" t="inlineStr" /><c r="N441" s="2" t="inlineStr" /><c r="O441" s="2" t="inlineStr" /><c r="P441" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q441" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="442"><c r="A442" s="2" t="inlineStr"><is><t>LEKI PRZECIWDEPRESYJNE</t></is></c><c r="B442" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C442" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D442" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E442" s="2" t="inlineStr"><is><t>W leczeniu epizodu depresyjnego można zastosować w monoterapii:</t></is></c><c r="F442" s="2" t="inlineStr"><is><t>sertralinę</t></is></c><c r="G442" s="2" t="inlineStr"><is><t>mirtazapinę</t></is></c><c r="H442" s="2" t="inlineStr" /><c r="I442" s="2" t="inlineStr" /><c r="J442" s="2" t="inlineStr" /><c r="K442" s="2" t="inlineStr"><is><t>sulpiryd</t></is></c><c r="L442" s="2" t="inlineStr"><is><t>sertindol</t></is></c><c r="M442" s="2" t="inlineStr" /><c r="N442" s="2" t="inlineStr" /><c r="O442" s="2" t="inlineStr" /><c r="P442" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q442" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="443"><c r="A443" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B443" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C443" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D443" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E443" s="2" t="inlineStr"><is><t>U chorego leczonego escitalopramem ryzyko wystąpienia zespołu serotoninergicznego rośnie gdy dołączymy do terapii:</t></is></c><c r="F443" s="2" t="inlineStr"><is><t>linezolid</t></is></c><c r="G443" s="2" t="inlineStr"><is><t>tramadol</t></is></c><c r="H443" s="2" t="inlineStr"><is><t>ziele dziurawca</t></is></c><c r="I443" s="2" t="inlineStr"><is><t>korzeń żeń-szenia</t></is></c><c r="J443" s="2" t="inlineStr" /><c r="K443" s="2" t="inlineStr" /><c r="L443" s="2" t="inlineStr" /><c r="M443" s="2" t="inlineStr" /><c r="N443" s="2" t="inlineStr" /><c r="O443" s="2" t="inlineStr" /><c r="P443" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q443" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="444"><c r="A444" s="2" t="inlineStr"><is><t>LEKI PRZECIWLĘKOWE</t></is></c><c r="B444" s="2" t="inlineStr"><is><t>Antidotum</t></is></c><c r="C444" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D444" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E444" s="2" t="inlineStr"><is><t>Podanie węgla aktywowanego nie przyniesie efektu w przypadku zatrucia:</t></is></c><c r="F444" s="2" t="inlineStr"><is><t>etanolem</t></is></c><c r="G444" s="2" t="inlineStr"><is><t>ołowiem</t></is></c><c r="H444" s="2" t="inlineStr"><is><t>benzyną</t></is></c><c r="I444" s="2" t="inlineStr" /><c r="J444" s="2" t="inlineStr" /><c r="K444" s="2" t="inlineStr"><is><t>benzodiazepinami</t></is></c><c r="L444" s="2" t="inlineStr" /><c r="M444" s="2" t="inlineStr" /><c r="N444" s="2" t="inlineStr" /><c r="O444" s="2" t="inlineStr" /><c r="P444" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q444" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="445"><c r="A445" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B445" s="2" t="inlineStr"><is><t>Farmakokinetyka</t></is></c><c r="C445" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D445" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E445" s="2" t="inlineStr"><is><t>U osób w starszym wieku na zmiany farmakokinetyki leków mogą wpływać:</t></is></c><c r="F445" s="2" t="inlineStr"><is><t>hipoproteinemia</t></is></c><c r="G445" s="2" t="inlineStr"><is><t>spadek masy wątroby</t></is></c><c r="H445" s="2" t="inlineStr" /><c r="I445" s="2" t="inlineStr" /><c r="J445" s="2" t="inlineStr" /><c r="K445" s="2" t="inlineStr"><is><t>zanik kosmków jelitowych</t></is></c><c r="L445" s="2" t="inlineStr"><is><t>obniżenie stężenia kwaśnej alfa-1 glikoproteiny</t></is></c><c r="M445" s="2" t="inlineStr" /><c r="N445" s="2" t="inlineStr" /><c r="O445" s="2" t="inlineStr" /><c r="P445" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q445" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="446"><c r="A446" s="2" t="inlineStr"><is><t>UKŁAD PRZYWSPÓŁCZULNY</t></is></c><c r="B446" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C446" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D446" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E446" s="2" t="inlineStr"><is><t>Inhibitorem fosfodiesterazy typu 5 jest:</t></is></c><c r="F446" s="2" t="inlineStr"><is><t>tadalafil</t></is></c><c r="G446" s="2" t="inlineStr" /><c r="H446" s="2" t="inlineStr" /><c r="I446" s="2" t="inlineStr" /><c r="J446" s="2" t="inlineStr" /><c r="K446" s="2" t="inlineStr"><is><t>trospium</t></is></c><c r="L446" s="2" t="inlineStr"><is><t>alprostadyl</t></is></c><c r="M446" s="2" t="inlineStr"><is><t>solifenacyna</t></is></c><c r="N446" s="2" t="inlineStr" /><c r="O446" s="2" t="inlineStr" /><c r="P446" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q446" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="447"><c r="A447" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B447" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C447" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D447" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E447" s="2" t="inlineStr"><is><t>W zespole jelita drażliwego może być skuteczne zastosowanie:</t></is></c><c r="F447" s="2" t="inlineStr"><is><t>mebeweryny</t></is></c><c r="G447" s="2" t="inlineStr"><is><t>atropiny z difenoksylatem</t></is></c><c r="H447" s="2" t="inlineStr"><is><t>trimebutyny</t></is></c><c r="I447" s="2" t="inlineStr"><is><t>Bifidobacterium</t></is></c><c r="J447" s="2" t="inlineStr" /><c r="K447" s="2" t="inlineStr" /><c r="L447" s="2" t="inlineStr" /><c r="M447" s="2" t="inlineStr" /><c r="N447" s="2" t="inlineStr" /><c r="O447" s="2" t="inlineStr" /><c r="P447" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q447" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="448"><c r="A448" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B448" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C448" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D448" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E448" s="2" t="inlineStr"><is><t>Przewlekłe stosowanie pantoprazolu:</t></is></c><c r="F448" s="2" t="inlineStr"><is><t>zwiększa ryzyko zakażeń dróg oddechowych</t></is></c><c r="G448" s="2" t="inlineStr"><is><t>zaburza wchłanianie wapnia z przewodu pokarmowego</t></is></c><c r="H448" s="2" t="inlineStr"><is><t>zmniejsza działanie klopidogrelu</t></is></c><c r="I448" s="2" t="inlineStr" /><c r="J448" s="2" t="inlineStr" /><c r="K448" s="2" t="inlineStr"><is><t>zmniejsza ryzyko złamania szyjki kości udowej</t></is></c><c r="L448" s="2" t="inlineStr" /><c r="M448" s="2" t="inlineStr" /><c r="N448" s="2" t="inlineStr" /><c r="O448" s="2" t="inlineStr" /><c r="P448" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q448" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="449"><c r="A449" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B449" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C449" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D449" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E449" s="2" t="inlineStr"><is><t>Wskazaniem do eradykacji Helicobacter pylori może być:</t></is></c><c r="F449" s="2" t="inlineStr"><is><t>planowane leczenie niesteroidowymi lekami przeciwzapalnymi</t></is></c><c r="G449" s="2" t="inlineStr"><is><t>niedokrwistość syderopeniczna</t></is></c><c r="H449" s="2" t="inlineStr"><is><t>chłoniak żołądka typu MALT</t></is></c><c r="I449" s="2" t="inlineStr"><is><t>aktywna choroba wrzodowa żołądka/dwunastnicy</t></is></c><c r="J449" s="2" t="inlineStr" /><c r="K449" s="2" t="inlineStr" /><c r="L449" s="2" t="inlineStr" /><c r="M449" s="2" t="inlineStr" /><c r="N449" s="2" t="inlineStr" /><c r="O449" s="2" t="inlineStr" /><c r="P449" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q449" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="450"><c r="A450" s="2" t="inlineStr"><is><t>NADCIŚNIENIE TĘTNICZE</t></is></c><c r="B450" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C450" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D450" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E450" s="2" t="inlineStr"><is><t>W profilaktyce krwawienia z żylaków przełyku w przebiegu nadciśnienia wrotnego stosuje się:</t></is></c><c r="F450" s="2" t="inlineStr"><is><t>propranolol</t></is></c><c r="G450" s="2" t="inlineStr"><is><t>karwedilol</t></is></c><c r="H450" s="2" t="inlineStr" /><c r="I450" s="2" t="inlineStr" /><c r="J450" s="2" t="inlineStr" /><c r="K450" s="2" t="inlineStr"><is><t>doksazosynę</t></is></c><c r="L450" s="2" t="inlineStr"><is><t>klonidynę</t></is></c><c r="M450" s="2" t="inlineStr" /><c r="N450" s="2" t="inlineStr" /><c r="O450" s="2" t="inlineStr" /><c r="P450" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q450" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="451"><c r="A451" s="2" t="inlineStr"><is><t>NIEWYDOLNOŚĆ SERCA</t></is></c><c r="B451" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C451" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D451" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E451" s="2" t="inlineStr"><is><t>Noradrenalinę (NA) podaje się w dawce 0,2-1 μg/kg/min rozpoczynając od najmniejszej dawki. Wskaż właściwą szybkość wlewu w początkowym leczeniu 50 kg kobiety z ciśnieniem skurczowym ok. 60 mmHg w przebiegu ostrej niewydolności serca:</t></is></c><c r="F451" s="2" t="inlineStr"><is><t>roztwór 4 mg NA/40 ml 0,9% NaCl – 6 ml/h</t></is></c><c r="G451" s="2" t="inlineStr"><is><t>roztwór 1 mg NA/50 ml 0,9% NaCl – 30 ml/h</t></is></c><c r="H451" s="2" t="inlineStr"><is><t>roztwór 5 mg NA/25 ml 0,9% NaCl - 3 ml/h</t></is></c><c r="I451" s="2" t="inlineStr"><is><t>roztwór 3 mg NA/30 ml 0,9 % NaCl – 6 ml/h</t></is></c><c r="J451" s="2" t="inlineStr" /><c r="K451" s="2" t="inlineStr" /><c r="L451" s="2" t="inlineStr" /><c r="M451" s="2" t="inlineStr" /><c r="N451" s="2" t="inlineStr" /><c r="O451" s="2" t="inlineStr" /><c r="P451" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q451" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="452"><c r="A452" s="2" t="inlineStr"><is><t>NADCIŚNIENIE TĘTNICZE</t></is></c><c r="B452" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C452" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D452" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E452" s="2" t="inlineStr"><is><t>Działanie naczyniorozszerzające ma:</t></is></c><c r="F452" s="2" t="inlineStr"><is><t>terazosyna</t></is></c><c r="G452" s="2" t="inlineStr"><is><t>nebiwolol</t></is></c><c r="H452" s="2" t="inlineStr"><is><t>zofenopryl</t></is></c><c r="I452" s="2" t="inlineStr"><is><t>lerkanidypina</t></is></c><c r="J452" s="2" t="inlineStr" /><c r="K452" s="2" t="inlineStr" /><c r="L452" s="2" t="inlineStr" /><c r="M452" s="2" t="inlineStr" /><c r="N452" s="2" t="inlineStr" /><c r="O452" s="2" t="inlineStr" /><c r="P452" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q452" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="453"><c r="A453" s="2" t="inlineStr"><is><t>CHOROBA NIEDOKRWIENNA SERCA</t></is></c><c r="B453" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C453" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D453" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E453" s="2" t="inlineStr"><is><t>Podobny mechanizm działania na poziomie molekularnym mają:</t></is></c><c r="F453" s="2" t="inlineStr"><is><t>monoazotan izosorbidu</t></is></c><c r="G453" s="2" t="inlineStr"><is><t>nesirytyd</t></is></c><c r="H453" s="2" t="inlineStr"><is><t>riociguat</t></is></c><c r="I453" s="2" t="inlineStr"><is><t>wardenafil</t></is></c><c r="J453" s="2" t="inlineStr" /><c r="K453" s="2" t="inlineStr" /><c r="L453" s="2" t="inlineStr" /><c r="M453" s="2" t="inlineStr" /><c r="N453" s="2" t="inlineStr" /><c r="O453" s="2" t="inlineStr" /><c r="P453" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q453" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="454"><c r="A454" s="2" t="inlineStr"><is><t>UKŁAD WSPÓŁCZULNY</t></is></c><c r="B454" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C454" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D454" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E454" s="2" t="inlineStr"><is><t>Beta-adrenolityki w chorobie niedokrwiennej serca:</t></is></c><c r="F454" s="2" t="inlineStr"><is><t>zmniejszają agregację płytek krwi</t></is></c><c r="G454" s="2" t="inlineStr"><is><t>zwiększają przepływ wieńcowy</t></is></c><c r="H454" s="2" t="inlineStr"><is><t>zapobiegają proarytmicznemu działaniu katecholamin</t></is></c><c r="I454" s="2" t="inlineStr"><is><t>zmniejszają kurczliwość mięśnia sercowego</t></is></c><c r="J454" s="2" t="inlineStr" /><c r="K454" s="2" t="inlineStr" /><c r="L454" s="2" t="inlineStr" /><c r="M454" s="2" t="inlineStr" /><c r="N454" s="2" t="inlineStr" /><c r="O454" s="2" t="inlineStr" /><c r="P454" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q454" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="455"><c r="A455" s="2" t="inlineStr"><is><t>NIEWYDOLNOŚĆ SERCA</t></is></c><c r="B455" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C455" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D455" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E455" s="2" t="inlineStr"><is><t>Digoksyna:</t></is></c><c r="F455" s="2" t="inlineStr"><is><t>zmniejsza aktywację układu współczulnego u osób z niewydolnością serca</t></is></c><c r="G455" s="2" t="inlineStr"><is><t>może sprzyjać wystąpieniu depresji</t></is></c><c r="H455" s="2" t="inlineStr"><is><t>jest stosowana w celu kontroli rytmu serca w utrwalonym migotaniu przedsionków</t></is></c><c r="I455" s="2" t="inlineStr"><is><t>może być nieskuteczna z powodu dezaktywacji przez bakterie jelitowe</t></is></c><c r="J455" s="2" t="inlineStr" /><c r="K455" s="2" t="inlineStr" /><c r="L455" s="2" t="inlineStr" /><c r="M455" s="2" t="inlineStr" /><c r="N455" s="2" t="inlineStr" /><c r="O455" s="2" t="inlineStr" /><c r="P455" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q455" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="456"><c r="A456" s="2" t="inlineStr"><is><t>NIEWYDOLNOŚĆ SERCA</t></is></c><c r="B456" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C456" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D456" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E456" s="2" t="inlineStr"><is><t>Ranolazyna ma działanie:</t></is></c><c r="F456" s="2" t="inlineStr"><is><t>antyarytmiczne</t></is></c><c r="G456" s="2" t="inlineStr"><is><t>korzystne metaboliczne w kardiomiocytach</t></is></c><c r="H456" s="2" t="inlineStr"><is><t>zmniejszające naprężenie ściany lewej komory</t></is></c><c r="I456" s="2" t="inlineStr" /><c r="J456" s="2" t="inlineStr" /><c r="K456" s="2" t="inlineStr"><is><t>inotropowe dodatnie</t></is></c><c r="L456" s="2" t="inlineStr" /><c r="M456" s="2" t="inlineStr" /><c r="N456" s="2" t="inlineStr" /><c r="O456" s="2" t="inlineStr" /><c r="P456" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q456" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="457"><c r="A457" s="2" t="inlineStr"><is><t>LEKI HIPOLIPEMIZUJĄCE</t></is></c><c r="B457" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C457" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D457" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E457" s="2" t="inlineStr"><is><t>Jakie leki zlecisz 48-letniemu bezobjawowemu mężczyźnie z BMI = 24,1 kg/m2, palącemu 20 papierosów dziennie od ok. 30 lat, z ciśnieniem tętniczym 150-155 mmHg w powtarzanych pomiarach i ze stężeniem cholesterolu LDL w surowicy = 200 mg/dl:</t></is></c><c r="F457" s="2" t="inlineStr"><is><t>ramipryl</t></is></c><c r="G457" s="2" t="inlineStr"><is><t>nikotynę w inhalacjach pod warunkiem zaprzestania palenia papierosów</t></is></c><c r="H457" s="2" t="inlineStr"><is><t>rosuwastatynę</t></is></c><c r="I457" s="2" t="inlineStr" /><c r="J457" s="2" t="inlineStr" /><c r="K457" s="2" t="inlineStr"><is><t>klopidogrel</t></is></c><c r="L457" s="2" t="inlineStr" /><c r="M457" s="2" t="inlineStr" /><c r="N457" s="2" t="inlineStr" /><c r="O457" s="2" t="inlineStr" /><c r="P457" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q457" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="458"><c r="A458" s="2" t="inlineStr"><is><t>NIEWYDOLNOŚĆ SERCA</t></is></c><c r="B458" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C458" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D458" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E458" s="2" t="inlineStr"><is><t>W niewydolności serca przeżycie chorych poprawia:</t></is></c><c r="F458" s="2" t="inlineStr"><is><t>eplerenon</t></is></c><c r="G458" s="2" t="inlineStr" /><c r="H458" s="2" t="inlineStr" /><c r="I458" s="2" t="inlineStr" /><c r="J458" s="2" t="inlineStr" /><c r="K458" s="2" t="inlineStr"><is><t>atenolol</t></is></c><c r="L458" s="2" t="inlineStr"><is><t>tolwaptan</t></is></c><c r="M458" s="2" t="inlineStr"><is><t>digoksyna</t></is></c><c r="N458" s="2" t="inlineStr" /><c r="O458" s="2" t="inlineStr" /><c r="P458" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q458" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="459"><c r="A459" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B459" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C459" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D459" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E459" s="2" t="inlineStr"><is><t>55-letni mężczyzna ma trwający od ok. 60-min ucisk za mostkiem, który wystąpił podczas ubierania się po wstaniu z łóżka, w EKG rozlane obniżenia ST w odprowadzeniach znad ściany przedniej. Jako lekarz pierwszego kontaktu medycznego zastosujesz:</t></is></c><c r="F459" s="2" t="inlineStr"><is><t>tikagrelor w dawce 180 mg p.o</t></is></c><c r="G459" s="2" t="inlineStr"><is><t>kwas acetylosalicylowy w dawce 300 mg p.o</t></is></c><c r="H459" s="2" t="inlineStr" /><c r="I459" s="2" t="inlineStr" /><c r="J459" s="2" t="inlineStr" /><c r="K459" s="2" t="inlineStr"><is><t>morfinę w dawkach frakcjonowanych i.v</t></is></c><c r="L459" s="2" t="inlineStr"><is><t>enoksaparynę w dawce leczniczej s.c</t></is></c><c r="M459" s="2" t="inlineStr" /><c r="N459" s="2" t="inlineStr" /><c r="O459" s="2" t="inlineStr" /><c r="P459" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q459" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="460"><c r="A460" s="2" t="inlineStr"><is><t>ZABURZENIA RYTMU SERCA</t></is></c><c r="B460" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C460" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D460" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E460" s="2" t="inlineStr"><is><t>Amiodaron:</t></is></c><c r="F460" s="2" t="inlineStr"><is><t>obniża energię potrzebną do skutecznej defibrylacji elektrycznej</t></is></c><c r="G460" s="2" t="inlineStr"><is><t>może być rozpuszczany w 5% glukozie</t></is></c><c r="H460" s="2" t="inlineStr" /><c r="I460" s="2" t="inlineStr" /><c r="J460" s="2" t="inlineStr" /><c r="K460" s="2" t="inlineStr"><is><t>jest antagonistą sercowych kanałów potasowych z wyjątkiem ikr</t></is></c><c r="L460" s="2" t="inlineStr"><is><t>jest stosowany alternatywnie z lidokainą w resuscytacji krążeniowo-oddechowej</t></is></c><c r="M460" s="2" t="inlineStr" /><c r="N460" s="2" t="inlineStr" /><c r="O460" s="2" t="inlineStr" /><c r="P460" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q460" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="461"><c r="A461" s="2" t="inlineStr"><is><t>CUKRZYCA</t></is></c><c r="B461" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C461" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D461" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E461" s="2" t="inlineStr"><is><t>Które stwierdzenie dotyczące redukcji ryzyka sercowo-naczyniowego jest prawdziwe:</t></is></c><c r="F461" s="2" t="inlineStr"><is><t>nikotynowa terapia zastępcza jest bezpieczna i powinna być rutynowo oferowana</t></is></c><c r="G461" s="2" t="inlineStr" /><c r="H461" s="2" t="inlineStr" /><c r="I461" s="2" t="inlineStr" /><c r="J461" s="2" t="inlineStr" /><c r="K461" s="2" t="inlineStr"><is><t>niezależnie od wieku należy dążyć do redukcji ciśnienia tętniczego do &lt; 140/90 mmHg</t></is></c><c r="L461" s="2" t="inlineStr"><is><t>obniżenie poziomu hemoglobiny glikowanej HgbA1c do ≤ 6% u osób z cukrzycą poprawia przeżycie w porównaniu z wyższymi wartościami HbA1c</t></is></c><c r="M461" s="2" t="inlineStr"><is><t>wysokie prawidłowe ciśnienie krwi powinno być leczone farmakologicznie</t></is></c><c r="N461" s="2" t="inlineStr" /><c r="O461" s="2" t="inlineStr" /><c r="P461" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q461" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="462"><c r="A462" s="2" t="inlineStr"><is><t>NADCIŚNIENIE TĘTNICZE</t></is></c><c r="B462" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C462" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D462" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E462" s="2" t="inlineStr"><is><t>W leczeniu nadciśnienia tętniczego przeciwwskazane jest połączenie:</t></is></c><c r="F462" s="2" t="inlineStr"><is><t>ramipryl + telmisartan</t></is></c><c r="G462" s="2" t="inlineStr" /><c r="H462" s="2" t="inlineStr" /><c r="I462" s="2" t="inlineStr" /><c r="J462" s="2" t="inlineStr" /><c r="K462" s="2" t="inlineStr"><is><t>amlodypina + chlortalidon</t></is></c><c r="L462" s="2" t="inlineStr"><is><t>amlodypina + peryndopryl</t></is></c><c r="M462" s="2" t="inlineStr"><is><t>peryndopryl + indapamid</t></is></c><c r="N462" s="2" t="inlineStr" /><c r="O462" s="2" t="inlineStr" /><c r="P462" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q462" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="463"><c r="A463" s="2" t="inlineStr"><is><t>CHOROBA NIEDOKRWIENNA SERCA</t></is></c><c r="B463" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C463" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D463" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E463" s="2" t="inlineStr"><is><t>U pacjenta z dławicą piersiową i niskim ciśnieniem tętniczym krwi można zastosować:</t></is></c><c r="F463" s="2" t="inlineStr"><is><t>ranolazynę</t></is></c><c r="G463" s="2" t="inlineStr"><is><t>iwabradynę</t></is></c><c r="H463" s="2" t="inlineStr"><is><t>trimetazydynę</t></is></c><c r="I463" s="2" t="inlineStr" /><c r="J463" s="2" t="inlineStr" /><c r="K463" s="2" t="inlineStr"><is><t>werapamil</t></is></c><c r="L463" s="2" t="inlineStr" /><c r="M463" s="2" t="inlineStr" /><c r="N463" s="2" t="inlineStr" /><c r="O463" s="2" t="inlineStr" /><c r="P463" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q463" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="464"><c r="A464" s="2" t="inlineStr"><is><t>ZABURZENIA RYTMU SERCA</t></is></c><c r="B464" s="2" t="inlineStr"><is><t>Przeciwwskazania</t></is></c><c r="C464" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D464" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E464" s="2" t="inlineStr"><is><t>Propafenon:</t></is></c><c r="F464" s="2" t="inlineStr"><is><t>jest antagonistą kanału sodowego</t></is></c><c r="G464" s="2" t="inlineStr"><is><t>ma działanie betaadrenolityczne</t></is></c><c r="H464" s="2" t="inlineStr" /><c r="I464" s="2" t="inlineStr" /><c r="J464" s="2" t="inlineStr" /><c r="K464" s="2" t="inlineStr"><is><t>rozszerza nasierdziowe tętnice wieńcowe</t></is></c><c r="L464" s="2" t="inlineStr"><is><t>jest przeciwwskazany w zespole preekscytacji (WPW)</t></is></c><c r="M464" s="2" t="inlineStr" /><c r="N464" s="2" t="inlineStr" /><c r="O464" s="2" t="inlineStr" /><c r="P464" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q464" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="465"><c r="A465" s="2" t="inlineStr"><is><t>NADCIŚNIENIE TĘTNICZE</t></is></c><c r="B465" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C465" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D465" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E465" s="2" t="inlineStr"><is><t>Teoretyczną przesłanką stosowania inhibitorów konwertazy angiotensyny w przewlekłej skurczowej niewydolności serca jest:</t></is></c><c r="F465" s="2" t="inlineStr"><is><t>odwracanie włóknienia miokardium</t></is></c><c r="G465" s="2" t="inlineStr"><is><t>odwracanie przerostu kardiomiocytów</t></is></c><c r="H465" s="2" t="inlineStr"><is><t>korzystne bezpośrednie działanie hemodynamiczne</t></is></c><c r="I465" s="2" t="inlineStr" /><c r="J465" s="2" t="inlineStr" /><c r="K465" s="2" t="inlineStr"><is><t>zwiększenie naprężenia ściany lewej komory</t></is></c><c r="L465" s="2" t="inlineStr" /><c r="M465" s="2" t="inlineStr" /><c r="N465" s="2" t="inlineStr" /><c r="O465" s="2" t="inlineStr" /><c r="P465" s="2" t="inlineStr"><is><t>EGZ 2016 I termin</t></is></c><c r="Q465" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="466"><c r="A466" s="2" t="inlineStr"><is><t>CUKRZYCA</t></is></c><c r="B466" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C466" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D466" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E466" s="2" t="inlineStr"><is><t>Metformina:</t></is></c><c r="F466" s="2" t="inlineStr"><is><t>wpływa korzystnie na profil lipidowy</t></is></c><c r="G466" s="2" t="inlineStr" /><c r="H466" s="2" t="inlineStr" /><c r="I466" s="2" t="inlineStr" /><c r="J466" s="2" t="inlineStr" /><c r="K466" s="2" t="inlineStr"><is><t>powoduje przyrost masy ciała</t></is></c><c r="L466" s="2" t="inlineStr"><is><t>zwiększa ryzyko hipoglikemii</t></is></c><c r="M466" s="2" t="inlineStr"><is><t>może być przyczyną uporczywych zaparć</t></is></c><c r="N466" s="2" t="inlineStr" /><c r="O466" s="2" t="inlineStr" /><c r="P466" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2019/20 - 1 termin</t></is></c><c r="Q466" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="467"><c r="A467" s="2" t="inlineStr"><is><t>NIEOPIOIDOWE LEKI PRZECIWBÓLOWE</t></is></c><c r="B467" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C467" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D467" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E467" s="2" t="inlineStr"><is><t>Wskaż prawidłowe stwierdzenie:</t></is></c><c r="F467" s="2" t="inlineStr"><is><t>Diklofenak działa hepatotoksycznie</t></is></c><c r="G467" s="2" t="inlineStr" /><c r="H467" s="2" t="inlineStr" /><c r="I467" s="2" t="inlineStr" /><c r="J467" s="2" t="inlineStr" /><c r="K467" s="2" t="inlineStr"><is><t>Paracetamol działa antyagregacyjnie</t></is></c><c r="L467" s="2" t="inlineStr"><is><t>Naproksen działa hipotensyjnie</t></is></c><c r="M467" s="2" t="inlineStr"><is><t>Metamizol działa prozakrzepowo</t></is></c><c r="N467" s="2" t="inlineStr" /><c r="O467" s="2" t="inlineStr" /><c r="P467" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2019/20 - 1 termin</t></is></c><c r="Q467" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="468"><c r="A468" s="2" t="inlineStr"><is><t>NARKOTYCZNE LEKI PRZECIWBÓLOWE</t></is></c><c r="B468" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C468" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D468" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E468" s="2" t="inlineStr"><is><t>Tramadol jest:</t></is></c><c r="F468" s="2" t="inlineStr"><is><t>Inhibitorem wychwytu zwrotnego serotoniny</t></is></c><c r="G468" s="2" t="inlineStr"><is><t>Agonistą receptorów opioidowych typu μ</t></is></c><c r="H468" s="2" t="inlineStr" /><c r="I468" s="2" t="inlineStr" /><c r="J468" s="2" t="inlineStr" /><c r="K468" s="2" t="inlineStr"><is><t>Inhibitorem wychwytu zwrotnego dopaminy</t></is></c><c r="L468" s="2" t="inlineStr"><is><t>Agonistą receptorów NMDA</t></is></c><c r="M468" s="2" t="inlineStr" /><c r="N468" s="2" t="inlineStr" /><c r="O468" s="2" t="inlineStr" /><c r="P468" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2019/20 - 1 termin</t></is></c><c r="Q468" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="469"><c r="A469" s="2" t="inlineStr"><is><t>CUKRZYCA</t></is></c><c r="B469" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C469" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D469" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E469" s="2" t="inlineStr"><is><t>Hamowanie enzymu stanowi zasadniczy mechanizm działania:</t></is></c><c r="F469" s="2" t="inlineStr"><is><t>cyklosporyny</t></is></c><c r="G469" s="2" t="inlineStr" /><c r="H469" s="2" t="inlineStr" /><c r="I469" s="2" t="inlineStr" /><c r="J469" s="2" t="inlineStr" /><c r="K469" s="2" t="inlineStr"><is><t>Liraglutydu</t></is></c><c r="L469" s="2" t="inlineStr"><is><t>Lorazepamu</t></is></c><c r="M469" s="2" t="inlineStr"><is><t>Buprenorfiny</t></is></c><c r="N469" s="2" t="inlineStr" /><c r="O469" s="2" t="inlineStr" /><c r="P469" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2019/20 - 1 termin</t></is></c><c r="Q469" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="470"><c r="A470" s="2" t="inlineStr"><is><t>CUKRZYCA</t></is></c><c r="B470" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C470" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D470" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E470" s="2" t="inlineStr"><is><t>Ryzyko wzrostu masy ciała jest związane z terapią:</t></is></c><c r="F470" s="2" t="inlineStr"><is><t>Olanzapiną</t></is></c><c r="G470" s="2" t="inlineStr"><is><t>Insuliną</t></is></c><c r="H470" s="2" t="inlineStr"><is><t>prednizonem</t></is></c><c r="I470" s="2" t="inlineStr" /><c r="J470" s="2" t="inlineStr" /><c r="K470" s="2" t="inlineStr"><is><t>Liraglutydem</t></is></c><c r="L470" s="2" t="inlineStr" /><c r="M470" s="2" t="inlineStr" /><c r="N470" s="2" t="inlineStr" /><c r="O470" s="2" t="inlineStr" /><c r="P470" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2019/20 - 1 termin</t></is></c><c r="Q470" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="471"><c r="A471" s="2" t="inlineStr"><is><t>NIEOPIOIDOWE LEKI PRZECIWBÓLOWE</t></is></c><c r="B471" s="2" t="inlineStr"><is><t>Sposób podania</t></is></c><c r="C471" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D471" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E471" s="2" t="inlineStr"><is><t>Lek A jest stosowany doustnie. Ma właściwości przeciwbólowe, ale nie ma właściwości przeciwzapalnych. Nie powoduje istotnego wzrostu ryzyka powikłań sercowo – naczyniowych. Lekiem A może być:</t></is></c><c r="F471" s="2" t="inlineStr"><is><t>Tramadol</t></is></c><c r="G471" s="2" t="inlineStr"><is><t>Paracetamol</t></is></c><c r="H471" s="2" t="inlineStr" /><c r="I471" s="2" t="inlineStr" /><c r="J471" s="2" t="inlineStr" /><c r="K471" s="2" t="inlineStr"><is><t>Naproksen</t></is></c><c r="L471" s="2" t="inlineStr"><is><t>Celekoksyb</t></is></c><c r="M471" s="2" t="inlineStr" /><c r="N471" s="2" t="inlineStr" /><c r="O471" s="2" t="inlineStr" /><c r="P471" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2019/20 - 1 termin</t></is></c><c r="Q471" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="472"><c r="A472" s="2" t="inlineStr"><is><t>OSTEOPOROZA</t></is></c><c r="B472" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C472" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D472" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E472" s="2" t="inlineStr"><is><t>Bisfosfoniany są stosowane:</t></is></c><c r="F472" s="2" t="inlineStr"><is><t>w leczeniu osteoporozy posteroidowej</t></is></c><c r="G472" s="2" t="inlineStr"><is><t>w leczeniu ciężkiej hiperkalcemii</t></is></c><c r="H472" s="2" t="inlineStr" /><c r="I472" s="2" t="inlineStr" /><c r="J472" s="2" t="inlineStr" /><c r="K472" s="2" t="inlineStr"><is><t>w celu przyspieszania zrostu kości po złamaniach</t></is></c><c r="L472" s="2" t="inlineStr"><is><t>przeciwbólowo w chorobie zwyrodnieniowej stawów</t></is></c><c r="M472" s="2" t="inlineStr" /><c r="N472" s="2" t="inlineStr" /><c r="O472" s="2" t="inlineStr" /><c r="P472" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2019/20 - 1 termin</t></is></c><c r="Q472" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="473"><c r="A473" s="2" t="inlineStr"><is><t>STANY NAGŁE</t></is></c><c r="B473" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C473" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D473" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E473" s="2" t="inlineStr"><is><t>20% roztwór albumin to:</t></is></c><c r="F473" s="2" t="inlineStr"><is><t>lek krwiopochodny</t></is></c><c r="G473" s="2" t="inlineStr"><is><t>koloid zatrzymujący płyny w przestrzeni wewnątrznaczyniowej</t></is></c><c r="H473" s="2" t="inlineStr" /><c r="I473" s="2" t="inlineStr" /><c r="J473" s="2" t="inlineStr" /><c r="K473" s="2" t="inlineStr"><is><t>substancja do żywienia pozajelitowego</t></is></c><c r="L473" s="2" t="inlineStr"><is><t>łatwo dostępny i tani płyn do nawadniania</t></is></c><c r="M473" s="2" t="inlineStr" /><c r="N473" s="2" t="inlineStr" /><c r="O473" s="2" t="inlineStr" /><c r="P473" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2019/20 - 1 termin</t></is></c><c r="Q473" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="474"><c r="A474" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B474" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C474" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D474" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E474" s="2" t="inlineStr"><is><t>W leczeniu wymiotów indukowanych chemioterapią znajduje zastosowanie:</t></is></c><c r="F474" s="2" t="inlineStr"><is><t>Deksametazon</t></is></c><c r="G474" s="2" t="inlineStr"><is><t>Palonosetron</t></is></c><c r="H474" s="2" t="inlineStr"><is><t>metoklopramid</t></is></c><c r="I474" s="2" t="inlineStr" /><c r="J474" s="2" t="inlineStr" /><c r="K474" s="2" t="inlineStr"><is><t>Dimenhydrynat</t></is></c><c r="L474" s="2" t="inlineStr" /><c r="M474" s="2" t="inlineStr" /><c r="N474" s="2" t="inlineStr" /><c r="O474" s="2" t="inlineStr" /><c r="P474" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2019/20 - 1 termin</t></is></c><c r="Q474" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="475"><c r="A475" s="2" t="inlineStr"><is><t>LEKI PRZECIWPSYCHOTYCZNE</t></is></c><c r="B475" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C475" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D475" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E475" s="2" t="inlineStr"><is><t>Klozapina może być przyczyną:</t></is></c><c r="F475" s="2" t="inlineStr"><is><t>obniżenia progu drgawkowego</t></is></c><c r="G475" s="2" t="inlineStr"><is><t>przyrostu masy ciała</t></is></c><c r="H475" s="2" t="inlineStr"><is><t>agranulocytozy</t></is></c><c r="I475" s="2" t="inlineStr" /><c r="J475" s="2" t="inlineStr" /><c r="K475" s="2" t="inlineStr"><is><t>Hiperprolaktynemii</t></is></c><c r="L475" s="2" t="inlineStr" /><c r="M475" s="2" t="inlineStr" /><c r="N475" s="2" t="inlineStr" /><c r="O475" s="2" t="inlineStr" /><c r="P475" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2019/20 - 1 termin</t></is></c><c r="Q475" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="476"><c r="A476" s="2" t="inlineStr"><is><t>LEKI PRZECIWLĘKOWE</t></is></c><c r="B476" s="2" t="inlineStr"><is><t>Interakcje</t></is></c><c r="C476" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D476" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E476" s="2" t="inlineStr"><is><t>Wskaż prawidłowe skojarzenie lek – mechanizm działania:</t></is></c><c r="F476" s="2" t="inlineStr"><is><t>buspiron – agonista rec. 5HT1A</t></is></c><c r="G476" s="2" t="inlineStr"><is><t>diazepam – agonista rec. GABA-A</t></is></c><c r="H476" s="2" t="inlineStr" /><c r="I476" s="2" t="inlineStr" /><c r="J476" s="2" t="inlineStr" /><c r="K476" s="2" t="inlineStr"><is><t>zolpidem – agonista rec. H2</t></is></c><c r="L476" s="2" t="inlineStr"><is><t>mirtazapina – agonista rec. alfa2</t></is></c><c r="M476" s="2" t="inlineStr" /><c r="N476" s="2" t="inlineStr" /><c r="O476" s="2" t="inlineStr" /><c r="P476" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2019/20 - 1 termin</t></is></c><c r="Q476" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="477"><c r="A477" s="2" t="inlineStr"><is><t>NARKOTYCZNE LEKI PRZECIWBÓLOWE</t></is></c><c r="B477" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C477" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D477" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E477" s="2" t="inlineStr"><is><t>Benzodiazepiny są stosowane w:</t></is></c><c r="F477" s="2" t="inlineStr"><is><t>premedykacji</t></is></c><c r="G477" s="2" t="inlineStr"><is><t>terapii padaczki</t></is></c><c r="H477" s="2" t="inlineStr" /><c r="I477" s="2" t="inlineStr" /><c r="J477" s="2" t="inlineStr" /><c r="K477" s="2" t="inlineStr"><is><t>długotrwałej terapii bezsenności</t></is></c><c r="L477" s="2" t="inlineStr"><is><t>zespole abstynencyjnym u chorych uzależnionych od morfiny</t></is></c><c r="M477" s="2" t="inlineStr" /><c r="N477" s="2" t="inlineStr" /><c r="O477" s="2" t="inlineStr" /><c r="P477" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2019/20 - 1 termin</t></is></c><c r="Q477" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="478"><c r="A478" s="2" t="inlineStr"><is><t>NARKOTYCZNE LEKI PRZECIWBÓLOWE</t></is></c><c r="B478" s="2" t="inlineStr"><is><t>Interakcje</t></is></c><c r="C478" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D478" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E478" s="2" t="inlineStr"><is><t>Zespół serotoninowy może być wynikiem interakcji cytalopramu z:</t></is></c><c r="F478" s="2" t="inlineStr"><is><t>Tramadolem</t></is></c><c r="G478" s="2" t="inlineStr"><is><t>klomipraminą</t></is></c><c r="H478" s="2" t="inlineStr" /><c r="I478" s="2" t="inlineStr" /><c r="J478" s="2" t="inlineStr" /><c r="K478" s="2" t="inlineStr"><is><t>Oksazepamem</t></is></c><c r="L478" s="2" t="inlineStr"><is><t>Buprenorfiną</t></is></c><c r="M478" s="2" t="inlineStr" /><c r="N478" s="2" t="inlineStr" /><c r="O478" s="2" t="inlineStr" /><c r="P478" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2019/20 - 1 termin</t></is></c><c r="Q478" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="479"><c r="A479" s="2" t="inlineStr"><is><t>FARMAKOLOGIA OGÓLNA I EBM</t></is></c><c r="B479" s="2" t="inlineStr"><is><t>Przeciwwskazania</t></is></c><c r="C479" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D479" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E479" s="2" t="inlineStr"><is><t>Charakterystyka Produktu Leczniczego zawiera informacje o:</t></is></c><c r="F479" s="2" t="inlineStr"><is><t>przeciwwskazaniach do stosowania</t></is></c><c r="G479" s="2" t="inlineStr"><is><t>właściwościach farmakokinetycznych</t></is></c><c r="H479" s="2" t="inlineStr"><is><t>okresie ważności</t></is></c><c r="I479" s="2" t="inlineStr" /><c r="J479" s="2" t="inlineStr" /><c r="K479" s="2" t="inlineStr"><is><t>zakresie refundacji</t></is></c><c r="L479" s="2" t="inlineStr" /><c r="M479" s="2" t="inlineStr" /><c r="N479" s="2" t="inlineStr" /><c r="O479" s="2" t="inlineStr" /><c r="P479" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2019/20 - 1 termin</t></is></c><c r="Q479" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="480"><c r="A480" s="2" t="inlineStr"><is><t>FARMAKOKINETYKA</t></is></c><c r="B480" s="2" t="inlineStr"><is><t>Farmakokinetyka</t></is></c><c r="C480" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D480" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E480" s="2" t="inlineStr"><is><t>Przyczyną nieliniowego przebiegu procesów farmakokinetycznych może być:</t></is></c><c r="F480" s="2" t="inlineStr"><is><t>autoindukcja metabolizmu</t></is></c><c r="G480" s="2" t="inlineStr"><is><t>niedobór kosubstratów w procesie sprzęgania</t></is></c><c r="H480" s="2" t="inlineStr"><is><t>wysycenie transporterów</t></is></c><c r="I480" s="2" t="inlineStr" /><c r="J480" s="2" t="inlineStr" /><c r="K480" s="2" t="inlineStr"><is><t>wąski wskaźnik terapeutyczny leku</t></is></c><c r="L480" s="2" t="inlineStr" /><c r="M480" s="2" t="inlineStr" /><c r="N480" s="2" t="inlineStr" /><c r="O480" s="2" t="inlineStr" /><c r="P480" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2019/20 - 1 termin</t></is></c><c r="Q480" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="481"><c r="A481" s="2" t="inlineStr"><is><t>CUKRZYCA</t></is></c><c r="B481" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C481" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D481" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E481" s="2" t="inlineStr"><is><t>Insulina aspart:</t></is></c><c r="F481" s="2" t="inlineStr"><is><t>działa za pośrednictwem receptora błonowego</t></is></c><c r="G481" s="2" t="inlineStr"><is><t>może być podawana we wstrzyknięciu podskórnym</t></is></c><c r="H481" s="2" t="inlineStr" /><c r="I481" s="2" t="inlineStr" /><c r="J481" s="2" t="inlineStr" /><c r="K481" s="2" t="inlineStr"><is><t>jest stosowana wyłącznie w cukrzycy typu 1</t></is></c><c r="L481" s="2" t="inlineStr"><is><t>jest analogiem długodziałającym</t></is></c><c r="M481" s="2" t="inlineStr" /><c r="N481" s="2" t="inlineStr" /><c r="O481" s="2" t="inlineStr" /><c r="P481" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2019/20 - 1 termin</t></is></c><c r="Q481" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="482"><c r="A482" s="2" t="inlineStr"><is><t>STANY NAGŁE</t></is></c><c r="B482" s="2" t="inlineStr"><is><t>Farmakokinetyka</t></is></c><c r="C482" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D482" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E482" s="2" t="inlineStr"><is><t>Na proces dystrybucji leku może mieć wpływ:</t></is></c><c r="F482" s="2" t="inlineStr"><is><t>niewydolność krążenia</t></is></c><c r="G482" s="2" t="inlineStr"><is><t>Hipoalbuminemia</t></is></c><c r="H482" s="2" t="inlineStr" /><c r="I482" s="2" t="inlineStr" /><c r="J482" s="2" t="inlineStr" /><c r="K482" s="2" t="inlineStr"><is><t>obecność pokarmu w przypadku podania doustnego</t></is></c><c r="L482" s="2" t="inlineStr"><is><t>możliwość sprzęgania z kwasem glukuronowym</t></is></c><c r="M482" s="2" t="inlineStr" /><c r="N482" s="2" t="inlineStr" /><c r="O482" s="2" t="inlineStr" /><c r="P482" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2019/20 - 1 termin</t></is></c><c r="Q482" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="483"><c r="A483" s="2" t="inlineStr"><is><t>NIEWYDOLNOŚĆ SERCA</t></is></c><c r="B483" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C483" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D483" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E483" s="2" t="inlineStr"><is><t>Agonistą receptorów jest:</t></is></c><c r="F483" s="2" t="inlineStr"><is><t>tapentadol</t></is></c><c r="G483" s="2" t="inlineStr" /><c r="H483" s="2" t="inlineStr" /><c r="I483" s="2" t="inlineStr" /><c r="J483" s="2" t="inlineStr" /><c r="K483" s="2" t="inlineStr"><is><t>Sertralina</t></is></c><c r="L483" s="2" t="inlineStr"><is><t>Eplerenon</t></is></c><c r="M483" s="2" t="inlineStr"><is><t>Fenytoina</t></is></c><c r="N483" s="2" t="inlineStr" /><c r="O483" s="2" t="inlineStr" /><c r="P483" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2019/20 - 1 termin</t></is></c><c r="Q483" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="484"><c r="A484" s="2" t="inlineStr"><is><t>NADCIŚNIENIE TĘTNICZE</t></is></c><c r="B484" s="2" t="inlineStr"><is><t>Monitorowanie</t></is></c><c r="C484" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D484" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E484" s="2" t="inlineStr"><is><t>W trakcie długotrwałej terapii glikokortykosteroidami, wskazane jest monitorowanie:</t></is></c><c r="F484" s="2" t="inlineStr"><is><t>stężenia potasu we krwi</t></is></c><c r="G484" s="2" t="inlineStr"><is><t>ciśnienia tętniczego krwi</t></is></c><c r="H484" s="2" t="inlineStr"><is><t>ciśnienia wewnątrzgałkowego</t></is></c><c r="I484" s="2" t="inlineStr"><is><t>glikemii</t></is></c><c r="J484" s="2" t="inlineStr" /><c r="K484" s="2" t="inlineStr" /><c r="L484" s="2" t="inlineStr" /><c r="M484" s="2" t="inlineStr" /><c r="N484" s="2" t="inlineStr" /><c r="O484" s="2" t="inlineStr" /><c r="P484" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2019/20 - 1 termin</t></is></c><c r="Q484" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="485"><c r="A485" s="2" t="inlineStr"><is><t>CUKRZYCA</t></is></c><c r="B485" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C485" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D485" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E485" s="2" t="inlineStr"><is><t>Inhibitory kotransportera sodowo-glukozowego 2 (SGLT-2, flozyny):</t></is></c><c r="F485" s="2" t="inlineStr"><is><t>Mogą być stosowane łącznie z metforminą</t></is></c><c r="G485" s="2" t="inlineStr"><is><t>Mogą zwiększać diurezę</t></is></c><c r="H485" s="2" t="inlineStr"><is><t>Mają udowodnione korzystne działanie w zakresie ryzyka sercowo-naczyniowego</t></is></c><c r="I485" s="2" t="inlineStr" /><c r="J485" s="2" t="inlineStr" /><c r="K485" s="2" t="inlineStr"><is><t>Charakteryzują się wysokim ryzykiem wystąpienia hipoglikemii</t></is></c><c r="L485" s="2" t="inlineStr" /><c r="M485" s="2" t="inlineStr" /><c r="N485" s="2" t="inlineStr" /><c r="O485" s="2" t="inlineStr" /><c r="P485" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2019/20 - 1 termin</t></is></c><c r="Q485" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="486"><c r="A486" s="2" t="inlineStr"><is><t>LEKI IMMUNOSUPRESYJNE</t></is></c><c r="B486" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C486" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D486" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E486" s="2" t="inlineStr"><is><t>Przeciwciała monoklonalne znajdują zastosowanie w terapii:</t></is></c><c r="F486" s="2" t="inlineStr"><is><t>choroby Leśniowskiego i Crohna</t></is></c><c r="G486" s="2" t="inlineStr"><is><t>stwardnienia rozsianego</t></is></c><c r="H486" s="2" t="inlineStr"><is><t>reumatoidalnego zapalenia stawów</t></is></c><c r="I486" s="2" t="inlineStr" /><c r="J486" s="2" t="inlineStr" /><c r="K486" s="2" t="inlineStr"><is><t>mononukleozy</t></is></c><c r="L486" s="2" t="inlineStr" /><c r="M486" s="2" t="inlineStr" /><c r="N486" s="2" t="inlineStr" /><c r="O486" s="2" t="inlineStr" /><c r="P486" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2019/20 - 1 termin</t></is></c><c r="Q486" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="487"><c r="A487" s="2" t="inlineStr"><is><t>LEKI PRZECIWPSYCHOTYCZNE</t></is></c><c r="B487" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C487" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D487" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E487" s="2" t="inlineStr"><is><t>Zaburzenia rytmu serca mogą wystąpić w trakcie podawania:</t></is></c><c r="F487" s="2" t="inlineStr"><is><t>Amisulpirydu</t></is></c><c r="G487" s="2" t="inlineStr"><is><t>Ondansetronu</t></is></c><c r="H487" s="2" t="inlineStr"><is><t>Chlorpromazyny</t></is></c><c r="I487" s="2" t="inlineStr"><is><t>metadonu</t></is></c><c r="J487" s="2" t="inlineStr" /><c r="K487" s="2" t="inlineStr" /><c r="L487" s="2" t="inlineStr" /><c r="M487" s="2" t="inlineStr" /><c r="N487" s="2" t="inlineStr" /><c r="O487" s="2" t="inlineStr" /><c r="P487" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2019/20 - 1 termin</t></is></c><c r="Q487" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="488"><c r="A488" s="2" t="inlineStr"><is><t>LEKI ROŚLINNE I SUPLEMENTY</t></is></c><c r="B488" s="2" t="inlineStr"><is><t>Przeciwwskazania</t></is></c><c r="C488" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D488" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E488" s="2" t="inlineStr"><is><t>Wskaż prawidłowe stwierdzenie dotyczące terapii niedokrwistości z niedoboru żelaza:</t></is></c><c r="F488" s="2" t="inlineStr"><is><t>preferowana jest doustna suplementacja żelaza</t></is></c><c r="G488" s="2" t="inlineStr" /><c r="H488" s="2" t="inlineStr" /><c r="I488" s="2" t="inlineStr" /><c r="J488" s="2" t="inlineStr" /><c r="K488" s="2" t="inlineStr"><is><t>terapia trwa 2 tygodnie</t></is></c><c r="L488" s="2" t="inlineStr"><is><t>preparaty dożylne żelaza są przeciwwskazane u chorych z przewlekłą niewydolnością nerek</t></is></c><c r="M488" s="2" t="inlineStr"><is><t>tabletki z żelazem należy popijać herbatą</t></is></c><c r="N488" s="2" t="inlineStr" /><c r="O488" s="2" t="inlineStr" /><c r="P488" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2019/20 - 1 termin</t></is></c><c r="Q488" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="489"><c r="A489" s="2" t="inlineStr"><is><t>PADACZKA</t></is></c><c r="B489" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C489" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D489" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E489" s="2" t="inlineStr"><is><t>Działanie normotymizujące wykazują:</t></is></c><c r="F489" s="2" t="inlineStr"><is><t>kwas walproinowy</t></is></c><c r="G489" s="2" t="inlineStr"><is><t>Lamotrygina</t></is></c><c r="H489" s="2" t="inlineStr"><is><t>Olanzapina</t></is></c><c r="I489" s="2" t="inlineStr"><is><t>sole litu</t></is></c><c r="J489" s="2" t="inlineStr" /><c r="K489" s="2" t="inlineStr" /><c r="L489" s="2" t="inlineStr" /><c r="M489" s="2" t="inlineStr" /><c r="N489" s="2" t="inlineStr" /><c r="O489" s="2" t="inlineStr" /><c r="P489" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2019/20 - 1 termin</t></is></c><c r="Q489" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="490"><c r="A490" s="2" t="inlineStr"><is><t>NARKOTYCZNE LEKI PRZECIWBÓLOWE</t></is></c><c r="B490" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C490" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D490" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E490" s="2" t="inlineStr"><is><t>Wskaż prawidłowe stwierdzenie:</t></is></c><c r="F490" s="2" t="inlineStr"><is><t>buprenorfina może być stosowana w leczeniu substytucyjnym zamiast metadonu</t></is></c><c r="G490" s="2" t="inlineStr"><is><t>petydyna nie powinna być stosowana w okołoporodowym postępowaniu</t></is></c><c r="H490" s="2" t="inlineStr" /><c r="I490" s="2" t="inlineStr" /><c r="J490" s="2" t="inlineStr" /><c r="K490" s="2" t="inlineStr"><is><t>nalokson jest podawany dożylnie, z oksykodonem, w celu zapobiegania występowaniu zaparć poopioidowych</t></is></c><c r="L490" s="2" t="inlineStr"><is><t>fentanyl w plastrach jest stosowany w terapii pooperacyjnego bólu ostrego</t></is></c><c r="M490" s="2" t="inlineStr" /><c r="N490" s="2" t="inlineStr" /><c r="O490" s="2" t="inlineStr" /><c r="P490" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2019/20 - 1 termin</t></is></c><c r="Q490" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="491"><c r="A491" s="2" t="inlineStr"><is><t>LEKI PRZECIWNOWOTWOROWE</t></is></c><c r="B491" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C491" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D491" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E491" s="2" t="inlineStr"><is><t>Udowodnione działanie immunostymulujące wykazuje:</t></is></c><c r="F491" s="2" t="inlineStr"><is><t>filgrastym</t></is></c><c r="G491" s="2" t="inlineStr" /><c r="H491" s="2" t="inlineStr" /><c r="I491" s="2" t="inlineStr" /><c r="J491" s="2" t="inlineStr" /><c r="K491" s="2" t="inlineStr"><is><t>wyciąg z korzenia jeżówki purpurowej</t></is></c><c r="L491" s="2" t="inlineStr"><is><t>pranobeks inozyny</t></is></c><c r="M491" s="2" t="inlineStr"><is><t>alkoholowy wyciąg z dziurawca</t></is></c><c r="N491" s="2" t="inlineStr" /><c r="O491" s="2" t="inlineStr" /><c r="P491" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2019/20 - 1 termin</t></is></c><c r="Q491" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="492"><c r="A492" s="2" t="inlineStr"><is><t>CHOROBA NIEDOKRWIENNA SERCA</t></is></c><c r="B492" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C492" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D492" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E492" s="2" t="inlineStr"><is><t>Ryzyka rozwoju zależności można się spodziewać przy stosowaniu:</t></is></c><c r="F492" s="2" t="inlineStr"><is><t>Dihydrokodeiny</t></is></c><c r="G492" s="2" t="inlineStr"><is><t>Diazepamu</t></is></c><c r="H492" s="2" t="inlineStr" /><c r="I492" s="2" t="inlineStr" /><c r="J492" s="2" t="inlineStr" /><c r="K492" s="2" t="inlineStr"><is><t>Diklofenaku</t></is></c><c r="L492" s="2" t="inlineStr"><is><t>duloksetyny</t></is></c><c r="M492" s="2" t="inlineStr" /><c r="N492" s="2" t="inlineStr" /><c r="O492" s="2" t="inlineStr" /><c r="P492" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2019/20 - 1 termin</t></is></c><c r="Q492" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="493"><c r="A493" s="2" t="inlineStr"><is><t>LEKI PRZECIWDEPRESYJNE</t></is></c><c r="B493" s="2" t="inlineStr"><is><t>Interakcje</t></is></c><c r="C493" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D493" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E493" s="2" t="inlineStr"><is><t>Wskaż prawidłowe skojarzenie lek przeciwdepresyjny – mechanizm działania:</t></is></c><c r="F493" s="2" t="inlineStr"><is><t>reboksetyna – selektywny inhibitor wychwytu zwrotnego noradrenaliny</t></is></c><c r="G493" s="2" t="inlineStr"><is><t>bupropion – inhibitor wychwytu zwrotnego noradrenaliny i dopaminy</t></is></c><c r="H493" s="2" t="inlineStr"><is><t>fluoksetyna – selektywny inhibitor wychwytu zwrotnego serotoniny</t></is></c><c r="I493" s="2" t="inlineStr"><is><t>wenlafaksyna – inhibitor wychwytu zwrotnego serotoniny i noradrenaliny</t></is></c><c r="J493" s="2" t="inlineStr" /><c r="K493" s="2" t="inlineStr" /><c r="L493" s="2" t="inlineStr" /><c r="M493" s="2" t="inlineStr" /><c r="N493" s="2" t="inlineStr" /><c r="O493" s="2" t="inlineStr" /><c r="P493" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2019/20 - 1 termin</t></is></c><c r="Q493" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="494"><c r="A494" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B494" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C494" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D494" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E494" s="2" t="inlineStr"><is><t>Ryzyko gastrotoksycznego działania ketoprofenu może istotnie wzrosnąć przy jednoczesnym podawaniu:</t></is></c><c r="F494" s="2" t="inlineStr"><is><t>Spironolaktonu</t></is></c><c r="G494" s="2" t="inlineStr"><is><t>prednizonu</t></is></c><c r="H494" s="2" t="inlineStr" /><c r="I494" s="2" t="inlineStr" /><c r="J494" s="2" t="inlineStr" /><c r="K494" s="2" t="inlineStr"><is><t>Mizoprostolu</t></is></c><c r="L494" s="2" t="inlineStr"><is><t>Omeprazolu</t></is></c><c r="M494" s="2" t="inlineStr" /><c r="N494" s="2" t="inlineStr" /><c r="O494" s="2" t="inlineStr" /><c r="P494" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2019/20 - 1 termin</t></is></c><c r="Q494" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="495"><c r="A495" s="2" t="inlineStr"><is><t>LEKI MOCZOPĘDNE</t></is></c><c r="B495" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C495" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D495" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E495" s="2" t="inlineStr"><is><t>Morfina może być przyczyną:</t></is></c><c r="F495" s="2" t="inlineStr"><is><t>obniżenia progu drgawkowego</t></is></c><c r="G495" s="2" t="inlineStr"><is><t>skurczu oskrzeli</t></is></c><c r="H495" s="2" t="inlineStr" /><c r="I495" s="2" t="inlineStr" /><c r="J495" s="2" t="inlineStr" /><c r="K495" s="2" t="inlineStr"><is><t>rozszerzenia źrenic</t></is></c><c r="L495" s="2" t="inlineStr"><is><t>działania moczopędnego</t></is></c><c r="M495" s="2" t="inlineStr" /><c r="N495" s="2" t="inlineStr" /><c r="O495" s="2" t="inlineStr" /><c r="P495" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2019/20 - 1 termin</t></is></c><c r="Q495" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="496"><c r="A496" s="2" t="inlineStr"><is><t>LEKI ROŚLINNE I SUPLEMENTY</t></is></c><c r="B496" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C496" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D496" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E496" s="2" t="inlineStr"><is><t>Wskaż fałszywe stwierdzenie:</t></is></c><c r="F496" s="2" t="inlineStr"><is><t>suplement diety to lek stosowany wspomagająco</t></is></c><c r="G496" s="2" t="inlineStr" /><c r="H496" s="2" t="inlineStr" /><c r="I496" s="2" t="inlineStr" /><c r="J496" s="2" t="inlineStr" /><c r="K496" s="2" t="inlineStr"><is><t>produkt leczniczy to substancja, której przypisuje się, między innymi, właściwości zapobiegania chorobom występującym u ludzi</t></is></c><c r="L496" s="2" t="inlineStr"><is><t>wyrób medyczny to przyrząd lub inny artykuł stosowany w celu diagnozowania, zapobiegania, monitorowania, leczenia lub łagodzenia przebiegu chorób</t></is></c><c r="M496" s="2" t="inlineStr"><is><t>roztwór albumin należy do kategorii produktów krwiopochodnych</t></is></c><c r="N496" s="2" t="inlineStr" /><c r="O496" s="2" t="inlineStr" /><c r="P496" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2019/20 - 2 termin</t></is></c><c r="Q496" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="497"><c r="A497" s="2" t="inlineStr"><is><t>CUKRZYCA</t></is></c><c r="B497" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C497" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D497" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E497" s="2" t="inlineStr"><is><t>Wskaż prawdziwe stwierdzenie:</t></is></c><c r="F497" s="2" t="inlineStr"><is><t>gliklazyd może powodować przyrost masy ciała</t></is></c><c r="G497" s="2" t="inlineStr"><is><t>metformina może być przyczyną kwasicy mleczanowej</t></is></c><c r="H497" s="2" t="inlineStr"><is><t>empagliflozyna zwiększa ryzyko zakażeń w obrębie miednicy mniejszej</t></is></c><c r="I497" s="2" t="inlineStr" /><c r="J497" s="2" t="inlineStr" /><c r="K497" s="2" t="inlineStr"><is><t>liraglutyd wykazuje niekorzystny efekt sercowo-naczyniowy</t></is></c><c r="L497" s="2" t="inlineStr" /><c r="M497" s="2" t="inlineStr" /><c r="N497" s="2" t="inlineStr" /><c r="O497" s="2" t="inlineStr" /><c r="P497" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2019/20 - 2 termin</t></is></c><c r="Q497" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="498"><c r="A498" s="2" t="inlineStr"><is><t>NARKOTYCZNE LEKI PRZECIWBÓLOWE</t></is></c><c r="B498" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C498" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D498" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E498" s="2" t="inlineStr"><is><t>Nalokson:</t></is></c><c r="F498" s="2" t="inlineStr"><is><t>słabo wchłania się z przewodu pokarmowego</t></is></c><c r="G498" s="2" t="inlineStr"><is><t>nie wywołuje uzależnienia</t></is></c><c r="H498" s="2" t="inlineStr" /><c r="I498" s="2" t="inlineStr" /><c r="J498" s="2" t="inlineStr" /><c r="K498" s="2" t="inlineStr"><is><t>jest agonistą receptorów opioidowych</t></is></c><c r="L498" s="2" t="inlineStr"><is><t>powoduje depresję ośrodka oddechowego</t></is></c><c r="M498" s="2" t="inlineStr" /><c r="N498" s="2" t="inlineStr" /><c r="O498" s="2" t="inlineStr" /><c r="P498" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2019/20 - 2 termin</t></is></c><c r="Q498" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="499"><c r="A499" s="2" t="inlineStr"><is><t>LEKI PRZECIWLĘKOWE</t></is></c><c r="B499" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C499" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D499" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E499" s="2" t="inlineStr"><is><t>Antagonizm wobec receptora stanowi zasadniczy mechanizm działania:</t></is></c><c r="F499" s="2" t="inlineStr"><is><t>flumazenilu</t></is></c><c r="G499" s="2" t="inlineStr" /><c r="H499" s="2" t="inlineStr" /><c r="I499" s="2" t="inlineStr" /><c r="J499" s="2" t="inlineStr" /><c r="K499" s="2" t="inlineStr"><is><t>Cyklosporyny</t></is></c><c r="L499" s="2" t="inlineStr"><is><t>Lorazepamu</t></is></c><c r="M499" s="2" t="inlineStr"><is><t>Tapentadolu</t></is></c><c r="N499" s="2" t="inlineStr" /><c r="O499" s="2" t="inlineStr" /><c r="P499" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2019/20 - 2 termin</t></is></c><c r="Q499" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="500"><c r="A500" s="2" t="inlineStr"><is><t>CUKRZYCA</t></is></c><c r="B500" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C500" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D500" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E500" s="2" t="inlineStr"><is><t>Zmniejszenie masy ciała może wiązać się z terapią:</t></is></c><c r="F500" s="2" t="inlineStr"><is><t>Lewotyroksyną</t></is></c><c r="G500" s="2" t="inlineStr"><is><t>metforminą</t></is></c><c r="H500" s="2" t="inlineStr" /><c r="I500" s="2" t="inlineStr" /><c r="J500" s="2" t="inlineStr" /><c r="K500" s="2" t="inlineStr"><is><t>Olanzapiną</t></is></c><c r="L500" s="2" t="inlineStr"><is><t>Prednizonem</t></is></c><c r="M500" s="2" t="inlineStr" /><c r="N500" s="2" t="inlineStr" /><c r="O500" s="2" t="inlineStr" /><c r="P500" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2019/20 - 2 termin</t></is></c><c r="Q500" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="501"><c r="A501" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B501" s="2" t="inlineStr"><is><t>Interakcje</t></is></c><c r="C501" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D501" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E501" s="2" t="inlineStr"><is><t>Wskaż prawidłowe skojarzenie lek – działanie niepożądane:</t></is></c><c r="F501" s="2" t="inlineStr"><is><t>tietylperazyna - akatyzja</t></is></c><c r="G501" s="2" t="inlineStr"><is><t>metoklopramid – późne dyskinezy</t></is></c><c r="H501" s="2" t="inlineStr"><is><t>ondansetron – wydłużenie odstępu QT</t></is></c><c r="I501" s="2" t="inlineStr" /><c r="J501" s="2" t="inlineStr" /><c r="K501" s="2" t="inlineStr"><is><t>dimenhydrynat - wymioty</t></is></c><c r="L501" s="2" t="inlineStr" /><c r="M501" s="2" t="inlineStr" /><c r="N501" s="2" t="inlineStr" /><c r="O501" s="2" t="inlineStr" /><c r="P501" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2019/20 - 2 termin</t></is></c><c r="Q501" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="502"><c r="A502" s="2" t="inlineStr"><is><t>FARMAKOKINETYKA</t></is></c><c r="B502" s="2" t="inlineStr"><is><t>Interakcje</t></is></c><c r="C502" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D502" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E502" s="2" t="inlineStr"><is><t>Charakterystyka Produktu Leczniczego zawiera informacje o:</t></is></c><c r="F502" s="2" t="inlineStr"><is><t>mechanizmie działania</t></is></c><c r="G502" s="2" t="inlineStr"><is><t>interakcjach</t></is></c><c r="H502" s="2" t="inlineStr"><is><t>substancjach pomocniczych</t></is></c><c r="I502" s="2" t="inlineStr"><is><t>działaniach niepożądanych</t></is></c><c r="J502" s="2" t="inlineStr" /><c r="K502" s="2" t="inlineStr" /><c r="L502" s="2" t="inlineStr" /><c r="M502" s="2" t="inlineStr" /><c r="N502" s="2" t="inlineStr" /><c r="O502" s="2" t="inlineStr" /><c r="P502" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2019/20 - 2 termin</t></is></c><c r="Q502" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="503"><c r="A503" s="2" t="inlineStr"><is><t>LEKI PRZECIWPSYCHOTYCZNE</t></is></c><c r="B503" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C503" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D503" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E503" s="2" t="inlineStr"><is><t>Kwetiapina:</t></is></c><c r="F503" s="2" t="inlineStr"><is><t>wpływa na przekaźnictwo serotoninergiczne</t></is></c><c r="G503" s="2" t="inlineStr"><is><t>może być przyczyną zwiększenia masy ciała</t></is></c><c r="H503" s="2" t="inlineStr"><is><t>jest preferowana u pacjentów z współistniejącą chorobą Parkinsona</t></is></c><c r="I503" s="2" t="inlineStr"><is><t>reprezentuje neuroleptyki atypowe</t></is></c><c r="J503" s="2" t="inlineStr" /><c r="K503" s="2" t="inlineStr" /><c r="L503" s="2" t="inlineStr" /><c r="M503" s="2" t="inlineStr" /><c r="N503" s="2" t="inlineStr" /><c r="O503" s="2" t="inlineStr" /><c r="P503" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2019/20 - 2 termin</t></is></c><c r="Q503" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="504"><c r="A504" s="2" t="inlineStr"><is><t>LEKI PRZECIWDEPRESYJNE</t></is></c><c r="B504" s="2" t="inlineStr"><is><t>Struktura chemiczna</t></is></c><c r="C504" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D504" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E504" s="2" t="inlineStr"><is><t>Trójpierścieniowe leki przeciwdepresyjne:</t></is></c><c r="F504" s="2" t="inlineStr"><is><t>blokują receptory histaminowe</t></is></c><c r="G504" s="2" t="inlineStr"><is><t>hamują wychwyt zwrotny dopaminy</t></is></c><c r="H504" s="2" t="inlineStr" /><c r="I504" s="2" t="inlineStr" /><c r="J504" s="2" t="inlineStr" /><c r="K504" s="2" t="inlineStr"><is><t>pobudzają receptory muskarynowe</t></is></c><c r="L504" s="2" t="inlineStr"><is><t>nie wpływają na przekaźnictwo serotoninergiczne</t></is></c><c r="M504" s="2" t="inlineStr" /><c r="N504" s="2" t="inlineStr" /><c r="O504" s="2" t="inlineStr" /><c r="P504" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2019/20 - 2 termin</t></is></c><c r="Q504" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="505"><c r="A505" s="2" t="inlineStr"><is><t>FARMAKOKINETYKA</t></is></c><c r="B505" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C505" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D505" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E505" s="2" t="inlineStr"><is><t>Na dostępność biologiczną leku może mieć wpływ:</t></is></c><c r="F505" s="2" t="inlineStr"><is><t>stopień uwalniania substancji czynnej</t></is></c><c r="G505" s="2" t="inlineStr"><is><t>efekt I przejścia</t></is></c><c r="H505" s="2" t="inlineStr"><is><t>szybkość transportu substancji czynnej przez błony biologiczne</t></is></c><c r="I505" s="2" t="inlineStr" /><c r="J505" s="2" t="inlineStr" /><c r="K505" s="2" t="inlineStr"><is><t>stopień wiązania z białkami krwi</t></is></c><c r="L505" s="2" t="inlineStr" /><c r="M505" s="2" t="inlineStr" /><c r="N505" s="2" t="inlineStr" /><c r="O505" s="2" t="inlineStr" /><c r="P505" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2019/20 - 2 termin</t></is></c><c r="Q505" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="506"><c r="A506" s="2" t="inlineStr"><is><t>FARMAKOKINETYKA</t></is></c><c r="B506" s="2" t="inlineStr"><is><t>Farmakokinetyka</t></is></c><c r="C506" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D506" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E506" s="2" t="inlineStr"><is><t>Stan stacjonarny leku ustala się:</t></is></c><c r="F506" s="2" t="inlineStr"><is><t>po okresie równym około 4–5 T1/2</t></is></c><c r="G506" s="2" t="inlineStr" /><c r="H506" s="2" t="inlineStr" /><c r="I506" s="2" t="inlineStr" /><c r="J506" s="2" t="inlineStr" /><c r="K506" s="2" t="inlineStr"><is><t>w momencie, który zależy od dawki leku</t></is></c><c r="L506" s="2" t="inlineStr"><is><t>jedynie w wyniku wielokrotnego podania doustnego</t></is></c><c r="M506" s="2" t="inlineStr"><is><t>w czasie wprost proporcjonalnym do klirensu leku</t></is></c><c r="N506" s="2" t="inlineStr" /><c r="O506" s="2" t="inlineStr" /><c r="P506" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2019/20 - 2 termin</t></is></c><c r="Q506" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="507"><c r="A507" s="2" t="inlineStr"><is><t>FARMAKOKINETYKA</t></is></c><c r="B507" s="2" t="inlineStr"><is><t>Farmakokinetyka</t></is></c><c r="C507" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D507" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E507" s="2" t="inlineStr"><is><t>Biologiczny okres półtrwania (T1/2):</t></is></c><c r="F507" s="2" t="inlineStr"><is><t>zależy od objętości dystrybucji</t></is></c><c r="G507" s="2" t="inlineStr"><is><t>jest odwrotnie proporcjonalny do klirensu całkowitego</t></is></c><c r="H507" s="2" t="inlineStr"><is><t>ma wpływ na moment osiągnięcia stanu stacjonarnego</t></is></c><c r="I507" s="2" t="inlineStr" /><c r="J507" s="2" t="inlineStr" /><c r="K507" s="2" t="inlineStr"><is><t>zależy od szybkości wchłaniania</t></is></c><c r="L507" s="2" t="inlineStr" /><c r="M507" s="2" t="inlineStr" /><c r="N507" s="2" t="inlineStr" /><c r="O507" s="2" t="inlineStr" /><c r="P507" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2019/20 - 2 termin</t></is></c><c r="Q507" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="508"><c r="A508" s="2" t="inlineStr"><is><t>NARKOTYCZNE LEKI PRZECIWBÓLOWE</t></is></c><c r="B508" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C508" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D508" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E508" s="2" t="inlineStr"><is><t>Wskaż prawidłowe stwierdzenie:</t></is></c><c r="F508" s="2" t="inlineStr"><is><t>tramadol jest inhibitorem wychwytu zwrotnego serotoniny</t></is></c><c r="G508" s="2" t="inlineStr"><is><t>petydyna jest metabolizowana do neurotoksycznego metabolitu</t></is></c><c r="H508" s="2" t="inlineStr" /><c r="I508" s="2" t="inlineStr" /><c r="J508" s="2" t="inlineStr" /><c r="K508" s="2" t="inlineStr"><is><t>buprenorfinę charakteryzuje wysoki potencjał uzależniający</t></is></c><c r="L508" s="2" t="inlineStr"><is><t>fentanyl w plastrach jest stosowany w leczeniu pooperacyjnego bólu ostrego</t></is></c><c r="M508" s="2" t="inlineStr" /><c r="N508" s="2" t="inlineStr" /><c r="O508" s="2" t="inlineStr" /><c r="P508" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2019/20 - 2 termin</t></is></c><c r="Q508" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="509"><c r="A509" s="2" t="inlineStr"><is><t>NADCIŚNIENIE TĘTNICZE</t></is></c><c r="B509" s="2" t="inlineStr"><is><t>Antidotum</t></is></c><c r="C509" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D509" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E509" s="2" t="inlineStr"><is><t>Do typowych objawów zatrucia opioidami należą:</t></is></c><c r="F509" s="2" t="inlineStr"><is><t>Śpiączka</t></is></c><c r="G509" s="2" t="inlineStr"><is><t>Depresja oddechowa</t></is></c><c r="H509" s="2" t="inlineStr" /><c r="I509" s="2" t="inlineStr" /><c r="J509" s="2" t="inlineStr" /><c r="K509" s="2" t="inlineStr"><is><t>Wzrost ciśnienia tętniczego</t></is></c><c r="L509" s="2" t="inlineStr"><is><t>wzrost temperatury ciała</t></is></c><c r="M509" s="2" t="inlineStr" /><c r="N509" s="2" t="inlineStr" /><c r="O509" s="2" t="inlineStr" /><c r="P509" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2019/20 - 2 termin</t></is></c><c r="Q509" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="510"><c r="A510" s="2" t="inlineStr"><is><t>CUKRZYCA</t></is></c><c r="B510" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C510" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D510" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E510" s="2" t="inlineStr"><is><t>Wskaż prawidłowe stwierdzenie dotyczące glikokortykosteroidów:</t></is></c><c r="F510" s="2" t="inlineStr"><is><t>Działają za pośrednictwem receptorów wewnątrzkomórkowych</t></is></c><c r="G510" s="2" t="inlineStr"><is><t>mechanizm niegenomowy odpowiedzialny jest za ich działanie rozkurczające mięśniówkę dróg oddechowych</t></is></c><c r="H510" s="2" t="inlineStr"><is><t>Nagłe ich odstawienie po co najmniej tygodniowym zastosowaniu dawek farmakologicznych może być przyczyną ostrej niewydolności kory nadnerczy</t></is></c><c r="I510" s="2" t="inlineStr" /><c r="J510" s="2" t="inlineStr" /><c r="K510" s="2" t="inlineStr"><is><t>Powodują zmniejszenie zapotrzebowania na insulinę u chorych na cukrzycę</t></is></c><c r="L510" s="2" t="inlineStr" /><c r="M510" s="2" t="inlineStr" /><c r="N510" s="2" t="inlineStr" /><c r="O510" s="2" t="inlineStr" /><c r="P510" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2019/20 - 2 termin</t></is></c><c r="Q510" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="511"><c r="A511" s="2" t="inlineStr"><is><t>CUKRZYCA</t></is></c><c r="B511" s="2" t="inlineStr"><is><t>Sposób podania</t></is></c><c r="C511" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D511" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E511" s="2" t="inlineStr"><is><t>Insulina ludzka neutralna:</t></is></c><c r="F511" s="2" t="inlineStr"><is><t>działa za pośrednictwem receptora błonowego</t></is></c><c r="G511" s="2" t="inlineStr"><is><t>jest otrzymywana metodą rekombinacji DNA</t></is></c><c r="H511" s="2" t="inlineStr" /><c r="I511" s="2" t="inlineStr" /><c r="J511" s="2" t="inlineStr" /><c r="K511" s="2" t="inlineStr"><is><t>może być podawana doustnie</t></is></c><c r="L511" s="2" t="inlineStr"><is><t>jest analogiem długodziałającym</t></is></c><c r="M511" s="2" t="inlineStr" /><c r="N511" s="2" t="inlineStr" /><c r="O511" s="2" t="inlineStr" /><c r="P511" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2019/20 - 2 termin</t></is></c><c r="Q511" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="512"><c r="A512" s="2" t="inlineStr"><is><t>LEKI PRZECIWNOWOTWOROWE</t></is></c><c r="B512" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C512" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D512" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E512" s="2" t="inlineStr"><is><t>Wskaż prawdziwe połączenie lek – wskazanie:</t></is></c><c r="F512" s="2" t="inlineStr"><is><t>zolpidem-bezsenność</t></is></c><c r="G512" s="2" t="inlineStr"><is><t>ondansetron – wymioty w przebiegu chemioterapii przeciwnowotworowej</t></is></c><c r="H512" s="2" t="inlineStr"><is><t>alprazolam-napady paniki</t></is></c><c r="I512" s="2" t="inlineStr"><is><t>fluoksetyna–epizody dużej depresji</t></is></c><c r="J512" s="2" t="inlineStr" /><c r="K512" s="2" t="inlineStr" /><c r="L512" s="2" t="inlineStr" /><c r="M512" s="2" t="inlineStr" /><c r="N512" s="2" t="inlineStr" /><c r="O512" s="2" t="inlineStr" /><c r="P512" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2019/20 - 2 termin</t></is></c><c r="Q512" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="513"><c r="A513" s="2" t="inlineStr"><is><t>NADCIŚNIENIE TĘTNICZE</t></is></c><c r="B513" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C513" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D513" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E513" s="2" t="inlineStr"><is><t>Stosowanie estrogenów może być przyczyną:</t></is></c><c r="F513" s="2" t="inlineStr"><is><t>wzrostu ciśnienia tętniczego krwi</t></is></c><c r="G513" s="2" t="inlineStr"><is><t>kamicy żółciowej</t></is></c><c r="H513" s="2" t="inlineStr"><is><t>wzrostu ryzyka wystąpienia raka piersi</t></is></c><c r="I513" s="2" t="inlineStr"><is><t>zatorowości płucnej</t></is></c><c r="J513" s="2" t="inlineStr" /><c r="K513" s="2" t="inlineStr" /><c r="L513" s="2" t="inlineStr" /><c r="M513" s="2" t="inlineStr" /><c r="N513" s="2" t="inlineStr" /><c r="O513" s="2" t="inlineStr" /><c r="P513" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2019/20 - 2 termin</t></is></c><c r="Q513" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="514"><c r="A514" s="2" t="inlineStr"><is><t>NIEOPIOIDOWE LEKI PRZECIWBÓLOWE</t></is></c><c r="B514" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C514" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D514" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E514" s="2" t="inlineStr"><is><t>Kwas acetylosalicylowy:</t></is></c><c r="F514" s="2" t="inlineStr"><is><t>może być przyczyną wystąpienia szczególnej postaci astmy</t></is></c><c r="G514" s="2" t="inlineStr"><is><t>nieodwracalnie hamuje COX</t></is></c><c r="H514" s="2" t="inlineStr" /><c r="I514" s="2" t="inlineStr" /><c r="J514" s="2" t="inlineStr" /><c r="K514" s="2" t="inlineStr"><is><t>zwiększa ryzyko sercowo-naczyniowe</t></is></c><c r="L514" s="2" t="inlineStr"><is><t>podawany łącznie z ibuprofenem wykazuje silniejszy efekt przeciwzapalny</t></is></c><c r="M514" s="2" t="inlineStr" /><c r="N514" s="2" t="inlineStr" /><c r="O514" s="2" t="inlineStr" /><c r="P514" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2019/20 - 2 termin</t></is></c><c r="Q514" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="515"><c r="A515" s="2" t="inlineStr"><is><t>NIEOPIOIDOWE LEKI PRZECIWBÓLOWE</t></is></c><c r="B515" s="2" t="inlineStr"><is><t>Ciąża</t></is></c><c r="C515" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D515" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E515" s="2" t="inlineStr"><is><t>Paracetamol:</t></is></c><c r="F515" s="2" t="inlineStr"><is><t>u chorych przewlekle niedożywionych może działać hepatotoksycznie</t></is></c><c r="G515" s="2" t="inlineStr" /><c r="H515" s="2" t="inlineStr" /><c r="I515" s="2" t="inlineStr" /><c r="J515" s="2" t="inlineStr" /><c r="K515" s="2" t="inlineStr"><is><t>działa przeciwbólowo i przeciwzapalnie</t></is></c><c r="L515" s="2" t="inlineStr"><is><t>zwiększa ryzyko sercowo-naczyniowe</t></is></c><c r="M515" s="2" t="inlineStr"><is><t>wykazuje działanie teratogenne</t></is></c><c r="N515" s="2" t="inlineStr" /><c r="O515" s="2" t="inlineStr" /><c r="P515" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2019/20 - 2 termin</t></is></c><c r="Q515" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="516"><c r="A516" s="2" t="inlineStr"><is><t>NIEOPIOIDOWE LEKI PRZECIWBÓLOWE</t></is></c><c r="B516" s="2" t="inlineStr"><is><t>Ciąża</t></is></c><c r="C516" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D516" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E516" s="2" t="inlineStr"><is><t>Metamizol:</t></is></c><c r="F516" s="2" t="inlineStr"><is><t>działa przeciwbólowo i przeciwgorączkowo</t></is></c><c r="G516" s="2" t="inlineStr"><is><t>działa spazmolitycznie</t></is></c><c r="H516" s="2" t="inlineStr"><is><t>może być przyczyną agranulocytozy</t></is></c><c r="I516" s="2" t="inlineStr" /><c r="J516" s="2" t="inlineStr" /><c r="K516" s="2" t="inlineStr"><is><t>może być bezpiecznie stosowany w ciąży</t></is></c><c r="L516" s="2" t="inlineStr" /><c r="M516" s="2" t="inlineStr" /><c r="N516" s="2" t="inlineStr" /><c r="O516" s="2" t="inlineStr" /><c r="P516" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2019/20 - 2 termin</t></is></c><c r="Q516" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="517"><c r="A517" s="2" t="inlineStr"><is><t>HEMOSTAZA</t></is></c><c r="B517" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C517" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D517" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E517" s="2" t="inlineStr"><is><t>Do leków biotechnologicznych należą:</t></is></c><c r="F517" s="2" t="inlineStr"><is><t>szczepionki</t></is></c><c r="G517" s="2" t="inlineStr"><is><t>przeciwciała monoklonalne</t></is></c><c r="H517" s="2" t="inlineStr"><is><t>Hormony</t></is></c><c r="I517" s="2" t="inlineStr"><is><t>czynniki krzepnięcia</t></is></c><c r="J517" s="2" t="inlineStr" /><c r="K517" s="2" t="inlineStr" /><c r="L517" s="2" t="inlineStr" /><c r="M517" s="2" t="inlineStr" /><c r="N517" s="2" t="inlineStr" /><c r="O517" s="2" t="inlineStr" /><c r="P517" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2019/20 - 2 termin</t></is></c><c r="Q517" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="518"><c r="A518" s="2" t="inlineStr"><is><t>LEKI PRZECIWDEPRESYJNE</t></is></c><c r="B518" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C518" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D518" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E518" s="2" t="inlineStr"><is><t>Wskaż prawidłowe stwierdzenie:</t></is></c><c r="F518" s="2" t="inlineStr"><is><t>amitryptylina znajduje zastosowanie w terapii bólu neuropatycznego</t></is></c><c r="G518" s="2" t="inlineStr"><is><t>escitalopram hamuje wychwyt zwrotny serotoniny</t></is></c><c r="H518" s="2" t="inlineStr"><is><t>moklobemid może być niebezpieczny u pacjentów spożywających sery dojrzewające</t></is></c><c r="I518" s="2" t="inlineStr"><is><t>mianseryna jest przeciwskazana u osób z padaczką</t></is></c><c r="J518" s="2" t="inlineStr" /><c r="K518" s="2" t="inlineStr" /><c r="L518" s="2" t="inlineStr" /><c r="M518" s="2" t="inlineStr" /><c r="N518" s="2" t="inlineStr" /><c r="O518" s="2" t="inlineStr" /><c r="P518" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2019/20 - 2 termin</t></is></c><c r="Q518" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="519"><c r="A519" s="2" t="inlineStr"><is><t>LEKI ROŚLINNE I SUPLEMENTY</t></is></c><c r="B519" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C519" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D519" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E519" s="2" t="inlineStr"><is><t>Doustne preparaty żelaza:</t></is></c><c r="F519" s="2" t="inlineStr"><is><t>najlepiej przyswajalne zawierają żelazo dwuwartościowe</t></is></c><c r="G519" s="2" t="inlineStr"><is><t>należy przyjmować przez okres 3 miesięcy po uzyskaniu normalizacji morfologii</t></is></c><c r="H519" s="2" t="inlineStr" /><c r="I519" s="2" t="inlineStr" /><c r="J519" s="2" t="inlineStr" /><c r="K519" s="2" t="inlineStr"><is><t>należy przyjmować z posiłkiem wysokotłuszczowym</t></is></c><c r="L519" s="2" t="inlineStr"><is><t>mogą być przyczyną jasno-żółtego zabarwienia stolca</t></is></c><c r="M519" s="2" t="inlineStr" /><c r="N519" s="2" t="inlineStr" /><c r="O519" s="2" t="inlineStr" /><c r="P519" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2019/20 - 2 termin</t></is></c><c r="Q519" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="520"><c r="A520" s="2" t="inlineStr"><is><t>PADACZKA</t></is></c><c r="B520" s="2" t="inlineStr"><is><t>Farmakokinetyka</t></is></c><c r="C520" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D520" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E520" s="2" t="inlineStr"><is><t>Diazepam:</t></is></c><c r="F520" s="2" t="inlineStr"><is><t>działa sedatywnie</t></is></c><c r="G520" s="2" t="inlineStr"><is><t>działa powyżej 24 godzin</t></is></c><c r="H520" s="2" t="inlineStr" /><c r="I520" s="2" t="inlineStr" /><c r="J520" s="2" t="inlineStr" /><c r="K520" s="2" t="inlineStr"><is><t>obniża próg drgawkowy</t></is></c><c r="L520" s="2" t="inlineStr"><is><t>nie podlega metabolizmowi</t></is></c><c r="M520" s="2" t="inlineStr" /><c r="N520" s="2" t="inlineStr" /><c r="O520" s="2" t="inlineStr" /><c r="P520" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2019/20 - 2 termin</t></is></c><c r="Q520" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="521"><c r="A521" s="2" t="inlineStr"><is><t>PADACZKA</t></is></c><c r="B521" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C521" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D521" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E521" s="2" t="inlineStr"><is><t>Wskaż prawidłowe połączenie lek przeciwpadaczkowy – mechanizm działania: B</t></is></c><c r="F521" s="2" t="inlineStr"><is><t>fenytoina – hamowanie kanałów sodowych</t></is></c><c r="G521" s="2" t="inlineStr"><is><t>karbamazepina - hamowanie kanałów sodowych i kanałów wapniowych</t></is></c><c r="H521" s="2" t="inlineStr" /><c r="I521" s="2" t="inlineStr" /><c r="J521" s="2" t="inlineStr" /><c r="K521" s="2" t="inlineStr"><is><t>fenobarbital – hamowanie transmisji GABA-ergicznej</t></is></c><c r="L521" s="2" t="inlineStr"><is><t>kwas walproinowy – hamowanie kanałów sodowych i transmisji GABA-ergicznej</t></is></c><c r="M521" s="2" t="inlineStr" /><c r="N521" s="2" t="inlineStr" /><c r="O521" s="2" t="inlineStr" /><c r="P521" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2019/20 - 2 termin</t></is></c><c r="Q521" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="522"><c r="A522" s="2" t="inlineStr"><is><t>PADACZKA</t></is></c><c r="B522" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C522" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D522" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E522" s="2" t="inlineStr"><is><t>Selektywne inhibitory wychwytu zwrotnego serotoniny (SSRI) charakteryzuje:</t></is></c><c r="F522" s="2" t="inlineStr"><is><t>niewielki wpływ na układ krążenia</t></is></c><c r="G522" s="2" t="inlineStr"><is><t>małe ryzyko teratogenności</t></is></c><c r="H522" s="2" t="inlineStr" /><c r="I522" s="2" t="inlineStr" /><c r="J522" s="2" t="inlineStr" /><c r="K522" s="2" t="inlineStr"><is><t>obniżanie progu drgawkowego</t></is></c><c r="L522" s="2" t="inlineStr"><is><t>brak ryzyka wystąpienia istotnych interakcji z inhibitorami MAO</t></is></c><c r="M522" s="2" t="inlineStr" /><c r="N522" s="2" t="inlineStr" /><c r="O522" s="2" t="inlineStr" /><c r="P522" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2019/20 - 2 termin</t></is></c><c r="Q522" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="523"><c r="A523" s="2" t="inlineStr"><is><t>NARKOTYCZNE LEKI PRZECIWBÓLOWE</t></is></c><c r="B523" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C523" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D523" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E523" s="2" t="inlineStr"><is><t>Potencjał uzależniający wykazują:</t></is></c><c r="F523" s="2" t="inlineStr"><is><t>Kanabinoidy</t></is></c><c r="G523" s="2" t="inlineStr"><is><t>dysocjacyjne środki znieczulające</t></is></c><c r="H523" s="2" t="inlineStr"><is><t>Benzodiazepiny</t></is></c><c r="I523" s="2" t="inlineStr"><is><t>opioidy</t></is></c><c r="J523" s="2" t="inlineStr" /><c r="K523" s="2" t="inlineStr" /><c r="L523" s="2" t="inlineStr" /><c r="M523" s="2" t="inlineStr" /><c r="N523" s="2" t="inlineStr" /><c r="O523" s="2" t="inlineStr" /><c r="P523" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2019/20 - 2 termin</t></is></c><c r="Q523" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="524"><c r="A524" s="2" t="inlineStr"><is><t>LEKI IMMUNOSUPRESYJNE</t></is></c><c r="B524" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C524" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D524" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E524" s="2" t="inlineStr"><is><t>Działanie immunosupresyjne wykazują:</t></is></c><c r="F524" s="2" t="inlineStr"><is><t>inhibitory kalcyneuryny</t></is></c><c r="G524" s="2" t="inlineStr"><is><t>alkilujące inhibitory proliferacji</t></is></c><c r="H524" s="2" t="inlineStr" /><c r="I524" s="2" t="inlineStr" /><c r="J524" s="2" t="inlineStr" /><c r="K524" s="2" t="inlineStr"><is><t>czynniki stymulujące tworzenie kolonii granulocytów</t></is></c><c r="L524" s="2" t="inlineStr"><is><t>interferon beta</t></is></c><c r="M524" s="2" t="inlineStr" /><c r="N524" s="2" t="inlineStr" /><c r="O524" s="2" t="inlineStr" /><c r="P524" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2019/20 - 2 termin</t></is></c><c r="Q524" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="525"><c r="A525" s="2" t="inlineStr"><is><t>UKŁAD POKARMOWY</t></is></c><c r="B525" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C525" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D525" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E525" s="2" t="inlineStr"><is><t>Hamowanie transmisji dopaminergicznej może być przyczyną wystąpienia:</t></is></c><c r="F525" s="2" t="inlineStr"><is><t>Dyskinez</t></is></c><c r="G525" s="2" t="inlineStr"><is><t>zwiększenia masy ciała</t></is></c><c r="H525" s="2" t="inlineStr"><is><t>działania przeciwwymiotnego</t></is></c><c r="I525" s="2" t="inlineStr" /><c r="J525" s="2" t="inlineStr" /><c r="K525" s="2" t="inlineStr"><is><t>hipoprolaktynemii</t></is></c><c r="L525" s="2" t="inlineStr" /><c r="M525" s="2" t="inlineStr" /><c r="N525" s="2" t="inlineStr" /><c r="O525" s="2" t="inlineStr" /><c r="P525" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2019/20 - 2 termin</t></is></c><c r="Q525" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="526"><c r="A526" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B526" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C526" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D526" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E526" s="2" t="inlineStr"><is><t>W przypadku rozpoznania anginy paciorkowcowej można zastosować:</t></is></c><c r="F526" s="2" t="inlineStr"><is><t>Klindamycynę</t></is></c><c r="G526" s="2" t="inlineStr"><is><t>Fenoksymetylopenicylinę</t></is></c><c r="H526" s="2" t="inlineStr" /><c r="I526" s="2" t="inlineStr" /><c r="J526" s="2" t="inlineStr" /><c r="K526" s="2" t="inlineStr"><is><t>Cyprofloksacynę</t></is></c><c r="L526" s="2" t="inlineStr"><is><t>Amikacynę</t></is></c><c r="M526" s="2" t="inlineStr" /><c r="N526" s="2" t="inlineStr" /><c r="O526" s="2" t="inlineStr" /><c r="P526" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2019/20 - 1 termin (online)</t></is></c><c r="Q526" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="527"><c r="A527" s="2" t="inlineStr"><is><t>LEKI PRZECIWWIRUSOWE</t></is></c><c r="B527" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C527" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D527" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E527" s="2" t="inlineStr"><is><t>Wskaż prawidłowe stwierdzenie:</t></is></c><c r="F527" s="2" t="inlineStr"><is><t>Replikacja wirusa może zostać wznowiona po odstawieniu leków, które hamują czynną replikację</t></is></c><c r="G527" s="2" t="inlineStr"><is><t>Obecnie stosowane leki wykazują aktywność wobec wirusów w fazie replikacji</t></is></c><c r="H527" s="2" t="inlineStr" /><c r="I527" s="2" t="inlineStr" /><c r="J527" s="2" t="inlineStr" /><c r="K527" s="2" t="inlineStr"><is><t>Niektóre leki działają na wirusy będące w fazie utajenia</t></is></c><c r="L527" s="2" t="inlineStr"><is><t>Większość wirusów opornych na lek pochodzi od pacjentów z prawidłową odpornością</t></is></c><c r="M527" s="2" t="inlineStr" /><c r="N527" s="2" t="inlineStr" /><c r="O527" s="2" t="inlineStr" /><c r="P527" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2019/20 - 1 termin (online)</t></is></c><c r="Q527" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="528"><c r="A528" s="2" t="inlineStr"><is><t>LEKI PRZECIWPASOŻYTNICZE</t></is></c><c r="B528" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C528" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D528" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E528" s="2" t="inlineStr"><is><t>Chlorochina:</t></is></c><c r="F528" s="2" t="inlineStr"><is><t>Może być przyczyną wypadania włosów</t></is></c><c r="G528" s="2" t="inlineStr"><is><t>Niszczy formy wewnątrzkrwinkowe pierwotniaka</t></is></c><c r="H528" s="2" t="inlineStr" /><c r="I528" s="2" t="inlineStr" /><c r="J528" s="2" t="inlineStr" /><c r="K528" s="2" t="inlineStr"><is><t>Jest stosowana w każdym schemacie profilaktyki malarii</t></is></c><c r="L528" s="2" t="inlineStr"><is><t>Jest szczególnie skuteczna w leczeniu zakażenia Plasmodium falciparium</t></is></c><c r="M528" s="2" t="inlineStr" /><c r="N528" s="2" t="inlineStr" /><c r="O528" s="2" t="inlineStr" /><c r="P528" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2019/20 - 1 termin (online)</t></is></c><c r="Q528" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="529"><c r="A529" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B529" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C529" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D529" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E529" s="2" t="inlineStr"><is><t>Lek bakteriobójczy, którego aktywność przeciwbakteryjną najlepiej charakteryzuje AUC24/MIC, działający na bakterie atypowe. Lek jest wydalany głównie z moczem i jego stosowanie związane jest z ryzykiem wydłużenia odstępu QT. Opis może dotyczyć:</t></is></c><c r="F529" s="2" t="inlineStr"><is><t>Lewofloksacyny</t></is></c><c r="G529" s="2" t="inlineStr" /><c r="H529" s="2" t="inlineStr" /><c r="I529" s="2" t="inlineStr" /><c r="J529" s="2" t="inlineStr" /><c r="K529" s="2" t="inlineStr"><is><t>Doksycyliny</t></is></c><c r="L529" s="2" t="inlineStr"><is><t>Klarytromycyny</t></is></c><c r="M529" s="2" t="inlineStr"><is><t>Linezolidu</t></is></c><c r="N529" s="2" t="inlineStr" /><c r="O529" s="2" t="inlineStr" /><c r="P529" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2019/20 - 1 termin (online)</t></is></c><c r="Q529" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="530"><c r="A530" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B530" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C530" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D530" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E530" s="2" t="inlineStr"><is><t>W zakażeniach o etiologii Pseudomonas aeruginosa uzasadnione może być podanie:</t></is></c><c r="F530" s="2" t="inlineStr"><is><t>Piperacykliny z tazobaktamem</t></is></c><c r="G530" s="2" t="inlineStr"><is><t>Gentamycyny</t></is></c><c r="H530" s="2" t="inlineStr"><is><t>Cyprofloksacyny</t></is></c><c r="I530" s="2" t="inlineStr"><is><t>Ceftazydymu</t></is></c><c r="J530" s="2" t="inlineStr" /><c r="K530" s="2" t="inlineStr" /><c r="L530" s="2" t="inlineStr" /><c r="M530" s="2" t="inlineStr" /><c r="N530" s="2" t="inlineStr" /><c r="O530" s="2" t="inlineStr" /><c r="P530" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2019/20 - 1 termin (online)</t></is></c><c r="Q530" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="531"><c r="A531" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B531" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C531" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D531" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E531" s="2" t="inlineStr"><is><t>Po podaniu doustnym działa miejscowo:</t></is></c><c r="F531" s="2" t="inlineStr"><is><t>Ryfaksymina</t></is></c><c r="G531" s="2" t="inlineStr"><is><t>Fidaksomycyna</t></is></c><c r="H531" s="2" t="inlineStr" /><c r="I531" s="2" t="inlineStr" /><c r="J531" s="2" t="inlineStr" /><c r="K531" s="2" t="inlineStr"><is><t>Kwas fusydowy</t></is></c><c r="L531" s="2" t="inlineStr"><is><t>Norfloksacyna</t></is></c><c r="M531" s="2" t="inlineStr" /><c r="N531" s="2" t="inlineStr" /><c r="O531" s="2" t="inlineStr" /><c r="P531" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2019/20 - 1 termin (online)</t></is></c><c r="Q531" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="532"><c r="A532" s="2" t="inlineStr"><is><t>LEKI PRZECIWWIRUSOWE</t></is></c><c r="B532" s="2" t="inlineStr"><is><t>Interakcje</t></is></c><c r="C532" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D532" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E532" s="2" t="inlineStr"><is><t>Wskaż prawidłowe skojarzenie lek – punkt uchwytu:</t></is></c><c r="F532" s="2" t="inlineStr"><is><t>Acyklowir – polimeraza DNA</t></is></c><c r="G532" s="2" t="inlineStr"><is><t>Oseltamiwir – neuraminidaza</t></is></c><c r="H532" s="2" t="inlineStr"><is><t>Lamiwudyna – odwrotna transkryptaza</t></is></c><c r="I532" s="2" t="inlineStr"><is><t>Raltegrawir – integraza</t></is></c><c r="J532" s="2" t="inlineStr" /><c r="K532" s="2" t="inlineStr" /><c r="L532" s="2" t="inlineStr" /><c r="M532" s="2" t="inlineStr" /><c r="N532" s="2" t="inlineStr" /><c r="O532" s="2" t="inlineStr" /><c r="P532" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2019/20 - 1 termin (online)</t></is></c><c r="Q532" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="533"><c r="A533" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B533" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C533" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D533" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E533" s="2" t="inlineStr"><is><t>Wybierz właściwe skojarzenie wskazanie – lek, który można zastosować jako alternatywę dla antybiotków beta-laktamowych u pacjenta z nadwrażliwością na tę grupę leków przeciwbakteryjnych</t></is></c><c r="F533" s="2" t="inlineStr"><is><t>Borelioza – azytromycyna</t></is></c><c r="G533" s="2" t="inlineStr"><is><t>Zapalenie płuc o etiologii pneumokokowej – lewofloksacyna</t></is></c><c r="H533" s="2" t="inlineStr"><is><t>Profilaktyka okołozabiegowa - wankomycyna</t></is></c><c r="I533" s="2" t="inlineStr" /><c r="J533" s="2" t="inlineStr" /><c r="K533" s="2" t="inlineStr"><is><t>Urosepsa o etiologii Escherichia coli – linezolid</t></is></c><c r="L533" s="2" t="inlineStr" /><c r="M533" s="2" t="inlineStr" /><c r="N533" s="2" t="inlineStr" /><c r="O533" s="2" t="inlineStr" /><c r="P533" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2019/20 - 1 termin (online)</t></is></c><c r="Q533" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="534"><c r="A534" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B534" s="2" t="inlineStr"><is><t>Interakcje</t></is></c><c r="C534" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D534" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E534" s="2" t="inlineStr"><is><t>Wskaż prawidłowe skojarzenie lek – wskazanie:</t></is></c><c r="F534" s="2" t="inlineStr"><is><t>Metronidazol – lamblioza</t></is></c><c r="G534" s="2" t="inlineStr"><is><t>Spiramycyna – toksoplazmoza</t></is></c><c r="H534" s="2" t="inlineStr" /><c r="I534" s="2" t="inlineStr" /><c r="J534" s="2" t="inlineStr" /><c r="K534" s="2" t="inlineStr"><is><t>Nifuroksazyd – biegunka poantybiotykowa</t></is></c><c r="L534" s="2" t="inlineStr"><is><t>Amikacyna – borelioza</t></is></c><c r="M534" s="2" t="inlineStr" /><c r="N534" s="2" t="inlineStr" /><c r="O534" s="2" t="inlineStr" /><c r="P534" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2019/20 - 1 termin (online)</t></is></c><c r="Q534" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="535"><c r="A535" s="2" t="inlineStr"><is><t>LEKI PRZECIWGRZYBICZE</t></is></c><c r="B535" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C535" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D535" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E535" s="2" t="inlineStr"><is><t>Wskazaniem do doustnej terapii przeciwgrzybiczej jest:</t></is></c><c r="F535" s="2" t="inlineStr"><is><t>Nieskuteczność leczenia miejscowego</t></is></c><c r="G535" s="2" t="inlineStr"><is><t>Grzybica inwazyjna</t></is></c><c r="H535" s="2" t="inlineStr"><is><t>Stwierdzenie rozległych zmian skórnych</t></is></c><c r="I535" s="2" t="inlineStr" /><c r="J535" s="2" t="inlineStr" /><c r="K535" s="2" t="inlineStr"><is><t>Grzybica paznokci dotycząca pojedynczych płytek paznokciowych</t></is></c><c r="L535" s="2" t="inlineStr" /><c r="M535" s="2" t="inlineStr" /><c r="N535" s="2" t="inlineStr" /><c r="O535" s="2" t="inlineStr" /><c r="P535" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2019/20 - 1 termin (online)</t></is></c><c r="Q535" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="536"><c r="A536" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B536" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C536" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D536" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E536" s="2" t="inlineStr"><is><t>Działanie neurotoksyczne wykazuje:</t></is></c><c r="F536" s="2" t="inlineStr"><is><t>Linezolid</t></is></c><c r="G536" s="2" t="inlineStr"><is><t>Cyprofloksacyna</t></is></c><c r="H536" s="2" t="inlineStr"><is><t>Metronidazol</t></is></c><c r="I536" s="2" t="inlineStr" /><c r="J536" s="2" t="inlineStr" /><c r="K536" s="2" t="inlineStr"><is><t>Klindamycyna</t></is></c><c r="L536" s="2" t="inlineStr" /><c r="M536" s="2" t="inlineStr" /><c r="N536" s="2" t="inlineStr" /><c r="O536" s="2" t="inlineStr" /><c r="P536" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2019/20 - 1 termin (online)</t></is></c><c r="Q536" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="537"><c r="A537" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B537" s="2" t="inlineStr"><is><t>Interakcje</t></is></c><c r="C537" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D537" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E537" s="2" t="inlineStr"><is><t>Wskaż prawidłowe skojarzenie lek – mechanizm działania (należy uwzględnić główny mechanizm działania):</t></is></c><c r="F537" s="2" t="inlineStr"><is><t>Azytromycyna – hamowanie syntezy białek</t></is></c><c r="G537" s="2" t="inlineStr"><is><t>Daptomycyna – uszkodzenie błony komórkowej</t></is></c><c r="H537" s="2" t="inlineStr" /><c r="I537" s="2" t="inlineStr" /><c r="J537" s="2" t="inlineStr" /><c r="K537" s="2" t="inlineStr"><is><t>Cyprofloksacyna – hamowanie biosyntezy ściany komórkowej</t></is></c><c r="L537" s="2" t="inlineStr"><is><t>Amoksycyina – hamowanie syntezy DNA</t></is></c><c r="M537" s="2" t="inlineStr" /><c r="N537" s="2" t="inlineStr" /><c r="O537" s="2" t="inlineStr" /><c r="P537" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2019/20 - 1 termin (online)</t></is></c><c r="Q537" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="538"><c r="A538" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B538" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C538" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D538" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E538" s="2" t="inlineStr"><is><t>W schematach eradykacji Helicobacter pylori znajdują zastosowanie:</t></is></c><c r="F538" s="2" t="inlineStr"><is><t>Amoksycylina</t></is></c><c r="G538" s="2" t="inlineStr"><is><t>Metronidazol</t></is></c><c r="H538" s="2" t="inlineStr" /><c r="I538" s="2" t="inlineStr" /><c r="J538" s="2" t="inlineStr" /><c r="K538" s="2" t="inlineStr"><is><t>Lewofloksacyna</t></is></c><c r="L538" s="2" t="inlineStr"><is><t>Tetracyklina</t></is></c><c r="M538" s="2" t="inlineStr" /><c r="N538" s="2" t="inlineStr" /><c r="O538" s="2" t="inlineStr" /><c r="P538" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2019/20 - 1 termin (online)</t></is></c><c r="Q538" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="539"><c r="A539" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B539" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C539" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D539" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E539" s="2" t="inlineStr"><is><t>Linezolid może być skuteczny w zakażeniach szczepami:</t></is></c><c r="F539" s="2" t="inlineStr"><is><t>MRSA (methicyllin-resistant Staphylococcus aureus)</t></is></c><c r="G539" s="2" t="inlineStr"><is><t>MSSA (methicyllin-sensitive Staphylococcus aureus)</t></is></c><c r="H539" s="2" t="inlineStr"><is><t>VRE (Vancomycin-resistant Enterococcus)</t></is></c><c r="I539" s="2" t="inlineStr" /><c r="J539" s="2" t="inlineStr" /><c r="K539" s="2" t="inlineStr"><is><t>CPE (Carbapenemase-producing Enterobacteriaceae)</t></is></c><c r="L539" s="2" t="inlineStr" /><c r="M539" s="2" t="inlineStr" /><c r="N539" s="2" t="inlineStr" /><c r="O539" s="2" t="inlineStr" /><c r="P539" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2019/20 - 1 termin (online)</t></is></c><c r="Q539" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="540"><c r="A540" s="2" t="inlineStr"><is><t>TARCZYCA</t></is></c><c r="B540" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C540" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D540" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E540" s="2" t="inlineStr"><is><t>Profilaktyczne zastosowanie leków przeciwinfekcyjnych jest uzasadnione:</t></is></c><c r="F540" s="2" t="inlineStr"><is><t>W planowej operacji cięcia cesarskiego (pole czyste-skażone)</t></is></c><c r="G540" s="2" t="inlineStr"><is><t>W planowej implantacji endoprotezy stawu kolanowego (pole czyste)</t></is></c><c r="H540" s="2" t="inlineStr" /><c r="I540" s="2" t="inlineStr" /><c r="J540" s="2" t="inlineStr" /><c r="K540" s="2" t="inlineStr"><is><t>W planowanym usunięciu zmiany skórnej w obrębie dłoni (pole czyste)</t></is></c><c r="L540" s="2" t="inlineStr"><is><t>W planowym usunięciu tarczycy w wolu guzkowym nadczynnym (pole czyste)</t></is></c><c r="M540" s="2" t="inlineStr" /><c r="N540" s="2" t="inlineStr" /><c r="O540" s="2" t="inlineStr" /><c r="P540" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2019/20 - 1 termin (online)</t></is></c><c r="Q540" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="541"><c r="A541" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B541" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C541" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D541" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E541" s="2" t="inlineStr"><is><t>Do bezpiecznych i skutecznych środków do dezynfekcji należą:</t></is></c><c r="F541" s="2" t="inlineStr"><is><t>Oktenidyna</t></is></c><c r="G541" s="2" t="inlineStr" /><c r="H541" s="2" t="inlineStr" /><c r="I541" s="2" t="inlineStr" /><c r="J541" s="2" t="inlineStr" /><c r="K541" s="2" t="inlineStr"><is><t>Spirytus salicylowy</t></is></c><c r="L541" s="2" t="inlineStr"><is><t>Woda utleniona</t></is></c><c r="M541" s="2" t="inlineStr"><is><t>Mleczan etakrydyny</t></is></c><c r="N541" s="2" t="inlineStr" /><c r="O541" s="2" t="inlineStr" /><c r="P541" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2019/20 - 1 termin (online)</t></is></c><c r="Q541" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="542"><c r="A542" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B542" s="2" t="inlineStr"><is><t>Interakcje</t></is></c><c r="C542" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D542" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E542" s="2" t="inlineStr"><is><t>Wskaż prawidłowe skojarzenie lek - działanie niepożądane:</t></is></c><c r="F542" s="2" t="inlineStr"><is><t>Izoniazyd – toczen polekowy</t></is></c><c r="G542" s="2" t="inlineStr"><is><t>Ryfampicyna - śródmiąższowe zapalenie nerek</t></is></c><c r="H542" s="2" t="inlineStr"><is><t>Pirazynamid – hiperurykemia</t></is></c><c r="I542" s="2" t="inlineStr"><is><t>Etambutol - pozagałkowa zapalenie nerwu wzrokowego</t></is></c><c r="J542" s="2" t="inlineStr" /><c r="K542" s="2" t="inlineStr" /><c r="L542" s="2" t="inlineStr" /><c r="M542" s="2" t="inlineStr" /><c r="N542" s="2" t="inlineStr" /><c r="O542" s="2" t="inlineStr" /><c r="P542" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2019/20 - 1 termin (online)</t></is></c><c r="Q542" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="543"><c r="A543" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B543" s="2" t="inlineStr"><is><t>Ciąża</t></is></c><c r="C543" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D543" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E543" s="2" t="inlineStr"><is><t>U kobiety w ciąży można bezpiecznie zastosować:</t></is></c><c r="F543" s="2" t="inlineStr"><is><t>Cefuroksym</t></is></c><c r="G543" s="2" t="inlineStr"><is><t>Fenoksymetylopenicylinę</t></is></c><c r="H543" s="2" t="inlineStr" /><c r="I543" s="2" t="inlineStr" /><c r="J543" s="2" t="inlineStr" /><c r="K543" s="2" t="inlineStr"><is><t>Amikacynę</t></is></c><c r="L543" s="2" t="inlineStr"><is><t>Moksyfloksacynę</t></is></c><c r="M543" s="2" t="inlineStr" /><c r="N543" s="2" t="inlineStr" /><c r="O543" s="2" t="inlineStr" /><c r="P543" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2019/20 - 1 termin (online)</t></is></c><c r="Q543" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="544"><c r="A544" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B544" s="2" t="inlineStr"><is><t>Interakcje</t></is></c><c r="C544" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D544" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E544" s="2" t="inlineStr"><is><t>Wskaż właściwe skojarzenie lek – potencjalne działanie nipożądane:</t></is></c><c r="F544" s="2" t="inlineStr"><is><t>Doksycyklina – fotodermatoza</t></is></c><c r="G544" s="2" t="inlineStr"><is><t>Linezolid - zespół serotoninowy</t></is></c><c r="H544" s="2" t="inlineStr" /><c r="I544" s="2" t="inlineStr" /><c r="J544" s="2" t="inlineStr" /><c r="K544" s="2" t="inlineStr"><is><t>Mupirocyna - zespół czerwonego dziecka</t></is></c><c r="L544" s="2" t="inlineStr"><is><t>Gentamycyna - żółtaczka cholestatyczna</t></is></c><c r="M544" s="2" t="inlineStr" /><c r="N544" s="2" t="inlineStr" /><c r="O544" s="2" t="inlineStr" /><c r="P544" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2019/20 - 1 termin (online)</t></is></c><c r="Q544" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="545"><c r="A545" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B545" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C545" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D545" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E545" s="2" t="inlineStr"><is><t>Działanie nefrotoksyczne wykazuje:</t></is></c><c r="F545" s="2" t="inlineStr"><is><t>Gentamycyna</t></is></c><c r="G545" s="2" t="inlineStr"><is><t>Kolistyna</t></is></c><c r="H545" s="2" t="inlineStr"><is><t>Wankomycyna</t></is></c><c r="I545" s="2" t="inlineStr" /><c r="J545" s="2" t="inlineStr" /><c r="K545" s="2" t="inlineStr"><is><t>Klindamycyna</t></is></c><c r="L545" s="2" t="inlineStr" /><c r="M545" s="2" t="inlineStr" /><c r="N545" s="2" t="inlineStr" /><c r="O545" s="2" t="inlineStr" /><c r="P545" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2019/20 - 1 termin (online)</t></is></c><c r="Q545" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="546"><c r="A546" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B546" s="2" t="inlineStr"><is><t>Mechanizm działania</t></is></c><c r="C546" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D546" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E546" s="2" t="inlineStr"><is><t>Syntezę ściany komórkowej hamuje:</t></is></c><c r="F546" s="2" t="inlineStr"><is><t>Kaspofungina</t></is></c><c r="G546" s="2" t="inlineStr"><is><t>Imipenem</t></is></c><c r="H546" s="2" t="inlineStr" /><c r="I546" s="2" t="inlineStr" /><c r="J546" s="2" t="inlineStr" /><c r="K546" s="2" t="inlineStr"><is><t>Nystatyna</t></is></c><c r="L546" s="2" t="inlineStr"><is><t>Tygecyklina</t></is></c><c r="M546" s="2" t="inlineStr" /><c r="N546" s="2" t="inlineStr" /><c r="O546" s="2" t="inlineStr" /><c r="P546" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2019/20 - 1 termin (online)</t></is></c><c r="Q546" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="547"><c r="A547" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B547" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C547" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D547" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E547" s="2" t="inlineStr"><is><t>W biegunce o etiologii Clostridioides difficile uzasadnione może być podanie doustne:</t></is></c><c r="F547" s="2" t="inlineStr"><is><t>Fidaksomycyny</t></is></c><c r="G547" s="2" t="inlineStr"><is><t>Metronidazolu</t></is></c><c r="H547" s="2" t="inlineStr" /><c r="I547" s="2" t="inlineStr" /><c r="J547" s="2" t="inlineStr" /><c r="K547" s="2" t="inlineStr"><is><t>Neomycyny</t></is></c><c r="L547" s="2" t="inlineStr"><is><t>Nifuroksazydu</t></is></c><c r="M547" s="2" t="inlineStr" /><c r="N547" s="2" t="inlineStr" /><c r="O547" s="2" t="inlineStr" /><c r="P547" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2019/20 - 1 termin (online)</t></is></c><c r="Q547" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="548"><c r="A548" s="2" t="inlineStr"><is><t>LEKI PRZECIWGRZYBICZE</t></is></c><c r="B548" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C548" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D548" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E548" s="2" t="inlineStr"><is><t>Wskaż stwierdzenie/a prawdziwe:</t></is></c><c r="F548" s="2" t="inlineStr"><is><t>Ketokonazol stosuje się wyłącznie miejscowo w leczeniu grzybic</t></is></c><c r="G548" s="2" t="inlineStr" /><c r="H548" s="2" t="inlineStr" /><c r="I548" s="2" t="inlineStr" /><c r="J548" s="2" t="inlineStr" /><c r="K548" s="2" t="inlineStr"><is><t>Terbinafina hamuje enzym związany z ukłądem CYP450</t></is></c><c r="L548" s="2" t="inlineStr"><is><t>Zastosowanie technologii liposomów pozwoliło na otrzymanie preparatów amfoterycyny B o istotnie zmniejszonej hepatotoksyczności</t></is></c><c r="M548" s="2" t="inlineStr"><is><t>Kaspofungina osiąga bardzo wysokie stężenia w OUN</t></is></c><c r="N548" s="2" t="inlineStr" /><c r="O548" s="2" t="inlineStr" /><c r="P548" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2019/20 - 1 termin (online)</t></is></c><c r="Q548" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="549"><c r="A549" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B549" s="2" t="inlineStr"><is><t>Wskazania</t></is></c><c r="C549" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D549" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E549" s="2" t="inlineStr"><is><t>Metronidazol:</t></is></c><c r="F549" s="2" t="inlineStr"><is><t>Dobrze penetruje do OUN</t></is></c><c r="G549" s="2" t="inlineStr"><is><t>Działa na Entamoeba histolytica</t></is></c><c r="H549" s="2" t="inlineStr" /><c r="I549" s="2" t="inlineStr" /><c r="J549" s="2" t="inlineStr" /><c r="K549" s="2" t="inlineStr"><is><t>Bardzo często jest przyczyną zapalenia ścięgna Achillesa</t></is></c><c r="L549" s="2" t="inlineStr"><is><t>Jest stosowany w wewnątrzbrzusznych zakażeniach szczepami wielolekoopornymi</t></is></c><c r="M549" s="2" t="inlineStr" /><c r="N549" s="2" t="inlineStr" /><c r="O549" s="2" t="inlineStr" /><c r="P549" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2019/20 - 1 termin (online)</t></is></c><c r="Q549" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="550"><c r="A550" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B550" s="2" t="inlineStr"><is><t>Działania niepożądane</t></is></c><c r="C550" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D550" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E550" s="2" t="inlineStr"><is><t>Lek bakteriobójczy, którego aktywność przeciwbakteryjną najlepiej charakteryzuje AUC24/MIC, działający na bakterie G(+). Lek nie ma aktywnych metabolitów i działa nefrotoksycznie. Opis może dotyczyć:</t></is></c><c r="F550" s="2" t="inlineStr"><is><t>Wankomycyny</t></is></c><c r="G550" s="2" t="inlineStr" /><c r="H550" s="2" t="inlineStr" /><c r="I550" s="2" t="inlineStr" /><c r="J550" s="2" t="inlineStr" /><c r="K550" s="2" t="inlineStr"><is><t>Kolistyny</t></is></c><c r="L550" s="2" t="inlineStr"><is><t>Klindamycyny</t></is></c><c r="M550" s="2" t="inlineStr"><is><t>Gentamycyny</t></is></c><c r="N550" s="2" t="inlineStr" /><c r="O550" s="2" t="inlineStr" /><c r="P550" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2019/20 - 1 termin (online)</t></is></c><c r="Q550" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="551"><c r="A551" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B551" s="2" t="inlineStr"><is><t>Interakcje</t></is></c><c r="C551" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D551" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E551" s="2" t="inlineStr"><is><t>Wskaż prawidłowe skojarzenie drobnoustrój - lek, który może być skuteczny w zakażeniu o takiej etiologii:</t></is></c><c r="F551" s="2" t="inlineStr"><is><t>Staphylococcus aureus (MSSA) - kloksacylina</t></is></c><c r="G551" s="2" t="inlineStr"><is><t>Clostridioides difficile – wankomycyna</t></is></c><c r="H551" s="2" t="inlineStr" /><c r="I551" s="2" t="inlineStr" /><c r="J551" s="2" t="inlineStr" /><c r="K551" s="2" t="inlineStr"><is><t>Staphylococcus aureus (MRSA) - meropenem</t></is></c><c r="L551" s="2" t="inlineStr"><is><t>Trichomonas vaginalis - ketokonazol</t></is></c><c r="M551" s="2" t="inlineStr" /><c r="N551" s="2" t="inlineStr" /><c r="O551" s="2" t="inlineStr" /><c r="P551" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2019/20 - 1 termin (online)</t></is></c><c r="Q551" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="552"><c r="A552" s="2" t="inlineStr"><is><t>LEKI PRZECIWGRZYBICZE</t></is></c><c r="B552" s="2" t="inlineStr"><is><t>Interakcje</t></is></c><c r="C552" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D552" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E552" s="2" t="inlineStr"><is><t>Wskaż prawidłowe stwierdzenie:</t></is></c><c r="F552" s="2" t="inlineStr"><is><t>Worykonazol wykazuje aktywność wobec Aspergillus spp</t></is></c><c r="G552" s="2" t="inlineStr" /><c r="H552" s="2" t="inlineStr" /><c r="I552" s="2" t="inlineStr" /><c r="J552" s="2" t="inlineStr" /><c r="K552" s="2" t="inlineStr"><is><t>Flukonazol nie wykazuje istotnych klinicznie interakcji na poziomie cytochromu P450</t></is></c><c r="L552" s="2" t="inlineStr"><is><t>Itrakonazol nie wchłania się po podaniu doustnym</t></is></c><c r="M552" s="2" t="inlineStr"><is><t>Posakonazol hamuje syntezę ściany komórkowej grzyba</t></is></c><c r="N552" s="2" t="inlineStr" /><c r="O552" s="2" t="inlineStr" /><c r="P552" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2019/20 - 1 termin (online)</t></is></c><c r="Q552" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="553"><c r="A553" s="2" t="inlineStr"><is><t>LEKI PRZECIWWIRUSOWE</t></is></c><c r="B553" s="2" t="inlineStr"><is><t>Interakcje</t></is></c><c r="C553" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D553" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E553" s="2" t="inlineStr"><is><t>Wskaż prawidłowe skojarzenie lek – wskazanie do leczenia:</t></is></c><c r="F553" s="2" t="inlineStr"><is><t>Acyklowir - półpasiec</t></is></c><c r="G553" s="2" t="inlineStr"><is><t>Gancyklowir – cytomegalowirusowe zapalenie siatkówki</t></is></c><c r="H553" s="2" t="inlineStr"><is><t>Osetamiwir – grypa</t></is></c><c r="I553" s="2" t="inlineStr" /><c r="J553" s="2" t="inlineStr" /><c r="K553" s="2" t="inlineStr"><is><t>Amantadyna – mononukleoza</t></is></c><c r="L553" s="2" t="inlineStr" /><c r="M553" s="2" t="inlineStr" /><c r="N553" s="2" t="inlineStr" /><c r="O553" s="2" t="inlineStr" /><c r="P553" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2019/20 - 1 termin (online)</t></is></c><c r="Q553" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="554"><c r="A554" s="2" t="inlineStr"><is><t>LEKI PRZECIWBAKTERYJNE</t></is></c><c r="B554" s="2" t="inlineStr"><is><t>Interakcje</t></is></c><c r="C554" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D554" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E554" s="2" t="inlineStr"><is><t>Wskaż prawidłowe skojarzenie drobnoustrój - lek, który może być skuteczny w zakażeniu o tej etiologii:</t></is></c><c r="F554" s="2" t="inlineStr"><is><t>Helicobacter pylori – tetracyklina</t></is></c><c r="G554" s="2" t="inlineStr"><is><t>Staphylococcus aureus (MSSA) - cefazolina</t></is></c><c r="H554" s="2" t="inlineStr" /><c r="I554" s="2" t="inlineStr" /><c r="J554" s="2" t="inlineStr" /><c r="K554" s="2" t="inlineStr"><is><t>Escherichia coli – klindamycyna</t></is></c><c r="L554" s="2" t="inlineStr"><is><t>Mycoplasma pneumoniae - teikoplanina</t></is></c><c r="M554" s="2" t="inlineStr" /><c r="N554" s="2" t="inlineStr" /><c r="O554" s="2" t="inlineStr" /><c r="P554" s="2" t="inlineStr"><is><t>KOLOKWIUM 2 – 2019/20 - 1 termin (online)</t></is></c><c r="Q554" s="2" t="inlineStr"><is><t>wysoka</t></is></c></row><row r="555"><c r="A555" s="2" t="inlineStr"><is><t>FARMAKOLOGIA OGÓLNA I EBM</t></is></c><c r="B555" s="2" t="inlineStr"><is><t>Klasyfikacja</t></is></c><c r="C555" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D555" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E555" s="2" t="inlineStr"><is><t>Wytyczne PRISMA:</t></is></c><c r="F555" s="2" t="inlineStr"><is><t>dotyczą prowadzenia przeglądów systematycznych i metaanaliz</t></is></c><c r="G555" s="2" t="inlineStr" /><c r="H555" s="2" t="inlineStr" /><c r="I555" s="2" t="inlineStr" /><c r="J555" s="2" t="inlineStr" /><c r="K555" s="2" t="inlineStr"><is><t>dotyczą prowadzenia randomizowanych badań klinicznych</t></is></c><c r="L555" s="2" t="inlineStr"><is><t>dotyczą formułowania wytycznych klinicznych</t></is></c><c r="M555" s="2" t="inlineStr"><is><t>dotyczą prowadzenia badań obserwacyjnych</t></is></c><c r="N555" s="2" t="inlineStr" /><c r="O555" s="2" t="inlineStr" /><c r="P555" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2018/19</t></is></c><c r="Q555" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="556"><c r="A556" s="2" t="inlineStr"><is><t>FARMAKOKINETYKA</t></is></c><c r="B556" s="2" t="inlineStr"><is><t>Dawkowanie</t></is></c><c r="C556" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D556" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E556" s="2" t="inlineStr"><is><t>Lek ma Vd=6 l/kg m.c. i CL=10 ml/min/kg m.c. Na tej podstawie spodziewasz się, że lek będzie:</t></is></c><c r="F556" s="2" t="inlineStr"><is><t>wymagał dużej dawki nasycającej</t></is></c><c r="G556" s="2" t="inlineStr" /><c r="H556" s="2" t="inlineStr" /><c r="I556" s="2" t="inlineStr" /><c r="J556" s="2" t="inlineStr" /><c r="K556" s="2" t="inlineStr"><is><t>kumulował się w tkance tłuszczowej</t></is></c><c r="L556" s="2" t="inlineStr"><is><t>miał długi okres półtrwania</t></is></c><c r="M556" s="2" t="inlineStr"><is><t>wymagał korekty dawkowania w niewydolności nerek</t></is></c><c r="N556" s="2" t="inlineStr" /><c r="O556" s="2" t="inlineStr" /><c r="P556" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2018/19</t></is></c><c r="Q556" s="2" t="inlineStr"><is><t>niska</t></is></c></row><row r="557"><c r="A557" s="2" t="inlineStr"><is><t>FARMAKOKINETYKA</t></is></c><c r="B557" s="2" t="inlineStr"><is><t>Interakcje</t></is></c><c r="C557" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D557" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E557" s="2" t="inlineStr"><is><t>Wskaż prawidłowe stwierdzenia dotyczące wiązania leków z białkami osocza:</t></is></c><c r="F557" s="2" t="inlineStr"><is><t>może być przyczyną istotnych klinicznie interakcji lekowych</t></is></c><c r="G557" s="2" t="inlineStr" /><c r="H557" s="2" t="inlineStr" /><c r="I557" s="2" t="inlineStr" /><c r="J557" s="2" t="inlineStr" /><c r="K557" s="2" t="inlineStr"><is><t>z powodu zmniejszenia stężenia albumin we krwi leki o dużym stopniu wiązaniu z albuminami mogą wykazywać niedostateczny efekt terapeutyczny</t></is></c><c r="L557" s="2" t="inlineStr"><is><t>jest istotne klinicznie wtedy, gdy frakcja wolna wynosi 80%</t></is></c><c r="M557" s="2" t="inlineStr"><is><t>przebiega w wątrobie, gdzie zachodzi sprzęganie leku z albuminami</t></is></c><c r="N557" s="2" t="inlineStr" /><c r="O557" s="2" t="inlineStr" /><c r="P557" s="2" t="inlineStr"><is><t>KOLOKWIUM 1 – 2018/19</t></is></c><c r="Q557" s="2" t="inlineStr"><is><t>srednia</t></is></c></row><row r="558"><c r="A558" s="2" t="inlineStr"><is><t>FARMAKOKINETYKA</t></is></c><c r="B558" s="2" t="inlineStr"><is><t>Sposób podania</t></is></c><c r="C558" s="2" t="inlineStr"><is><t>lekarski</t></is></c><c r="D558" s="2" t="inlineStr"><is><t>testowe</t></is></c><c r="E558" s="2" t="inlineStr"><is><t>Lek o kinetyce pierwszego rzędu po podaniu doustnym ma biodostępność ok. 100% i okres 